--- a/reports/member_funnel/downloads/member_funnel_7d_non_buyer.xlsx
+++ b/reports/member_funnel/downloads/member_funnel_7d_non_buyer.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G166"/>
+  <dimension ref="A1:G189"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,178 +468,178 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>kk_4829088785</t>
+          <t>kk_4831361074</t>
         </is>
       </c>
       <c r="B2" t="inlineStr"/>
       <c r="C2" t="inlineStr">
         <is>
-          <t>303454</t>
+          <t>303574</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Organic Traffic</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>6968489536332</t>
+          <t>(organic)</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>(not set)</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>(not set)</t>
+          <t>Unknown</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>rkddl4</t>
+          <t>kk_4830254905</t>
         </is>
       </c>
       <c r="B3" t="inlineStr"/>
       <c r="C3" t="inlineStr">
         <is>
-          <t>303596</t>
+          <t>303513</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>KAKAO_alimtalk</t>
+          <t>naver_brandsearch_mobile</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>(not set)</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>(not set)</t>
+          <t>Unknown</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>kk_4831842028</t>
+          <t>kk_4832204677</t>
         </is>
       </c>
       <c r="B4" t="inlineStr"/>
       <c r="C4" t="inlineStr">
         <is>
-          <t>303612</t>
+          <t>303653</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Awareness</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>benz_running_program_2026_coupon</t>
+          <t>sa</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>(not set)</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>(not set)</t>
+          <t>Unknown</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>kk_4830612400</t>
+          <t>kk_4830885654</t>
         </is>
       </c>
       <c r="B5" t="inlineStr"/>
       <c r="C5" t="inlineStr">
         <is>
-          <t>303542</t>
+          <t>303562</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Awareness</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>benz_running_program_2026_coupon</t>
+          <t>(not set)</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>(not set)</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>(not set)</t>
+          <t>Unknown</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>kk_4830513865</t>
+          <t>kk_4831895164</t>
         </is>
       </c>
       <c r="B6" t="inlineStr"/>
       <c r="C6" t="inlineStr">
         <is>
-          <t>303529</t>
+          <t>303616</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Organic Traffic</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>naver_brandsearch_mobile</t>
+          <t>(referral)</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>(not set)</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>(not set)</t>
+          <t>Unknown</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>kk_4829077261</t>
+          <t>kk_4829516327</t>
         </is>
       </c>
       <c r="B7" t="inlineStr"/>
       <c r="C7" t="inlineStr">
         <is>
-          <t>303453</t>
+          <t>303476</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -649,68 +649,68 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>6968489536332</t>
+          <t>naver_brandsearch_mobile</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>(not set)</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>(not set)</t>
+          <t>Unknown</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>kk_4830476438</t>
+          <t>kk_4829818548</t>
         </is>
       </c>
       <c r="B8" t="inlineStr"/>
       <c r="C8" t="inlineStr">
         <is>
-          <t>303525</t>
+          <t>303491</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Organic Traffic</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>EFW_04</t>
+          <t>[PF]A SC_상시(1865MF,구매 장바구니)</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>(not set)</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>(not set)</t>
+          <t>Unknown</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>kk_4831687251</t>
+          <t>kk_4831740520</t>
         </is>
       </c>
       <c r="B9" t="inlineStr"/>
       <c r="C9" t="inlineStr">
         <is>
-          <t>303598</t>
+          <t>303601</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Awareness</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -720,25 +720,25 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>(not set)</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>(not set)</t>
+          <t>Unknown</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>kk_4829440714</t>
+          <t>kk_4830523585</t>
         </is>
       </c>
       <c r="B10" t="inlineStr"/>
       <c r="C10" t="inlineStr">
         <is>
-          <t>303471</t>
+          <t>303530</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -753,25 +753,25 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>(not set)</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>(not set)</t>
+          <t>Unknown</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>kk_4830793813</t>
+          <t>kk_4830030364</t>
         </is>
       </c>
       <c r="B11" t="inlineStr"/>
       <c r="C11" t="inlineStr">
         <is>
-          <t>303557</t>
+          <t>303499</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -781,167 +781,167 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>naver_brandsearch_mobile</t>
+          <t>naversa_mo</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>(not set)</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>(not set)</t>
+          <t>Unknown</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>charismasm74</t>
+          <t>kk_4830247238</t>
         </is>
       </c>
       <c r="B12" t="inlineStr"/>
       <c r="C12" t="inlineStr">
         <is>
-          <t>303650</t>
+          <t>303510</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>naver_brandsearch_pc</t>
+          <t>(not set)</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>(not set)</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>(not set)</t>
+          <t>Unknown</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>kk_4831500868</t>
+          <t>kk_4830591832</t>
         </is>
       </c>
       <c r="B13" t="inlineStr"/>
       <c r="C13" t="inlineStr">
         <is>
-          <t>303582</t>
+          <t>303539</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Organic Traffic</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>6968489536332</t>
+          <t>(organic)</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>(not set)</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>(not set)</t>
+          <t>Unknown</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>kk_4830922114</t>
+          <t>chicken0890</t>
         </is>
       </c>
       <c r="B14" t="inlineStr"/>
       <c r="C14" t="inlineStr">
         <is>
-          <t>303563</t>
+          <t>303646</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Organic Traffic</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>[PF]전환_회원가입(유사)</t>
+          <t>(referral)</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>(not set)</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>(not set)</t>
+          <t>Unknown</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>hoonck1</t>
+          <t>kk_4832269209</t>
         </is>
       </c>
       <c r="B15" t="inlineStr"/>
       <c r="C15" t="inlineStr">
         <is>
-          <t>303433</t>
+          <t>303661</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Awareness</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>[PF]트래픽_유사+관심사</t>
+          <t>benz_running_program_2026_coupon</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>(not set)</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>(not set)</t>
+          <t>Unknown</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>kk_4832205664</t>
+          <t>kk_4832293158</t>
         </is>
       </c>
       <c r="B16" t="inlineStr"/>
       <c r="C16" t="inlineStr">
         <is>
-          <t>303654</t>
+          <t>303662</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Awareness</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -951,25 +951,25 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>(not set)</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>(not set)</t>
+          <t>Unknown</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>kk_4831995357</t>
+          <t>kk_4832162309</t>
         </is>
       </c>
       <c r="B17" t="inlineStr"/>
       <c r="C17" t="inlineStr">
         <is>
-          <t>303623</t>
+          <t>303643</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -979,195 +979,195 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>benz_running_program_2026_coupon</t>
+          <t>benz_running_program_2026​</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>(not set)</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>(not set)</t>
+          <t>Unknown</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>kk_4831768959</t>
+          <t>kk_4831572710</t>
         </is>
       </c>
       <c r="B18" t="inlineStr"/>
       <c r="C18" t="inlineStr">
         <is>
-          <t>303602</t>
+          <t>303590</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Awareness</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>benz_running_program_2026_coupon</t>
+          <t>naver_brandsearch_mobile</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>(not set)</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>(not set)</t>
+          <t>Unknown</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>kk_4830251299</t>
+          <t>kda01126</t>
         </is>
       </c>
       <c r="B19" t="inlineStr"/>
       <c r="C19" t="inlineStr">
         <is>
-          <t>303511</t>
+          <t>303656</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Awareness</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>benz_running_program_2026_coupon</t>
+          <t>naver_brandsearch_mobile</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>(not set)</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>(not set)</t>
+          <t>Unknown</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>kk_4831422357</t>
+          <t>masterk</t>
         </is>
       </c>
       <c r="B20" t="inlineStr"/>
       <c r="C20" t="inlineStr">
         <is>
-          <t>303577</t>
+          <t>303524</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Official SNS</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>benz_running_program_2026_coupon</t>
+          <t>sa</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>(not set)</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>(not set)</t>
+          <t>Unknown</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>kk_4831842112</t>
+          <t>kk_4832411690</t>
         </is>
       </c>
       <c r="B21" t="inlineStr"/>
       <c r="C21" t="inlineStr">
         <is>
-          <t>303613</t>
+          <t>303666</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>naver_brandsearch_mobile</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>(not set)</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>(not set)</t>
+          <t>Unknown</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>kk_4832105165</t>
+          <t>kk_4832425261</t>
         </is>
       </c>
       <c r="B22" t="inlineStr"/>
       <c r="C22" t="inlineStr">
         <is>
-          <t>303636</t>
+          <t>303667</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>naver_brandsearch_mobile</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>(not set)</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>(not set)</t>
+          <t>Unknown</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>kk_4830821550</t>
+          <t>kk_4832425669</t>
         </is>
       </c>
       <c r="B23" t="inlineStr"/>
       <c r="C23" t="inlineStr">
         <is>
-          <t>303559</t>
+          <t>303668</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -1177,63 +1177,63 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>(not set)</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>(not set)</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>(not set)</t>
+          <t>Unknown</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>kk_4832180009</t>
+          <t>kk_4832345614</t>
         </is>
       </c>
       <c r="B24" t="inlineStr"/>
       <c r="C24" t="inlineStr">
         <is>
-          <t>303647</t>
+          <t>303664</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>(not set)</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>(not set)</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>(not set)</t>
+          <t>Unknown</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>kk_4831394790</t>
+          <t>kk_4831784738</t>
         </is>
       </c>
       <c r="B25" t="inlineStr"/>
       <c r="C25" t="inlineStr">
         <is>
-          <t>303575</t>
+          <t>303607</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -1243,30 +1243,30 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>(not set)</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>(not set)</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>(not set)</t>
+          <t>Unknown</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>kk_4832023314</t>
+          <t>hotsnoopy</t>
         </is>
       </c>
       <c r="B26" t="inlineStr"/>
       <c r="C26" t="inlineStr">
         <is>
-          <t>303626</t>
+          <t>303585</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -1276,30 +1276,30 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>(not set)</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>(not set)</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>(not set)</t>
+          <t>Unknown</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>kk_4832114535</t>
+          <t>thdud9181</t>
         </is>
       </c>
       <c r="B27" t="inlineStr"/>
       <c r="C27" t="inlineStr">
         <is>
-          <t>303637</t>
+          <t>303644</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -1309,30 +1309,30 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>(not set)</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>(not set)</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>(not set)</t>
+          <t>Unknown</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>kk_4832248726</t>
+          <t>kk_4832310183</t>
         </is>
       </c>
       <c r="B28" t="inlineStr"/>
       <c r="C28" t="inlineStr">
         <is>
-          <t>303658</t>
+          <t>303663</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -1342,30 +1342,30 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>(not set)</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>(not set)</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>(not set)</t>
+          <t>Unknown</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>kk_4831346086</t>
+          <t>kk_4829979824</t>
         </is>
       </c>
       <c r="B29" t="inlineStr"/>
       <c r="C29" t="inlineStr">
         <is>
-          <t>303573</t>
+          <t>303497</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -1375,30 +1375,30 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>(not set)</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>(not set)</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>(not set)</t>
+          <t>Unknown</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>kk_4832201164</t>
+          <t>kk_4829348219</t>
         </is>
       </c>
       <c r="B30" t="inlineStr"/>
       <c r="C30" t="inlineStr">
         <is>
-          <t>303651</t>
+          <t>303468</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -1408,30 +1408,30 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>(not set)</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>(not set)</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>(not set)</t>
+          <t>Unknown</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>kk_4832076715</t>
+          <t>kk_4831402433</t>
         </is>
       </c>
       <c r="B31" t="inlineStr"/>
       <c r="C31" t="inlineStr">
         <is>
-          <t>303629</t>
+          <t>303576</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -1441,30 +1441,30 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>(not set)</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>(not set)</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>(not set)</t>
+          <t>Unknown</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>kk_4830767555</t>
+          <t>kk_4829294214</t>
         </is>
       </c>
       <c r="B32" t="inlineStr"/>
       <c r="C32" t="inlineStr">
         <is>
-          <t>303555</t>
+          <t>303466</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -1474,228 +1474,228 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>(not set)</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>(not set)</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>(not set)</t>
+          <t>Unknown</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>kk_4831495694</t>
+          <t>kk_4829088785</t>
         </is>
       </c>
       <c r="B33" t="inlineStr"/>
       <c r="C33" t="inlineStr">
         <is>
-          <t>303581</t>
+          <t>303454</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>Organic Traffic</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>(organic)</t>
+          <t>6968489536332</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>(not set)</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>(not set)</t>
+          <t>Unknown</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>kk_4832164589</t>
+          <t>rkddl4</t>
         </is>
       </c>
       <c r="B34" t="inlineStr"/>
       <c r="C34" t="inlineStr">
         <is>
-          <t>303645</t>
+          <t>303596</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>(organic)</t>
+          <t>KAKAO_alimtalk</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>(not set)</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>(not set)</t>
+          <t>Unknown</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>kk_4832078505</t>
+          <t>kk_4830612400</t>
         </is>
       </c>
       <c r="B35" t="inlineStr"/>
       <c r="C35" t="inlineStr">
         <is>
-          <t>303630</t>
+          <t>303542</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>Organic Traffic</t>
+          <t>Awareness</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>(referral)</t>
+          <t>benz_running_program_2026_coupon</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>(not set)</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>(not set)</t>
+          <t>Unknown</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>kk_4831340465</t>
+          <t>kk_4831842028</t>
         </is>
       </c>
       <c r="B36" t="inlineStr"/>
       <c r="C36" t="inlineStr">
         <is>
-          <t>303572</t>
+          <t>303612</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>Organic Traffic</t>
+          <t>Awareness</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>(referral)</t>
+          <t>benz_running_program_2026_coupon</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>(not set)</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>(not set)</t>
+          <t>Unknown</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>jambo8</t>
+          <t>kk_4830513865</t>
         </is>
       </c>
       <c r="B37" t="inlineStr"/>
       <c r="C37" t="inlineStr">
         <is>
-          <t>303558</t>
+          <t>303529</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>Organic Traffic</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>(referral)</t>
+          <t>naver_brandsearch_mobile</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>(not set)</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>(not set)</t>
+          <t>Unknown</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>kk_4832029124</t>
+          <t>kk_4829077261</t>
         </is>
       </c>
       <c r="B38" t="inlineStr"/>
       <c r="C38" t="inlineStr">
         <is>
-          <t>303627</t>
+          <t>303453</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>Organic Traffic</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>(referral)</t>
+          <t>6968489536332</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>(not set)</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>(not set)</t>
+          <t>Unknown</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>kk_4832100095</t>
+          <t>kk_4830476438</t>
         </is>
       </c>
       <c r="B39" t="inlineStr"/>
       <c r="C39" t="inlineStr">
         <is>
-          <t>303634</t>
+          <t>303525</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -1705,96 +1705,96 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>(referral)</t>
+          <t>EFW_04</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>(not set)</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>(not set)</t>
+          <t>Unknown</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>kk_4831649243</t>
+          <t>kk_4829440714</t>
         </is>
       </c>
       <c r="B40" t="inlineStr"/>
       <c r="C40" t="inlineStr">
         <is>
-          <t>303595</t>
+          <t>303471</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>Organic Traffic</t>
+          <t>Awareness</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>(referral)</t>
+          <t>benz_running_program_2026_coupon</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>(not set)</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>(not set)</t>
+          <t>Unknown</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>kk_4831830576</t>
+          <t>kk_4831687251</t>
         </is>
       </c>
       <c r="B41" t="inlineStr"/>
       <c r="C41" t="inlineStr">
         <is>
-          <t>303611</t>
+          <t>303598</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Awareness</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>6968489536332</t>
+          <t>benz_running_program_2026_coupon</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>(not set)</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>(not set)</t>
+          <t>Unknown</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>kk_4832202047</t>
+          <t>kk_4830793813</t>
         </is>
       </c>
       <c r="B42" t="inlineStr"/>
       <c r="C42" t="inlineStr">
         <is>
-          <t>303652</t>
+          <t>303557</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -1804,30 +1804,30 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>6968489536332</t>
+          <t>naver_brandsearch_mobile</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>(not set)</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>(not set)</t>
+          <t>Unknown</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>saty31</t>
+          <t>charismasm74</t>
         </is>
       </c>
       <c r="B43" t="inlineStr"/>
       <c r="C43" t="inlineStr">
         <is>
-          <t>303561</t>
+          <t>303650</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -1837,30 +1837,30 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>6968489536332</t>
+          <t>naver_brandsearch_pc</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>(not set)</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>(not set)</t>
+          <t>Unknown</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>kk_4832151833</t>
+          <t>kk_4831500868</t>
         </is>
       </c>
       <c r="B44" t="inlineStr"/>
       <c r="C44" t="inlineStr">
         <is>
-          <t>303641</t>
+          <t>303582</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -1875,25 +1875,25 @@
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>(not set)</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>(not set)</t>
+          <t>Unknown</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>jgj0503</t>
+          <t>kk_4830922114</t>
         </is>
       </c>
       <c r="B45" t="inlineStr"/>
       <c r="C45" t="inlineStr">
         <is>
-          <t>303605</t>
+          <t>303563</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -1903,30 +1903,30 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>6968489536332</t>
+          <t>[PF]전환_회원가입(유사)</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>(not set)</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>(not set)</t>
+          <t>Unknown</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>kk_4830989652</t>
+          <t>hoonck1</t>
         </is>
       </c>
       <c r="B46" t="inlineStr"/>
       <c r="C46" t="inlineStr">
         <is>
-          <t>303569</t>
+          <t>303433</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -1936,96 +1936,96 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>6968489536332</t>
+          <t>[PF]트래픽_유사+관심사</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>(not set)</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>(not set)</t>
+          <t>Unknown</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>kk_4832154317</t>
+          <t>kk_4831995357</t>
         </is>
       </c>
       <c r="B47" t="inlineStr"/>
       <c r="C47" t="inlineStr">
         <is>
-          <t>303642</t>
+          <t>303623</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Awareness</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>EFW</t>
+          <t>benz_running_program_2026_coupon</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>(not set)</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>(not set)</t>
+          <t>Unknown</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>kk_4831536902</t>
+          <t>kk_4831768959</t>
         </is>
       </c>
       <c r="B48" t="inlineStr"/>
       <c r="C48" t="inlineStr">
         <is>
-          <t>303588</t>
+          <t>303602</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>Official SNS</t>
+          <t>Awareness</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>EFW_04</t>
+          <t>benz_running_program_2026_coupon</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>(not set)</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>(not set)</t>
+          <t>Unknown</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>kk_4830836853</t>
+          <t>kk_4831422357</t>
         </is>
       </c>
       <c r="B49" t="inlineStr"/>
       <c r="C49" t="inlineStr">
         <is>
-          <t>303560</t>
+          <t>303577</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -2035,756 +2035,756 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>EFW_04</t>
+          <t>benz_running_program_2026_coupon</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>(not set)</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>(not set)</t>
+          <t>Unknown</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>kk_4832125929</t>
+          <t>kk_4832205664</t>
         </is>
       </c>
       <c r="B50" t="inlineStr"/>
       <c r="C50" t="inlineStr">
         <is>
-          <t>303638</t>
+          <t>303654</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>Official SNS</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>EFW_04</t>
+          <t>benz_running_program_2026_coupon</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>(not set)</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>(not set)</t>
+          <t>Unknown</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>kk_4831850638</t>
+          <t>kk_4830251299</t>
         </is>
       </c>
       <c r="B51" t="inlineStr"/>
       <c r="C51" t="inlineStr">
         <is>
-          <t>303615</t>
+          <t>303511</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>Official SNS</t>
+          <t>Awareness</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>EFW_04</t>
+          <t>benz_running_program_2026_coupon</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>(not set)</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>(not set)</t>
+          <t>Unknown</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>kk_4831922723</t>
+          <t>kk_4832105165</t>
         </is>
       </c>
       <c r="B52" t="inlineStr"/>
       <c r="C52" t="inlineStr">
         <is>
-          <t>303617</t>
+          <t>303636</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>Official SNS</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>EFW_04</t>
+          <t>naver_brandsearch_mobile</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>(not set)</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>(not set)</t>
+          <t>Unknown</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>kk_4830778741</t>
+          <t>kk_4831842112</t>
         </is>
       </c>
       <c r="B53" t="inlineStr"/>
       <c r="C53" t="inlineStr">
         <is>
-          <t>303556</t>
+          <t>303613</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>Official SNS</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>EFW_04</t>
+          <t>naver_brandsearch_mobile</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>(not set)</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>(not set)</t>
+          <t>Unknown</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>kk_4830943389</t>
+          <t>kk_4832180009</t>
         </is>
       </c>
       <c r="B54" t="inlineStr"/>
       <c r="C54" t="inlineStr">
         <is>
-          <t>303565</t>
+          <t>303647</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>KAKAO_alimtalk</t>
+          <t>(not set)</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>(not set)</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>(not set)</t>
+          <t>Unknown</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>kk_4831612250</t>
+          <t>kk_4832114535</t>
         </is>
       </c>
       <c r="B55" t="inlineStr"/>
       <c r="C55" t="inlineStr">
         <is>
-          <t>303593</t>
+          <t>303637</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>[PF]A SC_상시(1865MF,구매 장바구니)</t>
+          <t>(not set)</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>(not set)</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>(not set)</t>
+          <t>Unknown</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>kk_4830988405</t>
+          <t>kk_4831394790</t>
         </is>
       </c>
       <c r="B56" t="inlineStr"/>
       <c r="C56" t="inlineStr">
         <is>
-          <t>303567</t>
+          <t>303575</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>[PF]전환_상시(2565MF,비구매자)</t>
+          <t>(not set)</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>(not set)</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>(not set)</t>
+          <t>Unknown</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>kk_4830923952</t>
+          <t>kk_4832201164</t>
         </is>
       </c>
       <c r="B57" t="inlineStr"/>
       <c r="C57" t="inlineStr">
         <is>
-          <t>303564</t>
+          <t>303651</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>[PF]전환_회원가입(유사)</t>
+          <t>(not set)</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>(not set)</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>(not set)</t>
+          <t>Unknown</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>kk_4830963661</t>
+          <t>kk_4831346086</t>
         </is>
       </c>
       <c r="B58" t="inlineStr"/>
       <c r="C58" t="inlineStr">
         <is>
-          <t>303566</t>
+          <t>303573</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>[PF]전환_회원가입(유사)</t>
+          <t>(not set)</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>(not set)</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>(not set)</t>
+          <t>Unknown</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>kk_4832190692</t>
+          <t>kk_4832248726</t>
         </is>
       </c>
       <c r="B59" t="inlineStr"/>
       <c r="C59" t="inlineStr">
         <is>
-          <t>303649</t>
+          <t>303658</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>Awareness</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>benz_running_program_2026_coupon</t>
+          <t>(not set)</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>(not set)</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>(not set)</t>
+          <t>Unknown</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>kk_4831997957</t>
+          <t>kk_4830821550</t>
         </is>
       </c>
       <c r="B60" t="inlineStr"/>
       <c r="C60" t="inlineStr">
         <is>
-          <t>303624</t>
+          <t>303559</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>Awareness</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>benz_running_program_2026_coupon</t>
+          <t>(not set)</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>(not set)</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>(not set)</t>
+          <t>Unknown</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>kk_4831468314</t>
+          <t>kk_4832076715</t>
         </is>
       </c>
       <c r="B61" t="inlineStr"/>
       <c r="C61" t="inlineStr">
         <is>
-          <t>303578</t>
+          <t>303629</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>Awareness</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>benz_running_program_2026_coupon</t>
+          <t>(not set)</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>(not set)</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>(not set)</t>
+          <t>Unknown</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>kk_4832001343</t>
+          <t>kk_4830767555</t>
         </is>
       </c>
       <c r="B62" t="inlineStr"/>
       <c r="C62" t="inlineStr">
         <is>
-          <t>303625</t>
+          <t>303555</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>Awareness</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>benz_running_program_2026_coupon</t>
+          <t>(not set)</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>(not set)</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>(not set)</t>
+          <t>Unknown</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>kk_4831986570</t>
+          <t>kk_4832023314</t>
         </is>
       </c>
       <c r="B63" t="inlineStr"/>
       <c r="C63" t="inlineStr">
         <is>
-          <t>303622</t>
+          <t>303626</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>Awareness</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>benz_running_program_2026_coupon</t>
+          <t>(not set)</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>(not set)</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>(not set)</t>
+          <t>Unknown</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>kk_4831799020</t>
+          <t>kk_4832164589</t>
         </is>
       </c>
       <c r="B64" t="inlineStr"/>
       <c r="C64" t="inlineStr">
         <is>
-          <t>303609</t>
+          <t>303645</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>Awareness</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>benz_running_program_2026_coupon</t>
+          <t>(organic)</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>(not set)</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>(not set)</t>
+          <t>Unknown</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>kk_4832061430</t>
+          <t>kk_4831495694</t>
         </is>
       </c>
       <c r="B65" t="inlineStr"/>
       <c r="C65" t="inlineStr">
         <is>
-          <t>303628</t>
+          <t>303581</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>Awareness</t>
+          <t>Organic Traffic</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>benz_running_program_2026_coupon</t>
+          <t>(organic)</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>(not set)</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>(not set)</t>
+          <t>Unknown</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>kk_4832100101</t>
+          <t>kk_4832078505</t>
         </is>
       </c>
       <c r="B66" t="inlineStr"/>
       <c r="C66" t="inlineStr">
         <is>
-          <t>303635</t>
+          <t>303630</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>Awareness</t>
+          <t>Organic Traffic</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>benz_running_program_2026_coupon</t>
+          <t>(referral)</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>(not set)</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>(not set)</t>
+          <t>Unknown</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>kk_4831532519</t>
+          <t>kk_4831649243</t>
         </is>
       </c>
       <c r="B67" t="inlineStr"/>
       <c r="C67" t="inlineStr">
         <is>
-          <t>303587</t>
+          <t>303595</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>Awareness</t>
+          <t>Organic Traffic</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>benz_running_program_2026_coupon</t>
+          <t>(referral)</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>(not set)</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>(not set)</t>
+          <t>Unknown</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>kk_4831981914</t>
+          <t>kk_4832100095</t>
         </is>
       </c>
       <c r="B68" t="inlineStr"/>
       <c r="C68" t="inlineStr">
         <is>
-          <t>303620</t>
+          <t>303634</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>Awareness</t>
+          <t>Organic Traffic</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>benz_running_program_2026_coupon</t>
+          <t>(referral)</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>(not set)</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>(not set)</t>
+          <t>Unknown</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>kk_4831983348</t>
+          <t>kk_4832029124</t>
         </is>
       </c>
       <c r="B69" t="inlineStr"/>
       <c r="C69" t="inlineStr">
         <is>
-          <t>303621</t>
+          <t>303627</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>Awareness</t>
+          <t>Organic Traffic</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>benz_running_program_2026_coupon</t>
+          <t>(referral)</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>(not set)</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>(not set)</t>
+          <t>Unknown</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>kk_4831502482</t>
+          <t>jambo8</t>
         </is>
       </c>
       <c r="B70" t="inlineStr"/>
       <c r="C70" t="inlineStr">
         <is>
-          <t>303583</t>
+          <t>303558</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>Awareness</t>
+          <t>Organic Traffic</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>benz_running_program_2026_coupon</t>
+          <t>(referral)</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>(not set)</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>(not set)</t>
+          <t>Unknown</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>kk_4831257396</t>
+          <t>kk_4831340465</t>
         </is>
       </c>
       <c r="B71" t="inlineStr"/>
       <c r="C71" t="inlineStr">
         <is>
-          <t>303571</t>
+          <t>303572</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>Awareness</t>
+          <t>Organic Traffic</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>benz_running_program_2026_coupon</t>
+          <t>(referral)</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>(not set)</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>(not set)</t>
+          <t>Unknown</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>kk_4831517271</t>
+          <t>saty31</t>
         </is>
       </c>
       <c r="B72" t="inlineStr"/>
       <c r="C72" t="inlineStr">
         <is>
-          <t>303584</t>
+          <t>303561</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -2794,30 +2794,30 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>naver_brandsearch_mobile</t>
+          <t>6968489536332</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>(not set)</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>(not set)</t>
+          <t>Unknown</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>kk_4831951614</t>
+          <t>kk_4830989652</t>
         </is>
       </c>
       <c r="B73" t="inlineStr"/>
       <c r="C73" t="inlineStr">
         <is>
-          <t>303618</t>
+          <t>303569</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -2827,30 +2827,30 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>naver_brandsearch_mobile</t>
+          <t>6968489536332</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>(not set)</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>(not set)</t>
+          <t>Unknown</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>kk_4832186210</t>
+          <t>kk_4831830576</t>
         </is>
       </c>
       <c r="B74" t="inlineStr"/>
       <c r="C74" t="inlineStr">
         <is>
-          <t>303648</t>
+          <t>303611</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
@@ -2860,30 +2860,30 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>naver_brandsearch_mobile</t>
+          <t>6968489536332</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>(not set)</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>(not set)</t>
+          <t>Unknown</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>kk_4831723596</t>
+          <t>kk_4832151833</t>
         </is>
       </c>
       <c r="B75" t="inlineStr"/>
       <c r="C75" t="inlineStr">
         <is>
-          <t>303600</t>
+          <t>303641</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
@@ -2893,30 +2893,30 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>naver_brandsearch_mobile</t>
+          <t>6968489536332</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>(not set)</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>(not set)</t>
+          <t>Unknown</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>kk_4831822425</t>
+          <t>kk_4832202047</t>
         </is>
       </c>
       <c r="B76" t="inlineStr"/>
       <c r="C76" t="inlineStr">
         <is>
-          <t>303610</t>
+          <t>303652</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
@@ -2926,30 +2926,30 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>naver_brandsearch_mobile</t>
+          <t>6968489536332</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>(not set)</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>(not set)</t>
+          <t>Unknown</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>kk_4831774426</t>
+          <t>jgj0503</t>
         </is>
       </c>
       <c r="B77" t="inlineStr"/>
       <c r="C77" t="inlineStr">
         <is>
-          <t>303604</t>
+          <t>303605</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -2959,30 +2959,30 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>naver_brandsearch_mobile</t>
+          <t>6968489536332</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>(not set)</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>(not set)</t>
+          <t>Unknown</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>kk_4831585022</t>
+          <t>kk_4832154317</t>
         </is>
       </c>
       <c r="B78" t="inlineStr"/>
       <c r="C78" t="inlineStr">
         <is>
-          <t>303591</t>
+          <t>303642</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
@@ -2992,723 +2992,723 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>naver_brandsearch_mobile</t>
+          <t>EFW</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>(not set)</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>(not set)</t>
+          <t>Unknown</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>kk_4831488942</t>
+          <t>kk_4832125929</t>
         </is>
       </c>
       <c r="B79" t="inlineStr"/>
       <c r="C79" t="inlineStr">
         <is>
-          <t>303580</t>
+          <t>303638</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Official SNS</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>naver_brandsearch_pc</t>
+          <t>EFW_04</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>(not set)</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>(not set)</t>
+          <t>Unknown</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>minpark98</t>
+          <t>kk_4831922723</t>
         </is>
       </c>
       <c r="B80" t="inlineStr"/>
       <c r="C80" t="inlineStr">
         <is>
-          <t>303657</t>
+          <t>303617</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Official SNS</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>naver_brandsearch_pc</t>
+          <t>EFW_04</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>(not set)</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>(not set)</t>
+          <t>Unknown</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>kk_4831615271</t>
+          <t>kk_4830778741</t>
         </is>
       </c>
       <c r="B81" t="inlineStr"/>
       <c r="C81" t="inlineStr">
         <is>
-          <t>303594</t>
+          <t>303556</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Official SNS</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>sa</t>
+          <t>EFW_04</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>(not set)</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>(not set)</t>
+          <t>Unknown</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>kk_4831600231</t>
+          <t>kk_4831536902</t>
         </is>
       </c>
       <c r="B82" t="inlineStr"/>
       <c r="C82" t="inlineStr">
         <is>
-          <t>303592</t>
+          <t>303588</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Official SNS</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>sa</t>
+          <t>EFW_04</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>(not set)</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>(not set)</t>
+          <t>Unknown</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>hotsnoopy</t>
+          <t>kk_4831850638</t>
         </is>
       </c>
       <c r="B83" t="inlineStr"/>
       <c r="C83" t="inlineStr">
         <is>
-          <t>303585</t>
+          <t>303615</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>Official SNS</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>EFW_04</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>(not set)</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>(not set)</t>
+          <t>Unknown</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>kk_4829979824</t>
+          <t>kk_4830836853</t>
         </is>
       </c>
       <c r="B84" t="inlineStr"/>
       <c r="C84" t="inlineStr">
         <is>
-          <t>303497</t>
+          <t>303560</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>Official SNS</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>EFW_04</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>(not set)</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>(not set)</t>
+          <t>Unknown</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>kk_4832310183</t>
+          <t>kk_4830943389</t>
         </is>
       </c>
       <c r="B85" t="inlineStr"/>
       <c r="C85" t="inlineStr">
         <is>
-          <t>303663</t>
+          <t>303565</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>KAKAO_alimtalk</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>(not set)</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>(not set)</t>
+          <t>Unknown</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>kk_4831784738</t>
+          <t>kk_4831612250</t>
         </is>
       </c>
       <c r="B86" t="inlineStr"/>
       <c r="C86" t="inlineStr">
         <is>
-          <t>303607</t>
+          <t>303593</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>[PF]A SC_상시(1865MF,구매 장바구니)</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>(not set)</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>(not set)</t>
+          <t>Unknown</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>kk_4829348219</t>
+          <t>kk_4830988405</t>
         </is>
       </c>
       <c r="B87" t="inlineStr"/>
       <c r="C87" t="inlineStr">
         <is>
-          <t>303468</t>
+          <t>303567</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>[PF]전환_상시(2565MF,비구매자)</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>(not set)</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>(not set)</t>
+          <t>Unknown</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>thdud9181</t>
+          <t>kk_4830963661</t>
         </is>
       </c>
       <c r="B88" t="inlineStr"/>
       <c r="C88" t="inlineStr">
         <is>
-          <t>303644</t>
+          <t>303566</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>[PF]전환_회원가입(유사)</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>(not set)</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>(not set)</t>
+          <t>Unknown</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>kk_4831402433</t>
+          <t>kk_4830923952</t>
         </is>
       </c>
       <c r="B89" t="inlineStr"/>
       <c r="C89" t="inlineStr">
         <is>
-          <t>303576</t>
+          <t>303564</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>[PF]전환_회원가입(유사)</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>(not set)</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>(not set)</t>
+          <t>Unknown</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>kk_4829294214</t>
+          <t>kk_4831997957</t>
         </is>
       </c>
       <c r="B90" t="inlineStr"/>
       <c r="C90" t="inlineStr">
         <is>
-          <t>303466</t>
+          <t>303624</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>Awareness</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>benz_running_program_2026_coupon</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>(not set)</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>(not set)</t>
+          <t>Unknown</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>kk_4828653802</t>
+          <t>kk_4831983348</t>
         </is>
       </c>
       <c r="B91" t="inlineStr"/>
       <c r="C91" t="inlineStr">
         <is>
-          <t>303422</t>
+          <t>303621</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Awareness</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>(organic)</t>
+          <t>benz_running_program_2026_coupon</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>(not set)</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>(not set)</t>
+          <t>Unknown</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>kk_4829795736</t>
+          <t>kk_4831257396</t>
         </is>
       </c>
       <c r="B92" t="inlineStr"/>
       <c r="C92" t="inlineStr">
         <is>
-          <t>303489</t>
+          <t>303571</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>Awareness</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>(not set)</t>
+          <t>benz_running_program_2026_coupon</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>(not set)</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>(not set)</t>
+          <t>Unknown</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>kk_3964942719</t>
+          <t>kk_4832100101</t>
         </is>
       </c>
       <c r="B93" t="inlineStr"/>
       <c r="C93" t="inlineStr">
         <is>
-          <t>270600</t>
+          <t>303635</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Awareness</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>컬럼비아_DPA_240530</t>
+          <t>benz_running_program_2026_coupon</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>(not set)</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>(not set)</t>
+          <t>Unknown</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>kk_4828995903</t>
+          <t>kk_4831799020</t>
         </is>
       </c>
       <c r="B94" t="inlineStr"/>
       <c r="C94" t="inlineStr">
         <is>
-          <t>303445</t>
+          <t>303609</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Awareness</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>(not set)</t>
+          <t>benz_running_program_2026_coupon</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>(not set)</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>(not set)</t>
+          <t>Unknown</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>kk_4829109495</t>
+          <t>kk_4831532519</t>
         </is>
       </c>
       <c r="B95" t="inlineStr"/>
       <c r="C95" t="inlineStr">
         <is>
-          <t>303456</t>
+          <t>303587</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Awareness</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>da</t>
+          <t>benz_running_program_2026_coupon</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>(not set)</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>(not set)</t>
+          <t>Unknown</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>kk_4830147171</t>
+          <t>kk_4831981914</t>
         </is>
       </c>
       <c r="B96" t="inlineStr"/>
       <c r="C96" t="inlineStr">
         <is>
-          <t>303506</t>
+          <t>303620</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>Awareness</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>(not set)</t>
+          <t>benz_running_program_2026_coupon</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>(not set)</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>(not set)</t>
+          <t>Unknown</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>kk_4830615705</t>
+          <t>kk_4832190692</t>
         </is>
       </c>
       <c r="B97" t="inlineStr"/>
       <c r="C97" t="inlineStr">
         <is>
-          <t>303543</t>
+          <t>303649</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>Awareness</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>(not set)</t>
+          <t>benz_running_program_2026_coupon</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>(not set)</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>(not set)</t>
+          <t>Unknown</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>kk_4830462005</t>
+          <t>kk_4831986570</t>
         </is>
       </c>
       <c r="B98" t="inlineStr"/>
       <c r="C98" t="inlineStr">
         <is>
-          <t>303523</t>
+          <t>303622</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Awareness</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>6968489536332</t>
+          <t>benz_running_program_2026_coupon</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>(not set)</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>(not set)</t>
+          <t>Unknown</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>kk_4829888934</t>
+          <t>kk_4831468314</t>
         </is>
       </c>
       <c r="B99" t="inlineStr"/>
       <c r="C99" t="inlineStr">
         <is>
-          <t>303493</t>
+          <t>303578</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Awareness</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>EFW</t>
+          <t>benz_running_program_2026_coupon</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>(not set)</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>(not set)</t>
+          <t>Unknown</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>kk_4830552074</t>
+          <t>kk_4832001343</t>
         </is>
       </c>
       <c r="B100" t="inlineStr"/>
       <c r="C100" t="inlineStr">
         <is>
-          <t>303534</t>
+          <t>303625</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
@@ -3723,25 +3723,25 @@
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>(not set)</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>(not set)</t>
+          <t>Unknown</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>kk_4830585310</t>
+          <t>kk_4832061430</t>
         </is>
       </c>
       <c r="B101" t="inlineStr"/>
       <c r="C101" t="inlineStr">
         <is>
-          <t>303538</t>
+          <t>303628</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
@@ -3756,58 +3756,58 @@
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>(not set)</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>(not set)</t>
+          <t>Unknown</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>kk_4829567584</t>
+          <t>kk_4831502482</t>
         </is>
       </c>
       <c r="B102" t="inlineStr"/>
       <c r="C102" t="inlineStr">
         <is>
-          <t>303479</t>
+          <t>303583</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Awareness</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>naver_brandsearch_mobile</t>
+          <t>benz_running_program_2026_coupon</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>(not set)</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>(not set)</t>
+          <t>Unknown</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>kk_4829654698</t>
+          <t>kk_4831517271</t>
         </is>
       </c>
       <c r="B103" t="inlineStr"/>
       <c r="C103" t="inlineStr">
         <is>
-          <t>303481</t>
+          <t>303584</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
@@ -3817,162 +3817,162 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>컬럼비아_DPA_240530</t>
+          <t>naver_brandsearch_mobile</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>(not set)</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>(not set)</t>
+          <t>Unknown</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>kk_4830596422</t>
+          <t>kk_4831951614</t>
         </is>
       </c>
       <c r="B104" t="inlineStr"/>
       <c r="C104" t="inlineStr">
         <is>
-          <t>303540</t>
+          <t>303618</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>(not set)</t>
+          <t>naver_brandsearch_mobile</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>(not set)</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>(not set)</t>
+          <t>Unknown</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>kk_4830179868</t>
+          <t>kk_4832186210</t>
         </is>
       </c>
       <c r="B105" t="inlineStr"/>
       <c r="C105" t="inlineStr">
         <is>
-          <t>303508</t>
+          <t>303648</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>(not set)</t>
+          <t>naver_brandsearch_mobile</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>(not set)</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>(not set)</t>
+          <t>Unknown</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>kk_4829899341</t>
+          <t>kk_4831774426</t>
         </is>
       </c>
       <c r="B106" t="inlineStr"/>
       <c r="C106" t="inlineStr">
         <is>
-          <t>303495</t>
+          <t>303604</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>(not set)</t>
+          <t>naver_brandsearch_mobile</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>(not set)</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>(not set)</t>
+          <t>Unknown</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>kk_4829843383</t>
+          <t>kk_4831822425</t>
         </is>
       </c>
       <c r="B107" t="inlineStr"/>
       <c r="C107" t="inlineStr">
         <is>
-          <t>303492</t>
+          <t>303610</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>(not set)</t>
+          <t>naver_brandsearch_mobile</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>(not set)</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>(not set)</t>
+          <t>Unknown</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>kk_4830568801</t>
+          <t>kk_4831585022</t>
         </is>
       </c>
       <c r="B108" t="inlineStr"/>
       <c r="C108" t="inlineStr">
         <is>
-          <t>303537</t>
+          <t>303591</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
@@ -3982,30 +3982,30 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>(organic)</t>
+          <t>naver_brandsearch_mobile</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>(not set)</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>(not set)</t>
+          <t>Unknown</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>kk_4829500046</t>
+          <t>kk_4831723596</t>
         </is>
       </c>
       <c r="B109" t="inlineStr"/>
       <c r="C109" t="inlineStr">
         <is>
-          <t>303474</t>
+          <t>303600</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
@@ -4015,129 +4015,129 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>(organic)</t>
+          <t>naver_brandsearch_mobile</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>(not set)</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>(not set)</t>
+          <t>Unknown</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>kk_4829755741</t>
+          <t>minpark98</t>
         </is>
       </c>
       <c r="B110" t="inlineStr"/>
       <c r="C110" t="inlineStr">
         <is>
-          <t>303486</t>
+          <t>303657</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>Organic Traffic</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>(referral)</t>
+          <t>naver_brandsearch_pc</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>(not set)</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>(not set)</t>
+          <t>Unknown</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>onoff</t>
+          <t>kk_4831488942</t>
         </is>
       </c>
       <c r="B111" t="inlineStr"/>
       <c r="C111" t="inlineStr">
         <is>
-          <t>303518</t>
+          <t>303580</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>Organic Traffic</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>(referral)</t>
+          <t>naver_brandsearch_pc</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>(not set)</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>(not set)</t>
+          <t>Unknown</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>kk_4829255442</t>
+          <t>kk_4831615271</t>
         </is>
       </c>
       <c r="B112" t="inlineStr"/>
       <c r="C112" t="inlineStr">
         <is>
-          <t>303464</t>
+          <t>303594</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>Organic Traffic</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>(referral)</t>
+          <t>sa</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>(not set)</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>(not set)</t>
+          <t>Unknown</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>kk_4830541132</t>
+          <t>kk_4831600231</t>
         </is>
       </c>
       <c r="B113" t="inlineStr"/>
       <c r="C113" t="inlineStr">
         <is>
-          <t>303533</t>
+          <t>303592</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
@@ -4147,30 +4147,30 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>6968489536332</t>
+          <t>sa</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>(not set)</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>(not set)</t>
+          <t>Unknown</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>kk_4830409260</t>
+          <t>kk_4828653802</t>
         </is>
       </c>
       <c r="B114" t="inlineStr"/>
       <c r="C114" t="inlineStr">
         <is>
-          <t>303522</t>
+          <t>303422</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
@@ -4180,63 +4180,63 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>6968489536332</t>
+          <t>(organic)</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>(not set)</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>(not set)</t>
+          <t>Unknown</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>kk_4829999849</t>
+          <t>kk_4829795736</t>
         </is>
       </c>
       <c r="B115" t="inlineStr"/>
       <c r="C115" t="inlineStr">
         <is>
-          <t>303498</t>
+          <t>303489</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>6968489536332</t>
+          <t>(not set)</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>(not set)</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>(not set)</t>
+          <t>Unknown</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>kk_4830646394</t>
+          <t>kk_3964942719</t>
         </is>
       </c>
       <c r="B116" t="inlineStr"/>
       <c r="C116" t="inlineStr">
         <is>
-          <t>303547</t>
+          <t>270600</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
@@ -4246,63 +4246,63 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>6968489536332</t>
+          <t>컬럼비아_DPA_240530</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>(not set)</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>(not set)</t>
+          <t>Unknown</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>kk_4829674741</t>
+          <t>kk_4828995903</t>
         </is>
       </c>
       <c r="B117" t="inlineStr"/>
       <c r="C117" t="inlineStr">
         <is>
-          <t>303484</t>
+          <t>303445</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>6968489536332</t>
+          <t>(not set)</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>(not set)</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>(not set)</t>
+          <t>Unknown</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>kk_4830404781</t>
+          <t>kk_4829109495</t>
         </is>
       </c>
       <c r="B118" t="inlineStr"/>
       <c r="C118" t="inlineStr">
         <is>
-          <t>303521</t>
+          <t>303456</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
@@ -4312,228 +4312,228 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>6968489536332</t>
+          <t>da</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>(not set)</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>(not set)</t>
+          <t>Unknown</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>kk_4830692253</t>
+          <t>kk_4830147171</t>
         </is>
       </c>
       <c r="B119" t="inlineStr"/>
       <c r="C119" t="inlineStr">
         <is>
-          <t>303550</t>
+          <t>303506</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>6968489536332</t>
+          <t>(not set)</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>(not set)</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>(not set)</t>
+          <t>Unknown</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>akita1129</t>
+          <t>kk_4830615705</t>
         </is>
       </c>
       <c r="B120" t="inlineStr"/>
       <c r="C120" t="inlineStr">
         <is>
-          <t>303465</t>
+          <t>303543</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>EFW</t>
+          <t>(not set)</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>(not set)</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>(not set)</t>
+          <t>Unknown</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>kk_4830264628</t>
+          <t>kk_4830462005</t>
         </is>
       </c>
       <c r="B121" t="inlineStr"/>
       <c r="C121" t="inlineStr">
         <is>
-          <t>303514</t>
+          <t>303523</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>Official SNS</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>EFW_04</t>
+          <t>6968489536332</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>(not set)</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>(not set)</t>
+          <t>Unknown</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>kk_4830559393</t>
+          <t>kk_4829888934</t>
         </is>
       </c>
       <c r="B122" t="inlineStr"/>
       <c r="C122" t="inlineStr">
         <is>
-          <t>303535</t>
+          <t>303493</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>Official SNS</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>EFW_04</t>
+          <t>EFW</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>(not set)</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>(not set)</t>
+          <t>Unknown</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>kk_4829543360</t>
+          <t>kk_4830552074</t>
         </is>
       </c>
       <c r="B123" t="inlineStr"/>
       <c r="C123" t="inlineStr">
         <is>
-          <t>303478</t>
+          <t>303534</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>Official SNS</t>
+          <t>Awareness</t>
         </is>
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>EFW_04</t>
+          <t>benz_running_program_2026_coupon</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>(not set)</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>(not set)</t>
+          <t>Unknown</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>mong81</t>
+          <t>kk_4830585310</t>
         </is>
       </c>
       <c r="B124" t="inlineStr"/>
       <c r="C124" t="inlineStr">
         <is>
-          <t>303505</t>
+          <t>303538</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>Official SNS</t>
+          <t>Awareness</t>
         </is>
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>EFW_04</t>
+          <t>benz_running_program_2026_coupon</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>(not set)</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>(not set)</t>
+          <t>Unknown</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>kk_4830253885</t>
+          <t>kk_4829567584</t>
         </is>
       </c>
       <c r="B125" t="inlineStr"/>
       <c r="C125" t="inlineStr">
         <is>
-          <t>303512</t>
+          <t>303479</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
@@ -4543,30 +4543,30 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>KAKAO_CH_MENU_0211_NEW_WOMEN</t>
+          <t>naver_brandsearch_mobile</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>(not set)</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>(not set)</t>
+          <t>Unknown</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>kk_4829512827</t>
+          <t>kk_4829654698</t>
         </is>
       </c>
       <c r="B126" t="inlineStr"/>
       <c r="C126" t="inlineStr">
         <is>
-          <t>303475</t>
+          <t>303481</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
@@ -4576,360 +4576,360 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>[PF]전환_회원가입(유사)</t>
+          <t>컬럼비아_DPA_240530</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>(not set)</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>(not set)</t>
+          <t>Unknown</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>kk_4830637852</t>
+          <t>kk_4829843383</t>
         </is>
       </c>
       <c r="B127" t="inlineStr"/>
       <c r="C127" t="inlineStr">
         <is>
-          <t>303546</t>
+          <t>303492</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>Awareness</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>benz_running_program_2026_coupon</t>
+          <t>(not set)</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>(not set)</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>(not set)</t>
+          <t>Unknown</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>kk_4830704540</t>
+          <t>kk_4829899341</t>
         </is>
       </c>
       <c r="B128" t="inlineStr"/>
       <c r="C128" t="inlineStr">
         <is>
-          <t>303551</t>
+          <t>303495</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>Awareness</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>benz_running_program_2026_coupon</t>
+          <t>(not set)</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>(not set)</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>(not set)</t>
+          <t>Unknown</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>kk_4830308577</t>
+          <t>kk_4830596422</t>
         </is>
       </c>
       <c r="B129" t="inlineStr"/>
       <c r="C129" t="inlineStr">
         <is>
-          <t>303516</t>
+          <t>303540</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>Awareness</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>benz_running_program_2026_coupon</t>
+          <t>(not set)</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>(not set)</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>(not set)</t>
+          <t>Unknown</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>kk_4830497611</t>
+          <t>kk_4830179868</t>
         </is>
       </c>
       <c r="B130" t="inlineStr"/>
       <c r="C130" t="inlineStr">
         <is>
-          <t>303526</t>
+          <t>303508</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>Awareness</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>benz_running_program_2026_coupon</t>
+          <t>(not set)</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>(not set)</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>(not set)</t>
+          <t>Unknown</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>kk_4830722522</t>
+          <t>kk_4829500046</t>
         </is>
       </c>
       <c r="B131" t="inlineStr"/>
       <c r="C131" t="inlineStr">
         <is>
-          <t>303553</t>
+          <t>303474</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>Awareness</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>benz_running_program_2026_coupon</t>
+          <t>(organic)</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>(not set)</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>(not set)</t>
+          <t>Unknown</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>flydabi</t>
+          <t>kk_4830568801</t>
         </is>
       </c>
       <c r="B132" t="inlineStr"/>
       <c r="C132" t="inlineStr">
         <is>
-          <t>303531</t>
+          <t>303537</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>Awareness</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>benz_running_program_2026_coupon</t>
+          <t>(organic)</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>(not set)</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>(not set)</t>
+          <t>Unknown</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>kk_4830597347</t>
+          <t>kk_4829755741</t>
         </is>
       </c>
       <c r="B133" t="inlineStr"/>
       <c r="C133" t="inlineStr">
         <is>
-          <t>303541</t>
+          <t>303486</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>Awareness</t>
+          <t>Organic Traffic</t>
         </is>
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>benz_running_program_2026_coupon</t>
+          <t>(referral)</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>(not set)</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>(not set)</t>
+          <t>Unknown</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>kk_4830659012</t>
+          <t>kk_4829255442</t>
         </is>
       </c>
       <c r="B134" t="inlineStr"/>
       <c r="C134" t="inlineStr">
         <is>
-          <t>303549</t>
+          <t>303464</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>Awareness</t>
+          <t>Organic Traffic</t>
         </is>
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>benz_running_program_2026_coupon</t>
+          <t>(referral)</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>(not set)</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>(not set)</t>
+          <t>Unknown</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>kk_4830376206</t>
+          <t>onoff</t>
         </is>
       </c>
       <c r="B135" t="inlineStr"/>
       <c r="C135" t="inlineStr">
         <is>
-          <t>303520</t>
+          <t>303518</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>Awareness</t>
+          <t>Organic Traffic</t>
         </is>
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>benz_running_program_2026_coupon</t>
+          <t>(referral)</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>(not set)</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>(not set)</t>
+          <t>Unknown</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>kk_4830760298</t>
+          <t>kk_4830409260</t>
         </is>
       </c>
       <c r="B136" t="inlineStr"/>
       <c r="C136" t="inlineStr">
         <is>
-          <t>303554</t>
+          <t>303522</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>Awareness</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>benz_running_program_2026​</t>
+          <t>6968489536332</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>(not set)</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>(not set)</t>
+          <t>Unknown</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>kk_4830212469</t>
+          <t>kk_4830541132</t>
         </is>
       </c>
       <c r="B137" t="inlineStr"/>
       <c r="C137" t="inlineStr">
         <is>
-          <t>303509</t>
+          <t>303533</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
@@ -4939,30 +4939,30 @@
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>da</t>
+          <t>6968489536332</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>(not set)</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>(not set)</t>
+          <t>Unknown</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>kk_4830137292</t>
+          <t>kk_4830692253</t>
         </is>
       </c>
       <c r="B138" t="inlineStr"/>
       <c r="C138" t="inlineStr">
         <is>
-          <t>303504</t>
+          <t>303550</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
@@ -4972,30 +4972,30 @@
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>naver_brandsearch_mobile</t>
+          <t>6968489536332</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>(not set)</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>(not set)</t>
+          <t>Unknown</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>kk_4830540435</t>
+          <t>kk_4830646394</t>
         </is>
       </c>
       <c r="B139" t="inlineStr"/>
       <c r="C139" t="inlineStr">
         <is>
-          <t>303532</t>
+          <t>303547</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
@@ -5005,30 +5005,30 @@
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>naver_brandsearch_mobile</t>
+          <t>6968489536332</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>(not set)</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>(not set)</t>
+          <t>Unknown</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>susaeg202</t>
+          <t>kk_4829674741</t>
         </is>
       </c>
       <c r="B140" t="inlineStr"/>
       <c r="C140" t="inlineStr">
         <is>
-          <t>303469</t>
+          <t>303484</t>
         </is>
       </c>
       <c r="D140" t="inlineStr">
@@ -5038,30 +5038,30 @@
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>naver_brandsearch_pc</t>
+          <t>6968489536332</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>(not set)</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>(not set)</t>
+          <t>Unknown</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>kk_4829761376</t>
+          <t>kk_4829999849</t>
         </is>
       </c>
       <c r="B141" t="inlineStr"/>
       <c r="C141" t="inlineStr">
         <is>
-          <t>303487</t>
+          <t>303498</t>
         </is>
       </c>
       <c r="D141" t="inlineStr">
@@ -5071,30 +5071,30 @@
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>naversa_mo</t>
+          <t>6968489536332</t>
         </is>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>(not set)</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>(not set)</t>
+          <t>Unknown</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>kk_4830179048</t>
+          <t>kk_4830404781</t>
         </is>
       </c>
       <c r="B142" t="inlineStr"/>
       <c r="C142" t="inlineStr">
         <is>
-          <t>303507</t>
+          <t>303521</t>
         </is>
       </c>
       <c r="D142" t="inlineStr">
@@ -5104,228 +5104,228 @@
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>naversa_mo</t>
+          <t>6968489536332</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>(not set)</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>(not set)</t>
+          <t>Unknown</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>kk_4828679899</t>
+          <t>akita1129</t>
         </is>
       </c>
       <c r="B143" t="inlineStr"/>
       <c r="C143" t="inlineStr">
         <is>
-          <t>303425</t>
+          <t>303465</t>
         </is>
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>Official SNS</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>EFW_04</t>
+          <t>EFW</t>
         </is>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>(not set)</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>(not set)</t>
+          <t>Unknown</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>kk_4828953106</t>
+          <t>kk_4829543360</t>
         </is>
       </c>
       <c r="B144" t="inlineStr"/>
       <c r="C144" t="inlineStr">
         <is>
-          <t>303440</t>
+          <t>303478</t>
         </is>
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Official SNS</t>
         </is>
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>benz_running_program_2026_coupon</t>
+          <t>EFW_04</t>
         </is>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>(not set)</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>(not set)</t>
+          <t>Unknown</t>
         </is>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>kk_4828662042</t>
+          <t>kk_4830559393</t>
         </is>
       </c>
       <c r="B145" t="inlineStr"/>
       <c r="C145" t="inlineStr">
         <is>
-          <t>303423</t>
+          <t>303535</t>
         </is>
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>Awareness</t>
+          <t>Official SNS</t>
         </is>
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>benz_running_program_2026_coupon</t>
+          <t>EFW_04</t>
         </is>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>(not set)</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>(not set)</t>
+          <t>Unknown</t>
         </is>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>kk_4828776483</t>
+          <t>mong81</t>
         </is>
       </c>
       <c r="B146" t="inlineStr"/>
       <c r="C146" t="inlineStr">
         <is>
-          <t>303428</t>
+          <t>303505</t>
         </is>
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Official SNS</t>
         </is>
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>naver_brandsearch_mobile</t>
+          <t>EFW_04</t>
         </is>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>(not set)</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>(not set)</t>
+          <t>Unknown</t>
         </is>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>kk_4829004394</t>
+          <t>kk_4830264628</t>
         </is>
       </c>
       <c r="B147" t="inlineStr"/>
       <c r="C147" t="inlineStr">
         <is>
-          <t>303447</t>
+          <t>303514</t>
         </is>
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>Official SNS</t>
         </is>
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>(not set)</t>
+          <t>EFW_04</t>
         </is>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>(not set)</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>(not set)</t>
+          <t>Unknown</t>
         </is>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>kk_4828853669</t>
+          <t>kk_4830253885</t>
         </is>
       </c>
       <c r="B148" t="inlineStr"/>
       <c r="C148" t="inlineStr">
         <is>
-          <t>303431</t>
+          <t>303512</t>
         </is>
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>(organic)</t>
+          <t>KAKAO_CH_MENU_0211_NEW_WOMEN</t>
         </is>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>(not set)</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>(not set)</t>
+          <t>Unknown</t>
         </is>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>kk_4828870663</t>
+          <t>kk_4829512827</t>
         </is>
       </c>
       <c r="B149" t="inlineStr"/>
       <c r="C149" t="inlineStr">
         <is>
-          <t>303434</t>
+          <t>303475</t>
         </is>
       </c>
       <c r="D149" t="inlineStr">
@@ -5335,327 +5335,327 @@
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>(organic)</t>
+          <t>[PF]전환_회원가입(유사)</t>
         </is>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>(not set)</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>(not set)</t>
+          <t>Unknown</t>
         </is>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>kk_4829016429</t>
+          <t>kk_4830704540</t>
         </is>
       </c>
       <c r="B150" t="inlineStr"/>
       <c r="C150" t="inlineStr">
         <is>
-          <t>303450</t>
+          <t>303551</t>
         </is>
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>Organic Traffic</t>
+          <t>Awareness</t>
         </is>
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>(organic)</t>
+          <t>benz_running_program_2026_coupon</t>
         </is>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>(not set)</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>(not set)</t>
+          <t>Unknown</t>
         </is>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>kk_4829012080</t>
+          <t>kk_4830637852</t>
         </is>
       </c>
       <c r="B151" t="inlineStr"/>
       <c r="C151" t="inlineStr">
         <is>
-          <t>303448</t>
+          <t>303546</t>
         </is>
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>Organic Traffic</t>
+          <t>Awareness</t>
         </is>
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>(referral)</t>
+          <t>benz_running_program_2026_coupon</t>
         </is>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>(not set)</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>(not set)</t>
+          <t>Unknown</t>
         </is>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>kk_4829143684</t>
+          <t>kk_4830497611</t>
         </is>
       </c>
       <c r="B152" t="inlineStr"/>
       <c r="C152" t="inlineStr">
         <is>
-          <t>303458</t>
+          <t>303526</t>
         </is>
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Awareness</t>
         </is>
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>6968489536332</t>
+          <t>benz_running_program_2026_coupon</t>
         </is>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>(not set)</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>(not set)</t>
+          <t>Unknown</t>
         </is>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>kk_4828900771</t>
+          <t>kk_4830376206</t>
         </is>
       </c>
       <c r="B153" t="inlineStr"/>
       <c r="C153" t="inlineStr">
         <is>
-          <t>303438</t>
+          <t>303520</t>
         </is>
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Awareness</t>
         </is>
       </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t>6968489536332</t>
+          <t>benz_running_program_2026_coupon</t>
         </is>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>(not set)</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>(not set)</t>
+          <t>Unknown</t>
         </is>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>gee04171</t>
+          <t>kk_4830308577</t>
         </is>
       </c>
       <c r="B154" t="inlineStr"/>
       <c r="C154" t="inlineStr">
         <is>
-          <t>303449</t>
+          <t>303516</t>
         </is>
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Awareness</t>
         </is>
       </c>
       <c r="E154" t="inlineStr">
         <is>
-          <t>6968489536332</t>
+          <t>benz_running_program_2026_coupon</t>
         </is>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>(not set)</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>(not set)</t>
+          <t>Unknown</t>
         </is>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>kk_4828729325</t>
+          <t>kk_4830597347</t>
         </is>
       </c>
       <c r="B155" t="inlineStr"/>
       <c r="C155" t="inlineStr">
         <is>
-          <t>303426</t>
+          <t>303541</t>
         </is>
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Awareness</t>
         </is>
       </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t>EFW</t>
+          <t>benz_running_program_2026_coupon</t>
         </is>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>(not set)</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>(not set)</t>
+          <t>Unknown</t>
         </is>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>kk_4828995176</t>
+          <t>flydabi</t>
         </is>
       </c>
       <c r="B156" t="inlineStr"/>
       <c r="C156" t="inlineStr">
         <is>
-          <t>303444</t>
+          <t>303531</t>
         </is>
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t>Official SNS</t>
+          <t>Awareness</t>
         </is>
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t>Heritage</t>
+          <t>benz_running_program_2026_coupon</t>
         </is>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>(not set)</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>(not set)</t>
+          <t>Unknown</t>
         </is>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>kk_4828781963</t>
+          <t>kk_4830722522</t>
         </is>
       </c>
       <c r="B157" t="inlineStr"/>
       <c r="C157" t="inlineStr">
         <is>
-          <t>303429</t>
+          <t>303553</t>
         </is>
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Awareness</t>
         </is>
       </c>
       <c r="E157" t="inlineStr">
         <is>
-          <t>KAKAO_CH_MESSAGE_0325_S26NEW_CTA</t>
+          <t>benz_running_program_2026_coupon</t>
         </is>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>(not set)</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>(not set)</t>
+          <t>Unknown</t>
         </is>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>kk_4829073557</t>
+          <t>kk_4830659012</t>
         </is>
       </c>
       <c r="B158" t="inlineStr"/>
       <c r="C158" t="inlineStr">
         <is>
-          <t>303452</t>
+          <t>303549</t>
         </is>
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Awareness</t>
         </is>
       </c>
       <c r="E158" t="inlineStr">
         <is>
-          <t>[PF]전환_회원가입(유사)</t>
+          <t>benz_running_program_2026_coupon</t>
         </is>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>(not set)</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>(not set)</t>
+          <t>Unknown</t>
         </is>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>kk_4828671248</t>
+          <t>kk_4830760298</t>
         </is>
       </c>
       <c r="B159" t="inlineStr"/>
       <c r="C159" t="inlineStr">
         <is>
-          <t>303424</t>
+          <t>303554</t>
         </is>
       </c>
       <c r="D159" t="inlineStr">
@@ -5665,129 +5665,129 @@
       </c>
       <c r="E159" t="inlineStr">
         <is>
-          <t>benz_running_program_2026_coupon</t>
+          <t>benz_running_program_2026​</t>
         </is>
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>(not set)</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>(not set)</t>
+          <t>Unknown</t>
         </is>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>kk_4829107379</t>
+          <t>kk_4830212469</t>
         </is>
       </c>
       <c r="B160" t="inlineStr"/>
       <c r="C160" t="inlineStr">
         <is>
-          <t>303455</t>
+          <t>303509</t>
         </is>
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t>Awareness</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E160" t="inlineStr">
         <is>
-          <t>benz_running_program_2026_coupon</t>
+          <t>da</t>
         </is>
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>(not set)</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t>(not set)</t>
+          <t>Unknown</t>
         </is>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>kk_4829201314</t>
+          <t>kk_4830540435</t>
         </is>
       </c>
       <c r="B161" t="inlineStr"/>
       <c r="C161" t="inlineStr">
         <is>
-          <t>303461</t>
+          <t>303532</t>
         </is>
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>Awareness</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E161" t="inlineStr">
         <is>
-          <t>benz_running_program_2026_coupon</t>
+          <t>naver_brandsearch_mobile</t>
         </is>
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>(not set)</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="G161" t="inlineStr">
         <is>
-          <t>(not set)</t>
+          <t>Unknown</t>
         </is>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>kk_4828876907</t>
+          <t>kk_4830137292</t>
         </is>
       </c>
       <c r="B162" t="inlineStr"/>
       <c r="C162" t="inlineStr">
         <is>
-          <t>303436</t>
+          <t>303504</t>
         </is>
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>Awareness</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E162" t="inlineStr">
         <is>
-          <t>benz_running_program_2026_coupon</t>
+          <t>naver_brandsearch_mobile</t>
         </is>
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>(not set)</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="G162" t="inlineStr">
         <is>
-          <t>(not set)</t>
+          <t>Unknown</t>
         </is>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>kk_4828903098</t>
+          <t>susaeg202</t>
         </is>
       </c>
       <c r="B163" t="inlineStr"/>
       <c r="C163" t="inlineStr">
         <is>
-          <t>303439</t>
+          <t>303469</t>
         </is>
       </c>
       <c r="D163" t="inlineStr">
@@ -5797,30 +5797,30 @@
       </c>
       <c r="E163" t="inlineStr">
         <is>
-          <t>naver_brandsearch_mobile</t>
+          <t>naver_brandsearch_pc</t>
         </is>
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>(not set)</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="G163" t="inlineStr">
         <is>
-          <t>(not set)</t>
+          <t>Unknown</t>
         </is>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>kk_4828872529</t>
+          <t>kk_4829761376</t>
         </is>
       </c>
       <c r="B164" t="inlineStr"/>
       <c r="C164" t="inlineStr">
         <is>
-          <t>303435</t>
+          <t>303487</t>
         </is>
       </c>
       <c r="D164" t="inlineStr">
@@ -5830,30 +5830,30 @@
       </c>
       <c r="E164" t="inlineStr">
         <is>
-          <t>naver_brandsearch_mobile</t>
+          <t>naversa_mo</t>
         </is>
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>(not set)</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="G164" t="inlineStr">
         <is>
-          <t>(not set)</t>
+          <t>Unknown</t>
         </is>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>kk_4828987324</t>
+          <t>kk_4830179048</t>
         </is>
       </c>
       <c r="B165" t="inlineStr"/>
       <c r="C165" t="inlineStr">
         <is>
-          <t>303443</t>
+          <t>303507</t>
         </is>
       </c>
       <c r="D165" t="inlineStr">
@@ -5868,45 +5868,804 @@
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>(not set)</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="G165" t="inlineStr">
         <is>
-          <t>(not set)</t>
+          <t>Unknown</t>
         </is>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>kk_4828986759</t>
+          <t>kk_4828679899</t>
         </is>
       </c>
       <c r="B166" t="inlineStr"/>
       <c r="C166" t="inlineStr">
         <is>
+          <t>303425</t>
+        </is>
+      </c>
+      <c r="D166" t="inlineStr">
+        <is>
+          <t>Official SNS</t>
+        </is>
+      </c>
+      <c r="E166" t="inlineStr">
+        <is>
+          <t>EFW_04</t>
+        </is>
+      </c>
+      <c r="F166" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="G166" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" t="inlineStr">
+        <is>
+          <t>kk_4828662042</t>
+        </is>
+      </c>
+      <c r="B167" t="inlineStr"/>
+      <c r="C167" t="inlineStr">
+        <is>
+          <t>303423</t>
+        </is>
+      </c>
+      <c r="D167" t="inlineStr">
+        <is>
+          <t>Awareness</t>
+        </is>
+      </c>
+      <c r="E167" t="inlineStr">
+        <is>
+          <t>benz_running_program_2026_coupon</t>
+        </is>
+      </c>
+      <c r="F167" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="G167" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" t="inlineStr">
+        <is>
+          <t>kk_4828953106</t>
+        </is>
+      </c>
+      <c r="B168" t="inlineStr"/>
+      <c r="C168" t="inlineStr">
+        <is>
+          <t>303440</t>
+        </is>
+      </c>
+      <c r="D168" t="inlineStr">
+        <is>
+          <t>Owned Channel</t>
+        </is>
+      </c>
+      <c r="E168" t="inlineStr">
+        <is>
+          <t>benz_running_program_2026_coupon</t>
+        </is>
+      </c>
+      <c r="F168" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="G168" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" t="inlineStr">
+        <is>
+          <t>kk_4828776483</t>
+        </is>
+      </c>
+      <c r="B169" t="inlineStr"/>
+      <c r="C169" t="inlineStr">
+        <is>
+          <t>303428</t>
+        </is>
+      </c>
+      <c r="D169" t="inlineStr">
+        <is>
+          <t>Paid Ad</t>
+        </is>
+      </c>
+      <c r="E169" t="inlineStr">
+        <is>
+          <t>naver_brandsearch_mobile</t>
+        </is>
+      </c>
+      <c r="F169" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="G169" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" t="inlineStr">
+        <is>
+          <t>kk_4829004394</t>
+        </is>
+      </c>
+      <c r="B170" t="inlineStr"/>
+      <c r="C170" t="inlineStr">
+        <is>
+          <t>303447</t>
+        </is>
+      </c>
+      <c r="D170" t="inlineStr">
+        <is>
+          <t>Direct</t>
+        </is>
+      </c>
+      <c r="E170" t="inlineStr">
+        <is>
+          <t>(not set)</t>
+        </is>
+      </c>
+      <c r="F170" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="G170" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" t="inlineStr">
+        <is>
+          <t>kk_4829016429</t>
+        </is>
+      </c>
+      <c r="B171" t="inlineStr"/>
+      <c r="C171" t="inlineStr">
+        <is>
+          <t>303450</t>
+        </is>
+      </c>
+      <c r="D171" t="inlineStr">
+        <is>
+          <t>Organic Traffic</t>
+        </is>
+      </c>
+      <c r="E171" t="inlineStr">
+        <is>
+          <t>(organic)</t>
+        </is>
+      </c>
+      <c r="F171" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="G171" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" t="inlineStr">
+        <is>
+          <t>kk_4828853669</t>
+        </is>
+      </c>
+      <c r="B172" t="inlineStr"/>
+      <c r="C172" t="inlineStr">
+        <is>
+          <t>303431</t>
+        </is>
+      </c>
+      <c r="D172" t="inlineStr">
+        <is>
+          <t>Paid Ad</t>
+        </is>
+      </c>
+      <c r="E172" t="inlineStr">
+        <is>
+          <t>(organic)</t>
+        </is>
+      </c>
+      <c r="F172" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="G172" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" t="inlineStr">
+        <is>
+          <t>kk_4828870663</t>
+        </is>
+      </c>
+      <c r="B173" t="inlineStr"/>
+      <c r="C173" t="inlineStr">
+        <is>
+          <t>303434</t>
+        </is>
+      </c>
+      <c r="D173" t="inlineStr">
+        <is>
+          <t>Paid Ad</t>
+        </is>
+      </c>
+      <c r="E173" t="inlineStr">
+        <is>
+          <t>(organic)</t>
+        </is>
+      </c>
+      <c r="F173" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="G173" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" t="inlineStr">
+        <is>
+          <t>kk_4829012080</t>
+        </is>
+      </c>
+      <c r="B174" t="inlineStr"/>
+      <c r="C174" t="inlineStr">
+        <is>
+          <t>303448</t>
+        </is>
+      </c>
+      <c r="D174" t="inlineStr">
+        <is>
+          <t>Organic Traffic</t>
+        </is>
+      </c>
+      <c r="E174" t="inlineStr">
+        <is>
+          <t>(referral)</t>
+        </is>
+      </c>
+      <c r="F174" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="G174" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" t="inlineStr">
+        <is>
+          <t>gee04171</t>
+        </is>
+      </c>
+      <c r="B175" t="inlineStr"/>
+      <c r="C175" t="inlineStr">
+        <is>
+          <t>303449</t>
+        </is>
+      </c>
+      <c r="D175" t="inlineStr">
+        <is>
+          <t>Paid Ad</t>
+        </is>
+      </c>
+      <c r="E175" t="inlineStr">
+        <is>
+          <t>6968489536332</t>
+        </is>
+      </c>
+      <c r="F175" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="G175" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" t="inlineStr">
+        <is>
+          <t>kk_4829143684</t>
+        </is>
+      </c>
+      <c r="B176" t="inlineStr"/>
+      <c r="C176" t="inlineStr">
+        <is>
+          <t>303458</t>
+        </is>
+      </c>
+      <c r="D176" t="inlineStr">
+        <is>
+          <t>Paid Ad</t>
+        </is>
+      </c>
+      <c r="E176" t="inlineStr">
+        <is>
+          <t>6968489536332</t>
+        </is>
+      </c>
+      <c r="F176" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="G176" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" t="inlineStr">
+        <is>
+          <t>kk_4828900771</t>
+        </is>
+      </c>
+      <c r="B177" t="inlineStr"/>
+      <c r="C177" t="inlineStr">
+        <is>
+          <t>303438</t>
+        </is>
+      </c>
+      <c r="D177" t="inlineStr">
+        <is>
+          <t>Paid Ad</t>
+        </is>
+      </c>
+      <c r="E177" t="inlineStr">
+        <is>
+          <t>6968489536332</t>
+        </is>
+      </c>
+      <c r="F177" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="G177" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" t="inlineStr">
+        <is>
+          <t>kk_4828729325</t>
+        </is>
+      </c>
+      <c r="B178" t="inlineStr"/>
+      <c r="C178" t="inlineStr">
+        <is>
+          <t>303426</t>
+        </is>
+      </c>
+      <c r="D178" t="inlineStr">
+        <is>
+          <t>Paid Ad</t>
+        </is>
+      </c>
+      <c r="E178" t="inlineStr">
+        <is>
+          <t>EFW</t>
+        </is>
+      </c>
+      <c r="F178" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="G178" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" t="inlineStr">
+        <is>
+          <t>kk_4828995176</t>
+        </is>
+      </c>
+      <c r="B179" t="inlineStr"/>
+      <c r="C179" t="inlineStr">
+        <is>
+          <t>303444</t>
+        </is>
+      </c>
+      <c r="D179" t="inlineStr">
+        <is>
+          <t>Official SNS</t>
+        </is>
+      </c>
+      <c r="E179" t="inlineStr">
+        <is>
+          <t>Heritage</t>
+        </is>
+      </c>
+      <c r="F179" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="G179" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" t="inlineStr">
+        <is>
+          <t>kk_4828781963</t>
+        </is>
+      </c>
+      <c r="B180" t="inlineStr"/>
+      <c r="C180" t="inlineStr">
+        <is>
+          <t>303429</t>
+        </is>
+      </c>
+      <c r="D180" t="inlineStr">
+        <is>
+          <t>Owned Channel</t>
+        </is>
+      </c>
+      <c r="E180" t="inlineStr">
+        <is>
+          <t>KAKAO_CH_MESSAGE_0325_S26NEW_CTA</t>
+        </is>
+      </c>
+      <c r="F180" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="G180" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" t="inlineStr">
+        <is>
+          <t>kk_4829073557</t>
+        </is>
+      </c>
+      <c r="B181" t="inlineStr"/>
+      <c r="C181" t="inlineStr">
+        <is>
+          <t>303452</t>
+        </is>
+      </c>
+      <c r="D181" t="inlineStr">
+        <is>
+          <t>Paid Ad</t>
+        </is>
+      </c>
+      <c r="E181" t="inlineStr">
+        <is>
+          <t>[PF]전환_회원가입(유사)</t>
+        </is>
+      </c>
+      <c r="F181" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="G181" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" t="inlineStr">
+        <is>
+          <t>kk_4828671248</t>
+        </is>
+      </c>
+      <c r="B182" t="inlineStr"/>
+      <c r="C182" t="inlineStr">
+        <is>
+          <t>303424</t>
+        </is>
+      </c>
+      <c r="D182" t="inlineStr">
+        <is>
+          <t>Awareness</t>
+        </is>
+      </c>
+      <c r="E182" t="inlineStr">
+        <is>
+          <t>benz_running_program_2026_coupon</t>
+        </is>
+      </c>
+      <c r="F182" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="G182" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" t="inlineStr">
+        <is>
+          <t>kk_4829107379</t>
+        </is>
+      </c>
+      <c r="B183" t="inlineStr"/>
+      <c r="C183" t="inlineStr">
+        <is>
+          <t>303455</t>
+        </is>
+      </c>
+      <c r="D183" t="inlineStr">
+        <is>
+          <t>Awareness</t>
+        </is>
+      </c>
+      <c r="E183" t="inlineStr">
+        <is>
+          <t>benz_running_program_2026_coupon</t>
+        </is>
+      </c>
+      <c r="F183" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="G183" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" t="inlineStr">
+        <is>
+          <t>kk_4829201314</t>
+        </is>
+      </c>
+      <c r="B184" t="inlineStr"/>
+      <c r="C184" t="inlineStr">
+        <is>
+          <t>303461</t>
+        </is>
+      </c>
+      <c r="D184" t="inlineStr">
+        <is>
+          <t>Awareness</t>
+        </is>
+      </c>
+      <c r="E184" t="inlineStr">
+        <is>
+          <t>benz_running_program_2026_coupon</t>
+        </is>
+      </c>
+      <c r="F184" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="G184" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" t="inlineStr">
+        <is>
+          <t>kk_4828876907</t>
+        </is>
+      </c>
+      <c r="B185" t="inlineStr"/>
+      <c r="C185" t="inlineStr">
+        <is>
+          <t>303436</t>
+        </is>
+      </c>
+      <c r="D185" t="inlineStr">
+        <is>
+          <t>Awareness</t>
+        </is>
+      </c>
+      <c r="E185" t="inlineStr">
+        <is>
+          <t>benz_running_program_2026_coupon</t>
+        </is>
+      </c>
+      <c r="F185" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="G185" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" t="inlineStr">
+        <is>
+          <t>kk_4828872529</t>
+        </is>
+      </c>
+      <c r="B186" t="inlineStr"/>
+      <c r="C186" t="inlineStr">
+        <is>
+          <t>303435</t>
+        </is>
+      </c>
+      <c r="D186" t="inlineStr">
+        <is>
+          <t>Paid Ad</t>
+        </is>
+      </c>
+      <c r="E186" t="inlineStr">
+        <is>
+          <t>naver_brandsearch_mobile</t>
+        </is>
+      </c>
+      <c r="F186" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="G186" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" t="inlineStr">
+        <is>
+          <t>kk_4828903098</t>
+        </is>
+      </c>
+      <c r="B187" t="inlineStr"/>
+      <c r="C187" t="inlineStr">
+        <is>
+          <t>303439</t>
+        </is>
+      </c>
+      <c r="D187" t="inlineStr">
+        <is>
+          <t>Paid Ad</t>
+        </is>
+      </c>
+      <c r="E187" t="inlineStr">
+        <is>
+          <t>naver_brandsearch_mobile</t>
+        </is>
+      </c>
+      <c r="F187" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="G187" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" t="inlineStr">
+        <is>
+          <t>kk_4828987324</t>
+        </is>
+      </c>
+      <c r="B188" t="inlineStr"/>
+      <c r="C188" t="inlineStr">
+        <is>
+          <t>303443</t>
+        </is>
+      </c>
+      <c r="D188" t="inlineStr">
+        <is>
+          <t>Paid Ad</t>
+        </is>
+      </c>
+      <c r="E188" t="inlineStr">
+        <is>
+          <t>naversa_mo</t>
+        </is>
+      </c>
+      <c r="F188" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="G188" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" t="inlineStr">
+        <is>
+          <t>kk_4828986759</t>
+        </is>
+      </c>
+      <c r="B189" t="inlineStr"/>
+      <c r="C189" t="inlineStr">
+        <is>
           <t>303442</t>
         </is>
       </c>
-      <c r="D166" t="inlineStr">
-        <is>
-          <t>Paid Ad</t>
-        </is>
-      </c>
-      <c r="E166" t="inlineStr">
+      <c r="D189" t="inlineStr">
+        <is>
+          <t>Paid Ad</t>
+        </is>
+      </c>
+      <c r="E189" t="inlineStr">
         <is>
           <t>naversa_mo</t>
         </is>
       </c>
-      <c r="F166" t="inlineStr">
-        <is>
-          <t>(not set)</t>
-        </is>
-      </c>
-      <c r="G166" t="inlineStr">
-        <is>
-          <t>(not set)</t>
+      <c r="F189" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="G189" t="inlineStr">
+        <is>
+          <t>Unknown</t>
         </is>
       </c>
     </row>

--- a/reports/member_funnel/downloads/member_funnel_7d_non_buyer.xlsx
+++ b/reports/member_funnel/downloads/member_funnel_7d_non_buyer.xlsx
@@ -487,16 +487,8 @@
           <t>(organic)</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
+      <c r="F2" t="inlineStr"/>
+      <c r="G2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -520,16 +512,8 @@
           <t>naver_brandsearch_mobile</t>
         </is>
       </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
+      <c r="F3" t="inlineStr"/>
+      <c r="G3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -553,16 +537,8 @@
           <t>sa</t>
         </is>
       </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
+      <c r="F4" t="inlineStr"/>
+      <c r="G4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -581,21 +557,9 @@
           <t>Direct</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>(not set)</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
+      <c r="E5" t="inlineStr"/>
+      <c r="F5" t="inlineStr"/>
+      <c r="G5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -619,16 +583,8 @@
           <t>(referral)</t>
         </is>
       </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
+      <c r="F6" t="inlineStr"/>
+      <c r="G6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -652,16 +608,8 @@
           <t>naver_brandsearch_mobile</t>
         </is>
       </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
+      <c r="F7" t="inlineStr"/>
+      <c r="G7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -685,16 +633,8 @@
           <t>[PF]A SC_상시(1865MF,구매 장바구니)</t>
         </is>
       </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
+      <c r="F8" t="inlineStr"/>
+      <c r="G8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -718,16 +658,8 @@
           <t>benz_running_program_2026_coupon</t>
         </is>
       </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
+      <c r="F9" t="inlineStr"/>
+      <c r="G9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -751,16 +683,8 @@
           <t>benz_running_program_2026_coupon</t>
         </is>
       </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
+      <c r="F10" t="inlineStr"/>
+      <c r="G10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -784,16 +708,8 @@
           <t>naversa_mo</t>
         </is>
       </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
+      <c r="F11" t="inlineStr"/>
+      <c r="G11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -812,21 +728,9 @@
           <t>Direct</t>
         </is>
       </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>(not set)</t>
-        </is>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
+      <c r="E12" t="inlineStr"/>
+      <c r="F12" t="inlineStr"/>
+      <c r="G12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -850,16 +754,8 @@
           <t>(organic)</t>
         </is>
       </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
+      <c r="F13" t="inlineStr"/>
+      <c r="G13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -883,16 +779,8 @@
           <t>(referral)</t>
         </is>
       </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
+      <c r="F14" t="inlineStr"/>
+      <c r="G14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -916,16 +804,8 @@
           <t>benz_running_program_2026_coupon</t>
         </is>
       </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
+      <c r="F15" t="inlineStr"/>
+      <c r="G15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -949,16 +829,8 @@
           <t>benz_running_program_2026_coupon</t>
         </is>
       </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
+      <c r="F16" t="inlineStr"/>
+      <c r="G16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -982,16 +854,8 @@
           <t>benz_running_program_2026​</t>
         </is>
       </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
+      <c r="F17" t="inlineStr"/>
+      <c r="G17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -1015,16 +879,8 @@
           <t>naver_brandsearch_mobile</t>
         </is>
       </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G18" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
+      <c r="F18" t="inlineStr"/>
+      <c r="G18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -1048,16 +904,8 @@
           <t>naver_brandsearch_mobile</t>
         </is>
       </c>
-      <c r="F19" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G19" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
+      <c r="F19" t="inlineStr"/>
+      <c r="G19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -1081,16 +929,8 @@
           <t>sa</t>
         </is>
       </c>
-      <c r="F20" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G20" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
+      <c r="F20" t="inlineStr"/>
+      <c r="G20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -1109,21 +949,9 @@
           <t>Direct</t>
         </is>
       </c>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="F21" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G21" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
+      <c r="E21" t="inlineStr"/>
+      <c r="F21" t="inlineStr"/>
+      <c r="G21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -1142,21 +970,9 @@
           <t>Direct</t>
         </is>
       </c>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="F22" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G22" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
+      <c r="E22" t="inlineStr"/>
+      <c r="F22" t="inlineStr"/>
+      <c r="G22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -1175,21 +991,9 @@
           <t>Direct</t>
         </is>
       </c>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="F23" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G23" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
+      <c r="E23" t="inlineStr"/>
+      <c r="F23" t="inlineStr"/>
+      <c r="G23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -1208,32 +1012,20 @@
           <t>Paid Ad</t>
         </is>
       </c>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="F24" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G24" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
+      <c r="E24" t="inlineStr"/>
+      <c r="F24" t="inlineStr"/>
+      <c r="G24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>kk_4831784738</t>
+          <t>hotsnoopy</t>
         </is>
       </c>
       <c r="B25" t="inlineStr"/>
       <c r="C25" t="inlineStr">
         <is>
-          <t>303607</t>
+          <t>303585</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -1241,32 +1033,20 @@
           <t>Direct</t>
         </is>
       </c>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="F25" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G25" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
+      <c r="E25" t="inlineStr"/>
+      <c r="F25" t="inlineStr"/>
+      <c r="G25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>hotsnoopy</t>
+          <t>kk_4829979824</t>
         </is>
       </c>
       <c r="B26" t="inlineStr"/>
       <c r="C26" t="inlineStr">
         <is>
-          <t>303585</t>
+          <t>303497</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -1274,32 +1054,20 @@
           <t>Direct</t>
         </is>
       </c>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="F26" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G26" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
+      <c r="E26" t="inlineStr"/>
+      <c r="F26" t="inlineStr"/>
+      <c r="G26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>thdud9181</t>
+          <t>kk_4831784738</t>
         </is>
       </c>
       <c r="B27" t="inlineStr"/>
       <c r="C27" t="inlineStr">
         <is>
-          <t>303644</t>
+          <t>303607</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -1307,32 +1075,20 @@
           <t>Direct</t>
         </is>
       </c>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="F27" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G27" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
+      <c r="E27" t="inlineStr"/>
+      <c r="F27" t="inlineStr"/>
+      <c r="G27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>kk_4832310183</t>
+          <t>thdud9181</t>
         </is>
       </c>
       <c r="B28" t="inlineStr"/>
       <c r="C28" t="inlineStr">
         <is>
-          <t>303663</t>
+          <t>303644</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -1340,32 +1096,20 @@
           <t>Direct</t>
         </is>
       </c>
-      <c r="E28" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="F28" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G28" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
+      <c r="E28" t="inlineStr"/>
+      <c r="F28" t="inlineStr"/>
+      <c r="G28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>kk_4829979824</t>
+          <t>kk_4829348219</t>
         </is>
       </c>
       <c r="B29" t="inlineStr"/>
       <c r="C29" t="inlineStr">
         <is>
-          <t>303497</t>
+          <t>303468</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -1373,32 +1117,20 @@
           <t>Direct</t>
         </is>
       </c>
-      <c r="E29" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="F29" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G29" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
+      <c r="E29" t="inlineStr"/>
+      <c r="F29" t="inlineStr"/>
+      <c r="G29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>kk_4829348219</t>
+          <t>kk_4831402433</t>
         </is>
       </c>
       <c r="B30" t="inlineStr"/>
       <c r="C30" t="inlineStr">
         <is>
-          <t>303468</t>
+          <t>303576</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -1406,32 +1138,20 @@
           <t>Direct</t>
         </is>
       </c>
-      <c r="E30" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="F30" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G30" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
+      <c r="E30" t="inlineStr"/>
+      <c r="F30" t="inlineStr"/>
+      <c r="G30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>kk_4831402433</t>
+          <t>kk_4832310183</t>
         </is>
       </c>
       <c r="B31" t="inlineStr"/>
       <c r="C31" t="inlineStr">
         <is>
-          <t>303576</t>
+          <t>303663</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -1439,21 +1159,9 @@
           <t>Direct</t>
         </is>
       </c>
-      <c r="E31" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="F31" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G31" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
+      <c r="E31" t="inlineStr"/>
+      <c r="F31" t="inlineStr"/>
+      <c r="G31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -1472,21 +1180,9 @@
           <t>Direct</t>
         </is>
       </c>
-      <c r="E32" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="F32" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G32" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
+      <c r="E32" t="inlineStr"/>
+      <c r="F32" t="inlineStr"/>
+      <c r="G32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -1510,16 +1206,8 @@
           <t>6968489536332</t>
         </is>
       </c>
-      <c r="F33" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G33" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
+      <c r="F33" t="inlineStr"/>
+      <c r="G33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -1543,16 +1231,8 @@
           <t>KAKAO_alimtalk</t>
         </is>
       </c>
-      <c r="F34" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G34" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
+      <c r="F34" t="inlineStr"/>
+      <c r="G34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -1576,16 +1256,8 @@
           <t>benz_running_program_2026_coupon</t>
         </is>
       </c>
-      <c r="F35" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G35" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
+      <c r="F35" t="inlineStr"/>
+      <c r="G35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -1609,16 +1281,8 @@
           <t>benz_running_program_2026_coupon</t>
         </is>
       </c>
-      <c r="F36" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G36" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
+      <c r="F36" t="inlineStr"/>
+      <c r="G36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -1642,16 +1306,8 @@
           <t>naver_brandsearch_mobile</t>
         </is>
       </c>
-      <c r="F37" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G37" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
+      <c r="F37" t="inlineStr"/>
+      <c r="G37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -1675,16 +1331,8 @@
           <t>6968489536332</t>
         </is>
       </c>
-      <c r="F38" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G38" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
+      <c r="F38" t="inlineStr"/>
+      <c r="G38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -1708,27 +1356,19 @@
           <t>EFW_04</t>
         </is>
       </c>
-      <c r="F39" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G39" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
+      <c r="F39" t="inlineStr"/>
+      <c r="G39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>kk_4829440714</t>
+          <t>kk_4831687251</t>
         </is>
       </c>
       <c r="B40" t="inlineStr"/>
       <c r="C40" t="inlineStr">
         <is>
-          <t>303471</t>
+          <t>303598</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -1741,27 +1381,19 @@
           <t>benz_running_program_2026_coupon</t>
         </is>
       </c>
-      <c r="F40" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G40" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
+      <c r="F40" t="inlineStr"/>
+      <c r="G40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>kk_4831687251</t>
+          <t>kk_4829440714</t>
         </is>
       </c>
       <c r="B41" t="inlineStr"/>
       <c r="C41" t="inlineStr">
         <is>
-          <t>303598</t>
+          <t>303471</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -1774,16 +1406,8 @@
           <t>benz_running_program_2026_coupon</t>
         </is>
       </c>
-      <c r="F41" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G41" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
+      <c r="F41" t="inlineStr"/>
+      <c r="G41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -1807,16 +1431,8 @@
           <t>naver_brandsearch_mobile</t>
         </is>
       </c>
-      <c r="F42" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G42" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
+      <c r="F42" t="inlineStr"/>
+      <c r="G42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -1840,16 +1456,8 @@
           <t>naver_brandsearch_pc</t>
         </is>
       </c>
-      <c r="F43" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G43" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
+      <c r="F43" t="inlineStr"/>
+      <c r="G43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -1873,16 +1481,8 @@
           <t>6968489536332</t>
         </is>
       </c>
-      <c r="F44" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G44" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
+      <c r="F44" t="inlineStr"/>
+      <c r="G44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -1906,16 +1506,8 @@
           <t>[PF]전환_회원가입(유사)</t>
         </is>
       </c>
-      <c r="F45" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G45" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
+      <c r="F45" t="inlineStr"/>
+      <c r="G45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
@@ -1939,16 +1531,8 @@
           <t>[PF]트래픽_유사+관심사</t>
         </is>
       </c>
-      <c r="F46" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G46" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
+      <c r="F46" t="inlineStr"/>
+      <c r="G46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
@@ -1972,16 +1556,8 @@
           <t>benz_running_program_2026_coupon</t>
         </is>
       </c>
-      <c r="F47" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G47" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
+      <c r="F47" t="inlineStr"/>
+      <c r="G47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
@@ -2005,32 +1581,24 @@
           <t>benz_running_program_2026_coupon</t>
         </is>
       </c>
-      <c r="F48" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G48" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
+      <c r="F48" t="inlineStr"/>
+      <c r="G48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>kk_4831422357</t>
+          <t>kk_4832205664</t>
         </is>
       </c>
       <c r="B49" t="inlineStr"/>
       <c r="C49" t="inlineStr">
         <is>
-          <t>303577</t>
+          <t>303654</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>Official SNS</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
@@ -2038,32 +1606,24 @@
           <t>benz_running_program_2026_coupon</t>
         </is>
       </c>
-      <c r="F49" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G49" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
+      <c r="F49" t="inlineStr"/>
+      <c r="G49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>kk_4832205664</t>
+          <t>kk_4830251299</t>
         </is>
       </c>
       <c r="B50" t="inlineStr"/>
       <c r="C50" t="inlineStr">
         <is>
-          <t>303654</t>
+          <t>303511</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Awareness</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
@@ -2071,32 +1631,24 @@
           <t>benz_running_program_2026_coupon</t>
         </is>
       </c>
-      <c r="F50" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G50" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
+      <c r="F50" t="inlineStr"/>
+      <c r="G50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>kk_4830251299</t>
+          <t>kk_4831422357</t>
         </is>
       </c>
       <c r="B51" t="inlineStr"/>
       <c r="C51" t="inlineStr">
         <is>
-          <t>303511</t>
+          <t>303577</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>Awareness</t>
+          <t>Official SNS</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
@@ -2104,16 +1656,8 @@
           <t>benz_running_program_2026_coupon</t>
         </is>
       </c>
-      <c r="F51" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G51" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
+      <c r="F51" t="inlineStr"/>
+      <c r="G51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
@@ -2137,16 +1681,8 @@
           <t>naver_brandsearch_mobile</t>
         </is>
       </c>
-      <c r="F52" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G52" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
+      <c r="F52" t="inlineStr"/>
+      <c r="G52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
@@ -2170,27 +1706,19 @@
           <t>naver_brandsearch_mobile</t>
         </is>
       </c>
-      <c r="F53" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G53" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
+      <c r="F53" t="inlineStr"/>
+      <c r="G53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>kk_4832180009</t>
+          <t>kk_4832076715</t>
         </is>
       </c>
       <c r="B54" t="inlineStr"/>
       <c r="C54" t="inlineStr">
         <is>
-          <t>303647</t>
+          <t>303629</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -2198,21 +1726,9 @@
           <t>Direct</t>
         </is>
       </c>
-      <c r="E54" t="inlineStr">
-        <is>
-          <t>(not set)</t>
-        </is>
-      </c>
-      <c r="F54" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G54" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
+      <c r="E54" t="inlineStr"/>
+      <c r="F54" t="inlineStr"/>
+      <c r="G54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
@@ -2231,32 +1747,20 @@
           <t>Direct</t>
         </is>
       </c>
-      <c r="E55" t="inlineStr">
-        <is>
-          <t>(not set)</t>
-        </is>
-      </c>
-      <c r="F55" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G55" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
+      <c r="E55" t="inlineStr"/>
+      <c r="F55" t="inlineStr"/>
+      <c r="G55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>kk_4831394790</t>
+          <t>kk_4830821550</t>
         </is>
       </c>
       <c r="B56" t="inlineStr"/>
       <c r="C56" t="inlineStr">
         <is>
-          <t>303575</t>
+          <t>303559</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -2264,32 +1768,20 @@
           <t>Direct</t>
         </is>
       </c>
-      <c r="E56" t="inlineStr">
-        <is>
-          <t>(not set)</t>
-        </is>
-      </c>
-      <c r="F56" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G56" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
+      <c r="E56" t="inlineStr"/>
+      <c r="F56" t="inlineStr"/>
+      <c r="G56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>kk_4832201164</t>
+          <t>kk_4832180009</t>
         </is>
       </c>
       <c r="B57" t="inlineStr"/>
       <c r="C57" t="inlineStr">
         <is>
-          <t>303651</t>
+          <t>303647</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -2297,21 +1789,9 @@
           <t>Direct</t>
         </is>
       </c>
-      <c r="E57" t="inlineStr">
-        <is>
-          <t>(not set)</t>
-        </is>
-      </c>
-      <c r="F57" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G57" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
+      <c r="E57" t="inlineStr"/>
+      <c r="F57" t="inlineStr"/>
+      <c r="G57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
@@ -2330,32 +1810,20 @@
           <t>Direct</t>
         </is>
       </c>
-      <c r="E58" t="inlineStr">
-        <is>
-          <t>(not set)</t>
-        </is>
-      </c>
-      <c r="F58" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G58" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
+      <c r="E58" t="inlineStr"/>
+      <c r="F58" t="inlineStr"/>
+      <c r="G58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>kk_4832248726</t>
+          <t>kk_4831394790</t>
         </is>
       </c>
       <c r="B59" t="inlineStr"/>
       <c r="C59" t="inlineStr">
         <is>
-          <t>303658</t>
+          <t>303575</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -2363,32 +1831,20 @@
           <t>Direct</t>
         </is>
       </c>
-      <c r="E59" t="inlineStr">
-        <is>
-          <t>(not set)</t>
-        </is>
-      </c>
-      <c r="F59" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G59" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
+      <c r="E59" t="inlineStr"/>
+      <c r="F59" t="inlineStr"/>
+      <c r="G59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>kk_4830821550</t>
+          <t>kk_4832201164</t>
         </is>
       </c>
       <c r="B60" t="inlineStr"/>
       <c r="C60" t="inlineStr">
         <is>
-          <t>303559</t>
+          <t>303651</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -2396,32 +1852,20 @@
           <t>Direct</t>
         </is>
       </c>
-      <c r="E60" t="inlineStr">
-        <is>
-          <t>(not set)</t>
-        </is>
-      </c>
-      <c r="F60" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G60" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
+      <c r="E60" t="inlineStr"/>
+      <c r="F60" t="inlineStr"/>
+      <c r="G60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>kk_4832076715</t>
+          <t>kk_4830767555</t>
         </is>
       </c>
       <c r="B61" t="inlineStr"/>
       <c r="C61" t="inlineStr">
         <is>
-          <t>303629</t>
+          <t>303555</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -2429,32 +1873,20 @@
           <t>Direct</t>
         </is>
       </c>
-      <c r="E61" t="inlineStr">
-        <is>
-          <t>(not set)</t>
-        </is>
-      </c>
-      <c r="F61" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G61" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
+      <c r="E61" t="inlineStr"/>
+      <c r="F61" t="inlineStr"/>
+      <c r="G61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>kk_4830767555</t>
+          <t>kk_4832248726</t>
         </is>
       </c>
       <c r="B62" t="inlineStr"/>
       <c r="C62" t="inlineStr">
         <is>
-          <t>303555</t>
+          <t>303658</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -2462,21 +1894,9 @@
           <t>Direct</t>
         </is>
       </c>
-      <c r="E62" t="inlineStr">
-        <is>
-          <t>(not set)</t>
-        </is>
-      </c>
-      <c r="F62" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G62" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
+      <c r="E62" t="inlineStr"/>
+      <c r="F62" t="inlineStr"/>
+      <c r="G62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
@@ -2495,37 +1915,25 @@
           <t>Direct</t>
         </is>
       </c>
-      <c r="E63" t="inlineStr">
-        <is>
-          <t>(not set)</t>
-        </is>
-      </c>
-      <c r="F63" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G63" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
+      <c r="E63" t="inlineStr"/>
+      <c r="F63" t="inlineStr"/>
+      <c r="G63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>kk_4832164589</t>
+          <t>kk_4831495694</t>
         </is>
       </c>
       <c r="B64" t="inlineStr"/>
       <c r="C64" t="inlineStr">
         <is>
-          <t>303645</t>
+          <t>303581</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Organic Traffic</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
@@ -2533,32 +1941,24 @@
           <t>(organic)</t>
         </is>
       </c>
-      <c r="F64" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G64" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
+      <c r="F64" t="inlineStr"/>
+      <c r="G64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>kk_4831495694</t>
+          <t>kk_4832164589</t>
         </is>
       </c>
       <c r="B65" t="inlineStr"/>
       <c r="C65" t="inlineStr">
         <is>
-          <t>303581</t>
+          <t>303645</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>Organic Traffic</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
@@ -2566,27 +1966,19 @@
           <t>(organic)</t>
         </is>
       </c>
-      <c r="F65" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G65" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
+      <c r="F65" t="inlineStr"/>
+      <c r="G65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>kk_4832078505</t>
+          <t>kk_4832100095</t>
         </is>
       </c>
       <c r="B66" t="inlineStr"/>
       <c r="C66" t="inlineStr">
         <is>
-          <t>303630</t>
+          <t>303634</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -2599,27 +1991,19 @@
           <t>(referral)</t>
         </is>
       </c>
-      <c r="F66" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G66" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
+      <c r="F66" t="inlineStr"/>
+      <c r="G66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>kk_4831649243</t>
+          <t>kk_4832078505</t>
         </is>
       </c>
       <c r="B67" t="inlineStr"/>
       <c r="C67" t="inlineStr">
         <is>
-          <t>303595</t>
+          <t>303630</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -2632,27 +2016,19 @@
           <t>(referral)</t>
         </is>
       </c>
-      <c r="F67" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G67" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
+      <c r="F67" t="inlineStr"/>
+      <c r="G67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>kk_4832100095</t>
+          <t>kk_4831649243</t>
         </is>
       </c>
       <c r="B68" t="inlineStr"/>
       <c r="C68" t="inlineStr">
         <is>
-          <t>303634</t>
+          <t>303595</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -2665,16 +2041,8 @@
           <t>(referral)</t>
         </is>
       </c>
-      <c r="F68" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G68" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
+      <c r="F68" t="inlineStr"/>
+      <c r="G68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
@@ -2698,16 +2066,8 @@
           <t>(referral)</t>
         </is>
       </c>
-      <c r="F69" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G69" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
+      <c r="F69" t="inlineStr"/>
+      <c r="G69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
@@ -2731,16 +2091,8 @@
           <t>(referral)</t>
         </is>
       </c>
-      <c r="F70" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G70" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
+      <c r="F70" t="inlineStr"/>
+      <c r="G70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
@@ -2764,27 +2116,19 @@
           <t>(referral)</t>
         </is>
       </c>
-      <c r="F71" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G71" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
+      <c r="F71" t="inlineStr"/>
+      <c r="G71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>saty31</t>
+          <t>kk_4831830576</t>
         </is>
       </c>
       <c r="B72" t="inlineStr"/>
       <c r="C72" t="inlineStr">
         <is>
-          <t>303561</t>
+          <t>303611</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -2797,27 +2141,19 @@
           <t>6968489536332</t>
         </is>
       </c>
-      <c r="F72" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G72" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
+      <c r="F72" t="inlineStr"/>
+      <c r="G72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>kk_4830989652</t>
+          <t>jgj0503</t>
         </is>
       </c>
       <c r="B73" t="inlineStr"/>
       <c r="C73" t="inlineStr">
         <is>
-          <t>303569</t>
+          <t>303605</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -2830,27 +2166,19 @@
           <t>6968489536332</t>
         </is>
       </c>
-      <c r="F73" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G73" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
+      <c r="F73" t="inlineStr"/>
+      <c r="G73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>kk_4831830576</t>
+          <t>kk_4832202047</t>
         </is>
       </c>
       <c r="B74" t="inlineStr"/>
       <c r="C74" t="inlineStr">
         <is>
-          <t>303611</t>
+          <t>303652</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
@@ -2863,16 +2191,8 @@
           <t>6968489536332</t>
         </is>
       </c>
-      <c r="F74" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G74" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
+      <c r="F74" t="inlineStr"/>
+      <c r="G74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
@@ -2896,27 +2216,19 @@
           <t>6968489536332</t>
         </is>
       </c>
-      <c r="F75" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G75" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
+      <c r="F75" t="inlineStr"/>
+      <c r="G75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>kk_4832202047</t>
+          <t>kk_4830989652</t>
         </is>
       </c>
       <c r="B76" t="inlineStr"/>
       <c r="C76" t="inlineStr">
         <is>
-          <t>303652</t>
+          <t>303569</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
@@ -2929,27 +2241,19 @@
           <t>6968489536332</t>
         </is>
       </c>
-      <c r="F76" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G76" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
+      <c r="F76" t="inlineStr"/>
+      <c r="G76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>jgj0503</t>
+          <t>saty31</t>
         </is>
       </c>
       <c r="B77" t="inlineStr"/>
       <c r="C77" t="inlineStr">
         <is>
-          <t>303605</t>
+          <t>303561</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -2962,16 +2266,8 @@
           <t>6968489536332</t>
         </is>
       </c>
-      <c r="F77" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G77" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
+      <c r="F77" t="inlineStr"/>
+      <c r="G77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
@@ -2995,27 +2291,19 @@
           <t>EFW</t>
         </is>
       </c>
-      <c r="F78" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G78" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
+      <c r="F78" t="inlineStr"/>
+      <c r="G78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>kk_4832125929</t>
+          <t>kk_4831850638</t>
         </is>
       </c>
       <c r="B79" t="inlineStr"/>
       <c r="C79" t="inlineStr">
         <is>
-          <t>303638</t>
+          <t>303615</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
@@ -3028,27 +2316,19 @@
           <t>EFW_04</t>
         </is>
       </c>
-      <c r="F79" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G79" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
+      <c r="F79" t="inlineStr"/>
+      <c r="G79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>kk_4831922723</t>
+          <t>kk_4830778741</t>
         </is>
       </c>
       <c r="B80" t="inlineStr"/>
       <c r="C80" t="inlineStr">
         <is>
-          <t>303617</t>
+          <t>303556</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
@@ -3061,27 +2341,19 @@
           <t>EFW_04</t>
         </is>
       </c>
-      <c r="F80" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G80" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
+      <c r="F80" t="inlineStr"/>
+      <c r="G80" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>kk_4830778741</t>
+          <t>kk_4831922723</t>
         </is>
       </c>
       <c r="B81" t="inlineStr"/>
       <c r="C81" t="inlineStr">
         <is>
-          <t>303556</t>
+          <t>303617</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
@@ -3094,16 +2366,8 @@
           <t>EFW_04</t>
         </is>
       </c>
-      <c r="F81" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G81" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
+      <c r="F81" t="inlineStr"/>
+      <c r="G81" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
@@ -3127,27 +2391,19 @@
           <t>EFW_04</t>
         </is>
       </c>
-      <c r="F82" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G82" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
+      <c r="F82" t="inlineStr"/>
+      <c r="G82" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>kk_4831850638</t>
+          <t>kk_4830836853</t>
         </is>
       </c>
       <c r="B83" t="inlineStr"/>
       <c r="C83" t="inlineStr">
         <is>
-          <t>303615</t>
+          <t>303560</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
@@ -3160,27 +2416,19 @@
           <t>EFW_04</t>
         </is>
       </c>
-      <c r="F83" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G83" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
+      <c r="F83" t="inlineStr"/>
+      <c r="G83" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>kk_4830836853</t>
+          <t>kk_4832125929</t>
         </is>
       </c>
       <c r="B84" t="inlineStr"/>
       <c r="C84" t="inlineStr">
         <is>
-          <t>303560</t>
+          <t>303638</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
@@ -3193,16 +2441,8 @@
           <t>EFW_04</t>
         </is>
       </c>
-      <c r="F84" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G84" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
+      <c r="F84" t="inlineStr"/>
+      <c r="G84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
@@ -3226,16 +2466,8 @@
           <t>KAKAO_alimtalk</t>
         </is>
       </c>
-      <c r="F85" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G85" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
+      <c r="F85" t="inlineStr"/>
+      <c r="G85" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
@@ -3259,16 +2491,8 @@
           <t>[PF]A SC_상시(1865MF,구매 장바구니)</t>
         </is>
       </c>
-      <c r="F86" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G86" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
+      <c r="F86" t="inlineStr"/>
+      <c r="G86" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
@@ -3292,27 +2516,19 @@
           <t>[PF]전환_상시(2565MF,비구매자)</t>
         </is>
       </c>
-      <c r="F87" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G87" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
+      <c r="F87" t="inlineStr"/>
+      <c r="G87" t="inlineStr"/>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>kk_4830963661</t>
+          <t>kk_4830923952</t>
         </is>
       </c>
       <c r="B88" t="inlineStr"/>
       <c r="C88" t="inlineStr">
         <is>
-          <t>303566</t>
+          <t>303564</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
@@ -3325,27 +2541,19 @@
           <t>[PF]전환_회원가입(유사)</t>
         </is>
       </c>
-      <c r="F88" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G88" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
+      <c r="F88" t="inlineStr"/>
+      <c r="G88" t="inlineStr"/>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>kk_4830923952</t>
+          <t>kk_4830963661</t>
         </is>
       </c>
       <c r="B89" t="inlineStr"/>
       <c r="C89" t="inlineStr">
         <is>
-          <t>303564</t>
+          <t>303566</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
@@ -3358,27 +2566,19 @@
           <t>[PF]전환_회원가입(유사)</t>
         </is>
       </c>
-      <c r="F89" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G89" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
+      <c r="F89" t="inlineStr"/>
+      <c r="G89" t="inlineStr"/>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>kk_4831997957</t>
+          <t>kk_4831799020</t>
         </is>
       </c>
       <c r="B90" t="inlineStr"/>
       <c r="C90" t="inlineStr">
         <is>
-          <t>303624</t>
+          <t>303609</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
@@ -3391,27 +2591,19 @@
           <t>benz_running_program_2026_coupon</t>
         </is>
       </c>
-      <c r="F90" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G90" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
+      <c r="F90" t="inlineStr"/>
+      <c r="G90" t="inlineStr"/>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>kk_4831983348</t>
+          <t>kk_4831981914</t>
         </is>
       </c>
       <c r="B91" t="inlineStr"/>
       <c r="C91" t="inlineStr">
         <is>
-          <t>303621</t>
+          <t>303620</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
@@ -3424,27 +2616,19 @@
           <t>benz_running_program_2026_coupon</t>
         </is>
       </c>
-      <c r="F91" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G91" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
+      <c r="F91" t="inlineStr"/>
+      <c r="G91" t="inlineStr"/>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>kk_4831257396</t>
+          <t>kk_4831502482</t>
         </is>
       </c>
       <c r="B92" t="inlineStr"/>
       <c r="C92" t="inlineStr">
         <is>
-          <t>303571</t>
+          <t>303583</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
@@ -3457,16 +2641,8 @@
           <t>benz_running_program_2026_coupon</t>
         </is>
       </c>
-      <c r="F92" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G92" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
+      <c r="F92" t="inlineStr"/>
+      <c r="G92" t="inlineStr"/>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
@@ -3490,27 +2666,19 @@
           <t>benz_running_program_2026_coupon</t>
         </is>
       </c>
-      <c r="F93" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G93" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
+      <c r="F93" t="inlineStr"/>
+      <c r="G93" t="inlineStr"/>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>kk_4831799020</t>
+          <t>kk_4831997957</t>
         </is>
       </c>
       <c r="B94" t="inlineStr"/>
       <c r="C94" t="inlineStr">
         <is>
-          <t>303609</t>
+          <t>303624</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
@@ -3523,27 +2691,19 @@
           <t>benz_running_program_2026_coupon</t>
         </is>
       </c>
-      <c r="F94" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G94" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
+      <c r="F94" t="inlineStr"/>
+      <c r="G94" t="inlineStr"/>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>kk_4831532519</t>
+          <t>kk_4831983348</t>
         </is>
       </c>
       <c r="B95" t="inlineStr"/>
       <c r="C95" t="inlineStr">
         <is>
-          <t>303587</t>
+          <t>303621</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
@@ -3556,27 +2716,19 @@
           <t>benz_running_program_2026_coupon</t>
         </is>
       </c>
-      <c r="F95" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G95" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
+      <c r="F95" t="inlineStr"/>
+      <c r="G95" t="inlineStr"/>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>kk_4831981914</t>
+          <t>kk_4831986570</t>
         </is>
       </c>
       <c r="B96" t="inlineStr"/>
       <c r="C96" t="inlineStr">
         <is>
-          <t>303620</t>
+          <t>303622</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
@@ -3589,27 +2741,19 @@
           <t>benz_running_program_2026_coupon</t>
         </is>
       </c>
-      <c r="F96" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G96" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
+      <c r="F96" t="inlineStr"/>
+      <c r="G96" t="inlineStr"/>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>kk_4832190692</t>
+          <t>kk_4831532519</t>
         </is>
       </c>
       <c r="B97" t="inlineStr"/>
       <c r="C97" t="inlineStr">
         <is>
-          <t>303649</t>
+          <t>303587</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
@@ -3622,27 +2766,19 @@
           <t>benz_running_program_2026_coupon</t>
         </is>
       </c>
-      <c r="F97" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G97" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
+      <c r="F97" t="inlineStr"/>
+      <c r="G97" t="inlineStr"/>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>kk_4831986570</t>
+          <t>kk_4832001343</t>
         </is>
       </c>
       <c r="B98" t="inlineStr"/>
       <c r="C98" t="inlineStr">
         <is>
-          <t>303622</t>
+          <t>303625</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
@@ -3655,27 +2791,19 @@
           <t>benz_running_program_2026_coupon</t>
         </is>
       </c>
-      <c r="F98" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G98" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
+      <c r="F98" t="inlineStr"/>
+      <c r="G98" t="inlineStr"/>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>kk_4831468314</t>
+          <t>kk_4832061430</t>
         </is>
       </c>
       <c r="B99" t="inlineStr"/>
       <c r="C99" t="inlineStr">
         <is>
-          <t>303578</t>
+          <t>303628</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
@@ -3688,27 +2816,19 @@
           <t>benz_running_program_2026_coupon</t>
         </is>
       </c>
-      <c r="F99" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G99" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
+      <c r="F99" t="inlineStr"/>
+      <c r="G99" t="inlineStr"/>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>kk_4832001343</t>
+          <t>kk_4832190692</t>
         </is>
       </c>
       <c r="B100" t="inlineStr"/>
       <c r="C100" t="inlineStr">
         <is>
-          <t>303625</t>
+          <t>303649</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
@@ -3721,27 +2841,19 @@
           <t>benz_running_program_2026_coupon</t>
         </is>
       </c>
-      <c r="F100" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G100" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
+      <c r="F100" t="inlineStr"/>
+      <c r="G100" t="inlineStr"/>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>kk_4832061430</t>
+          <t>kk_4831257396</t>
         </is>
       </c>
       <c r="B101" t="inlineStr"/>
       <c r="C101" t="inlineStr">
         <is>
-          <t>303628</t>
+          <t>303571</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
@@ -3754,27 +2866,19 @@
           <t>benz_running_program_2026_coupon</t>
         </is>
       </c>
-      <c r="F101" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G101" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
+      <c r="F101" t="inlineStr"/>
+      <c r="G101" t="inlineStr"/>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>kk_4831502482</t>
+          <t>kk_4831468314</t>
         </is>
       </c>
       <c r="B102" t="inlineStr"/>
       <c r="C102" t="inlineStr">
         <is>
-          <t>303583</t>
+          <t>303578</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
@@ -3787,27 +2891,19 @@
           <t>benz_running_program_2026_coupon</t>
         </is>
       </c>
-      <c r="F102" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G102" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
+      <c r="F102" t="inlineStr"/>
+      <c r="G102" t="inlineStr"/>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>kk_4831517271</t>
+          <t>kk_4831951614</t>
         </is>
       </c>
       <c r="B103" t="inlineStr"/>
       <c r="C103" t="inlineStr">
         <is>
-          <t>303584</t>
+          <t>303618</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
@@ -3820,27 +2916,19 @@
           <t>naver_brandsearch_mobile</t>
         </is>
       </c>
-      <c r="F103" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G103" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
+      <c r="F103" t="inlineStr"/>
+      <c r="G103" t="inlineStr"/>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>kk_4831951614</t>
+          <t>kk_4832186210</t>
         </is>
       </c>
       <c r="B104" t="inlineStr"/>
       <c r="C104" t="inlineStr">
         <is>
-          <t>303618</t>
+          <t>303648</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
@@ -3853,27 +2941,19 @@
           <t>naver_brandsearch_mobile</t>
         </is>
       </c>
-      <c r="F104" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G104" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
+      <c r="F104" t="inlineStr"/>
+      <c r="G104" t="inlineStr"/>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>kk_4832186210</t>
+          <t>kk_4831774426</t>
         </is>
       </c>
       <c r="B105" t="inlineStr"/>
       <c r="C105" t="inlineStr">
         <is>
-          <t>303648</t>
+          <t>303604</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
@@ -3886,27 +2966,19 @@
           <t>naver_brandsearch_mobile</t>
         </is>
       </c>
-      <c r="F105" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G105" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
+      <c r="F105" t="inlineStr"/>
+      <c r="G105" t="inlineStr"/>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>kk_4831774426</t>
+          <t>kk_4831585022</t>
         </is>
       </c>
       <c r="B106" t="inlineStr"/>
       <c r="C106" t="inlineStr">
         <is>
-          <t>303604</t>
+          <t>303591</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
@@ -3919,16 +2991,8 @@
           <t>naver_brandsearch_mobile</t>
         </is>
       </c>
-      <c r="F106" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G106" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
+      <c r="F106" t="inlineStr"/>
+      <c r="G106" t="inlineStr"/>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
@@ -3952,27 +3016,19 @@
           <t>naver_brandsearch_mobile</t>
         </is>
       </c>
-      <c r="F107" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G107" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
+      <c r="F107" t="inlineStr"/>
+      <c r="G107" t="inlineStr"/>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>kk_4831585022</t>
+          <t>kk_4831517271</t>
         </is>
       </c>
       <c r="B108" t="inlineStr"/>
       <c r="C108" t="inlineStr">
         <is>
-          <t>303591</t>
+          <t>303584</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
@@ -3985,16 +3041,8 @@
           <t>naver_brandsearch_mobile</t>
         </is>
       </c>
-      <c r="F108" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G108" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
+      <c r="F108" t="inlineStr"/>
+      <c r="G108" t="inlineStr"/>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
@@ -4018,27 +3066,19 @@
           <t>naver_brandsearch_mobile</t>
         </is>
       </c>
-      <c r="F109" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G109" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
+      <c r="F109" t="inlineStr"/>
+      <c r="G109" t="inlineStr"/>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>minpark98</t>
+          <t>kk_4831488942</t>
         </is>
       </c>
       <c r="B110" t="inlineStr"/>
       <c r="C110" t="inlineStr">
         <is>
-          <t>303657</t>
+          <t>303580</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
@@ -4051,27 +3091,19 @@
           <t>naver_brandsearch_pc</t>
         </is>
       </c>
-      <c r="F110" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G110" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
+      <c r="F110" t="inlineStr"/>
+      <c r="G110" t="inlineStr"/>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>kk_4831488942</t>
+          <t>minpark98</t>
         </is>
       </c>
       <c r="B111" t="inlineStr"/>
       <c r="C111" t="inlineStr">
         <is>
-          <t>303580</t>
+          <t>303657</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
@@ -4084,27 +3116,19 @@
           <t>naver_brandsearch_pc</t>
         </is>
       </c>
-      <c r="F111" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G111" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
+      <c r="F111" t="inlineStr"/>
+      <c r="G111" t="inlineStr"/>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>kk_4831615271</t>
+          <t>kk_4831600231</t>
         </is>
       </c>
       <c r="B112" t="inlineStr"/>
       <c r="C112" t="inlineStr">
         <is>
-          <t>303594</t>
+          <t>303592</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
@@ -4117,27 +3141,19 @@
           <t>sa</t>
         </is>
       </c>
-      <c r="F112" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G112" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
+      <c r="F112" t="inlineStr"/>
+      <c r="G112" t="inlineStr"/>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>kk_4831600231</t>
+          <t>kk_4831615271</t>
         </is>
       </c>
       <c r="B113" t="inlineStr"/>
       <c r="C113" t="inlineStr">
         <is>
-          <t>303592</t>
+          <t>303594</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
@@ -4150,16 +3166,8 @@
           <t>sa</t>
         </is>
       </c>
-      <c r="F113" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G113" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
+      <c r="F113" t="inlineStr"/>
+      <c r="G113" t="inlineStr"/>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
@@ -4183,16 +3191,8 @@
           <t>(organic)</t>
         </is>
       </c>
-      <c r="F114" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G114" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
+      <c r="F114" t="inlineStr"/>
+      <c r="G114" t="inlineStr"/>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
@@ -4211,21 +3211,9 @@
           <t>Direct</t>
         </is>
       </c>
-      <c r="E115" t="inlineStr">
-        <is>
-          <t>(not set)</t>
-        </is>
-      </c>
-      <c r="F115" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G115" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
+      <c r="E115" t="inlineStr"/>
+      <c r="F115" t="inlineStr"/>
+      <c r="G115" t="inlineStr"/>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
@@ -4249,16 +3237,8 @@
           <t>컬럼비아_DPA_240530</t>
         </is>
       </c>
-      <c r="F116" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G116" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
+      <c r="F116" t="inlineStr"/>
+      <c r="G116" t="inlineStr"/>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
@@ -4277,21 +3257,9 @@
           <t>Owned Channel</t>
         </is>
       </c>
-      <c r="E117" t="inlineStr">
-        <is>
-          <t>(not set)</t>
-        </is>
-      </c>
-      <c r="F117" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G117" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
+      <c r="E117" t="inlineStr"/>
+      <c r="F117" t="inlineStr"/>
+      <c r="G117" t="inlineStr"/>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
@@ -4315,27 +3283,19 @@
           <t>da</t>
         </is>
       </c>
-      <c r="F118" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G118" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
+      <c r="F118" t="inlineStr"/>
+      <c r="G118" t="inlineStr"/>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>kk_4830147171</t>
+          <t>kk_4830615705</t>
         </is>
       </c>
       <c r="B119" t="inlineStr"/>
       <c r="C119" t="inlineStr">
         <is>
-          <t>303506</t>
+          <t>303543</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
@@ -4343,32 +3303,20 @@
           <t>Direct</t>
         </is>
       </c>
-      <c r="E119" t="inlineStr">
-        <is>
-          <t>(not set)</t>
-        </is>
-      </c>
-      <c r="F119" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G119" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
+      <c r="E119" t="inlineStr"/>
+      <c r="F119" t="inlineStr"/>
+      <c r="G119" t="inlineStr"/>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>kk_4830615705</t>
+          <t>kk_4830147171</t>
         </is>
       </c>
       <c r="B120" t="inlineStr"/>
       <c r="C120" t="inlineStr">
         <is>
-          <t>303543</t>
+          <t>303506</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
@@ -4376,21 +3324,9 @@
           <t>Direct</t>
         </is>
       </c>
-      <c r="E120" t="inlineStr">
-        <is>
-          <t>(not set)</t>
-        </is>
-      </c>
-      <c r="F120" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G120" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
+      <c r="E120" t="inlineStr"/>
+      <c r="F120" t="inlineStr"/>
+      <c r="G120" t="inlineStr"/>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
@@ -4414,16 +3350,8 @@
           <t>6968489536332</t>
         </is>
       </c>
-      <c r="F121" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G121" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
+      <c r="F121" t="inlineStr"/>
+      <c r="G121" t="inlineStr"/>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
@@ -4447,27 +3375,19 @@
           <t>EFW</t>
         </is>
       </c>
-      <c r="F122" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G122" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
+      <c r="F122" t="inlineStr"/>
+      <c r="G122" t="inlineStr"/>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>kk_4830552074</t>
+          <t>kk_4830585310</t>
         </is>
       </c>
       <c r="B123" t="inlineStr"/>
       <c r="C123" t="inlineStr">
         <is>
-          <t>303534</t>
+          <t>303538</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
@@ -4480,27 +3400,19 @@
           <t>benz_running_program_2026_coupon</t>
         </is>
       </c>
-      <c r="F123" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G123" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
+      <c r="F123" t="inlineStr"/>
+      <c r="G123" t="inlineStr"/>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>kk_4830585310</t>
+          <t>kk_4830552074</t>
         </is>
       </c>
       <c r="B124" t="inlineStr"/>
       <c r="C124" t="inlineStr">
         <is>
-          <t>303538</t>
+          <t>303534</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
@@ -4513,16 +3425,8 @@
           <t>benz_running_program_2026_coupon</t>
         </is>
       </c>
-      <c r="F124" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G124" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
+      <c r="F124" t="inlineStr"/>
+      <c r="G124" t="inlineStr"/>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
@@ -4546,16 +3450,8 @@
           <t>naver_brandsearch_mobile</t>
         </is>
       </c>
-      <c r="F125" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G125" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
+      <c r="F125" t="inlineStr"/>
+      <c r="G125" t="inlineStr"/>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
@@ -4579,16 +3475,8 @@
           <t>컬럼비아_DPA_240530</t>
         </is>
       </c>
-      <c r="F126" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G126" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
+      <c r="F126" t="inlineStr"/>
+      <c r="G126" t="inlineStr"/>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
@@ -4607,32 +3495,20 @@
           <t>Direct</t>
         </is>
       </c>
-      <c r="E127" t="inlineStr">
-        <is>
-          <t>(not set)</t>
-        </is>
-      </c>
-      <c r="F127" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G127" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
+      <c r="E127" t="inlineStr"/>
+      <c r="F127" t="inlineStr"/>
+      <c r="G127" t="inlineStr"/>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>kk_4829899341</t>
+          <t>kk_4830596422</t>
         </is>
       </c>
       <c r="B128" t="inlineStr"/>
       <c r="C128" t="inlineStr">
         <is>
-          <t>303495</t>
+          <t>303540</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
@@ -4640,32 +3516,20 @@
           <t>Direct</t>
         </is>
       </c>
-      <c r="E128" t="inlineStr">
-        <is>
-          <t>(not set)</t>
-        </is>
-      </c>
-      <c r="F128" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G128" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
+      <c r="E128" t="inlineStr"/>
+      <c r="F128" t="inlineStr"/>
+      <c r="G128" t="inlineStr"/>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>kk_4830596422</t>
+          <t>kk_4829899341</t>
         </is>
       </c>
       <c r="B129" t="inlineStr"/>
       <c r="C129" t="inlineStr">
         <is>
-          <t>303540</t>
+          <t>303495</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
@@ -4673,21 +3537,9 @@
           <t>Direct</t>
         </is>
       </c>
-      <c r="E129" t="inlineStr">
-        <is>
-          <t>(not set)</t>
-        </is>
-      </c>
-      <c r="F129" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G129" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
+      <c r="E129" t="inlineStr"/>
+      <c r="F129" t="inlineStr"/>
+      <c r="G129" t="inlineStr"/>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
@@ -4706,21 +3558,9 @@
           <t>Direct</t>
         </is>
       </c>
-      <c r="E130" t="inlineStr">
-        <is>
-          <t>(not set)</t>
-        </is>
-      </c>
-      <c r="F130" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G130" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
+      <c r="E130" t="inlineStr"/>
+      <c r="F130" t="inlineStr"/>
+      <c r="G130" t="inlineStr"/>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
@@ -4744,16 +3584,8 @@
           <t>(organic)</t>
         </is>
       </c>
-      <c r="F131" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G131" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
+      <c r="F131" t="inlineStr"/>
+      <c r="G131" t="inlineStr"/>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
@@ -4777,27 +3609,19 @@
           <t>(organic)</t>
         </is>
       </c>
-      <c r="F132" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G132" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
+      <c r="F132" t="inlineStr"/>
+      <c r="G132" t="inlineStr"/>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>kk_4829755741</t>
+          <t>onoff</t>
         </is>
       </c>
       <c r="B133" t="inlineStr"/>
       <c r="C133" t="inlineStr">
         <is>
-          <t>303486</t>
+          <t>303518</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
@@ -4810,16 +3634,8 @@
           <t>(referral)</t>
         </is>
       </c>
-      <c r="F133" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G133" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
+      <c r="F133" t="inlineStr"/>
+      <c r="G133" t="inlineStr"/>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
@@ -4843,27 +3659,19 @@
           <t>(referral)</t>
         </is>
       </c>
-      <c r="F134" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G134" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
+      <c r="F134" t="inlineStr"/>
+      <c r="G134" t="inlineStr"/>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>onoff</t>
+          <t>kk_4829755741</t>
         </is>
       </c>
       <c r="B135" t="inlineStr"/>
       <c r="C135" t="inlineStr">
         <is>
-          <t>303518</t>
+          <t>303486</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
@@ -4876,27 +3684,19 @@
           <t>(referral)</t>
         </is>
       </c>
-      <c r="F135" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G135" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
+      <c r="F135" t="inlineStr"/>
+      <c r="G135" t="inlineStr"/>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>kk_4830409260</t>
+          <t>kk_4830404781</t>
         </is>
       </c>
       <c r="B136" t="inlineStr"/>
       <c r="C136" t="inlineStr">
         <is>
-          <t>303522</t>
+          <t>303521</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
@@ -4909,27 +3709,19 @@
           <t>6968489536332</t>
         </is>
       </c>
-      <c r="F136" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G136" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
+      <c r="F136" t="inlineStr"/>
+      <c r="G136" t="inlineStr"/>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>kk_4830541132</t>
+          <t>kk_4830692253</t>
         </is>
       </c>
       <c r="B137" t="inlineStr"/>
       <c r="C137" t="inlineStr">
         <is>
-          <t>303533</t>
+          <t>303550</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
@@ -4942,27 +3734,19 @@
           <t>6968489536332</t>
         </is>
       </c>
-      <c r="F137" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G137" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
+      <c r="F137" t="inlineStr"/>
+      <c r="G137" t="inlineStr"/>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>kk_4830692253</t>
+          <t>kk_4829674741</t>
         </is>
       </c>
       <c r="B138" t="inlineStr"/>
       <c r="C138" t="inlineStr">
         <is>
-          <t>303550</t>
+          <t>303484</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
@@ -4975,27 +3759,19 @@
           <t>6968489536332</t>
         </is>
       </c>
-      <c r="F138" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G138" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
+      <c r="F138" t="inlineStr"/>
+      <c r="G138" t="inlineStr"/>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>kk_4830646394</t>
+          <t>kk_4830541132</t>
         </is>
       </c>
       <c r="B139" t="inlineStr"/>
       <c r="C139" t="inlineStr">
         <is>
-          <t>303547</t>
+          <t>303533</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
@@ -5008,27 +3784,19 @@
           <t>6968489536332</t>
         </is>
       </c>
-      <c r="F139" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G139" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
+      <c r="F139" t="inlineStr"/>
+      <c r="G139" t="inlineStr"/>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>kk_4829674741</t>
+          <t>kk_4830409260</t>
         </is>
       </c>
       <c r="B140" t="inlineStr"/>
       <c r="C140" t="inlineStr">
         <is>
-          <t>303484</t>
+          <t>303522</t>
         </is>
       </c>
       <c r="D140" t="inlineStr">
@@ -5041,27 +3809,19 @@
           <t>6968489536332</t>
         </is>
       </c>
-      <c r="F140" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G140" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
+      <c r="F140" t="inlineStr"/>
+      <c r="G140" t="inlineStr"/>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>kk_4829999849</t>
+          <t>kk_4830646394</t>
         </is>
       </c>
       <c r="B141" t="inlineStr"/>
       <c r="C141" t="inlineStr">
         <is>
-          <t>303498</t>
+          <t>303547</t>
         </is>
       </c>
       <c r="D141" t="inlineStr">
@@ -5074,27 +3834,19 @@
           <t>6968489536332</t>
         </is>
       </c>
-      <c r="F141" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G141" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
+      <c r="F141" t="inlineStr"/>
+      <c r="G141" t="inlineStr"/>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>kk_4830404781</t>
+          <t>kk_4829999849</t>
         </is>
       </c>
       <c r="B142" t="inlineStr"/>
       <c r="C142" t="inlineStr">
         <is>
-          <t>303521</t>
+          <t>303498</t>
         </is>
       </c>
       <c r="D142" t="inlineStr">
@@ -5107,16 +3859,8 @@
           <t>6968489536332</t>
         </is>
       </c>
-      <c r="F142" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G142" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
+      <c r="F142" t="inlineStr"/>
+      <c r="G142" t="inlineStr"/>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
@@ -5140,27 +3884,19 @@
           <t>EFW</t>
         </is>
       </c>
-      <c r="F143" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G143" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
+      <c r="F143" t="inlineStr"/>
+      <c r="G143" t="inlineStr"/>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>kk_4829543360</t>
+          <t>kk_4830264628</t>
         </is>
       </c>
       <c r="B144" t="inlineStr"/>
       <c r="C144" t="inlineStr">
         <is>
-          <t>303478</t>
+          <t>303514</t>
         </is>
       </c>
       <c r="D144" t="inlineStr">
@@ -5173,27 +3909,19 @@
           <t>EFW_04</t>
         </is>
       </c>
-      <c r="F144" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G144" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
+      <c r="F144" t="inlineStr"/>
+      <c r="G144" t="inlineStr"/>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>kk_4830559393</t>
+          <t>kk_4829543360</t>
         </is>
       </c>
       <c r="B145" t="inlineStr"/>
       <c r="C145" t="inlineStr">
         <is>
-          <t>303535</t>
+          <t>303478</t>
         </is>
       </c>
       <c r="D145" t="inlineStr">
@@ -5206,27 +3934,19 @@
           <t>EFW_04</t>
         </is>
       </c>
-      <c r="F145" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G145" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
+      <c r="F145" t="inlineStr"/>
+      <c r="G145" t="inlineStr"/>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>mong81</t>
+          <t>kk_4830559393</t>
         </is>
       </c>
       <c r="B146" t="inlineStr"/>
       <c r="C146" t="inlineStr">
         <is>
-          <t>303505</t>
+          <t>303535</t>
         </is>
       </c>
       <c r="D146" t="inlineStr">
@@ -5239,27 +3959,19 @@
           <t>EFW_04</t>
         </is>
       </c>
-      <c r="F146" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G146" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
+      <c r="F146" t="inlineStr"/>
+      <c r="G146" t="inlineStr"/>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>kk_4830264628</t>
+          <t>mong81</t>
         </is>
       </c>
       <c r="B147" t="inlineStr"/>
       <c r="C147" t="inlineStr">
         <is>
-          <t>303514</t>
+          <t>303505</t>
         </is>
       </c>
       <c r="D147" t="inlineStr">
@@ -5272,16 +3984,8 @@
           <t>EFW_04</t>
         </is>
       </c>
-      <c r="F147" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G147" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
+      <c r="F147" t="inlineStr"/>
+      <c r="G147" t="inlineStr"/>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
@@ -5305,16 +4009,8 @@
           <t>KAKAO_CH_MENU_0211_NEW_WOMEN</t>
         </is>
       </c>
-      <c r="F148" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G148" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
+      <c r="F148" t="inlineStr"/>
+      <c r="G148" t="inlineStr"/>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
@@ -5338,27 +4034,19 @@
           <t>[PF]전환_회원가입(유사)</t>
         </is>
       </c>
-      <c r="F149" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G149" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
+      <c r="F149" t="inlineStr"/>
+      <c r="G149" t="inlineStr"/>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>kk_4830704540</t>
+          <t>kk_4830308577</t>
         </is>
       </c>
       <c r="B150" t="inlineStr"/>
       <c r="C150" t="inlineStr">
         <is>
-          <t>303551</t>
+          <t>303516</t>
         </is>
       </c>
       <c r="D150" t="inlineStr">
@@ -5371,27 +4059,19 @@
           <t>benz_running_program_2026_coupon</t>
         </is>
       </c>
-      <c r="F150" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G150" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
+      <c r="F150" t="inlineStr"/>
+      <c r="G150" t="inlineStr"/>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>kk_4830637852</t>
+          <t>kk_4830722522</t>
         </is>
       </c>
       <c r="B151" t="inlineStr"/>
       <c r="C151" t="inlineStr">
         <is>
-          <t>303546</t>
+          <t>303553</t>
         </is>
       </c>
       <c r="D151" t="inlineStr">
@@ -5404,27 +4084,19 @@
           <t>benz_running_program_2026_coupon</t>
         </is>
       </c>
-      <c r="F151" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G151" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
+      <c r="F151" t="inlineStr"/>
+      <c r="G151" t="inlineStr"/>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>kk_4830497611</t>
+          <t>kk_4830704540</t>
         </is>
       </c>
       <c r="B152" t="inlineStr"/>
       <c r="C152" t="inlineStr">
         <is>
-          <t>303526</t>
+          <t>303551</t>
         </is>
       </c>
       <c r="D152" t="inlineStr">
@@ -5437,27 +4109,19 @@
           <t>benz_running_program_2026_coupon</t>
         </is>
       </c>
-      <c r="F152" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G152" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
+      <c r="F152" t="inlineStr"/>
+      <c r="G152" t="inlineStr"/>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>kk_4830376206</t>
+          <t>kk_4830497611</t>
         </is>
       </c>
       <c r="B153" t="inlineStr"/>
       <c r="C153" t="inlineStr">
         <is>
-          <t>303520</t>
+          <t>303526</t>
         </is>
       </c>
       <c r="D153" t="inlineStr">
@@ -5470,27 +4134,19 @@
           <t>benz_running_program_2026_coupon</t>
         </is>
       </c>
-      <c r="F153" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G153" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
+      <c r="F153" t="inlineStr"/>
+      <c r="G153" t="inlineStr"/>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>kk_4830308577</t>
+          <t>flydabi</t>
         </is>
       </c>
       <c r="B154" t="inlineStr"/>
       <c r="C154" t="inlineStr">
         <is>
-          <t>303516</t>
+          <t>303531</t>
         </is>
       </c>
       <c r="D154" t="inlineStr">
@@ -5503,27 +4159,19 @@
           <t>benz_running_program_2026_coupon</t>
         </is>
       </c>
-      <c r="F154" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G154" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
+      <c r="F154" t="inlineStr"/>
+      <c r="G154" t="inlineStr"/>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>kk_4830597347</t>
+          <t>kk_4830376206</t>
         </is>
       </c>
       <c r="B155" t="inlineStr"/>
       <c r="C155" t="inlineStr">
         <is>
-          <t>303541</t>
+          <t>303520</t>
         </is>
       </c>
       <c r="D155" t="inlineStr">
@@ -5536,27 +4184,19 @@
           <t>benz_running_program_2026_coupon</t>
         </is>
       </c>
-      <c r="F155" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G155" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
+      <c r="F155" t="inlineStr"/>
+      <c r="G155" t="inlineStr"/>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>flydabi</t>
+          <t>kk_4830637852</t>
         </is>
       </c>
       <c r="B156" t="inlineStr"/>
       <c r="C156" t="inlineStr">
         <is>
-          <t>303531</t>
+          <t>303546</t>
         </is>
       </c>
       <c r="D156" t="inlineStr">
@@ -5569,27 +4209,19 @@
           <t>benz_running_program_2026_coupon</t>
         </is>
       </c>
-      <c r="F156" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G156" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
+      <c r="F156" t="inlineStr"/>
+      <c r="G156" t="inlineStr"/>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>kk_4830722522</t>
+          <t>kk_4830659012</t>
         </is>
       </c>
       <c r="B157" t="inlineStr"/>
       <c r="C157" t="inlineStr">
         <is>
-          <t>303553</t>
+          <t>303549</t>
         </is>
       </c>
       <c r="D157" t="inlineStr">
@@ -5602,27 +4234,19 @@
           <t>benz_running_program_2026_coupon</t>
         </is>
       </c>
-      <c r="F157" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G157" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
+      <c r="F157" t="inlineStr"/>
+      <c r="G157" t="inlineStr"/>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>kk_4830659012</t>
+          <t>kk_4830597347</t>
         </is>
       </c>
       <c r="B158" t="inlineStr"/>
       <c r="C158" t="inlineStr">
         <is>
-          <t>303549</t>
+          <t>303541</t>
         </is>
       </c>
       <c r="D158" t="inlineStr">
@@ -5635,16 +4259,8 @@
           <t>benz_running_program_2026_coupon</t>
         </is>
       </c>
-      <c r="F158" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G158" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
+      <c r="F158" t="inlineStr"/>
+      <c r="G158" t="inlineStr"/>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
@@ -5668,16 +4284,8 @@
           <t>benz_running_program_2026​</t>
         </is>
       </c>
-      <c r="F159" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G159" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
+      <c r="F159" t="inlineStr"/>
+      <c r="G159" t="inlineStr"/>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
@@ -5701,27 +4309,19 @@
           <t>da</t>
         </is>
       </c>
-      <c r="F160" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G160" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
+      <c r="F160" t="inlineStr"/>
+      <c r="G160" t="inlineStr"/>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>kk_4830540435</t>
+          <t>kk_4830137292</t>
         </is>
       </c>
       <c r="B161" t="inlineStr"/>
       <c r="C161" t="inlineStr">
         <is>
-          <t>303532</t>
+          <t>303504</t>
         </is>
       </c>
       <c r="D161" t="inlineStr">
@@ -5734,27 +4334,19 @@
           <t>naver_brandsearch_mobile</t>
         </is>
       </c>
-      <c r="F161" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G161" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
+      <c r="F161" t="inlineStr"/>
+      <c r="G161" t="inlineStr"/>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>kk_4830137292</t>
+          <t>kk_4830540435</t>
         </is>
       </c>
       <c r="B162" t="inlineStr"/>
       <c r="C162" t="inlineStr">
         <is>
-          <t>303504</t>
+          <t>303532</t>
         </is>
       </c>
       <c r="D162" t="inlineStr">
@@ -5767,16 +4359,8 @@
           <t>naver_brandsearch_mobile</t>
         </is>
       </c>
-      <c r="F162" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G162" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
+      <c r="F162" t="inlineStr"/>
+      <c r="G162" t="inlineStr"/>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
@@ -5800,27 +4384,19 @@
           <t>naver_brandsearch_pc</t>
         </is>
       </c>
-      <c r="F163" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G163" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
+      <c r="F163" t="inlineStr"/>
+      <c r="G163" t="inlineStr"/>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>kk_4829761376</t>
+          <t>kk_4830179048</t>
         </is>
       </c>
       <c r="B164" t="inlineStr"/>
       <c r="C164" t="inlineStr">
         <is>
-          <t>303487</t>
+          <t>303507</t>
         </is>
       </c>
       <c r="D164" t="inlineStr">
@@ -5833,27 +4409,19 @@
           <t>naversa_mo</t>
         </is>
       </c>
-      <c r="F164" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G164" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
+      <c r="F164" t="inlineStr"/>
+      <c r="G164" t="inlineStr"/>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>kk_4830179048</t>
+          <t>kk_4829761376</t>
         </is>
       </c>
       <c r="B165" t="inlineStr"/>
       <c r="C165" t="inlineStr">
         <is>
-          <t>303507</t>
+          <t>303487</t>
         </is>
       </c>
       <c r="D165" t="inlineStr">
@@ -5866,16 +4434,8 @@
           <t>naversa_mo</t>
         </is>
       </c>
-      <c r="F165" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G165" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
+      <c r="F165" t="inlineStr"/>
+      <c r="G165" t="inlineStr"/>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
@@ -5899,16 +4459,8 @@
           <t>EFW_04</t>
         </is>
       </c>
-      <c r="F166" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G166" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
+      <c r="F166" t="inlineStr"/>
+      <c r="G166" t="inlineStr"/>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
@@ -5932,16 +4484,8 @@
           <t>benz_running_program_2026_coupon</t>
         </is>
       </c>
-      <c r="F167" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G167" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
+      <c r="F167" t="inlineStr"/>
+      <c r="G167" t="inlineStr"/>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
@@ -5965,16 +4509,8 @@
           <t>benz_running_program_2026_coupon</t>
         </is>
       </c>
-      <c r="F168" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G168" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
+      <c r="F168" t="inlineStr"/>
+      <c r="G168" t="inlineStr"/>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
@@ -5998,16 +4534,8 @@
           <t>naver_brandsearch_mobile</t>
         </is>
       </c>
-      <c r="F169" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G169" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
+      <c r="F169" t="inlineStr"/>
+      <c r="G169" t="inlineStr"/>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
@@ -6026,21 +4554,9 @@
           <t>Direct</t>
         </is>
       </c>
-      <c r="E170" t="inlineStr">
-        <is>
-          <t>(not set)</t>
-        </is>
-      </c>
-      <c r="F170" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G170" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
+      <c r="E170" t="inlineStr"/>
+      <c r="F170" t="inlineStr"/>
+      <c r="G170" t="inlineStr"/>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
@@ -6064,27 +4580,19 @@
           <t>(organic)</t>
         </is>
       </c>
-      <c r="F171" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G171" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
+      <c r="F171" t="inlineStr"/>
+      <c r="G171" t="inlineStr"/>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>kk_4828853669</t>
+          <t>kk_4828870663</t>
         </is>
       </c>
       <c r="B172" t="inlineStr"/>
       <c r="C172" t="inlineStr">
         <is>
-          <t>303431</t>
+          <t>303434</t>
         </is>
       </c>
       <c r="D172" t="inlineStr">
@@ -6097,27 +4605,19 @@
           <t>(organic)</t>
         </is>
       </c>
-      <c r="F172" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G172" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
+      <c r="F172" t="inlineStr"/>
+      <c r="G172" t="inlineStr"/>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>kk_4828870663</t>
+          <t>kk_4828853669</t>
         </is>
       </c>
       <c r="B173" t="inlineStr"/>
       <c r="C173" t="inlineStr">
         <is>
-          <t>303434</t>
+          <t>303431</t>
         </is>
       </c>
       <c r="D173" t="inlineStr">
@@ -6130,16 +4630,8 @@
           <t>(organic)</t>
         </is>
       </c>
-      <c r="F173" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G173" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
+      <c r="F173" t="inlineStr"/>
+      <c r="G173" t="inlineStr"/>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
@@ -6163,16 +4655,8 @@
           <t>(referral)</t>
         </is>
       </c>
-      <c r="F174" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G174" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
+      <c r="F174" t="inlineStr"/>
+      <c r="G174" t="inlineStr"/>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
@@ -6196,16 +4680,8 @@
           <t>6968489536332</t>
         </is>
       </c>
-      <c r="F175" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G175" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
+      <c r="F175" t="inlineStr"/>
+      <c r="G175" t="inlineStr"/>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
@@ -6229,16 +4705,8 @@
           <t>6968489536332</t>
         </is>
       </c>
-      <c r="F176" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G176" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
+      <c r="F176" t="inlineStr"/>
+      <c r="G176" t="inlineStr"/>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
@@ -6262,16 +4730,8 @@
           <t>6968489536332</t>
         </is>
       </c>
-      <c r="F177" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G177" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
+      <c r="F177" t="inlineStr"/>
+      <c r="G177" t="inlineStr"/>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
@@ -6295,16 +4755,8 @@
           <t>EFW</t>
         </is>
       </c>
-      <c r="F178" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G178" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
+      <c r="F178" t="inlineStr"/>
+      <c r="G178" t="inlineStr"/>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
@@ -6328,16 +4780,8 @@
           <t>Heritage</t>
         </is>
       </c>
-      <c r="F179" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G179" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
+      <c r="F179" t="inlineStr"/>
+      <c r="G179" t="inlineStr"/>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
@@ -6361,16 +4805,8 @@
           <t>KAKAO_CH_MESSAGE_0325_S26NEW_CTA</t>
         </is>
       </c>
-      <c r="F180" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G180" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
+      <c r="F180" t="inlineStr"/>
+      <c r="G180" t="inlineStr"/>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
@@ -6394,16 +4830,8 @@
           <t>[PF]전환_회원가입(유사)</t>
         </is>
       </c>
-      <c r="F181" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G181" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
+      <c r="F181" t="inlineStr"/>
+      <c r="G181" t="inlineStr"/>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
@@ -6427,27 +4855,19 @@
           <t>benz_running_program_2026_coupon</t>
         </is>
       </c>
-      <c r="F182" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G182" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
+      <c r="F182" t="inlineStr"/>
+      <c r="G182" t="inlineStr"/>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>kk_4829107379</t>
+          <t>kk_4828876907</t>
         </is>
       </c>
       <c r="B183" t="inlineStr"/>
       <c r="C183" t="inlineStr">
         <is>
-          <t>303455</t>
+          <t>303436</t>
         </is>
       </c>
       <c r="D183" t="inlineStr">
@@ -6460,27 +4880,19 @@
           <t>benz_running_program_2026_coupon</t>
         </is>
       </c>
-      <c r="F183" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G183" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
+      <c r="F183" t="inlineStr"/>
+      <c r="G183" t="inlineStr"/>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>kk_4829201314</t>
+          <t>kk_4829107379</t>
         </is>
       </c>
       <c r="B184" t="inlineStr"/>
       <c r="C184" t="inlineStr">
         <is>
-          <t>303461</t>
+          <t>303455</t>
         </is>
       </c>
       <c r="D184" t="inlineStr">
@@ -6493,27 +4905,19 @@
           <t>benz_running_program_2026_coupon</t>
         </is>
       </c>
-      <c r="F184" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G184" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
+      <c r="F184" t="inlineStr"/>
+      <c r="G184" t="inlineStr"/>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>kk_4828876907</t>
+          <t>kk_4829201314</t>
         </is>
       </c>
       <c r="B185" t="inlineStr"/>
       <c r="C185" t="inlineStr">
         <is>
-          <t>303436</t>
+          <t>303461</t>
         </is>
       </c>
       <c r="D185" t="inlineStr">
@@ -6526,27 +4930,19 @@
           <t>benz_running_program_2026_coupon</t>
         </is>
       </c>
-      <c r="F185" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G185" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
+      <c r="F185" t="inlineStr"/>
+      <c r="G185" t="inlineStr"/>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>kk_4828872529</t>
+          <t>kk_4828903098</t>
         </is>
       </c>
       <c r="B186" t="inlineStr"/>
       <c r="C186" t="inlineStr">
         <is>
-          <t>303435</t>
+          <t>303439</t>
         </is>
       </c>
       <c r="D186" t="inlineStr">
@@ -6559,27 +4955,19 @@
           <t>naver_brandsearch_mobile</t>
         </is>
       </c>
-      <c r="F186" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G186" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
+      <c r="F186" t="inlineStr"/>
+      <c r="G186" t="inlineStr"/>
     </row>
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>kk_4828903098</t>
+          <t>kk_4828872529</t>
         </is>
       </c>
       <c r="B187" t="inlineStr"/>
       <c r="C187" t="inlineStr">
         <is>
-          <t>303439</t>
+          <t>303435</t>
         </is>
       </c>
       <c r="D187" t="inlineStr">
@@ -6592,16 +4980,8 @@
           <t>naver_brandsearch_mobile</t>
         </is>
       </c>
-      <c r="F187" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G187" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
+      <c r="F187" t="inlineStr"/>
+      <c r="G187" t="inlineStr"/>
     </row>
     <row r="188">
       <c r="A188" t="inlineStr">
@@ -6625,16 +5005,8 @@
           <t>naversa_mo</t>
         </is>
       </c>
-      <c r="F188" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G188" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
+      <c r="F188" t="inlineStr"/>
+      <c r="G188" t="inlineStr"/>
     </row>
     <row r="189">
       <c r="A189" t="inlineStr">
@@ -6658,16 +5030,8 @@
           <t>naversa_mo</t>
         </is>
       </c>
-      <c r="F189" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G189" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
+      <c r="F189" t="inlineStr"/>
+      <c r="G189" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/reports/member_funnel/downloads/member_funnel_7d_non_buyer.xlsx
+++ b/reports/member_funnel/downloads/member_funnel_7d_non_buyer.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G189"/>
+  <dimension ref="A1:F192"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -456,50 +456,44 @@
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>last_category</t>
-        </is>
-      </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>top_product</t>
+          <t>purchase_product_name</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>kk_4831361074</t>
+          <t>kk_4830885654</t>
         </is>
       </c>
       <c r="B2" t="inlineStr"/>
       <c r="C2" t="inlineStr">
         <is>
-          <t>303574</t>
+          <t>303562</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Organic Traffic</t>
+          <t>Official SNS</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>(organic)</t>
+          <t>Official SNS</t>
         </is>
       </c>
       <c r="F2" t="inlineStr"/>
-      <c r="G2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>kk_4830254905</t>
+          <t>kk_4831895164</t>
         </is>
       </c>
       <c r="B3" t="inlineStr"/>
       <c r="C3" t="inlineStr">
         <is>
-          <t>303513</t>
+          <t>303616</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -509,22 +503,21 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>naver_brandsearch_mobile</t>
+          <t>(referral)</t>
         </is>
       </c>
       <c r="F3" t="inlineStr"/>
-      <c r="G3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>kk_4832204677</t>
+          <t>ydh1184</t>
         </is>
       </c>
       <c r="B4" t="inlineStr"/>
       <c r="C4" t="inlineStr">
         <is>
-          <t>303653</t>
+          <t>303696</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -534,193 +527,189 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>sa</t>
+          <t>6968489536332</t>
         </is>
       </c>
       <c r="F4" t="inlineStr"/>
-      <c r="G4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>kk_4830885654</t>
+          <t>kk_4832961884</t>
         </is>
       </c>
       <c r="B5" t="inlineStr"/>
       <c r="C5" t="inlineStr">
         <is>
-          <t>303562</t>
+          <t>303698</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Direct</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr"/>
+          <t>Owned Channel</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>(referral)</t>
+        </is>
+      </c>
       <c r="F5" t="inlineStr"/>
-      <c r="G5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>kk_4831895164</t>
+          <t>kk_4832593419</t>
         </is>
       </c>
       <c r="B6" t="inlineStr"/>
       <c r="C6" t="inlineStr">
         <is>
-          <t>303616</t>
+          <t>303677</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Organic Traffic</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>(referral)</t>
+          <t>6968489536332</t>
         </is>
       </c>
       <c r="F6" t="inlineStr"/>
-      <c r="G6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>kk_4829516327</t>
+          <t>kk_4831740520</t>
         </is>
       </c>
       <c r="B7" t="inlineStr"/>
       <c r="C7" t="inlineStr">
         <is>
-          <t>303476</t>
+          <t>303601</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>naver_brandsearch_mobile</t>
+          <t>benz_running_program_2026_coupon</t>
         </is>
       </c>
       <c r="F7" t="inlineStr"/>
-      <c r="G7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>kk_4829818548</t>
+          <t>kk_4830523585</t>
         </is>
       </c>
       <c r="B8" t="inlineStr"/>
       <c r="C8" t="inlineStr">
         <is>
-          <t>303491</t>
+          <t>303530</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Awareness</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>[PF]A SC_상시(1865MF,구매 장바구니)</t>
+          <t>benz_running_program_2026_coupon</t>
         </is>
       </c>
       <c r="F8" t="inlineStr"/>
-      <c r="G8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>kk_4831740520</t>
+          <t>kk_4833676515</t>
         </is>
       </c>
       <c r="B9" t="inlineStr"/>
       <c r="C9" t="inlineStr">
         <is>
-          <t>303601</t>
+          <t>303738</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>benz_running_program_2026_coupon</t>
+          <t>naver_brandsearch_mobile</t>
         </is>
       </c>
       <c r="F9" t="inlineStr"/>
-      <c r="G9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>kk_4830523585</t>
+          <t>kk_4833576113</t>
         </is>
       </c>
       <c r="B10" t="inlineStr"/>
       <c r="C10" t="inlineStr">
         <is>
-          <t>303530</t>
+          <t>303731</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Awareness</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>benz_running_program_2026_coupon</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="F10" t="inlineStr"/>
-      <c r="G10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>kk_4830030364</t>
+          <t>kk_4832799612</t>
         </is>
       </c>
       <c r="B11" t="inlineStr"/>
       <c r="C11" t="inlineStr">
         <is>
-          <t>303499</t>
+          <t>303686</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>naversa_mo</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="F11" t="inlineStr"/>
-      <c r="G11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>kk_4830247238</t>
+          <t>kk_4832659421</t>
         </is>
       </c>
       <c r="B12" t="inlineStr"/>
       <c r="C12" t="inlineStr">
         <is>
-          <t>303510</t>
+          <t>303680</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -728,34 +717,36 @@
           <t>Direct</t>
         </is>
       </c>
-      <c r="E12" t="inlineStr"/>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>Direct</t>
+        </is>
+      </c>
       <c r="F12" t="inlineStr"/>
-      <c r="G12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>kk_4830591832</t>
+          <t>kk_4833493849</t>
         </is>
       </c>
       <c r="B13" t="inlineStr"/>
       <c r="C13" t="inlineStr">
         <is>
-          <t>303539</t>
+          <t>303728</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Organic Traffic</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>(organic)</t>
+          <t>(referral)</t>
         </is>
       </c>
       <c r="F13" t="inlineStr"/>
-      <c r="G13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -780,7 +771,6 @@
         </is>
       </c>
       <c r="F14" t="inlineStr"/>
-      <c r="G14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -805,18 +795,17 @@
         </is>
       </c>
       <c r="F15" t="inlineStr"/>
-      <c r="G15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>kk_4832293158</t>
+          <t>kk_4833894015</t>
         </is>
       </c>
       <c r="B16" t="inlineStr"/>
       <c r="C16" t="inlineStr">
         <is>
-          <t>303662</t>
+          <t>303761</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -830,18 +819,17 @@
         </is>
       </c>
       <c r="F16" t="inlineStr"/>
-      <c r="G16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>kk_4832162309</t>
+          <t>kk_4832293158</t>
         </is>
       </c>
       <c r="B17" t="inlineStr"/>
       <c r="C17" t="inlineStr">
         <is>
-          <t>303643</t>
+          <t>303662</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -851,160 +839,165 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>benz_running_program_2026​</t>
+          <t>benz_running_program_2026_coupon</t>
         </is>
       </c>
       <c r="F17" t="inlineStr"/>
-      <c r="G17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>kk_4831572710</t>
+          <t>kk_4833753902</t>
         </is>
       </c>
       <c r="B18" t="inlineStr"/>
       <c r="C18" t="inlineStr">
         <is>
-          <t>303590</t>
+          <t>303747</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Awareness</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>naver_brandsearch_mobile</t>
+          <t>benz_running_program_2026_coupon</t>
         </is>
       </c>
       <c r="F18" t="inlineStr"/>
-      <c r="G18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>kda01126</t>
+          <t>kk_4833855255</t>
         </is>
       </c>
       <c r="B19" t="inlineStr"/>
       <c r="C19" t="inlineStr">
         <is>
-          <t>303656</t>
+          <t>303757</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>naver_brandsearch_mobile</t>
+          <t>benz_running_program_2026_coupon</t>
         </is>
       </c>
       <c r="F19" t="inlineStr"/>
-      <c r="G19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>masterk</t>
+          <t>kk_4832162309</t>
         </is>
       </c>
       <c r="B20" t="inlineStr"/>
       <c r="C20" t="inlineStr">
         <is>
-          <t>303524</t>
+          <t>303643</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Awareness</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>sa</t>
+          <t>benz_running_program_2026​</t>
         </is>
       </c>
       <c r="F20" t="inlineStr"/>
-      <c r="G20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>kk_4832411690</t>
+          <t>kk_4833840470</t>
         </is>
       </c>
       <c r="B21" t="inlineStr"/>
       <c r="C21" t="inlineStr">
         <is>
-          <t>303666</t>
+          <t>303756</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Direct</t>
-        </is>
-      </c>
-      <c r="E21" t="inlineStr"/>
+          <t>Awareness</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>benz_running_program_2026​</t>
+        </is>
+      </c>
       <c r="F21" t="inlineStr"/>
-      <c r="G21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>kk_4832425261</t>
+          <t>kk_4830212469</t>
         </is>
       </c>
       <c r="B22" t="inlineStr"/>
       <c r="C22" t="inlineStr">
         <is>
-          <t>303667</t>
+          <t>303509</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Direct</t>
-        </is>
-      </c>
-      <c r="E22" t="inlineStr"/>
+          <t>Paid Ad</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>da</t>
+        </is>
+      </c>
       <c r="F22" t="inlineStr"/>
-      <c r="G22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>kk_4832425669</t>
+          <t>kk_4833715500</t>
         </is>
       </c>
       <c r="B23" t="inlineStr"/>
       <c r="C23" t="inlineStr">
         <is>
-          <t>303668</t>
+          <t>303745</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Direct</t>
-        </is>
-      </c>
-      <c r="E23" t="inlineStr"/>
+          <t>Paid Ad</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>naversa_mo</t>
+        </is>
+      </c>
       <c r="F23" t="inlineStr"/>
-      <c r="G23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>kk_4832345614</t>
+          <t>masterk</t>
         </is>
       </c>
       <c r="B24" t="inlineStr"/>
       <c r="C24" t="inlineStr">
         <is>
-          <t>303664</t>
+          <t>303524</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -1012,20 +1005,23 @@
           <t>Paid Ad</t>
         </is>
       </c>
-      <c r="E24" t="inlineStr"/>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>sa</t>
+        </is>
+      </c>
       <c r="F24" t="inlineStr"/>
-      <c r="G24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>hotsnoopy</t>
+          <t>sjjeon1928</t>
         </is>
       </c>
       <c r="B25" t="inlineStr"/>
       <c r="C25" t="inlineStr">
         <is>
-          <t>303585</t>
+          <t>303749</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -1033,20 +1029,23 @@
           <t>Direct</t>
         </is>
       </c>
-      <c r="E25" t="inlineStr"/>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>Direct</t>
+        </is>
+      </c>
       <c r="F25" t="inlineStr"/>
-      <c r="G25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>kk_4829979824</t>
+          <t>kk_4832656308</t>
         </is>
       </c>
       <c r="B26" t="inlineStr"/>
       <c r="C26" t="inlineStr">
         <is>
-          <t>303497</t>
+          <t>303679</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -1054,20 +1053,23 @@
           <t>Direct</t>
         </is>
       </c>
-      <c r="E26" t="inlineStr"/>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>Direct</t>
+        </is>
+      </c>
       <c r="F26" t="inlineStr"/>
-      <c r="G26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>kk_4831784738</t>
+          <t>kk_4832738942</t>
         </is>
       </c>
       <c r="B27" t="inlineStr"/>
       <c r="C27" t="inlineStr">
         <is>
-          <t>303607</t>
+          <t>303683</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -1075,20 +1077,23 @@
           <t>Direct</t>
         </is>
       </c>
-      <c r="E27" t="inlineStr"/>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>Direct</t>
+        </is>
+      </c>
       <c r="F27" t="inlineStr"/>
-      <c r="G27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>thdud9181</t>
+          <t>kk_4833682381</t>
         </is>
       </c>
       <c r="B28" t="inlineStr"/>
       <c r="C28" t="inlineStr">
         <is>
-          <t>303644</t>
+          <t>303739</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -1096,20 +1101,23 @@
           <t>Direct</t>
         </is>
       </c>
-      <c r="E28" t="inlineStr"/>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>Direct</t>
+        </is>
+      </c>
       <c r="F28" t="inlineStr"/>
-      <c r="G28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>kk_4829348219</t>
+          <t>whitehole147</t>
         </is>
       </c>
       <c r="B29" t="inlineStr"/>
       <c r="C29" t="inlineStr">
         <is>
-          <t>303468</t>
+          <t>303673</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -1117,20 +1125,23 @@
           <t>Direct</t>
         </is>
       </c>
-      <c r="E29" t="inlineStr"/>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>Direct</t>
+        </is>
+      </c>
       <c r="F29" t="inlineStr"/>
-      <c r="G29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>kk_4831402433</t>
+          <t>kk_4833013784</t>
         </is>
       </c>
       <c r="B30" t="inlineStr"/>
       <c r="C30" t="inlineStr">
         <is>
-          <t>303576</t>
+          <t>303703</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -1138,20 +1149,23 @@
           <t>Direct</t>
         </is>
       </c>
-      <c r="E30" t="inlineStr"/>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>Direct</t>
+        </is>
+      </c>
       <c r="F30" t="inlineStr"/>
-      <c r="G30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>kk_4832310183</t>
+          <t>kk_4833797203</t>
         </is>
       </c>
       <c r="B31" t="inlineStr"/>
       <c r="C31" t="inlineStr">
         <is>
-          <t>303663</t>
+          <t>303750</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -1159,20 +1173,23 @@
           <t>Direct</t>
         </is>
       </c>
-      <c r="E31" t="inlineStr"/>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>Direct</t>
+        </is>
+      </c>
       <c r="F31" t="inlineStr"/>
-      <c r="G31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>kk_4829294214</t>
+          <t>kk_4832648970</t>
         </is>
       </c>
       <c r="B32" t="inlineStr"/>
       <c r="C32" t="inlineStr">
         <is>
-          <t>303466</t>
+          <t>303678</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -1180,245 +1197,239 @@
           <t>Direct</t>
         </is>
       </c>
-      <c r="E32" t="inlineStr"/>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>Direct</t>
+        </is>
+      </c>
       <c r="F32" t="inlineStr"/>
-      <c r="G32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>kk_4829088785</t>
+          <t>arumabc</t>
         </is>
       </c>
       <c r="B33" t="inlineStr"/>
       <c r="C33" t="inlineStr">
         <is>
-          <t>303454</t>
+          <t>303689</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>6968489536332</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="F33" t="inlineStr"/>
-      <c r="G33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>rkddl4</t>
+          <t>kk_4832411690</t>
         </is>
       </c>
       <c r="B34" t="inlineStr"/>
       <c r="C34" t="inlineStr">
         <is>
-          <t>303596</t>
+          <t>303666</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>KAKAO_alimtalk</t>
+          <t>(organic)</t>
         </is>
       </c>
       <c r="F34" t="inlineStr"/>
-      <c r="G34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>kk_4830612400</t>
+          <t>kk_4833617385</t>
         </is>
       </c>
       <c r="B35" t="inlineStr"/>
       <c r="C35" t="inlineStr">
         <is>
-          <t>303542</t>
+          <t>303734</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>Awareness</t>
+          <t>Organic Traffic</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>benz_running_program_2026_coupon</t>
+          <t>(referral)</t>
         </is>
       </c>
       <c r="F35" t="inlineStr"/>
-      <c r="G35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>kk_4831842028</t>
+          <t>kk_4833733292</t>
         </is>
       </c>
       <c r="B36" t="inlineStr"/>
       <c r="C36" t="inlineStr">
         <is>
-          <t>303612</t>
+          <t>303746</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>Awareness</t>
+          <t>Organic Traffic</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>benz_running_program_2026_coupon</t>
+          <t>(referral)</t>
         </is>
       </c>
       <c r="F36" t="inlineStr"/>
-      <c r="G36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>kk_4830513865</t>
+          <t>lily50</t>
         </is>
       </c>
       <c r="B37" t="inlineStr"/>
       <c r="C37" t="inlineStr">
         <is>
-          <t>303529</t>
+          <t>303714</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Organic Traffic</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>naver_brandsearch_mobile</t>
+          <t>(referral)</t>
         </is>
       </c>
       <c r="F37" t="inlineStr"/>
-      <c r="G37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>kk_4829077261</t>
+          <t>kk_4832556634</t>
         </is>
       </c>
       <c r="B38" t="inlineStr"/>
       <c r="C38" t="inlineStr">
         <is>
-          <t>303453</t>
+          <t>303674</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Organic Traffic</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>6968489536332</t>
+          <t>(referral)</t>
         </is>
       </c>
       <c r="F38" t="inlineStr"/>
-      <c r="G38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>kk_4830476438</t>
+          <t>kk_4833397488</t>
         </is>
       </c>
       <c r="B39" t="inlineStr"/>
       <c r="C39" t="inlineStr">
         <is>
-          <t>303525</t>
+          <t>303723</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>Organic Traffic</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>EFW_04</t>
+          <t>6968489536332</t>
         </is>
       </c>
       <c r="F39" t="inlineStr"/>
-      <c r="G39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>kk_4831687251</t>
+          <t>kk_4833698569</t>
         </is>
       </c>
       <c r="B40" t="inlineStr"/>
       <c r="C40" t="inlineStr">
         <is>
-          <t>303598</t>
+          <t>303743</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>Awareness</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>benz_running_program_2026_coupon</t>
+          <t>6968489536332</t>
         </is>
       </c>
       <c r="F40" t="inlineStr"/>
-      <c r="G40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>kk_4829440714</t>
+          <t>kk_4833115356</t>
         </is>
       </c>
       <c r="B41" t="inlineStr"/>
       <c r="C41" t="inlineStr">
         <is>
-          <t>303471</t>
+          <t>303707</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>Awareness</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>benz_running_program_2026_coupon</t>
+          <t>6968489536332</t>
         </is>
       </c>
       <c r="F41" t="inlineStr"/>
-      <c r="G41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>kk_4830793813</t>
+          <t>dave1102</t>
         </is>
       </c>
       <c r="B42" t="inlineStr"/>
       <c r="C42" t="inlineStr">
         <is>
-          <t>303557</t>
+          <t>303697</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -1428,22 +1439,21 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>naver_brandsearch_mobile</t>
+          <t>6968489536332</t>
         </is>
       </c>
       <c r="F42" t="inlineStr"/>
-      <c r="G42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>charismasm74</t>
+          <t>kk_4832345614</t>
         </is>
       </c>
       <c r="B43" t="inlineStr"/>
       <c r="C43" t="inlineStr">
         <is>
-          <t>303650</t>
+          <t>303664</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -1453,22 +1463,21 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>naver_brandsearch_pc</t>
+          <t>6968489536332</t>
         </is>
       </c>
       <c r="F43" t="inlineStr"/>
-      <c r="G43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>kk_4831500868</t>
+          <t>kk_4832562814</t>
         </is>
       </c>
       <c r="B44" t="inlineStr"/>
       <c r="C44" t="inlineStr">
         <is>
-          <t>303582</t>
+          <t>303675</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -1482,18 +1491,17 @@
         </is>
       </c>
       <c r="F44" t="inlineStr"/>
-      <c r="G44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>kk_4830922114</t>
+          <t>kk_4833867742</t>
         </is>
       </c>
       <c r="B45" t="inlineStr"/>
       <c r="C45" t="inlineStr">
         <is>
-          <t>303563</t>
+          <t>303760</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -1503,22 +1511,21 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>[PF]전환_회원가입(유사)</t>
+          <t>6968489536332</t>
         </is>
       </c>
       <c r="F45" t="inlineStr"/>
-      <c r="G45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>hoonck1</t>
+          <t>kk_4832564458</t>
         </is>
       </c>
       <c r="B46" t="inlineStr"/>
       <c r="C46" t="inlineStr">
         <is>
-          <t>303433</t>
+          <t>303676</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -1528,147 +1535,141 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>[PF]트래픽_유사+관심사</t>
+          <t>6968489536332</t>
         </is>
       </c>
       <c r="F46" t="inlineStr"/>
-      <c r="G46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>kk_4831995357</t>
+          <t>kk_4832425261</t>
         </is>
       </c>
       <c r="B47" t="inlineStr"/>
       <c r="C47" t="inlineStr">
         <is>
-          <t>303623</t>
+          <t>303667</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>Awareness</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>benz_running_program_2026_coupon</t>
+          <t>6968489536332</t>
         </is>
       </c>
       <c r="F47" t="inlineStr"/>
-      <c r="G47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>kk_4831768959</t>
+          <t>kk_4832735078</t>
         </is>
       </c>
       <c r="B48" t="inlineStr"/>
       <c r="C48" t="inlineStr">
         <is>
-          <t>303602</t>
+          <t>303682</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>Awareness</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>benz_running_program_2026_coupon</t>
+          <t>6968489536332</t>
         </is>
       </c>
       <c r="F48" t="inlineStr"/>
-      <c r="G48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>kk_4832205664</t>
+          <t>kk_4832986577</t>
         </is>
       </c>
       <c r="B49" t="inlineStr"/>
       <c r="C49" t="inlineStr">
         <is>
-          <t>303654</t>
+          <t>303701</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>benz_running_program_2026_coupon</t>
+          <t>6968489536332</t>
         </is>
       </c>
       <c r="F49" t="inlineStr"/>
-      <c r="G49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>kk_4830251299</t>
+          <t>wngml5609</t>
         </is>
       </c>
       <c r="B50" t="inlineStr"/>
       <c r="C50" t="inlineStr">
         <is>
-          <t>303511</t>
+          <t>303704</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>Awareness</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>benz_running_program_2026_coupon</t>
+          <t>6968489536332</t>
         </is>
       </c>
       <c r="F50" t="inlineStr"/>
-      <c r="G50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>kk_4831422357</t>
+          <t>kk_4832771015</t>
         </is>
       </c>
       <c r="B51" t="inlineStr"/>
       <c r="C51" t="inlineStr">
         <is>
-          <t>303577</t>
+          <t>303685</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>Official SNS</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>benz_running_program_2026_coupon</t>
+          <t>6968489536332</t>
         </is>
       </c>
       <c r="F51" t="inlineStr"/>
-      <c r="G51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>kk_4832105165</t>
+          <t>ckddbs4958</t>
         </is>
       </c>
       <c r="B52" t="inlineStr"/>
       <c r="C52" t="inlineStr">
         <is>
-          <t>303636</t>
+          <t>303722</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -1678,457 +1679,477 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>naver_brandsearch_mobile</t>
+          <t>6968489536332</t>
         </is>
       </c>
       <c r="F52" t="inlineStr"/>
-      <c r="G52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>kk_4831842112</t>
+          <t>kk_4833234218</t>
         </is>
       </c>
       <c r="B53" t="inlineStr"/>
       <c r="C53" t="inlineStr">
         <is>
-          <t>303613</t>
+          <t>303711</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Official SNS</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>naver_brandsearch_mobile</t>
+          <t>EFW_04</t>
         </is>
       </c>
       <c r="F53" t="inlineStr"/>
-      <c r="G53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>kk_4832076715</t>
+          <t>kk_4833435690</t>
         </is>
       </c>
       <c r="B54" t="inlineStr"/>
       <c r="C54" t="inlineStr">
         <is>
-          <t>303629</t>
+          <t>303726</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>Direct</t>
-        </is>
-      </c>
-      <c r="E54" t="inlineStr"/>
+          <t>Official SNS</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>EFW_04</t>
+        </is>
+      </c>
       <c r="F54" t="inlineStr"/>
-      <c r="G54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>kk_4832114535</t>
+          <t>kk_4833215714</t>
         </is>
       </c>
       <c r="B55" t="inlineStr"/>
       <c r="C55" t="inlineStr">
         <is>
-          <t>303637</t>
+          <t>303709</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>Direct</t>
-        </is>
-      </c>
-      <c r="E55" t="inlineStr"/>
+          <t>Official SNS</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>EFW_04</t>
+        </is>
+      </c>
       <c r="F55" t="inlineStr"/>
-      <c r="G55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>kk_4830821550</t>
+          <t>kk_4832874454</t>
         </is>
       </c>
       <c r="B56" t="inlineStr"/>
       <c r="C56" t="inlineStr">
         <is>
-          <t>303559</t>
+          <t>303691</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>Direct</t>
-        </is>
-      </c>
-      <c r="E56" t="inlineStr"/>
+          <t>Official SNS</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>EFW_04</t>
+        </is>
+      </c>
       <c r="F56" t="inlineStr"/>
-      <c r="G56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>kk_4832180009</t>
+          <t>kk_4833692238</t>
         </is>
       </c>
       <c r="B57" t="inlineStr"/>
       <c r="C57" t="inlineStr">
         <is>
-          <t>303647</t>
+          <t>303741</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>Direct</t>
-        </is>
-      </c>
-      <c r="E57" t="inlineStr"/>
+          <t>Paid Ad</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>[PF]전환_회원가입(유사)</t>
+        </is>
+      </c>
       <c r="F57" t="inlineStr"/>
-      <c r="G57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>kk_4831346086</t>
+          <t>kk_4833915167</t>
         </is>
       </c>
       <c r="B58" t="inlineStr"/>
       <c r="C58" t="inlineStr">
         <is>
-          <t>303573</t>
+          <t>303764</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>Direct</t>
-        </is>
-      </c>
-      <c r="E58" t="inlineStr"/>
+          <t>Paid Ad</t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>[PF]트래픽_유사+관심사</t>
+        </is>
+      </c>
       <c r="F58" t="inlineStr"/>
-      <c r="G58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>kk_4831394790</t>
+          <t>kk_4833289287</t>
         </is>
       </c>
       <c r="B59" t="inlineStr"/>
       <c r="C59" t="inlineStr">
         <is>
-          <t>303575</t>
+          <t>303716</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>Direct</t>
-        </is>
-      </c>
-      <c r="E59" t="inlineStr"/>
+          <t>Awareness</t>
+        </is>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>benz_running_program_2026_coupon</t>
+        </is>
+      </c>
       <c r="F59" t="inlineStr"/>
-      <c r="G59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>kk_4832201164</t>
+          <t>kk_4833588305</t>
         </is>
       </c>
       <c r="B60" t="inlineStr"/>
       <c r="C60" t="inlineStr">
         <is>
-          <t>303651</t>
+          <t>303733</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>Direct</t>
-        </is>
-      </c>
-      <c r="E60" t="inlineStr"/>
+          <t>Awareness</t>
+        </is>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>benz_running_program_2026_coupon</t>
+        </is>
+      </c>
       <c r="F60" t="inlineStr"/>
-      <c r="G60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>kk_4830767555</t>
+          <t>kk_4833858368</t>
         </is>
       </c>
       <c r="B61" t="inlineStr"/>
       <c r="C61" t="inlineStr">
         <is>
-          <t>303555</t>
+          <t>303758</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>Direct</t>
-        </is>
-      </c>
-      <c r="E61" t="inlineStr"/>
+          <t>Awareness</t>
+        </is>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>benz_running_program_2026_coupon</t>
+        </is>
+      </c>
       <c r="F61" t="inlineStr"/>
-      <c r="G61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>kk_4832248726</t>
+          <t>kk_4833937502</t>
         </is>
       </c>
       <c r="B62" t="inlineStr"/>
       <c r="C62" t="inlineStr">
         <is>
-          <t>303658</t>
+          <t>303767</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>Direct</t>
-        </is>
-      </c>
-      <c r="E62" t="inlineStr"/>
+          <t>Awareness</t>
+        </is>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>benz_running_program_2026_coupon</t>
+        </is>
+      </c>
       <c r="F62" t="inlineStr"/>
-      <c r="G62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>kk_4832023314</t>
+          <t>kk_4832963009</t>
         </is>
       </c>
       <c r="B63" t="inlineStr"/>
       <c r="C63" t="inlineStr">
         <is>
-          <t>303626</t>
+          <t>303699</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>Direct</t>
-        </is>
-      </c>
-      <c r="E63" t="inlineStr"/>
+          <t>Awareness</t>
+        </is>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>benz_running_program_2026_coupon</t>
+        </is>
+      </c>
       <c r="F63" t="inlineStr"/>
-      <c r="G63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>kk_4831495694</t>
+          <t>kk_4832497383</t>
         </is>
       </c>
       <c r="B64" t="inlineStr"/>
       <c r="C64" t="inlineStr">
         <is>
-          <t>303581</t>
+          <t>303669</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>Organic Traffic</t>
+          <t>Awareness</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>(organic)</t>
+          <t>benz_running_program_2026_coupon</t>
         </is>
       </c>
       <c r="F64" t="inlineStr"/>
-      <c r="G64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>kk_4832164589</t>
+          <t>kk_4833788564</t>
         </is>
       </c>
       <c r="B65" t="inlineStr"/>
       <c r="C65" t="inlineStr">
         <is>
-          <t>303645</t>
+          <t>303748</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Awareness</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>(organic)</t>
+          <t>benz_running_program_2026​</t>
         </is>
       </c>
       <c r="F65" t="inlineStr"/>
-      <c r="G65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>kk_4832100095</t>
+          <t>hlpt10</t>
         </is>
       </c>
       <c r="B66" t="inlineStr"/>
       <c r="C66" t="inlineStr">
         <is>
-          <t>303634</t>
+          <t>303715</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>Organic Traffic</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>(referral)</t>
+          <t>naver_brandsearch_mobile</t>
         </is>
       </c>
       <c r="F66" t="inlineStr"/>
-      <c r="G66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>kk_4832078505</t>
+          <t>kk_4832855902</t>
         </is>
       </c>
       <c r="B67" t="inlineStr"/>
       <c r="C67" t="inlineStr">
         <is>
-          <t>303630</t>
+          <t>303690</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>Organic Traffic</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>(referral)</t>
+          <t>naver_brandsearch_mobile</t>
         </is>
       </c>
       <c r="F67" t="inlineStr"/>
-      <c r="G67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>kk_4831649243</t>
+          <t>kk_4832804456</t>
         </is>
       </c>
       <c r="B68" t="inlineStr"/>
       <c r="C68" t="inlineStr">
         <is>
-          <t>303595</t>
+          <t>303687</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>Organic Traffic</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>(referral)</t>
+          <t>naver_brandsearch_mobile</t>
         </is>
       </c>
       <c r="F68" t="inlineStr"/>
-      <c r="G68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>kk_4832029124</t>
+          <t>kk_4832888908</t>
         </is>
       </c>
       <c r="B69" t="inlineStr"/>
       <c r="C69" t="inlineStr">
         <is>
-          <t>303627</t>
+          <t>303693</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>Organic Traffic</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>(referral)</t>
+          <t>naver_brandsearch_mobile</t>
         </is>
       </c>
       <c r="F69" t="inlineStr"/>
-      <c r="G69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>jambo8</t>
+          <t>mystyle1999</t>
         </is>
       </c>
       <c r="B70" t="inlineStr"/>
       <c r="C70" t="inlineStr">
         <is>
-          <t>303558</t>
+          <t>303695</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>Organic Traffic</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>(referral)</t>
+          <t>naver_brandsearch_mobile</t>
         </is>
       </c>
       <c r="F70" t="inlineStr"/>
-      <c r="G70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>kk_4831340465</t>
+          <t>kk_4832527479</t>
         </is>
       </c>
       <c r="B71" t="inlineStr"/>
       <c r="C71" t="inlineStr">
         <is>
-          <t>303572</t>
+          <t>303672</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>Organic Traffic</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>(referral)</t>
+          <t>naver_brandsearch_pc</t>
         </is>
       </c>
       <c r="F71" t="inlineStr"/>
-      <c r="G71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>kk_4831830576</t>
+          <t>kk_4832745335</t>
         </is>
       </c>
       <c r="B72" t="inlineStr"/>
       <c r="C72" t="inlineStr">
         <is>
-          <t>303611</t>
+          <t>303684</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -2138,22 +2159,21 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>6968489536332</t>
+          <t>naver_brandsearch_pc</t>
         </is>
       </c>
       <c r="F72" t="inlineStr"/>
-      <c r="G72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>jgj0503</t>
+          <t>jinchoi24</t>
         </is>
       </c>
       <c r="B73" t="inlineStr"/>
       <c r="C73" t="inlineStr">
         <is>
-          <t>303605</t>
+          <t>303754</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -2163,22 +2183,21 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>6968489536332</t>
+          <t>naver_brandsearch_pc</t>
         </is>
       </c>
       <c r="F73" t="inlineStr"/>
-      <c r="G73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>kk_4832202047</t>
+          <t>kk_4832811973</t>
         </is>
       </c>
       <c r="B74" t="inlineStr"/>
       <c r="C74" t="inlineStr">
         <is>
-          <t>303652</t>
+          <t>303688</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
@@ -2188,22 +2207,21 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>6968489536332</t>
+          <t>naversa_mo</t>
         </is>
       </c>
       <c r="F74" t="inlineStr"/>
-      <c r="G74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>kk_4832151833</t>
+          <t>kk_4833676329</t>
         </is>
       </c>
       <c r="B75" t="inlineStr"/>
       <c r="C75" t="inlineStr">
         <is>
-          <t>303641</t>
+          <t>303737</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
@@ -2213,22 +2231,21 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>6968489536332</t>
+          <t>sa</t>
         </is>
       </c>
       <c r="F75" t="inlineStr"/>
-      <c r="G75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>kk_4830989652</t>
+          <t>kk_4833836842</t>
         </is>
       </c>
       <c r="B76" t="inlineStr"/>
       <c r="C76" t="inlineStr">
         <is>
-          <t>303569</t>
+          <t>303753</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
@@ -2238,397 +2255,381 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>6968489536332</t>
+          <t>sa</t>
         </is>
       </c>
       <c r="F76" t="inlineStr"/>
-      <c r="G76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>saty31</t>
+          <t>hotsnoopy</t>
         </is>
       </c>
       <c r="B77" t="inlineStr"/>
       <c r="C77" t="inlineStr">
         <is>
-          <t>303561</t>
+          <t>303585</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>6968489536332</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="F77" t="inlineStr"/>
-      <c r="G77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>kk_4832154317</t>
+          <t>thdud9181</t>
         </is>
       </c>
       <c r="B78" t="inlineStr"/>
       <c r="C78" t="inlineStr">
         <is>
-          <t>303642</t>
+          <t>303644</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>EFW</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="F78" t="inlineStr"/>
-      <c r="G78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>kk_4831850638</t>
+          <t>kk_4831402433</t>
         </is>
       </c>
       <c r="B79" t="inlineStr"/>
       <c r="C79" t="inlineStr">
         <is>
-          <t>303615</t>
+          <t>303576</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>Official SNS</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>EFW_04</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="F79" t="inlineStr"/>
-      <c r="G79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>kk_4830778741</t>
+          <t>kk_4833961109</t>
         </is>
       </c>
       <c r="B80" t="inlineStr"/>
       <c r="C80" t="inlineStr">
         <is>
-          <t>303556</t>
+          <t>303770</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>Official SNS</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>EFW_04</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="F80" t="inlineStr"/>
-      <c r="G80" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>kk_4831922723</t>
+          <t>kk_4833294708</t>
         </is>
       </c>
       <c r="B81" t="inlineStr"/>
       <c r="C81" t="inlineStr">
         <is>
-          <t>303617</t>
+          <t>303717</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>Official SNS</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>EFW_04</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="F81" t="inlineStr"/>
-      <c r="G81" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>kk_4831536902</t>
+          <t>kk_4831784738</t>
         </is>
       </c>
       <c r="B82" t="inlineStr"/>
       <c r="C82" t="inlineStr">
         <is>
-          <t>303588</t>
+          <t>303607</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>Official SNS</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>EFW_04</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="F82" t="inlineStr"/>
-      <c r="G82" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>kk_4830836853</t>
+          <t>kk_4833706874</t>
         </is>
       </c>
       <c r="B83" t="inlineStr"/>
       <c r="C83" t="inlineStr">
         <is>
-          <t>303560</t>
+          <t>303744</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>Official SNS</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>EFW_04</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="F83" t="inlineStr"/>
-      <c r="G83" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>kk_4832125929</t>
+          <t>kk_4832310183</t>
         </is>
       </c>
       <c r="B84" t="inlineStr"/>
       <c r="C84" t="inlineStr">
         <is>
-          <t>303638</t>
+          <t>303663</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>Official SNS</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>EFW_04</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="F84" t="inlineStr"/>
-      <c r="G84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>kk_4830943389</t>
+          <t>kk_4833232918</t>
         </is>
       </c>
       <c r="B85" t="inlineStr"/>
       <c r="C85" t="inlineStr">
         <is>
-          <t>303565</t>
+          <t>303710</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>KAKAO_alimtalk</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="F85" t="inlineStr"/>
-      <c r="G85" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>kk_4831612250</t>
+          <t>pjj1758</t>
         </is>
       </c>
       <c r="B86" t="inlineStr"/>
       <c r="C86" t="inlineStr">
         <is>
-          <t>303593</t>
+          <t>303708</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>[PF]A SC_상시(1865MF,구매 장바구니)</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="F86" t="inlineStr"/>
-      <c r="G86" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>kk_4830988405</t>
+          <t>rkddl4</t>
         </is>
       </c>
       <c r="B87" t="inlineStr"/>
       <c r="C87" t="inlineStr">
         <is>
-          <t>303567</t>
+          <t>303596</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>[PF]전환_상시(2565MF,비구매자)</t>
+          <t>KAKAO_alimtalk</t>
         </is>
       </c>
       <c r="F87" t="inlineStr"/>
-      <c r="G87" t="inlineStr"/>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>kk_4830923952</t>
+          <t>kk_4830612400</t>
         </is>
       </c>
       <c r="B88" t="inlineStr"/>
       <c r="C88" t="inlineStr">
         <is>
-          <t>303564</t>
+          <t>303542</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Awareness</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>[PF]전환_회원가입(유사)</t>
+          <t>benz_running_program_2026_coupon</t>
         </is>
       </c>
       <c r="F88" t="inlineStr"/>
-      <c r="G88" t="inlineStr"/>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>kk_4830963661</t>
+          <t>kk_4831842028</t>
         </is>
       </c>
       <c r="B89" t="inlineStr"/>
       <c r="C89" t="inlineStr">
         <is>
-          <t>303566</t>
+          <t>303612</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Awareness</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>[PF]전환_회원가입(유사)</t>
+          <t>benz_running_program_2026_coupon</t>
         </is>
       </c>
       <c r="F89" t="inlineStr"/>
-      <c r="G89" t="inlineStr"/>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>kk_4831799020</t>
+          <t>kk_4830513865</t>
         </is>
       </c>
       <c r="B90" t="inlineStr"/>
       <c r="C90" t="inlineStr">
         <is>
-          <t>303609</t>
+          <t>303529</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>Awareness</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>benz_running_program_2026_coupon</t>
+          <t>naver_brandsearch_mobile</t>
         </is>
       </c>
       <c r="F90" t="inlineStr"/>
-      <c r="G90" t="inlineStr"/>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>kk_4831981914</t>
+          <t>kk_4830476438</t>
         </is>
       </c>
       <c r="B91" t="inlineStr"/>
       <c r="C91" t="inlineStr">
         <is>
-          <t>303620</t>
+          <t>303525</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>Awareness</t>
+          <t>Organic Traffic</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>benz_running_program_2026_coupon</t>
+          <t>EFW_04</t>
         </is>
       </c>
       <c r="F91" t="inlineStr"/>
-      <c r="G91" t="inlineStr"/>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>kk_4831502482</t>
+          <t>kk_4831687251</t>
         </is>
       </c>
       <c r="B92" t="inlineStr"/>
       <c r="C92" t="inlineStr">
         <is>
-          <t>303583</t>
+          <t>303598</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
@@ -2642,123 +2643,118 @@
         </is>
       </c>
       <c r="F92" t="inlineStr"/>
-      <c r="G92" t="inlineStr"/>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>kk_4832100101</t>
+          <t>kk_4830793813</t>
         </is>
       </c>
       <c r="B93" t="inlineStr"/>
       <c r="C93" t="inlineStr">
         <is>
-          <t>303635</t>
+          <t>303557</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>Awareness</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>benz_running_program_2026_coupon</t>
+          <t>naver_brandsearch_mobile</t>
         </is>
       </c>
       <c r="F93" t="inlineStr"/>
-      <c r="G93" t="inlineStr"/>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>kk_4831997957</t>
+          <t>charismasm74</t>
         </is>
       </c>
       <c r="B94" t="inlineStr"/>
       <c r="C94" t="inlineStr">
         <is>
-          <t>303624</t>
+          <t>303650</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>Awareness</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>benz_running_program_2026_coupon</t>
+          <t>naver_brandsearch_pc</t>
         </is>
       </c>
       <c r="F94" t="inlineStr"/>
-      <c r="G94" t="inlineStr"/>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>kk_4831983348</t>
+          <t>kk_4831500868</t>
         </is>
       </c>
       <c r="B95" t="inlineStr"/>
       <c r="C95" t="inlineStr">
         <is>
-          <t>303621</t>
+          <t>303582</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>Awareness</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>benz_running_program_2026_coupon</t>
+          <t>6968489536332</t>
         </is>
       </c>
       <c r="F95" t="inlineStr"/>
-      <c r="G95" t="inlineStr"/>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>kk_4831986570</t>
+          <t>kk_4830922114</t>
         </is>
       </c>
       <c r="B96" t="inlineStr"/>
       <c r="C96" t="inlineStr">
         <is>
-          <t>303622</t>
+          <t>303563</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>Awareness</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>benz_running_program_2026_coupon</t>
+          <t>[PF]전환_회원가입(유사)</t>
         </is>
       </c>
       <c r="F96" t="inlineStr"/>
-      <c r="G96" t="inlineStr"/>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>kk_4831532519</t>
+          <t>kk_4832205664</t>
         </is>
       </c>
       <c r="B97" t="inlineStr"/>
       <c r="C97" t="inlineStr">
         <is>
-          <t>303587</t>
+          <t>303654</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>Awareness</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
@@ -2767,18 +2763,17 @@
         </is>
       </c>
       <c r="F97" t="inlineStr"/>
-      <c r="G97" t="inlineStr"/>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>kk_4832001343</t>
+          <t>kk_4831995357</t>
         </is>
       </c>
       <c r="B98" t="inlineStr"/>
       <c r="C98" t="inlineStr">
         <is>
-          <t>303625</t>
+          <t>303623</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
@@ -2792,18 +2787,17 @@
         </is>
       </c>
       <c r="F98" t="inlineStr"/>
-      <c r="G98" t="inlineStr"/>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>kk_4832061430</t>
+          <t>kk_4831768959</t>
         </is>
       </c>
       <c r="B99" t="inlineStr"/>
       <c r="C99" t="inlineStr">
         <is>
-          <t>303628</t>
+          <t>303602</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
@@ -2817,23 +2811,22 @@
         </is>
       </c>
       <c r="F99" t="inlineStr"/>
-      <c r="G99" t="inlineStr"/>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>kk_4832190692</t>
+          <t>kk_4831422357</t>
         </is>
       </c>
       <c r="B100" t="inlineStr"/>
       <c r="C100" t="inlineStr">
         <is>
-          <t>303649</t>
+          <t>303577</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>Awareness</t>
+          <t>Official SNS</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
@@ -2842,18 +2835,17 @@
         </is>
       </c>
       <c r="F100" t="inlineStr"/>
-      <c r="G100" t="inlineStr"/>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>kk_4831257396</t>
+          <t>kk_4830251299</t>
         </is>
       </c>
       <c r="B101" t="inlineStr"/>
       <c r="C101" t="inlineStr">
         <is>
-          <t>303571</t>
+          <t>303511</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
@@ -2867,43 +2859,41 @@
         </is>
       </c>
       <c r="F101" t="inlineStr"/>
-      <c r="G101" t="inlineStr"/>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>kk_4831468314</t>
+          <t>kk_4832105165</t>
         </is>
       </c>
       <c r="B102" t="inlineStr"/>
       <c r="C102" t="inlineStr">
         <is>
-          <t>303578</t>
+          <t>303636</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>Awareness</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>benz_running_program_2026_coupon</t>
+          <t>naver_brandsearch_mobile</t>
         </is>
       </c>
       <c r="F102" t="inlineStr"/>
-      <c r="G102" t="inlineStr"/>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>kk_4831951614</t>
+          <t>kk_4831842112</t>
         </is>
       </c>
       <c r="B103" t="inlineStr"/>
       <c r="C103" t="inlineStr">
         <is>
-          <t>303618</t>
+          <t>303613</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
@@ -2917,268 +2907,257 @@
         </is>
       </c>
       <c r="F103" t="inlineStr"/>
-      <c r="G103" t="inlineStr"/>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>kk_4832186210</t>
+          <t>kk_4830767555</t>
         </is>
       </c>
       <c r="B104" t="inlineStr"/>
       <c r="C104" t="inlineStr">
         <is>
-          <t>303648</t>
+          <t>303555</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>naver_brandsearch_mobile</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="F104" t="inlineStr"/>
-      <c r="G104" t="inlineStr"/>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>kk_4831774426</t>
+          <t>kk_4832248726</t>
         </is>
       </c>
       <c r="B105" t="inlineStr"/>
       <c r="C105" t="inlineStr">
         <is>
-          <t>303604</t>
+          <t>303658</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>naver_brandsearch_mobile</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="F105" t="inlineStr"/>
-      <c r="G105" t="inlineStr"/>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>kk_4831585022</t>
+          <t>kk_4831346086</t>
         </is>
       </c>
       <c r="B106" t="inlineStr"/>
       <c r="C106" t="inlineStr">
         <is>
-          <t>303591</t>
+          <t>303573</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>naver_brandsearch_mobile</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="F106" t="inlineStr"/>
-      <c r="G106" t="inlineStr"/>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>kk_4831822425</t>
+          <t>kk_4832180009</t>
         </is>
       </c>
       <c r="B107" t="inlineStr"/>
       <c r="C107" t="inlineStr">
         <is>
-          <t>303610</t>
+          <t>303647</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>naver_brandsearch_mobile</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="F107" t="inlineStr"/>
-      <c r="G107" t="inlineStr"/>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>kk_4831517271</t>
+          <t>kk_4831394790</t>
         </is>
       </c>
       <c r="B108" t="inlineStr"/>
       <c r="C108" t="inlineStr">
         <is>
-          <t>303584</t>
+          <t>303575</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>naver_brandsearch_mobile</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="F108" t="inlineStr"/>
-      <c r="G108" t="inlineStr"/>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>kk_4831723596</t>
+          <t>kk_4832023314</t>
         </is>
       </c>
       <c r="B109" t="inlineStr"/>
       <c r="C109" t="inlineStr">
         <is>
-          <t>303600</t>
+          <t>303626</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>naver_brandsearch_mobile</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="F109" t="inlineStr"/>
-      <c r="G109" t="inlineStr"/>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>kk_4831488942</t>
+          <t>kk_4830821550</t>
         </is>
       </c>
       <c r="B110" t="inlineStr"/>
       <c r="C110" t="inlineStr">
         <is>
-          <t>303580</t>
+          <t>303559</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>naver_brandsearch_pc</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="F110" t="inlineStr"/>
-      <c r="G110" t="inlineStr"/>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>minpark98</t>
+          <t>kk_4832114535</t>
         </is>
       </c>
       <c r="B111" t="inlineStr"/>
       <c r="C111" t="inlineStr">
         <is>
-          <t>303657</t>
+          <t>303637</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>naver_brandsearch_pc</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="F111" t="inlineStr"/>
-      <c r="G111" t="inlineStr"/>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>kk_4831600231</t>
+          <t>kk_4832076715</t>
         </is>
       </c>
       <c r="B112" t="inlineStr"/>
       <c r="C112" t="inlineStr">
         <is>
-          <t>303592</t>
+          <t>303629</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>sa</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="F112" t="inlineStr"/>
-      <c r="G112" t="inlineStr"/>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>kk_4831615271</t>
+          <t>kk_4832201164</t>
         </is>
       </c>
       <c r="B113" t="inlineStr"/>
       <c r="C113" t="inlineStr">
         <is>
-          <t>303594</t>
+          <t>303651</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>sa</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="F113" t="inlineStr"/>
-      <c r="G113" t="inlineStr"/>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>kk_4828653802</t>
+          <t>kk_4832164589</t>
         </is>
       </c>
       <c r="B114" t="inlineStr"/>
       <c r="C114" t="inlineStr">
         <is>
-          <t>303422</t>
+          <t>303645</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
@@ -3192,177 +3171,185 @@
         </is>
       </c>
       <c r="F114" t="inlineStr"/>
-      <c r="G114" t="inlineStr"/>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>kk_4829795736</t>
+          <t>kk_4831495694</t>
         </is>
       </c>
       <c r="B115" t="inlineStr"/>
       <c r="C115" t="inlineStr">
         <is>
-          <t>303489</t>
+          <t>303581</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>Direct</t>
-        </is>
-      </c>
-      <c r="E115" t="inlineStr"/>
+          <t>Organic Traffic</t>
+        </is>
+      </c>
+      <c r="E115" t="inlineStr">
+        <is>
+          <t>(organic)</t>
+        </is>
+      </c>
       <c r="F115" t="inlineStr"/>
-      <c r="G115" t="inlineStr"/>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>kk_3964942719</t>
+          <t>kk_4831649243</t>
         </is>
       </c>
       <c r="B116" t="inlineStr"/>
       <c r="C116" t="inlineStr">
         <is>
-          <t>270600</t>
+          <t>303595</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Organic Traffic</t>
         </is>
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>컬럼비아_DPA_240530</t>
+          <t>(referral)</t>
         </is>
       </c>
       <c r="F116" t="inlineStr"/>
-      <c r="G116" t="inlineStr"/>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>kk_4828995903</t>
+          <t>kk_4832078505</t>
         </is>
       </c>
       <c r="B117" t="inlineStr"/>
       <c r="C117" t="inlineStr">
         <is>
-          <t>303445</t>
+          <t>303630</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
-        </is>
-      </c>
-      <c r="E117" t="inlineStr"/>
+          <t>Organic Traffic</t>
+        </is>
+      </c>
+      <c r="E117" t="inlineStr">
+        <is>
+          <t>(referral)</t>
+        </is>
+      </c>
       <c r="F117" t="inlineStr"/>
-      <c r="G117" t="inlineStr"/>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>kk_4829109495</t>
+          <t>kk_4831340465</t>
         </is>
       </c>
       <c r="B118" t="inlineStr"/>
       <c r="C118" t="inlineStr">
         <is>
-          <t>303456</t>
+          <t>303572</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Organic Traffic</t>
         </is>
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>da</t>
+          <t>(referral)</t>
         </is>
       </c>
       <c r="F118" t="inlineStr"/>
-      <c r="G118" t="inlineStr"/>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>kk_4830615705</t>
+          <t>kk_4832100095</t>
         </is>
       </c>
       <c r="B119" t="inlineStr"/>
       <c r="C119" t="inlineStr">
         <is>
-          <t>303543</t>
+          <t>303634</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>Direct</t>
-        </is>
-      </c>
-      <c r="E119" t="inlineStr"/>
+          <t>Organic Traffic</t>
+        </is>
+      </c>
+      <c r="E119" t="inlineStr">
+        <is>
+          <t>(referral)</t>
+        </is>
+      </c>
       <c r="F119" t="inlineStr"/>
-      <c r="G119" t="inlineStr"/>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>kk_4830147171</t>
+          <t>kk_4832029124</t>
         </is>
       </c>
       <c r="B120" t="inlineStr"/>
       <c r="C120" t="inlineStr">
         <is>
-          <t>303506</t>
+          <t>303627</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>Direct</t>
-        </is>
-      </c>
-      <c r="E120" t="inlineStr"/>
+          <t>Organic Traffic</t>
+        </is>
+      </c>
+      <c r="E120" t="inlineStr">
+        <is>
+          <t>(referral)</t>
+        </is>
+      </c>
       <c r="F120" t="inlineStr"/>
-      <c r="G120" t="inlineStr"/>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>kk_4830462005</t>
+          <t>jambo8</t>
         </is>
       </c>
       <c r="B121" t="inlineStr"/>
       <c r="C121" t="inlineStr">
         <is>
-          <t>303523</t>
+          <t>303558</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Organic Traffic</t>
         </is>
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>6968489536332</t>
+          <t>(referral)</t>
         </is>
       </c>
       <c r="F121" t="inlineStr"/>
-      <c r="G121" t="inlineStr"/>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>kk_4829888934</t>
+          <t>kk_4832151833</t>
         </is>
       </c>
       <c r="B122" t="inlineStr"/>
       <c r="C122" t="inlineStr">
         <is>
-          <t>303493</t>
+          <t>303641</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
@@ -3372,97 +3359,93 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>EFW</t>
+          <t>6968489536332</t>
         </is>
       </c>
       <c r="F122" t="inlineStr"/>
-      <c r="G122" t="inlineStr"/>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>kk_4830585310</t>
+          <t>kk_4832202047</t>
         </is>
       </c>
       <c r="B123" t="inlineStr"/>
       <c r="C123" t="inlineStr">
         <is>
-          <t>303538</t>
+          <t>303652</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>Awareness</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>benz_running_program_2026_coupon</t>
+          <t>6968489536332</t>
         </is>
       </c>
       <c r="F123" t="inlineStr"/>
-      <c r="G123" t="inlineStr"/>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>kk_4830552074</t>
+          <t>kk_4831830576</t>
         </is>
       </c>
       <c r="B124" t="inlineStr"/>
       <c r="C124" t="inlineStr">
         <is>
-          <t>303534</t>
+          <t>303611</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>Awareness</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>benz_running_program_2026_coupon</t>
+          <t>6968489536332</t>
         </is>
       </c>
       <c r="F124" t="inlineStr"/>
-      <c r="G124" t="inlineStr"/>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>kk_4829567584</t>
+          <t>saty31</t>
         </is>
       </c>
       <c r="B125" t="inlineStr"/>
       <c r="C125" t="inlineStr">
         <is>
-          <t>303479</t>
+          <t>303561</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>naver_brandsearch_mobile</t>
+          <t>6968489536332</t>
         </is>
       </c>
       <c r="F125" t="inlineStr"/>
-      <c r="G125" t="inlineStr"/>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>kk_4829654698</t>
+          <t>jgj0503</t>
         </is>
       </c>
       <c r="B126" t="inlineStr"/>
       <c r="C126" t="inlineStr">
         <is>
-          <t>303481</t>
+          <t>303605</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
@@ -3472,231 +3455,237 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>컬럼비아_DPA_240530</t>
+          <t>6968489536332</t>
         </is>
       </c>
       <c r="F126" t="inlineStr"/>
-      <c r="G126" t="inlineStr"/>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>kk_4829843383</t>
+          <t>kk_4830989652</t>
         </is>
       </c>
       <c r="B127" t="inlineStr"/>
       <c r="C127" t="inlineStr">
         <is>
-          <t>303492</t>
+          <t>303569</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>Direct</t>
-        </is>
-      </c>
-      <c r="E127" t="inlineStr"/>
+          <t>Paid Ad</t>
+        </is>
+      </c>
+      <c r="E127" t="inlineStr">
+        <is>
+          <t>6968489536332</t>
+        </is>
+      </c>
       <c r="F127" t="inlineStr"/>
-      <c r="G127" t="inlineStr"/>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>kk_4830596422</t>
+          <t>kk_4832154317</t>
         </is>
       </c>
       <c r="B128" t="inlineStr"/>
       <c r="C128" t="inlineStr">
         <is>
-          <t>303540</t>
+          <t>303642</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>Direct</t>
-        </is>
-      </c>
-      <c r="E128" t="inlineStr"/>
+          <t>Paid Ad</t>
+        </is>
+      </c>
+      <c r="E128" t="inlineStr">
+        <is>
+          <t>EFW</t>
+        </is>
+      </c>
       <c r="F128" t="inlineStr"/>
-      <c r="G128" t="inlineStr"/>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>kk_4829899341</t>
+          <t>kk_4831922723</t>
         </is>
       </c>
       <c r="B129" t="inlineStr"/>
       <c r="C129" t="inlineStr">
         <is>
-          <t>303495</t>
+          <t>303617</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>Direct</t>
-        </is>
-      </c>
-      <c r="E129" t="inlineStr"/>
+          <t>Official SNS</t>
+        </is>
+      </c>
+      <c r="E129" t="inlineStr">
+        <is>
+          <t>EFW_04</t>
+        </is>
+      </c>
       <c r="F129" t="inlineStr"/>
-      <c r="G129" t="inlineStr"/>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>kk_4830179868</t>
+          <t>kk_4832125929</t>
         </is>
       </c>
       <c r="B130" t="inlineStr"/>
       <c r="C130" t="inlineStr">
         <is>
-          <t>303508</t>
+          <t>303638</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>Direct</t>
-        </is>
-      </c>
-      <c r="E130" t="inlineStr"/>
+          <t>Official SNS</t>
+        </is>
+      </c>
+      <c r="E130" t="inlineStr">
+        <is>
+          <t>EFW_04</t>
+        </is>
+      </c>
       <c r="F130" t="inlineStr"/>
-      <c r="G130" t="inlineStr"/>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>kk_4829500046</t>
+          <t>kk_4830836853</t>
         </is>
       </c>
       <c r="B131" t="inlineStr"/>
       <c r="C131" t="inlineStr">
         <is>
-          <t>303474</t>
+          <t>303560</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Official SNS</t>
         </is>
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>(organic)</t>
+          <t>EFW_04</t>
         </is>
       </c>
       <c r="F131" t="inlineStr"/>
-      <c r="G131" t="inlineStr"/>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>kk_4830568801</t>
+          <t>kk_4831850638</t>
         </is>
       </c>
       <c r="B132" t="inlineStr"/>
       <c r="C132" t="inlineStr">
         <is>
-          <t>303537</t>
+          <t>303615</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Official SNS</t>
         </is>
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>(organic)</t>
+          <t>EFW_04</t>
         </is>
       </c>
       <c r="F132" t="inlineStr"/>
-      <c r="G132" t="inlineStr"/>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>onoff</t>
+          <t>kk_4830778741</t>
         </is>
       </c>
       <c r="B133" t="inlineStr"/>
       <c r="C133" t="inlineStr">
         <is>
-          <t>303518</t>
+          <t>303556</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>Organic Traffic</t>
+          <t>Official SNS</t>
         </is>
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>(referral)</t>
+          <t>EFW_04</t>
         </is>
       </c>
       <c r="F133" t="inlineStr"/>
-      <c r="G133" t="inlineStr"/>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>kk_4829255442</t>
+          <t>kk_4830943389</t>
         </is>
       </c>
       <c r="B134" t="inlineStr"/>
       <c r="C134" t="inlineStr">
         <is>
-          <t>303464</t>
+          <t>303565</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>Organic Traffic</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>(referral)</t>
+          <t>KAKAO_alimtalk</t>
         </is>
       </c>
       <c r="F134" t="inlineStr"/>
-      <c r="G134" t="inlineStr"/>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>kk_4829755741</t>
+          <t>kk_4831612250</t>
         </is>
       </c>
       <c r="B135" t="inlineStr"/>
       <c r="C135" t="inlineStr">
         <is>
-          <t>303486</t>
+          <t>303593</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>Organic Traffic</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>(referral)</t>
+          <t>[PF]A SC_상시(1865MF,구매 장바구니)</t>
         </is>
       </c>
       <c r="F135" t="inlineStr"/>
-      <c r="G135" t="inlineStr"/>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>kk_4830404781</t>
+          <t>kk_4830988405</t>
         </is>
       </c>
       <c r="B136" t="inlineStr"/>
       <c r="C136" t="inlineStr">
         <is>
-          <t>303521</t>
+          <t>303567</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
@@ -3706,322 +3695,309 @@
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>6968489536332</t>
+          <t>[PF]전환_상시(2565MF,비구매자)</t>
         </is>
       </c>
       <c r="F136" t="inlineStr"/>
-      <c r="G136" t="inlineStr"/>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>kk_4830692253</t>
+          <t>kk_4831532519</t>
         </is>
       </c>
       <c r="B137" t="inlineStr"/>
       <c r="C137" t="inlineStr">
         <is>
-          <t>303550</t>
+          <t>303587</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Awareness</t>
         </is>
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>6968489536332</t>
+          <t>benz_running_program_2026_coupon</t>
         </is>
       </c>
       <c r="F137" t="inlineStr"/>
-      <c r="G137" t="inlineStr"/>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>kk_4829674741</t>
+          <t>kk_4831986570</t>
         </is>
       </c>
       <c r="B138" t="inlineStr"/>
       <c r="C138" t="inlineStr">
         <is>
-          <t>303484</t>
+          <t>303622</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Awareness</t>
         </is>
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>6968489536332</t>
+          <t>benz_running_program_2026_coupon</t>
         </is>
       </c>
       <c r="F138" t="inlineStr"/>
-      <c r="G138" t="inlineStr"/>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>kk_4830541132</t>
+          <t>kk_4832100101</t>
         </is>
       </c>
       <c r="B139" t="inlineStr"/>
       <c r="C139" t="inlineStr">
         <is>
-          <t>303533</t>
+          <t>303635</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Awareness</t>
         </is>
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>6968489536332</t>
+          <t>benz_running_program_2026_coupon</t>
         </is>
       </c>
       <c r="F139" t="inlineStr"/>
-      <c r="G139" t="inlineStr"/>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>kk_4830409260</t>
+          <t>kk_4831981914</t>
         </is>
       </c>
       <c r="B140" t="inlineStr"/>
       <c r="C140" t="inlineStr">
         <is>
-          <t>303522</t>
+          <t>303620</t>
         </is>
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Awareness</t>
         </is>
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>6968489536332</t>
+          <t>benz_running_program_2026_coupon</t>
         </is>
       </c>
       <c r="F140" t="inlineStr"/>
-      <c r="G140" t="inlineStr"/>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>kk_4830646394</t>
+          <t>kk_4831799020</t>
         </is>
       </c>
       <c r="B141" t="inlineStr"/>
       <c r="C141" t="inlineStr">
         <is>
-          <t>303547</t>
+          <t>303609</t>
         </is>
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Awareness</t>
         </is>
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>6968489536332</t>
+          <t>benz_running_program_2026_coupon</t>
         </is>
       </c>
       <c r="F141" t="inlineStr"/>
-      <c r="G141" t="inlineStr"/>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>kk_4829999849</t>
+          <t>kk_4831983348</t>
         </is>
       </c>
       <c r="B142" t="inlineStr"/>
       <c r="C142" t="inlineStr">
         <is>
-          <t>303498</t>
+          <t>303621</t>
         </is>
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Awareness</t>
         </is>
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>6968489536332</t>
+          <t>benz_running_program_2026_coupon</t>
         </is>
       </c>
       <c r="F142" t="inlineStr"/>
-      <c r="G142" t="inlineStr"/>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>akita1129</t>
+          <t>kk_4832061430</t>
         </is>
       </c>
       <c r="B143" t="inlineStr"/>
       <c r="C143" t="inlineStr">
         <is>
-          <t>303465</t>
+          <t>303628</t>
         </is>
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Awareness</t>
         </is>
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>EFW</t>
+          <t>benz_running_program_2026_coupon</t>
         </is>
       </c>
       <c r="F143" t="inlineStr"/>
-      <c r="G143" t="inlineStr"/>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>kk_4830264628</t>
+          <t>kk_4832001343</t>
         </is>
       </c>
       <c r="B144" t="inlineStr"/>
       <c r="C144" t="inlineStr">
         <is>
-          <t>303514</t>
+          <t>303625</t>
         </is>
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>Official SNS</t>
+          <t>Awareness</t>
         </is>
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>EFW_04</t>
+          <t>benz_running_program_2026_coupon</t>
         </is>
       </c>
       <c r="F144" t="inlineStr"/>
-      <c r="G144" t="inlineStr"/>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>kk_4829543360</t>
+          <t>kk_4831502482</t>
         </is>
       </c>
       <c r="B145" t="inlineStr"/>
       <c r="C145" t="inlineStr">
         <is>
-          <t>303478</t>
+          <t>303583</t>
         </is>
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>Official SNS</t>
+          <t>Awareness</t>
         </is>
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>EFW_04</t>
+          <t>benz_running_program_2026_coupon</t>
         </is>
       </c>
       <c r="F145" t="inlineStr"/>
-      <c r="G145" t="inlineStr"/>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>kk_4830559393</t>
+          <t>kk_4831257396</t>
         </is>
       </c>
       <c r="B146" t="inlineStr"/>
       <c r="C146" t="inlineStr">
         <is>
-          <t>303535</t>
+          <t>303571</t>
         </is>
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>Official SNS</t>
+          <t>Awareness</t>
         </is>
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>EFW_04</t>
+          <t>benz_running_program_2026_coupon</t>
         </is>
       </c>
       <c r="F146" t="inlineStr"/>
-      <c r="G146" t="inlineStr"/>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>mong81</t>
+          <t>kk_4832190692</t>
         </is>
       </c>
       <c r="B147" t="inlineStr"/>
       <c r="C147" t="inlineStr">
         <is>
-          <t>303505</t>
+          <t>303649</t>
         </is>
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>Official SNS</t>
+          <t>Awareness</t>
         </is>
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>EFW_04</t>
+          <t>benz_running_program_2026_coupon</t>
         </is>
       </c>
       <c r="F147" t="inlineStr"/>
-      <c r="G147" t="inlineStr"/>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>kk_4830253885</t>
+          <t>kk_4831997957</t>
         </is>
       </c>
       <c r="B148" t="inlineStr"/>
       <c r="C148" t="inlineStr">
         <is>
-          <t>303512</t>
+          <t>303624</t>
         </is>
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Awareness</t>
         </is>
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>KAKAO_CH_MENU_0211_NEW_WOMEN</t>
+          <t>benz_running_program_2026_coupon</t>
         </is>
       </c>
       <c r="F148" t="inlineStr"/>
-      <c r="G148" t="inlineStr"/>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>kk_4829512827</t>
+          <t>kk_4832186210</t>
         </is>
       </c>
       <c r="B149" t="inlineStr"/>
       <c r="C149" t="inlineStr">
         <is>
-          <t>303475</t>
+          <t>303648</t>
         </is>
       </c>
       <c r="D149" t="inlineStr">
@@ -4031,272 +4007,261 @@
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>[PF]전환_회원가입(유사)</t>
+          <t>naver_brandsearch_mobile</t>
         </is>
       </c>
       <c r="F149" t="inlineStr"/>
-      <c r="G149" t="inlineStr"/>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>kk_4830308577</t>
+          <t>kk_4831774426</t>
         </is>
       </c>
       <c r="B150" t="inlineStr"/>
       <c r="C150" t="inlineStr">
         <is>
-          <t>303516</t>
+          <t>303604</t>
         </is>
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>Awareness</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>benz_running_program_2026_coupon</t>
+          <t>naver_brandsearch_mobile</t>
         </is>
       </c>
       <c r="F150" t="inlineStr"/>
-      <c r="G150" t="inlineStr"/>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>kk_4830722522</t>
+          <t>kk_4831822425</t>
         </is>
       </c>
       <c r="B151" t="inlineStr"/>
       <c r="C151" t="inlineStr">
         <is>
-          <t>303553</t>
+          <t>303610</t>
         </is>
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>Awareness</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>benz_running_program_2026_coupon</t>
+          <t>naver_brandsearch_mobile</t>
         </is>
       </c>
       <c r="F151" t="inlineStr"/>
-      <c r="G151" t="inlineStr"/>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>kk_4830704540</t>
+          <t>kk_4831723596</t>
         </is>
       </c>
       <c r="B152" t="inlineStr"/>
       <c r="C152" t="inlineStr">
         <is>
-          <t>303551</t>
+          <t>303600</t>
         </is>
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>Awareness</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>benz_running_program_2026_coupon</t>
+          <t>naver_brandsearch_mobile</t>
         </is>
       </c>
       <c r="F152" t="inlineStr"/>
-      <c r="G152" t="inlineStr"/>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>kk_4830497611</t>
+          <t>kk_4831951614</t>
         </is>
       </c>
       <c r="B153" t="inlineStr"/>
       <c r="C153" t="inlineStr">
         <is>
-          <t>303526</t>
+          <t>303618</t>
         </is>
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>Awareness</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t>benz_running_program_2026_coupon</t>
+          <t>naver_brandsearch_mobile</t>
         </is>
       </c>
       <c r="F153" t="inlineStr"/>
-      <c r="G153" t="inlineStr"/>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>flydabi</t>
+          <t>kk_4831585022</t>
         </is>
       </c>
       <c r="B154" t="inlineStr"/>
       <c r="C154" t="inlineStr">
         <is>
-          <t>303531</t>
+          <t>303591</t>
         </is>
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t>Awareness</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E154" t="inlineStr">
         <is>
-          <t>benz_running_program_2026_coupon</t>
+          <t>naver_brandsearch_mobile</t>
         </is>
       </c>
       <c r="F154" t="inlineStr"/>
-      <c r="G154" t="inlineStr"/>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>kk_4830376206</t>
+          <t>kk_4831517271</t>
         </is>
       </c>
       <c r="B155" t="inlineStr"/>
       <c r="C155" t="inlineStr">
         <is>
-          <t>303520</t>
+          <t>303584</t>
         </is>
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>Awareness</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t>benz_running_program_2026_coupon</t>
+          <t>naver_brandsearch_mobile</t>
         </is>
       </c>
       <c r="F155" t="inlineStr"/>
-      <c r="G155" t="inlineStr"/>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>kk_4830637852</t>
+          <t>minpark98</t>
         </is>
       </c>
       <c r="B156" t="inlineStr"/>
       <c r="C156" t="inlineStr">
         <is>
-          <t>303546</t>
+          <t>303657</t>
         </is>
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t>Awareness</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t>benz_running_program_2026_coupon</t>
+          <t>naver_brandsearch_pc</t>
         </is>
       </c>
       <c r="F156" t="inlineStr"/>
-      <c r="G156" t="inlineStr"/>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>kk_4830659012</t>
+          <t>kk_4831488942</t>
         </is>
       </c>
       <c r="B157" t="inlineStr"/>
       <c r="C157" t="inlineStr">
         <is>
-          <t>303549</t>
+          <t>303580</t>
         </is>
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>Awareness</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E157" t="inlineStr">
         <is>
-          <t>benz_running_program_2026_coupon</t>
+          <t>naver_brandsearch_pc</t>
         </is>
       </c>
       <c r="F157" t="inlineStr"/>
-      <c r="G157" t="inlineStr"/>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>kk_4830597347</t>
+          <t>kk_4831615271</t>
         </is>
       </c>
       <c r="B158" t="inlineStr"/>
       <c r="C158" t="inlineStr">
         <is>
-          <t>303541</t>
+          <t>303594</t>
         </is>
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>Awareness</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E158" t="inlineStr">
         <is>
-          <t>benz_running_program_2026_coupon</t>
+          <t>sa</t>
         </is>
       </c>
       <c r="F158" t="inlineStr"/>
-      <c r="G158" t="inlineStr"/>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>kk_4830760298</t>
+          <t>kk_4831600231</t>
         </is>
       </c>
       <c r="B159" t="inlineStr"/>
       <c r="C159" t="inlineStr">
         <is>
-          <t>303554</t>
+          <t>303592</t>
         </is>
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>Awareness</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E159" t="inlineStr">
         <is>
-          <t>benz_running_program_2026​</t>
+          <t>sa</t>
         </is>
       </c>
       <c r="F159" t="inlineStr"/>
-      <c r="G159" t="inlineStr"/>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>kk_4830212469</t>
+          <t>kk_3964942719</t>
         </is>
       </c>
       <c r="B160" t="inlineStr"/>
       <c r="C160" t="inlineStr">
         <is>
-          <t>303509</t>
+          <t>270600</t>
         </is>
       </c>
       <c r="D160" t="inlineStr">
@@ -4306,72 +4271,69 @@
       </c>
       <c r="E160" t="inlineStr">
         <is>
-          <t>da</t>
+          <t>컬럼비아_DPA_240530</t>
         </is>
       </c>
       <c r="F160" t="inlineStr"/>
-      <c r="G160" t="inlineStr"/>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>kk_4830137292</t>
+          <t>kk_4830147171</t>
         </is>
       </c>
       <c r="B161" t="inlineStr"/>
       <c r="C161" t="inlineStr">
         <is>
-          <t>303504</t>
+          <t>303506</t>
         </is>
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="E161" t="inlineStr">
         <is>
-          <t>naver_brandsearch_mobile</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="F161" t="inlineStr"/>
-      <c r="G161" t="inlineStr"/>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>kk_4830540435</t>
+          <t>kk_4830615705</t>
         </is>
       </c>
       <c r="B162" t="inlineStr"/>
       <c r="C162" t="inlineStr">
         <is>
-          <t>303532</t>
+          <t>303543</t>
         </is>
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="E162" t="inlineStr">
         <is>
-          <t>naver_brandsearch_mobile</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="F162" t="inlineStr"/>
-      <c r="G162" t="inlineStr"/>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>susaeg202</t>
+          <t>kk_4830462005</t>
         </is>
       </c>
       <c r="B163" t="inlineStr"/>
       <c r="C163" t="inlineStr">
         <is>
-          <t>303469</t>
+          <t>303523</t>
         </is>
       </c>
       <c r="D163" t="inlineStr">
@@ -4381,218 +4343,213 @@
       </c>
       <c r="E163" t="inlineStr">
         <is>
-          <t>naver_brandsearch_pc</t>
+          <t>6968489536332</t>
         </is>
       </c>
       <c r="F163" t="inlineStr"/>
-      <c r="G163" t="inlineStr"/>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>kk_4830179048</t>
+          <t>kk_4830552074</t>
         </is>
       </c>
       <c r="B164" t="inlineStr"/>
       <c r="C164" t="inlineStr">
         <is>
-          <t>303507</t>
+          <t>303534</t>
         </is>
       </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Awareness</t>
         </is>
       </c>
       <c r="E164" t="inlineStr">
         <is>
-          <t>naversa_mo</t>
+          <t>benz_running_program_2026_coupon</t>
         </is>
       </c>
       <c r="F164" t="inlineStr"/>
-      <c r="G164" t="inlineStr"/>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>kk_4829761376</t>
+          <t>kk_4830585310</t>
         </is>
       </c>
       <c r="B165" t="inlineStr"/>
       <c r="C165" t="inlineStr">
         <is>
-          <t>303487</t>
+          <t>303538</t>
         </is>
       </c>
       <c r="D165" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Awareness</t>
         </is>
       </c>
       <c r="E165" t="inlineStr">
         <is>
-          <t>naversa_mo</t>
+          <t>benz_running_program_2026_coupon</t>
         </is>
       </c>
       <c r="F165" t="inlineStr"/>
-      <c r="G165" t="inlineStr"/>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>kk_4828679899</t>
+          <t>kk_4830179868</t>
         </is>
       </c>
       <c r="B166" t="inlineStr"/>
       <c r="C166" t="inlineStr">
         <is>
-          <t>303425</t>
+          <t>303508</t>
         </is>
       </c>
       <c r="D166" t="inlineStr">
         <is>
-          <t>Official SNS</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="E166" t="inlineStr">
         <is>
-          <t>EFW_04</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="F166" t="inlineStr"/>
-      <c r="G166" t="inlineStr"/>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>kk_4828662042</t>
+          <t>kk_4830596422</t>
         </is>
       </c>
       <c r="B167" t="inlineStr"/>
       <c r="C167" t="inlineStr">
         <is>
-          <t>303423</t>
+          <t>303540</t>
         </is>
       </c>
       <c r="D167" t="inlineStr">
         <is>
-          <t>Awareness</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="E167" t="inlineStr">
         <is>
-          <t>benz_running_program_2026_coupon</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="F167" t="inlineStr"/>
-      <c r="G167" t="inlineStr"/>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>kk_4828953106</t>
+          <t>kk_4830568801</t>
         </is>
       </c>
       <c r="B168" t="inlineStr"/>
       <c r="C168" t="inlineStr">
         <is>
-          <t>303440</t>
+          <t>303537</t>
         </is>
       </c>
       <c r="D168" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E168" t="inlineStr">
         <is>
-          <t>benz_running_program_2026_coupon</t>
+          <t>(organic)</t>
         </is>
       </c>
       <c r="F168" t="inlineStr"/>
-      <c r="G168" t="inlineStr"/>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>kk_4828776483</t>
+          <t>onoff</t>
         </is>
       </c>
       <c r="B169" t="inlineStr"/>
       <c r="C169" t="inlineStr">
         <is>
-          <t>303428</t>
+          <t>303518</t>
         </is>
       </c>
       <c r="D169" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Organic Traffic</t>
         </is>
       </c>
       <c r="E169" t="inlineStr">
         <is>
-          <t>naver_brandsearch_mobile</t>
+          <t>(referral)</t>
         </is>
       </c>
       <c r="F169" t="inlineStr"/>
-      <c r="G169" t="inlineStr"/>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>kk_4829004394</t>
+          <t>kk_4829999849</t>
         </is>
       </c>
       <c r="B170" t="inlineStr"/>
       <c r="C170" t="inlineStr">
         <is>
-          <t>303447</t>
+          <t>303498</t>
         </is>
       </c>
       <c r="D170" t="inlineStr">
         <is>
-          <t>Direct</t>
-        </is>
-      </c>
-      <c r="E170" t="inlineStr"/>
+          <t>Paid Ad</t>
+        </is>
+      </c>
+      <c r="E170" t="inlineStr">
+        <is>
+          <t>6968489536332</t>
+        </is>
+      </c>
       <c r="F170" t="inlineStr"/>
-      <c r="G170" t="inlineStr"/>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>kk_4829016429</t>
+          <t>kk_4830692253</t>
         </is>
       </c>
       <c r="B171" t="inlineStr"/>
       <c r="C171" t="inlineStr">
         <is>
-          <t>303450</t>
+          <t>303550</t>
         </is>
       </c>
       <c r="D171" t="inlineStr">
         <is>
-          <t>Organic Traffic</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E171" t="inlineStr">
         <is>
-          <t>(organic)</t>
+          <t>6968489536332</t>
         </is>
       </c>
       <c r="F171" t="inlineStr"/>
-      <c r="G171" t="inlineStr"/>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>kk_4828870663</t>
+          <t>kk_4830409260</t>
         </is>
       </c>
       <c r="B172" t="inlineStr"/>
       <c r="C172" t="inlineStr">
         <is>
-          <t>303434</t>
+          <t>303522</t>
         </is>
       </c>
       <c r="D172" t="inlineStr">
@@ -4602,22 +4559,21 @@
       </c>
       <c r="E172" t="inlineStr">
         <is>
-          <t>(organic)</t>
+          <t>6968489536332</t>
         </is>
       </c>
       <c r="F172" t="inlineStr"/>
-      <c r="G172" t="inlineStr"/>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>kk_4828853669</t>
+          <t>kk_4830404781</t>
         </is>
       </c>
       <c r="B173" t="inlineStr"/>
       <c r="C173" t="inlineStr">
         <is>
-          <t>303431</t>
+          <t>303521</t>
         </is>
       </c>
       <c r="D173" t="inlineStr">
@@ -4627,47 +4583,45 @@
       </c>
       <c r="E173" t="inlineStr">
         <is>
-          <t>(organic)</t>
+          <t>6968489536332</t>
         </is>
       </c>
       <c r="F173" t="inlineStr"/>
-      <c r="G173" t="inlineStr"/>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>kk_4829012080</t>
+          <t>kk_4830646394</t>
         </is>
       </c>
       <c r="B174" t="inlineStr"/>
       <c r="C174" t="inlineStr">
         <is>
-          <t>303448</t>
+          <t>303547</t>
         </is>
       </c>
       <c r="D174" t="inlineStr">
         <is>
-          <t>Organic Traffic</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E174" t="inlineStr">
         <is>
-          <t>(referral)</t>
+          <t>6968489536332</t>
         </is>
       </c>
       <c r="F174" t="inlineStr"/>
-      <c r="G174" t="inlineStr"/>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>gee04171</t>
+          <t>kk_4830541132</t>
         </is>
       </c>
       <c r="B175" t="inlineStr"/>
       <c r="C175" t="inlineStr">
         <is>
-          <t>303449</t>
+          <t>303533</t>
         </is>
       </c>
       <c r="D175" t="inlineStr">
@@ -4681,168 +4635,161 @@
         </is>
       </c>
       <c r="F175" t="inlineStr"/>
-      <c r="G175" t="inlineStr"/>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>kk_4829143684</t>
+          <t>kk_4830559393</t>
         </is>
       </c>
       <c r="B176" t="inlineStr"/>
       <c r="C176" t="inlineStr">
         <is>
-          <t>303458</t>
+          <t>303535</t>
         </is>
       </c>
       <c r="D176" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Official SNS</t>
         </is>
       </c>
       <c r="E176" t="inlineStr">
         <is>
-          <t>6968489536332</t>
+          <t>EFW_04</t>
         </is>
       </c>
       <c r="F176" t="inlineStr"/>
-      <c r="G176" t="inlineStr"/>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>kk_4828900771</t>
+          <t>mong81</t>
         </is>
       </c>
       <c r="B177" t="inlineStr"/>
       <c r="C177" t="inlineStr">
         <is>
-          <t>303438</t>
+          <t>303505</t>
         </is>
       </c>
       <c r="D177" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Official SNS</t>
         </is>
       </c>
       <c r="E177" t="inlineStr">
         <is>
-          <t>6968489536332</t>
+          <t>EFW_04</t>
         </is>
       </c>
       <c r="F177" t="inlineStr"/>
-      <c r="G177" t="inlineStr"/>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>kk_4828729325</t>
+          <t>kk_4830264628</t>
         </is>
       </c>
       <c r="B178" t="inlineStr"/>
       <c r="C178" t="inlineStr">
         <is>
-          <t>303426</t>
+          <t>303514</t>
         </is>
       </c>
       <c r="D178" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Official SNS</t>
         </is>
       </c>
       <c r="E178" t="inlineStr">
         <is>
-          <t>EFW</t>
+          <t>EFW_04</t>
         </is>
       </c>
       <c r="F178" t="inlineStr"/>
-      <c r="G178" t="inlineStr"/>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>kk_4828995176</t>
+          <t>kk_4830253885</t>
         </is>
       </c>
       <c r="B179" t="inlineStr"/>
       <c r="C179" t="inlineStr">
         <is>
-          <t>303444</t>
+          <t>303512</t>
         </is>
       </c>
       <c r="D179" t="inlineStr">
         <is>
-          <t>Official SNS</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E179" t="inlineStr">
         <is>
-          <t>Heritage</t>
+          <t>KAKAO_CH_MENU_0211_NEW_WOMEN</t>
         </is>
       </c>
       <c r="F179" t="inlineStr"/>
-      <c r="G179" t="inlineStr"/>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>kk_4828781963</t>
+          <t>kk_4830704540</t>
         </is>
       </c>
       <c r="B180" t="inlineStr"/>
       <c r="C180" t="inlineStr">
         <is>
-          <t>303429</t>
+          <t>303551</t>
         </is>
       </c>
       <c r="D180" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Awareness</t>
         </is>
       </c>
       <c r="E180" t="inlineStr">
         <is>
-          <t>KAKAO_CH_MESSAGE_0325_S26NEW_CTA</t>
+          <t>benz_running_program_2026_coupon</t>
         </is>
       </c>
       <c r="F180" t="inlineStr"/>
-      <c r="G180" t="inlineStr"/>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>kk_4829073557</t>
+          <t>kk_4830497611</t>
         </is>
       </c>
       <c r="B181" t="inlineStr"/>
       <c r="C181" t="inlineStr">
         <is>
-          <t>303452</t>
+          <t>303526</t>
         </is>
       </c>
       <c r="D181" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Awareness</t>
         </is>
       </c>
       <c r="E181" t="inlineStr">
         <is>
-          <t>[PF]전환_회원가입(유사)</t>
+          <t>benz_running_program_2026_coupon</t>
         </is>
       </c>
       <c r="F181" t="inlineStr"/>
-      <c r="G181" t="inlineStr"/>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>kk_4828671248</t>
+          <t>kk_4830637852</t>
         </is>
       </c>
       <c r="B182" t="inlineStr"/>
       <c r="C182" t="inlineStr">
         <is>
-          <t>303424</t>
+          <t>303546</t>
         </is>
       </c>
       <c r="D182" t="inlineStr">
@@ -4856,18 +4803,17 @@
         </is>
       </c>
       <c r="F182" t="inlineStr"/>
-      <c r="G182" t="inlineStr"/>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>kk_4828876907</t>
+          <t>kk_4830597347</t>
         </is>
       </c>
       <c r="B183" t="inlineStr"/>
       <c r="C183" t="inlineStr">
         <is>
-          <t>303436</t>
+          <t>303541</t>
         </is>
       </c>
       <c r="D183" t="inlineStr">
@@ -4881,18 +4827,17 @@
         </is>
       </c>
       <c r="F183" t="inlineStr"/>
-      <c r="G183" t="inlineStr"/>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>kk_4829107379</t>
+          <t>flydabi</t>
         </is>
       </c>
       <c r="B184" t="inlineStr"/>
       <c r="C184" t="inlineStr">
         <is>
-          <t>303455</t>
+          <t>303531</t>
         </is>
       </c>
       <c r="D184" t="inlineStr">
@@ -4906,18 +4851,17 @@
         </is>
       </c>
       <c r="F184" t="inlineStr"/>
-      <c r="G184" t="inlineStr"/>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>kk_4829201314</t>
+          <t>kk_4830376206</t>
         </is>
       </c>
       <c r="B185" t="inlineStr"/>
       <c r="C185" t="inlineStr">
         <is>
-          <t>303461</t>
+          <t>303520</t>
         </is>
       </c>
       <c r="D185" t="inlineStr">
@@ -4931,107 +4875,174 @@
         </is>
       </c>
       <c r="F185" t="inlineStr"/>
-      <c r="G185" t="inlineStr"/>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>kk_4828903098</t>
+          <t>kk_4830308577</t>
         </is>
       </c>
       <c r="B186" t="inlineStr"/>
       <c r="C186" t="inlineStr">
         <is>
-          <t>303439</t>
+          <t>303516</t>
         </is>
       </c>
       <c r="D186" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Awareness</t>
         </is>
       </c>
       <c r="E186" t="inlineStr">
         <is>
-          <t>naver_brandsearch_mobile</t>
+          <t>benz_running_program_2026_coupon</t>
         </is>
       </c>
       <c r="F186" t="inlineStr"/>
-      <c r="G186" t="inlineStr"/>
     </row>
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>kk_4828872529</t>
+          <t>kk_4830659012</t>
         </is>
       </c>
       <c r="B187" t="inlineStr"/>
       <c r="C187" t="inlineStr">
         <is>
-          <t>303435</t>
+          <t>303549</t>
         </is>
       </c>
       <c r="D187" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Awareness</t>
         </is>
       </c>
       <c r="E187" t="inlineStr">
         <is>
-          <t>naver_brandsearch_mobile</t>
+          <t>benz_running_program_2026_coupon</t>
         </is>
       </c>
       <c r="F187" t="inlineStr"/>
-      <c r="G187" t="inlineStr"/>
     </row>
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>kk_4828987324</t>
+          <t>kk_4830722522</t>
         </is>
       </c>
       <c r="B188" t="inlineStr"/>
       <c r="C188" t="inlineStr">
         <is>
-          <t>303443</t>
+          <t>303553</t>
         </is>
       </c>
       <c r="D188" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Awareness</t>
         </is>
       </c>
       <c r="E188" t="inlineStr">
         <is>
-          <t>naversa_mo</t>
+          <t>benz_running_program_2026_coupon</t>
         </is>
       </c>
       <c r="F188" t="inlineStr"/>
-      <c r="G188" t="inlineStr"/>
     </row>
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>kk_4828986759</t>
+          <t>kk_4830760298</t>
         </is>
       </c>
       <c r="B189" t="inlineStr"/>
       <c r="C189" t="inlineStr">
         <is>
-          <t>303442</t>
+          <t>303554</t>
         </is>
       </c>
       <c r="D189" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Awareness</t>
         </is>
       </c>
       <c r="E189" t="inlineStr">
         <is>
+          <t>benz_running_program_2026​</t>
+        </is>
+      </c>
+      <c r="F189" t="inlineStr"/>
+    </row>
+    <row r="190">
+      <c r="A190" t="inlineStr">
+        <is>
+          <t>kk_4830137292</t>
+        </is>
+      </c>
+      <c r="B190" t="inlineStr"/>
+      <c r="C190" t="inlineStr">
+        <is>
+          <t>303504</t>
+        </is>
+      </c>
+      <c r="D190" t="inlineStr">
+        <is>
+          <t>Paid Ad</t>
+        </is>
+      </c>
+      <c r="E190" t="inlineStr">
+        <is>
+          <t>naver_brandsearch_mobile</t>
+        </is>
+      </c>
+      <c r="F190" t="inlineStr"/>
+    </row>
+    <row r="191">
+      <c r="A191" t="inlineStr">
+        <is>
+          <t>kk_4830540435</t>
+        </is>
+      </c>
+      <c r="B191" t="inlineStr"/>
+      <c r="C191" t="inlineStr">
+        <is>
+          <t>303532</t>
+        </is>
+      </c>
+      <c r="D191" t="inlineStr">
+        <is>
+          <t>Paid Ad</t>
+        </is>
+      </c>
+      <c r="E191" t="inlineStr">
+        <is>
+          <t>naver_brandsearch_mobile</t>
+        </is>
+      </c>
+      <c r="F191" t="inlineStr"/>
+    </row>
+    <row r="192">
+      <c r="A192" t="inlineStr">
+        <is>
+          <t>kk_4830179048</t>
+        </is>
+      </c>
+      <c r="B192" t="inlineStr"/>
+      <c r="C192" t="inlineStr">
+        <is>
+          <t>303507</t>
+        </is>
+      </c>
+      <c r="D192" t="inlineStr">
+        <is>
+          <t>Paid Ad</t>
+        </is>
+      </c>
+      <c r="E192" t="inlineStr">
+        <is>
           <t>naversa_mo</t>
         </is>
       </c>
-      <c r="F189" t="inlineStr"/>
-      <c r="G189" t="inlineStr"/>
+      <c r="F192" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/reports/member_funnel/downloads/member_funnel_7d_non_buyer.xlsx
+++ b/reports/member_funnel/downloads/member_funnel_7d_non_buyer.xlsx
@@ -799,13 +799,13 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>kk_4833894015</t>
+          <t>kk_4833753902</t>
         </is>
       </c>
       <c r="B16" t="inlineStr"/>
       <c r="C16" t="inlineStr">
         <is>
-          <t>303761</t>
+          <t>303747</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -847,13 +847,13 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>kk_4833753902</t>
+          <t>kk_4833894015</t>
         </is>
       </c>
       <c r="B18" t="inlineStr"/>
       <c r="C18" t="inlineStr">
         <is>
-          <t>303747</t>
+          <t>303761</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -1039,13 +1039,13 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>kk_4832656308</t>
+          <t>kk_4832648970</t>
         </is>
       </c>
       <c r="B26" t="inlineStr"/>
       <c r="C26" t="inlineStr">
         <is>
-          <t>303679</t>
+          <t>303678</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -1063,13 +1063,13 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>kk_4832738942</t>
+          <t>kk_4832656308</t>
         </is>
       </c>
       <c r="B27" t="inlineStr"/>
       <c r="C27" t="inlineStr">
         <is>
-          <t>303683</t>
+          <t>303679</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -1087,13 +1087,13 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>kk_4833682381</t>
+          <t>arumabc</t>
         </is>
       </c>
       <c r="B28" t="inlineStr"/>
       <c r="C28" t="inlineStr">
         <is>
-          <t>303739</t>
+          <t>303689</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -1111,13 +1111,13 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>whitehole147</t>
+          <t>kk_4833682381</t>
         </is>
       </c>
       <c r="B29" t="inlineStr"/>
       <c r="C29" t="inlineStr">
         <is>
-          <t>303673</t>
+          <t>303739</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -1135,13 +1135,13 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>kk_4833013784</t>
+          <t>kk_4832738942</t>
         </is>
       </c>
       <c r="B30" t="inlineStr"/>
       <c r="C30" t="inlineStr">
         <is>
-          <t>303703</t>
+          <t>303683</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -1159,13 +1159,13 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>kk_4833797203</t>
+          <t>kk_4833013784</t>
         </is>
       </c>
       <c r="B31" t="inlineStr"/>
       <c r="C31" t="inlineStr">
         <is>
-          <t>303750</t>
+          <t>303703</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -1183,13 +1183,13 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>kk_4832648970</t>
+          <t>kk_4833797203</t>
         </is>
       </c>
       <c r="B32" t="inlineStr"/>
       <c r="C32" t="inlineStr">
         <is>
-          <t>303678</t>
+          <t>303750</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -1207,13 +1207,13 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>arumabc</t>
+          <t>whitehole147</t>
         </is>
       </c>
       <c r="B33" t="inlineStr"/>
       <c r="C33" t="inlineStr">
         <is>
-          <t>303689</t>
+          <t>303673</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -1255,13 +1255,13 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>kk_4833617385</t>
+          <t>lily50</t>
         </is>
       </c>
       <c r="B35" t="inlineStr"/>
       <c r="C35" t="inlineStr">
         <is>
-          <t>303734</t>
+          <t>303714</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -1303,13 +1303,13 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>lily50</t>
+          <t>kk_4833617385</t>
         </is>
       </c>
       <c r="B37" t="inlineStr"/>
       <c r="C37" t="inlineStr">
         <is>
-          <t>303714</t>
+          <t>303734</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -1351,13 +1351,13 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>kk_4833397488</t>
+          <t>kk_4832564458</t>
         </is>
       </c>
       <c r="B39" t="inlineStr"/>
       <c r="C39" t="inlineStr">
         <is>
-          <t>303723</t>
+          <t>303676</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -1375,13 +1375,13 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>kk_4833698569</t>
+          <t>kk_4833397488</t>
         </is>
       </c>
       <c r="B40" t="inlineStr"/>
       <c r="C40" t="inlineStr">
         <is>
-          <t>303743</t>
+          <t>303723</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -1399,13 +1399,13 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>kk_4833115356</t>
+          <t>kk_4833867742</t>
         </is>
       </c>
       <c r="B41" t="inlineStr"/>
       <c r="C41" t="inlineStr">
         <is>
-          <t>303707</t>
+          <t>303760</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -1447,13 +1447,13 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>kk_4832345614</t>
+          <t>ckddbs4958</t>
         </is>
       </c>
       <c r="B43" t="inlineStr"/>
       <c r="C43" t="inlineStr">
         <is>
-          <t>303664</t>
+          <t>303722</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -1471,13 +1471,13 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>kk_4832562814</t>
+          <t>kk_4833115356</t>
         </is>
       </c>
       <c r="B44" t="inlineStr"/>
       <c r="C44" t="inlineStr">
         <is>
-          <t>303675</t>
+          <t>303707</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -1495,13 +1495,13 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>kk_4833867742</t>
+          <t>kk_4832735078</t>
         </is>
       </c>
       <c r="B45" t="inlineStr"/>
       <c r="C45" t="inlineStr">
         <is>
-          <t>303760</t>
+          <t>303682</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -1519,13 +1519,13 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>kk_4832564458</t>
+          <t>kk_4832986577</t>
         </is>
       </c>
       <c r="B46" t="inlineStr"/>
       <c r="C46" t="inlineStr">
         <is>
-          <t>303676</t>
+          <t>303701</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -1543,13 +1543,13 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>kk_4832425261</t>
+          <t>kk_4833698569</t>
         </is>
       </c>
       <c r="B47" t="inlineStr"/>
       <c r="C47" t="inlineStr">
         <is>
-          <t>303667</t>
+          <t>303743</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -1567,13 +1567,13 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>kk_4832735078</t>
+          <t>kk_4832345614</t>
         </is>
       </c>
       <c r="B48" t="inlineStr"/>
       <c r="C48" t="inlineStr">
         <is>
-          <t>303682</t>
+          <t>303664</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -1591,13 +1591,13 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>kk_4832986577</t>
+          <t>wngml5609</t>
         </is>
       </c>
       <c r="B49" t="inlineStr"/>
       <c r="C49" t="inlineStr">
         <is>
-          <t>303701</t>
+          <t>303704</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -1615,13 +1615,13 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>wngml5609</t>
+          <t>kk_4832425261</t>
         </is>
       </c>
       <c r="B50" t="inlineStr"/>
       <c r="C50" t="inlineStr">
         <is>
-          <t>303704</t>
+          <t>303667</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -1663,13 +1663,13 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>ckddbs4958</t>
+          <t>kk_4832562814</t>
         </is>
       </c>
       <c r="B52" t="inlineStr"/>
       <c r="C52" t="inlineStr">
         <is>
-          <t>303722</t>
+          <t>303675</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -1687,13 +1687,13 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>kk_4833234218</t>
+          <t>kk_4832874454</t>
         </is>
       </c>
       <c r="B53" t="inlineStr"/>
       <c r="C53" t="inlineStr">
         <is>
-          <t>303711</t>
+          <t>303691</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -1759,13 +1759,13 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>kk_4832874454</t>
+          <t>kk_4833234218</t>
         </is>
       </c>
       <c r="B56" t="inlineStr"/>
       <c r="C56" t="inlineStr">
         <is>
-          <t>303691</t>
+          <t>303711</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -1831,13 +1831,13 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>kk_4833289287</t>
+          <t>kk_4833937502</t>
         </is>
       </c>
       <c r="B59" t="inlineStr"/>
       <c r="C59" t="inlineStr">
         <is>
-          <t>303716</t>
+          <t>303767</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -1855,13 +1855,13 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>kk_4833588305</t>
+          <t>kk_4833289287</t>
         </is>
       </c>
       <c r="B60" t="inlineStr"/>
       <c r="C60" t="inlineStr">
         <is>
-          <t>303733</t>
+          <t>303716</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -1879,13 +1879,13 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>kk_4833858368</t>
+          <t>kk_4832497383</t>
         </is>
       </c>
       <c r="B61" t="inlineStr"/>
       <c r="C61" t="inlineStr">
         <is>
-          <t>303758</t>
+          <t>303669</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -1903,13 +1903,13 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>kk_4833937502</t>
+          <t>kk_4833858368</t>
         </is>
       </c>
       <c r="B62" t="inlineStr"/>
       <c r="C62" t="inlineStr">
         <is>
-          <t>303767</t>
+          <t>303758</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -1951,13 +1951,13 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>kk_4832497383</t>
+          <t>kk_4833588305</t>
         </is>
       </c>
       <c r="B64" t="inlineStr"/>
       <c r="C64" t="inlineStr">
         <is>
-          <t>303669</t>
+          <t>303733</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -1999,13 +1999,13 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>hlpt10</t>
+          <t>kk_4832855902</t>
         </is>
       </c>
       <c r="B66" t="inlineStr"/>
       <c r="C66" t="inlineStr">
         <is>
-          <t>303715</t>
+          <t>303690</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -2023,13 +2023,13 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>kk_4832855902</t>
+          <t>kk_4832888908</t>
         </is>
       </c>
       <c r="B67" t="inlineStr"/>
       <c r="C67" t="inlineStr">
         <is>
-          <t>303690</t>
+          <t>303693</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -2071,13 +2071,13 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>kk_4832888908</t>
+          <t>mystyle1999</t>
         </is>
       </c>
       <c r="B69" t="inlineStr"/>
       <c r="C69" t="inlineStr">
         <is>
-          <t>303693</t>
+          <t>303695</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -2095,13 +2095,13 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>mystyle1999</t>
+          <t>hlpt10</t>
         </is>
       </c>
       <c r="B70" t="inlineStr"/>
       <c r="C70" t="inlineStr">
         <is>
-          <t>303695</t>
+          <t>303715</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -2119,13 +2119,13 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>kk_4832527479</t>
+          <t>kk_4832745335</t>
         </is>
       </c>
       <c r="B71" t="inlineStr"/>
       <c r="C71" t="inlineStr">
         <is>
-          <t>303672</t>
+          <t>303684</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -2143,13 +2143,13 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>kk_4832745335</t>
+          <t>kk_4832527479</t>
         </is>
       </c>
       <c r="B72" t="inlineStr"/>
       <c r="C72" t="inlineStr">
         <is>
-          <t>303684</t>
+          <t>303672</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -2263,13 +2263,13 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>hotsnoopy</t>
+          <t>kk_4831402433</t>
         </is>
       </c>
       <c r="B77" t="inlineStr"/>
       <c r="C77" t="inlineStr">
         <is>
-          <t>303585</t>
+          <t>303576</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -2287,13 +2287,13 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>thdud9181</t>
+          <t>kk_4833294708</t>
         </is>
       </c>
       <c r="B78" t="inlineStr"/>
       <c r="C78" t="inlineStr">
         <is>
-          <t>303644</t>
+          <t>303717</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
@@ -2311,13 +2311,13 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>kk_4831402433</t>
+          <t>kk_4833232918</t>
         </is>
       </c>
       <c r="B79" t="inlineStr"/>
       <c r="C79" t="inlineStr">
         <is>
-          <t>303576</t>
+          <t>303710</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
@@ -2335,13 +2335,13 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>kk_4833961109</t>
+          <t>kk_4832310183</t>
         </is>
       </c>
       <c r="B80" t="inlineStr"/>
       <c r="C80" t="inlineStr">
         <is>
-          <t>303770</t>
+          <t>303663</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
@@ -2359,13 +2359,13 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>kk_4833294708</t>
+          <t>thdud9181</t>
         </is>
       </c>
       <c r="B81" t="inlineStr"/>
       <c r="C81" t="inlineStr">
         <is>
-          <t>303717</t>
+          <t>303644</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
@@ -2383,13 +2383,13 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>kk_4831784738</t>
+          <t>pjj1758</t>
         </is>
       </c>
       <c r="B82" t="inlineStr"/>
       <c r="C82" t="inlineStr">
         <is>
-          <t>303607</t>
+          <t>303708</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
@@ -2407,13 +2407,13 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>kk_4833706874</t>
+          <t>kk_4831784738</t>
         </is>
       </c>
       <c r="B83" t="inlineStr"/>
       <c r="C83" t="inlineStr">
         <is>
-          <t>303744</t>
+          <t>303607</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
@@ -2431,13 +2431,13 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>kk_4832310183</t>
+          <t>hotsnoopy</t>
         </is>
       </c>
       <c r="B84" t="inlineStr"/>
       <c r="C84" t="inlineStr">
         <is>
-          <t>303663</t>
+          <t>303585</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
@@ -2455,13 +2455,13 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>kk_4833232918</t>
+          <t>kk_4833706874</t>
         </is>
       </c>
       <c r="B85" t="inlineStr"/>
       <c r="C85" t="inlineStr">
         <is>
-          <t>303710</t>
+          <t>303744</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
@@ -2479,13 +2479,13 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>pjj1758</t>
+          <t>kk_4833961109</t>
         </is>
       </c>
       <c r="B86" t="inlineStr"/>
       <c r="C86" t="inlineStr">
         <is>
-          <t>303708</t>
+          <t>303770</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
@@ -2527,13 +2527,13 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>kk_4830612400</t>
+          <t>kk_4831842028</t>
         </is>
       </c>
       <c r="B88" t="inlineStr"/>
       <c r="C88" t="inlineStr">
         <is>
-          <t>303542</t>
+          <t>303612</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
@@ -2551,13 +2551,13 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>kk_4831842028</t>
+          <t>kk_4830612400</t>
         </is>
       </c>
       <c r="B89" t="inlineStr"/>
       <c r="C89" t="inlineStr">
         <is>
-          <t>303612</t>
+          <t>303542</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
@@ -2767,13 +2767,13 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>kk_4831995357</t>
+          <t>kk_4831768959</t>
         </is>
       </c>
       <c r="B98" t="inlineStr"/>
       <c r="C98" t="inlineStr">
         <is>
-          <t>303623</t>
+          <t>303602</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
@@ -2791,13 +2791,13 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>kk_4831768959</t>
+          <t>kk_4830251299</t>
         </is>
       </c>
       <c r="B99" t="inlineStr"/>
       <c r="C99" t="inlineStr">
         <is>
-          <t>303602</t>
+          <t>303511</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
@@ -2839,13 +2839,13 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>kk_4830251299</t>
+          <t>kk_4831995357</t>
         </is>
       </c>
       <c r="B101" t="inlineStr"/>
       <c r="C101" t="inlineStr">
         <is>
-          <t>303511</t>
+          <t>303623</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
@@ -2863,13 +2863,13 @@
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>kk_4832105165</t>
+          <t>kk_4831842112</t>
         </is>
       </c>
       <c r="B102" t="inlineStr"/>
       <c r="C102" t="inlineStr">
         <is>
-          <t>303636</t>
+          <t>303613</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
@@ -2887,13 +2887,13 @@
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>kk_4831842112</t>
+          <t>kk_4832105165</t>
         </is>
       </c>
       <c r="B103" t="inlineStr"/>
       <c r="C103" t="inlineStr">
         <is>
-          <t>303613</t>
+          <t>303636</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
@@ -2911,13 +2911,13 @@
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>kk_4830767555</t>
+          <t>kk_4832023314</t>
         </is>
       </c>
       <c r="B104" t="inlineStr"/>
       <c r="C104" t="inlineStr">
         <is>
-          <t>303555</t>
+          <t>303626</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
@@ -2935,13 +2935,13 @@
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>kk_4832248726</t>
+          <t>kk_4831394790</t>
         </is>
       </c>
       <c r="B105" t="inlineStr"/>
       <c r="C105" t="inlineStr">
         <is>
-          <t>303658</t>
+          <t>303575</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
@@ -2959,13 +2959,13 @@
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>kk_4831346086</t>
+          <t>kk_4830767555</t>
         </is>
       </c>
       <c r="B106" t="inlineStr"/>
       <c r="C106" t="inlineStr">
         <is>
-          <t>303573</t>
+          <t>303555</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
@@ -2983,13 +2983,13 @@
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>kk_4832180009</t>
+          <t>kk_4832248726</t>
         </is>
       </c>
       <c r="B107" t="inlineStr"/>
       <c r="C107" t="inlineStr">
         <is>
-          <t>303647</t>
+          <t>303658</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
@@ -3007,13 +3007,13 @@
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>kk_4831394790</t>
+          <t>kk_4832201164</t>
         </is>
       </c>
       <c r="B108" t="inlineStr"/>
       <c r="C108" t="inlineStr">
         <is>
-          <t>303575</t>
+          <t>303651</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
@@ -3031,13 +3031,13 @@
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>kk_4832023314</t>
+          <t>kk_4832180009</t>
         </is>
       </c>
       <c r="B109" t="inlineStr"/>
       <c r="C109" t="inlineStr">
         <is>
-          <t>303626</t>
+          <t>303647</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
@@ -3079,13 +3079,13 @@
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>kk_4832114535</t>
+          <t>kk_4831346086</t>
         </is>
       </c>
       <c r="B111" t="inlineStr"/>
       <c r="C111" t="inlineStr">
         <is>
-          <t>303637</t>
+          <t>303573</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
@@ -3127,13 +3127,13 @@
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>kk_4832201164</t>
+          <t>kk_4832114535</t>
         </is>
       </c>
       <c r="B113" t="inlineStr"/>
       <c r="C113" t="inlineStr">
         <is>
-          <t>303651</t>
+          <t>303637</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
@@ -3223,13 +3223,13 @@
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>kk_4832078505</t>
+          <t>kk_4832100095</t>
         </is>
       </c>
       <c r="B117" t="inlineStr"/>
       <c r="C117" t="inlineStr">
         <is>
-          <t>303630</t>
+          <t>303634</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
@@ -3247,13 +3247,13 @@
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>kk_4831340465</t>
+          <t>jambo8</t>
         </is>
       </c>
       <c r="B118" t="inlineStr"/>
       <c r="C118" t="inlineStr">
         <is>
-          <t>303572</t>
+          <t>303558</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
@@ -3271,13 +3271,13 @@
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>kk_4832100095</t>
+          <t>kk_4832029124</t>
         </is>
       </c>
       <c r="B119" t="inlineStr"/>
       <c r="C119" t="inlineStr">
         <is>
-          <t>303634</t>
+          <t>303627</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
@@ -3295,13 +3295,13 @@
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>kk_4832029124</t>
+          <t>kk_4832078505</t>
         </is>
       </c>
       <c r="B120" t="inlineStr"/>
       <c r="C120" t="inlineStr">
         <is>
-          <t>303627</t>
+          <t>303630</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
@@ -3319,13 +3319,13 @@
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>jambo8</t>
+          <t>kk_4831340465</t>
         </is>
       </c>
       <c r="B121" t="inlineStr"/>
       <c r="C121" t="inlineStr">
         <is>
-          <t>303558</t>
+          <t>303572</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
@@ -3391,13 +3391,13 @@
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>kk_4831830576</t>
+          <t>jgj0503</t>
         </is>
       </c>
       <c r="B124" t="inlineStr"/>
       <c r="C124" t="inlineStr">
         <is>
-          <t>303611</t>
+          <t>303605</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
@@ -3439,13 +3439,13 @@
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>jgj0503</t>
+          <t>kk_4830989652</t>
         </is>
       </c>
       <c r="B126" t="inlineStr"/>
       <c r="C126" t="inlineStr">
         <is>
-          <t>303605</t>
+          <t>303569</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
@@ -3463,13 +3463,13 @@
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>kk_4830989652</t>
+          <t>kk_4831830576</t>
         </is>
       </c>
       <c r="B127" t="inlineStr"/>
       <c r="C127" t="inlineStr">
         <is>
-          <t>303569</t>
+          <t>303611</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
@@ -3511,13 +3511,13 @@
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>kk_4831922723</t>
+          <t>kk_4831850638</t>
         </is>
       </c>
       <c r="B129" t="inlineStr"/>
       <c r="C129" t="inlineStr">
         <is>
-          <t>303617</t>
+          <t>303615</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
@@ -3559,13 +3559,13 @@
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>kk_4830836853</t>
+          <t>kk_4830778741</t>
         </is>
       </c>
       <c r="B131" t="inlineStr"/>
       <c r="C131" t="inlineStr">
         <is>
-          <t>303560</t>
+          <t>303556</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
@@ -3583,13 +3583,13 @@
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>kk_4831850638</t>
+          <t>kk_4831922723</t>
         </is>
       </c>
       <c r="B132" t="inlineStr"/>
       <c r="C132" t="inlineStr">
         <is>
-          <t>303615</t>
+          <t>303617</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
@@ -3607,13 +3607,13 @@
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>kk_4830778741</t>
+          <t>kk_4830836853</t>
         </is>
       </c>
       <c r="B133" t="inlineStr"/>
       <c r="C133" t="inlineStr">
         <is>
-          <t>303556</t>
+          <t>303560</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
@@ -3703,13 +3703,13 @@
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>kk_4831532519</t>
+          <t>kk_4832001343</t>
         </is>
       </c>
       <c r="B137" t="inlineStr"/>
       <c r="C137" t="inlineStr">
         <is>
-          <t>303587</t>
+          <t>303625</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
@@ -3727,13 +3727,13 @@
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>kk_4831986570</t>
+          <t>kk_4832061430</t>
         </is>
       </c>
       <c r="B138" t="inlineStr"/>
       <c r="C138" t="inlineStr">
         <is>
-          <t>303622</t>
+          <t>303628</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
@@ -3751,13 +3751,13 @@
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>kk_4832100101</t>
+          <t>kk_4832190692</t>
         </is>
       </c>
       <c r="B139" t="inlineStr"/>
       <c r="C139" t="inlineStr">
         <is>
-          <t>303635</t>
+          <t>303649</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
@@ -3775,13 +3775,13 @@
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>kk_4831981914</t>
+          <t>kk_4831983348</t>
         </is>
       </c>
       <c r="B140" t="inlineStr"/>
       <c r="C140" t="inlineStr">
         <is>
-          <t>303620</t>
+          <t>303621</t>
         </is>
       </c>
       <c r="D140" t="inlineStr">
@@ -3799,13 +3799,13 @@
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>kk_4831799020</t>
+          <t>kk_4831997957</t>
         </is>
       </c>
       <c r="B141" t="inlineStr"/>
       <c r="C141" t="inlineStr">
         <is>
-          <t>303609</t>
+          <t>303624</t>
         </is>
       </c>
       <c r="D141" t="inlineStr">
@@ -3823,13 +3823,13 @@
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>kk_4831983348</t>
+          <t>kk_4831799020</t>
         </is>
       </c>
       <c r="B142" t="inlineStr"/>
       <c r="C142" t="inlineStr">
         <is>
-          <t>303621</t>
+          <t>303609</t>
         </is>
       </c>
       <c r="D142" t="inlineStr">
@@ -3847,13 +3847,13 @@
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>kk_4832061430</t>
+          <t>kk_4831981914</t>
         </is>
       </c>
       <c r="B143" t="inlineStr"/>
       <c r="C143" t="inlineStr">
         <is>
-          <t>303628</t>
+          <t>303620</t>
         </is>
       </c>
       <c r="D143" t="inlineStr">
@@ -3871,13 +3871,13 @@
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>kk_4832001343</t>
+          <t>kk_4831502482</t>
         </is>
       </c>
       <c r="B144" t="inlineStr"/>
       <c r="C144" t="inlineStr">
         <is>
-          <t>303625</t>
+          <t>303583</t>
         </is>
       </c>
       <c r="D144" t="inlineStr">
@@ -3895,13 +3895,13 @@
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>kk_4831502482</t>
+          <t>kk_4831986570</t>
         </is>
       </c>
       <c r="B145" t="inlineStr"/>
       <c r="C145" t="inlineStr">
         <is>
-          <t>303583</t>
+          <t>303622</t>
         </is>
       </c>
       <c r="D145" t="inlineStr">
@@ -3919,13 +3919,13 @@
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>kk_4831257396</t>
+          <t>kk_4831532519</t>
         </is>
       </c>
       <c r="B146" t="inlineStr"/>
       <c r="C146" t="inlineStr">
         <is>
-          <t>303571</t>
+          <t>303587</t>
         </is>
       </c>
       <c r="D146" t="inlineStr">
@@ -3943,13 +3943,13 @@
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>kk_4832190692</t>
+          <t>kk_4832100101</t>
         </is>
       </c>
       <c r="B147" t="inlineStr"/>
       <c r="C147" t="inlineStr">
         <is>
-          <t>303649</t>
+          <t>303635</t>
         </is>
       </c>
       <c r="D147" t="inlineStr">
@@ -3967,13 +3967,13 @@
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>kk_4831997957</t>
+          <t>kk_4831257396</t>
         </is>
       </c>
       <c r="B148" t="inlineStr"/>
       <c r="C148" t="inlineStr">
         <is>
-          <t>303624</t>
+          <t>303571</t>
         </is>
       </c>
       <c r="D148" t="inlineStr">
@@ -3991,13 +3991,13 @@
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>kk_4832186210</t>
+          <t>kk_4831774426</t>
         </is>
       </c>
       <c r="B149" t="inlineStr"/>
       <c r="C149" t="inlineStr">
         <is>
-          <t>303648</t>
+          <t>303604</t>
         </is>
       </c>
       <c r="D149" t="inlineStr">
@@ -4015,13 +4015,13 @@
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>kk_4831774426</t>
+          <t>kk_4832186210</t>
         </is>
       </c>
       <c r="B150" t="inlineStr"/>
       <c r="C150" t="inlineStr">
         <is>
-          <t>303604</t>
+          <t>303648</t>
         </is>
       </c>
       <c r="D150" t="inlineStr">
@@ -4039,13 +4039,13 @@
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>kk_4831822425</t>
+          <t>kk_4831585022</t>
         </is>
       </c>
       <c r="B151" t="inlineStr"/>
       <c r="C151" t="inlineStr">
         <is>
-          <t>303610</t>
+          <t>303591</t>
         </is>
       </c>
       <c r="D151" t="inlineStr">
@@ -4087,13 +4087,13 @@
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>kk_4831951614</t>
+          <t>kk_4831822425</t>
         </is>
       </c>
       <c r="B153" t="inlineStr"/>
       <c r="C153" t="inlineStr">
         <is>
-          <t>303618</t>
+          <t>303610</t>
         </is>
       </c>
       <c r="D153" t="inlineStr">
@@ -4111,13 +4111,13 @@
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>kk_4831585022</t>
+          <t>kk_4831951614</t>
         </is>
       </c>
       <c r="B154" t="inlineStr"/>
       <c r="C154" t="inlineStr">
         <is>
-          <t>303591</t>
+          <t>303618</t>
         </is>
       </c>
       <c r="D154" t="inlineStr">
@@ -4159,13 +4159,13 @@
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>minpark98</t>
+          <t>kk_4831488942</t>
         </is>
       </c>
       <c r="B156" t="inlineStr"/>
       <c r="C156" t="inlineStr">
         <is>
-          <t>303657</t>
+          <t>303580</t>
         </is>
       </c>
       <c r="D156" t="inlineStr">
@@ -4183,13 +4183,13 @@
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>kk_4831488942</t>
+          <t>minpark98</t>
         </is>
       </c>
       <c r="B157" t="inlineStr"/>
       <c r="C157" t="inlineStr">
         <is>
-          <t>303580</t>
+          <t>303657</t>
         </is>
       </c>
       <c r="D157" t="inlineStr">
@@ -4207,13 +4207,13 @@
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>kk_4831615271</t>
+          <t>kk_4831600231</t>
         </is>
       </c>
       <c r="B158" t="inlineStr"/>
       <c r="C158" t="inlineStr">
         <is>
-          <t>303594</t>
+          <t>303592</t>
         </is>
       </c>
       <c r="D158" t="inlineStr">
@@ -4231,13 +4231,13 @@
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>kk_4831600231</t>
+          <t>kk_4831615271</t>
         </is>
       </c>
       <c r="B159" t="inlineStr"/>
       <c r="C159" t="inlineStr">
         <is>
-          <t>303592</t>
+          <t>303594</t>
         </is>
       </c>
       <c r="D159" t="inlineStr">
@@ -4279,13 +4279,13 @@
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>kk_4830147171</t>
+          <t>kk_4830615705</t>
         </is>
       </c>
       <c r="B161" t="inlineStr"/>
       <c r="C161" t="inlineStr">
         <is>
-          <t>303506</t>
+          <t>303543</t>
         </is>
       </c>
       <c r="D161" t="inlineStr">
@@ -4303,13 +4303,13 @@
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>kk_4830615705</t>
+          <t>kk_4830147171</t>
         </is>
       </c>
       <c r="B162" t="inlineStr"/>
       <c r="C162" t="inlineStr">
         <is>
-          <t>303543</t>
+          <t>303506</t>
         </is>
       </c>
       <c r="D162" t="inlineStr">
@@ -4399,13 +4399,13 @@
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>kk_4830179868</t>
+          <t>kk_4830596422</t>
         </is>
       </c>
       <c r="B166" t="inlineStr"/>
       <c r="C166" t="inlineStr">
         <is>
-          <t>303508</t>
+          <t>303540</t>
         </is>
       </c>
       <c r="D166" t="inlineStr">
@@ -4423,13 +4423,13 @@
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>kk_4830596422</t>
+          <t>kk_4830179868</t>
         </is>
       </c>
       <c r="B167" t="inlineStr"/>
       <c r="C167" t="inlineStr">
         <is>
-          <t>303540</t>
+          <t>303508</t>
         </is>
       </c>
       <c r="D167" t="inlineStr">
@@ -4495,13 +4495,13 @@
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>kk_4829999849</t>
+          <t>kk_4830404781</t>
         </is>
       </c>
       <c r="B170" t="inlineStr"/>
       <c r="C170" t="inlineStr">
         <is>
-          <t>303498</t>
+          <t>303521</t>
         </is>
       </c>
       <c r="D170" t="inlineStr">
@@ -4519,13 +4519,13 @@
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>kk_4830692253</t>
+          <t>kk_4830541132</t>
         </is>
       </c>
       <c r="B171" t="inlineStr"/>
       <c r="C171" t="inlineStr">
         <is>
-          <t>303550</t>
+          <t>303533</t>
         </is>
       </c>
       <c r="D171" t="inlineStr">
@@ -4543,13 +4543,13 @@
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>kk_4830409260</t>
+          <t>kk_4829999849</t>
         </is>
       </c>
       <c r="B172" t="inlineStr"/>
       <c r="C172" t="inlineStr">
         <is>
-          <t>303522</t>
+          <t>303498</t>
         </is>
       </c>
       <c r="D172" t="inlineStr">
@@ -4567,13 +4567,13 @@
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>kk_4830404781</t>
+          <t>kk_4830692253</t>
         </is>
       </c>
       <c r="B173" t="inlineStr"/>
       <c r="C173" t="inlineStr">
         <is>
-          <t>303521</t>
+          <t>303550</t>
         </is>
       </c>
       <c r="D173" t="inlineStr">
@@ -4615,13 +4615,13 @@
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>kk_4830541132</t>
+          <t>kk_4830409260</t>
         </is>
       </c>
       <c r="B175" t="inlineStr"/>
       <c r="C175" t="inlineStr">
         <is>
-          <t>303533</t>
+          <t>303522</t>
         </is>
       </c>
       <c r="D175" t="inlineStr">
@@ -4639,13 +4639,13 @@
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>kk_4830559393</t>
+          <t>mong81</t>
         </is>
       </c>
       <c r="B176" t="inlineStr"/>
       <c r="C176" t="inlineStr">
         <is>
-          <t>303535</t>
+          <t>303505</t>
         </is>
       </c>
       <c r="D176" t="inlineStr">
@@ -4663,13 +4663,13 @@
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>mong81</t>
+          <t>kk_4830559393</t>
         </is>
       </c>
       <c r="B177" t="inlineStr"/>
       <c r="C177" t="inlineStr">
         <is>
-          <t>303505</t>
+          <t>303535</t>
         </is>
       </c>
       <c r="D177" t="inlineStr">
@@ -4735,13 +4735,13 @@
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>kk_4830704540</t>
+          <t>flydabi</t>
         </is>
       </c>
       <c r="B180" t="inlineStr"/>
       <c r="C180" t="inlineStr">
         <is>
-          <t>303551</t>
+          <t>303531</t>
         </is>
       </c>
       <c r="D180" t="inlineStr">
@@ -4807,13 +4807,13 @@
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>kk_4830597347</t>
+          <t>kk_4830376206</t>
         </is>
       </c>
       <c r="B183" t="inlineStr"/>
       <c r="C183" t="inlineStr">
         <is>
-          <t>303541</t>
+          <t>303520</t>
         </is>
       </c>
       <c r="D183" t="inlineStr">
@@ -4831,13 +4831,13 @@
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>flydabi</t>
+          <t>kk_4830308577</t>
         </is>
       </c>
       <c r="B184" t="inlineStr"/>
       <c r="C184" t="inlineStr">
         <is>
-          <t>303531</t>
+          <t>303516</t>
         </is>
       </c>
       <c r="D184" t="inlineStr">
@@ -4855,13 +4855,13 @@
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>kk_4830376206</t>
+          <t>kk_4830704540</t>
         </is>
       </c>
       <c r="B185" t="inlineStr"/>
       <c r="C185" t="inlineStr">
         <is>
-          <t>303520</t>
+          <t>303551</t>
         </is>
       </c>
       <c r="D185" t="inlineStr">
@@ -4879,13 +4879,13 @@
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>kk_4830308577</t>
+          <t>kk_4830722522</t>
         </is>
       </c>
       <c r="B186" t="inlineStr"/>
       <c r="C186" t="inlineStr">
         <is>
-          <t>303516</t>
+          <t>303553</t>
         </is>
       </c>
       <c r="D186" t="inlineStr">
@@ -4927,13 +4927,13 @@
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>kk_4830722522</t>
+          <t>kk_4830597347</t>
         </is>
       </c>
       <c r="B188" t="inlineStr"/>
       <c r="C188" t="inlineStr">
         <is>
-          <t>303553</t>
+          <t>303541</t>
         </is>
       </c>
       <c r="D188" t="inlineStr">

--- a/reports/member_funnel/downloads/member_funnel_7d_non_buyer.xlsx
+++ b/reports/member_funnel/downloads/member_funnel_7d_non_buyer.xlsx
@@ -11771,54 +11771,54 @@
     <row r="421">
       <c r="A421" t="inlineStr">
         <is>
-          <t>kwon9493</t>
+          <t>kk_4839170665</t>
         </is>
       </c>
       <c r="B421" t="inlineStr">
         <is>
-          <t>01035589493</t>
+          <t>01050116666</t>
         </is>
       </c>
       <c r="C421" t="inlineStr">
         <is>
-          <t>107077</t>
+          <t>304086</t>
         </is>
       </c>
       <c r="D421" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E421" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>EFW</t>
         </is>
       </c>
     </row>
     <row r="422">
       <c r="A422" t="inlineStr">
         <is>
-          <t>kk_4839170665</t>
+          <t>kwon9493</t>
         </is>
       </c>
       <c r="B422" t="inlineStr">
         <is>
-          <t>01050116666</t>
+          <t>01035589493</t>
         </is>
       </c>
       <c r="C422" t="inlineStr">
         <is>
-          <t>304086</t>
+          <t>107077</t>
         </is>
       </c>
       <c r="D422" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="E422" t="inlineStr">
         <is>
-          <t>EFW</t>
+          <t>Direct</t>
         </is>
       </c>
     </row>
@@ -15686,54 +15686,54 @@
     <row r="566">
       <c r="A566" t="inlineStr">
         <is>
-          <t>kk_3483300064</t>
+          <t>kk_4837763007</t>
         </is>
       </c>
       <c r="B566" t="inlineStr">
         <is>
-          <t>01092213404</t>
+          <t>01088993992</t>
         </is>
       </c>
       <c r="C566" t="inlineStr">
         <is>
-          <t>244619</t>
+          <t>304013</t>
         </is>
       </c>
       <c r="D566" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E566" t="inlineStr">
         <is>
-          <t>naver_brandsearch_mobile</t>
+          <t>(referral)</t>
         </is>
       </c>
     </row>
     <row r="567">
       <c r="A567" t="inlineStr">
         <is>
-          <t>kk_4837763007</t>
+          <t>kk_3483300064</t>
         </is>
       </c>
       <c r="B567" t="inlineStr">
         <is>
-          <t>01088993992</t>
+          <t>01092213404</t>
         </is>
       </c>
       <c r="C567" t="inlineStr">
         <is>
-          <t>304013</t>
+          <t>244619</t>
         </is>
       </c>
       <c r="D567" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E567" t="inlineStr">
         <is>
-          <t>(referral)</t>
+          <t>naver_brandsearch_mobile</t>
         </is>
       </c>
     </row>
@@ -18629,54 +18629,54 @@
     <row r="675">
       <c r="A675" t="inlineStr">
         <is>
-          <t>kk_3633964155</t>
+          <t>kk_3913679442</t>
         </is>
       </c>
       <c r="B675" t="inlineStr">
         <is>
-          <t>01097743709</t>
+          <t>01085569215</t>
         </is>
       </c>
       <c r="C675" t="inlineStr">
         <is>
-          <t>248300</t>
+          <t>268330</t>
         </is>
       </c>
       <c r="D675" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="E675" t="inlineStr">
         <is>
-          <t>KAKAO_CH_MENU_0226_EFW</t>
+          <t>미분류</t>
         </is>
       </c>
     </row>
     <row r="676">
       <c r="A676" t="inlineStr">
         <is>
-          <t>kk_3913679442</t>
+          <t>kk_3633964155</t>
         </is>
       </c>
       <c r="B676" t="inlineStr">
         <is>
-          <t>01085569215</t>
+          <t>01097743709</t>
         </is>
       </c>
       <c r="C676" t="inlineStr">
         <is>
-          <t>268330</t>
+          <t>248300</t>
         </is>
       </c>
       <c r="D676" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E676" t="inlineStr">
         <is>
-          <t>미분류</t>
+          <t>KAKAO_CH_MENU_0226_EFW</t>
         </is>
       </c>
     </row>
@@ -19277,54 +19277,54 @@
     <row r="699">
       <c r="A699" t="inlineStr">
         <is>
-          <t>hisgogo</t>
+          <t>kk_3671070277</t>
         </is>
       </c>
       <c r="B699" t="inlineStr">
         <is>
-          <t>01054110956</t>
+          <t>01065561446</t>
         </is>
       </c>
       <c r="C699" t="inlineStr">
         <is>
-          <t>174486</t>
+          <t>250075</t>
         </is>
       </c>
       <c r="D699" t="inlineStr">
         <is>
-          <t>Organic Traffic</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E699" t="inlineStr">
         <is>
-          <t>(referral)</t>
+          <t>KAKAO_CH_MESSAGE_0409_HIKE365SUMMER</t>
         </is>
       </c>
     </row>
     <row r="700">
       <c r="A700" t="inlineStr">
         <is>
-          <t>kk_3671070277</t>
+          <t>hisgogo</t>
         </is>
       </c>
       <c r="B700" t="inlineStr">
         <is>
-          <t>01065561446</t>
+          <t>01054110956</t>
         </is>
       </c>
       <c r="C700" t="inlineStr">
         <is>
-          <t>250075</t>
+          <t>174486</t>
         </is>
       </c>
       <c r="D700" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Organic Traffic</t>
         </is>
       </c>
       <c r="E700" t="inlineStr">
         <is>
-          <t>KAKAO_CH_MESSAGE_0409_HIKE365SUMMER</t>
+          <t>(referral)</t>
         </is>
       </c>
     </row>
@@ -20141,54 +20141,54 @@
     <row r="731">
       <c r="A731" t="inlineStr">
         <is>
-          <t>kk_4839145768</t>
+          <t>sun1381</t>
         </is>
       </c>
       <c r="B731" t="inlineStr">
         <is>
-          <t>01097367898</t>
+          <t>01037709416</t>
         </is>
       </c>
       <c r="C731" t="inlineStr">
         <is>
-          <t>304085</t>
+          <t>278160</t>
         </is>
       </c>
       <c r="D731" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E731" t="inlineStr">
         <is>
-          <t>naver_brandsearch_pc</t>
+          <t>LMS_ECOM_0410exclusive2</t>
         </is>
       </c>
     </row>
     <row r="732">
       <c r="A732" t="inlineStr">
         <is>
-          <t>sun1381</t>
+          <t>kk_4839145768</t>
         </is>
       </c>
       <c r="B732" t="inlineStr">
         <is>
-          <t>01037709416</t>
+          <t>01097367898</t>
         </is>
       </c>
       <c r="C732" t="inlineStr">
         <is>
-          <t>278160</t>
+          <t>304085</t>
         </is>
       </c>
       <c r="D732" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E732" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0410exclusive2</t>
+          <t>naver_brandsearch_pc</t>
         </is>
       </c>
     </row>
@@ -20222,17 +20222,17 @@
     <row r="734">
       <c r="A734" t="inlineStr">
         <is>
-          <t>kwon1207</t>
+          <t>kk_4324736295</t>
         </is>
       </c>
       <c r="B734" t="inlineStr">
         <is>
-          <t>01055647413</t>
+          <t>01077616385</t>
         </is>
       </c>
       <c r="C734" t="inlineStr">
         <is>
-          <t>129663</t>
+          <t>278190</t>
         </is>
       </c>
       <c r="D734" t="inlineStr">
@@ -20242,24 +20242,24 @@
       </c>
       <c r="E734" t="inlineStr">
         <is>
-          <t>KAKAO_CH_MESSAGE_0409_TRAIL</t>
+          <t>KAKAO_CH_MESSAGE_0409_EXCLUSIVE</t>
         </is>
       </c>
     </row>
     <row r="735">
       <c r="A735" t="inlineStr">
         <is>
-          <t>kk_4324736295</t>
+          <t>kwon1207</t>
         </is>
       </c>
       <c r="B735" t="inlineStr">
         <is>
-          <t>01077616385</t>
+          <t>01055647413</t>
         </is>
       </c>
       <c r="C735" t="inlineStr">
         <is>
-          <t>278190</t>
+          <t>129663</t>
         </is>
       </c>
       <c r="D735" t="inlineStr">
@@ -20269,7 +20269,7 @@
       </c>
       <c r="E735" t="inlineStr">
         <is>
-          <t>KAKAO_CH_MESSAGE_0409_EXCLUSIVE</t>
+          <t>KAKAO_CH_MESSAGE_0409_TRAIL</t>
         </is>
       </c>
     </row>
@@ -20303,17 +20303,17 @@
     <row r="737">
       <c r="A737" t="inlineStr">
         <is>
-          <t>kk_4617674866</t>
+          <t>kk_4641269666</t>
         </is>
       </c>
       <c r="B737" t="inlineStr">
         <is>
-          <t>01062147077</t>
+          <t>01041565334</t>
         </is>
       </c>
       <c r="C737" t="inlineStr">
         <is>
-          <t>290764</t>
+          <t>292505</t>
         </is>
       </c>
       <c r="D737" t="inlineStr">
@@ -20323,24 +20323,24 @@
       </c>
       <c r="E737" t="inlineStr">
         <is>
-          <t>KAKAO_CH_MESSAGE_0409_TRAIL</t>
+          <t>KAKAO_CH_MESSAGE_0409_HIKE365SUMMER</t>
         </is>
       </c>
     </row>
     <row r="738">
       <c r="A738" t="inlineStr">
         <is>
-          <t>kk_4641269666</t>
+          <t>kk_4617674866</t>
         </is>
       </c>
       <c r="B738" t="inlineStr">
         <is>
-          <t>01041565334</t>
+          <t>01062147077</t>
         </is>
       </c>
       <c r="C738" t="inlineStr">
         <is>
-          <t>292505</t>
+          <t>290764</t>
         </is>
       </c>
       <c r="D738" t="inlineStr">
@@ -20350,7 +20350,7 @@
       </c>
       <c r="E738" t="inlineStr">
         <is>
-          <t>KAKAO_CH_MESSAGE_0409_HIKE365SUMMER</t>
+          <t>KAKAO_CH_MESSAGE_0409_TRAIL</t>
         </is>
       </c>
     </row>
@@ -20924,17 +20924,17 @@
     <row r="760">
       <c r="A760" t="inlineStr">
         <is>
-          <t>abril80</t>
+          <t>kang481127</t>
         </is>
       </c>
       <c r="B760" t="inlineStr">
         <is>
-          <t>01032942835</t>
+          <t>01053764012</t>
         </is>
       </c>
       <c r="C760" t="inlineStr">
         <is>
-          <t>192610</t>
+          <t>304276</t>
         </is>
       </c>
       <c r="D760" t="inlineStr">
@@ -20951,17 +20951,17 @@
     <row r="761">
       <c r="A761" t="inlineStr">
         <is>
-          <t>kang481127</t>
+          <t>abril80</t>
         </is>
       </c>
       <c r="B761" t="inlineStr">
         <is>
-          <t>01053764012</t>
+          <t>01032942835</t>
         </is>
       </c>
       <c r="C761" t="inlineStr">
         <is>
-          <t>304276</t>
+          <t>192610</t>
         </is>
       </c>
       <c r="D761" t="inlineStr">
@@ -21167,17 +21167,17 @@
     <row r="769">
       <c r="A769" t="inlineStr">
         <is>
-          <t>kk_3392066640</t>
+          <t>athend</t>
         </is>
       </c>
       <c r="B769" t="inlineStr">
         <is>
-          <t>01065021283</t>
+          <t>01041786462</t>
         </is>
       </c>
       <c r="C769" t="inlineStr">
         <is>
-          <t>240983</t>
+          <t>285491</t>
         </is>
       </c>
       <c r="D769" t="inlineStr">
@@ -21187,7 +21187,7 @@
       </c>
       <c r="E769" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0410exclusive2</t>
+          <t>KAKAO_alimtalk</t>
         </is>
       </c>
     </row>
@@ -21248,17 +21248,17 @@
     <row r="772">
       <c r="A772" t="inlineStr">
         <is>
-          <t>athend</t>
+          <t>kk_3392066640</t>
         </is>
       </c>
       <c r="B772" t="inlineStr">
         <is>
-          <t>01041786462</t>
+          <t>01065021283</t>
         </is>
       </c>
       <c r="C772" t="inlineStr">
         <is>
-          <t>285491</t>
+          <t>240983</t>
         </is>
       </c>
       <c r="D772" t="inlineStr">
@@ -21268,24 +21268,24 @@
       </c>
       <c r="E772" t="inlineStr">
         <is>
-          <t>KAKAO_alimtalk</t>
+          <t>LMS_ECOM_0410exclusive2</t>
         </is>
       </c>
     </row>
     <row r="773">
       <c r="A773" t="inlineStr">
         <is>
-          <t>kk_3404142353</t>
+          <t>kk_3184667648</t>
         </is>
       </c>
       <c r="B773" t="inlineStr">
         <is>
-          <t>01053293239</t>
+          <t>01043440321</t>
         </is>
       </c>
       <c r="C773" t="inlineStr">
         <is>
-          <t>241289</t>
+          <t>229128</t>
         </is>
       </c>
       <c r="D773" t="inlineStr">
@@ -21295,61 +21295,61 @@
       </c>
       <c r="E773" t="inlineStr">
         <is>
-          <t>[PF]전환_상시(2565MF,비구매자)</t>
+          <t>sa</t>
         </is>
       </c>
     </row>
     <row r="774">
       <c r="A774" t="inlineStr">
         <is>
-          <t>kk_4431727915</t>
+          <t>kk_3404142353</t>
         </is>
       </c>
       <c r="B774" t="inlineStr">
         <is>
-          <t>01047182896</t>
+          <t>01053293239</t>
         </is>
       </c>
       <c r="C774" t="inlineStr">
         <is>
-          <t>281759</t>
+          <t>241289</t>
         </is>
       </c>
       <c r="D774" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E774" t="inlineStr">
         <is>
-          <t>KAKAO_CH_MESSAGE_0409_HIKE365SUMMER</t>
+          <t>[PF]전환_상시(2565MF,비구매자)</t>
         </is>
       </c>
     </row>
     <row r="775">
       <c r="A775" t="inlineStr">
         <is>
-          <t>kk_3184667648</t>
+          <t>kk_4431727915</t>
         </is>
       </c>
       <c r="B775" t="inlineStr">
         <is>
-          <t>01043440321</t>
+          <t>01047182896</t>
         </is>
       </c>
       <c r="C775" t="inlineStr">
         <is>
-          <t>229128</t>
+          <t>281759</t>
         </is>
       </c>
       <c r="D775" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E775" t="inlineStr">
         <is>
-          <t>sa</t>
+          <t>KAKAO_CH_MESSAGE_0409_HIKE365SUMMER</t>
         </is>
       </c>
     </row>
@@ -21437,44 +21437,44 @@
     <row r="779">
       <c r="A779" t="inlineStr">
         <is>
-          <t>ganjing78</t>
+          <t>isaackwak</t>
         </is>
       </c>
       <c r="B779" t="inlineStr">
         <is>
-          <t>01065121424</t>
+          <t>01090599860</t>
         </is>
       </c>
       <c r="C779" t="inlineStr">
         <is>
-          <t>78590</t>
+          <t>275913</t>
         </is>
       </c>
       <c r="D779" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="E779" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0410exclusive2</t>
+          <t>Direct</t>
         </is>
       </c>
     </row>
     <row r="780">
       <c r="A780" t="inlineStr">
         <is>
-          <t>kk_3678962368</t>
+          <t>ganjing78</t>
         </is>
       </c>
       <c r="B780" t="inlineStr">
         <is>
-          <t>01041028567</t>
+          <t>01065121424</t>
         </is>
       </c>
       <c r="C780" t="inlineStr">
         <is>
-          <t>250374</t>
+          <t>78590</t>
         </is>
       </c>
       <c r="D780" t="inlineStr">
@@ -21491,81 +21491,81 @@
     <row r="781">
       <c r="A781" t="inlineStr">
         <is>
-          <t>kk_4839433808</t>
+          <t>mtbok</t>
         </is>
       </c>
       <c r="B781" t="inlineStr">
         <is>
-          <t>01025333388</t>
+          <t>01051284339</t>
         </is>
       </c>
       <c r="C781" t="inlineStr">
         <is>
-          <t>304100</t>
+          <t>26917</t>
         </is>
       </c>
       <c r="D781" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E781" t="inlineStr">
         <is>
-          <t>naver_brandsearch_mobile</t>
+          <t>LMS_ECOM_0410exclusive2</t>
         </is>
       </c>
     </row>
     <row r="782">
       <c r="A782" t="inlineStr">
         <is>
-          <t>mtbok</t>
+          <t>kk_4839433808</t>
         </is>
       </c>
       <c r="B782" t="inlineStr">
         <is>
-          <t>01051284339</t>
+          <t>01025333388</t>
         </is>
       </c>
       <c r="C782" t="inlineStr">
         <is>
-          <t>26917</t>
+          <t>304100</t>
         </is>
       </c>
       <c r="D782" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E782" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0410exclusive2</t>
+          <t>naver_brandsearch_mobile</t>
         </is>
       </c>
     </row>
     <row r="783">
       <c r="A783" t="inlineStr">
         <is>
-          <t>isaackwak</t>
+          <t>kk_3678962368</t>
         </is>
       </c>
       <c r="B783" t="inlineStr">
         <is>
-          <t>01090599860</t>
+          <t>01041028567</t>
         </is>
       </c>
       <c r="C783" t="inlineStr">
         <is>
-          <t>275913</t>
+          <t>250374</t>
         </is>
       </c>
       <c r="D783" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E783" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>LMS_ECOM_0410exclusive2</t>
         </is>
       </c>
     </row>
@@ -21680,98 +21680,98 @@
     <row r="788">
       <c r="A788" t="inlineStr">
         <is>
-          <t>kk_4727921763</t>
+          <t>kk_3181873063</t>
         </is>
       </c>
       <c r="B788" t="inlineStr">
         <is>
-          <t>01045673975</t>
+          <t>01026527131</t>
         </is>
       </c>
       <c r="C788" t="inlineStr">
         <is>
-          <t>298138</t>
+          <t>227343</t>
         </is>
       </c>
       <c r="D788" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E788" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>LMS_ECOM_0410exclusive2</t>
         </is>
       </c>
     </row>
     <row r="789">
       <c r="A789" t="inlineStr">
         <is>
-          <t>kk_4839026541</t>
+          <t>kk_4727921763</t>
         </is>
       </c>
       <c r="B789" t="inlineStr">
         <is>
-          <t>01089431507</t>
+          <t>01045673975</t>
         </is>
       </c>
       <c r="C789" t="inlineStr">
         <is>
-          <t>304082</t>
+          <t>298138</t>
         </is>
       </c>
       <c r="D789" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="E789" t="inlineStr">
         <is>
-          <t>[PF]전환_상시(2565MF,비구매자)</t>
+          <t>Direct</t>
         </is>
       </c>
     </row>
     <row r="790">
       <c r="A790" t="inlineStr">
         <is>
-          <t>kk_2757380967</t>
+          <t>kk_4839026541</t>
         </is>
       </c>
       <c r="B790" t="inlineStr">
         <is>
-          <t>01034635649</t>
+          <t>01089431507</t>
         </is>
       </c>
       <c r="C790" t="inlineStr">
         <is>
-          <t>208245</t>
+          <t>304082</t>
         </is>
       </c>
       <c r="D790" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E790" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0410exclusive2</t>
+          <t>[PF]전환_상시(2565MF,비구매자)</t>
         </is>
       </c>
     </row>
     <row r="791">
       <c r="A791" t="inlineStr">
         <is>
-          <t>kk_3181873063</t>
+          <t>kk_2757380967</t>
         </is>
       </c>
       <c r="B791" t="inlineStr">
         <is>
-          <t>01026527131</t>
+          <t>01034635649</t>
         </is>
       </c>
       <c r="C791" t="inlineStr">
         <is>
-          <t>227343</t>
+          <t>208245</t>
         </is>
       </c>
       <c r="D791" t="inlineStr">
@@ -21815,54 +21815,54 @@
     <row r="793">
       <c r="A793" t="inlineStr">
         <is>
-          <t>kk_4519505330</t>
+          <t>kk_3156128258</t>
         </is>
       </c>
       <c r="B793" t="inlineStr">
         <is>
-          <t>01024320028</t>
+          <t>01093995884</t>
         </is>
       </c>
       <c r="C793" t="inlineStr">
         <is>
-          <t>286150</t>
+          <t>223742</t>
         </is>
       </c>
       <c r="D793" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="E793" t="inlineStr">
         <is>
-          <t>KAKAO_CH_MESSAGE_0409_HIKE365SUMMER</t>
+          <t>Direct</t>
         </is>
       </c>
     </row>
     <row r="794">
       <c r="A794" t="inlineStr">
         <is>
-          <t>kk_3156128258</t>
+          <t>kk_4519505330</t>
         </is>
       </c>
       <c r="B794" t="inlineStr">
         <is>
-          <t>01093995884</t>
+          <t>01024320028</t>
         </is>
       </c>
       <c r="C794" t="inlineStr">
         <is>
-          <t>223742</t>
+          <t>286150</t>
         </is>
       </c>
       <c r="D794" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E794" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>KAKAO_CH_MESSAGE_0409_HIKE365SUMMER</t>
         </is>
       </c>
     </row>
@@ -22004,17 +22004,17 @@
     <row r="800">
       <c r="A800" t="inlineStr">
         <is>
-          <t>kk_4368805733</t>
+          <t>kk_3967419156</t>
         </is>
       </c>
       <c r="B800" t="inlineStr">
         <is>
-          <t>01075528863</t>
+          <t>01030207947</t>
         </is>
       </c>
       <c r="C800" t="inlineStr">
         <is>
-          <t>279909</t>
+          <t>270708</t>
         </is>
       </c>
       <c r="D800" t="inlineStr">
@@ -22031,17 +22031,17 @@
     <row r="801">
       <c r="A801" t="inlineStr">
         <is>
-          <t>kk_3967419156</t>
+          <t>kk_4368805733</t>
         </is>
       </c>
       <c r="B801" t="inlineStr">
         <is>
-          <t>01030207947</t>
+          <t>01075528863</t>
         </is>
       </c>
       <c r="C801" t="inlineStr">
         <is>
-          <t>270708</t>
+          <t>279909</t>
         </is>
       </c>
       <c r="D801" t="inlineStr">
@@ -22220,71 +22220,71 @@
     <row r="808">
       <c r="A808" t="inlineStr">
         <is>
-          <t>seizeh</t>
+          <t>l00years</t>
         </is>
       </c>
       <c r="B808" t="inlineStr">
         <is>
-          <t>01090302539</t>
+          <t>01053925529</t>
         </is>
       </c>
       <c r="C808" t="inlineStr">
         <is>
-          <t>68751</t>
+          <t>229454</t>
         </is>
       </c>
       <c r="D808" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E808" t="inlineStr">
         <is>
-          <t>sa</t>
+          <t>LMS_ECOM_0410exclusive2</t>
         </is>
       </c>
     </row>
     <row r="809">
       <c r="A809" t="inlineStr">
         <is>
-          <t>l00years</t>
+          <t>seizeh</t>
         </is>
       </c>
       <c r="B809" t="inlineStr">
         <is>
-          <t>01053925529</t>
+          <t>01090302539</t>
         </is>
       </c>
       <c r="C809" t="inlineStr">
         <is>
-          <t>229454</t>
+          <t>68751</t>
         </is>
       </c>
       <c r="D809" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E809" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0410exclusive2</t>
+          <t>sa</t>
         </is>
       </c>
     </row>
     <row r="810">
       <c r="A810" t="inlineStr">
         <is>
-          <t>noma6420</t>
+          <t>pieerot1</t>
         </is>
       </c>
       <c r="B810" t="inlineStr">
         <is>
-          <t>01071574279</t>
+          <t>01054503186</t>
         </is>
       </c>
       <c r="C810" t="inlineStr">
         <is>
-          <t>304023</t>
+          <t>29988</t>
         </is>
       </c>
       <c r="D810" t="inlineStr">
@@ -22294,24 +22294,24 @@
       </c>
       <c r="E810" t="inlineStr">
         <is>
-          <t>[PF]A SC_상시(1865MF,구매 장바구니)</t>
+          <t>naver_brandsearch_mobile</t>
         </is>
       </c>
     </row>
     <row r="811">
       <c r="A811" t="inlineStr">
         <is>
-          <t>mplkh</t>
+          <t>noma6420</t>
         </is>
       </c>
       <c r="B811" t="inlineStr">
         <is>
-          <t>01085245802</t>
+          <t>01071574279</t>
         </is>
       </c>
       <c r="C811" t="inlineStr">
         <is>
-          <t>160698</t>
+          <t>304023</t>
         </is>
       </c>
       <c r="D811" t="inlineStr">
@@ -22321,24 +22321,24 @@
       </c>
       <c r="E811" t="inlineStr">
         <is>
-          <t>sa</t>
+          <t>[PF]A SC_상시(1865MF,구매 장바구니)</t>
         </is>
       </c>
     </row>
     <row r="812">
       <c r="A812" t="inlineStr">
         <is>
-          <t>pieerot1</t>
+          <t>mplkh</t>
         </is>
       </c>
       <c r="B812" t="inlineStr">
         <is>
-          <t>01054503186</t>
+          <t>01085245802</t>
         </is>
       </c>
       <c r="C812" t="inlineStr">
         <is>
-          <t>29988</t>
+          <t>160698</t>
         </is>
       </c>
       <c r="D812" t="inlineStr">
@@ -22348,7 +22348,7 @@
       </c>
       <c r="E812" t="inlineStr">
         <is>
-          <t>naver_brandsearch_mobile</t>
+          <t>sa</t>
         </is>
       </c>
     </row>
@@ -23327,54 +23327,54 @@
     <row r="849">
       <c r="A849" t="inlineStr">
         <is>
-          <t>kk_4839354093</t>
+          <t>kk_4835738911</t>
         </is>
       </c>
       <c r="B849" t="inlineStr">
         <is>
-          <t>01052243562</t>
+          <t>01034422073</t>
         </is>
       </c>
       <c r="C849" t="inlineStr">
         <is>
-          <t>304098</t>
+          <t>303885</t>
         </is>
       </c>
       <c r="D849" t="inlineStr">
         <is>
-          <t>Organic Traffic</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E849" t="inlineStr">
         <is>
-          <t>(organic)</t>
+          <t>6968489536332</t>
         </is>
       </c>
     </row>
     <row r="850">
       <c r="A850" t="inlineStr">
         <is>
-          <t>kk_4835738911</t>
+          <t>kk_4839354093</t>
         </is>
       </c>
       <c r="B850" t="inlineStr">
         <is>
-          <t>01034422073</t>
+          <t>01052243562</t>
         </is>
       </c>
       <c r="C850" t="inlineStr">
         <is>
-          <t>303885</t>
+          <t>304098</t>
         </is>
       </c>
       <c r="D850" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Organic Traffic</t>
         </is>
       </c>
       <c r="E850" t="inlineStr">
         <is>
-          <t>6968489536332</t>
+          <t>(organic)</t>
         </is>
       </c>
     </row>
@@ -24056,54 +24056,54 @@
     <row r="876">
       <c r="A876" t="inlineStr">
         <is>
-          <t>kk_4840108009</t>
+          <t>xey5000</t>
         </is>
       </c>
       <c r="B876" t="inlineStr">
         <is>
-          <t>01053461423</t>
+          <t>01087768710</t>
         </is>
       </c>
       <c r="C876" t="inlineStr">
         <is>
-          <t>304129</t>
+          <t>143826</t>
         </is>
       </c>
       <c r="D876" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E876" t="inlineStr">
         <is>
-          <t>6968489536332</t>
+          <t>KAKAO_CH_MESSAGE_0409_PANTS</t>
         </is>
       </c>
     </row>
     <row r="877">
       <c r="A877" t="inlineStr">
         <is>
-          <t>xey5000</t>
+          <t>kk_4840108009</t>
         </is>
       </c>
       <c r="B877" t="inlineStr">
         <is>
-          <t>01087768710</t>
+          <t>01053461423</t>
         </is>
       </c>
       <c r="C877" t="inlineStr">
         <is>
-          <t>143826</t>
+          <t>304129</t>
         </is>
       </c>
       <c r="D877" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E877" t="inlineStr">
         <is>
-          <t>KAKAO_CH_MESSAGE_0409_PANTS</t>
+          <t>6968489536332</t>
         </is>
       </c>
     </row>
@@ -24434,54 +24434,54 @@
     <row r="890">
       <c r="A890" t="inlineStr">
         <is>
-          <t>kk_4375973589</t>
+          <t>kmh7710</t>
         </is>
       </c>
       <c r="B890" t="inlineStr">
         <is>
-          <t>01096223641</t>
+          <t>01077108716</t>
         </is>
       </c>
       <c r="C890" t="inlineStr">
         <is>
-          <t>280163</t>
+          <t>164951</t>
         </is>
       </c>
       <c r="D890" t="inlineStr">
         <is>
-          <t>Organic Traffic</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E890" t="inlineStr">
         <is>
-          <t>LMS_ECOM_familycoupon</t>
+          <t>LMS_ECOM_0214_newyear</t>
         </is>
       </c>
     </row>
     <row r="891">
       <c r="A891" t="inlineStr">
         <is>
-          <t>kmh7710</t>
+          <t>kk_4375973589</t>
         </is>
       </c>
       <c r="B891" t="inlineStr">
         <is>
-          <t>01077108716</t>
+          <t>01096223641</t>
         </is>
       </c>
       <c r="C891" t="inlineStr">
         <is>
-          <t>164951</t>
+          <t>280163</t>
         </is>
       </c>
       <c r="D891" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Organic Traffic</t>
         </is>
       </c>
       <c r="E891" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0214_newyear</t>
+          <t>LMS_ECOM_familycoupon</t>
         </is>
       </c>
     </row>
@@ -24542,71 +24542,71 @@
     <row r="894">
       <c r="A894" t="inlineStr">
         <is>
-          <t>kk_4844665214</t>
+          <t>kk_4843611952</t>
         </is>
       </c>
       <c r="B894" t="inlineStr">
         <is>
-          <t>01033424745</t>
+          <t>01068610131</t>
         </is>
       </c>
       <c r="C894" t="inlineStr">
         <is>
-          <t>304377</t>
+          <t>304327</t>
         </is>
       </c>
       <c r="D894" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E894" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>6968489536332</t>
         </is>
       </c>
     </row>
     <row r="895">
       <c r="A895" t="inlineStr">
         <is>
-          <t>kk_4843611952</t>
+          <t>kk_2954504655</t>
         </is>
       </c>
       <c r="B895" t="inlineStr">
         <is>
-          <t>01068610131</t>
+          <t>01024942984</t>
         </is>
       </c>
       <c r="C895" t="inlineStr">
         <is>
-          <t>304327</t>
+          <t>242733</t>
         </is>
       </c>
       <c r="D895" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="E895" t="inlineStr">
         <is>
-          <t>6968489536332</t>
+          <t>Direct</t>
         </is>
       </c>
     </row>
     <row r="896">
       <c r="A896" t="inlineStr">
         <is>
-          <t>kk_2954504655</t>
+          <t>kk_4844665214</t>
         </is>
       </c>
       <c r="B896" t="inlineStr">
         <is>
-          <t>01024942984</t>
+          <t>01033424745</t>
         </is>
       </c>
       <c r="C896" t="inlineStr">
         <is>
-          <t>242733</t>
+          <t>304377</t>
         </is>
       </c>
       <c r="D896" t="inlineStr">
@@ -24704,17 +24704,17 @@
     <row r="900">
       <c r="A900" t="inlineStr">
         <is>
-          <t>kk_4839544665</t>
+          <t>kk_4839477951</t>
         </is>
       </c>
       <c r="B900" t="inlineStr">
         <is>
-          <t>01055350199</t>
+          <t>01020868012</t>
         </is>
       </c>
       <c r="C900" t="inlineStr">
         <is>
-          <t>304104</t>
+          <t>304101</t>
         </is>
       </c>
       <c r="D900" t="inlineStr">
@@ -24731,17 +24731,17 @@
     <row r="901">
       <c r="A901" t="inlineStr">
         <is>
-          <t>kk_4839477951</t>
+          <t>kk_4839544665</t>
         </is>
       </c>
       <c r="B901" t="inlineStr">
         <is>
-          <t>01020868012</t>
+          <t>01055350199</t>
         </is>
       </c>
       <c r="C901" t="inlineStr">
         <is>
-          <t>304101</t>
+          <t>304104</t>
         </is>
       </c>
       <c r="D901" t="inlineStr">
@@ -24839,81 +24839,81 @@
     <row r="905">
       <c r="A905" t="inlineStr">
         <is>
-          <t>kk_2800477789</t>
+          <t>kk_4843439707</t>
         </is>
       </c>
       <c r="B905" t="inlineStr">
         <is>
-          <t>01035177105</t>
+          <t>01022248653</t>
         </is>
       </c>
       <c r="C905" t="inlineStr">
         <is>
-          <t>211095</t>
+          <t>304310</t>
         </is>
       </c>
       <c r="D905" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E905" t="inlineStr">
         <is>
-          <t>KAKAO_alimtalk</t>
+          <t>6968489536332</t>
         </is>
       </c>
     </row>
     <row r="906">
       <c r="A906" t="inlineStr">
         <is>
-          <t>kk_4843439707</t>
+          <t>kk_2800477789</t>
         </is>
       </c>
       <c r="B906" t="inlineStr">
         <is>
-          <t>01022248653</t>
+          <t>01035177105</t>
         </is>
       </c>
       <c r="C906" t="inlineStr">
         <is>
-          <t>304310</t>
+          <t>211095</t>
         </is>
       </c>
       <c r="D906" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E906" t="inlineStr">
         <is>
-          <t>6968489536332</t>
+          <t>KAKAO_alimtalk</t>
         </is>
       </c>
     </row>
     <row r="907">
       <c r="A907" t="inlineStr">
         <is>
-          <t>dmsdud552</t>
+          <t>kk_4844657024</t>
         </is>
       </c>
       <c r="B907" t="inlineStr">
         <is>
-          <t>01054633672</t>
+          <t>01033551784</t>
         </is>
       </c>
       <c r="C907" t="inlineStr">
         <is>
-          <t>132110</t>
+          <t>304376</t>
         </is>
       </c>
       <c r="D907" t="inlineStr">
         <is>
-          <t>Organic Traffic</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E907" t="inlineStr">
         <is>
-          <t>(referral)</t>
+          <t>6968489536332</t>
         </is>
       </c>
     </row>
@@ -24947,81 +24947,81 @@
     <row r="909">
       <c r="A909" t="inlineStr">
         <is>
-          <t>kk_4844657024</t>
+          <t>dmsdud552</t>
         </is>
       </c>
       <c r="B909" t="inlineStr">
         <is>
-          <t>01033551784</t>
+          <t>01054633672</t>
         </is>
       </c>
       <c r="C909" t="inlineStr">
         <is>
-          <t>304376</t>
+          <t>132110</t>
         </is>
       </c>
       <c r="D909" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Organic Traffic</t>
         </is>
       </c>
       <c r="E909" t="inlineStr">
         <is>
-          <t>6968489536332</t>
+          <t>(referral)</t>
         </is>
       </c>
     </row>
     <row r="910">
       <c r="A910" t="inlineStr">
         <is>
-          <t>kk_4839643736</t>
+          <t>kk_4543882817</t>
         </is>
       </c>
       <c r="B910" t="inlineStr">
         <is>
-          <t>01063617035</t>
+          <t>01023875300</t>
         </is>
       </c>
       <c r="C910" t="inlineStr">
         <is>
-          <t>304107</t>
+          <t>287573</t>
         </is>
       </c>
       <c r="D910" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="E910" t="inlineStr">
         <is>
-          <t>naver_brandsearch_mobile</t>
+          <t>미분류</t>
         </is>
       </c>
     </row>
     <row r="911">
       <c r="A911" t="inlineStr">
         <is>
-          <t>kk_4543882817</t>
+          <t>kk_4839643736</t>
         </is>
       </c>
       <c r="B911" t="inlineStr">
         <is>
-          <t>01023875300</t>
+          <t>01063617035</t>
         </is>
       </c>
       <c r="C911" t="inlineStr">
         <is>
-          <t>287573</t>
+          <t>304107</t>
         </is>
       </c>
       <c r="D911" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E911" t="inlineStr">
         <is>
-          <t>미분류</t>
+          <t>naver_brandsearch_mobile</t>
         </is>
       </c>
     </row>
@@ -25055,17 +25055,17 @@
     <row r="913">
       <c r="A913" t="inlineStr">
         <is>
-          <t>kk_4845121221</t>
+          <t>kk_4845173313</t>
         </is>
       </c>
       <c r="B913" t="inlineStr">
         <is>
-          <t>01044632332</t>
+          <t>01024436341</t>
         </is>
       </c>
       <c r="C913" t="inlineStr">
         <is>
-          <t>304393</t>
+          <t>304397</t>
         </is>
       </c>
       <c r="D913" t="inlineStr">
@@ -25082,98 +25082,98 @@
     <row r="914">
       <c r="A914" t="inlineStr">
         <is>
-          <t>kk_4843926419</t>
+          <t>kidultyo</t>
         </is>
       </c>
       <c r="B914" t="inlineStr">
         <is>
-          <t>01034583174</t>
+          <t>01037980315</t>
         </is>
       </c>
       <c r="C914" t="inlineStr">
         <is>
-          <t>304338</t>
+          <t>304331</t>
         </is>
       </c>
       <c r="D914" t="inlineStr">
         <is>
-          <t>Official SNS</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E914" t="inlineStr">
         <is>
-          <t>EFW_04</t>
+          <t>6968489536332</t>
         </is>
       </c>
     </row>
     <row r="915">
       <c r="A915" t="inlineStr">
         <is>
-          <t>kk_4843847622</t>
+          <t>kk_4845121221</t>
         </is>
       </c>
       <c r="B915" t="inlineStr">
         <is>
-          <t>01046990393</t>
+          <t>01044632332</t>
         </is>
       </c>
       <c r="C915" t="inlineStr">
         <is>
-          <t>304336</t>
+          <t>304393</t>
         </is>
       </c>
       <c r="D915" t="inlineStr">
         <is>
-          <t>Organic Traffic</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E915" t="inlineStr">
         <is>
-          <t>(organic)</t>
+          <t>6968489536332</t>
         </is>
       </c>
     </row>
     <row r="916">
       <c r="A916" t="inlineStr">
         <is>
-          <t>kidultyo</t>
+          <t>kk_4843926419</t>
         </is>
       </c>
       <c r="B916" t="inlineStr">
         <is>
-          <t>01037980315</t>
+          <t>01034583174</t>
         </is>
       </c>
       <c r="C916" t="inlineStr">
         <is>
-          <t>304331</t>
+          <t>304338</t>
         </is>
       </c>
       <c r="D916" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Official SNS</t>
         </is>
       </c>
       <c r="E916" t="inlineStr">
         <is>
-          <t>6968489536332</t>
+          <t>EFW_04</t>
         </is>
       </c>
     </row>
     <row r="917">
       <c r="A917" t="inlineStr">
         <is>
-          <t>kk_4845173313</t>
+          <t>kk_4844453283</t>
         </is>
       </c>
       <c r="B917" t="inlineStr">
         <is>
-          <t>01024436341</t>
+          <t>01090262556</t>
         </is>
       </c>
       <c r="C917" t="inlineStr">
         <is>
-          <t>304397</t>
+          <t>304360</t>
         </is>
       </c>
       <c r="D917" t="inlineStr">
@@ -25190,27 +25190,27 @@
     <row r="918">
       <c r="A918" t="inlineStr">
         <is>
-          <t>kk_4844453283</t>
+          <t>kk_4843847622</t>
         </is>
       </c>
       <c r="B918" t="inlineStr">
         <is>
-          <t>01090262556</t>
+          <t>01046990393</t>
         </is>
       </c>
       <c r="C918" t="inlineStr">
         <is>
-          <t>304360</t>
+          <t>304336</t>
         </is>
       </c>
       <c r="D918" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Organic Traffic</t>
         </is>
       </c>
       <c r="E918" t="inlineStr">
         <is>
-          <t>6968489536332</t>
+          <t>(organic)</t>
         </is>
       </c>
     </row>
@@ -25244,17 +25244,17 @@
     <row r="920">
       <c r="A920" t="inlineStr">
         <is>
-          <t>kyoungs424</t>
+          <t>kk_2961062530</t>
         </is>
       </c>
       <c r="B920" t="inlineStr">
         <is>
-          <t>01041509204</t>
+          <t>01050052823</t>
         </is>
       </c>
       <c r="C920" t="inlineStr">
         <is>
-          <t>153760</t>
+          <t>217199</t>
         </is>
       </c>
       <c r="D920" t="inlineStr">
@@ -25264,24 +25264,24 @@
       </c>
       <c r="E920" t="inlineStr">
         <is>
-          <t>KAKAO_alimtalk</t>
+          <t>KAKAO_CH_MENU_0317_S26NEW</t>
         </is>
       </c>
     </row>
     <row r="921">
       <c r="A921" t="inlineStr">
         <is>
-          <t>kk_2961062530</t>
+          <t>kyoungs424</t>
         </is>
       </c>
       <c r="B921" t="inlineStr">
         <is>
-          <t>01050052823</t>
+          <t>01041509204</t>
         </is>
       </c>
       <c r="C921" t="inlineStr">
         <is>
-          <t>217199</t>
+          <t>153760</t>
         </is>
       </c>
       <c r="D921" t="inlineStr">
@@ -25291,7 +25291,7 @@
       </c>
       <c r="E921" t="inlineStr">
         <is>
-          <t>KAKAO_CH_MENU_0317_S26NEW</t>
+          <t>KAKAO_alimtalk</t>
         </is>
       </c>
     </row>
@@ -25352,135 +25352,135 @@
     <row r="924">
       <c r="A924" t="inlineStr">
         <is>
-          <t>kk_4838574281</t>
+          <t>vvip6905</t>
         </is>
       </c>
       <c r="B924" t="inlineStr">
         <is>
-          <t>01092229876</t>
+          <t>01085855275</t>
         </is>
       </c>
       <c r="C924" t="inlineStr">
         <is>
-          <t>304061</t>
+          <t>304027</t>
         </is>
       </c>
       <c r="D924" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E924" t="inlineStr">
         <is>
-          <t>6968489536332</t>
+          <t>Email_mkt</t>
         </is>
       </c>
     </row>
     <row r="925">
       <c r="A925" t="inlineStr">
         <is>
-          <t>vvip6905</t>
+          <t>kk_4838574281</t>
         </is>
       </c>
       <c r="B925" t="inlineStr">
         <is>
-          <t>01085855275</t>
+          <t>01092229876</t>
         </is>
       </c>
       <c r="C925" t="inlineStr">
         <is>
-          <t>304027</t>
+          <t>304061</t>
         </is>
       </c>
       <c r="D925" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E925" t="inlineStr">
         <is>
-          <t>Email_mkt</t>
+          <t>6968489536332</t>
         </is>
       </c>
     </row>
     <row r="926">
       <c r="A926" t="inlineStr">
         <is>
-          <t>kk_4835912712</t>
+          <t>kjo1726</t>
         </is>
       </c>
       <c r="B926" t="inlineStr">
         <is>
-          <t>01094418375</t>
+          <t>01087840160</t>
         </is>
       </c>
       <c r="C926" t="inlineStr">
         <is>
-          <t>303898</t>
+          <t>155918</t>
         </is>
       </c>
       <c r="D926" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E926" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>KAKAO_alimtalk</t>
         </is>
       </c>
     </row>
     <row r="927">
       <c r="A927" t="inlineStr">
         <is>
-          <t>kjo1726</t>
+          <t>plumrhkr1</t>
         </is>
       </c>
       <c r="B927" t="inlineStr">
         <is>
-          <t>01087840160</t>
+          <t>01074112056</t>
         </is>
       </c>
       <c r="C927" t="inlineStr">
         <is>
-          <t>155918</t>
+          <t>303916</t>
         </is>
       </c>
       <c r="D927" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Organic Traffic</t>
         </is>
       </c>
       <c r="E927" t="inlineStr">
         <is>
-          <t>KAKAO_alimtalk</t>
+          <t>(organic)</t>
         </is>
       </c>
     </row>
     <row r="928">
       <c r="A928" t="inlineStr">
         <is>
-          <t>plumrhkr1</t>
+          <t>kk_4835912712</t>
         </is>
       </c>
       <c r="B928" t="inlineStr">
         <is>
-          <t>01074112056</t>
+          <t>01094418375</t>
         </is>
       </c>
       <c r="C928" t="inlineStr">
         <is>
-          <t>303916</t>
+          <t>303898</t>
         </is>
       </c>
       <c r="D928" t="inlineStr">
         <is>
-          <t>Organic Traffic</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="E928" t="inlineStr">
         <is>
-          <t>(organic)</t>
+          <t>Direct</t>
         </is>
       </c>
     </row>
@@ -25568,54 +25568,54 @@
     <row r="932">
       <c r="A932" t="inlineStr">
         <is>
-          <t>kk_4446020087</t>
+          <t>kk_3798545067</t>
         </is>
       </c>
       <c r="B932" t="inlineStr">
         <is>
-          <t>01089773053</t>
+          <t>01023751319</t>
         </is>
       </c>
       <c r="C932" t="inlineStr">
         <is>
-          <t>282273</t>
+          <t>258449</t>
         </is>
       </c>
       <c r="D932" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E932" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0214_newyear</t>
+          <t>sa</t>
         </is>
       </c>
     </row>
     <row r="933">
       <c r="A933" t="inlineStr">
         <is>
-          <t>kk_3798545067</t>
+          <t>kk_4446020087</t>
         </is>
       </c>
       <c r="B933" t="inlineStr">
         <is>
-          <t>01023751319</t>
+          <t>01089773053</t>
         </is>
       </c>
       <c r="C933" t="inlineStr">
         <is>
-          <t>258449</t>
+          <t>282273</t>
         </is>
       </c>
       <c r="D933" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E933" t="inlineStr">
         <is>
-          <t>sa</t>
+          <t>LMS_ECOM_0214_newyear</t>
         </is>
       </c>
     </row>
@@ -25676,54 +25676,54 @@
     <row r="936">
       <c r="A936" t="inlineStr">
         <is>
-          <t>kk_4844452226</t>
+          <t>kk_4844609437</t>
         </is>
       </c>
       <c r="B936" t="inlineStr">
         <is>
-          <t>01096801866</t>
+          <t>01046808931</t>
         </is>
       </c>
       <c r="C936" t="inlineStr">
         <is>
-          <t>304359</t>
+          <t>304372</t>
         </is>
       </c>
       <c r="D936" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Official SNS</t>
         </is>
       </c>
       <c r="E936" t="inlineStr">
         <is>
-          <t>6968489536332</t>
+          <t>(referral)</t>
         </is>
       </c>
     </row>
     <row r="937">
       <c r="A937" t="inlineStr">
         <is>
-          <t>kk_4844609437</t>
+          <t>kk_4844452226</t>
         </is>
       </c>
       <c r="B937" t="inlineStr">
         <is>
-          <t>01046808931</t>
+          <t>01096801866</t>
         </is>
       </c>
       <c r="C937" t="inlineStr">
         <is>
-          <t>304372</t>
+          <t>304359</t>
         </is>
       </c>
       <c r="D937" t="inlineStr">
         <is>
-          <t>Official SNS</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E937" t="inlineStr">
         <is>
-          <t>(referral)</t>
+          <t>6968489536332</t>
         </is>
       </c>
     </row>
@@ -25811,27 +25811,27 @@
     <row r="941">
       <c r="A941" t="inlineStr">
         <is>
-          <t>kk_4840913383</t>
+          <t>kk_4841278242</t>
         </is>
       </c>
       <c r="B941" t="inlineStr">
         <is>
-          <t>01099887927</t>
+          <t>01046197965</t>
         </is>
       </c>
       <c r="C941" t="inlineStr">
         <is>
-          <t>304174</t>
+          <t>304190</t>
         </is>
       </c>
       <c r="D941" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>Organic Traffic</t>
         </is>
       </c>
       <c r="E941" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>(referral)</t>
         </is>
       </c>
     </row>
@@ -25865,54 +25865,54 @@
     <row r="943">
       <c r="A943" t="inlineStr">
         <is>
-          <t>kk_4840417532</t>
+          <t>kk_2750710108</t>
         </is>
       </c>
       <c r="B943" t="inlineStr">
         <is>
-          <t>01053409288</t>
+          <t>01062707475</t>
         </is>
       </c>
       <c r="C943" t="inlineStr">
         <is>
-          <t>304147</t>
+          <t>207211</t>
         </is>
       </c>
       <c r="D943" t="inlineStr">
         <is>
-          <t>Official SNS</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="E943" t="inlineStr">
         <is>
-          <t>EFW_04</t>
+          <t>Direct</t>
         </is>
       </c>
     </row>
     <row r="944">
       <c r="A944" t="inlineStr">
         <is>
-          <t>kk_2750710108</t>
+          <t>kk_4840417532</t>
         </is>
       </c>
       <c r="B944" t="inlineStr">
         <is>
-          <t>01062707475</t>
+          <t>01053409288</t>
         </is>
       </c>
       <c r="C944" t="inlineStr">
         <is>
-          <t>207211</t>
+          <t>304147</t>
         </is>
       </c>
       <c r="D944" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>Official SNS</t>
         </is>
       </c>
       <c r="E944" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>EFW_04</t>
         </is>
       </c>
     </row>
@@ -25946,81 +25946,81 @@
     <row r="946">
       <c r="A946" t="inlineStr">
         <is>
-          <t>kk_4841278242</t>
+          <t>kk_4840913383</t>
         </is>
       </c>
       <c r="B946" t="inlineStr">
         <is>
-          <t>01046197965</t>
+          <t>01099887927</t>
         </is>
       </c>
       <c r="C946" t="inlineStr">
         <is>
-          <t>304190</t>
+          <t>304174</t>
         </is>
       </c>
       <c r="D946" t="inlineStr">
         <is>
-          <t>Organic Traffic</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="E946" t="inlineStr">
         <is>
-          <t>(referral)</t>
+          <t>Direct</t>
         </is>
       </c>
     </row>
     <row r="947">
       <c r="A947" t="inlineStr">
         <is>
-          <t>kk_4837971410</t>
+          <t>music214</t>
         </is>
       </c>
       <c r="B947" t="inlineStr">
         <is>
-          <t>01045750650</t>
+          <t>01031023988</t>
         </is>
       </c>
       <c r="C947" t="inlineStr">
         <is>
-          <t>304028</t>
+          <t>303965</t>
         </is>
       </c>
       <c r="D947" t="inlineStr">
         <is>
-          <t>Official SNS</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E947" t="inlineStr">
         <is>
-          <t>EFW_04</t>
+          <t>6968489536332</t>
         </is>
       </c>
     </row>
     <row r="948">
       <c r="A948" t="inlineStr">
         <is>
-          <t>music214</t>
+          <t>kk_4837971410</t>
         </is>
       </c>
       <c r="B948" t="inlineStr">
         <is>
-          <t>01031023988</t>
+          <t>01045750650</t>
         </is>
       </c>
       <c r="C948" t="inlineStr">
         <is>
-          <t>303965</t>
+          <t>304028</t>
         </is>
       </c>
       <c r="D948" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Official SNS</t>
         </is>
       </c>
       <c r="E948" t="inlineStr">
         <is>
-          <t>6968489536332</t>
+          <t>EFW_04</t>
         </is>
       </c>
     </row>
@@ -26135,17 +26135,17 @@
     <row r="953">
       <c r="A953" t="inlineStr">
         <is>
-          <t>kk_3776403631</t>
+          <t>kimchhgood</t>
         </is>
       </c>
       <c r="B953" t="inlineStr">
         <is>
-          <t>01034755755</t>
+          <t>01092133961</t>
         </is>
       </c>
       <c r="C953" t="inlineStr">
         <is>
-          <t>255908</t>
+          <t>53493</t>
         </is>
       </c>
       <c r="D953" t="inlineStr">
@@ -26155,24 +26155,24 @@
       </c>
       <c r="E953" t="inlineStr">
         <is>
-          <t>KAKAO_alimtalk</t>
+          <t>EDM_TOP</t>
         </is>
       </c>
     </row>
     <row r="954">
       <c r="A954" t="inlineStr">
         <is>
-          <t>kimchhgood</t>
+          <t>kk_3776403631</t>
         </is>
       </c>
       <c r="B954" t="inlineStr">
         <is>
-          <t>01092133961</t>
+          <t>01034755755</t>
         </is>
       </c>
       <c r="C954" t="inlineStr">
         <is>
-          <t>53493</t>
+          <t>255908</t>
         </is>
       </c>
       <c r="D954" t="inlineStr">
@@ -26182,7 +26182,7 @@
       </c>
       <c r="E954" t="inlineStr">
         <is>
-          <t>EDM_TOP</t>
+          <t>KAKAO_alimtalk</t>
         </is>
       </c>
     </row>
@@ -26324,17 +26324,17 @@
     <row r="960">
       <c r="A960" t="inlineStr">
         <is>
-          <t>nikemkr</t>
+          <t>kk_4841799872</t>
         </is>
       </c>
       <c r="B960" t="inlineStr">
         <is>
-          <t>01032361592</t>
+          <t>01023236956</t>
         </is>
       </c>
       <c r="C960" t="inlineStr">
         <is>
-          <t>145423</t>
+          <t>304205</t>
         </is>
       </c>
       <c r="D960" t="inlineStr">
@@ -26344,7 +26344,7 @@
       </c>
       <c r="E960" t="inlineStr">
         <is>
-          <t>naver_brandsearch_mobile</t>
+          <t>컬럼비아_DPA_240530</t>
         </is>
       </c>
     </row>
@@ -26378,17 +26378,17 @@
     <row r="962">
       <c r="A962" t="inlineStr">
         <is>
-          <t>kk_4841799872</t>
+          <t>nikemkr</t>
         </is>
       </c>
       <c r="B962" t="inlineStr">
         <is>
-          <t>01023236956</t>
+          <t>01032361592</t>
         </is>
       </c>
       <c r="C962" t="inlineStr">
         <is>
-          <t>304205</t>
+          <t>145423</t>
         </is>
       </c>
       <c r="D962" t="inlineStr">
@@ -26398,105 +26398,105 @@
       </c>
       <c r="E962" t="inlineStr">
         <is>
-          <t>컬럼비아_DPA_240530</t>
+          <t>naver_brandsearch_mobile</t>
         </is>
       </c>
     </row>
     <row r="963">
       <c r="A963" t="inlineStr">
         <is>
-          <t>sbhbi</t>
+          <t>lolia875</t>
         </is>
       </c>
       <c r="B963" t="inlineStr">
         <is>
-          <t>01047153767</t>
+          <t>01067138715</t>
         </is>
       </c>
       <c r="C963" t="inlineStr">
         <is>
-          <t>174291</t>
+          <t>161251</t>
         </is>
       </c>
       <c r="D963" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E963" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>6968489536332</t>
         </is>
       </c>
     </row>
     <row r="964">
       <c r="A964" t="inlineStr">
         <is>
-          <t>lolia875</t>
+          <t>kk_3241081989</t>
         </is>
       </c>
       <c r="B964" t="inlineStr">
         <is>
-          <t>01067138715</t>
+          <t>01072287165</t>
         </is>
       </c>
       <c r="C964" t="inlineStr">
         <is>
-          <t>161251</t>
+          <t>234608</t>
         </is>
       </c>
       <c r="D964" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E964" t="inlineStr">
         <is>
-          <t>6968489536332</t>
+          <t>KAKAO_alimtalk</t>
         </is>
       </c>
     </row>
     <row r="965">
       <c r="A965" t="inlineStr">
         <is>
-          <t>kk_3241081989</t>
+          <t>sbhbi</t>
         </is>
       </c>
       <c r="B965" t="inlineStr">
         <is>
-          <t>01072287165</t>
+          <t>01047153767</t>
         </is>
       </c>
       <c r="C965" t="inlineStr">
         <is>
-          <t>234608</t>
+          <t>174291</t>
         </is>
       </c>
       <c r="D965" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="E965" t="inlineStr">
         <is>
-          <t>KAKAO_alimtalk</t>
+          <t>Direct</t>
         </is>
       </c>
     </row>
     <row r="966">
       <c r="A966" t="inlineStr">
         <is>
-          <t>makaveli</t>
+          <t>kk_4837595875</t>
         </is>
       </c>
       <c r="B966" t="inlineStr">
         <is>
-          <t>01086237086</t>
+          <t>01057852463</t>
         </is>
       </c>
       <c r="C966" t="inlineStr">
         <is>
-          <t>66164</t>
+          <t>304000</t>
         </is>
       </c>
       <c r="D966" t="inlineStr">
@@ -26506,78 +26506,78 @@
       </c>
       <c r="E966" t="inlineStr">
         <is>
-          <t>naver_brandsearch_mobile</t>
+          <t>6968489536332</t>
         </is>
       </c>
     </row>
     <row r="967">
       <c r="A967" t="inlineStr">
         <is>
-          <t>kk_4837152929</t>
+          <t>sjl4534</t>
         </is>
       </c>
       <c r="B967" t="inlineStr">
         <is>
-          <t>01047050730</t>
+          <t>01028023660</t>
         </is>
       </c>
       <c r="C967" t="inlineStr">
         <is>
-          <t>303966</t>
+          <t>174607</t>
         </is>
       </c>
       <c r="D967" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E967" t="inlineStr">
         <is>
-          <t>6968489536332</t>
+          <t>KAKAO_CH_MESSAGE_0409_EXCLUSIVE</t>
         </is>
       </c>
     </row>
     <row r="968">
       <c r="A968" t="inlineStr">
         <is>
-          <t>kk_3430866338</t>
+          <t>makaveli</t>
         </is>
       </c>
       <c r="B968" t="inlineStr">
         <is>
-          <t>01026364692</t>
+          <t>01086237086</t>
         </is>
       </c>
       <c r="C968" t="inlineStr">
         <is>
-          <t>242249</t>
+          <t>66164</t>
         </is>
       </c>
       <c r="D968" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E968" t="inlineStr">
         <is>
-          <t>Email_mkt</t>
+          <t>naver_brandsearch_mobile</t>
         </is>
       </c>
     </row>
     <row r="969">
       <c r="A969" t="inlineStr">
         <is>
-          <t>sjl4534</t>
+          <t>kk_3430866338</t>
         </is>
       </c>
       <c r="B969" t="inlineStr">
         <is>
-          <t>01028023660</t>
+          <t>01026364692</t>
         </is>
       </c>
       <c r="C969" t="inlineStr">
         <is>
-          <t>174607</t>
+          <t>242249</t>
         </is>
       </c>
       <c r="D969" t="inlineStr">
@@ -26587,24 +26587,24 @@
       </c>
       <c r="E969" t="inlineStr">
         <is>
-          <t>KAKAO_CH_MESSAGE_0409_EXCLUSIVE</t>
+          <t>Email_mkt</t>
         </is>
       </c>
     </row>
     <row r="970">
       <c r="A970" t="inlineStr">
         <is>
-          <t>kk_4837595875</t>
+          <t>kk_4837152929</t>
         </is>
       </c>
       <c r="B970" t="inlineStr">
         <is>
-          <t>01057852463</t>
+          <t>01047050730</t>
         </is>
       </c>
       <c r="C970" t="inlineStr">
         <is>
-          <t>304000</t>
+          <t>303966</t>
         </is>
       </c>
       <c r="D970" t="inlineStr">
@@ -26621,54 +26621,54 @@
     <row r="971">
       <c r="A971" t="inlineStr">
         <is>
-          <t>sagtp</t>
+          <t>kk_3483542670</t>
         </is>
       </c>
       <c r="B971" t="inlineStr">
         <is>
-          <t>01087431193</t>
+          <t>01025352246</t>
         </is>
       </c>
       <c r="C971" t="inlineStr">
         <is>
-          <t>203717</t>
+          <t>244637</t>
         </is>
       </c>
       <c r="D971" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Awareness</t>
         </is>
       </c>
       <c r="E971" t="inlineStr">
         <is>
-          <t>6968489536332</t>
+          <t>benz_running_program_2026_coupon</t>
         </is>
       </c>
     </row>
     <row r="972">
       <c r="A972" t="inlineStr">
         <is>
-          <t>kk_3483542670</t>
+          <t>sagtp</t>
         </is>
       </c>
       <c r="B972" t="inlineStr">
         <is>
-          <t>01025352246</t>
+          <t>01087431193</t>
         </is>
       </c>
       <c r="C972" t="inlineStr">
         <is>
-          <t>244637</t>
+          <t>203717</t>
         </is>
       </c>
       <c r="D972" t="inlineStr">
         <is>
-          <t>Awareness</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E972" t="inlineStr">
         <is>
-          <t>benz_running_program_2026_coupon</t>
+          <t>6968489536332</t>
         </is>
       </c>
     </row>
@@ -26756,17 +26756,17 @@
     <row r="976">
       <c r="A976" t="inlineStr">
         <is>
-          <t>kk_3183517395</t>
+          <t>kk_4846729102</t>
         </is>
       </c>
       <c r="B976" t="inlineStr">
         <is>
-          <t>01082019936</t>
+          <t>01084771303</t>
         </is>
       </c>
       <c r="C976" t="inlineStr">
         <is>
-          <t>228501</t>
+          <t>304461</t>
         </is>
       </c>
       <c r="D976" t="inlineStr">
@@ -26783,44 +26783,44 @@
     <row r="977">
       <c r="A977" t="inlineStr">
         <is>
-          <t>kk_2788668233</t>
+          <t>imgain0422</t>
         </is>
       </c>
       <c r="B977" t="inlineStr">
         <is>
-          <t>01041696139</t>
+          <t>01029135546</t>
         </is>
       </c>
       <c r="C977" t="inlineStr">
         <is>
-          <t>210002</t>
+          <t>181451</t>
         </is>
       </c>
       <c r="D977" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="E977" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Direct</t>
         </is>
       </c>
     </row>
     <row r="978">
       <c r="A978" t="inlineStr">
         <is>
-          <t>imgain0422</t>
+          <t>ch5115</t>
         </is>
       </c>
       <c r="B978" t="inlineStr">
         <is>
-          <t>01029135546</t>
+          <t>01084479339</t>
         </is>
       </c>
       <c r="C978" t="inlineStr">
         <is>
-          <t>181451</t>
+          <t>240557</t>
         </is>
       </c>
       <c r="D978" t="inlineStr">
@@ -26864,27 +26864,27 @@
     <row r="980">
       <c r="A980" t="inlineStr">
         <is>
-          <t>ch5115</t>
+          <t>kk_2788668233</t>
         </is>
       </c>
       <c r="B980" t="inlineStr">
         <is>
-          <t>01084479339</t>
+          <t>01041696139</t>
         </is>
       </c>
       <c r="C980" t="inlineStr">
         <is>
-          <t>240557</t>
+          <t>210002</t>
         </is>
       </c>
       <c r="D980" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E980" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>Paid Ad</t>
         </is>
       </c>
     </row>
@@ -26918,17 +26918,17 @@
     <row r="982">
       <c r="A982" t="inlineStr">
         <is>
-          <t>kk_4846729102</t>
+          <t>kk_3183517395</t>
         </is>
       </c>
       <c r="B982" t="inlineStr">
         <is>
-          <t>01084771303</t>
+          <t>01082019936</t>
         </is>
       </c>
       <c r="C982" t="inlineStr">
         <is>
-          <t>304461</t>
+          <t>228501</t>
         </is>
       </c>
       <c r="D982" t="inlineStr">
@@ -26945,135 +26945,135 @@
     <row r="983">
       <c r="A983" t="inlineStr">
         <is>
-          <t>kjhk5404</t>
+          <t>kk_2775500473</t>
         </is>
       </c>
       <c r="B983" t="inlineStr">
         <is>
-          <t>01027390700</t>
+          <t>01045659020</t>
         </is>
       </c>
       <c r="C983" t="inlineStr">
         <is>
-          <t>280120</t>
+          <t>209371</t>
         </is>
       </c>
       <c r="D983" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Organic Traffic</t>
         </is>
       </c>
       <c r="E983" t="inlineStr">
         <is>
-          <t>KAKAO_alimtalk</t>
+          <t>(referral)</t>
         </is>
       </c>
     </row>
     <row r="984">
       <c r="A984" t="inlineStr">
         <is>
-          <t>kk_2775500473</t>
+          <t>kk_3650586439</t>
         </is>
       </c>
       <c r="B984" t="inlineStr">
         <is>
-          <t>01045659020</t>
+          <t>01029107056</t>
         </is>
       </c>
       <c r="C984" t="inlineStr">
         <is>
-          <t>209371</t>
+          <t>249153</t>
         </is>
       </c>
       <c r="D984" t="inlineStr">
         <is>
-          <t>Organic Traffic</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="E984" t="inlineStr">
         <is>
-          <t>(referral)</t>
+          <t>Direct</t>
         </is>
       </c>
     </row>
     <row r="985">
       <c r="A985" t="inlineStr">
         <is>
-          <t>kk_3242479813</t>
+          <t>kk_4844076820</t>
         </is>
       </c>
       <c r="B985" t="inlineStr">
         <is>
-          <t>01040431115</t>
+          <t>01091346366</t>
         </is>
       </c>
       <c r="C985" t="inlineStr">
         <is>
-          <t>234768</t>
+          <t>304343</t>
         </is>
       </c>
       <c r="D985" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E985" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0410exclusive2</t>
+          <t>6968489536332</t>
         </is>
       </c>
     </row>
     <row r="986">
       <c r="A986" t="inlineStr">
         <is>
-          <t>kk_3650586439</t>
+          <t>kjhk5404</t>
         </is>
       </c>
       <c r="B986" t="inlineStr">
         <is>
-          <t>01029107056</t>
+          <t>01027390700</t>
         </is>
       </c>
       <c r="C986" t="inlineStr">
         <is>
-          <t>249153</t>
+          <t>280120</t>
         </is>
       </c>
       <c r="D986" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E986" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>KAKAO_alimtalk</t>
         </is>
       </c>
     </row>
     <row r="987">
       <c r="A987" t="inlineStr">
         <is>
-          <t>kk_4844076820</t>
+          <t>kk_3242479813</t>
         </is>
       </c>
       <c r="B987" t="inlineStr">
         <is>
-          <t>01091346366</t>
+          <t>01040431115</t>
         </is>
       </c>
       <c r="C987" t="inlineStr">
         <is>
-          <t>304343</t>
+          <t>234768</t>
         </is>
       </c>
       <c r="D987" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E987" t="inlineStr">
         <is>
-          <t>6968489536332</t>
+          <t>LMS_ECOM_0410exclusive2</t>
         </is>
       </c>
     </row>
@@ -27107,54 +27107,54 @@
     <row r="989">
       <c r="A989" t="inlineStr">
         <is>
-          <t>kk_4434329905</t>
+          <t>kk_4522711623</t>
         </is>
       </c>
       <c r="B989" t="inlineStr">
         <is>
-          <t>01071724035</t>
+          <t>01089870313</t>
         </is>
       </c>
       <c r="C989" t="inlineStr">
         <is>
-          <t>281922</t>
+          <t>286306</t>
         </is>
       </c>
       <c r="D989" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E989" t="inlineStr">
         <is>
-          <t>Email_mkt</t>
+          <t>6968489536332</t>
         </is>
       </c>
     </row>
     <row r="990">
       <c r="A990" t="inlineStr">
         <is>
-          <t>kk_4522711623</t>
+          <t>kk_4434329905</t>
         </is>
       </c>
       <c r="B990" t="inlineStr">
         <is>
-          <t>01089870313</t>
+          <t>01071724035</t>
         </is>
       </c>
       <c r="C990" t="inlineStr">
         <is>
-          <t>286306</t>
+          <t>281922</t>
         </is>
       </c>
       <c r="D990" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E990" t="inlineStr">
         <is>
-          <t>6968489536332</t>
+          <t>Email_mkt</t>
         </is>
       </c>
     </row>
@@ -27242,17 +27242,17 @@
     <row r="994">
       <c r="A994" t="inlineStr">
         <is>
-          <t>gus7526</t>
+          <t>kk_3213636735</t>
         </is>
       </c>
       <c r="B994" t="inlineStr">
         <is>
-          <t>01050931023</t>
+          <t>01071338973</t>
         </is>
       </c>
       <c r="C994" t="inlineStr">
         <is>
-          <t>140860</t>
+          <t>232010</t>
         </is>
       </c>
       <c r="D994" t="inlineStr">
@@ -27262,34 +27262,34 @@
       </c>
       <c r="E994" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0410exclusive2</t>
+          <t>KAKAO_CH_MENU_0226_TRAILRUN</t>
         </is>
       </c>
     </row>
     <row r="995">
       <c r="A995" t="inlineStr">
         <is>
-          <t>kk_4839241951</t>
+          <t>kk_4228106377</t>
         </is>
       </c>
       <c r="B995" t="inlineStr">
         <is>
-          <t>01079146776</t>
+          <t>01063165271</t>
         </is>
       </c>
       <c r="C995" t="inlineStr">
         <is>
-          <t>304090</t>
+          <t>273193</t>
         </is>
       </c>
       <c r="D995" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E995" t="inlineStr">
         <is>
-          <t>6968489536332</t>
+          <t>LMS_ECOM_0410exclusive2</t>
         </is>
       </c>
     </row>
@@ -27323,17 +27323,17 @@
     <row r="997">
       <c r="A997" t="inlineStr">
         <is>
-          <t>z090909x</t>
+          <t>kk_4839241951</t>
         </is>
       </c>
       <c r="B997" t="inlineStr">
         <is>
-          <t>01092058111</t>
+          <t>01079146776</t>
         </is>
       </c>
       <c r="C997" t="inlineStr">
         <is>
-          <t>113003</t>
+          <t>304090</t>
         </is>
       </c>
       <c r="D997" t="inlineStr">
@@ -27350,17 +27350,17 @@
     <row r="998">
       <c r="A998" t="inlineStr">
         <is>
-          <t>kk_4228106377</t>
+          <t>gus7526</t>
         </is>
       </c>
       <c r="B998" t="inlineStr">
         <is>
-          <t>01063165271</t>
+          <t>01050931023</t>
         </is>
       </c>
       <c r="C998" t="inlineStr">
         <is>
-          <t>273193</t>
+          <t>140860</t>
         </is>
       </c>
       <c r="D998" t="inlineStr">
@@ -27377,71 +27377,71 @@
     <row r="999">
       <c r="A999" t="inlineStr">
         <is>
-          <t>xoxoie2</t>
+          <t>ssama</t>
         </is>
       </c>
       <c r="B999" t="inlineStr">
         <is>
-          <t>01043560834</t>
+          <t>01056271982</t>
         </is>
       </c>
       <c r="C999" t="inlineStr">
         <is>
-          <t>304072</t>
+          <t>47874</t>
         </is>
       </c>
       <c r="D999" t="inlineStr">
         <is>
-          <t>Official SNS</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E999" t="inlineStr">
         <is>
-          <t>EFW_04</t>
+          <t>LMS_ECOM_0410exclusive2</t>
         </is>
       </c>
     </row>
     <row r="1000">
       <c r="A1000" t="inlineStr">
         <is>
-          <t>kk_3213636735</t>
+          <t>xoxoie2</t>
         </is>
       </c>
       <c r="B1000" t="inlineStr">
         <is>
-          <t>01071338973</t>
+          <t>01043560834</t>
         </is>
       </c>
       <c r="C1000" t="inlineStr">
         <is>
-          <t>232010</t>
+          <t>304072</t>
         </is>
       </c>
       <c r="D1000" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Official SNS</t>
         </is>
       </c>
       <c r="E1000" t="inlineStr">
         <is>
-          <t>KAKAO_CH_MENU_0226_TRAILRUN</t>
+          <t>EFW_04</t>
         </is>
       </c>
     </row>
     <row r="1001">
       <c r="A1001" t="inlineStr">
         <is>
-          <t>kk_4840045474</t>
+          <t>z090909x</t>
         </is>
       </c>
       <c r="B1001" t="inlineStr">
         <is>
-          <t>01096310429</t>
+          <t>01092058111</t>
         </is>
       </c>
       <c r="C1001" t="inlineStr">
         <is>
-          <t>304122</t>
+          <t>113003</t>
         </is>
       </c>
       <c r="D1001" t="inlineStr">
@@ -27458,98 +27458,98 @@
     <row r="1002">
       <c r="A1002" t="inlineStr">
         <is>
-          <t>ssama</t>
+          <t>kk_4840045474</t>
         </is>
       </c>
       <c r="B1002" t="inlineStr">
         <is>
-          <t>01056271982</t>
+          <t>01096310429</t>
         </is>
       </c>
       <c r="C1002" t="inlineStr">
         <is>
-          <t>47874</t>
+          <t>304122</t>
         </is>
       </c>
       <c r="D1002" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E1002" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0410exclusive2</t>
+          <t>6968489536332</t>
         </is>
       </c>
     </row>
     <row r="1003">
       <c r="A1003" t="inlineStr">
         <is>
-          <t>enel778</t>
+          <t>kk_3234166915</t>
         </is>
       </c>
       <c r="B1003" t="inlineStr">
         <is>
-          <t>01086066364</t>
+          <t>01082632995</t>
         </is>
       </c>
       <c r="C1003" t="inlineStr">
         <is>
-          <t>207732</t>
+          <t>233887</t>
         </is>
       </c>
       <c r="D1003" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="E1003" t="inlineStr">
         <is>
-          <t>Email_mkt</t>
+          <t>Direct</t>
         </is>
       </c>
     </row>
     <row r="1004">
       <c r="A1004" t="inlineStr">
         <is>
-          <t>kk_3234166915</t>
+          <t>scaler</t>
         </is>
       </c>
       <c r="B1004" t="inlineStr">
         <is>
-          <t>01082632995</t>
+          <t>01037090080</t>
         </is>
       </c>
       <c r="C1004" t="inlineStr">
         <is>
-          <t>233887</t>
+          <t>178752</t>
         </is>
       </c>
       <c r="D1004" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E1004" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>KAKAO_CH_MESSAGE_0409_EXCLUSIVE</t>
         </is>
       </c>
     </row>
     <row r="1005">
       <c r="A1005" t="inlineStr">
         <is>
-          <t>scaler</t>
+          <t>kk_4837597613</t>
         </is>
       </c>
       <c r="B1005" t="inlineStr">
         <is>
-          <t>01037090080</t>
+          <t>01089218630</t>
         </is>
       </c>
       <c r="C1005" t="inlineStr">
         <is>
-          <t>178752</t>
+          <t>304001</t>
         </is>
       </c>
       <c r="D1005" t="inlineStr">
@@ -27593,17 +27593,17 @@
     <row r="1007">
       <c r="A1007" t="inlineStr">
         <is>
-          <t>kk_4837597613</t>
+          <t>enel778</t>
         </is>
       </c>
       <c r="B1007" t="inlineStr">
         <is>
-          <t>01089218630</t>
+          <t>01086066364</t>
         </is>
       </c>
       <c r="C1007" t="inlineStr">
         <is>
-          <t>304001</t>
+          <t>207732</t>
         </is>
       </c>
       <c r="D1007" t="inlineStr">
@@ -27613,24 +27613,24 @@
       </c>
       <c r="E1007" t="inlineStr">
         <is>
-          <t>KAKAO_CH_MESSAGE_0409_EXCLUSIVE</t>
+          <t>Email_mkt</t>
         </is>
       </c>
     </row>
     <row r="1008">
       <c r="A1008" t="inlineStr">
         <is>
-          <t>kk_4444429966</t>
+          <t>kk_2757334528</t>
         </is>
       </c>
       <c r="B1008" t="inlineStr">
         <is>
-          <t>01032219702</t>
+          <t>01089379633</t>
         </is>
       </c>
       <c r="C1008" t="inlineStr">
         <is>
-          <t>282222</t>
+          <t>208240</t>
         </is>
       </c>
       <c r="D1008" t="inlineStr">
@@ -27674,17 +27674,17 @@
     <row r="1010">
       <c r="A1010" t="inlineStr">
         <is>
-          <t>kk_2757334528</t>
+          <t>kk_4444429966</t>
         </is>
       </c>
       <c r="B1010" t="inlineStr">
         <is>
-          <t>01089379633</t>
+          <t>01032219702</t>
         </is>
       </c>
       <c r="C1010" t="inlineStr">
         <is>
-          <t>208240</t>
+          <t>282222</t>
         </is>
       </c>
       <c r="D1010" t="inlineStr">
@@ -27728,54 +27728,54 @@
     <row r="1012">
       <c r="A1012" t="inlineStr">
         <is>
-          <t>mse001</t>
+          <t>kk_4218204827</t>
         </is>
       </c>
       <c r="B1012" t="inlineStr">
         <is>
-          <t>01085185510</t>
+          <t>01023704903</t>
         </is>
       </c>
       <c r="C1012" t="inlineStr">
         <is>
-          <t>227227</t>
+          <t>272698</t>
         </is>
       </c>
       <c r="D1012" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="E1012" t="inlineStr">
         <is>
-          <t>KAKAO_alimtalk</t>
+          <t>Direct</t>
         </is>
       </c>
     </row>
     <row r="1013">
       <c r="A1013" t="inlineStr">
         <is>
-          <t>kk_4218204827</t>
+          <t>mse001</t>
         </is>
       </c>
       <c r="B1013" t="inlineStr">
         <is>
-          <t>01023704903</t>
+          <t>01085185510</t>
         </is>
       </c>
       <c r="C1013" t="inlineStr">
         <is>
-          <t>272698</t>
+          <t>227227</t>
         </is>
       </c>
       <c r="D1013" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E1013" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>KAKAO_alimtalk</t>
         </is>
       </c>
     </row>
@@ -27809,27 +27809,27 @@
     <row r="1015">
       <c r="A1015" t="inlineStr">
         <is>
-          <t>kk_3169777000</t>
+          <t>kk_4375003446</t>
         </is>
       </c>
       <c r="B1015" t="inlineStr">
         <is>
-          <t>01089348462</t>
+          <t>01087457282</t>
         </is>
       </c>
       <c r="C1015" t="inlineStr">
         <is>
-          <t>224876</t>
+          <t>280131</t>
         </is>
       </c>
       <c r="D1015" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E1015" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>LMS_ECOM_0410exclusive2</t>
         </is>
       </c>
     </row>
@@ -27863,27 +27863,27 @@
     <row r="1017">
       <c r="A1017" t="inlineStr">
         <is>
-          <t>kk_4375003446</t>
+          <t>kk_3169777000</t>
         </is>
       </c>
       <c r="B1017" t="inlineStr">
         <is>
-          <t>01087457282</t>
+          <t>01089348462</t>
         </is>
       </c>
       <c r="C1017" t="inlineStr">
         <is>
-          <t>280131</t>
+          <t>224876</t>
         </is>
       </c>
       <c r="D1017" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="E1017" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0410exclusive2</t>
+          <t>Direct</t>
         </is>
       </c>
     </row>
@@ -27944,17 +27944,17 @@
     <row r="1020">
       <c r="A1020" t="inlineStr">
         <is>
-          <t>kk_4472536591</t>
+          <t>kk_3688034999</t>
         </is>
       </c>
       <c r="B1020" t="inlineStr">
         <is>
-          <t>01037057526</t>
+          <t>01025408262</t>
         </is>
       </c>
       <c r="C1020" t="inlineStr">
         <is>
-          <t>283897</t>
+          <t>250755</t>
         </is>
       </c>
       <c r="D1020" t="inlineStr">
@@ -27971,44 +27971,44 @@
     <row r="1021">
       <c r="A1021" t="inlineStr">
         <is>
-          <t>ohsm0065</t>
+          <t>kk_4472536591</t>
         </is>
       </c>
       <c r="B1021" t="inlineStr">
         <is>
-          <t>01056170065</t>
+          <t>01037057526</t>
         </is>
       </c>
       <c r="C1021" t="inlineStr">
         <is>
-          <t>74567</t>
+          <t>283897</t>
         </is>
       </c>
       <c r="D1021" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E1021" t="inlineStr">
         <is>
-          <t>[PF]트래픽_유사+관심사</t>
+          <t>KAKAO_alimtalk</t>
         </is>
       </c>
     </row>
     <row r="1022">
       <c r="A1022" t="inlineStr">
         <is>
-          <t>xuswldls</t>
+          <t>kk_3444865211</t>
         </is>
       </c>
       <c r="B1022" t="inlineStr">
         <is>
-          <t>01027349414</t>
+          <t>01021964871</t>
         </is>
       </c>
       <c r="C1022" t="inlineStr">
         <is>
-          <t>133308</t>
+          <t>242799</t>
         </is>
       </c>
       <c r="D1022" t="inlineStr">
@@ -28025,71 +28025,71 @@
     <row r="1023">
       <c r="A1023" t="inlineStr">
         <is>
-          <t>kk_3688034999</t>
+          <t>kk_2768989214</t>
         </is>
       </c>
       <c r="B1023" t="inlineStr">
         <is>
-          <t>01025408262</t>
+          <t>01095004289</t>
         </is>
       </c>
       <c r="C1023" t="inlineStr">
         <is>
-          <t>250755</t>
+          <t>209015</t>
         </is>
       </c>
       <c r="D1023" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="E1023" t="inlineStr">
         <is>
-          <t>KAKAO_alimtalk</t>
+          <t>Direct</t>
         </is>
       </c>
     </row>
     <row r="1024">
       <c r="A1024" t="inlineStr">
         <is>
-          <t>kk_2768989214</t>
+          <t>kk_4247630261</t>
         </is>
       </c>
       <c r="B1024" t="inlineStr">
         <is>
-          <t>01095004289</t>
+          <t>01091437323</t>
         </is>
       </c>
       <c r="C1024" t="inlineStr">
         <is>
-          <t>209015</t>
+          <t>274140</t>
         </is>
       </c>
       <c r="D1024" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>Organic Traffic</t>
         </is>
       </c>
       <c r="E1024" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>(referral)</t>
         </is>
       </c>
     </row>
     <row r="1025">
       <c r="A1025" t="inlineStr">
         <is>
-          <t>kk_3444865211</t>
+          <t>xuswldls</t>
         </is>
       </c>
       <c r="B1025" t="inlineStr">
         <is>
-          <t>01021964871</t>
+          <t>01027349414</t>
         </is>
       </c>
       <c r="C1025" t="inlineStr">
         <is>
-          <t>242799</t>
+          <t>133308</t>
         </is>
       </c>
       <c r="D1025" t="inlineStr">
@@ -28106,98 +28106,98 @@
     <row r="1026">
       <c r="A1026" t="inlineStr">
         <is>
-          <t>kk_4247630261</t>
+          <t>ohsm0065</t>
         </is>
       </c>
       <c r="B1026" t="inlineStr">
         <is>
-          <t>01091437323</t>
+          <t>01056170065</t>
         </is>
       </c>
       <c r="C1026" t="inlineStr">
         <is>
-          <t>274140</t>
+          <t>74567</t>
         </is>
       </c>
       <c r="D1026" t="inlineStr">
         <is>
-          <t>Organic Traffic</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E1026" t="inlineStr">
         <is>
-          <t>(referral)</t>
+          <t>[PF]트래픽_유사+관심사</t>
         </is>
       </c>
     </row>
     <row r="1027">
       <c r="A1027" t="inlineStr">
         <is>
-          <t>chibird</t>
+          <t>escalater</t>
         </is>
       </c>
       <c r="B1027" t="inlineStr">
         <is>
-          <t>01031187674</t>
+          <t>01090911461</t>
         </is>
       </c>
       <c r="C1027" t="inlineStr">
         <is>
-          <t>219288</t>
+          <t>240051</t>
         </is>
       </c>
       <c r="D1027" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="E1027" t="inlineStr">
         <is>
-          <t>sa</t>
+          <t>Direct</t>
         </is>
       </c>
     </row>
     <row r="1028">
       <c r="A1028" t="inlineStr">
         <is>
-          <t>kk_3837527580</t>
+          <t>kk_3181917333</t>
         </is>
       </c>
       <c r="B1028" t="inlineStr">
         <is>
-          <t>01084311738</t>
+          <t>01072258509</t>
         </is>
       </c>
       <c r="C1028" t="inlineStr">
         <is>
-          <t>264113</t>
+          <t>227380</t>
         </is>
       </c>
       <c r="D1028" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="E1028" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0410exclusive2</t>
+          <t>Direct</t>
         </is>
       </c>
     </row>
     <row r="1029">
       <c r="A1029" t="inlineStr">
         <is>
-          <t>kk_3858585698</t>
+          <t>kk_3837527580</t>
         </is>
       </c>
       <c r="B1029" t="inlineStr">
         <is>
-          <t>01092163429</t>
+          <t>01084311738</t>
         </is>
       </c>
       <c r="C1029" t="inlineStr">
         <is>
-          <t>265508</t>
+          <t>264113</t>
         </is>
       </c>
       <c r="D1029" t="inlineStr">
@@ -28207,34 +28207,34 @@
       </c>
       <c r="E1029" t="inlineStr">
         <is>
-          <t>KAKAO_alimtalk</t>
+          <t>LMS_ECOM_0410exclusive2</t>
         </is>
       </c>
     </row>
     <row r="1030">
       <c r="A1030" t="inlineStr">
         <is>
-          <t>kk_3181917333</t>
+          <t>chibird</t>
         </is>
       </c>
       <c r="B1030" t="inlineStr">
         <is>
-          <t>01072258509</t>
+          <t>01031187674</t>
         </is>
       </c>
       <c r="C1030" t="inlineStr">
         <is>
-          <t>227380</t>
+          <t>219288</t>
         </is>
       </c>
       <c r="D1030" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E1030" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>sa</t>
         </is>
       </c>
     </row>
@@ -28268,27 +28268,27 @@
     <row r="1032">
       <c r="A1032" t="inlineStr">
         <is>
-          <t>escalater</t>
+          <t>kk_3858585698</t>
         </is>
       </c>
       <c r="B1032" t="inlineStr">
         <is>
-          <t>01090911461</t>
+          <t>01092163429</t>
         </is>
       </c>
       <c r="C1032" t="inlineStr">
         <is>
-          <t>240051</t>
+          <t>265508</t>
         </is>
       </c>
       <c r="D1032" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E1032" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>KAKAO_alimtalk</t>
         </is>
       </c>
     </row>
@@ -28322,17 +28322,17 @@
     <row r="1034">
       <c r="A1034" t="inlineStr">
         <is>
-          <t>aya6969</t>
+          <t>seul6169</t>
         </is>
       </c>
       <c r="B1034" t="inlineStr">
         <is>
-          <t>01076590009</t>
+          <t>01066116699</t>
         </is>
       </c>
       <c r="C1034" t="inlineStr">
         <is>
-          <t>162562</t>
+          <t>234239</t>
         </is>
       </c>
       <c r="D1034" t="inlineStr">
@@ -28342,24 +28342,24 @@
       </c>
       <c r="E1034" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0410exclusive2</t>
+          <t>KAKAO_alimtalk</t>
         </is>
       </c>
     </row>
     <row r="1035">
       <c r="A1035" t="inlineStr">
         <is>
-          <t>kk_4523594127</t>
+          <t>kk_4517851709</t>
         </is>
       </c>
       <c r="B1035" t="inlineStr">
         <is>
-          <t>01085735215</t>
+          <t>01066445714</t>
         </is>
       </c>
       <c r="C1035" t="inlineStr">
         <is>
-          <t>286358</t>
+          <t>286074</t>
         </is>
       </c>
       <c r="D1035" t="inlineStr">
@@ -28376,71 +28376,71 @@
     <row r="1036">
       <c r="A1036" t="inlineStr">
         <is>
-          <t>kk_4467707148</t>
+          <t>kk_3933534683</t>
         </is>
       </c>
       <c r="B1036" t="inlineStr">
         <is>
-          <t>01030843332</t>
+          <t>01030153796</t>
         </is>
       </c>
       <c r="C1036" t="inlineStr">
         <is>
-          <t>283560</t>
+          <t>269069</t>
         </is>
       </c>
       <c r="D1036" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="E1036" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0410exclusive2</t>
+          <t>Direct</t>
         </is>
       </c>
     </row>
     <row r="1037">
       <c r="A1037" t="inlineStr">
         <is>
-          <t>seul6169</t>
+          <t>kk_3013902343</t>
         </is>
       </c>
       <c r="B1037" t="inlineStr">
         <is>
-          <t>01066116699</t>
+          <t>01051802326</t>
         </is>
       </c>
       <c r="C1037" t="inlineStr">
         <is>
-          <t>234239</t>
+          <t>219219</t>
         </is>
       </c>
       <c r="D1037" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E1037" t="inlineStr">
         <is>
-          <t>KAKAO_alimtalk</t>
+          <t>6968489536332</t>
         </is>
       </c>
     </row>
     <row r="1038">
       <c r="A1038" t="inlineStr">
         <is>
-          <t>mansoogi</t>
+          <t>hursean</t>
         </is>
       </c>
       <c r="B1038" t="inlineStr">
         <is>
-          <t>01093240897</t>
+          <t>01091975738</t>
         </is>
       </c>
       <c r="C1038" t="inlineStr">
         <is>
-          <t>25243</t>
+          <t>123130</t>
         </is>
       </c>
       <c r="D1038" t="inlineStr">
@@ -28450,24 +28450,24 @@
       </c>
       <c r="E1038" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0410exclusive2</t>
+          <t>Email_mkt</t>
         </is>
       </c>
     </row>
     <row r="1039">
       <c r="A1039" t="inlineStr">
         <is>
-          <t>kk_3185867832</t>
+          <t>kk_2940110361</t>
         </is>
       </c>
       <c r="B1039" t="inlineStr">
         <is>
-          <t>01022086508</t>
+          <t>01035353200</t>
         </is>
       </c>
       <c r="C1039" t="inlineStr">
         <is>
-          <t>229863</t>
+          <t>216362</t>
         </is>
       </c>
       <c r="D1039" t="inlineStr">
@@ -28484,98 +28484,98 @@
     <row r="1040">
       <c r="A1040" t="inlineStr">
         <is>
-          <t>kk_4840061178</t>
+          <t>kk_4523594127</t>
         </is>
       </c>
       <c r="B1040" t="inlineStr">
         <is>
-          <t>01082357895</t>
+          <t>01085735215</t>
         </is>
       </c>
       <c r="C1040" t="inlineStr">
         <is>
-          <t>304124</t>
+          <t>286358</t>
         </is>
       </c>
       <c r="D1040" t="inlineStr">
         <is>
-          <t>Awareness</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E1040" t="inlineStr">
         <is>
-          <t>benz_running_program_2026_coupon</t>
+          <t>LMS_ECOM_0410exclusive2</t>
         </is>
       </c>
     </row>
     <row r="1041">
       <c r="A1041" t="inlineStr">
         <is>
-          <t>kk_4338209948</t>
+          <t>kk_4840061178</t>
         </is>
       </c>
       <c r="B1041" t="inlineStr">
         <is>
-          <t>01088132379</t>
+          <t>01082357895</t>
         </is>
       </c>
       <c r="C1041" t="inlineStr">
         <is>
-          <t>278781</t>
+          <t>304124</t>
         </is>
       </c>
       <c r="D1041" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Awareness</t>
         </is>
       </c>
       <c r="E1041" t="inlineStr">
         <is>
-          <t>KAKAO_alimtalk</t>
+          <t>benz_running_program_2026_coupon</t>
         </is>
       </c>
     </row>
     <row r="1042">
       <c r="A1042" t="inlineStr">
         <is>
-          <t>kk_3933534683</t>
+          <t>kk_4338209948</t>
         </is>
       </c>
       <c r="B1042" t="inlineStr">
         <is>
-          <t>01030153796</t>
+          <t>01088132379</t>
         </is>
       </c>
       <c r="C1042" t="inlineStr">
         <is>
-          <t>269069</t>
+          <t>278781</t>
         </is>
       </c>
       <c r="D1042" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E1042" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>KAKAO_alimtalk</t>
         </is>
       </c>
     </row>
     <row r="1043">
       <c r="A1043" t="inlineStr">
         <is>
-          <t>hursean</t>
+          <t>mansoogi</t>
         </is>
       </c>
       <c r="B1043" t="inlineStr">
         <is>
-          <t>01091975738</t>
+          <t>01093240897</t>
         </is>
       </c>
       <c r="C1043" t="inlineStr">
         <is>
-          <t>123130</t>
+          <t>25243</t>
         </is>
       </c>
       <c r="D1043" t="inlineStr">
@@ -28585,51 +28585,51 @@
       </c>
       <c r="E1043" t="inlineStr">
         <is>
-          <t>Email_mkt</t>
+          <t>LMS_ECOM_0410exclusive2</t>
         </is>
       </c>
     </row>
     <row r="1044">
       <c r="A1044" t="inlineStr">
         <is>
-          <t>kk_3013902343</t>
+          <t>kk_4467707148</t>
         </is>
       </c>
       <c r="B1044" t="inlineStr">
         <is>
-          <t>01051802326</t>
+          <t>01030843332</t>
         </is>
       </c>
       <c r="C1044" t="inlineStr">
         <is>
-          <t>219219</t>
+          <t>283560</t>
         </is>
       </c>
       <c r="D1044" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E1044" t="inlineStr">
         <is>
-          <t>6968489536332</t>
+          <t>LMS_ECOM_0410exclusive2</t>
         </is>
       </c>
     </row>
     <row r="1045">
       <c r="A1045" t="inlineStr">
         <is>
-          <t>kk_2940110361</t>
+          <t>aya6969</t>
         </is>
       </c>
       <c r="B1045" t="inlineStr">
         <is>
-          <t>01035353200</t>
+          <t>01076590009</t>
         </is>
       </c>
       <c r="C1045" t="inlineStr">
         <is>
-          <t>216362</t>
+          <t>162562</t>
         </is>
       </c>
       <c r="D1045" t="inlineStr">
@@ -28646,17 +28646,17 @@
     <row r="1046">
       <c r="A1046" t="inlineStr">
         <is>
-          <t>kk_4517851709</t>
+          <t>kk_3185867832</t>
         </is>
       </c>
       <c r="B1046" t="inlineStr">
         <is>
-          <t>01066445714</t>
+          <t>01022086508</t>
         </is>
       </c>
       <c r="C1046" t="inlineStr">
         <is>
-          <t>286074</t>
+          <t>229863</t>
         </is>
       </c>
       <c r="D1046" t="inlineStr">
@@ -28673,98 +28673,98 @@
     <row r="1047">
       <c r="A1047" t="inlineStr">
         <is>
-          <t>boram1991</t>
+          <t>kk_4526169965</t>
         </is>
       </c>
       <c r="B1047" t="inlineStr">
         <is>
-          <t>01023431078</t>
+          <t>01076289838</t>
         </is>
       </c>
       <c r="C1047" t="inlineStr">
         <is>
-          <t>119498</t>
+          <t>286553</t>
         </is>
       </c>
       <c r="D1047" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E1047" t="inlineStr">
         <is>
-          <t>6968489536332</t>
+          <t>KAKAO_CH_MESSAGE_0409_HIKE365SUMMER</t>
         </is>
       </c>
     </row>
     <row r="1048">
       <c r="A1048" t="inlineStr">
         <is>
-          <t>jhmin000</t>
+          <t>kk_4351086966</t>
         </is>
       </c>
       <c r="B1048" t="inlineStr">
         <is>
-          <t>01086241606</t>
+          <t>01042088262</t>
         </is>
       </c>
       <c r="C1048" t="inlineStr">
         <is>
-          <t>201165</t>
+          <t>279266</t>
         </is>
       </c>
       <c r="D1048" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="E1048" t="inlineStr">
         <is>
-          <t>KAKAO_CH_MESSAGE_0409_HIKE365SUMMER</t>
+          <t>Direct</t>
         </is>
       </c>
     </row>
     <row r="1049">
       <c r="A1049" t="inlineStr">
         <is>
-          <t>kk_3154612153</t>
+          <t>bbluesea</t>
         </is>
       </c>
       <c r="B1049" t="inlineStr">
         <is>
-          <t>01056681753</t>
+          <t>01076473601</t>
         </is>
       </c>
       <c r="C1049" t="inlineStr">
         <is>
-          <t>223664</t>
+          <t>152067</t>
         </is>
       </c>
       <c r="D1049" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E1049" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>KAKAO_CH_MENU_260406_LIGHTJACKET</t>
         </is>
       </c>
     </row>
     <row r="1050">
       <c r="A1050" t="inlineStr">
         <is>
-          <t>kk_4726499171</t>
+          <t>kk_3665803645</t>
         </is>
       </c>
       <c r="B1050" t="inlineStr">
         <is>
-          <t>01093851013</t>
+          <t>01095549123</t>
         </is>
       </c>
       <c r="C1050" t="inlineStr">
         <is>
-          <t>297987</t>
+          <t>249835</t>
         </is>
       </c>
       <c r="D1050" t="inlineStr">
@@ -28774,24 +28774,24 @@
       </c>
       <c r="E1050" t="inlineStr">
         <is>
-          <t>KAKAO_CH_MESSAGE_0409_HIKE365SUMMER</t>
+          <t>KAKAO_CH_MESSAGE_0409_EXCLUSIVE</t>
         </is>
       </c>
     </row>
     <row r="1051">
       <c r="A1051" t="inlineStr">
         <is>
-          <t>bbluesea</t>
+          <t>kk_3155938902</t>
         </is>
       </c>
       <c r="B1051" t="inlineStr">
         <is>
-          <t>01076473601</t>
+          <t>01098557018</t>
         </is>
       </c>
       <c r="C1051" t="inlineStr">
         <is>
-          <t>152067</t>
+          <t>223731</t>
         </is>
       </c>
       <c r="D1051" t="inlineStr">
@@ -28801,159 +28801,159 @@
       </c>
       <c r="E1051" t="inlineStr">
         <is>
-          <t>KAKAO_CH_MENU_260406_LIGHTJACKET</t>
+          <t>KAKAO_CH_MESSAGE_0409_HIKE365SUMMER</t>
         </is>
       </c>
     </row>
     <row r="1052">
       <c r="A1052" t="inlineStr">
         <is>
-          <t>kk_4837943303</t>
+          <t>kk_3638512879</t>
         </is>
       </c>
       <c r="B1052" t="inlineStr">
         <is>
-          <t>01054817243</t>
+          <t>01053330589</t>
         </is>
       </c>
       <c r="C1052" t="inlineStr">
         <is>
-          <t>304025</t>
+          <t>248574</t>
         </is>
       </c>
       <c r="D1052" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E1052" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>KAKAO_CH_MESSAGE_0409_HIKE365SUMMER</t>
         </is>
       </c>
     </row>
     <row r="1053">
       <c r="A1053" t="inlineStr">
         <is>
-          <t>kk_4351086966</t>
+          <t>kk_4726499171</t>
         </is>
       </c>
       <c r="B1053" t="inlineStr">
         <is>
-          <t>01042088262</t>
+          <t>01093851013</t>
         </is>
       </c>
       <c r="C1053" t="inlineStr">
         <is>
-          <t>279266</t>
+          <t>297987</t>
         </is>
       </c>
       <c r="D1053" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E1053" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>KAKAO_CH_MESSAGE_0409_HIKE365SUMMER</t>
         </is>
       </c>
     </row>
     <row r="1054">
       <c r="A1054" t="inlineStr">
         <is>
-          <t>kk_4526169965</t>
+          <t>kk_4837943303</t>
         </is>
       </c>
       <c r="B1054" t="inlineStr">
         <is>
-          <t>01076289838</t>
+          <t>01054817243</t>
         </is>
       </c>
       <c r="C1054" t="inlineStr">
         <is>
-          <t>286553</t>
+          <t>304025</t>
         </is>
       </c>
       <c r="D1054" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="E1054" t="inlineStr">
         <is>
-          <t>KAKAO_CH_MESSAGE_0409_HIKE365SUMMER</t>
+          <t>Direct</t>
         </is>
       </c>
     </row>
     <row r="1055">
       <c r="A1055" t="inlineStr">
         <is>
-          <t>kk_3155938902</t>
+          <t>boram1991</t>
         </is>
       </c>
       <c r="B1055" t="inlineStr">
         <is>
-          <t>01098557018</t>
+          <t>01023431078</t>
         </is>
       </c>
       <c r="C1055" t="inlineStr">
         <is>
-          <t>223731</t>
+          <t>119498</t>
         </is>
       </c>
       <c r="D1055" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E1055" t="inlineStr">
         <is>
-          <t>KAKAO_CH_MESSAGE_0409_HIKE365SUMMER</t>
+          <t>6968489536332</t>
         </is>
       </c>
     </row>
     <row r="1056">
       <c r="A1056" t="inlineStr">
         <is>
-          <t>kk_3638512879</t>
+          <t>kk_3154612153</t>
         </is>
       </c>
       <c r="B1056" t="inlineStr">
         <is>
-          <t>01053330589</t>
+          <t>01056681753</t>
         </is>
       </c>
       <c r="C1056" t="inlineStr">
         <is>
-          <t>248574</t>
+          <t>223664</t>
         </is>
       </c>
       <c r="D1056" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="E1056" t="inlineStr">
         <is>
-          <t>KAKAO_CH_MESSAGE_0409_HIKE365SUMMER</t>
+          <t>Direct</t>
         </is>
       </c>
     </row>
     <row r="1057">
       <c r="A1057" t="inlineStr">
         <is>
-          <t>kk_3665803645</t>
+          <t>jhmin000</t>
         </is>
       </c>
       <c r="B1057" t="inlineStr">
         <is>
-          <t>01095549123</t>
+          <t>01086241606</t>
         </is>
       </c>
       <c r="C1057" t="inlineStr">
         <is>
-          <t>249835</t>
+          <t>201165</t>
         </is>
       </c>
       <c r="D1057" t="inlineStr">
@@ -28963,7 +28963,7 @@
       </c>
       <c r="E1057" t="inlineStr">
         <is>
-          <t>KAKAO_CH_MESSAGE_0409_EXCLUSIVE</t>
+          <t>KAKAO_CH_MESSAGE_0409_HIKE365SUMMER</t>
         </is>
       </c>
     </row>
@@ -29024,17 +29024,17 @@
     <row r="1060">
       <c r="A1060" t="inlineStr">
         <is>
-          <t>kk_3693586748</t>
+          <t>kk_3180615052</t>
         </is>
       </c>
       <c r="B1060" t="inlineStr">
         <is>
-          <t>01063679756</t>
+          <t>01077203676</t>
         </is>
       </c>
       <c r="C1060" t="inlineStr">
         <is>
-          <t>251013</t>
+          <t>226112</t>
         </is>
       </c>
       <c r="D1060" t="inlineStr">
@@ -29044,7 +29044,7 @@
       </c>
       <c r="E1060" t="inlineStr">
         <is>
-          <t>KAKAO_alimtalk</t>
+          <t>Email_mkt</t>
         </is>
       </c>
     </row>
@@ -29078,27 +29078,27 @@
     <row r="1062">
       <c r="A1062" t="inlineStr">
         <is>
-          <t>wns1118</t>
+          <t>kk_3693586748</t>
         </is>
       </c>
       <c r="B1062" t="inlineStr">
         <is>
-          <t>01090185590</t>
+          <t>01063679756</t>
         </is>
       </c>
       <c r="C1062" t="inlineStr">
         <is>
-          <t>303893</t>
+          <t>251013</t>
         </is>
       </c>
       <c r="D1062" t="inlineStr">
         <is>
-          <t>Organic Traffic</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E1062" t="inlineStr">
         <is>
-          <t>(organic)</t>
+          <t>KAKAO_alimtalk</t>
         </is>
       </c>
     </row>
@@ -29132,17 +29132,17 @@
     <row r="1064">
       <c r="A1064" t="inlineStr">
         <is>
-          <t>jeen1228</t>
+          <t>wns1118</t>
         </is>
       </c>
       <c r="B1064" t="inlineStr">
         <is>
-          <t>01033512662</t>
+          <t>01090185590</t>
         </is>
       </c>
       <c r="C1064" t="inlineStr">
         <is>
-          <t>223087</t>
+          <t>303893</t>
         </is>
       </c>
       <c r="D1064" t="inlineStr">
@@ -29159,27 +29159,27 @@
     <row r="1065">
       <c r="A1065" t="inlineStr">
         <is>
-          <t>kk_3180615052</t>
+          <t>jeen1228</t>
         </is>
       </c>
       <c r="B1065" t="inlineStr">
         <is>
-          <t>01077203676</t>
+          <t>01033512662</t>
         </is>
       </c>
       <c r="C1065" t="inlineStr">
         <is>
-          <t>226112</t>
+          <t>223087</t>
         </is>
       </c>
       <c r="D1065" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Organic Traffic</t>
         </is>
       </c>
       <c r="E1065" t="inlineStr">
         <is>
-          <t>Email_mkt</t>
+          <t>(organic)</t>
         </is>
       </c>
     </row>
@@ -29240,71 +29240,71 @@
     <row r="1068">
       <c r="A1068" t="inlineStr">
         <is>
-          <t>pentagram</t>
+          <t>kk_2807863527</t>
         </is>
       </c>
       <c r="B1068" t="inlineStr">
         <is>
-          <t>01093327353</t>
+          <t>01042669625</t>
         </is>
       </c>
       <c r="C1068" t="inlineStr">
         <is>
-          <t>131085</t>
+          <t>211605</t>
         </is>
       </c>
       <c r="D1068" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E1068" t="inlineStr">
         <is>
-          <t>KAKAO_alimtalk</t>
+          <t>[PF]전환_회원가입(유사)</t>
         </is>
       </c>
     </row>
     <row r="1069">
       <c r="A1069" t="inlineStr">
         <is>
-          <t>dltndgy99</t>
+          <t>pentagram</t>
         </is>
       </c>
       <c r="B1069" t="inlineStr">
         <is>
-          <t>01024587982</t>
+          <t>01093327353</t>
         </is>
       </c>
       <c r="C1069" t="inlineStr">
         <is>
-          <t>156217</t>
+          <t>131085</t>
         </is>
       </c>
       <c r="D1069" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E1069" t="inlineStr">
         <is>
-          <t>naver_brandsearch_mobile</t>
+          <t>KAKAO_alimtalk</t>
         </is>
       </c>
     </row>
     <row r="1070">
       <c r="A1070" t="inlineStr">
         <is>
-          <t>kk_2807863527</t>
+          <t>dltndgy99</t>
         </is>
       </c>
       <c r="B1070" t="inlineStr">
         <is>
-          <t>01042669625</t>
+          <t>01024587982</t>
         </is>
       </c>
       <c r="C1070" t="inlineStr">
         <is>
-          <t>211605</t>
+          <t>156217</t>
         </is>
       </c>
       <c r="D1070" t="inlineStr">
@@ -29314,7 +29314,7 @@
       </c>
       <c r="E1070" t="inlineStr">
         <is>
-          <t>[PF]전환_회원가입(유사)</t>
+          <t>naver_brandsearch_mobile</t>
         </is>
       </c>
     </row>
@@ -29348,54 +29348,54 @@
     <row r="1072">
       <c r="A1072" t="inlineStr">
         <is>
-          <t>wisbrain</t>
+          <t>hihijs34</t>
         </is>
       </c>
       <c r="B1072" t="inlineStr">
         <is>
-          <t>01047220186</t>
+          <t>01093230529</t>
         </is>
       </c>
       <c r="C1072" t="inlineStr">
         <is>
-          <t>188067</t>
+          <t>128947</t>
         </is>
       </c>
       <c r="D1072" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E1072" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>[PF]A+SC_상시(1865MF,구매+장바구니)</t>
         </is>
       </c>
     </row>
     <row r="1073">
       <c r="A1073" t="inlineStr">
         <is>
-          <t>kk_4427490834</t>
+          <t>wisbrain</t>
         </is>
       </c>
       <c r="B1073" t="inlineStr">
         <is>
-          <t>01034704205</t>
+          <t>01047220186</t>
         </is>
       </c>
       <c r="C1073" t="inlineStr">
         <is>
-          <t>281590</t>
+          <t>188067</t>
         </is>
       </c>
       <c r="D1073" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="E1073" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0410exclusive2</t>
+          <t>Direct</t>
         </is>
       </c>
     </row>
@@ -29429,44 +29429,44 @@
     <row r="1075">
       <c r="A1075" t="inlineStr">
         <is>
-          <t>hihijs34</t>
+          <t>kk_4427490834</t>
         </is>
       </c>
       <c r="B1075" t="inlineStr">
         <is>
-          <t>01093230529</t>
+          <t>01034704205</t>
         </is>
       </c>
       <c r="C1075" t="inlineStr">
         <is>
-          <t>128947</t>
+          <t>281590</t>
         </is>
       </c>
       <c r="D1075" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E1075" t="inlineStr">
         <is>
-          <t>[PF]A+SC_상시(1865MF,구매+장바구니)</t>
+          <t>LMS_ECOM_0410exclusive2</t>
         </is>
       </c>
     </row>
     <row r="1076">
       <c r="A1076" t="inlineStr">
         <is>
-          <t>kk_3349199057</t>
+          <t>kk_3973703558</t>
         </is>
       </c>
       <c r="B1076" t="inlineStr">
         <is>
-          <t>01071630312</t>
+          <t>01048590748</t>
         </is>
       </c>
       <c r="C1076" t="inlineStr">
         <is>
-          <t>239388</t>
+          <t>271020</t>
         </is>
       </c>
       <c r="D1076" t="inlineStr">
@@ -29483,17 +29483,17 @@
     <row r="1077">
       <c r="A1077" t="inlineStr">
         <is>
-          <t>kk_3024318364</t>
+          <t>kk_4578503399</t>
         </is>
       </c>
       <c r="B1077" t="inlineStr">
         <is>
-          <t>01050308038</t>
+          <t>01088660330</t>
         </is>
       </c>
       <c r="C1077" t="inlineStr">
         <is>
-          <t>219525</t>
+          <t>288374</t>
         </is>
       </c>
       <c r="D1077" t="inlineStr">
@@ -29510,17 +29510,17 @@
     <row r="1078">
       <c r="A1078" t="inlineStr">
         <is>
-          <t>hyschant</t>
+          <t>pls4u</t>
         </is>
       </c>
       <c r="B1078" t="inlineStr">
         <is>
-          <t>01065306675</t>
+          <t>01085985482</t>
         </is>
       </c>
       <c r="C1078" t="inlineStr">
         <is>
-          <t>108579</t>
+          <t>88257</t>
         </is>
       </c>
       <c r="D1078" t="inlineStr">
@@ -29530,24 +29530,24 @@
       </c>
       <c r="E1078" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0410exclusive2</t>
+          <t>LMS_ECOM_0401_trailrunning</t>
         </is>
       </c>
     </row>
     <row r="1079">
       <c r="A1079" t="inlineStr">
         <is>
-          <t>kk_4525043459</t>
+          <t>kk_3754052831</t>
         </is>
       </c>
       <c r="B1079" t="inlineStr">
         <is>
-          <t>01088312135</t>
+          <t>01092180804</t>
         </is>
       </c>
       <c r="C1079" t="inlineStr">
         <is>
-          <t>286464</t>
+          <t>254339</t>
         </is>
       </c>
       <c r="D1079" t="inlineStr">
@@ -29564,71 +29564,71 @@
     <row r="1080">
       <c r="A1080" t="inlineStr">
         <is>
-          <t>kk_2825715315</t>
+          <t>yongshin</t>
         </is>
       </c>
       <c r="B1080" t="inlineStr">
         <is>
-          <t>01077229654</t>
+          <t>01053867821</t>
         </is>
       </c>
       <c r="C1080" t="inlineStr">
         <is>
-          <t>212719</t>
+          <t>277896</t>
         </is>
       </c>
       <c r="D1080" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="E1080" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0410exclusive2</t>
+          <t>Direct</t>
         </is>
       </c>
     </row>
     <row r="1081">
       <c r="A1081" t="inlineStr">
         <is>
-          <t>camiblanco</t>
+          <t>kk_3024318364</t>
         </is>
       </c>
       <c r="B1081" t="inlineStr">
         <is>
-          <t>01072190103</t>
+          <t>01050308038</t>
         </is>
       </c>
       <c r="C1081" t="inlineStr">
         <is>
-          <t>232545</t>
+          <t>219525</t>
         </is>
       </c>
       <c r="D1081" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E1081" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>LMS_ECOM_0410exclusive2</t>
         </is>
       </c>
     </row>
     <row r="1082">
       <c r="A1082" t="inlineStr">
         <is>
-          <t>pls4u</t>
+          <t>kk_3349199057</t>
         </is>
       </c>
       <c r="B1082" t="inlineStr">
         <is>
-          <t>01085985482</t>
+          <t>01071630312</t>
         </is>
       </c>
       <c r="C1082" t="inlineStr">
         <is>
-          <t>88257</t>
+          <t>239388</t>
         </is>
       </c>
       <c r="D1082" t="inlineStr">
@@ -29638,7 +29638,7 @@
       </c>
       <c r="E1082" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0401_trailrunning</t>
+          <t>LMS_ECOM_0410exclusive2</t>
         </is>
       </c>
     </row>
@@ -29672,17 +29672,17 @@
     <row r="1084">
       <c r="A1084" t="inlineStr">
         <is>
-          <t>kk_4292190414</t>
+          <t>kk_3721447783</t>
         </is>
       </c>
       <c r="B1084" t="inlineStr">
         <is>
-          <t>01095177478</t>
+          <t>01051311087</t>
         </is>
       </c>
       <c r="C1084" t="inlineStr">
         <is>
-          <t>275998</t>
+          <t>252252</t>
         </is>
       </c>
       <c r="D1084" t="inlineStr">
@@ -29699,17 +29699,17 @@
     <row r="1085">
       <c r="A1085" t="inlineStr">
         <is>
-          <t>sjm700</t>
+          <t>inu21c</t>
         </is>
       </c>
       <c r="B1085" t="inlineStr">
         <is>
-          <t>01077331591</t>
+          <t>01035128236</t>
         </is>
       </c>
       <c r="C1085" t="inlineStr">
         <is>
-          <t>118769</t>
+          <t>131940</t>
         </is>
       </c>
       <c r="D1085" t="inlineStr">
@@ -29726,17 +29726,17 @@
     <row r="1086">
       <c r="A1086" t="inlineStr">
         <is>
-          <t>kk_4578503399</t>
+          <t>kk_4525043459</t>
         </is>
       </c>
       <c r="B1086" t="inlineStr">
         <is>
-          <t>01088660330</t>
+          <t>01088312135</t>
         </is>
       </c>
       <c r="C1086" t="inlineStr">
         <is>
-          <t>288374</t>
+          <t>286464</t>
         </is>
       </c>
       <c r="D1086" t="inlineStr">
@@ -29753,17 +29753,17 @@
     <row r="1087">
       <c r="A1087" t="inlineStr">
         <is>
-          <t>kk_3973703558</t>
+          <t>kk_2825715315</t>
         </is>
       </c>
       <c r="B1087" t="inlineStr">
         <is>
-          <t>01048590748</t>
+          <t>01077229654</t>
         </is>
       </c>
       <c r="C1087" t="inlineStr">
         <is>
-          <t>271020</t>
+          <t>212719</t>
         </is>
       </c>
       <c r="D1087" t="inlineStr">
@@ -29807,17 +29807,17 @@
     <row r="1089">
       <c r="A1089" t="inlineStr">
         <is>
-          <t>columbia7</t>
+          <t>kk_3180736217</t>
         </is>
       </c>
       <c r="B1089" t="inlineStr">
         <is>
-          <t>01050080025</t>
+          <t>01036000343</t>
         </is>
       </c>
       <c r="C1089" t="inlineStr">
         <is>
-          <t>109980</t>
+          <t>226314</t>
         </is>
       </c>
       <c r="D1089" t="inlineStr">
@@ -29834,17 +29834,17 @@
     <row r="1090">
       <c r="A1090" t="inlineStr">
         <is>
-          <t>kk_3180736217</t>
+          <t>sjm700</t>
         </is>
       </c>
       <c r="B1090" t="inlineStr">
         <is>
-          <t>01036000343</t>
+          <t>01077331591</t>
         </is>
       </c>
       <c r="C1090" t="inlineStr">
         <is>
-          <t>226314</t>
+          <t>118769</t>
         </is>
       </c>
       <c r="D1090" t="inlineStr">
@@ -29861,17 +29861,17 @@
     <row r="1091">
       <c r="A1091" t="inlineStr">
         <is>
-          <t>yongshin</t>
+          <t>camiblanco</t>
         </is>
       </c>
       <c r="B1091" t="inlineStr">
         <is>
-          <t>01053867821</t>
+          <t>01072190103</t>
         </is>
       </c>
       <c r="C1091" t="inlineStr">
         <is>
-          <t>277896</t>
+          <t>232545</t>
         </is>
       </c>
       <c r="D1091" t="inlineStr">
@@ -29888,27 +29888,27 @@
     <row r="1092">
       <c r="A1092" t="inlineStr">
         <is>
-          <t>kk_3754052831</t>
+          <t>kk_4292190414</t>
         </is>
       </c>
       <c r="B1092" t="inlineStr">
         <is>
-          <t>01092180804</t>
+          <t>01095177478</t>
         </is>
       </c>
       <c r="C1092" t="inlineStr">
         <is>
-          <t>254339</t>
+          <t>275998</t>
         </is>
       </c>
       <c r="D1092" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="E1092" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0410exclusive2</t>
+          <t>Direct</t>
         </is>
       </c>
     </row>
@@ -29942,17 +29942,17 @@
     <row r="1094">
       <c r="A1094" t="inlineStr">
         <is>
-          <t>inu21c</t>
+          <t>hyschant</t>
         </is>
       </c>
       <c r="B1094" t="inlineStr">
         <is>
-          <t>01035128236</t>
+          <t>01065306675</t>
         </is>
       </c>
       <c r="C1094" t="inlineStr">
         <is>
-          <t>131940</t>
+          <t>108579</t>
         </is>
       </c>
       <c r="D1094" t="inlineStr">
@@ -29969,44 +29969,44 @@
     <row r="1095">
       <c r="A1095" t="inlineStr">
         <is>
-          <t>kk_3721447783</t>
+          <t>columbia7</t>
         </is>
       </c>
       <c r="B1095" t="inlineStr">
         <is>
-          <t>01051311087</t>
+          <t>01050080025</t>
         </is>
       </c>
       <c r="C1095" t="inlineStr">
         <is>
-          <t>252252</t>
+          <t>109980</t>
         </is>
       </c>
       <c r="D1095" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E1095" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>LMS_ECOM_0410exclusive2</t>
         </is>
       </c>
     </row>
     <row r="1096">
       <c r="A1096" t="inlineStr">
         <is>
-          <t>kk_3813115836</t>
+          <t>kk_4838419826</t>
         </is>
       </c>
       <c r="B1096" t="inlineStr">
         <is>
-          <t>01066721591</t>
+          <t>01037240798</t>
         </is>
       </c>
       <c r="C1096" t="inlineStr">
         <is>
-          <t>261736</t>
+          <t>304050</t>
         </is>
       </c>
       <c r="D1096" t="inlineStr">
@@ -30016,7 +30016,7 @@
       </c>
       <c r="E1096" t="inlineStr">
         <is>
-          <t>EFW</t>
+          <t>[PF]트래픽_유사+관심사</t>
         </is>
       </c>
     </row>
@@ -30050,17 +30050,17 @@
     <row r="1098">
       <c r="A1098" t="inlineStr">
         <is>
-          <t>kk_4838419826</t>
+          <t>kk_3813115836</t>
         </is>
       </c>
       <c r="B1098" t="inlineStr">
         <is>
-          <t>01037240798</t>
+          <t>01066721591</t>
         </is>
       </c>
       <c r="C1098" t="inlineStr">
         <is>
-          <t>304050</t>
+          <t>261736</t>
         </is>
       </c>
       <c r="D1098" t="inlineStr">
@@ -30070,7 +30070,7 @@
       </c>
       <c r="E1098" t="inlineStr">
         <is>
-          <t>[PF]트래픽_유사+관심사</t>
+          <t>EFW</t>
         </is>
       </c>
     </row>
@@ -30104,17 +30104,17 @@
     <row r="1100">
       <c r="A1100" t="inlineStr">
         <is>
-          <t>honga22</t>
+          <t>cjcangel</t>
         </is>
       </c>
       <c r="B1100" t="inlineStr">
         <is>
-          <t>01022690322</t>
+          <t>01089325858</t>
         </is>
       </c>
       <c r="C1100" t="inlineStr">
         <is>
-          <t>147568</t>
+          <t>292800</t>
         </is>
       </c>
       <c r="D1100" t="inlineStr">
@@ -30124,7 +30124,7 @@
       </c>
       <c r="E1100" t="inlineStr">
         <is>
-          <t>KAKAO_alimtalk</t>
+          <t>Email_mkt</t>
         </is>
       </c>
     </row>
@@ -30158,44 +30158,44 @@
     <row r="1102">
       <c r="A1102" t="inlineStr">
         <is>
-          <t>kk_4717085515</t>
+          <t>honga22</t>
         </is>
       </c>
       <c r="B1102" t="inlineStr">
         <is>
-          <t>01052078703</t>
+          <t>01022690322</t>
         </is>
       </c>
       <c r="C1102" t="inlineStr">
         <is>
-          <t>297221</t>
+          <t>147568</t>
         </is>
       </c>
       <c r="D1102" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E1102" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>KAKAO_alimtalk</t>
         </is>
       </c>
     </row>
     <row r="1103">
       <c r="A1103" t="inlineStr">
         <is>
-          <t>kk_3184270744</t>
+          <t>kk_4717085515</t>
         </is>
       </c>
       <c r="B1103" t="inlineStr">
         <is>
-          <t>01077689325</t>
+          <t>01052078703</t>
         </is>
       </c>
       <c r="C1103" t="inlineStr">
         <is>
-          <t>228883</t>
+          <t>297221</t>
         </is>
       </c>
       <c r="D1103" t="inlineStr">
@@ -30212,27 +30212,27 @@
     <row r="1104">
       <c r="A1104" t="inlineStr">
         <is>
-          <t>cjcangel</t>
+          <t>kk_3184270744</t>
         </is>
       </c>
       <c r="B1104" t="inlineStr">
         <is>
-          <t>01089325858</t>
+          <t>01077689325</t>
         </is>
       </c>
       <c r="C1104" t="inlineStr">
         <is>
-          <t>292800</t>
+          <t>228883</t>
         </is>
       </c>
       <c r="D1104" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="E1104" t="inlineStr">
         <is>
-          <t>Email_mkt</t>
+          <t>Direct</t>
         </is>
       </c>
     </row>
@@ -30266,17 +30266,17 @@
     <row r="1106">
       <c r="A1106" t="inlineStr">
         <is>
-          <t>happy201106</t>
+          <t>alcoholpower</t>
         </is>
       </c>
       <c r="B1106" t="inlineStr">
         <is>
-          <t>01090012622</t>
+          <t>01027629868</t>
         </is>
       </c>
       <c r="C1106" t="inlineStr">
         <is>
-          <t>136050</t>
+          <t>252954</t>
         </is>
       </c>
       <c r="D1106" t="inlineStr">
@@ -30293,17 +30293,17 @@
     <row r="1107">
       <c r="A1107" t="inlineStr">
         <is>
-          <t>alcoholpower</t>
+          <t>happy201106</t>
         </is>
       </c>
       <c r="B1107" t="inlineStr">
         <is>
-          <t>01027629868</t>
+          <t>01090012622</t>
         </is>
       </c>
       <c r="C1107" t="inlineStr">
         <is>
-          <t>252954</t>
+          <t>136050</t>
         </is>
       </c>
       <c r="D1107" t="inlineStr">

--- a/reports/member_funnel/downloads/member_funnel_7d_non_buyer.xlsx
+++ b/reports/member_funnel/downloads/member_funnel_7d_non_buyer.xlsx
@@ -8990,54 +8990,54 @@
     <row r="318">
       <c r="A318" t="inlineStr">
         <is>
-          <t>kk_4231959784</t>
+          <t>dsccool</t>
         </is>
       </c>
       <c r="B318" t="inlineStr">
         <is>
-          <t>01035343111</t>
+          <t>01040100422</t>
         </is>
       </c>
       <c r="C318" t="inlineStr">
         <is>
-          <t>273395</t>
+          <t>284754</t>
         </is>
       </c>
       <c r="D318" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="E318" t="inlineStr">
         <is>
-          <t>KAKAO_CH_MESSAGE_0325_S26NEW_CTA</t>
+          <t>Direct</t>
         </is>
       </c>
     </row>
     <row r="319">
       <c r="A319" t="inlineStr">
         <is>
-          <t>dsccool</t>
+          <t>kk_4231959784</t>
         </is>
       </c>
       <c r="B319" t="inlineStr">
         <is>
-          <t>01040100422</t>
+          <t>01035343111</t>
         </is>
       </c>
       <c r="C319" t="inlineStr">
         <is>
-          <t>284754</t>
+          <t>273395</t>
         </is>
       </c>
       <c r="D319" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E319" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>KAKAO_CH_MESSAGE_0325_S26NEW_CTA</t>
         </is>
       </c>
     </row>
@@ -15686,71 +15686,71 @@
     <row r="566">
       <c r="A566" t="inlineStr">
         <is>
-          <t>kk_4837763007</t>
+          <t>kk_4789688431</t>
         </is>
       </c>
       <c r="B566" t="inlineStr">
         <is>
-          <t>01088993992</t>
+          <t>01099981265</t>
         </is>
       </c>
       <c r="C566" t="inlineStr">
         <is>
-          <t>304013</t>
+          <t>302023</t>
         </is>
       </c>
       <c r="D566" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E566" t="inlineStr">
         <is>
-          <t>(referral)</t>
+          <t>sa</t>
         </is>
       </c>
     </row>
     <row r="567">
       <c r="A567" t="inlineStr">
         <is>
-          <t>kk_3483300064</t>
+          <t>kk_4837763007</t>
         </is>
       </c>
       <c r="B567" t="inlineStr">
         <is>
-          <t>01092213404</t>
+          <t>01088993992</t>
         </is>
       </c>
       <c r="C567" t="inlineStr">
         <is>
-          <t>244619</t>
+          <t>304013</t>
         </is>
       </c>
       <c r="D567" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E567" t="inlineStr">
         <is>
-          <t>naver_brandsearch_mobile</t>
+          <t>(referral)</t>
         </is>
       </c>
     </row>
     <row r="568">
       <c r="A568" t="inlineStr">
         <is>
-          <t>kk_4789688431</t>
+          <t>kk_3483300064</t>
         </is>
       </c>
       <c r="B568" t="inlineStr">
         <is>
-          <t>01099981265</t>
+          <t>01092213404</t>
         </is>
       </c>
       <c r="C568" t="inlineStr">
         <is>
-          <t>302023</t>
+          <t>244619</t>
         </is>
       </c>
       <c r="D568" t="inlineStr">
@@ -15760,7 +15760,7 @@
       </c>
       <c r="E568" t="inlineStr">
         <is>
-          <t>sa</t>
+          <t>naver_brandsearch_mobile</t>
         </is>
       </c>
     </row>
@@ -20141,54 +20141,54 @@
     <row r="731">
       <c r="A731" t="inlineStr">
         <is>
-          <t>sun1381</t>
+          <t>kk_4839145768</t>
         </is>
       </c>
       <c r="B731" t="inlineStr">
         <is>
-          <t>01037709416</t>
+          <t>01097367898</t>
         </is>
       </c>
       <c r="C731" t="inlineStr">
         <is>
-          <t>278160</t>
+          <t>304085</t>
         </is>
       </c>
       <c r="D731" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E731" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0410exclusive2</t>
+          <t>naver_brandsearch_pc</t>
         </is>
       </c>
     </row>
     <row r="732">
       <c r="A732" t="inlineStr">
         <is>
-          <t>kk_4839145768</t>
+          <t>sun1381</t>
         </is>
       </c>
       <c r="B732" t="inlineStr">
         <is>
-          <t>01097367898</t>
+          <t>01037709416</t>
         </is>
       </c>
       <c r="C732" t="inlineStr">
         <is>
-          <t>304085</t>
+          <t>278160</t>
         </is>
       </c>
       <c r="D732" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E732" t="inlineStr">
         <is>
-          <t>naver_brandsearch_pc</t>
+          <t>LMS_ECOM_0410exclusive2</t>
         </is>
       </c>
     </row>
@@ -20924,17 +20924,17 @@
     <row r="760">
       <c r="A760" t="inlineStr">
         <is>
-          <t>kang481127</t>
+          <t>abril80</t>
         </is>
       </c>
       <c r="B760" t="inlineStr">
         <is>
-          <t>01053764012</t>
+          <t>01032942835</t>
         </is>
       </c>
       <c r="C760" t="inlineStr">
         <is>
-          <t>304276</t>
+          <t>192610</t>
         </is>
       </c>
       <c r="D760" t="inlineStr">
@@ -20951,17 +20951,17 @@
     <row r="761">
       <c r="A761" t="inlineStr">
         <is>
-          <t>abril80</t>
+          <t>kang481127</t>
         </is>
       </c>
       <c r="B761" t="inlineStr">
         <is>
-          <t>01032942835</t>
+          <t>01053764012</t>
         </is>
       </c>
       <c r="C761" t="inlineStr">
         <is>
-          <t>192610</t>
+          <t>304276</t>
         </is>
       </c>
       <c r="D761" t="inlineStr">
@@ -21194,44 +21194,44 @@
     <row r="770">
       <c r="A770" t="inlineStr">
         <is>
-          <t>kk_4839680663</t>
+          <t>kk_3392066640</t>
         </is>
       </c>
       <c r="B770" t="inlineStr">
         <is>
-          <t>01046429530</t>
+          <t>01065021283</t>
         </is>
       </c>
       <c r="C770" t="inlineStr">
         <is>
-          <t>304109</t>
+          <t>240983</t>
         </is>
       </c>
       <c r="D770" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E770" t="inlineStr">
         <is>
-          <t>6968489536332</t>
+          <t>LMS_ECOM_0410exclusive2</t>
         </is>
       </c>
     </row>
     <row r="771">
       <c r="A771" t="inlineStr">
         <is>
-          <t>kk_4639169718</t>
+          <t>kk_4839680663</t>
         </is>
       </c>
       <c r="B771" t="inlineStr">
         <is>
-          <t>01041380770</t>
+          <t>01046429530</t>
         </is>
       </c>
       <c r="C771" t="inlineStr">
         <is>
-          <t>292319</t>
+          <t>304109</t>
         </is>
       </c>
       <c r="D771" t="inlineStr">
@@ -21241,51 +21241,51 @@
       </c>
       <c r="E771" t="inlineStr">
         <is>
-          <t>naver_brandsearch_mobile</t>
+          <t>6968489536332</t>
         </is>
       </c>
     </row>
     <row r="772">
       <c r="A772" t="inlineStr">
         <is>
-          <t>kk_3392066640</t>
+          <t>kk_4639169718</t>
         </is>
       </c>
       <c r="B772" t="inlineStr">
         <is>
-          <t>01065021283</t>
+          <t>01041380770</t>
         </is>
       </c>
       <c r="C772" t="inlineStr">
         <is>
-          <t>240983</t>
+          <t>292319</t>
         </is>
       </c>
       <c r="D772" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E772" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0410exclusive2</t>
+          <t>naver_brandsearch_mobile</t>
         </is>
       </c>
     </row>
     <row r="773">
       <c r="A773" t="inlineStr">
         <is>
-          <t>kk_3184667648</t>
+          <t>kk_3404142353</t>
         </is>
       </c>
       <c r="B773" t="inlineStr">
         <is>
-          <t>01043440321</t>
+          <t>01053293239</t>
         </is>
       </c>
       <c r="C773" t="inlineStr">
         <is>
-          <t>229128</t>
+          <t>241289</t>
         </is>
       </c>
       <c r="D773" t="inlineStr">
@@ -21295,61 +21295,61 @@
       </c>
       <c r="E773" t="inlineStr">
         <is>
-          <t>sa</t>
+          <t>[PF]전환_상시(2565MF,비구매자)</t>
         </is>
       </c>
     </row>
     <row r="774">
       <c r="A774" t="inlineStr">
         <is>
-          <t>kk_3404142353</t>
+          <t>kk_4431727915</t>
         </is>
       </c>
       <c r="B774" t="inlineStr">
         <is>
-          <t>01053293239</t>
+          <t>01047182896</t>
         </is>
       </c>
       <c r="C774" t="inlineStr">
         <is>
-          <t>241289</t>
+          <t>281759</t>
         </is>
       </c>
       <c r="D774" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E774" t="inlineStr">
         <is>
-          <t>[PF]전환_상시(2565MF,비구매자)</t>
+          <t>KAKAO_CH_MESSAGE_0409_HIKE365SUMMER</t>
         </is>
       </c>
     </row>
     <row r="775">
       <c r="A775" t="inlineStr">
         <is>
-          <t>kk_4431727915</t>
+          <t>kk_3184667648</t>
         </is>
       </c>
       <c r="B775" t="inlineStr">
         <is>
-          <t>01047182896</t>
+          <t>01043440321</t>
         </is>
       </c>
       <c r="C775" t="inlineStr">
         <is>
-          <t>281759</t>
+          <t>229128</t>
         </is>
       </c>
       <c r="D775" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E775" t="inlineStr">
         <is>
-          <t>KAKAO_CH_MESSAGE_0409_HIKE365SUMMER</t>
+          <t>sa</t>
         </is>
       </c>
     </row>
@@ -21491,17 +21491,17 @@
     <row r="781">
       <c r="A781" t="inlineStr">
         <is>
-          <t>mtbok</t>
+          <t>kk_3678962368</t>
         </is>
       </c>
       <c r="B781" t="inlineStr">
         <is>
-          <t>01051284339</t>
+          <t>01041028567</t>
         </is>
       </c>
       <c r="C781" t="inlineStr">
         <is>
-          <t>26917</t>
+          <t>250374</t>
         </is>
       </c>
       <c r="D781" t="inlineStr">
@@ -21545,17 +21545,17 @@
     <row r="783">
       <c r="A783" t="inlineStr">
         <is>
-          <t>kk_3678962368</t>
+          <t>mtbok</t>
         </is>
       </c>
       <c r="B783" t="inlineStr">
         <is>
-          <t>01041028567</t>
+          <t>01051284339</t>
         </is>
       </c>
       <c r="C783" t="inlineStr">
         <is>
-          <t>250374</t>
+          <t>26917</t>
         </is>
       </c>
       <c r="D783" t="inlineStr">
@@ -21680,81 +21680,81 @@
     <row r="788">
       <c r="A788" t="inlineStr">
         <is>
-          <t>kk_3181873063</t>
+          <t>kk_4727921763</t>
         </is>
       </c>
       <c r="B788" t="inlineStr">
         <is>
-          <t>01026527131</t>
+          <t>01045673975</t>
         </is>
       </c>
       <c r="C788" t="inlineStr">
         <is>
-          <t>227343</t>
+          <t>298138</t>
         </is>
       </c>
       <c r="D788" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="E788" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0410exclusive2</t>
+          <t>Direct</t>
         </is>
       </c>
     </row>
     <row r="789">
       <c r="A789" t="inlineStr">
         <is>
-          <t>kk_4727921763</t>
+          <t>kk_4839026541</t>
         </is>
       </c>
       <c r="B789" t="inlineStr">
         <is>
-          <t>01045673975</t>
+          <t>01089431507</t>
         </is>
       </c>
       <c r="C789" t="inlineStr">
         <is>
-          <t>298138</t>
+          <t>304082</t>
         </is>
       </c>
       <c r="D789" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E789" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>[PF]전환_상시(2565MF,비구매자)</t>
         </is>
       </c>
     </row>
     <row r="790">
       <c r="A790" t="inlineStr">
         <is>
-          <t>kk_4839026541</t>
+          <t>kk_3181873063</t>
         </is>
       </c>
       <c r="B790" t="inlineStr">
         <is>
-          <t>01089431507</t>
+          <t>01026527131</t>
         </is>
       </c>
       <c r="C790" t="inlineStr">
         <is>
-          <t>304082</t>
+          <t>227343</t>
         </is>
       </c>
       <c r="D790" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E790" t="inlineStr">
         <is>
-          <t>[PF]전환_상시(2565MF,비구매자)</t>
+          <t>LMS_ECOM_0410exclusive2</t>
         </is>
       </c>
     </row>
@@ -21788,17 +21788,17 @@
     <row r="792">
       <c r="A792" t="inlineStr">
         <is>
-          <t>kk_4532357752</t>
+          <t>kk_4519505330</t>
         </is>
       </c>
       <c r="B792" t="inlineStr">
         <is>
-          <t>01023210419</t>
+          <t>01024320028</t>
         </is>
       </c>
       <c r="C792" t="inlineStr">
         <is>
-          <t>286900</t>
+          <t>286150</t>
         </is>
       </c>
       <c r="D792" t="inlineStr">
@@ -21808,7 +21808,7 @@
       </c>
       <c r="E792" t="inlineStr">
         <is>
-          <t>KAKAO_CH_MESSAGE_0409_EXCLUSIVE</t>
+          <t>KAKAO_CH_MESSAGE_0409_HIKE365SUMMER</t>
         </is>
       </c>
     </row>
@@ -21842,17 +21842,17 @@
     <row r="794">
       <c r="A794" t="inlineStr">
         <is>
-          <t>kk_4519505330</t>
+          <t>kk_4532357752</t>
         </is>
       </c>
       <c r="B794" t="inlineStr">
         <is>
-          <t>01024320028</t>
+          <t>01023210419</t>
         </is>
       </c>
       <c r="C794" t="inlineStr">
         <is>
-          <t>286150</t>
+          <t>286900</t>
         </is>
       </c>
       <c r="D794" t="inlineStr">
@@ -21862,7 +21862,7 @@
       </c>
       <c r="E794" t="inlineStr">
         <is>
-          <t>KAKAO_CH_MESSAGE_0409_HIKE365SUMMER</t>
+          <t>KAKAO_CH_MESSAGE_0409_EXCLUSIVE</t>
         </is>
       </c>
     </row>
@@ -22031,17 +22031,17 @@
     <row r="801">
       <c r="A801" t="inlineStr">
         <is>
-          <t>kk_4368805733</t>
+          <t>kk_4600405600</t>
         </is>
       </c>
       <c r="B801" t="inlineStr">
         <is>
-          <t>01075528863</t>
+          <t>01053449477</t>
         </is>
       </c>
       <c r="C801" t="inlineStr">
         <is>
-          <t>279909</t>
+          <t>289364</t>
         </is>
       </c>
       <c r="D801" t="inlineStr">
@@ -22058,17 +22058,17 @@
     <row r="802">
       <c r="A802" t="inlineStr">
         <is>
-          <t>kk_4600405600</t>
+          <t>kk_4368805733</t>
         </is>
       </c>
       <c r="B802" t="inlineStr">
         <is>
-          <t>01053449477</t>
+          <t>01075528863</t>
         </is>
       </c>
       <c r="C802" t="inlineStr">
         <is>
-          <t>289364</t>
+          <t>279909</t>
         </is>
       </c>
       <c r="D802" t="inlineStr">
@@ -22274,17 +22274,17 @@
     <row r="810">
       <c r="A810" t="inlineStr">
         <is>
-          <t>pieerot1</t>
+          <t>noma6420</t>
         </is>
       </c>
       <c r="B810" t="inlineStr">
         <is>
-          <t>01054503186</t>
+          <t>01071574279</t>
         </is>
       </c>
       <c r="C810" t="inlineStr">
         <is>
-          <t>29988</t>
+          <t>304023</t>
         </is>
       </c>
       <c r="D810" t="inlineStr">
@@ -22294,24 +22294,24 @@
       </c>
       <c r="E810" t="inlineStr">
         <is>
-          <t>naver_brandsearch_mobile</t>
+          <t>[PF]A SC_상시(1865MF,구매 장바구니)</t>
         </is>
       </c>
     </row>
     <row r="811">
       <c r="A811" t="inlineStr">
         <is>
-          <t>noma6420</t>
+          <t>pieerot1</t>
         </is>
       </c>
       <c r="B811" t="inlineStr">
         <is>
-          <t>01071574279</t>
+          <t>01054503186</t>
         </is>
       </c>
       <c r="C811" t="inlineStr">
         <is>
-          <t>304023</t>
+          <t>29988</t>
         </is>
       </c>
       <c r="D811" t="inlineStr">
@@ -22321,7 +22321,7 @@
       </c>
       <c r="E811" t="inlineStr">
         <is>
-          <t>[PF]A SC_상시(1865MF,구매 장바구니)</t>
+          <t>naver_brandsearch_mobile</t>
         </is>
       </c>
     </row>
@@ -24056,54 +24056,54 @@
     <row r="876">
       <c r="A876" t="inlineStr">
         <is>
-          <t>xey5000</t>
+          <t>kk_4840108009</t>
         </is>
       </c>
       <c r="B876" t="inlineStr">
         <is>
-          <t>01087768710</t>
+          <t>01053461423</t>
         </is>
       </c>
       <c r="C876" t="inlineStr">
         <is>
-          <t>143826</t>
+          <t>304129</t>
         </is>
       </c>
       <c r="D876" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E876" t="inlineStr">
         <is>
-          <t>KAKAO_CH_MESSAGE_0409_PANTS</t>
+          <t>6968489536332</t>
         </is>
       </c>
     </row>
     <row r="877">
       <c r="A877" t="inlineStr">
         <is>
-          <t>kk_4840108009</t>
+          <t>xey5000</t>
         </is>
       </c>
       <c r="B877" t="inlineStr">
         <is>
-          <t>01053461423</t>
+          <t>01087768710</t>
         </is>
       </c>
       <c r="C877" t="inlineStr">
         <is>
-          <t>304129</t>
+          <t>143826</t>
         </is>
       </c>
       <c r="D877" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E877" t="inlineStr">
         <is>
-          <t>6968489536332</t>
+          <t>KAKAO_CH_MESSAGE_0409_PANTS</t>
         </is>
       </c>
     </row>
@@ -24191,54 +24191,54 @@
     <row r="881">
       <c r="A881" t="inlineStr">
         <is>
-          <t>qssa2000</t>
+          <t>kk_4841482998</t>
         </is>
       </c>
       <c r="B881" t="inlineStr">
         <is>
-          <t>01020284430</t>
+          <t>01050082734</t>
         </is>
       </c>
       <c r="C881" t="inlineStr">
         <is>
-          <t>202308</t>
+          <t>304194</t>
         </is>
       </c>
       <c r="D881" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="E881" t="inlineStr">
         <is>
-          <t>6968489536332</t>
+          <t>Direct</t>
         </is>
       </c>
     </row>
     <row r="882">
       <c r="A882" t="inlineStr">
         <is>
-          <t>kk_4841482998</t>
+          <t>qssa2000</t>
         </is>
       </c>
       <c r="B882" t="inlineStr">
         <is>
-          <t>01050082734</t>
+          <t>01020284430</t>
         </is>
       </c>
       <c r="C882" t="inlineStr">
         <is>
-          <t>304194</t>
+          <t>202308</t>
         </is>
       </c>
       <c r="D882" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E882" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>6968489536332</t>
         </is>
       </c>
     </row>
@@ -24272,17 +24272,17 @@
     <row r="884">
       <c r="A884" t="inlineStr">
         <is>
-          <t>holstein</t>
+          <t>kk_3595551743</t>
         </is>
       </c>
       <c r="B884" t="inlineStr">
         <is>
-          <t>01050502500</t>
+          <t>01025839326</t>
         </is>
       </c>
       <c r="C884" t="inlineStr">
         <is>
-          <t>14062</t>
+          <t>246836</t>
         </is>
       </c>
       <c r="D884" t="inlineStr">
@@ -24292,24 +24292,24 @@
       </c>
       <c r="E884" t="inlineStr">
         <is>
-          <t>EDM_TOP</t>
+          <t>LMS_ECOM_0410exclusive2</t>
         </is>
       </c>
     </row>
     <row r="885">
       <c r="A885" t="inlineStr">
         <is>
-          <t>kk_3595551743</t>
+          <t>holstein</t>
         </is>
       </c>
       <c r="B885" t="inlineStr">
         <is>
-          <t>01025839326</t>
+          <t>01050502500</t>
         </is>
       </c>
       <c r="C885" t="inlineStr">
         <is>
-          <t>246836</t>
+          <t>14062</t>
         </is>
       </c>
       <c r="D885" t="inlineStr">
@@ -24319,7 +24319,7 @@
       </c>
       <c r="E885" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0410exclusive2</t>
+          <t>EDM_TOP</t>
         </is>
       </c>
     </row>
@@ -24569,17 +24569,17 @@
     <row r="895">
       <c r="A895" t="inlineStr">
         <is>
-          <t>kk_2954504655</t>
+          <t>kk_4844665214</t>
         </is>
       </c>
       <c r="B895" t="inlineStr">
         <is>
-          <t>01024942984</t>
+          <t>01033424745</t>
         </is>
       </c>
       <c r="C895" t="inlineStr">
         <is>
-          <t>242733</t>
+          <t>304377</t>
         </is>
       </c>
       <c r="D895" t="inlineStr">
@@ -24596,17 +24596,17 @@
     <row r="896">
       <c r="A896" t="inlineStr">
         <is>
-          <t>kk_4844665214</t>
+          <t>kk_2954504655</t>
         </is>
       </c>
       <c r="B896" t="inlineStr">
         <is>
-          <t>01033424745</t>
+          <t>01024942984</t>
         </is>
       </c>
       <c r="C896" t="inlineStr">
         <is>
-          <t>304377</t>
+          <t>242733</t>
         </is>
       </c>
       <c r="D896" t="inlineStr">
@@ -24677,17 +24677,17 @@
     <row r="899">
       <c r="A899" t="inlineStr">
         <is>
-          <t>kk_4840093815</t>
+          <t>kk_4839544665</t>
         </is>
       </c>
       <c r="B899" t="inlineStr">
         <is>
-          <t>01095450820</t>
+          <t>01055350199</t>
         </is>
       </c>
       <c r="C899" t="inlineStr">
         <is>
-          <t>304126</t>
+          <t>304104</t>
         </is>
       </c>
       <c r="D899" t="inlineStr">
@@ -24697,7 +24697,7 @@
       </c>
       <c r="E899" t="inlineStr">
         <is>
-          <t>EFW</t>
+          <t>6968489536332</t>
         </is>
       </c>
     </row>
@@ -24731,17 +24731,17 @@
     <row r="901">
       <c r="A901" t="inlineStr">
         <is>
-          <t>kk_4839544665</t>
+          <t>kk_4840093815</t>
         </is>
       </c>
       <c r="B901" t="inlineStr">
         <is>
-          <t>01055350199</t>
+          <t>01095450820</t>
         </is>
       </c>
       <c r="C901" t="inlineStr">
         <is>
-          <t>304104</t>
+          <t>304126</t>
         </is>
       </c>
       <c r="D901" t="inlineStr">
@@ -24751,61 +24751,61 @@
       </c>
       <c r="E901" t="inlineStr">
         <is>
-          <t>6968489536332</t>
+          <t>EFW</t>
         </is>
       </c>
     </row>
     <row r="902">
       <c r="A902" t="inlineStr">
         <is>
-          <t>kk_4837471959</t>
+          <t>kk_3775491761</t>
         </is>
       </c>
       <c r="B902" t="inlineStr">
         <is>
-          <t>01022201041</t>
+          <t>01042990425</t>
         </is>
       </c>
       <c r="C902" t="inlineStr">
         <is>
-          <t>303988</t>
+          <t>255841</t>
         </is>
       </c>
       <c r="D902" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="E902" t="inlineStr">
         <is>
-          <t>6968489536332</t>
+          <t>Direct</t>
         </is>
       </c>
     </row>
     <row r="903">
       <c r="A903" t="inlineStr">
         <is>
-          <t>kk_3775491761</t>
+          <t>kk_4837471959</t>
         </is>
       </c>
       <c r="B903" t="inlineStr">
         <is>
-          <t>01042990425</t>
+          <t>01022201041</t>
         </is>
       </c>
       <c r="C903" t="inlineStr">
         <is>
-          <t>255841</t>
+          <t>303988</t>
         </is>
       </c>
       <c r="D903" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E903" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>6968489536332</t>
         </is>
       </c>
     </row>
@@ -24839,54 +24839,54 @@
     <row r="905">
       <c r="A905" t="inlineStr">
         <is>
-          <t>kk_4843439707</t>
+          <t>kk_2800477789</t>
         </is>
       </c>
       <c r="B905" t="inlineStr">
         <is>
-          <t>01022248653</t>
+          <t>01035177105</t>
         </is>
       </c>
       <c r="C905" t="inlineStr">
         <is>
-          <t>304310</t>
+          <t>211095</t>
         </is>
       </c>
       <c r="D905" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E905" t="inlineStr">
         <is>
-          <t>6968489536332</t>
+          <t>KAKAO_alimtalk</t>
         </is>
       </c>
     </row>
     <row r="906">
       <c r="A906" t="inlineStr">
         <is>
-          <t>kk_2800477789</t>
+          <t>kk_4843439707</t>
         </is>
       </c>
       <c r="B906" t="inlineStr">
         <is>
-          <t>01035177105</t>
+          <t>01022248653</t>
         </is>
       </c>
       <c r="C906" t="inlineStr">
         <is>
-          <t>211095</t>
+          <t>304310</t>
         </is>
       </c>
       <c r="D906" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E906" t="inlineStr">
         <is>
-          <t>KAKAO_alimtalk</t>
+          <t>6968489536332</t>
         </is>
       </c>
     </row>
@@ -24920,108 +24920,108 @@
     <row r="908">
       <c r="A908" t="inlineStr">
         <is>
-          <t>kk_4844530515</t>
+          <t>dmsdud552</t>
         </is>
       </c>
       <c r="B908" t="inlineStr">
         <is>
-          <t>01054558799</t>
+          <t>01054633672</t>
         </is>
       </c>
       <c r="C908" t="inlineStr">
         <is>
-          <t>304366</t>
+          <t>132110</t>
         </is>
       </c>
       <c r="D908" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Organic Traffic</t>
         </is>
       </c>
       <c r="E908" t="inlineStr">
         <is>
-          <t>6968489536332</t>
+          <t>(referral)</t>
         </is>
       </c>
     </row>
     <row r="909">
       <c r="A909" t="inlineStr">
         <is>
-          <t>dmsdud552</t>
+          <t>kk_4844530515</t>
         </is>
       </c>
       <c r="B909" t="inlineStr">
         <is>
-          <t>01054633672</t>
+          <t>01054558799</t>
         </is>
       </c>
       <c r="C909" t="inlineStr">
         <is>
-          <t>132110</t>
+          <t>304366</t>
         </is>
       </c>
       <c r="D909" t="inlineStr">
         <is>
-          <t>Organic Traffic</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E909" t="inlineStr">
         <is>
-          <t>(referral)</t>
+          <t>6968489536332</t>
         </is>
       </c>
     </row>
     <row r="910">
       <c r="A910" t="inlineStr">
         <is>
-          <t>kk_4543882817</t>
+          <t>kk_4839643736</t>
         </is>
       </c>
       <c r="B910" t="inlineStr">
         <is>
-          <t>01023875300</t>
+          <t>01063617035</t>
         </is>
       </c>
       <c r="C910" t="inlineStr">
         <is>
-          <t>287573</t>
+          <t>304107</t>
         </is>
       </c>
       <c r="D910" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E910" t="inlineStr">
         <is>
-          <t>미분류</t>
+          <t>naver_brandsearch_mobile</t>
         </is>
       </c>
     </row>
     <row r="911">
       <c r="A911" t="inlineStr">
         <is>
-          <t>kk_4839643736</t>
+          <t>kk_4543882817</t>
         </is>
       </c>
       <c r="B911" t="inlineStr">
         <is>
-          <t>01063617035</t>
+          <t>01023875300</t>
         </is>
       </c>
       <c r="C911" t="inlineStr">
         <is>
-          <t>304107</t>
+          <t>287573</t>
         </is>
       </c>
       <c r="D911" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="E911" t="inlineStr">
         <is>
-          <t>naver_brandsearch_mobile</t>
+          <t>미분류</t>
         </is>
       </c>
     </row>
@@ -25055,17 +25055,17 @@
     <row r="913">
       <c r="A913" t="inlineStr">
         <is>
-          <t>kk_4845173313</t>
+          <t>kk_4844453283</t>
         </is>
       </c>
       <c r="B913" t="inlineStr">
         <is>
-          <t>01024436341</t>
+          <t>01090262556</t>
         </is>
       </c>
       <c r="C913" t="inlineStr">
         <is>
-          <t>304397</t>
+          <t>304360</t>
         </is>
       </c>
       <c r="D913" t="inlineStr">
@@ -25109,179 +25109,179 @@
     <row r="915">
       <c r="A915" t="inlineStr">
         <is>
-          <t>kk_4845121221</t>
+          <t>kk_4843926419</t>
         </is>
       </c>
       <c r="B915" t="inlineStr">
         <is>
-          <t>01044632332</t>
+          <t>01034583174</t>
         </is>
       </c>
       <c r="C915" t="inlineStr">
         <is>
-          <t>304393</t>
+          <t>304338</t>
         </is>
       </c>
       <c r="D915" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Official SNS</t>
         </is>
       </c>
       <c r="E915" t="inlineStr">
         <is>
-          <t>6968489536332</t>
+          <t>EFW_04</t>
         </is>
       </c>
     </row>
     <row r="916">
       <c r="A916" t="inlineStr">
         <is>
-          <t>kk_4843926419</t>
+          <t>kk_4845121221</t>
         </is>
       </c>
       <c r="B916" t="inlineStr">
         <is>
-          <t>01034583174</t>
+          <t>01044632332</t>
         </is>
       </c>
       <c r="C916" t="inlineStr">
         <is>
-          <t>304338</t>
+          <t>304393</t>
         </is>
       </c>
       <c r="D916" t="inlineStr">
         <is>
-          <t>Official SNS</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E916" t="inlineStr">
         <is>
-          <t>EFW_04</t>
+          <t>6968489536332</t>
         </is>
       </c>
     </row>
     <row r="917">
       <c r="A917" t="inlineStr">
         <is>
-          <t>kk_4844453283</t>
+          <t>kk_4843847622</t>
         </is>
       </c>
       <c r="B917" t="inlineStr">
         <is>
-          <t>01090262556</t>
+          <t>01046990393</t>
         </is>
       </c>
       <c r="C917" t="inlineStr">
         <is>
-          <t>304360</t>
+          <t>304336</t>
         </is>
       </c>
       <c r="D917" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Organic Traffic</t>
         </is>
       </c>
       <c r="E917" t="inlineStr">
         <is>
-          <t>6968489536332</t>
+          <t>(organic)</t>
         </is>
       </c>
     </row>
     <row r="918">
       <c r="A918" t="inlineStr">
         <is>
-          <t>kk_4843847622</t>
+          <t>kk_4845173313</t>
         </is>
       </c>
       <c r="B918" t="inlineStr">
         <is>
-          <t>01046990393</t>
+          <t>01024436341</t>
         </is>
       </c>
       <c r="C918" t="inlineStr">
         <is>
-          <t>304336</t>
+          <t>304397</t>
         </is>
       </c>
       <c r="D918" t="inlineStr">
         <is>
-          <t>Organic Traffic</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E918" t="inlineStr">
         <is>
-          <t>(organic)</t>
+          <t>6968489536332</t>
         </is>
       </c>
     </row>
     <row r="919">
       <c r="A919" t="inlineStr">
         <is>
-          <t>kk_4840857472</t>
+          <t>kyoungs424</t>
         </is>
       </c>
       <c r="B919" t="inlineStr">
         <is>
-          <t>01040551807</t>
+          <t>01041509204</t>
         </is>
       </c>
       <c r="C919" t="inlineStr">
         <is>
-          <t>304172</t>
+          <t>153760</t>
         </is>
       </c>
       <c r="D919" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E919" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>KAKAO_alimtalk</t>
         </is>
       </c>
     </row>
     <row r="920">
       <c r="A920" t="inlineStr">
         <is>
-          <t>kk_2961062530</t>
+          <t>kk_4840857472</t>
         </is>
       </c>
       <c r="B920" t="inlineStr">
         <is>
-          <t>01050052823</t>
+          <t>01040551807</t>
         </is>
       </c>
       <c r="C920" t="inlineStr">
         <is>
-          <t>217199</t>
+          <t>304172</t>
         </is>
       </c>
       <c r="D920" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="E920" t="inlineStr">
         <is>
-          <t>KAKAO_CH_MENU_0317_S26NEW</t>
+          <t>Direct</t>
         </is>
       </c>
     </row>
     <row r="921">
       <c r="A921" t="inlineStr">
         <is>
-          <t>kyoungs424</t>
+          <t>kk_2961062530</t>
         </is>
       </c>
       <c r="B921" t="inlineStr">
         <is>
-          <t>01041509204</t>
+          <t>01050052823</t>
         </is>
       </c>
       <c r="C921" t="inlineStr">
         <is>
-          <t>153760</t>
+          <t>217199</t>
         </is>
       </c>
       <c r="D921" t="inlineStr">
@@ -25291,115 +25291,115 @@
       </c>
       <c r="E921" t="inlineStr">
         <is>
-          <t>KAKAO_alimtalk</t>
+          <t>KAKAO_CH_MENU_0317_S26NEW</t>
         </is>
       </c>
     </row>
     <row r="922">
       <c r="A922" t="inlineStr">
         <is>
-          <t>kk_4839542021</t>
+          <t>kk_4357899204</t>
         </is>
       </c>
       <c r="B922" t="inlineStr">
         <is>
-          <t>01089909663</t>
+          <t>01082772838</t>
         </is>
       </c>
       <c r="C922" t="inlineStr">
         <is>
-          <t>304103</t>
+          <t>279564</t>
         </is>
       </c>
       <c r="D922" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Official SNS</t>
         </is>
       </c>
       <c r="E922" t="inlineStr">
         <is>
-          <t>(organic)</t>
+          <t>(referral)</t>
         </is>
       </c>
     </row>
     <row r="923">
       <c r="A923" t="inlineStr">
         <is>
-          <t>kk_4357899204</t>
+          <t>kk_4839542021</t>
         </is>
       </c>
       <c r="B923" t="inlineStr">
         <is>
-          <t>01082772838</t>
+          <t>01089909663</t>
         </is>
       </c>
       <c r="C923" t="inlineStr">
         <is>
-          <t>279564</t>
+          <t>304103</t>
         </is>
       </c>
       <c r="D923" t="inlineStr">
         <is>
-          <t>Official SNS</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E923" t="inlineStr">
         <is>
-          <t>(referral)</t>
+          <t>(organic)</t>
         </is>
       </c>
     </row>
     <row r="924">
       <c r="A924" t="inlineStr">
         <is>
-          <t>vvip6905</t>
+          <t>kk_4838574281</t>
         </is>
       </c>
       <c r="B924" t="inlineStr">
         <is>
-          <t>01085855275</t>
+          <t>01092229876</t>
         </is>
       </c>
       <c r="C924" t="inlineStr">
         <is>
-          <t>304027</t>
+          <t>304061</t>
         </is>
       </c>
       <c r="D924" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E924" t="inlineStr">
         <is>
-          <t>Email_mkt</t>
+          <t>6968489536332</t>
         </is>
       </c>
     </row>
     <row r="925">
       <c r="A925" t="inlineStr">
         <is>
-          <t>kk_4838574281</t>
+          <t>vvip6905</t>
         </is>
       </c>
       <c r="B925" t="inlineStr">
         <is>
-          <t>01092229876</t>
+          <t>01085855275</t>
         </is>
       </c>
       <c r="C925" t="inlineStr">
         <is>
-          <t>304061</t>
+          <t>304027</t>
         </is>
       </c>
       <c r="D925" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E925" t="inlineStr">
         <is>
-          <t>6968489536332</t>
+          <t>Email_mkt</t>
         </is>
       </c>
     </row>
@@ -25433,54 +25433,54 @@
     <row r="927">
       <c r="A927" t="inlineStr">
         <is>
-          <t>plumrhkr1</t>
+          <t>kk_4835912712</t>
         </is>
       </c>
       <c r="B927" t="inlineStr">
         <is>
-          <t>01074112056</t>
+          <t>01094418375</t>
         </is>
       </c>
       <c r="C927" t="inlineStr">
         <is>
-          <t>303916</t>
+          <t>303898</t>
         </is>
       </c>
       <c r="D927" t="inlineStr">
         <is>
-          <t>Organic Traffic</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="E927" t="inlineStr">
         <is>
-          <t>(organic)</t>
+          <t>Direct</t>
         </is>
       </c>
     </row>
     <row r="928">
       <c r="A928" t="inlineStr">
         <is>
-          <t>kk_4835912712</t>
+          <t>plumrhkr1</t>
         </is>
       </c>
       <c r="B928" t="inlineStr">
         <is>
-          <t>01094418375</t>
+          <t>01074112056</t>
         </is>
       </c>
       <c r="C928" t="inlineStr">
         <is>
-          <t>303898</t>
+          <t>303916</t>
         </is>
       </c>
       <c r="D928" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>Organic Traffic</t>
         </is>
       </c>
       <c r="E928" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>(organic)</t>
         </is>
       </c>
     </row>
@@ -25514,54 +25514,54 @@
     <row r="930">
       <c r="A930" t="inlineStr">
         <is>
-          <t>kk_4839906396</t>
+          <t>kk_3725118384</t>
         </is>
       </c>
       <c r="B930" t="inlineStr">
         <is>
-          <t>01044486524</t>
+          <t>01035977118</t>
         </is>
       </c>
       <c r="C930" t="inlineStr">
         <is>
-          <t>304113</t>
+          <t>252440</t>
         </is>
       </c>
       <c r="D930" t="inlineStr">
         <is>
-          <t>Organic Traffic</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E930" t="inlineStr">
         <is>
-          <t>(organic)</t>
+          <t>LMS_ECOM_0214_newyear</t>
         </is>
       </c>
     </row>
     <row r="931">
       <c r="A931" t="inlineStr">
         <is>
-          <t>kk_3725118384</t>
+          <t>kk_4839906396</t>
         </is>
       </c>
       <c r="B931" t="inlineStr">
         <is>
-          <t>01035977118</t>
+          <t>01044486524</t>
         </is>
       </c>
       <c r="C931" t="inlineStr">
         <is>
-          <t>252440</t>
+          <t>304113</t>
         </is>
       </c>
       <c r="D931" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Organic Traffic</t>
         </is>
       </c>
       <c r="E931" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0214_newyear</t>
+          <t>(organic)</t>
         </is>
       </c>
     </row>
@@ -25703,17 +25703,17 @@
     <row r="937">
       <c r="A937" t="inlineStr">
         <is>
-          <t>kk_4844452226</t>
+          <t>kk_4843809795</t>
         </is>
       </c>
       <c r="B937" t="inlineStr">
         <is>
-          <t>01096801866</t>
+          <t>01072864741</t>
         </is>
       </c>
       <c r="C937" t="inlineStr">
         <is>
-          <t>304359</t>
+          <t>304335</t>
         </is>
       </c>
       <c r="D937" t="inlineStr">
@@ -25730,17 +25730,17 @@
     <row r="938">
       <c r="A938" t="inlineStr">
         <is>
-          <t>kk_4843809795</t>
+          <t>kk_4844452226</t>
         </is>
       </c>
       <c r="B938" t="inlineStr">
         <is>
-          <t>01072864741</t>
+          <t>01096801866</t>
         </is>
       </c>
       <c r="C938" t="inlineStr">
         <is>
-          <t>304335</t>
+          <t>304359</t>
         </is>
       </c>
       <c r="D938" t="inlineStr">
@@ -25757,98 +25757,98 @@
     <row r="939">
       <c r="A939" t="inlineStr">
         <is>
-          <t>kona143</t>
+          <t>blblhh</t>
         </is>
       </c>
       <c r="B939" t="inlineStr">
         <is>
-          <t>01021001916</t>
+          <t>01033446769</t>
         </is>
       </c>
       <c r="C939" t="inlineStr">
         <is>
-          <t>304260</t>
+          <t>304297</t>
         </is>
       </c>
       <c r="D939" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Organic Traffic</t>
         </is>
       </c>
       <c r="E939" t="inlineStr">
         <is>
-          <t>[PF]전환_회원가입(유사)</t>
+          <t>(referral)</t>
         </is>
       </c>
     </row>
     <row r="940">
       <c r="A940" t="inlineStr">
         <is>
-          <t>blblhh</t>
+          <t>kona143</t>
         </is>
       </c>
       <c r="B940" t="inlineStr">
         <is>
-          <t>01033446769</t>
+          <t>01021001916</t>
         </is>
       </c>
       <c r="C940" t="inlineStr">
         <is>
-          <t>304297</t>
+          <t>304260</t>
         </is>
       </c>
       <c r="D940" t="inlineStr">
         <is>
-          <t>Organic Traffic</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E940" t="inlineStr">
         <is>
-          <t>(referral)</t>
+          <t>[PF]전환_회원가입(유사)</t>
         </is>
       </c>
     </row>
     <row r="941">
       <c r="A941" t="inlineStr">
         <is>
-          <t>kk_4841278242</t>
+          <t>jsb0425</t>
         </is>
       </c>
       <c r="B941" t="inlineStr">
         <is>
-          <t>01046197965</t>
+          <t>01037883670</t>
         </is>
       </c>
       <c r="C941" t="inlineStr">
         <is>
-          <t>304190</t>
+          <t>104766</t>
         </is>
       </c>
       <c r="D941" t="inlineStr">
         <is>
-          <t>Organic Traffic</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="E941" t="inlineStr">
         <is>
-          <t>(referral)</t>
+          <t>Direct</t>
         </is>
       </c>
     </row>
     <row r="942">
       <c r="A942" t="inlineStr">
         <is>
-          <t>jsb0425</t>
+          <t>kk_4840913383</t>
         </is>
       </c>
       <c r="B942" t="inlineStr">
         <is>
-          <t>01037883670</t>
+          <t>01099887927</t>
         </is>
       </c>
       <c r="C942" t="inlineStr">
         <is>
-          <t>104766</t>
+          <t>304174</t>
         </is>
       </c>
       <c r="D942" t="inlineStr">
@@ -25865,98 +25865,98 @@
     <row r="943">
       <c r="A943" t="inlineStr">
         <is>
-          <t>kk_2750710108</t>
+          <t>kk_4840417532</t>
         </is>
       </c>
       <c r="B943" t="inlineStr">
         <is>
-          <t>01062707475</t>
+          <t>01053409288</t>
         </is>
       </c>
       <c r="C943" t="inlineStr">
         <is>
-          <t>207211</t>
+          <t>304147</t>
         </is>
       </c>
       <c r="D943" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>Official SNS</t>
         </is>
       </c>
       <c r="E943" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>EFW_04</t>
         </is>
       </c>
     </row>
     <row r="944">
       <c r="A944" t="inlineStr">
         <is>
-          <t>kk_4840417532</t>
+          <t>kk_3977730443</t>
         </is>
       </c>
       <c r="B944" t="inlineStr">
         <is>
-          <t>01053409288</t>
+          <t>01064291828</t>
         </is>
       </c>
       <c r="C944" t="inlineStr">
         <is>
-          <t>304147</t>
+          <t>271278</t>
         </is>
       </c>
       <c r="D944" t="inlineStr">
         <is>
-          <t>Official SNS</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E944" t="inlineStr">
         <is>
-          <t>EFW_04</t>
+          <t>naver_brandsearch_mobile</t>
         </is>
       </c>
     </row>
     <row r="945">
       <c r="A945" t="inlineStr">
         <is>
-          <t>kk_3977730443</t>
+          <t>kk_4841278242</t>
         </is>
       </c>
       <c r="B945" t="inlineStr">
         <is>
-          <t>01064291828</t>
+          <t>01046197965</t>
         </is>
       </c>
       <c r="C945" t="inlineStr">
         <is>
-          <t>271278</t>
+          <t>304190</t>
         </is>
       </c>
       <c r="D945" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Organic Traffic</t>
         </is>
       </c>
       <c r="E945" t="inlineStr">
         <is>
-          <t>naver_brandsearch_mobile</t>
+          <t>(referral)</t>
         </is>
       </c>
     </row>
     <row r="946">
       <c r="A946" t="inlineStr">
         <is>
-          <t>kk_4840913383</t>
+          <t>kk_2750710108</t>
         </is>
       </c>
       <c r="B946" t="inlineStr">
         <is>
-          <t>01099887927</t>
+          <t>01062707475</t>
         </is>
       </c>
       <c r="C946" t="inlineStr">
         <is>
-          <t>304174</t>
+          <t>207211</t>
         </is>
       </c>
       <c r="D946" t="inlineStr">
@@ -25973,108 +25973,108 @@
     <row r="947">
       <c r="A947" t="inlineStr">
         <is>
-          <t>music214</t>
+          <t>kk_4837971410</t>
         </is>
       </c>
       <c r="B947" t="inlineStr">
         <is>
-          <t>01031023988</t>
+          <t>01045750650</t>
         </is>
       </c>
       <c r="C947" t="inlineStr">
         <is>
-          <t>303965</t>
+          <t>304028</t>
         </is>
       </c>
       <c r="D947" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Official SNS</t>
         </is>
       </c>
       <c r="E947" t="inlineStr">
         <is>
-          <t>6968489536332</t>
+          <t>EFW_04</t>
         </is>
       </c>
     </row>
     <row r="948">
       <c r="A948" t="inlineStr">
         <is>
-          <t>kk_4837971410</t>
+          <t>music214</t>
         </is>
       </c>
       <c r="B948" t="inlineStr">
         <is>
-          <t>01045750650</t>
+          <t>01031023988</t>
         </is>
       </c>
       <c r="C948" t="inlineStr">
         <is>
-          <t>304028</t>
+          <t>303965</t>
         </is>
       </c>
       <c r="D948" t="inlineStr">
         <is>
-          <t>Official SNS</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E948" t="inlineStr">
         <is>
-          <t>EFW_04</t>
+          <t>6968489536332</t>
         </is>
       </c>
     </row>
     <row r="949">
       <c r="A949" t="inlineStr">
         <is>
-          <t>kk_3465185882</t>
+          <t>kk_4835699259</t>
         </is>
       </c>
       <c r="B949" t="inlineStr">
         <is>
-          <t>01036194497</t>
+          <t>01045029445</t>
         </is>
       </c>
       <c r="C949" t="inlineStr">
         <is>
-          <t>243704</t>
+          <t>303881</t>
         </is>
       </c>
       <c r="D949" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E949" t="inlineStr">
         <is>
-          <t>KAKAO_alimtalk</t>
+          <t>6968489536332</t>
         </is>
       </c>
     </row>
     <row r="950">
       <c r="A950" t="inlineStr">
         <is>
-          <t>kk_4835699259</t>
+          <t>kk_3465185882</t>
         </is>
       </c>
       <c r="B950" t="inlineStr">
         <is>
-          <t>01045029445</t>
+          <t>01036194497</t>
         </is>
       </c>
       <c r="C950" t="inlineStr">
         <is>
-          <t>303881</t>
+          <t>243704</t>
         </is>
       </c>
       <c r="D950" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E950" t="inlineStr">
         <is>
-          <t>6968489536332</t>
+          <t>KAKAO_alimtalk</t>
         </is>
       </c>
     </row>
@@ -26135,17 +26135,17 @@
     <row r="953">
       <c r="A953" t="inlineStr">
         <is>
-          <t>kimchhgood</t>
+          <t>kk_3776403631</t>
         </is>
       </c>
       <c r="B953" t="inlineStr">
         <is>
-          <t>01092133961</t>
+          <t>01034755755</t>
         </is>
       </c>
       <c r="C953" t="inlineStr">
         <is>
-          <t>53493</t>
+          <t>255908</t>
         </is>
       </c>
       <c r="D953" t="inlineStr">
@@ -26155,24 +26155,24 @@
       </c>
       <c r="E953" t="inlineStr">
         <is>
-          <t>EDM_TOP</t>
+          <t>KAKAO_alimtalk</t>
         </is>
       </c>
     </row>
     <row r="954">
       <c r="A954" t="inlineStr">
         <is>
-          <t>kk_3776403631</t>
+          <t>kimchhgood</t>
         </is>
       </c>
       <c r="B954" t="inlineStr">
         <is>
-          <t>01034755755</t>
+          <t>01092133961</t>
         </is>
       </c>
       <c r="C954" t="inlineStr">
         <is>
-          <t>255908</t>
+          <t>53493</t>
         </is>
       </c>
       <c r="D954" t="inlineStr">
@@ -26182,34 +26182,34 @@
       </c>
       <c r="E954" t="inlineStr">
         <is>
-          <t>KAKAO_alimtalk</t>
+          <t>EDM_TOP</t>
         </is>
       </c>
     </row>
     <row r="955">
       <c r="A955" t="inlineStr">
         <is>
-          <t>willper</t>
+          <t>kk_4651201605</t>
         </is>
       </c>
       <c r="B955" t="inlineStr">
         <is>
-          <t>01085343440</t>
+          <t>01045489411</t>
         </is>
       </c>
       <c r="C955" t="inlineStr">
         <is>
-          <t>304408</t>
+          <t>293053</t>
         </is>
       </c>
       <c r="D955" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E955" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>Paid Ad</t>
         </is>
       </c>
     </row>
@@ -26243,27 +26243,27 @@
     <row r="957">
       <c r="A957" t="inlineStr">
         <is>
-          <t>kk_4651201605</t>
+          <t>willper</t>
         </is>
       </c>
       <c r="B957" t="inlineStr">
         <is>
-          <t>01045489411</t>
+          <t>01085343440</t>
         </is>
       </c>
       <c r="C957" t="inlineStr">
         <is>
-          <t>293053</t>
+          <t>304408</t>
         </is>
       </c>
       <c r="D957" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="E957" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Direct</t>
         </is>
       </c>
     </row>
@@ -26324,17 +26324,17 @@
     <row r="960">
       <c r="A960" t="inlineStr">
         <is>
-          <t>kk_4841799872</t>
+          <t>nikemkr</t>
         </is>
       </c>
       <c r="B960" t="inlineStr">
         <is>
-          <t>01023236956</t>
+          <t>01032361592</t>
         </is>
       </c>
       <c r="C960" t="inlineStr">
         <is>
-          <t>304205</t>
+          <t>145423</t>
         </is>
       </c>
       <c r="D960" t="inlineStr">
@@ -26344,61 +26344,61 @@
       </c>
       <c r="E960" t="inlineStr">
         <is>
-          <t>컬럼비아_DPA_240530</t>
+          <t>naver_brandsearch_mobile</t>
         </is>
       </c>
     </row>
     <row r="961">
       <c r="A961" t="inlineStr">
         <is>
-          <t>kk_4703272205</t>
+          <t>kk_4841799872</t>
         </is>
       </c>
       <c r="B961" t="inlineStr">
         <is>
-          <t>01062682325</t>
+          <t>01023236956</t>
         </is>
       </c>
       <c r="C961" t="inlineStr">
         <is>
-          <t>296093</t>
+          <t>304205</t>
         </is>
       </c>
       <c r="D961" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E961" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0410exclusive2</t>
+          <t>컬럼비아_DPA_240530</t>
         </is>
       </c>
     </row>
     <row r="962">
       <c r="A962" t="inlineStr">
         <is>
-          <t>nikemkr</t>
+          <t>kk_4703272205</t>
         </is>
       </c>
       <c r="B962" t="inlineStr">
         <is>
-          <t>01032361592</t>
+          <t>01062682325</t>
         </is>
       </c>
       <c r="C962" t="inlineStr">
         <is>
-          <t>145423</t>
+          <t>296093</t>
         </is>
       </c>
       <c r="D962" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E962" t="inlineStr">
         <is>
-          <t>naver_brandsearch_mobile</t>
+          <t>LMS_ECOM_0410exclusive2</t>
         </is>
       </c>
     </row>
@@ -26486,54 +26486,54 @@
     <row r="966">
       <c r="A966" t="inlineStr">
         <is>
-          <t>kk_4837595875</t>
+          <t>sjl4534</t>
         </is>
       </c>
       <c r="B966" t="inlineStr">
         <is>
-          <t>01057852463</t>
+          <t>01028023660</t>
         </is>
       </c>
       <c r="C966" t="inlineStr">
         <is>
-          <t>304000</t>
+          <t>174607</t>
         </is>
       </c>
       <c r="D966" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E966" t="inlineStr">
         <is>
-          <t>6968489536332</t>
+          <t>KAKAO_CH_MESSAGE_0409_EXCLUSIVE</t>
         </is>
       </c>
     </row>
     <row r="967">
       <c r="A967" t="inlineStr">
         <is>
-          <t>sjl4534</t>
+          <t>kk_4837152929</t>
         </is>
       </c>
       <c r="B967" t="inlineStr">
         <is>
-          <t>01028023660</t>
+          <t>01047050730</t>
         </is>
       </c>
       <c r="C967" t="inlineStr">
         <is>
-          <t>174607</t>
+          <t>303966</t>
         </is>
       </c>
       <c r="D967" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E967" t="inlineStr">
         <is>
-          <t>KAKAO_CH_MESSAGE_0409_EXCLUSIVE</t>
+          <t>6968489536332</t>
         </is>
       </c>
     </row>
@@ -26567,54 +26567,54 @@
     <row r="969">
       <c r="A969" t="inlineStr">
         <is>
-          <t>kk_3430866338</t>
+          <t>kk_4837595875</t>
         </is>
       </c>
       <c r="B969" t="inlineStr">
         <is>
-          <t>01026364692</t>
+          <t>01057852463</t>
         </is>
       </c>
       <c r="C969" t="inlineStr">
         <is>
-          <t>242249</t>
+          <t>304000</t>
         </is>
       </c>
       <c r="D969" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E969" t="inlineStr">
         <is>
-          <t>Email_mkt</t>
+          <t>6968489536332</t>
         </is>
       </c>
     </row>
     <row r="970">
       <c r="A970" t="inlineStr">
         <is>
-          <t>kk_4837152929</t>
+          <t>kk_3430866338</t>
         </is>
       </c>
       <c r="B970" t="inlineStr">
         <is>
-          <t>01047050730</t>
+          <t>01026364692</t>
         </is>
       </c>
       <c r="C970" t="inlineStr">
         <is>
-          <t>303966</t>
+          <t>242249</t>
         </is>
       </c>
       <c r="D970" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E970" t="inlineStr">
         <is>
-          <t>6968489536332</t>
+          <t>Email_mkt</t>
         </is>
       </c>
     </row>
@@ -26756,17 +26756,17 @@
     <row r="976">
       <c r="A976" t="inlineStr">
         <is>
-          <t>kk_4846729102</t>
+          <t>imgain0422</t>
         </is>
       </c>
       <c r="B976" t="inlineStr">
         <is>
-          <t>01084771303</t>
+          <t>01029135546</t>
         </is>
       </c>
       <c r="C976" t="inlineStr">
         <is>
-          <t>304461</t>
+          <t>181451</t>
         </is>
       </c>
       <c r="D976" t="inlineStr">
@@ -26783,17 +26783,17 @@
     <row r="977">
       <c r="A977" t="inlineStr">
         <is>
-          <t>imgain0422</t>
+          <t>kk_4846729102</t>
         </is>
       </c>
       <c r="B977" t="inlineStr">
         <is>
-          <t>01029135546</t>
+          <t>01084771303</t>
         </is>
       </c>
       <c r="C977" t="inlineStr">
         <is>
-          <t>181451</t>
+          <t>304461</t>
         </is>
       </c>
       <c r="D977" t="inlineStr">
@@ -26810,125 +26810,125 @@
     <row r="978">
       <c r="A978" t="inlineStr">
         <is>
-          <t>ch5115</t>
+          <t>kk_2788668233</t>
         </is>
       </c>
       <c r="B978" t="inlineStr">
         <is>
-          <t>01084479339</t>
+          <t>01041696139</t>
         </is>
       </c>
       <c r="C978" t="inlineStr">
         <is>
-          <t>240557</t>
+          <t>210002</t>
         </is>
       </c>
       <c r="D978" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E978" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>Paid Ad</t>
         </is>
       </c>
     </row>
     <row r="979">
       <c r="A979" t="inlineStr">
         <is>
-          <t>kk_4845661756</t>
+          <t>ch5115</t>
         </is>
       </c>
       <c r="B979" t="inlineStr">
         <is>
-          <t>01095936572</t>
+          <t>01084479339</t>
         </is>
       </c>
       <c r="C979" t="inlineStr">
         <is>
-          <t>304422</t>
+          <t>240557</t>
         </is>
       </c>
       <c r="D979" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="E979" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Direct</t>
         </is>
       </c>
     </row>
     <row r="980">
       <c r="A980" t="inlineStr">
         <is>
-          <t>kk_2788668233</t>
+          <t>kk_3183517395</t>
         </is>
       </c>
       <c r="B980" t="inlineStr">
         <is>
-          <t>01041696139</t>
+          <t>01082019936</t>
         </is>
       </c>
       <c r="C980" t="inlineStr">
         <is>
-          <t>210002</t>
+          <t>228501</t>
         </is>
       </c>
       <c r="D980" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="E980" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Direct</t>
         </is>
       </c>
     </row>
     <row r="981">
       <c r="A981" t="inlineStr">
         <is>
-          <t>chpuss74</t>
+          <t>kk_4845661756</t>
         </is>
       </c>
       <c r="B981" t="inlineStr">
         <is>
-          <t>01035361091</t>
+          <t>01095936572</t>
         </is>
       </c>
       <c r="C981" t="inlineStr">
         <is>
-          <t>154462</t>
+          <t>304422</t>
         </is>
       </c>
       <c r="D981" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E981" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>Paid Ad</t>
         </is>
       </c>
     </row>
     <row r="982">
       <c r="A982" t="inlineStr">
         <is>
-          <t>kk_3183517395</t>
+          <t>chpuss74</t>
         </is>
       </c>
       <c r="B982" t="inlineStr">
         <is>
-          <t>01082019936</t>
+          <t>01035361091</t>
         </is>
       </c>
       <c r="C982" t="inlineStr">
         <is>
-          <t>228501</t>
+          <t>154462</t>
         </is>
       </c>
       <c r="D982" t="inlineStr">
@@ -26945,27 +26945,27 @@
     <row r="983">
       <c r="A983" t="inlineStr">
         <is>
-          <t>kk_2775500473</t>
+          <t>kk_4844076820</t>
         </is>
       </c>
       <c r="B983" t="inlineStr">
         <is>
-          <t>01045659020</t>
+          <t>01091346366</t>
         </is>
       </c>
       <c r="C983" t="inlineStr">
         <is>
-          <t>209371</t>
+          <t>304343</t>
         </is>
       </c>
       <c r="D983" t="inlineStr">
         <is>
-          <t>Organic Traffic</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E983" t="inlineStr">
         <is>
-          <t>(referral)</t>
+          <t>6968489536332</t>
         </is>
       </c>
     </row>
@@ -26999,44 +26999,44 @@
     <row r="985">
       <c r="A985" t="inlineStr">
         <is>
-          <t>kk_4844076820</t>
+          <t>kjhk5404</t>
         </is>
       </c>
       <c r="B985" t="inlineStr">
         <is>
-          <t>01091346366</t>
+          <t>01027390700</t>
         </is>
       </c>
       <c r="C985" t="inlineStr">
         <is>
-          <t>304343</t>
+          <t>280120</t>
         </is>
       </c>
       <c r="D985" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E985" t="inlineStr">
         <is>
-          <t>6968489536332</t>
+          <t>KAKAO_alimtalk</t>
         </is>
       </c>
     </row>
     <row r="986">
       <c r="A986" t="inlineStr">
         <is>
-          <t>kjhk5404</t>
+          <t>kk_3242479813</t>
         </is>
       </c>
       <c r="B986" t="inlineStr">
         <is>
-          <t>01027390700</t>
+          <t>01040431115</t>
         </is>
       </c>
       <c r="C986" t="inlineStr">
         <is>
-          <t>280120</t>
+          <t>234768</t>
         </is>
       </c>
       <c r="D986" t="inlineStr">
@@ -27046,34 +27046,34 @@
       </c>
       <c r="E986" t="inlineStr">
         <is>
-          <t>KAKAO_alimtalk</t>
+          <t>LMS_ECOM_0410exclusive2</t>
         </is>
       </c>
     </row>
     <row r="987">
       <c r="A987" t="inlineStr">
         <is>
-          <t>kk_3242479813</t>
+          <t>kk_2775500473</t>
         </is>
       </c>
       <c r="B987" t="inlineStr">
         <is>
-          <t>01040431115</t>
+          <t>01045659020</t>
         </is>
       </c>
       <c r="C987" t="inlineStr">
         <is>
-          <t>234768</t>
+          <t>209371</t>
         </is>
       </c>
       <c r="D987" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Organic Traffic</t>
         </is>
       </c>
       <c r="E987" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0410exclusive2</t>
+          <t>(referral)</t>
         </is>
       </c>
     </row>
@@ -27107,54 +27107,54 @@
     <row r="989">
       <c r="A989" t="inlineStr">
         <is>
-          <t>kk_4522711623</t>
+          <t>kk_4434329905</t>
         </is>
       </c>
       <c r="B989" t="inlineStr">
         <is>
-          <t>01089870313</t>
+          <t>01071724035</t>
         </is>
       </c>
       <c r="C989" t="inlineStr">
         <is>
-          <t>286306</t>
+          <t>281922</t>
         </is>
       </c>
       <c r="D989" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E989" t="inlineStr">
         <is>
-          <t>6968489536332</t>
+          <t>Email_mkt</t>
         </is>
       </c>
     </row>
     <row r="990">
       <c r="A990" t="inlineStr">
         <is>
-          <t>kk_4434329905</t>
+          <t>kk_4522711623</t>
         </is>
       </c>
       <c r="B990" t="inlineStr">
         <is>
-          <t>01071724035</t>
+          <t>01089870313</t>
         </is>
       </c>
       <c r="C990" t="inlineStr">
         <is>
-          <t>281922</t>
+          <t>286306</t>
         </is>
       </c>
       <c r="D990" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E990" t="inlineStr">
         <is>
-          <t>Email_mkt</t>
+          <t>6968489536332</t>
         </is>
       </c>
     </row>
@@ -27188,17 +27188,17 @@
     <row r="992">
       <c r="A992" t="inlineStr">
         <is>
-          <t>kk_4841778210</t>
+          <t>kk_4840817001</t>
         </is>
       </c>
       <c r="B992" t="inlineStr">
         <is>
-          <t>01087814274</t>
+          <t>01085963383</t>
         </is>
       </c>
       <c r="C992" t="inlineStr">
         <is>
-          <t>304202</t>
+          <t>304168</t>
         </is>
       </c>
       <c r="D992" t="inlineStr">
@@ -27208,24 +27208,24 @@
       </c>
       <c r="E992" t="inlineStr">
         <is>
-          <t>naver_brandsearch_mobile</t>
+          <t>6968489536332</t>
         </is>
       </c>
     </row>
     <row r="993">
       <c r="A993" t="inlineStr">
         <is>
-          <t>kk_4840817001</t>
+          <t>kk_4841778210</t>
         </is>
       </c>
       <c r="B993" t="inlineStr">
         <is>
-          <t>01085963383</t>
+          <t>01087814274</t>
         </is>
       </c>
       <c r="C993" t="inlineStr">
         <is>
-          <t>304168</t>
+          <t>304202</t>
         </is>
       </c>
       <c r="D993" t="inlineStr">
@@ -27235,24 +27235,24 @@
       </c>
       <c r="E993" t="inlineStr">
         <is>
-          <t>6968489536332</t>
+          <t>naver_brandsearch_mobile</t>
         </is>
       </c>
     </row>
     <row r="994">
       <c r="A994" t="inlineStr">
         <is>
-          <t>kk_3213636735</t>
+          <t>eyounjoo</t>
         </is>
       </c>
       <c r="B994" t="inlineStr">
         <is>
-          <t>01071338973</t>
+          <t>01036167949</t>
         </is>
       </c>
       <c r="C994" t="inlineStr">
         <is>
-          <t>232010</t>
+          <t>283223</t>
         </is>
       </c>
       <c r="D994" t="inlineStr">
@@ -27262,78 +27262,78 @@
       </c>
       <c r="E994" t="inlineStr">
         <is>
-          <t>KAKAO_CH_MENU_0226_TRAILRUN</t>
+          <t>LMS_ECOM_0410exclusive2</t>
         </is>
       </c>
     </row>
     <row r="995">
       <c r="A995" t="inlineStr">
         <is>
-          <t>kk_4228106377</t>
+          <t>xoxoie2</t>
         </is>
       </c>
       <c r="B995" t="inlineStr">
         <is>
-          <t>01063165271</t>
+          <t>01043560834</t>
         </is>
       </c>
       <c r="C995" t="inlineStr">
         <is>
-          <t>273193</t>
+          <t>304072</t>
         </is>
       </c>
       <c r="D995" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Official SNS</t>
         </is>
       </c>
       <c r="E995" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0410exclusive2</t>
+          <t>EFW_04</t>
         </is>
       </c>
     </row>
     <row r="996">
       <c r="A996" t="inlineStr">
         <is>
-          <t>eyounjoo</t>
+          <t>kk_4839241951</t>
         </is>
       </c>
       <c r="B996" t="inlineStr">
         <is>
-          <t>01036167949</t>
+          <t>01079146776</t>
         </is>
       </c>
       <c r="C996" t="inlineStr">
         <is>
-          <t>283223</t>
+          <t>304090</t>
         </is>
       </c>
       <c r="D996" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E996" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0410exclusive2</t>
+          <t>6968489536332</t>
         </is>
       </c>
     </row>
     <row r="997">
       <c r="A997" t="inlineStr">
         <is>
-          <t>kk_4839241951</t>
+          <t>kk_4840045474</t>
         </is>
       </c>
       <c r="B997" t="inlineStr">
         <is>
-          <t>01079146776</t>
+          <t>01096310429</t>
         </is>
       </c>
       <c r="C997" t="inlineStr">
         <is>
-          <t>304090</t>
+          <t>304122</t>
         </is>
       </c>
       <c r="D997" t="inlineStr">
@@ -27350,17 +27350,17 @@
     <row r="998">
       <c r="A998" t="inlineStr">
         <is>
-          <t>gus7526</t>
+          <t>kk_3213636735</t>
         </is>
       </c>
       <c r="B998" t="inlineStr">
         <is>
-          <t>01050931023</t>
+          <t>01071338973</t>
         </is>
       </c>
       <c r="C998" t="inlineStr">
         <is>
-          <t>140860</t>
+          <t>232010</t>
         </is>
       </c>
       <c r="D998" t="inlineStr">
@@ -27370,159 +27370,159 @@
       </c>
       <c r="E998" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0410exclusive2</t>
+          <t>KAKAO_CH_MENU_0226_TRAILRUN</t>
         </is>
       </c>
     </row>
     <row r="999">
       <c r="A999" t="inlineStr">
         <is>
-          <t>ssama</t>
+          <t>z090909x</t>
         </is>
       </c>
       <c r="B999" t="inlineStr">
         <is>
-          <t>01056271982</t>
+          <t>01092058111</t>
         </is>
       </c>
       <c r="C999" t="inlineStr">
         <is>
-          <t>47874</t>
+          <t>113003</t>
         </is>
       </c>
       <c r="D999" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E999" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0410exclusive2</t>
+          <t>6968489536332</t>
         </is>
       </c>
     </row>
     <row r="1000">
       <c r="A1000" t="inlineStr">
         <is>
-          <t>xoxoie2</t>
+          <t>ssama</t>
         </is>
       </c>
       <c r="B1000" t="inlineStr">
         <is>
-          <t>01043560834</t>
+          <t>01056271982</t>
         </is>
       </c>
       <c r="C1000" t="inlineStr">
         <is>
-          <t>304072</t>
+          <t>47874</t>
         </is>
       </c>
       <c r="D1000" t="inlineStr">
         <is>
-          <t>Official SNS</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E1000" t="inlineStr">
         <is>
-          <t>EFW_04</t>
+          <t>LMS_ECOM_0410exclusive2</t>
         </is>
       </c>
     </row>
     <row r="1001">
       <c r="A1001" t="inlineStr">
         <is>
-          <t>z090909x</t>
+          <t>gus7526</t>
         </is>
       </c>
       <c r="B1001" t="inlineStr">
         <is>
-          <t>01092058111</t>
+          <t>01050931023</t>
         </is>
       </c>
       <c r="C1001" t="inlineStr">
         <is>
-          <t>113003</t>
+          <t>140860</t>
         </is>
       </c>
       <c r="D1001" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E1001" t="inlineStr">
         <is>
-          <t>6968489536332</t>
+          <t>LMS_ECOM_0410exclusive2</t>
         </is>
       </c>
     </row>
     <row r="1002">
       <c r="A1002" t="inlineStr">
         <is>
-          <t>kk_4840045474</t>
+          <t>kk_4228106377</t>
         </is>
       </c>
       <c r="B1002" t="inlineStr">
         <is>
-          <t>01096310429</t>
+          <t>01063165271</t>
         </is>
       </c>
       <c r="C1002" t="inlineStr">
         <is>
-          <t>304122</t>
+          <t>273193</t>
         </is>
       </c>
       <c r="D1002" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E1002" t="inlineStr">
         <is>
-          <t>6968489536332</t>
+          <t>LMS_ECOM_0410exclusive2</t>
         </is>
       </c>
     </row>
     <row r="1003">
       <c r="A1003" t="inlineStr">
         <is>
-          <t>kk_3234166915</t>
+          <t>enel778</t>
         </is>
       </c>
       <c r="B1003" t="inlineStr">
         <is>
-          <t>01082632995</t>
+          <t>01086066364</t>
         </is>
       </c>
       <c r="C1003" t="inlineStr">
         <is>
-          <t>233887</t>
+          <t>207732</t>
         </is>
       </c>
       <c r="D1003" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E1003" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>Email_mkt</t>
         </is>
       </c>
     </row>
     <row r="1004">
       <c r="A1004" t="inlineStr">
         <is>
-          <t>scaler</t>
+          <t>sjk6231</t>
         </is>
       </c>
       <c r="B1004" t="inlineStr">
         <is>
-          <t>01037090080</t>
+          <t>01031985034</t>
         </is>
       </c>
       <c r="C1004" t="inlineStr">
         <is>
-          <t>178752</t>
+          <t>281342</t>
         </is>
       </c>
       <c r="D1004" t="inlineStr">
@@ -27532,7 +27532,7 @@
       </c>
       <c r="E1004" t="inlineStr">
         <is>
-          <t>KAKAO_CH_MESSAGE_0409_EXCLUSIVE</t>
+          <t>Email_mkt</t>
         </is>
       </c>
     </row>
@@ -27566,44 +27566,44 @@
     <row r="1006">
       <c r="A1006" t="inlineStr">
         <is>
-          <t>sjk6231</t>
+          <t>kk_3234166915</t>
         </is>
       </c>
       <c r="B1006" t="inlineStr">
         <is>
-          <t>01031985034</t>
+          <t>01082632995</t>
         </is>
       </c>
       <c r="C1006" t="inlineStr">
         <is>
-          <t>281342</t>
+          <t>233887</t>
         </is>
       </c>
       <c r="D1006" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="E1006" t="inlineStr">
         <is>
-          <t>Email_mkt</t>
+          <t>Direct</t>
         </is>
       </c>
     </row>
     <row r="1007">
       <c r="A1007" t="inlineStr">
         <is>
-          <t>enel778</t>
+          <t>scaler</t>
         </is>
       </c>
       <c r="B1007" t="inlineStr">
         <is>
-          <t>01086066364</t>
+          <t>01037090080</t>
         </is>
       </c>
       <c r="C1007" t="inlineStr">
         <is>
-          <t>207732</t>
+          <t>178752</t>
         </is>
       </c>
       <c r="D1007" t="inlineStr">
@@ -27613,24 +27613,24 @@
       </c>
       <c r="E1007" t="inlineStr">
         <is>
-          <t>Email_mkt</t>
+          <t>KAKAO_CH_MESSAGE_0409_EXCLUSIVE</t>
         </is>
       </c>
     </row>
     <row r="1008">
       <c r="A1008" t="inlineStr">
         <is>
-          <t>kk_2757334528</t>
+          <t>kk_4444429966</t>
         </is>
       </c>
       <c r="B1008" t="inlineStr">
         <is>
-          <t>01089379633</t>
+          <t>01032219702</t>
         </is>
       </c>
       <c r="C1008" t="inlineStr">
         <is>
-          <t>208240</t>
+          <t>282222</t>
         </is>
       </c>
       <c r="D1008" t="inlineStr">
@@ -27647,54 +27647,54 @@
     <row r="1009">
       <c r="A1009" t="inlineStr">
         <is>
-          <t>zodiacz</t>
+          <t>kk_2757334528</t>
         </is>
       </c>
       <c r="B1009" t="inlineStr">
         <is>
-          <t>01093671032</t>
+          <t>01089379633</t>
         </is>
       </c>
       <c r="C1009" t="inlineStr">
         <is>
-          <t>108304</t>
+          <t>208240</t>
         </is>
       </c>
       <c r="D1009" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="E1009" t="inlineStr">
         <is>
-          <t>pmax</t>
+          <t>Direct</t>
         </is>
       </c>
     </row>
     <row r="1010">
       <c r="A1010" t="inlineStr">
         <is>
-          <t>kk_4444429966</t>
+          <t>zodiacz</t>
         </is>
       </c>
       <c r="B1010" t="inlineStr">
         <is>
-          <t>01032219702</t>
+          <t>01093671032</t>
         </is>
       </c>
       <c r="C1010" t="inlineStr">
         <is>
-          <t>282222</t>
+          <t>108304</t>
         </is>
       </c>
       <c r="D1010" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E1010" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>pmax</t>
         </is>
       </c>
     </row>
@@ -27728,54 +27728,54 @@
     <row r="1012">
       <c r="A1012" t="inlineStr">
         <is>
-          <t>kk_4218204827</t>
+          <t>mse001</t>
         </is>
       </c>
       <c r="B1012" t="inlineStr">
         <is>
-          <t>01023704903</t>
+          <t>01085185510</t>
         </is>
       </c>
       <c r="C1012" t="inlineStr">
         <is>
-          <t>272698</t>
+          <t>227227</t>
         </is>
       </c>
       <c r="D1012" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E1012" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>KAKAO_alimtalk</t>
         </is>
       </c>
     </row>
     <row r="1013">
       <c r="A1013" t="inlineStr">
         <is>
-          <t>mse001</t>
+          <t>kk_4218204827</t>
         </is>
       </c>
       <c r="B1013" t="inlineStr">
         <is>
-          <t>01085185510</t>
+          <t>01023704903</t>
         </is>
       </c>
       <c r="C1013" t="inlineStr">
         <is>
-          <t>227227</t>
+          <t>272698</t>
         </is>
       </c>
       <c r="D1013" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="E1013" t="inlineStr">
         <is>
-          <t>KAKAO_alimtalk</t>
+          <t>Direct</t>
         </is>
       </c>
     </row>
@@ -27809,27 +27809,27 @@
     <row r="1015">
       <c r="A1015" t="inlineStr">
         <is>
-          <t>kk_4375003446</t>
+          <t>kk_3169777000</t>
         </is>
       </c>
       <c r="B1015" t="inlineStr">
         <is>
-          <t>01087457282</t>
+          <t>01089348462</t>
         </is>
       </c>
       <c r="C1015" t="inlineStr">
         <is>
-          <t>280131</t>
+          <t>224876</t>
         </is>
       </c>
       <c r="D1015" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="E1015" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0410exclusive2</t>
+          <t>Direct</t>
         </is>
       </c>
     </row>
@@ -27863,27 +27863,27 @@
     <row r="1017">
       <c r="A1017" t="inlineStr">
         <is>
-          <t>kk_3169777000</t>
+          <t>kk_4375003446</t>
         </is>
       </c>
       <c r="B1017" t="inlineStr">
         <is>
-          <t>01089348462</t>
+          <t>01087457282</t>
         </is>
       </c>
       <c r="C1017" t="inlineStr">
         <is>
-          <t>224876</t>
+          <t>280131</t>
         </is>
       </c>
       <c r="D1017" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E1017" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>LMS_ECOM_0410exclusive2</t>
         </is>
       </c>
     </row>
@@ -27917,71 +27917,71 @@
     <row r="1019">
       <c r="A1019" t="inlineStr">
         <is>
-          <t>dongheon20</t>
+          <t>xuswldls</t>
         </is>
       </c>
       <c r="B1019" t="inlineStr">
         <is>
-          <t>01052298928</t>
+          <t>01027349414</t>
         </is>
       </c>
       <c r="C1019" t="inlineStr">
         <is>
-          <t>155362</t>
+          <t>133308</t>
         </is>
       </c>
       <c r="D1019" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="E1019" t="inlineStr">
         <is>
-          <t>6968489536332</t>
+          <t>Direct</t>
         </is>
       </c>
     </row>
     <row r="1020">
       <c r="A1020" t="inlineStr">
         <is>
-          <t>kk_3688034999</t>
+          <t>kk_4247630261</t>
         </is>
       </c>
       <c r="B1020" t="inlineStr">
         <is>
-          <t>01025408262</t>
+          <t>01091437323</t>
         </is>
       </c>
       <c r="C1020" t="inlineStr">
         <is>
-          <t>250755</t>
+          <t>274140</t>
         </is>
       </c>
       <c r="D1020" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Organic Traffic</t>
         </is>
       </c>
       <c r="E1020" t="inlineStr">
         <is>
-          <t>KAKAO_alimtalk</t>
+          <t>(referral)</t>
         </is>
       </c>
     </row>
     <row r="1021">
       <c r="A1021" t="inlineStr">
         <is>
-          <t>kk_4472536591</t>
+          <t>kk_3688034999</t>
         </is>
       </c>
       <c r="B1021" t="inlineStr">
         <is>
-          <t>01037057526</t>
+          <t>01025408262</t>
         </is>
       </c>
       <c r="C1021" t="inlineStr">
         <is>
-          <t>283897</t>
+          <t>250755</t>
         </is>
       </c>
       <c r="D1021" t="inlineStr">
@@ -27998,98 +27998,98 @@
     <row r="1022">
       <c r="A1022" t="inlineStr">
         <is>
-          <t>kk_3444865211</t>
+          <t>ohsm0065</t>
         </is>
       </c>
       <c r="B1022" t="inlineStr">
         <is>
-          <t>01021964871</t>
+          <t>01056170065</t>
         </is>
       </c>
       <c r="C1022" t="inlineStr">
         <is>
-          <t>242799</t>
+          <t>74567</t>
         </is>
       </c>
       <c r="D1022" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E1022" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>[PF]트래픽_유사+관심사</t>
         </is>
       </c>
     </row>
     <row r="1023">
       <c r="A1023" t="inlineStr">
         <is>
-          <t>kk_2768989214</t>
+          <t>dongheon20</t>
         </is>
       </c>
       <c r="B1023" t="inlineStr">
         <is>
-          <t>01095004289</t>
+          <t>01052298928</t>
         </is>
       </c>
       <c r="C1023" t="inlineStr">
         <is>
-          <t>209015</t>
+          <t>155362</t>
         </is>
       </c>
       <c r="D1023" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E1023" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>6968489536332</t>
         </is>
       </c>
     </row>
     <row r="1024">
       <c r="A1024" t="inlineStr">
         <is>
-          <t>kk_4247630261</t>
+          <t>kk_4472536591</t>
         </is>
       </c>
       <c r="B1024" t="inlineStr">
         <is>
-          <t>01091437323</t>
+          <t>01037057526</t>
         </is>
       </c>
       <c r="C1024" t="inlineStr">
         <is>
-          <t>274140</t>
+          <t>283897</t>
         </is>
       </c>
       <c r="D1024" t="inlineStr">
         <is>
-          <t>Organic Traffic</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E1024" t="inlineStr">
         <is>
-          <t>(referral)</t>
+          <t>KAKAO_alimtalk</t>
         </is>
       </c>
     </row>
     <row r="1025">
       <c r="A1025" t="inlineStr">
         <is>
-          <t>xuswldls</t>
+          <t>kk_3444865211</t>
         </is>
       </c>
       <c r="B1025" t="inlineStr">
         <is>
-          <t>01027349414</t>
+          <t>01021964871</t>
         </is>
       </c>
       <c r="C1025" t="inlineStr">
         <is>
-          <t>133308</t>
+          <t>242799</t>
         </is>
       </c>
       <c r="D1025" t="inlineStr">
@@ -28106,54 +28106,54 @@
     <row r="1026">
       <c r="A1026" t="inlineStr">
         <is>
-          <t>ohsm0065</t>
+          <t>kk_2768989214</t>
         </is>
       </c>
       <c r="B1026" t="inlineStr">
         <is>
-          <t>01056170065</t>
+          <t>01095004289</t>
         </is>
       </c>
       <c r="C1026" t="inlineStr">
         <is>
-          <t>74567</t>
+          <t>209015</t>
         </is>
       </c>
       <c r="D1026" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="E1026" t="inlineStr">
         <is>
-          <t>[PF]트래픽_유사+관심사</t>
+          <t>Direct</t>
         </is>
       </c>
     </row>
     <row r="1027">
       <c r="A1027" t="inlineStr">
         <is>
-          <t>escalater</t>
+          <t>chibird</t>
         </is>
       </c>
       <c r="B1027" t="inlineStr">
         <is>
-          <t>01090911461</t>
+          <t>01031187674</t>
         </is>
       </c>
       <c r="C1027" t="inlineStr">
         <is>
-          <t>240051</t>
+          <t>219288</t>
         </is>
       </c>
       <c r="D1027" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E1027" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>sa</t>
         </is>
       </c>
     </row>
@@ -28187,17 +28187,17 @@
     <row r="1029">
       <c r="A1029" t="inlineStr">
         <is>
-          <t>kk_3837527580</t>
+          <t>kk_3858585698</t>
         </is>
       </c>
       <c r="B1029" t="inlineStr">
         <is>
-          <t>01084311738</t>
+          <t>01092163429</t>
         </is>
       </c>
       <c r="C1029" t="inlineStr">
         <is>
-          <t>264113</t>
+          <t>265508</t>
         </is>
       </c>
       <c r="D1029" t="inlineStr">
@@ -28207,51 +28207,51 @@
       </c>
       <c r="E1029" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0410exclusive2</t>
+          <t>KAKAO_alimtalk</t>
         </is>
       </c>
     </row>
     <row r="1030">
       <c r="A1030" t="inlineStr">
         <is>
-          <t>chibird</t>
+          <t>escalater</t>
         </is>
       </c>
       <c r="B1030" t="inlineStr">
         <is>
-          <t>01031187674</t>
+          <t>01090911461</t>
         </is>
       </c>
       <c r="C1030" t="inlineStr">
         <is>
-          <t>219288</t>
+          <t>240051</t>
         </is>
       </c>
       <c r="D1030" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="E1030" t="inlineStr">
         <is>
-          <t>sa</t>
+          <t>Direct</t>
         </is>
       </c>
     </row>
     <row r="1031">
       <c r="A1031" t="inlineStr">
         <is>
-          <t>nesto1</t>
+          <t>kk_3837527580</t>
         </is>
       </c>
       <c r="B1031" t="inlineStr">
         <is>
-          <t>01056603953</t>
+          <t>01084311738</t>
         </is>
       </c>
       <c r="C1031" t="inlineStr">
         <is>
-          <t>125251</t>
+          <t>264113</t>
         </is>
       </c>
       <c r="D1031" t="inlineStr">
@@ -28261,24 +28261,24 @@
       </c>
       <c r="E1031" t="inlineStr">
         <is>
-          <t>KAKAO_alimtalk</t>
+          <t>LMS_ECOM_0410exclusive2</t>
         </is>
       </c>
     </row>
     <row r="1032">
       <c r="A1032" t="inlineStr">
         <is>
-          <t>kk_3858585698</t>
+          <t>nesto1</t>
         </is>
       </c>
       <c r="B1032" t="inlineStr">
         <is>
-          <t>01092163429</t>
+          <t>01056603953</t>
         </is>
       </c>
       <c r="C1032" t="inlineStr">
         <is>
-          <t>265508</t>
+          <t>125251</t>
         </is>
       </c>
       <c r="D1032" t="inlineStr">
@@ -28322,17 +28322,17 @@
     <row r="1034">
       <c r="A1034" t="inlineStr">
         <is>
-          <t>seul6169</t>
+          <t>kk_3185867832</t>
         </is>
       </c>
       <c r="B1034" t="inlineStr">
         <is>
-          <t>01066116699</t>
+          <t>01022086508</t>
         </is>
       </c>
       <c r="C1034" t="inlineStr">
         <is>
-          <t>234239</t>
+          <t>229863</t>
         </is>
       </c>
       <c r="D1034" t="inlineStr">
@@ -28342,105 +28342,105 @@
       </c>
       <c r="E1034" t="inlineStr">
         <is>
-          <t>KAKAO_alimtalk</t>
+          <t>LMS_ECOM_0410exclusive2</t>
         </is>
       </c>
     </row>
     <row r="1035">
       <c r="A1035" t="inlineStr">
         <is>
-          <t>kk_4517851709</t>
+          <t>kk_3013902343</t>
         </is>
       </c>
       <c r="B1035" t="inlineStr">
         <is>
-          <t>01066445714</t>
+          <t>01051802326</t>
         </is>
       </c>
       <c r="C1035" t="inlineStr">
         <is>
-          <t>286074</t>
+          <t>219219</t>
         </is>
       </c>
       <c r="D1035" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E1035" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0410exclusive2</t>
+          <t>6968489536332</t>
         </is>
       </c>
     </row>
     <row r="1036">
       <c r="A1036" t="inlineStr">
         <is>
-          <t>kk_3933534683</t>
+          <t>kk_4840061178</t>
         </is>
       </c>
       <c r="B1036" t="inlineStr">
         <is>
-          <t>01030153796</t>
+          <t>01082357895</t>
         </is>
       </c>
       <c r="C1036" t="inlineStr">
         <is>
-          <t>269069</t>
+          <t>304124</t>
         </is>
       </c>
       <c r="D1036" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>Awareness</t>
         </is>
       </c>
       <c r="E1036" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>benz_running_program_2026_coupon</t>
         </is>
       </c>
     </row>
     <row r="1037">
       <c r="A1037" t="inlineStr">
         <is>
-          <t>kk_3013902343</t>
+          <t>hursean</t>
         </is>
       </c>
       <c r="B1037" t="inlineStr">
         <is>
-          <t>01051802326</t>
+          <t>01091975738</t>
         </is>
       </c>
       <c r="C1037" t="inlineStr">
         <is>
-          <t>219219</t>
+          <t>123130</t>
         </is>
       </c>
       <c r="D1037" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E1037" t="inlineStr">
         <is>
-          <t>6968489536332</t>
+          <t>Email_mkt</t>
         </is>
       </c>
     </row>
     <row r="1038">
       <c r="A1038" t="inlineStr">
         <is>
-          <t>hursean</t>
+          <t>kk_4523594127</t>
         </is>
       </c>
       <c r="B1038" t="inlineStr">
         <is>
-          <t>01091975738</t>
+          <t>01085735215</t>
         </is>
       </c>
       <c r="C1038" t="inlineStr">
         <is>
-          <t>123130</t>
+          <t>286358</t>
         </is>
       </c>
       <c r="D1038" t="inlineStr">
@@ -28450,24 +28450,24 @@
       </c>
       <c r="E1038" t="inlineStr">
         <is>
-          <t>Email_mkt</t>
+          <t>LMS_ECOM_0410exclusive2</t>
         </is>
       </c>
     </row>
     <row r="1039">
       <c r="A1039" t="inlineStr">
         <is>
-          <t>kk_2940110361</t>
+          <t>mansoogi</t>
         </is>
       </c>
       <c r="B1039" t="inlineStr">
         <is>
-          <t>01035353200</t>
+          <t>01093240897</t>
         </is>
       </c>
       <c r="C1039" t="inlineStr">
         <is>
-          <t>216362</t>
+          <t>25243</t>
         </is>
       </c>
       <c r="D1039" t="inlineStr">
@@ -28484,17 +28484,17 @@
     <row r="1040">
       <c r="A1040" t="inlineStr">
         <is>
-          <t>kk_4523594127</t>
+          <t>kk_4467707148</t>
         </is>
       </c>
       <c r="B1040" t="inlineStr">
         <is>
-          <t>01085735215</t>
+          <t>01030843332</t>
         </is>
       </c>
       <c r="C1040" t="inlineStr">
         <is>
-          <t>286358</t>
+          <t>283560</t>
         </is>
       </c>
       <c r="D1040" t="inlineStr">
@@ -28511,71 +28511,71 @@
     <row r="1041">
       <c r="A1041" t="inlineStr">
         <is>
-          <t>kk_4840061178</t>
+          <t>kk_4338209948</t>
         </is>
       </c>
       <c r="B1041" t="inlineStr">
         <is>
-          <t>01082357895</t>
+          <t>01088132379</t>
         </is>
       </c>
       <c r="C1041" t="inlineStr">
         <is>
-          <t>304124</t>
+          <t>278781</t>
         </is>
       </c>
       <c r="D1041" t="inlineStr">
         <is>
-          <t>Awareness</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E1041" t="inlineStr">
         <is>
-          <t>benz_running_program_2026_coupon</t>
+          <t>KAKAO_alimtalk</t>
         </is>
       </c>
     </row>
     <row r="1042">
       <c r="A1042" t="inlineStr">
         <is>
-          <t>kk_4338209948</t>
+          <t>kk_3933534683</t>
         </is>
       </c>
       <c r="B1042" t="inlineStr">
         <is>
-          <t>01088132379</t>
+          <t>01030153796</t>
         </is>
       </c>
       <c r="C1042" t="inlineStr">
         <is>
-          <t>278781</t>
+          <t>269069</t>
         </is>
       </c>
       <c r="D1042" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="E1042" t="inlineStr">
         <is>
-          <t>KAKAO_alimtalk</t>
+          <t>Direct</t>
         </is>
       </c>
     </row>
     <row r="1043">
       <c r="A1043" t="inlineStr">
         <is>
-          <t>mansoogi</t>
+          <t>kk_2940110361</t>
         </is>
       </c>
       <c r="B1043" t="inlineStr">
         <is>
-          <t>01093240897</t>
+          <t>01035353200</t>
         </is>
       </c>
       <c r="C1043" t="inlineStr">
         <is>
-          <t>25243</t>
+          <t>216362</t>
         </is>
       </c>
       <c r="D1043" t="inlineStr">
@@ -28592,17 +28592,17 @@
     <row r="1044">
       <c r="A1044" t="inlineStr">
         <is>
-          <t>kk_4467707148</t>
+          <t>aya6969</t>
         </is>
       </c>
       <c r="B1044" t="inlineStr">
         <is>
-          <t>01030843332</t>
+          <t>01076590009</t>
         </is>
       </c>
       <c r="C1044" t="inlineStr">
         <is>
-          <t>283560</t>
+          <t>162562</t>
         </is>
       </c>
       <c r="D1044" t="inlineStr">
@@ -28619,17 +28619,17 @@
     <row r="1045">
       <c r="A1045" t="inlineStr">
         <is>
-          <t>aya6969</t>
+          <t>seul6169</t>
         </is>
       </c>
       <c r="B1045" t="inlineStr">
         <is>
-          <t>01076590009</t>
+          <t>01066116699</t>
         </is>
       </c>
       <c r="C1045" t="inlineStr">
         <is>
-          <t>162562</t>
+          <t>234239</t>
         </is>
       </c>
       <c r="D1045" t="inlineStr">
@@ -28639,24 +28639,24 @@
       </c>
       <c r="E1045" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0410exclusive2</t>
+          <t>KAKAO_alimtalk</t>
         </is>
       </c>
     </row>
     <row r="1046">
       <c r="A1046" t="inlineStr">
         <is>
-          <t>kk_3185867832</t>
+          <t>kk_4517851709</t>
         </is>
       </c>
       <c r="B1046" t="inlineStr">
         <is>
-          <t>01022086508</t>
+          <t>01066445714</t>
         </is>
       </c>
       <c r="C1046" t="inlineStr">
         <is>
-          <t>229863</t>
+          <t>286074</t>
         </is>
       </c>
       <c r="D1046" t="inlineStr">
@@ -28673,17 +28673,17 @@
     <row r="1047">
       <c r="A1047" t="inlineStr">
         <is>
-          <t>kk_4526169965</t>
+          <t>kk_3155938902</t>
         </is>
       </c>
       <c r="B1047" t="inlineStr">
         <is>
-          <t>01076289838</t>
+          <t>01098557018</t>
         </is>
       </c>
       <c r="C1047" t="inlineStr">
         <is>
-          <t>286553</t>
+          <t>223731</t>
         </is>
       </c>
       <c r="D1047" t="inlineStr">
@@ -28700,71 +28700,71 @@
     <row r="1048">
       <c r="A1048" t="inlineStr">
         <is>
-          <t>kk_4351086966</t>
+          <t>kk_3665803645</t>
         </is>
       </c>
       <c r="B1048" t="inlineStr">
         <is>
-          <t>01042088262</t>
+          <t>01095549123</t>
         </is>
       </c>
       <c r="C1048" t="inlineStr">
         <is>
-          <t>279266</t>
+          <t>249835</t>
         </is>
       </c>
       <c r="D1048" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E1048" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>KAKAO_CH_MESSAGE_0409_EXCLUSIVE</t>
         </is>
       </c>
     </row>
     <row r="1049">
       <c r="A1049" t="inlineStr">
         <is>
-          <t>bbluesea</t>
+          <t>kk_3154612153</t>
         </is>
       </c>
       <c r="B1049" t="inlineStr">
         <is>
-          <t>01076473601</t>
+          <t>01056681753</t>
         </is>
       </c>
       <c r="C1049" t="inlineStr">
         <is>
-          <t>152067</t>
+          <t>223664</t>
         </is>
       </c>
       <c r="D1049" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="E1049" t="inlineStr">
         <is>
-          <t>KAKAO_CH_MENU_260406_LIGHTJACKET</t>
+          <t>Direct</t>
         </is>
       </c>
     </row>
     <row r="1050">
       <c r="A1050" t="inlineStr">
         <is>
-          <t>kk_3665803645</t>
+          <t>kk_4526169965</t>
         </is>
       </c>
       <c r="B1050" t="inlineStr">
         <is>
-          <t>01095549123</t>
+          <t>01076289838</t>
         </is>
       </c>
       <c r="C1050" t="inlineStr">
         <is>
-          <t>249835</t>
+          <t>286553</t>
         </is>
       </c>
       <c r="D1050" t="inlineStr">
@@ -28774,24 +28774,24 @@
       </c>
       <c r="E1050" t="inlineStr">
         <is>
-          <t>KAKAO_CH_MESSAGE_0409_EXCLUSIVE</t>
+          <t>KAKAO_CH_MESSAGE_0409_HIKE365SUMMER</t>
         </is>
       </c>
     </row>
     <row r="1051">
       <c r="A1051" t="inlineStr">
         <is>
-          <t>kk_3155938902</t>
+          <t>jhmin000</t>
         </is>
       </c>
       <c r="B1051" t="inlineStr">
         <is>
-          <t>01098557018</t>
+          <t>01086241606</t>
         </is>
       </c>
       <c r="C1051" t="inlineStr">
         <is>
-          <t>223731</t>
+          <t>201165</t>
         </is>
       </c>
       <c r="D1051" t="inlineStr">
@@ -28808,17 +28808,17 @@
     <row r="1052">
       <c r="A1052" t="inlineStr">
         <is>
-          <t>kk_3638512879</t>
+          <t>kk_3373939453</t>
         </is>
       </c>
       <c r="B1052" t="inlineStr">
         <is>
-          <t>01053330589</t>
+          <t>01020110604</t>
         </is>
       </c>
       <c r="C1052" t="inlineStr">
         <is>
-          <t>248574</t>
+          <t>240269</t>
         </is>
       </c>
       <c r="D1052" t="inlineStr">
@@ -28828,34 +28828,34 @@
       </c>
       <c r="E1052" t="inlineStr">
         <is>
-          <t>KAKAO_CH_MESSAGE_0409_HIKE365SUMMER</t>
+          <t>KAKAO_CH_MESSAGE_0409_EXCLUSIVE</t>
         </is>
       </c>
     </row>
     <row r="1053">
       <c r="A1053" t="inlineStr">
         <is>
-          <t>kk_4726499171</t>
+          <t>boram1991</t>
         </is>
       </c>
       <c r="B1053" t="inlineStr">
         <is>
-          <t>01093851013</t>
+          <t>01023431078</t>
         </is>
       </c>
       <c r="C1053" t="inlineStr">
         <is>
-          <t>297987</t>
+          <t>119498</t>
         </is>
       </c>
       <c r="D1053" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E1053" t="inlineStr">
         <is>
-          <t>KAKAO_CH_MESSAGE_0409_HIKE365SUMMER</t>
+          <t>6968489536332</t>
         </is>
       </c>
     </row>
@@ -28889,71 +28889,71 @@
     <row r="1055">
       <c r="A1055" t="inlineStr">
         <is>
-          <t>boram1991</t>
+          <t>kk_4351086966</t>
         </is>
       </c>
       <c r="B1055" t="inlineStr">
         <is>
-          <t>01023431078</t>
+          <t>01042088262</t>
         </is>
       </c>
       <c r="C1055" t="inlineStr">
         <is>
-          <t>119498</t>
+          <t>279266</t>
         </is>
       </c>
       <c r="D1055" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="E1055" t="inlineStr">
         <is>
-          <t>6968489536332</t>
+          <t>Direct</t>
         </is>
       </c>
     </row>
     <row r="1056">
       <c r="A1056" t="inlineStr">
         <is>
-          <t>kk_3154612153</t>
+          <t>bbluesea</t>
         </is>
       </c>
       <c r="B1056" t="inlineStr">
         <is>
-          <t>01056681753</t>
+          <t>01076473601</t>
         </is>
       </c>
       <c r="C1056" t="inlineStr">
         <is>
-          <t>223664</t>
+          <t>152067</t>
         </is>
       </c>
       <c r="D1056" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E1056" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>KAKAO_CH_MENU_260406_LIGHTJACKET</t>
         </is>
       </c>
     </row>
     <row r="1057">
       <c r="A1057" t="inlineStr">
         <is>
-          <t>jhmin000</t>
+          <t>kk_4726499171</t>
         </is>
       </c>
       <c r="B1057" t="inlineStr">
         <is>
-          <t>01086241606</t>
+          <t>01093851013</t>
         </is>
       </c>
       <c r="C1057" t="inlineStr">
         <is>
-          <t>201165</t>
+          <t>297987</t>
         </is>
       </c>
       <c r="D1057" t="inlineStr">
@@ -28970,17 +28970,17 @@
     <row r="1058">
       <c r="A1058" t="inlineStr">
         <is>
-          <t>kk_3373939453</t>
+          <t>kk_3638512879</t>
         </is>
       </c>
       <c r="B1058" t="inlineStr">
         <is>
-          <t>01020110604</t>
+          <t>01053330589</t>
         </is>
       </c>
       <c r="C1058" t="inlineStr">
         <is>
-          <t>240269</t>
+          <t>248574</t>
         </is>
       </c>
       <c r="D1058" t="inlineStr">
@@ -28990,105 +28990,105 @@
       </c>
       <c r="E1058" t="inlineStr">
         <is>
-          <t>KAKAO_CH_MESSAGE_0409_EXCLUSIVE</t>
+          <t>KAKAO_CH_MESSAGE_0409_HIKE365SUMMER</t>
         </is>
       </c>
     </row>
     <row r="1059">
       <c r="A1059" t="inlineStr">
         <is>
-          <t>kk_3805755788</t>
+          <t>jeen1228</t>
         </is>
       </c>
       <c r="B1059" t="inlineStr">
         <is>
-          <t>01092305284</t>
+          <t>01033512662</t>
         </is>
       </c>
       <c r="C1059" t="inlineStr">
         <is>
-          <t>260128</t>
+          <t>223087</t>
         </is>
       </c>
       <c r="D1059" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Organic Traffic</t>
         </is>
       </c>
       <c r="E1059" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>(organic)</t>
         </is>
       </c>
     </row>
     <row r="1060">
       <c r="A1060" t="inlineStr">
         <is>
-          <t>kk_3180615052</t>
+          <t>kk_4835694986</t>
         </is>
       </c>
       <c r="B1060" t="inlineStr">
         <is>
-          <t>01077203676</t>
+          <t>01053746268</t>
         </is>
       </c>
       <c r="C1060" t="inlineStr">
         <is>
-          <t>226112</t>
+          <t>303879</t>
         </is>
       </c>
       <c r="D1060" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E1060" t="inlineStr">
         <is>
-          <t>Email_mkt</t>
+          <t>EFW</t>
         </is>
       </c>
     </row>
     <row r="1061">
       <c r="A1061" t="inlineStr">
         <is>
-          <t>kk_4835694986</t>
+          <t>wns1118</t>
         </is>
       </c>
       <c r="B1061" t="inlineStr">
         <is>
-          <t>01053746268</t>
+          <t>01090185590</t>
         </is>
       </c>
       <c r="C1061" t="inlineStr">
         <is>
-          <t>303879</t>
+          <t>303893</t>
         </is>
       </c>
       <c r="D1061" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Organic Traffic</t>
         </is>
       </c>
       <c r="E1061" t="inlineStr">
         <is>
-          <t>EFW</t>
+          <t>(organic)</t>
         </is>
       </c>
     </row>
     <row r="1062">
       <c r="A1062" t="inlineStr">
         <is>
-          <t>kk_3693586748</t>
+          <t>pearpear</t>
         </is>
       </c>
       <c r="B1062" t="inlineStr">
         <is>
-          <t>01063679756</t>
+          <t>01048098405</t>
         </is>
       </c>
       <c r="C1062" t="inlineStr">
         <is>
-          <t>251013</t>
+          <t>29743</t>
         </is>
       </c>
       <c r="D1062" t="inlineStr">
@@ -29098,24 +29098,24 @@
       </c>
       <c r="E1062" t="inlineStr">
         <is>
-          <t>KAKAO_alimtalk</t>
+          <t>Email_mkt</t>
         </is>
       </c>
     </row>
     <row r="1063">
       <c r="A1063" t="inlineStr">
         <is>
-          <t>pearpear</t>
+          <t>kk_3805755788</t>
         </is>
       </c>
       <c r="B1063" t="inlineStr">
         <is>
-          <t>01048098405</t>
+          <t>01092305284</t>
         </is>
       </c>
       <c r="C1063" t="inlineStr">
         <is>
-          <t>29743</t>
+          <t>260128</t>
         </is>
       </c>
       <c r="D1063" t="inlineStr">
@@ -29125,61 +29125,61 @@
       </c>
       <c r="E1063" t="inlineStr">
         <is>
-          <t>Email_mkt</t>
+          <t>Owned Channel</t>
         </is>
       </c>
     </row>
     <row r="1064">
       <c r="A1064" t="inlineStr">
         <is>
-          <t>wns1118</t>
+          <t>kk_3180615052</t>
         </is>
       </c>
       <c r="B1064" t="inlineStr">
         <is>
-          <t>01090185590</t>
+          <t>01077203676</t>
         </is>
       </c>
       <c r="C1064" t="inlineStr">
         <is>
-          <t>303893</t>
+          <t>226112</t>
         </is>
       </c>
       <c r="D1064" t="inlineStr">
         <is>
-          <t>Organic Traffic</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E1064" t="inlineStr">
         <is>
-          <t>(organic)</t>
+          <t>Email_mkt</t>
         </is>
       </c>
     </row>
     <row r="1065">
       <c r="A1065" t="inlineStr">
         <is>
-          <t>jeen1228</t>
+          <t>kk_3693586748</t>
         </is>
       </c>
       <c r="B1065" t="inlineStr">
         <is>
-          <t>01033512662</t>
+          <t>01063679756</t>
         </is>
       </c>
       <c r="C1065" t="inlineStr">
         <is>
-          <t>223087</t>
+          <t>251013</t>
         </is>
       </c>
       <c r="D1065" t="inlineStr">
         <is>
-          <t>Organic Traffic</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E1065" t="inlineStr">
         <is>
-          <t>(organic)</t>
+          <t>KAKAO_alimtalk</t>
         </is>
       </c>
     </row>
@@ -29348,54 +29348,54 @@
     <row r="1072">
       <c r="A1072" t="inlineStr">
         <is>
-          <t>hihijs34</t>
+          <t>wisbrain</t>
         </is>
       </c>
       <c r="B1072" t="inlineStr">
         <is>
-          <t>01093230529</t>
+          <t>01047220186</t>
         </is>
       </c>
       <c r="C1072" t="inlineStr">
         <is>
-          <t>128947</t>
+          <t>188067</t>
         </is>
       </c>
       <c r="D1072" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="E1072" t="inlineStr">
         <is>
-          <t>[PF]A+SC_상시(1865MF,구매+장바구니)</t>
+          <t>Direct</t>
         </is>
       </c>
     </row>
     <row r="1073">
       <c r="A1073" t="inlineStr">
         <is>
-          <t>wisbrain</t>
+          <t>kk_4427490834</t>
         </is>
       </c>
       <c r="B1073" t="inlineStr">
         <is>
-          <t>01047220186</t>
+          <t>01034704205</t>
         </is>
       </c>
       <c r="C1073" t="inlineStr">
         <is>
-          <t>188067</t>
+          <t>281590</t>
         </is>
       </c>
       <c r="D1073" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E1073" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>LMS_ECOM_0410exclusive2</t>
         </is>
       </c>
     </row>
@@ -29429,71 +29429,71 @@
     <row r="1075">
       <c r="A1075" t="inlineStr">
         <is>
-          <t>kk_4427490834</t>
+          <t>hihijs34</t>
         </is>
       </c>
       <c r="B1075" t="inlineStr">
         <is>
-          <t>01034704205</t>
+          <t>01093230529</t>
         </is>
       </c>
       <c r="C1075" t="inlineStr">
         <is>
-          <t>281590</t>
+          <t>128947</t>
         </is>
       </c>
       <c r="D1075" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E1075" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0410exclusive2</t>
+          <t>[PF]A+SC_상시(1865MF,구매+장바구니)</t>
         </is>
       </c>
     </row>
     <row r="1076">
       <c r="A1076" t="inlineStr">
         <is>
-          <t>kk_3973703558</t>
+          <t>yongshin</t>
         </is>
       </c>
       <c r="B1076" t="inlineStr">
         <is>
-          <t>01048590748</t>
+          <t>01053867821</t>
         </is>
       </c>
       <c r="C1076" t="inlineStr">
         <is>
-          <t>271020</t>
+          <t>277896</t>
         </is>
       </c>
       <c r="D1076" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="E1076" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0410exclusive2</t>
+          <t>Direct</t>
         </is>
       </c>
     </row>
     <row r="1077">
       <c r="A1077" t="inlineStr">
         <is>
-          <t>kk_4578503399</t>
+          <t>kk_4525043459</t>
         </is>
       </c>
       <c r="B1077" t="inlineStr">
         <is>
-          <t>01088660330</t>
+          <t>01088312135</t>
         </is>
       </c>
       <c r="C1077" t="inlineStr">
         <is>
-          <t>288374</t>
+          <t>286464</t>
         </is>
       </c>
       <c r="D1077" t="inlineStr">
@@ -29510,17 +29510,17 @@
     <row r="1078">
       <c r="A1078" t="inlineStr">
         <is>
-          <t>pls4u</t>
+          <t>sjm700</t>
         </is>
       </c>
       <c r="B1078" t="inlineStr">
         <is>
-          <t>01085985482</t>
+          <t>01077331591</t>
         </is>
       </c>
       <c r="C1078" t="inlineStr">
         <is>
-          <t>88257</t>
+          <t>118769</t>
         </is>
       </c>
       <c r="D1078" t="inlineStr">
@@ -29530,24 +29530,24 @@
       </c>
       <c r="E1078" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0401_trailrunning</t>
+          <t>LMS_ECOM_0410exclusive2</t>
         </is>
       </c>
     </row>
     <row r="1079">
       <c r="A1079" t="inlineStr">
         <is>
-          <t>kk_3754052831</t>
+          <t>kk_3180736217</t>
         </is>
       </c>
       <c r="B1079" t="inlineStr">
         <is>
-          <t>01092180804</t>
+          <t>01036000343</t>
         </is>
       </c>
       <c r="C1079" t="inlineStr">
         <is>
-          <t>254339</t>
+          <t>226314</t>
         </is>
       </c>
       <c r="D1079" t="inlineStr">
@@ -29564,44 +29564,44 @@
     <row r="1080">
       <c r="A1080" t="inlineStr">
         <is>
-          <t>yongshin</t>
+          <t>bobjazz</t>
         </is>
       </c>
       <c r="B1080" t="inlineStr">
         <is>
-          <t>01053867821</t>
+          <t>01084090677</t>
         </is>
       </c>
       <c r="C1080" t="inlineStr">
         <is>
-          <t>277896</t>
+          <t>186218</t>
         </is>
       </c>
       <c r="D1080" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E1080" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>LMS_ECOM_0410exclusive2</t>
         </is>
       </c>
     </row>
     <row r="1081">
       <c r="A1081" t="inlineStr">
         <is>
-          <t>kk_3024318364</t>
+          <t>dmsql785612</t>
         </is>
       </c>
       <c r="B1081" t="inlineStr">
         <is>
-          <t>01050308038</t>
+          <t>01051590364</t>
         </is>
       </c>
       <c r="C1081" t="inlineStr">
         <is>
-          <t>219525</t>
+          <t>137279</t>
         </is>
       </c>
       <c r="D1081" t="inlineStr">
@@ -29611,132 +29611,132 @@
       </c>
       <c r="E1081" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0410exclusive2</t>
+          <t>Email_mkt</t>
         </is>
       </c>
     </row>
     <row r="1082">
       <c r="A1082" t="inlineStr">
         <is>
-          <t>kk_3349199057</t>
+          <t>camiblanco</t>
         </is>
       </c>
       <c r="B1082" t="inlineStr">
         <is>
-          <t>01071630312</t>
+          <t>01072190103</t>
         </is>
       </c>
       <c r="C1082" t="inlineStr">
         <is>
-          <t>239388</t>
+          <t>232545</t>
         </is>
       </c>
       <c r="D1082" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="E1082" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0410exclusive2</t>
+          <t>Direct</t>
         </is>
       </c>
     </row>
     <row r="1083">
       <c r="A1083" t="inlineStr">
         <is>
-          <t>bobjazz</t>
+          <t>kk_3721447783</t>
         </is>
       </c>
       <c r="B1083" t="inlineStr">
         <is>
-          <t>01084090677</t>
+          <t>01051311087</t>
         </is>
       </c>
       <c r="C1083" t="inlineStr">
         <is>
-          <t>186218</t>
+          <t>252252</t>
         </is>
       </c>
       <c r="D1083" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="E1083" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0410exclusive2</t>
+          <t>Direct</t>
         </is>
       </c>
     </row>
     <row r="1084">
       <c r="A1084" t="inlineStr">
         <is>
-          <t>kk_3721447783</t>
+          <t>kk_3349199057</t>
         </is>
       </c>
       <c r="B1084" t="inlineStr">
         <is>
-          <t>01051311087</t>
+          <t>01071630312</t>
         </is>
       </c>
       <c r="C1084" t="inlineStr">
         <is>
-          <t>252252</t>
+          <t>239388</t>
         </is>
       </c>
       <c r="D1084" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E1084" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>LMS_ECOM_0410exclusive2</t>
         </is>
       </c>
     </row>
     <row r="1085">
       <c r="A1085" t="inlineStr">
         <is>
-          <t>inu21c</t>
+          <t>kk_4292190414</t>
         </is>
       </c>
       <c r="B1085" t="inlineStr">
         <is>
-          <t>01035128236</t>
+          <t>01095177478</t>
         </is>
       </c>
       <c r="C1085" t="inlineStr">
         <is>
-          <t>131940</t>
+          <t>275998</t>
         </is>
       </c>
       <c r="D1085" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="E1085" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0410exclusive2</t>
+          <t>Direct</t>
         </is>
       </c>
     </row>
     <row r="1086">
       <c r="A1086" t="inlineStr">
         <is>
-          <t>kk_4525043459</t>
+          <t>kk_4578503399</t>
         </is>
       </c>
       <c r="B1086" t="inlineStr">
         <is>
-          <t>01088312135</t>
+          <t>01088660330</t>
         </is>
       </c>
       <c r="C1086" t="inlineStr">
         <is>
-          <t>286464</t>
+          <t>288374</t>
         </is>
       </c>
       <c r="D1086" t="inlineStr">
@@ -29753,17 +29753,17 @@
     <row r="1087">
       <c r="A1087" t="inlineStr">
         <is>
-          <t>kk_2825715315</t>
+          <t>pls4u</t>
         </is>
       </c>
       <c r="B1087" t="inlineStr">
         <is>
-          <t>01077229654</t>
+          <t>01085985482</t>
         </is>
       </c>
       <c r="C1087" t="inlineStr">
         <is>
-          <t>212719</t>
+          <t>88257</t>
         </is>
       </c>
       <c r="D1087" t="inlineStr">
@@ -29773,24 +29773,24 @@
       </c>
       <c r="E1087" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0410exclusive2</t>
+          <t>LMS_ECOM_0401_trailrunning</t>
         </is>
       </c>
     </row>
     <row r="1088">
       <c r="A1088" t="inlineStr">
         <is>
-          <t>kk_4452401577</t>
+          <t>kk_2825715315</t>
         </is>
       </c>
       <c r="B1088" t="inlineStr">
         <is>
-          <t>01047428000</t>
+          <t>01077229654</t>
         </is>
       </c>
       <c r="C1088" t="inlineStr">
         <is>
-          <t>282525</t>
+          <t>212719</t>
         </is>
       </c>
       <c r="D1088" t="inlineStr">
@@ -29807,17 +29807,17 @@
     <row r="1089">
       <c r="A1089" t="inlineStr">
         <is>
-          <t>kk_3180736217</t>
+          <t>kk_3024318364</t>
         </is>
       </c>
       <c r="B1089" t="inlineStr">
         <is>
-          <t>01036000343</t>
+          <t>01050308038</t>
         </is>
       </c>
       <c r="C1089" t="inlineStr">
         <is>
-          <t>226314</t>
+          <t>219525</t>
         </is>
       </c>
       <c r="D1089" t="inlineStr">
@@ -29834,17 +29834,17 @@
     <row r="1090">
       <c r="A1090" t="inlineStr">
         <is>
-          <t>sjm700</t>
+          <t>inu21c</t>
         </is>
       </c>
       <c r="B1090" t="inlineStr">
         <is>
-          <t>01077331591</t>
+          <t>01035128236</t>
         </is>
       </c>
       <c r="C1090" t="inlineStr">
         <is>
-          <t>118769</t>
+          <t>131940</t>
         </is>
       </c>
       <c r="D1090" t="inlineStr">
@@ -29861,71 +29861,71 @@
     <row r="1091">
       <c r="A1091" t="inlineStr">
         <is>
-          <t>camiblanco</t>
+          <t>kk_3973703558</t>
         </is>
       </c>
       <c r="B1091" t="inlineStr">
         <is>
-          <t>01072190103</t>
+          <t>01048590748</t>
         </is>
       </c>
       <c r="C1091" t="inlineStr">
         <is>
-          <t>232545</t>
+          <t>271020</t>
         </is>
       </c>
       <c r="D1091" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E1091" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>LMS_ECOM_0410exclusive2</t>
         </is>
       </c>
     </row>
     <row r="1092">
       <c r="A1092" t="inlineStr">
         <is>
-          <t>kk_4292190414</t>
+          <t>columbia7</t>
         </is>
       </c>
       <c r="B1092" t="inlineStr">
         <is>
-          <t>01095177478</t>
+          <t>01050080025</t>
         </is>
       </c>
       <c r="C1092" t="inlineStr">
         <is>
-          <t>275998</t>
+          <t>109980</t>
         </is>
       </c>
       <c r="D1092" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E1092" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>LMS_ECOM_0410exclusive2</t>
         </is>
       </c>
     </row>
     <row r="1093">
       <c r="A1093" t="inlineStr">
         <is>
-          <t>dmsql785612</t>
+          <t>hyschant</t>
         </is>
       </c>
       <c r="B1093" t="inlineStr">
         <is>
-          <t>01051590364</t>
+          <t>01065306675</t>
         </is>
       </c>
       <c r="C1093" t="inlineStr">
         <is>
-          <t>137279</t>
+          <t>108579</t>
         </is>
       </c>
       <c r="D1093" t="inlineStr">
@@ -29935,24 +29935,24 @@
       </c>
       <c r="E1093" t="inlineStr">
         <is>
-          <t>Email_mkt</t>
+          <t>LMS_ECOM_0410exclusive2</t>
         </is>
       </c>
     </row>
     <row r="1094">
       <c r="A1094" t="inlineStr">
         <is>
-          <t>hyschant</t>
+          <t>kk_3754052831</t>
         </is>
       </c>
       <c r="B1094" t="inlineStr">
         <is>
-          <t>01065306675</t>
+          <t>01092180804</t>
         </is>
       </c>
       <c r="C1094" t="inlineStr">
         <is>
-          <t>108579</t>
+          <t>254339</t>
         </is>
       </c>
       <c r="D1094" t="inlineStr">
@@ -29969,17 +29969,17 @@
     <row r="1095">
       <c r="A1095" t="inlineStr">
         <is>
-          <t>columbia7</t>
+          <t>kk_4452401577</t>
         </is>
       </c>
       <c r="B1095" t="inlineStr">
         <is>
-          <t>01050080025</t>
+          <t>01047428000</t>
         </is>
       </c>
       <c r="C1095" t="inlineStr">
         <is>
-          <t>109980</t>
+          <t>282525</t>
         </is>
       </c>
       <c r="D1095" t="inlineStr">
@@ -29996,27 +29996,27 @@
     <row r="1096">
       <c r="A1096" t="inlineStr">
         <is>
-          <t>kk_4838419826</t>
+          <t>kk_3626939480</t>
         </is>
       </c>
       <c r="B1096" t="inlineStr">
         <is>
-          <t>01037240798</t>
+          <t>01030537990</t>
         </is>
       </c>
       <c r="C1096" t="inlineStr">
         <is>
-          <t>304050</t>
+          <t>247893</t>
         </is>
       </c>
       <c r="D1096" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E1096" t="inlineStr">
         <is>
-          <t>[PF]트래픽_유사+관심사</t>
+          <t>KAKAO_CH_MESSAGE_0409_EXCLUSIVE</t>
         </is>
       </c>
     </row>
@@ -30050,17 +30050,17 @@
     <row r="1098">
       <c r="A1098" t="inlineStr">
         <is>
-          <t>kk_3813115836</t>
+          <t>kk_4838419826</t>
         </is>
       </c>
       <c r="B1098" t="inlineStr">
         <is>
-          <t>01066721591</t>
+          <t>01037240798</t>
         </is>
       </c>
       <c r="C1098" t="inlineStr">
         <is>
-          <t>261736</t>
+          <t>304050</t>
         </is>
       </c>
       <c r="D1098" t="inlineStr">
@@ -30070,78 +30070,78 @@
       </c>
       <c r="E1098" t="inlineStr">
         <is>
-          <t>EFW</t>
+          <t>[PF]트래픽_유사+관심사</t>
         </is>
       </c>
     </row>
     <row r="1099">
       <c r="A1099" t="inlineStr">
         <is>
-          <t>kk_3626939480</t>
+          <t>kk_3813115836</t>
         </is>
       </c>
       <c r="B1099" t="inlineStr">
         <is>
-          <t>01030537990</t>
+          <t>01066721591</t>
         </is>
       </c>
       <c r="C1099" t="inlineStr">
         <is>
-          <t>247893</t>
+          <t>261736</t>
         </is>
       </c>
       <c r="D1099" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E1099" t="inlineStr">
         <is>
-          <t>KAKAO_CH_MESSAGE_0409_EXCLUSIVE</t>
+          <t>EFW</t>
         </is>
       </c>
     </row>
     <row r="1100">
       <c r="A1100" t="inlineStr">
         <is>
-          <t>cjcangel</t>
+          <t>kk_4717085515</t>
         </is>
       </c>
       <c r="B1100" t="inlineStr">
         <is>
-          <t>01089325858</t>
+          <t>01052078703</t>
         </is>
       </c>
       <c r="C1100" t="inlineStr">
         <is>
-          <t>292800</t>
+          <t>297221</t>
         </is>
       </c>
       <c r="D1100" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="E1100" t="inlineStr">
         <is>
-          <t>Email_mkt</t>
+          <t>Direct</t>
         </is>
       </c>
     </row>
     <row r="1101">
       <c r="A1101" t="inlineStr">
         <is>
-          <t>kk_4255987550</t>
+          <t>cjcangel</t>
         </is>
       </c>
       <c r="B1101" t="inlineStr">
         <is>
-          <t>01026453656</t>
+          <t>01089325858</t>
         </is>
       </c>
       <c r="C1101" t="inlineStr">
         <is>
-          <t>274389</t>
+          <t>292800</t>
         </is>
       </c>
       <c r="D1101" t="inlineStr">
@@ -30158,81 +30158,81 @@
     <row r="1102">
       <c r="A1102" t="inlineStr">
         <is>
-          <t>honga22</t>
+          <t>kk_3184270744</t>
         </is>
       </c>
       <c r="B1102" t="inlineStr">
         <is>
-          <t>01022690322</t>
+          <t>01077689325</t>
         </is>
       </c>
       <c r="C1102" t="inlineStr">
         <is>
-          <t>147568</t>
+          <t>228883</t>
         </is>
       </c>
       <c r="D1102" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="E1102" t="inlineStr">
         <is>
-          <t>KAKAO_alimtalk</t>
+          <t>Direct</t>
         </is>
       </c>
     </row>
     <row r="1103">
       <c r="A1103" t="inlineStr">
         <is>
-          <t>kk_4717085515</t>
+          <t>honga22</t>
         </is>
       </c>
       <c r="B1103" t="inlineStr">
         <is>
-          <t>01052078703</t>
+          <t>01022690322</t>
         </is>
       </c>
       <c r="C1103" t="inlineStr">
         <is>
-          <t>297221</t>
+          <t>147568</t>
         </is>
       </c>
       <c r="D1103" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E1103" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>KAKAO_alimtalk</t>
         </is>
       </c>
     </row>
     <row r="1104">
       <c r="A1104" t="inlineStr">
         <is>
-          <t>kk_3184270744</t>
+          <t>kk_4255987550</t>
         </is>
       </c>
       <c r="B1104" t="inlineStr">
         <is>
-          <t>01077689325</t>
+          <t>01026453656</t>
         </is>
       </c>
       <c r="C1104" t="inlineStr">
         <is>
-          <t>228883</t>
+          <t>274389</t>
         </is>
       </c>
       <c r="D1104" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E1104" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>Email_mkt</t>
         </is>
       </c>
     </row>
@@ -30266,17 +30266,17 @@
     <row r="1106">
       <c r="A1106" t="inlineStr">
         <is>
-          <t>alcoholpower</t>
+          <t>kimms66</t>
         </is>
       </c>
       <c r="B1106" t="inlineStr">
         <is>
-          <t>01027629868</t>
+          <t>01057634626</t>
         </is>
       </c>
       <c r="C1106" t="inlineStr">
         <is>
-          <t>252954</t>
+          <t>180321</t>
         </is>
       </c>
       <c r="D1106" t="inlineStr">
@@ -30320,17 +30320,17 @@
     <row r="1108">
       <c r="A1108" t="inlineStr">
         <is>
-          <t>kimms66</t>
+          <t>alcoholpower</t>
         </is>
       </c>
       <c r="B1108" t="inlineStr">
         <is>
-          <t>01057634626</t>
+          <t>01027629868</t>
         </is>
       </c>
       <c r="C1108" t="inlineStr">
         <is>
-          <t>180321</t>
+          <t>252954</t>
         </is>
       </c>
       <c r="D1108" t="inlineStr">

--- a/reports/member_funnel/downloads/member_funnel_7d_non_buyer.xlsx
+++ b/reports/member_funnel/downloads/member_funnel_7d_non_buyer.xlsx
@@ -11771,54 +11771,54 @@
     <row r="421">
       <c r="A421" t="inlineStr">
         <is>
-          <t>kk_4839170665</t>
+          <t>kwon9493</t>
         </is>
       </c>
       <c r="B421" t="inlineStr">
         <is>
-          <t>01050116666</t>
+          <t>01035589493</t>
         </is>
       </c>
       <c r="C421" t="inlineStr">
         <is>
-          <t>304086</t>
+          <t>107077</t>
         </is>
       </c>
       <c r="D421" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="E421" t="inlineStr">
         <is>
-          <t>EFW</t>
+          <t>Direct</t>
         </is>
       </c>
     </row>
     <row r="422">
       <c r="A422" t="inlineStr">
         <is>
-          <t>kwon9493</t>
+          <t>kk_4839170665</t>
         </is>
       </c>
       <c r="B422" t="inlineStr">
         <is>
-          <t>01035589493</t>
+          <t>01050116666</t>
         </is>
       </c>
       <c r="C422" t="inlineStr">
         <is>
-          <t>107077</t>
+          <t>304086</t>
         </is>
       </c>
       <c r="D422" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E422" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>EFW</t>
         </is>
       </c>
     </row>
@@ -15686,54 +15686,54 @@
     <row r="566">
       <c r="A566" t="inlineStr">
         <is>
-          <t>kk_4789688431</t>
+          <t>kk_4837763007</t>
         </is>
       </c>
       <c r="B566" t="inlineStr">
         <is>
-          <t>01099981265</t>
+          <t>01088993992</t>
         </is>
       </c>
       <c r="C566" t="inlineStr">
         <is>
-          <t>302023</t>
+          <t>304013</t>
         </is>
       </c>
       <c r="D566" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E566" t="inlineStr">
         <is>
-          <t>sa</t>
+          <t>(referral)</t>
         </is>
       </c>
     </row>
     <row r="567">
       <c r="A567" t="inlineStr">
         <is>
-          <t>kk_4837763007</t>
+          <t>kk_4789688431</t>
         </is>
       </c>
       <c r="B567" t="inlineStr">
         <is>
-          <t>01088993992</t>
+          <t>01099981265</t>
         </is>
       </c>
       <c r="C567" t="inlineStr">
         <is>
-          <t>304013</t>
+          <t>302023</t>
         </is>
       </c>
       <c r="D567" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E567" t="inlineStr">
         <is>
-          <t>(referral)</t>
+          <t>sa</t>
         </is>
       </c>
     </row>
@@ -17603,54 +17603,54 @@
     <row r="637">
       <c r="A637" t="inlineStr">
         <is>
-          <t>kk_4841965432</t>
+          <t>khkim6620</t>
         </is>
       </c>
       <c r="B637" t="inlineStr">
         <is>
-          <t>01032510712</t>
+          <t>01076876567</t>
         </is>
       </c>
       <c r="C637" t="inlineStr">
         <is>
-          <t>304213</t>
+          <t>105445</t>
         </is>
       </c>
       <c r="D637" t="inlineStr">
         <is>
-          <t>Organic Traffic</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E637" t="inlineStr">
         <is>
-          <t>(referral)</t>
+          <t>컬럼비아_DPA_240530</t>
         </is>
       </c>
     </row>
     <row r="638">
       <c r="A638" t="inlineStr">
         <is>
-          <t>khkim6620</t>
+          <t>kk_4841965432</t>
         </is>
       </c>
       <c r="B638" t="inlineStr">
         <is>
-          <t>01076876567</t>
+          <t>01032510712</t>
         </is>
       </c>
       <c r="C638" t="inlineStr">
         <is>
-          <t>105445</t>
+          <t>304213</t>
         </is>
       </c>
       <c r="D638" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Organic Traffic</t>
         </is>
       </c>
       <c r="E638" t="inlineStr">
         <is>
-          <t>컬럼비아_DPA_240530</t>
+          <t>(referral)</t>
         </is>
       </c>
     </row>
@@ -18629,54 +18629,54 @@
     <row r="675">
       <c r="A675" t="inlineStr">
         <is>
-          <t>kk_3913679442</t>
+          <t>kk_3633964155</t>
         </is>
       </c>
       <c r="B675" t="inlineStr">
         <is>
-          <t>01085569215</t>
+          <t>01097743709</t>
         </is>
       </c>
       <c r="C675" t="inlineStr">
         <is>
-          <t>268330</t>
+          <t>248300</t>
         </is>
       </c>
       <c r="D675" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E675" t="inlineStr">
         <is>
-          <t>미분류</t>
+          <t>KAKAO_CH_MENU_0226_EFW</t>
         </is>
       </c>
     </row>
     <row r="676">
       <c r="A676" t="inlineStr">
         <is>
-          <t>kk_3633964155</t>
+          <t>kk_3913679442</t>
         </is>
       </c>
       <c r="B676" t="inlineStr">
         <is>
-          <t>01097743709</t>
+          <t>01085569215</t>
         </is>
       </c>
       <c r="C676" t="inlineStr">
         <is>
-          <t>248300</t>
+          <t>268330</t>
         </is>
       </c>
       <c r="D676" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="E676" t="inlineStr">
         <is>
-          <t>KAKAO_CH_MENU_0226_EFW</t>
+          <t>미분류</t>
         </is>
       </c>
     </row>
@@ -19709,17 +19709,17 @@
     <row r="715">
       <c r="A715" t="inlineStr">
         <is>
-          <t>kk_3101119679</t>
+          <t>hun7662</t>
         </is>
       </c>
       <c r="B715" t="inlineStr">
         <is>
-          <t>01093993852</t>
+          <t>01042311474</t>
         </is>
       </c>
       <c r="C715" t="inlineStr">
         <is>
-          <t>221630</t>
+          <t>172790</t>
         </is>
       </c>
       <c r="D715" t="inlineStr">
@@ -19736,17 +19736,17 @@
     <row r="716">
       <c r="A716" t="inlineStr">
         <is>
-          <t>hun7662</t>
+          <t>kk_3101119679</t>
         </is>
       </c>
       <c r="B716" t="inlineStr">
         <is>
-          <t>01042311474</t>
+          <t>01093993852</t>
         </is>
       </c>
       <c r="C716" t="inlineStr">
         <is>
-          <t>172790</t>
+          <t>221630</t>
         </is>
       </c>
       <c r="D716" t="inlineStr">
@@ -20141,98 +20141,98 @@
     <row r="731">
       <c r="A731" t="inlineStr">
         <is>
-          <t>kk_4839145768</t>
+          <t>kk_4839765445</t>
         </is>
       </c>
       <c r="B731" t="inlineStr">
         <is>
-          <t>01097367898</t>
+          <t>01076118972</t>
         </is>
       </c>
       <c r="C731" t="inlineStr">
         <is>
-          <t>304085</t>
+          <t>304111</t>
         </is>
       </c>
       <c r="D731" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Organic Traffic</t>
         </is>
       </c>
       <c r="E731" t="inlineStr">
         <is>
-          <t>naver_brandsearch_pc</t>
+          <t>(referral)</t>
         </is>
       </c>
     </row>
     <row r="732">
       <c r="A732" t="inlineStr">
         <is>
-          <t>sun1381</t>
+          <t>kk_4839145768</t>
         </is>
       </c>
       <c r="B732" t="inlineStr">
         <is>
-          <t>01037709416</t>
+          <t>01097367898</t>
         </is>
       </c>
       <c r="C732" t="inlineStr">
         <is>
-          <t>278160</t>
+          <t>304085</t>
         </is>
       </c>
       <c r="D732" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E732" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0410exclusive2</t>
+          <t>naver_brandsearch_pc</t>
         </is>
       </c>
     </row>
     <row r="733">
       <c r="A733" t="inlineStr">
         <is>
-          <t>kk_4839765445</t>
+          <t>sun1381</t>
         </is>
       </c>
       <c r="B733" t="inlineStr">
         <is>
-          <t>01076118972</t>
+          <t>01037709416</t>
         </is>
       </c>
       <c r="C733" t="inlineStr">
         <is>
-          <t>304111</t>
+          <t>278160</t>
         </is>
       </c>
       <c r="D733" t="inlineStr">
         <is>
-          <t>Organic Traffic</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E733" t="inlineStr">
         <is>
-          <t>(referral)</t>
+          <t>LMS_ECOM_0410exclusive2</t>
         </is>
       </c>
     </row>
     <row r="734">
       <c r="A734" t="inlineStr">
         <is>
-          <t>kk_4324736295</t>
+          <t>kwon1207</t>
         </is>
       </c>
       <c r="B734" t="inlineStr">
         <is>
-          <t>01077616385</t>
+          <t>01055647413</t>
         </is>
       </c>
       <c r="C734" t="inlineStr">
         <is>
-          <t>278190</t>
+          <t>129663</t>
         </is>
       </c>
       <c r="D734" t="inlineStr">
@@ -20242,24 +20242,24 @@
       </c>
       <c r="E734" t="inlineStr">
         <is>
-          <t>KAKAO_CH_MESSAGE_0409_EXCLUSIVE</t>
+          <t>KAKAO_CH_MESSAGE_0409_TRAIL</t>
         </is>
       </c>
     </row>
     <row r="735">
       <c r="A735" t="inlineStr">
         <is>
-          <t>kwon1207</t>
+          <t>kk_4324736295</t>
         </is>
       </c>
       <c r="B735" t="inlineStr">
         <is>
-          <t>01055647413</t>
+          <t>01077616385</t>
         </is>
       </c>
       <c r="C735" t="inlineStr">
         <is>
-          <t>129663</t>
+          <t>278190</t>
         </is>
       </c>
       <c r="D735" t="inlineStr">
@@ -20269,7 +20269,7 @@
       </c>
       <c r="E735" t="inlineStr">
         <is>
-          <t>KAKAO_CH_MESSAGE_0409_TRAIL</t>
+          <t>KAKAO_CH_MESSAGE_0409_EXCLUSIVE</t>
         </is>
       </c>
     </row>
@@ -20303,17 +20303,17 @@
     <row r="737">
       <c r="A737" t="inlineStr">
         <is>
-          <t>kk_4641269666</t>
+          <t>kk_4617674866</t>
         </is>
       </c>
       <c r="B737" t="inlineStr">
         <is>
-          <t>01041565334</t>
+          <t>01062147077</t>
         </is>
       </c>
       <c r="C737" t="inlineStr">
         <is>
-          <t>292505</t>
+          <t>290764</t>
         </is>
       </c>
       <c r="D737" t="inlineStr">
@@ -20323,24 +20323,24 @@
       </c>
       <c r="E737" t="inlineStr">
         <is>
-          <t>KAKAO_CH_MESSAGE_0409_HIKE365SUMMER</t>
+          <t>KAKAO_CH_MESSAGE_0409_TRAIL</t>
         </is>
       </c>
     </row>
     <row r="738">
       <c r="A738" t="inlineStr">
         <is>
-          <t>kk_4617674866</t>
+          <t>kk_4641269666</t>
         </is>
       </c>
       <c r="B738" t="inlineStr">
         <is>
-          <t>01062147077</t>
+          <t>01041565334</t>
         </is>
       </c>
       <c r="C738" t="inlineStr">
         <is>
-          <t>290764</t>
+          <t>292505</t>
         </is>
       </c>
       <c r="D738" t="inlineStr">
@@ -20350,7 +20350,7 @@
       </c>
       <c r="E738" t="inlineStr">
         <is>
-          <t>KAKAO_CH_MESSAGE_0409_TRAIL</t>
+          <t>KAKAO_CH_MESSAGE_0409_HIKE365SUMMER</t>
         </is>
       </c>
     </row>
@@ -21167,17 +21167,17 @@
     <row r="769">
       <c r="A769" t="inlineStr">
         <is>
-          <t>athend</t>
+          <t>kk_3392066640</t>
         </is>
       </c>
       <c r="B769" t="inlineStr">
         <is>
-          <t>01041786462</t>
+          <t>01065021283</t>
         </is>
       </c>
       <c r="C769" t="inlineStr">
         <is>
-          <t>285491</t>
+          <t>240983</t>
         </is>
       </c>
       <c r="D769" t="inlineStr">
@@ -21187,78 +21187,78 @@
       </c>
       <c r="E769" t="inlineStr">
         <is>
-          <t>KAKAO_alimtalk</t>
+          <t>LMS_ECOM_0410exclusive2</t>
         </is>
       </c>
     </row>
     <row r="770">
       <c r="A770" t="inlineStr">
         <is>
-          <t>kk_3392066640</t>
+          <t>kk_4639169718</t>
         </is>
       </c>
       <c r="B770" t="inlineStr">
         <is>
-          <t>01065021283</t>
+          <t>01041380770</t>
         </is>
       </c>
       <c r="C770" t="inlineStr">
         <is>
-          <t>240983</t>
+          <t>292319</t>
         </is>
       </c>
       <c r="D770" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E770" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0410exclusive2</t>
+          <t>naver_brandsearch_mobile</t>
         </is>
       </c>
     </row>
     <row r="771">
       <c r="A771" t="inlineStr">
         <is>
-          <t>kk_4839680663</t>
+          <t>athend</t>
         </is>
       </c>
       <c r="B771" t="inlineStr">
         <is>
-          <t>01046429530</t>
+          <t>01041786462</t>
         </is>
       </c>
       <c r="C771" t="inlineStr">
         <is>
-          <t>304109</t>
+          <t>285491</t>
         </is>
       </c>
       <c r="D771" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E771" t="inlineStr">
         <is>
-          <t>6968489536332</t>
+          <t>KAKAO_alimtalk</t>
         </is>
       </c>
     </row>
     <row r="772">
       <c r="A772" t="inlineStr">
         <is>
-          <t>kk_4639169718</t>
+          <t>kk_4839680663</t>
         </is>
       </c>
       <c r="B772" t="inlineStr">
         <is>
-          <t>01041380770</t>
+          <t>01046429530</t>
         </is>
       </c>
       <c r="C772" t="inlineStr">
         <is>
-          <t>292319</t>
+          <t>304109</t>
         </is>
       </c>
       <c r="D772" t="inlineStr">
@@ -21268,7 +21268,7 @@
       </c>
       <c r="E772" t="inlineStr">
         <is>
-          <t>naver_brandsearch_mobile</t>
+          <t>6968489536332</t>
         </is>
       </c>
     </row>
@@ -21437,71 +21437,71 @@
     <row r="779">
       <c r="A779" t="inlineStr">
         <is>
-          <t>isaackwak</t>
+          <t>kk_4839433808</t>
         </is>
       </c>
       <c r="B779" t="inlineStr">
         <is>
-          <t>01090599860</t>
+          <t>01025333388</t>
         </is>
       </c>
       <c r="C779" t="inlineStr">
         <is>
-          <t>275913</t>
+          <t>304100</t>
         </is>
       </c>
       <c r="D779" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E779" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>naver_brandsearch_mobile</t>
         </is>
       </c>
     </row>
     <row r="780">
       <c r="A780" t="inlineStr">
         <is>
-          <t>ganjing78</t>
+          <t>isaackwak</t>
         </is>
       </c>
       <c r="B780" t="inlineStr">
         <is>
-          <t>01065121424</t>
+          <t>01090599860</t>
         </is>
       </c>
       <c r="C780" t="inlineStr">
         <is>
-          <t>78590</t>
+          <t>275913</t>
         </is>
       </c>
       <c r="D780" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="E780" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0410exclusive2</t>
+          <t>Direct</t>
         </is>
       </c>
     </row>
     <row r="781">
       <c r="A781" t="inlineStr">
         <is>
-          <t>kk_3678962368</t>
+          <t>ganjing78</t>
         </is>
       </c>
       <c r="B781" t="inlineStr">
         <is>
-          <t>01041028567</t>
+          <t>01065121424</t>
         </is>
       </c>
       <c r="C781" t="inlineStr">
         <is>
-          <t>250374</t>
+          <t>78590</t>
         </is>
       </c>
       <c r="D781" t="inlineStr">
@@ -21518,44 +21518,44 @@
     <row r="782">
       <c r="A782" t="inlineStr">
         <is>
-          <t>kk_4839433808</t>
+          <t>mtbok</t>
         </is>
       </c>
       <c r="B782" t="inlineStr">
         <is>
-          <t>01025333388</t>
+          <t>01051284339</t>
         </is>
       </c>
       <c r="C782" t="inlineStr">
         <is>
-          <t>304100</t>
+          <t>26917</t>
         </is>
       </c>
       <c r="D782" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E782" t="inlineStr">
         <is>
-          <t>naver_brandsearch_mobile</t>
+          <t>LMS_ECOM_0410exclusive2</t>
         </is>
       </c>
     </row>
     <row r="783">
       <c r="A783" t="inlineStr">
         <is>
-          <t>mtbok</t>
+          <t>kk_3678962368</t>
         </is>
       </c>
       <c r="B783" t="inlineStr">
         <is>
-          <t>01051284339</t>
+          <t>01041028567</t>
         </is>
       </c>
       <c r="C783" t="inlineStr">
         <is>
-          <t>26917</t>
+          <t>250374</t>
         </is>
       </c>
       <c r="D783" t="inlineStr">
@@ -21680,179 +21680,179 @@
     <row r="788">
       <c r="A788" t="inlineStr">
         <is>
-          <t>kk_4727921763</t>
+          <t>kk_3181873063</t>
         </is>
       </c>
       <c r="B788" t="inlineStr">
         <is>
-          <t>01045673975</t>
+          <t>01026527131</t>
         </is>
       </c>
       <c r="C788" t="inlineStr">
         <is>
-          <t>298138</t>
+          <t>227343</t>
         </is>
       </c>
       <c r="D788" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E788" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>LMS_ECOM_0410exclusive2</t>
         </is>
       </c>
     </row>
     <row r="789">
       <c r="A789" t="inlineStr">
         <is>
-          <t>kk_4839026541</t>
+          <t>kk_2757380967</t>
         </is>
       </c>
       <c r="B789" t="inlineStr">
         <is>
-          <t>01089431507</t>
+          <t>01034635649</t>
         </is>
       </c>
       <c r="C789" t="inlineStr">
         <is>
-          <t>304082</t>
+          <t>208245</t>
         </is>
       </c>
       <c r="D789" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E789" t="inlineStr">
         <is>
-          <t>[PF]전환_상시(2565MF,비구매자)</t>
+          <t>LMS_ECOM_0410exclusive2</t>
         </is>
       </c>
     </row>
     <row r="790">
       <c r="A790" t="inlineStr">
         <is>
-          <t>kk_3181873063</t>
+          <t>kk_4727921763</t>
         </is>
       </c>
       <c r="B790" t="inlineStr">
         <is>
-          <t>01026527131</t>
+          <t>01045673975</t>
         </is>
       </c>
       <c r="C790" t="inlineStr">
         <is>
-          <t>227343</t>
+          <t>298138</t>
         </is>
       </c>
       <c r="D790" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="E790" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0410exclusive2</t>
+          <t>Direct</t>
         </is>
       </c>
     </row>
     <row r="791">
       <c r="A791" t="inlineStr">
         <is>
-          <t>kk_2757380967</t>
+          <t>kk_4839026541</t>
         </is>
       </c>
       <c r="B791" t="inlineStr">
         <is>
-          <t>01034635649</t>
+          <t>01089431507</t>
         </is>
       </c>
       <c r="C791" t="inlineStr">
         <is>
-          <t>208245</t>
+          <t>304082</t>
         </is>
       </c>
       <c r="D791" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E791" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0410exclusive2</t>
+          <t>[PF]전환_상시(2565MF,비구매자)</t>
         </is>
       </c>
     </row>
     <row r="792">
       <c r="A792" t="inlineStr">
         <is>
-          <t>kk_4519505330</t>
+          <t>kk_3156128258</t>
         </is>
       </c>
       <c r="B792" t="inlineStr">
         <is>
-          <t>01024320028</t>
+          <t>01093995884</t>
         </is>
       </c>
       <c r="C792" t="inlineStr">
         <is>
-          <t>286150</t>
+          <t>223742</t>
         </is>
       </c>
       <c r="D792" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="E792" t="inlineStr">
         <is>
-          <t>KAKAO_CH_MESSAGE_0409_HIKE365SUMMER</t>
+          <t>Direct</t>
         </is>
       </c>
     </row>
     <row r="793">
       <c r="A793" t="inlineStr">
         <is>
-          <t>kk_3156128258</t>
+          <t>kk_4532357752</t>
         </is>
       </c>
       <c r="B793" t="inlineStr">
         <is>
-          <t>01093995884</t>
+          <t>01023210419</t>
         </is>
       </c>
       <c r="C793" t="inlineStr">
         <is>
-          <t>223742</t>
+          <t>286900</t>
         </is>
       </c>
       <c r="D793" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E793" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>KAKAO_CH_MESSAGE_0409_EXCLUSIVE</t>
         </is>
       </c>
     </row>
     <row r="794">
       <c r="A794" t="inlineStr">
         <is>
-          <t>kk_4532357752</t>
+          <t>kk_4519505330</t>
         </is>
       </c>
       <c r="B794" t="inlineStr">
         <is>
-          <t>01023210419</t>
+          <t>01024320028</t>
         </is>
       </c>
       <c r="C794" t="inlineStr">
         <is>
-          <t>286900</t>
+          <t>286150</t>
         </is>
       </c>
       <c r="D794" t="inlineStr">
@@ -21862,7 +21862,7 @@
       </c>
       <c r="E794" t="inlineStr">
         <is>
-          <t>KAKAO_CH_MESSAGE_0409_EXCLUSIVE</t>
+          <t>KAKAO_CH_MESSAGE_0409_HIKE365SUMMER</t>
         </is>
       </c>
     </row>
@@ -22004,17 +22004,17 @@
     <row r="800">
       <c r="A800" t="inlineStr">
         <is>
-          <t>kk_3967419156</t>
+          <t>kk_4600405600</t>
         </is>
       </c>
       <c r="B800" t="inlineStr">
         <is>
-          <t>01030207947</t>
+          <t>01053449477</t>
         </is>
       </c>
       <c r="C800" t="inlineStr">
         <is>
-          <t>270708</t>
+          <t>289364</t>
         </is>
       </c>
       <c r="D800" t="inlineStr">
@@ -22031,17 +22031,17 @@
     <row r="801">
       <c r="A801" t="inlineStr">
         <is>
-          <t>kk_4600405600</t>
+          <t>kk_3967419156</t>
         </is>
       </c>
       <c r="B801" t="inlineStr">
         <is>
-          <t>01053449477</t>
+          <t>01030207947</t>
         </is>
       </c>
       <c r="C801" t="inlineStr">
         <is>
-          <t>289364</t>
+          <t>270708</t>
         </is>
       </c>
       <c r="D801" t="inlineStr">
@@ -22274,17 +22274,17 @@
     <row r="810">
       <c r="A810" t="inlineStr">
         <is>
-          <t>noma6420</t>
+          <t>mplkh</t>
         </is>
       </c>
       <c r="B810" t="inlineStr">
         <is>
-          <t>01071574279</t>
+          <t>01085245802</t>
         </is>
       </c>
       <c r="C810" t="inlineStr">
         <is>
-          <t>304023</t>
+          <t>160698</t>
         </is>
       </c>
       <c r="D810" t="inlineStr">
@@ -22294,24 +22294,24 @@
       </c>
       <c r="E810" t="inlineStr">
         <is>
-          <t>[PF]A SC_상시(1865MF,구매 장바구니)</t>
+          <t>sa</t>
         </is>
       </c>
     </row>
     <row r="811">
       <c r="A811" t="inlineStr">
         <is>
-          <t>pieerot1</t>
+          <t>noma6420</t>
         </is>
       </c>
       <c r="B811" t="inlineStr">
         <is>
-          <t>01054503186</t>
+          <t>01071574279</t>
         </is>
       </c>
       <c r="C811" t="inlineStr">
         <is>
-          <t>29988</t>
+          <t>304023</t>
         </is>
       </c>
       <c r="D811" t="inlineStr">
@@ -22321,24 +22321,24 @@
       </c>
       <c r="E811" t="inlineStr">
         <is>
-          <t>naver_brandsearch_mobile</t>
+          <t>[PF]A SC_상시(1865MF,구매 장바구니)</t>
         </is>
       </c>
     </row>
     <row r="812">
       <c r="A812" t="inlineStr">
         <is>
-          <t>mplkh</t>
+          <t>pieerot1</t>
         </is>
       </c>
       <c r="B812" t="inlineStr">
         <is>
-          <t>01085245802</t>
+          <t>01054503186</t>
         </is>
       </c>
       <c r="C812" t="inlineStr">
         <is>
-          <t>160698</t>
+          <t>29988</t>
         </is>
       </c>
       <c r="D812" t="inlineStr">
@@ -22348,7 +22348,7 @@
       </c>
       <c r="E812" t="inlineStr">
         <is>
-          <t>sa</t>
+          <t>naver_brandsearch_mobile</t>
         </is>
       </c>
     </row>
@@ -23327,54 +23327,54 @@
     <row r="849">
       <c r="A849" t="inlineStr">
         <is>
-          <t>kk_4835738911</t>
+          <t>kk_4839354093</t>
         </is>
       </c>
       <c r="B849" t="inlineStr">
         <is>
-          <t>01034422073</t>
+          <t>01052243562</t>
         </is>
       </c>
       <c r="C849" t="inlineStr">
         <is>
-          <t>303885</t>
+          <t>304098</t>
         </is>
       </c>
       <c r="D849" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Organic Traffic</t>
         </is>
       </c>
       <c r="E849" t="inlineStr">
         <is>
-          <t>6968489536332</t>
+          <t>(organic)</t>
         </is>
       </c>
     </row>
     <row r="850">
       <c r="A850" t="inlineStr">
         <is>
-          <t>kk_4839354093</t>
+          <t>kk_4835738911</t>
         </is>
       </c>
       <c r="B850" t="inlineStr">
         <is>
-          <t>01052243562</t>
+          <t>01034422073</t>
         </is>
       </c>
       <c r="C850" t="inlineStr">
         <is>
-          <t>304098</t>
+          <t>303885</t>
         </is>
       </c>
       <c r="D850" t="inlineStr">
         <is>
-          <t>Organic Traffic</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E850" t="inlineStr">
         <is>
-          <t>(organic)</t>
+          <t>6968489536332</t>
         </is>
       </c>
     </row>
@@ -23840,17 +23840,17 @@
     <row r="868">
       <c r="A868" t="inlineStr">
         <is>
-          <t>kk_2773979393</t>
+          <t>kk_4837339232</t>
         </is>
       </c>
       <c r="B868" t="inlineStr">
         <is>
-          <t>01026079844</t>
+          <t>01057714655</t>
         </is>
       </c>
       <c r="C868" t="inlineStr">
         <is>
-          <t>209309</t>
+          <t>303975</t>
         </is>
       </c>
       <c r="D868" t="inlineStr">
@@ -23860,24 +23860,24 @@
       </c>
       <c r="E868" t="inlineStr">
         <is>
-          <t>6968489536332</t>
+          <t>naver_brandsearch_mobile</t>
         </is>
       </c>
     </row>
     <row r="869">
       <c r="A869" t="inlineStr">
         <is>
-          <t>kk_4837339232</t>
+          <t>kk_2773979393</t>
         </is>
       </c>
       <c r="B869" t="inlineStr">
         <is>
-          <t>01057714655</t>
+          <t>01026079844</t>
         </is>
       </c>
       <c r="C869" t="inlineStr">
         <is>
-          <t>303975</t>
+          <t>209309</t>
         </is>
       </c>
       <c r="D869" t="inlineStr">
@@ -23887,7 +23887,7 @@
       </c>
       <c r="E869" t="inlineStr">
         <is>
-          <t>naver_brandsearch_mobile</t>
+          <t>6968489536332</t>
         </is>
       </c>
     </row>
@@ -23948,17 +23948,17 @@
     <row r="872">
       <c r="A872" t="inlineStr">
         <is>
-          <t>chi1641</t>
+          <t>iceman</t>
         </is>
       </c>
       <c r="B872" t="inlineStr">
         <is>
-          <t>01082781641</t>
+          <t>01025317943</t>
         </is>
       </c>
       <c r="C872" t="inlineStr">
         <is>
-          <t>206726</t>
+          <t>92416</t>
         </is>
       </c>
       <c r="D872" t="inlineStr">
@@ -23968,24 +23968,24 @@
       </c>
       <c r="E872" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>LMS_ECOM_0214_newyear</t>
         </is>
       </c>
     </row>
     <row r="873">
       <c r="A873" t="inlineStr">
         <is>
-          <t>iceman</t>
+          <t>chi1641</t>
         </is>
       </c>
       <c r="B873" t="inlineStr">
         <is>
-          <t>01025317943</t>
+          <t>01082781641</t>
         </is>
       </c>
       <c r="C873" t="inlineStr">
         <is>
-          <t>92416</t>
+          <t>206726</t>
         </is>
       </c>
       <c r="D873" t="inlineStr">
@@ -23995,7 +23995,7 @@
       </c>
       <c r="E873" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0214_newyear</t>
+          <t>Owned Channel</t>
         </is>
       </c>
     </row>
@@ -24056,54 +24056,54 @@
     <row r="876">
       <c r="A876" t="inlineStr">
         <is>
-          <t>kk_4840108009</t>
+          <t>xey5000</t>
         </is>
       </c>
       <c r="B876" t="inlineStr">
         <is>
-          <t>01053461423</t>
+          <t>01087768710</t>
         </is>
       </c>
       <c r="C876" t="inlineStr">
         <is>
-          <t>304129</t>
+          <t>143826</t>
         </is>
       </c>
       <c r="D876" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E876" t="inlineStr">
         <is>
-          <t>6968489536332</t>
+          <t>KAKAO_CH_MESSAGE_0409_PANTS</t>
         </is>
       </c>
     </row>
     <row r="877">
       <c r="A877" t="inlineStr">
         <is>
-          <t>xey5000</t>
+          <t>kk_4840108009</t>
         </is>
       </c>
       <c r="B877" t="inlineStr">
         <is>
-          <t>01087768710</t>
+          <t>01053461423</t>
         </is>
       </c>
       <c r="C877" t="inlineStr">
         <is>
-          <t>143826</t>
+          <t>304129</t>
         </is>
       </c>
       <c r="D877" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E877" t="inlineStr">
         <is>
-          <t>KAKAO_CH_MESSAGE_0409_PANTS</t>
+          <t>6968489536332</t>
         </is>
       </c>
     </row>
@@ -24272,17 +24272,17 @@
     <row r="884">
       <c r="A884" t="inlineStr">
         <is>
-          <t>kk_3595551743</t>
+          <t>holstein</t>
         </is>
       </c>
       <c r="B884" t="inlineStr">
         <is>
-          <t>01025839326</t>
+          <t>01050502500</t>
         </is>
       </c>
       <c r="C884" t="inlineStr">
         <is>
-          <t>246836</t>
+          <t>14062</t>
         </is>
       </c>
       <c r="D884" t="inlineStr">
@@ -24292,24 +24292,24 @@
       </c>
       <c r="E884" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0410exclusive2</t>
+          <t>EDM_TOP</t>
         </is>
       </c>
     </row>
     <row r="885">
       <c r="A885" t="inlineStr">
         <is>
-          <t>holstein</t>
+          <t>kk_3595551743</t>
         </is>
       </c>
       <c r="B885" t="inlineStr">
         <is>
-          <t>01050502500</t>
+          <t>01025839326</t>
         </is>
       </c>
       <c r="C885" t="inlineStr">
         <is>
-          <t>14062</t>
+          <t>246836</t>
         </is>
       </c>
       <c r="D885" t="inlineStr">
@@ -24319,7 +24319,7 @@
       </c>
       <c r="E885" t="inlineStr">
         <is>
-          <t>EDM_TOP</t>
+          <t>LMS_ECOM_0410exclusive2</t>
         </is>
       </c>
     </row>
@@ -24434,54 +24434,54 @@
     <row r="890">
       <c r="A890" t="inlineStr">
         <is>
-          <t>kmh7710</t>
+          <t>kk_4375973589</t>
         </is>
       </c>
       <c r="B890" t="inlineStr">
         <is>
-          <t>01077108716</t>
+          <t>01096223641</t>
         </is>
       </c>
       <c r="C890" t="inlineStr">
         <is>
-          <t>164951</t>
+          <t>280163</t>
         </is>
       </c>
       <c r="D890" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Organic Traffic</t>
         </is>
       </c>
       <c r="E890" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0214_newyear</t>
+          <t>LMS_ECOM_familycoupon</t>
         </is>
       </c>
     </row>
     <row r="891">
       <c r="A891" t="inlineStr">
         <is>
-          <t>kk_4375973589</t>
+          <t>kmh7710</t>
         </is>
       </c>
       <c r="B891" t="inlineStr">
         <is>
-          <t>01096223641</t>
+          <t>01077108716</t>
         </is>
       </c>
       <c r="C891" t="inlineStr">
         <is>
-          <t>280163</t>
+          <t>164951</t>
         </is>
       </c>
       <c r="D891" t="inlineStr">
         <is>
-          <t>Organic Traffic</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E891" t="inlineStr">
         <is>
-          <t>LMS_ECOM_familycoupon</t>
+          <t>LMS_ECOM_0214_newyear</t>
         </is>
       </c>
     </row>
@@ -24542,71 +24542,71 @@
     <row r="894">
       <c r="A894" t="inlineStr">
         <is>
-          <t>kk_4843611952</t>
+          <t>kk_2954504655</t>
         </is>
       </c>
       <c r="B894" t="inlineStr">
         <is>
-          <t>01068610131</t>
+          <t>01024942984</t>
         </is>
       </c>
       <c r="C894" t="inlineStr">
         <is>
-          <t>304327</t>
+          <t>242733</t>
         </is>
       </c>
       <c r="D894" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="E894" t="inlineStr">
         <is>
-          <t>6968489536332</t>
+          <t>Direct</t>
         </is>
       </c>
     </row>
     <row r="895">
       <c r="A895" t="inlineStr">
         <is>
-          <t>kk_4844665214</t>
+          <t>kk_4843611952</t>
         </is>
       </c>
       <c r="B895" t="inlineStr">
         <is>
-          <t>01033424745</t>
+          <t>01068610131</t>
         </is>
       </c>
       <c r="C895" t="inlineStr">
         <is>
-          <t>304377</t>
+          <t>304327</t>
         </is>
       </c>
       <c r="D895" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E895" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>6968489536332</t>
         </is>
       </c>
     </row>
     <row r="896">
       <c r="A896" t="inlineStr">
         <is>
-          <t>kk_2954504655</t>
+          <t>kk_4844665214</t>
         </is>
       </c>
       <c r="B896" t="inlineStr">
         <is>
-          <t>01024942984</t>
+          <t>01033424745</t>
         </is>
       </c>
       <c r="C896" t="inlineStr">
         <is>
-          <t>242733</t>
+          <t>304377</t>
         </is>
       </c>
       <c r="D896" t="inlineStr">
@@ -24677,17 +24677,17 @@
     <row r="899">
       <c r="A899" t="inlineStr">
         <is>
-          <t>kk_4839544665</t>
+          <t>kk_4839477951</t>
         </is>
       </c>
       <c r="B899" t="inlineStr">
         <is>
-          <t>01055350199</t>
+          <t>01020868012</t>
         </is>
       </c>
       <c r="C899" t="inlineStr">
         <is>
-          <t>304104</t>
+          <t>304101</t>
         </is>
       </c>
       <c r="D899" t="inlineStr">
@@ -24704,17 +24704,17 @@
     <row r="900">
       <c r="A900" t="inlineStr">
         <is>
-          <t>kk_4839477951</t>
+          <t>kk_4840093815</t>
         </is>
       </c>
       <c r="B900" t="inlineStr">
         <is>
-          <t>01020868012</t>
+          <t>01095450820</t>
         </is>
       </c>
       <c r="C900" t="inlineStr">
         <is>
-          <t>304101</t>
+          <t>304126</t>
         </is>
       </c>
       <c r="D900" t="inlineStr">
@@ -24724,24 +24724,24 @@
       </c>
       <c r="E900" t="inlineStr">
         <is>
-          <t>6968489536332</t>
+          <t>EFW</t>
         </is>
       </c>
     </row>
     <row r="901">
       <c r="A901" t="inlineStr">
         <is>
-          <t>kk_4840093815</t>
+          <t>kk_4839544665</t>
         </is>
       </c>
       <c r="B901" t="inlineStr">
         <is>
-          <t>01095450820</t>
+          <t>01055350199</t>
         </is>
       </c>
       <c r="C901" t="inlineStr">
         <is>
-          <t>304126</t>
+          <t>304104</t>
         </is>
       </c>
       <c r="D901" t="inlineStr">
@@ -24751,61 +24751,61 @@
       </c>
       <c r="E901" t="inlineStr">
         <is>
-          <t>EFW</t>
+          <t>6968489536332</t>
         </is>
       </c>
     </row>
     <row r="902">
       <c r="A902" t="inlineStr">
         <is>
-          <t>kk_3775491761</t>
+          <t>kk_4837471959</t>
         </is>
       </c>
       <c r="B902" t="inlineStr">
         <is>
-          <t>01042990425</t>
+          <t>01022201041</t>
         </is>
       </c>
       <c r="C902" t="inlineStr">
         <is>
-          <t>255841</t>
+          <t>303988</t>
         </is>
       </c>
       <c r="D902" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E902" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>6968489536332</t>
         </is>
       </c>
     </row>
     <row r="903">
       <c r="A903" t="inlineStr">
         <is>
-          <t>kk_4837471959</t>
+          <t>kk_3775491761</t>
         </is>
       </c>
       <c r="B903" t="inlineStr">
         <is>
-          <t>01022201041</t>
+          <t>01042990425</t>
         </is>
       </c>
       <c r="C903" t="inlineStr">
         <is>
-          <t>303988</t>
+          <t>255841</t>
         </is>
       </c>
       <c r="D903" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="E903" t="inlineStr">
         <is>
-          <t>6968489536332</t>
+          <t>Direct</t>
         </is>
       </c>
     </row>
@@ -24893,17 +24893,17 @@
     <row r="907">
       <c r="A907" t="inlineStr">
         <is>
-          <t>kk_4844657024</t>
+          <t>kk_4844530515</t>
         </is>
       </c>
       <c r="B907" t="inlineStr">
         <is>
-          <t>01033551784</t>
+          <t>01054558799</t>
         </is>
       </c>
       <c r="C907" t="inlineStr">
         <is>
-          <t>304376</t>
+          <t>304366</t>
         </is>
       </c>
       <c r="D907" t="inlineStr">
@@ -24947,17 +24947,17 @@
     <row r="909">
       <c r="A909" t="inlineStr">
         <is>
-          <t>kk_4844530515</t>
+          <t>kk_4844657024</t>
         </is>
       </c>
       <c r="B909" t="inlineStr">
         <is>
-          <t>01054558799</t>
+          <t>01033551784</t>
         </is>
       </c>
       <c r="C909" t="inlineStr">
         <is>
-          <t>304366</t>
+          <t>304376</t>
         </is>
       </c>
       <c r="D909" t="inlineStr">
@@ -24974,54 +24974,54 @@
     <row r="910">
       <c r="A910" t="inlineStr">
         <is>
-          <t>kk_4839643736</t>
+          <t>kk_4543882817</t>
         </is>
       </c>
       <c r="B910" t="inlineStr">
         <is>
-          <t>01063617035</t>
+          <t>01023875300</t>
         </is>
       </c>
       <c r="C910" t="inlineStr">
         <is>
-          <t>304107</t>
+          <t>287573</t>
         </is>
       </c>
       <c r="D910" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="E910" t="inlineStr">
         <is>
-          <t>naver_brandsearch_mobile</t>
+          <t>미분류</t>
         </is>
       </c>
     </row>
     <row r="911">
       <c r="A911" t="inlineStr">
         <is>
-          <t>kk_4543882817</t>
+          <t>kk_4839643736</t>
         </is>
       </c>
       <c r="B911" t="inlineStr">
         <is>
-          <t>01023875300</t>
+          <t>01063617035</t>
         </is>
       </c>
       <c r="C911" t="inlineStr">
         <is>
-          <t>287573</t>
+          <t>304107</t>
         </is>
       </c>
       <c r="D911" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E911" t="inlineStr">
         <is>
-          <t>미분류</t>
+          <t>naver_brandsearch_mobile</t>
         </is>
       </c>
     </row>
@@ -25055,17 +25055,17 @@
     <row r="913">
       <c r="A913" t="inlineStr">
         <is>
-          <t>kk_4844453283</t>
+          <t>kk_4845173313</t>
         </is>
       </c>
       <c r="B913" t="inlineStr">
         <is>
-          <t>01090262556</t>
+          <t>01024436341</t>
         </is>
       </c>
       <c r="C913" t="inlineStr">
         <is>
-          <t>304360</t>
+          <t>304397</t>
         </is>
       </c>
       <c r="D913" t="inlineStr">
@@ -25082,54 +25082,54 @@
     <row r="914">
       <c r="A914" t="inlineStr">
         <is>
-          <t>kidultyo</t>
+          <t>kk_4843926419</t>
         </is>
       </c>
       <c r="B914" t="inlineStr">
         <is>
-          <t>01037980315</t>
+          <t>01034583174</t>
         </is>
       </c>
       <c r="C914" t="inlineStr">
         <is>
-          <t>304331</t>
+          <t>304338</t>
         </is>
       </c>
       <c r="D914" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Official SNS</t>
         </is>
       </c>
       <c r="E914" t="inlineStr">
         <is>
-          <t>6968489536332</t>
+          <t>EFW_04</t>
         </is>
       </c>
     </row>
     <row r="915">
       <c r="A915" t="inlineStr">
         <is>
-          <t>kk_4843926419</t>
+          <t>kk_4844453283</t>
         </is>
       </c>
       <c r="B915" t="inlineStr">
         <is>
-          <t>01034583174</t>
+          <t>01090262556</t>
         </is>
       </c>
       <c r="C915" t="inlineStr">
         <is>
-          <t>304338</t>
+          <t>304360</t>
         </is>
       </c>
       <c r="D915" t="inlineStr">
         <is>
-          <t>Official SNS</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E915" t="inlineStr">
         <is>
-          <t>EFW_04</t>
+          <t>6968489536332</t>
         </is>
       </c>
     </row>
@@ -25163,108 +25163,108 @@
     <row r="917">
       <c r="A917" t="inlineStr">
         <is>
-          <t>kk_4843847622</t>
+          <t>kidultyo</t>
         </is>
       </c>
       <c r="B917" t="inlineStr">
         <is>
-          <t>01046990393</t>
+          <t>01037980315</t>
         </is>
       </c>
       <c r="C917" t="inlineStr">
         <is>
-          <t>304336</t>
+          <t>304331</t>
         </is>
       </c>
       <c r="D917" t="inlineStr">
         <is>
-          <t>Organic Traffic</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E917" t="inlineStr">
         <is>
-          <t>(organic)</t>
+          <t>6968489536332</t>
         </is>
       </c>
     </row>
     <row r="918">
       <c r="A918" t="inlineStr">
         <is>
-          <t>kk_4845173313</t>
+          <t>kk_4843847622</t>
         </is>
       </c>
       <c r="B918" t="inlineStr">
         <is>
-          <t>01024436341</t>
+          <t>01046990393</t>
         </is>
       </c>
       <c r="C918" t="inlineStr">
         <is>
-          <t>304397</t>
+          <t>304336</t>
         </is>
       </c>
       <c r="D918" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Organic Traffic</t>
         </is>
       </c>
       <c r="E918" t="inlineStr">
         <is>
-          <t>6968489536332</t>
+          <t>(organic)</t>
         </is>
       </c>
     </row>
     <row r="919">
       <c r="A919" t="inlineStr">
         <is>
-          <t>kyoungs424</t>
+          <t>kk_4840857472</t>
         </is>
       </c>
       <c r="B919" t="inlineStr">
         <is>
-          <t>01041509204</t>
+          <t>01040551807</t>
         </is>
       </c>
       <c r="C919" t="inlineStr">
         <is>
-          <t>153760</t>
+          <t>304172</t>
         </is>
       </c>
       <c r="D919" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="E919" t="inlineStr">
         <is>
-          <t>KAKAO_alimtalk</t>
+          <t>Direct</t>
         </is>
       </c>
     </row>
     <row r="920">
       <c r="A920" t="inlineStr">
         <is>
-          <t>kk_4840857472</t>
+          <t>kyoungs424</t>
         </is>
       </c>
       <c r="B920" t="inlineStr">
         <is>
-          <t>01040551807</t>
+          <t>01041509204</t>
         </is>
       </c>
       <c r="C920" t="inlineStr">
         <is>
-          <t>304172</t>
+          <t>153760</t>
         </is>
       </c>
       <c r="D920" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E920" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>KAKAO_alimtalk</t>
         </is>
       </c>
     </row>
@@ -25298,54 +25298,54 @@
     <row r="922">
       <c r="A922" t="inlineStr">
         <is>
-          <t>kk_4357899204</t>
+          <t>kk_4839542021</t>
         </is>
       </c>
       <c r="B922" t="inlineStr">
         <is>
-          <t>01082772838</t>
+          <t>01089909663</t>
         </is>
       </c>
       <c r="C922" t="inlineStr">
         <is>
-          <t>279564</t>
+          <t>304103</t>
         </is>
       </c>
       <c r="D922" t="inlineStr">
         <is>
-          <t>Official SNS</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E922" t="inlineStr">
         <is>
-          <t>(referral)</t>
+          <t>(organic)</t>
         </is>
       </c>
     </row>
     <row r="923">
       <c r="A923" t="inlineStr">
         <is>
-          <t>kk_4839542021</t>
+          <t>kk_4357899204</t>
         </is>
       </c>
       <c r="B923" t="inlineStr">
         <is>
-          <t>01089909663</t>
+          <t>01082772838</t>
         </is>
       </c>
       <c r="C923" t="inlineStr">
         <is>
-          <t>304103</t>
+          <t>279564</t>
         </is>
       </c>
       <c r="D923" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Official SNS</t>
         </is>
       </c>
       <c r="E923" t="inlineStr">
         <is>
-          <t>(organic)</t>
+          <t>(referral)</t>
         </is>
       </c>
     </row>
@@ -25406,27 +25406,27 @@
     <row r="926">
       <c r="A926" t="inlineStr">
         <is>
-          <t>kjo1726</t>
+          <t>plumrhkr1</t>
         </is>
       </c>
       <c r="B926" t="inlineStr">
         <is>
-          <t>01087840160</t>
+          <t>01074112056</t>
         </is>
       </c>
       <c r="C926" t="inlineStr">
         <is>
-          <t>155918</t>
+          <t>303916</t>
         </is>
       </c>
       <c r="D926" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Organic Traffic</t>
         </is>
       </c>
       <c r="E926" t="inlineStr">
         <is>
-          <t>KAKAO_alimtalk</t>
+          <t>(organic)</t>
         </is>
       </c>
     </row>
@@ -25460,27 +25460,27 @@
     <row r="928">
       <c r="A928" t="inlineStr">
         <is>
-          <t>plumrhkr1</t>
+          <t>kjo1726</t>
         </is>
       </c>
       <c r="B928" t="inlineStr">
         <is>
-          <t>01074112056</t>
+          <t>01087840160</t>
         </is>
       </c>
       <c r="C928" t="inlineStr">
         <is>
-          <t>303916</t>
+          <t>155918</t>
         </is>
       </c>
       <c r="D928" t="inlineStr">
         <is>
-          <t>Organic Traffic</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E928" t="inlineStr">
         <is>
-          <t>(organic)</t>
+          <t>KAKAO_alimtalk</t>
         </is>
       </c>
     </row>
@@ -25838,54 +25838,54 @@
     <row r="942">
       <c r="A942" t="inlineStr">
         <is>
-          <t>kk_4840913383</t>
+          <t>kk_4840417532</t>
         </is>
       </c>
       <c r="B942" t="inlineStr">
         <is>
-          <t>01099887927</t>
+          <t>01053409288</t>
         </is>
       </c>
       <c r="C942" t="inlineStr">
         <is>
-          <t>304174</t>
+          <t>304147</t>
         </is>
       </c>
       <c r="D942" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>Official SNS</t>
         </is>
       </c>
       <c r="E942" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>EFW_04</t>
         </is>
       </c>
     </row>
     <row r="943">
       <c r="A943" t="inlineStr">
         <is>
-          <t>kk_4840417532</t>
+          <t>kk_4840913383</t>
         </is>
       </c>
       <c r="B943" t="inlineStr">
         <is>
-          <t>01053409288</t>
+          <t>01099887927</t>
         </is>
       </c>
       <c r="C943" t="inlineStr">
         <is>
-          <t>304147</t>
+          <t>304174</t>
         </is>
       </c>
       <c r="D943" t="inlineStr">
         <is>
-          <t>Official SNS</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="E943" t="inlineStr">
         <is>
-          <t>EFW_04</t>
+          <t>Direct</t>
         </is>
       </c>
     </row>
@@ -25973,54 +25973,54 @@
     <row r="947">
       <c r="A947" t="inlineStr">
         <is>
-          <t>kk_4837971410</t>
+          <t>music214</t>
         </is>
       </c>
       <c r="B947" t="inlineStr">
         <is>
-          <t>01045750650</t>
+          <t>01031023988</t>
         </is>
       </c>
       <c r="C947" t="inlineStr">
         <is>
-          <t>304028</t>
+          <t>303965</t>
         </is>
       </c>
       <c r="D947" t="inlineStr">
         <is>
-          <t>Official SNS</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E947" t="inlineStr">
         <is>
-          <t>EFW_04</t>
+          <t>6968489536332</t>
         </is>
       </c>
     </row>
     <row r="948">
       <c r="A948" t="inlineStr">
         <is>
-          <t>music214</t>
+          <t>kk_4837971410</t>
         </is>
       </c>
       <c r="B948" t="inlineStr">
         <is>
-          <t>01031023988</t>
+          <t>01045750650</t>
         </is>
       </c>
       <c r="C948" t="inlineStr">
         <is>
-          <t>303965</t>
+          <t>304028</t>
         </is>
       </c>
       <c r="D948" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Official SNS</t>
         </is>
       </c>
       <c r="E948" t="inlineStr">
         <is>
-          <t>6968489536332</t>
+          <t>EFW_04</t>
         </is>
       </c>
     </row>
@@ -26216,17 +26216,17 @@
     <row r="956">
       <c r="A956" t="inlineStr">
         <is>
-          <t>kk_4846761310</t>
+          <t>willper</t>
         </is>
       </c>
       <c r="B956" t="inlineStr">
         <is>
-          <t>01091189951</t>
+          <t>01085343440</t>
         </is>
       </c>
       <c r="C956" t="inlineStr">
         <is>
-          <t>304464</t>
+          <t>304408</t>
         </is>
       </c>
       <c r="D956" t="inlineStr">
@@ -26243,17 +26243,17 @@
     <row r="957">
       <c r="A957" t="inlineStr">
         <is>
-          <t>willper</t>
+          <t>kk_4846761310</t>
         </is>
       </c>
       <c r="B957" t="inlineStr">
         <is>
-          <t>01085343440</t>
+          <t>01091189951</t>
         </is>
       </c>
       <c r="C957" t="inlineStr">
         <is>
-          <t>304408</t>
+          <t>304464</t>
         </is>
       </c>
       <c r="D957" t="inlineStr">
@@ -26405,125 +26405,125 @@
     <row r="963">
       <c r="A963" t="inlineStr">
         <is>
-          <t>lolia875</t>
+          <t>sbhbi</t>
         </is>
       </c>
       <c r="B963" t="inlineStr">
         <is>
-          <t>01067138715</t>
+          <t>01047153767</t>
         </is>
       </c>
       <c r="C963" t="inlineStr">
         <is>
-          <t>161251</t>
+          <t>174291</t>
         </is>
       </c>
       <c r="D963" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="E963" t="inlineStr">
         <is>
-          <t>6968489536332</t>
+          <t>Direct</t>
         </is>
       </c>
     </row>
     <row r="964">
       <c r="A964" t="inlineStr">
         <is>
-          <t>kk_3241081989</t>
+          <t>lolia875</t>
         </is>
       </c>
       <c r="B964" t="inlineStr">
         <is>
-          <t>01072287165</t>
+          <t>01067138715</t>
         </is>
       </c>
       <c r="C964" t="inlineStr">
         <is>
-          <t>234608</t>
+          <t>161251</t>
         </is>
       </c>
       <c r="D964" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E964" t="inlineStr">
         <is>
-          <t>KAKAO_alimtalk</t>
+          <t>6968489536332</t>
         </is>
       </c>
     </row>
     <row r="965">
       <c r="A965" t="inlineStr">
         <is>
-          <t>sbhbi</t>
+          <t>kk_3241081989</t>
         </is>
       </c>
       <c r="B965" t="inlineStr">
         <is>
-          <t>01047153767</t>
+          <t>01072287165</t>
         </is>
       </c>
       <c r="C965" t="inlineStr">
         <is>
-          <t>174291</t>
+          <t>234608</t>
         </is>
       </c>
       <c r="D965" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E965" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>KAKAO_alimtalk</t>
         </is>
       </c>
     </row>
     <row r="966">
       <c r="A966" t="inlineStr">
         <is>
-          <t>sjl4534</t>
+          <t>makaveli</t>
         </is>
       </c>
       <c r="B966" t="inlineStr">
         <is>
-          <t>01028023660</t>
+          <t>01086237086</t>
         </is>
       </c>
       <c r="C966" t="inlineStr">
         <is>
-          <t>174607</t>
+          <t>66164</t>
         </is>
       </c>
       <c r="D966" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E966" t="inlineStr">
         <is>
-          <t>KAKAO_CH_MESSAGE_0409_EXCLUSIVE</t>
+          <t>naver_brandsearch_mobile</t>
         </is>
       </c>
     </row>
     <row r="967">
       <c r="A967" t="inlineStr">
         <is>
-          <t>kk_4837152929</t>
+          <t>kk_4837595875</t>
         </is>
       </c>
       <c r="B967" t="inlineStr">
         <is>
-          <t>01047050730</t>
+          <t>01057852463</t>
         </is>
       </c>
       <c r="C967" t="inlineStr">
         <is>
-          <t>303966</t>
+          <t>304000</t>
         </is>
       </c>
       <c r="D967" t="inlineStr">
@@ -26540,44 +26540,44 @@
     <row r="968">
       <c r="A968" t="inlineStr">
         <is>
-          <t>makaveli</t>
+          <t>kk_3430866338</t>
         </is>
       </c>
       <c r="B968" t="inlineStr">
         <is>
-          <t>01086237086</t>
+          <t>01026364692</t>
         </is>
       </c>
       <c r="C968" t="inlineStr">
         <is>
-          <t>66164</t>
+          <t>242249</t>
         </is>
       </c>
       <c r="D968" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E968" t="inlineStr">
         <is>
-          <t>naver_brandsearch_mobile</t>
+          <t>Email_mkt</t>
         </is>
       </c>
     </row>
     <row r="969">
       <c r="A969" t="inlineStr">
         <is>
-          <t>kk_4837595875</t>
+          <t>kk_4837152929</t>
         </is>
       </c>
       <c r="B969" t="inlineStr">
         <is>
-          <t>01057852463</t>
+          <t>01047050730</t>
         </is>
       </c>
       <c r="C969" t="inlineStr">
         <is>
-          <t>304000</t>
+          <t>303966</t>
         </is>
       </c>
       <c r="D969" t="inlineStr">
@@ -26594,17 +26594,17 @@
     <row r="970">
       <c r="A970" t="inlineStr">
         <is>
-          <t>kk_3430866338</t>
+          <t>sjl4534</t>
         </is>
       </c>
       <c r="B970" t="inlineStr">
         <is>
-          <t>01026364692</t>
+          <t>01028023660</t>
         </is>
       </c>
       <c r="C970" t="inlineStr">
         <is>
-          <t>242249</t>
+          <t>174607</t>
         </is>
       </c>
       <c r="D970" t="inlineStr">
@@ -26614,7 +26614,7 @@
       </c>
       <c r="E970" t="inlineStr">
         <is>
-          <t>Email_mkt</t>
+          <t>KAKAO_CH_MESSAGE_0409_EXCLUSIVE</t>
         </is>
       </c>
     </row>
@@ -26702,17 +26702,17 @@
     <row r="974">
       <c r="A974" t="inlineStr">
         <is>
-          <t>kk_4612713787</t>
+          <t>kk_4703414773</t>
         </is>
       </c>
       <c r="B974" t="inlineStr">
         <is>
-          <t>01095027601</t>
+          <t>01093547510</t>
         </is>
       </c>
       <c r="C974" t="inlineStr">
         <is>
-          <t>290278</t>
+          <t>296108</t>
         </is>
       </c>
       <c r="D974" t="inlineStr">
@@ -26722,24 +26722,24 @@
       </c>
       <c r="E974" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0214_newyear</t>
+          <t>KAKAO_CH_MENU_0212_GOODBYEWINTER</t>
         </is>
       </c>
     </row>
     <row r="975">
       <c r="A975" t="inlineStr">
         <is>
-          <t>kk_4703414773</t>
+          <t>kk_4612713787</t>
         </is>
       </c>
       <c r="B975" t="inlineStr">
         <is>
-          <t>01093547510</t>
+          <t>01095027601</t>
         </is>
       </c>
       <c r="C975" t="inlineStr">
         <is>
-          <t>296108</t>
+          <t>290278</t>
         </is>
       </c>
       <c r="D975" t="inlineStr">
@@ -26749,51 +26749,51 @@
       </c>
       <c r="E975" t="inlineStr">
         <is>
-          <t>KAKAO_CH_MENU_0212_GOODBYEWINTER</t>
+          <t>LMS_ECOM_0214_newyear</t>
         </is>
       </c>
     </row>
     <row r="976">
       <c r="A976" t="inlineStr">
         <is>
-          <t>imgain0422</t>
+          <t>kk_4845661756</t>
         </is>
       </c>
       <c r="B976" t="inlineStr">
         <is>
-          <t>01029135546</t>
+          <t>01095936572</t>
         </is>
       </c>
       <c r="C976" t="inlineStr">
         <is>
-          <t>181451</t>
+          <t>304422</t>
         </is>
       </c>
       <c r="D976" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E976" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>Paid Ad</t>
         </is>
       </c>
     </row>
     <row r="977">
       <c r="A977" t="inlineStr">
         <is>
-          <t>kk_4846729102</t>
+          <t>imgain0422</t>
         </is>
       </c>
       <c r="B977" t="inlineStr">
         <is>
-          <t>01084771303</t>
+          <t>01029135546</t>
         </is>
       </c>
       <c r="C977" t="inlineStr">
         <is>
-          <t>304461</t>
+          <t>181451</t>
         </is>
       </c>
       <c r="D977" t="inlineStr">
@@ -26810,27 +26810,27 @@
     <row r="978">
       <c r="A978" t="inlineStr">
         <is>
-          <t>kk_2788668233</t>
+          <t>kk_3183517395</t>
         </is>
       </c>
       <c r="B978" t="inlineStr">
         <is>
-          <t>01041696139</t>
+          <t>01082019936</t>
         </is>
       </c>
       <c r="C978" t="inlineStr">
         <is>
-          <t>210002</t>
+          <t>228501</t>
         </is>
       </c>
       <c r="D978" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="E978" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Direct</t>
         </is>
       </c>
     </row>
@@ -26864,54 +26864,54 @@
     <row r="980">
       <c r="A980" t="inlineStr">
         <is>
-          <t>kk_3183517395</t>
+          <t>kk_2788668233</t>
         </is>
       </c>
       <c r="B980" t="inlineStr">
         <is>
-          <t>01082019936</t>
+          <t>01041696139</t>
         </is>
       </c>
       <c r="C980" t="inlineStr">
         <is>
-          <t>228501</t>
+          <t>210002</t>
         </is>
       </c>
       <c r="D980" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E980" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>Paid Ad</t>
         </is>
       </c>
     </row>
     <row r="981">
       <c r="A981" t="inlineStr">
         <is>
-          <t>kk_4845661756</t>
+          <t>kk_4846729102</t>
         </is>
       </c>
       <c r="B981" t="inlineStr">
         <is>
-          <t>01095936572</t>
+          <t>01084771303</t>
         </is>
       </c>
       <c r="C981" t="inlineStr">
         <is>
-          <t>304422</t>
+          <t>304461</t>
         </is>
       </c>
       <c r="D981" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="E981" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Direct</t>
         </is>
       </c>
     </row>
@@ -26972,27 +26972,27 @@
     <row r="984">
       <c r="A984" t="inlineStr">
         <is>
-          <t>kk_3650586439</t>
+          <t>kk_2775500473</t>
         </is>
       </c>
       <c r="B984" t="inlineStr">
         <is>
-          <t>01029107056</t>
+          <t>01045659020</t>
         </is>
       </c>
       <c r="C984" t="inlineStr">
         <is>
-          <t>249153</t>
+          <t>209371</t>
         </is>
       </c>
       <c r="D984" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>Organic Traffic</t>
         </is>
       </c>
       <c r="E984" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>(referral)</t>
         </is>
       </c>
     </row>
@@ -27053,27 +27053,27 @@
     <row r="987">
       <c r="A987" t="inlineStr">
         <is>
-          <t>kk_2775500473</t>
+          <t>kk_3650586439</t>
         </is>
       </c>
       <c r="B987" t="inlineStr">
         <is>
-          <t>01045659020</t>
+          <t>01029107056</t>
         </is>
       </c>
       <c r="C987" t="inlineStr">
         <is>
-          <t>209371</t>
+          <t>249153</t>
         </is>
       </c>
       <c r="D987" t="inlineStr">
         <is>
-          <t>Organic Traffic</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="E987" t="inlineStr">
         <is>
-          <t>(referral)</t>
+          <t>Direct</t>
         </is>
       </c>
     </row>
@@ -27107,54 +27107,54 @@
     <row r="989">
       <c r="A989" t="inlineStr">
         <is>
-          <t>kk_4434329905</t>
+          <t>kk_4522711623</t>
         </is>
       </c>
       <c r="B989" t="inlineStr">
         <is>
-          <t>01071724035</t>
+          <t>01089870313</t>
         </is>
       </c>
       <c r="C989" t="inlineStr">
         <is>
-          <t>281922</t>
+          <t>286306</t>
         </is>
       </c>
       <c r="D989" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E989" t="inlineStr">
         <is>
-          <t>Email_mkt</t>
+          <t>6968489536332</t>
         </is>
       </c>
     </row>
     <row r="990">
       <c r="A990" t="inlineStr">
         <is>
-          <t>kk_4522711623</t>
+          <t>kk_4434329905</t>
         </is>
       </c>
       <c r="B990" t="inlineStr">
         <is>
-          <t>01089870313</t>
+          <t>01071724035</t>
         </is>
       </c>
       <c r="C990" t="inlineStr">
         <is>
-          <t>286306</t>
+          <t>281922</t>
         </is>
       </c>
       <c r="D990" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E990" t="inlineStr">
         <is>
-          <t>6968489536332</t>
+          <t>Email_mkt</t>
         </is>
       </c>
     </row>
@@ -27242,17 +27242,17 @@
     <row r="994">
       <c r="A994" t="inlineStr">
         <is>
-          <t>eyounjoo</t>
+          <t>kk_4228106377</t>
         </is>
       </c>
       <c r="B994" t="inlineStr">
         <is>
-          <t>01036167949</t>
+          <t>01063165271</t>
         </is>
       </c>
       <c r="C994" t="inlineStr">
         <is>
-          <t>283223</t>
+          <t>273193</t>
         </is>
       </c>
       <c r="D994" t="inlineStr">
@@ -27269,98 +27269,98 @@
     <row r="995">
       <c r="A995" t="inlineStr">
         <is>
-          <t>xoxoie2</t>
+          <t>kk_4839241951</t>
         </is>
       </c>
       <c r="B995" t="inlineStr">
         <is>
-          <t>01043560834</t>
+          <t>01079146776</t>
         </is>
       </c>
       <c r="C995" t="inlineStr">
         <is>
-          <t>304072</t>
+          <t>304090</t>
         </is>
       </c>
       <c r="D995" t="inlineStr">
         <is>
-          <t>Official SNS</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E995" t="inlineStr">
         <is>
-          <t>EFW_04</t>
+          <t>6968489536332</t>
         </is>
       </c>
     </row>
     <row r="996">
       <c r="A996" t="inlineStr">
         <is>
-          <t>kk_4839241951</t>
+          <t>kk_3213636735</t>
         </is>
       </c>
       <c r="B996" t="inlineStr">
         <is>
-          <t>01079146776</t>
+          <t>01071338973</t>
         </is>
       </c>
       <c r="C996" t="inlineStr">
         <is>
-          <t>304090</t>
+          <t>232010</t>
         </is>
       </c>
       <c r="D996" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E996" t="inlineStr">
         <is>
-          <t>6968489536332</t>
+          <t>KAKAO_CH_MENU_0226_TRAILRUN</t>
         </is>
       </c>
     </row>
     <row r="997">
       <c r="A997" t="inlineStr">
         <is>
-          <t>kk_4840045474</t>
+          <t>xoxoie2</t>
         </is>
       </c>
       <c r="B997" t="inlineStr">
         <is>
-          <t>01096310429</t>
+          <t>01043560834</t>
         </is>
       </c>
       <c r="C997" t="inlineStr">
         <is>
-          <t>304122</t>
+          <t>304072</t>
         </is>
       </c>
       <c r="D997" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Official SNS</t>
         </is>
       </c>
       <c r="E997" t="inlineStr">
         <is>
-          <t>6968489536332</t>
+          <t>EFW_04</t>
         </is>
       </c>
     </row>
     <row r="998">
       <c r="A998" t="inlineStr">
         <is>
-          <t>kk_3213636735</t>
+          <t>ssama</t>
         </is>
       </c>
       <c r="B998" t="inlineStr">
         <is>
-          <t>01071338973</t>
+          <t>01056271982</t>
         </is>
       </c>
       <c r="C998" t="inlineStr">
         <is>
-          <t>232010</t>
+          <t>47874</t>
         </is>
       </c>
       <c r="D998" t="inlineStr">
@@ -27370,61 +27370,61 @@
       </c>
       <c r="E998" t="inlineStr">
         <is>
-          <t>KAKAO_CH_MENU_0226_TRAILRUN</t>
+          <t>LMS_ECOM_0410exclusive2</t>
         </is>
       </c>
     </row>
     <row r="999">
       <c r="A999" t="inlineStr">
         <is>
-          <t>z090909x</t>
+          <t>eyounjoo</t>
         </is>
       </c>
       <c r="B999" t="inlineStr">
         <is>
-          <t>01092058111</t>
+          <t>01036167949</t>
         </is>
       </c>
       <c r="C999" t="inlineStr">
         <is>
-          <t>113003</t>
+          <t>283223</t>
         </is>
       </c>
       <c r="D999" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E999" t="inlineStr">
         <is>
-          <t>6968489536332</t>
+          <t>LMS_ECOM_0410exclusive2</t>
         </is>
       </c>
     </row>
     <row r="1000">
       <c r="A1000" t="inlineStr">
         <is>
-          <t>ssama</t>
+          <t>kk_4840045474</t>
         </is>
       </c>
       <c r="B1000" t="inlineStr">
         <is>
-          <t>01056271982</t>
+          <t>01096310429</t>
         </is>
       </c>
       <c r="C1000" t="inlineStr">
         <is>
-          <t>47874</t>
+          <t>304122</t>
         </is>
       </c>
       <c r="D1000" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E1000" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0410exclusive2</t>
+          <t>6968489536332</t>
         </is>
       </c>
     </row>
@@ -27458,27 +27458,27 @@
     <row r="1002">
       <c r="A1002" t="inlineStr">
         <is>
-          <t>kk_4228106377</t>
+          <t>z090909x</t>
         </is>
       </c>
       <c r="B1002" t="inlineStr">
         <is>
-          <t>01063165271</t>
+          <t>01092058111</t>
         </is>
       </c>
       <c r="C1002" t="inlineStr">
         <is>
-          <t>273193</t>
+          <t>113003</t>
         </is>
       </c>
       <c r="D1002" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E1002" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0410exclusive2</t>
+          <t>6968489536332</t>
         </is>
       </c>
     </row>
@@ -27512,17 +27512,17 @@
     <row r="1004">
       <c r="A1004" t="inlineStr">
         <is>
-          <t>sjk6231</t>
+          <t>kk_4837597613</t>
         </is>
       </c>
       <c r="B1004" t="inlineStr">
         <is>
-          <t>01031985034</t>
+          <t>01089218630</t>
         </is>
       </c>
       <c r="C1004" t="inlineStr">
         <is>
-          <t>281342</t>
+          <t>304001</t>
         </is>
       </c>
       <c r="D1004" t="inlineStr">
@@ -27532,24 +27532,24 @@
       </c>
       <c r="E1004" t="inlineStr">
         <is>
-          <t>Email_mkt</t>
+          <t>KAKAO_CH_MESSAGE_0409_EXCLUSIVE</t>
         </is>
       </c>
     </row>
     <row r="1005">
       <c r="A1005" t="inlineStr">
         <is>
-          <t>kk_4837597613</t>
+          <t>sjk6231</t>
         </is>
       </c>
       <c r="B1005" t="inlineStr">
         <is>
-          <t>01089218630</t>
+          <t>01031985034</t>
         </is>
       </c>
       <c r="C1005" t="inlineStr">
         <is>
-          <t>304001</t>
+          <t>281342</t>
         </is>
       </c>
       <c r="D1005" t="inlineStr">
@@ -27559,7 +27559,7 @@
       </c>
       <c r="E1005" t="inlineStr">
         <is>
-          <t>KAKAO_CH_MESSAGE_0409_EXCLUSIVE</t>
+          <t>Email_mkt</t>
         </is>
       </c>
     </row>
@@ -27620,17 +27620,17 @@
     <row r="1008">
       <c r="A1008" t="inlineStr">
         <is>
-          <t>kk_4444429966</t>
+          <t>kk_2757334528</t>
         </is>
       </c>
       <c r="B1008" t="inlineStr">
         <is>
-          <t>01032219702</t>
+          <t>01089379633</t>
         </is>
       </c>
       <c r="C1008" t="inlineStr">
         <is>
-          <t>282222</t>
+          <t>208240</t>
         </is>
       </c>
       <c r="D1008" t="inlineStr">
@@ -27647,17 +27647,17 @@
     <row r="1009">
       <c r="A1009" t="inlineStr">
         <is>
-          <t>kk_2757334528</t>
+          <t>kk_4444429966</t>
         </is>
       </c>
       <c r="B1009" t="inlineStr">
         <is>
-          <t>01089379633</t>
+          <t>01032219702</t>
         </is>
       </c>
       <c r="C1009" t="inlineStr">
         <is>
-          <t>208240</t>
+          <t>282222</t>
         </is>
       </c>
       <c r="D1009" t="inlineStr">
@@ -27728,54 +27728,54 @@
     <row r="1012">
       <c r="A1012" t="inlineStr">
         <is>
-          <t>mse001</t>
+          <t>kk_4218204827</t>
         </is>
       </c>
       <c r="B1012" t="inlineStr">
         <is>
-          <t>01085185510</t>
+          <t>01023704903</t>
         </is>
       </c>
       <c r="C1012" t="inlineStr">
         <is>
-          <t>227227</t>
+          <t>272698</t>
         </is>
       </c>
       <c r="D1012" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="E1012" t="inlineStr">
         <is>
-          <t>KAKAO_alimtalk</t>
+          <t>Direct</t>
         </is>
       </c>
     </row>
     <row r="1013">
       <c r="A1013" t="inlineStr">
         <is>
-          <t>kk_4218204827</t>
+          <t>mse001</t>
         </is>
       </c>
       <c r="B1013" t="inlineStr">
         <is>
-          <t>01023704903</t>
+          <t>01085185510</t>
         </is>
       </c>
       <c r="C1013" t="inlineStr">
         <is>
-          <t>272698</t>
+          <t>227227</t>
         </is>
       </c>
       <c r="D1013" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E1013" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>KAKAO_alimtalk</t>
         </is>
       </c>
     </row>
@@ -27809,27 +27809,27 @@
     <row r="1015">
       <c r="A1015" t="inlineStr">
         <is>
-          <t>kk_3169777000</t>
+          <t>kk_4844817541</t>
         </is>
       </c>
       <c r="B1015" t="inlineStr">
         <is>
-          <t>01089348462</t>
+          <t>01046631832</t>
         </is>
       </c>
       <c r="C1015" t="inlineStr">
         <is>
-          <t>224876</t>
+          <t>304380</t>
         </is>
       </c>
       <c r="D1015" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E1015" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>[PF]전환_회원가입(유사)</t>
         </is>
       </c>
     </row>
@@ -27863,233 +27863,233 @@
     <row r="1017">
       <c r="A1017" t="inlineStr">
         <is>
-          <t>kk_4375003446</t>
+          <t>kk_3169777000</t>
         </is>
       </c>
       <c r="B1017" t="inlineStr">
         <is>
-          <t>01087457282</t>
+          <t>01089348462</t>
         </is>
       </c>
       <c r="C1017" t="inlineStr">
         <is>
-          <t>280131</t>
+          <t>224876</t>
         </is>
       </c>
       <c r="D1017" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="E1017" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0410exclusive2</t>
+          <t>Direct</t>
         </is>
       </c>
     </row>
     <row r="1018">
       <c r="A1018" t="inlineStr">
         <is>
-          <t>kk_4844817541</t>
+          <t>kk_4375003446</t>
         </is>
       </c>
       <c r="B1018" t="inlineStr">
         <is>
-          <t>01046631832</t>
+          <t>01087457282</t>
         </is>
       </c>
       <c r="C1018" t="inlineStr">
         <is>
-          <t>304380</t>
+          <t>280131</t>
         </is>
       </c>
       <c r="D1018" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E1018" t="inlineStr">
         <is>
-          <t>[PF]전환_회원가입(유사)</t>
+          <t>LMS_ECOM_0410exclusive2</t>
         </is>
       </c>
     </row>
     <row r="1019">
       <c r="A1019" t="inlineStr">
         <is>
-          <t>xuswldls</t>
+          <t>kk_3688034999</t>
         </is>
       </c>
       <c r="B1019" t="inlineStr">
         <is>
-          <t>01027349414</t>
+          <t>01025408262</t>
         </is>
       </c>
       <c r="C1019" t="inlineStr">
         <is>
-          <t>133308</t>
+          <t>250755</t>
         </is>
       </c>
       <c r="D1019" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E1019" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>KAKAO_alimtalk</t>
         </is>
       </c>
     </row>
     <row r="1020">
       <c r="A1020" t="inlineStr">
         <is>
-          <t>kk_4247630261</t>
+          <t>kk_2768989214</t>
         </is>
       </c>
       <c r="B1020" t="inlineStr">
         <is>
-          <t>01091437323</t>
+          <t>01095004289</t>
         </is>
       </c>
       <c r="C1020" t="inlineStr">
         <is>
-          <t>274140</t>
+          <t>209015</t>
         </is>
       </c>
       <c r="D1020" t="inlineStr">
         <is>
-          <t>Organic Traffic</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="E1020" t="inlineStr">
         <is>
-          <t>(referral)</t>
+          <t>Direct</t>
         </is>
       </c>
     </row>
     <row r="1021">
       <c r="A1021" t="inlineStr">
         <is>
-          <t>kk_3688034999</t>
+          <t>ohsm0065</t>
         </is>
       </c>
       <c r="B1021" t="inlineStr">
         <is>
-          <t>01025408262</t>
+          <t>01056170065</t>
         </is>
       </c>
       <c r="C1021" t="inlineStr">
         <is>
-          <t>250755</t>
+          <t>74567</t>
         </is>
       </c>
       <c r="D1021" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E1021" t="inlineStr">
         <is>
-          <t>KAKAO_alimtalk</t>
+          <t>[PF]트래픽_유사+관심사</t>
         </is>
       </c>
     </row>
     <row r="1022">
       <c r="A1022" t="inlineStr">
         <is>
-          <t>ohsm0065</t>
+          <t>kk_4472536591</t>
         </is>
       </c>
       <c r="B1022" t="inlineStr">
         <is>
-          <t>01056170065</t>
+          <t>01037057526</t>
         </is>
       </c>
       <c r="C1022" t="inlineStr">
         <is>
-          <t>74567</t>
+          <t>283897</t>
         </is>
       </c>
       <c r="D1022" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E1022" t="inlineStr">
         <is>
-          <t>[PF]트래픽_유사+관심사</t>
+          <t>KAKAO_alimtalk</t>
         </is>
       </c>
     </row>
     <row r="1023">
       <c r="A1023" t="inlineStr">
         <is>
-          <t>dongheon20</t>
+          <t>kk_4247630261</t>
         </is>
       </c>
       <c r="B1023" t="inlineStr">
         <is>
-          <t>01052298928</t>
+          <t>01091437323</t>
         </is>
       </c>
       <c r="C1023" t="inlineStr">
         <is>
-          <t>155362</t>
+          <t>274140</t>
         </is>
       </c>
       <c r="D1023" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Organic Traffic</t>
         </is>
       </c>
       <c r="E1023" t="inlineStr">
         <is>
-          <t>6968489536332</t>
+          <t>(referral)</t>
         </is>
       </c>
     </row>
     <row r="1024">
       <c r="A1024" t="inlineStr">
         <is>
-          <t>kk_4472536591</t>
+          <t>dongheon20</t>
         </is>
       </c>
       <c r="B1024" t="inlineStr">
         <is>
-          <t>01037057526</t>
+          <t>01052298928</t>
         </is>
       </c>
       <c r="C1024" t="inlineStr">
         <is>
-          <t>283897</t>
+          <t>155362</t>
         </is>
       </c>
       <c r="D1024" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E1024" t="inlineStr">
         <is>
-          <t>KAKAO_alimtalk</t>
+          <t>6968489536332</t>
         </is>
       </c>
     </row>
     <row r="1025">
       <c r="A1025" t="inlineStr">
         <is>
-          <t>kk_3444865211</t>
+          <t>xuswldls</t>
         </is>
       </c>
       <c r="B1025" t="inlineStr">
         <is>
-          <t>01021964871</t>
+          <t>01027349414</t>
         </is>
       </c>
       <c r="C1025" t="inlineStr">
         <is>
-          <t>242799</t>
+          <t>133308</t>
         </is>
       </c>
       <c r="D1025" t="inlineStr">
@@ -28106,17 +28106,17 @@
     <row r="1026">
       <c r="A1026" t="inlineStr">
         <is>
-          <t>kk_2768989214</t>
+          <t>kk_3444865211</t>
         </is>
       </c>
       <c r="B1026" t="inlineStr">
         <is>
-          <t>01095004289</t>
+          <t>01021964871</t>
         </is>
       </c>
       <c r="C1026" t="inlineStr">
         <is>
-          <t>209015</t>
+          <t>242799</t>
         </is>
       </c>
       <c r="D1026" t="inlineStr">
@@ -28133,44 +28133,44 @@
     <row r="1027">
       <c r="A1027" t="inlineStr">
         <is>
-          <t>chibird</t>
+          <t>kk_3837527580</t>
         </is>
       </c>
       <c r="B1027" t="inlineStr">
         <is>
-          <t>01031187674</t>
+          <t>01084311738</t>
         </is>
       </c>
       <c r="C1027" t="inlineStr">
         <is>
-          <t>219288</t>
+          <t>264113</t>
         </is>
       </c>
       <c r="D1027" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E1027" t="inlineStr">
         <is>
-          <t>sa</t>
+          <t>LMS_ECOM_0410exclusive2</t>
         </is>
       </c>
     </row>
     <row r="1028">
       <c r="A1028" t="inlineStr">
         <is>
-          <t>kk_3181917333</t>
+          <t>jobguidance</t>
         </is>
       </c>
       <c r="B1028" t="inlineStr">
         <is>
-          <t>01072258509</t>
+          <t>01026756920</t>
         </is>
       </c>
       <c r="C1028" t="inlineStr">
         <is>
-          <t>227380</t>
+          <t>134664</t>
         </is>
       </c>
       <c r="D1028" t="inlineStr">
@@ -28187,27 +28187,27 @@
     <row r="1029">
       <c r="A1029" t="inlineStr">
         <is>
-          <t>kk_3858585698</t>
+          <t>kk_3181917333</t>
         </is>
       </c>
       <c r="B1029" t="inlineStr">
         <is>
-          <t>01092163429</t>
+          <t>01072258509</t>
         </is>
       </c>
       <c r="C1029" t="inlineStr">
         <is>
-          <t>265508</t>
+          <t>227380</t>
         </is>
       </c>
       <c r="D1029" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="E1029" t="inlineStr">
         <is>
-          <t>KAKAO_alimtalk</t>
+          <t>Direct</t>
         </is>
       </c>
     </row>
@@ -28241,17 +28241,17 @@
     <row r="1031">
       <c r="A1031" t="inlineStr">
         <is>
-          <t>kk_3837527580</t>
+          <t>kk_3858585698</t>
         </is>
       </c>
       <c r="B1031" t="inlineStr">
         <is>
-          <t>01084311738</t>
+          <t>01092163429</t>
         </is>
       </c>
       <c r="C1031" t="inlineStr">
         <is>
-          <t>264113</t>
+          <t>265508</t>
         </is>
       </c>
       <c r="D1031" t="inlineStr">
@@ -28261,78 +28261,78 @@
       </c>
       <c r="E1031" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0410exclusive2</t>
+          <t>KAKAO_alimtalk</t>
         </is>
       </c>
     </row>
     <row r="1032">
       <c r="A1032" t="inlineStr">
         <is>
-          <t>nesto1</t>
+          <t>chibird</t>
         </is>
       </c>
       <c r="B1032" t="inlineStr">
         <is>
-          <t>01056603953</t>
+          <t>01031187674</t>
         </is>
       </c>
       <c r="C1032" t="inlineStr">
         <is>
-          <t>125251</t>
+          <t>219288</t>
         </is>
       </c>
       <c r="D1032" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E1032" t="inlineStr">
         <is>
-          <t>KAKAO_alimtalk</t>
+          <t>sa</t>
         </is>
       </c>
     </row>
     <row r="1033">
       <c r="A1033" t="inlineStr">
         <is>
-          <t>jobguidance</t>
+          <t>nesto1</t>
         </is>
       </c>
       <c r="B1033" t="inlineStr">
         <is>
-          <t>01026756920</t>
+          <t>01056603953</t>
         </is>
       </c>
       <c r="C1033" t="inlineStr">
         <is>
-          <t>134664</t>
+          <t>125251</t>
         </is>
       </c>
       <c r="D1033" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E1033" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>KAKAO_alimtalk</t>
         </is>
       </c>
     </row>
     <row r="1034">
       <c r="A1034" t="inlineStr">
         <is>
-          <t>kk_3185867832</t>
+          <t>hursean</t>
         </is>
       </c>
       <c r="B1034" t="inlineStr">
         <is>
-          <t>01022086508</t>
+          <t>01091975738</t>
         </is>
       </c>
       <c r="C1034" t="inlineStr">
         <is>
-          <t>229863</t>
+          <t>123130</t>
         </is>
       </c>
       <c r="D1034" t="inlineStr">
@@ -28342,105 +28342,105 @@
       </c>
       <c r="E1034" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0410exclusive2</t>
+          <t>Email_mkt</t>
         </is>
       </c>
     </row>
     <row r="1035">
       <c r="A1035" t="inlineStr">
         <is>
-          <t>kk_3013902343</t>
+          <t>kk_3933534683</t>
         </is>
       </c>
       <c r="B1035" t="inlineStr">
         <is>
-          <t>01051802326</t>
+          <t>01030153796</t>
         </is>
       </c>
       <c r="C1035" t="inlineStr">
         <is>
-          <t>219219</t>
+          <t>269069</t>
         </is>
       </c>
       <c r="D1035" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="E1035" t="inlineStr">
         <is>
-          <t>6968489536332</t>
+          <t>Direct</t>
         </is>
       </c>
     </row>
     <row r="1036">
       <c r="A1036" t="inlineStr">
         <is>
-          <t>kk_4840061178</t>
+          <t>kk_4517851709</t>
         </is>
       </c>
       <c r="B1036" t="inlineStr">
         <is>
-          <t>01082357895</t>
+          <t>01066445714</t>
         </is>
       </c>
       <c r="C1036" t="inlineStr">
         <is>
-          <t>304124</t>
+          <t>286074</t>
         </is>
       </c>
       <c r="D1036" t="inlineStr">
         <is>
-          <t>Awareness</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E1036" t="inlineStr">
         <is>
-          <t>benz_running_program_2026_coupon</t>
+          <t>LMS_ECOM_0410exclusive2</t>
         </is>
       </c>
     </row>
     <row r="1037">
       <c r="A1037" t="inlineStr">
         <is>
-          <t>hursean</t>
+          <t>kk_3013902343</t>
         </is>
       </c>
       <c r="B1037" t="inlineStr">
         <is>
-          <t>01091975738</t>
+          <t>01051802326</t>
         </is>
       </c>
       <c r="C1037" t="inlineStr">
         <is>
-          <t>123130</t>
+          <t>219219</t>
         </is>
       </c>
       <c r="D1037" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E1037" t="inlineStr">
         <is>
-          <t>Email_mkt</t>
+          <t>6968489536332</t>
         </is>
       </c>
     </row>
     <row r="1038">
       <c r="A1038" t="inlineStr">
         <is>
-          <t>kk_4523594127</t>
+          <t>mansoogi</t>
         </is>
       </c>
       <c r="B1038" t="inlineStr">
         <is>
-          <t>01085735215</t>
+          <t>01093240897</t>
         </is>
       </c>
       <c r="C1038" t="inlineStr">
         <is>
-          <t>286358</t>
+          <t>25243</t>
         </is>
       </c>
       <c r="D1038" t="inlineStr">
@@ -28457,44 +28457,44 @@
     <row r="1039">
       <c r="A1039" t="inlineStr">
         <is>
-          <t>mansoogi</t>
+          <t>kk_4840061178</t>
         </is>
       </c>
       <c r="B1039" t="inlineStr">
         <is>
-          <t>01093240897</t>
+          <t>01082357895</t>
         </is>
       </c>
       <c r="C1039" t="inlineStr">
         <is>
-          <t>25243</t>
+          <t>304124</t>
         </is>
       </c>
       <c r="D1039" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Awareness</t>
         </is>
       </c>
       <c r="E1039" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0410exclusive2</t>
+          <t>benz_running_program_2026_coupon</t>
         </is>
       </c>
     </row>
     <row r="1040">
       <c r="A1040" t="inlineStr">
         <is>
-          <t>kk_4467707148</t>
+          <t>aya6969</t>
         </is>
       </c>
       <c r="B1040" t="inlineStr">
         <is>
-          <t>01030843332</t>
+          <t>01076590009</t>
         </is>
       </c>
       <c r="C1040" t="inlineStr">
         <is>
-          <t>283560</t>
+          <t>162562</t>
         </is>
       </c>
       <c r="D1040" t="inlineStr">
@@ -28511,17 +28511,17 @@
     <row r="1041">
       <c r="A1041" t="inlineStr">
         <is>
-          <t>kk_4338209948</t>
+          <t>kk_3185867832</t>
         </is>
       </c>
       <c r="B1041" t="inlineStr">
         <is>
-          <t>01088132379</t>
+          <t>01022086508</t>
         </is>
       </c>
       <c r="C1041" t="inlineStr">
         <is>
-          <t>278781</t>
+          <t>229863</t>
         </is>
       </c>
       <c r="D1041" t="inlineStr">
@@ -28531,51 +28531,51 @@
       </c>
       <c r="E1041" t="inlineStr">
         <is>
-          <t>KAKAO_alimtalk</t>
+          <t>LMS_ECOM_0410exclusive2</t>
         </is>
       </c>
     </row>
     <row r="1042">
       <c r="A1042" t="inlineStr">
         <is>
-          <t>kk_3933534683</t>
+          <t>kk_4338209948</t>
         </is>
       </c>
       <c r="B1042" t="inlineStr">
         <is>
-          <t>01030153796</t>
+          <t>01088132379</t>
         </is>
       </c>
       <c r="C1042" t="inlineStr">
         <is>
-          <t>269069</t>
+          <t>278781</t>
         </is>
       </c>
       <c r="D1042" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E1042" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>KAKAO_alimtalk</t>
         </is>
       </c>
     </row>
     <row r="1043">
       <c r="A1043" t="inlineStr">
         <is>
-          <t>kk_2940110361</t>
+          <t>kk_4523594127</t>
         </is>
       </c>
       <c r="B1043" t="inlineStr">
         <is>
-          <t>01035353200</t>
+          <t>01085735215</t>
         </is>
       </c>
       <c r="C1043" t="inlineStr">
         <is>
-          <t>216362</t>
+          <t>286358</t>
         </is>
       </c>
       <c r="D1043" t="inlineStr">
@@ -28592,17 +28592,17 @@
     <row r="1044">
       <c r="A1044" t="inlineStr">
         <is>
-          <t>aya6969</t>
+          <t>seul6169</t>
         </is>
       </c>
       <c r="B1044" t="inlineStr">
         <is>
-          <t>01076590009</t>
+          <t>01066116699</t>
         </is>
       </c>
       <c r="C1044" t="inlineStr">
         <is>
-          <t>162562</t>
+          <t>234239</t>
         </is>
       </c>
       <c r="D1044" t="inlineStr">
@@ -28612,24 +28612,24 @@
       </c>
       <c r="E1044" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0410exclusive2</t>
+          <t>KAKAO_alimtalk</t>
         </is>
       </c>
     </row>
     <row r="1045">
       <c r="A1045" t="inlineStr">
         <is>
-          <t>seul6169</t>
+          <t>kk_4467707148</t>
         </is>
       </c>
       <c r="B1045" t="inlineStr">
         <is>
-          <t>01066116699</t>
+          <t>01030843332</t>
         </is>
       </c>
       <c r="C1045" t="inlineStr">
         <is>
-          <t>234239</t>
+          <t>283560</t>
         </is>
       </c>
       <c r="D1045" t="inlineStr">
@@ -28639,24 +28639,24 @@
       </c>
       <c r="E1045" t="inlineStr">
         <is>
-          <t>KAKAO_alimtalk</t>
+          <t>LMS_ECOM_0410exclusive2</t>
         </is>
       </c>
     </row>
     <row r="1046">
       <c r="A1046" t="inlineStr">
         <is>
-          <t>kk_4517851709</t>
+          <t>kk_2940110361</t>
         </is>
       </c>
       <c r="B1046" t="inlineStr">
         <is>
-          <t>01066445714</t>
+          <t>01035353200</t>
         </is>
       </c>
       <c r="C1046" t="inlineStr">
         <is>
-          <t>286074</t>
+          <t>216362</t>
         </is>
       </c>
       <c r="D1046" t="inlineStr">
@@ -28673,44 +28673,44 @@
     <row r="1047">
       <c r="A1047" t="inlineStr">
         <is>
-          <t>kk_3155938902</t>
+          <t>kk_3154612153</t>
         </is>
       </c>
       <c r="B1047" t="inlineStr">
         <is>
-          <t>01098557018</t>
+          <t>01056681753</t>
         </is>
       </c>
       <c r="C1047" t="inlineStr">
         <is>
-          <t>223731</t>
+          <t>223664</t>
         </is>
       </c>
       <c r="D1047" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="E1047" t="inlineStr">
         <is>
-          <t>KAKAO_CH_MESSAGE_0409_HIKE365SUMMER</t>
+          <t>Direct</t>
         </is>
       </c>
     </row>
     <row r="1048">
       <c r="A1048" t="inlineStr">
         <is>
-          <t>kk_3665803645</t>
+          <t>kk_3155938902</t>
         </is>
       </c>
       <c r="B1048" t="inlineStr">
         <is>
-          <t>01095549123</t>
+          <t>01098557018</t>
         </is>
       </c>
       <c r="C1048" t="inlineStr">
         <is>
-          <t>249835</t>
+          <t>223731</t>
         </is>
       </c>
       <c r="D1048" t="inlineStr">
@@ -28720,105 +28720,105 @@
       </c>
       <c r="E1048" t="inlineStr">
         <is>
-          <t>KAKAO_CH_MESSAGE_0409_EXCLUSIVE</t>
+          <t>KAKAO_CH_MESSAGE_0409_HIKE365SUMMER</t>
         </is>
       </c>
     </row>
     <row r="1049">
       <c r="A1049" t="inlineStr">
         <is>
-          <t>kk_3154612153</t>
+          <t>kk_3373939453</t>
         </is>
       </c>
       <c r="B1049" t="inlineStr">
         <is>
-          <t>01056681753</t>
+          <t>01020110604</t>
         </is>
       </c>
       <c r="C1049" t="inlineStr">
         <is>
-          <t>223664</t>
+          <t>240269</t>
         </is>
       </c>
       <c r="D1049" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E1049" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>KAKAO_CH_MESSAGE_0409_EXCLUSIVE</t>
         </is>
       </c>
     </row>
     <row r="1050">
       <c r="A1050" t="inlineStr">
         <is>
-          <t>kk_4526169965</t>
+          <t>kk_4837943303</t>
         </is>
       </c>
       <c r="B1050" t="inlineStr">
         <is>
-          <t>01076289838</t>
+          <t>01054817243</t>
         </is>
       </c>
       <c r="C1050" t="inlineStr">
         <is>
-          <t>286553</t>
+          <t>304025</t>
         </is>
       </c>
       <c r="D1050" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="E1050" t="inlineStr">
         <is>
-          <t>KAKAO_CH_MESSAGE_0409_HIKE365SUMMER</t>
+          <t>Direct</t>
         </is>
       </c>
     </row>
     <row r="1051">
       <c r="A1051" t="inlineStr">
         <is>
-          <t>jhmin000</t>
+          <t>boram1991</t>
         </is>
       </c>
       <c r="B1051" t="inlineStr">
         <is>
-          <t>01086241606</t>
+          <t>01023431078</t>
         </is>
       </c>
       <c r="C1051" t="inlineStr">
         <is>
-          <t>201165</t>
+          <t>119498</t>
         </is>
       </c>
       <c r="D1051" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E1051" t="inlineStr">
         <is>
-          <t>KAKAO_CH_MESSAGE_0409_HIKE365SUMMER</t>
+          <t>6968489536332</t>
         </is>
       </c>
     </row>
     <row r="1052">
       <c r="A1052" t="inlineStr">
         <is>
-          <t>kk_3373939453</t>
+          <t>kk_3638512879</t>
         </is>
       </c>
       <c r="B1052" t="inlineStr">
         <is>
-          <t>01020110604</t>
+          <t>01053330589</t>
         </is>
       </c>
       <c r="C1052" t="inlineStr">
         <is>
-          <t>240269</t>
+          <t>248574</t>
         </is>
       </c>
       <c r="D1052" t="inlineStr">
@@ -28828,61 +28828,61 @@
       </c>
       <c r="E1052" t="inlineStr">
         <is>
-          <t>KAKAO_CH_MESSAGE_0409_EXCLUSIVE</t>
+          <t>KAKAO_CH_MESSAGE_0409_HIKE365SUMMER</t>
         </is>
       </c>
     </row>
     <row r="1053">
       <c r="A1053" t="inlineStr">
         <is>
-          <t>boram1991</t>
+          <t>kk_4526169965</t>
         </is>
       </c>
       <c r="B1053" t="inlineStr">
         <is>
-          <t>01023431078</t>
+          <t>01076289838</t>
         </is>
       </c>
       <c r="C1053" t="inlineStr">
         <is>
-          <t>119498</t>
+          <t>286553</t>
         </is>
       </c>
       <c r="D1053" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E1053" t="inlineStr">
         <is>
-          <t>6968489536332</t>
+          <t>KAKAO_CH_MESSAGE_0409_HIKE365SUMMER</t>
         </is>
       </c>
     </row>
     <row r="1054">
       <c r="A1054" t="inlineStr">
         <is>
-          <t>kk_4837943303</t>
+          <t>kk_4726499171</t>
         </is>
       </c>
       <c r="B1054" t="inlineStr">
         <is>
-          <t>01054817243</t>
+          <t>01093851013</t>
         </is>
       </c>
       <c r="C1054" t="inlineStr">
         <is>
-          <t>304025</t>
+          <t>297987</t>
         </is>
       </c>
       <c r="D1054" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E1054" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>KAKAO_CH_MESSAGE_0409_HIKE365SUMMER</t>
         </is>
       </c>
     </row>
@@ -28916,17 +28916,17 @@
     <row r="1056">
       <c r="A1056" t="inlineStr">
         <is>
-          <t>bbluesea</t>
+          <t>jhmin000</t>
         </is>
       </c>
       <c r="B1056" t="inlineStr">
         <is>
-          <t>01076473601</t>
+          <t>01086241606</t>
         </is>
       </c>
       <c r="C1056" t="inlineStr">
         <is>
-          <t>152067</t>
+          <t>201165</t>
         </is>
       </c>
       <c r="D1056" t="inlineStr">
@@ -28936,24 +28936,24 @@
       </c>
       <c r="E1056" t="inlineStr">
         <is>
-          <t>KAKAO_CH_MENU_260406_LIGHTJACKET</t>
+          <t>KAKAO_CH_MESSAGE_0409_HIKE365SUMMER</t>
         </is>
       </c>
     </row>
     <row r="1057">
       <c r="A1057" t="inlineStr">
         <is>
-          <t>kk_4726499171</t>
+          <t>bbluesea</t>
         </is>
       </c>
       <c r="B1057" t="inlineStr">
         <is>
-          <t>01093851013</t>
+          <t>01076473601</t>
         </is>
       </c>
       <c r="C1057" t="inlineStr">
         <is>
-          <t>297987</t>
+          <t>152067</t>
         </is>
       </c>
       <c r="D1057" t="inlineStr">
@@ -28963,24 +28963,24 @@
       </c>
       <c r="E1057" t="inlineStr">
         <is>
-          <t>KAKAO_CH_MESSAGE_0409_HIKE365SUMMER</t>
+          <t>KAKAO_CH_MENU_260406_LIGHTJACKET</t>
         </is>
       </c>
     </row>
     <row r="1058">
       <c r="A1058" t="inlineStr">
         <is>
-          <t>kk_3638512879</t>
+          <t>kk_3665803645</t>
         </is>
       </c>
       <c r="B1058" t="inlineStr">
         <is>
-          <t>01053330589</t>
+          <t>01095549123</t>
         </is>
       </c>
       <c r="C1058" t="inlineStr">
         <is>
-          <t>248574</t>
+          <t>249835</t>
         </is>
       </c>
       <c r="D1058" t="inlineStr">
@@ -28990,132 +28990,132 @@
       </c>
       <c r="E1058" t="inlineStr">
         <is>
-          <t>KAKAO_CH_MESSAGE_0409_HIKE365SUMMER</t>
+          <t>KAKAO_CH_MESSAGE_0409_EXCLUSIVE</t>
         </is>
       </c>
     </row>
     <row r="1059">
       <c r="A1059" t="inlineStr">
         <is>
-          <t>jeen1228</t>
+          <t>kk_3805755788</t>
         </is>
       </c>
       <c r="B1059" t="inlineStr">
         <is>
-          <t>01033512662</t>
+          <t>01092305284</t>
         </is>
       </c>
       <c r="C1059" t="inlineStr">
         <is>
-          <t>223087</t>
+          <t>260128</t>
         </is>
       </c>
       <c r="D1059" t="inlineStr">
         <is>
-          <t>Organic Traffic</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E1059" t="inlineStr">
         <is>
-          <t>(organic)</t>
+          <t>Owned Channel</t>
         </is>
       </c>
     </row>
     <row r="1060">
       <c r="A1060" t="inlineStr">
         <is>
-          <t>kk_4835694986</t>
+          <t>jeen1228</t>
         </is>
       </c>
       <c r="B1060" t="inlineStr">
         <is>
-          <t>01053746268</t>
+          <t>01033512662</t>
         </is>
       </c>
       <c r="C1060" t="inlineStr">
         <is>
-          <t>303879</t>
+          <t>223087</t>
         </is>
       </c>
       <c r="D1060" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Organic Traffic</t>
         </is>
       </c>
       <c r="E1060" t="inlineStr">
         <is>
-          <t>EFW</t>
+          <t>(organic)</t>
         </is>
       </c>
     </row>
     <row r="1061">
       <c r="A1061" t="inlineStr">
         <is>
-          <t>wns1118</t>
+          <t>pearpear</t>
         </is>
       </c>
       <c r="B1061" t="inlineStr">
         <is>
-          <t>01090185590</t>
+          <t>01048098405</t>
         </is>
       </c>
       <c r="C1061" t="inlineStr">
         <is>
-          <t>303893</t>
+          <t>29743</t>
         </is>
       </c>
       <c r="D1061" t="inlineStr">
         <is>
-          <t>Organic Traffic</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E1061" t="inlineStr">
         <is>
-          <t>(organic)</t>
+          <t>Email_mkt</t>
         </is>
       </c>
     </row>
     <row r="1062">
       <c r="A1062" t="inlineStr">
         <is>
-          <t>pearpear</t>
+          <t>wns1118</t>
         </is>
       </c>
       <c r="B1062" t="inlineStr">
         <is>
-          <t>01048098405</t>
+          <t>01090185590</t>
         </is>
       </c>
       <c r="C1062" t="inlineStr">
         <is>
-          <t>29743</t>
+          <t>303893</t>
         </is>
       </c>
       <c r="D1062" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Organic Traffic</t>
         </is>
       </c>
       <c r="E1062" t="inlineStr">
         <is>
-          <t>Email_mkt</t>
+          <t>(organic)</t>
         </is>
       </c>
     </row>
     <row r="1063">
       <c r="A1063" t="inlineStr">
         <is>
-          <t>kk_3805755788</t>
+          <t>kk_3693586748</t>
         </is>
       </c>
       <c r="B1063" t="inlineStr">
         <is>
-          <t>01092305284</t>
+          <t>01063679756</t>
         </is>
       </c>
       <c r="C1063" t="inlineStr">
         <is>
-          <t>260128</t>
+          <t>251013</t>
         </is>
       </c>
       <c r="D1063" t="inlineStr">
@@ -29125,7 +29125,7 @@
       </c>
       <c r="E1063" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>KAKAO_alimtalk</t>
         </is>
       </c>
     </row>
@@ -29159,27 +29159,27 @@
     <row r="1065">
       <c r="A1065" t="inlineStr">
         <is>
-          <t>kk_3693586748</t>
+          <t>kk_4835694986</t>
         </is>
       </c>
       <c r="B1065" t="inlineStr">
         <is>
-          <t>01063679756</t>
+          <t>01053746268</t>
         </is>
       </c>
       <c r="C1065" t="inlineStr">
         <is>
-          <t>251013</t>
+          <t>303879</t>
         </is>
       </c>
       <c r="D1065" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E1065" t="inlineStr">
         <is>
-          <t>KAKAO_alimtalk</t>
+          <t>EFW</t>
         </is>
       </c>
     </row>
@@ -29267,54 +29267,54 @@
     <row r="1069">
       <c r="A1069" t="inlineStr">
         <is>
-          <t>pentagram</t>
+          <t>dltndgy99</t>
         </is>
       </c>
       <c r="B1069" t="inlineStr">
         <is>
-          <t>01093327353</t>
+          <t>01024587982</t>
         </is>
       </c>
       <c r="C1069" t="inlineStr">
         <is>
-          <t>131085</t>
+          <t>156217</t>
         </is>
       </c>
       <c r="D1069" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E1069" t="inlineStr">
         <is>
-          <t>KAKAO_alimtalk</t>
+          <t>naver_brandsearch_mobile</t>
         </is>
       </c>
     </row>
     <row r="1070">
       <c r="A1070" t="inlineStr">
         <is>
-          <t>dltndgy99</t>
+          <t>pentagram</t>
         </is>
       </c>
       <c r="B1070" t="inlineStr">
         <is>
-          <t>01024587982</t>
+          <t>01093327353</t>
         </is>
       </c>
       <c r="C1070" t="inlineStr">
         <is>
-          <t>156217</t>
+          <t>131085</t>
         </is>
       </c>
       <c r="D1070" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E1070" t="inlineStr">
         <is>
-          <t>naver_brandsearch_mobile</t>
+          <t>KAKAO_alimtalk</t>
         </is>
       </c>
     </row>
@@ -29348,27 +29348,27 @@
     <row r="1072">
       <c r="A1072" t="inlineStr">
         <is>
-          <t>wisbrain</t>
+          <t>hihijs34</t>
         </is>
       </c>
       <c r="B1072" t="inlineStr">
         <is>
-          <t>01047220186</t>
+          <t>01093230529</t>
         </is>
       </c>
       <c r="C1072" t="inlineStr">
         <is>
-          <t>188067</t>
+          <t>128947</t>
         </is>
       </c>
       <c r="D1072" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E1072" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>[PF]A+SC_상시(1865MF,구매+장바구니)</t>
         </is>
       </c>
     </row>
@@ -29402,98 +29402,98 @@
     <row r="1074">
       <c r="A1074" t="inlineStr">
         <is>
-          <t>loyed24</t>
+          <t>wisbrain</t>
         </is>
       </c>
       <c r="B1074" t="inlineStr">
         <is>
-          <t>01085487901</t>
+          <t>01047220186</t>
         </is>
       </c>
       <c r="C1074" t="inlineStr">
         <is>
-          <t>244062</t>
+          <t>188067</t>
         </is>
       </c>
       <c r="D1074" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="E1074" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0410exclusive2</t>
+          <t>Direct</t>
         </is>
       </c>
     </row>
     <row r="1075">
       <c r="A1075" t="inlineStr">
         <is>
-          <t>hihijs34</t>
+          <t>loyed24</t>
         </is>
       </c>
       <c r="B1075" t="inlineStr">
         <is>
-          <t>01093230529</t>
+          <t>01085487901</t>
         </is>
       </c>
       <c r="C1075" t="inlineStr">
         <is>
-          <t>128947</t>
+          <t>244062</t>
         </is>
       </c>
       <c r="D1075" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E1075" t="inlineStr">
         <is>
-          <t>[PF]A+SC_상시(1865MF,구매+장바구니)</t>
+          <t>LMS_ECOM_0410exclusive2</t>
         </is>
       </c>
     </row>
     <row r="1076">
       <c r="A1076" t="inlineStr">
         <is>
-          <t>yongshin</t>
+          <t>kk_4452401577</t>
         </is>
       </c>
       <c r="B1076" t="inlineStr">
         <is>
-          <t>01053867821</t>
+          <t>01047428000</t>
         </is>
       </c>
       <c r="C1076" t="inlineStr">
         <is>
-          <t>277896</t>
+          <t>282525</t>
         </is>
       </c>
       <c r="D1076" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E1076" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>LMS_ECOM_0410exclusive2</t>
         </is>
       </c>
     </row>
     <row r="1077">
       <c r="A1077" t="inlineStr">
         <is>
-          <t>kk_4525043459</t>
+          <t>kk_3024318364</t>
         </is>
       </c>
       <c r="B1077" t="inlineStr">
         <is>
-          <t>01088312135</t>
+          <t>01050308038</t>
         </is>
       </c>
       <c r="C1077" t="inlineStr">
         <is>
-          <t>286464</t>
+          <t>219525</t>
         </is>
       </c>
       <c r="D1077" t="inlineStr">
@@ -29510,17 +29510,17 @@
     <row r="1078">
       <c r="A1078" t="inlineStr">
         <is>
-          <t>sjm700</t>
+          <t>dmsql785612</t>
         </is>
       </c>
       <c r="B1078" t="inlineStr">
         <is>
-          <t>01077331591</t>
+          <t>01051590364</t>
         </is>
       </c>
       <c r="C1078" t="inlineStr">
         <is>
-          <t>118769</t>
+          <t>137279</t>
         </is>
       </c>
       <c r="D1078" t="inlineStr">
@@ -29530,51 +29530,51 @@
       </c>
       <c r="E1078" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0410exclusive2</t>
+          <t>Email_mkt</t>
         </is>
       </c>
     </row>
     <row r="1079">
       <c r="A1079" t="inlineStr">
         <is>
-          <t>kk_3180736217</t>
+          <t>camiblanco</t>
         </is>
       </c>
       <c r="B1079" t="inlineStr">
         <is>
-          <t>01036000343</t>
+          <t>01072190103</t>
         </is>
       </c>
       <c r="C1079" t="inlineStr">
         <is>
-          <t>226314</t>
+          <t>232545</t>
         </is>
       </c>
       <c r="D1079" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="E1079" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0410exclusive2</t>
+          <t>Direct</t>
         </is>
       </c>
     </row>
     <row r="1080">
       <c r="A1080" t="inlineStr">
         <is>
-          <t>bobjazz</t>
+          <t>kk_4578503399</t>
         </is>
       </c>
       <c r="B1080" t="inlineStr">
         <is>
-          <t>01084090677</t>
+          <t>01088660330</t>
         </is>
       </c>
       <c r="C1080" t="inlineStr">
         <is>
-          <t>186218</t>
+          <t>288374</t>
         </is>
       </c>
       <c r="D1080" t="inlineStr">
@@ -29591,17 +29591,17 @@
     <row r="1081">
       <c r="A1081" t="inlineStr">
         <is>
-          <t>dmsql785612</t>
+          <t>kk_2825715315</t>
         </is>
       </c>
       <c r="B1081" t="inlineStr">
         <is>
-          <t>01051590364</t>
+          <t>01077229654</t>
         </is>
       </c>
       <c r="C1081" t="inlineStr">
         <is>
-          <t>137279</t>
+          <t>212719</t>
         </is>
       </c>
       <c r="D1081" t="inlineStr">
@@ -29611,78 +29611,78 @@
       </c>
       <c r="E1081" t="inlineStr">
         <is>
-          <t>Email_mkt</t>
+          <t>LMS_ECOM_0410exclusive2</t>
         </is>
       </c>
     </row>
     <row r="1082">
       <c r="A1082" t="inlineStr">
         <is>
-          <t>camiblanco</t>
+          <t>kk_3349199057</t>
         </is>
       </c>
       <c r="B1082" t="inlineStr">
         <is>
-          <t>01072190103</t>
+          <t>01071630312</t>
         </is>
       </c>
       <c r="C1082" t="inlineStr">
         <is>
-          <t>232545</t>
+          <t>239388</t>
         </is>
       </c>
       <c r="D1082" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E1082" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>LMS_ECOM_0410exclusive2</t>
         </is>
       </c>
     </row>
     <row r="1083">
       <c r="A1083" t="inlineStr">
         <is>
-          <t>kk_3721447783</t>
+          <t>kk_3754052831</t>
         </is>
       </c>
       <c r="B1083" t="inlineStr">
         <is>
-          <t>01051311087</t>
+          <t>01092180804</t>
         </is>
       </c>
       <c r="C1083" t="inlineStr">
         <is>
-          <t>252252</t>
+          <t>254339</t>
         </is>
       </c>
       <c r="D1083" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E1083" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>LMS_ECOM_0410exclusive2</t>
         </is>
       </c>
     </row>
     <row r="1084">
       <c r="A1084" t="inlineStr">
         <is>
-          <t>kk_3349199057</t>
+          <t>sjm700</t>
         </is>
       </c>
       <c r="B1084" t="inlineStr">
         <is>
-          <t>01071630312</t>
+          <t>01077331591</t>
         </is>
       </c>
       <c r="C1084" t="inlineStr">
         <is>
-          <t>239388</t>
+          <t>118769</t>
         </is>
       </c>
       <c r="D1084" t="inlineStr">
@@ -29699,17 +29699,17 @@
     <row r="1085">
       <c r="A1085" t="inlineStr">
         <is>
-          <t>kk_4292190414</t>
+          <t>kk_3721447783</t>
         </is>
       </c>
       <c r="B1085" t="inlineStr">
         <is>
-          <t>01095177478</t>
+          <t>01051311087</t>
         </is>
       </c>
       <c r="C1085" t="inlineStr">
         <is>
-          <t>275998</t>
+          <t>252252</t>
         </is>
       </c>
       <c r="D1085" t="inlineStr">
@@ -29726,17 +29726,17 @@
     <row r="1086">
       <c r="A1086" t="inlineStr">
         <is>
-          <t>kk_4578503399</t>
+          <t>inu21c</t>
         </is>
       </c>
       <c r="B1086" t="inlineStr">
         <is>
-          <t>01088660330</t>
+          <t>01035128236</t>
         </is>
       </c>
       <c r="C1086" t="inlineStr">
         <is>
-          <t>288374</t>
+          <t>131940</t>
         </is>
       </c>
       <c r="D1086" t="inlineStr">
@@ -29753,17 +29753,17 @@
     <row r="1087">
       <c r="A1087" t="inlineStr">
         <is>
-          <t>pls4u</t>
+          <t>hyschant</t>
         </is>
       </c>
       <c r="B1087" t="inlineStr">
         <is>
-          <t>01085985482</t>
+          <t>01065306675</t>
         </is>
       </c>
       <c r="C1087" t="inlineStr">
         <is>
-          <t>88257</t>
+          <t>108579</t>
         </is>
       </c>
       <c r="D1087" t="inlineStr">
@@ -29773,24 +29773,24 @@
       </c>
       <c r="E1087" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0401_trailrunning</t>
+          <t>LMS_ECOM_0410exclusive2</t>
         </is>
       </c>
     </row>
     <row r="1088">
       <c r="A1088" t="inlineStr">
         <is>
-          <t>kk_2825715315</t>
+          <t>kk_4525043459</t>
         </is>
       </c>
       <c r="B1088" t="inlineStr">
         <is>
-          <t>01077229654</t>
+          <t>01088312135</t>
         </is>
       </c>
       <c r="C1088" t="inlineStr">
         <is>
-          <t>212719</t>
+          <t>286464</t>
         </is>
       </c>
       <c r="D1088" t="inlineStr">
@@ -29807,17 +29807,17 @@
     <row r="1089">
       <c r="A1089" t="inlineStr">
         <is>
-          <t>kk_3024318364</t>
+          <t>kk_3180736217</t>
         </is>
       </c>
       <c r="B1089" t="inlineStr">
         <is>
-          <t>01050308038</t>
+          <t>01036000343</t>
         </is>
       </c>
       <c r="C1089" t="inlineStr">
         <is>
-          <t>219525</t>
+          <t>226314</t>
         </is>
       </c>
       <c r="D1089" t="inlineStr">
@@ -29834,17 +29834,17 @@
     <row r="1090">
       <c r="A1090" t="inlineStr">
         <is>
-          <t>inu21c</t>
+          <t>kk_3973703558</t>
         </is>
       </c>
       <c r="B1090" t="inlineStr">
         <is>
-          <t>01035128236</t>
+          <t>01048590748</t>
         </is>
       </c>
       <c r="C1090" t="inlineStr">
         <is>
-          <t>131940</t>
+          <t>271020</t>
         </is>
       </c>
       <c r="D1090" t="inlineStr">
@@ -29861,44 +29861,44 @@
     <row r="1091">
       <c r="A1091" t="inlineStr">
         <is>
-          <t>kk_3973703558</t>
+          <t>yongshin</t>
         </is>
       </c>
       <c r="B1091" t="inlineStr">
         <is>
-          <t>01048590748</t>
+          <t>01053867821</t>
         </is>
       </c>
       <c r="C1091" t="inlineStr">
         <is>
-          <t>271020</t>
+          <t>277896</t>
         </is>
       </c>
       <c r="D1091" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="E1091" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0410exclusive2</t>
+          <t>Direct</t>
         </is>
       </c>
     </row>
     <row r="1092">
       <c r="A1092" t="inlineStr">
         <is>
-          <t>columbia7</t>
+          <t>pls4u</t>
         </is>
       </c>
       <c r="B1092" t="inlineStr">
         <is>
-          <t>01050080025</t>
+          <t>01085985482</t>
         </is>
       </c>
       <c r="C1092" t="inlineStr">
         <is>
-          <t>109980</t>
+          <t>88257</t>
         </is>
       </c>
       <c r="D1092" t="inlineStr">
@@ -29908,24 +29908,24 @@
       </c>
       <c r="E1092" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0410exclusive2</t>
+          <t>LMS_ECOM_0401_trailrunning</t>
         </is>
       </c>
     </row>
     <row r="1093">
       <c r="A1093" t="inlineStr">
         <is>
-          <t>hyschant</t>
+          <t>columbia7</t>
         </is>
       </c>
       <c r="B1093" t="inlineStr">
         <is>
-          <t>01065306675</t>
+          <t>01050080025</t>
         </is>
       </c>
       <c r="C1093" t="inlineStr">
         <is>
-          <t>108579</t>
+          <t>109980</t>
         </is>
       </c>
       <c r="D1093" t="inlineStr">
@@ -29942,17 +29942,17 @@
     <row r="1094">
       <c r="A1094" t="inlineStr">
         <is>
-          <t>kk_3754052831</t>
+          <t>bobjazz</t>
         </is>
       </c>
       <c r="B1094" t="inlineStr">
         <is>
-          <t>01092180804</t>
+          <t>01084090677</t>
         </is>
       </c>
       <c r="C1094" t="inlineStr">
         <is>
-          <t>254339</t>
+          <t>186218</t>
         </is>
       </c>
       <c r="D1094" t="inlineStr">
@@ -29969,71 +29969,71 @@
     <row r="1095">
       <c r="A1095" t="inlineStr">
         <is>
-          <t>kk_4452401577</t>
+          <t>kk_4292190414</t>
         </is>
       </c>
       <c r="B1095" t="inlineStr">
         <is>
-          <t>01047428000</t>
+          <t>01095177478</t>
         </is>
       </c>
       <c r="C1095" t="inlineStr">
         <is>
-          <t>282525</t>
+          <t>275998</t>
         </is>
       </c>
       <c r="D1095" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="E1095" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0410exclusive2</t>
+          <t>Direct</t>
         </is>
       </c>
     </row>
     <row r="1096">
       <c r="A1096" t="inlineStr">
         <is>
-          <t>kk_3626939480</t>
+          <t>kk_4838419826</t>
         </is>
       </c>
       <c r="B1096" t="inlineStr">
         <is>
-          <t>01030537990</t>
+          <t>01037240798</t>
         </is>
       </c>
       <c r="C1096" t="inlineStr">
         <is>
-          <t>247893</t>
+          <t>304050</t>
         </is>
       </c>
       <c r="D1096" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E1096" t="inlineStr">
         <is>
-          <t>KAKAO_CH_MESSAGE_0409_EXCLUSIVE</t>
+          <t>[PF]트래픽_유사+관심사</t>
         </is>
       </c>
     </row>
     <row r="1097">
       <c r="A1097" t="inlineStr">
         <is>
-          <t>kk_3912725759</t>
+          <t>kk_3626939480</t>
         </is>
       </c>
       <c r="B1097" t="inlineStr">
         <is>
-          <t>01062505257</t>
+          <t>01030537990</t>
         </is>
       </c>
       <c r="C1097" t="inlineStr">
         <is>
-          <t>268286</t>
+          <t>247893</t>
         </is>
       </c>
       <c r="D1097" t="inlineStr">
@@ -30050,27 +30050,27 @@
     <row r="1098">
       <c r="A1098" t="inlineStr">
         <is>
-          <t>kk_4838419826</t>
+          <t>kk_3912725759</t>
         </is>
       </c>
       <c r="B1098" t="inlineStr">
         <is>
-          <t>01037240798</t>
+          <t>01062505257</t>
         </is>
       </c>
       <c r="C1098" t="inlineStr">
         <is>
-          <t>304050</t>
+          <t>268286</t>
         </is>
       </c>
       <c r="D1098" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E1098" t="inlineStr">
         <is>
-          <t>[PF]트래픽_유사+관심사</t>
+          <t>KAKAO_CH_MESSAGE_0409_EXCLUSIVE</t>
         </is>
       </c>
     </row>
@@ -30131,71 +30131,71 @@
     <row r="1101">
       <c r="A1101" t="inlineStr">
         <is>
-          <t>cjcangel</t>
+          <t>kk_3184270744</t>
         </is>
       </c>
       <c r="B1101" t="inlineStr">
         <is>
-          <t>01089325858</t>
+          <t>01077689325</t>
         </is>
       </c>
       <c r="C1101" t="inlineStr">
         <is>
-          <t>292800</t>
+          <t>228883</t>
         </is>
       </c>
       <c r="D1101" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="E1101" t="inlineStr">
         <is>
-          <t>Email_mkt</t>
+          <t>Direct</t>
         </is>
       </c>
     </row>
     <row r="1102">
       <c r="A1102" t="inlineStr">
         <is>
-          <t>kk_3184270744</t>
+          <t>honga22</t>
         </is>
       </c>
       <c r="B1102" t="inlineStr">
         <is>
-          <t>01077689325</t>
+          <t>01022690322</t>
         </is>
       </c>
       <c r="C1102" t="inlineStr">
         <is>
-          <t>228883</t>
+          <t>147568</t>
         </is>
       </c>
       <c r="D1102" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E1102" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>KAKAO_alimtalk</t>
         </is>
       </c>
     </row>
     <row r="1103">
       <c r="A1103" t="inlineStr">
         <is>
-          <t>honga22</t>
+          <t>kk_4255987550</t>
         </is>
       </c>
       <c r="B1103" t="inlineStr">
         <is>
-          <t>01022690322</t>
+          <t>01026453656</t>
         </is>
       </c>
       <c r="C1103" t="inlineStr">
         <is>
-          <t>147568</t>
+          <t>274389</t>
         </is>
       </c>
       <c r="D1103" t="inlineStr">
@@ -30205,24 +30205,24 @@
       </c>
       <c r="E1103" t="inlineStr">
         <is>
-          <t>KAKAO_alimtalk</t>
+          <t>Email_mkt</t>
         </is>
       </c>
     </row>
     <row r="1104">
       <c r="A1104" t="inlineStr">
         <is>
-          <t>kk_4255987550</t>
+          <t>cjcangel</t>
         </is>
       </c>
       <c r="B1104" t="inlineStr">
         <is>
-          <t>01026453656</t>
+          <t>01089325858</t>
         </is>
       </c>
       <c r="C1104" t="inlineStr">
         <is>
-          <t>274389</t>
+          <t>292800</t>
         </is>
       </c>
       <c r="D1104" t="inlineStr">
@@ -30293,17 +30293,17 @@
     <row r="1107">
       <c r="A1107" t="inlineStr">
         <is>
-          <t>happy201106</t>
+          <t>alcoholpower</t>
         </is>
       </c>
       <c r="B1107" t="inlineStr">
         <is>
-          <t>01090012622</t>
+          <t>01027629868</t>
         </is>
       </c>
       <c r="C1107" t="inlineStr">
         <is>
-          <t>136050</t>
+          <t>252954</t>
         </is>
       </c>
       <c r="D1107" t="inlineStr">
@@ -30320,17 +30320,17 @@
     <row r="1108">
       <c r="A1108" t="inlineStr">
         <is>
-          <t>alcoholpower</t>
+          <t>happy201106</t>
         </is>
       </c>
       <c r="B1108" t="inlineStr">
         <is>
-          <t>01027629868</t>
+          <t>01090012622</t>
         </is>
       </c>
       <c r="C1108" t="inlineStr">
         <is>
-          <t>252954</t>
+          <t>136050</t>
         </is>
       </c>
       <c r="D1108" t="inlineStr">

--- a/reports/member_funnel/downloads/member_funnel_7d_non_buyer.xlsx
+++ b/reports/member_funnel/downloads/member_funnel_7d_non_buyer.xlsx
@@ -8693,54 +8693,54 @@
     <row r="307">
       <c r="A307" t="inlineStr">
         <is>
-          <t>kk_4231959784</t>
+          <t>dsccool</t>
         </is>
       </c>
       <c r="B307" t="inlineStr">
         <is>
-          <t>01035343111</t>
+          <t>01040100422</t>
         </is>
       </c>
       <c r="C307" t="inlineStr">
         <is>
-          <t>273395</t>
+          <t>284754</t>
         </is>
       </c>
       <c r="D307" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="E307" t="inlineStr">
         <is>
-          <t>KAKAO_CH_MESSAGE_0325_S26NEW_CTA</t>
+          <t>Direct</t>
         </is>
       </c>
     </row>
     <row r="308">
       <c r="A308" t="inlineStr">
         <is>
-          <t>dsccool</t>
+          <t>kk_4231959784</t>
         </is>
       </c>
       <c r="B308" t="inlineStr">
         <is>
-          <t>01040100422</t>
+          <t>01035343111</t>
         </is>
       </c>
       <c r="C308" t="inlineStr">
         <is>
-          <t>284754</t>
+          <t>273395</t>
         </is>
       </c>
       <c r="D308" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E308" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>KAKAO_CH_MESSAGE_0325_S26NEW_CTA</t>
         </is>
       </c>
     </row>
@@ -11474,54 +11474,54 @@
     <row r="410">
       <c r="A410" t="inlineStr">
         <is>
-          <t>kwon9493</t>
+          <t>kk_4839170665</t>
         </is>
       </c>
       <c r="B410" t="inlineStr">
         <is>
-          <t>01035589493</t>
+          <t>01050116666</t>
         </is>
       </c>
       <c r="C410" t="inlineStr">
         <is>
-          <t>107077</t>
+          <t>304086</t>
         </is>
       </c>
       <c r="D410" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E410" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>EFW</t>
         </is>
       </c>
     </row>
     <row r="411">
       <c r="A411" t="inlineStr">
         <is>
-          <t>kk_4839170665</t>
+          <t>kwon9493</t>
         </is>
       </c>
       <c r="B411" t="inlineStr">
         <is>
-          <t>01050116666</t>
+          <t>01035589493</t>
         </is>
       </c>
       <c r="C411" t="inlineStr">
         <is>
-          <t>304086</t>
+          <t>107077</t>
         </is>
       </c>
       <c r="D411" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="E411" t="inlineStr">
         <is>
-          <t>EFW</t>
+          <t>Direct</t>
         </is>
       </c>
     </row>
@@ -15308,17 +15308,17 @@
     <row r="552">
       <c r="A552" t="inlineStr">
         <is>
-          <t>kk_3483300064</t>
+          <t>kk_4789688431</t>
         </is>
       </c>
       <c r="B552" t="inlineStr">
         <is>
-          <t>01092213404</t>
+          <t>01099981265</t>
         </is>
       </c>
       <c r="C552" t="inlineStr">
         <is>
-          <t>244619</t>
+          <t>302023</t>
         </is>
       </c>
       <c r="D552" t="inlineStr">
@@ -15328,7 +15328,7 @@
       </c>
       <c r="E552" t="inlineStr">
         <is>
-          <t>naver_brandsearch_mobile</t>
+          <t>sa</t>
         </is>
       </c>
     </row>
@@ -15362,17 +15362,17 @@
     <row r="554">
       <c r="A554" t="inlineStr">
         <is>
-          <t>kk_4789688431</t>
+          <t>kk_3483300064</t>
         </is>
       </c>
       <c r="B554" t="inlineStr">
         <is>
-          <t>01099981265</t>
+          <t>01092213404</t>
         </is>
       </c>
       <c r="C554" t="inlineStr">
         <is>
-          <t>302023</t>
+          <t>244619</t>
         </is>
       </c>
       <c r="D554" t="inlineStr">
@@ -15382,7 +15382,7 @@
       </c>
       <c r="E554" t="inlineStr">
         <is>
-          <t>sa</t>
+          <t>naver_brandsearch_mobile</t>
         </is>
       </c>
     </row>
@@ -18872,54 +18872,54 @@
     <row r="684">
       <c r="A684" t="inlineStr">
         <is>
-          <t>kk_3671070277</t>
+          <t>hisgogo</t>
         </is>
       </c>
       <c r="B684" t="inlineStr">
         <is>
-          <t>01065561446</t>
+          <t>01054110956</t>
         </is>
       </c>
       <c r="C684" t="inlineStr">
         <is>
-          <t>250075</t>
+          <t>174486</t>
         </is>
       </c>
       <c r="D684" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Organic Traffic</t>
         </is>
       </c>
       <c r="E684" t="inlineStr">
         <is>
-          <t>KAKAO_CH_MESSAGE_0409_HIKE365SUMMER</t>
+          <t>(referral)</t>
         </is>
       </c>
     </row>
     <row r="685">
       <c r="A685" t="inlineStr">
         <is>
-          <t>hisgogo</t>
+          <t>kk_3671070277</t>
         </is>
       </c>
       <c r="B685" t="inlineStr">
         <is>
-          <t>01054110956</t>
+          <t>01065561446</t>
         </is>
       </c>
       <c r="C685" t="inlineStr">
         <is>
-          <t>174486</t>
+          <t>250075</t>
         </is>
       </c>
       <c r="D685" t="inlineStr">
         <is>
-          <t>Organic Traffic</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E685" t="inlineStr">
         <is>
-          <t>(referral)</t>
+          <t>KAKAO_CH_MESSAGE_0409_HIKE365SUMMER</t>
         </is>
       </c>
     </row>
@@ -18980,54 +18980,54 @@
     <row r="688">
       <c r="A688" t="inlineStr">
         <is>
-          <t>kk_3244752214</t>
+          <t>kk_4367946268</t>
         </is>
       </c>
       <c r="B688" t="inlineStr">
         <is>
-          <t>01052959157</t>
+          <t>01098834648</t>
         </is>
       </c>
       <c r="C688" t="inlineStr">
         <is>
-          <t>234935</t>
+          <t>279882</t>
         </is>
       </c>
       <c r="D688" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="E688" t="inlineStr">
         <is>
-          <t>KAKAO_CH_MESSAGE_0409_EXCLUSIVE</t>
+          <t>Direct</t>
         </is>
       </c>
     </row>
     <row r="689">
       <c r="A689" t="inlineStr">
         <is>
-          <t>kk_4367946268</t>
+          <t>kk_3244752214</t>
         </is>
       </c>
       <c r="B689" t="inlineStr">
         <is>
-          <t>01098834648</t>
+          <t>01052959157</t>
         </is>
       </c>
       <c r="C689" t="inlineStr">
         <is>
-          <t>279882</t>
+          <t>234935</t>
         </is>
       </c>
       <c r="D689" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E689" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>KAKAO_CH_MESSAGE_0409_EXCLUSIVE</t>
         </is>
       </c>
     </row>
@@ -19169,17 +19169,17 @@
     <row r="695">
       <c r="A695" t="inlineStr">
         <is>
-          <t>kk_4288273717</t>
+          <t>kk_2915134680</t>
         </is>
       </c>
       <c r="B695" t="inlineStr">
         <is>
-          <t>01020746624</t>
+          <t>01085224711</t>
         </is>
       </c>
       <c r="C695" t="inlineStr">
         <is>
-          <t>275762</t>
+          <t>215670</t>
         </is>
       </c>
       <c r="D695" t="inlineStr">
@@ -19189,24 +19189,24 @@
       </c>
       <c r="E695" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0410exclusive2</t>
+          <t>KAKAO_CH_MESSAGE_0409_HIKE365SUMMER</t>
         </is>
       </c>
     </row>
     <row r="696">
       <c r="A696" t="inlineStr">
         <is>
-          <t>kk_2915134680</t>
+          <t>kk_4288273717</t>
         </is>
       </c>
       <c r="B696" t="inlineStr">
         <is>
-          <t>01085224711</t>
+          <t>01020746624</t>
         </is>
       </c>
       <c r="C696" t="inlineStr">
         <is>
-          <t>215670</t>
+          <t>275762</t>
         </is>
       </c>
       <c r="D696" t="inlineStr">
@@ -19216,7 +19216,7 @@
       </c>
       <c r="E696" t="inlineStr">
         <is>
-          <t>KAKAO_CH_MESSAGE_0409_HIKE365SUMMER</t>
+          <t>LMS_ECOM_0410exclusive2</t>
         </is>
       </c>
     </row>
@@ -19304,17 +19304,17 @@
     <row r="700">
       <c r="A700" t="inlineStr">
         <is>
-          <t>hun7662</t>
+          <t>kk_3101119679</t>
         </is>
       </c>
       <c r="B700" t="inlineStr">
         <is>
-          <t>01042311474</t>
+          <t>01093993852</t>
         </is>
       </c>
       <c r="C700" t="inlineStr">
         <is>
-          <t>172790</t>
+          <t>221630</t>
         </is>
       </c>
       <c r="D700" t="inlineStr">
@@ -19331,17 +19331,17 @@
     <row r="701">
       <c r="A701" t="inlineStr">
         <is>
-          <t>kk_3101119679</t>
+          <t>hun7662</t>
         </is>
       </c>
       <c r="B701" t="inlineStr">
         <is>
-          <t>01093993852</t>
+          <t>01042311474</t>
         </is>
       </c>
       <c r="C701" t="inlineStr">
         <is>
-          <t>221630</t>
+          <t>172790</t>
         </is>
       </c>
       <c r="D701" t="inlineStr">
@@ -19736,27 +19736,27 @@
     <row r="716">
       <c r="A716" t="inlineStr">
         <is>
-          <t>sun1381</t>
+          <t>kk_4839145768</t>
         </is>
       </c>
       <c r="B716" t="inlineStr">
         <is>
-          <t>01037709416</t>
+          <t>01097367898</t>
         </is>
       </c>
       <c r="C716" t="inlineStr">
         <is>
-          <t>278160</t>
+          <t>304085</t>
         </is>
       </c>
       <c r="D716" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E716" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0410exclusive2</t>
+          <t>naver_brandsearch_pc</t>
         </is>
       </c>
     </row>
@@ -19790,27 +19790,27 @@
     <row r="718">
       <c r="A718" t="inlineStr">
         <is>
-          <t>kk_4839145768</t>
+          <t>sun1381</t>
         </is>
       </c>
       <c r="B718" t="inlineStr">
         <is>
-          <t>01097367898</t>
+          <t>01037709416</t>
         </is>
       </c>
       <c r="C718" t="inlineStr">
         <is>
-          <t>304085</t>
+          <t>278160</t>
         </is>
       </c>
       <c r="D718" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E718" t="inlineStr">
         <is>
-          <t>naver_brandsearch_pc</t>
+          <t>LMS_ECOM_0410exclusive2</t>
         </is>
       </c>
     </row>
@@ -20762,27 +20762,27 @@
     <row r="754">
       <c r="A754" t="inlineStr">
         <is>
-          <t>athend</t>
+          <t>kk_4839680663</t>
         </is>
       </c>
       <c r="B754" t="inlineStr">
         <is>
-          <t>01041786462</t>
+          <t>01046429530</t>
         </is>
       </c>
       <c r="C754" t="inlineStr">
         <is>
-          <t>285491</t>
+          <t>304109</t>
         </is>
       </c>
       <c r="D754" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E754" t="inlineStr">
         <is>
-          <t>KAKAO_alimtalk</t>
+          <t>6968489536332</t>
         </is>
       </c>
     </row>
@@ -20816,98 +20816,98 @@
     <row r="756">
       <c r="A756" t="inlineStr">
         <is>
-          <t>kk_4839680663</t>
+          <t>athend</t>
         </is>
       </c>
       <c r="B756" t="inlineStr">
         <is>
-          <t>01046429530</t>
+          <t>01041786462</t>
         </is>
       </c>
       <c r="C756" t="inlineStr">
         <is>
-          <t>304109</t>
+          <t>285491</t>
         </is>
       </c>
       <c r="D756" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E756" t="inlineStr">
         <is>
-          <t>6968489536332</t>
+          <t>KAKAO_alimtalk</t>
         </is>
       </c>
     </row>
     <row r="757">
       <c r="A757" t="inlineStr">
         <is>
-          <t>kk_4431727915</t>
+          <t>kk_3184667648</t>
         </is>
       </c>
       <c r="B757" t="inlineStr">
         <is>
-          <t>01047182896</t>
+          <t>01043440321</t>
         </is>
       </c>
       <c r="C757" t="inlineStr">
         <is>
-          <t>281759</t>
+          <t>229128</t>
         </is>
       </c>
       <c r="D757" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E757" t="inlineStr">
         <is>
-          <t>KAKAO_CH_MESSAGE_0409_HIKE365SUMMER</t>
+          <t>sa</t>
         </is>
       </c>
     </row>
     <row r="758">
       <c r="A758" t="inlineStr">
         <is>
-          <t>kk_3404142353</t>
+          <t>kk_4431727915</t>
         </is>
       </c>
       <c r="B758" t="inlineStr">
         <is>
-          <t>01053293239</t>
+          <t>01047182896</t>
         </is>
       </c>
       <c r="C758" t="inlineStr">
         <is>
-          <t>241289</t>
+          <t>281759</t>
         </is>
       </c>
       <c r="D758" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E758" t="inlineStr">
         <is>
-          <t>[PF]전환_상시(2565MF,비구매자)</t>
+          <t>KAKAO_CH_MESSAGE_0409_HIKE365SUMMER</t>
         </is>
       </c>
     </row>
     <row r="759">
       <c r="A759" t="inlineStr">
         <is>
-          <t>kk_3184667648</t>
+          <t>kk_3404142353</t>
         </is>
       </c>
       <c r="B759" t="inlineStr">
         <is>
-          <t>01043440321</t>
+          <t>01053293239</t>
         </is>
       </c>
       <c r="C759" t="inlineStr">
         <is>
-          <t>229128</t>
+          <t>241289</t>
         </is>
       </c>
       <c r="D759" t="inlineStr">
@@ -20917,7 +20917,7 @@
       </c>
       <c r="E759" t="inlineStr">
         <is>
-          <t>sa</t>
+          <t>[PF]전환_상시(2565MF,비구매자)</t>
         </is>
       </c>
     </row>
@@ -21005,17 +21005,17 @@
     <row r="763">
       <c r="A763" t="inlineStr">
         <is>
-          <t>ganjing78</t>
+          <t>kk_3678962368</t>
         </is>
       </c>
       <c r="B763" t="inlineStr">
         <is>
-          <t>01065121424</t>
+          <t>01041028567</t>
         </is>
       </c>
       <c r="C763" t="inlineStr">
         <is>
-          <t>78590</t>
+          <t>250374</t>
         </is>
       </c>
       <c r="D763" t="inlineStr">
@@ -21032,17 +21032,17 @@
     <row r="764">
       <c r="A764" t="inlineStr">
         <is>
-          <t>mtbok</t>
+          <t>ganjing78</t>
         </is>
       </c>
       <c r="B764" t="inlineStr">
         <is>
-          <t>01051284339</t>
+          <t>01065121424</t>
         </is>
       </c>
       <c r="C764" t="inlineStr">
         <is>
-          <t>26917</t>
+          <t>78590</t>
         </is>
       </c>
       <c r="D764" t="inlineStr">
@@ -21059,54 +21059,54 @@
     <row r="765">
       <c r="A765" t="inlineStr">
         <is>
-          <t>kk_4839433808</t>
+          <t>mtbok</t>
         </is>
       </c>
       <c r="B765" t="inlineStr">
         <is>
-          <t>01025333388</t>
+          <t>01051284339</t>
         </is>
       </c>
       <c r="C765" t="inlineStr">
         <is>
-          <t>304100</t>
+          <t>26917</t>
         </is>
       </c>
       <c r="D765" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E765" t="inlineStr">
         <is>
-          <t>naver_brandsearch_mobile</t>
+          <t>LMS_ECOM_0410exclusive2</t>
         </is>
       </c>
     </row>
     <row r="766">
       <c r="A766" t="inlineStr">
         <is>
-          <t>kk_3678962368</t>
+          <t>kk_4839433808</t>
         </is>
       </c>
       <c r="B766" t="inlineStr">
         <is>
-          <t>01041028567</t>
+          <t>01025333388</t>
         </is>
       </c>
       <c r="C766" t="inlineStr">
         <is>
-          <t>250374</t>
+          <t>304100</t>
         </is>
       </c>
       <c r="D766" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E766" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0410exclusive2</t>
+          <t>naver_brandsearch_mobile</t>
         </is>
       </c>
     </row>
@@ -21140,54 +21140,54 @@
     <row r="768">
       <c r="A768" t="inlineStr">
         <is>
-          <t>ldh7go</t>
+          <t>lee6007</t>
         </is>
       </c>
       <c r="B768" t="inlineStr">
         <is>
-          <t>01034075007</t>
+          <t>01039973613</t>
         </is>
       </c>
       <c r="C768" t="inlineStr">
         <is>
-          <t>221575</t>
+          <t>168179</t>
         </is>
       </c>
       <c r="D768" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="E768" t="inlineStr">
         <is>
-          <t>KAKAO_CH_MESSAGE_0409_HIKE365SUMMER</t>
+          <t>Direct</t>
         </is>
       </c>
     </row>
     <row r="769">
       <c r="A769" t="inlineStr">
         <is>
-          <t>lee6007</t>
+          <t>ldh7go</t>
         </is>
       </c>
       <c r="B769" t="inlineStr">
         <is>
-          <t>01039973613</t>
+          <t>01034075007</t>
         </is>
       </c>
       <c r="C769" t="inlineStr">
         <is>
-          <t>168179</t>
+          <t>221575</t>
         </is>
       </c>
       <c r="D769" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E769" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>KAKAO_CH_MESSAGE_0409_HIKE365SUMMER</t>
         </is>
       </c>
     </row>
@@ -21221,54 +21221,54 @@
     <row r="771">
       <c r="A771" t="inlineStr">
         <is>
-          <t>kk_3181873063</t>
+          <t>kk_4727921763</t>
         </is>
       </c>
       <c r="B771" t="inlineStr">
         <is>
-          <t>01026527131</t>
+          <t>01045673975</t>
         </is>
       </c>
       <c r="C771" t="inlineStr">
         <is>
-          <t>227343</t>
+          <t>298138</t>
         </is>
       </c>
       <c r="D771" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="E771" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0410exclusive2</t>
+          <t>Direct</t>
         </is>
       </c>
     </row>
     <row r="772">
       <c r="A772" t="inlineStr">
         <is>
-          <t>kk_4727921763</t>
+          <t>kk_2757380967</t>
         </is>
       </c>
       <c r="B772" t="inlineStr">
         <is>
-          <t>01045673975</t>
+          <t>01034635649</t>
         </is>
       </c>
       <c r="C772" t="inlineStr">
         <is>
-          <t>298138</t>
+          <t>208245</t>
         </is>
       </c>
       <c r="D772" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E772" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>LMS_ECOM_0410exclusive2</t>
         </is>
       </c>
     </row>
@@ -21302,17 +21302,17 @@
     <row r="774">
       <c r="A774" t="inlineStr">
         <is>
-          <t>kk_2757380967</t>
+          <t>kk_3181873063</t>
         </is>
       </c>
       <c r="B774" t="inlineStr">
         <is>
-          <t>01034635649</t>
+          <t>01026527131</t>
         </is>
       </c>
       <c r="C774" t="inlineStr">
         <is>
-          <t>208245</t>
+          <t>227343</t>
         </is>
       </c>
       <c r="D774" t="inlineStr">
@@ -21329,17 +21329,17 @@
     <row r="775">
       <c r="A775" t="inlineStr">
         <is>
-          <t>kk_4532357752</t>
+          <t>kk_4519505330</t>
         </is>
       </c>
       <c r="B775" t="inlineStr">
         <is>
-          <t>01023210419</t>
+          <t>01024320028</t>
         </is>
       </c>
       <c r="C775" t="inlineStr">
         <is>
-          <t>286900</t>
+          <t>286150</t>
         </is>
       </c>
       <c r="D775" t="inlineStr">
@@ -21349,61 +21349,61 @@
       </c>
       <c r="E775" t="inlineStr">
         <is>
-          <t>KAKAO_CH_MESSAGE_0409_EXCLUSIVE</t>
+          <t>KAKAO_CH_MESSAGE_0409_HIKE365SUMMER</t>
         </is>
       </c>
     </row>
     <row r="776">
       <c r="A776" t="inlineStr">
         <is>
-          <t>kk_3156128258</t>
+          <t>kk_4532357752</t>
         </is>
       </c>
       <c r="B776" t="inlineStr">
         <is>
-          <t>01093995884</t>
+          <t>01023210419</t>
         </is>
       </c>
       <c r="C776" t="inlineStr">
         <is>
-          <t>223742</t>
+          <t>286900</t>
         </is>
       </c>
       <c r="D776" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E776" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>KAKAO_CH_MESSAGE_0409_EXCLUSIVE</t>
         </is>
       </c>
     </row>
     <row r="777">
       <c r="A777" t="inlineStr">
         <is>
-          <t>kk_4519505330</t>
+          <t>kk_3156128258</t>
         </is>
       </c>
       <c r="B777" t="inlineStr">
         <is>
-          <t>01024320028</t>
+          <t>01093995884</t>
         </is>
       </c>
       <c r="C777" t="inlineStr">
         <is>
-          <t>286150</t>
+          <t>223742</t>
         </is>
       </c>
       <c r="D777" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="E777" t="inlineStr">
         <is>
-          <t>KAKAO_CH_MESSAGE_0409_HIKE365SUMMER</t>
+          <t>Direct</t>
         </is>
       </c>
     </row>
@@ -21437,17 +21437,17 @@
     <row r="779">
       <c r="A779" t="inlineStr">
         <is>
-          <t>kk_4469973568</t>
+          <t>kk_3210379887</t>
         </is>
       </c>
       <c r="B779" t="inlineStr">
         <is>
-          <t>01087158602</t>
+          <t>01024748405</t>
         </is>
       </c>
       <c r="C779" t="inlineStr">
         <is>
-          <t>283741</t>
+          <t>231651</t>
         </is>
       </c>
       <c r="D779" t="inlineStr">
@@ -21457,24 +21457,24 @@
       </c>
       <c r="E779" t="inlineStr">
         <is>
-          <t>KAKAO_CH_MENU_0211_NEW_MEN</t>
+          <t>LMS_ECOM_0410exclusive2</t>
         </is>
       </c>
     </row>
     <row r="780">
       <c r="A780" t="inlineStr">
         <is>
-          <t>kk_3210379887</t>
+          <t>kk_4469973568</t>
         </is>
       </c>
       <c r="B780" t="inlineStr">
         <is>
-          <t>01024748405</t>
+          <t>01087158602</t>
         </is>
       </c>
       <c r="C780" t="inlineStr">
         <is>
-          <t>231651</t>
+          <t>283741</t>
         </is>
       </c>
       <c r="D780" t="inlineStr">
@@ -21484,7 +21484,7 @@
       </c>
       <c r="E780" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0410exclusive2</t>
+          <t>KAKAO_CH_MENU_0211_NEW_MEN</t>
         </is>
       </c>
     </row>
@@ -21545,17 +21545,17 @@
     <row r="783">
       <c r="A783" t="inlineStr">
         <is>
-          <t>kk_4368805733</t>
+          <t>kk_3967419156</t>
         </is>
       </c>
       <c r="B783" t="inlineStr">
         <is>
-          <t>01075528863</t>
+          <t>01030207947</t>
         </is>
       </c>
       <c r="C783" t="inlineStr">
         <is>
-          <t>279909</t>
+          <t>270708</t>
         </is>
       </c>
       <c r="D783" t="inlineStr">
@@ -21599,17 +21599,17 @@
     <row r="785">
       <c r="A785" t="inlineStr">
         <is>
-          <t>kk_3967419156</t>
+          <t>kk_4368805733</t>
         </is>
       </c>
       <c r="B785" t="inlineStr">
         <is>
-          <t>01030207947</t>
+          <t>01075528863</t>
         </is>
       </c>
       <c r="C785" t="inlineStr">
         <is>
-          <t>270708</t>
+          <t>279909</t>
         </is>
       </c>
       <c r="D785" t="inlineStr">
@@ -21626,17 +21626,17 @@
     <row r="786">
       <c r="A786" t="inlineStr">
         <is>
-          <t>kk_3795414578</t>
+          <t>kk_4514902337</t>
         </is>
       </c>
       <c r="B786" t="inlineStr">
         <is>
-          <t>01023131674</t>
+          <t>01024416928</t>
         </is>
       </c>
       <c r="C786" t="inlineStr">
         <is>
-          <t>257620</t>
+          <t>285925</t>
         </is>
       </c>
       <c r="D786" t="inlineStr">
@@ -21653,17 +21653,17 @@
     <row r="787">
       <c r="A787" t="inlineStr">
         <is>
-          <t>kk_4514902337</t>
+          <t>kk_3795414578</t>
         </is>
       </c>
       <c r="B787" t="inlineStr">
         <is>
-          <t>01024416928</t>
+          <t>01023131674</t>
         </is>
       </c>
       <c r="C787" t="inlineStr">
         <is>
-          <t>285925</t>
+          <t>257620</t>
         </is>
       </c>
       <c r="D787" t="inlineStr">
@@ -21815,17 +21815,17 @@
     <row r="793">
       <c r="A793" t="inlineStr">
         <is>
-          <t>mplkh</t>
+          <t>noma6420</t>
         </is>
       </c>
       <c r="B793" t="inlineStr">
         <is>
-          <t>01085245802</t>
+          <t>01071574279</t>
         </is>
       </c>
       <c r="C793" t="inlineStr">
         <is>
-          <t>160698</t>
+          <t>304023</t>
         </is>
       </c>
       <c r="D793" t="inlineStr">
@@ -21835,24 +21835,24 @@
       </c>
       <c r="E793" t="inlineStr">
         <is>
-          <t>sa</t>
+          <t>[PF]A SC_상시(1865MF,구매 장바구니)</t>
         </is>
       </c>
     </row>
     <row r="794">
       <c r="A794" t="inlineStr">
         <is>
-          <t>noma6420</t>
+          <t>mplkh</t>
         </is>
       </c>
       <c r="B794" t="inlineStr">
         <is>
-          <t>01071574279</t>
+          <t>01085245802</t>
         </is>
       </c>
       <c r="C794" t="inlineStr">
         <is>
-          <t>304023</t>
+          <t>160698</t>
         </is>
       </c>
       <c r="D794" t="inlineStr">
@@ -21862,7 +21862,7 @@
       </c>
       <c r="E794" t="inlineStr">
         <is>
-          <t>[PF]A SC_상시(1865MF,구매 장바구니)</t>
+          <t>sa</t>
         </is>
       </c>
     </row>
@@ -22841,54 +22841,54 @@
     <row r="831">
       <c r="A831" t="inlineStr">
         <is>
-          <t>kk_4839354093</t>
+          <t>kk_4835738911</t>
         </is>
       </c>
       <c r="B831" t="inlineStr">
         <is>
-          <t>01052243562</t>
+          <t>01034422073</t>
         </is>
       </c>
       <c r="C831" t="inlineStr">
         <is>
-          <t>304098</t>
+          <t>303885</t>
         </is>
       </c>
       <c r="D831" t="inlineStr">
         <is>
-          <t>Organic Traffic</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E831" t="inlineStr">
         <is>
-          <t>(organic)</t>
+          <t>6968489536332</t>
         </is>
       </c>
     </row>
     <row r="832">
       <c r="A832" t="inlineStr">
         <is>
-          <t>kk_4835738911</t>
+          <t>kk_4839354093</t>
         </is>
       </c>
       <c r="B832" t="inlineStr">
         <is>
-          <t>01034422073</t>
+          <t>01052243562</t>
         </is>
       </c>
       <c r="C832" t="inlineStr">
         <is>
-          <t>303885</t>
+          <t>304098</t>
         </is>
       </c>
       <c r="D832" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Organic Traffic</t>
         </is>
       </c>
       <c r="E832" t="inlineStr">
         <is>
-          <t>6968489536332</t>
+          <t>(organic)</t>
         </is>
       </c>
     </row>
@@ -23543,54 +23543,54 @@
     <row r="857">
       <c r="A857" t="inlineStr">
         <is>
-          <t>kk_4840108009</t>
+          <t>xey5000</t>
         </is>
       </c>
       <c r="B857" t="inlineStr">
         <is>
-          <t>01053461423</t>
+          <t>01087768710</t>
         </is>
       </c>
       <c r="C857" t="inlineStr">
         <is>
-          <t>304129</t>
+          <t>143826</t>
         </is>
       </c>
       <c r="D857" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E857" t="inlineStr">
         <is>
-          <t>6968489536332</t>
+          <t>KAKAO_CH_MESSAGE_0409_PANTS</t>
         </is>
       </c>
     </row>
     <row r="858">
       <c r="A858" t="inlineStr">
         <is>
-          <t>xey5000</t>
+          <t>kk_4840108009</t>
         </is>
       </c>
       <c r="B858" t="inlineStr">
         <is>
-          <t>01087768710</t>
+          <t>01053461423</t>
         </is>
       </c>
       <c r="C858" t="inlineStr">
         <is>
-          <t>143826</t>
+          <t>304129</t>
         </is>
       </c>
       <c r="D858" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E858" t="inlineStr">
         <is>
-          <t>KAKAO_CH_MESSAGE_0409_PANTS</t>
+          <t>6968489536332</t>
         </is>
       </c>
     </row>
@@ -23678,54 +23678,54 @@
     <row r="862">
       <c r="A862" t="inlineStr">
         <is>
-          <t>kk_4841482998</t>
+          <t>qssa2000</t>
         </is>
       </c>
       <c r="B862" t="inlineStr">
         <is>
-          <t>01050082734</t>
+          <t>01020284430</t>
         </is>
       </c>
       <c r="C862" t="inlineStr">
         <is>
-          <t>304194</t>
+          <t>202308</t>
         </is>
       </c>
       <c r="D862" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E862" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>6968489536332</t>
         </is>
       </c>
     </row>
     <row r="863">
       <c r="A863" t="inlineStr">
         <is>
-          <t>qssa2000</t>
+          <t>kk_4841482998</t>
         </is>
       </c>
       <c r="B863" t="inlineStr">
         <is>
-          <t>01020284430</t>
+          <t>01050082734</t>
         </is>
       </c>
       <c r="C863" t="inlineStr">
         <is>
-          <t>202308</t>
+          <t>304194</t>
         </is>
       </c>
       <c r="D863" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="E863" t="inlineStr">
         <is>
-          <t>6968489536332</t>
+          <t>Direct</t>
         </is>
       </c>
     </row>
@@ -23813,54 +23813,54 @@
     <row r="867">
       <c r="A867" t="inlineStr">
         <is>
-          <t>ellieee</t>
+          <t>kk_4841501713</t>
         </is>
       </c>
       <c r="B867" t="inlineStr">
         <is>
-          <t>01098996425</t>
+          <t>01042996002</t>
         </is>
       </c>
       <c r="C867" t="inlineStr">
         <is>
-          <t>203688</t>
+          <t>304195</t>
         </is>
       </c>
       <c r="D867" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E867" t="inlineStr">
         <is>
-          <t>KAKAO_alimtalk</t>
+          <t>6968489536332</t>
         </is>
       </c>
     </row>
     <row r="868">
       <c r="A868" t="inlineStr">
         <is>
-          <t>kk_4841501713</t>
+          <t>ellieee</t>
         </is>
       </c>
       <c r="B868" t="inlineStr">
         <is>
-          <t>01042996002</t>
+          <t>01098996425</t>
         </is>
       </c>
       <c r="C868" t="inlineStr">
         <is>
-          <t>304195</t>
+          <t>203688</t>
         </is>
       </c>
       <c r="D868" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E868" t="inlineStr">
         <is>
-          <t>6968489536332</t>
+          <t>KAKAO_alimtalk</t>
         </is>
       </c>
     </row>
@@ -23921,54 +23921,54 @@
     <row r="871">
       <c r="A871" t="inlineStr">
         <is>
-          <t>kk_4375973589</t>
+          <t>kmh7710</t>
         </is>
       </c>
       <c r="B871" t="inlineStr">
         <is>
-          <t>01096223641</t>
+          <t>01077108716</t>
         </is>
       </c>
       <c r="C871" t="inlineStr">
         <is>
-          <t>280163</t>
+          <t>164951</t>
         </is>
       </c>
       <c r="D871" t="inlineStr">
         <is>
-          <t>Organic Traffic</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E871" t="inlineStr">
         <is>
-          <t>LMS_ECOM_familycoupon</t>
+          <t>LMS_ECOM_0214_newyear</t>
         </is>
       </c>
     </row>
     <row r="872">
       <c r="A872" t="inlineStr">
         <is>
-          <t>kmh7710</t>
+          <t>kk_4375973589</t>
         </is>
       </c>
       <c r="B872" t="inlineStr">
         <is>
-          <t>01077108716</t>
+          <t>01096223641</t>
         </is>
       </c>
       <c r="C872" t="inlineStr">
         <is>
-          <t>164951</t>
+          <t>280163</t>
         </is>
       </c>
       <c r="D872" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Organic Traffic</t>
         </is>
       </c>
       <c r="E872" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0214_newyear</t>
+          <t>LMS_ECOM_familycoupon</t>
         </is>
       </c>
     </row>
@@ -24029,27 +24029,27 @@
     <row r="875">
       <c r="A875" t="inlineStr">
         <is>
-          <t>kk_4843611952</t>
+          <t>kk_2954504655</t>
         </is>
       </c>
       <c r="B875" t="inlineStr">
         <is>
-          <t>01068610131</t>
+          <t>01024942984</t>
         </is>
       </c>
       <c r="C875" t="inlineStr">
         <is>
-          <t>304327</t>
+          <t>242733</t>
         </is>
       </c>
       <c r="D875" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="E875" t="inlineStr">
         <is>
-          <t>6968489536332</t>
+          <t>Direct</t>
         </is>
       </c>
     </row>
@@ -24083,27 +24083,27 @@
     <row r="877">
       <c r="A877" t="inlineStr">
         <is>
-          <t>kk_2954504655</t>
+          <t>kk_4843611952</t>
         </is>
       </c>
       <c r="B877" t="inlineStr">
         <is>
-          <t>01024942984</t>
+          <t>01068610131</t>
         </is>
       </c>
       <c r="C877" t="inlineStr">
         <is>
-          <t>242733</t>
+          <t>304327</t>
         </is>
       </c>
       <c r="D877" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E877" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>6968489536332</t>
         </is>
       </c>
     </row>
@@ -24164,17 +24164,17 @@
     <row r="880">
       <c r="A880" t="inlineStr">
         <is>
-          <t>kk_4839544665</t>
+          <t>kk_4840093815</t>
         </is>
       </c>
       <c r="B880" t="inlineStr">
         <is>
-          <t>01055350199</t>
+          <t>01095450820</t>
         </is>
       </c>
       <c r="C880" t="inlineStr">
         <is>
-          <t>304104</t>
+          <t>304126</t>
         </is>
       </c>
       <c r="D880" t="inlineStr">
@@ -24184,24 +24184,24 @@
       </c>
       <c r="E880" t="inlineStr">
         <is>
-          <t>6968489536332</t>
+          <t>EFW</t>
         </is>
       </c>
     </row>
     <row r="881">
       <c r="A881" t="inlineStr">
         <is>
-          <t>kk_4840093815</t>
+          <t>kk_4839477951</t>
         </is>
       </c>
       <c r="B881" t="inlineStr">
         <is>
-          <t>01095450820</t>
+          <t>01020868012</t>
         </is>
       </c>
       <c r="C881" t="inlineStr">
         <is>
-          <t>304126</t>
+          <t>304101</t>
         </is>
       </c>
       <c r="D881" t="inlineStr">
@@ -24211,24 +24211,24 @@
       </c>
       <c r="E881" t="inlineStr">
         <is>
-          <t>EFW</t>
+          <t>6968489536332</t>
         </is>
       </c>
     </row>
     <row r="882">
       <c r="A882" t="inlineStr">
         <is>
-          <t>kk_4839477951</t>
+          <t>kk_4839544665</t>
         </is>
       </c>
       <c r="B882" t="inlineStr">
         <is>
-          <t>01020868012</t>
+          <t>01055350199</t>
         </is>
       </c>
       <c r="C882" t="inlineStr">
         <is>
-          <t>304101</t>
+          <t>304104</t>
         </is>
       </c>
       <c r="D882" t="inlineStr">
@@ -24326,54 +24326,54 @@
     <row r="886">
       <c r="A886" t="inlineStr">
         <is>
-          <t>kk_2800477789</t>
+          <t>kk_4843439707</t>
         </is>
       </c>
       <c r="B886" t="inlineStr">
         <is>
-          <t>01035177105</t>
+          <t>01022248653</t>
         </is>
       </c>
       <c r="C886" t="inlineStr">
         <is>
-          <t>211095</t>
+          <t>304310</t>
         </is>
       </c>
       <c r="D886" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E886" t="inlineStr">
         <is>
-          <t>KAKAO_alimtalk</t>
+          <t>6968489536332</t>
         </is>
       </c>
     </row>
     <row r="887">
       <c r="A887" t="inlineStr">
         <is>
-          <t>kk_4843439707</t>
+          <t>kk_2800477789</t>
         </is>
       </c>
       <c r="B887" t="inlineStr">
         <is>
-          <t>01022248653</t>
+          <t>01035177105</t>
         </is>
       </c>
       <c r="C887" t="inlineStr">
         <is>
-          <t>304310</t>
+          <t>211095</t>
         </is>
       </c>
       <c r="D887" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E887" t="inlineStr">
         <is>
-          <t>6968489536332</t>
+          <t>KAKAO_alimtalk</t>
         </is>
       </c>
     </row>
@@ -24461,54 +24461,54 @@
     <row r="891">
       <c r="A891" t="inlineStr">
         <is>
-          <t>kk_4839643736</t>
+          <t>kk_4543882817</t>
         </is>
       </c>
       <c r="B891" t="inlineStr">
         <is>
-          <t>01063617035</t>
+          <t>01023875300</t>
         </is>
       </c>
       <c r="C891" t="inlineStr">
         <is>
-          <t>304107</t>
+          <t>287573</t>
         </is>
       </c>
       <c r="D891" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="E891" t="inlineStr">
         <is>
-          <t>naver_brandsearch_mobile</t>
+          <t>미분류</t>
         </is>
       </c>
     </row>
     <row r="892">
       <c r="A892" t="inlineStr">
         <is>
-          <t>kk_4543882817</t>
+          <t>kk_4839643736</t>
         </is>
       </c>
       <c r="B892" t="inlineStr">
         <is>
-          <t>01023875300</t>
+          <t>01063617035</t>
         </is>
       </c>
       <c r="C892" t="inlineStr">
         <is>
-          <t>287573</t>
+          <t>304107</t>
         </is>
       </c>
       <c r="D892" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E892" t="inlineStr">
         <is>
-          <t>미분류</t>
+          <t>naver_brandsearch_mobile</t>
         </is>
       </c>
     </row>
@@ -24596,98 +24596,98 @@
     <row r="896">
       <c r="A896" t="inlineStr">
         <is>
-          <t>kk_4845121221</t>
+          <t>kk_4843926419</t>
         </is>
       </c>
       <c r="B896" t="inlineStr">
         <is>
-          <t>01044632332</t>
+          <t>01034583174</t>
         </is>
       </c>
       <c r="C896" t="inlineStr">
         <is>
-          <t>304393</t>
+          <t>304338</t>
         </is>
       </c>
       <c r="D896" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Official SNS</t>
         </is>
       </c>
       <c r="E896" t="inlineStr">
         <is>
-          <t>6968489536332</t>
+          <t>EFW_04</t>
         </is>
       </c>
     </row>
     <row r="897">
       <c r="A897" t="inlineStr">
         <is>
-          <t>kk_4843847622</t>
+          <t>kk_4844453283</t>
         </is>
       </c>
       <c r="B897" t="inlineStr">
         <is>
-          <t>01046990393</t>
+          <t>01090262556</t>
         </is>
       </c>
       <c r="C897" t="inlineStr">
         <is>
-          <t>304336</t>
+          <t>304360</t>
         </is>
       </c>
       <c r="D897" t="inlineStr">
         <is>
-          <t>Organic Traffic</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E897" t="inlineStr">
         <is>
-          <t>(organic)</t>
+          <t>6968489536332</t>
         </is>
       </c>
     </row>
     <row r="898">
       <c r="A898" t="inlineStr">
         <is>
-          <t>kk_4843926419</t>
+          <t>kk_4843847622</t>
         </is>
       </c>
       <c r="B898" t="inlineStr">
         <is>
-          <t>01034583174</t>
+          <t>01046990393</t>
         </is>
       </c>
       <c r="C898" t="inlineStr">
         <is>
-          <t>304338</t>
+          <t>304336</t>
         </is>
       </c>
       <c r="D898" t="inlineStr">
         <is>
-          <t>Official SNS</t>
+          <t>Organic Traffic</t>
         </is>
       </c>
       <c r="E898" t="inlineStr">
         <is>
-          <t>EFW_04</t>
+          <t>(organic)</t>
         </is>
       </c>
     </row>
     <row r="899">
       <c r="A899" t="inlineStr">
         <is>
-          <t>kk_4844453283</t>
+          <t>kk_4845121221</t>
         </is>
       </c>
       <c r="B899" t="inlineStr">
         <is>
-          <t>01090262556</t>
+          <t>01044632332</t>
         </is>
       </c>
       <c r="C899" t="inlineStr">
         <is>
-          <t>304360</t>
+          <t>304393</t>
         </is>
       </c>
       <c r="D899" t="inlineStr">
@@ -24704,17 +24704,17 @@
     <row r="900">
       <c r="A900" t="inlineStr">
         <is>
-          <t>kk_2961062530</t>
+          <t>kyoungs424</t>
         </is>
       </c>
       <c r="B900" t="inlineStr">
         <is>
-          <t>01050052823</t>
+          <t>01041509204</t>
         </is>
       </c>
       <c r="C900" t="inlineStr">
         <is>
-          <t>217199</t>
+          <t>153760</t>
         </is>
       </c>
       <c r="D900" t="inlineStr">
@@ -24724,61 +24724,61 @@
       </c>
       <c r="E900" t="inlineStr">
         <is>
-          <t>KAKAO_CH_MENU_0317_S26NEW</t>
+          <t>KAKAO_alimtalk</t>
         </is>
       </c>
     </row>
     <row r="901">
       <c r="A901" t="inlineStr">
         <is>
-          <t>kk_4840857472</t>
+          <t>kk_2961062530</t>
         </is>
       </c>
       <c r="B901" t="inlineStr">
         <is>
-          <t>01040551807</t>
+          <t>01050052823</t>
         </is>
       </c>
       <c r="C901" t="inlineStr">
         <is>
-          <t>304172</t>
+          <t>217199</t>
         </is>
       </c>
       <c r="D901" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E901" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>KAKAO_CH_MENU_0317_S26NEW</t>
         </is>
       </c>
     </row>
     <row r="902">
       <c r="A902" t="inlineStr">
         <is>
-          <t>kyoungs424</t>
+          <t>kk_4840857472</t>
         </is>
       </c>
       <c r="B902" t="inlineStr">
         <is>
-          <t>01041509204</t>
+          <t>01040551807</t>
         </is>
       </c>
       <c r="C902" t="inlineStr">
         <is>
-          <t>153760</t>
+          <t>304172</t>
         </is>
       </c>
       <c r="D902" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="E902" t="inlineStr">
         <is>
-          <t>KAKAO_alimtalk</t>
+          <t>Direct</t>
         </is>
       </c>
     </row>
@@ -24839,135 +24839,135 @@
     <row r="905">
       <c r="A905" t="inlineStr">
         <is>
-          <t>kk_4838574281</t>
+          <t>vvip6905</t>
         </is>
       </c>
       <c r="B905" t="inlineStr">
         <is>
-          <t>01092229876</t>
+          <t>01085855275</t>
         </is>
       </c>
       <c r="C905" t="inlineStr">
         <is>
-          <t>304061</t>
+          <t>304027</t>
         </is>
       </c>
       <c r="D905" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E905" t="inlineStr">
         <is>
-          <t>6968489536332</t>
+          <t>Email_mkt</t>
         </is>
       </c>
     </row>
     <row r="906">
       <c r="A906" t="inlineStr">
         <is>
-          <t>vvip6905</t>
+          <t>kk_4838574281</t>
         </is>
       </c>
       <c r="B906" t="inlineStr">
         <is>
-          <t>01085855275</t>
+          <t>01092229876</t>
         </is>
       </c>
       <c r="C906" t="inlineStr">
         <is>
-          <t>304027</t>
+          <t>304061</t>
         </is>
       </c>
       <c r="D906" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E906" t="inlineStr">
         <is>
-          <t>Email_mkt</t>
+          <t>6968489536332</t>
         </is>
       </c>
     </row>
     <row r="907">
       <c r="A907" t="inlineStr">
         <is>
-          <t>plumrhkr1</t>
+          <t>kjo1726</t>
         </is>
       </c>
       <c r="B907" t="inlineStr">
         <is>
-          <t>01074112056</t>
+          <t>01087840160</t>
         </is>
       </c>
       <c r="C907" t="inlineStr">
         <is>
-          <t>303916</t>
+          <t>155918</t>
         </is>
       </c>
       <c r="D907" t="inlineStr">
         <is>
-          <t>Organic Traffic</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E907" t="inlineStr">
         <is>
-          <t>(organic)</t>
+          <t>KAKAO_alimtalk</t>
         </is>
       </c>
     </row>
     <row r="908">
       <c r="A908" t="inlineStr">
         <is>
-          <t>kjo1726</t>
+          <t>kk_4835912712</t>
         </is>
       </c>
       <c r="B908" t="inlineStr">
         <is>
-          <t>01087840160</t>
+          <t>01094418375</t>
         </is>
       </c>
       <c r="C908" t="inlineStr">
         <is>
-          <t>155918</t>
+          <t>303898</t>
         </is>
       </c>
       <c r="D908" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="E908" t="inlineStr">
         <is>
-          <t>KAKAO_alimtalk</t>
+          <t>Direct</t>
         </is>
       </c>
     </row>
     <row r="909">
       <c r="A909" t="inlineStr">
         <is>
-          <t>kk_4835912712</t>
+          <t>plumrhkr1</t>
         </is>
       </c>
       <c r="B909" t="inlineStr">
         <is>
-          <t>01094418375</t>
+          <t>01074112056</t>
         </is>
       </c>
       <c r="C909" t="inlineStr">
         <is>
-          <t>303898</t>
+          <t>303916</t>
         </is>
       </c>
       <c r="D909" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>Organic Traffic</t>
         </is>
       </c>
       <c r="E909" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>(organic)</t>
         </is>
       </c>
     </row>
@@ -25001,233 +25001,233 @@
     <row r="911">
       <c r="A911" t="inlineStr">
         <is>
-          <t>kk_4839906396</t>
+          <t>kk_3725118384</t>
         </is>
       </c>
       <c r="B911" t="inlineStr">
         <is>
-          <t>01044486524</t>
+          <t>01035977118</t>
         </is>
       </c>
       <c r="C911" t="inlineStr">
         <is>
-          <t>304113</t>
+          <t>252440</t>
         </is>
       </c>
       <c r="D911" t="inlineStr">
         <is>
-          <t>Organic Traffic</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E911" t="inlineStr">
         <is>
-          <t>(organic)</t>
+          <t>LMS_ECOM_0214_newyear</t>
         </is>
       </c>
     </row>
     <row r="912">
       <c r="A912" t="inlineStr">
         <is>
-          <t>kk_3725118384</t>
+          <t>kk_4839906396</t>
         </is>
       </c>
       <c r="B912" t="inlineStr">
         <is>
-          <t>01035977118</t>
+          <t>01044486524</t>
         </is>
       </c>
       <c r="C912" t="inlineStr">
         <is>
-          <t>252440</t>
+          <t>304113</t>
         </is>
       </c>
       <c r="D912" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Organic Traffic</t>
         </is>
       </c>
       <c r="E912" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0214_newyear</t>
+          <t>(organic)</t>
         </is>
       </c>
     </row>
     <row r="913">
       <c r="A913" t="inlineStr">
         <is>
-          <t>kk_4446020087</t>
+          <t>kk_3798545067</t>
         </is>
       </c>
       <c r="B913" t="inlineStr">
         <is>
-          <t>01089773053</t>
+          <t>01023751319</t>
         </is>
       </c>
       <c r="C913" t="inlineStr">
         <is>
-          <t>282273</t>
+          <t>258449</t>
         </is>
       </c>
       <c r="D913" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E913" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0214_newyear</t>
+          <t>sa</t>
         </is>
       </c>
     </row>
     <row r="914">
       <c r="A914" t="inlineStr">
         <is>
-          <t>kk_3798545067</t>
+          <t>kk_4446020087</t>
         </is>
       </c>
       <c r="B914" t="inlineStr">
         <is>
-          <t>01023751319</t>
+          <t>01089773053</t>
         </is>
       </c>
       <c r="C914" t="inlineStr">
         <is>
-          <t>258449</t>
+          <t>282273</t>
         </is>
       </c>
       <c r="D914" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E914" t="inlineStr">
         <is>
-          <t>sa</t>
+          <t>LMS_ECOM_0214_newyear</t>
         </is>
       </c>
     </row>
     <row r="915">
       <c r="A915" t="inlineStr">
         <is>
-          <t>kk_4846749411</t>
+          <t>kk_4846692829</t>
         </is>
       </c>
       <c r="B915" t="inlineStr">
         <is>
-          <t>01031226749</t>
+          <t>01023649887</t>
         </is>
       </c>
       <c r="C915" t="inlineStr">
         <is>
-          <t>304462</t>
+          <t>304457</t>
         </is>
       </c>
       <c r="D915" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Organic Traffic</t>
         </is>
       </c>
       <c r="E915" t="inlineStr">
         <is>
-          <t>6968489536332</t>
+          <t>(referral)</t>
         </is>
       </c>
     </row>
     <row r="916">
       <c r="A916" t="inlineStr">
         <is>
-          <t>kk_4846692829</t>
+          <t>kk_4846749411</t>
         </is>
       </c>
       <c r="B916" t="inlineStr">
         <is>
-          <t>01023649887</t>
+          <t>01031226749</t>
         </is>
       </c>
       <c r="C916" t="inlineStr">
         <is>
-          <t>304457</t>
+          <t>304462</t>
         </is>
       </c>
       <c r="D916" t="inlineStr">
         <is>
-          <t>Organic Traffic</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E916" t="inlineStr">
         <is>
-          <t>(referral)</t>
+          <t>6968489536332</t>
         </is>
       </c>
     </row>
     <row r="917">
       <c r="A917" t="inlineStr">
         <is>
-          <t>kk_4843809795</t>
+          <t>kk_4844609437</t>
         </is>
       </c>
       <c r="B917" t="inlineStr">
         <is>
-          <t>01072864741</t>
+          <t>01046808931</t>
         </is>
       </c>
       <c r="C917" t="inlineStr">
         <is>
-          <t>304335</t>
+          <t>304372</t>
         </is>
       </c>
       <c r="D917" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Official SNS</t>
         </is>
       </c>
       <c r="E917" t="inlineStr">
         <is>
-          <t>6968489536332</t>
+          <t>(referral)</t>
         </is>
       </c>
     </row>
     <row r="918">
       <c r="A918" t="inlineStr">
         <is>
-          <t>kk_4844609437</t>
+          <t>kk_4844452226</t>
         </is>
       </c>
       <c r="B918" t="inlineStr">
         <is>
-          <t>01046808931</t>
+          <t>01096801866</t>
         </is>
       </c>
       <c r="C918" t="inlineStr">
         <is>
-          <t>304372</t>
+          <t>304359</t>
         </is>
       </c>
       <c r="D918" t="inlineStr">
         <is>
-          <t>Official SNS</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E918" t="inlineStr">
         <is>
-          <t>(referral)</t>
+          <t>6968489536332</t>
         </is>
       </c>
     </row>
     <row r="919">
       <c r="A919" t="inlineStr">
         <is>
-          <t>kk_4844452226</t>
+          <t>kk_4843809795</t>
         </is>
       </c>
       <c r="B919" t="inlineStr">
         <is>
-          <t>01096801866</t>
+          <t>01072864741</t>
         </is>
       </c>
       <c r="C919" t="inlineStr">
         <is>
-          <t>304359</t>
+          <t>304335</t>
         </is>
       </c>
       <c r="D919" t="inlineStr">
@@ -25244,206 +25244,206 @@
     <row r="920">
       <c r="A920" t="inlineStr">
         <is>
-          <t>kona143</t>
+          <t>blblhh</t>
         </is>
       </c>
       <c r="B920" t="inlineStr">
         <is>
-          <t>01021001916</t>
+          <t>01033446769</t>
         </is>
       </c>
       <c r="C920" t="inlineStr">
         <is>
-          <t>304260</t>
+          <t>304297</t>
         </is>
       </c>
       <c r="D920" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Organic Traffic</t>
         </is>
       </c>
       <c r="E920" t="inlineStr">
         <is>
-          <t>[PF]전환_회원가입(유사)</t>
+          <t>(referral)</t>
         </is>
       </c>
     </row>
     <row r="921">
       <c r="A921" t="inlineStr">
         <is>
-          <t>blblhh</t>
+          <t>kona143</t>
         </is>
       </c>
       <c r="B921" t="inlineStr">
         <is>
-          <t>01033446769</t>
+          <t>01021001916</t>
         </is>
       </c>
       <c r="C921" t="inlineStr">
         <is>
-          <t>304297</t>
+          <t>304260</t>
         </is>
       </c>
       <c r="D921" t="inlineStr">
         <is>
-          <t>Organic Traffic</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E921" t="inlineStr">
         <is>
-          <t>(referral)</t>
+          <t>[PF]전환_회원가입(유사)</t>
         </is>
       </c>
     </row>
     <row r="922">
       <c r="A922" t="inlineStr">
         <is>
-          <t>kk_3977730443</t>
+          <t>jsb0425</t>
         </is>
       </c>
       <c r="B922" t="inlineStr">
         <is>
-          <t>01064291828</t>
+          <t>01037883670</t>
         </is>
       </c>
       <c r="C922" t="inlineStr">
         <is>
-          <t>271278</t>
+          <t>104766</t>
         </is>
       </c>
       <c r="D922" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="E922" t="inlineStr">
         <is>
-          <t>naver_brandsearch_mobile</t>
+          <t>Direct</t>
         </is>
       </c>
     </row>
     <row r="923">
       <c r="A923" t="inlineStr">
         <is>
-          <t>jsb0425</t>
+          <t>kk_4840417532</t>
         </is>
       </c>
       <c r="B923" t="inlineStr">
         <is>
-          <t>01037883670</t>
+          <t>01053409288</t>
         </is>
       </c>
       <c r="C923" t="inlineStr">
         <is>
-          <t>104766</t>
+          <t>304147</t>
         </is>
       </c>
       <c r="D923" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>Official SNS</t>
         </is>
       </c>
       <c r="E923" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>EFW_04</t>
         </is>
       </c>
     </row>
     <row r="924">
       <c r="A924" t="inlineStr">
         <is>
-          <t>kk_4841278242</t>
+          <t>kk_2750710108</t>
         </is>
       </c>
       <c r="B924" t="inlineStr">
         <is>
-          <t>01046197965</t>
+          <t>01062707475</t>
         </is>
       </c>
       <c r="C924" t="inlineStr">
         <is>
-          <t>304190</t>
+          <t>207211</t>
         </is>
       </c>
       <c r="D924" t="inlineStr">
         <is>
-          <t>Organic Traffic</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="E924" t="inlineStr">
         <is>
-          <t>(referral)</t>
+          <t>Direct</t>
         </is>
       </c>
     </row>
     <row r="925">
       <c r="A925" t="inlineStr">
         <is>
-          <t>kk_4840417532</t>
+          <t>kk_3977730443</t>
         </is>
       </c>
       <c r="B925" t="inlineStr">
         <is>
-          <t>01053409288</t>
+          <t>01064291828</t>
         </is>
       </c>
       <c r="C925" t="inlineStr">
         <is>
-          <t>304147</t>
+          <t>271278</t>
         </is>
       </c>
       <c r="D925" t="inlineStr">
         <is>
-          <t>Official SNS</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E925" t="inlineStr">
         <is>
-          <t>EFW_04</t>
+          <t>naver_brandsearch_mobile</t>
         </is>
       </c>
     </row>
     <row r="926">
       <c r="A926" t="inlineStr">
         <is>
-          <t>kk_4840913383</t>
+          <t>kk_4841278242</t>
         </is>
       </c>
       <c r="B926" t="inlineStr">
         <is>
-          <t>01099887927</t>
+          <t>01046197965</t>
         </is>
       </c>
       <c r="C926" t="inlineStr">
         <is>
-          <t>304174</t>
+          <t>304190</t>
         </is>
       </c>
       <c r="D926" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>Organic Traffic</t>
         </is>
       </c>
       <c r="E926" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>(referral)</t>
         </is>
       </c>
     </row>
     <row r="927">
       <c r="A927" t="inlineStr">
         <is>
-          <t>kk_2750710108</t>
+          <t>kk_4840913383</t>
         </is>
       </c>
       <c r="B927" t="inlineStr">
         <is>
-          <t>01062707475</t>
+          <t>01099887927</t>
         </is>
       </c>
       <c r="C927" t="inlineStr">
         <is>
-          <t>207211</t>
+          <t>304174</t>
         </is>
       </c>
       <c r="D927" t="inlineStr">
@@ -25460,108 +25460,108 @@
     <row r="928">
       <c r="A928" t="inlineStr">
         <is>
-          <t>kk_4837971410</t>
+          <t>music214</t>
         </is>
       </c>
       <c r="B928" t="inlineStr">
         <is>
-          <t>01045750650</t>
+          <t>01031023988</t>
         </is>
       </c>
       <c r="C928" t="inlineStr">
         <is>
-          <t>304028</t>
+          <t>303965</t>
         </is>
       </c>
       <c r="D928" t="inlineStr">
         <is>
-          <t>Official SNS</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E928" t="inlineStr">
         <is>
-          <t>EFW_04</t>
+          <t>6968489536332</t>
         </is>
       </c>
     </row>
     <row r="929">
       <c r="A929" t="inlineStr">
         <is>
-          <t>music214</t>
+          <t>kk_4837971410</t>
         </is>
       </c>
       <c r="B929" t="inlineStr">
         <is>
-          <t>01031023988</t>
+          <t>01045750650</t>
         </is>
       </c>
       <c r="C929" t="inlineStr">
         <is>
-          <t>303965</t>
+          <t>304028</t>
         </is>
       </c>
       <c r="D929" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Official SNS</t>
         </is>
       </c>
       <c r="E929" t="inlineStr">
         <is>
-          <t>6968489536332</t>
+          <t>EFW_04</t>
         </is>
       </c>
     </row>
     <row r="930">
       <c r="A930" t="inlineStr">
         <is>
-          <t>kk_3465185882</t>
+          <t>kk_4835699259</t>
         </is>
       </c>
       <c r="B930" t="inlineStr">
         <is>
-          <t>01036194497</t>
+          <t>01045029445</t>
         </is>
       </c>
       <c r="C930" t="inlineStr">
         <is>
-          <t>243704</t>
+          <t>303881</t>
         </is>
       </c>
       <c r="D930" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E930" t="inlineStr">
         <is>
-          <t>KAKAO_alimtalk</t>
+          <t>6968489536332</t>
         </is>
       </c>
     </row>
     <row r="931">
       <c r="A931" t="inlineStr">
         <is>
-          <t>kk_4835699259</t>
+          <t>kk_3465185882</t>
         </is>
       </c>
       <c r="B931" t="inlineStr">
         <is>
-          <t>01045029445</t>
+          <t>01036194497</t>
         </is>
       </c>
       <c r="C931" t="inlineStr">
         <is>
-          <t>303881</t>
+          <t>243704</t>
         </is>
       </c>
       <c r="D931" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E931" t="inlineStr">
         <is>
-          <t>6968489536332</t>
+          <t>KAKAO_alimtalk</t>
         </is>
       </c>
     </row>
@@ -25622,17 +25622,17 @@
     <row r="934">
       <c r="A934" t="inlineStr">
         <is>
-          <t>kk_3776403631</t>
+          <t>kimchhgood</t>
         </is>
       </c>
       <c r="B934" t="inlineStr">
         <is>
-          <t>01034755755</t>
+          <t>01092133961</t>
         </is>
       </c>
       <c r="C934" t="inlineStr">
         <is>
-          <t>255908</t>
+          <t>53493</t>
         </is>
       </c>
       <c r="D934" t="inlineStr">
@@ -25642,24 +25642,24 @@
       </c>
       <c r="E934" t="inlineStr">
         <is>
-          <t>KAKAO_alimtalk</t>
+          <t>EDM_TOP</t>
         </is>
       </c>
     </row>
     <row r="935">
       <c r="A935" t="inlineStr">
         <is>
-          <t>kimchhgood</t>
+          <t>kk_3776403631</t>
         </is>
       </c>
       <c r="B935" t="inlineStr">
         <is>
-          <t>01092133961</t>
+          <t>01034755755</t>
         </is>
       </c>
       <c r="C935" t="inlineStr">
         <is>
-          <t>53493</t>
+          <t>255908</t>
         </is>
       </c>
       <c r="D935" t="inlineStr">
@@ -25669,51 +25669,51 @@
       </c>
       <c r="E935" t="inlineStr">
         <is>
-          <t>EDM_TOP</t>
+          <t>KAKAO_alimtalk</t>
         </is>
       </c>
     </row>
     <row r="936">
       <c r="A936" t="inlineStr">
         <is>
-          <t>kk_4651201605</t>
+          <t>kk_4846761310</t>
         </is>
       </c>
       <c r="B936" t="inlineStr">
         <is>
-          <t>01045489411</t>
+          <t>01091189951</t>
         </is>
       </c>
       <c r="C936" t="inlineStr">
         <is>
-          <t>293053</t>
+          <t>304464</t>
         </is>
       </c>
       <c r="D936" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E936" t="inlineStr">
         <is>
-          <t>EDM_0411</t>
+          <t>naver_brandsearch_mobile</t>
         </is>
       </c>
     </row>
     <row r="937">
       <c r="A937" t="inlineStr">
         <is>
-          <t>kk_4846761310</t>
+          <t>willper</t>
         </is>
       </c>
       <c r="B937" t="inlineStr">
         <is>
-          <t>01091189951</t>
+          <t>01085343440</t>
         </is>
       </c>
       <c r="C937" t="inlineStr">
         <is>
-          <t>304464</t>
+          <t>304408</t>
         </is>
       </c>
       <c r="D937" t="inlineStr">
@@ -25723,34 +25723,34 @@
       </c>
       <c r="E937" t="inlineStr">
         <is>
-          <t>naver_brandsearch_mobile</t>
+          <t>6968489536332</t>
         </is>
       </c>
     </row>
     <row r="938">
       <c r="A938" t="inlineStr">
         <is>
-          <t>willper</t>
+          <t>kk_4651201605</t>
         </is>
       </c>
       <c r="B938" t="inlineStr">
         <is>
-          <t>01085343440</t>
+          <t>01045489411</t>
         </is>
       </c>
       <c r="C938" t="inlineStr">
         <is>
-          <t>304408</t>
+          <t>293053</t>
         </is>
       </c>
       <c r="D938" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E938" t="inlineStr">
         <is>
-          <t>6968489536332</t>
+          <t>EDM_0411</t>
         </is>
       </c>
     </row>
@@ -25919,152 +25919,152 @@
     <row r="945">
       <c r="A945" t="inlineStr">
         <is>
-          <t>lolia875</t>
+          <t>kk_3241081989</t>
         </is>
       </c>
       <c r="B945" t="inlineStr">
         <is>
-          <t>01067138715</t>
+          <t>01072287165</t>
         </is>
       </c>
       <c r="C945" t="inlineStr">
         <is>
-          <t>161251</t>
+          <t>234608</t>
         </is>
       </c>
       <c r="D945" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E945" t="inlineStr">
         <is>
-          <t>6968489536332</t>
+          <t>KAKAO_alimtalk</t>
         </is>
       </c>
     </row>
     <row r="946">
       <c r="A946" t="inlineStr">
         <is>
-          <t>kk_3241081989</t>
+          <t>lolia875</t>
         </is>
       </c>
       <c r="B946" t="inlineStr">
         <is>
-          <t>01072287165</t>
+          <t>01067138715</t>
         </is>
       </c>
       <c r="C946" t="inlineStr">
         <is>
-          <t>234608</t>
+          <t>161251</t>
         </is>
       </c>
       <c r="D946" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E946" t="inlineStr">
         <is>
-          <t>KAKAO_alimtalk</t>
+          <t>6968489536332</t>
         </is>
       </c>
     </row>
     <row r="947">
       <c r="A947" t="inlineStr">
         <is>
-          <t>kk_3430866338</t>
+          <t>kk_4837152929</t>
         </is>
       </c>
       <c r="B947" t="inlineStr">
         <is>
-          <t>01026364692</t>
+          <t>01047050730</t>
         </is>
       </c>
       <c r="C947" t="inlineStr">
         <is>
-          <t>242249</t>
+          <t>303966</t>
         </is>
       </c>
       <c r="D947" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E947" t="inlineStr">
         <is>
-          <t>Email_mkt</t>
+          <t>6968489536332</t>
         </is>
       </c>
     </row>
     <row r="948">
       <c r="A948" t="inlineStr">
         <is>
-          <t>sjl4534</t>
+          <t>kk_4837595875</t>
         </is>
       </c>
       <c r="B948" t="inlineStr">
         <is>
-          <t>01028023660</t>
+          <t>01057852463</t>
         </is>
       </c>
       <c r="C948" t="inlineStr">
         <is>
-          <t>174607</t>
+          <t>304000</t>
         </is>
       </c>
       <c r="D948" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E948" t="inlineStr">
         <is>
-          <t>KAKAO_CH_MESSAGE_0409_EXCLUSIVE</t>
+          <t>6968489536332</t>
         </is>
       </c>
     </row>
     <row r="949">
       <c r="A949" t="inlineStr">
         <is>
-          <t>kk_4837595875</t>
+          <t>sjl4534</t>
         </is>
       </c>
       <c r="B949" t="inlineStr">
         <is>
-          <t>01057852463</t>
+          <t>01028023660</t>
         </is>
       </c>
       <c r="C949" t="inlineStr">
         <is>
-          <t>304000</t>
+          <t>174607</t>
         </is>
       </c>
       <c r="D949" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E949" t="inlineStr">
         <is>
-          <t>6968489536332</t>
+          <t>KAKAO_CH_MESSAGE_0409_EXCLUSIVE</t>
         </is>
       </c>
     </row>
     <row r="950">
       <c r="A950" t="inlineStr">
         <is>
-          <t>kk_4837152929</t>
+          <t>makaveli</t>
         </is>
       </c>
       <c r="B950" t="inlineStr">
         <is>
-          <t>01047050730</t>
+          <t>01086237086</t>
         </is>
       </c>
       <c r="C950" t="inlineStr">
         <is>
-          <t>303966</t>
+          <t>66164</t>
         </is>
       </c>
       <c r="D950" t="inlineStr">
@@ -26074,34 +26074,34 @@
       </c>
       <c r="E950" t="inlineStr">
         <is>
-          <t>6968489536332</t>
+          <t>naver_brandsearch_mobile</t>
         </is>
       </c>
     </row>
     <row r="951">
       <c r="A951" t="inlineStr">
         <is>
-          <t>makaveli</t>
+          <t>kk_3430866338</t>
         </is>
       </c>
       <c r="B951" t="inlineStr">
         <is>
-          <t>01086237086</t>
+          <t>01026364692</t>
         </is>
       </c>
       <c r="C951" t="inlineStr">
         <is>
-          <t>66164</t>
+          <t>242249</t>
         </is>
       </c>
       <c r="D951" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E951" t="inlineStr">
         <is>
-          <t>naver_brandsearch_mobile</t>
+          <t>Email_mkt</t>
         </is>
       </c>
     </row>
@@ -26189,17 +26189,17 @@
     <row r="955">
       <c r="A955" t="inlineStr">
         <is>
-          <t>kk_4612713787</t>
+          <t>kk_4703414773</t>
         </is>
       </c>
       <c r="B955" t="inlineStr">
         <is>
-          <t>01095027601</t>
+          <t>01093547510</t>
         </is>
       </c>
       <c r="C955" t="inlineStr">
         <is>
-          <t>290278</t>
+          <t>296108</t>
         </is>
       </c>
       <c r="D955" t="inlineStr">
@@ -26209,24 +26209,24 @@
       </c>
       <c r="E955" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0214_newyear</t>
+          <t>KAKAO_CH_MENU_0212_GOODBYEWINTER</t>
         </is>
       </c>
     </row>
     <row r="956">
       <c r="A956" t="inlineStr">
         <is>
-          <t>kk_4703414773</t>
+          <t>kk_4612713787</t>
         </is>
       </c>
       <c r="B956" t="inlineStr">
         <is>
-          <t>01093547510</t>
+          <t>01095027601</t>
         </is>
       </c>
       <c r="C956" t="inlineStr">
         <is>
-          <t>296108</t>
+          <t>290278</t>
         </is>
       </c>
       <c r="D956" t="inlineStr">
@@ -26236,105 +26236,105 @@
       </c>
       <c r="E956" t="inlineStr">
         <is>
-          <t>KAKAO_CH_MENU_0212_GOODBYEWINTER</t>
+          <t>LMS_ECOM_0214_newyear</t>
         </is>
       </c>
     </row>
     <row r="957">
       <c r="A957" t="inlineStr">
         <is>
-          <t>kk_2788668233</t>
+          <t>ch5115</t>
         </is>
       </c>
       <c r="B957" t="inlineStr">
         <is>
-          <t>01041696139</t>
+          <t>01084479339</t>
         </is>
       </c>
       <c r="C957" t="inlineStr">
         <is>
-          <t>210002</t>
+          <t>240557</t>
         </is>
       </c>
       <c r="D957" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="E957" t="inlineStr">
         <is>
-          <t>6968489536332</t>
+          <t>Direct</t>
         </is>
       </c>
     </row>
     <row r="958">
       <c r="A958" t="inlineStr">
         <is>
-          <t>imgain0422</t>
+          <t>kk_4845661756</t>
         </is>
       </c>
       <c r="B958" t="inlineStr">
         <is>
-          <t>01029135546</t>
+          <t>01095936572</t>
         </is>
       </c>
       <c r="C958" t="inlineStr">
         <is>
-          <t>181451</t>
+          <t>304422</t>
         </is>
       </c>
       <c r="D958" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E958" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>6968489536332</t>
         </is>
       </c>
     </row>
     <row r="959">
       <c r="A959" t="inlineStr">
         <is>
-          <t>chpuss74</t>
+          <t>kk_4846729102</t>
         </is>
       </c>
       <c r="B959" t="inlineStr">
         <is>
-          <t>01035361091</t>
+          <t>01084771303</t>
         </is>
       </c>
       <c r="C959" t="inlineStr">
         <is>
-          <t>154462</t>
+          <t>304461</t>
         </is>
       </c>
       <c r="D959" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E959" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>6968489536332</t>
         </is>
       </c>
     </row>
     <row r="960">
       <c r="A960" t="inlineStr">
         <is>
-          <t>ch5115</t>
+          <t>kk_3183517395</t>
         </is>
       </c>
       <c r="B960" t="inlineStr">
         <is>
-          <t>01084479339</t>
+          <t>01082019936</t>
         </is>
       </c>
       <c r="C960" t="inlineStr">
         <is>
-          <t>240557</t>
+          <t>228501</t>
         </is>
       </c>
       <c r="D960" t="inlineStr">
@@ -26351,243 +26351,243 @@
     <row r="961">
       <c r="A961" t="inlineStr">
         <is>
-          <t>kk_4846729102</t>
+          <t>imgain0422</t>
         </is>
       </c>
       <c r="B961" t="inlineStr">
         <is>
-          <t>01084771303</t>
+          <t>01029135546</t>
         </is>
       </c>
       <c r="C961" t="inlineStr">
         <is>
-          <t>304461</t>
+          <t>181451</t>
         </is>
       </c>
       <c r="D961" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="E961" t="inlineStr">
         <is>
-          <t>6968489536332</t>
+          <t>Direct</t>
         </is>
       </c>
     </row>
     <row r="962">
       <c r="A962" t="inlineStr">
         <is>
-          <t>kk_4845661756</t>
+          <t>chpuss74</t>
         </is>
       </c>
       <c r="B962" t="inlineStr">
         <is>
-          <t>01095936572</t>
+          <t>01035361091</t>
         </is>
       </c>
       <c r="C962" t="inlineStr">
         <is>
-          <t>304422</t>
+          <t>154462</t>
         </is>
       </c>
       <c r="D962" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="E962" t="inlineStr">
         <is>
-          <t>6968489536332</t>
+          <t>Direct</t>
         </is>
       </c>
     </row>
     <row r="963">
       <c r="A963" t="inlineStr">
         <is>
-          <t>kk_3183517395</t>
+          <t>kk_2788668233</t>
         </is>
       </c>
       <c r="B963" t="inlineStr">
         <is>
-          <t>01082019936</t>
+          <t>01041696139</t>
         </is>
       </c>
       <c r="C963" t="inlineStr">
         <is>
-          <t>228501</t>
+          <t>210002</t>
         </is>
       </c>
       <c r="D963" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E963" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>6968489536332</t>
         </is>
       </c>
     </row>
     <row r="964">
       <c r="A964" t="inlineStr">
         <is>
-          <t>kk_3242479813</t>
+          <t>kk_4844076820</t>
         </is>
       </c>
       <c r="B964" t="inlineStr">
         <is>
-          <t>01040431115</t>
+          <t>01091346366</t>
         </is>
       </c>
       <c r="C964" t="inlineStr">
         <is>
-          <t>234768</t>
+          <t>304343</t>
         </is>
       </c>
       <c r="D964" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E964" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0410exclusive2</t>
+          <t>6968489536332</t>
         </is>
       </c>
     </row>
     <row r="965">
       <c r="A965" t="inlineStr">
         <is>
-          <t>kjhk5404</t>
+          <t>kk_3650586439</t>
         </is>
       </c>
       <c r="B965" t="inlineStr">
         <is>
-          <t>01027390700</t>
+          <t>01029107056</t>
         </is>
       </c>
       <c r="C965" t="inlineStr">
         <is>
-          <t>280120</t>
+          <t>249153</t>
         </is>
       </c>
       <c r="D965" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="E965" t="inlineStr">
         <is>
-          <t>KAKAO_alimtalk</t>
+          <t>Direct</t>
         </is>
       </c>
     </row>
     <row r="966">
       <c r="A966" t="inlineStr">
         <is>
-          <t>kk_2775500473</t>
+          <t>goawind</t>
         </is>
       </c>
       <c r="B966" t="inlineStr">
         <is>
-          <t>01045659020</t>
+          <t>01032738938</t>
         </is>
       </c>
       <c r="C966" t="inlineStr">
         <is>
-          <t>209371</t>
+          <t>232021</t>
         </is>
       </c>
       <c r="D966" t="inlineStr">
         <is>
-          <t>Organic Traffic</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="E966" t="inlineStr">
         <is>
-          <t>(referral)</t>
+          <t>Direct</t>
         </is>
       </c>
     </row>
     <row r="967">
       <c r="A967" t="inlineStr">
         <is>
-          <t>kk_4844076820</t>
+          <t>kk_2775500473</t>
         </is>
       </c>
       <c r="B967" t="inlineStr">
         <is>
-          <t>01091346366</t>
+          <t>01045659020</t>
         </is>
       </c>
       <c r="C967" t="inlineStr">
         <is>
-          <t>304343</t>
+          <t>209371</t>
         </is>
       </c>
       <c r="D967" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Organic Traffic</t>
         </is>
       </c>
       <c r="E967" t="inlineStr">
         <is>
-          <t>6968489536332</t>
+          <t>(referral)</t>
         </is>
       </c>
     </row>
     <row r="968">
       <c r="A968" t="inlineStr">
         <is>
-          <t>goawind</t>
+          <t>kjhk5404</t>
         </is>
       </c>
       <c r="B968" t="inlineStr">
         <is>
-          <t>01032738938</t>
+          <t>01027390700</t>
         </is>
       </c>
       <c r="C968" t="inlineStr">
         <is>
-          <t>232021</t>
+          <t>280120</t>
         </is>
       </c>
       <c r="D968" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E968" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>KAKAO_alimtalk</t>
         </is>
       </c>
     </row>
     <row r="969">
       <c r="A969" t="inlineStr">
         <is>
-          <t>kk_3650586439</t>
+          <t>kk_3242479813</t>
         </is>
       </c>
       <c r="B969" t="inlineStr">
         <is>
-          <t>01029107056</t>
+          <t>01040431115</t>
         </is>
       </c>
       <c r="C969" t="inlineStr">
         <is>
-          <t>249153</t>
+          <t>234768</t>
         </is>
       </c>
       <c r="D969" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E969" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>LMS_ECOM_0410exclusive2</t>
         </is>
       </c>
     </row>
@@ -26648,54 +26648,54 @@
     <row r="972">
       <c r="A972" t="inlineStr">
         <is>
-          <t>w0309</t>
+          <t>kk_4840817001</t>
         </is>
       </c>
       <c r="B972" t="inlineStr">
         <is>
-          <t>01053481702</t>
+          <t>01085963383</t>
         </is>
       </c>
       <c r="C972" t="inlineStr">
         <is>
-          <t>126315</t>
+          <t>304168</t>
         </is>
       </c>
       <c r="D972" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E972" t="inlineStr">
         <is>
-          <t>Email_mkt</t>
+          <t>6968489536332</t>
         </is>
       </c>
     </row>
     <row r="973">
       <c r="A973" t="inlineStr">
         <is>
-          <t>kk_4840817001</t>
+          <t>w0309</t>
         </is>
       </c>
       <c r="B973" t="inlineStr">
         <is>
-          <t>01085963383</t>
+          <t>01053481702</t>
         </is>
       </c>
       <c r="C973" t="inlineStr">
         <is>
-          <t>304168</t>
+          <t>126315</t>
         </is>
       </c>
       <c r="D973" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E973" t="inlineStr">
         <is>
-          <t>6968489536332</t>
+          <t>Email_mkt</t>
         </is>
       </c>
     </row>
@@ -26729,17 +26729,17 @@
     <row r="975">
       <c r="A975" t="inlineStr">
         <is>
-          <t>eyounjoo</t>
+          <t>kk_3213636735</t>
         </is>
       </c>
       <c r="B975" t="inlineStr">
         <is>
-          <t>01036167949</t>
+          <t>01071338973</t>
         </is>
       </c>
       <c r="C975" t="inlineStr">
         <is>
-          <t>283223</t>
+          <t>232010</t>
         </is>
       </c>
       <c r="D975" t="inlineStr">
@@ -26749,51 +26749,51 @@
       </c>
       <c r="E975" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0410exclusive2</t>
+          <t>KAKAO_CH_MENU_0226_TRAILRUN</t>
         </is>
       </c>
     </row>
     <row r="976">
       <c r="A976" t="inlineStr">
         <is>
-          <t>z090909x</t>
+          <t>ssama</t>
         </is>
       </c>
       <c r="B976" t="inlineStr">
         <is>
-          <t>01092058111</t>
+          <t>01056271982</t>
         </is>
       </c>
       <c r="C976" t="inlineStr">
         <is>
-          <t>113003</t>
+          <t>47874</t>
         </is>
       </c>
       <c r="D976" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E976" t="inlineStr">
         <is>
-          <t>6968489536332</t>
+          <t>LMS_ECOM_0410exclusive2</t>
         </is>
       </c>
     </row>
     <row r="977">
       <c r="A977" t="inlineStr">
         <is>
-          <t>kk_3213636735</t>
+          <t>kk_4228106377</t>
         </is>
       </c>
       <c r="B977" t="inlineStr">
         <is>
-          <t>01071338973</t>
+          <t>01063165271</t>
         </is>
       </c>
       <c r="C977" t="inlineStr">
         <is>
-          <t>232010</t>
+          <t>273193</t>
         </is>
       </c>
       <c r="D977" t="inlineStr">
@@ -26803,7 +26803,7 @@
       </c>
       <c r="E977" t="inlineStr">
         <is>
-          <t>KAKAO_CH_MENU_0226_TRAILRUN</t>
+          <t>LMS_ECOM_0410exclusive2</t>
         </is>
       </c>
     </row>
@@ -26837,54 +26837,54 @@
     <row r="979">
       <c r="A979" t="inlineStr">
         <is>
-          <t>kk_4228106377</t>
+          <t>xoxoie2</t>
         </is>
       </c>
       <c r="B979" t="inlineStr">
         <is>
-          <t>01063165271</t>
+          <t>01043560834</t>
         </is>
       </c>
       <c r="C979" t="inlineStr">
         <is>
-          <t>273193</t>
+          <t>304072</t>
         </is>
       </c>
       <c r="D979" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Official SNS</t>
         </is>
       </c>
       <c r="E979" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0410exclusive2</t>
+          <t>EFW_04</t>
         </is>
       </c>
     </row>
     <row r="980">
       <c r="A980" t="inlineStr">
         <is>
-          <t>ssama</t>
+          <t>kk_4840045474</t>
         </is>
       </c>
       <c r="B980" t="inlineStr">
         <is>
-          <t>01056271982</t>
+          <t>01096310429</t>
         </is>
       </c>
       <c r="C980" t="inlineStr">
         <is>
-          <t>47874</t>
+          <t>304122</t>
         </is>
       </c>
       <c r="D980" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E980" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0410exclusive2</t>
+          <t>6968489536332</t>
         </is>
       </c>
     </row>
@@ -26918,17 +26918,17 @@
     <row r="982">
       <c r="A982" t="inlineStr">
         <is>
-          <t>kk_4840045474</t>
+          <t>z090909x</t>
         </is>
       </c>
       <c r="B982" t="inlineStr">
         <is>
-          <t>01096310429</t>
+          <t>01092058111</t>
         </is>
       </c>
       <c r="C982" t="inlineStr">
         <is>
-          <t>304122</t>
+          <t>113003</t>
         </is>
       </c>
       <c r="D982" t="inlineStr">
@@ -26945,98 +26945,98 @@
     <row r="983">
       <c r="A983" t="inlineStr">
         <is>
-          <t>xoxoie2</t>
+          <t>eyounjoo</t>
         </is>
       </c>
       <c r="B983" t="inlineStr">
         <is>
-          <t>01043560834</t>
+          <t>01036167949</t>
         </is>
       </c>
       <c r="C983" t="inlineStr">
         <is>
-          <t>304072</t>
+          <t>283223</t>
         </is>
       </c>
       <c r="D983" t="inlineStr">
         <is>
-          <t>Official SNS</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E983" t="inlineStr">
         <is>
-          <t>EFW_04</t>
+          <t>LMS_ECOM_0410exclusive2</t>
         </is>
       </c>
     </row>
     <row r="984">
       <c r="A984" t="inlineStr">
         <is>
-          <t>kk_3234166915</t>
+          <t>kk_4837597613</t>
         </is>
       </c>
       <c r="B984" t="inlineStr">
         <is>
-          <t>01082632995</t>
+          <t>01089218630</t>
         </is>
       </c>
       <c r="C984" t="inlineStr">
         <is>
-          <t>233887</t>
+          <t>304001</t>
         </is>
       </c>
       <c r="D984" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E984" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>KAKAO_CH_MESSAGE_0409_EXCLUSIVE</t>
         </is>
       </c>
     </row>
     <row r="985">
       <c r="A985" t="inlineStr">
         <is>
-          <t>scaler</t>
+          <t>kk_3234166915</t>
         </is>
       </c>
       <c r="B985" t="inlineStr">
         <is>
-          <t>01037090080</t>
+          <t>01082632995</t>
         </is>
       </c>
       <c r="C985" t="inlineStr">
         <is>
-          <t>178752</t>
+          <t>233887</t>
         </is>
       </c>
       <c r="D985" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="E985" t="inlineStr">
         <is>
-          <t>KAKAO_CH_MESSAGE_0409_EXCLUSIVE</t>
+          <t>Direct</t>
         </is>
       </c>
     </row>
     <row r="986">
       <c r="A986" t="inlineStr">
         <is>
-          <t>enel778</t>
+          <t>sjk6231</t>
         </is>
       </c>
       <c r="B986" t="inlineStr">
         <is>
-          <t>01086066364</t>
+          <t>01031985034</t>
         </is>
       </c>
       <c r="C986" t="inlineStr">
         <is>
-          <t>207732</t>
+          <t>281342</t>
         </is>
       </c>
       <c r="D986" t="inlineStr">
@@ -27053,17 +27053,17 @@
     <row r="987">
       <c r="A987" t="inlineStr">
         <is>
-          <t>kk_4837597613</t>
+          <t>scaler</t>
         </is>
       </c>
       <c r="B987" t="inlineStr">
         <is>
-          <t>01089218630</t>
+          <t>01037090080</t>
         </is>
       </c>
       <c r="C987" t="inlineStr">
         <is>
-          <t>304001</t>
+          <t>178752</t>
         </is>
       </c>
       <c r="D987" t="inlineStr">
@@ -27080,17 +27080,17 @@
     <row r="988">
       <c r="A988" t="inlineStr">
         <is>
-          <t>sjk6231</t>
+          <t>enel778</t>
         </is>
       </c>
       <c r="B988" t="inlineStr">
         <is>
-          <t>01031985034</t>
+          <t>01086066364</t>
         </is>
       </c>
       <c r="C988" t="inlineStr">
         <is>
-          <t>281342</t>
+          <t>207732</t>
         </is>
       </c>
       <c r="D988" t="inlineStr">
@@ -27107,27 +27107,27 @@
     <row r="989">
       <c r="A989" t="inlineStr">
         <is>
-          <t>zodiacz</t>
+          <t>kk_4444429966</t>
         </is>
       </c>
       <c r="B989" t="inlineStr">
         <is>
-          <t>01093671032</t>
+          <t>01032219702</t>
         </is>
       </c>
       <c r="C989" t="inlineStr">
         <is>
-          <t>108304</t>
+          <t>282222</t>
         </is>
       </c>
       <c r="D989" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="E989" t="inlineStr">
         <is>
-          <t>pmax</t>
+          <t>Direct</t>
         </is>
       </c>
     </row>
@@ -27161,27 +27161,27 @@
     <row r="991">
       <c r="A991" t="inlineStr">
         <is>
-          <t>kk_4444429966</t>
+          <t>zodiacz</t>
         </is>
       </c>
       <c r="B991" t="inlineStr">
         <is>
-          <t>01032219702</t>
+          <t>01093671032</t>
         </is>
       </c>
       <c r="C991" t="inlineStr">
         <is>
-          <t>282222</t>
+          <t>108304</t>
         </is>
       </c>
       <c r="D991" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E991" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>pmax</t>
         </is>
       </c>
     </row>
@@ -27215,54 +27215,54 @@
     <row r="993">
       <c r="A993" t="inlineStr">
         <is>
-          <t>mse001</t>
+          <t>kk_4218204827</t>
         </is>
       </c>
       <c r="B993" t="inlineStr">
         <is>
-          <t>01085185510</t>
+          <t>01023704903</t>
         </is>
       </c>
       <c r="C993" t="inlineStr">
         <is>
-          <t>227227</t>
+          <t>272698</t>
         </is>
       </c>
       <c r="D993" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="E993" t="inlineStr">
         <is>
-          <t>KAKAO_alimtalk</t>
+          <t>Direct</t>
         </is>
       </c>
     </row>
     <row r="994">
       <c r="A994" t="inlineStr">
         <is>
-          <t>kk_4218204827</t>
+          <t>mse001</t>
         </is>
       </c>
       <c r="B994" t="inlineStr">
         <is>
-          <t>01023704903</t>
+          <t>01085185510</t>
         </is>
       </c>
       <c r="C994" t="inlineStr">
         <is>
-          <t>272698</t>
+          <t>227227</t>
         </is>
       </c>
       <c r="D994" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E994" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>KAKAO_alimtalk</t>
         </is>
       </c>
     </row>
@@ -27296,71 +27296,71 @@
     <row r="996">
       <c r="A996" t="inlineStr">
         <is>
-          <t>kk_3169777000</t>
+          <t>kk_2768186596</t>
         </is>
       </c>
       <c r="B996" t="inlineStr">
         <is>
-          <t>01089348462</t>
+          <t>01029241198</t>
         </is>
       </c>
       <c r="C996" t="inlineStr">
         <is>
-          <t>224876</t>
+          <t>208962</t>
         </is>
       </c>
       <c r="D996" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E996" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>KAKAO_alimtalk</t>
         </is>
       </c>
     </row>
     <row r="997">
       <c r="A997" t="inlineStr">
         <is>
-          <t>kk_4844817541</t>
+          <t>kk_3169777000</t>
         </is>
       </c>
       <c r="B997" t="inlineStr">
         <is>
-          <t>01046631832</t>
+          <t>01089348462</t>
         </is>
       </c>
       <c r="C997" t="inlineStr">
         <is>
-          <t>304380</t>
+          <t>224876</t>
         </is>
       </c>
       <c r="D997" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="E997" t="inlineStr">
         <is>
-          <t>[PF]전환_회원가입(유사)</t>
+          <t>Direct</t>
         </is>
       </c>
     </row>
     <row r="998">
       <c r="A998" t="inlineStr">
         <is>
-          <t>kk_2768186596</t>
+          <t>kk_4375003446</t>
         </is>
       </c>
       <c r="B998" t="inlineStr">
         <is>
-          <t>01029241198</t>
+          <t>01087457282</t>
         </is>
       </c>
       <c r="C998" t="inlineStr">
         <is>
-          <t>208962</t>
+          <t>280131</t>
         </is>
       </c>
       <c r="D998" t="inlineStr">
@@ -27370,159 +27370,159 @@
       </c>
       <c r="E998" t="inlineStr">
         <is>
-          <t>KAKAO_alimtalk</t>
+          <t>LMS_ECOM_0410exclusive2</t>
         </is>
       </c>
     </row>
     <row r="999">
       <c r="A999" t="inlineStr">
         <is>
-          <t>kk_4375003446</t>
+          <t>kk_4844817541</t>
         </is>
       </c>
       <c r="B999" t="inlineStr">
         <is>
-          <t>01087457282</t>
+          <t>01046631832</t>
         </is>
       </c>
       <c r="C999" t="inlineStr">
         <is>
-          <t>280131</t>
+          <t>304380</t>
         </is>
       </c>
       <c r="D999" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E999" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0410exclusive2</t>
+          <t>[PF]전환_회원가입(유사)</t>
         </is>
       </c>
     </row>
     <row r="1000">
       <c r="A1000" t="inlineStr">
         <is>
-          <t>kk_3444865211</t>
+          <t>kk_3688034999</t>
         </is>
       </c>
       <c r="B1000" t="inlineStr">
         <is>
-          <t>01021964871</t>
+          <t>01025408262</t>
         </is>
       </c>
       <c r="C1000" t="inlineStr">
         <is>
-          <t>242799</t>
+          <t>250755</t>
         </is>
       </c>
       <c r="D1000" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E1000" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>KAKAO_alimtalk</t>
         </is>
       </c>
     </row>
     <row r="1001">
       <c r="A1001" t="inlineStr">
         <is>
-          <t>kk_3688034999</t>
+          <t>xuswldls</t>
         </is>
       </c>
       <c r="B1001" t="inlineStr">
         <is>
-          <t>01025408262</t>
+          <t>01027349414</t>
         </is>
       </c>
       <c r="C1001" t="inlineStr">
         <is>
-          <t>250755</t>
+          <t>133308</t>
         </is>
       </c>
       <c r="D1001" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="E1001" t="inlineStr">
         <is>
-          <t>KAKAO_alimtalk</t>
+          <t>Direct</t>
         </is>
       </c>
     </row>
     <row r="1002">
       <c r="A1002" t="inlineStr">
         <is>
-          <t>kk_4247630261</t>
+          <t>kk_3444865211</t>
         </is>
       </c>
       <c r="B1002" t="inlineStr">
         <is>
-          <t>01091437323</t>
+          <t>01021964871</t>
         </is>
       </c>
       <c r="C1002" t="inlineStr">
         <is>
-          <t>274140</t>
+          <t>242799</t>
         </is>
       </c>
       <c r="D1002" t="inlineStr">
         <is>
-          <t>Organic Traffic</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="E1002" t="inlineStr">
         <is>
-          <t>(referral)</t>
+          <t>Direct</t>
         </is>
       </c>
     </row>
     <row r="1003">
       <c r="A1003" t="inlineStr">
         <is>
-          <t>xuswldls</t>
+          <t>kk_4247630261</t>
         </is>
       </c>
       <c r="B1003" t="inlineStr">
         <is>
-          <t>01027349414</t>
+          <t>01091437323</t>
         </is>
       </c>
       <c r="C1003" t="inlineStr">
         <is>
-          <t>133308</t>
+          <t>274140</t>
         </is>
       </c>
       <c r="D1003" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>Organic Traffic</t>
         </is>
       </c>
       <c r="E1003" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>(referral)</t>
         </is>
       </c>
     </row>
     <row r="1004">
       <c r="A1004" t="inlineStr">
         <is>
-          <t>ohsm0065</t>
+          <t>dongheon20</t>
         </is>
       </c>
       <c r="B1004" t="inlineStr">
         <is>
-          <t>01056170065</t>
+          <t>01052298928</t>
         </is>
       </c>
       <c r="C1004" t="inlineStr">
         <is>
-          <t>74567</t>
+          <t>155362</t>
         </is>
       </c>
       <c r="D1004" t="inlineStr">
@@ -27532,34 +27532,34 @@
       </c>
       <c r="E1004" t="inlineStr">
         <is>
-          <t>[PF]트래픽_유사+관심사</t>
+          <t>6968489536332</t>
         </is>
       </c>
     </row>
     <row r="1005">
       <c r="A1005" t="inlineStr">
         <is>
-          <t>dongheon20</t>
+          <t>kk_4472536591</t>
         </is>
       </c>
       <c r="B1005" t="inlineStr">
         <is>
-          <t>01052298928</t>
+          <t>01037057526</t>
         </is>
       </c>
       <c r="C1005" t="inlineStr">
         <is>
-          <t>155362</t>
+          <t>283897</t>
         </is>
       </c>
       <c r="D1005" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E1005" t="inlineStr">
         <is>
-          <t>6968489536332</t>
+          <t>KAKAO_alimtalk</t>
         </is>
       </c>
     </row>
@@ -27593,71 +27593,71 @@
     <row r="1007">
       <c r="A1007" t="inlineStr">
         <is>
-          <t>kk_4472536591</t>
+          <t>ohsm0065</t>
         </is>
       </c>
       <c r="B1007" t="inlineStr">
         <is>
-          <t>01037057526</t>
+          <t>01056170065</t>
         </is>
       </c>
       <c r="C1007" t="inlineStr">
         <is>
-          <t>283897</t>
+          <t>74567</t>
         </is>
       </c>
       <c r="D1007" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E1007" t="inlineStr">
         <is>
-          <t>KAKAO_alimtalk</t>
+          <t>[PF]트래픽_유사+관심사</t>
         </is>
       </c>
     </row>
     <row r="1008">
       <c r="A1008" t="inlineStr">
         <is>
-          <t>kk_3858585698</t>
+          <t>jobguidance</t>
         </is>
       </c>
       <c r="B1008" t="inlineStr">
         <is>
-          <t>01092163429</t>
+          <t>01026756920</t>
         </is>
       </c>
       <c r="C1008" t="inlineStr">
         <is>
-          <t>265508</t>
+          <t>134664</t>
         </is>
       </c>
       <c r="D1008" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="E1008" t="inlineStr">
         <is>
-          <t>KAKAO_alimtalk</t>
+          <t>Direct</t>
         </is>
       </c>
     </row>
     <row r="1009">
       <c r="A1009" t="inlineStr">
         <is>
-          <t>jobguidance</t>
+          <t>escalater</t>
         </is>
       </c>
       <c r="B1009" t="inlineStr">
         <is>
-          <t>01026756920</t>
+          <t>01090911461</t>
         </is>
       </c>
       <c r="C1009" t="inlineStr">
         <is>
-          <t>134664</t>
+          <t>240051</t>
         </is>
       </c>
       <c r="D1009" t="inlineStr">
@@ -27674,17 +27674,17 @@
     <row r="1010">
       <c r="A1010" t="inlineStr">
         <is>
-          <t>kk_3837527580</t>
+          <t>nesto1</t>
         </is>
       </c>
       <c r="B1010" t="inlineStr">
         <is>
-          <t>01084311738</t>
+          <t>01056603953</t>
         </is>
       </c>
       <c r="C1010" t="inlineStr">
         <is>
-          <t>264113</t>
+          <t>125251</t>
         </is>
       </c>
       <c r="D1010" t="inlineStr">
@@ -27694,34 +27694,34 @@
       </c>
       <c r="E1010" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0410exclusive2</t>
+          <t>KAKAO_alimtalk</t>
         </is>
       </c>
     </row>
     <row r="1011">
       <c r="A1011" t="inlineStr">
         <is>
-          <t>escalater</t>
+          <t>kk_3837527580</t>
         </is>
       </c>
       <c r="B1011" t="inlineStr">
         <is>
-          <t>01090911461</t>
+          <t>01084311738</t>
         </is>
       </c>
       <c r="C1011" t="inlineStr">
         <is>
-          <t>240051</t>
+          <t>264113</t>
         </is>
       </c>
       <c r="D1011" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E1011" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>LMS_ECOM_0410exclusive2</t>
         </is>
       </c>
     </row>
@@ -27755,17 +27755,17 @@
     <row r="1013">
       <c r="A1013" t="inlineStr">
         <is>
-          <t>nesto1</t>
+          <t>kk_3858585698</t>
         </is>
       </c>
       <c r="B1013" t="inlineStr">
         <is>
-          <t>01056603953</t>
+          <t>01092163429</t>
         </is>
       </c>
       <c r="C1013" t="inlineStr">
         <is>
-          <t>125251</t>
+          <t>265508</t>
         </is>
       </c>
       <c r="D1013" t="inlineStr">
@@ -27782,27 +27782,27 @@
     <row r="1014">
       <c r="A1014" t="inlineStr">
         <is>
-          <t>kk_3013902343</t>
+          <t>kk_3185867832</t>
         </is>
       </c>
       <c r="B1014" t="inlineStr">
         <is>
-          <t>01051802326</t>
+          <t>01022086508</t>
         </is>
       </c>
       <c r="C1014" t="inlineStr">
         <is>
-          <t>219219</t>
+          <t>229863</t>
         </is>
       </c>
       <c r="D1014" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E1014" t="inlineStr">
         <is>
-          <t>6968489536332</t>
+          <t>LMS_ECOM_0410exclusive2</t>
         </is>
       </c>
     </row>
@@ -27836,44 +27836,44 @@
     <row r="1016">
       <c r="A1016" t="inlineStr">
         <is>
-          <t>kk_4338209948</t>
+          <t>kk_4840061178</t>
         </is>
       </c>
       <c r="B1016" t="inlineStr">
         <is>
-          <t>01088132379</t>
+          <t>01082357895</t>
         </is>
       </c>
       <c r="C1016" t="inlineStr">
         <is>
-          <t>278781</t>
+          <t>304124</t>
         </is>
       </c>
       <c r="D1016" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Awareness</t>
         </is>
       </c>
       <c r="E1016" t="inlineStr">
         <is>
-          <t>KAKAO_alimtalk</t>
+          <t>benz_running_program_2026_coupon</t>
         </is>
       </c>
     </row>
     <row r="1017">
       <c r="A1017" t="inlineStr">
         <is>
-          <t>kk_4523594127</t>
+          <t>kk_2940110361</t>
         </is>
       </c>
       <c r="B1017" t="inlineStr">
         <is>
-          <t>01085735215</t>
+          <t>01035353200</t>
         </is>
       </c>
       <c r="C1017" t="inlineStr">
         <is>
-          <t>286358</t>
+          <t>216362</t>
         </is>
       </c>
       <c r="D1017" t="inlineStr">
@@ -27890,17 +27890,17 @@
     <row r="1018">
       <c r="A1018" t="inlineStr">
         <is>
-          <t>kk_4517851709</t>
+          <t>kk_4338209948</t>
         </is>
       </c>
       <c r="B1018" t="inlineStr">
         <is>
-          <t>01066445714</t>
+          <t>01088132379</t>
         </is>
       </c>
       <c r="C1018" t="inlineStr">
         <is>
-          <t>286074</t>
+          <t>278781</t>
         </is>
       </c>
       <c r="D1018" t="inlineStr">
@@ -27910,78 +27910,78 @@
       </c>
       <c r="E1018" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0410exclusive2</t>
+          <t>KAKAO_alimtalk</t>
         </is>
       </c>
     </row>
     <row r="1019">
       <c r="A1019" t="inlineStr">
         <is>
-          <t>kk_4467707148</t>
+          <t>kk_3933534683</t>
         </is>
       </c>
       <c r="B1019" t="inlineStr">
         <is>
-          <t>01030843332</t>
+          <t>01030153796</t>
         </is>
       </c>
       <c r="C1019" t="inlineStr">
         <is>
-          <t>283560</t>
+          <t>269069</t>
         </is>
       </c>
       <c r="D1019" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="E1019" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0410exclusive2</t>
+          <t>Direct</t>
         </is>
       </c>
     </row>
     <row r="1020">
       <c r="A1020" t="inlineStr">
         <is>
-          <t>kk_3933534683</t>
+          <t>seul6169</t>
         </is>
       </c>
       <c r="B1020" t="inlineStr">
         <is>
-          <t>01030153796</t>
+          <t>01066116699</t>
         </is>
       </c>
       <c r="C1020" t="inlineStr">
         <is>
-          <t>269069</t>
+          <t>234239</t>
         </is>
       </c>
       <c r="D1020" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E1020" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>KAKAO_alimtalk</t>
         </is>
       </c>
     </row>
     <row r="1021">
       <c r="A1021" t="inlineStr">
         <is>
-          <t>seul6169</t>
+          <t>aya6969</t>
         </is>
       </c>
       <c r="B1021" t="inlineStr">
         <is>
-          <t>01066116699</t>
+          <t>01076590009</t>
         </is>
       </c>
       <c r="C1021" t="inlineStr">
         <is>
-          <t>234239</t>
+          <t>162562</t>
         </is>
       </c>
       <c r="D1021" t="inlineStr">
@@ -27991,24 +27991,24 @@
       </c>
       <c r="E1021" t="inlineStr">
         <is>
-          <t>KAKAO_alimtalk</t>
+          <t>LMS_ECOM_0410exclusive2</t>
         </is>
       </c>
     </row>
     <row r="1022">
       <c r="A1022" t="inlineStr">
         <is>
-          <t>mansoogi</t>
+          <t>kk_4467707148</t>
         </is>
       </c>
       <c r="B1022" t="inlineStr">
         <is>
-          <t>01093240897</t>
+          <t>01030843332</t>
         </is>
       </c>
       <c r="C1022" t="inlineStr">
         <is>
-          <t>25243</t>
+          <t>283560</t>
         </is>
       </c>
       <c r="D1022" t="inlineStr">
@@ -28025,17 +28025,17 @@
     <row r="1023">
       <c r="A1023" t="inlineStr">
         <is>
-          <t>aya6969</t>
+          <t>mansoogi</t>
         </is>
       </c>
       <c r="B1023" t="inlineStr">
         <is>
-          <t>01076590009</t>
+          <t>01093240897</t>
         </is>
       </c>
       <c r="C1023" t="inlineStr">
         <is>
-          <t>162562</t>
+          <t>25243</t>
         </is>
       </c>
       <c r="D1023" t="inlineStr">
@@ -28052,44 +28052,44 @@
     <row r="1024">
       <c r="A1024" t="inlineStr">
         <is>
-          <t>kk_4840061178</t>
+          <t>kk_4523594127</t>
         </is>
       </c>
       <c r="B1024" t="inlineStr">
         <is>
-          <t>01082357895</t>
+          <t>01085735215</t>
         </is>
       </c>
       <c r="C1024" t="inlineStr">
         <is>
-          <t>304124</t>
+          <t>286358</t>
         </is>
       </c>
       <c r="D1024" t="inlineStr">
         <is>
-          <t>Awareness</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E1024" t="inlineStr">
         <is>
-          <t>benz_running_program_2026_coupon</t>
+          <t>LMS_ECOM_0410exclusive2</t>
         </is>
       </c>
     </row>
     <row r="1025">
       <c r="A1025" t="inlineStr">
         <is>
-          <t>kk_3185867832</t>
+          <t>kk_4517851709</t>
         </is>
       </c>
       <c r="B1025" t="inlineStr">
         <is>
-          <t>01022086508</t>
+          <t>01066445714</t>
         </is>
       </c>
       <c r="C1025" t="inlineStr">
         <is>
-          <t>229863</t>
+          <t>286074</t>
         </is>
       </c>
       <c r="D1025" t="inlineStr">
@@ -28106,54 +28106,54 @@
     <row r="1026">
       <c r="A1026" t="inlineStr">
         <is>
-          <t>kk_2940110361</t>
+          <t>kk_3013902343</t>
         </is>
       </c>
       <c r="B1026" t="inlineStr">
         <is>
-          <t>01035353200</t>
+          <t>01051802326</t>
         </is>
       </c>
       <c r="C1026" t="inlineStr">
         <is>
-          <t>216362</t>
+          <t>219219</t>
         </is>
       </c>
       <c r="D1026" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E1026" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0410exclusive2</t>
+          <t>6968489536332</t>
         </is>
       </c>
     </row>
     <row r="1027">
       <c r="A1027" t="inlineStr">
         <is>
-          <t>kk_4351086966</t>
+          <t>kk_3155938902</t>
         </is>
       </c>
       <c r="B1027" t="inlineStr">
         <is>
-          <t>01042088262</t>
+          <t>01098557018</t>
         </is>
       </c>
       <c r="C1027" t="inlineStr">
         <is>
-          <t>279266</t>
+          <t>223731</t>
         </is>
       </c>
       <c r="D1027" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E1027" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>KAKAO_CH_MESSAGE_0409_HIKE365SUMMER</t>
         </is>
       </c>
     </row>
@@ -28187,71 +28187,71 @@
     <row r="1029">
       <c r="A1029" t="inlineStr">
         <is>
-          <t>kk_3154612153</t>
+          <t>kk_3373939453</t>
         </is>
       </c>
       <c r="B1029" t="inlineStr">
         <is>
-          <t>01056681753</t>
+          <t>01020110604</t>
         </is>
       </c>
       <c r="C1029" t="inlineStr">
         <is>
-          <t>223664</t>
+          <t>240269</t>
         </is>
       </c>
       <c r="D1029" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E1029" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>KAKAO_CH_MESSAGE_0409_EXCLUSIVE</t>
         </is>
       </c>
     </row>
     <row r="1030">
       <c r="A1030" t="inlineStr">
         <is>
-          <t>kk_4837943303</t>
+          <t>kk_3665803645</t>
         </is>
       </c>
       <c r="B1030" t="inlineStr">
         <is>
-          <t>01054817243</t>
+          <t>01095549123</t>
         </is>
       </c>
       <c r="C1030" t="inlineStr">
         <is>
-          <t>304025</t>
+          <t>249835</t>
         </is>
       </c>
       <c r="D1030" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E1030" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>KAKAO_CH_MESSAGE_0409_EXCLUSIVE</t>
         </is>
       </c>
     </row>
     <row r="1031">
       <c r="A1031" t="inlineStr">
         <is>
-          <t>kk_3155938902</t>
+          <t>kk_3638512879</t>
         </is>
       </c>
       <c r="B1031" t="inlineStr">
         <is>
-          <t>01098557018</t>
+          <t>01053330589</t>
         </is>
       </c>
       <c r="C1031" t="inlineStr">
         <is>
-          <t>223731</t>
+          <t>248574</t>
         </is>
       </c>
       <c r="D1031" t="inlineStr">
@@ -28268,44 +28268,44 @@
     <row r="1032">
       <c r="A1032" t="inlineStr">
         <is>
-          <t>kk_3638512879</t>
+          <t>kk_3154612153</t>
         </is>
       </c>
       <c r="B1032" t="inlineStr">
         <is>
-          <t>01053330589</t>
+          <t>01056681753</t>
         </is>
       </c>
       <c r="C1032" t="inlineStr">
         <is>
-          <t>248574</t>
+          <t>223664</t>
         </is>
       </c>
       <c r="D1032" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="E1032" t="inlineStr">
         <is>
-          <t>KAKAO_CH_MESSAGE_0409_HIKE365SUMMER</t>
+          <t>Direct</t>
         </is>
       </c>
     </row>
     <row r="1033">
       <c r="A1033" t="inlineStr">
         <is>
-          <t>kk_3665803645</t>
+          <t>bbluesea</t>
         </is>
       </c>
       <c r="B1033" t="inlineStr">
         <is>
-          <t>01095549123</t>
+          <t>01076473601</t>
         </is>
       </c>
       <c r="C1033" t="inlineStr">
         <is>
-          <t>249835</t>
+          <t>152067</t>
         </is>
       </c>
       <c r="D1033" t="inlineStr">
@@ -28315,51 +28315,51 @@
       </c>
       <c r="E1033" t="inlineStr">
         <is>
-          <t>KAKAO_CH_MESSAGE_0409_EXCLUSIVE</t>
+          <t>KAKAO_CH_MENU_260406_LIGHTJACKET</t>
         </is>
       </c>
     </row>
     <row r="1034">
       <c r="A1034" t="inlineStr">
         <is>
-          <t>jhmin000</t>
+          <t>kk_4351086966</t>
         </is>
       </c>
       <c r="B1034" t="inlineStr">
         <is>
-          <t>01086241606</t>
+          <t>01042088262</t>
         </is>
       </c>
       <c r="C1034" t="inlineStr">
         <is>
-          <t>201165</t>
+          <t>279266</t>
         </is>
       </c>
       <c r="D1034" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="E1034" t="inlineStr">
         <is>
-          <t>KAKAO_CH_MESSAGE_0409_HIKE365SUMMER</t>
+          <t>Direct</t>
         </is>
       </c>
     </row>
     <row r="1035">
       <c r="A1035" t="inlineStr">
         <is>
-          <t>kk_4726499171</t>
+          <t>jhmin000</t>
         </is>
       </c>
       <c r="B1035" t="inlineStr">
         <is>
-          <t>01093851013</t>
+          <t>01086241606</t>
         </is>
       </c>
       <c r="C1035" t="inlineStr">
         <is>
-          <t>297987</t>
+          <t>201165</t>
         </is>
       </c>
       <c r="D1035" t="inlineStr">
@@ -28376,17 +28376,17 @@
     <row r="1036">
       <c r="A1036" t="inlineStr">
         <is>
-          <t>bbluesea</t>
+          <t>kk_4726499171</t>
         </is>
       </c>
       <c r="B1036" t="inlineStr">
         <is>
-          <t>01076473601</t>
+          <t>01093851013</t>
         </is>
       </c>
       <c r="C1036" t="inlineStr">
         <is>
-          <t>152067</t>
+          <t>297987</t>
         </is>
       </c>
       <c r="D1036" t="inlineStr">
@@ -28396,142 +28396,142 @@
       </c>
       <c r="E1036" t="inlineStr">
         <is>
-          <t>KAKAO_CH_MENU_260406_LIGHTJACKET</t>
+          <t>KAKAO_CH_MESSAGE_0409_HIKE365SUMMER</t>
         </is>
       </c>
     </row>
     <row r="1037">
       <c r="A1037" t="inlineStr">
         <is>
-          <t>kk_3373939453</t>
+          <t>boram1991</t>
         </is>
       </c>
       <c r="B1037" t="inlineStr">
         <is>
-          <t>01020110604</t>
+          <t>01023431078</t>
         </is>
       </c>
       <c r="C1037" t="inlineStr">
         <is>
-          <t>240269</t>
+          <t>119498</t>
         </is>
       </c>
       <c r="D1037" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E1037" t="inlineStr">
         <is>
-          <t>KAKAO_CH_MESSAGE_0409_EXCLUSIVE</t>
+          <t>6968489536332</t>
         </is>
       </c>
     </row>
     <row r="1038">
       <c r="A1038" t="inlineStr">
         <is>
-          <t>boram1991</t>
+          <t>kk_4837943303</t>
         </is>
       </c>
       <c r="B1038" t="inlineStr">
         <is>
-          <t>01023431078</t>
+          <t>01054817243</t>
         </is>
       </c>
       <c r="C1038" t="inlineStr">
         <is>
-          <t>119498</t>
+          <t>304025</t>
         </is>
       </c>
       <c r="D1038" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="E1038" t="inlineStr">
         <is>
-          <t>6968489536332</t>
+          <t>Direct</t>
         </is>
       </c>
     </row>
     <row r="1039">
       <c r="A1039" t="inlineStr">
         <is>
-          <t>wns1118</t>
+          <t>pearpear</t>
         </is>
       </c>
       <c r="B1039" t="inlineStr">
         <is>
-          <t>01090185590</t>
+          <t>01048098405</t>
         </is>
       </c>
       <c r="C1039" t="inlineStr">
         <is>
-          <t>303893</t>
+          <t>29743</t>
         </is>
       </c>
       <c r="D1039" t="inlineStr">
         <is>
-          <t>Organic Traffic</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E1039" t="inlineStr">
         <is>
-          <t>(organic)</t>
+          <t>Email_mkt</t>
         </is>
       </c>
     </row>
     <row r="1040">
       <c r="A1040" t="inlineStr">
         <is>
-          <t>kk_3805755788</t>
+          <t>jeen1228</t>
         </is>
       </c>
       <c r="B1040" t="inlineStr">
         <is>
-          <t>01092305284</t>
+          <t>01033512662</t>
         </is>
       </c>
       <c r="C1040" t="inlineStr">
         <is>
-          <t>260128</t>
+          <t>223087</t>
         </is>
       </c>
       <c r="D1040" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Organic Traffic</t>
         </is>
       </c>
       <c r="E1040" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>(organic)</t>
         </is>
       </c>
     </row>
     <row r="1041">
       <c r="A1041" t="inlineStr">
         <is>
-          <t>pearpear</t>
+          <t>wns1118</t>
         </is>
       </c>
       <c r="B1041" t="inlineStr">
         <is>
-          <t>01048098405</t>
+          <t>01090185590</t>
         </is>
       </c>
       <c r="C1041" t="inlineStr">
         <is>
-          <t>29743</t>
+          <t>303893</t>
         </is>
       </c>
       <c r="D1041" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Organic Traffic</t>
         </is>
       </c>
       <c r="E1041" t="inlineStr">
         <is>
-          <t>Email_mkt</t>
+          <t>(organic)</t>
         </is>
       </c>
     </row>
@@ -28592,27 +28592,27 @@
     <row r="1044">
       <c r="A1044" t="inlineStr">
         <is>
-          <t>jeen1228</t>
+          <t>kk_3805755788</t>
         </is>
       </c>
       <c r="B1044" t="inlineStr">
         <is>
-          <t>01033512662</t>
+          <t>01092305284</t>
         </is>
       </c>
       <c r="C1044" t="inlineStr">
         <is>
-          <t>223087</t>
+          <t>260128</t>
         </is>
       </c>
       <c r="D1044" t="inlineStr">
         <is>
-          <t>Organic Traffic</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E1044" t="inlineStr">
         <is>
-          <t>(organic)</t>
+          <t>Owned Channel</t>
         </is>
       </c>
     </row>
@@ -28673,44 +28673,44 @@
     <row r="1047">
       <c r="A1047" t="inlineStr">
         <is>
-          <t>pentagram</t>
+          <t>dltndgy99</t>
         </is>
       </c>
       <c r="B1047" t="inlineStr">
         <is>
-          <t>01093327353</t>
+          <t>01024587982</t>
         </is>
       </c>
       <c r="C1047" t="inlineStr">
         <is>
-          <t>131085</t>
+          <t>156217</t>
         </is>
       </c>
       <c r="D1047" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E1047" t="inlineStr">
         <is>
-          <t>KAKAO_alimtalk</t>
+          <t>naver_brandsearch_mobile</t>
         </is>
       </c>
     </row>
     <row r="1048">
       <c r="A1048" t="inlineStr">
         <is>
-          <t>dltndgy99</t>
+          <t>kk_2807863527</t>
         </is>
       </c>
       <c r="B1048" t="inlineStr">
         <is>
-          <t>01024587982</t>
+          <t>01042669625</t>
         </is>
       </c>
       <c r="C1048" t="inlineStr">
         <is>
-          <t>156217</t>
+          <t>211605</t>
         </is>
       </c>
       <c r="D1048" t="inlineStr">
@@ -28720,34 +28720,34 @@
       </c>
       <c r="E1048" t="inlineStr">
         <is>
-          <t>naver_brandsearch_mobile</t>
+          <t>[PF]전환_회원가입(유사)</t>
         </is>
       </c>
     </row>
     <row r="1049">
       <c r="A1049" t="inlineStr">
         <is>
-          <t>kk_2807863527</t>
+          <t>pentagram</t>
         </is>
       </c>
       <c r="B1049" t="inlineStr">
         <is>
-          <t>01042669625</t>
+          <t>01093327353</t>
         </is>
       </c>
       <c r="C1049" t="inlineStr">
         <is>
-          <t>211605</t>
+          <t>131085</t>
         </is>
       </c>
       <c r="D1049" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E1049" t="inlineStr">
         <is>
-          <t>[PF]전환_회원가입(유사)</t>
+          <t>KAKAO_alimtalk</t>
         </is>
       </c>
     </row>
@@ -28781,125 +28781,125 @@
     <row r="1051">
       <c r="A1051" t="inlineStr">
         <is>
-          <t>hihijs34</t>
+          <t>kk_4427490834</t>
         </is>
       </c>
       <c r="B1051" t="inlineStr">
         <is>
-          <t>01093230529</t>
+          <t>01034704205</t>
         </is>
       </c>
       <c r="C1051" t="inlineStr">
         <is>
-          <t>128947</t>
+          <t>281590</t>
         </is>
       </c>
       <c r="D1051" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E1051" t="inlineStr">
         <is>
-          <t>[PF]A+SC_상시(1865MF,구매+장바구니)</t>
+          <t>LMS_ECOM_0410exclusive2</t>
         </is>
       </c>
     </row>
     <row r="1052">
       <c r="A1052" t="inlineStr">
         <is>
-          <t>kk_4427490834</t>
+          <t>hihijs34</t>
         </is>
       </c>
       <c r="B1052" t="inlineStr">
         <is>
-          <t>01034704205</t>
+          <t>01093230529</t>
         </is>
       </c>
       <c r="C1052" t="inlineStr">
         <is>
-          <t>281590</t>
+          <t>128947</t>
         </is>
       </c>
       <c r="D1052" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E1052" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0410exclusive2</t>
+          <t>[PF]A+SC_상시(1865MF,구매+장바구니)</t>
         </is>
       </c>
     </row>
     <row r="1053">
       <c r="A1053" t="inlineStr">
         <is>
-          <t>loyed24</t>
+          <t>wisbrain</t>
         </is>
       </c>
       <c r="B1053" t="inlineStr">
         <is>
-          <t>01085487901</t>
+          <t>01047220186</t>
         </is>
       </c>
       <c r="C1053" t="inlineStr">
         <is>
-          <t>244062</t>
+          <t>188067</t>
         </is>
       </c>
       <c r="D1053" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="E1053" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0410exclusive2</t>
+          <t>Direct</t>
         </is>
       </c>
     </row>
     <row r="1054">
       <c r="A1054" t="inlineStr">
         <is>
-          <t>wisbrain</t>
+          <t>loyed24</t>
         </is>
       </c>
       <c r="B1054" t="inlineStr">
         <is>
-          <t>01047220186</t>
+          <t>01085487901</t>
         </is>
       </c>
       <c r="C1054" t="inlineStr">
         <is>
-          <t>188067</t>
+          <t>244062</t>
         </is>
       </c>
       <c r="D1054" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E1054" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>LMS_ECOM_0410exclusive2</t>
         </is>
       </c>
     </row>
     <row r="1055">
       <c r="A1055" t="inlineStr">
         <is>
-          <t>kk_3349199057</t>
+          <t>kk_3180736217</t>
         </is>
       </c>
       <c r="B1055" t="inlineStr">
         <is>
-          <t>01071630312</t>
+          <t>01036000343</t>
         </is>
       </c>
       <c r="C1055" t="inlineStr">
         <is>
-          <t>239388</t>
+          <t>226314</t>
         </is>
       </c>
       <c r="D1055" t="inlineStr">
@@ -28916,17 +28916,17 @@
     <row r="1056">
       <c r="A1056" t="inlineStr">
         <is>
-          <t>bobjazz</t>
+          <t>columbia7</t>
         </is>
       </c>
       <c r="B1056" t="inlineStr">
         <is>
-          <t>01084090677</t>
+          <t>01050080025</t>
         </is>
       </c>
       <c r="C1056" t="inlineStr">
         <is>
-          <t>186218</t>
+          <t>109980</t>
         </is>
       </c>
       <c r="D1056" t="inlineStr">
@@ -28943,44 +28943,44 @@
     <row r="1057">
       <c r="A1057" t="inlineStr">
         <is>
-          <t>camiblanco</t>
+          <t>pls4u</t>
         </is>
       </c>
       <c r="B1057" t="inlineStr">
         <is>
-          <t>01072190103</t>
+          <t>01085985482</t>
         </is>
       </c>
       <c r="C1057" t="inlineStr">
         <is>
-          <t>232545</t>
+          <t>88257</t>
         </is>
       </c>
       <c r="D1057" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E1057" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>LMS_ECOM_0401_trailrunning</t>
         </is>
       </c>
     </row>
     <row r="1058">
       <c r="A1058" t="inlineStr">
         <is>
-          <t>pls4u</t>
+          <t>kk_4452401577</t>
         </is>
       </c>
       <c r="B1058" t="inlineStr">
         <is>
-          <t>01085985482</t>
+          <t>01047428000</t>
         </is>
       </c>
       <c r="C1058" t="inlineStr">
         <is>
-          <t>88257</t>
+          <t>282525</t>
         </is>
       </c>
       <c r="D1058" t="inlineStr">
@@ -28990,24 +28990,24 @@
       </c>
       <c r="E1058" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0401_trailrunning</t>
+          <t>LMS_ECOM_0410exclusive2</t>
         </is>
       </c>
     </row>
     <row r="1059">
       <c r="A1059" t="inlineStr">
         <is>
-          <t>kk_3180736217</t>
+          <t>hyschant</t>
         </is>
       </c>
       <c r="B1059" t="inlineStr">
         <is>
-          <t>01036000343</t>
+          <t>01065306675</t>
         </is>
       </c>
       <c r="C1059" t="inlineStr">
         <is>
-          <t>226314</t>
+          <t>108579</t>
         </is>
       </c>
       <c r="D1059" t="inlineStr">
@@ -29024,27 +29024,27 @@
     <row r="1060">
       <c r="A1060" t="inlineStr">
         <is>
-          <t>sjm700</t>
+          <t>camiblanco</t>
         </is>
       </c>
       <c r="B1060" t="inlineStr">
         <is>
-          <t>01077331591</t>
+          <t>01072190103</t>
         </is>
       </c>
       <c r="C1060" t="inlineStr">
         <is>
-          <t>118769</t>
+          <t>232545</t>
         </is>
       </c>
       <c r="D1060" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="E1060" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0410exclusive2</t>
+          <t>Direct</t>
         </is>
       </c>
     </row>
@@ -29078,17 +29078,17 @@
     <row r="1062">
       <c r="A1062" t="inlineStr">
         <is>
-          <t>hyschant</t>
+          <t>kk_4525043459</t>
         </is>
       </c>
       <c r="B1062" t="inlineStr">
         <is>
-          <t>01065306675</t>
+          <t>01088312135</t>
         </is>
       </c>
       <c r="C1062" t="inlineStr">
         <is>
-          <t>108579</t>
+          <t>286464</t>
         </is>
       </c>
       <c r="D1062" t="inlineStr">
@@ -29105,17 +29105,17 @@
     <row r="1063">
       <c r="A1063" t="inlineStr">
         <is>
-          <t>kk_4578503399</t>
+          <t>dmsql785612</t>
         </is>
       </c>
       <c r="B1063" t="inlineStr">
         <is>
-          <t>01088660330</t>
+          <t>01051590364</t>
         </is>
       </c>
       <c r="C1063" t="inlineStr">
         <is>
-          <t>288374</t>
+          <t>137279</t>
         </is>
       </c>
       <c r="D1063" t="inlineStr">
@@ -29125,51 +29125,51 @@
       </c>
       <c r="E1063" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0410exclusive2</t>
+          <t>Email_mkt</t>
         </is>
       </c>
     </row>
     <row r="1064">
       <c r="A1064" t="inlineStr">
         <is>
-          <t>yongshin</t>
+          <t>inu21c</t>
         </is>
       </c>
       <c r="B1064" t="inlineStr">
         <is>
-          <t>01053867821</t>
+          <t>01035128236</t>
         </is>
       </c>
       <c r="C1064" t="inlineStr">
         <is>
-          <t>277896</t>
+          <t>131940</t>
         </is>
       </c>
       <c r="D1064" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E1064" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>LMS_ECOM_0410exclusive2</t>
         </is>
       </c>
     </row>
     <row r="1065">
       <c r="A1065" t="inlineStr">
         <is>
-          <t>kk_3973703558</t>
+          <t>kk_3754052831</t>
         </is>
       </c>
       <c r="B1065" t="inlineStr">
         <is>
-          <t>01048590748</t>
+          <t>01092180804</t>
         </is>
       </c>
       <c r="C1065" t="inlineStr">
         <is>
-          <t>271020</t>
+          <t>254339</t>
         </is>
       </c>
       <c r="D1065" t="inlineStr">
@@ -29186,17 +29186,17 @@
     <row r="1066">
       <c r="A1066" t="inlineStr">
         <is>
-          <t>kk_3754052831</t>
+          <t>sjm700</t>
         </is>
       </c>
       <c r="B1066" t="inlineStr">
         <is>
-          <t>01092180804</t>
+          <t>01077331591</t>
         </is>
       </c>
       <c r="C1066" t="inlineStr">
         <is>
-          <t>254339</t>
+          <t>118769</t>
         </is>
       </c>
       <c r="D1066" t="inlineStr">
@@ -29213,44 +29213,44 @@
     <row r="1067">
       <c r="A1067" t="inlineStr">
         <is>
-          <t>inu21c</t>
+          <t>kk_3721447783</t>
         </is>
       </c>
       <c r="B1067" t="inlineStr">
         <is>
-          <t>01035128236</t>
+          <t>01051311087</t>
         </is>
       </c>
       <c r="C1067" t="inlineStr">
         <is>
-          <t>131940</t>
+          <t>252252</t>
         </is>
       </c>
       <c r="D1067" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="E1067" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0410exclusive2</t>
+          <t>Direct</t>
         </is>
       </c>
     </row>
     <row r="1068">
       <c r="A1068" t="inlineStr">
         <is>
-          <t>kk_4525043459</t>
+          <t>kk_4578503399</t>
         </is>
       </c>
       <c r="B1068" t="inlineStr">
         <is>
-          <t>01088312135</t>
+          <t>01088660330</t>
         </is>
       </c>
       <c r="C1068" t="inlineStr">
         <is>
-          <t>286464</t>
+          <t>288374</t>
         </is>
       </c>
       <c r="D1068" t="inlineStr">
@@ -29267,44 +29267,44 @@
     <row r="1069">
       <c r="A1069" t="inlineStr">
         <is>
-          <t>columbia7</t>
+          <t>yongshin</t>
         </is>
       </c>
       <c r="B1069" t="inlineStr">
         <is>
-          <t>01050080025</t>
+          <t>01053867821</t>
         </is>
       </c>
       <c r="C1069" t="inlineStr">
         <is>
-          <t>109980</t>
+          <t>277896</t>
         </is>
       </c>
       <c r="D1069" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="E1069" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0410exclusive2</t>
+          <t>Direct</t>
         </is>
       </c>
     </row>
     <row r="1070">
       <c r="A1070" t="inlineStr">
         <is>
-          <t>kk_4452401577</t>
+          <t>kk_3973703558</t>
         </is>
       </c>
       <c r="B1070" t="inlineStr">
         <is>
-          <t>01047428000</t>
+          <t>01048590748</t>
         </is>
       </c>
       <c r="C1070" t="inlineStr">
         <is>
-          <t>282525</t>
+          <t>271020</t>
         </is>
       </c>
       <c r="D1070" t="inlineStr">
@@ -29321,17 +29321,17 @@
     <row r="1071">
       <c r="A1071" t="inlineStr">
         <is>
-          <t>kk_3024318364</t>
+          <t>kk_3349199057</t>
         </is>
       </c>
       <c r="B1071" t="inlineStr">
         <is>
-          <t>01050308038</t>
+          <t>01071630312</t>
         </is>
       </c>
       <c r="C1071" t="inlineStr">
         <is>
-          <t>219525</t>
+          <t>239388</t>
         </is>
       </c>
       <c r="D1071" t="inlineStr">
@@ -29348,44 +29348,44 @@
     <row r="1072">
       <c r="A1072" t="inlineStr">
         <is>
-          <t>kk_3721447783</t>
+          <t>kk_3024318364</t>
         </is>
       </c>
       <c r="B1072" t="inlineStr">
         <is>
-          <t>01051311087</t>
+          <t>01050308038</t>
         </is>
       </c>
       <c r="C1072" t="inlineStr">
         <is>
-          <t>252252</t>
+          <t>219525</t>
         </is>
       </c>
       <c r="D1072" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E1072" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>LMS_ECOM_0410exclusive2</t>
         </is>
       </c>
     </row>
     <row r="1073">
       <c r="A1073" t="inlineStr">
         <is>
-          <t>dmsql785612</t>
+          <t>kk_2825715315</t>
         </is>
       </c>
       <c r="B1073" t="inlineStr">
         <is>
-          <t>01051590364</t>
+          <t>01077229654</t>
         </is>
       </c>
       <c r="C1073" t="inlineStr">
         <is>
-          <t>137279</t>
+          <t>212719</t>
         </is>
       </c>
       <c r="D1073" t="inlineStr">
@@ -29395,24 +29395,24 @@
       </c>
       <c r="E1073" t="inlineStr">
         <is>
-          <t>Email_mkt</t>
+          <t>LMS_ECOM_0410exclusive2</t>
         </is>
       </c>
     </row>
     <row r="1074">
       <c r="A1074" t="inlineStr">
         <is>
-          <t>kk_2825715315</t>
+          <t>bobjazz</t>
         </is>
       </c>
       <c r="B1074" t="inlineStr">
         <is>
-          <t>01077229654</t>
+          <t>01084090677</t>
         </is>
       </c>
       <c r="C1074" t="inlineStr">
         <is>
-          <t>212719</t>
+          <t>186218</t>
         </is>
       </c>
       <c r="D1074" t="inlineStr">
@@ -29429,27 +29429,27 @@
     <row r="1075">
       <c r="A1075" t="inlineStr">
         <is>
-          <t>kk_4838419826</t>
+          <t>kk_3626939480</t>
         </is>
       </c>
       <c r="B1075" t="inlineStr">
         <is>
-          <t>01037240798</t>
+          <t>01030537990</t>
         </is>
       </c>
       <c r="C1075" t="inlineStr">
         <is>
-          <t>304050</t>
+          <t>247893</t>
         </is>
       </c>
       <c r="D1075" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E1075" t="inlineStr">
         <is>
-          <t>[PF]트래픽_유사+관심사</t>
+          <t>KAKAO_CH_MESSAGE_0409_EXCLUSIVE</t>
         </is>
       </c>
     </row>
@@ -29483,17 +29483,17 @@
     <row r="1077">
       <c r="A1077" t="inlineStr">
         <is>
-          <t>kk_3626939480</t>
+          <t>kk_3912725759</t>
         </is>
       </c>
       <c r="B1077" t="inlineStr">
         <is>
-          <t>01030537990</t>
+          <t>01062505257</t>
         </is>
       </c>
       <c r="C1077" t="inlineStr">
         <is>
-          <t>247893</t>
+          <t>268286</t>
         </is>
       </c>
       <c r="D1077" t="inlineStr">
@@ -29510,27 +29510,27 @@
     <row r="1078">
       <c r="A1078" t="inlineStr">
         <is>
-          <t>kk_3912725759</t>
+          <t>kk_4838419826</t>
         </is>
       </c>
       <c r="B1078" t="inlineStr">
         <is>
-          <t>01062505257</t>
+          <t>01037240798</t>
         </is>
       </c>
       <c r="C1078" t="inlineStr">
         <is>
-          <t>268286</t>
+          <t>304050</t>
         </is>
       </c>
       <c r="D1078" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E1078" t="inlineStr">
         <is>
-          <t>KAKAO_CH_MESSAGE_0409_EXCLUSIVE</t>
+          <t>[PF]트래픽_유사+관심사</t>
         </is>
       </c>
     </row>
@@ -29564,27 +29564,27 @@
     <row r="1080">
       <c r="A1080" t="inlineStr">
         <is>
-          <t>kk_4255987550</t>
+          <t>kk_4717085515</t>
         </is>
       </c>
       <c r="B1080" t="inlineStr">
         <is>
-          <t>01026453656</t>
+          <t>01052078703</t>
         </is>
       </c>
       <c r="C1080" t="inlineStr">
         <is>
-          <t>274389</t>
+          <t>297221</t>
         </is>
       </c>
       <c r="D1080" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="E1080" t="inlineStr">
         <is>
-          <t>Email_mkt</t>
+          <t>Direct</t>
         </is>
       </c>
     </row>
@@ -29618,27 +29618,27 @@
     <row r="1082">
       <c r="A1082" t="inlineStr">
         <is>
-          <t>kk_4717085515</t>
+          <t>kk_4255987550</t>
         </is>
       </c>
       <c r="B1082" t="inlineStr">
         <is>
-          <t>01052078703</t>
+          <t>01026453656</t>
         </is>
       </c>
       <c r="C1082" t="inlineStr">
         <is>
-          <t>297221</t>
+          <t>274389</t>
         </is>
       </c>
       <c r="D1082" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E1082" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>Email_mkt</t>
         </is>
       </c>
     </row>
@@ -29699,17 +29699,17 @@
     <row r="1085">
       <c r="A1085" t="inlineStr">
         <is>
-          <t>alcoholpower</t>
+          <t>kimms66</t>
         </is>
       </c>
       <c r="B1085" t="inlineStr">
         <is>
-          <t>01027629868</t>
+          <t>01057634626</t>
         </is>
       </c>
       <c r="C1085" t="inlineStr">
         <is>
-          <t>252954</t>
+          <t>180321</t>
         </is>
       </c>
       <c r="D1085" t="inlineStr">
@@ -29726,17 +29726,17 @@
     <row r="1086">
       <c r="A1086" t="inlineStr">
         <is>
-          <t>kimms66</t>
+          <t>happy201106</t>
         </is>
       </c>
       <c r="B1086" t="inlineStr">
         <is>
-          <t>01057634626</t>
+          <t>01090012622</t>
         </is>
       </c>
       <c r="C1086" t="inlineStr">
         <is>
-          <t>180321</t>
+          <t>136050</t>
         </is>
       </c>
       <c r="D1086" t="inlineStr">
@@ -29753,17 +29753,17 @@
     <row r="1087">
       <c r="A1087" t="inlineStr">
         <is>
-          <t>happy201106</t>
+          <t>alcoholpower</t>
         </is>
       </c>
       <c r="B1087" t="inlineStr">
         <is>
-          <t>01090012622</t>
+          <t>01027629868</t>
         </is>
       </c>
       <c r="C1087" t="inlineStr">
         <is>
-          <t>136050</t>
+          <t>252954</t>
         </is>
       </c>
       <c r="D1087" t="inlineStr">

--- a/reports/member_funnel/downloads/member_funnel_7d_non_buyer.xlsx
+++ b/reports/member_funnel/downloads/member_funnel_7d_non_buyer.xlsx
@@ -8693,54 +8693,54 @@
     <row r="307">
       <c r="A307" t="inlineStr">
         <is>
-          <t>dsccool</t>
+          <t>kk_4231959784</t>
         </is>
       </c>
       <c r="B307" t="inlineStr">
         <is>
-          <t>01040100422</t>
+          <t>01035343111</t>
         </is>
       </c>
       <c r="C307" t="inlineStr">
         <is>
-          <t>284754</t>
+          <t>273395</t>
         </is>
       </c>
       <c r="D307" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E307" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>KAKAO_CH_MESSAGE_0325_S26NEW_CTA</t>
         </is>
       </c>
     </row>
     <row r="308">
       <c r="A308" t="inlineStr">
         <is>
-          <t>kk_4231959784</t>
+          <t>dsccool</t>
         </is>
       </c>
       <c r="B308" t="inlineStr">
         <is>
-          <t>01035343111</t>
+          <t>01040100422</t>
         </is>
       </c>
       <c r="C308" t="inlineStr">
         <is>
-          <t>273395</t>
+          <t>284754</t>
         </is>
       </c>
       <c r="D308" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="E308" t="inlineStr">
         <is>
-          <t>KAKAO_CH_MESSAGE_0325_S26NEW_CTA</t>
+          <t>Direct</t>
         </is>
       </c>
     </row>
@@ -17225,54 +17225,54 @@
     <row r="623">
       <c r="A623" t="inlineStr">
         <is>
-          <t>kk_4841965432</t>
+          <t>khkim6620</t>
         </is>
       </c>
       <c r="B623" t="inlineStr">
         <is>
-          <t>01032510712</t>
+          <t>01076876567</t>
         </is>
       </c>
       <c r="C623" t="inlineStr">
         <is>
-          <t>304213</t>
+          <t>105445</t>
         </is>
       </c>
       <c r="D623" t="inlineStr">
         <is>
-          <t>Organic Traffic</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E623" t="inlineStr">
         <is>
-          <t>(referral)</t>
+          <t>컬럼비아_DPA_240530</t>
         </is>
       </c>
     </row>
     <row r="624">
       <c r="A624" t="inlineStr">
         <is>
-          <t>khkim6620</t>
+          <t>kk_4841965432</t>
         </is>
       </c>
       <c r="B624" t="inlineStr">
         <is>
-          <t>01076876567</t>
+          <t>01032510712</t>
         </is>
       </c>
       <c r="C624" t="inlineStr">
         <is>
-          <t>105445</t>
+          <t>304213</t>
         </is>
       </c>
       <c r="D624" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Organic Traffic</t>
         </is>
       </c>
       <c r="E624" t="inlineStr">
         <is>
-          <t>컬럼비아_DPA_240530</t>
+          <t>(referral)</t>
         </is>
       </c>
     </row>
@@ -17738,17 +17738,17 @@
     <row r="642">
       <c r="A642" t="inlineStr">
         <is>
-          <t>kk_4840846776</t>
+          <t>kk_4840658838</t>
         </is>
       </c>
       <c r="B642" t="inlineStr">
         <is>
-          <t>01055961435</t>
+          <t>01039292600</t>
         </is>
       </c>
       <c r="C642" t="inlineStr">
         <is>
-          <t>304170</t>
+          <t>304158</t>
         </is>
       </c>
       <c r="D642" t="inlineStr">
@@ -17758,24 +17758,24 @@
       </c>
       <c r="E642" t="inlineStr">
         <is>
-          <t>[PF]전환_회원가입(유사)</t>
+          <t>EFW</t>
         </is>
       </c>
     </row>
     <row r="643">
       <c r="A643" t="inlineStr">
         <is>
-          <t>kk_4840658838</t>
+          <t>kk_4840846776</t>
         </is>
       </c>
       <c r="B643" t="inlineStr">
         <is>
-          <t>01039292600</t>
+          <t>01055961435</t>
         </is>
       </c>
       <c r="C643" t="inlineStr">
         <is>
-          <t>304158</t>
+          <t>304170</t>
         </is>
       </c>
       <c r="D643" t="inlineStr">
@@ -17785,7 +17785,7 @@
       </c>
       <c r="E643" t="inlineStr">
         <is>
-          <t>EFW</t>
+          <t>[PF]전환_회원가입(유사)</t>
         </is>
       </c>
     </row>
@@ -19169,17 +19169,17 @@
     <row r="695">
       <c r="A695" t="inlineStr">
         <is>
-          <t>kk_2915134680</t>
+          <t>kk_4288273717</t>
         </is>
       </c>
       <c r="B695" t="inlineStr">
         <is>
-          <t>01085224711</t>
+          <t>01020746624</t>
         </is>
       </c>
       <c r="C695" t="inlineStr">
         <is>
-          <t>215670</t>
+          <t>275762</t>
         </is>
       </c>
       <c r="D695" t="inlineStr">
@@ -19189,24 +19189,24 @@
       </c>
       <c r="E695" t="inlineStr">
         <is>
-          <t>KAKAO_CH_MESSAGE_0409_HIKE365SUMMER</t>
+          <t>LMS_ECOM_0410exclusive2</t>
         </is>
       </c>
     </row>
     <row r="696">
       <c r="A696" t="inlineStr">
         <is>
-          <t>kk_4288273717</t>
+          <t>kk_2915134680</t>
         </is>
       </c>
       <c r="B696" t="inlineStr">
         <is>
-          <t>01020746624</t>
+          <t>01085224711</t>
         </is>
       </c>
       <c r="C696" t="inlineStr">
         <is>
-          <t>275762</t>
+          <t>215670</t>
         </is>
       </c>
       <c r="D696" t="inlineStr">
@@ -19216,7 +19216,7 @@
       </c>
       <c r="E696" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0410exclusive2</t>
+          <t>KAKAO_CH_MESSAGE_0409_HIKE365SUMMER</t>
         </is>
       </c>
     </row>
@@ -19304,17 +19304,17 @@
     <row r="700">
       <c r="A700" t="inlineStr">
         <is>
-          <t>kk_3101119679</t>
+          <t>hun7662</t>
         </is>
       </c>
       <c r="B700" t="inlineStr">
         <is>
-          <t>01093993852</t>
+          <t>01042311474</t>
         </is>
       </c>
       <c r="C700" t="inlineStr">
         <is>
-          <t>221630</t>
+          <t>172790</t>
         </is>
       </c>
       <c r="D700" t="inlineStr">
@@ -19331,17 +19331,17 @@
     <row r="701">
       <c r="A701" t="inlineStr">
         <is>
-          <t>hun7662</t>
+          <t>kk_3101119679</t>
         </is>
       </c>
       <c r="B701" t="inlineStr">
         <is>
-          <t>01042311474</t>
+          <t>01093993852</t>
         </is>
       </c>
       <c r="C701" t="inlineStr">
         <is>
-          <t>172790</t>
+          <t>221630</t>
         </is>
       </c>
       <c r="D701" t="inlineStr">
@@ -19763,71 +19763,71 @@
     <row r="717">
       <c r="A717" t="inlineStr">
         <is>
-          <t>kk_4839765445</t>
+          <t>sun1381</t>
         </is>
       </c>
       <c r="B717" t="inlineStr">
         <is>
-          <t>01076118972</t>
+          <t>01037709416</t>
         </is>
       </c>
       <c r="C717" t="inlineStr">
         <is>
-          <t>304111</t>
+          <t>278160</t>
         </is>
       </c>
       <c r="D717" t="inlineStr">
         <is>
-          <t>Organic Traffic</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E717" t="inlineStr">
         <is>
-          <t>(referral)</t>
+          <t>LMS_ECOM_0410exclusive2</t>
         </is>
       </c>
     </row>
     <row r="718">
       <c r="A718" t="inlineStr">
         <is>
-          <t>sun1381</t>
+          <t>kk_4839765445</t>
         </is>
       </c>
       <c r="B718" t="inlineStr">
         <is>
-          <t>01037709416</t>
+          <t>01076118972</t>
         </is>
       </c>
       <c r="C718" t="inlineStr">
         <is>
-          <t>278160</t>
+          <t>304111</t>
         </is>
       </c>
       <c r="D718" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Organic Traffic</t>
         </is>
       </c>
       <c r="E718" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0410exclusive2</t>
+          <t>(referral)</t>
         </is>
       </c>
     </row>
     <row r="719">
       <c r="A719" t="inlineStr">
         <is>
-          <t>kk_4324736295</t>
+          <t>kwon1207</t>
         </is>
       </c>
       <c r="B719" t="inlineStr">
         <is>
-          <t>01077616385</t>
+          <t>01055647413</t>
         </is>
       </c>
       <c r="C719" t="inlineStr">
         <is>
-          <t>278190</t>
+          <t>129663</t>
         </is>
       </c>
       <c r="D719" t="inlineStr">
@@ -19837,24 +19837,24 @@
       </c>
       <c r="E719" t="inlineStr">
         <is>
-          <t>KAKAO_CH_MESSAGE_0409_EXCLUSIVE</t>
+          <t>KAKAO_CH_MESSAGE_0409_TRAIL</t>
         </is>
       </c>
     </row>
     <row r="720">
       <c r="A720" t="inlineStr">
         <is>
-          <t>kwon1207</t>
+          <t>kk_4324736295</t>
         </is>
       </c>
       <c r="B720" t="inlineStr">
         <is>
-          <t>01055647413</t>
+          <t>01077616385</t>
         </is>
       </c>
       <c r="C720" t="inlineStr">
         <is>
-          <t>129663</t>
+          <t>278190</t>
         </is>
       </c>
       <c r="D720" t="inlineStr">
@@ -19864,7 +19864,7 @@
       </c>
       <c r="E720" t="inlineStr">
         <is>
-          <t>KAKAO_CH_MESSAGE_0409_TRAIL</t>
+          <t>KAKAO_CH_MESSAGE_0409_EXCLUSIVE</t>
         </is>
       </c>
     </row>
@@ -20762,27 +20762,27 @@
     <row r="754">
       <c r="A754" t="inlineStr">
         <is>
-          <t>kk_4839680663</t>
+          <t>athend</t>
         </is>
       </c>
       <c r="B754" t="inlineStr">
         <is>
-          <t>01046429530</t>
+          <t>01041786462</t>
         </is>
       </c>
       <c r="C754" t="inlineStr">
         <is>
-          <t>304109</t>
+          <t>285491</t>
         </is>
       </c>
       <c r="D754" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E754" t="inlineStr">
         <is>
-          <t>6968489536332</t>
+          <t>KAKAO_alimtalk</t>
         </is>
       </c>
     </row>
@@ -20816,44 +20816,44 @@
     <row r="756">
       <c r="A756" t="inlineStr">
         <is>
-          <t>athend</t>
+          <t>kk_4839680663</t>
         </is>
       </c>
       <c r="B756" t="inlineStr">
         <is>
-          <t>01041786462</t>
+          <t>01046429530</t>
         </is>
       </c>
       <c r="C756" t="inlineStr">
         <is>
-          <t>285491</t>
+          <t>304109</t>
         </is>
       </c>
       <c r="D756" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E756" t="inlineStr">
         <is>
-          <t>KAKAO_alimtalk</t>
+          <t>6968489536332</t>
         </is>
       </c>
     </row>
     <row r="757">
       <c r="A757" t="inlineStr">
         <is>
-          <t>kk_3184667648</t>
+          <t>kk_3404142353</t>
         </is>
       </c>
       <c r="B757" t="inlineStr">
         <is>
-          <t>01043440321</t>
+          <t>01053293239</t>
         </is>
       </c>
       <c r="C757" t="inlineStr">
         <is>
-          <t>229128</t>
+          <t>241289</t>
         </is>
       </c>
       <c r="D757" t="inlineStr">
@@ -20863,61 +20863,61 @@
       </c>
       <c r="E757" t="inlineStr">
         <is>
-          <t>sa</t>
+          <t>[PF]전환_상시(2565MF,비구매자)</t>
         </is>
       </c>
     </row>
     <row r="758">
       <c r="A758" t="inlineStr">
         <is>
-          <t>kk_4431727915</t>
+          <t>kk_3184667648</t>
         </is>
       </c>
       <c r="B758" t="inlineStr">
         <is>
-          <t>01047182896</t>
+          <t>01043440321</t>
         </is>
       </c>
       <c r="C758" t="inlineStr">
         <is>
-          <t>281759</t>
+          <t>229128</t>
         </is>
       </c>
       <c r="D758" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E758" t="inlineStr">
         <is>
-          <t>KAKAO_CH_MESSAGE_0409_HIKE365SUMMER</t>
+          <t>sa</t>
         </is>
       </c>
     </row>
     <row r="759">
       <c r="A759" t="inlineStr">
         <is>
-          <t>kk_3404142353</t>
+          <t>kk_4431727915</t>
         </is>
       </c>
       <c r="B759" t="inlineStr">
         <is>
-          <t>01053293239</t>
+          <t>01047182896</t>
         </is>
       </c>
       <c r="C759" t="inlineStr">
         <is>
-          <t>241289</t>
+          <t>281759</t>
         </is>
       </c>
       <c r="D759" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E759" t="inlineStr">
         <is>
-          <t>[PF]전환_상시(2565MF,비구매자)</t>
+          <t>KAKAO_CH_MESSAGE_0409_HIKE365SUMMER</t>
         </is>
       </c>
     </row>
@@ -21005,17 +21005,17 @@
     <row r="763">
       <c r="A763" t="inlineStr">
         <is>
-          <t>kk_3678962368</t>
+          <t>ganjing78</t>
         </is>
       </c>
       <c r="B763" t="inlineStr">
         <is>
-          <t>01041028567</t>
+          <t>01065121424</t>
         </is>
       </c>
       <c r="C763" t="inlineStr">
         <is>
-          <t>250374</t>
+          <t>78590</t>
         </is>
       </c>
       <c r="D763" t="inlineStr">
@@ -21032,162 +21032,162 @@
     <row r="764">
       <c r="A764" t="inlineStr">
         <is>
-          <t>ganjing78</t>
+          <t>isaackwak</t>
         </is>
       </c>
       <c r="B764" t="inlineStr">
         <is>
-          <t>01065121424</t>
+          <t>01090599860</t>
         </is>
       </c>
       <c r="C764" t="inlineStr">
         <is>
-          <t>78590</t>
+          <t>275913</t>
         </is>
       </c>
       <c r="D764" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="E764" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0410exclusive2</t>
+          <t>Direct</t>
         </is>
       </c>
     </row>
     <row r="765">
       <c r="A765" t="inlineStr">
         <is>
-          <t>mtbok</t>
+          <t>kk_4839433808</t>
         </is>
       </c>
       <c r="B765" t="inlineStr">
         <is>
-          <t>01051284339</t>
+          <t>01025333388</t>
         </is>
       </c>
       <c r="C765" t="inlineStr">
         <is>
-          <t>26917</t>
+          <t>304100</t>
         </is>
       </c>
       <c r="D765" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E765" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0410exclusive2</t>
+          <t>naver_brandsearch_mobile</t>
         </is>
       </c>
     </row>
     <row r="766">
       <c r="A766" t="inlineStr">
         <is>
-          <t>kk_4839433808</t>
+          <t>mtbok</t>
         </is>
       </c>
       <c r="B766" t="inlineStr">
         <is>
-          <t>01025333388</t>
+          <t>01051284339</t>
         </is>
       </c>
       <c r="C766" t="inlineStr">
         <is>
-          <t>304100</t>
+          <t>26917</t>
         </is>
       </c>
       <c r="D766" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E766" t="inlineStr">
         <is>
-          <t>naver_brandsearch_mobile</t>
+          <t>LMS_ECOM_0410exclusive2</t>
         </is>
       </c>
     </row>
     <row r="767">
       <c r="A767" t="inlineStr">
         <is>
-          <t>isaackwak</t>
+          <t>kk_3678962368</t>
         </is>
       </c>
       <c r="B767" t="inlineStr">
         <is>
-          <t>01090599860</t>
+          <t>01041028567</t>
         </is>
       </c>
       <c r="C767" t="inlineStr">
         <is>
-          <t>275913</t>
+          <t>250374</t>
         </is>
       </c>
       <c r="D767" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E767" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>LMS_ECOM_0410exclusive2</t>
         </is>
       </c>
     </row>
     <row r="768">
       <c r="A768" t="inlineStr">
         <is>
-          <t>lee6007</t>
+          <t>ldh7go</t>
         </is>
       </c>
       <c r="B768" t="inlineStr">
         <is>
-          <t>01039973613</t>
+          <t>01034075007</t>
         </is>
       </c>
       <c r="C768" t="inlineStr">
         <is>
-          <t>168179</t>
+          <t>221575</t>
         </is>
       </c>
       <c r="D768" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E768" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>KAKAO_CH_MESSAGE_0409_HIKE365SUMMER</t>
         </is>
       </c>
     </row>
     <row r="769">
       <c r="A769" t="inlineStr">
         <is>
-          <t>ldh7go</t>
+          <t>lee6007</t>
         </is>
       </c>
       <c r="B769" t="inlineStr">
         <is>
-          <t>01034075007</t>
+          <t>01039973613</t>
         </is>
       </c>
       <c r="C769" t="inlineStr">
         <is>
-          <t>221575</t>
+          <t>168179</t>
         </is>
       </c>
       <c r="D769" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="E769" t="inlineStr">
         <is>
-          <t>KAKAO_CH_MESSAGE_0409_HIKE365SUMMER</t>
+          <t>Direct</t>
         </is>
       </c>
     </row>
@@ -21221,81 +21221,81 @@
     <row r="771">
       <c r="A771" t="inlineStr">
         <is>
-          <t>kk_4727921763</t>
+          <t>kk_2757380967</t>
         </is>
       </c>
       <c r="B771" t="inlineStr">
         <is>
-          <t>01045673975</t>
+          <t>01034635649</t>
         </is>
       </c>
       <c r="C771" t="inlineStr">
         <is>
-          <t>298138</t>
+          <t>208245</t>
         </is>
       </c>
       <c r="D771" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E771" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>LMS_ECOM_0410exclusive2</t>
         </is>
       </c>
     </row>
     <row r="772">
       <c r="A772" t="inlineStr">
         <is>
-          <t>kk_2757380967</t>
+          <t>kk_4839026541</t>
         </is>
       </c>
       <c r="B772" t="inlineStr">
         <is>
-          <t>01034635649</t>
+          <t>01089431507</t>
         </is>
       </c>
       <c r="C772" t="inlineStr">
         <is>
-          <t>208245</t>
+          <t>304082</t>
         </is>
       </c>
       <c r="D772" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E772" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0410exclusive2</t>
+          <t>[PF]전환_상시(2565MF,비구매자)</t>
         </is>
       </c>
     </row>
     <row r="773">
       <c r="A773" t="inlineStr">
         <is>
-          <t>kk_4839026541</t>
+          <t>kk_4727921763</t>
         </is>
       </c>
       <c r="B773" t="inlineStr">
         <is>
-          <t>01089431507</t>
+          <t>01045673975</t>
         </is>
       </c>
       <c r="C773" t="inlineStr">
         <is>
-          <t>304082</t>
+          <t>298138</t>
         </is>
       </c>
       <c r="D773" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="E773" t="inlineStr">
         <is>
-          <t>[PF]전환_상시(2565MF,비구매자)</t>
+          <t>Direct</t>
         </is>
       </c>
     </row>
@@ -21356,54 +21356,54 @@
     <row r="776">
       <c r="A776" t="inlineStr">
         <is>
-          <t>kk_4532357752</t>
+          <t>kk_3156128258</t>
         </is>
       </c>
       <c r="B776" t="inlineStr">
         <is>
-          <t>01023210419</t>
+          <t>01093995884</t>
         </is>
       </c>
       <c r="C776" t="inlineStr">
         <is>
-          <t>286900</t>
+          <t>223742</t>
         </is>
       </c>
       <c r="D776" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="E776" t="inlineStr">
         <is>
-          <t>KAKAO_CH_MESSAGE_0409_EXCLUSIVE</t>
+          <t>Direct</t>
         </is>
       </c>
     </row>
     <row r="777">
       <c r="A777" t="inlineStr">
         <is>
-          <t>kk_3156128258</t>
+          <t>kk_4532357752</t>
         </is>
       </c>
       <c r="B777" t="inlineStr">
         <is>
-          <t>01093995884</t>
+          <t>01023210419</t>
         </is>
       </c>
       <c r="C777" t="inlineStr">
         <is>
-          <t>223742</t>
+          <t>286900</t>
         </is>
       </c>
       <c r="D777" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E777" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>KAKAO_CH_MESSAGE_0409_EXCLUSIVE</t>
         </is>
       </c>
     </row>
@@ -21437,17 +21437,17 @@
     <row r="779">
       <c r="A779" t="inlineStr">
         <is>
-          <t>kk_3210379887</t>
+          <t>kk_4469973568</t>
         </is>
       </c>
       <c r="B779" t="inlineStr">
         <is>
-          <t>01024748405</t>
+          <t>01087158602</t>
         </is>
       </c>
       <c r="C779" t="inlineStr">
         <is>
-          <t>231651</t>
+          <t>283741</t>
         </is>
       </c>
       <c r="D779" t="inlineStr">
@@ -21457,24 +21457,24 @@
       </c>
       <c r="E779" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0410exclusive2</t>
+          <t>KAKAO_CH_MENU_0211_NEW_MEN</t>
         </is>
       </c>
     </row>
     <row r="780">
       <c r="A780" t="inlineStr">
         <is>
-          <t>kk_4469973568</t>
+          <t>kk_3210379887</t>
         </is>
       </c>
       <c r="B780" t="inlineStr">
         <is>
-          <t>01087158602</t>
+          <t>01024748405</t>
         </is>
       </c>
       <c r="C780" t="inlineStr">
         <is>
-          <t>283741</t>
+          <t>231651</t>
         </is>
       </c>
       <c r="D780" t="inlineStr">
@@ -21484,7 +21484,7 @@
       </c>
       <c r="E780" t="inlineStr">
         <is>
-          <t>KAKAO_CH_MENU_0211_NEW_MEN</t>
+          <t>LMS_ECOM_0410exclusive2</t>
         </is>
       </c>
     </row>
@@ -21572,17 +21572,17 @@
     <row r="784">
       <c r="A784" t="inlineStr">
         <is>
-          <t>kk_4600405600</t>
+          <t>kk_4368805733</t>
         </is>
       </c>
       <c r="B784" t="inlineStr">
         <is>
-          <t>01053449477</t>
+          <t>01075528863</t>
         </is>
       </c>
       <c r="C784" t="inlineStr">
         <is>
-          <t>289364</t>
+          <t>279909</t>
         </is>
       </c>
       <c r="D784" t="inlineStr">
@@ -21599,17 +21599,17 @@
     <row r="785">
       <c r="A785" t="inlineStr">
         <is>
-          <t>kk_4368805733</t>
+          <t>kk_4600405600</t>
         </is>
       </c>
       <c r="B785" t="inlineStr">
         <is>
-          <t>01075528863</t>
+          <t>01053449477</t>
         </is>
       </c>
       <c r="C785" t="inlineStr">
         <is>
-          <t>279909</t>
+          <t>289364</t>
         </is>
       </c>
       <c r="D785" t="inlineStr">
@@ -21626,17 +21626,17 @@
     <row r="786">
       <c r="A786" t="inlineStr">
         <is>
-          <t>kk_4514902337</t>
+          <t>kk_3795414578</t>
         </is>
       </c>
       <c r="B786" t="inlineStr">
         <is>
-          <t>01024416928</t>
+          <t>01023131674</t>
         </is>
       </c>
       <c r="C786" t="inlineStr">
         <is>
-          <t>285925</t>
+          <t>257620</t>
         </is>
       </c>
       <c r="D786" t="inlineStr">
@@ -21653,17 +21653,17 @@
     <row r="787">
       <c r="A787" t="inlineStr">
         <is>
-          <t>kk_3795414578</t>
+          <t>kk_4514902337</t>
         </is>
       </c>
       <c r="B787" t="inlineStr">
         <is>
-          <t>01023131674</t>
+          <t>01024416928</t>
         </is>
       </c>
       <c r="C787" t="inlineStr">
         <is>
-          <t>257620</t>
+          <t>285925</t>
         </is>
       </c>
       <c r="D787" t="inlineStr">
@@ -21734,71 +21734,71 @@
     <row r="790">
       <c r="A790" t="inlineStr">
         <is>
-          <t>l00years</t>
+          <t>seizeh</t>
         </is>
       </c>
       <c r="B790" t="inlineStr">
         <is>
-          <t>01053925529</t>
+          <t>01090302539</t>
         </is>
       </c>
       <c r="C790" t="inlineStr">
         <is>
-          <t>229454</t>
+          <t>68751</t>
         </is>
       </c>
       <c r="D790" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E790" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0410exclusive2</t>
+          <t>sa</t>
         </is>
       </c>
     </row>
     <row r="791">
       <c r="A791" t="inlineStr">
         <is>
-          <t>seizeh</t>
+          <t>l00years</t>
         </is>
       </c>
       <c r="B791" t="inlineStr">
         <is>
-          <t>01090302539</t>
+          <t>01053925529</t>
         </is>
       </c>
       <c r="C791" t="inlineStr">
         <is>
-          <t>68751</t>
+          <t>229454</t>
         </is>
       </c>
       <c r="D791" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E791" t="inlineStr">
         <is>
-          <t>sa</t>
+          <t>LMS_ECOM_0410exclusive2</t>
         </is>
       </c>
     </row>
     <row r="792">
       <c r="A792" t="inlineStr">
         <is>
-          <t>pieerot1</t>
+          <t>mplkh</t>
         </is>
       </c>
       <c r="B792" t="inlineStr">
         <is>
-          <t>01054503186</t>
+          <t>01085245802</t>
         </is>
       </c>
       <c r="C792" t="inlineStr">
         <is>
-          <t>29988</t>
+          <t>160698</t>
         </is>
       </c>
       <c r="D792" t="inlineStr">
@@ -21808,24 +21808,24 @@
       </c>
       <c r="E792" t="inlineStr">
         <is>
-          <t>naver_brandsearch_mobile</t>
+          <t>sa</t>
         </is>
       </c>
     </row>
     <row r="793">
       <c r="A793" t="inlineStr">
         <is>
-          <t>noma6420</t>
+          <t>pieerot1</t>
         </is>
       </c>
       <c r="B793" t="inlineStr">
         <is>
-          <t>01071574279</t>
+          <t>01054503186</t>
         </is>
       </c>
       <c r="C793" t="inlineStr">
         <is>
-          <t>304023</t>
+          <t>29988</t>
         </is>
       </c>
       <c r="D793" t="inlineStr">
@@ -21835,24 +21835,24 @@
       </c>
       <c r="E793" t="inlineStr">
         <is>
-          <t>[PF]A SC_상시(1865MF,구매 장바구니)</t>
+          <t>naver_brandsearch_mobile</t>
         </is>
       </c>
     </row>
     <row r="794">
       <c r="A794" t="inlineStr">
         <is>
-          <t>mplkh</t>
+          <t>noma6420</t>
         </is>
       </c>
       <c r="B794" t="inlineStr">
         <is>
-          <t>01085245802</t>
+          <t>01071574279</t>
         </is>
       </c>
       <c r="C794" t="inlineStr">
         <is>
-          <t>160698</t>
+          <t>304023</t>
         </is>
       </c>
       <c r="D794" t="inlineStr">
@@ -21862,7 +21862,7 @@
       </c>
       <c r="E794" t="inlineStr">
         <is>
-          <t>sa</t>
+          <t>[PF]A SC_상시(1865MF,구매 장바구니)</t>
         </is>
       </c>
     </row>
@@ -22841,54 +22841,54 @@
     <row r="831">
       <c r="A831" t="inlineStr">
         <is>
-          <t>kk_4835738911</t>
+          <t>kk_4839354093</t>
         </is>
       </c>
       <c r="B831" t="inlineStr">
         <is>
-          <t>01034422073</t>
+          <t>01052243562</t>
         </is>
       </c>
       <c r="C831" t="inlineStr">
         <is>
-          <t>303885</t>
+          <t>304098</t>
         </is>
       </c>
       <c r="D831" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Organic Traffic</t>
         </is>
       </c>
       <c r="E831" t="inlineStr">
         <is>
-          <t>6968489536332</t>
+          <t>(organic)</t>
         </is>
       </c>
     </row>
     <row r="832">
       <c r="A832" t="inlineStr">
         <is>
-          <t>kk_4839354093</t>
+          <t>kk_4835738911</t>
         </is>
       </c>
       <c r="B832" t="inlineStr">
         <is>
-          <t>01052243562</t>
+          <t>01034422073</t>
         </is>
       </c>
       <c r="C832" t="inlineStr">
         <is>
-          <t>304098</t>
+          <t>303885</t>
         </is>
       </c>
       <c r="D832" t="inlineStr">
         <is>
-          <t>Organic Traffic</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E832" t="inlineStr">
         <is>
-          <t>(organic)</t>
+          <t>6968489536332</t>
         </is>
       </c>
     </row>
@@ -23435,17 +23435,17 @@
     <row r="853">
       <c r="A853" t="inlineStr">
         <is>
-          <t>iceman</t>
+          <t>chi1641</t>
         </is>
       </c>
       <c r="B853" t="inlineStr">
         <is>
-          <t>01025317943</t>
+          <t>01082781641</t>
         </is>
       </c>
       <c r="C853" t="inlineStr">
         <is>
-          <t>92416</t>
+          <t>206726</t>
         </is>
       </c>
       <c r="D853" t="inlineStr">
@@ -23455,24 +23455,24 @@
       </c>
       <c r="E853" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0214_newyear</t>
+          <t>Owned Channel</t>
         </is>
       </c>
     </row>
     <row r="854">
       <c r="A854" t="inlineStr">
         <is>
-          <t>chi1641</t>
+          <t>iceman</t>
         </is>
       </c>
       <c r="B854" t="inlineStr">
         <is>
-          <t>01082781641</t>
+          <t>01025317943</t>
         </is>
       </c>
       <c r="C854" t="inlineStr">
         <is>
-          <t>206726</t>
+          <t>92416</t>
         </is>
       </c>
       <c r="D854" t="inlineStr">
@@ -23482,7 +23482,7 @@
       </c>
       <c r="E854" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>LMS_ECOM_0214_newyear</t>
         </is>
       </c>
     </row>
@@ -23543,54 +23543,54 @@
     <row r="857">
       <c r="A857" t="inlineStr">
         <is>
-          <t>xey5000</t>
+          <t>kk_4840108009</t>
         </is>
       </c>
       <c r="B857" t="inlineStr">
         <is>
-          <t>01087768710</t>
+          <t>01053461423</t>
         </is>
       </c>
       <c r="C857" t="inlineStr">
         <is>
-          <t>143826</t>
+          <t>304129</t>
         </is>
       </c>
       <c r="D857" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E857" t="inlineStr">
         <is>
-          <t>KAKAO_CH_MESSAGE_0409_PANTS</t>
+          <t>6968489536332</t>
         </is>
       </c>
     </row>
     <row r="858">
       <c r="A858" t="inlineStr">
         <is>
-          <t>kk_4840108009</t>
+          <t>xey5000</t>
         </is>
       </c>
       <c r="B858" t="inlineStr">
         <is>
-          <t>01053461423</t>
+          <t>01087768710</t>
         </is>
       </c>
       <c r="C858" t="inlineStr">
         <is>
-          <t>304129</t>
+          <t>143826</t>
         </is>
       </c>
       <c r="D858" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E858" t="inlineStr">
         <is>
-          <t>6968489536332</t>
+          <t>KAKAO_CH_MESSAGE_0409_PANTS</t>
         </is>
       </c>
     </row>
@@ -24029,17 +24029,17 @@
     <row r="875">
       <c r="A875" t="inlineStr">
         <is>
-          <t>kk_2954504655</t>
+          <t>kk_4844665214</t>
         </is>
       </c>
       <c r="B875" t="inlineStr">
         <is>
-          <t>01024942984</t>
+          <t>01033424745</t>
         </is>
       </c>
       <c r="C875" t="inlineStr">
         <is>
-          <t>242733</t>
+          <t>304377</t>
         </is>
       </c>
       <c r="D875" t="inlineStr">
@@ -24056,54 +24056,54 @@
     <row r="876">
       <c r="A876" t="inlineStr">
         <is>
-          <t>kk_4844665214</t>
+          <t>kk_4843611952</t>
         </is>
       </c>
       <c r="B876" t="inlineStr">
         <is>
-          <t>01033424745</t>
+          <t>01068610131</t>
         </is>
       </c>
       <c r="C876" t="inlineStr">
         <is>
-          <t>304377</t>
+          <t>304327</t>
         </is>
       </c>
       <c r="D876" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E876" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>6968489536332</t>
         </is>
       </c>
     </row>
     <row r="877">
       <c r="A877" t="inlineStr">
         <is>
-          <t>kk_4843611952</t>
+          <t>kk_2954504655</t>
         </is>
       </c>
       <c r="B877" t="inlineStr">
         <is>
-          <t>01068610131</t>
+          <t>01024942984</t>
         </is>
       </c>
       <c r="C877" t="inlineStr">
         <is>
-          <t>304327</t>
+          <t>242733</t>
         </is>
       </c>
       <c r="D877" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="E877" t="inlineStr">
         <is>
-          <t>6968489536332</t>
+          <t>Direct</t>
         </is>
       </c>
     </row>
@@ -24326,125 +24326,125 @@
     <row r="886">
       <c r="A886" t="inlineStr">
         <is>
-          <t>kk_4843439707</t>
+          <t>kk_2800477789</t>
         </is>
       </c>
       <c r="B886" t="inlineStr">
         <is>
-          <t>01022248653</t>
+          <t>01035177105</t>
         </is>
       </c>
       <c r="C886" t="inlineStr">
         <is>
-          <t>304310</t>
+          <t>211095</t>
         </is>
       </c>
       <c r="D886" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E886" t="inlineStr">
         <is>
-          <t>6968489536332</t>
+          <t>KAKAO_alimtalk</t>
         </is>
       </c>
     </row>
     <row r="887">
       <c r="A887" t="inlineStr">
         <is>
-          <t>kk_2800477789</t>
+          <t>kk_4843439707</t>
         </is>
       </c>
       <c r="B887" t="inlineStr">
         <is>
-          <t>01035177105</t>
+          <t>01022248653</t>
         </is>
       </c>
       <c r="C887" t="inlineStr">
         <is>
-          <t>211095</t>
+          <t>304310</t>
         </is>
       </c>
       <c r="D887" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E887" t="inlineStr">
         <is>
-          <t>KAKAO_alimtalk</t>
+          <t>6968489536332</t>
         </is>
       </c>
     </row>
     <row r="888">
       <c r="A888" t="inlineStr">
         <is>
-          <t>kk_4844657024</t>
+          <t>dmsdud552</t>
         </is>
       </c>
       <c r="B888" t="inlineStr">
         <is>
-          <t>01033551784</t>
+          <t>01054633672</t>
         </is>
       </c>
       <c r="C888" t="inlineStr">
         <is>
-          <t>304376</t>
+          <t>132110</t>
         </is>
       </c>
       <c r="D888" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Organic Traffic</t>
         </is>
       </c>
       <c r="E888" t="inlineStr">
         <is>
-          <t>6968489536332</t>
+          <t>(referral)</t>
         </is>
       </c>
     </row>
     <row r="889">
       <c r="A889" t="inlineStr">
         <is>
-          <t>dmsdud552</t>
+          <t>kk_4844530515</t>
         </is>
       </c>
       <c r="B889" t="inlineStr">
         <is>
-          <t>01054633672</t>
+          <t>01054558799</t>
         </is>
       </c>
       <c r="C889" t="inlineStr">
         <is>
-          <t>132110</t>
+          <t>304366</t>
         </is>
       </c>
       <c r="D889" t="inlineStr">
         <is>
-          <t>Organic Traffic</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E889" t="inlineStr">
         <is>
-          <t>(referral)</t>
+          <t>6968489536332</t>
         </is>
       </c>
     </row>
     <row r="890">
       <c r="A890" t="inlineStr">
         <is>
-          <t>kk_4844530515</t>
+          <t>kk_4844657024</t>
         </is>
       </c>
       <c r="B890" t="inlineStr">
         <is>
-          <t>01054558799</t>
+          <t>01033551784</t>
         </is>
       </c>
       <c r="C890" t="inlineStr">
         <is>
-          <t>304366</t>
+          <t>304376</t>
         </is>
       </c>
       <c r="D890" t="inlineStr">
@@ -24461,54 +24461,54 @@
     <row r="891">
       <c r="A891" t="inlineStr">
         <is>
-          <t>kk_4543882817</t>
+          <t>kk_4839643736</t>
         </is>
       </c>
       <c r="B891" t="inlineStr">
         <is>
-          <t>01023875300</t>
+          <t>01063617035</t>
         </is>
       </c>
       <c r="C891" t="inlineStr">
         <is>
-          <t>287573</t>
+          <t>304107</t>
         </is>
       </c>
       <c r="D891" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E891" t="inlineStr">
         <is>
-          <t>미분류</t>
+          <t>naver_brandsearch_mobile</t>
         </is>
       </c>
     </row>
     <row r="892">
       <c r="A892" t="inlineStr">
         <is>
-          <t>kk_4839643736</t>
+          <t>kk_4543882817</t>
         </is>
       </c>
       <c r="B892" t="inlineStr">
         <is>
-          <t>01063617035</t>
+          <t>01023875300</t>
         </is>
       </c>
       <c r="C892" t="inlineStr">
         <is>
-          <t>304107</t>
+          <t>287573</t>
         </is>
       </c>
       <c r="D892" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="E892" t="inlineStr">
         <is>
-          <t>naver_brandsearch_mobile</t>
+          <t>미분류</t>
         </is>
       </c>
     </row>
@@ -24542,17 +24542,17 @@
     <row r="894">
       <c r="A894" t="inlineStr">
         <is>
-          <t>kk_4845173313</t>
+          <t>kk_4844453283</t>
         </is>
       </c>
       <c r="B894" t="inlineStr">
         <is>
-          <t>01024436341</t>
+          <t>01090262556</t>
         </is>
       </c>
       <c r="C894" t="inlineStr">
         <is>
-          <t>304397</t>
+          <t>304360</t>
         </is>
       </c>
       <c r="D894" t="inlineStr">
@@ -24569,27 +24569,27 @@
     <row r="895">
       <c r="A895" t="inlineStr">
         <is>
-          <t>kidultyo</t>
+          <t>kk_4843847622</t>
         </is>
       </c>
       <c r="B895" t="inlineStr">
         <is>
-          <t>01037980315</t>
+          <t>01046990393</t>
         </is>
       </c>
       <c r="C895" t="inlineStr">
         <is>
-          <t>304331</t>
+          <t>304336</t>
         </is>
       </c>
       <c r="D895" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Organic Traffic</t>
         </is>
       </c>
       <c r="E895" t="inlineStr">
         <is>
-          <t>6968489536332</t>
+          <t>(organic)</t>
         </is>
       </c>
     </row>
@@ -24623,17 +24623,17 @@
     <row r="897">
       <c r="A897" t="inlineStr">
         <is>
-          <t>kk_4844453283</t>
+          <t>kidultyo</t>
         </is>
       </c>
       <c r="B897" t="inlineStr">
         <is>
-          <t>01090262556</t>
+          <t>01037980315</t>
         </is>
       </c>
       <c r="C897" t="inlineStr">
         <is>
-          <t>304360</t>
+          <t>304331</t>
         </is>
       </c>
       <c r="D897" t="inlineStr">
@@ -24650,27 +24650,27 @@
     <row r="898">
       <c r="A898" t="inlineStr">
         <is>
-          <t>kk_4843847622</t>
+          <t>kk_4845173313</t>
         </is>
       </c>
       <c r="B898" t="inlineStr">
         <is>
-          <t>01046990393</t>
+          <t>01024436341</t>
         </is>
       </c>
       <c r="C898" t="inlineStr">
         <is>
-          <t>304336</t>
+          <t>304397</t>
         </is>
       </c>
       <c r="D898" t="inlineStr">
         <is>
-          <t>Organic Traffic</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E898" t="inlineStr">
         <is>
-          <t>(organic)</t>
+          <t>6968489536332</t>
         </is>
       </c>
     </row>
@@ -24704,17 +24704,17 @@
     <row r="900">
       <c r="A900" t="inlineStr">
         <is>
-          <t>kyoungs424</t>
+          <t>kk_2961062530</t>
         </is>
       </c>
       <c r="B900" t="inlineStr">
         <is>
-          <t>01041509204</t>
+          <t>01050052823</t>
         </is>
       </c>
       <c r="C900" t="inlineStr">
         <is>
-          <t>153760</t>
+          <t>217199</t>
         </is>
       </c>
       <c r="D900" t="inlineStr">
@@ -24724,115 +24724,115 @@
       </c>
       <c r="E900" t="inlineStr">
         <is>
-          <t>KAKAO_alimtalk</t>
+          <t>KAKAO_CH_MENU_0317_S26NEW</t>
         </is>
       </c>
     </row>
     <row r="901">
       <c r="A901" t="inlineStr">
         <is>
-          <t>kk_2961062530</t>
+          <t>kk_4840857472</t>
         </is>
       </c>
       <c r="B901" t="inlineStr">
         <is>
-          <t>01050052823</t>
+          <t>01040551807</t>
         </is>
       </c>
       <c r="C901" t="inlineStr">
         <is>
-          <t>217199</t>
+          <t>304172</t>
         </is>
       </c>
       <c r="D901" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="E901" t="inlineStr">
         <is>
-          <t>KAKAO_CH_MENU_0317_S26NEW</t>
+          <t>Direct</t>
         </is>
       </c>
     </row>
     <row r="902">
       <c r="A902" t="inlineStr">
         <is>
-          <t>kk_4840857472</t>
+          <t>kyoungs424</t>
         </is>
       </c>
       <c r="B902" t="inlineStr">
         <is>
-          <t>01040551807</t>
+          <t>01041509204</t>
         </is>
       </c>
       <c r="C902" t="inlineStr">
         <is>
-          <t>304172</t>
+          <t>153760</t>
         </is>
       </c>
       <c r="D902" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E902" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>KAKAO_alimtalk</t>
         </is>
       </c>
     </row>
     <row r="903">
       <c r="A903" t="inlineStr">
         <is>
-          <t>kk_4839542021</t>
+          <t>kk_4357899204</t>
         </is>
       </c>
       <c r="B903" t="inlineStr">
         <is>
-          <t>01089909663</t>
+          <t>01082772838</t>
         </is>
       </c>
       <c r="C903" t="inlineStr">
         <is>
-          <t>304103</t>
+          <t>279564</t>
         </is>
       </c>
       <c r="D903" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Official SNS</t>
         </is>
       </c>
       <c r="E903" t="inlineStr">
         <is>
-          <t>(organic)</t>
+          <t>(referral)</t>
         </is>
       </c>
     </row>
     <row r="904">
       <c r="A904" t="inlineStr">
         <is>
-          <t>kk_4357899204</t>
+          <t>kk_4839542021</t>
         </is>
       </c>
       <c r="B904" t="inlineStr">
         <is>
-          <t>01082772838</t>
+          <t>01089909663</t>
         </is>
       </c>
       <c r="C904" t="inlineStr">
         <is>
-          <t>279564</t>
+          <t>304103</t>
         </is>
       </c>
       <c r="D904" t="inlineStr">
         <is>
-          <t>Official SNS</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E904" t="inlineStr">
         <is>
-          <t>(referral)</t>
+          <t>(organic)</t>
         </is>
       </c>
     </row>
@@ -24893,81 +24893,81 @@
     <row r="907">
       <c r="A907" t="inlineStr">
         <is>
-          <t>kjo1726</t>
+          <t>plumrhkr1</t>
         </is>
       </c>
       <c r="B907" t="inlineStr">
         <is>
-          <t>01087840160</t>
+          <t>01074112056</t>
         </is>
       </c>
       <c r="C907" t="inlineStr">
         <is>
-          <t>155918</t>
+          <t>303916</t>
         </is>
       </c>
       <c r="D907" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Organic Traffic</t>
         </is>
       </c>
       <c r="E907" t="inlineStr">
         <is>
-          <t>KAKAO_alimtalk</t>
+          <t>(organic)</t>
         </is>
       </c>
     </row>
     <row r="908">
       <c r="A908" t="inlineStr">
         <is>
-          <t>kk_4835912712</t>
+          <t>kjo1726</t>
         </is>
       </c>
       <c r="B908" t="inlineStr">
         <is>
-          <t>01094418375</t>
+          <t>01087840160</t>
         </is>
       </c>
       <c r="C908" t="inlineStr">
         <is>
-          <t>303898</t>
+          <t>155918</t>
         </is>
       </c>
       <c r="D908" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E908" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>KAKAO_alimtalk</t>
         </is>
       </c>
     </row>
     <row r="909">
       <c r="A909" t="inlineStr">
         <is>
-          <t>plumrhkr1</t>
+          <t>kk_4835912712</t>
         </is>
       </c>
       <c r="B909" t="inlineStr">
         <is>
-          <t>01074112056</t>
+          <t>01094418375</t>
         </is>
       </c>
       <c r="C909" t="inlineStr">
         <is>
-          <t>303916</t>
+          <t>303898</t>
         </is>
       </c>
       <c r="D909" t="inlineStr">
         <is>
-          <t>Organic Traffic</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="E909" t="inlineStr">
         <is>
-          <t>(organic)</t>
+          <t>Direct</t>
         </is>
       </c>
     </row>
@@ -25001,162 +25001,162 @@
     <row r="911">
       <c r="A911" t="inlineStr">
         <is>
-          <t>kk_3725118384</t>
+          <t>kk_4839906396</t>
         </is>
       </c>
       <c r="B911" t="inlineStr">
         <is>
-          <t>01035977118</t>
+          <t>01044486524</t>
         </is>
       </c>
       <c r="C911" t="inlineStr">
         <is>
-          <t>252440</t>
+          <t>304113</t>
         </is>
       </c>
       <c r="D911" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Organic Traffic</t>
         </is>
       </c>
       <c r="E911" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0214_newyear</t>
+          <t>(organic)</t>
         </is>
       </c>
     </row>
     <row r="912">
       <c r="A912" t="inlineStr">
         <is>
-          <t>kk_4839906396</t>
+          <t>kk_3725118384</t>
         </is>
       </c>
       <c r="B912" t="inlineStr">
         <is>
-          <t>01044486524</t>
+          <t>01035977118</t>
         </is>
       </c>
       <c r="C912" t="inlineStr">
         <is>
-          <t>304113</t>
+          <t>252440</t>
         </is>
       </c>
       <c r="D912" t="inlineStr">
         <is>
-          <t>Organic Traffic</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E912" t="inlineStr">
         <is>
-          <t>(organic)</t>
+          <t>LMS_ECOM_0214_newyear</t>
         </is>
       </c>
     </row>
     <row r="913">
       <c r="A913" t="inlineStr">
         <is>
-          <t>kk_3798545067</t>
+          <t>kk_4446020087</t>
         </is>
       </c>
       <c r="B913" t="inlineStr">
         <is>
-          <t>01023751319</t>
+          <t>01089773053</t>
         </is>
       </c>
       <c r="C913" t="inlineStr">
         <is>
-          <t>258449</t>
+          <t>282273</t>
         </is>
       </c>
       <c r="D913" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E913" t="inlineStr">
         <is>
-          <t>sa</t>
+          <t>LMS_ECOM_0214_newyear</t>
         </is>
       </c>
     </row>
     <row r="914">
       <c r="A914" t="inlineStr">
         <is>
-          <t>kk_4446020087</t>
+          <t>kk_3798545067</t>
         </is>
       </c>
       <c r="B914" t="inlineStr">
         <is>
-          <t>01089773053</t>
+          <t>01023751319</t>
         </is>
       </c>
       <c r="C914" t="inlineStr">
         <is>
-          <t>282273</t>
+          <t>258449</t>
         </is>
       </c>
       <c r="D914" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E914" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0214_newyear</t>
+          <t>sa</t>
         </is>
       </c>
     </row>
     <row r="915">
       <c r="A915" t="inlineStr">
         <is>
-          <t>kk_4846692829</t>
+          <t>kk_4846749411</t>
         </is>
       </c>
       <c r="B915" t="inlineStr">
         <is>
-          <t>01023649887</t>
+          <t>01031226749</t>
         </is>
       </c>
       <c r="C915" t="inlineStr">
         <is>
-          <t>304457</t>
+          <t>304462</t>
         </is>
       </c>
       <c r="D915" t="inlineStr">
         <is>
-          <t>Organic Traffic</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E915" t="inlineStr">
         <is>
-          <t>(referral)</t>
+          <t>6968489536332</t>
         </is>
       </c>
     </row>
     <row r="916">
       <c r="A916" t="inlineStr">
         <is>
-          <t>kk_4846749411</t>
+          <t>kk_4846692829</t>
         </is>
       </c>
       <c r="B916" t="inlineStr">
         <is>
-          <t>01031226749</t>
+          <t>01023649887</t>
         </is>
       </c>
       <c r="C916" t="inlineStr">
         <is>
-          <t>304462</t>
+          <t>304457</t>
         </is>
       </c>
       <c r="D916" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Organic Traffic</t>
         </is>
       </c>
       <c r="E916" t="inlineStr">
         <is>
-          <t>6968489536332</t>
+          <t>(referral)</t>
         </is>
       </c>
     </row>
@@ -25190,17 +25190,17 @@
     <row r="918">
       <c r="A918" t="inlineStr">
         <is>
-          <t>kk_4844452226</t>
+          <t>kk_4843809795</t>
         </is>
       </c>
       <c r="B918" t="inlineStr">
         <is>
-          <t>01096801866</t>
+          <t>01072864741</t>
         </is>
       </c>
       <c r="C918" t="inlineStr">
         <is>
-          <t>304359</t>
+          <t>304335</t>
         </is>
       </c>
       <c r="D918" t="inlineStr">
@@ -25217,17 +25217,17 @@
     <row r="919">
       <c r="A919" t="inlineStr">
         <is>
-          <t>kk_4843809795</t>
+          <t>kk_4844452226</t>
         </is>
       </c>
       <c r="B919" t="inlineStr">
         <is>
-          <t>01072864741</t>
+          <t>01096801866</t>
         </is>
       </c>
       <c r="C919" t="inlineStr">
         <is>
-          <t>304335</t>
+          <t>304359</t>
         </is>
       </c>
       <c r="D919" t="inlineStr">
@@ -25244,71 +25244,71 @@
     <row r="920">
       <c r="A920" t="inlineStr">
         <is>
-          <t>blblhh</t>
+          <t>kona143</t>
         </is>
       </c>
       <c r="B920" t="inlineStr">
         <is>
-          <t>01033446769</t>
+          <t>01021001916</t>
         </is>
       </c>
       <c r="C920" t="inlineStr">
         <is>
-          <t>304297</t>
+          <t>304260</t>
         </is>
       </c>
       <c r="D920" t="inlineStr">
         <is>
-          <t>Organic Traffic</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E920" t="inlineStr">
         <is>
-          <t>(referral)</t>
+          <t>[PF]전환_회원가입(유사)</t>
         </is>
       </c>
     </row>
     <row r="921">
       <c r="A921" t="inlineStr">
         <is>
-          <t>kona143</t>
+          <t>blblhh</t>
         </is>
       </c>
       <c r="B921" t="inlineStr">
         <is>
-          <t>01021001916</t>
+          <t>01033446769</t>
         </is>
       </c>
       <c r="C921" t="inlineStr">
         <is>
-          <t>304260</t>
+          <t>304297</t>
         </is>
       </c>
       <c r="D921" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Organic Traffic</t>
         </is>
       </c>
       <c r="E921" t="inlineStr">
         <is>
-          <t>[PF]전환_회원가입(유사)</t>
+          <t>(referral)</t>
         </is>
       </c>
     </row>
     <row r="922">
       <c r="A922" t="inlineStr">
         <is>
-          <t>jsb0425</t>
+          <t>kk_4840913383</t>
         </is>
       </c>
       <c r="B922" t="inlineStr">
         <is>
-          <t>01037883670</t>
+          <t>01099887927</t>
         </is>
       </c>
       <c r="C922" t="inlineStr">
         <is>
-          <t>104766</t>
+          <t>304174</t>
         </is>
       </c>
       <c r="D922" t="inlineStr">
@@ -25325,44 +25325,44 @@
     <row r="923">
       <c r="A923" t="inlineStr">
         <is>
-          <t>kk_4840417532</t>
+          <t>kk_3977730443</t>
         </is>
       </c>
       <c r="B923" t="inlineStr">
         <is>
-          <t>01053409288</t>
+          <t>01064291828</t>
         </is>
       </c>
       <c r="C923" t="inlineStr">
         <is>
-          <t>304147</t>
+          <t>271278</t>
         </is>
       </c>
       <c r="D923" t="inlineStr">
         <is>
-          <t>Official SNS</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E923" t="inlineStr">
         <is>
-          <t>EFW_04</t>
+          <t>naver_brandsearch_mobile</t>
         </is>
       </c>
     </row>
     <row r="924">
       <c r="A924" t="inlineStr">
         <is>
-          <t>kk_2750710108</t>
+          <t>jsb0425</t>
         </is>
       </c>
       <c r="B924" t="inlineStr">
         <is>
-          <t>01062707475</t>
+          <t>01037883670</t>
         </is>
       </c>
       <c r="C924" t="inlineStr">
         <is>
-          <t>207211</t>
+          <t>104766</t>
         </is>
       </c>
       <c r="D924" t="inlineStr">
@@ -25379,27 +25379,27 @@
     <row r="925">
       <c r="A925" t="inlineStr">
         <is>
-          <t>kk_3977730443</t>
+          <t>kk_2750710108</t>
         </is>
       </c>
       <c r="B925" t="inlineStr">
         <is>
-          <t>01064291828</t>
+          <t>01062707475</t>
         </is>
       </c>
       <c r="C925" t="inlineStr">
         <is>
-          <t>271278</t>
+          <t>207211</t>
         </is>
       </c>
       <c r="D925" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="E925" t="inlineStr">
         <is>
-          <t>naver_brandsearch_mobile</t>
+          <t>Direct</t>
         </is>
       </c>
     </row>
@@ -25433,81 +25433,81 @@
     <row r="927">
       <c r="A927" t="inlineStr">
         <is>
-          <t>kk_4840913383</t>
+          <t>kk_4840417532</t>
         </is>
       </c>
       <c r="B927" t="inlineStr">
         <is>
-          <t>01099887927</t>
+          <t>01053409288</t>
         </is>
       </c>
       <c r="C927" t="inlineStr">
         <is>
-          <t>304174</t>
+          <t>304147</t>
         </is>
       </c>
       <c r="D927" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>Official SNS</t>
         </is>
       </c>
       <c r="E927" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>EFW_04</t>
         </is>
       </c>
     </row>
     <row r="928">
       <c r="A928" t="inlineStr">
         <is>
-          <t>music214</t>
+          <t>kk_4837971410</t>
         </is>
       </c>
       <c r="B928" t="inlineStr">
         <is>
-          <t>01031023988</t>
+          <t>01045750650</t>
         </is>
       </c>
       <c r="C928" t="inlineStr">
         <is>
-          <t>303965</t>
+          <t>304028</t>
         </is>
       </c>
       <c r="D928" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Official SNS</t>
         </is>
       </c>
       <c r="E928" t="inlineStr">
         <is>
-          <t>6968489536332</t>
+          <t>EFW_04</t>
         </is>
       </c>
     </row>
     <row r="929">
       <c r="A929" t="inlineStr">
         <is>
-          <t>kk_4837971410</t>
+          <t>music214</t>
         </is>
       </c>
       <c r="B929" t="inlineStr">
         <is>
-          <t>01045750650</t>
+          <t>01031023988</t>
         </is>
       </c>
       <c r="C929" t="inlineStr">
         <is>
-          <t>304028</t>
+          <t>303965</t>
         </is>
       </c>
       <c r="D929" t="inlineStr">
         <is>
-          <t>Official SNS</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E929" t="inlineStr">
         <is>
-          <t>EFW_04</t>
+          <t>6968489536332</t>
         </is>
       </c>
     </row>
@@ -25676,44 +25676,44 @@
     <row r="936">
       <c r="A936" t="inlineStr">
         <is>
-          <t>kk_4846761310</t>
+          <t>kk_4651201605</t>
         </is>
       </c>
       <c r="B936" t="inlineStr">
         <is>
-          <t>01091189951</t>
+          <t>01045489411</t>
         </is>
       </c>
       <c r="C936" t="inlineStr">
         <is>
-          <t>304464</t>
+          <t>293053</t>
         </is>
       </c>
       <c r="D936" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E936" t="inlineStr">
         <is>
-          <t>naver_brandsearch_mobile</t>
+          <t>EDM_0411</t>
         </is>
       </c>
     </row>
     <row r="937">
       <c r="A937" t="inlineStr">
         <is>
-          <t>willper</t>
+          <t>kk_4846761310</t>
         </is>
       </c>
       <c r="B937" t="inlineStr">
         <is>
-          <t>01085343440</t>
+          <t>01091189951</t>
         </is>
       </c>
       <c r="C937" t="inlineStr">
         <is>
-          <t>304408</t>
+          <t>304464</t>
         </is>
       </c>
       <c r="D937" t="inlineStr">
@@ -25723,34 +25723,34 @@
       </c>
       <c r="E937" t="inlineStr">
         <is>
-          <t>6968489536332</t>
+          <t>naver_brandsearch_mobile</t>
         </is>
       </c>
     </row>
     <row r="938">
       <c r="A938" t="inlineStr">
         <is>
-          <t>kk_4651201605</t>
+          <t>willper</t>
         </is>
       </c>
       <c r="B938" t="inlineStr">
         <is>
-          <t>01045489411</t>
+          <t>01085343440</t>
         </is>
       </c>
       <c r="C938" t="inlineStr">
         <is>
-          <t>293053</t>
+          <t>304408</t>
         </is>
       </c>
       <c r="D938" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E938" t="inlineStr">
         <is>
-          <t>EDM_0411</t>
+          <t>6968489536332</t>
         </is>
       </c>
     </row>
@@ -25811,17 +25811,17 @@
     <row r="941">
       <c r="A941" t="inlineStr">
         <is>
-          <t>nikemkr</t>
+          <t>kk_4841799872</t>
         </is>
       </c>
       <c r="B941" t="inlineStr">
         <is>
-          <t>01032361592</t>
+          <t>01023236956</t>
         </is>
       </c>
       <c r="C941" t="inlineStr">
         <is>
-          <t>145423</t>
+          <t>304205</t>
         </is>
       </c>
       <c r="D941" t="inlineStr">
@@ -25831,7 +25831,7 @@
       </c>
       <c r="E941" t="inlineStr">
         <is>
-          <t>naver_brandsearch_mobile</t>
+          <t>컬럼비아_DPA_240530</t>
         </is>
       </c>
     </row>
@@ -25865,17 +25865,17 @@
     <row r="943">
       <c r="A943" t="inlineStr">
         <is>
-          <t>kk_4841799872</t>
+          <t>nikemkr</t>
         </is>
       </c>
       <c r="B943" t="inlineStr">
         <is>
-          <t>01023236956</t>
+          <t>01032361592</t>
         </is>
       </c>
       <c r="C943" t="inlineStr">
         <is>
-          <t>304205</t>
+          <t>145423</t>
         </is>
       </c>
       <c r="D943" t="inlineStr">
@@ -25885,61 +25885,61 @@
       </c>
       <c r="E943" t="inlineStr">
         <is>
-          <t>컬럼비아_DPA_240530</t>
+          <t>naver_brandsearch_mobile</t>
         </is>
       </c>
     </row>
     <row r="944">
       <c r="A944" t="inlineStr">
         <is>
-          <t>sbhbi</t>
+          <t>kk_3241081989</t>
         </is>
       </c>
       <c r="B944" t="inlineStr">
         <is>
-          <t>01047153767</t>
+          <t>01072287165</t>
         </is>
       </c>
       <c r="C944" t="inlineStr">
         <is>
-          <t>174291</t>
+          <t>234608</t>
         </is>
       </c>
       <c r="D944" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E944" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>KAKAO_alimtalk</t>
         </is>
       </c>
     </row>
     <row r="945">
       <c r="A945" t="inlineStr">
         <is>
-          <t>kk_3241081989</t>
+          <t>sbhbi</t>
         </is>
       </c>
       <c r="B945" t="inlineStr">
         <is>
-          <t>01072287165</t>
+          <t>01047153767</t>
         </is>
       </c>
       <c r="C945" t="inlineStr">
         <is>
-          <t>234608</t>
+          <t>174291</t>
         </is>
       </c>
       <c r="D945" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="E945" t="inlineStr">
         <is>
-          <t>KAKAO_alimtalk</t>
+          <t>Direct</t>
         </is>
       </c>
     </row>
@@ -25973,17 +25973,17 @@
     <row r="947">
       <c r="A947" t="inlineStr">
         <is>
-          <t>kk_4837152929</t>
+          <t>makaveli</t>
         </is>
       </c>
       <c r="B947" t="inlineStr">
         <is>
-          <t>01047050730</t>
+          <t>01086237086</t>
         </is>
       </c>
       <c r="C947" t="inlineStr">
         <is>
-          <t>303966</t>
+          <t>66164</t>
         </is>
       </c>
       <c r="D947" t="inlineStr">
@@ -25993,24 +25993,24 @@
       </c>
       <c r="E947" t="inlineStr">
         <is>
-          <t>6968489536332</t>
+          <t>naver_brandsearch_mobile</t>
         </is>
       </c>
     </row>
     <row r="948">
       <c r="A948" t="inlineStr">
         <is>
-          <t>kk_4837595875</t>
+          <t>kk_4837152929</t>
         </is>
       </c>
       <c r="B948" t="inlineStr">
         <is>
-          <t>01057852463</t>
+          <t>01047050730</t>
         </is>
       </c>
       <c r="C948" t="inlineStr">
         <is>
-          <t>304000</t>
+          <t>303966</t>
         </is>
       </c>
       <c r="D948" t="inlineStr">
@@ -26027,17 +26027,17 @@
     <row r="949">
       <c r="A949" t="inlineStr">
         <is>
-          <t>sjl4534</t>
+          <t>kk_3430866338</t>
         </is>
       </c>
       <c r="B949" t="inlineStr">
         <is>
-          <t>01028023660</t>
+          <t>01026364692</t>
         </is>
       </c>
       <c r="C949" t="inlineStr">
         <is>
-          <t>174607</t>
+          <t>242249</t>
         </is>
       </c>
       <c r="D949" t="inlineStr">
@@ -26047,115 +26047,115 @@
       </c>
       <c r="E949" t="inlineStr">
         <is>
-          <t>KAKAO_CH_MESSAGE_0409_EXCLUSIVE</t>
+          <t>Email_mkt</t>
         </is>
       </c>
     </row>
     <row r="950">
       <c r="A950" t="inlineStr">
         <is>
-          <t>makaveli</t>
+          <t>sjl4534</t>
         </is>
       </c>
       <c r="B950" t="inlineStr">
         <is>
-          <t>01086237086</t>
+          <t>01028023660</t>
         </is>
       </c>
       <c r="C950" t="inlineStr">
         <is>
-          <t>66164</t>
+          <t>174607</t>
         </is>
       </c>
       <c r="D950" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E950" t="inlineStr">
         <is>
-          <t>naver_brandsearch_mobile</t>
+          <t>KAKAO_CH_MESSAGE_0409_EXCLUSIVE</t>
         </is>
       </c>
     </row>
     <row r="951">
       <c r="A951" t="inlineStr">
         <is>
-          <t>kk_3430866338</t>
+          <t>kk_4837595875</t>
         </is>
       </c>
       <c r="B951" t="inlineStr">
         <is>
-          <t>01026364692</t>
+          <t>01057852463</t>
         </is>
       </c>
       <c r="C951" t="inlineStr">
         <is>
-          <t>242249</t>
+          <t>304000</t>
         </is>
       </c>
       <c r="D951" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E951" t="inlineStr">
         <is>
-          <t>Email_mkt</t>
+          <t>6968489536332</t>
         </is>
       </c>
     </row>
     <row r="952">
       <c r="A952" t="inlineStr">
         <is>
-          <t>sagtp</t>
+          <t>kk_3483542670</t>
         </is>
       </c>
       <c r="B952" t="inlineStr">
         <is>
-          <t>01087431193</t>
+          <t>01025352246</t>
         </is>
       </c>
       <c r="C952" t="inlineStr">
         <is>
-          <t>203717</t>
+          <t>244637</t>
         </is>
       </c>
       <c r="D952" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Awareness</t>
         </is>
       </c>
       <c r="E952" t="inlineStr">
         <is>
-          <t>6968489536332</t>
+          <t>benz_running_program_2026_coupon</t>
         </is>
       </c>
     </row>
     <row r="953">
       <c r="A953" t="inlineStr">
         <is>
-          <t>kk_3483542670</t>
+          <t>sagtp</t>
         </is>
       </c>
       <c r="B953" t="inlineStr">
         <is>
-          <t>01025352246</t>
+          <t>01087431193</t>
         </is>
       </c>
       <c r="C953" t="inlineStr">
         <is>
-          <t>244637</t>
+          <t>203717</t>
         </is>
       </c>
       <c r="D953" t="inlineStr">
         <is>
-          <t>Awareness</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E953" t="inlineStr">
         <is>
-          <t>benz_running_program_2026_coupon</t>
+          <t>6968489536332</t>
         </is>
       </c>
     </row>
@@ -26243,17 +26243,17 @@
     <row r="957">
       <c r="A957" t="inlineStr">
         <is>
-          <t>ch5115</t>
+          <t>imgain0422</t>
         </is>
       </c>
       <c r="B957" t="inlineStr">
         <is>
-          <t>01084479339</t>
+          <t>01029135546</t>
         </is>
       </c>
       <c r="C957" t="inlineStr">
         <is>
-          <t>240557</t>
+          <t>181451</t>
         </is>
       </c>
       <c r="D957" t="inlineStr">
@@ -26270,17 +26270,17 @@
     <row r="958">
       <c r="A958" t="inlineStr">
         <is>
-          <t>kk_4845661756</t>
+          <t>kk_4846729102</t>
         </is>
       </c>
       <c r="B958" t="inlineStr">
         <is>
-          <t>01095936572</t>
+          <t>01084771303</t>
         </is>
       </c>
       <c r="C958" t="inlineStr">
         <is>
-          <t>304422</t>
+          <t>304461</t>
         </is>
       </c>
       <c r="D958" t="inlineStr">
@@ -26297,17 +26297,17 @@
     <row r="959">
       <c r="A959" t="inlineStr">
         <is>
-          <t>kk_4846729102</t>
+          <t>kk_4845661756</t>
         </is>
       </c>
       <c r="B959" t="inlineStr">
         <is>
-          <t>01084771303</t>
+          <t>01095936572</t>
         </is>
       </c>
       <c r="C959" t="inlineStr">
         <is>
-          <t>304461</t>
+          <t>304422</t>
         </is>
       </c>
       <c r="D959" t="inlineStr">
@@ -26324,17 +26324,17 @@
     <row r="960">
       <c r="A960" t="inlineStr">
         <is>
-          <t>kk_3183517395</t>
+          <t>chpuss74</t>
         </is>
       </c>
       <c r="B960" t="inlineStr">
         <is>
-          <t>01082019936</t>
+          <t>01035361091</t>
         </is>
       </c>
       <c r="C960" t="inlineStr">
         <is>
-          <t>228501</t>
+          <t>154462</t>
         </is>
       </c>
       <c r="D960" t="inlineStr">
@@ -26351,44 +26351,44 @@
     <row r="961">
       <c r="A961" t="inlineStr">
         <is>
-          <t>imgain0422</t>
+          <t>kk_2788668233</t>
         </is>
       </c>
       <c r="B961" t="inlineStr">
         <is>
-          <t>01029135546</t>
+          <t>01041696139</t>
         </is>
       </c>
       <c r="C961" t="inlineStr">
         <is>
-          <t>181451</t>
+          <t>210002</t>
         </is>
       </c>
       <c r="D961" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E961" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>6968489536332</t>
         </is>
       </c>
     </row>
     <row r="962">
       <c r="A962" t="inlineStr">
         <is>
-          <t>chpuss74</t>
+          <t>kk_3183517395</t>
         </is>
       </c>
       <c r="B962" t="inlineStr">
         <is>
-          <t>01035361091</t>
+          <t>01082019936</t>
         </is>
       </c>
       <c r="C962" t="inlineStr">
         <is>
-          <t>154462</t>
+          <t>228501</t>
         </is>
       </c>
       <c r="D962" t="inlineStr">
@@ -26405,71 +26405,71 @@
     <row r="963">
       <c r="A963" t="inlineStr">
         <is>
-          <t>kk_2788668233</t>
+          <t>ch5115</t>
         </is>
       </c>
       <c r="B963" t="inlineStr">
         <is>
-          <t>01041696139</t>
+          <t>01084479339</t>
         </is>
       </c>
       <c r="C963" t="inlineStr">
         <is>
-          <t>210002</t>
+          <t>240557</t>
         </is>
       </c>
       <c r="D963" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="E963" t="inlineStr">
         <is>
-          <t>6968489536332</t>
+          <t>Direct</t>
         </is>
       </c>
     </row>
     <row r="964">
       <c r="A964" t="inlineStr">
         <is>
-          <t>kk_4844076820</t>
+          <t>kk_2775500473</t>
         </is>
       </c>
       <c r="B964" t="inlineStr">
         <is>
-          <t>01091346366</t>
+          <t>01045659020</t>
         </is>
       </c>
       <c r="C964" t="inlineStr">
         <is>
-          <t>304343</t>
+          <t>209371</t>
         </is>
       </c>
       <c r="D964" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Organic Traffic</t>
         </is>
       </c>
       <c r="E964" t="inlineStr">
         <is>
-          <t>6968489536332</t>
+          <t>(referral)</t>
         </is>
       </c>
     </row>
     <row r="965">
       <c r="A965" t="inlineStr">
         <is>
-          <t>kk_3650586439</t>
+          <t>goawind</t>
         </is>
       </c>
       <c r="B965" t="inlineStr">
         <is>
-          <t>01029107056</t>
+          <t>01032738938</t>
         </is>
       </c>
       <c r="C965" t="inlineStr">
         <is>
-          <t>249153</t>
+          <t>232021</t>
         </is>
       </c>
       <c r="D965" t="inlineStr">
@@ -26486,108 +26486,108 @@
     <row r="966">
       <c r="A966" t="inlineStr">
         <is>
-          <t>goawind</t>
+          <t>kjhk5404</t>
         </is>
       </c>
       <c r="B966" t="inlineStr">
         <is>
-          <t>01032738938</t>
+          <t>01027390700</t>
         </is>
       </c>
       <c r="C966" t="inlineStr">
         <is>
-          <t>232021</t>
+          <t>280120</t>
         </is>
       </c>
       <c r="D966" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E966" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>KAKAO_alimtalk</t>
         </is>
       </c>
     </row>
     <row r="967">
       <c r="A967" t="inlineStr">
         <is>
-          <t>kk_2775500473</t>
+          <t>kk_3242479813</t>
         </is>
       </c>
       <c r="B967" t="inlineStr">
         <is>
-          <t>01045659020</t>
+          <t>01040431115</t>
         </is>
       </c>
       <c r="C967" t="inlineStr">
         <is>
-          <t>209371</t>
+          <t>234768</t>
         </is>
       </c>
       <c r="D967" t="inlineStr">
         <is>
-          <t>Organic Traffic</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E967" t="inlineStr">
         <is>
-          <t>(referral)</t>
+          <t>LMS_ECOM_0410exclusive2</t>
         </is>
       </c>
     </row>
     <row r="968">
       <c r="A968" t="inlineStr">
         <is>
-          <t>kjhk5404</t>
+          <t>kk_4844076820</t>
         </is>
       </c>
       <c r="B968" t="inlineStr">
         <is>
-          <t>01027390700</t>
+          <t>01091346366</t>
         </is>
       </c>
       <c r="C968" t="inlineStr">
         <is>
-          <t>280120</t>
+          <t>304343</t>
         </is>
       </c>
       <c r="D968" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E968" t="inlineStr">
         <is>
-          <t>KAKAO_alimtalk</t>
+          <t>6968489536332</t>
         </is>
       </c>
     </row>
     <row r="969">
       <c r="A969" t="inlineStr">
         <is>
-          <t>kk_3242479813</t>
+          <t>kk_3650586439</t>
         </is>
       </c>
       <c r="B969" t="inlineStr">
         <is>
-          <t>01040431115</t>
+          <t>01029107056</t>
         </is>
       </c>
       <c r="C969" t="inlineStr">
         <is>
-          <t>234768</t>
+          <t>249153</t>
         </is>
       </c>
       <c r="D969" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="E969" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0410exclusive2</t>
+          <t>Direct</t>
         </is>
       </c>
     </row>
@@ -26648,54 +26648,54 @@
     <row r="972">
       <c r="A972" t="inlineStr">
         <is>
-          <t>kk_4840817001</t>
+          <t>w0309</t>
         </is>
       </c>
       <c r="B972" t="inlineStr">
         <is>
-          <t>01085963383</t>
+          <t>01053481702</t>
         </is>
       </c>
       <c r="C972" t="inlineStr">
         <is>
-          <t>304168</t>
+          <t>126315</t>
         </is>
       </c>
       <c r="D972" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E972" t="inlineStr">
         <is>
-          <t>6968489536332</t>
+          <t>Email_mkt</t>
         </is>
       </c>
     </row>
     <row r="973">
       <c r="A973" t="inlineStr">
         <is>
-          <t>w0309</t>
+          <t>kk_4840817001</t>
         </is>
       </c>
       <c r="B973" t="inlineStr">
         <is>
-          <t>01053481702</t>
+          <t>01085963383</t>
         </is>
       </c>
       <c r="C973" t="inlineStr">
         <is>
-          <t>126315</t>
+          <t>304168</t>
         </is>
       </c>
       <c r="D973" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E973" t="inlineStr">
         <is>
-          <t>Email_mkt</t>
+          <t>6968489536332</t>
         </is>
       </c>
     </row>
@@ -26729,44 +26729,44 @@
     <row r="975">
       <c r="A975" t="inlineStr">
         <is>
-          <t>kk_3213636735</t>
+          <t>xoxoie2</t>
         </is>
       </c>
       <c r="B975" t="inlineStr">
         <is>
-          <t>01071338973</t>
+          <t>01043560834</t>
         </is>
       </c>
       <c r="C975" t="inlineStr">
         <is>
-          <t>232010</t>
+          <t>304072</t>
         </is>
       </c>
       <c r="D975" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Official SNS</t>
         </is>
       </c>
       <c r="E975" t="inlineStr">
         <is>
-          <t>KAKAO_CH_MENU_0226_TRAILRUN</t>
+          <t>EFW_04</t>
         </is>
       </c>
     </row>
     <row r="976">
       <c r="A976" t="inlineStr">
         <is>
-          <t>ssama</t>
+          <t>gus7526</t>
         </is>
       </c>
       <c r="B976" t="inlineStr">
         <is>
-          <t>01056271982</t>
+          <t>01050931023</t>
         </is>
       </c>
       <c r="C976" t="inlineStr">
         <is>
-          <t>47874</t>
+          <t>140860</t>
         </is>
       </c>
       <c r="D976" t="inlineStr">
@@ -26783,44 +26783,44 @@
     <row r="977">
       <c r="A977" t="inlineStr">
         <is>
-          <t>kk_4228106377</t>
+          <t>z090909x</t>
         </is>
       </c>
       <c r="B977" t="inlineStr">
         <is>
-          <t>01063165271</t>
+          <t>01092058111</t>
         </is>
       </c>
       <c r="C977" t="inlineStr">
         <is>
-          <t>273193</t>
+          <t>113003</t>
         </is>
       </c>
       <c r="D977" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E977" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0410exclusive2</t>
+          <t>6968489536332</t>
         </is>
       </c>
     </row>
     <row r="978">
       <c r="A978" t="inlineStr">
         <is>
-          <t>gus7526</t>
+          <t>kk_4228106377</t>
         </is>
       </c>
       <c r="B978" t="inlineStr">
         <is>
-          <t>01050931023</t>
+          <t>01063165271</t>
         </is>
       </c>
       <c r="C978" t="inlineStr">
         <is>
-          <t>140860</t>
+          <t>273193</t>
         </is>
       </c>
       <c r="D978" t="inlineStr">
@@ -26837,54 +26837,54 @@
     <row r="979">
       <c r="A979" t="inlineStr">
         <is>
-          <t>xoxoie2</t>
+          <t>eyounjoo</t>
         </is>
       </c>
       <c r="B979" t="inlineStr">
         <is>
-          <t>01043560834</t>
+          <t>01036167949</t>
         </is>
       </c>
       <c r="C979" t="inlineStr">
         <is>
-          <t>304072</t>
+          <t>283223</t>
         </is>
       </c>
       <c r="D979" t="inlineStr">
         <is>
-          <t>Official SNS</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E979" t="inlineStr">
         <is>
-          <t>EFW_04</t>
+          <t>LMS_ECOM_0410exclusive2</t>
         </is>
       </c>
     </row>
     <row r="980">
       <c r="A980" t="inlineStr">
         <is>
-          <t>kk_4840045474</t>
+          <t>ssama</t>
         </is>
       </c>
       <c r="B980" t="inlineStr">
         <is>
-          <t>01096310429</t>
+          <t>01056271982</t>
         </is>
       </c>
       <c r="C980" t="inlineStr">
         <is>
-          <t>304122</t>
+          <t>47874</t>
         </is>
       </c>
       <c r="D980" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E980" t="inlineStr">
         <is>
-          <t>6968489536332</t>
+          <t>LMS_ECOM_0410exclusive2</t>
         </is>
       </c>
     </row>
@@ -26918,17 +26918,17 @@
     <row r="982">
       <c r="A982" t="inlineStr">
         <is>
-          <t>z090909x</t>
+          <t>kk_4840045474</t>
         </is>
       </c>
       <c r="B982" t="inlineStr">
         <is>
-          <t>01092058111</t>
+          <t>01096310429</t>
         </is>
       </c>
       <c r="C982" t="inlineStr">
         <is>
-          <t>113003</t>
+          <t>304122</t>
         </is>
       </c>
       <c r="D982" t="inlineStr">
@@ -26945,17 +26945,17 @@
     <row r="983">
       <c r="A983" t="inlineStr">
         <is>
-          <t>eyounjoo</t>
+          <t>kk_3213636735</t>
         </is>
       </c>
       <c r="B983" t="inlineStr">
         <is>
-          <t>01036167949</t>
+          <t>01071338973</t>
         </is>
       </c>
       <c r="C983" t="inlineStr">
         <is>
-          <t>283223</t>
+          <t>232010</t>
         </is>
       </c>
       <c r="D983" t="inlineStr">
@@ -26965,24 +26965,24 @@
       </c>
       <c r="E983" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0410exclusive2</t>
+          <t>KAKAO_CH_MENU_0226_TRAILRUN</t>
         </is>
       </c>
     </row>
     <row r="984">
       <c r="A984" t="inlineStr">
         <is>
-          <t>kk_4837597613</t>
+          <t>enel778</t>
         </is>
       </c>
       <c r="B984" t="inlineStr">
         <is>
-          <t>01089218630</t>
+          <t>01086066364</t>
         </is>
       </c>
       <c r="C984" t="inlineStr">
         <is>
-          <t>304001</t>
+          <t>207732</t>
         </is>
       </c>
       <c r="D984" t="inlineStr">
@@ -26992,7 +26992,7 @@
       </c>
       <c r="E984" t="inlineStr">
         <is>
-          <t>KAKAO_CH_MESSAGE_0409_EXCLUSIVE</t>
+          <t>Email_mkt</t>
         </is>
       </c>
     </row>
@@ -27026,17 +27026,17 @@
     <row r="986">
       <c r="A986" t="inlineStr">
         <is>
-          <t>sjk6231</t>
+          <t>scaler</t>
         </is>
       </c>
       <c r="B986" t="inlineStr">
         <is>
-          <t>01031985034</t>
+          <t>01037090080</t>
         </is>
       </c>
       <c r="C986" t="inlineStr">
         <is>
-          <t>281342</t>
+          <t>178752</t>
         </is>
       </c>
       <c r="D986" t="inlineStr">
@@ -27046,24 +27046,24 @@
       </c>
       <c r="E986" t="inlineStr">
         <is>
-          <t>Email_mkt</t>
+          <t>KAKAO_CH_MESSAGE_0409_EXCLUSIVE</t>
         </is>
       </c>
     </row>
     <row r="987">
       <c r="A987" t="inlineStr">
         <is>
-          <t>scaler</t>
+          <t>kk_4837597613</t>
         </is>
       </c>
       <c r="B987" t="inlineStr">
         <is>
-          <t>01037090080</t>
+          <t>01089218630</t>
         </is>
       </c>
       <c r="C987" t="inlineStr">
         <is>
-          <t>178752</t>
+          <t>304001</t>
         </is>
       </c>
       <c r="D987" t="inlineStr">
@@ -27080,17 +27080,17 @@
     <row r="988">
       <c r="A988" t="inlineStr">
         <is>
-          <t>enel778</t>
+          <t>sjk6231</t>
         </is>
       </c>
       <c r="B988" t="inlineStr">
         <is>
-          <t>01086066364</t>
+          <t>01031985034</t>
         </is>
       </c>
       <c r="C988" t="inlineStr">
         <is>
-          <t>207732</t>
+          <t>281342</t>
         </is>
       </c>
       <c r="D988" t="inlineStr">
@@ -27107,17 +27107,17 @@
     <row r="989">
       <c r="A989" t="inlineStr">
         <is>
-          <t>kk_4444429966</t>
+          <t>kk_2757334528</t>
         </is>
       </c>
       <c r="B989" t="inlineStr">
         <is>
-          <t>01032219702</t>
+          <t>01089379633</t>
         </is>
       </c>
       <c r="C989" t="inlineStr">
         <is>
-          <t>282222</t>
+          <t>208240</t>
         </is>
       </c>
       <c r="D989" t="inlineStr">
@@ -27134,54 +27134,54 @@
     <row r="990">
       <c r="A990" t="inlineStr">
         <is>
-          <t>kk_2757334528</t>
+          <t>zodiacz</t>
         </is>
       </c>
       <c r="B990" t="inlineStr">
         <is>
-          <t>01089379633</t>
+          <t>01093671032</t>
         </is>
       </c>
       <c r="C990" t="inlineStr">
         <is>
-          <t>208240</t>
+          <t>108304</t>
         </is>
       </c>
       <c r="D990" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E990" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>pmax</t>
         </is>
       </c>
     </row>
     <row r="991">
       <c r="A991" t="inlineStr">
         <is>
-          <t>zodiacz</t>
+          <t>kk_4444429966</t>
         </is>
       </c>
       <c r="B991" t="inlineStr">
         <is>
-          <t>01093671032</t>
+          <t>01032219702</t>
         </is>
       </c>
       <c r="C991" t="inlineStr">
         <is>
-          <t>108304</t>
+          <t>282222</t>
         </is>
       </c>
       <c r="D991" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="E991" t="inlineStr">
         <is>
-          <t>pmax</t>
+          <t>Direct</t>
         </is>
       </c>
     </row>
@@ -27323,81 +27323,81 @@
     <row r="997">
       <c r="A997" t="inlineStr">
         <is>
-          <t>kk_3169777000</t>
+          <t>kk_4375003446</t>
         </is>
       </c>
       <c r="B997" t="inlineStr">
         <is>
-          <t>01089348462</t>
+          <t>01087457282</t>
         </is>
       </c>
       <c r="C997" t="inlineStr">
         <is>
-          <t>224876</t>
+          <t>280131</t>
         </is>
       </c>
       <c r="D997" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E997" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>LMS_ECOM_0410exclusive2</t>
         </is>
       </c>
     </row>
     <row r="998">
       <c r="A998" t="inlineStr">
         <is>
-          <t>kk_4375003446</t>
+          <t>kk_4844817541</t>
         </is>
       </c>
       <c r="B998" t="inlineStr">
         <is>
-          <t>01087457282</t>
+          <t>01046631832</t>
         </is>
       </c>
       <c r="C998" t="inlineStr">
         <is>
-          <t>280131</t>
+          <t>304380</t>
         </is>
       </c>
       <c r="D998" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E998" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0410exclusive2</t>
+          <t>[PF]전환_회원가입(유사)</t>
         </is>
       </c>
     </row>
     <row r="999">
       <c r="A999" t="inlineStr">
         <is>
-          <t>kk_4844817541</t>
+          <t>kk_3169777000</t>
         </is>
       </c>
       <c r="B999" t="inlineStr">
         <is>
-          <t>01046631832</t>
+          <t>01089348462</t>
         </is>
       </c>
       <c r="C999" t="inlineStr">
         <is>
-          <t>304380</t>
+          <t>224876</t>
         </is>
       </c>
       <c r="D999" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="E999" t="inlineStr">
         <is>
-          <t>[PF]전환_회원가입(유사)</t>
+          <t>Direct</t>
         </is>
       </c>
     </row>
@@ -27431,17 +27431,17 @@
     <row r="1001">
       <c r="A1001" t="inlineStr">
         <is>
-          <t>xuswldls</t>
+          <t>kk_2768989214</t>
         </is>
       </c>
       <c r="B1001" t="inlineStr">
         <is>
-          <t>01027349414</t>
+          <t>01095004289</t>
         </is>
       </c>
       <c r="C1001" t="inlineStr">
         <is>
-          <t>133308</t>
+          <t>209015</t>
         </is>
       </c>
       <c r="D1001" t="inlineStr">
@@ -27485,27 +27485,27 @@
     <row r="1003">
       <c r="A1003" t="inlineStr">
         <is>
-          <t>kk_4247630261</t>
+          <t>ohsm0065</t>
         </is>
       </c>
       <c r="B1003" t="inlineStr">
         <is>
-          <t>01091437323</t>
+          <t>01056170065</t>
         </is>
       </c>
       <c r="C1003" t="inlineStr">
         <is>
-          <t>274140</t>
+          <t>74567</t>
         </is>
       </c>
       <c r="D1003" t="inlineStr">
         <is>
-          <t>Organic Traffic</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E1003" t="inlineStr">
         <is>
-          <t>(referral)</t>
+          <t>[PF]트래픽_유사+관심사</t>
         </is>
       </c>
     </row>
@@ -27539,44 +27539,44 @@
     <row r="1005">
       <c r="A1005" t="inlineStr">
         <is>
-          <t>kk_4472536591</t>
+          <t>kk_4247630261</t>
         </is>
       </c>
       <c r="B1005" t="inlineStr">
         <is>
-          <t>01037057526</t>
+          <t>01091437323</t>
         </is>
       </c>
       <c r="C1005" t="inlineStr">
         <is>
-          <t>283897</t>
+          <t>274140</t>
         </is>
       </c>
       <c r="D1005" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Organic Traffic</t>
         </is>
       </c>
       <c r="E1005" t="inlineStr">
         <is>
-          <t>KAKAO_alimtalk</t>
+          <t>(referral)</t>
         </is>
       </c>
     </row>
     <row r="1006">
       <c r="A1006" t="inlineStr">
         <is>
-          <t>kk_2768989214</t>
+          <t>xuswldls</t>
         </is>
       </c>
       <c r="B1006" t="inlineStr">
         <is>
-          <t>01095004289</t>
+          <t>01027349414</t>
         </is>
       </c>
       <c r="C1006" t="inlineStr">
         <is>
-          <t>209015</t>
+          <t>133308</t>
         </is>
       </c>
       <c r="D1006" t="inlineStr">
@@ -27593,27 +27593,27 @@
     <row r="1007">
       <c r="A1007" t="inlineStr">
         <is>
-          <t>ohsm0065</t>
+          <t>kk_4472536591</t>
         </is>
       </c>
       <c r="B1007" t="inlineStr">
         <is>
-          <t>01056170065</t>
+          <t>01037057526</t>
         </is>
       </c>
       <c r="C1007" t="inlineStr">
         <is>
-          <t>74567</t>
+          <t>283897</t>
         </is>
       </c>
       <c r="D1007" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E1007" t="inlineStr">
         <is>
-          <t>[PF]트래픽_유사+관심사</t>
+          <t>KAKAO_alimtalk</t>
         </is>
       </c>
     </row>
@@ -27674,44 +27674,44 @@
     <row r="1010">
       <c r="A1010" t="inlineStr">
         <is>
-          <t>nesto1</t>
+          <t>kk_3181917333</t>
         </is>
       </c>
       <c r="B1010" t="inlineStr">
         <is>
-          <t>01056603953</t>
+          <t>01072258509</t>
         </is>
       </c>
       <c r="C1010" t="inlineStr">
         <is>
-          <t>125251</t>
+          <t>227380</t>
         </is>
       </c>
       <c r="D1010" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="E1010" t="inlineStr">
         <is>
-          <t>KAKAO_alimtalk</t>
+          <t>Direct</t>
         </is>
       </c>
     </row>
     <row r="1011">
       <c r="A1011" t="inlineStr">
         <is>
-          <t>kk_3837527580</t>
+          <t>nesto1</t>
         </is>
       </c>
       <c r="B1011" t="inlineStr">
         <is>
-          <t>01084311738</t>
+          <t>01056603953</t>
         </is>
       </c>
       <c r="C1011" t="inlineStr">
         <is>
-          <t>264113</t>
+          <t>125251</t>
         </is>
       </c>
       <c r="D1011" t="inlineStr">
@@ -27721,51 +27721,51 @@
       </c>
       <c r="E1011" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0410exclusive2</t>
+          <t>KAKAO_alimtalk</t>
         </is>
       </c>
     </row>
     <row r="1012">
       <c r="A1012" t="inlineStr">
         <is>
-          <t>kk_3181917333</t>
+          <t>kk_3858585698</t>
         </is>
       </c>
       <c r="B1012" t="inlineStr">
         <is>
-          <t>01072258509</t>
+          <t>01092163429</t>
         </is>
       </c>
       <c r="C1012" t="inlineStr">
         <is>
-          <t>227380</t>
+          <t>265508</t>
         </is>
       </c>
       <c r="D1012" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E1012" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>KAKAO_alimtalk</t>
         </is>
       </c>
     </row>
     <row r="1013">
       <c r="A1013" t="inlineStr">
         <is>
-          <t>kk_3858585698</t>
+          <t>kk_3837527580</t>
         </is>
       </c>
       <c r="B1013" t="inlineStr">
         <is>
-          <t>01092163429</t>
+          <t>01084311738</t>
         </is>
       </c>
       <c r="C1013" t="inlineStr">
         <is>
-          <t>265508</t>
+          <t>264113</t>
         </is>
       </c>
       <c r="D1013" t="inlineStr">
@@ -27775,24 +27775,24 @@
       </c>
       <c r="E1013" t="inlineStr">
         <is>
-          <t>KAKAO_alimtalk</t>
+          <t>LMS_ECOM_0410exclusive2</t>
         </is>
       </c>
     </row>
     <row r="1014">
       <c r="A1014" t="inlineStr">
         <is>
-          <t>kk_3185867832</t>
+          <t>kk_4467707148</t>
         </is>
       </c>
       <c r="B1014" t="inlineStr">
         <is>
-          <t>01022086508</t>
+          <t>01030843332</t>
         </is>
       </c>
       <c r="C1014" t="inlineStr">
         <is>
-          <t>229863</t>
+          <t>283560</t>
         </is>
       </c>
       <c r="D1014" t="inlineStr">
@@ -27809,17 +27809,17 @@
     <row r="1015">
       <c r="A1015" t="inlineStr">
         <is>
-          <t>hursean</t>
+          <t>kk_2940110361</t>
         </is>
       </c>
       <c r="B1015" t="inlineStr">
         <is>
-          <t>01091975738</t>
+          <t>01035353200</t>
         </is>
       </c>
       <c r="C1015" t="inlineStr">
         <is>
-          <t>123130</t>
+          <t>216362</t>
         </is>
       </c>
       <c r="D1015" t="inlineStr">
@@ -27829,51 +27829,51 @@
       </c>
       <c r="E1015" t="inlineStr">
         <is>
-          <t>Email_mkt</t>
+          <t>LMS_ECOM_0410exclusive2</t>
         </is>
       </c>
     </row>
     <row r="1016">
       <c r="A1016" t="inlineStr">
         <is>
-          <t>kk_4840061178</t>
+          <t>kk_3933534683</t>
         </is>
       </c>
       <c r="B1016" t="inlineStr">
         <is>
-          <t>01082357895</t>
+          <t>01030153796</t>
         </is>
       </c>
       <c r="C1016" t="inlineStr">
         <is>
-          <t>304124</t>
+          <t>269069</t>
         </is>
       </c>
       <c r="D1016" t="inlineStr">
         <is>
-          <t>Awareness</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="E1016" t="inlineStr">
         <is>
-          <t>benz_running_program_2026_coupon</t>
+          <t>Direct</t>
         </is>
       </c>
     </row>
     <row r="1017">
       <c r="A1017" t="inlineStr">
         <is>
-          <t>kk_2940110361</t>
+          <t>kk_3185867832</t>
         </is>
       </c>
       <c r="B1017" t="inlineStr">
         <is>
-          <t>01035353200</t>
+          <t>01022086508</t>
         </is>
       </c>
       <c r="C1017" t="inlineStr">
         <is>
-          <t>216362</t>
+          <t>229863</t>
         </is>
       </c>
       <c r="D1017" t="inlineStr">
@@ -27890,17 +27890,17 @@
     <row r="1018">
       <c r="A1018" t="inlineStr">
         <is>
-          <t>kk_4338209948</t>
+          <t>mansoogi</t>
         </is>
       </c>
       <c r="B1018" t="inlineStr">
         <is>
-          <t>01088132379</t>
+          <t>01093240897</t>
         </is>
       </c>
       <c r="C1018" t="inlineStr">
         <is>
-          <t>278781</t>
+          <t>25243</t>
         </is>
       </c>
       <c r="D1018" t="inlineStr">
@@ -27910,51 +27910,51 @@
       </c>
       <c r="E1018" t="inlineStr">
         <is>
-          <t>KAKAO_alimtalk</t>
+          <t>LMS_ECOM_0410exclusive2</t>
         </is>
       </c>
     </row>
     <row r="1019">
       <c r="A1019" t="inlineStr">
         <is>
-          <t>kk_3933534683</t>
+          <t>kk_4517851709</t>
         </is>
       </c>
       <c r="B1019" t="inlineStr">
         <is>
-          <t>01030153796</t>
+          <t>01066445714</t>
         </is>
       </c>
       <c r="C1019" t="inlineStr">
         <is>
-          <t>269069</t>
+          <t>286074</t>
         </is>
       </c>
       <c r="D1019" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E1019" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>LMS_ECOM_0410exclusive2</t>
         </is>
       </c>
     </row>
     <row r="1020">
       <c r="A1020" t="inlineStr">
         <is>
-          <t>seul6169</t>
+          <t>kk_4523594127</t>
         </is>
       </c>
       <c r="B1020" t="inlineStr">
         <is>
-          <t>01066116699</t>
+          <t>01085735215</t>
         </is>
       </c>
       <c r="C1020" t="inlineStr">
         <is>
-          <t>234239</t>
+          <t>286358</t>
         </is>
       </c>
       <c r="D1020" t="inlineStr">
@@ -27964,24 +27964,24 @@
       </c>
       <c r="E1020" t="inlineStr">
         <is>
-          <t>KAKAO_alimtalk</t>
+          <t>LMS_ECOM_0410exclusive2</t>
         </is>
       </c>
     </row>
     <row r="1021">
       <c r="A1021" t="inlineStr">
         <is>
-          <t>aya6969</t>
+          <t>seul6169</t>
         </is>
       </c>
       <c r="B1021" t="inlineStr">
         <is>
-          <t>01076590009</t>
+          <t>01066116699</t>
         </is>
       </c>
       <c r="C1021" t="inlineStr">
         <is>
-          <t>162562</t>
+          <t>234239</t>
         </is>
       </c>
       <c r="D1021" t="inlineStr">
@@ -27991,51 +27991,51 @@
       </c>
       <c r="E1021" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0410exclusive2</t>
+          <t>KAKAO_alimtalk</t>
         </is>
       </c>
     </row>
     <row r="1022">
       <c r="A1022" t="inlineStr">
         <is>
-          <t>kk_4467707148</t>
+          <t>kk_4840061178</t>
         </is>
       </c>
       <c r="B1022" t="inlineStr">
         <is>
-          <t>01030843332</t>
+          <t>01082357895</t>
         </is>
       </c>
       <c r="C1022" t="inlineStr">
         <is>
-          <t>283560</t>
+          <t>304124</t>
         </is>
       </c>
       <c r="D1022" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Awareness</t>
         </is>
       </c>
       <c r="E1022" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0410exclusive2</t>
+          <t>benz_running_program_2026_coupon</t>
         </is>
       </c>
     </row>
     <row r="1023">
       <c r="A1023" t="inlineStr">
         <is>
-          <t>mansoogi</t>
+          <t>aya6969</t>
         </is>
       </c>
       <c r="B1023" t="inlineStr">
         <is>
-          <t>01093240897</t>
+          <t>01076590009</t>
         </is>
       </c>
       <c r="C1023" t="inlineStr">
         <is>
-          <t>25243</t>
+          <t>162562</t>
         </is>
       </c>
       <c r="D1023" t="inlineStr">
@@ -28052,44 +28052,44 @@
     <row r="1024">
       <c r="A1024" t="inlineStr">
         <is>
-          <t>kk_4523594127</t>
+          <t>kk_3013902343</t>
         </is>
       </c>
       <c r="B1024" t="inlineStr">
         <is>
-          <t>01085735215</t>
+          <t>01051802326</t>
         </is>
       </c>
       <c r="C1024" t="inlineStr">
         <is>
-          <t>286358</t>
+          <t>219219</t>
         </is>
       </c>
       <c r="D1024" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E1024" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0410exclusive2</t>
+          <t>6968489536332</t>
         </is>
       </c>
     </row>
     <row r="1025">
       <c r="A1025" t="inlineStr">
         <is>
-          <t>kk_4517851709</t>
+          <t>kk_4338209948</t>
         </is>
       </c>
       <c r="B1025" t="inlineStr">
         <is>
-          <t>01066445714</t>
+          <t>01088132379</t>
         </is>
       </c>
       <c r="C1025" t="inlineStr">
         <is>
-          <t>286074</t>
+          <t>278781</t>
         </is>
       </c>
       <c r="D1025" t="inlineStr">
@@ -28099,105 +28099,105 @@
       </c>
       <c r="E1025" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0410exclusive2</t>
+          <t>KAKAO_alimtalk</t>
         </is>
       </c>
     </row>
     <row r="1026">
       <c r="A1026" t="inlineStr">
         <is>
-          <t>kk_3013902343</t>
+          <t>hursean</t>
         </is>
       </c>
       <c r="B1026" t="inlineStr">
         <is>
-          <t>01051802326</t>
+          <t>01091975738</t>
         </is>
       </c>
       <c r="C1026" t="inlineStr">
         <is>
-          <t>219219</t>
+          <t>123130</t>
         </is>
       </c>
       <c r="D1026" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E1026" t="inlineStr">
         <is>
-          <t>6968489536332</t>
+          <t>Email_mkt</t>
         </is>
       </c>
     </row>
     <row r="1027">
       <c r="A1027" t="inlineStr">
         <is>
-          <t>kk_3155938902</t>
+          <t>kk_4351086966</t>
         </is>
       </c>
       <c r="B1027" t="inlineStr">
         <is>
-          <t>01098557018</t>
+          <t>01042088262</t>
         </is>
       </c>
       <c r="C1027" t="inlineStr">
         <is>
-          <t>223731</t>
+          <t>279266</t>
         </is>
       </c>
       <c r="D1027" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="E1027" t="inlineStr">
         <is>
-          <t>KAKAO_CH_MESSAGE_0409_HIKE365SUMMER</t>
+          <t>Direct</t>
         </is>
       </c>
     </row>
     <row r="1028">
       <c r="A1028" t="inlineStr">
         <is>
-          <t>kk_4526169965</t>
+          <t>boram1991</t>
         </is>
       </c>
       <c r="B1028" t="inlineStr">
         <is>
-          <t>01076289838</t>
+          <t>01023431078</t>
         </is>
       </c>
       <c r="C1028" t="inlineStr">
         <is>
-          <t>286553</t>
+          <t>119498</t>
         </is>
       </c>
       <c r="D1028" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E1028" t="inlineStr">
         <is>
-          <t>KAKAO_CH_MESSAGE_0409_HIKE365SUMMER</t>
+          <t>6968489536332</t>
         </is>
       </c>
     </row>
     <row r="1029">
       <c r="A1029" t="inlineStr">
         <is>
-          <t>kk_3373939453</t>
+          <t>kk_3665803645</t>
         </is>
       </c>
       <c r="B1029" t="inlineStr">
         <is>
-          <t>01020110604</t>
+          <t>01095549123</t>
         </is>
       </c>
       <c r="C1029" t="inlineStr">
         <is>
-          <t>240269</t>
+          <t>249835</t>
         </is>
       </c>
       <c r="D1029" t="inlineStr">
@@ -28214,17 +28214,17 @@
     <row r="1030">
       <c r="A1030" t="inlineStr">
         <is>
-          <t>kk_3665803645</t>
+          <t>bbluesea</t>
         </is>
       </c>
       <c r="B1030" t="inlineStr">
         <is>
-          <t>01095549123</t>
+          <t>01076473601</t>
         </is>
       </c>
       <c r="C1030" t="inlineStr">
         <is>
-          <t>249835</t>
+          <t>152067</t>
         </is>
       </c>
       <c r="D1030" t="inlineStr">
@@ -28234,24 +28234,24 @@
       </c>
       <c r="E1030" t="inlineStr">
         <is>
-          <t>KAKAO_CH_MESSAGE_0409_EXCLUSIVE</t>
+          <t>KAKAO_CH_MENU_260406_LIGHTJACKET</t>
         </is>
       </c>
     </row>
     <row r="1031">
       <c r="A1031" t="inlineStr">
         <is>
-          <t>kk_3638512879</t>
+          <t>jhmin000</t>
         </is>
       </c>
       <c r="B1031" t="inlineStr">
         <is>
-          <t>01053330589</t>
+          <t>01086241606</t>
         </is>
       </c>
       <c r="C1031" t="inlineStr">
         <is>
-          <t>248574</t>
+          <t>201165</t>
         </is>
       </c>
       <c r="D1031" t="inlineStr">
@@ -28268,98 +28268,98 @@
     <row r="1032">
       <c r="A1032" t="inlineStr">
         <is>
-          <t>kk_3154612153</t>
+          <t>kk_4726499171</t>
         </is>
       </c>
       <c r="B1032" t="inlineStr">
         <is>
-          <t>01056681753</t>
+          <t>01093851013</t>
         </is>
       </c>
       <c r="C1032" t="inlineStr">
         <is>
-          <t>223664</t>
+          <t>297987</t>
         </is>
       </c>
       <c r="D1032" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E1032" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>KAKAO_CH_MESSAGE_0409_HIKE365SUMMER</t>
         </is>
       </c>
     </row>
     <row r="1033">
       <c r="A1033" t="inlineStr">
         <is>
-          <t>bbluesea</t>
+          <t>kk_3154612153</t>
         </is>
       </c>
       <c r="B1033" t="inlineStr">
         <is>
-          <t>01076473601</t>
+          <t>01056681753</t>
         </is>
       </c>
       <c r="C1033" t="inlineStr">
         <is>
-          <t>152067</t>
+          <t>223664</t>
         </is>
       </c>
       <c r="D1033" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="E1033" t="inlineStr">
         <is>
-          <t>KAKAO_CH_MENU_260406_LIGHTJACKET</t>
+          <t>Direct</t>
         </is>
       </c>
     </row>
     <row r="1034">
       <c r="A1034" t="inlineStr">
         <is>
-          <t>kk_4351086966</t>
+          <t>kk_3155938902</t>
         </is>
       </c>
       <c r="B1034" t="inlineStr">
         <is>
-          <t>01042088262</t>
+          <t>01098557018</t>
         </is>
       </c>
       <c r="C1034" t="inlineStr">
         <is>
-          <t>279266</t>
+          <t>223731</t>
         </is>
       </c>
       <c r="D1034" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E1034" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>KAKAO_CH_MESSAGE_0409_HIKE365SUMMER</t>
         </is>
       </c>
     </row>
     <row r="1035">
       <c r="A1035" t="inlineStr">
         <is>
-          <t>jhmin000</t>
+          <t>kk_4526169965</t>
         </is>
       </c>
       <c r="B1035" t="inlineStr">
         <is>
-          <t>01086241606</t>
+          <t>01076289838</t>
         </is>
       </c>
       <c r="C1035" t="inlineStr">
         <is>
-          <t>201165</t>
+          <t>286553</t>
         </is>
       </c>
       <c r="D1035" t="inlineStr">
@@ -28376,17 +28376,17 @@
     <row r="1036">
       <c r="A1036" t="inlineStr">
         <is>
-          <t>kk_4726499171</t>
+          <t>kk_3638512879</t>
         </is>
       </c>
       <c r="B1036" t="inlineStr">
         <is>
-          <t>01093851013</t>
+          <t>01053330589</t>
         </is>
       </c>
       <c r="C1036" t="inlineStr">
         <is>
-          <t>297987</t>
+          <t>248574</t>
         </is>
       </c>
       <c r="D1036" t="inlineStr">
@@ -28403,27 +28403,27 @@
     <row r="1037">
       <c r="A1037" t="inlineStr">
         <is>
-          <t>boram1991</t>
+          <t>kk_3373939453</t>
         </is>
       </c>
       <c r="B1037" t="inlineStr">
         <is>
-          <t>01023431078</t>
+          <t>01020110604</t>
         </is>
       </c>
       <c r="C1037" t="inlineStr">
         <is>
-          <t>119498</t>
+          <t>240269</t>
         </is>
       </c>
       <c r="D1037" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E1037" t="inlineStr">
         <is>
-          <t>6968489536332</t>
+          <t>KAKAO_CH_MESSAGE_0409_EXCLUSIVE</t>
         </is>
       </c>
     </row>
@@ -28457,17 +28457,17 @@
     <row r="1039">
       <c r="A1039" t="inlineStr">
         <is>
-          <t>pearpear</t>
+          <t>kk_3693586748</t>
         </is>
       </c>
       <c r="B1039" t="inlineStr">
         <is>
-          <t>01048098405</t>
+          <t>01063679756</t>
         </is>
       </c>
       <c r="C1039" t="inlineStr">
         <is>
-          <t>29743</t>
+          <t>251013</t>
         </is>
       </c>
       <c r="D1039" t="inlineStr">
@@ -28477,24 +28477,24 @@
       </c>
       <c r="E1039" t="inlineStr">
         <is>
-          <t>Email_mkt</t>
+          <t>KAKAO_alimtalk</t>
         </is>
       </c>
     </row>
     <row r="1040">
       <c r="A1040" t="inlineStr">
         <is>
-          <t>jeen1228</t>
+          <t>wns1118</t>
         </is>
       </c>
       <c r="B1040" t="inlineStr">
         <is>
-          <t>01033512662</t>
+          <t>01090185590</t>
         </is>
       </c>
       <c r="C1040" t="inlineStr">
         <is>
-          <t>223087</t>
+          <t>303893</t>
         </is>
       </c>
       <c r="D1040" t="inlineStr">
@@ -28511,44 +28511,44 @@
     <row r="1041">
       <c r="A1041" t="inlineStr">
         <is>
-          <t>wns1118</t>
+          <t>kk_3180615052</t>
         </is>
       </c>
       <c r="B1041" t="inlineStr">
         <is>
-          <t>01090185590</t>
+          <t>01077203676</t>
         </is>
       </c>
       <c r="C1041" t="inlineStr">
         <is>
-          <t>303893</t>
+          <t>226112</t>
         </is>
       </c>
       <c r="D1041" t="inlineStr">
         <is>
-          <t>Organic Traffic</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E1041" t="inlineStr">
         <is>
-          <t>(organic)</t>
+          <t>Email_mkt</t>
         </is>
       </c>
     </row>
     <row r="1042">
       <c r="A1042" t="inlineStr">
         <is>
-          <t>kk_3693586748</t>
+          <t>kk_3805755788</t>
         </is>
       </c>
       <c r="B1042" t="inlineStr">
         <is>
-          <t>01063679756</t>
+          <t>01092305284</t>
         </is>
       </c>
       <c r="C1042" t="inlineStr">
         <is>
-          <t>251013</t>
+          <t>260128</t>
         </is>
       </c>
       <c r="D1042" t="inlineStr">
@@ -28558,51 +28558,51 @@
       </c>
       <c r="E1042" t="inlineStr">
         <is>
-          <t>KAKAO_alimtalk</t>
+          <t>Owned Channel</t>
         </is>
       </c>
     </row>
     <row r="1043">
       <c r="A1043" t="inlineStr">
         <is>
-          <t>kk_3180615052</t>
+          <t>jeen1228</t>
         </is>
       </c>
       <c r="B1043" t="inlineStr">
         <is>
-          <t>01077203676</t>
+          <t>01033512662</t>
         </is>
       </c>
       <c r="C1043" t="inlineStr">
         <is>
-          <t>226112</t>
+          <t>223087</t>
         </is>
       </c>
       <c r="D1043" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Organic Traffic</t>
         </is>
       </c>
       <c r="E1043" t="inlineStr">
         <is>
-          <t>Email_mkt</t>
+          <t>(organic)</t>
         </is>
       </c>
     </row>
     <row r="1044">
       <c r="A1044" t="inlineStr">
         <is>
-          <t>kk_3805755788</t>
+          <t>pearpear</t>
         </is>
       </c>
       <c r="B1044" t="inlineStr">
         <is>
-          <t>01092305284</t>
+          <t>01048098405</t>
         </is>
       </c>
       <c r="C1044" t="inlineStr">
         <is>
-          <t>260128</t>
+          <t>29743</t>
         </is>
       </c>
       <c r="D1044" t="inlineStr">
@@ -28612,7 +28612,7 @@
       </c>
       <c r="E1044" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Email_mkt</t>
         </is>
       </c>
     </row>
@@ -28808,27 +28808,27 @@
     <row r="1052">
       <c r="A1052" t="inlineStr">
         <is>
-          <t>hihijs34</t>
+          <t>loyed24</t>
         </is>
       </c>
       <c r="B1052" t="inlineStr">
         <is>
-          <t>01093230529</t>
+          <t>01085487901</t>
         </is>
       </c>
       <c r="C1052" t="inlineStr">
         <is>
-          <t>128947</t>
+          <t>244062</t>
         </is>
       </c>
       <c r="D1052" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E1052" t="inlineStr">
         <is>
-          <t>[PF]A+SC_상시(1865MF,구매+장바구니)</t>
+          <t>LMS_ECOM_0410exclusive2</t>
         </is>
       </c>
     </row>
@@ -28862,44 +28862,44 @@
     <row r="1054">
       <c r="A1054" t="inlineStr">
         <is>
-          <t>loyed24</t>
+          <t>hihijs34</t>
         </is>
       </c>
       <c r="B1054" t="inlineStr">
         <is>
-          <t>01085487901</t>
+          <t>01093230529</t>
         </is>
       </c>
       <c r="C1054" t="inlineStr">
         <is>
-          <t>244062</t>
+          <t>128947</t>
         </is>
       </c>
       <c r="D1054" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E1054" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0410exclusive2</t>
+          <t>[PF]A+SC_상시(1865MF,구매+장바구니)</t>
         </is>
       </c>
     </row>
     <row r="1055">
       <c r="A1055" t="inlineStr">
         <is>
-          <t>kk_3180736217</t>
+          <t>kk_4525043459</t>
         </is>
       </c>
       <c r="B1055" t="inlineStr">
         <is>
-          <t>01036000343</t>
+          <t>01088312135</t>
         </is>
       </c>
       <c r="C1055" t="inlineStr">
         <is>
-          <t>226314</t>
+          <t>286464</t>
         </is>
       </c>
       <c r="D1055" t="inlineStr">
@@ -28916,17 +28916,17 @@
     <row r="1056">
       <c r="A1056" t="inlineStr">
         <is>
-          <t>columbia7</t>
+          <t>dmsql785612</t>
         </is>
       </c>
       <c r="B1056" t="inlineStr">
         <is>
-          <t>01050080025</t>
+          <t>01051590364</t>
         </is>
       </c>
       <c r="C1056" t="inlineStr">
         <is>
-          <t>109980</t>
+          <t>137279</t>
         </is>
       </c>
       <c r="D1056" t="inlineStr">
@@ -28936,24 +28936,24 @@
       </c>
       <c r="E1056" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0410exclusive2</t>
+          <t>Email_mkt</t>
         </is>
       </c>
     </row>
     <row r="1057">
       <c r="A1057" t="inlineStr">
         <is>
-          <t>pls4u</t>
+          <t>inu21c</t>
         </is>
       </c>
       <c r="B1057" t="inlineStr">
         <is>
-          <t>01085985482</t>
+          <t>01035128236</t>
         </is>
       </c>
       <c r="C1057" t="inlineStr">
         <is>
-          <t>88257</t>
+          <t>131940</t>
         </is>
       </c>
       <c r="D1057" t="inlineStr">
@@ -28963,78 +28963,78 @@
       </c>
       <c r="E1057" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0401_trailrunning</t>
+          <t>LMS_ECOM_0410exclusive2</t>
         </is>
       </c>
     </row>
     <row r="1058">
       <c r="A1058" t="inlineStr">
         <is>
-          <t>kk_4452401577</t>
+          <t>kk_4292190414</t>
         </is>
       </c>
       <c r="B1058" t="inlineStr">
         <is>
-          <t>01047428000</t>
+          <t>01095177478</t>
         </is>
       </c>
       <c r="C1058" t="inlineStr">
         <is>
-          <t>282525</t>
+          <t>275998</t>
         </is>
       </c>
       <c r="D1058" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="E1058" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0410exclusive2</t>
+          <t>Direct</t>
         </is>
       </c>
     </row>
     <row r="1059">
       <c r="A1059" t="inlineStr">
         <is>
-          <t>hyschant</t>
+          <t>kk_3721447783</t>
         </is>
       </c>
       <c r="B1059" t="inlineStr">
         <is>
-          <t>01065306675</t>
+          <t>01051311087</t>
         </is>
       </c>
       <c r="C1059" t="inlineStr">
         <is>
-          <t>108579</t>
+          <t>252252</t>
         </is>
       </c>
       <c r="D1059" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="E1059" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0410exclusive2</t>
+          <t>Direct</t>
         </is>
       </c>
     </row>
     <row r="1060">
       <c r="A1060" t="inlineStr">
         <is>
-          <t>camiblanco</t>
+          <t>yongshin</t>
         </is>
       </c>
       <c r="B1060" t="inlineStr">
         <is>
-          <t>01072190103</t>
+          <t>01053867821</t>
         </is>
       </c>
       <c r="C1060" t="inlineStr">
         <is>
-          <t>232545</t>
+          <t>277896</t>
         </is>
       </c>
       <c r="D1060" t="inlineStr">
@@ -29051,44 +29051,44 @@
     <row r="1061">
       <c r="A1061" t="inlineStr">
         <is>
-          <t>kk_4292190414</t>
+          <t>columbia7</t>
         </is>
       </c>
       <c r="B1061" t="inlineStr">
         <is>
-          <t>01095177478</t>
+          <t>01050080025</t>
         </is>
       </c>
       <c r="C1061" t="inlineStr">
         <is>
-          <t>275998</t>
+          <t>109980</t>
         </is>
       </c>
       <c r="D1061" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E1061" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>LMS_ECOM_0410exclusive2</t>
         </is>
       </c>
     </row>
     <row r="1062">
       <c r="A1062" t="inlineStr">
         <is>
-          <t>kk_4525043459</t>
+          <t>kk_4578503399</t>
         </is>
       </c>
       <c r="B1062" t="inlineStr">
         <is>
-          <t>01088312135</t>
+          <t>01088660330</t>
         </is>
       </c>
       <c r="C1062" t="inlineStr">
         <is>
-          <t>286464</t>
+          <t>288374</t>
         </is>
       </c>
       <c r="D1062" t="inlineStr">
@@ -29105,17 +29105,17 @@
     <row r="1063">
       <c r="A1063" t="inlineStr">
         <is>
-          <t>dmsql785612</t>
+          <t>hyschant</t>
         </is>
       </c>
       <c r="B1063" t="inlineStr">
         <is>
-          <t>01051590364</t>
+          <t>01065306675</t>
         </is>
       </c>
       <c r="C1063" t="inlineStr">
         <is>
-          <t>137279</t>
+          <t>108579</t>
         </is>
       </c>
       <c r="D1063" t="inlineStr">
@@ -29125,24 +29125,24 @@
       </c>
       <c r="E1063" t="inlineStr">
         <is>
-          <t>Email_mkt</t>
+          <t>LMS_ECOM_0410exclusive2</t>
         </is>
       </c>
     </row>
     <row r="1064">
       <c r="A1064" t="inlineStr">
         <is>
-          <t>inu21c</t>
+          <t>bobjazz</t>
         </is>
       </c>
       <c r="B1064" t="inlineStr">
         <is>
-          <t>01035128236</t>
+          <t>01084090677</t>
         </is>
       </c>
       <c r="C1064" t="inlineStr">
         <is>
-          <t>131940</t>
+          <t>186218</t>
         </is>
       </c>
       <c r="D1064" t="inlineStr">
@@ -29159,17 +29159,17 @@
     <row r="1065">
       <c r="A1065" t="inlineStr">
         <is>
-          <t>kk_3754052831</t>
+          <t>kk_2825715315</t>
         </is>
       </c>
       <c r="B1065" t="inlineStr">
         <is>
-          <t>01092180804</t>
+          <t>01077229654</t>
         </is>
       </c>
       <c r="C1065" t="inlineStr">
         <is>
-          <t>254339</t>
+          <t>212719</t>
         </is>
       </c>
       <c r="D1065" t="inlineStr">
@@ -29186,17 +29186,17 @@
     <row r="1066">
       <c r="A1066" t="inlineStr">
         <is>
-          <t>sjm700</t>
+          <t>kk_3024318364</t>
         </is>
       </c>
       <c r="B1066" t="inlineStr">
         <is>
-          <t>01077331591</t>
+          <t>01050308038</t>
         </is>
       </c>
       <c r="C1066" t="inlineStr">
         <is>
-          <t>118769</t>
+          <t>219525</t>
         </is>
       </c>
       <c r="D1066" t="inlineStr">
@@ -29213,44 +29213,44 @@
     <row r="1067">
       <c r="A1067" t="inlineStr">
         <is>
-          <t>kk_3721447783</t>
+          <t>kk_3349199057</t>
         </is>
       </c>
       <c r="B1067" t="inlineStr">
         <is>
-          <t>01051311087</t>
+          <t>01071630312</t>
         </is>
       </c>
       <c r="C1067" t="inlineStr">
         <is>
-          <t>252252</t>
+          <t>239388</t>
         </is>
       </c>
       <c r="D1067" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E1067" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>LMS_ECOM_0410exclusive2</t>
         </is>
       </c>
     </row>
     <row r="1068">
       <c r="A1068" t="inlineStr">
         <is>
-          <t>kk_4578503399</t>
+          <t>sjm700</t>
         </is>
       </c>
       <c r="B1068" t="inlineStr">
         <is>
-          <t>01088660330</t>
+          <t>01077331591</t>
         </is>
       </c>
       <c r="C1068" t="inlineStr">
         <is>
-          <t>288374</t>
+          <t>118769</t>
         </is>
       </c>
       <c r="D1068" t="inlineStr">
@@ -29267,44 +29267,44 @@
     <row r="1069">
       <c r="A1069" t="inlineStr">
         <is>
-          <t>yongshin</t>
+          <t>kk_4452401577</t>
         </is>
       </c>
       <c r="B1069" t="inlineStr">
         <is>
-          <t>01053867821</t>
+          <t>01047428000</t>
         </is>
       </c>
       <c r="C1069" t="inlineStr">
         <is>
-          <t>277896</t>
+          <t>282525</t>
         </is>
       </c>
       <c r="D1069" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E1069" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>LMS_ECOM_0410exclusive2</t>
         </is>
       </c>
     </row>
     <row r="1070">
       <c r="A1070" t="inlineStr">
         <is>
-          <t>kk_3973703558</t>
+          <t>kk_3754052831</t>
         </is>
       </c>
       <c r="B1070" t="inlineStr">
         <is>
-          <t>01048590748</t>
+          <t>01092180804</t>
         </is>
       </c>
       <c r="C1070" t="inlineStr">
         <is>
-          <t>271020</t>
+          <t>254339</t>
         </is>
       </c>
       <c r="D1070" t="inlineStr">
@@ -29321,17 +29321,17 @@
     <row r="1071">
       <c r="A1071" t="inlineStr">
         <is>
-          <t>kk_3349199057</t>
+          <t>kk_3973703558</t>
         </is>
       </c>
       <c r="B1071" t="inlineStr">
         <is>
-          <t>01071630312</t>
+          <t>01048590748</t>
         </is>
       </c>
       <c r="C1071" t="inlineStr">
         <is>
-          <t>239388</t>
+          <t>271020</t>
         </is>
       </c>
       <c r="D1071" t="inlineStr">
@@ -29348,44 +29348,44 @@
     <row r="1072">
       <c r="A1072" t="inlineStr">
         <is>
-          <t>kk_3024318364</t>
+          <t>camiblanco</t>
         </is>
       </c>
       <c r="B1072" t="inlineStr">
         <is>
-          <t>01050308038</t>
+          <t>01072190103</t>
         </is>
       </c>
       <c r="C1072" t="inlineStr">
         <is>
-          <t>219525</t>
+          <t>232545</t>
         </is>
       </c>
       <c r="D1072" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="E1072" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0410exclusive2</t>
+          <t>Direct</t>
         </is>
       </c>
     </row>
     <row r="1073">
       <c r="A1073" t="inlineStr">
         <is>
-          <t>kk_2825715315</t>
+          <t>kk_3180736217</t>
         </is>
       </c>
       <c r="B1073" t="inlineStr">
         <is>
-          <t>01077229654</t>
+          <t>01036000343</t>
         </is>
       </c>
       <c r="C1073" t="inlineStr">
         <is>
-          <t>212719</t>
+          <t>226314</t>
         </is>
       </c>
       <c r="D1073" t="inlineStr">
@@ -29402,17 +29402,17 @@
     <row r="1074">
       <c r="A1074" t="inlineStr">
         <is>
-          <t>bobjazz</t>
+          <t>pls4u</t>
         </is>
       </c>
       <c r="B1074" t="inlineStr">
         <is>
-          <t>01084090677</t>
+          <t>01085985482</t>
         </is>
       </c>
       <c r="C1074" t="inlineStr">
         <is>
-          <t>186218</t>
+          <t>88257</t>
         </is>
       </c>
       <c r="D1074" t="inlineStr">
@@ -29422,7 +29422,7 @@
       </c>
       <c r="E1074" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0410exclusive2</t>
+          <t>LMS_ECOM_0401_trailrunning</t>
         </is>
       </c>
     </row>
@@ -29483,71 +29483,71 @@
     <row r="1077">
       <c r="A1077" t="inlineStr">
         <is>
-          <t>kk_3912725759</t>
+          <t>kk_4838419826</t>
         </is>
       </c>
       <c r="B1077" t="inlineStr">
         <is>
-          <t>01062505257</t>
+          <t>01037240798</t>
         </is>
       </c>
       <c r="C1077" t="inlineStr">
         <is>
-          <t>268286</t>
+          <t>304050</t>
         </is>
       </c>
       <c r="D1077" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E1077" t="inlineStr">
         <is>
-          <t>KAKAO_CH_MESSAGE_0409_EXCLUSIVE</t>
+          <t>[PF]트래픽_유사+관심사</t>
         </is>
       </c>
     </row>
     <row r="1078">
       <c r="A1078" t="inlineStr">
         <is>
-          <t>kk_4838419826</t>
+          <t>kk_3912725759</t>
         </is>
       </c>
       <c r="B1078" t="inlineStr">
         <is>
-          <t>01037240798</t>
+          <t>01062505257</t>
         </is>
       </c>
       <c r="C1078" t="inlineStr">
         <is>
-          <t>304050</t>
+          <t>268286</t>
         </is>
       </c>
       <c r="D1078" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E1078" t="inlineStr">
         <is>
-          <t>[PF]트래픽_유사+관심사</t>
+          <t>KAKAO_CH_MESSAGE_0409_EXCLUSIVE</t>
         </is>
       </c>
     </row>
     <row r="1079">
       <c r="A1079" t="inlineStr">
         <is>
-          <t>honga22</t>
+          <t>cjcangel</t>
         </is>
       </c>
       <c r="B1079" t="inlineStr">
         <is>
-          <t>01022690322</t>
+          <t>01089325858</t>
         </is>
       </c>
       <c r="C1079" t="inlineStr">
         <is>
-          <t>147568</t>
+          <t>292800</t>
         </is>
       </c>
       <c r="D1079" t="inlineStr">
@@ -29557,34 +29557,34 @@
       </c>
       <c r="E1079" t="inlineStr">
         <is>
-          <t>KAKAO_alimtalk</t>
+          <t>Email_mkt</t>
         </is>
       </c>
     </row>
     <row r="1080">
       <c r="A1080" t="inlineStr">
         <is>
-          <t>kk_4717085515</t>
+          <t>honga22</t>
         </is>
       </c>
       <c r="B1080" t="inlineStr">
         <is>
-          <t>01052078703</t>
+          <t>01022690322</t>
         </is>
       </c>
       <c r="C1080" t="inlineStr">
         <is>
-          <t>297221</t>
+          <t>147568</t>
         </is>
       </c>
       <c r="D1080" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E1080" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>KAKAO_alimtalk</t>
         </is>
       </c>
     </row>
@@ -29645,27 +29645,27 @@
     <row r="1083">
       <c r="A1083" t="inlineStr">
         <is>
-          <t>cjcangel</t>
+          <t>kk_4717085515</t>
         </is>
       </c>
       <c r="B1083" t="inlineStr">
         <is>
-          <t>01089325858</t>
+          <t>01052078703</t>
         </is>
       </c>
       <c r="C1083" t="inlineStr">
         <is>
-          <t>292800</t>
+          <t>297221</t>
         </is>
       </c>
       <c r="D1083" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="E1083" t="inlineStr">
         <is>
-          <t>Email_mkt</t>
+          <t>Direct</t>
         </is>
       </c>
     </row>
@@ -29699,17 +29699,17 @@
     <row r="1085">
       <c r="A1085" t="inlineStr">
         <is>
-          <t>kimms66</t>
+          <t>happy201106</t>
         </is>
       </c>
       <c r="B1085" t="inlineStr">
         <is>
-          <t>01057634626</t>
+          <t>01090012622</t>
         </is>
       </c>
       <c r="C1085" t="inlineStr">
         <is>
-          <t>180321</t>
+          <t>136050</t>
         </is>
       </c>
       <c r="D1085" t="inlineStr">
@@ -29726,17 +29726,17 @@
     <row r="1086">
       <c r="A1086" t="inlineStr">
         <is>
-          <t>happy201106</t>
+          <t>kimms66</t>
         </is>
       </c>
       <c r="B1086" t="inlineStr">
         <is>
-          <t>01090012622</t>
+          <t>01057634626</t>
         </is>
       </c>
       <c r="C1086" t="inlineStr">
         <is>
-          <t>136050</t>
+          <t>180321</t>
         </is>
       </c>
       <c r="D1086" t="inlineStr">

--- a/reports/member_funnel/downloads/member_funnel_7d_non_buyer.xlsx
+++ b/reports/member_funnel/downloads/member_funnel_7d_non_buyer.xlsx
@@ -15308,17 +15308,17 @@
     <row r="552">
       <c r="A552" t="inlineStr">
         <is>
-          <t>kk_4789688431</t>
+          <t>kk_3483300064</t>
         </is>
       </c>
       <c r="B552" t="inlineStr">
         <is>
-          <t>01099981265</t>
+          <t>01092213404</t>
         </is>
       </c>
       <c r="C552" t="inlineStr">
         <is>
-          <t>302023</t>
+          <t>244619</t>
         </is>
       </c>
       <c r="D552" t="inlineStr">
@@ -15328,7 +15328,7 @@
       </c>
       <c r="E552" t="inlineStr">
         <is>
-          <t>sa</t>
+          <t>naver_brandsearch_mobile</t>
         </is>
       </c>
     </row>
@@ -15362,17 +15362,17 @@
     <row r="554">
       <c r="A554" t="inlineStr">
         <is>
-          <t>kk_3483300064</t>
+          <t>kk_4789688431</t>
         </is>
       </c>
       <c r="B554" t="inlineStr">
         <is>
-          <t>01092213404</t>
+          <t>01099981265</t>
         </is>
       </c>
       <c r="C554" t="inlineStr">
         <is>
-          <t>244619</t>
+          <t>302023</t>
         </is>
       </c>
       <c r="D554" t="inlineStr">
@@ -15382,7 +15382,7 @@
       </c>
       <c r="E554" t="inlineStr">
         <is>
-          <t>naver_brandsearch_mobile</t>
+          <t>sa</t>
         </is>
       </c>
     </row>
@@ -18251,54 +18251,54 @@
     <row r="661">
       <c r="A661" t="inlineStr">
         <is>
-          <t>kk_3913679442</t>
+          <t>kk_3633964155</t>
         </is>
       </c>
       <c r="B661" t="inlineStr">
         <is>
-          <t>01085569215</t>
+          <t>01097743709</t>
         </is>
       </c>
       <c r="C661" t="inlineStr">
         <is>
-          <t>268330</t>
+          <t>248300</t>
         </is>
       </c>
       <c r="D661" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E661" t="inlineStr">
         <is>
-          <t>미분류</t>
+          <t>KAKAO_CH_MENU_0226_EFW</t>
         </is>
       </c>
     </row>
     <row r="662">
       <c r="A662" t="inlineStr">
         <is>
-          <t>kk_3633964155</t>
+          <t>kk_3913679442</t>
         </is>
       </c>
       <c r="B662" t="inlineStr">
         <is>
-          <t>01097743709</t>
+          <t>01085569215</t>
         </is>
       </c>
       <c r="C662" t="inlineStr">
         <is>
-          <t>248300</t>
+          <t>268330</t>
         </is>
       </c>
       <c r="D662" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="E662" t="inlineStr">
         <is>
-          <t>KAKAO_CH_MENU_0226_EFW</t>
+          <t>미분류</t>
         </is>
       </c>
     </row>
@@ -18980,54 +18980,54 @@
     <row r="688">
       <c r="A688" t="inlineStr">
         <is>
-          <t>kk_4367946268</t>
+          <t>kk_3244752214</t>
         </is>
       </c>
       <c r="B688" t="inlineStr">
         <is>
-          <t>01098834648</t>
+          <t>01052959157</t>
         </is>
       </c>
       <c r="C688" t="inlineStr">
         <is>
-          <t>279882</t>
+          <t>234935</t>
         </is>
       </c>
       <c r="D688" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E688" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>KAKAO_CH_MESSAGE_0409_EXCLUSIVE</t>
         </is>
       </c>
     </row>
     <row r="689">
       <c r="A689" t="inlineStr">
         <is>
-          <t>kk_3244752214</t>
+          <t>kk_4367946268</t>
         </is>
       </c>
       <c r="B689" t="inlineStr">
         <is>
-          <t>01052959157</t>
+          <t>01098834648</t>
         </is>
       </c>
       <c r="C689" t="inlineStr">
         <is>
-          <t>234935</t>
+          <t>279882</t>
         </is>
       </c>
       <c r="D689" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="E689" t="inlineStr">
         <is>
-          <t>KAKAO_CH_MESSAGE_0409_EXCLUSIVE</t>
+          <t>Direct</t>
         </is>
       </c>
     </row>
@@ -19169,17 +19169,17 @@
     <row r="695">
       <c r="A695" t="inlineStr">
         <is>
-          <t>kk_4288273717</t>
+          <t>kk_2915134680</t>
         </is>
       </c>
       <c r="B695" t="inlineStr">
         <is>
-          <t>01020746624</t>
+          <t>01085224711</t>
         </is>
       </c>
       <c r="C695" t="inlineStr">
         <is>
-          <t>275762</t>
+          <t>215670</t>
         </is>
       </c>
       <c r="D695" t="inlineStr">
@@ -19189,24 +19189,24 @@
       </c>
       <c r="E695" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0410exclusive2</t>
+          <t>KAKAO_CH_MESSAGE_0409_HIKE365SUMMER</t>
         </is>
       </c>
     </row>
     <row r="696">
       <c r="A696" t="inlineStr">
         <is>
-          <t>kk_2915134680</t>
+          <t>kk_4288273717</t>
         </is>
       </c>
       <c r="B696" t="inlineStr">
         <is>
-          <t>01085224711</t>
+          <t>01020746624</t>
         </is>
       </c>
       <c r="C696" t="inlineStr">
         <is>
-          <t>215670</t>
+          <t>275762</t>
         </is>
       </c>
       <c r="D696" t="inlineStr">
@@ -19216,7 +19216,7 @@
       </c>
       <c r="E696" t="inlineStr">
         <is>
-          <t>KAKAO_CH_MESSAGE_0409_HIKE365SUMMER</t>
+          <t>LMS_ECOM_0410exclusive2</t>
         </is>
       </c>
     </row>
@@ -19304,17 +19304,17 @@
     <row r="700">
       <c r="A700" t="inlineStr">
         <is>
-          <t>hun7662</t>
+          <t>kk_3101119679</t>
         </is>
       </c>
       <c r="B700" t="inlineStr">
         <is>
-          <t>01042311474</t>
+          <t>01093993852</t>
         </is>
       </c>
       <c r="C700" t="inlineStr">
         <is>
-          <t>172790</t>
+          <t>221630</t>
         </is>
       </c>
       <c r="D700" t="inlineStr">
@@ -19331,17 +19331,17 @@
     <row r="701">
       <c r="A701" t="inlineStr">
         <is>
-          <t>kk_3101119679</t>
+          <t>hun7662</t>
         </is>
       </c>
       <c r="B701" t="inlineStr">
         <is>
-          <t>01093993852</t>
+          <t>01042311474</t>
         </is>
       </c>
       <c r="C701" t="inlineStr">
         <is>
-          <t>221630</t>
+          <t>172790</t>
         </is>
       </c>
       <c r="D701" t="inlineStr">
@@ -19736,54 +19736,54 @@
     <row r="716">
       <c r="A716" t="inlineStr">
         <is>
-          <t>kk_4839145768</t>
+          <t>sun1381</t>
         </is>
       </c>
       <c r="B716" t="inlineStr">
         <is>
-          <t>01097367898</t>
+          <t>01037709416</t>
         </is>
       </c>
       <c r="C716" t="inlineStr">
         <is>
-          <t>304085</t>
+          <t>278160</t>
         </is>
       </c>
       <c r="D716" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E716" t="inlineStr">
         <is>
-          <t>naver_brandsearch_pc</t>
+          <t>LMS_ECOM_0410exclusive2</t>
         </is>
       </c>
     </row>
     <row r="717">
       <c r="A717" t="inlineStr">
         <is>
-          <t>sun1381</t>
+          <t>kk_4839145768</t>
         </is>
       </c>
       <c r="B717" t="inlineStr">
         <is>
-          <t>01037709416</t>
+          <t>01097367898</t>
         </is>
       </c>
       <c r="C717" t="inlineStr">
         <is>
-          <t>278160</t>
+          <t>304085</t>
         </is>
       </c>
       <c r="D717" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E717" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0410exclusive2</t>
+          <t>naver_brandsearch_pc</t>
         </is>
       </c>
     </row>
@@ -19817,17 +19817,17 @@
     <row r="719">
       <c r="A719" t="inlineStr">
         <is>
-          <t>kwon1207</t>
+          <t>kk_4324736295</t>
         </is>
       </c>
       <c r="B719" t="inlineStr">
         <is>
-          <t>01055647413</t>
+          <t>01077616385</t>
         </is>
       </c>
       <c r="C719" t="inlineStr">
         <is>
-          <t>129663</t>
+          <t>278190</t>
         </is>
       </c>
       <c r="D719" t="inlineStr">
@@ -19837,24 +19837,24 @@
       </c>
       <c r="E719" t="inlineStr">
         <is>
-          <t>KAKAO_CH_MESSAGE_0409_TRAIL</t>
+          <t>KAKAO_CH_MESSAGE_0409_EXCLUSIVE</t>
         </is>
       </c>
     </row>
     <row r="720">
       <c r="A720" t="inlineStr">
         <is>
-          <t>kk_4324736295</t>
+          <t>kwon1207</t>
         </is>
       </c>
       <c r="B720" t="inlineStr">
         <is>
-          <t>01077616385</t>
+          <t>01055647413</t>
         </is>
       </c>
       <c r="C720" t="inlineStr">
         <is>
-          <t>278190</t>
+          <t>129663</t>
         </is>
       </c>
       <c r="D720" t="inlineStr">
@@ -19864,7 +19864,7 @@
       </c>
       <c r="E720" t="inlineStr">
         <is>
-          <t>KAKAO_CH_MESSAGE_0409_EXCLUSIVE</t>
+          <t>KAKAO_CH_MESSAGE_0409_TRAIL</t>
         </is>
       </c>
     </row>
@@ -19898,17 +19898,17 @@
     <row r="722">
       <c r="A722" t="inlineStr">
         <is>
-          <t>kk_4617674866</t>
+          <t>kk_4641269666</t>
         </is>
       </c>
       <c r="B722" t="inlineStr">
         <is>
-          <t>01062147077</t>
+          <t>01041565334</t>
         </is>
       </c>
       <c r="C722" t="inlineStr">
         <is>
-          <t>290764</t>
+          <t>292505</t>
         </is>
       </c>
       <c r="D722" t="inlineStr">
@@ -19918,24 +19918,24 @@
       </c>
       <c r="E722" t="inlineStr">
         <is>
-          <t>KAKAO_CH_MESSAGE_0409_TRAIL</t>
+          <t>KAKAO_CH_MESSAGE_0409_HIKE365SUMMER</t>
         </is>
       </c>
     </row>
     <row r="723">
       <c r="A723" t="inlineStr">
         <is>
-          <t>kk_4641269666</t>
+          <t>kk_4617674866</t>
         </is>
       </c>
       <c r="B723" t="inlineStr">
         <is>
-          <t>01041565334</t>
+          <t>01062147077</t>
         </is>
       </c>
       <c r="C723" t="inlineStr">
         <is>
-          <t>292505</t>
+          <t>290764</t>
         </is>
       </c>
       <c r="D723" t="inlineStr">
@@ -19945,7 +19945,7 @@
       </c>
       <c r="E723" t="inlineStr">
         <is>
-          <t>KAKAO_CH_MESSAGE_0409_HIKE365SUMMER</t>
+          <t>KAKAO_CH_MESSAGE_0409_TRAIL</t>
         </is>
       </c>
     </row>
@@ -20222,54 +20222,54 @@
     <row r="734">
       <c r="A734" t="inlineStr">
         <is>
-          <t>kk_3631606950</t>
+          <t>kk_2999650964</t>
         </is>
       </c>
       <c r="B734" t="inlineStr">
         <is>
-          <t>01063256163</t>
+          <t>01073667501</t>
         </is>
       </c>
       <c r="C734" t="inlineStr">
         <is>
-          <t>248164</t>
+          <t>218535</t>
         </is>
       </c>
       <c r="D734" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E734" t="inlineStr">
         <is>
-          <t>미분류</t>
+          <t>bizboard</t>
         </is>
       </c>
     </row>
     <row r="735">
       <c r="A735" t="inlineStr">
         <is>
-          <t>kk_2999650964</t>
+          <t>kk_3631606950</t>
         </is>
       </c>
       <c r="B735" t="inlineStr">
         <is>
-          <t>01073667501</t>
+          <t>01063256163</t>
         </is>
       </c>
       <c r="C735" t="inlineStr">
         <is>
-          <t>218535</t>
+          <t>248164</t>
         </is>
       </c>
       <c r="D735" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="E735" t="inlineStr">
         <is>
-          <t>bizboard</t>
+          <t>미분류</t>
         </is>
       </c>
     </row>
@@ -20735,17 +20735,17 @@
     <row r="753">
       <c r="A753" t="inlineStr">
         <is>
-          <t>kk_4639169718</t>
+          <t>kk_4839680663</t>
         </is>
       </c>
       <c r="B753" t="inlineStr">
         <is>
-          <t>01041380770</t>
+          <t>01046429530</t>
         </is>
       </c>
       <c r="C753" t="inlineStr">
         <is>
-          <t>292319</t>
+          <t>304109</t>
         </is>
       </c>
       <c r="D753" t="inlineStr">
@@ -20755,7 +20755,7 @@
       </c>
       <c r="E753" t="inlineStr">
         <is>
-          <t>naver_brandsearch_mobile</t>
+          <t>6968489536332</t>
         </is>
       </c>
     </row>
@@ -20816,17 +20816,17 @@
     <row r="756">
       <c r="A756" t="inlineStr">
         <is>
-          <t>kk_4839680663</t>
+          <t>kk_4639169718</t>
         </is>
       </c>
       <c r="B756" t="inlineStr">
         <is>
-          <t>01046429530</t>
+          <t>01041380770</t>
         </is>
       </c>
       <c r="C756" t="inlineStr">
         <is>
-          <t>304109</t>
+          <t>292319</t>
         </is>
       </c>
       <c r="D756" t="inlineStr">
@@ -20836,24 +20836,24 @@
       </c>
       <c r="E756" t="inlineStr">
         <is>
-          <t>6968489536332</t>
+          <t>naver_brandsearch_mobile</t>
         </is>
       </c>
     </row>
     <row r="757">
       <c r="A757" t="inlineStr">
         <is>
-          <t>kk_3404142353</t>
+          <t>kk_3184667648</t>
         </is>
       </c>
       <c r="B757" t="inlineStr">
         <is>
-          <t>01053293239</t>
+          <t>01043440321</t>
         </is>
       </c>
       <c r="C757" t="inlineStr">
         <is>
-          <t>241289</t>
+          <t>229128</t>
         </is>
       </c>
       <c r="D757" t="inlineStr">
@@ -20863,61 +20863,61 @@
       </c>
       <c r="E757" t="inlineStr">
         <is>
-          <t>[PF]전환_상시(2565MF,비구매자)</t>
+          <t>sa</t>
         </is>
       </c>
     </row>
     <row r="758">
       <c r="A758" t="inlineStr">
         <is>
-          <t>kk_3184667648</t>
+          <t>kk_4431727915</t>
         </is>
       </c>
       <c r="B758" t="inlineStr">
         <is>
-          <t>01043440321</t>
+          <t>01047182896</t>
         </is>
       </c>
       <c r="C758" t="inlineStr">
         <is>
-          <t>229128</t>
+          <t>281759</t>
         </is>
       </c>
       <c r="D758" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E758" t="inlineStr">
         <is>
-          <t>sa</t>
+          <t>KAKAO_CH_MESSAGE_0409_HIKE365SUMMER</t>
         </is>
       </c>
     </row>
     <row r="759">
       <c r="A759" t="inlineStr">
         <is>
-          <t>kk_4431727915</t>
+          <t>kk_3404142353</t>
         </is>
       </c>
       <c r="B759" t="inlineStr">
         <is>
-          <t>01047182896</t>
+          <t>01053293239</t>
         </is>
       </c>
       <c r="C759" t="inlineStr">
         <is>
-          <t>281759</t>
+          <t>241289</t>
         </is>
       </c>
       <c r="D759" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E759" t="inlineStr">
         <is>
-          <t>KAKAO_CH_MESSAGE_0409_HIKE365SUMMER</t>
+          <t>[PF]전환_상시(2565MF,비구매자)</t>
         </is>
       </c>
     </row>
@@ -21086,17 +21086,17 @@
     <row r="766">
       <c r="A766" t="inlineStr">
         <is>
-          <t>mtbok</t>
+          <t>kk_3678962368</t>
         </is>
       </c>
       <c r="B766" t="inlineStr">
         <is>
-          <t>01051284339</t>
+          <t>01041028567</t>
         </is>
       </c>
       <c r="C766" t="inlineStr">
         <is>
-          <t>26917</t>
+          <t>250374</t>
         </is>
       </c>
       <c r="D766" t="inlineStr">
@@ -21113,17 +21113,17 @@
     <row r="767">
       <c r="A767" t="inlineStr">
         <is>
-          <t>kk_3678962368</t>
+          <t>mtbok</t>
         </is>
       </c>
       <c r="B767" t="inlineStr">
         <is>
-          <t>01041028567</t>
+          <t>01051284339</t>
         </is>
       </c>
       <c r="C767" t="inlineStr">
         <is>
-          <t>250374</t>
+          <t>26917</t>
         </is>
       </c>
       <c r="D767" t="inlineStr">
@@ -21221,17 +21221,17 @@
     <row r="771">
       <c r="A771" t="inlineStr">
         <is>
-          <t>kk_2757380967</t>
+          <t>kk_3181873063</t>
         </is>
       </c>
       <c r="B771" t="inlineStr">
         <is>
-          <t>01034635649</t>
+          <t>01026527131</t>
         </is>
       </c>
       <c r="C771" t="inlineStr">
         <is>
-          <t>208245</t>
+          <t>227343</t>
         </is>
       </c>
       <c r="D771" t="inlineStr">
@@ -21248,135 +21248,135 @@
     <row r="772">
       <c r="A772" t="inlineStr">
         <is>
-          <t>kk_4839026541</t>
+          <t>kk_2757380967</t>
         </is>
       </c>
       <c r="B772" t="inlineStr">
         <is>
-          <t>01089431507</t>
+          <t>01034635649</t>
         </is>
       </c>
       <c r="C772" t="inlineStr">
         <is>
-          <t>304082</t>
+          <t>208245</t>
         </is>
       </c>
       <c r="D772" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E772" t="inlineStr">
         <is>
-          <t>[PF]전환_상시(2565MF,비구매자)</t>
+          <t>LMS_ECOM_0410exclusive2</t>
         </is>
       </c>
     </row>
     <row r="773">
       <c r="A773" t="inlineStr">
         <is>
-          <t>kk_4727921763</t>
+          <t>kk_4839026541</t>
         </is>
       </c>
       <c r="B773" t="inlineStr">
         <is>
-          <t>01045673975</t>
+          <t>01089431507</t>
         </is>
       </c>
       <c r="C773" t="inlineStr">
         <is>
-          <t>298138</t>
+          <t>304082</t>
         </is>
       </c>
       <c r="D773" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E773" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>[PF]전환_상시(2565MF,비구매자)</t>
         </is>
       </c>
     </row>
     <row r="774">
       <c r="A774" t="inlineStr">
         <is>
-          <t>kk_3181873063</t>
+          <t>kk_4727921763</t>
         </is>
       </c>
       <c r="B774" t="inlineStr">
         <is>
-          <t>01026527131</t>
+          <t>01045673975</t>
         </is>
       </c>
       <c r="C774" t="inlineStr">
         <is>
-          <t>227343</t>
+          <t>298138</t>
         </is>
       </c>
       <c r="D774" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="E774" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0410exclusive2</t>
+          <t>Direct</t>
         </is>
       </c>
     </row>
     <row r="775">
       <c r="A775" t="inlineStr">
         <is>
-          <t>kk_4519505330</t>
+          <t>kk_3156128258</t>
         </is>
       </c>
       <c r="B775" t="inlineStr">
         <is>
-          <t>01024320028</t>
+          <t>01093995884</t>
         </is>
       </c>
       <c r="C775" t="inlineStr">
         <is>
-          <t>286150</t>
+          <t>223742</t>
         </is>
       </c>
       <c r="D775" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="E775" t="inlineStr">
         <is>
-          <t>KAKAO_CH_MESSAGE_0409_HIKE365SUMMER</t>
+          <t>Direct</t>
         </is>
       </c>
     </row>
     <row r="776">
       <c r="A776" t="inlineStr">
         <is>
-          <t>kk_3156128258</t>
+          <t>kk_4519505330</t>
         </is>
       </c>
       <c r="B776" t="inlineStr">
         <is>
-          <t>01093995884</t>
+          <t>01024320028</t>
         </is>
       </c>
       <c r="C776" t="inlineStr">
         <is>
-          <t>223742</t>
+          <t>286150</t>
         </is>
       </c>
       <c r="D776" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E776" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>KAKAO_CH_MESSAGE_0409_HIKE365SUMMER</t>
         </is>
       </c>
     </row>
@@ -21437,17 +21437,17 @@
     <row r="779">
       <c r="A779" t="inlineStr">
         <is>
-          <t>kk_4469973568</t>
+          <t>kk_3210379887</t>
         </is>
       </c>
       <c r="B779" t="inlineStr">
         <is>
-          <t>01087158602</t>
+          <t>01024748405</t>
         </is>
       </c>
       <c r="C779" t="inlineStr">
         <is>
-          <t>283741</t>
+          <t>231651</t>
         </is>
       </c>
       <c r="D779" t="inlineStr">
@@ -21457,24 +21457,24 @@
       </c>
       <c r="E779" t="inlineStr">
         <is>
-          <t>KAKAO_CH_MENU_0211_NEW_MEN</t>
+          <t>LMS_ECOM_0410exclusive2</t>
         </is>
       </c>
     </row>
     <row r="780">
       <c r="A780" t="inlineStr">
         <is>
-          <t>kk_3210379887</t>
+          <t>kk_4469973568</t>
         </is>
       </c>
       <c r="B780" t="inlineStr">
         <is>
-          <t>01024748405</t>
+          <t>01087158602</t>
         </is>
       </c>
       <c r="C780" t="inlineStr">
         <is>
-          <t>231651</t>
+          <t>283741</t>
         </is>
       </c>
       <c r="D780" t="inlineStr">
@@ -21484,7 +21484,7 @@
       </c>
       <c r="E780" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0410exclusive2</t>
+          <t>KAKAO_CH_MENU_0211_NEW_MEN</t>
         </is>
       </c>
     </row>
@@ -21572,17 +21572,17 @@
     <row r="784">
       <c r="A784" t="inlineStr">
         <is>
-          <t>kk_4368805733</t>
+          <t>kk_4600405600</t>
         </is>
       </c>
       <c r="B784" t="inlineStr">
         <is>
-          <t>01075528863</t>
+          <t>01053449477</t>
         </is>
       </c>
       <c r="C784" t="inlineStr">
         <is>
-          <t>279909</t>
+          <t>289364</t>
         </is>
       </c>
       <c r="D784" t="inlineStr">
@@ -21599,17 +21599,17 @@
     <row r="785">
       <c r="A785" t="inlineStr">
         <is>
-          <t>kk_4600405600</t>
+          <t>kk_4368805733</t>
         </is>
       </c>
       <c r="B785" t="inlineStr">
         <is>
-          <t>01053449477</t>
+          <t>01075528863</t>
         </is>
       </c>
       <c r="C785" t="inlineStr">
         <is>
-          <t>289364</t>
+          <t>279909</t>
         </is>
       </c>
       <c r="D785" t="inlineStr">
@@ -21626,17 +21626,17 @@
     <row r="786">
       <c r="A786" t="inlineStr">
         <is>
-          <t>kk_3795414578</t>
+          <t>kk_4514902337</t>
         </is>
       </c>
       <c r="B786" t="inlineStr">
         <is>
-          <t>01023131674</t>
+          <t>01024416928</t>
         </is>
       </c>
       <c r="C786" t="inlineStr">
         <is>
-          <t>257620</t>
+          <t>285925</t>
         </is>
       </c>
       <c r="D786" t="inlineStr">
@@ -21653,17 +21653,17 @@
     <row r="787">
       <c r="A787" t="inlineStr">
         <is>
-          <t>kk_4514902337</t>
+          <t>kk_3795414578</t>
         </is>
       </c>
       <c r="B787" t="inlineStr">
         <is>
-          <t>01024416928</t>
+          <t>01023131674</t>
         </is>
       </c>
       <c r="C787" t="inlineStr">
         <is>
-          <t>285925</t>
+          <t>257620</t>
         </is>
       </c>
       <c r="D787" t="inlineStr">
@@ -21734,54 +21734,54 @@
     <row r="790">
       <c r="A790" t="inlineStr">
         <is>
-          <t>seizeh</t>
+          <t>l00years</t>
         </is>
       </c>
       <c r="B790" t="inlineStr">
         <is>
-          <t>01090302539</t>
+          <t>01053925529</t>
         </is>
       </c>
       <c r="C790" t="inlineStr">
         <is>
-          <t>68751</t>
+          <t>229454</t>
         </is>
       </c>
       <c r="D790" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E790" t="inlineStr">
         <is>
-          <t>sa</t>
+          <t>LMS_ECOM_0410exclusive2</t>
         </is>
       </c>
     </row>
     <row r="791">
       <c r="A791" t="inlineStr">
         <is>
-          <t>l00years</t>
+          <t>seizeh</t>
         </is>
       </c>
       <c r="B791" t="inlineStr">
         <is>
-          <t>01053925529</t>
+          <t>01090302539</t>
         </is>
       </c>
       <c r="C791" t="inlineStr">
         <is>
-          <t>229454</t>
+          <t>68751</t>
         </is>
       </c>
       <c r="D791" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E791" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0410exclusive2</t>
+          <t>sa</t>
         </is>
       </c>
     </row>
@@ -21815,17 +21815,17 @@
     <row r="793">
       <c r="A793" t="inlineStr">
         <is>
-          <t>pieerot1</t>
+          <t>noma6420</t>
         </is>
       </c>
       <c r="B793" t="inlineStr">
         <is>
-          <t>01054503186</t>
+          <t>01071574279</t>
         </is>
       </c>
       <c r="C793" t="inlineStr">
         <is>
-          <t>29988</t>
+          <t>304023</t>
         </is>
       </c>
       <c r="D793" t="inlineStr">
@@ -21835,24 +21835,24 @@
       </c>
       <c r="E793" t="inlineStr">
         <is>
-          <t>naver_brandsearch_mobile</t>
+          <t>[PF]A SC_상시(1865MF,구매 장바구니)</t>
         </is>
       </c>
     </row>
     <row r="794">
       <c r="A794" t="inlineStr">
         <is>
-          <t>noma6420</t>
+          <t>pieerot1</t>
         </is>
       </c>
       <c r="B794" t="inlineStr">
         <is>
-          <t>01071574279</t>
+          <t>01054503186</t>
         </is>
       </c>
       <c r="C794" t="inlineStr">
         <is>
-          <t>304023</t>
+          <t>29988</t>
         </is>
       </c>
       <c r="D794" t="inlineStr">
@@ -21862,7 +21862,7 @@
       </c>
       <c r="E794" t="inlineStr">
         <is>
-          <t>[PF]A SC_상시(1865MF,구매 장바구니)</t>
+          <t>naver_brandsearch_mobile</t>
         </is>
       </c>
     </row>
@@ -23435,17 +23435,17 @@
     <row r="853">
       <c r="A853" t="inlineStr">
         <is>
-          <t>chi1641</t>
+          <t>iceman</t>
         </is>
       </c>
       <c r="B853" t="inlineStr">
         <is>
-          <t>01082781641</t>
+          <t>01025317943</t>
         </is>
       </c>
       <c r="C853" t="inlineStr">
         <is>
-          <t>206726</t>
+          <t>92416</t>
         </is>
       </c>
       <c r="D853" t="inlineStr">
@@ -23455,24 +23455,24 @@
       </c>
       <c r="E853" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>LMS_ECOM_0214_newyear</t>
         </is>
       </c>
     </row>
     <row r="854">
       <c r="A854" t="inlineStr">
         <is>
-          <t>iceman</t>
+          <t>chi1641</t>
         </is>
       </c>
       <c r="B854" t="inlineStr">
         <is>
-          <t>01025317943</t>
+          <t>01082781641</t>
         </is>
       </c>
       <c r="C854" t="inlineStr">
         <is>
-          <t>92416</t>
+          <t>206726</t>
         </is>
       </c>
       <c r="D854" t="inlineStr">
@@ -23482,7 +23482,7 @@
       </c>
       <c r="E854" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0214_newyear</t>
+          <t>Owned Channel</t>
         </is>
       </c>
     </row>
@@ -23543,54 +23543,54 @@
     <row r="857">
       <c r="A857" t="inlineStr">
         <is>
-          <t>kk_4840108009</t>
+          <t>xey5000</t>
         </is>
       </c>
       <c r="B857" t="inlineStr">
         <is>
-          <t>01053461423</t>
+          <t>01087768710</t>
         </is>
       </c>
       <c r="C857" t="inlineStr">
         <is>
-          <t>304129</t>
+          <t>143826</t>
         </is>
       </c>
       <c r="D857" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E857" t="inlineStr">
         <is>
-          <t>6968489536332</t>
+          <t>KAKAO_CH_MESSAGE_0409_PANTS</t>
         </is>
       </c>
     </row>
     <row r="858">
       <c r="A858" t="inlineStr">
         <is>
-          <t>xey5000</t>
+          <t>kk_4840108009</t>
         </is>
       </c>
       <c r="B858" t="inlineStr">
         <is>
-          <t>01087768710</t>
+          <t>01053461423</t>
         </is>
       </c>
       <c r="C858" t="inlineStr">
         <is>
-          <t>143826</t>
+          <t>304129</t>
         </is>
       </c>
       <c r="D858" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E858" t="inlineStr">
         <is>
-          <t>KAKAO_CH_MESSAGE_0409_PANTS</t>
+          <t>6968489536332</t>
         </is>
       </c>
     </row>
@@ -23678,54 +23678,54 @@
     <row r="862">
       <c r="A862" t="inlineStr">
         <is>
-          <t>qssa2000</t>
+          <t>kk_4841482998</t>
         </is>
       </c>
       <c r="B862" t="inlineStr">
         <is>
-          <t>01020284430</t>
+          <t>01050082734</t>
         </is>
       </c>
       <c r="C862" t="inlineStr">
         <is>
-          <t>202308</t>
+          <t>304194</t>
         </is>
       </c>
       <c r="D862" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="E862" t="inlineStr">
         <is>
-          <t>6968489536332</t>
+          <t>Direct</t>
         </is>
       </c>
     </row>
     <row r="863">
       <c r="A863" t="inlineStr">
         <is>
-          <t>kk_4841482998</t>
+          <t>qssa2000</t>
         </is>
       </c>
       <c r="B863" t="inlineStr">
         <is>
-          <t>01050082734</t>
+          <t>01020284430</t>
         </is>
       </c>
       <c r="C863" t="inlineStr">
         <is>
-          <t>304194</t>
+          <t>202308</t>
         </is>
       </c>
       <c r="D863" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E863" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>6968489536332</t>
         </is>
       </c>
     </row>
@@ -23921,54 +23921,54 @@
     <row r="871">
       <c r="A871" t="inlineStr">
         <is>
-          <t>kmh7710</t>
+          <t>kk_4375973589</t>
         </is>
       </c>
       <c r="B871" t="inlineStr">
         <is>
-          <t>01077108716</t>
+          <t>01096223641</t>
         </is>
       </c>
       <c r="C871" t="inlineStr">
         <is>
-          <t>164951</t>
+          <t>280163</t>
         </is>
       </c>
       <c r="D871" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Organic Traffic</t>
         </is>
       </c>
       <c r="E871" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0214_newyear</t>
+          <t>LMS_ECOM_familycoupon</t>
         </is>
       </c>
     </row>
     <row r="872">
       <c r="A872" t="inlineStr">
         <is>
-          <t>kk_4375973589</t>
+          <t>kmh7710</t>
         </is>
       </c>
       <c r="B872" t="inlineStr">
         <is>
-          <t>01096223641</t>
+          <t>01077108716</t>
         </is>
       </c>
       <c r="C872" t="inlineStr">
         <is>
-          <t>280163</t>
+          <t>164951</t>
         </is>
       </c>
       <c r="D872" t="inlineStr">
         <is>
-          <t>Organic Traffic</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E872" t="inlineStr">
         <is>
-          <t>LMS_ECOM_familycoupon</t>
+          <t>LMS_ECOM_0214_newyear</t>
         </is>
       </c>
     </row>
@@ -24029,17 +24029,17 @@
     <row r="875">
       <c r="A875" t="inlineStr">
         <is>
-          <t>kk_4844665214</t>
+          <t>kk_2954504655</t>
         </is>
       </c>
       <c r="B875" t="inlineStr">
         <is>
-          <t>01033424745</t>
+          <t>01024942984</t>
         </is>
       </c>
       <c r="C875" t="inlineStr">
         <is>
-          <t>304377</t>
+          <t>242733</t>
         </is>
       </c>
       <c r="D875" t="inlineStr">
@@ -24056,54 +24056,54 @@
     <row r="876">
       <c r="A876" t="inlineStr">
         <is>
-          <t>kk_4843611952</t>
+          <t>kk_4844665214</t>
         </is>
       </c>
       <c r="B876" t="inlineStr">
         <is>
-          <t>01068610131</t>
+          <t>01033424745</t>
         </is>
       </c>
       <c r="C876" t="inlineStr">
         <is>
-          <t>304327</t>
+          <t>304377</t>
         </is>
       </c>
       <c r="D876" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="E876" t="inlineStr">
         <is>
-          <t>6968489536332</t>
+          <t>Direct</t>
         </is>
       </c>
     </row>
     <row r="877">
       <c r="A877" t="inlineStr">
         <is>
-          <t>kk_2954504655</t>
+          <t>kk_4843611952</t>
         </is>
       </c>
       <c r="B877" t="inlineStr">
         <is>
-          <t>01024942984</t>
+          <t>01068610131</t>
         </is>
       </c>
       <c r="C877" t="inlineStr">
         <is>
-          <t>242733</t>
+          <t>304327</t>
         </is>
       </c>
       <c r="D877" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E877" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>6968489536332</t>
         </is>
       </c>
     </row>
@@ -24164,17 +24164,17 @@
     <row r="880">
       <c r="A880" t="inlineStr">
         <is>
-          <t>kk_4840093815</t>
+          <t>kk_4839477951</t>
         </is>
       </c>
       <c r="B880" t="inlineStr">
         <is>
-          <t>01095450820</t>
+          <t>01020868012</t>
         </is>
       </c>
       <c r="C880" t="inlineStr">
         <is>
-          <t>304126</t>
+          <t>304101</t>
         </is>
       </c>
       <c r="D880" t="inlineStr">
@@ -24184,24 +24184,24 @@
       </c>
       <c r="E880" t="inlineStr">
         <is>
-          <t>EFW</t>
+          <t>6968489536332</t>
         </is>
       </c>
     </row>
     <row r="881">
       <c r="A881" t="inlineStr">
         <is>
-          <t>kk_4839477951</t>
+          <t>kk_4839544665</t>
         </is>
       </c>
       <c r="B881" t="inlineStr">
         <is>
-          <t>01020868012</t>
+          <t>01055350199</t>
         </is>
       </c>
       <c r="C881" t="inlineStr">
         <is>
-          <t>304101</t>
+          <t>304104</t>
         </is>
       </c>
       <c r="D881" t="inlineStr">
@@ -24218,17 +24218,17 @@
     <row r="882">
       <c r="A882" t="inlineStr">
         <is>
-          <t>kk_4839544665</t>
+          <t>kk_4840093815</t>
         </is>
       </c>
       <c r="B882" t="inlineStr">
         <is>
-          <t>01055350199</t>
+          <t>01095450820</t>
         </is>
       </c>
       <c r="C882" t="inlineStr">
         <is>
-          <t>304104</t>
+          <t>304126</t>
         </is>
       </c>
       <c r="D882" t="inlineStr">
@@ -24238,61 +24238,61 @@
       </c>
       <c r="E882" t="inlineStr">
         <is>
-          <t>6968489536332</t>
+          <t>EFW</t>
         </is>
       </c>
     </row>
     <row r="883">
       <c r="A883" t="inlineStr">
         <is>
-          <t>kk_4837471959</t>
+          <t>kk_3775491761</t>
         </is>
       </c>
       <c r="B883" t="inlineStr">
         <is>
-          <t>01022201041</t>
+          <t>01042990425</t>
         </is>
       </c>
       <c r="C883" t="inlineStr">
         <is>
-          <t>303988</t>
+          <t>255841</t>
         </is>
       </c>
       <c r="D883" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="E883" t="inlineStr">
         <is>
-          <t>6968489536332</t>
+          <t>Direct</t>
         </is>
       </c>
     </row>
     <row r="884">
       <c r="A884" t="inlineStr">
         <is>
-          <t>kk_3775491761</t>
+          <t>kk_4837471959</t>
         </is>
       </c>
       <c r="B884" t="inlineStr">
         <is>
-          <t>01042990425</t>
+          <t>01022201041</t>
         </is>
       </c>
       <c r="C884" t="inlineStr">
         <is>
-          <t>255841</t>
+          <t>303988</t>
         </is>
       </c>
       <c r="D884" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E884" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>6968489536332</t>
         </is>
       </c>
     </row>
@@ -24326,54 +24326,54 @@
     <row r="886">
       <c r="A886" t="inlineStr">
         <is>
-          <t>kk_2800477789</t>
+          <t>kk_4843439707</t>
         </is>
       </c>
       <c r="B886" t="inlineStr">
         <is>
-          <t>01035177105</t>
+          <t>01022248653</t>
         </is>
       </c>
       <c r="C886" t="inlineStr">
         <is>
-          <t>211095</t>
+          <t>304310</t>
         </is>
       </c>
       <c r="D886" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E886" t="inlineStr">
         <is>
-          <t>KAKAO_alimtalk</t>
+          <t>6968489536332</t>
         </is>
       </c>
     </row>
     <row r="887">
       <c r="A887" t="inlineStr">
         <is>
-          <t>kk_4843439707</t>
+          <t>kk_2800477789</t>
         </is>
       </c>
       <c r="B887" t="inlineStr">
         <is>
-          <t>01022248653</t>
+          <t>01035177105</t>
         </is>
       </c>
       <c r="C887" t="inlineStr">
         <is>
-          <t>304310</t>
+          <t>211095</t>
         </is>
       </c>
       <c r="D887" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E887" t="inlineStr">
         <is>
-          <t>6968489536332</t>
+          <t>KAKAO_alimtalk</t>
         </is>
       </c>
     </row>
@@ -24407,17 +24407,17 @@
     <row r="889">
       <c r="A889" t="inlineStr">
         <is>
-          <t>kk_4844530515</t>
+          <t>kk_4844657024</t>
         </is>
       </c>
       <c r="B889" t="inlineStr">
         <is>
-          <t>01054558799</t>
+          <t>01033551784</t>
         </is>
       </c>
       <c r="C889" t="inlineStr">
         <is>
-          <t>304366</t>
+          <t>304376</t>
         </is>
       </c>
       <c r="D889" t="inlineStr">
@@ -24434,17 +24434,17 @@
     <row r="890">
       <c r="A890" t="inlineStr">
         <is>
-          <t>kk_4844657024</t>
+          <t>kk_4844530515</t>
         </is>
       </c>
       <c r="B890" t="inlineStr">
         <is>
-          <t>01033551784</t>
+          <t>01054558799</t>
         </is>
       </c>
       <c r="C890" t="inlineStr">
         <is>
-          <t>304376</t>
+          <t>304366</t>
         </is>
       </c>
       <c r="D890" t="inlineStr">
@@ -24461,54 +24461,54 @@
     <row r="891">
       <c r="A891" t="inlineStr">
         <is>
-          <t>kk_4839643736</t>
+          <t>kk_4543882817</t>
         </is>
       </c>
       <c r="B891" t="inlineStr">
         <is>
-          <t>01063617035</t>
+          <t>01023875300</t>
         </is>
       </c>
       <c r="C891" t="inlineStr">
         <is>
-          <t>304107</t>
+          <t>287573</t>
         </is>
       </c>
       <c r="D891" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="E891" t="inlineStr">
         <is>
-          <t>naver_brandsearch_mobile</t>
+          <t>미분류</t>
         </is>
       </c>
     </row>
     <row r="892">
       <c r="A892" t="inlineStr">
         <is>
-          <t>kk_4543882817</t>
+          <t>kk_4839643736</t>
         </is>
       </c>
       <c r="B892" t="inlineStr">
         <is>
-          <t>01023875300</t>
+          <t>01063617035</t>
         </is>
       </c>
       <c r="C892" t="inlineStr">
         <is>
-          <t>287573</t>
+          <t>304107</t>
         </is>
       </c>
       <c r="D892" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E892" t="inlineStr">
         <is>
-          <t>미분류</t>
+          <t>naver_brandsearch_mobile</t>
         </is>
       </c>
     </row>
@@ -24542,17 +24542,17 @@
     <row r="894">
       <c r="A894" t="inlineStr">
         <is>
-          <t>kk_4844453283</t>
+          <t>kk_4845173313</t>
         </is>
       </c>
       <c r="B894" t="inlineStr">
         <is>
-          <t>01090262556</t>
+          <t>01024436341</t>
         </is>
       </c>
       <c r="C894" t="inlineStr">
         <is>
-          <t>304360</t>
+          <t>304397</t>
         </is>
       </c>
       <c r="D894" t="inlineStr">
@@ -24623,17 +24623,17 @@
     <row r="897">
       <c r="A897" t="inlineStr">
         <is>
-          <t>kidultyo</t>
+          <t>kk_4844453283</t>
         </is>
       </c>
       <c r="B897" t="inlineStr">
         <is>
-          <t>01037980315</t>
+          <t>01090262556</t>
         </is>
       </c>
       <c r="C897" t="inlineStr">
         <is>
-          <t>304331</t>
+          <t>304360</t>
         </is>
       </c>
       <c r="D897" t="inlineStr">
@@ -24650,17 +24650,17 @@
     <row r="898">
       <c r="A898" t="inlineStr">
         <is>
-          <t>kk_4845173313</t>
+          <t>kk_4845121221</t>
         </is>
       </c>
       <c r="B898" t="inlineStr">
         <is>
-          <t>01024436341</t>
+          <t>01044632332</t>
         </is>
       </c>
       <c r="C898" t="inlineStr">
         <is>
-          <t>304397</t>
+          <t>304393</t>
         </is>
       </c>
       <c r="D898" t="inlineStr">
@@ -24677,17 +24677,17 @@
     <row r="899">
       <c r="A899" t="inlineStr">
         <is>
-          <t>kk_4845121221</t>
+          <t>kidultyo</t>
         </is>
       </c>
       <c r="B899" t="inlineStr">
         <is>
-          <t>01044632332</t>
+          <t>01037980315</t>
         </is>
       </c>
       <c r="C899" t="inlineStr">
         <is>
-          <t>304393</t>
+          <t>304331</t>
         </is>
       </c>
       <c r="D899" t="inlineStr">
@@ -24839,135 +24839,135 @@
     <row r="905">
       <c r="A905" t="inlineStr">
         <is>
-          <t>vvip6905</t>
+          <t>kk_4838574281</t>
         </is>
       </c>
       <c r="B905" t="inlineStr">
         <is>
-          <t>01085855275</t>
+          <t>01092229876</t>
         </is>
       </c>
       <c r="C905" t="inlineStr">
         <is>
-          <t>304027</t>
+          <t>304061</t>
         </is>
       </c>
       <c r="D905" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E905" t="inlineStr">
         <is>
-          <t>Email_mkt</t>
+          <t>6968489536332</t>
         </is>
       </c>
     </row>
     <row r="906">
       <c r="A906" t="inlineStr">
         <is>
-          <t>kk_4838574281</t>
+          <t>vvip6905</t>
         </is>
       </c>
       <c r="B906" t="inlineStr">
         <is>
-          <t>01092229876</t>
+          <t>01085855275</t>
         </is>
       </c>
       <c r="C906" t="inlineStr">
         <is>
-          <t>304061</t>
+          <t>304027</t>
         </is>
       </c>
       <c r="D906" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E906" t="inlineStr">
         <is>
-          <t>6968489536332</t>
+          <t>Email_mkt</t>
         </is>
       </c>
     </row>
     <row r="907">
       <c r="A907" t="inlineStr">
         <is>
-          <t>plumrhkr1</t>
+          <t>kk_4835912712</t>
         </is>
       </c>
       <c r="B907" t="inlineStr">
         <is>
-          <t>01074112056</t>
+          <t>01094418375</t>
         </is>
       </c>
       <c r="C907" t="inlineStr">
         <is>
-          <t>303916</t>
+          <t>303898</t>
         </is>
       </c>
       <c r="D907" t="inlineStr">
         <is>
-          <t>Organic Traffic</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="E907" t="inlineStr">
         <is>
-          <t>(organic)</t>
+          <t>Direct</t>
         </is>
       </c>
     </row>
     <row r="908">
       <c r="A908" t="inlineStr">
         <is>
-          <t>kjo1726</t>
+          <t>plumrhkr1</t>
         </is>
       </c>
       <c r="B908" t="inlineStr">
         <is>
-          <t>01087840160</t>
+          <t>01074112056</t>
         </is>
       </c>
       <c r="C908" t="inlineStr">
         <is>
-          <t>155918</t>
+          <t>303916</t>
         </is>
       </c>
       <c r="D908" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Organic Traffic</t>
         </is>
       </c>
       <c r="E908" t="inlineStr">
         <is>
-          <t>KAKAO_alimtalk</t>
+          <t>(organic)</t>
         </is>
       </c>
     </row>
     <row r="909">
       <c r="A909" t="inlineStr">
         <is>
-          <t>kk_4835912712</t>
+          <t>kjo1726</t>
         </is>
       </c>
       <c r="B909" t="inlineStr">
         <is>
-          <t>01094418375</t>
+          <t>01087840160</t>
         </is>
       </c>
       <c r="C909" t="inlineStr">
         <is>
-          <t>303898</t>
+          <t>155918</t>
         </is>
       </c>
       <c r="D909" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E909" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>KAKAO_alimtalk</t>
         </is>
       </c>
     </row>
@@ -25001,108 +25001,108 @@
     <row r="911">
       <c r="A911" t="inlineStr">
         <is>
-          <t>kk_4839906396</t>
+          <t>kk_3725118384</t>
         </is>
       </c>
       <c r="B911" t="inlineStr">
         <is>
-          <t>01044486524</t>
+          <t>01035977118</t>
         </is>
       </c>
       <c r="C911" t="inlineStr">
         <is>
-          <t>304113</t>
+          <t>252440</t>
         </is>
       </c>
       <c r="D911" t="inlineStr">
         <is>
-          <t>Organic Traffic</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E911" t="inlineStr">
         <is>
-          <t>(organic)</t>
+          <t>LMS_ECOM_0214_newyear</t>
         </is>
       </c>
     </row>
     <row r="912">
       <c r="A912" t="inlineStr">
         <is>
-          <t>kk_3725118384</t>
+          <t>kk_4839906396</t>
         </is>
       </c>
       <c r="B912" t="inlineStr">
         <is>
-          <t>01035977118</t>
+          <t>01044486524</t>
         </is>
       </c>
       <c r="C912" t="inlineStr">
         <is>
-          <t>252440</t>
+          <t>304113</t>
         </is>
       </c>
       <c r="D912" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Organic Traffic</t>
         </is>
       </c>
       <c r="E912" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0214_newyear</t>
+          <t>(organic)</t>
         </is>
       </c>
     </row>
     <row r="913">
       <c r="A913" t="inlineStr">
         <is>
-          <t>kk_4446020087</t>
+          <t>kk_3798545067</t>
         </is>
       </c>
       <c r="B913" t="inlineStr">
         <is>
-          <t>01089773053</t>
+          <t>01023751319</t>
         </is>
       </c>
       <c r="C913" t="inlineStr">
         <is>
-          <t>282273</t>
+          <t>258449</t>
         </is>
       </c>
       <c r="D913" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E913" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0214_newyear</t>
+          <t>sa</t>
         </is>
       </c>
     </row>
     <row r="914">
       <c r="A914" t="inlineStr">
         <is>
-          <t>kk_3798545067</t>
+          <t>kk_4446020087</t>
         </is>
       </c>
       <c r="B914" t="inlineStr">
         <is>
-          <t>01023751319</t>
+          <t>01089773053</t>
         </is>
       </c>
       <c r="C914" t="inlineStr">
         <is>
-          <t>258449</t>
+          <t>282273</t>
         </is>
       </c>
       <c r="D914" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E914" t="inlineStr">
         <is>
-          <t>sa</t>
+          <t>LMS_ECOM_0214_newyear</t>
         </is>
       </c>
     </row>
@@ -25163,27 +25163,27 @@
     <row r="917">
       <c r="A917" t="inlineStr">
         <is>
-          <t>kk_4844609437</t>
+          <t>kk_4844452226</t>
         </is>
       </c>
       <c r="B917" t="inlineStr">
         <is>
-          <t>01046808931</t>
+          <t>01096801866</t>
         </is>
       </c>
       <c r="C917" t="inlineStr">
         <is>
-          <t>304372</t>
+          <t>304359</t>
         </is>
       </c>
       <c r="D917" t="inlineStr">
         <is>
-          <t>Official SNS</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E917" t="inlineStr">
         <is>
-          <t>(referral)</t>
+          <t>6968489536332</t>
         </is>
       </c>
     </row>
@@ -25217,27 +25217,27 @@
     <row r="919">
       <c r="A919" t="inlineStr">
         <is>
-          <t>kk_4844452226</t>
+          <t>kk_4844609437</t>
         </is>
       </c>
       <c r="B919" t="inlineStr">
         <is>
-          <t>01096801866</t>
+          <t>01046808931</t>
         </is>
       </c>
       <c r="C919" t="inlineStr">
         <is>
-          <t>304359</t>
+          <t>304372</t>
         </is>
       </c>
       <c r="D919" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Official SNS</t>
         </is>
       </c>
       <c r="E919" t="inlineStr">
         <is>
-          <t>6968489536332</t>
+          <t>(referral)</t>
         </is>
       </c>
     </row>
@@ -25325,44 +25325,44 @@
     <row r="923">
       <c r="A923" t="inlineStr">
         <is>
-          <t>kk_3977730443</t>
+          <t>kk_4840417532</t>
         </is>
       </c>
       <c r="B923" t="inlineStr">
         <is>
-          <t>01064291828</t>
+          <t>01053409288</t>
         </is>
       </c>
       <c r="C923" t="inlineStr">
         <is>
-          <t>271278</t>
+          <t>304147</t>
         </is>
       </c>
       <c r="D923" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Official SNS</t>
         </is>
       </c>
       <c r="E923" t="inlineStr">
         <is>
-          <t>naver_brandsearch_mobile</t>
+          <t>EFW_04</t>
         </is>
       </c>
     </row>
     <row r="924">
       <c r="A924" t="inlineStr">
         <is>
-          <t>jsb0425</t>
+          <t>kk_2750710108</t>
         </is>
       </c>
       <c r="B924" t="inlineStr">
         <is>
-          <t>01037883670</t>
+          <t>01062707475</t>
         </is>
       </c>
       <c r="C924" t="inlineStr">
         <is>
-          <t>104766</t>
+          <t>207211</t>
         </is>
       </c>
       <c r="D924" t="inlineStr">
@@ -25379,81 +25379,81 @@
     <row r="925">
       <c r="A925" t="inlineStr">
         <is>
-          <t>kk_2750710108</t>
+          <t>kk_4841278242</t>
         </is>
       </c>
       <c r="B925" t="inlineStr">
         <is>
-          <t>01062707475</t>
+          <t>01046197965</t>
         </is>
       </c>
       <c r="C925" t="inlineStr">
         <is>
-          <t>207211</t>
+          <t>304190</t>
         </is>
       </c>
       <c r="D925" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>Organic Traffic</t>
         </is>
       </c>
       <c r="E925" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>(referral)</t>
         </is>
       </c>
     </row>
     <row r="926">
       <c r="A926" t="inlineStr">
         <is>
-          <t>kk_4841278242</t>
+          <t>kk_3977730443</t>
         </is>
       </c>
       <c r="B926" t="inlineStr">
         <is>
-          <t>01046197965</t>
+          <t>01064291828</t>
         </is>
       </c>
       <c r="C926" t="inlineStr">
         <is>
-          <t>304190</t>
+          <t>271278</t>
         </is>
       </c>
       <c r="D926" t="inlineStr">
         <is>
-          <t>Organic Traffic</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E926" t="inlineStr">
         <is>
-          <t>(referral)</t>
+          <t>naver_brandsearch_mobile</t>
         </is>
       </c>
     </row>
     <row r="927">
       <c r="A927" t="inlineStr">
         <is>
-          <t>kk_4840417532</t>
+          <t>jsb0425</t>
         </is>
       </c>
       <c r="B927" t="inlineStr">
         <is>
-          <t>01053409288</t>
+          <t>01037883670</t>
         </is>
       </c>
       <c r="C927" t="inlineStr">
         <is>
-          <t>304147</t>
+          <t>104766</t>
         </is>
       </c>
       <c r="D927" t="inlineStr">
         <is>
-          <t>Official SNS</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="E927" t="inlineStr">
         <is>
-          <t>EFW_04</t>
+          <t>Direct</t>
         </is>
       </c>
     </row>
@@ -25622,17 +25622,17 @@
     <row r="934">
       <c r="A934" t="inlineStr">
         <is>
-          <t>kimchhgood</t>
+          <t>kk_3776403631</t>
         </is>
       </c>
       <c r="B934" t="inlineStr">
         <is>
-          <t>01092133961</t>
+          <t>01034755755</t>
         </is>
       </c>
       <c r="C934" t="inlineStr">
         <is>
-          <t>53493</t>
+          <t>255908</t>
         </is>
       </c>
       <c r="D934" t="inlineStr">
@@ -25642,24 +25642,24 @@
       </c>
       <c r="E934" t="inlineStr">
         <is>
-          <t>EDM_TOP</t>
+          <t>KAKAO_alimtalk</t>
         </is>
       </c>
     </row>
     <row r="935">
       <c r="A935" t="inlineStr">
         <is>
-          <t>kk_3776403631</t>
+          <t>kimchhgood</t>
         </is>
       </c>
       <c r="B935" t="inlineStr">
         <is>
-          <t>01034755755</t>
+          <t>01092133961</t>
         </is>
       </c>
       <c r="C935" t="inlineStr">
         <is>
-          <t>255908</t>
+          <t>53493</t>
         </is>
       </c>
       <c r="D935" t="inlineStr">
@@ -25669,78 +25669,78 @@
       </c>
       <c r="E935" t="inlineStr">
         <is>
-          <t>KAKAO_alimtalk</t>
+          <t>EDM_TOP</t>
         </is>
       </c>
     </row>
     <row r="936">
       <c r="A936" t="inlineStr">
         <is>
-          <t>kk_4651201605</t>
+          <t>willper</t>
         </is>
       </c>
       <c r="B936" t="inlineStr">
         <is>
-          <t>01045489411</t>
+          <t>01085343440</t>
         </is>
       </c>
       <c r="C936" t="inlineStr">
         <is>
-          <t>293053</t>
+          <t>304408</t>
         </is>
       </c>
       <c r="D936" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E936" t="inlineStr">
         <is>
-          <t>EDM_0411</t>
+          <t>6968489536332</t>
         </is>
       </c>
     </row>
     <row r="937">
       <c r="A937" t="inlineStr">
         <is>
-          <t>kk_4846761310</t>
+          <t>kk_4651201605</t>
         </is>
       </c>
       <c r="B937" t="inlineStr">
         <is>
-          <t>01091189951</t>
+          <t>01045489411</t>
         </is>
       </c>
       <c r="C937" t="inlineStr">
         <is>
-          <t>304464</t>
+          <t>293053</t>
         </is>
       </c>
       <c r="D937" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E937" t="inlineStr">
         <is>
-          <t>naver_brandsearch_mobile</t>
+          <t>EDM_0411</t>
         </is>
       </c>
     </row>
     <row r="938">
       <c r="A938" t="inlineStr">
         <is>
-          <t>willper</t>
+          <t>kk_4846761310</t>
         </is>
       </c>
       <c r="B938" t="inlineStr">
         <is>
-          <t>01085343440</t>
+          <t>01091189951</t>
         </is>
       </c>
       <c r="C938" t="inlineStr">
         <is>
-          <t>304408</t>
+          <t>304464</t>
         </is>
       </c>
       <c r="D938" t="inlineStr">
@@ -25750,7 +25750,7 @@
       </c>
       <c r="E938" t="inlineStr">
         <is>
-          <t>6968489536332</t>
+          <t>naver_brandsearch_mobile</t>
         </is>
       </c>
     </row>
@@ -25811,17 +25811,17 @@
     <row r="941">
       <c r="A941" t="inlineStr">
         <is>
-          <t>kk_4841799872</t>
+          <t>nikemkr</t>
         </is>
       </c>
       <c r="B941" t="inlineStr">
         <is>
-          <t>01023236956</t>
+          <t>01032361592</t>
         </is>
       </c>
       <c r="C941" t="inlineStr">
         <is>
-          <t>304205</t>
+          <t>145423</t>
         </is>
       </c>
       <c r="D941" t="inlineStr">
@@ -25831,61 +25831,61 @@
       </c>
       <c r="E941" t="inlineStr">
         <is>
-          <t>컬럼비아_DPA_240530</t>
+          <t>naver_brandsearch_mobile</t>
         </is>
       </c>
     </row>
     <row r="942">
       <c r="A942" t="inlineStr">
         <is>
-          <t>kk_4703272205</t>
+          <t>kk_4841799872</t>
         </is>
       </c>
       <c r="B942" t="inlineStr">
         <is>
-          <t>01062682325</t>
+          <t>01023236956</t>
         </is>
       </c>
       <c r="C942" t="inlineStr">
         <is>
-          <t>296093</t>
+          <t>304205</t>
         </is>
       </c>
       <c r="D942" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E942" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0410exclusive2</t>
+          <t>컬럼비아_DPA_240530</t>
         </is>
       </c>
     </row>
     <row r="943">
       <c r="A943" t="inlineStr">
         <is>
-          <t>nikemkr</t>
+          <t>kk_4703272205</t>
         </is>
       </c>
       <c r="B943" t="inlineStr">
         <is>
-          <t>01032361592</t>
+          <t>01062682325</t>
         </is>
       </c>
       <c r="C943" t="inlineStr">
         <is>
-          <t>145423</t>
+          <t>296093</t>
         </is>
       </c>
       <c r="D943" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E943" t="inlineStr">
         <is>
-          <t>naver_brandsearch_mobile</t>
+          <t>LMS_ECOM_0410exclusive2</t>
         </is>
       </c>
     </row>
@@ -25919,179 +25919,179 @@
     <row r="945">
       <c r="A945" t="inlineStr">
         <is>
-          <t>sbhbi</t>
+          <t>lolia875</t>
         </is>
       </c>
       <c r="B945" t="inlineStr">
         <is>
-          <t>01047153767</t>
+          <t>01067138715</t>
         </is>
       </c>
       <c r="C945" t="inlineStr">
         <is>
-          <t>174291</t>
+          <t>161251</t>
         </is>
       </c>
       <c r="D945" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E945" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>6968489536332</t>
         </is>
       </c>
     </row>
     <row r="946">
       <c r="A946" t="inlineStr">
         <is>
-          <t>lolia875</t>
+          <t>sbhbi</t>
         </is>
       </c>
       <c r="B946" t="inlineStr">
         <is>
-          <t>01067138715</t>
+          <t>01047153767</t>
         </is>
       </c>
       <c r="C946" t="inlineStr">
         <is>
-          <t>161251</t>
+          <t>174291</t>
         </is>
       </c>
       <c r="D946" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="E946" t="inlineStr">
         <is>
-          <t>6968489536332</t>
+          <t>Direct</t>
         </is>
       </c>
     </row>
     <row r="947">
       <c r="A947" t="inlineStr">
         <is>
-          <t>makaveli</t>
+          <t>kk_3430866338</t>
         </is>
       </c>
       <c r="B947" t="inlineStr">
         <is>
-          <t>01086237086</t>
+          <t>01026364692</t>
         </is>
       </c>
       <c r="C947" t="inlineStr">
         <is>
-          <t>66164</t>
+          <t>242249</t>
         </is>
       </c>
       <c r="D947" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E947" t="inlineStr">
         <is>
-          <t>naver_brandsearch_mobile</t>
+          <t>Email_mkt</t>
         </is>
       </c>
     </row>
     <row r="948">
       <c r="A948" t="inlineStr">
         <is>
-          <t>kk_4837152929</t>
+          <t>sjl4534</t>
         </is>
       </c>
       <c r="B948" t="inlineStr">
         <is>
-          <t>01047050730</t>
+          <t>01028023660</t>
         </is>
       </c>
       <c r="C948" t="inlineStr">
         <is>
-          <t>303966</t>
+          <t>174607</t>
         </is>
       </c>
       <c r="D948" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E948" t="inlineStr">
         <is>
-          <t>6968489536332</t>
+          <t>KAKAO_CH_MESSAGE_0409_EXCLUSIVE</t>
         </is>
       </c>
     </row>
     <row r="949">
       <c r="A949" t="inlineStr">
         <is>
-          <t>kk_3430866338</t>
+          <t>kk_4837595875</t>
         </is>
       </c>
       <c r="B949" t="inlineStr">
         <is>
-          <t>01026364692</t>
+          <t>01057852463</t>
         </is>
       </c>
       <c r="C949" t="inlineStr">
         <is>
-          <t>242249</t>
+          <t>304000</t>
         </is>
       </c>
       <c r="D949" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E949" t="inlineStr">
         <is>
-          <t>Email_mkt</t>
+          <t>6968489536332</t>
         </is>
       </c>
     </row>
     <row r="950">
       <c r="A950" t="inlineStr">
         <is>
-          <t>sjl4534</t>
+          <t>makaveli</t>
         </is>
       </c>
       <c r="B950" t="inlineStr">
         <is>
-          <t>01028023660</t>
+          <t>01086237086</t>
         </is>
       </c>
       <c r="C950" t="inlineStr">
         <is>
-          <t>174607</t>
+          <t>66164</t>
         </is>
       </c>
       <c r="D950" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E950" t="inlineStr">
         <is>
-          <t>KAKAO_CH_MESSAGE_0409_EXCLUSIVE</t>
+          <t>naver_brandsearch_mobile</t>
         </is>
       </c>
     </row>
     <row r="951">
       <c r="A951" t="inlineStr">
         <is>
-          <t>kk_4837595875</t>
+          <t>kk_4837152929</t>
         </is>
       </c>
       <c r="B951" t="inlineStr">
         <is>
-          <t>01057852463</t>
+          <t>01047050730</t>
         </is>
       </c>
       <c r="C951" t="inlineStr">
         <is>
-          <t>304000</t>
+          <t>303966</t>
         </is>
       </c>
       <c r="D951" t="inlineStr">
@@ -26108,54 +26108,54 @@
     <row r="952">
       <c r="A952" t="inlineStr">
         <is>
-          <t>kk_3483542670</t>
+          <t>sagtp</t>
         </is>
       </c>
       <c r="B952" t="inlineStr">
         <is>
-          <t>01025352246</t>
+          <t>01087431193</t>
         </is>
       </c>
       <c r="C952" t="inlineStr">
         <is>
-          <t>244637</t>
+          <t>203717</t>
         </is>
       </c>
       <c r="D952" t="inlineStr">
         <is>
-          <t>Awareness</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E952" t="inlineStr">
         <is>
-          <t>benz_running_program_2026_coupon</t>
+          <t>6968489536332</t>
         </is>
       </c>
     </row>
     <row r="953">
       <c r="A953" t="inlineStr">
         <is>
-          <t>sagtp</t>
+          <t>kk_3483542670</t>
         </is>
       </c>
       <c r="B953" t="inlineStr">
         <is>
-          <t>01087431193</t>
+          <t>01025352246</t>
         </is>
       </c>
       <c r="C953" t="inlineStr">
         <is>
-          <t>203717</t>
+          <t>244637</t>
         </is>
       </c>
       <c r="D953" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Awareness</t>
         </is>
       </c>
       <c r="E953" t="inlineStr">
         <is>
-          <t>6968489536332</t>
+          <t>benz_running_program_2026_coupon</t>
         </is>
       </c>
     </row>
@@ -26243,71 +26243,71 @@
     <row r="957">
       <c r="A957" t="inlineStr">
         <is>
-          <t>imgain0422</t>
+          <t>kk_4845661756</t>
         </is>
       </c>
       <c r="B957" t="inlineStr">
         <is>
-          <t>01029135546</t>
+          <t>01095936572</t>
         </is>
       </c>
       <c r="C957" t="inlineStr">
         <is>
-          <t>181451</t>
+          <t>304422</t>
         </is>
       </c>
       <c r="D957" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E957" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>6968489536332</t>
         </is>
       </c>
     </row>
     <row r="958">
       <c r="A958" t="inlineStr">
         <is>
-          <t>kk_4846729102</t>
+          <t>kk_3183517395</t>
         </is>
       </c>
       <c r="B958" t="inlineStr">
         <is>
-          <t>01084771303</t>
+          <t>01082019936</t>
         </is>
       </c>
       <c r="C958" t="inlineStr">
         <is>
-          <t>304461</t>
+          <t>228501</t>
         </is>
       </c>
       <c r="D958" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="E958" t="inlineStr">
         <is>
-          <t>6968489536332</t>
+          <t>Direct</t>
         </is>
       </c>
     </row>
     <row r="959">
       <c r="A959" t="inlineStr">
         <is>
-          <t>kk_4845661756</t>
+          <t>kk_4846729102</t>
         </is>
       </c>
       <c r="B959" t="inlineStr">
         <is>
-          <t>01095936572</t>
+          <t>01084771303</t>
         </is>
       </c>
       <c r="C959" t="inlineStr">
         <is>
-          <t>304422</t>
+          <t>304461</t>
         </is>
       </c>
       <c r="D959" t="inlineStr">
@@ -26324,17 +26324,17 @@
     <row r="960">
       <c r="A960" t="inlineStr">
         <is>
-          <t>chpuss74</t>
+          <t>ch5115</t>
         </is>
       </c>
       <c r="B960" t="inlineStr">
         <is>
-          <t>01035361091</t>
+          <t>01084479339</t>
         </is>
       </c>
       <c r="C960" t="inlineStr">
         <is>
-          <t>154462</t>
+          <t>240557</t>
         </is>
       </c>
       <c r="D960" t="inlineStr">
@@ -26378,17 +26378,17 @@
     <row r="962">
       <c r="A962" t="inlineStr">
         <is>
-          <t>kk_3183517395</t>
+          <t>chpuss74</t>
         </is>
       </c>
       <c r="B962" t="inlineStr">
         <is>
-          <t>01082019936</t>
+          <t>01035361091</t>
         </is>
       </c>
       <c r="C962" t="inlineStr">
         <is>
-          <t>228501</t>
+          <t>154462</t>
         </is>
       </c>
       <c r="D962" t="inlineStr">
@@ -26405,17 +26405,17 @@
     <row r="963">
       <c r="A963" t="inlineStr">
         <is>
-          <t>ch5115</t>
+          <t>imgain0422</t>
         </is>
       </c>
       <c r="B963" t="inlineStr">
         <is>
-          <t>01084479339</t>
+          <t>01029135546</t>
         </is>
       </c>
       <c r="C963" t="inlineStr">
         <is>
-          <t>240557</t>
+          <t>181451</t>
         </is>
       </c>
       <c r="D963" t="inlineStr">
@@ -26432,81 +26432,81 @@
     <row r="964">
       <c r="A964" t="inlineStr">
         <is>
-          <t>kk_2775500473</t>
+          <t>kjhk5404</t>
         </is>
       </c>
       <c r="B964" t="inlineStr">
         <is>
-          <t>01045659020</t>
+          <t>01027390700</t>
         </is>
       </c>
       <c r="C964" t="inlineStr">
         <is>
-          <t>209371</t>
+          <t>280120</t>
         </is>
       </c>
       <c r="D964" t="inlineStr">
         <is>
-          <t>Organic Traffic</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E964" t="inlineStr">
         <is>
-          <t>(referral)</t>
+          <t>KAKAO_alimtalk</t>
         </is>
       </c>
     </row>
     <row r="965">
       <c r="A965" t="inlineStr">
         <is>
-          <t>goawind</t>
+          <t>kk_2775500473</t>
         </is>
       </c>
       <c r="B965" t="inlineStr">
         <is>
-          <t>01032738938</t>
+          <t>01045659020</t>
         </is>
       </c>
       <c r="C965" t="inlineStr">
         <is>
-          <t>232021</t>
+          <t>209371</t>
         </is>
       </c>
       <c r="D965" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>Organic Traffic</t>
         </is>
       </c>
       <c r="E965" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>(referral)</t>
         </is>
       </c>
     </row>
     <row r="966">
       <c r="A966" t="inlineStr">
         <is>
-          <t>kjhk5404</t>
+          <t>kk_3650586439</t>
         </is>
       </c>
       <c r="B966" t="inlineStr">
         <is>
-          <t>01027390700</t>
+          <t>01029107056</t>
         </is>
       </c>
       <c r="C966" t="inlineStr">
         <is>
-          <t>280120</t>
+          <t>249153</t>
         </is>
       </c>
       <c r="D966" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="E966" t="inlineStr">
         <is>
-          <t>KAKAO_alimtalk</t>
+          <t>Direct</t>
         </is>
       </c>
     </row>
@@ -26540,54 +26540,54 @@
     <row r="968">
       <c r="A968" t="inlineStr">
         <is>
-          <t>kk_4844076820</t>
+          <t>goawind</t>
         </is>
       </c>
       <c r="B968" t="inlineStr">
         <is>
-          <t>01091346366</t>
+          <t>01032738938</t>
         </is>
       </c>
       <c r="C968" t="inlineStr">
         <is>
-          <t>304343</t>
+          <t>232021</t>
         </is>
       </c>
       <c r="D968" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="E968" t="inlineStr">
         <is>
-          <t>6968489536332</t>
+          <t>Direct</t>
         </is>
       </c>
     </row>
     <row r="969">
       <c r="A969" t="inlineStr">
         <is>
-          <t>kk_3650586439</t>
+          <t>kk_4844076820</t>
         </is>
       </c>
       <c r="B969" t="inlineStr">
         <is>
-          <t>01029107056</t>
+          <t>01091346366</t>
         </is>
       </c>
       <c r="C969" t="inlineStr">
         <is>
-          <t>249153</t>
+          <t>304343</t>
         </is>
       </c>
       <c r="D969" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E969" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>6968489536332</t>
         </is>
       </c>
     </row>
@@ -26675,17 +26675,17 @@
     <row r="973">
       <c r="A973" t="inlineStr">
         <is>
-          <t>kk_4840817001</t>
+          <t>kk_4841778210</t>
         </is>
       </c>
       <c r="B973" t="inlineStr">
         <is>
-          <t>01085963383</t>
+          <t>01087814274</t>
         </is>
       </c>
       <c r="C973" t="inlineStr">
         <is>
-          <t>304168</t>
+          <t>304202</t>
         </is>
       </c>
       <c r="D973" t="inlineStr">
@@ -26695,24 +26695,24 @@
       </c>
       <c r="E973" t="inlineStr">
         <is>
-          <t>6968489536332</t>
+          <t>naver_brandsearch_mobile</t>
         </is>
       </c>
     </row>
     <row r="974">
       <c r="A974" t="inlineStr">
         <is>
-          <t>kk_4841778210</t>
+          <t>kk_4840817001</t>
         </is>
       </c>
       <c r="B974" t="inlineStr">
         <is>
-          <t>01087814274</t>
+          <t>01085963383</t>
         </is>
       </c>
       <c r="C974" t="inlineStr">
         <is>
-          <t>304202</t>
+          <t>304168</t>
         </is>
       </c>
       <c r="D974" t="inlineStr">
@@ -26722,105 +26722,105 @@
       </c>
       <c r="E974" t="inlineStr">
         <is>
-          <t>naver_brandsearch_mobile</t>
+          <t>6968489536332</t>
         </is>
       </c>
     </row>
     <row r="975">
       <c r="A975" t="inlineStr">
         <is>
-          <t>xoxoie2</t>
+          <t>kk_4840045474</t>
         </is>
       </c>
       <c r="B975" t="inlineStr">
         <is>
-          <t>01043560834</t>
+          <t>01096310429</t>
         </is>
       </c>
       <c r="C975" t="inlineStr">
         <is>
-          <t>304072</t>
+          <t>304122</t>
         </is>
       </c>
       <c r="D975" t="inlineStr">
         <is>
-          <t>Official SNS</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E975" t="inlineStr">
         <is>
-          <t>EFW_04</t>
+          <t>6968489536332</t>
         </is>
       </c>
     </row>
     <row r="976">
       <c r="A976" t="inlineStr">
         <is>
-          <t>gus7526</t>
+          <t>z090909x</t>
         </is>
       </c>
       <c r="B976" t="inlineStr">
         <is>
-          <t>01050931023</t>
+          <t>01092058111</t>
         </is>
       </c>
       <c r="C976" t="inlineStr">
         <is>
-          <t>140860</t>
+          <t>113003</t>
         </is>
       </c>
       <c r="D976" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E976" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0410exclusive2</t>
+          <t>6968489536332</t>
         </is>
       </c>
     </row>
     <row r="977">
       <c r="A977" t="inlineStr">
         <is>
-          <t>z090909x</t>
+          <t>kk_4228106377</t>
         </is>
       </c>
       <c r="B977" t="inlineStr">
         <is>
-          <t>01092058111</t>
+          <t>01063165271</t>
         </is>
       </c>
       <c r="C977" t="inlineStr">
         <is>
-          <t>113003</t>
+          <t>273193</t>
         </is>
       </c>
       <c r="D977" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E977" t="inlineStr">
         <is>
-          <t>6968489536332</t>
+          <t>LMS_ECOM_0410exclusive2</t>
         </is>
       </c>
     </row>
     <row r="978">
       <c r="A978" t="inlineStr">
         <is>
-          <t>kk_4228106377</t>
+          <t>ssama</t>
         </is>
       </c>
       <c r="B978" t="inlineStr">
         <is>
-          <t>01063165271</t>
+          <t>01056271982</t>
         </is>
       </c>
       <c r="C978" t="inlineStr">
         <is>
-          <t>273193</t>
+          <t>47874</t>
         </is>
       </c>
       <c r="D978" t="inlineStr">
@@ -26837,17 +26837,17 @@
     <row r="979">
       <c r="A979" t="inlineStr">
         <is>
-          <t>eyounjoo</t>
+          <t>kk_3213636735</t>
         </is>
       </c>
       <c r="B979" t="inlineStr">
         <is>
-          <t>01036167949</t>
+          <t>01071338973</t>
         </is>
       </c>
       <c r="C979" t="inlineStr">
         <is>
-          <t>283223</t>
+          <t>232010</t>
         </is>
       </c>
       <c r="D979" t="inlineStr">
@@ -26857,132 +26857,132 @@
       </c>
       <c r="E979" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0410exclusive2</t>
+          <t>KAKAO_CH_MENU_0226_TRAILRUN</t>
         </is>
       </c>
     </row>
     <row r="980">
       <c r="A980" t="inlineStr">
         <is>
-          <t>ssama</t>
+          <t>kk_4839241951</t>
         </is>
       </c>
       <c r="B980" t="inlineStr">
         <is>
-          <t>01056271982</t>
+          <t>01079146776</t>
         </is>
       </c>
       <c r="C980" t="inlineStr">
         <is>
-          <t>47874</t>
+          <t>304090</t>
         </is>
       </c>
       <c r="D980" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E980" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0410exclusive2</t>
+          <t>6968489536332</t>
         </is>
       </c>
     </row>
     <row r="981">
       <c r="A981" t="inlineStr">
         <is>
-          <t>kk_4839241951</t>
+          <t>gus7526</t>
         </is>
       </c>
       <c r="B981" t="inlineStr">
         <is>
-          <t>01079146776</t>
+          <t>01050931023</t>
         </is>
       </c>
       <c r="C981" t="inlineStr">
         <is>
-          <t>304090</t>
+          <t>140860</t>
         </is>
       </c>
       <c r="D981" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E981" t="inlineStr">
         <is>
-          <t>6968489536332</t>
+          <t>LMS_ECOM_0410exclusive2</t>
         </is>
       </c>
     </row>
     <row r="982">
       <c r="A982" t="inlineStr">
         <is>
-          <t>kk_4840045474</t>
+          <t>eyounjoo</t>
         </is>
       </c>
       <c r="B982" t="inlineStr">
         <is>
-          <t>01096310429</t>
+          <t>01036167949</t>
         </is>
       </c>
       <c r="C982" t="inlineStr">
         <is>
-          <t>304122</t>
+          <t>283223</t>
         </is>
       </c>
       <c r="D982" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E982" t="inlineStr">
         <is>
-          <t>6968489536332</t>
+          <t>LMS_ECOM_0410exclusive2</t>
         </is>
       </c>
     </row>
     <row r="983">
       <c r="A983" t="inlineStr">
         <is>
-          <t>kk_3213636735</t>
+          <t>xoxoie2</t>
         </is>
       </c>
       <c r="B983" t="inlineStr">
         <is>
-          <t>01071338973</t>
+          <t>01043560834</t>
         </is>
       </c>
       <c r="C983" t="inlineStr">
         <is>
-          <t>232010</t>
+          <t>304072</t>
         </is>
       </c>
       <c r="D983" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Official SNS</t>
         </is>
       </c>
       <c r="E983" t="inlineStr">
         <is>
-          <t>KAKAO_CH_MENU_0226_TRAILRUN</t>
+          <t>EFW_04</t>
         </is>
       </c>
     </row>
     <row r="984">
       <c r="A984" t="inlineStr">
         <is>
-          <t>enel778</t>
+          <t>scaler</t>
         </is>
       </c>
       <c r="B984" t="inlineStr">
         <is>
-          <t>01086066364</t>
+          <t>01037090080</t>
         </is>
       </c>
       <c r="C984" t="inlineStr">
         <is>
-          <t>207732</t>
+          <t>178752</t>
         </is>
       </c>
       <c r="D984" t="inlineStr">
@@ -26992,78 +26992,78 @@
       </c>
       <c r="E984" t="inlineStr">
         <is>
-          <t>Email_mkt</t>
+          <t>KAKAO_CH_MESSAGE_0409_EXCLUSIVE</t>
         </is>
       </c>
     </row>
     <row r="985">
       <c r="A985" t="inlineStr">
         <is>
-          <t>kk_3234166915</t>
+          <t>kk_4837597613</t>
         </is>
       </c>
       <c r="B985" t="inlineStr">
         <is>
-          <t>01082632995</t>
+          <t>01089218630</t>
         </is>
       </c>
       <c r="C985" t="inlineStr">
         <is>
-          <t>233887</t>
+          <t>304001</t>
         </is>
       </c>
       <c r="D985" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E985" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>KAKAO_CH_MESSAGE_0409_EXCLUSIVE</t>
         </is>
       </c>
     </row>
     <row r="986">
       <c r="A986" t="inlineStr">
         <is>
-          <t>scaler</t>
+          <t>kk_3234166915</t>
         </is>
       </c>
       <c r="B986" t="inlineStr">
         <is>
-          <t>01037090080</t>
+          <t>01082632995</t>
         </is>
       </c>
       <c r="C986" t="inlineStr">
         <is>
-          <t>178752</t>
+          <t>233887</t>
         </is>
       </c>
       <c r="D986" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="E986" t="inlineStr">
         <is>
-          <t>KAKAO_CH_MESSAGE_0409_EXCLUSIVE</t>
+          <t>Direct</t>
         </is>
       </c>
     </row>
     <row r="987">
       <c r="A987" t="inlineStr">
         <is>
-          <t>kk_4837597613</t>
+          <t>enel778</t>
         </is>
       </c>
       <c r="B987" t="inlineStr">
         <is>
-          <t>01089218630</t>
+          <t>01086066364</t>
         </is>
       </c>
       <c r="C987" t="inlineStr">
         <is>
-          <t>304001</t>
+          <t>207732</t>
         </is>
       </c>
       <c r="D987" t="inlineStr">
@@ -27073,7 +27073,7 @@
       </c>
       <c r="E987" t="inlineStr">
         <is>
-          <t>KAKAO_CH_MESSAGE_0409_EXCLUSIVE</t>
+          <t>Email_mkt</t>
         </is>
       </c>
     </row>
@@ -27107,17 +27107,17 @@
     <row r="989">
       <c r="A989" t="inlineStr">
         <is>
-          <t>kk_2757334528</t>
+          <t>kk_4444429966</t>
         </is>
       </c>
       <c r="B989" t="inlineStr">
         <is>
-          <t>01089379633</t>
+          <t>01032219702</t>
         </is>
       </c>
       <c r="C989" t="inlineStr">
         <is>
-          <t>208240</t>
+          <t>282222</t>
         </is>
       </c>
       <c r="D989" t="inlineStr">
@@ -27161,17 +27161,17 @@
     <row r="991">
       <c r="A991" t="inlineStr">
         <is>
-          <t>kk_4444429966</t>
+          <t>kk_2757334528</t>
         </is>
       </c>
       <c r="B991" t="inlineStr">
         <is>
-          <t>01032219702</t>
+          <t>01089379633</t>
         </is>
       </c>
       <c r="C991" t="inlineStr">
         <is>
-          <t>282222</t>
+          <t>208240</t>
         </is>
       </c>
       <c r="D991" t="inlineStr">
@@ -27215,54 +27215,54 @@
     <row r="993">
       <c r="A993" t="inlineStr">
         <is>
-          <t>kk_4218204827</t>
+          <t>mse001</t>
         </is>
       </c>
       <c r="B993" t="inlineStr">
         <is>
-          <t>01023704903</t>
+          <t>01085185510</t>
         </is>
       </c>
       <c r="C993" t="inlineStr">
         <is>
-          <t>272698</t>
+          <t>227227</t>
         </is>
       </c>
       <c r="D993" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E993" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>KAKAO_alimtalk</t>
         </is>
       </c>
     </row>
     <row r="994">
       <c r="A994" t="inlineStr">
         <is>
-          <t>mse001</t>
+          <t>kk_4218204827</t>
         </is>
       </c>
       <c r="B994" t="inlineStr">
         <is>
-          <t>01085185510</t>
+          <t>01023704903</t>
         </is>
       </c>
       <c r="C994" t="inlineStr">
         <is>
-          <t>227227</t>
+          <t>272698</t>
         </is>
       </c>
       <c r="D994" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="E994" t="inlineStr">
         <is>
-          <t>KAKAO_alimtalk</t>
+          <t>Direct</t>
         </is>
       </c>
     </row>
@@ -27323,54 +27323,54 @@
     <row r="997">
       <c r="A997" t="inlineStr">
         <is>
-          <t>kk_4375003446</t>
+          <t>kk_4844817541</t>
         </is>
       </c>
       <c r="B997" t="inlineStr">
         <is>
-          <t>01087457282</t>
+          <t>01046631832</t>
         </is>
       </c>
       <c r="C997" t="inlineStr">
         <is>
-          <t>280131</t>
+          <t>304380</t>
         </is>
       </c>
       <c r="D997" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E997" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0410exclusive2</t>
+          <t>[PF]전환_회원가입(유사)</t>
         </is>
       </c>
     </row>
     <row r="998">
       <c r="A998" t="inlineStr">
         <is>
-          <t>kk_4844817541</t>
+          <t>kk_4375003446</t>
         </is>
       </c>
       <c r="B998" t="inlineStr">
         <is>
-          <t>01046631832</t>
+          <t>01087457282</t>
         </is>
       </c>
       <c r="C998" t="inlineStr">
         <is>
-          <t>304380</t>
+          <t>280131</t>
         </is>
       </c>
       <c r="D998" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E998" t="inlineStr">
         <is>
-          <t>[PF]전환_회원가입(유사)</t>
+          <t>LMS_ECOM_0410exclusive2</t>
         </is>
       </c>
     </row>
@@ -27404,71 +27404,71 @@
     <row r="1000">
       <c r="A1000" t="inlineStr">
         <is>
-          <t>kk_3688034999</t>
+          <t>kk_2768989214</t>
         </is>
       </c>
       <c r="B1000" t="inlineStr">
         <is>
-          <t>01025408262</t>
+          <t>01095004289</t>
         </is>
       </c>
       <c r="C1000" t="inlineStr">
         <is>
-          <t>250755</t>
+          <t>209015</t>
         </is>
       </c>
       <c r="D1000" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="E1000" t="inlineStr">
         <is>
-          <t>KAKAO_alimtalk</t>
+          <t>Direct</t>
         </is>
       </c>
     </row>
     <row r="1001">
       <c r="A1001" t="inlineStr">
         <is>
-          <t>kk_2768989214</t>
+          <t>kk_3688034999</t>
         </is>
       </c>
       <c r="B1001" t="inlineStr">
         <is>
-          <t>01095004289</t>
+          <t>01025408262</t>
         </is>
       </c>
       <c r="C1001" t="inlineStr">
         <is>
-          <t>209015</t>
+          <t>250755</t>
         </is>
       </c>
       <c r="D1001" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E1001" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>KAKAO_alimtalk</t>
         </is>
       </c>
     </row>
     <row r="1002">
       <c r="A1002" t="inlineStr">
         <is>
-          <t>kk_3444865211</t>
+          <t>xuswldls</t>
         </is>
       </c>
       <c r="B1002" t="inlineStr">
         <is>
-          <t>01021964871</t>
+          <t>01027349414</t>
         </is>
       </c>
       <c r="C1002" t="inlineStr">
         <is>
-          <t>242799</t>
+          <t>133308</t>
         </is>
       </c>
       <c r="D1002" t="inlineStr">
@@ -27566,54 +27566,54 @@
     <row r="1006">
       <c r="A1006" t="inlineStr">
         <is>
-          <t>xuswldls</t>
+          <t>kk_4472536591</t>
         </is>
       </c>
       <c r="B1006" t="inlineStr">
         <is>
-          <t>01027349414</t>
+          <t>01037057526</t>
         </is>
       </c>
       <c r="C1006" t="inlineStr">
         <is>
-          <t>133308</t>
+          <t>283897</t>
         </is>
       </c>
       <c r="D1006" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E1006" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>KAKAO_alimtalk</t>
         </is>
       </c>
     </row>
     <row r="1007">
       <c r="A1007" t="inlineStr">
         <is>
-          <t>kk_4472536591</t>
+          <t>kk_3444865211</t>
         </is>
       </c>
       <c r="B1007" t="inlineStr">
         <is>
-          <t>01037057526</t>
+          <t>01021964871</t>
         </is>
       </c>
       <c r="C1007" t="inlineStr">
         <is>
-          <t>283897</t>
+          <t>242799</t>
         </is>
       </c>
       <c r="D1007" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="E1007" t="inlineStr">
         <is>
-          <t>KAKAO_alimtalk</t>
+          <t>Direct</t>
         </is>
       </c>
     </row>
@@ -27647,71 +27647,71 @@
     <row r="1009">
       <c r="A1009" t="inlineStr">
         <is>
-          <t>escalater</t>
+          <t>kk_3858585698</t>
         </is>
       </c>
       <c r="B1009" t="inlineStr">
         <is>
-          <t>01090911461</t>
+          <t>01092163429</t>
         </is>
       </c>
       <c r="C1009" t="inlineStr">
         <is>
-          <t>240051</t>
+          <t>265508</t>
         </is>
       </c>
       <c r="D1009" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E1009" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>KAKAO_alimtalk</t>
         </is>
       </c>
     </row>
     <row r="1010">
       <c r="A1010" t="inlineStr">
         <is>
-          <t>kk_3181917333</t>
+          <t>nesto1</t>
         </is>
       </c>
       <c r="B1010" t="inlineStr">
         <is>
-          <t>01072258509</t>
+          <t>01056603953</t>
         </is>
       </c>
       <c r="C1010" t="inlineStr">
         <is>
-          <t>227380</t>
+          <t>125251</t>
         </is>
       </c>
       <c r="D1010" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E1010" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>KAKAO_alimtalk</t>
         </is>
       </c>
     </row>
     <row r="1011">
       <c r="A1011" t="inlineStr">
         <is>
-          <t>nesto1</t>
+          <t>kk_3837527580</t>
         </is>
       </c>
       <c r="B1011" t="inlineStr">
         <is>
-          <t>01056603953</t>
+          <t>01084311738</t>
         </is>
       </c>
       <c r="C1011" t="inlineStr">
         <is>
-          <t>125251</t>
+          <t>264113</t>
         </is>
       </c>
       <c r="D1011" t="inlineStr">
@@ -27721,105 +27721,105 @@
       </c>
       <c r="E1011" t="inlineStr">
         <is>
-          <t>KAKAO_alimtalk</t>
+          <t>LMS_ECOM_0410exclusive2</t>
         </is>
       </c>
     </row>
     <row r="1012">
       <c r="A1012" t="inlineStr">
         <is>
-          <t>kk_3858585698</t>
+          <t>kk_3181917333</t>
         </is>
       </c>
       <c r="B1012" t="inlineStr">
         <is>
-          <t>01092163429</t>
+          <t>01072258509</t>
         </is>
       </c>
       <c r="C1012" t="inlineStr">
         <is>
-          <t>265508</t>
+          <t>227380</t>
         </is>
       </c>
       <c r="D1012" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="E1012" t="inlineStr">
         <is>
-          <t>KAKAO_alimtalk</t>
+          <t>Direct</t>
         </is>
       </c>
     </row>
     <row r="1013">
       <c r="A1013" t="inlineStr">
         <is>
-          <t>kk_3837527580</t>
+          <t>escalater</t>
         </is>
       </c>
       <c r="B1013" t="inlineStr">
         <is>
-          <t>01084311738</t>
+          <t>01090911461</t>
         </is>
       </c>
       <c r="C1013" t="inlineStr">
         <is>
-          <t>264113</t>
+          <t>240051</t>
         </is>
       </c>
       <c r="D1013" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="E1013" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0410exclusive2</t>
+          <t>Direct</t>
         </is>
       </c>
     </row>
     <row r="1014">
       <c r="A1014" t="inlineStr">
         <is>
-          <t>kk_4467707148</t>
+          <t>kk_3933534683</t>
         </is>
       </c>
       <c r="B1014" t="inlineStr">
         <is>
-          <t>01030843332</t>
+          <t>01030153796</t>
         </is>
       </c>
       <c r="C1014" t="inlineStr">
         <is>
-          <t>283560</t>
+          <t>269069</t>
         </is>
       </c>
       <c r="D1014" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="E1014" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0410exclusive2</t>
+          <t>Direct</t>
         </is>
       </c>
     </row>
     <row r="1015">
       <c r="A1015" t="inlineStr">
         <is>
-          <t>kk_2940110361</t>
+          <t>kk_4467707148</t>
         </is>
       </c>
       <c r="B1015" t="inlineStr">
         <is>
-          <t>01035353200</t>
+          <t>01030843332</t>
         </is>
       </c>
       <c r="C1015" t="inlineStr">
         <is>
-          <t>216362</t>
+          <t>283560</t>
         </is>
       </c>
       <c r="D1015" t="inlineStr">
@@ -27836,44 +27836,44 @@
     <row r="1016">
       <c r="A1016" t="inlineStr">
         <is>
-          <t>kk_3933534683</t>
+          <t>kk_4523594127</t>
         </is>
       </c>
       <c r="B1016" t="inlineStr">
         <is>
-          <t>01030153796</t>
+          <t>01085735215</t>
         </is>
       </c>
       <c r="C1016" t="inlineStr">
         <is>
-          <t>269069</t>
+          <t>286358</t>
         </is>
       </c>
       <c r="D1016" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E1016" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>LMS_ECOM_0410exclusive2</t>
         </is>
       </c>
     </row>
     <row r="1017">
       <c r="A1017" t="inlineStr">
         <is>
-          <t>kk_3185867832</t>
+          <t>seul6169</t>
         </is>
       </c>
       <c r="B1017" t="inlineStr">
         <is>
-          <t>01022086508</t>
+          <t>01066116699</t>
         </is>
       </c>
       <c r="C1017" t="inlineStr">
         <is>
-          <t>229863</t>
+          <t>234239</t>
         </is>
       </c>
       <c r="D1017" t="inlineStr">
@@ -27883,24 +27883,24 @@
       </c>
       <c r="E1017" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0410exclusive2</t>
+          <t>KAKAO_alimtalk</t>
         </is>
       </c>
     </row>
     <row r="1018">
       <c r="A1018" t="inlineStr">
         <is>
-          <t>mansoogi</t>
+          <t>kk_3185867832</t>
         </is>
       </c>
       <c r="B1018" t="inlineStr">
         <is>
-          <t>01093240897</t>
+          <t>01022086508</t>
         </is>
       </c>
       <c r="C1018" t="inlineStr">
         <is>
-          <t>25243</t>
+          <t>229863</t>
         </is>
       </c>
       <c r="D1018" t="inlineStr">
@@ -27944,44 +27944,44 @@
     <row r="1020">
       <c r="A1020" t="inlineStr">
         <is>
-          <t>kk_4523594127</t>
+          <t>kk_4840061178</t>
         </is>
       </c>
       <c r="B1020" t="inlineStr">
         <is>
-          <t>01085735215</t>
+          <t>01082357895</t>
         </is>
       </c>
       <c r="C1020" t="inlineStr">
         <is>
-          <t>286358</t>
+          <t>304124</t>
         </is>
       </c>
       <c r="D1020" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Awareness</t>
         </is>
       </c>
       <c r="E1020" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0410exclusive2</t>
+          <t>benz_running_program_2026_coupon</t>
         </is>
       </c>
     </row>
     <row r="1021">
       <c r="A1021" t="inlineStr">
         <is>
-          <t>seul6169</t>
+          <t>kk_2940110361</t>
         </is>
       </c>
       <c r="B1021" t="inlineStr">
         <is>
-          <t>01066116699</t>
+          <t>01035353200</t>
         </is>
       </c>
       <c r="C1021" t="inlineStr">
         <is>
-          <t>234239</t>
+          <t>216362</t>
         </is>
       </c>
       <c r="D1021" t="inlineStr">
@@ -27991,105 +27991,105 @@
       </c>
       <c r="E1021" t="inlineStr">
         <is>
-          <t>KAKAO_alimtalk</t>
+          <t>LMS_ECOM_0410exclusive2</t>
         </is>
       </c>
     </row>
     <row r="1022">
       <c r="A1022" t="inlineStr">
         <is>
-          <t>kk_4840061178</t>
+          <t>hursean</t>
         </is>
       </c>
       <c r="B1022" t="inlineStr">
         <is>
-          <t>01082357895</t>
+          <t>01091975738</t>
         </is>
       </c>
       <c r="C1022" t="inlineStr">
         <is>
-          <t>304124</t>
+          <t>123130</t>
         </is>
       </c>
       <c r="D1022" t="inlineStr">
         <is>
-          <t>Awareness</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E1022" t="inlineStr">
         <is>
-          <t>benz_running_program_2026_coupon</t>
+          <t>Email_mkt</t>
         </is>
       </c>
     </row>
     <row r="1023">
       <c r="A1023" t="inlineStr">
         <is>
-          <t>aya6969</t>
+          <t>kk_3013902343</t>
         </is>
       </c>
       <c r="B1023" t="inlineStr">
         <is>
-          <t>01076590009</t>
+          <t>01051802326</t>
         </is>
       </c>
       <c r="C1023" t="inlineStr">
         <is>
-          <t>162562</t>
+          <t>219219</t>
         </is>
       </c>
       <c r="D1023" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E1023" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0410exclusive2</t>
+          <t>6968489536332</t>
         </is>
       </c>
     </row>
     <row r="1024">
       <c r="A1024" t="inlineStr">
         <is>
-          <t>kk_3013902343</t>
+          <t>kk_4338209948</t>
         </is>
       </c>
       <c r="B1024" t="inlineStr">
         <is>
-          <t>01051802326</t>
+          <t>01088132379</t>
         </is>
       </c>
       <c r="C1024" t="inlineStr">
         <is>
-          <t>219219</t>
+          <t>278781</t>
         </is>
       </c>
       <c r="D1024" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E1024" t="inlineStr">
         <is>
-          <t>6968489536332</t>
+          <t>KAKAO_alimtalk</t>
         </is>
       </c>
     </row>
     <row r="1025">
       <c r="A1025" t="inlineStr">
         <is>
-          <t>kk_4338209948</t>
+          <t>mansoogi</t>
         </is>
       </c>
       <c r="B1025" t="inlineStr">
         <is>
-          <t>01088132379</t>
+          <t>01093240897</t>
         </is>
       </c>
       <c r="C1025" t="inlineStr">
         <is>
-          <t>278781</t>
+          <t>25243</t>
         </is>
       </c>
       <c r="D1025" t="inlineStr">
@@ -28099,24 +28099,24 @@
       </c>
       <c r="E1025" t="inlineStr">
         <is>
-          <t>KAKAO_alimtalk</t>
+          <t>LMS_ECOM_0410exclusive2</t>
         </is>
       </c>
     </row>
     <row r="1026">
       <c r="A1026" t="inlineStr">
         <is>
-          <t>hursean</t>
+          <t>aya6969</t>
         </is>
       </c>
       <c r="B1026" t="inlineStr">
         <is>
-          <t>01091975738</t>
+          <t>01076590009</t>
         </is>
       </c>
       <c r="C1026" t="inlineStr">
         <is>
-          <t>123130</t>
+          <t>162562</t>
         </is>
       </c>
       <c r="D1026" t="inlineStr">
@@ -28126,78 +28126,78 @@
       </c>
       <c r="E1026" t="inlineStr">
         <is>
-          <t>Email_mkt</t>
+          <t>LMS_ECOM_0410exclusive2</t>
         </is>
       </c>
     </row>
     <row r="1027">
       <c r="A1027" t="inlineStr">
         <is>
-          <t>kk_4351086966</t>
+          <t>bbluesea</t>
         </is>
       </c>
       <c r="B1027" t="inlineStr">
         <is>
-          <t>01042088262</t>
+          <t>01076473601</t>
         </is>
       </c>
       <c r="C1027" t="inlineStr">
         <is>
-          <t>279266</t>
+          <t>152067</t>
         </is>
       </c>
       <c r="D1027" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E1027" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>KAKAO_CH_MENU_260406_LIGHTJACKET</t>
         </is>
       </c>
     </row>
     <row r="1028">
       <c r="A1028" t="inlineStr">
         <is>
-          <t>boram1991</t>
+          <t>kk_4726499171</t>
         </is>
       </c>
       <c r="B1028" t="inlineStr">
         <is>
-          <t>01023431078</t>
+          <t>01093851013</t>
         </is>
       </c>
       <c r="C1028" t="inlineStr">
         <is>
-          <t>119498</t>
+          <t>297987</t>
         </is>
       </c>
       <c r="D1028" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E1028" t="inlineStr">
         <is>
-          <t>6968489536332</t>
+          <t>KAKAO_CH_MESSAGE_0409_HIKE365SUMMER</t>
         </is>
       </c>
     </row>
     <row r="1029">
       <c r="A1029" t="inlineStr">
         <is>
-          <t>kk_3665803645</t>
+          <t>jhmin000</t>
         </is>
       </c>
       <c r="B1029" t="inlineStr">
         <is>
-          <t>01095549123</t>
+          <t>01086241606</t>
         </is>
       </c>
       <c r="C1029" t="inlineStr">
         <is>
-          <t>249835</t>
+          <t>201165</t>
         </is>
       </c>
       <c r="D1029" t="inlineStr">
@@ -28207,24 +28207,24 @@
       </c>
       <c r="E1029" t="inlineStr">
         <is>
-          <t>KAKAO_CH_MESSAGE_0409_EXCLUSIVE</t>
+          <t>KAKAO_CH_MESSAGE_0409_HIKE365SUMMER</t>
         </is>
       </c>
     </row>
     <row r="1030">
       <c r="A1030" t="inlineStr">
         <is>
-          <t>bbluesea</t>
+          <t>kk_3665803645</t>
         </is>
       </c>
       <c r="B1030" t="inlineStr">
         <is>
-          <t>01076473601</t>
+          <t>01095549123</t>
         </is>
       </c>
       <c r="C1030" t="inlineStr">
         <is>
-          <t>152067</t>
+          <t>249835</t>
         </is>
       </c>
       <c r="D1030" t="inlineStr">
@@ -28234,24 +28234,24 @@
       </c>
       <c r="E1030" t="inlineStr">
         <is>
-          <t>KAKAO_CH_MENU_260406_LIGHTJACKET</t>
+          <t>KAKAO_CH_MESSAGE_0409_EXCLUSIVE</t>
         </is>
       </c>
     </row>
     <row r="1031">
       <c r="A1031" t="inlineStr">
         <is>
-          <t>jhmin000</t>
+          <t>kk_3638512879</t>
         </is>
       </c>
       <c r="B1031" t="inlineStr">
         <is>
-          <t>01086241606</t>
+          <t>01053330589</t>
         </is>
       </c>
       <c r="C1031" t="inlineStr">
         <is>
-          <t>201165</t>
+          <t>248574</t>
         </is>
       </c>
       <c r="D1031" t="inlineStr">
@@ -28268,125 +28268,125 @@
     <row r="1032">
       <c r="A1032" t="inlineStr">
         <is>
-          <t>kk_4726499171</t>
+          <t>kk_3154612153</t>
         </is>
       </c>
       <c r="B1032" t="inlineStr">
         <is>
-          <t>01093851013</t>
+          <t>01056681753</t>
         </is>
       </c>
       <c r="C1032" t="inlineStr">
         <is>
-          <t>297987</t>
+          <t>223664</t>
         </is>
       </c>
       <c r="D1032" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="E1032" t="inlineStr">
         <is>
-          <t>KAKAO_CH_MESSAGE_0409_HIKE365SUMMER</t>
+          <t>Direct</t>
         </is>
       </c>
     </row>
     <row r="1033">
       <c r="A1033" t="inlineStr">
         <is>
-          <t>kk_3154612153</t>
+          <t>boram1991</t>
         </is>
       </c>
       <c r="B1033" t="inlineStr">
         <is>
-          <t>01056681753</t>
+          <t>01023431078</t>
         </is>
       </c>
       <c r="C1033" t="inlineStr">
         <is>
-          <t>223664</t>
+          <t>119498</t>
         </is>
       </c>
       <c r="D1033" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E1033" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>6968489536332</t>
         </is>
       </c>
     </row>
     <row r="1034">
       <c r="A1034" t="inlineStr">
         <is>
-          <t>kk_3155938902</t>
+          <t>kk_4351086966</t>
         </is>
       </c>
       <c r="B1034" t="inlineStr">
         <is>
-          <t>01098557018</t>
+          <t>01042088262</t>
         </is>
       </c>
       <c r="C1034" t="inlineStr">
         <is>
-          <t>223731</t>
+          <t>279266</t>
         </is>
       </c>
       <c r="D1034" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="E1034" t="inlineStr">
         <is>
-          <t>KAKAO_CH_MESSAGE_0409_HIKE365SUMMER</t>
+          <t>Direct</t>
         </is>
       </c>
     </row>
     <row r="1035">
       <c r="A1035" t="inlineStr">
         <is>
-          <t>kk_4526169965</t>
+          <t>kk_4837943303</t>
         </is>
       </c>
       <c r="B1035" t="inlineStr">
         <is>
-          <t>01076289838</t>
+          <t>01054817243</t>
         </is>
       </c>
       <c r="C1035" t="inlineStr">
         <is>
-          <t>286553</t>
+          <t>304025</t>
         </is>
       </c>
       <c r="D1035" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="E1035" t="inlineStr">
         <is>
-          <t>KAKAO_CH_MESSAGE_0409_HIKE365SUMMER</t>
+          <t>Direct</t>
         </is>
       </c>
     </row>
     <row r="1036">
       <c r="A1036" t="inlineStr">
         <is>
-          <t>kk_3638512879</t>
+          <t>kk_3373939453</t>
         </is>
       </c>
       <c r="B1036" t="inlineStr">
         <is>
-          <t>01053330589</t>
+          <t>01020110604</t>
         </is>
       </c>
       <c r="C1036" t="inlineStr">
         <is>
-          <t>248574</t>
+          <t>240269</t>
         </is>
       </c>
       <c r="D1036" t="inlineStr">
@@ -28396,24 +28396,24 @@
       </c>
       <c r="E1036" t="inlineStr">
         <is>
-          <t>KAKAO_CH_MESSAGE_0409_HIKE365SUMMER</t>
+          <t>KAKAO_CH_MESSAGE_0409_EXCLUSIVE</t>
         </is>
       </c>
     </row>
     <row r="1037">
       <c r="A1037" t="inlineStr">
         <is>
-          <t>kk_3373939453</t>
+          <t>kk_3155938902</t>
         </is>
       </c>
       <c r="B1037" t="inlineStr">
         <is>
-          <t>01020110604</t>
+          <t>01098557018</t>
         </is>
       </c>
       <c r="C1037" t="inlineStr">
         <is>
-          <t>240269</t>
+          <t>223731</t>
         </is>
       </c>
       <c r="D1037" t="inlineStr">
@@ -28423,34 +28423,34 @@
       </c>
       <c r="E1037" t="inlineStr">
         <is>
-          <t>KAKAO_CH_MESSAGE_0409_EXCLUSIVE</t>
+          <t>KAKAO_CH_MESSAGE_0409_HIKE365SUMMER</t>
         </is>
       </c>
     </row>
     <row r="1038">
       <c r="A1038" t="inlineStr">
         <is>
-          <t>kk_4837943303</t>
+          <t>kk_4526169965</t>
         </is>
       </c>
       <c r="B1038" t="inlineStr">
         <is>
-          <t>01054817243</t>
+          <t>01076289838</t>
         </is>
       </c>
       <c r="C1038" t="inlineStr">
         <is>
-          <t>304025</t>
+          <t>286553</t>
         </is>
       </c>
       <c r="D1038" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E1038" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>KAKAO_CH_MESSAGE_0409_HIKE365SUMMER</t>
         </is>
       </c>
     </row>
@@ -28484,54 +28484,54 @@
     <row r="1040">
       <c r="A1040" t="inlineStr">
         <is>
-          <t>wns1118</t>
+          <t>pearpear</t>
         </is>
       </c>
       <c r="B1040" t="inlineStr">
         <is>
-          <t>01090185590</t>
+          <t>01048098405</t>
         </is>
       </c>
       <c r="C1040" t="inlineStr">
         <is>
-          <t>303893</t>
+          <t>29743</t>
         </is>
       </c>
       <c r="D1040" t="inlineStr">
         <is>
-          <t>Organic Traffic</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E1040" t="inlineStr">
         <is>
-          <t>(organic)</t>
+          <t>Email_mkt</t>
         </is>
       </c>
     </row>
     <row r="1041">
       <c r="A1041" t="inlineStr">
         <is>
-          <t>kk_3180615052</t>
+          <t>wns1118</t>
         </is>
       </c>
       <c r="B1041" t="inlineStr">
         <is>
-          <t>01077203676</t>
+          <t>01090185590</t>
         </is>
       </c>
       <c r="C1041" t="inlineStr">
         <is>
-          <t>226112</t>
+          <t>303893</t>
         </is>
       </c>
       <c r="D1041" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Organic Traffic</t>
         </is>
       </c>
       <c r="E1041" t="inlineStr">
         <is>
-          <t>Email_mkt</t>
+          <t>(organic)</t>
         </is>
       </c>
     </row>
@@ -28592,17 +28592,17 @@
     <row r="1044">
       <c r="A1044" t="inlineStr">
         <is>
-          <t>pearpear</t>
+          <t>kk_3180615052</t>
         </is>
       </c>
       <c r="B1044" t="inlineStr">
         <is>
-          <t>01048098405</t>
+          <t>01077203676</t>
         </is>
       </c>
       <c r="C1044" t="inlineStr">
         <is>
-          <t>29743</t>
+          <t>226112</t>
         </is>
       </c>
       <c r="D1044" t="inlineStr">
@@ -28700,54 +28700,54 @@
     <row r="1048">
       <c r="A1048" t="inlineStr">
         <is>
-          <t>kk_2807863527</t>
+          <t>pentagram</t>
         </is>
       </c>
       <c r="B1048" t="inlineStr">
         <is>
-          <t>01042669625</t>
+          <t>01093327353</t>
         </is>
       </c>
       <c r="C1048" t="inlineStr">
         <is>
-          <t>211605</t>
+          <t>131085</t>
         </is>
       </c>
       <c r="D1048" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E1048" t="inlineStr">
         <is>
-          <t>[PF]전환_회원가입(유사)</t>
+          <t>KAKAO_alimtalk</t>
         </is>
       </c>
     </row>
     <row r="1049">
       <c r="A1049" t="inlineStr">
         <is>
-          <t>pentagram</t>
+          <t>kk_2807863527</t>
         </is>
       </c>
       <c r="B1049" t="inlineStr">
         <is>
-          <t>01093327353</t>
+          <t>01042669625</t>
         </is>
       </c>
       <c r="C1049" t="inlineStr">
         <is>
-          <t>131085</t>
+          <t>211605</t>
         </is>
       </c>
       <c r="D1049" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E1049" t="inlineStr">
         <is>
-          <t>KAKAO_alimtalk</t>
+          <t>[PF]전환_회원가입(유사)</t>
         </is>
       </c>
     </row>
@@ -28835,71 +28835,71 @@
     <row r="1053">
       <c r="A1053" t="inlineStr">
         <is>
-          <t>wisbrain</t>
+          <t>hihijs34</t>
         </is>
       </c>
       <c r="B1053" t="inlineStr">
         <is>
-          <t>01047220186</t>
+          <t>01093230529</t>
         </is>
       </c>
       <c r="C1053" t="inlineStr">
         <is>
-          <t>188067</t>
+          <t>128947</t>
         </is>
       </c>
       <c r="D1053" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E1053" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>[PF]A+SC_상시(1865MF,구매+장바구니)</t>
         </is>
       </c>
     </row>
     <row r="1054">
       <c r="A1054" t="inlineStr">
         <is>
-          <t>hihijs34</t>
+          <t>wisbrain</t>
         </is>
       </c>
       <c r="B1054" t="inlineStr">
         <is>
-          <t>01093230529</t>
+          <t>01047220186</t>
         </is>
       </c>
       <c r="C1054" t="inlineStr">
         <is>
-          <t>128947</t>
+          <t>188067</t>
         </is>
       </c>
       <c r="D1054" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="E1054" t="inlineStr">
         <is>
-          <t>[PF]A+SC_상시(1865MF,구매+장바구니)</t>
+          <t>Direct</t>
         </is>
       </c>
     </row>
     <row r="1055">
       <c r="A1055" t="inlineStr">
         <is>
-          <t>kk_4525043459</t>
+          <t>hyschant</t>
         </is>
       </c>
       <c r="B1055" t="inlineStr">
         <is>
-          <t>01088312135</t>
+          <t>01065306675</t>
         </is>
       </c>
       <c r="C1055" t="inlineStr">
         <is>
-          <t>286464</t>
+          <t>108579</t>
         </is>
       </c>
       <c r="D1055" t="inlineStr">
@@ -28916,17 +28916,17 @@
     <row r="1056">
       <c r="A1056" t="inlineStr">
         <is>
-          <t>dmsql785612</t>
+          <t>kk_4578503399</t>
         </is>
       </c>
       <c r="B1056" t="inlineStr">
         <is>
-          <t>01051590364</t>
+          <t>01088660330</t>
         </is>
       </c>
       <c r="C1056" t="inlineStr">
         <is>
-          <t>137279</t>
+          <t>288374</t>
         </is>
       </c>
       <c r="D1056" t="inlineStr">
@@ -28936,24 +28936,24 @@
       </c>
       <c r="E1056" t="inlineStr">
         <is>
-          <t>Email_mkt</t>
+          <t>LMS_ECOM_0410exclusive2</t>
         </is>
       </c>
     </row>
     <row r="1057">
       <c r="A1057" t="inlineStr">
         <is>
-          <t>inu21c</t>
+          <t>sjm700</t>
         </is>
       </c>
       <c r="B1057" t="inlineStr">
         <is>
-          <t>01035128236</t>
+          <t>01077331591</t>
         </is>
       </c>
       <c r="C1057" t="inlineStr">
         <is>
-          <t>131940</t>
+          <t>118769</t>
         </is>
       </c>
       <c r="D1057" t="inlineStr">
@@ -28970,71 +28970,71 @@
     <row r="1058">
       <c r="A1058" t="inlineStr">
         <is>
-          <t>kk_4292190414</t>
+          <t>kk_3349199057</t>
         </is>
       </c>
       <c r="B1058" t="inlineStr">
         <is>
-          <t>01095177478</t>
+          <t>01071630312</t>
         </is>
       </c>
       <c r="C1058" t="inlineStr">
         <is>
-          <t>275998</t>
+          <t>239388</t>
         </is>
       </c>
       <c r="D1058" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E1058" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>LMS_ECOM_0410exclusive2</t>
         </is>
       </c>
     </row>
     <row r="1059">
       <c r="A1059" t="inlineStr">
         <is>
-          <t>kk_3721447783</t>
+          <t>kk_3754052831</t>
         </is>
       </c>
       <c r="B1059" t="inlineStr">
         <is>
-          <t>01051311087</t>
+          <t>01092180804</t>
         </is>
       </c>
       <c r="C1059" t="inlineStr">
         <is>
-          <t>252252</t>
+          <t>254339</t>
         </is>
       </c>
       <c r="D1059" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E1059" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>LMS_ECOM_0410exclusive2</t>
         </is>
       </c>
     </row>
     <row r="1060">
       <c r="A1060" t="inlineStr">
         <is>
-          <t>yongshin</t>
+          <t>camiblanco</t>
         </is>
       </c>
       <c r="B1060" t="inlineStr">
         <is>
-          <t>01053867821</t>
+          <t>01072190103</t>
         </is>
       </c>
       <c r="C1060" t="inlineStr">
         <is>
-          <t>277896</t>
+          <t>232545</t>
         </is>
       </c>
       <c r="D1060" t="inlineStr">
@@ -29051,17 +29051,17 @@
     <row r="1061">
       <c r="A1061" t="inlineStr">
         <is>
-          <t>columbia7</t>
+          <t>dmsql785612</t>
         </is>
       </c>
       <c r="B1061" t="inlineStr">
         <is>
-          <t>01050080025</t>
+          <t>01051590364</t>
         </is>
       </c>
       <c r="C1061" t="inlineStr">
         <is>
-          <t>109980</t>
+          <t>137279</t>
         </is>
       </c>
       <c r="D1061" t="inlineStr">
@@ -29071,24 +29071,24 @@
       </c>
       <c r="E1061" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0410exclusive2</t>
+          <t>Email_mkt</t>
         </is>
       </c>
     </row>
     <row r="1062">
       <c r="A1062" t="inlineStr">
         <is>
-          <t>kk_4578503399</t>
+          <t>kk_3973703558</t>
         </is>
       </c>
       <c r="B1062" t="inlineStr">
         <is>
-          <t>01088660330</t>
+          <t>01048590748</t>
         </is>
       </c>
       <c r="C1062" t="inlineStr">
         <is>
-          <t>288374</t>
+          <t>271020</t>
         </is>
       </c>
       <c r="D1062" t="inlineStr">
@@ -29105,44 +29105,44 @@
     <row r="1063">
       <c r="A1063" t="inlineStr">
         <is>
-          <t>hyschant</t>
+          <t>yongshin</t>
         </is>
       </c>
       <c r="B1063" t="inlineStr">
         <is>
-          <t>01065306675</t>
+          <t>01053867821</t>
         </is>
       </c>
       <c r="C1063" t="inlineStr">
         <is>
-          <t>108579</t>
+          <t>277896</t>
         </is>
       </c>
       <c r="D1063" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="E1063" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0410exclusive2</t>
+          <t>Direct</t>
         </is>
       </c>
     </row>
     <row r="1064">
       <c r="A1064" t="inlineStr">
         <is>
-          <t>bobjazz</t>
+          <t>pls4u</t>
         </is>
       </c>
       <c r="B1064" t="inlineStr">
         <is>
-          <t>01084090677</t>
+          <t>01085985482</t>
         </is>
       </c>
       <c r="C1064" t="inlineStr">
         <is>
-          <t>186218</t>
+          <t>88257</t>
         </is>
       </c>
       <c r="D1064" t="inlineStr">
@@ -29152,24 +29152,24 @@
       </c>
       <c r="E1064" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0410exclusive2</t>
+          <t>LMS_ECOM_0401_trailrunning</t>
         </is>
       </c>
     </row>
     <row r="1065">
       <c r="A1065" t="inlineStr">
         <is>
-          <t>kk_2825715315</t>
+          <t>columbia7</t>
         </is>
       </c>
       <c r="B1065" t="inlineStr">
         <is>
-          <t>01077229654</t>
+          <t>01050080025</t>
         </is>
       </c>
       <c r="C1065" t="inlineStr">
         <is>
-          <t>212719</t>
+          <t>109980</t>
         </is>
       </c>
       <c r="D1065" t="inlineStr">
@@ -29186,17 +29186,17 @@
     <row r="1066">
       <c r="A1066" t="inlineStr">
         <is>
-          <t>kk_3024318364</t>
+          <t>kk_2825715315</t>
         </is>
       </c>
       <c r="B1066" t="inlineStr">
         <is>
-          <t>01050308038</t>
+          <t>01077229654</t>
         </is>
       </c>
       <c r="C1066" t="inlineStr">
         <is>
-          <t>219525</t>
+          <t>212719</t>
         </is>
       </c>
       <c r="D1066" t="inlineStr">
@@ -29213,17 +29213,17 @@
     <row r="1067">
       <c r="A1067" t="inlineStr">
         <is>
-          <t>kk_3349199057</t>
+          <t>kk_4525043459</t>
         </is>
       </c>
       <c r="B1067" t="inlineStr">
         <is>
-          <t>01071630312</t>
+          <t>01088312135</t>
         </is>
       </c>
       <c r="C1067" t="inlineStr">
         <is>
-          <t>239388</t>
+          <t>286464</t>
         </is>
       </c>
       <c r="D1067" t="inlineStr">
@@ -29240,17 +29240,17 @@
     <row r="1068">
       <c r="A1068" t="inlineStr">
         <is>
-          <t>sjm700</t>
+          <t>kk_4452401577</t>
         </is>
       </c>
       <c r="B1068" t="inlineStr">
         <is>
-          <t>01077331591</t>
+          <t>01047428000</t>
         </is>
       </c>
       <c r="C1068" t="inlineStr">
         <is>
-          <t>118769</t>
+          <t>282525</t>
         </is>
       </c>
       <c r="D1068" t="inlineStr">
@@ -29267,17 +29267,17 @@
     <row r="1069">
       <c r="A1069" t="inlineStr">
         <is>
-          <t>kk_4452401577</t>
+          <t>kk_3180736217</t>
         </is>
       </c>
       <c r="B1069" t="inlineStr">
         <is>
-          <t>01047428000</t>
+          <t>01036000343</t>
         </is>
       </c>
       <c r="C1069" t="inlineStr">
         <is>
-          <t>282525</t>
+          <t>226314</t>
         </is>
       </c>
       <c r="D1069" t="inlineStr">
@@ -29294,17 +29294,17 @@
     <row r="1070">
       <c r="A1070" t="inlineStr">
         <is>
-          <t>kk_3754052831</t>
+          <t>inu21c</t>
         </is>
       </c>
       <c r="B1070" t="inlineStr">
         <is>
-          <t>01092180804</t>
+          <t>01035128236</t>
         </is>
       </c>
       <c r="C1070" t="inlineStr">
         <is>
-          <t>254339</t>
+          <t>131940</t>
         </is>
       </c>
       <c r="D1070" t="inlineStr">
@@ -29321,17 +29321,17 @@
     <row r="1071">
       <c r="A1071" t="inlineStr">
         <is>
-          <t>kk_3973703558</t>
+          <t>kk_3024318364</t>
         </is>
       </c>
       <c r="B1071" t="inlineStr">
         <is>
-          <t>01048590748</t>
+          <t>01050308038</t>
         </is>
       </c>
       <c r="C1071" t="inlineStr">
         <is>
-          <t>271020</t>
+          <t>219525</t>
         </is>
       </c>
       <c r="D1071" t="inlineStr">
@@ -29348,17 +29348,17 @@
     <row r="1072">
       <c r="A1072" t="inlineStr">
         <is>
-          <t>camiblanco</t>
+          <t>kk_3721447783</t>
         </is>
       </c>
       <c r="B1072" t="inlineStr">
         <is>
-          <t>01072190103</t>
+          <t>01051311087</t>
         </is>
       </c>
       <c r="C1072" t="inlineStr">
         <is>
-          <t>232545</t>
+          <t>252252</t>
         </is>
       </c>
       <c r="D1072" t="inlineStr">
@@ -29375,17 +29375,17 @@
     <row r="1073">
       <c r="A1073" t="inlineStr">
         <is>
-          <t>kk_3180736217</t>
+          <t>bobjazz</t>
         </is>
       </c>
       <c r="B1073" t="inlineStr">
         <is>
-          <t>01036000343</t>
+          <t>01084090677</t>
         </is>
       </c>
       <c r="C1073" t="inlineStr">
         <is>
-          <t>226314</t>
+          <t>186218</t>
         </is>
       </c>
       <c r="D1073" t="inlineStr">
@@ -29402,98 +29402,98 @@
     <row r="1074">
       <c r="A1074" t="inlineStr">
         <is>
-          <t>pls4u</t>
+          <t>kk_4292190414</t>
         </is>
       </c>
       <c r="B1074" t="inlineStr">
         <is>
-          <t>01085985482</t>
+          <t>01095177478</t>
         </is>
       </c>
       <c r="C1074" t="inlineStr">
         <is>
-          <t>88257</t>
+          <t>275998</t>
         </is>
       </c>
       <c r="D1074" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="E1074" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0401_trailrunning</t>
+          <t>Direct</t>
         </is>
       </c>
     </row>
     <row r="1075">
       <c r="A1075" t="inlineStr">
         <is>
-          <t>kk_3626939480</t>
+          <t>kk_4838419826</t>
         </is>
       </c>
       <c r="B1075" t="inlineStr">
         <is>
-          <t>01030537990</t>
+          <t>01037240798</t>
         </is>
       </c>
       <c r="C1075" t="inlineStr">
         <is>
-          <t>247893</t>
+          <t>304050</t>
         </is>
       </c>
       <c r="D1075" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E1075" t="inlineStr">
         <is>
-          <t>KAKAO_CH_MESSAGE_0409_EXCLUSIVE</t>
+          <t>[PF]트래픽_유사+관심사</t>
         </is>
       </c>
     </row>
     <row r="1076">
       <c r="A1076" t="inlineStr">
         <is>
-          <t>kk_3813115836</t>
+          <t>kk_3912725759</t>
         </is>
       </c>
       <c r="B1076" t="inlineStr">
         <is>
-          <t>01066721591</t>
+          <t>01062505257</t>
         </is>
       </c>
       <c r="C1076" t="inlineStr">
         <is>
-          <t>261736</t>
+          <t>268286</t>
         </is>
       </c>
       <c r="D1076" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E1076" t="inlineStr">
         <is>
-          <t>EFW</t>
+          <t>KAKAO_CH_MESSAGE_0409_EXCLUSIVE</t>
         </is>
       </c>
     </row>
     <row r="1077">
       <c r="A1077" t="inlineStr">
         <is>
-          <t>kk_4838419826</t>
+          <t>kk_3813115836</t>
         </is>
       </c>
       <c r="B1077" t="inlineStr">
         <is>
-          <t>01037240798</t>
+          <t>01066721591</t>
         </is>
       </c>
       <c r="C1077" t="inlineStr">
         <is>
-          <t>304050</t>
+          <t>261736</t>
         </is>
       </c>
       <c r="D1077" t="inlineStr">
@@ -29503,24 +29503,24 @@
       </c>
       <c r="E1077" t="inlineStr">
         <is>
-          <t>[PF]트래픽_유사+관심사</t>
+          <t>EFW</t>
         </is>
       </c>
     </row>
     <row r="1078">
       <c r="A1078" t="inlineStr">
         <is>
-          <t>kk_3912725759</t>
+          <t>kk_3626939480</t>
         </is>
       </c>
       <c r="B1078" t="inlineStr">
         <is>
-          <t>01062505257</t>
+          <t>01030537990</t>
         </is>
       </c>
       <c r="C1078" t="inlineStr">
         <is>
-          <t>268286</t>
+          <t>247893</t>
         </is>
       </c>
       <c r="D1078" t="inlineStr">
@@ -29537,17 +29537,17 @@
     <row r="1079">
       <c r="A1079" t="inlineStr">
         <is>
-          <t>cjcangel</t>
+          <t>kk_4255987550</t>
         </is>
       </c>
       <c r="B1079" t="inlineStr">
         <is>
-          <t>01089325858</t>
+          <t>01026453656</t>
         </is>
       </c>
       <c r="C1079" t="inlineStr">
         <is>
-          <t>292800</t>
+          <t>274389</t>
         </is>
       </c>
       <c r="D1079" t="inlineStr">
@@ -29564,108 +29564,108 @@
     <row r="1080">
       <c r="A1080" t="inlineStr">
         <is>
-          <t>honga22</t>
+          <t>kk_4717085515</t>
         </is>
       </c>
       <c r="B1080" t="inlineStr">
         <is>
-          <t>01022690322</t>
+          <t>01052078703</t>
         </is>
       </c>
       <c r="C1080" t="inlineStr">
         <is>
-          <t>147568</t>
+          <t>297221</t>
         </is>
       </c>
       <c r="D1080" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="E1080" t="inlineStr">
         <is>
-          <t>KAKAO_alimtalk</t>
+          <t>Direct</t>
         </is>
       </c>
     </row>
     <row r="1081">
       <c r="A1081" t="inlineStr">
         <is>
-          <t>kk_3184270744</t>
+          <t>honga22</t>
         </is>
       </c>
       <c r="B1081" t="inlineStr">
         <is>
-          <t>01077689325</t>
+          <t>01022690322</t>
         </is>
       </c>
       <c r="C1081" t="inlineStr">
         <is>
-          <t>228883</t>
+          <t>147568</t>
         </is>
       </c>
       <c r="D1081" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E1081" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>KAKAO_alimtalk</t>
         </is>
       </c>
     </row>
     <row r="1082">
       <c r="A1082" t="inlineStr">
         <is>
-          <t>kk_4255987550</t>
+          <t>kk_3184270744</t>
         </is>
       </c>
       <c r="B1082" t="inlineStr">
         <is>
-          <t>01026453656</t>
+          <t>01077689325</t>
         </is>
       </c>
       <c r="C1082" t="inlineStr">
         <is>
-          <t>274389</t>
+          <t>228883</t>
         </is>
       </c>
       <c r="D1082" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="E1082" t="inlineStr">
         <is>
-          <t>Email_mkt</t>
+          <t>Direct</t>
         </is>
       </c>
     </row>
     <row r="1083">
       <c r="A1083" t="inlineStr">
         <is>
-          <t>kk_4717085515</t>
+          <t>cjcangel</t>
         </is>
       </c>
       <c r="B1083" t="inlineStr">
         <is>
-          <t>01052078703</t>
+          <t>01089325858</t>
         </is>
       </c>
       <c r="C1083" t="inlineStr">
         <is>
-          <t>297221</t>
+          <t>292800</t>
         </is>
       </c>
       <c r="D1083" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E1083" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>Email_mkt</t>
         </is>
       </c>
     </row>
@@ -29699,17 +29699,17 @@
     <row r="1085">
       <c r="A1085" t="inlineStr">
         <is>
-          <t>happy201106</t>
+          <t>alcoholpower</t>
         </is>
       </c>
       <c r="B1085" t="inlineStr">
         <is>
-          <t>01090012622</t>
+          <t>01027629868</t>
         </is>
       </c>
       <c r="C1085" t="inlineStr">
         <is>
-          <t>136050</t>
+          <t>252954</t>
         </is>
       </c>
       <c r="D1085" t="inlineStr">
@@ -29753,17 +29753,17 @@
     <row r="1087">
       <c r="A1087" t="inlineStr">
         <is>
-          <t>alcoholpower</t>
+          <t>happy201106</t>
         </is>
       </c>
       <c r="B1087" t="inlineStr">
         <is>
-          <t>01027629868</t>
+          <t>01090012622</t>
         </is>
       </c>
       <c r="C1087" t="inlineStr">
         <is>
-          <t>252954</t>
+          <t>136050</t>
         </is>
       </c>
       <c r="D1087" t="inlineStr">

--- a/reports/member_funnel/downloads/member_funnel_7d_non_buyer.xlsx
+++ b/reports/member_funnel/downloads/member_funnel_7d_non_buyer.xlsx
@@ -11096,54 +11096,54 @@
     <row r="396">
       <c r="A396" t="inlineStr">
         <is>
-          <t>kk_4839170665</t>
+          <t>kwon9493</t>
         </is>
       </c>
       <c r="B396" t="inlineStr">
         <is>
-          <t>01050116666</t>
+          <t>01035589493</t>
         </is>
       </c>
       <c r="C396" t="inlineStr">
         <is>
-          <t>304086</t>
+          <t>107077</t>
         </is>
       </c>
       <c r="D396" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="E396" t="inlineStr">
         <is>
-          <t>EFW</t>
+          <t>Direct</t>
         </is>
       </c>
     </row>
     <row r="397">
       <c r="A397" t="inlineStr">
         <is>
-          <t>kwon9493</t>
+          <t>kk_4839170665</t>
         </is>
       </c>
       <c r="B397" t="inlineStr">
         <is>
-          <t>01035589493</t>
+          <t>01050116666</t>
         </is>
       </c>
       <c r="C397" t="inlineStr">
         <is>
-          <t>107077</t>
+          <t>304086</t>
         </is>
       </c>
       <c r="D397" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E397" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>EFW</t>
         </is>
       </c>
     </row>
@@ -15227,17 +15227,17 @@
     <row r="549">
       <c r="A549" t="inlineStr">
         <is>
-          <t>kk_4789688431</t>
+          <t>kk_3483300064</t>
         </is>
       </c>
       <c r="B549" t="inlineStr">
         <is>
-          <t>01099981265</t>
+          <t>01092213404</t>
         </is>
       </c>
       <c r="C549" t="inlineStr">
         <is>
-          <t>302023</t>
+          <t>244619</t>
         </is>
       </c>
       <c r="D549" t="inlineStr">
@@ -15247,61 +15247,61 @@
       </c>
       <c r="E549" t="inlineStr">
         <is>
-          <t>sa</t>
+          <t>naver_brandsearch_mobile</t>
         </is>
       </c>
     </row>
     <row r="550">
       <c r="A550" t="inlineStr">
         <is>
-          <t>kk_4837763007</t>
+          <t>kk_4789688431</t>
         </is>
       </c>
       <c r="B550" t="inlineStr">
         <is>
-          <t>01088993992</t>
+          <t>01099981265</t>
         </is>
       </c>
       <c r="C550" t="inlineStr">
         <is>
-          <t>304013</t>
+          <t>302023</t>
         </is>
       </c>
       <c r="D550" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E550" t="inlineStr">
         <is>
-          <t>(referral)</t>
+          <t>sa</t>
         </is>
       </c>
     </row>
     <row r="551">
       <c r="A551" t="inlineStr">
         <is>
-          <t>kk_3483300064</t>
+          <t>kk_4837763007</t>
         </is>
       </c>
       <c r="B551" t="inlineStr">
         <is>
-          <t>01092213404</t>
+          <t>01088993992</t>
         </is>
       </c>
       <c r="C551" t="inlineStr">
         <is>
-          <t>244619</t>
+          <t>304013</t>
         </is>
       </c>
       <c r="D551" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E551" t="inlineStr">
         <is>
-          <t>naver_brandsearch_mobile</t>
+          <t>(referral)</t>
         </is>
       </c>
     </row>
@@ -17549,17 +17549,17 @@
     <row r="635">
       <c r="A635" t="inlineStr">
         <is>
-          <t>kk_4840846776</t>
+          <t>kk_4840658838</t>
         </is>
       </c>
       <c r="B635" t="inlineStr">
         <is>
-          <t>01055961435</t>
+          <t>01039292600</t>
         </is>
       </c>
       <c r="C635" t="inlineStr">
         <is>
-          <t>304170</t>
+          <t>304158</t>
         </is>
       </c>
       <c r="D635" t="inlineStr">
@@ -17569,24 +17569,24 @@
       </c>
       <c r="E635" t="inlineStr">
         <is>
-          <t>[PF]전환_회원가입(유사)</t>
+          <t>EFW</t>
         </is>
       </c>
     </row>
     <row r="636">
       <c r="A636" t="inlineStr">
         <is>
-          <t>kk_4840658838</t>
+          <t>kk_4840846776</t>
         </is>
       </c>
       <c r="B636" t="inlineStr">
         <is>
-          <t>01039292600</t>
+          <t>01055961435</t>
         </is>
       </c>
       <c r="C636" t="inlineStr">
         <is>
-          <t>304158</t>
+          <t>304170</t>
         </is>
       </c>
       <c r="D636" t="inlineStr">
@@ -17596,7 +17596,7 @@
       </c>
       <c r="E636" t="inlineStr">
         <is>
-          <t>EFW</t>
+          <t>[PF]전환_회원가입(유사)</t>
         </is>
       </c>
     </row>
@@ -18683,54 +18683,54 @@
     <row r="677">
       <c r="A677" t="inlineStr">
         <is>
-          <t>hisgogo</t>
+          <t>kk_3671070277</t>
         </is>
       </c>
       <c r="B677" t="inlineStr">
         <is>
-          <t>01054110956</t>
+          <t>01065561446</t>
         </is>
       </c>
       <c r="C677" t="inlineStr">
         <is>
-          <t>174486</t>
+          <t>250075</t>
         </is>
       </c>
       <c r="D677" t="inlineStr">
         <is>
-          <t>Organic Traffic</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E677" t="inlineStr">
         <is>
-          <t>(referral)</t>
+          <t>KAKAO_CH_MESSAGE_0409_HIKE365SUMMER</t>
         </is>
       </c>
     </row>
     <row r="678">
       <c r="A678" t="inlineStr">
         <is>
-          <t>kk_3671070277</t>
+          <t>hisgogo</t>
         </is>
       </c>
       <c r="B678" t="inlineStr">
         <is>
-          <t>01065561446</t>
+          <t>01054110956</t>
         </is>
       </c>
       <c r="C678" t="inlineStr">
         <is>
-          <t>250075</t>
+          <t>174486</t>
         </is>
       </c>
       <c r="D678" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Organic Traffic</t>
         </is>
       </c>
       <c r="E678" t="inlineStr">
         <is>
-          <t>KAKAO_CH_MESSAGE_0409_HIKE365SUMMER</t>
+          <t>(referral)</t>
         </is>
       </c>
     </row>
@@ -18818,54 +18818,54 @@
     <row r="682">
       <c r="A682" t="inlineStr">
         <is>
-          <t>kk_3244752214</t>
+          <t>kk_4367946268</t>
         </is>
       </c>
       <c r="B682" t="inlineStr">
         <is>
-          <t>01052959157</t>
+          <t>01098834648</t>
         </is>
       </c>
       <c r="C682" t="inlineStr">
         <is>
-          <t>234935</t>
+          <t>279882</t>
         </is>
       </c>
       <c r="D682" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="E682" t="inlineStr">
         <is>
-          <t>KAKAO_CH_MESSAGE_0409_EXCLUSIVE</t>
+          <t>Direct</t>
         </is>
       </c>
     </row>
     <row r="683">
       <c r="A683" t="inlineStr">
         <is>
-          <t>kk_4367946268</t>
+          <t>kk_3244752214</t>
         </is>
       </c>
       <c r="B683" t="inlineStr">
         <is>
-          <t>01098834648</t>
+          <t>01052959157</t>
         </is>
       </c>
       <c r="C683" t="inlineStr">
         <is>
-          <t>279882</t>
+          <t>234935</t>
         </is>
       </c>
       <c r="D683" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E683" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>KAKAO_CH_MESSAGE_0409_EXCLUSIVE</t>
         </is>
       </c>
     </row>
@@ -19493,54 +19493,54 @@
     <row r="707">
       <c r="A707" t="inlineStr">
         <is>
-          <t>kk_4839145768</t>
+          <t>sun1381</t>
         </is>
       </c>
       <c r="B707" t="inlineStr">
         <is>
-          <t>01097367898</t>
+          <t>01037709416</t>
         </is>
       </c>
       <c r="C707" t="inlineStr">
         <is>
-          <t>304085</t>
+          <t>278160</t>
         </is>
       </c>
       <c r="D707" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E707" t="inlineStr">
         <is>
-          <t>naver_brandsearch_pc</t>
+          <t>LMS_ECOM_0410exclusive2</t>
         </is>
       </c>
     </row>
     <row r="708">
       <c r="A708" t="inlineStr">
         <is>
-          <t>sun1381</t>
+          <t>kk_4839145768</t>
         </is>
       </c>
       <c r="B708" t="inlineStr">
         <is>
-          <t>01037709416</t>
+          <t>01097367898</t>
         </is>
       </c>
       <c r="C708" t="inlineStr">
         <is>
-          <t>278160</t>
+          <t>304085</t>
         </is>
       </c>
       <c r="D708" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E708" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0410exclusive2</t>
+          <t>naver_brandsearch_pc</t>
         </is>
       </c>
     </row>
@@ -19655,17 +19655,17 @@
     <row r="713">
       <c r="A713" t="inlineStr">
         <is>
-          <t>kk_4617674866</t>
+          <t>kk_4641269666</t>
         </is>
       </c>
       <c r="B713" t="inlineStr">
         <is>
-          <t>01062147077</t>
+          <t>01041565334</t>
         </is>
       </c>
       <c r="C713" t="inlineStr">
         <is>
-          <t>290764</t>
+          <t>292505</t>
         </is>
       </c>
       <c r="D713" t="inlineStr">
@@ -19675,24 +19675,24 @@
       </c>
       <c r="E713" t="inlineStr">
         <is>
-          <t>KAKAO_CH_MESSAGE_0409_TRAIL</t>
+          <t>KAKAO_CH_MESSAGE_0409_HIKE365SUMMER</t>
         </is>
       </c>
     </row>
     <row r="714">
       <c r="A714" t="inlineStr">
         <is>
-          <t>kk_4641269666</t>
+          <t>kk_4617674866</t>
         </is>
       </c>
       <c r="B714" t="inlineStr">
         <is>
-          <t>01041565334</t>
+          <t>01062147077</t>
         </is>
       </c>
       <c r="C714" t="inlineStr">
         <is>
-          <t>292505</t>
+          <t>290764</t>
         </is>
       </c>
       <c r="D714" t="inlineStr">
@@ -19702,7 +19702,7 @@
       </c>
       <c r="E714" t="inlineStr">
         <is>
-          <t>KAKAO_CH_MESSAGE_0409_HIKE365SUMMER</t>
+          <t>KAKAO_CH_MESSAGE_0409_TRAIL</t>
         </is>
       </c>
     </row>
@@ -19979,54 +19979,54 @@
     <row r="725">
       <c r="A725" t="inlineStr">
         <is>
-          <t>kk_4848049317</t>
+          <t>kk_4848573198</t>
         </is>
       </c>
       <c r="B725" t="inlineStr">
         <is>
-          <t>01064006801</t>
+          <t>01081135059</t>
         </is>
       </c>
       <c r="C725" t="inlineStr">
         <is>
-          <t>304514</t>
+          <t>304535</t>
         </is>
       </c>
       <c r="D725" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="E725" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Direct</t>
         </is>
       </c>
     </row>
     <row r="726">
       <c r="A726" t="inlineStr">
         <is>
-          <t>kk_4848573198</t>
+          <t>kk_4848049317</t>
         </is>
       </c>
       <c r="B726" t="inlineStr">
         <is>
-          <t>01081135059</t>
+          <t>01064006801</t>
         </is>
       </c>
       <c r="C726" t="inlineStr">
         <is>
-          <t>304535</t>
+          <t>304514</t>
         </is>
       </c>
       <c r="D726" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E726" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>Paid Ad</t>
         </is>
       </c>
     </row>
@@ -20060,54 +20060,54 @@
     <row r="728">
       <c r="A728" t="inlineStr">
         <is>
-          <t>kk_2999650964</t>
+          <t>kk_3631606950</t>
         </is>
       </c>
       <c r="B728" t="inlineStr">
         <is>
-          <t>01073667501</t>
+          <t>01063256163</t>
         </is>
       </c>
       <c r="C728" t="inlineStr">
         <is>
-          <t>218535</t>
+          <t>248164</t>
         </is>
       </c>
       <c r="D728" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="E728" t="inlineStr">
         <is>
-          <t>bizboard</t>
+          <t>미분류</t>
         </is>
       </c>
     </row>
     <row r="729">
       <c r="A729" t="inlineStr">
         <is>
-          <t>kk_3631606950</t>
+          <t>kk_2999650964</t>
         </is>
       </c>
       <c r="B729" t="inlineStr">
         <is>
-          <t>01063256163</t>
+          <t>01073667501</t>
         </is>
       </c>
       <c r="C729" t="inlineStr">
         <is>
-          <t>248164</t>
+          <t>218535</t>
         </is>
       </c>
       <c r="D729" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E729" t="inlineStr">
         <is>
-          <t>미분류</t>
+          <t>bizboard</t>
         </is>
       </c>
     </row>
@@ -20330,17 +20330,17 @@
     <row r="738">
       <c r="A738" t="inlineStr">
         <is>
-          <t>abril80</t>
+          <t>kang481127</t>
         </is>
       </c>
       <c r="B738" t="inlineStr">
         <is>
-          <t>01032942835</t>
+          <t>01053764012</t>
         </is>
       </c>
       <c r="C738" t="inlineStr">
         <is>
-          <t>192610</t>
+          <t>304276</t>
         </is>
       </c>
       <c r="D738" t="inlineStr">
@@ -20350,24 +20350,24 @@
       </c>
       <c r="E738" t="inlineStr">
         <is>
-          <t>Email_mkt</t>
+          <t>LMS_ECOM_NEWMEMBER</t>
         </is>
       </c>
     </row>
     <row r="739">
       <c r="A739" t="inlineStr">
         <is>
-          <t>kang481127</t>
+          <t>abril80</t>
         </is>
       </c>
       <c r="B739" t="inlineStr">
         <is>
-          <t>01053764012</t>
+          <t>01032942835</t>
         </is>
       </c>
       <c r="C739" t="inlineStr">
         <is>
-          <t>304276</t>
+          <t>192610</t>
         </is>
       </c>
       <c r="D739" t="inlineStr">
@@ -20377,7 +20377,7 @@
       </c>
       <c r="E739" t="inlineStr">
         <is>
-          <t>LMS_ECOM_NEWMEMBER</t>
+          <t>Email_mkt</t>
         </is>
       </c>
     </row>
@@ -20546,17 +20546,17 @@
     <row r="746">
       <c r="A746" t="inlineStr">
         <is>
-          <t>kk_4839680663</t>
+          <t>kk_4639169718</t>
         </is>
       </c>
       <c r="B746" t="inlineStr">
         <is>
-          <t>01046429530</t>
+          <t>01041380770</t>
         </is>
       </c>
       <c r="C746" t="inlineStr">
         <is>
-          <t>304109</t>
+          <t>292319</t>
         </is>
       </c>
       <c r="D746" t="inlineStr">
@@ -20566,24 +20566,24 @@
       </c>
       <c r="E746" t="inlineStr">
         <is>
-          <t>6968489536332</t>
+          <t>naver_brandsearch_mobile</t>
         </is>
       </c>
     </row>
     <row r="747">
       <c r="A747" t="inlineStr">
         <is>
-          <t>kk_3392066640</t>
+          <t>athend</t>
         </is>
       </c>
       <c r="B747" t="inlineStr">
         <is>
-          <t>01065021283</t>
+          <t>01041786462</t>
         </is>
       </c>
       <c r="C747" t="inlineStr">
         <is>
-          <t>240983</t>
+          <t>285491</t>
         </is>
       </c>
       <c r="D747" t="inlineStr">
@@ -20593,24 +20593,24 @@
       </c>
       <c r="E747" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0410exclusive2</t>
+          <t>KAKAO_alimtalk</t>
         </is>
       </c>
     </row>
     <row r="748">
       <c r="A748" t="inlineStr">
         <is>
-          <t>athend</t>
+          <t>kk_3392066640</t>
         </is>
       </c>
       <c r="B748" t="inlineStr">
         <is>
-          <t>01041786462</t>
+          <t>01065021283</t>
         </is>
       </c>
       <c r="C748" t="inlineStr">
         <is>
-          <t>285491</t>
+          <t>240983</t>
         </is>
       </c>
       <c r="D748" t="inlineStr">
@@ -20620,24 +20620,24 @@
       </c>
       <c r="E748" t="inlineStr">
         <is>
-          <t>KAKAO_alimtalk</t>
+          <t>LMS_ECOM_0410exclusive2</t>
         </is>
       </c>
     </row>
     <row r="749">
       <c r="A749" t="inlineStr">
         <is>
-          <t>kk_4639169718</t>
+          <t>kk_4839680663</t>
         </is>
       </c>
       <c r="B749" t="inlineStr">
         <is>
-          <t>01041380770</t>
+          <t>01046429530</t>
         </is>
       </c>
       <c r="C749" t="inlineStr">
         <is>
-          <t>292319</t>
+          <t>304109</t>
         </is>
       </c>
       <c r="D749" t="inlineStr">
@@ -20647,78 +20647,78 @@
       </c>
       <c r="E749" t="inlineStr">
         <is>
-          <t>naver_brandsearch_mobile</t>
+          <t>6968489536332</t>
         </is>
       </c>
     </row>
     <row r="750">
       <c r="A750" t="inlineStr">
         <is>
-          <t>kk_4431727915</t>
+          <t>kk_3404142353</t>
         </is>
       </c>
       <c r="B750" t="inlineStr">
         <is>
-          <t>01047182896</t>
+          <t>01053293239</t>
         </is>
       </c>
       <c r="C750" t="inlineStr">
         <is>
-          <t>281759</t>
+          <t>241289</t>
         </is>
       </c>
       <c r="D750" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E750" t="inlineStr">
         <is>
-          <t>KAKAO_CH_MESSAGE_0409_HIKE365SUMMER</t>
+          <t>[PF]전환_상시(2565MF,비구매자)</t>
         </is>
       </c>
     </row>
     <row r="751">
       <c r="A751" t="inlineStr">
         <is>
-          <t>kk_3184667648</t>
+          <t>kk_4431727915</t>
         </is>
       </c>
       <c r="B751" t="inlineStr">
         <is>
-          <t>01043440321</t>
+          <t>01047182896</t>
         </is>
       </c>
       <c r="C751" t="inlineStr">
         <is>
-          <t>229128</t>
+          <t>281759</t>
         </is>
       </c>
       <c r="D751" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E751" t="inlineStr">
         <is>
-          <t>sa</t>
+          <t>KAKAO_CH_MESSAGE_0409_HIKE365SUMMER</t>
         </is>
       </c>
     </row>
     <row r="752">
       <c r="A752" t="inlineStr">
         <is>
-          <t>kk_3404142353</t>
+          <t>kk_3184667648</t>
         </is>
       </c>
       <c r="B752" t="inlineStr">
         <is>
-          <t>01053293239</t>
+          <t>01043440321</t>
         </is>
       </c>
       <c r="C752" t="inlineStr">
         <is>
-          <t>241289</t>
+          <t>229128</t>
         </is>
       </c>
       <c r="D752" t="inlineStr">
@@ -20728,7 +20728,7 @@
       </c>
       <c r="E752" t="inlineStr">
         <is>
-          <t>[PF]전환_상시(2565MF,비구매자)</t>
+          <t>sa</t>
         </is>
       </c>
     </row>
@@ -20843,54 +20843,54 @@
     <row r="757">
       <c r="A757" t="inlineStr">
         <is>
-          <t>kk_4839433808</t>
+          <t>isaackwak</t>
         </is>
       </c>
       <c r="B757" t="inlineStr">
         <is>
-          <t>01025333388</t>
+          <t>01090599860</t>
         </is>
       </c>
       <c r="C757" t="inlineStr">
         <is>
-          <t>304100</t>
+          <t>275913</t>
         </is>
       </c>
       <c r="D757" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="E757" t="inlineStr">
         <is>
-          <t>naver_brandsearch_mobile</t>
+          <t>Direct</t>
         </is>
       </c>
     </row>
     <row r="758">
       <c r="A758" t="inlineStr">
         <is>
-          <t>ganjing78</t>
+          <t>kk_4839433808</t>
         </is>
       </c>
       <c r="B758" t="inlineStr">
         <is>
-          <t>01065121424</t>
+          <t>01025333388</t>
         </is>
       </c>
       <c r="C758" t="inlineStr">
         <is>
-          <t>78590</t>
+          <t>304100</t>
         </is>
       </c>
       <c r="D758" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E758" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0410exclusive2</t>
+          <t>naver_brandsearch_mobile</t>
         </is>
       </c>
     </row>
@@ -20924,81 +20924,81 @@
     <row r="760">
       <c r="A760" t="inlineStr">
         <is>
-          <t>isaackwak</t>
+          <t>ganjing78</t>
         </is>
       </c>
       <c r="B760" t="inlineStr">
         <is>
-          <t>01090599860</t>
+          <t>01065121424</t>
         </is>
       </c>
       <c r="C760" t="inlineStr">
         <is>
-          <t>275913</t>
+          <t>78590</t>
         </is>
       </c>
       <c r="D760" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E760" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>LMS_ECOM_0410exclusive2</t>
         </is>
       </c>
     </row>
     <row r="761">
       <c r="A761" t="inlineStr">
         <is>
-          <t>ldh7go</t>
+          <t>lee6007</t>
         </is>
       </c>
       <c r="B761" t="inlineStr">
         <is>
-          <t>01034075007</t>
+          <t>01039973613</t>
         </is>
       </c>
       <c r="C761" t="inlineStr">
         <is>
-          <t>221575</t>
+          <t>168179</t>
         </is>
       </c>
       <c r="D761" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="E761" t="inlineStr">
         <is>
-          <t>KAKAO_CH_MESSAGE_0409_HIKE365SUMMER</t>
+          <t>Direct</t>
         </is>
       </c>
     </row>
     <row r="762">
       <c r="A762" t="inlineStr">
         <is>
-          <t>lee6007</t>
+          <t>ldh7go</t>
         </is>
       </c>
       <c r="B762" t="inlineStr">
         <is>
-          <t>01039973613</t>
+          <t>01034075007</t>
         </is>
       </c>
       <c r="C762" t="inlineStr">
         <is>
-          <t>168179</t>
+          <t>221575</t>
         </is>
       </c>
       <c r="D762" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E762" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>KAKAO_CH_MESSAGE_0409_HIKE365SUMMER</t>
         </is>
       </c>
     </row>
@@ -21032,81 +21032,81 @@
     <row r="764">
       <c r="A764" t="inlineStr">
         <is>
-          <t>kk_4727921763</t>
+          <t>kk_4839026541</t>
         </is>
       </c>
       <c r="B764" t="inlineStr">
         <is>
-          <t>01045673975</t>
+          <t>01089431507</t>
         </is>
       </c>
       <c r="C764" t="inlineStr">
         <is>
-          <t>298138</t>
+          <t>304082</t>
         </is>
       </c>
       <c r="D764" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E764" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>[PF]전환_상시(2565MF,비구매자)</t>
         </is>
       </c>
     </row>
     <row r="765">
       <c r="A765" t="inlineStr">
         <is>
-          <t>kk_4839026541</t>
+          <t>kk_2757380967</t>
         </is>
       </c>
       <c r="B765" t="inlineStr">
         <is>
-          <t>01089431507</t>
+          <t>01034635649</t>
         </is>
       </c>
       <c r="C765" t="inlineStr">
         <is>
-          <t>304082</t>
+          <t>208245</t>
         </is>
       </c>
       <c r="D765" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E765" t="inlineStr">
         <is>
-          <t>[PF]전환_상시(2565MF,비구매자)</t>
+          <t>LMS_ECOM_0410exclusive2</t>
         </is>
       </c>
     </row>
     <row r="766">
       <c r="A766" t="inlineStr">
         <is>
-          <t>kk_2757380967</t>
+          <t>kk_4727921763</t>
         </is>
       </c>
       <c r="B766" t="inlineStr">
         <is>
-          <t>01034635649</t>
+          <t>01045673975</t>
         </is>
       </c>
       <c r="C766" t="inlineStr">
         <is>
-          <t>208245</t>
+          <t>298138</t>
         </is>
       </c>
       <c r="D766" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="E766" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0410exclusive2</t>
+          <t>Direct</t>
         </is>
       </c>
     </row>
@@ -21356,17 +21356,17 @@
     <row r="776">
       <c r="A776" t="inlineStr">
         <is>
-          <t>kk_4600405600</t>
+          <t>kk_4368805733</t>
         </is>
       </c>
       <c r="B776" t="inlineStr">
         <is>
-          <t>01053449477</t>
+          <t>01075528863</t>
         </is>
       </c>
       <c r="C776" t="inlineStr">
         <is>
-          <t>289364</t>
+          <t>279909</t>
         </is>
       </c>
       <c r="D776" t="inlineStr">
@@ -21383,17 +21383,17 @@
     <row r="777">
       <c r="A777" t="inlineStr">
         <is>
-          <t>kk_3967419156</t>
+          <t>kk_4600405600</t>
         </is>
       </c>
       <c r="B777" t="inlineStr">
         <is>
-          <t>01030207947</t>
+          <t>01053449477</t>
         </is>
       </c>
       <c r="C777" t="inlineStr">
         <is>
-          <t>270708</t>
+          <t>289364</t>
         </is>
       </c>
       <c r="D777" t="inlineStr">
@@ -21410,17 +21410,17 @@
     <row r="778">
       <c r="A778" t="inlineStr">
         <is>
-          <t>kk_4368805733</t>
+          <t>kk_3967419156</t>
         </is>
       </c>
       <c r="B778" t="inlineStr">
         <is>
-          <t>01075528863</t>
+          <t>01030207947</t>
         </is>
       </c>
       <c r="C778" t="inlineStr">
         <is>
-          <t>279909</t>
+          <t>270708</t>
         </is>
       </c>
       <c r="D778" t="inlineStr">
@@ -21437,17 +21437,17 @@
     <row r="779">
       <c r="A779" t="inlineStr">
         <is>
-          <t>kk_3795414578</t>
+          <t>kk_4514902337</t>
         </is>
       </c>
       <c r="B779" t="inlineStr">
         <is>
-          <t>01023131674</t>
+          <t>01024416928</t>
         </is>
       </c>
       <c r="C779" t="inlineStr">
         <is>
-          <t>257620</t>
+          <t>285925</t>
         </is>
       </c>
       <c r="D779" t="inlineStr">
@@ -21464,17 +21464,17 @@
     <row r="780">
       <c r="A780" t="inlineStr">
         <is>
-          <t>kk_4514902337</t>
+          <t>kk_3795414578</t>
         </is>
       </c>
       <c r="B780" t="inlineStr">
         <is>
-          <t>01024416928</t>
+          <t>01023131674</t>
         </is>
       </c>
       <c r="C780" t="inlineStr">
         <is>
-          <t>285925</t>
+          <t>257620</t>
         </is>
       </c>
       <c r="D780" t="inlineStr">
@@ -21518,71 +21518,71 @@
     <row r="782">
       <c r="A782" t="inlineStr">
         <is>
-          <t>l00years</t>
+          <t>seizeh</t>
         </is>
       </c>
       <c r="B782" t="inlineStr">
         <is>
-          <t>01053925529</t>
+          <t>01090302539</t>
         </is>
       </c>
       <c r="C782" t="inlineStr">
         <is>
-          <t>229454</t>
+          <t>68751</t>
         </is>
       </c>
       <c r="D782" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E782" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0410exclusive2</t>
+          <t>sa</t>
         </is>
       </c>
     </row>
     <row r="783">
       <c r="A783" t="inlineStr">
         <is>
-          <t>seizeh</t>
+          <t>l00years</t>
         </is>
       </c>
       <c r="B783" t="inlineStr">
         <is>
-          <t>01090302539</t>
+          <t>01053925529</t>
         </is>
       </c>
       <c r="C783" t="inlineStr">
         <is>
-          <t>68751</t>
+          <t>229454</t>
         </is>
       </c>
       <c r="D783" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E783" t="inlineStr">
         <is>
-          <t>sa</t>
+          <t>LMS_ECOM_0410exclusive2</t>
         </is>
       </c>
     </row>
     <row r="784">
       <c r="A784" t="inlineStr">
         <is>
-          <t>noma6420</t>
+          <t>mplkh</t>
         </is>
       </c>
       <c r="B784" t="inlineStr">
         <is>
-          <t>01071574279</t>
+          <t>01085245802</t>
         </is>
       </c>
       <c r="C784" t="inlineStr">
         <is>
-          <t>304023</t>
+          <t>160698</t>
         </is>
       </c>
       <c r="D784" t="inlineStr">
@@ -21592,24 +21592,24 @@
       </c>
       <c r="E784" t="inlineStr">
         <is>
-          <t>[PF]A SC_상시(1865MF,구매 장바구니)</t>
+          <t>sa</t>
         </is>
       </c>
     </row>
     <row r="785">
       <c r="A785" t="inlineStr">
         <is>
-          <t>mplkh</t>
+          <t>pieerot1</t>
         </is>
       </c>
       <c r="B785" t="inlineStr">
         <is>
-          <t>01085245802</t>
+          <t>01054503186</t>
         </is>
       </c>
       <c r="C785" t="inlineStr">
         <is>
-          <t>160698</t>
+          <t>29988</t>
         </is>
       </c>
       <c r="D785" t="inlineStr">
@@ -21619,24 +21619,24 @@
       </c>
       <c r="E785" t="inlineStr">
         <is>
-          <t>sa</t>
+          <t>naver_brandsearch_mobile</t>
         </is>
       </c>
     </row>
     <row r="786">
       <c r="A786" t="inlineStr">
         <is>
-          <t>pieerot1</t>
+          <t>noma6420</t>
         </is>
       </c>
       <c r="B786" t="inlineStr">
         <is>
-          <t>01054503186</t>
+          <t>01071574279</t>
         </is>
       </c>
       <c r="C786" t="inlineStr">
         <is>
-          <t>29988</t>
+          <t>304023</t>
         </is>
       </c>
       <c r="D786" t="inlineStr">
@@ -21646,7 +21646,7 @@
       </c>
       <c r="E786" t="inlineStr">
         <is>
-          <t>naver_brandsearch_mobile</t>
+          <t>[PF]A SC_상시(1865MF,구매 장바구니)</t>
         </is>
       </c>
     </row>
@@ -22193,54 +22193,54 @@
     <row r="807">
       <c r="A807" t="inlineStr">
         <is>
-          <t>kk_4847555695</t>
+          <t>kk_4847128332</t>
         </is>
       </c>
       <c r="B807" t="inlineStr">
         <is>
-          <t>01064202720</t>
+          <t>01098812833</t>
         </is>
       </c>
       <c r="C807" t="inlineStr">
         <is>
-          <t>304499</t>
+          <t>304480</t>
         </is>
       </c>
       <c r="D807" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E807" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>Paid Ad</t>
         </is>
       </c>
     </row>
     <row r="808">
       <c r="A808" t="inlineStr">
         <is>
-          <t>kk_4847128332</t>
+          <t>kk_4847555695</t>
         </is>
       </c>
       <c r="B808" t="inlineStr">
         <is>
-          <t>01098812833</t>
+          <t>01064202720</t>
         </is>
       </c>
       <c r="C808" t="inlineStr">
         <is>
-          <t>304480</t>
+          <t>304499</t>
         </is>
       </c>
       <c r="D808" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="E808" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Direct</t>
         </is>
       </c>
     </row>
@@ -22760,54 +22760,54 @@
     <row r="828">
       <c r="A828" t="inlineStr">
         <is>
-          <t>kk_4835738911</t>
+          <t>kk_4839354093</t>
         </is>
       </c>
       <c r="B828" t="inlineStr">
         <is>
-          <t>01034422073</t>
+          <t>01052243562</t>
         </is>
       </c>
       <c r="C828" t="inlineStr">
         <is>
-          <t>303885</t>
+          <t>304098</t>
         </is>
       </c>
       <c r="D828" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Organic Traffic</t>
         </is>
       </c>
       <c r="E828" t="inlineStr">
         <is>
-          <t>6968489536332</t>
+          <t>(organic)</t>
         </is>
       </c>
     </row>
     <row r="829">
       <c r="A829" t="inlineStr">
         <is>
-          <t>kk_4839354093</t>
+          <t>kk_4835738911</t>
         </is>
       </c>
       <c r="B829" t="inlineStr">
         <is>
-          <t>01052243562</t>
+          <t>01034422073</t>
         </is>
       </c>
       <c r="C829" t="inlineStr">
         <is>
-          <t>304098</t>
+          <t>303885</t>
         </is>
       </c>
       <c r="D829" t="inlineStr">
         <is>
-          <t>Organic Traffic</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E829" t="inlineStr">
         <is>
-          <t>(organic)</t>
+          <t>6968489536332</t>
         </is>
       </c>
     </row>
@@ -23273,17 +23273,17 @@
     <row r="847">
       <c r="A847" t="inlineStr">
         <is>
-          <t>kk_4847354450</t>
+          <t>kk_4847975154</t>
         </is>
       </c>
       <c r="B847" t="inlineStr">
         <is>
-          <t>01088042346</t>
+          <t>01062199172</t>
         </is>
       </c>
       <c r="C847" t="inlineStr">
         <is>
-          <t>304489</t>
+          <t>304512</t>
         </is>
       </c>
       <c r="D847" t="inlineStr">
@@ -23300,17 +23300,17 @@
     <row r="848">
       <c r="A848" t="inlineStr">
         <is>
-          <t>kk_4847975154</t>
+          <t>kk_4847354450</t>
         </is>
       </c>
       <c r="B848" t="inlineStr">
         <is>
-          <t>01062199172</t>
+          <t>01088042346</t>
         </is>
       </c>
       <c r="C848" t="inlineStr">
         <is>
-          <t>304512</t>
+          <t>304489</t>
         </is>
       </c>
       <c r="D848" t="inlineStr">
@@ -23813,17 +23813,17 @@
     <row r="867">
       <c r="A867" t="inlineStr">
         <is>
-          <t>holstein</t>
+          <t>kk_3595551743</t>
         </is>
       </c>
       <c r="B867" t="inlineStr">
         <is>
-          <t>01050502500</t>
+          <t>01025839326</t>
         </is>
       </c>
       <c r="C867" t="inlineStr">
         <is>
-          <t>14062</t>
+          <t>246836</t>
         </is>
       </c>
       <c r="D867" t="inlineStr">
@@ -23833,24 +23833,24 @@
       </c>
       <c r="E867" t="inlineStr">
         <is>
-          <t>EDM_TOP</t>
+          <t>LMS_ECOM_0410exclusive2</t>
         </is>
       </c>
     </row>
     <row r="868">
       <c r="A868" t="inlineStr">
         <is>
-          <t>kk_3595551743</t>
+          <t>holstein</t>
         </is>
       </c>
       <c r="B868" t="inlineStr">
         <is>
-          <t>01025839326</t>
+          <t>01050502500</t>
         </is>
       </c>
       <c r="C868" t="inlineStr">
         <is>
-          <t>246836</t>
+          <t>14062</t>
         </is>
       </c>
       <c r="D868" t="inlineStr">
@@ -23860,7 +23860,7 @@
       </c>
       <c r="E868" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0410exclusive2</t>
+          <t>EDM_TOP</t>
         </is>
       </c>
     </row>
@@ -24083,17 +24083,17 @@
     <row r="877">
       <c r="A877" t="inlineStr">
         <is>
-          <t>kk_2954504655</t>
+          <t>kk_4844665214</t>
         </is>
       </c>
       <c r="B877" t="inlineStr">
         <is>
-          <t>01024942984</t>
+          <t>01033424745</t>
         </is>
       </c>
       <c r="C877" t="inlineStr">
         <is>
-          <t>242733</t>
+          <t>304377</t>
         </is>
       </c>
       <c r="D877" t="inlineStr">
@@ -24110,17 +24110,17 @@
     <row r="878">
       <c r="A878" t="inlineStr">
         <is>
-          <t>kk_4844665214</t>
+          <t>kk_2954504655</t>
         </is>
       </c>
       <c r="B878" t="inlineStr">
         <is>
-          <t>01033424745</t>
+          <t>01024942984</t>
         </is>
       </c>
       <c r="C878" t="inlineStr">
         <is>
-          <t>304377</t>
+          <t>242733</t>
         </is>
       </c>
       <c r="D878" t="inlineStr">
@@ -24245,17 +24245,17 @@
     <row r="883">
       <c r="A883" t="inlineStr">
         <is>
-          <t>kk_4840093815</t>
+          <t>kk_4839544665</t>
         </is>
       </c>
       <c r="B883" t="inlineStr">
         <is>
-          <t>01095450820</t>
+          <t>01055350199</t>
         </is>
       </c>
       <c r="C883" t="inlineStr">
         <is>
-          <t>304126</t>
+          <t>304104</t>
         </is>
       </c>
       <c r="D883" t="inlineStr">
@@ -24265,24 +24265,24 @@
       </c>
       <c r="E883" t="inlineStr">
         <is>
-          <t>EFW</t>
+          <t>6968489536332</t>
         </is>
       </c>
     </row>
     <row r="884">
       <c r="A884" t="inlineStr">
         <is>
-          <t>kk_4839544665</t>
+          <t>kk_4840093815</t>
         </is>
       </c>
       <c r="B884" t="inlineStr">
         <is>
-          <t>01055350199</t>
+          <t>01095450820</t>
         </is>
       </c>
       <c r="C884" t="inlineStr">
         <is>
-          <t>304104</t>
+          <t>304126</t>
         </is>
       </c>
       <c r="D884" t="inlineStr">
@@ -24292,7 +24292,7 @@
       </c>
       <c r="E884" t="inlineStr">
         <is>
-          <t>6968489536332</t>
+          <t>EFW</t>
         </is>
       </c>
     </row>
@@ -24380,54 +24380,54 @@
     <row r="888">
       <c r="A888" t="inlineStr">
         <is>
-          <t>kk_4843439707</t>
+          <t>kk_2800477789</t>
         </is>
       </c>
       <c r="B888" t="inlineStr">
         <is>
-          <t>01022248653</t>
+          <t>01035177105</t>
         </is>
       </c>
       <c r="C888" t="inlineStr">
         <is>
-          <t>304310</t>
+          <t>211095</t>
         </is>
       </c>
       <c r="D888" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E888" t="inlineStr">
         <is>
-          <t>6968489536332</t>
+          <t>KAKAO_alimtalk</t>
         </is>
       </c>
     </row>
     <row r="889">
       <c r="A889" t="inlineStr">
         <is>
-          <t>kk_2800477789</t>
+          <t>kk_4843439707</t>
         </is>
       </c>
       <c r="B889" t="inlineStr">
         <is>
-          <t>01035177105</t>
+          <t>01022248653</t>
         </is>
       </c>
       <c r="C889" t="inlineStr">
         <is>
-          <t>211095</t>
+          <t>304310</t>
         </is>
       </c>
       <c r="D889" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E889" t="inlineStr">
         <is>
-          <t>KAKAO_alimtalk</t>
+          <t>6968489536332</t>
         </is>
       </c>
     </row>
@@ -24569,54 +24569,54 @@
     <row r="895">
       <c r="A895" t="inlineStr">
         <is>
-          <t>kk_4406693806</t>
+          <t>kk_3792750872</t>
         </is>
       </c>
       <c r="B895" t="inlineStr">
         <is>
-          <t>01088675050</t>
+          <t>01084382636</t>
         </is>
       </c>
       <c r="C895" t="inlineStr">
         <is>
-          <t>280999</t>
+          <t>256807</t>
         </is>
       </c>
       <c r="D895" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E895" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>Owned Channel</t>
         </is>
       </c>
     </row>
     <row r="896">
       <c r="A896" t="inlineStr">
         <is>
-          <t>kk_3792750872</t>
+          <t>kk_4406693806</t>
         </is>
       </c>
       <c r="B896" t="inlineStr">
         <is>
-          <t>01084382636</t>
+          <t>01088675050</t>
         </is>
       </c>
       <c r="C896" t="inlineStr">
         <is>
-          <t>256807</t>
+          <t>280999</t>
         </is>
       </c>
       <c r="D896" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="E896" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Direct</t>
         </is>
       </c>
     </row>
@@ -24704,125 +24704,125 @@
     <row r="900">
       <c r="A900" t="inlineStr">
         <is>
-          <t>kk_4844453283</t>
+          <t>kk_4843926419</t>
         </is>
       </c>
       <c r="B900" t="inlineStr">
         <is>
-          <t>01090262556</t>
+          <t>01034583174</t>
         </is>
       </c>
       <c r="C900" t="inlineStr">
         <is>
-          <t>304360</t>
+          <t>304338</t>
         </is>
       </c>
       <c r="D900" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Official SNS</t>
         </is>
       </c>
       <c r="E900" t="inlineStr">
         <is>
-          <t>6968489536332</t>
+          <t>EFW_04</t>
         </is>
       </c>
     </row>
     <row r="901">
       <c r="A901" t="inlineStr">
         <is>
-          <t>kk_4843847622</t>
+          <t>kk_4845121221</t>
         </is>
       </c>
       <c r="B901" t="inlineStr">
         <is>
-          <t>01046990393</t>
+          <t>01044632332</t>
         </is>
       </c>
       <c r="C901" t="inlineStr">
         <is>
-          <t>304336</t>
+          <t>304393</t>
         </is>
       </c>
       <c r="D901" t="inlineStr">
         <is>
-          <t>Organic Traffic</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E901" t="inlineStr">
         <is>
-          <t>(organic)</t>
+          <t>6968489536332</t>
         </is>
       </c>
     </row>
     <row r="902">
       <c r="A902" t="inlineStr">
         <is>
-          <t>kk_4843926419</t>
+          <t>kk_4845173313</t>
         </is>
       </c>
       <c r="B902" t="inlineStr">
         <is>
-          <t>01034583174</t>
+          <t>01024436341</t>
         </is>
       </c>
       <c r="C902" t="inlineStr">
         <is>
-          <t>304338</t>
+          <t>304397</t>
         </is>
       </c>
       <c r="D902" t="inlineStr">
         <is>
-          <t>Official SNS</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E902" t="inlineStr">
         <is>
-          <t>EFW_04</t>
+          <t>6968489536332</t>
         </is>
       </c>
     </row>
     <row r="903">
       <c r="A903" t="inlineStr">
         <is>
-          <t>kk_4845173313</t>
+          <t>kk_4843847622</t>
         </is>
       </c>
       <c r="B903" t="inlineStr">
         <is>
-          <t>01024436341</t>
+          <t>01046990393</t>
         </is>
       </c>
       <c r="C903" t="inlineStr">
         <is>
-          <t>304397</t>
+          <t>304336</t>
         </is>
       </c>
       <c r="D903" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Organic Traffic</t>
         </is>
       </c>
       <c r="E903" t="inlineStr">
         <is>
-          <t>6968489536332</t>
+          <t>(organic)</t>
         </is>
       </c>
     </row>
     <row r="904">
       <c r="A904" t="inlineStr">
         <is>
-          <t>kk_4845121221</t>
+          <t>kk_4844453283</t>
         </is>
       </c>
       <c r="B904" t="inlineStr">
         <is>
-          <t>01044632332</t>
+          <t>01090262556</t>
         </is>
       </c>
       <c r="C904" t="inlineStr">
         <is>
-          <t>304393</t>
+          <t>304360</t>
         </is>
       </c>
       <c r="D904" t="inlineStr">
@@ -24920,54 +24920,54 @@
     <row r="908">
       <c r="A908" t="inlineStr">
         <is>
-          <t>kk_4357899204</t>
+          <t>kk_4839542021</t>
         </is>
       </c>
       <c r="B908" t="inlineStr">
         <is>
-          <t>01082772838</t>
+          <t>01089909663</t>
         </is>
       </c>
       <c r="C908" t="inlineStr">
         <is>
-          <t>279564</t>
+          <t>304103</t>
         </is>
       </c>
       <c r="D908" t="inlineStr">
         <is>
-          <t>Official SNS</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E908" t="inlineStr">
         <is>
-          <t>(referral)</t>
+          <t>(organic)</t>
         </is>
       </c>
     </row>
     <row r="909">
       <c r="A909" t="inlineStr">
         <is>
-          <t>kk_4839542021</t>
+          <t>kk_4357899204</t>
         </is>
       </c>
       <c r="B909" t="inlineStr">
         <is>
-          <t>01089909663</t>
+          <t>01082772838</t>
         </is>
       </c>
       <c r="C909" t="inlineStr">
         <is>
-          <t>304103</t>
+          <t>279564</t>
         </is>
       </c>
       <c r="D909" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Official SNS</t>
         </is>
       </c>
       <c r="E909" t="inlineStr">
         <is>
-          <t>(organic)</t>
+          <t>(referral)</t>
         </is>
       </c>
     </row>
@@ -25190,125 +25190,125 @@
     <row r="918">
       <c r="A918" t="inlineStr">
         <is>
-          <t>kk_4846692829</t>
+          <t>kk_4846749411</t>
         </is>
       </c>
       <c r="B918" t="inlineStr">
         <is>
-          <t>01023649887</t>
+          <t>01031226749</t>
         </is>
       </c>
       <c r="C918" t="inlineStr">
         <is>
-          <t>304457</t>
+          <t>304462</t>
         </is>
       </c>
       <c r="D918" t="inlineStr">
         <is>
-          <t>Organic Traffic</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E918" t="inlineStr">
         <is>
-          <t>(referral)</t>
+          <t>6968489536332</t>
         </is>
       </c>
     </row>
     <row r="919">
       <c r="A919" t="inlineStr">
         <is>
-          <t>kk_4846749411</t>
+          <t>kk_4846692829</t>
         </is>
       </c>
       <c r="B919" t="inlineStr">
         <is>
-          <t>01031226749</t>
+          <t>01023649887</t>
         </is>
       </c>
       <c r="C919" t="inlineStr">
         <is>
-          <t>304462</t>
+          <t>304457</t>
         </is>
       </c>
       <c r="D919" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Organic Traffic</t>
         </is>
       </c>
       <c r="E919" t="inlineStr">
         <is>
-          <t>6968489536332</t>
+          <t>(referral)</t>
         </is>
       </c>
     </row>
     <row r="920">
       <c r="A920" t="inlineStr">
         <is>
-          <t>kk_4844609437</t>
+          <t>kk_4843809795</t>
         </is>
       </c>
       <c r="B920" t="inlineStr">
         <is>
-          <t>01046808931</t>
+          <t>01072864741</t>
         </is>
       </c>
       <c r="C920" t="inlineStr">
         <is>
-          <t>304372</t>
+          <t>304335</t>
         </is>
       </c>
       <c r="D920" t="inlineStr">
         <is>
-          <t>Official SNS</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E920" t="inlineStr">
         <is>
-          <t>(referral)</t>
+          <t>6968489536332</t>
         </is>
       </c>
     </row>
     <row r="921">
       <c r="A921" t="inlineStr">
         <is>
-          <t>kk_4844452226</t>
+          <t>kk_4844609437</t>
         </is>
       </c>
       <c r="B921" t="inlineStr">
         <is>
-          <t>01096801866</t>
+          <t>01046808931</t>
         </is>
       </c>
       <c r="C921" t="inlineStr">
         <is>
-          <t>304359</t>
+          <t>304372</t>
         </is>
       </c>
       <c r="D921" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Official SNS</t>
         </is>
       </c>
       <c r="E921" t="inlineStr">
         <is>
-          <t>6968489536332</t>
+          <t>(referral)</t>
         </is>
       </c>
     </row>
     <row r="922">
       <c r="A922" t="inlineStr">
         <is>
-          <t>kk_4843809795</t>
+          <t>kk_4844452226</t>
         </is>
       </c>
       <c r="B922" t="inlineStr">
         <is>
-          <t>01072864741</t>
+          <t>01096801866</t>
         </is>
       </c>
       <c r="C922" t="inlineStr">
         <is>
-          <t>304335</t>
+          <t>304359</t>
         </is>
       </c>
       <c r="D922" t="inlineStr">
@@ -25379,27 +25379,27 @@
     <row r="925">
       <c r="A925" t="inlineStr">
         <is>
-          <t>kk_3977730443</t>
+          <t>jsb0425</t>
         </is>
       </c>
       <c r="B925" t="inlineStr">
         <is>
-          <t>01064291828</t>
+          <t>01037883670</t>
         </is>
       </c>
       <c r="C925" t="inlineStr">
         <is>
-          <t>271278</t>
+          <t>104766</t>
         </is>
       </c>
       <c r="D925" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="E925" t="inlineStr">
         <is>
-          <t>naver_brandsearch_mobile</t>
+          <t>Direct</t>
         </is>
       </c>
     </row>
@@ -25433,54 +25433,54 @@
     <row r="927">
       <c r="A927" t="inlineStr">
         <is>
-          <t>kk_4840417532</t>
+          <t>kk_3977730443</t>
         </is>
       </c>
       <c r="B927" t="inlineStr">
         <is>
-          <t>01053409288</t>
+          <t>01064291828</t>
         </is>
       </c>
       <c r="C927" t="inlineStr">
         <is>
-          <t>304147</t>
+          <t>271278</t>
         </is>
       </c>
       <c r="D927" t="inlineStr">
         <is>
-          <t>Official SNS</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E927" t="inlineStr">
         <is>
-          <t>EFW_04</t>
+          <t>naver_brandsearch_mobile</t>
         </is>
       </c>
     </row>
     <row r="928">
       <c r="A928" t="inlineStr">
         <is>
-          <t>kk_4841278242</t>
+          <t>kk_4840417532</t>
         </is>
       </c>
       <c r="B928" t="inlineStr">
         <is>
-          <t>01046197965</t>
+          <t>01053409288</t>
         </is>
       </c>
       <c r="C928" t="inlineStr">
         <is>
-          <t>304190</t>
+          <t>304147</t>
         </is>
       </c>
       <c r="D928" t="inlineStr">
         <is>
-          <t>Organic Traffic</t>
+          <t>Official SNS</t>
         </is>
       </c>
       <c r="E928" t="inlineStr">
         <is>
-          <t>(referral)</t>
+          <t>EFW_04</t>
         </is>
       </c>
     </row>
@@ -25514,81 +25514,81 @@
     <row r="930">
       <c r="A930" t="inlineStr">
         <is>
-          <t>jsb0425</t>
+          <t>kk_4841278242</t>
         </is>
       </c>
       <c r="B930" t="inlineStr">
         <is>
-          <t>01037883670</t>
+          <t>01046197965</t>
         </is>
       </c>
       <c r="C930" t="inlineStr">
         <is>
-          <t>104766</t>
+          <t>304190</t>
         </is>
       </c>
       <c r="D930" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>Organic Traffic</t>
         </is>
       </c>
       <c r="E930" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>(referral)</t>
         </is>
       </c>
     </row>
     <row r="931">
       <c r="A931" t="inlineStr">
         <is>
-          <t>music214</t>
+          <t>kk_4837971410</t>
         </is>
       </c>
       <c r="B931" t="inlineStr">
         <is>
-          <t>01031023988</t>
+          <t>01045750650</t>
         </is>
       </c>
       <c r="C931" t="inlineStr">
         <is>
-          <t>303965</t>
+          <t>304028</t>
         </is>
       </c>
       <c r="D931" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Official SNS</t>
         </is>
       </c>
       <c r="E931" t="inlineStr">
         <is>
-          <t>6968489536332</t>
+          <t>EFW_04</t>
         </is>
       </c>
     </row>
     <row r="932">
       <c r="A932" t="inlineStr">
         <is>
-          <t>kk_4837971410</t>
+          <t>music214</t>
         </is>
       </c>
       <c r="B932" t="inlineStr">
         <is>
-          <t>01045750650</t>
+          <t>01031023988</t>
         </is>
       </c>
       <c r="C932" t="inlineStr">
         <is>
-          <t>304028</t>
+          <t>303965</t>
         </is>
       </c>
       <c r="D932" t="inlineStr">
         <is>
-          <t>Official SNS</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E932" t="inlineStr">
         <is>
-          <t>EFW_04</t>
+          <t>6968489536332</t>
         </is>
       </c>
     </row>
@@ -25676,17 +25676,17 @@
     <row r="936">
       <c r="A936" t="inlineStr">
         <is>
-          <t>kk_3894722641</t>
+          <t>kk_3765548639</t>
         </is>
       </c>
       <c r="B936" t="inlineStr">
         <is>
-          <t>01064889500</t>
+          <t>01024327187</t>
         </is>
       </c>
       <c r="C936" t="inlineStr">
         <is>
-          <t>267511</t>
+          <t>255087</t>
         </is>
       </c>
       <c r="D936" t="inlineStr">
@@ -25703,17 +25703,17 @@
     <row r="937">
       <c r="A937" t="inlineStr">
         <is>
-          <t>kk_3765548639</t>
+          <t>kk_3894722641</t>
         </is>
       </c>
       <c r="B937" t="inlineStr">
         <is>
-          <t>01024327187</t>
+          <t>01064889500</t>
         </is>
       </c>
       <c r="C937" t="inlineStr">
         <is>
-          <t>255087</t>
+          <t>267511</t>
         </is>
       </c>
       <c r="D937" t="inlineStr">
@@ -25730,17 +25730,17 @@
     <row r="938">
       <c r="A938" t="inlineStr">
         <is>
-          <t>willper</t>
+          <t>kk_4846761310</t>
         </is>
       </c>
       <c r="B938" t="inlineStr">
         <is>
-          <t>01085343440</t>
+          <t>01091189951</t>
         </is>
       </c>
       <c r="C938" t="inlineStr">
         <is>
-          <t>304408</t>
+          <t>304464</t>
         </is>
       </c>
       <c r="D938" t="inlineStr">
@@ -25750,24 +25750,24 @@
       </c>
       <c r="E938" t="inlineStr">
         <is>
-          <t>6968489536332</t>
+          <t>naver_brandsearch_mobile</t>
         </is>
       </c>
     </row>
     <row r="939">
       <c r="A939" t="inlineStr">
         <is>
-          <t>kk_4846761310</t>
+          <t>willper</t>
         </is>
       </c>
       <c r="B939" t="inlineStr">
         <is>
-          <t>01091189951</t>
+          <t>01085343440</t>
         </is>
       </c>
       <c r="C939" t="inlineStr">
         <is>
-          <t>304464</t>
+          <t>304408</t>
         </is>
       </c>
       <c r="D939" t="inlineStr">
@@ -25777,7 +25777,7 @@
       </c>
       <c r="E939" t="inlineStr">
         <is>
-          <t>naver_brandsearch_mobile</t>
+          <t>6968489536332</t>
         </is>
       </c>
     </row>
@@ -25892,152 +25892,152 @@
     <row r="944">
       <c r="A944" t="inlineStr">
         <is>
-          <t>nikemkr</t>
+          <t>kk_4703272205</t>
         </is>
       </c>
       <c r="B944" t="inlineStr">
         <is>
-          <t>01032361592</t>
+          <t>01062682325</t>
         </is>
       </c>
       <c r="C944" t="inlineStr">
         <is>
-          <t>145423</t>
+          <t>296093</t>
         </is>
       </c>
       <c r="D944" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E944" t="inlineStr">
         <is>
-          <t>naver_brandsearch_mobile</t>
+          <t>LMS_ECOM_0410exclusive2</t>
         </is>
       </c>
     </row>
     <row r="945">
       <c r="A945" t="inlineStr">
         <is>
-          <t>kk_4703272205</t>
+          <t>nikemkr</t>
         </is>
       </c>
       <c r="B945" t="inlineStr">
         <is>
-          <t>01062682325</t>
+          <t>01032361592</t>
         </is>
       </c>
       <c r="C945" t="inlineStr">
         <is>
-          <t>296093</t>
+          <t>145423</t>
         </is>
       </c>
       <c r="D945" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E945" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0410exclusive2</t>
+          <t>naver_brandsearch_mobile</t>
         </is>
       </c>
     </row>
     <row r="946">
       <c r="A946" t="inlineStr">
         <is>
-          <t>kk_3241081989</t>
+          <t>lolia875</t>
         </is>
       </c>
       <c r="B946" t="inlineStr">
         <is>
-          <t>01072287165</t>
+          <t>01067138715</t>
         </is>
       </c>
       <c r="C946" t="inlineStr">
         <is>
-          <t>234608</t>
+          <t>161251</t>
         </is>
       </c>
       <c r="D946" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E946" t="inlineStr">
         <is>
-          <t>KAKAO_alimtalk</t>
+          <t>6968489536332</t>
         </is>
       </c>
     </row>
     <row r="947">
       <c r="A947" t="inlineStr">
         <is>
-          <t>sbhbi</t>
+          <t>kk_3241081989</t>
         </is>
       </c>
       <c r="B947" t="inlineStr">
         <is>
-          <t>01047153767</t>
+          <t>01072287165</t>
         </is>
       </c>
       <c r="C947" t="inlineStr">
         <is>
-          <t>174291</t>
+          <t>234608</t>
         </is>
       </c>
       <c r="D947" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E947" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>KAKAO_alimtalk</t>
         </is>
       </c>
     </row>
     <row r="948">
       <c r="A948" t="inlineStr">
         <is>
-          <t>lolia875</t>
+          <t>sbhbi</t>
         </is>
       </c>
       <c r="B948" t="inlineStr">
         <is>
-          <t>01067138715</t>
+          <t>01047153767</t>
         </is>
       </c>
       <c r="C948" t="inlineStr">
         <is>
-          <t>161251</t>
+          <t>174291</t>
         </is>
       </c>
       <c r="D948" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="E948" t="inlineStr">
         <is>
-          <t>6968489536332</t>
+          <t>Direct</t>
         </is>
       </c>
     </row>
     <row r="949">
       <c r="A949" t="inlineStr">
         <is>
-          <t>kk_4837595875</t>
+          <t>makaveli</t>
         </is>
       </c>
       <c r="B949" t="inlineStr">
         <is>
-          <t>01057852463</t>
+          <t>01086237086</t>
         </is>
       </c>
       <c r="C949" t="inlineStr">
         <is>
-          <t>304000</t>
+          <t>66164</t>
         </is>
       </c>
       <c r="D949" t="inlineStr">
@@ -26047,115 +26047,115 @@
       </c>
       <c r="E949" t="inlineStr">
         <is>
-          <t>6968489536332</t>
+          <t>naver_brandsearch_mobile</t>
         </is>
       </c>
     </row>
     <row r="950">
       <c r="A950" t="inlineStr">
         <is>
-          <t>kk_4837152929</t>
+          <t>kk_3430866338</t>
         </is>
       </c>
       <c r="B950" t="inlineStr">
         <is>
-          <t>01047050730</t>
+          <t>01026364692</t>
         </is>
       </c>
       <c r="C950" t="inlineStr">
         <is>
-          <t>303966</t>
+          <t>242249</t>
         </is>
       </c>
       <c r="D950" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E950" t="inlineStr">
         <is>
-          <t>6968489536332</t>
+          <t>Email_mkt</t>
         </is>
       </c>
     </row>
     <row r="951">
       <c r="A951" t="inlineStr">
         <is>
-          <t>sjl4534</t>
+          <t>kk_4837152929</t>
         </is>
       </c>
       <c r="B951" t="inlineStr">
         <is>
-          <t>01028023660</t>
+          <t>01047050730</t>
         </is>
       </c>
       <c r="C951" t="inlineStr">
         <is>
-          <t>174607</t>
+          <t>303966</t>
         </is>
       </c>
       <c r="D951" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E951" t="inlineStr">
         <is>
-          <t>KAKAO_CH_MESSAGE_0409_EXCLUSIVE</t>
+          <t>6968489536332</t>
         </is>
       </c>
     </row>
     <row r="952">
       <c r="A952" t="inlineStr">
         <is>
-          <t>makaveli</t>
+          <t>sjl4534</t>
         </is>
       </c>
       <c r="B952" t="inlineStr">
         <is>
-          <t>01086237086</t>
+          <t>01028023660</t>
         </is>
       </c>
       <c r="C952" t="inlineStr">
         <is>
-          <t>66164</t>
+          <t>174607</t>
         </is>
       </c>
       <c r="D952" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E952" t="inlineStr">
         <is>
-          <t>naver_brandsearch_mobile</t>
+          <t>KAKAO_CH_MESSAGE_0409_EXCLUSIVE</t>
         </is>
       </c>
     </row>
     <row r="953">
       <c r="A953" t="inlineStr">
         <is>
-          <t>kk_3430866338</t>
+          <t>kk_4837595875</t>
         </is>
       </c>
       <c r="B953" t="inlineStr">
         <is>
-          <t>01026364692</t>
+          <t>01057852463</t>
         </is>
       </c>
       <c r="C953" t="inlineStr">
         <is>
-          <t>242249</t>
+          <t>304000</t>
         </is>
       </c>
       <c r="D953" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E953" t="inlineStr">
         <is>
-          <t>Email_mkt</t>
+          <t>6968489536332</t>
         </is>
       </c>
     </row>
@@ -26189,17 +26189,17 @@
     <row r="955">
       <c r="A955" t="inlineStr">
         <is>
-          <t>kk_4612713787</t>
+          <t>kk_4703414773</t>
         </is>
       </c>
       <c r="B955" t="inlineStr">
         <is>
-          <t>01095027601</t>
+          <t>01093547510</t>
         </is>
       </c>
       <c r="C955" t="inlineStr">
         <is>
-          <t>290278</t>
+          <t>296108</t>
         </is>
       </c>
       <c r="D955" t="inlineStr">
@@ -26209,24 +26209,24 @@
       </c>
       <c r="E955" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0214_newyear</t>
+          <t>KAKAO_CH_MENU_0212_GOODBYEWINTER</t>
         </is>
       </c>
     </row>
     <row r="956">
       <c r="A956" t="inlineStr">
         <is>
-          <t>kk_4703414773</t>
+          <t>kk_4612713787</t>
         </is>
       </c>
       <c r="B956" t="inlineStr">
         <is>
-          <t>01093547510</t>
+          <t>01095027601</t>
         </is>
       </c>
       <c r="C956" t="inlineStr">
         <is>
-          <t>296108</t>
+          <t>290278</t>
         </is>
       </c>
       <c r="D956" t="inlineStr">
@@ -26236,51 +26236,51 @@
       </c>
       <c r="E956" t="inlineStr">
         <is>
-          <t>KAKAO_CH_MENU_0212_GOODBYEWINTER</t>
+          <t>LMS_ECOM_0214_newyear</t>
         </is>
       </c>
     </row>
     <row r="957">
       <c r="A957" t="inlineStr">
         <is>
-          <t>chpuss74</t>
+          <t>kk_2788668233</t>
         </is>
       </c>
       <c r="B957" t="inlineStr">
         <is>
-          <t>01035361091</t>
+          <t>01041696139</t>
         </is>
       </c>
       <c r="C957" t="inlineStr">
         <is>
-          <t>154462</t>
+          <t>210002</t>
         </is>
       </c>
       <c r="D957" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E957" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>6968489536332</t>
         </is>
       </c>
     </row>
     <row r="958">
       <c r="A958" t="inlineStr">
         <is>
-          <t>kk_2788668233</t>
+          <t>kk_4846729102</t>
         </is>
       </c>
       <c r="B958" t="inlineStr">
         <is>
-          <t>01041696139</t>
+          <t>01084771303</t>
         </is>
       </c>
       <c r="C958" t="inlineStr">
         <is>
-          <t>210002</t>
+          <t>304461</t>
         </is>
       </c>
       <c r="D958" t="inlineStr">
@@ -26297,17 +26297,17 @@
     <row r="959">
       <c r="A959" t="inlineStr">
         <is>
-          <t>ch5115</t>
+          <t>kk_3183517395</t>
         </is>
       </c>
       <c r="B959" t="inlineStr">
         <is>
-          <t>01084479339</t>
+          <t>01082019936</t>
         </is>
       </c>
       <c r="C959" t="inlineStr">
         <is>
-          <t>240557</t>
+          <t>228501</t>
         </is>
       </c>
       <c r="D959" t="inlineStr">
@@ -26324,98 +26324,98 @@
     <row r="960">
       <c r="A960" t="inlineStr">
         <is>
-          <t>kk_4845661756</t>
+          <t>imgain0422</t>
         </is>
       </c>
       <c r="B960" t="inlineStr">
         <is>
-          <t>01095936572</t>
+          <t>01029135546</t>
         </is>
       </c>
       <c r="C960" t="inlineStr">
         <is>
-          <t>304422</t>
+          <t>181451</t>
         </is>
       </c>
       <c r="D960" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="E960" t="inlineStr">
         <is>
-          <t>6968489536332</t>
+          <t>Direct</t>
         </is>
       </c>
     </row>
     <row r="961">
       <c r="A961" t="inlineStr">
         <is>
-          <t>kk_4846729102</t>
+          <t>ch5115</t>
         </is>
       </c>
       <c r="B961" t="inlineStr">
         <is>
-          <t>01084771303</t>
+          <t>01084479339</t>
         </is>
       </c>
       <c r="C961" t="inlineStr">
         <is>
-          <t>304461</t>
+          <t>240557</t>
         </is>
       </c>
       <c r="D961" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="E961" t="inlineStr">
         <is>
-          <t>6968489536332</t>
+          <t>Direct</t>
         </is>
       </c>
     </row>
     <row r="962">
       <c r="A962" t="inlineStr">
         <is>
-          <t>kk_3183517395</t>
+          <t>kk_4845661756</t>
         </is>
       </c>
       <c r="B962" t="inlineStr">
         <is>
-          <t>01082019936</t>
+          <t>01095936572</t>
         </is>
       </c>
       <c r="C962" t="inlineStr">
         <is>
-          <t>228501</t>
+          <t>304422</t>
         </is>
       </c>
       <c r="D962" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E962" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>6968489536332</t>
         </is>
       </c>
     </row>
     <row r="963">
       <c r="A963" t="inlineStr">
         <is>
-          <t>imgain0422</t>
+          <t>chpuss74</t>
         </is>
       </c>
       <c r="B963" t="inlineStr">
         <is>
-          <t>01029135546</t>
+          <t>01035361091</t>
         </is>
       </c>
       <c r="C963" t="inlineStr">
         <is>
-          <t>181451</t>
+          <t>154462</t>
         </is>
       </c>
       <c r="D963" t="inlineStr">
@@ -26432,27 +26432,27 @@
     <row r="964">
       <c r="A964" t="inlineStr">
         <is>
-          <t>kk_3650586439</t>
+          <t>kk_4844076820</t>
         </is>
       </c>
       <c r="B964" t="inlineStr">
         <is>
-          <t>01029107056</t>
+          <t>01091346366</t>
         </is>
       </c>
       <c r="C964" t="inlineStr">
         <is>
-          <t>249153</t>
+          <t>304343</t>
         </is>
       </c>
       <c r="D964" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E964" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>6968489536332</t>
         </is>
       </c>
     </row>
@@ -26486,162 +26486,162 @@
     <row r="966">
       <c r="A966" t="inlineStr">
         <is>
-          <t>kk_4844076820</t>
+          <t>goawind</t>
         </is>
       </c>
       <c r="B966" t="inlineStr">
         <is>
-          <t>01091346366</t>
+          <t>01032738938</t>
         </is>
       </c>
       <c r="C966" t="inlineStr">
         <is>
-          <t>304343</t>
+          <t>232021</t>
         </is>
       </c>
       <c r="D966" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="E966" t="inlineStr">
         <is>
-          <t>6968489536332</t>
+          <t>Direct</t>
         </is>
       </c>
     </row>
     <row r="967">
       <c r="A967" t="inlineStr">
         <is>
-          <t>kjhk5404</t>
+          <t>kk_2775500473</t>
         </is>
       </c>
       <c r="B967" t="inlineStr">
         <is>
-          <t>01027390700</t>
+          <t>01045659020</t>
         </is>
       </c>
       <c r="C967" t="inlineStr">
         <is>
-          <t>280120</t>
+          <t>209371</t>
         </is>
       </c>
       <c r="D967" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Organic Traffic</t>
         </is>
       </c>
       <c r="E967" t="inlineStr">
         <is>
-          <t>KAKAO_alimtalk</t>
+          <t>(referral)</t>
         </is>
       </c>
     </row>
     <row r="968">
       <c r="A968" t="inlineStr">
         <is>
-          <t>kk_2775500473</t>
+          <t>kk_3650586439</t>
         </is>
       </c>
       <c r="B968" t="inlineStr">
         <is>
-          <t>01045659020</t>
+          <t>01029107056</t>
         </is>
       </c>
       <c r="C968" t="inlineStr">
         <is>
-          <t>209371</t>
+          <t>249153</t>
         </is>
       </c>
       <c r="D968" t="inlineStr">
         <is>
-          <t>Organic Traffic</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="E968" t="inlineStr">
         <is>
-          <t>(referral)</t>
+          <t>Direct</t>
         </is>
       </c>
     </row>
     <row r="969">
       <c r="A969" t="inlineStr">
         <is>
-          <t>goawind</t>
+          <t>kjhk5404</t>
         </is>
       </c>
       <c r="B969" t="inlineStr">
         <is>
-          <t>01032738938</t>
+          <t>01027390700</t>
         </is>
       </c>
       <c r="C969" t="inlineStr">
         <is>
-          <t>232021</t>
+          <t>280120</t>
         </is>
       </c>
       <c r="D969" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E969" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>KAKAO_alimtalk</t>
         </is>
       </c>
     </row>
     <row r="970">
       <c r="A970" t="inlineStr">
         <is>
-          <t>kk_4434329905</t>
+          <t>kk_4522711623</t>
         </is>
       </c>
       <c r="B970" t="inlineStr">
         <is>
-          <t>01071724035</t>
+          <t>01089870313</t>
         </is>
       </c>
       <c r="C970" t="inlineStr">
         <is>
-          <t>281922</t>
+          <t>286306</t>
         </is>
       </c>
       <c r="D970" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E970" t="inlineStr">
         <is>
-          <t>Email_mkt</t>
+          <t>6968489536332</t>
         </is>
       </c>
     </row>
     <row r="971">
       <c r="A971" t="inlineStr">
         <is>
-          <t>kk_4522711623</t>
+          <t>kk_4434329905</t>
         </is>
       </c>
       <c r="B971" t="inlineStr">
         <is>
-          <t>01089870313</t>
+          <t>01071724035</t>
         </is>
       </c>
       <c r="C971" t="inlineStr">
         <is>
-          <t>286306</t>
+          <t>281922</t>
         </is>
       </c>
       <c r="D971" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E971" t="inlineStr">
         <is>
-          <t>6968489536332</t>
+          <t>Email_mkt</t>
         </is>
       </c>
     </row>
@@ -26675,71 +26675,71 @@
     <row r="973">
       <c r="A973" t="inlineStr">
         <is>
-          <t>w0309</t>
+          <t>kk_4840817001</t>
         </is>
       </c>
       <c r="B973" t="inlineStr">
         <is>
-          <t>01053481702</t>
+          <t>01085963383</t>
         </is>
       </c>
       <c r="C973" t="inlineStr">
         <is>
-          <t>126315</t>
+          <t>304168</t>
         </is>
       </c>
       <c r="D973" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E973" t="inlineStr">
         <is>
-          <t>Email_mkt</t>
+          <t>6968489536332</t>
         </is>
       </c>
     </row>
     <row r="974">
       <c r="A974" t="inlineStr">
         <is>
-          <t>kk_4840817001</t>
+          <t>w0309</t>
         </is>
       </c>
       <c r="B974" t="inlineStr">
         <is>
-          <t>01085963383</t>
+          <t>01053481702</t>
         </is>
       </c>
       <c r="C974" t="inlineStr">
         <is>
-          <t>304168</t>
+          <t>126315</t>
         </is>
       </c>
       <c r="D974" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E974" t="inlineStr">
         <is>
-          <t>6968489536332</t>
+          <t>Email_mkt</t>
         </is>
       </c>
     </row>
     <row r="975">
       <c r="A975" t="inlineStr">
         <is>
-          <t>kk_4839241951</t>
+          <t>kk_4840045474</t>
         </is>
       </c>
       <c r="B975" t="inlineStr">
         <is>
-          <t>01079146776</t>
+          <t>01096310429</t>
         </is>
       </c>
       <c r="C975" t="inlineStr">
         <is>
-          <t>304090</t>
+          <t>304122</t>
         </is>
       </c>
       <c r="D975" t="inlineStr">
@@ -26810,17 +26810,17 @@
     <row r="978">
       <c r="A978" t="inlineStr">
         <is>
-          <t>eyounjoo</t>
+          <t>ssama</t>
         </is>
       </c>
       <c r="B978" t="inlineStr">
         <is>
-          <t>01036167949</t>
+          <t>01056271982</t>
         </is>
       </c>
       <c r="C978" t="inlineStr">
         <is>
-          <t>283223</t>
+          <t>47874</t>
         </is>
       </c>
       <c r="D978" t="inlineStr">
@@ -26837,108 +26837,108 @@
     <row r="979">
       <c r="A979" t="inlineStr">
         <is>
-          <t>kk_4840045474</t>
+          <t>xoxoie2</t>
         </is>
       </c>
       <c r="B979" t="inlineStr">
         <is>
-          <t>01096310429</t>
+          <t>01043560834</t>
         </is>
       </c>
       <c r="C979" t="inlineStr">
         <is>
-          <t>304122</t>
+          <t>304072</t>
         </is>
       </c>
       <c r="D979" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Official SNS</t>
         </is>
       </c>
       <c r="E979" t="inlineStr">
         <is>
-          <t>6968489536332</t>
+          <t>EFW_04</t>
         </is>
       </c>
     </row>
     <row r="980">
       <c r="A980" t="inlineStr">
         <is>
-          <t>ssama</t>
+          <t>z090909x</t>
         </is>
       </c>
       <c r="B980" t="inlineStr">
         <is>
-          <t>01056271982</t>
+          <t>01092058111</t>
         </is>
       </c>
       <c r="C980" t="inlineStr">
         <is>
-          <t>47874</t>
+          <t>113003</t>
         </is>
       </c>
       <c r="D980" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E980" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0410exclusive2</t>
+          <t>6968489536332</t>
         </is>
       </c>
     </row>
     <row r="981">
       <c r="A981" t="inlineStr">
         <is>
-          <t>xoxoie2</t>
+          <t>kk_4839241951</t>
         </is>
       </c>
       <c r="B981" t="inlineStr">
         <is>
-          <t>01043560834</t>
+          <t>01079146776</t>
         </is>
       </c>
       <c r="C981" t="inlineStr">
         <is>
-          <t>304072</t>
+          <t>304090</t>
         </is>
       </c>
       <c r="D981" t="inlineStr">
         <is>
-          <t>Official SNS</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E981" t="inlineStr">
         <is>
-          <t>EFW_04</t>
+          <t>6968489536332</t>
         </is>
       </c>
     </row>
     <row r="982">
       <c r="A982" t="inlineStr">
         <is>
-          <t>z090909x</t>
+          <t>eyounjoo</t>
         </is>
       </c>
       <c r="B982" t="inlineStr">
         <is>
-          <t>01092058111</t>
+          <t>01036167949</t>
         </is>
       </c>
       <c r="C982" t="inlineStr">
         <is>
-          <t>113003</t>
+          <t>283223</t>
         </is>
       </c>
       <c r="D982" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E982" t="inlineStr">
         <is>
-          <t>6968489536332</t>
+          <t>LMS_ECOM_0410exclusive2</t>
         </is>
       </c>
     </row>
@@ -26972,17 +26972,17 @@
     <row r="984">
       <c r="A984" t="inlineStr">
         <is>
-          <t>kk_4837597613</t>
+          <t>scaler</t>
         </is>
       </c>
       <c r="B984" t="inlineStr">
         <is>
-          <t>01089218630</t>
+          <t>01037090080</t>
         </is>
       </c>
       <c r="C984" t="inlineStr">
         <is>
-          <t>304001</t>
+          <t>178752</t>
         </is>
       </c>
       <c r="D984" t="inlineStr">
@@ -27026,17 +27026,17 @@
     <row r="986">
       <c r="A986" t="inlineStr">
         <is>
-          <t>sjk6231</t>
+          <t>enel778</t>
         </is>
       </c>
       <c r="B986" t="inlineStr">
         <is>
-          <t>01031985034</t>
+          <t>01086066364</t>
         </is>
       </c>
       <c r="C986" t="inlineStr">
         <is>
-          <t>281342</t>
+          <t>207732</t>
         </is>
       </c>
       <c r="D986" t="inlineStr">
@@ -27053,17 +27053,17 @@
     <row r="987">
       <c r="A987" t="inlineStr">
         <is>
-          <t>enel778</t>
+          <t>kk_4837597613</t>
         </is>
       </c>
       <c r="B987" t="inlineStr">
         <is>
-          <t>01086066364</t>
+          <t>01089218630</t>
         </is>
       </c>
       <c r="C987" t="inlineStr">
         <is>
-          <t>207732</t>
+          <t>304001</t>
         </is>
       </c>
       <c r="D987" t="inlineStr">
@@ -27073,24 +27073,24 @@
       </c>
       <c r="E987" t="inlineStr">
         <is>
-          <t>Email_mkt</t>
+          <t>KAKAO_CH_MESSAGE_0409_EXCLUSIVE</t>
         </is>
       </c>
     </row>
     <row r="988">
       <c r="A988" t="inlineStr">
         <is>
-          <t>scaler</t>
+          <t>sjk6231</t>
         </is>
       </c>
       <c r="B988" t="inlineStr">
         <is>
-          <t>01037090080</t>
+          <t>01031985034</t>
         </is>
       </c>
       <c r="C988" t="inlineStr">
         <is>
-          <t>178752</t>
+          <t>281342</t>
         </is>
       </c>
       <c r="D988" t="inlineStr">
@@ -27100,7 +27100,7 @@
       </c>
       <c r="E988" t="inlineStr">
         <is>
-          <t>KAKAO_CH_MESSAGE_0409_EXCLUSIVE</t>
+          <t>Email_mkt</t>
         </is>
       </c>
     </row>
@@ -27134,54 +27134,54 @@
     <row r="990">
       <c r="A990" t="inlineStr">
         <is>
-          <t>kk_4218204827</t>
+          <t>mse001</t>
         </is>
       </c>
       <c r="B990" t="inlineStr">
         <is>
-          <t>01023704903</t>
+          <t>01085185510</t>
         </is>
       </c>
       <c r="C990" t="inlineStr">
         <is>
-          <t>272698</t>
+          <t>227227</t>
         </is>
       </c>
       <c r="D990" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E990" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>KAKAO_alimtalk</t>
         </is>
       </c>
     </row>
     <row r="991">
       <c r="A991" t="inlineStr">
         <is>
-          <t>mse001</t>
+          <t>kk_4218204827</t>
         </is>
       </c>
       <c r="B991" t="inlineStr">
         <is>
-          <t>01085185510</t>
+          <t>01023704903</t>
         </is>
       </c>
       <c r="C991" t="inlineStr">
         <is>
-          <t>227227</t>
+          <t>272698</t>
         </is>
       </c>
       <c r="D991" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="E991" t="inlineStr">
         <is>
-          <t>KAKAO_alimtalk</t>
+          <t>Direct</t>
         </is>
       </c>
     </row>
@@ -27269,108 +27269,108 @@
     <row r="995">
       <c r="A995" t="inlineStr">
         <is>
-          <t>kk_4844817541</t>
+          <t>kk_3169777000</t>
         </is>
       </c>
       <c r="B995" t="inlineStr">
         <is>
-          <t>01046631832</t>
+          <t>01089348462</t>
         </is>
       </c>
       <c r="C995" t="inlineStr">
         <is>
-          <t>304380</t>
+          <t>224876</t>
         </is>
       </c>
       <c r="D995" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="E995" t="inlineStr">
         <is>
-          <t>[PF]전환_회원가입(유사)</t>
+          <t>Direct</t>
         </is>
       </c>
     </row>
     <row r="996">
       <c r="A996" t="inlineStr">
         <is>
-          <t>kk_3169777000</t>
+          <t>kk_4375003446</t>
         </is>
       </c>
       <c r="B996" t="inlineStr">
         <is>
-          <t>01089348462</t>
+          <t>01087457282</t>
         </is>
       </c>
       <c r="C996" t="inlineStr">
         <is>
-          <t>224876</t>
+          <t>280131</t>
         </is>
       </c>
       <c r="D996" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E996" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>LMS_ECOM_0410exclusive2</t>
         </is>
       </c>
     </row>
     <row r="997">
       <c r="A997" t="inlineStr">
         <is>
-          <t>kk_4375003446</t>
+          <t>kk_4844817541</t>
         </is>
       </c>
       <c r="B997" t="inlineStr">
         <is>
-          <t>01087457282</t>
+          <t>01046631832</t>
         </is>
       </c>
       <c r="C997" t="inlineStr">
         <is>
-          <t>280131</t>
+          <t>304380</t>
         </is>
       </c>
       <c r="D997" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E997" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0410exclusive2</t>
+          <t>[PF]전환_회원가입(유사)</t>
         </is>
       </c>
     </row>
     <row r="998">
       <c r="A998" t="inlineStr">
         <is>
-          <t>kk_4472536591</t>
+          <t>dongheon20</t>
         </is>
       </c>
       <c r="B998" t="inlineStr">
         <is>
-          <t>01037057526</t>
+          <t>01052298928</t>
         </is>
       </c>
       <c r="C998" t="inlineStr">
         <is>
-          <t>283897</t>
+          <t>155362</t>
         </is>
       </c>
       <c r="D998" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E998" t="inlineStr">
         <is>
-          <t>KAKAO_alimtalk</t>
+          <t>6968489536332</t>
         </is>
       </c>
     </row>
@@ -27512,17 +27512,17 @@
     <row r="1004">
       <c r="A1004" t="inlineStr">
         <is>
-          <t>kk_3688034999</t>
+          <t>kk_4472536591</t>
         </is>
       </c>
       <c r="B1004" t="inlineStr">
         <is>
-          <t>01025408262</t>
+          <t>01037057526</t>
         </is>
       </c>
       <c r="C1004" t="inlineStr">
         <is>
-          <t>250755</t>
+          <t>283897</t>
         </is>
       </c>
       <c r="D1004" t="inlineStr">
@@ -27539,27 +27539,27 @@
     <row r="1005">
       <c r="A1005" t="inlineStr">
         <is>
-          <t>dongheon20</t>
+          <t>kk_3688034999</t>
         </is>
       </c>
       <c r="B1005" t="inlineStr">
         <is>
-          <t>01052298928</t>
+          <t>01025408262</t>
         </is>
       </c>
       <c r="C1005" t="inlineStr">
         <is>
-          <t>155362</t>
+          <t>250755</t>
         </is>
       </c>
       <c r="D1005" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E1005" t="inlineStr">
         <is>
-          <t>6968489536332</t>
+          <t>KAKAO_alimtalk</t>
         </is>
       </c>
     </row>
@@ -27620,17 +27620,17 @@
     <row r="1008">
       <c r="A1008" t="inlineStr">
         <is>
-          <t>jobguidance</t>
+          <t>kk_3181917333</t>
         </is>
       </c>
       <c r="B1008" t="inlineStr">
         <is>
-          <t>01026756920</t>
+          <t>01072258509</t>
         </is>
       </c>
       <c r="C1008" t="inlineStr">
         <is>
-          <t>134664</t>
+          <t>227380</t>
         </is>
       </c>
       <c r="D1008" t="inlineStr">
@@ -27647,54 +27647,54 @@
     <row r="1009">
       <c r="A1009" t="inlineStr">
         <is>
-          <t>kk_3837527580</t>
+          <t>jobguidance</t>
         </is>
       </c>
       <c r="B1009" t="inlineStr">
         <is>
-          <t>01084311738</t>
+          <t>01026756920</t>
         </is>
       </c>
       <c r="C1009" t="inlineStr">
         <is>
-          <t>264113</t>
+          <t>134664</t>
         </is>
       </c>
       <c r="D1009" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="E1009" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0410exclusive2</t>
+          <t>Direct</t>
         </is>
       </c>
     </row>
     <row r="1010">
       <c r="A1010" t="inlineStr">
         <is>
-          <t>kk_3181917333</t>
+          <t>kk_3837527580</t>
         </is>
       </c>
       <c r="B1010" t="inlineStr">
         <is>
-          <t>01072258509</t>
+          <t>01084311738</t>
         </is>
       </c>
       <c r="C1010" t="inlineStr">
         <is>
-          <t>227380</t>
+          <t>264113</t>
         </is>
       </c>
       <c r="D1010" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E1010" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>LMS_ECOM_0410exclusive2</t>
         </is>
       </c>
     </row>
@@ -27728,17 +27728,17 @@
     <row r="1012">
       <c r="A1012" t="inlineStr">
         <is>
-          <t>seul6169</t>
+          <t>kk_4338209948</t>
         </is>
       </c>
       <c r="B1012" t="inlineStr">
         <is>
-          <t>01066116699</t>
+          <t>01088132379</t>
         </is>
       </c>
       <c r="C1012" t="inlineStr">
         <is>
-          <t>234239</t>
+          <t>278781</t>
         </is>
       </c>
       <c r="D1012" t="inlineStr">
@@ -27755,27 +27755,27 @@
     <row r="1013">
       <c r="A1013" t="inlineStr">
         <is>
-          <t>kk_3013902343</t>
+          <t>kk_3185867832</t>
         </is>
       </c>
       <c r="B1013" t="inlineStr">
         <is>
-          <t>01051802326</t>
+          <t>01022086508</t>
         </is>
       </c>
       <c r="C1013" t="inlineStr">
         <is>
-          <t>219219</t>
+          <t>229863</t>
         </is>
       </c>
       <c r="D1013" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E1013" t="inlineStr">
         <is>
-          <t>6968489536332</t>
+          <t>LMS_ECOM_0410exclusive2</t>
         </is>
       </c>
     </row>
@@ -27809,17 +27809,17 @@
     <row r="1015">
       <c r="A1015" t="inlineStr">
         <is>
-          <t>kk_4467707148</t>
+          <t>aya6969</t>
         </is>
       </c>
       <c r="B1015" t="inlineStr">
         <is>
-          <t>01030843332</t>
+          <t>01076590009</t>
         </is>
       </c>
       <c r="C1015" t="inlineStr">
         <is>
-          <t>283560</t>
+          <t>162562</t>
         </is>
       </c>
       <c r="D1015" t="inlineStr">
@@ -27836,17 +27836,17 @@
     <row r="1016">
       <c r="A1016" t="inlineStr">
         <is>
-          <t>kk_4523594127</t>
+          <t>kk_4517851709</t>
         </is>
       </c>
       <c r="B1016" t="inlineStr">
         <is>
-          <t>01085735215</t>
+          <t>01066445714</t>
         </is>
       </c>
       <c r="C1016" t="inlineStr">
         <is>
-          <t>286358</t>
+          <t>286074</t>
         </is>
       </c>
       <c r="D1016" t="inlineStr">
@@ -27863,44 +27863,44 @@
     <row r="1017">
       <c r="A1017" t="inlineStr">
         <is>
-          <t>kk_3933534683</t>
+          <t>kk_2940110361</t>
         </is>
       </c>
       <c r="B1017" t="inlineStr">
         <is>
-          <t>01030153796</t>
+          <t>01035353200</t>
         </is>
       </c>
       <c r="C1017" t="inlineStr">
         <is>
-          <t>269069</t>
+          <t>216362</t>
         </is>
       </c>
       <c r="D1017" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E1017" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>LMS_ECOM_0410exclusive2</t>
         </is>
       </c>
     </row>
     <row r="1018">
       <c r="A1018" t="inlineStr">
         <is>
-          <t>kk_4517851709</t>
+          <t>kk_4467707148</t>
         </is>
       </c>
       <c r="B1018" t="inlineStr">
         <is>
-          <t>01066445714</t>
+          <t>01030843332</t>
         </is>
       </c>
       <c r="C1018" t="inlineStr">
         <is>
-          <t>286074</t>
+          <t>283560</t>
         </is>
       </c>
       <c r="D1018" t="inlineStr">
@@ -27917,71 +27917,71 @@
     <row r="1019">
       <c r="A1019" t="inlineStr">
         <is>
-          <t>mansoogi</t>
+          <t>kk_4840061178</t>
         </is>
       </c>
       <c r="B1019" t="inlineStr">
         <is>
-          <t>01093240897</t>
+          <t>01082357895</t>
         </is>
       </c>
       <c r="C1019" t="inlineStr">
         <is>
-          <t>25243</t>
+          <t>304124</t>
         </is>
       </c>
       <c r="D1019" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Awareness</t>
         </is>
       </c>
       <c r="E1019" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0410exclusive2</t>
+          <t>benz_running_program_2026_coupon</t>
         </is>
       </c>
     </row>
     <row r="1020">
       <c r="A1020" t="inlineStr">
         <is>
-          <t>kk_4338209948</t>
+          <t>kk_3933534683</t>
         </is>
       </c>
       <c r="B1020" t="inlineStr">
         <is>
-          <t>01088132379</t>
+          <t>01030153796</t>
         </is>
       </c>
       <c r="C1020" t="inlineStr">
         <is>
-          <t>278781</t>
+          <t>269069</t>
         </is>
       </c>
       <c r="D1020" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="E1020" t="inlineStr">
         <is>
-          <t>KAKAO_alimtalk</t>
+          <t>Direct</t>
         </is>
       </c>
     </row>
     <row r="1021">
       <c r="A1021" t="inlineStr">
         <is>
-          <t>aya6969</t>
+          <t>mansoogi</t>
         </is>
       </c>
       <c r="B1021" t="inlineStr">
         <is>
-          <t>01076590009</t>
+          <t>01093240897</t>
         </is>
       </c>
       <c r="C1021" t="inlineStr">
         <is>
-          <t>162562</t>
+          <t>25243</t>
         </is>
       </c>
       <c r="D1021" t="inlineStr">
@@ -27998,71 +27998,71 @@
     <row r="1022">
       <c r="A1022" t="inlineStr">
         <is>
-          <t>kk_2940110361</t>
+          <t>kk_3013902343</t>
         </is>
       </c>
       <c r="B1022" t="inlineStr">
         <is>
-          <t>01035353200</t>
+          <t>01051802326</t>
         </is>
       </c>
       <c r="C1022" t="inlineStr">
         <is>
-          <t>216362</t>
+          <t>219219</t>
         </is>
       </c>
       <c r="D1022" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E1022" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0410exclusive2</t>
+          <t>6968489536332</t>
         </is>
       </c>
     </row>
     <row r="1023">
       <c r="A1023" t="inlineStr">
         <is>
-          <t>kk_4840061178</t>
+          <t>seul6169</t>
         </is>
       </c>
       <c r="B1023" t="inlineStr">
         <is>
-          <t>01082357895</t>
+          <t>01066116699</t>
         </is>
       </c>
       <c r="C1023" t="inlineStr">
         <is>
-          <t>304124</t>
+          <t>234239</t>
         </is>
       </c>
       <c r="D1023" t="inlineStr">
         <is>
-          <t>Awareness</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E1023" t="inlineStr">
         <is>
-          <t>benz_running_program_2026_coupon</t>
+          <t>KAKAO_alimtalk</t>
         </is>
       </c>
     </row>
     <row r="1024">
       <c r="A1024" t="inlineStr">
         <is>
-          <t>kk_3185867832</t>
+          <t>kk_4523594127</t>
         </is>
       </c>
       <c r="B1024" t="inlineStr">
         <is>
-          <t>01022086508</t>
+          <t>01085735215</t>
         </is>
       </c>
       <c r="C1024" t="inlineStr">
         <is>
-          <t>229863</t>
+          <t>286358</t>
         </is>
       </c>
       <c r="D1024" t="inlineStr">
@@ -28079,27 +28079,27 @@
     <row r="1025">
       <c r="A1025" t="inlineStr">
         <is>
-          <t>jhmin000</t>
+          <t>kk_4837943303</t>
         </is>
       </c>
       <c r="B1025" t="inlineStr">
         <is>
-          <t>01086241606</t>
+          <t>01054817243</t>
         </is>
       </c>
       <c r="C1025" t="inlineStr">
         <is>
-          <t>201165</t>
+          <t>304025</t>
         </is>
       </c>
       <c r="D1025" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="E1025" t="inlineStr">
         <is>
-          <t>KAKAO_CH_MESSAGE_0409_HIKE365SUMMER</t>
+          <t>Direct</t>
         </is>
       </c>
     </row>
@@ -28133,44 +28133,44 @@
     <row r="1027">
       <c r="A1027" t="inlineStr">
         <is>
-          <t>kk_4351086966</t>
+          <t>jhmin000</t>
         </is>
       </c>
       <c r="B1027" t="inlineStr">
         <is>
-          <t>01042088262</t>
+          <t>01086241606</t>
         </is>
       </c>
       <c r="C1027" t="inlineStr">
         <is>
-          <t>279266</t>
+          <t>201165</t>
         </is>
       </c>
       <c r="D1027" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E1027" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>KAKAO_CH_MESSAGE_0409_HIKE365SUMMER</t>
         </is>
       </c>
     </row>
     <row r="1028">
       <c r="A1028" t="inlineStr">
         <is>
-          <t>bbluesea</t>
+          <t>kk_4526169965</t>
         </is>
       </c>
       <c r="B1028" t="inlineStr">
         <is>
-          <t>01076473601</t>
+          <t>01076289838</t>
         </is>
       </c>
       <c r="C1028" t="inlineStr">
         <is>
-          <t>152067</t>
+          <t>286553</t>
         </is>
       </c>
       <c r="D1028" t="inlineStr">
@@ -28180,51 +28180,51 @@
       </c>
       <c r="E1028" t="inlineStr">
         <is>
-          <t>KAKAO_CH_MENU_260406_LIGHTJACKET</t>
+          <t>KAKAO_CH_MESSAGE_0409_HIKE365SUMMER</t>
         </is>
       </c>
     </row>
     <row r="1029">
       <c r="A1029" t="inlineStr">
         <is>
-          <t>kk_3638512879</t>
+          <t>kk_4351086966</t>
         </is>
       </c>
       <c r="B1029" t="inlineStr">
         <is>
-          <t>01053330589</t>
+          <t>01042088262</t>
         </is>
       </c>
       <c r="C1029" t="inlineStr">
         <is>
-          <t>248574</t>
+          <t>279266</t>
         </is>
       </c>
       <c r="D1029" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="E1029" t="inlineStr">
         <is>
-          <t>KAKAO_CH_MESSAGE_0409_HIKE365SUMMER</t>
+          <t>Direct</t>
         </is>
       </c>
     </row>
     <row r="1030">
       <c r="A1030" t="inlineStr">
         <is>
-          <t>kk_4526169965</t>
+          <t>kk_3638512879</t>
         </is>
       </c>
       <c r="B1030" t="inlineStr">
         <is>
-          <t>01076289838</t>
+          <t>01053330589</t>
         </is>
       </c>
       <c r="C1030" t="inlineStr">
         <is>
-          <t>286553</t>
+          <t>248574</t>
         </is>
       </c>
       <c r="D1030" t="inlineStr">
@@ -28241,17 +28241,17 @@
     <row r="1031">
       <c r="A1031" t="inlineStr">
         <is>
-          <t>kk_3155938902</t>
+          <t>kk_4726499171</t>
         </is>
       </c>
       <c r="B1031" t="inlineStr">
         <is>
-          <t>01098557018</t>
+          <t>01093851013</t>
         </is>
       </c>
       <c r="C1031" t="inlineStr">
         <is>
-          <t>223731</t>
+          <t>297987</t>
         </is>
       </c>
       <c r="D1031" t="inlineStr">
@@ -28268,17 +28268,17 @@
     <row r="1032">
       <c r="A1032" t="inlineStr">
         <is>
-          <t>kk_3665803645</t>
+          <t>bbluesea</t>
         </is>
       </c>
       <c r="B1032" t="inlineStr">
         <is>
-          <t>01095549123</t>
+          <t>01076473601</t>
         </is>
       </c>
       <c r="C1032" t="inlineStr">
         <is>
-          <t>249835</t>
+          <t>152067</t>
         </is>
       </c>
       <c r="D1032" t="inlineStr">
@@ -28288,24 +28288,24 @@
       </c>
       <c r="E1032" t="inlineStr">
         <is>
-          <t>KAKAO_CH_MESSAGE_0409_EXCLUSIVE</t>
+          <t>KAKAO_CH_MENU_260406_LIGHTJACKET</t>
         </is>
       </c>
     </row>
     <row r="1033">
       <c r="A1033" t="inlineStr">
         <is>
-          <t>kk_4837943303</t>
+          <t>kk_3154612153</t>
         </is>
       </c>
       <c r="B1033" t="inlineStr">
         <is>
-          <t>01054817243</t>
+          <t>01056681753</t>
         </is>
       </c>
       <c r="C1033" t="inlineStr">
         <is>
-          <t>304025</t>
+          <t>223664</t>
         </is>
       </c>
       <c r="D1033" t="inlineStr">
@@ -28322,17 +28322,17 @@
     <row r="1034">
       <c r="A1034" t="inlineStr">
         <is>
-          <t>kk_4726499171</t>
+          <t>kk_3155938902</t>
         </is>
       </c>
       <c r="B1034" t="inlineStr">
         <is>
-          <t>01093851013</t>
+          <t>01098557018</t>
         </is>
       </c>
       <c r="C1034" t="inlineStr">
         <is>
-          <t>297987</t>
+          <t>223731</t>
         </is>
       </c>
       <c r="D1034" t="inlineStr">
@@ -28349,27 +28349,27 @@
     <row r="1035">
       <c r="A1035" t="inlineStr">
         <is>
-          <t>kk_3154612153</t>
+          <t>kk_3665803645</t>
         </is>
       </c>
       <c r="B1035" t="inlineStr">
         <is>
-          <t>01056681753</t>
+          <t>01095549123</t>
         </is>
       </c>
       <c r="C1035" t="inlineStr">
         <is>
-          <t>223664</t>
+          <t>249835</t>
         </is>
       </c>
       <c r="D1035" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E1035" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>KAKAO_CH_MESSAGE_0409_EXCLUSIVE</t>
         </is>
       </c>
     </row>
@@ -28457,17 +28457,17 @@
     <row r="1039">
       <c r="A1039" t="inlineStr">
         <is>
-          <t>dltndgy99</t>
+          <t>kk_2807863527</t>
         </is>
       </c>
       <c r="B1039" t="inlineStr">
         <is>
-          <t>01024587982</t>
+          <t>01042669625</t>
         </is>
       </c>
       <c r="C1039" t="inlineStr">
         <is>
-          <t>156217</t>
+          <t>211605</t>
         </is>
       </c>
       <c r="D1039" t="inlineStr">
@@ -28477,61 +28477,61 @@
       </c>
       <c r="E1039" t="inlineStr">
         <is>
-          <t>naver_brandsearch_mobile</t>
+          <t>[PF]전환_회원가입(유사)</t>
         </is>
       </c>
     </row>
     <row r="1040">
       <c r="A1040" t="inlineStr">
         <is>
-          <t>pentagram</t>
+          <t>dltndgy99</t>
         </is>
       </c>
       <c r="B1040" t="inlineStr">
         <is>
-          <t>01093327353</t>
+          <t>01024587982</t>
         </is>
       </c>
       <c r="C1040" t="inlineStr">
         <is>
-          <t>131085</t>
+          <t>156217</t>
         </is>
       </c>
       <c r="D1040" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E1040" t="inlineStr">
         <is>
-          <t>KAKAO_alimtalk</t>
+          <t>naver_brandsearch_mobile</t>
         </is>
       </c>
     </row>
     <row r="1041">
       <c r="A1041" t="inlineStr">
         <is>
-          <t>kk_2807863527</t>
+          <t>pentagram</t>
         </is>
       </c>
       <c r="B1041" t="inlineStr">
         <is>
-          <t>01042669625</t>
+          <t>01093327353</t>
         </is>
       </c>
       <c r="C1041" t="inlineStr">
         <is>
-          <t>211605</t>
+          <t>131085</t>
         </is>
       </c>
       <c r="D1041" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E1041" t="inlineStr">
         <is>
-          <t>[PF]전환_회원가입(유사)</t>
+          <t>KAKAO_alimtalk</t>
         </is>
       </c>
     </row>
@@ -28565,152 +28565,152 @@
     <row r="1043">
       <c r="A1043" t="inlineStr">
         <is>
-          <t>wisbrain</t>
+          <t>kk_4427490834</t>
         </is>
       </c>
       <c r="B1043" t="inlineStr">
         <is>
-          <t>01047220186</t>
+          <t>01034704205</t>
         </is>
       </c>
       <c r="C1043" t="inlineStr">
         <is>
-          <t>188067</t>
+          <t>281590</t>
         </is>
       </c>
       <c r="D1043" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E1043" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>LMS_ECOM_0410exclusive2</t>
         </is>
       </c>
     </row>
     <row r="1044">
       <c r="A1044" t="inlineStr">
         <is>
-          <t>hihijs34</t>
+          <t>loyed24</t>
         </is>
       </c>
       <c r="B1044" t="inlineStr">
         <is>
-          <t>01093230529</t>
+          <t>01085487901</t>
         </is>
       </c>
       <c r="C1044" t="inlineStr">
         <is>
-          <t>128947</t>
+          <t>244062</t>
         </is>
       </c>
       <c r="D1044" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E1044" t="inlineStr">
         <is>
-          <t>[PF]A+SC_상시(1865MF,구매+장바구니)</t>
+          <t>LMS_ECOM_0410exclusive2</t>
         </is>
       </c>
     </row>
     <row r="1045">
       <c r="A1045" t="inlineStr">
         <is>
-          <t>loyed24</t>
+          <t>wisbrain</t>
         </is>
       </c>
       <c r="B1045" t="inlineStr">
         <is>
-          <t>01085487901</t>
+          <t>01047220186</t>
         </is>
       </c>
       <c r="C1045" t="inlineStr">
         <is>
-          <t>244062</t>
+          <t>188067</t>
         </is>
       </c>
       <c r="D1045" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="E1045" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0410exclusive2</t>
+          <t>Direct</t>
         </is>
       </c>
     </row>
     <row r="1046">
       <c r="A1046" t="inlineStr">
         <is>
-          <t>kk_4427490834</t>
+          <t>hihijs34</t>
         </is>
       </c>
       <c r="B1046" t="inlineStr">
         <is>
-          <t>01034704205</t>
+          <t>01093230529</t>
         </is>
       </c>
       <c r="C1046" t="inlineStr">
         <is>
-          <t>281590</t>
+          <t>128947</t>
         </is>
       </c>
       <c r="D1046" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E1046" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0410exclusive2</t>
+          <t>[PF]A+SC_상시(1865MF,구매+장바구니)</t>
         </is>
       </c>
     </row>
     <row r="1047">
       <c r="A1047" t="inlineStr">
         <is>
-          <t>kk_2825715315</t>
+          <t>kk_4292190414</t>
         </is>
       </c>
       <c r="B1047" t="inlineStr">
         <is>
-          <t>01077229654</t>
+          <t>01095177478</t>
         </is>
       </c>
       <c r="C1047" t="inlineStr">
         <is>
-          <t>212719</t>
+          <t>275998</t>
         </is>
       </c>
       <c r="D1047" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="E1047" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0410exclusive2</t>
+          <t>Direct</t>
         </is>
       </c>
     </row>
     <row r="1048">
       <c r="A1048" t="inlineStr">
         <is>
-          <t>kk_3973703558</t>
+          <t>kk_3024318364</t>
         </is>
       </c>
       <c r="B1048" t="inlineStr">
         <is>
-          <t>01048590748</t>
+          <t>01050308038</t>
         </is>
       </c>
       <c r="C1048" t="inlineStr">
         <is>
-          <t>271020</t>
+          <t>219525</t>
         </is>
       </c>
       <c r="D1048" t="inlineStr">
@@ -28727,17 +28727,17 @@
     <row r="1049">
       <c r="A1049" t="inlineStr">
         <is>
-          <t>bobjazz</t>
+          <t>kk_3180736217</t>
         </is>
       </c>
       <c r="B1049" t="inlineStr">
         <is>
-          <t>01084090677</t>
+          <t>01036000343</t>
         </is>
       </c>
       <c r="C1049" t="inlineStr">
         <is>
-          <t>186218</t>
+          <t>226314</t>
         </is>
       </c>
       <c r="D1049" t="inlineStr">
@@ -28754,17 +28754,17 @@
     <row r="1050">
       <c r="A1050" t="inlineStr">
         <is>
-          <t>inu21c</t>
+          <t>bobjazz</t>
         </is>
       </c>
       <c r="B1050" t="inlineStr">
         <is>
-          <t>01035128236</t>
+          <t>01084090677</t>
         </is>
       </c>
       <c r="C1050" t="inlineStr">
         <is>
-          <t>131940</t>
+          <t>186218</t>
         </is>
       </c>
       <c r="D1050" t="inlineStr">
@@ -28781,17 +28781,17 @@
     <row r="1051">
       <c r="A1051" t="inlineStr">
         <is>
-          <t>kk_4578503399</t>
+          <t>kk_3349199057</t>
         </is>
       </c>
       <c r="B1051" t="inlineStr">
         <is>
-          <t>01088660330</t>
+          <t>01071630312</t>
         </is>
       </c>
       <c r="C1051" t="inlineStr">
         <is>
-          <t>288374</t>
+          <t>239388</t>
         </is>
       </c>
       <c r="D1051" t="inlineStr">
@@ -28808,17 +28808,17 @@
     <row r="1052">
       <c r="A1052" t="inlineStr">
         <is>
-          <t>kk_3721447783</t>
+          <t>yongshin</t>
         </is>
       </c>
       <c r="B1052" t="inlineStr">
         <is>
-          <t>01051311087</t>
+          <t>01053867821</t>
         </is>
       </c>
       <c r="C1052" t="inlineStr">
         <is>
-          <t>252252</t>
+          <t>277896</t>
         </is>
       </c>
       <c r="D1052" t="inlineStr">
@@ -28835,44 +28835,44 @@
     <row r="1053">
       <c r="A1053" t="inlineStr">
         <is>
-          <t>yongshin</t>
+          <t>pls4u</t>
         </is>
       </c>
       <c r="B1053" t="inlineStr">
         <is>
-          <t>01053867821</t>
+          <t>01085985482</t>
         </is>
       </c>
       <c r="C1053" t="inlineStr">
         <is>
-          <t>277896</t>
+          <t>88257</t>
         </is>
       </c>
       <c r="D1053" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E1053" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>LMS_ECOM_0401_trailrunning</t>
         </is>
       </c>
     </row>
     <row r="1054">
       <c r="A1054" t="inlineStr">
         <is>
-          <t>kk_3180736217</t>
+          <t>kk_3973703558</t>
         </is>
       </c>
       <c r="B1054" t="inlineStr">
         <is>
-          <t>01036000343</t>
+          <t>01048590748</t>
         </is>
       </c>
       <c r="C1054" t="inlineStr">
         <is>
-          <t>226314</t>
+          <t>271020</t>
         </is>
       </c>
       <c r="D1054" t="inlineStr">
@@ -28889,17 +28889,17 @@
     <row r="1055">
       <c r="A1055" t="inlineStr">
         <is>
-          <t>kk_3024318364</t>
+          <t>sjm700</t>
         </is>
       </c>
       <c r="B1055" t="inlineStr">
         <is>
-          <t>01050308038</t>
+          <t>01077331591</t>
         </is>
       </c>
       <c r="C1055" t="inlineStr">
         <is>
-          <t>219525</t>
+          <t>118769</t>
         </is>
       </c>
       <c r="D1055" t="inlineStr">
@@ -28916,44 +28916,44 @@
     <row r="1056">
       <c r="A1056" t="inlineStr">
         <is>
-          <t>kk_4292190414</t>
+          <t>dmsql785612</t>
         </is>
       </c>
       <c r="B1056" t="inlineStr">
         <is>
-          <t>01095177478</t>
+          <t>01051590364</t>
         </is>
       </c>
       <c r="C1056" t="inlineStr">
         <is>
-          <t>275998</t>
+          <t>137279</t>
         </is>
       </c>
       <c r="D1056" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E1056" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>Email_mkt</t>
         </is>
       </c>
     </row>
     <row r="1057">
       <c r="A1057" t="inlineStr">
         <is>
-          <t>hyschant</t>
+          <t>kk_4525043459</t>
         </is>
       </c>
       <c r="B1057" t="inlineStr">
         <is>
-          <t>01065306675</t>
+          <t>01088312135</t>
         </is>
       </c>
       <c r="C1057" t="inlineStr">
         <is>
-          <t>108579</t>
+          <t>286464</t>
         </is>
       </c>
       <c r="D1057" t="inlineStr">
@@ -28970,17 +28970,17 @@
     <row r="1058">
       <c r="A1058" t="inlineStr">
         <is>
-          <t>sjm700</t>
+          <t>columbia7</t>
         </is>
       </c>
       <c r="B1058" t="inlineStr">
         <is>
-          <t>01077331591</t>
+          <t>01050080025</t>
         </is>
       </c>
       <c r="C1058" t="inlineStr">
         <is>
-          <t>118769</t>
+          <t>109980</t>
         </is>
       </c>
       <c r="D1058" t="inlineStr">
@@ -28997,17 +28997,17 @@
     <row r="1059">
       <c r="A1059" t="inlineStr">
         <is>
-          <t>kk_4452401577</t>
+          <t>kk_2825715315</t>
         </is>
       </c>
       <c r="B1059" t="inlineStr">
         <is>
-          <t>01047428000</t>
+          <t>01077229654</t>
         </is>
       </c>
       <c r="C1059" t="inlineStr">
         <is>
-          <t>282525</t>
+          <t>212719</t>
         </is>
       </c>
       <c r="D1059" t="inlineStr">
@@ -29024,44 +29024,44 @@
     <row r="1060">
       <c r="A1060" t="inlineStr">
         <is>
-          <t>dmsql785612</t>
+          <t>camiblanco</t>
         </is>
       </c>
       <c r="B1060" t="inlineStr">
         <is>
-          <t>01051590364</t>
+          <t>01072190103</t>
         </is>
       </c>
       <c r="C1060" t="inlineStr">
         <is>
-          <t>137279</t>
+          <t>232545</t>
         </is>
       </c>
       <c r="D1060" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="E1060" t="inlineStr">
         <is>
-          <t>Email_mkt</t>
+          <t>Direct</t>
         </is>
       </c>
     </row>
     <row r="1061">
       <c r="A1061" t="inlineStr">
         <is>
-          <t>kk_4525043459</t>
+          <t>kk_4578503399</t>
         </is>
       </c>
       <c r="B1061" t="inlineStr">
         <is>
-          <t>01088312135</t>
+          <t>01088660330</t>
         </is>
       </c>
       <c r="C1061" t="inlineStr">
         <is>
-          <t>286464</t>
+          <t>288374</t>
         </is>
       </c>
       <c r="D1061" t="inlineStr">
@@ -29078,17 +29078,17 @@
     <row r="1062">
       <c r="A1062" t="inlineStr">
         <is>
-          <t>columbia7</t>
+          <t>inu21c</t>
         </is>
       </c>
       <c r="B1062" t="inlineStr">
         <is>
-          <t>01050080025</t>
+          <t>01035128236</t>
         </is>
       </c>
       <c r="C1062" t="inlineStr">
         <is>
-          <t>109980</t>
+          <t>131940</t>
         </is>
       </c>
       <c r="D1062" t="inlineStr">
@@ -29105,17 +29105,17 @@
     <row r="1063">
       <c r="A1063" t="inlineStr">
         <is>
-          <t>kk_3349199057</t>
+          <t>kk_4452401577</t>
         </is>
       </c>
       <c r="B1063" t="inlineStr">
         <is>
-          <t>01071630312</t>
+          <t>01047428000</t>
         </is>
       </c>
       <c r="C1063" t="inlineStr">
         <is>
-          <t>239388</t>
+          <t>282525</t>
         </is>
       </c>
       <c r="D1063" t="inlineStr">
@@ -29132,17 +29132,17 @@
     <row r="1064">
       <c r="A1064" t="inlineStr">
         <is>
-          <t>pls4u</t>
+          <t>hyschant</t>
         </is>
       </c>
       <c r="B1064" t="inlineStr">
         <is>
-          <t>01085985482</t>
+          <t>01065306675</t>
         </is>
       </c>
       <c r="C1064" t="inlineStr">
         <is>
-          <t>88257</t>
+          <t>108579</t>
         </is>
       </c>
       <c r="D1064" t="inlineStr">
@@ -29152,78 +29152,78 @@
       </c>
       <c r="E1064" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0401_trailrunning</t>
+          <t>LMS_ECOM_0410exclusive2</t>
         </is>
       </c>
     </row>
     <row r="1065">
       <c r="A1065" t="inlineStr">
         <is>
-          <t>camiblanco</t>
+          <t>kk_3754052831</t>
         </is>
       </c>
       <c r="B1065" t="inlineStr">
         <is>
-          <t>01072190103</t>
+          <t>01092180804</t>
         </is>
       </c>
       <c r="C1065" t="inlineStr">
         <is>
-          <t>232545</t>
+          <t>254339</t>
         </is>
       </c>
       <c r="D1065" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E1065" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>LMS_ECOM_0410exclusive2</t>
         </is>
       </c>
     </row>
     <row r="1066">
       <c r="A1066" t="inlineStr">
         <is>
-          <t>kk_3754052831</t>
+          <t>kk_3721447783</t>
         </is>
       </c>
       <c r="B1066" t="inlineStr">
         <is>
-          <t>01092180804</t>
+          <t>01051311087</t>
         </is>
       </c>
       <c r="C1066" t="inlineStr">
         <is>
-          <t>254339</t>
+          <t>252252</t>
         </is>
       </c>
       <c r="D1066" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="E1066" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0410exclusive2</t>
+          <t>Direct</t>
         </is>
       </c>
     </row>
     <row r="1067">
       <c r="A1067" t="inlineStr">
         <is>
-          <t>kk_3626939480</t>
+          <t>kk_3912725759</t>
         </is>
       </c>
       <c r="B1067" t="inlineStr">
         <is>
-          <t>01030537990</t>
+          <t>01062505257</t>
         </is>
       </c>
       <c r="C1067" t="inlineStr">
         <is>
-          <t>247893</t>
+          <t>268286</t>
         </is>
       </c>
       <c r="D1067" t="inlineStr">
@@ -29240,17 +29240,17 @@
     <row r="1068">
       <c r="A1068" t="inlineStr">
         <is>
-          <t>kk_3912725759</t>
+          <t>kk_3626939480</t>
         </is>
       </c>
       <c r="B1068" t="inlineStr">
         <is>
-          <t>01062505257</t>
+          <t>01030537990</t>
         </is>
       </c>
       <c r="C1068" t="inlineStr">
         <is>
-          <t>268286</t>
+          <t>247893</t>
         </is>
       </c>
       <c r="D1068" t="inlineStr">
@@ -29348,17 +29348,17 @@
     <row r="1072">
       <c r="A1072" t="inlineStr">
         <is>
-          <t>kimms66</t>
+          <t>alcoholpower</t>
         </is>
       </c>
       <c r="B1072" t="inlineStr">
         <is>
-          <t>01057634626</t>
+          <t>01027629868</t>
         </is>
       </c>
       <c r="C1072" t="inlineStr">
         <is>
-          <t>180321</t>
+          <t>252954</t>
         </is>
       </c>
       <c r="D1072" t="inlineStr">
@@ -29375,17 +29375,17 @@
     <row r="1073">
       <c r="A1073" t="inlineStr">
         <is>
-          <t>alcoholpower</t>
+          <t>kimms66</t>
         </is>
       </c>
       <c r="B1073" t="inlineStr">
         <is>
-          <t>01027629868</t>
+          <t>01057634626</t>
         </is>
       </c>
       <c r="C1073" t="inlineStr">
         <is>
-          <t>252954</t>
+          <t>180321</t>
         </is>
       </c>
       <c r="D1073" t="inlineStr">

--- a/reports/member_funnel/downloads/member_funnel_7d_non_buyer.xlsx
+++ b/reports/member_funnel/downloads/member_funnel_7d_non_buyer.xlsx
@@ -22409,54 +22409,54 @@
     <row r="815">
       <c r="A815" t="inlineStr">
         <is>
-          <t>kk_3180181891</t>
+          <t>kk_4615020382</t>
         </is>
       </c>
       <c r="B815" t="inlineStr">
         <is>
-          <t>01065587969</t>
+          <t>01092438164</t>
         </is>
       </c>
       <c r="C815" t="inlineStr">
         <is>
-          <t>225645</t>
+          <t>290598</t>
         </is>
       </c>
       <c r="D815" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E815" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>Paid Ad</t>
         </is>
       </c>
     </row>
     <row r="816">
       <c r="A816" t="inlineStr">
         <is>
-          <t>kk_4615020382</t>
+          <t>kk_3180181891</t>
         </is>
       </c>
       <c r="B816" t="inlineStr">
         <is>
-          <t>01092438164</t>
+          <t>01065587969</t>
         </is>
       </c>
       <c r="C816" t="inlineStr">
         <is>
-          <t>290598</t>
+          <t>225645</t>
         </is>
       </c>
       <c r="D816" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="E816" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Direct</t>
         </is>
       </c>
     </row>
@@ -23651,17 +23651,17 @@
     <row r="861">
       <c r="A861" t="inlineStr">
         <is>
-          <t>kk_3101119679</t>
+          <t>hun7662</t>
         </is>
       </c>
       <c r="B861" t="inlineStr">
         <is>
-          <t>01093993852</t>
+          <t>01042311474</t>
         </is>
       </c>
       <c r="C861" t="inlineStr">
         <is>
-          <t>221630</t>
+          <t>172790</t>
         </is>
       </c>
       <c r="D861" t="inlineStr">
@@ -23678,17 +23678,17 @@
     <row r="862">
       <c r="A862" t="inlineStr">
         <is>
-          <t>hun7662</t>
+          <t>kk_3101119679</t>
         </is>
       </c>
       <c r="B862" t="inlineStr">
         <is>
-          <t>01042311474</t>
+          <t>01093993852</t>
         </is>
       </c>
       <c r="C862" t="inlineStr">
         <is>
-          <t>172790</t>
+          <t>221630</t>
         </is>
       </c>
       <c r="D862" t="inlineStr">
@@ -24083,54 +24083,54 @@
     <row r="877">
       <c r="A877" t="inlineStr">
         <is>
-          <t>sun1381</t>
+          <t>kk_4839145768</t>
         </is>
       </c>
       <c r="B877" t="inlineStr">
         <is>
-          <t>01037709416</t>
+          <t>01097367898</t>
         </is>
       </c>
       <c r="C877" t="inlineStr">
         <is>
-          <t>278160</t>
+          <t>304085</t>
         </is>
       </c>
       <c r="D877" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E877" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0410exclusive2</t>
+          <t>naver_brandsearch_pc</t>
         </is>
       </c>
     </row>
     <row r="878">
       <c r="A878" t="inlineStr">
         <is>
-          <t>kk_4839145768</t>
+          <t>sun1381</t>
         </is>
       </c>
       <c r="B878" t="inlineStr">
         <is>
-          <t>01097367898</t>
+          <t>01037709416</t>
         </is>
       </c>
       <c r="C878" t="inlineStr">
         <is>
-          <t>304085</t>
+          <t>278160</t>
         </is>
       </c>
       <c r="D878" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E878" t="inlineStr">
         <is>
-          <t>naver_brandsearch_pc</t>
+          <t>LMS_ECOM_0410exclusive2</t>
         </is>
       </c>
     </row>
@@ -24893,17 +24893,17 @@
     <row r="907">
       <c r="A907" t="inlineStr">
         <is>
-          <t>abril80</t>
+          <t>kang481127</t>
         </is>
       </c>
       <c r="B907" t="inlineStr">
         <is>
-          <t>01032942835</t>
+          <t>01053764012</t>
         </is>
       </c>
       <c r="C907" t="inlineStr">
         <is>
-          <t>192610</t>
+          <t>304276</t>
         </is>
       </c>
       <c r="D907" t="inlineStr">
@@ -24913,24 +24913,24 @@
       </c>
       <c r="E907" t="inlineStr">
         <is>
-          <t>Email_mkt</t>
+          <t>LMS_ECOM_NEWMEMBER</t>
         </is>
       </c>
     </row>
     <row r="908">
       <c r="A908" t="inlineStr">
         <is>
-          <t>kang481127</t>
+          <t>abril80</t>
         </is>
       </c>
       <c r="B908" t="inlineStr">
         <is>
-          <t>01053764012</t>
+          <t>01032942835</t>
         </is>
       </c>
       <c r="C908" t="inlineStr">
         <is>
-          <t>304276</t>
+          <t>192610</t>
         </is>
       </c>
       <c r="D908" t="inlineStr">
@@ -24940,7 +24940,7 @@
       </c>
       <c r="E908" t="inlineStr">
         <is>
-          <t>LMS_ECOM_NEWMEMBER</t>
+          <t>Email_mkt</t>
         </is>
       </c>
     </row>
@@ -25136,27 +25136,27 @@
     <row r="916">
       <c r="A916" t="inlineStr">
         <is>
-          <t>athend</t>
+          <t>kk_4639169718</t>
         </is>
       </c>
       <c r="B916" t="inlineStr">
         <is>
-          <t>01041786462</t>
+          <t>01041380770</t>
         </is>
       </c>
       <c r="C916" t="inlineStr">
         <is>
-          <t>285491</t>
+          <t>292319</t>
         </is>
       </c>
       <c r="D916" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E916" t="inlineStr">
         <is>
-          <t>KAKAO_alimtalk</t>
+          <t>naver_brandsearch_mobile</t>
         </is>
       </c>
     </row>
@@ -25217,27 +25217,27 @@
     <row r="919">
       <c r="A919" t="inlineStr">
         <is>
-          <t>kk_4639169718</t>
+          <t>athend</t>
         </is>
       </c>
       <c r="B919" t="inlineStr">
         <is>
-          <t>01041380770</t>
+          <t>01041786462</t>
         </is>
       </c>
       <c r="C919" t="inlineStr">
         <is>
-          <t>292319</t>
+          <t>285491</t>
         </is>
       </c>
       <c r="D919" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E919" t="inlineStr">
         <is>
-          <t>naver_brandsearch_mobile</t>
+          <t>KAKAO_alimtalk</t>
         </is>
       </c>
     </row>
@@ -25271,17 +25271,17 @@
     <row r="921">
       <c r="A921" t="inlineStr">
         <is>
-          <t>yockk23</t>
+          <t>toplaser</t>
         </is>
       </c>
       <c r="B921" t="inlineStr">
         <is>
-          <t>01031774006</t>
+          <t>01056735155</t>
         </is>
       </c>
       <c r="C921" t="inlineStr">
         <is>
-          <t>192898</t>
+          <t>288028</t>
         </is>
       </c>
       <c r="D921" t="inlineStr">
@@ -25291,24 +25291,24 @@
       </c>
       <c r="E921" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0304</t>
+          <t>LMS_ECOM_0214_newyear</t>
         </is>
       </c>
     </row>
     <row r="922">
       <c r="A922" t="inlineStr">
         <is>
-          <t>toplaser</t>
+          <t>yockk23</t>
         </is>
       </c>
       <c r="B922" t="inlineStr">
         <is>
-          <t>01056735155</t>
+          <t>01031774006</t>
         </is>
       </c>
       <c r="C922" t="inlineStr">
         <is>
-          <t>288028</t>
+          <t>192898</t>
         </is>
       </c>
       <c r="D922" t="inlineStr">
@@ -25318,7 +25318,7 @@
       </c>
       <c r="E922" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0214_newyear</t>
+          <t>LMS_ECOM_0304</t>
         </is>
       </c>
     </row>
@@ -25460,54 +25460,54 @@
     <row r="928">
       <c r="A928" t="inlineStr">
         <is>
-          <t>kk_4839433808</t>
+          <t>mtbok</t>
         </is>
       </c>
       <c r="B928" t="inlineStr">
         <is>
-          <t>01025333388</t>
+          <t>01051284339</t>
         </is>
       </c>
       <c r="C928" t="inlineStr">
         <is>
-          <t>304100</t>
+          <t>26917</t>
         </is>
       </c>
       <c r="D928" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E928" t="inlineStr">
         <is>
-          <t>naver_brandsearch_mobile</t>
+          <t>LMS_ECOM_0410exclusive2</t>
         </is>
       </c>
     </row>
     <row r="929">
       <c r="A929" t="inlineStr">
         <is>
-          <t>mtbok</t>
+          <t>kk_4839433808</t>
         </is>
       </c>
       <c r="B929" t="inlineStr">
         <is>
-          <t>01051284339</t>
+          <t>01025333388</t>
         </is>
       </c>
       <c r="C929" t="inlineStr">
         <is>
-          <t>26917</t>
+          <t>304100</t>
         </is>
       </c>
       <c r="D929" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E929" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0410exclusive2</t>
+          <t>naver_brandsearch_mobile</t>
         </is>
       </c>
     </row>
@@ -25676,108 +25676,108 @@
     <row r="936">
       <c r="A936" t="inlineStr">
         <is>
-          <t>kk_4727921763</t>
+          <t>kk_3181873063</t>
         </is>
       </c>
       <c r="B936" t="inlineStr">
         <is>
-          <t>01045673975</t>
+          <t>01026527131</t>
         </is>
       </c>
       <c r="C936" t="inlineStr">
         <is>
-          <t>298138</t>
+          <t>227343</t>
         </is>
       </c>
       <c r="D936" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E936" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>LMS_ECOM_0410exclusive2</t>
         </is>
       </c>
     </row>
     <row r="937">
       <c r="A937" t="inlineStr">
         <is>
-          <t>kk_3181873063</t>
+          <t>kk_4839026541</t>
         </is>
       </c>
       <c r="B937" t="inlineStr">
         <is>
-          <t>01026527131</t>
+          <t>01089431507</t>
         </is>
       </c>
       <c r="C937" t="inlineStr">
         <is>
-          <t>227343</t>
+          <t>304082</t>
         </is>
       </c>
       <c r="D937" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E937" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0410exclusive2</t>
+          <t>[PF]전환_상시(2565MF,비구매자)</t>
         </is>
       </c>
     </row>
     <row r="938">
       <c r="A938" t="inlineStr">
         <is>
-          <t>kk_4839026541</t>
+          <t>kk_2757380967</t>
         </is>
       </c>
       <c r="B938" t="inlineStr">
         <is>
-          <t>01089431507</t>
+          <t>01034635649</t>
         </is>
       </c>
       <c r="C938" t="inlineStr">
         <is>
-          <t>304082</t>
+          <t>208245</t>
         </is>
       </c>
       <c r="D938" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E938" t="inlineStr">
         <is>
-          <t>[PF]전환_상시(2565MF,비구매자)</t>
+          <t>LMS_ECOM_0410exclusive2</t>
         </is>
       </c>
     </row>
     <row r="939">
       <c r="A939" t="inlineStr">
         <is>
-          <t>kk_2757380967</t>
+          <t>kk_4727921763</t>
         </is>
       </c>
       <c r="B939" t="inlineStr">
         <is>
-          <t>01034635649</t>
+          <t>01045673975</t>
         </is>
       </c>
       <c r="C939" t="inlineStr">
         <is>
-          <t>208245</t>
+          <t>298138</t>
         </is>
       </c>
       <c r="D939" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="E939" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0410exclusive2</t>
+          <t>Direct</t>
         </is>
       </c>
     </row>
@@ -25838,71 +25838,71 @@
     <row r="942">
       <c r="A942" t="inlineStr">
         <is>
-          <t>jeanne</t>
+          <t>kk_3810304670</t>
         </is>
       </c>
       <c r="B942" t="inlineStr">
         <is>
-          <t>01047490850</t>
+          <t>01041348052</t>
         </is>
       </c>
       <c r="C942" t="inlineStr">
         <is>
-          <t>195346</t>
+          <t>261190</t>
         </is>
       </c>
       <c r="D942" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="E942" t="inlineStr">
         <is>
-          <t>etc</t>
+          <t>Direct</t>
         </is>
       </c>
     </row>
     <row r="943">
       <c r="A943" t="inlineStr">
         <is>
-          <t>kk_3334413020</t>
+          <t>kk_3975997627</t>
         </is>
       </c>
       <c r="B943" t="inlineStr">
         <is>
-          <t>01080806386</t>
+          <t>01066448502</t>
         </is>
       </c>
       <c r="C943" t="inlineStr">
         <is>
-          <t>238829</t>
+          <t>271178</t>
         </is>
       </c>
       <c r="D943" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="E943" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Direct</t>
         </is>
       </c>
     </row>
     <row r="944">
       <c r="A944" t="inlineStr">
         <is>
-          <t>sarang21</t>
+          <t>pbhds102306</t>
         </is>
       </c>
       <c r="B944" t="inlineStr">
         <is>
-          <t>01054975535</t>
+          <t>01062816264</t>
         </is>
       </c>
       <c r="C944" t="inlineStr">
         <is>
-          <t>268553</t>
+          <t>266784</t>
         </is>
       </c>
       <c r="D944" t="inlineStr">
@@ -25919,17 +25919,17 @@
     <row r="945">
       <c r="A945" t="inlineStr">
         <is>
-          <t>pbhds102306</t>
+          <t>jeanne</t>
         </is>
       </c>
       <c r="B945" t="inlineStr">
         <is>
-          <t>01062816264</t>
+          <t>01047490850</t>
         </is>
       </c>
       <c r="C945" t="inlineStr">
         <is>
-          <t>266784</t>
+          <t>195346</t>
         </is>
       </c>
       <c r="D945" t="inlineStr">
@@ -25946,71 +25946,71 @@
     <row r="946">
       <c r="A946" t="inlineStr">
         <is>
-          <t>kk_3975997627</t>
+          <t>sarang21</t>
         </is>
       </c>
       <c r="B946" t="inlineStr">
         <is>
-          <t>01066448502</t>
+          <t>01054975535</t>
         </is>
       </c>
       <c r="C946" t="inlineStr">
         <is>
-          <t>271178</t>
+          <t>268553</t>
         </is>
       </c>
       <c r="D946" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E946" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>etc</t>
         </is>
       </c>
     </row>
     <row r="947">
       <c r="A947" t="inlineStr">
         <is>
-          <t>kk_3251799831</t>
+          <t>kk_3334413020</t>
         </is>
       </c>
       <c r="B947" t="inlineStr">
         <is>
-          <t>01040006581</t>
+          <t>01080806386</t>
         </is>
       </c>
       <c r="C947" t="inlineStr">
         <is>
-          <t>235398</t>
+          <t>238829</t>
         </is>
       </c>
       <c r="D947" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E947" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>Paid Ad</t>
         </is>
       </c>
     </row>
     <row r="948">
       <c r="A948" t="inlineStr">
         <is>
-          <t>kk_3810304670</t>
+          <t>kk_3251799831</t>
         </is>
       </c>
       <c r="B948" t="inlineStr">
         <is>
-          <t>01041348052</t>
+          <t>01040006581</t>
         </is>
       </c>
       <c r="C948" t="inlineStr">
         <is>
-          <t>261190</t>
+          <t>235398</t>
         </is>
       </c>
       <c r="D948" t="inlineStr">
@@ -26027,17 +26027,17 @@
     <row r="949">
       <c r="A949" t="inlineStr">
         <is>
-          <t>kk_4469973568</t>
+          <t>kk_3210379887</t>
         </is>
       </c>
       <c r="B949" t="inlineStr">
         <is>
-          <t>01087158602</t>
+          <t>01024748405</t>
         </is>
       </c>
       <c r="C949" t="inlineStr">
         <is>
-          <t>283741</t>
+          <t>231651</t>
         </is>
       </c>
       <c r="D949" t="inlineStr">
@@ -26047,24 +26047,24 @@
       </c>
       <c r="E949" t="inlineStr">
         <is>
-          <t>KAKAO_CH_MENU_0211_NEW_MEN</t>
+          <t>LMS_ECOM_0410exclusive2</t>
         </is>
       </c>
     </row>
     <row r="950">
       <c r="A950" t="inlineStr">
         <is>
-          <t>kk_3210379887</t>
+          <t>kk_4469973568</t>
         </is>
       </c>
       <c r="B950" t="inlineStr">
         <is>
-          <t>01024748405</t>
+          <t>01087158602</t>
         </is>
       </c>
       <c r="C950" t="inlineStr">
         <is>
-          <t>231651</t>
+          <t>283741</t>
         </is>
       </c>
       <c r="D950" t="inlineStr">
@@ -26074,7 +26074,7 @@
       </c>
       <c r="E950" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0410exclusive2</t>
+          <t>KAKAO_CH_MENU_0211_NEW_MEN</t>
         </is>
       </c>
     </row>
@@ -26135,17 +26135,17 @@
     <row r="953">
       <c r="A953" t="inlineStr">
         <is>
-          <t>kk_3967419156</t>
+          <t>kk_4368805733</t>
         </is>
       </c>
       <c r="B953" t="inlineStr">
         <is>
-          <t>01030207947</t>
+          <t>01075528863</t>
         </is>
       </c>
       <c r="C953" t="inlineStr">
         <is>
-          <t>270708</t>
+          <t>279909</t>
         </is>
       </c>
       <c r="D953" t="inlineStr">
@@ -26162,17 +26162,17 @@
     <row r="954">
       <c r="A954" t="inlineStr">
         <is>
-          <t>kk_4368805733</t>
+          <t>kk_3967419156</t>
         </is>
       </c>
       <c r="B954" t="inlineStr">
         <is>
-          <t>01075528863</t>
+          <t>01030207947</t>
         </is>
       </c>
       <c r="C954" t="inlineStr">
         <is>
-          <t>279909</t>
+          <t>270708</t>
         </is>
       </c>
       <c r="D954" t="inlineStr">
@@ -26216,17 +26216,17 @@
     <row r="956">
       <c r="A956" t="inlineStr">
         <is>
-          <t>lovemac</t>
+          <t>soslsc</t>
         </is>
       </c>
       <c r="B956" t="inlineStr">
         <is>
-          <t>01058421351</t>
+          <t>01023174693</t>
         </is>
       </c>
       <c r="C956" t="inlineStr">
         <is>
-          <t>69911</t>
+          <t>171035</t>
         </is>
       </c>
       <c r="D956" t="inlineStr">
@@ -26243,17 +26243,17 @@
     <row r="957">
       <c r="A957" t="inlineStr">
         <is>
-          <t>soslsc</t>
+          <t>a3789</t>
         </is>
       </c>
       <c r="B957" t="inlineStr">
         <is>
-          <t>01023174693</t>
+          <t>01053102148</t>
         </is>
       </c>
       <c r="C957" t="inlineStr">
         <is>
-          <t>171035</t>
+          <t>244924</t>
         </is>
       </c>
       <c r="D957" t="inlineStr">
@@ -26270,17 +26270,17 @@
     <row r="958">
       <c r="A958" t="inlineStr">
         <is>
-          <t>a3789</t>
+          <t>lovemac</t>
         </is>
       </c>
       <c r="B958" t="inlineStr">
         <is>
-          <t>01053102148</t>
+          <t>01058421351</t>
         </is>
       </c>
       <c r="C958" t="inlineStr">
         <is>
-          <t>244924</t>
+          <t>69911</t>
         </is>
       </c>
       <c r="D958" t="inlineStr">
@@ -26324,54 +26324,54 @@
     <row r="960">
       <c r="A960" t="inlineStr">
         <is>
-          <t>l00years</t>
+          <t>seizeh</t>
         </is>
       </c>
       <c r="B960" t="inlineStr">
         <is>
-          <t>01053925529</t>
+          <t>01090302539</t>
         </is>
       </c>
       <c r="C960" t="inlineStr">
         <is>
-          <t>229454</t>
+          <t>68751</t>
         </is>
       </c>
       <c r="D960" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E960" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0410exclusive2</t>
+          <t>sa</t>
         </is>
       </c>
     </row>
     <row r="961">
       <c r="A961" t="inlineStr">
         <is>
-          <t>seizeh</t>
+          <t>l00years</t>
         </is>
       </c>
       <c r="B961" t="inlineStr">
         <is>
-          <t>01090302539</t>
+          <t>01053925529</t>
         </is>
       </c>
       <c r="C961" t="inlineStr">
         <is>
-          <t>68751</t>
+          <t>229454</t>
         </is>
       </c>
       <c r="D961" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E961" t="inlineStr">
         <is>
-          <t>sa</t>
+          <t>LMS_ECOM_0410exclusive2</t>
         </is>
       </c>
     </row>
@@ -26837,17 +26837,17 @@
     <row r="979">
       <c r="A979" t="inlineStr">
         <is>
-          <t>kk_3793117898</t>
+          <t>kk_3180854377</t>
         </is>
       </c>
       <c r="B979" t="inlineStr">
         <is>
-          <t>01052318168</t>
+          <t>01031216377</t>
         </is>
       </c>
       <c r="C979" t="inlineStr">
         <is>
-          <t>257099</t>
+          <t>226467</t>
         </is>
       </c>
       <c r="D979" t="inlineStr">
@@ -26864,17 +26864,17 @@
     <row r="980">
       <c r="A980" t="inlineStr">
         <is>
-          <t>kk_3800712629</t>
+          <t>kk_3793117898</t>
         </is>
       </c>
       <c r="B980" t="inlineStr">
         <is>
-          <t>01037690698</t>
+          <t>01052318168</t>
         </is>
       </c>
       <c r="C980" t="inlineStr">
         <is>
-          <t>258873</t>
+          <t>257099</t>
         </is>
       </c>
       <c r="D980" t="inlineStr">
@@ -26891,17 +26891,17 @@
     <row r="981">
       <c r="A981" t="inlineStr">
         <is>
-          <t>kk_3180854377</t>
+          <t>kk_3800712629</t>
         </is>
       </c>
       <c r="B981" t="inlineStr">
         <is>
-          <t>01031216377</t>
+          <t>01037690698</t>
         </is>
       </c>
       <c r="C981" t="inlineStr">
         <is>
-          <t>226467</t>
+          <t>258873</t>
         </is>
       </c>
       <c r="D981" t="inlineStr">
@@ -27836,54 +27836,54 @@
     <row r="1016">
       <c r="A1016" t="inlineStr">
         <is>
-          <t>kk_3955208505</t>
+          <t>kk_3919493388</t>
         </is>
       </c>
       <c r="B1016" t="inlineStr">
         <is>
-          <t>01084144311</t>
+          <t>01084315028</t>
         </is>
       </c>
       <c r="C1016" t="inlineStr">
         <is>
-          <t>270134</t>
+          <t>268572</t>
         </is>
       </c>
       <c r="D1016" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="E1016" t="inlineStr">
         <is>
-          <t>KAKAO_CH_MENU_0212_TITANIUM</t>
+          <t>Direct</t>
         </is>
       </c>
     </row>
     <row r="1017">
       <c r="A1017" t="inlineStr">
         <is>
-          <t>kk_3919493388</t>
+          <t>kk_3955208505</t>
         </is>
       </c>
       <c r="B1017" t="inlineStr">
         <is>
-          <t>01084315028</t>
+          <t>01084144311</t>
         </is>
       </c>
       <c r="C1017" t="inlineStr">
         <is>
-          <t>268572</t>
+          <t>270134</t>
         </is>
       </c>
       <c r="D1017" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E1017" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>KAKAO_CH_MENU_0212_TITANIUM</t>
         </is>
       </c>
     </row>
@@ -28457,54 +28457,54 @@
     <row r="1039">
       <c r="A1039" t="inlineStr">
         <is>
-          <t>kk_4841501713</t>
+          <t>ellieee</t>
         </is>
       </c>
       <c r="B1039" t="inlineStr">
         <is>
-          <t>01042996002</t>
+          <t>01098996425</t>
         </is>
       </c>
       <c r="C1039" t="inlineStr">
         <is>
-          <t>304195</t>
+          <t>203688</t>
         </is>
       </c>
       <c r="D1039" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E1039" t="inlineStr">
         <is>
-          <t>6968489536332</t>
+          <t>KAKAO_alimtalk</t>
         </is>
       </c>
     </row>
     <row r="1040">
       <c r="A1040" t="inlineStr">
         <is>
-          <t>ellieee</t>
+          <t>kk_4841501713</t>
         </is>
       </c>
       <c r="B1040" t="inlineStr">
         <is>
-          <t>01098996425</t>
+          <t>01042996002</t>
         </is>
       </c>
       <c r="C1040" t="inlineStr">
         <is>
-          <t>203688</t>
+          <t>304195</t>
         </is>
       </c>
       <c r="D1040" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E1040" t="inlineStr">
         <is>
-          <t>KAKAO_alimtalk</t>
+          <t>6968489536332</t>
         </is>
       </c>
     </row>
@@ -28592,54 +28592,54 @@
     <row r="1044">
       <c r="A1044" t="inlineStr">
         <is>
-          <t>kmh7710</t>
+          <t>kk_4375973589</t>
         </is>
       </c>
       <c r="B1044" t="inlineStr">
         <is>
-          <t>01077108716</t>
+          <t>01096223641</t>
         </is>
       </c>
       <c r="C1044" t="inlineStr">
         <is>
-          <t>164951</t>
+          <t>280163</t>
         </is>
       </c>
       <c r="D1044" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Organic Traffic</t>
         </is>
       </c>
       <c r="E1044" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0214_newyear</t>
+          <t>LMS_ECOM_familycoupon</t>
         </is>
       </c>
     </row>
     <row r="1045">
       <c r="A1045" t="inlineStr">
         <is>
-          <t>kk_4375973589</t>
+          <t>kmh7710</t>
         </is>
       </c>
       <c r="B1045" t="inlineStr">
         <is>
-          <t>01096223641</t>
+          <t>01077108716</t>
         </is>
       </c>
       <c r="C1045" t="inlineStr">
         <is>
-          <t>280163</t>
+          <t>164951</t>
         </is>
       </c>
       <c r="D1045" t="inlineStr">
         <is>
-          <t>Organic Traffic</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E1045" t="inlineStr">
         <is>
-          <t>LMS_ECOM_familycoupon</t>
+          <t>LMS_ECOM_0214_newyear</t>
         </is>
       </c>
     </row>
@@ -28700,71 +28700,71 @@
     <row r="1048">
       <c r="A1048" t="inlineStr">
         <is>
-          <t>kk_4844665214</t>
+          <t>kk_4843611952</t>
         </is>
       </c>
       <c r="B1048" t="inlineStr">
         <is>
-          <t>01033424745</t>
+          <t>01068610131</t>
         </is>
       </c>
       <c r="C1048" t="inlineStr">
         <is>
-          <t>304377</t>
+          <t>304327</t>
         </is>
       </c>
       <c r="D1048" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E1048" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>6968489536332</t>
         </is>
       </c>
     </row>
     <row r="1049">
       <c r="A1049" t="inlineStr">
         <is>
-          <t>kk_4843611952</t>
+          <t>kk_2954504655</t>
         </is>
       </c>
       <c r="B1049" t="inlineStr">
         <is>
-          <t>01068610131</t>
+          <t>01024942984</t>
         </is>
       </c>
       <c r="C1049" t="inlineStr">
         <is>
-          <t>304327</t>
+          <t>242733</t>
         </is>
       </c>
       <c r="D1049" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="E1049" t="inlineStr">
         <is>
-          <t>6968489536332</t>
+          <t>Direct</t>
         </is>
       </c>
     </row>
     <row r="1050">
       <c r="A1050" t="inlineStr">
         <is>
-          <t>kk_2954504655</t>
+          <t>kk_4844665214</t>
         </is>
       </c>
       <c r="B1050" t="inlineStr">
         <is>
-          <t>01024942984</t>
+          <t>01033424745</t>
         </is>
       </c>
       <c r="C1050" t="inlineStr">
         <is>
-          <t>242733</t>
+          <t>304377</t>
         </is>
       </c>
       <c r="D1050" t="inlineStr">
@@ -28835,17 +28835,17 @@
     <row r="1053">
       <c r="A1053" t="inlineStr">
         <is>
-          <t>kk_4839477951</t>
+          <t>kk_4840093815</t>
         </is>
       </c>
       <c r="B1053" t="inlineStr">
         <is>
-          <t>01020868012</t>
+          <t>01095450820</t>
         </is>
       </c>
       <c r="C1053" t="inlineStr">
         <is>
-          <t>304101</t>
+          <t>304126</t>
         </is>
       </c>
       <c r="D1053" t="inlineStr">
@@ -28855,24 +28855,24 @@
       </c>
       <c r="E1053" t="inlineStr">
         <is>
-          <t>6968489536332</t>
+          <t>EFW</t>
         </is>
       </c>
     </row>
     <row r="1054">
       <c r="A1054" t="inlineStr">
         <is>
-          <t>kk_4839544665</t>
+          <t>kk_4839477951</t>
         </is>
       </c>
       <c r="B1054" t="inlineStr">
         <is>
-          <t>01055350199</t>
+          <t>01020868012</t>
         </is>
       </c>
       <c r="C1054" t="inlineStr">
         <is>
-          <t>304104</t>
+          <t>304101</t>
         </is>
       </c>
       <c r="D1054" t="inlineStr">
@@ -28889,17 +28889,17 @@
     <row r="1055">
       <c r="A1055" t="inlineStr">
         <is>
-          <t>kk_4840093815</t>
+          <t>kk_4839544665</t>
         </is>
       </c>
       <c r="B1055" t="inlineStr">
         <is>
-          <t>01095450820</t>
+          <t>01055350199</t>
         </is>
       </c>
       <c r="C1055" t="inlineStr">
         <is>
-          <t>304126</t>
+          <t>304104</t>
         </is>
       </c>
       <c r="D1055" t="inlineStr">
@@ -28909,7 +28909,7 @@
       </c>
       <c r="E1055" t="inlineStr">
         <is>
-          <t>EFW</t>
+          <t>6968489536332</t>
         </is>
       </c>
     </row>
@@ -28997,108 +28997,108 @@
     <row r="1059">
       <c r="A1059" t="inlineStr">
         <is>
-          <t>kk_2800477789</t>
+          <t>kk_4843439707</t>
         </is>
       </c>
       <c r="B1059" t="inlineStr">
         <is>
-          <t>01035177105</t>
+          <t>01022248653</t>
         </is>
       </c>
       <c r="C1059" t="inlineStr">
         <is>
-          <t>211095</t>
+          <t>304310</t>
         </is>
       </c>
       <c r="D1059" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E1059" t="inlineStr">
         <is>
-          <t>KAKAO_alimtalk</t>
+          <t>6968489536332</t>
         </is>
       </c>
     </row>
     <row r="1060">
       <c r="A1060" t="inlineStr">
         <is>
-          <t>kk_4843439707</t>
+          <t>kk_2800477789</t>
         </is>
       </c>
       <c r="B1060" t="inlineStr">
         <is>
-          <t>01022248653</t>
+          <t>01035177105</t>
         </is>
       </c>
       <c r="C1060" t="inlineStr">
         <is>
-          <t>304310</t>
+          <t>211095</t>
         </is>
       </c>
       <c r="D1060" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E1060" t="inlineStr">
         <is>
-          <t>6968489536332</t>
+          <t>KAKAO_alimtalk</t>
         </is>
       </c>
     </row>
     <row r="1061">
       <c r="A1061" t="inlineStr">
         <is>
-          <t>dmsdud552</t>
+          <t>kk_4844530515</t>
         </is>
       </c>
       <c r="B1061" t="inlineStr">
         <is>
-          <t>01054633672</t>
+          <t>01054558799</t>
         </is>
       </c>
       <c r="C1061" t="inlineStr">
         <is>
-          <t>132110</t>
+          <t>304366</t>
         </is>
       </c>
       <c r="D1061" t="inlineStr">
         <is>
-          <t>Organic Traffic</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E1061" t="inlineStr">
         <is>
-          <t>(referral)</t>
+          <t>6968489536332</t>
         </is>
       </c>
     </row>
     <row r="1062">
       <c r="A1062" t="inlineStr">
         <is>
-          <t>kk_4844530515</t>
+          <t>dmsdud552</t>
         </is>
       </c>
       <c r="B1062" t="inlineStr">
         <is>
-          <t>01054558799</t>
+          <t>01054633672</t>
         </is>
       </c>
       <c r="C1062" t="inlineStr">
         <is>
-          <t>304366</t>
+          <t>132110</t>
         </is>
       </c>
       <c r="D1062" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Organic Traffic</t>
         </is>
       </c>
       <c r="E1062" t="inlineStr">
         <is>
-          <t>6968489536332</t>
+          <t>(referral)</t>
         </is>
       </c>
     </row>
@@ -29132,54 +29132,54 @@
     <row r="1064">
       <c r="A1064" t="inlineStr">
         <is>
-          <t>kk_4543882817</t>
+          <t>kk_4839643736</t>
         </is>
       </c>
       <c r="B1064" t="inlineStr">
         <is>
-          <t>01023875300</t>
+          <t>01063617035</t>
         </is>
       </c>
       <c r="C1064" t="inlineStr">
         <is>
-          <t>287573</t>
+          <t>304107</t>
         </is>
       </c>
       <c r="D1064" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E1064" t="inlineStr">
         <is>
-          <t>미분류</t>
+          <t>naver_brandsearch_mobile</t>
         </is>
       </c>
     </row>
     <row r="1065">
       <c r="A1065" t="inlineStr">
         <is>
-          <t>kk_4839643736</t>
+          <t>kk_4543882817</t>
         </is>
       </c>
       <c r="B1065" t="inlineStr">
         <is>
-          <t>01063617035</t>
+          <t>01023875300</t>
         </is>
       </c>
       <c r="C1065" t="inlineStr">
         <is>
-          <t>304107</t>
+          <t>287573</t>
         </is>
       </c>
       <c r="D1065" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="E1065" t="inlineStr">
         <is>
-          <t>naver_brandsearch_mobile</t>
+          <t>미분류</t>
         </is>
       </c>
     </row>
@@ -29294,125 +29294,125 @@
     <row r="1070">
       <c r="A1070" t="inlineStr">
         <is>
-          <t>kk_4843847622</t>
+          <t>kk_4845173313</t>
         </is>
       </c>
       <c r="B1070" t="inlineStr">
         <is>
-          <t>01046990393</t>
+          <t>01024436341</t>
         </is>
       </c>
       <c r="C1070" t="inlineStr">
         <is>
-          <t>304336</t>
+          <t>304397</t>
         </is>
       </c>
       <c r="D1070" t="inlineStr">
         <is>
-          <t>Organic Traffic</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E1070" t="inlineStr">
         <is>
-          <t>(organic)</t>
+          <t>6968489536332</t>
         </is>
       </c>
     </row>
     <row r="1071">
       <c r="A1071" t="inlineStr">
         <is>
-          <t>kk_4844453283</t>
+          <t>kk_4843926419</t>
         </is>
       </c>
       <c r="B1071" t="inlineStr">
         <is>
-          <t>01090262556</t>
+          <t>01034583174</t>
         </is>
       </c>
       <c r="C1071" t="inlineStr">
         <is>
-          <t>304360</t>
+          <t>304338</t>
         </is>
       </c>
       <c r="D1071" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Official SNS</t>
         </is>
       </c>
       <c r="E1071" t="inlineStr">
         <is>
-          <t>6968489536332</t>
+          <t>EFW_04</t>
         </is>
       </c>
     </row>
     <row r="1072">
       <c r="A1072" t="inlineStr">
         <is>
-          <t>kk_4843926419</t>
+          <t>kk_4844453283</t>
         </is>
       </c>
       <c r="B1072" t="inlineStr">
         <is>
-          <t>01034583174</t>
+          <t>01090262556</t>
         </is>
       </c>
       <c r="C1072" t="inlineStr">
         <is>
-          <t>304338</t>
+          <t>304360</t>
         </is>
       </c>
       <c r="D1072" t="inlineStr">
         <is>
-          <t>Official SNS</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E1072" t="inlineStr">
         <is>
-          <t>EFW_04</t>
+          <t>6968489536332</t>
         </is>
       </c>
     </row>
     <row r="1073">
       <c r="A1073" t="inlineStr">
         <is>
-          <t>kk_4845173313</t>
+          <t>kk_4843847622</t>
         </is>
       </c>
       <c r="B1073" t="inlineStr">
         <is>
-          <t>01024436341</t>
+          <t>01046990393</t>
         </is>
       </c>
       <c r="C1073" t="inlineStr">
         <is>
-          <t>304397</t>
+          <t>304336</t>
         </is>
       </c>
       <c r="D1073" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Organic Traffic</t>
         </is>
       </c>
       <c r="E1073" t="inlineStr">
         <is>
-          <t>6968489536332</t>
+          <t>(organic)</t>
         </is>
       </c>
     </row>
     <row r="1074">
       <c r="A1074" t="inlineStr">
         <is>
-          <t>kyoungs424</t>
+          <t>kk_2961062530</t>
         </is>
       </c>
       <c r="B1074" t="inlineStr">
         <is>
-          <t>01041509204</t>
+          <t>01050052823</t>
         </is>
       </c>
       <c r="C1074" t="inlineStr">
         <is>
-          <t>153760</t>
+          <t>217199</t>
         </is>
       </c>
       <c r="D1074" t="inlineStr">
@@ -29422,24 +29422,24 @@
       </c>
       <c r="E1074" t="inlineStr">
         <is>
-          <t>KAKAO_alimtalk</t>
+          <t>KAKAO_CH_MENU_0317_S26NEW</t>
         </is>
       </c>
     </row>
     <row r="1075">
       <c r="A1075" t="inlineStr">
         <is>
-          <t>kk_2961062530</t>
+          <t>kyoungs424</t>
         </is>
       </c>
       <c r="B1075" t="inlineStr">
         <is>
-          <t>01050052823</t>
+          <t>01041509204</t>
         </is>
       </c>
       <c r="C1075" t="inlineStr">
         <is>
-          <t>217199</t>
+          <t>153760</t>
         </is>
       </c>
       <c r="D1075" t="inlineStr">
@@ -29449,7 +29449,7 @@
       </c>
       <c r="E1075" t="inlineStr">
         <is>
-          <t>KAKAO_CH_MENU_0317_S26NEW</t>
+          <t>KAKAO_alimtalk</t>
         </is>
       </c>
     </row>
@@ -29564,108 +29564,108 @@
     <row r="1080">
       <c r="A1080" t="inlineStr">
         <is>
-          <t>kk_4518898382</t>
+          <t>kphilius</t>
         </is>
       </c>
       <c r="B1080" t="inlineStr">
         <is>
-          <t>01063727378</t>
+          <t>01026117522</t>
         </is>
       </c>
       <c r="C1080" t="inlineStr">
         <is>
-          <t>286129</t>
+          <t>217796</t>
         </is>
       </c>
       <c r="D1080" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="E1080" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0214_newyear</t>
+          <t>etc</t>
         </is>
       </c>
     </row>
     <row r="1081">
       <c r="A1081" t="inlineStr">
         <is>
-          <t>kphilius</t>
+          <t>kk_4518898382</t>
         </is>
       </c>
       <c r="B1081" t="inlineStr">
         <is>
-          <t>01026117522</t>
+          <t>01063727378</t>
         </is>
       </c>
       <c r="C1081" t="inlineStr">
         <is>
-          <t>217796</t>
+          <t>286129</t>
         </is>
       </c>
       <c r="D1081" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E1081" t="inlineStr">
         <is>
-          <t>etc</t>
+          <t>LMS_ECOM_0214_newyear</t>
         </is>
       </c>
     </row>
     <row r="1082">
       <c r="A1082" t="inlineStr">
         <is>
-          <t>kk_3601210201</t>
+          <t>chibird</t>
         </is>
       </c>
       <c r="B1082" t="inlineStr">
         <is>
-          <t>01092460423</t>
+          <t>01031187674</t>
         </is>
       </c>
       <c r="C1082" t="inlineStr">
         <is>
-          <t>247035</t>
+          <t>219288</t>
         </is>
       </c>
       <c r="D1082" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E1082" t="inlineStr">
         <is>
-          <t>미분류</t>
+          <t>sa</t>
         </is>
       </c>
     </row>
     <row r="1083">
       <c r="A1083" t="inlineStr">
         <is>
-          <t>chibird</t>
+          <t>kk_3601210201</t>
         </is>
       </c>
       <c r="B1083" t="inlineStr">
         <is>
-          <t>01031187674</t>
+          <t>01092460423</t>
         </is>
       </c>
       <c r="C1083" t="inlineStr">
         <is>
-          <t>219288</t>
+          <t>247035</t>
         </is>
       </c>
       <c r="D1083" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="E1083" t="inlineStr">
         <is>
-          <t>sa</t>
+          <t>미분류</t>
         </is>
       </c>
     </row>
@@ -29969,54 +29969,54 @@
     <row r="1095">
       <c r="A1095" t="inlineStr">
         <is>
-          <t>kk_4844609437</t>
+          <t>kk_4844452226</t>
         </is>
       </c>
       <c r="B1095" t="inlineStr">
         <is>
-          <t>01046808931</t>
+          <t>01096801866</t>
         </is>
       </c>
       <c r="C1095" t="inlineStr">
         <is>
-          <t>304372</t>
+          <t>304359</t>
         </is>
       </c>
       <c r="D1095" t="inlineStr">
         <is>
-          <t>Official SNS</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E1095" t="inlineStr">
         <is>
-          <t>(referral)</t>
+          <t>6968489536332</t>
         </is>
       </c>
     </row>
     <row r="1096">
       <c r="A1096" t="inlineStr">
         <is>
-          <t>kk_4844452226</t>
+          <t>kk_4844609437</t>
         </is>
       </c>
       <c r="B1096" t="inlineStr">
         <is>
-          <t>01096801866</t>
+          <t>01046808931</t>
         </is>
       </c>
       <c r="C1096" t="inlineStr">
         <is>
-          <t>304359</t>
+          <t>304372</t>
         </is>
       </c>
       <c r="D1096" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Official SNS</t>
         </is>
       </c>
       <c r="E1096" t="inlineStr">
         <is>
-          <t>6968489536332</t>
+          <t>(referral)</t>
         </is>
       </c>
     </row>
@@ -30077,17 +30077,17 @@
     <row r="1099">
       <c r="A1099" t="inlineStr">
         <is>
-          <t>kk_2750710108</t>
+          <t>jsb0425</t>
         </is>
       </c>
       <c r="B1099" t="inlineStr">
         <is>
-          <t>01062707475</t>
+          <t>01037883670</t>
         </is>
       </c>
       <c r="C1099" t="inlineStr">
         <is>
-          <t>207211</t>
+          <t>104766</t>
         </is>
       </c>
       <c r="D1099" t="inlineStr">
@@ -30131,54 +30131,54 @@
     <row r="1101">
       <c r="A1101" t="inlineStr">
         <is>
-          <t>kk_4841278242</t>
+          <t>kk_3977730443</t>
         </is>
       </c>
       <c r="B1101" t="inlineStr">
         <is>
-          <t>01046197965</t>
+          <t>01064291828</t>
         </is>
       </c>
       <c r="C1101" t="inlineStr">
         <is>
-          <t>304190</t>
+          <t>271278</t>
         </is>
       </c>
       <c r="D1101" t="inlineStr">
         <is>
-          <t>Organic Traffic</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E1101" t="inlineStr">
         <is>
-          <t>(referral)</t>
+          <t>naver_brandsearch_mobile</t>
         </is>
       </c>
     </row>
     <row r="1102">
       <c r="A1102" t="inlineStr">
         <is>
-          <t>jsb0425</t>
+          <t>kk_4841278242</t>
         </is>
       </c>
       <c r="B1102" t="inlineStr">
         <is>
-          <t>01037883670</t>
+          <t>01046197965</t>
         </is>
       </c>
       <c r="C1102" t="inlineStr">
         <is>
-          <t>104766</t>
+          <t>304190</t>
         </is>
       </c>
       <c r="D1102" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>Organic Traffic</t>
         </is>
       </c>
       <c r="E1102" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>(referral)</t>
         </is>
       </c>
     </row>
@@ -30212,27 +30212,27 @@
     <row r="1104">
       <c r="A1104" t="inlineStr">
         <is>
-          <t>kk_3977730443</t>
+          <t>kk_2750710108</t>
         </is>
       </c>
       <c r="B1104" t="inlineStr">
         <is>
-          <t>01064291828</t>
+          <t>01062707475</t>
         </is>
       </c>
       <c r="C1104" t="inlineStr">
         <is>
-          <t>271278</t>
+          <t>207211</t>
         </is>
       </c>
       <c r="D1104" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="E1104" t="inlineStr">
         <is>
-          <t>naver_brandsearch_mobile</t>
+          <t>Direct</t>
         </is>
       </c>
     </row>
@@ -30320,17 +30320,17 @@
     <row r="1108">
       <c r="A1108" t="inlineStr">
         <is>
-          <t>kk_3776403631</t>
+          <t>kimchhgood</t>
         </is>
       </c>
       <c r="B1108" t="inlineStr">
         <is>
-          <t>01034755755</t>
+          <t>01092133961</t>
         </is>
       </c>
       <c r="C1108" t="inlineStr">
         <is>
-          <t>255908</t>
+          <t>53493</t>
         </is>
       </c>
       <c r="D1108" t="inlineStr">
@@ -30340,24 +30340,24 @@
       </c>
       <c r="E1108" t="inlineStr">
         <is>
-          <t>KAKAO_alimtalk</t>
+          <t>EDM_TOP</t>
         </is>
       </c>
     </row>
     <row r="1109">
       <c r="A1109" t="inlineStr">
         <is>
-          <t>kimchhgood</t>
+          <t>kk_3776403631</t>
         </is>
       </c>
       <c r="B1109" t="inlineStr">
         <is>
-          <t>01092133961</t>
+          <t>01034755755</t>
         </is>
       </c>
       <c r="C1109" t="inlineStr">
         <is>
-          <t>53493</t>
+          <t>255908</t>
         </is>
       </c>
       <c r="D1109" t="inlineStr">
@@ -30367,7 +30367,7 @@
       </c>
       <c r="E1109" t="inlineStr">
         <is>
-          <t>EDM_TOP</t>
+          <t>KAKAO_alimtalk</t>
         </is>
       </c>
     </row>
@@ -30401,27 +30401,27 @@
     <row r="1111">
       <c r="A1111" t="inlineStr">
         <is>
-          <t>kk_4351060530</t>
+          <t>kk_4375683656</t>
         </is>
       </c>
       <c r="B1111" t="inlineStr">
         <is>
-          <t>01037920661</t>
+          <t>01090522987</t>
         </is>
       </c>
       <c r="C1111" t="inlineStr">
         <is>
-          <t>279264</t>
+          <t>280157</t>
         </is>
       </c>
       <c r="D1111" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="E1111" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Direct</t>
         </is>
       </c>
     </row>
@@ -30482,27 +30482,27 @@
     <row r="1114">
       <c r="A1114" t="inlineStr">
         <is>
-          <t>kk_4375683656</t>
+          <t>kk_4351060530</t>
         </is>
       </c>
       <c r="B1114" t="inlineStr">
         <is>
-          <t>01090522987</t>
+          <t>01037920661</t>
         </is>
       </c>
       <c r="C1114" t="inlineStr">
         <is>
-          <t>280157</t>
+          <t>279264</t>
         </is>
       </c>
       <c r="D1114" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E1114" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>Paid Ad</t>
         </is>
       </c>
     </row>
@@ -30536,17 +30536,17 @@
     <row r="1116">
       <c r="A1116" t="inlineStr">
         <is>
-          <t>kk_4846761310</t>
+          <t>willper</t>
         </is>
       </c>
       <c r="B1116" t="inlineStr">
         <is>
-          <t>01091189951</t>
+          <t>01085343440</t>
         </is>
       </c>
       <c r="C1116" t="inlineStr">
         <is>
-          <t>304464</t>
+          <t>304408</t>
         </is>
       </c>
       <c r="D1116" t="inlineStr">
@@ -30556,24 +30556,24 @@
       </c>
       <c r="E1116" t="inlineStr">
         <is>
-          <t>naver_brandsearch_mobile</t>
+          <t>6968489536332</t>
         </is>
       </c>
     </row>
     <row r="1117">
       <c r="A1117" t="inlineStr">
         <is>
-          <t>willper</t>
+          <t>kk_4846761310</t>
         </is>
       </c>
       <c r="B1117" t="inlineStr">
         <is>
-          <t>01085343440</t>
+          <t>01091189951</t>
         </is>
       </c>
       <c r="C1117" t="inlineStr">
         <is>
-          <t>304408</t>
+          <t>304464</t>
         </is>
       </c>
       <c r="D1117" t="inlineStr">
@@ -30583,7 +30583,7 @@
       </c>
       <c r="E1117" t="inlineStr">
         <is>
-          <t>6968489536332</t>
+          <t>naver_brandsearch_mobile</t>
         </is>
       </c>
     </row>
@@ -30671,54 +30671,54 @@
     <row r="1121">
       <c r="A1121" t="inlineStr">
         <is>
-          <t>kk_4841799872</t>
+          <t>kk_4703272205</t>
         </is>
       </c>
       <c r="B1121" t="inlineStr">
         <is>
-          <t>01023236956</t>
+          <t>01062682325</t>
         </is>
       </c>
       <c r="C1121" t="inlineStr">
         <is>
-          <t>304205</t>
+          <t>296093</t>
         </is>
       </c>
       <c r="D1121" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E1121" t="inlineStr">
         <is>
-          <t>컬럼비아_DPA_240530</t>
+          <t>LMS_ECOM_0410exclusive2</t>
         </is>
       </c>
     </row>
     <row r="1122">
       <c r="A1122" t="inlineStr">
         <is>
-          <t>kk_4703272205</t>
+          <t>kk_4841799872</t>
         </is>
       </c>
       <c r="B1122" t="inlineStr">
         <is>
-          <t>01062682325</t>
+          <t>01023236956</t>
         </is>
       </c>
       <c r="C1122" t="inlineStr">
         <is>
-          <t>296093</t>
+          <t>304205</t>
         </is>
       </c>
       <c r="D1122" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E1122" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0410exclusive2</t>
+          <t>컬럼비아_DPA_240530</t>
         </is>
       </c>
     </row>
@@ -30752,54 +30752,54 @@
     <row r="1124">
       <c r="A1124" t="inlineStr">
         <is>
-          <t>lolia875</t>
+          <t>sbhbi</t>
         </is>
       </c>
       <c r="B1124" t="inlineStr">
         <is>
-          <t>01067138715</t>
+          <t>01047153767</t>
         </is>
       </c>
       <c r="C1124" t="inlineStr">
         <is>
-          <t>161251</t>
+          <t>174291</t>
         </is>
       </c>
       <c r="D1124" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="E1124" t="inlineStr">
         <is>
-          <t>6968489536332</t>
+          <t>Direct</t>
         </is>
       </c>
     </row>
     <row r="1125">
       <c r="A1125" t="inlineStr">
         <is>
-          <t>sbhbi</t>
+          <t>lolia875</t>
         </is>
       </c>
       <c r="B1125" t="inlineStr">
         <is>
-          <t>01047153767</t>
+          <t>01067138715</t>
         </is>
       </c>
       <c r="C1125" t="inlineStr">
         <is>
-          <t>174291</t>
+          <t>161251</t>
         </is>
       </c>
       <c r="D1125" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E1125" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>6968489536332</t>
         </is>
       </c>
     </row>
@@ -30833,54 +30833,54 @@
     <row r="1127">
       <c r="A1127" t="inlineStr">
         <is>
-          <t>kk_3393400723</t>
+          <t>kk_3140575996</t>
         </is>
       </c>
       <c r="B1127" t="inlineStr">
         <is>
-          <t>01089700082</t>
+          <t>01098546266</t>
         </is>
       </c>
       <c r="C1127" t="inlineStr">
         <is>
-          <t>241049</t>
+          <t>222820</t>
         </is>
       </c>
       <c r="D1127" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E1127" t="inlineStr">
         <is>
-          <t>KAKAO_alimtalk</t>
+          <t>naver_brandsearch_mobile</t>
         </is>
       </c>
     </row>
     <row r="1128">
       <c r="A1128" t="inlineStr">
         <is>
-          <t>kk_3140575996</t>
+          <t>kk_3393400723</t>
         </is>
       </c>
       <c r="B1128" t="inlineStr">
         <is>
-          <t>01098546266</t>
+          <t>01089700082</t>
         </is>
       </c>
       <c r="C1128" t="inlineStr">
         <is>
-          <t>222820</t>
+          <t>241049</t>
         </is>
       </c>
       <c r="D1128" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E1128" t="inlineStr">
         <is>
-          <t>naver_brandsearch_mobile</t>
+          <t>KAKAO_alimtalk</t>
         </is>
       </c>
     </row>
@@ -30968,17 +30968,17 @@
     <row r="1132">
       <c r="A1132" t="inlineStr">
         <is>
-          <t>hyoju1981</t>
+          <t>kk_2750963357</t>
         </is>
       </c>
       <c r="B1132" t="inlineStr">
         <is>
-          <t>01045321445</t>
+          <t>01033989099</t>
         </is>
       </c>
       <c r="C1132" t="inlineStr">
         <is>
-          <t>107362</t>
+          <t>207617</t>
         </is>
       </c>
       <c r="D1132" t="inlineStr">
@@ -31022,17 +31022,17 @@
     <row r="1134">
       <c r="A1134" t="inlineStr">
         <is>
-          <t>kk_2750963357</t>
+          <t>hyoju1981</t>
         </is>
       </c>
       <c r="B1134" t="inlineStr">
         <is>
-          <t>01033989099</t>
+          <t>01045321445</t>
         </is>
       </c>
       <c r="C1134" t="inlineStr">
         <is>
-          <t>207617</t>
+          <t>107362</t>
         </is>
       </c>
       <c r="D1134" t="inlineStr">
@@ -31076,27 +31076,27 @@
     <row r="1136">
       <c r="A1136" t="inlineStr">
         <is>
-          <t>kk_3792750872</t>
+          <t>kk_4848093455</t>
         </is>
       </c>
       <c r="B1136" t="inlineStr">
         <is>
-          <t>01084382636</t>
+          <t>01023043154</t>
         </is>
       </c>
       <c r="C1136" t="inlineStr">
         <is>
-          <t>256807</t>
+          <t>304517</t>
         </is>
       </c>
       <c r="D1136" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E1136" t="inlineStr">
         <is>
-          <t>KAKAO_CH_MENU_0211_NEW_MEN</t>
+          <t>6968489536332</t>
         </is>
       </c>
     </row>
@@ -31130,71 +31130,71 @@
     <row r="1138">
       <c r="A1138" t="inlineStr">
         <is>
-          <t>kk_4848093455</t>
+          <t>kk_3792750872</t>
         </is>
       </c>
       <c r="B1138" t="inlineStr">
         <is>
-          <t>01023043154</t>
+          <t>01084382636</t>
         </is>
       </c>
       <c r="C1138" t="inlineStr">
         <is>
-          <t>304517</t>
+          <t>256807</t>
         </is>
       </c>
       <c r="D1138" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E1138" t="inlineStr">
         <is>
-          <t>6968489536332</t>
+          <t>KAKAO_CH_MENU_0211_NEW_MEN</t>
         </is>
       </c>
     </row>
     <row r="1139">
       <c r="A1139" t="inlineStr">
         <is>
-          <t>chpuss74</t>
+          <t>kk_2788668233</t>
         </is>
       </c>
       <c r="B1139" t="inlineStr">
         <is>
-          <t>01035361091</t>
+          <t>01041696139</t>
         </is>
       </c>
       <c r="C1139" t="inlineStr">
         <is>
-          <t>154462</t>
+          <t>210002</t>
         </is>
       </c>
       <c r="D1139" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E1139" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>6968489536332</t>
         </is>
       </c>
     </row>
     <row r="1140">
       <c r="A1140" t="inlineStr">
         <is>
-          <t>imgain0422</t>
+          <t>ch5115</t>
         </is>
       </c>
       <c r="B1140" t="inlineStr">
         <is>
-          <t>01029135546</t>
+          <t>01084479339</t>
         </is>
       </c>
       <c r="C1140" t="inlineStr">
         <is>
-          <t>181451</t>
+          <t>240557</t>
         </is>
       </c>
       <c r="D1140" t="inlineStr">
@@ -31211,44 +31211,44 @@
     <row r="1141">
       <c r="A1141" t="inlineStr">
         <is>
-          <t>kk_4845661756</t>
+          <t>imgain0422</t>
         </is>
       </c>
       <c r="B1141" t="inlineStr">
         <is>
-          <t>01095936572</t>
+          <t>01029135546</t>
         </is>
       </c>
       <c r="C1141" t="inlineStr">
         <is>
-          <t>304422</t>
+          <t>181451</t>
         </is>
       </c>
       <c r="D1141" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="E1141" t="inlineStr">
         <is>
-          <t>6968489536332</t>
+          <t>Direct</t>
         </is>
       </c>
     </row>
     <row r="1142">
       <c r="A1142" t="inlineStr">
         <is>
-          <t>ch5115</t>
+          <t>chpuss74</t>
         </is>
       </c>
       <c r="B1142" t="inlineStr">
         <is>
-          <t>01084479339</t>
+          <t>01035361091</t>
         </is>
       </c>
       <c r="C1142" t="inlineStr">
         <is>
-          <t>240557</t>
+          <t>154462</t>
         </is>
       </c>
       <c r="D1142" t="inlineStr">
@@ -31265,17 +31265,17 @@
     <row r="1143">
       <c r="A1143" t="inlineStr">
         <is>
-          <t>kk_2788668233</t>
+          <t>kk_4846729102</t>
         </is>
       </c>
       <c r="B1143" t="inlineStr">
         <is>
-          <t>01041696139</t>
+          <t>01084771303</t>
         </is>
       </c>
       <c r="C1143" t="inlineStr">
         <is>
-          <t>210002</t>
+          <t>304461</t>
         </is>
       </c>
       <c r="D1143" t="inlineStr">
@@ -31319,17 +31319,17 @@
     <row r="1145">
       <c r="A1145" t="inlineStr">
         <is>
-          <t>kk_4846729102</t>
+          <t>kk_4845661756</t>
         </is>
       </c>
       <c r="B1145" t="inlineStr">
         <is>
-          <t>01084771303</t>
+          <t>01095936572</t>
         </is>
       </c>
       <c r="C1145" t="inlineStr">
         <is>
-          <t>304461</t>
+          <t>304422</t>
         </is>
       </c>
       <c r="D1145" t="inlineStr">
@@ -31346,27 +31346,27 @@
     <row r="1146">
       <c r="A1146" t="inlineStr">
         <is>
-          <t>kjhk5404</t>
+          <t>kk_4844076820</t>
         </is>
       </c>
       <c r="B1146" t="inlineStr">
         <is>
-          <t>01027390700</t>
+          <t>01091346366</t>
         </is>
       </c>
       <c r="C1146" t="inlineStr">
         <is>
-          <t>280120</t>
+          <t>304343</t>
         </is>
       </c>
       <c r="D1146" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E1146" t="inlineStr">
         <is>
-          <t>KAKAO_alimtalk</t>
+          <t>6968489536332</t>
         </is>
       </c>
     </row>
@@ -31400,206 +31400,206 @@
     <row r="1148">
       <c r="A1148" t="inlineStr">
         <is>
-          <t>kk_3242479813</t>
+          <t>goawind</t>
         </is>
       </c>
       <c r="B1148" t="inlineStr">
         <is>
-          <t>01040431115</t>
+          <t>01032738938</t>
         </is>
       </c>
       <c r="C1148" t="inlineStr">
         <is>
-          <t>234768</t>
+          <t>232021</t>
         </is>
       </c>
       <c r="D1148" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="E1148" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0410exclusive2</t>
+          <t>Direct</t>
         </is>
       </c>
     </row>
     <row r="1149">
       <c r="A1149" t="inlineStr">
         <is>
-          <t>kk_2775500473</t>
+          <t>kk_3242479813</t>
         </is>
       </c>
       <c r="B1149" t="inlineStr">
         <is>
-          <t>01045659020</t>
+          <t>01040431115</t>
         </is>
       </c>
       <c r="C1149" t="inlineStr">
         <is>
-          <t>209371</t>
+          <t>234768</t>
         </is>
       </c>
       <c r="D1149" t="inlineStr">
         <is>
-          <t>Organic Traffic</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E1149" t="inlineStr">
         <is>
-          <t>(referral)</t>
+          <t>LMS_ECOM_0410exclusive2</t>
         </is>
       </c>
     </row>
     <row r="1150">
       <c r="A1150" t="inlineStr">
         <is>
-          <t>goawind</t>
+          <t>kjhk5404</t>
         </is>
       </c>
       <c r="B1150" t="inlineStr">
         <is>
-          <t>01032738938</t>
+          <t>01027390700</t>
         </is>
       </c>
       <c r="C1150" t="inlineStr">
         <is>
-          <t>232021</t>
+          <t>280120</t>
         </is>
       </c>
       <c r="D1150" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E1150" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>KAKAO_alimtalk</t>
         </is>
       </c>
     </row>
     <row r="1151">
       <c r="A1151" t="inlineStr">
         <is>
-          <t>kk_4844076820</t>
+          <t>kk_2775500473</t>
         </is>
       </c>
       <c r="B1151" t="inlineStr">
         <is>
-          <t>01091346366</t>
+          <t>01045659020</t>
         </is>
       </c>
       <c r="C1151" t="inlineStr">
         <is>
-          <t>304343</t>
+          <t>209371</t>
         </is>
       </c>
       <c r="D1151" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Organic Traffic</t>
         </is>
       </c>
       <c r="E1151" t="inlineStr">
         <is>
-          <t>6968489536332</t>
+          <t>(referral)</t>
         </is>
       </c>
     </row>
     <row r="1152">
       <c r="A1152" t="inlineStr">
         <is>
-          <t>kk_4522711623</t>
+          <t>kk_4434329905</t>
         </is>
       </c>
       <c r="B1152" t="inlineStr">
         <is>
-          <t>01089870313</t>
+          <t>01071724035</t>
         </is>
       </c>
       <c r="C1152" t="inlineStr">
         <is>
-          <t>286306</t>
+          <t>281922</t>
         </is>
       </c>
       <c r="D1152" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E1152" t="inlineStr">
         <is>
-          <t>6968489536332</t>
+          <t>Email_mkt</t>
         </is>
       </c>
     </row>
     <row r="1153">
       <c r="A1153" t="inlineStr">
         <is>
-          <t>kk_4434329905</t>
+          <t>kk_4522711623</t>
         </is>
       </c>
       <c r="B1153" t="inlineStr">
         <is>
-          <t>01071724035</t>
+          <t>01089870313</t>
         </is>
       </c>
       <c r="C1153" t="inlineStr">
         <is>
-          <t>281922</t>
+          <t>286306</t>
         </is>
       </c>
       <c r="D1153" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E1153" t="inlineStr">
         <is>
-          <t>Email_mkt</t>
+          <t>6968489536332</t>
         </is>
       </c>
     </row>
     <row r="1154">
       <c r="A1154" t="inlineStr">
         <is>
-          <t>w0309</t>
+          <t>kk_4841778210</t>
         </is>
       </c>
       <c r="B1154" t="inlineStr">
         <is>
-          <t>01053481702</t>
+          <t>01087814274</t>
         </is>
       </c>
       <c r="C1154" t="inlineStr">
         <is>
-          <t>126315</t>
+          <t>304202</t>
         </is>
       </c>
       <c r="D1154" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E1154" t="inlineStr">
         <is>
-          <t>Email_mkt</t>
+          <t>naver_brandsearch_mobile</t>
         </is>
       </c>
     </row>
     <row r="1155">
       <c r="A1155" t="inlineStr">
         <is>
-          <t>kk_4841778210</t>
+          <t>kk_4840817001</t>
         </is>
       </c>
       <c r="B1155" t="inlineStr">
         <is>
-          <t>01087814274</t>
+          <t>01085963383</t>
         </is>
       </c>
       <c r="C1155" t="inlineStr">
         <is>
-          <t>304202</t>
+          <t>304168</t>
         </is>
       </c>
       <c r="D1155" t="inlineStr">
@@ -31609,88 +31609,88 @@
       </c>
       <c r="E1155" t="inlineStr">
         <is>
-          <t>naver_brandsearch_mobile</t>
+          <t>6968489536332</t>
         </is>
       </c>
     </row>
     <row r="1156">
       <c r="A1156" t="inlineStr">
         <is>
-          <t>kk_4840817001</t>
+          <t>w0309</t>
         </is>
       </c>
       <c r="B1156" t="inlineStr">
         <is>
-          <t>01085963383</t>
+          <t>01053481702</t>
         </is>
       </c>
       <c r="C1156" t="inlineStr">
         <is>
-          <t>304168</t>
+          <t>126315</t>
         </is>
       </c>
       <c r="D1156" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E1156" t="inlineStr">
         <is>
-          <t>6968489536332</t>
+          <t>Email_mkt</t>
         </is>
       </c>
     </row>
     <row r="1157">
       <c r="A1157" t="inlineStr">
         <is>
-          <t>z090909x</t>
+          <t>ssama</t>
         </is>
       </c>
       <c r="B1157" t="inlineStr">
         <is>
-          <t>01092058111</t>
+          <t>01056271982</t>
         </is>
       </c>
       <c r="C1157" t="inlineStr">
         <is>
-          <t>113003</t>
+          <t>47874</t>
         </is>
       </c>
       <c r="D1157" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E1157" t="inlineStr">
         <is>
-          <t>6968489536332</t>
+          <t>LMS_ECOM_0410exclusive2</t>
         </is>
       </c>
     </row>
     <row r="1158">
       <c r="A1158" t="inlineStr">
         <is>
-          <t>xoxoie2</t>
+          <t>z090909x</t>
         </is>
       </c>
       <c r="B1158" t="inlineStr">
         <is>
-          <t>01043560834</t>
+          <t>01092058111</t>
         </is>
       </c>
       <c r="C1158" t="inlineStr">
         <is>
-          <t>304072</t>
+          <t>113003</t>
         </is>
       </c>
       <c r="D1158" t="inlineStr">
         <is>
-          <t>Official SNS</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E1158" t="inlineStr">
         <is>
-          <t>EFW_04</t>
+          <t>6968489536332</t>
         </is>
       </c>
     </row>
@@ -31751,71 +31751,71 @@
     <row r="1161">
       <c r="A1161" t="inlineStr">
         <is>
-          <t>ssama</t>
+          <t>kk_4840045474</t>
         </is>
       </c>
       <c r="B1161" t="inlineStr">
         <is>
-          <t>01056271982</t>
+          <t>01096310429</t>
         </is>
       </c>
       <c r="C1161" t="inlineStr">
         <is>
-          <t>47874</t>
+          <t>304122</t>
         </is>
       </c>
       <c r="D1161" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E1161" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0410exclusive2</t>
+          <t>6968489536332</t>
         </is>
       </c>
     </row>
     <row r="1162">
       <c r="A1162" t="inlineStr">
         <is>
-          <t>kk_4840045474</t>
+          <t>gus7526</t>
         </is>
       </c>
       <c r="B1162" t="inlineStr">
         <is>
-          <t>01096310429</t>
+          <t>01050931023</t>
         </is>
       </c>
       <c r="C1162" t="inlineStr">
         <is>
-          <t>304122</t>
+          <t>140860</t>
         </is>
       </c>
       <c r="D1162" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E1162" t="inlineStr">
         <is>
-          <t>6968489536332</t>
+          <t>LMS_ECOM_0410exclusive2</t>
         </is>
       </c>
     </row>
     <row r="1163">
       <c r="A1163" t="inlineStr">
         <is>
-          <t>gus7526</t>
+          <t>kk_4228106377</t>
         </is>
       </c>
       <c r="B1163" t="inlineStr">
         <is>
-          <t>01050931023</t>
+          <t>01063165271</t>
         </is>
       </c>
       <c r="C1163" t="inlineStr">
         <is>
-          <t>140860</t>
+          <t>273193</t>
         </is>
       </c>
       <c r="D1163" t="inlineStr">
@@ -31832,108 +31832,108 @@
     <row r="1164">
       <c r="A1164" t="inlineStr">
         <is>
-          <t>kk_4228106377</t>
+          <t>xoxoie2</t>
         </is>
       </c>
       <c r="B1164" t="inlineStr">
         <is>
-          <t>01063165271</t>
+          <t>01043560834</t>
         </is>
       </c>
       <c r="C1164" t="inlineStr">
         <is>
-          <t>273193</t>
+          <t>304072</t>
         </is>
       </c>
       <c r="D1164" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Official SNS</t>
         </is>
       </c>
       <c r="E1164" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0410exclusive2</t>
+          <t>EFW_04</t>
         </is>
       </c>
     </row>
     <row r="1165">
       <c r="A1165" t="inlineStr">
         <is>
-          <t>kk_3875113278</t>
+          <t>tnwks1115</t>
         </is>
       </c>
       <c r="B1165" t="inlineStr">
         <is>
-          <t>01099620269</t>
+          <t>01024221364</t>
         </is>
       </c>
       <c r="C1165" t="inlineStr">
         <is>
-          <t>266546</t>
+          <t>275948</t>
         </is>
       </c>
       <c r="D1165" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="E1165" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>미분류</t>
         </is>
       </c>
     </row>
     <row r="1166">
       <c r="A1166" t="inlineStr">
         <is>
-          <t>tnwks1115</t>
+          <t>kk_3024318364</t>
         </is>
       </c>
       <c r="B1166" t="inlineStr">
         <is>
-          <t>01024221364</t>
+          <t>01050308038</t>
         </is>
       </c>
       <c r="C1166" t="inlineStr">
         <is>
-          <t>275948</t>
+          <t>219525</t>
         </is>
       </c>
       <c r="D1166" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E1166" t="inlineStr">
         <is>
-          <t>미분류</t>
+          <t>LMS_ECOM_0410exclusive2</t>
         </is>
       </c>
     </row>
     <row r="1167">
       <c r="A1167" t="inlineStr">
         <is>
-          <t>kk_3024318364</t>
+          <t>kk_3875113278</t>
         </is>
       </c>
       <c r="B1167" t="inlineStr">
         <is>
-          <t>01050308038</t>
+          <t>01099620269</t>
         </is>
       </c>
       <c r="C1167" t="inlineStr">
         <is>
-          <t>219525</t>
+          <t>266546</t>
         </is>
       </c>
       <c r="D1167" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="E1167" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0410exclusive2</t>
+          <t>Direct</t>
         </is>
       </c>
     </row>
@@ -31967,54 +31967,54 @@
     <row r="1169">
       <c r="A1169" t="inlineStr">
         <is>
-          <t>mse001</t>
+          <t>kk_4218204827</t>
         </is>
       </c>
       <c r="B1169" t="inlineStr">
         <is>
-          <t>01085185510</t>
+          <t>01023704903</t>
         </is>
       </c>
       <c r="C1169" t="inlineStr">
         <is>
-          <t>227227</t>
+          <t>272698</t>
         </is>
       </c>
       <c r="D1169" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="E1169" t="inlineStr">
         <is>
-          <t>KAKAO_alimtalk</t>
+          <t>Direct</t>
         </is>
       </c>
     </row>
     <row r="1170">
       <c r="A1170" t="inlineStr">
         <is>
-          <t>kk_4218204827</t>
+          <t>mse001</t>
         </is>
       </c>
       <c r="B1170" t="inlineStr">
         <is>
-          <t>01023704903</t>
+          <t>01085185510</t>
         </is>
       </c>
       <c r="C1170" t="inlineStr">
         <is>
-          <t>272698</t>
+          <t>227227</t>
         </is>
       </c>
       <c r="D1170" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E1170" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>KAKAO_alimtalk</t>
         </is>
       </c>
     </row>
@@ -32048,44 +32048,44 @@
     <row r="1172">
       <c r="A1172" t="inlineStr">
         <is>
-          <t>emfl22</t>
+          <t>bluesea063</t>
         </is>
       </c>
       <c r="B1172" t="inlineStr">
         <is>
-          <t>01049038806</t>
+          <t>01032902625</t>
         </is>
       </c>
       <c r="C1172" t="inlineStr">
         <is>
-          <t>288087</t>
+          <t>116772</t>
         </is>
       </c>
       <c r="D1172" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E1172" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
     </row>
     <row r="1173">
       <c r="A1173" t="inlineStr">
         <is>
-          <t>kk_4352927664</t>
+          <t>anfrorla</t>
         </is>
       </c>
       <c r="B1173" t="inlineStr">
         <is>
-          <t>01058770905</t>
+          <t>01050991521</t>
         </is>
       </c>
       <c r="C1173" t="inlineStr">
         <is>
-          <t>279347</t>
+          <t>137379</t>
         </is>
       </c>
       <c r="D1173" t="inlineStr">
@@ -32102,44 +32102,44 @@
     <row r="1174">
       <c r="A1174" t="inlineStr">
         <is>
-          <t>bluesea063</t>
+          <t>kk_3654717861</t>
         </is>
       </c>
       <c r="B1174" t="inlineStr">
         <is>
-          <t>01032902625</t>
+          <t>01022661489</t>
         </is>
       </c>
       <c r="C1174" t="inlineStr">
         <is>
-          <t>116772</t>
+          <t>249347</t>
         </is>
       </c>
       <c r="D1174" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="E1174" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Direct</t>
         </is>
       </c>
     </row>
     <row r="1175">
       <c r="A1175" t="inlineStr">
         <is>
-          <t>kk_3001595757</t>
+          <t>kk_4352927664</t>
         </is>
       </c>
       <c r="B1175" t="inlineStr">
         <is>
-          <t>01059491458</t>
+          <t>01058770905</t>
         </is>
       </c>
       <c r="C1175" t="inlineStr">
         <is>
-          <t>218616</t>
+          <t>279347</t>
         </is>
       </c>
       <c r="D1175" t="inlineStr">
@@ -32149,24 +32149,24 @@
       </c>
       <c r="E1175" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>etc</t>
         </is>
       </c>
     </row>
     <row r="1176">
       <c r="A1176" t="inlineStr">
         <is>
-          <t>kk_3654717861</t>
+          <t>quito3</t>
         </is>
       </c>
       <c r="B1176" t="inlineStr">
         <is>
-          <t>01022661489</t>
+          <t>01073440379</t>
         </is>
       </c>
       <c r="C1176" t="inlineStr">
         <is>
-          <t>249347</t>
+          <t>126578</t>
         </is>
       </c>
       <c r="D1176" t="inlineStr">
@@ -32183,71 +32183,71 @@
     <row r="1177">
       <c r="A1177" t="inlineStr">
         <is>
-          <t>quito3</t>
+          <t>kk_3001595757</t>
         </is>
       </c>
       <c r="B1177" t="inlineStr">
         <is>
-          <t>01073440379</t>
+          <t>01059491458</t>
         </is>
       </c>
       <c r="C1177" t="inlineStr">
         <is>
-          <t>126578</t>
+          <t>218616</t>
         </is>
       </c>
       <c r="D1177" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E1177" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>Owned Channel</t>
         </is>
       </c>
     </row>
     <row r="1178">
       <c r="A1178" t="inlineStr">
         <is>
-          <t>anfrorla</t>
+          <t>emfl22</t>
         </is>
       </c>
       <c r="B1178" t="inlineStr">
         <is>
-          <t>01050991521</t>
+          <t>01049038806</t>
         </is>
       </c>
       <c r="C1178" t="inlineStr">
         <is>
-          <t>137379</t>
+          <t>288087</t>
         </is>
       </c>
       <c r="D1178" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E1178" t="inlineStr">
         <is>
-          <t>etc</t>
+          <t>Paid Ad</t>
         </is>
       </c>
     </row>
     <row r="1179">
       <c r="A1179" t="inlineStr">
         <is>
-          <t>kk_3765548639</t>
+          <t>kk_3894722641</t>
         </is>
       </c>
       <c r="B1179" t="inlineStr">
         <is>
-          <t>01024327187</t>
+          <t>01064889500</t>
         </is>
       </c>
       <c r="C1179" t="inlineStr">
         <is>
-          <t>255087</t>
+          <t>267511</t>
         </is>
       </c>
       <c r="D1179" t="inlineStr">
@@ -32257,24 +32257,24 @@
       </c>
       <c r="E1179" t="inlineStr">
         <is>
-          <t>KAKAO_CH_MESSAGE_0409_RAINBOOTS</t>
+          <t>Email_mkt</t>
         </is>
       </c>
     </row>
     <row r="1180">
       <c r="A1180" t="inlineStr">
         <is>
-          <t>kk_3894722641</t>
+          <t>kk_3765548639</t>
         </is>
       </c>
       <c r="B1180" t="inlineStr">
         <is>
-          <t>01064889500</t>
+          <t>01024327187</t>
         </is>
       </c>
       <c r="C1180" t="inlineStr">
         <is>
-          <t>267511</t>
+          <t>255087</t>
         </is>
       </c>
       <c r="D1180" t="inlineStr">
@@ -32284,7 +32284,7 @@
       </c>
       <c r="E1180" t="inlineStr">
         <is>
-          <t>Email_mkt</t>
+          <t>KAKAO_CH_MESSAGE_0409_RAINBOOTS</t>
         </is>
       </c>
     </row>
@@ -32318,108 +32318,108 @@
     <row r="1182">
       <c r="A1182" t="inlineStr">
         <is>
-          <t>kk_4844817541</t>
+          <t>kk_4375003446</t>
         </is>
       </c>
       <c r="B1182" t="inlineStr">
         <is>
-          <t>01046631832</t>
+          <t>01087457282</t>
         </is>
       </c>
       <c r="C1182" t="inlineStr">
         <is>
-          <t>304380</t>
+          <t>280131</t>
         </is>
       </c>
       <c r="D1182" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E1182" t="inlineStr">
         <is>
-          <t>[PF]전환_회원가입(유사)</t>
+          <t>LMS_ECOM_0410exclusive2</t>
         </is>
       </c>
     </row>
     <row r="1183">
       <c r="A1183" t="inlineStr">
         <is>
-          <t>kk_4375003446</t>
+          <t>kk_4844817541</t>
         </is>
       </c>
       <c r="B1183" t="inlineStr">
         <is>
-          <t>01087457282</t>
+          <t>01046631832</t>
         </is>
       </c>
       <c r="C1183" t="inlineStr">
         <is>
-          <t>280131</t>
+          <t>304380</t>
         </is>
       </c>
       <c r="D1183" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E1183" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0410exclusive2</t>
+          <t>[PF]전환_회원가입(유사)</t>
         </is>
       </c>
     </row>
     <row r="1184">
       <c r="A1184" t="inlineStr">
         <is>
-          <t>kk_2768186596</t>
+          <t>kk_3169777000</t>
         </is>
       </c>
       <c r="B1184" t="inlineStr">
         <is>
-          <t>01029241198</t>
+          <t>01089348462</t>
         </is>
       </c>
       <c r="C1184" t="inlineStr">
         <is>
-          <t>208962</t>
+          <t>224876</t>
         </is>
       </c>
       <c r="D1184" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="E1184" t="inlineStr">
         <is>
-          <t>KAKAO_alimtalk</t>
+          <t>Direct</t>
         </is>
       </c>
     </row>
     <row r="1185">
       <c r="A1185" t="inlineStr">
         <is>
-          <t>kk_3169777000</t>
+          <t>kk_2768186596</t>
         </is>
       </c>
       <c r="B1185" t="inlineStr">
         <is>
-          <t>01089348462</t>
+          <t>01029241198</t>
         </is>
       </c>
       <c r="C1185" t="inlineStr">
         <is>
-          <t>224876</t>
+          <t>208962</t>
         </is>
       </c>
       <c r="D1185" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E1185" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>KAKAO_alimtalk</t>
         </is>
       </c>
     </row>
@@ -32453,98 +32453,98 @@
     <row r="1187">
       <c r="A1187" t="inlineStr">
         <is>
-          <t>ohsm0065</t>
+          <t>kk_2768989214</t>
         </is>
       </c>
       <c r="B1187" t="inlineStr">
         <is>
-          <t>01056170065</t>
+          <t>01095004289</t>
         </is>
       </c>
       <c r="C1187" t="inlineStr">
         <is>
-          <t>74567</t>
+          <t>209015</t>
         </is>
       </c>
       <c r="D1187" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="E1187" t="inlineStr">
         <is>
-          <t>[PF]트래픽_유사+관심사</t>
+          <t>Direct</t>
         </is>
       </c>
     </row>
     <row r="1188">
       <c r="A1188" t="inlineStr">
         <is>
-          <t>xuswldls</t>
+          <t>kk_3688034999</t>
         </is>
       </c>
       <c r="B1188" t="inlineStr">
         <is>
-          <t>01027349414</t>
+          <t>01025408262</t>
         </is>
       </c>
       <c r="C1188" t="inlineStr">
         <is>
-          <t>133308</t>
+          <t>250755</t>
         </is>
       </c>
       <c r="D1188" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E1188" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>KAKAO_alimtalk</t>
         </is>
       </c>
     </row>
     <row r="1189">
       <c r="A1189" t="inlineStr">
         <is>
-          <t>kk_3688034999</t>
+          <t>kk_4247630261</t>
         </is>
       </c>
       <c r="B1189" t="inlineStr">
         <is>
-          <t>01025408262</t>
+          <t>01091437323</t>
         </is>
       </c>
       <c r="C1189" t="inlineStr">
         <is>
-          <t>250755</t>
+          <t>274140</t>
         </is>
       </c>
       <c r="D1189" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Organic Traffic</t>
         </is>
       </c>
       <c r="E1189" t="inlineStr">
         <is>
-          <t>KAKAO_alimtalk</t>
+          <t>(referral)</t>
         </is>
       </c>
     </row>
     <row r="1190">
       <c r="A1190" t="inlineStr">
         <is>
-          <t>kk_2768989214</t>
+          <t>kk_3444865211</t>
         </is>
       </c>
       <c r="B1190" t="inlineStr">
         <is>
-          <t>01095004289</t>
+          <t>01021964871</t>
         </is>
       </c>
       <c r="C1190" t="inlineStr">
         <is>
-          <t>209015</t>
+          <t>242799</t>
         </is>
       </c>
       <c r="D1190" t="inlineStr">
@@ -32561,98 +32561,98 @@
     <row r="1191">
       <c r="A1191" t="inlineStr">
         <is>
-          <t>kk_4472536591</t>
+          <t>ohsm0065</t>
         </is>
       </c>
       <c r="B1191" t="inlineStr">
         <is>
-          <t>01037057526</t>
+          <t>01056170065</t>
         </is>
       </c>
       <c r="C1191" t="inlineStr">
         <is>
-          <t>283897</t>
+          <t>74567</t>
         </is>
       </c>
       <c r="D1191" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E1191" t="inlineStr">
         <is>
-          <t>KAKAO_alimtalk</t>
+          <t>[PF]트래픽_유사+관심사</t>
         </is>
       </c>
     </row>
     <row r="1192">
       <c r="A1192" t="inlineStr">
         <is>
-          <t>kk_3444865211</t>
+          <t>kk_4472536591</t>
         </is>
       </c>
       <c r="B1192" t="inlineStr">
         <is>
-          <t>01021964871</t>
+          <t>01037057526</t>
         </is>
       </c>
       <c r="C1192" t="inlineStr">
         <is>
-          <t>242799</t>
+          <t>283897</t>
         </is>
       </c>
       <c r="D1192" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E1192" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>KAKAO_alimtalk</t>
         </is>
       </c>
     </row>
     <row r="1193">
       <c r="A1193" t="inlineStr">
         <is>
-          <t>kk_4247630261</t>
+          <t>xuswldls</t>
         </is>
       </c>
       <c r="B1193" t="inlineStr">
         <is>
-          <t>01091437323</t>
+          <t>01027349414</t>
         </is>
       </c>
       <c r="C1193" t="inlineStr">
         <is>
-          <t>274140</t>
+          <t>133308</t>
         </is>
       </c>
       <c r="D1193" t="inlineStr">
         <is>
-          <t>Organic Traffic</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="E1193" t="inlineStr">
         <is>
-          <t>(referral)</t>
+          <t>Direct</t>
         </is>
       </c>
     </row>
     <row r="1194">
       <c r="A1194" t="inlineStr">
         <is>
-          <t>kk_3837527580</t>
+          <t>nesto1</t>
         </is>
       </c>
       <c r="B1194" t="inlineStr">
         <is>
-          <t>01084311738</t>
+          <t>01056603953</t>
         </is>
       </c>
       <c r="C1194" t="inlineStr">
         <is>
-          <t>264113</t>
+          <t>125251</t>
         </is>
       </c>
       <c r="D1194" t="inlineStr">
@@ -32662,24 +32662,24 @@
       </c>
       <c r="E1194" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0410exclusive2</t>
+          <t>KAKAO_alimtalk</t>
         </is>
       </c>
     </row>
     <row r="1195">
       <c r="A1195" t="inlineStr">
         <is>
-          <t>escalater</t>
+          <t>kk_3181917333</t>
         </is>
       </c>
       <c r="B1195" t="inlineStr">
         <is>
-          <t>01090911461</t>
+          <t>01072258509</t>
         </is>
       </c>
       <c r="C1195" t="inlineStr">
         <is>
-          <t>240051</t>
+          <t>227380</t>
         </is>
       </c>
       <c r="D1195" t="inlineStr">
@@ -32696,27 +32696,27 @@
     <row r="1196">
       <c r="A1196" t="inlineStr">
         <is>
-          <t>kk_3181917333</t>
+          <t>kk_3837527580</t>
         </is>
       </c>
       <c r="B1196" t="inlineStr">
         <is>
-          <t>01072258509</t>
+          <t>01084311738</t>
         </is>
       </c>
       <c r="C1196" t="inlineStr">
         <is>
-          <t>227380</t>
+          <t>264113</t>
         </is>
       </c>
       <c r="D1196" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E1196" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>LMS_ECOM_0410exclusive2</t>
         </is>
       </c>
     </row>
@@ -32777,71 +32777,71 @@
     <row r="1199">
       <c r="A1199" t="inlineStr">
         <is>
-          <t>nesto1</t>
+          <t>escalater</t>
         </is>
       </c>
       <c r="B1199" t="inlineStr">
         <is>
-          <t>01056603953</t>
+          <t>01090911461</t>
         </is>
       </c>
       <c r="C1199" t="inlineStr">
         <is>
-          <t>125251</t>
+          <t>240051</t>
         </is>
       </c>
       <c r="D1199" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="E1199" t="inlineStr">
         <is>
-          <t>KAKAO_alimtalk</t>
+          <t>Direct</t>
         </is>
       </c>
     </row>
     <row r="1200">
       <c r="A1200" t="inlineStr">
         <is>
-          <t>kk_3933534683</t>
+          <t>kk_4467707148</t>
         </is>
       </c>
       <c r="B1200" t="inlineStr">
         <is>
-          <t>01030153796</t>
+          <t>01030843332</t>
         </is>
       </c>
       <c r="C1200" t="inlineStr">
         <is>
-          <t>269069</t>
+          <t>283560</t>
         </is>
       </c>
       <c r="D1200" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E1200" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>LMS_ECOM_0410exclusive2</t>
         </is>
       </c>
     </row>
     <row r="1201">
       <c r="A1201" t="inlineStr">
         <is>
-          <t>kk_4338209948</t>
+          <t>kk_2940110361</t>
         </is>
       </c>
       <c r="B1201" t="inlineStr">
         <is>
-          <t>01088132379</t>
+          <t>01035353200</t>
         </is>
       </c>
       <c r="C1201" t="inlineStr">
         <is>
-          <t>278781</t>
+          <t>216362</t>
         </is>
       </c>
       <c r="D1201" t="inlineStr">
@@ -32851,51 +32851,51 @@
       </c>
       <c r="E1201" t="inlineStr">
         <is>
-          <t>KAKAO_alimtalk</t>
+          <t>LMS_ECOM_0410exclusive2</t>
         </is>
       </c>
     </row>
     <row r="1202">
       <c r="A1202" t="inlineStr">
         <is>
-          <t>mansoogi</t>
+          <t>kk_3013902343</t>
         </is>
       </c>
       <c r="B1202" t="inlineStr">
         <is>
-          <t>01093240897</t>
+          <t>01051802326</t>
         </is>
       </c>
       <c r="C1202" t="inlineStr">
         <is>
-          <t>25243</t>
+          <t>219219</t>
         </is>
       </c>
       <c r="D1202" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E1202" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0410exclusive2</t>
+          <t>6968489536332</t>
         </is>
       </c>
     </row>
     <row r="1203">
       <c r="A1203" t="inlineStr">
         <is>
-          <t>kk_2940110361</t>
+          <t>hursean</t>
         </is>
       </c>
       <c r="B1203" t="inlineStr">
         <is>
-          <t>01035353200</t>
+          <t>01091975738</t>
         </is>
       </c>
       <c r="C1203" t="inlineStr">
         <is>
-          <t>216362</t>
+          <t>123130</t>
         </is>
       </c>
       <c r="D1203" t="inlineStr">
@@ -32905,24 +32905,24 @@
       </c>
       <c r="E1203" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0410exclusive2</t>
+          <t>Email_mkt</t>
         </is>
       </c>
     </row>
     <row r="1204">
       <c r="A1204" t="inlineStr">
         <is>
-          <t>kk_4523594127</t>
+          <t>mansoogi</t>
         </is>
       </c>
       <c r="B1204" t="inlineStr">
         <is>
-          <t>01085735215</t>
+          <t>01093240897</t>
         </is>
       </c>
       <c r="C1204" t="inlineStr">
         <is>
-          <t>286358</t>
+          <t>25243</t>
         </is>
       </c>
       <c r="D1204" t="inlineStr">
@@ -32966,17 +32966,17 @@
     <row r="1206">
       <c r="A1206" t="inlineStr">
         <is>
-          <t>kk_4467707148</t>
+          <t>seul6169</t>
         </is>
       </c>
       <c r="B1206" t="inlineStr">
         <is>
-          <t>01030843332</t>
+          <t>01066116699</t>
         </is>
       </c>
       <c r="C1206" t="inlineStr">
         <is>
-          <t>283560</t>
+          <t>234239</t>
         </is>
       </c>
       <c r="D1206" t="inlineStr">
@@ -32986,51 +32986,51 @@
       </c>
       <c r="E1206" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0410exclusive2</t>
+          <t>KAKAO_alimtalk</t>
         </is>
       </c>
     </row>
     <row r="1207">
       <c r="A1207" t="inlineStr">
         <is>
-          <t>kk_3013902343</t>
+          <t>kk_4523594127</t>
         </is>
       </c>
       <c r="B1207" t="inlineStr">
         <is>
-          <t>01051802326</t>
+          <t>01085735215</t>
         </is>
       </c>
       <c r="C1207" t="inlineStr">
         <is>
-          <t>219219</t>
+          <t>286358</t>
         </is>
       </c>
       <c r="D1207" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E1207" t="inlineStr">
         <is>
-          <t>6968489536332</t>
+          <t>LMS_ECOM_0410exclusive2</t>
         </is>
       </c>
     </row>
     <row r="1208">
       <c r="A1208" t="inlineStr">
         <is>
-          <t>hursean</t>
+          <t>kk_4338209948</t>
         </is>
       </c>
       <c r="B1208" t="inlineStr">
         <is>
-          <t>01091975738</t>
+          <t>01088132379</t>
         </is>
       </c>
       <c r="C1208" t="inlineStr">
         <is>
-          <t>123130</t>
+          <t>278781</t>
         </is>
       </c>
       <c r="D1208" t="inlineStr">
@@ -33040,7 +33040,7 @@
       </c>
       <c r="E1208" t="inlineStr">
         <is>
-          <t>Email_mkt</t>
+          <t>KAKAO_alimtalk</t>
         </is>
       </c>
     </row>
@@ -33101,27 +33101,27 @@
     <row r="1211">
       <c r="A1211" t="inlineStr">
         <is>
-          <t>seul6169</t>
+          <t>kk_3933534683</t>
         </is>
       </c>
       <c r="B1211" t="inlineStr">
         <is>
-          <t>01066116699</t>
+          <t>01030153796</t>
         </is>
       </c>
       <c r="C1211" t="inlineStr">
         <is>
-          <t>234239</t>
+          <t>269069</t>
         </is>
       </c>
       <c r="D1211" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="E1211" t="inlineStr">
         <is>
-          <t>KAKAO_alimtalk</t>
+          <t>Direct</t>
         </is>
       </c>
     </row>
@@ -33182,17 +33182,17 @@
     <row r="1214">
       <c r="A1214" t="inlineStr">
         <is>
-          <t>kk_4608940431</t>
+          <t>kk_4358499671</t>
         </is>
       </c>
       <c r="B1214" t="inlineStr">
         <is>
-          <t>01034834753</t>
+          <t>01066507573</t>
         </is>
       </c>
       <c r="C1214" t="inlineStr">
         <is>
-          <t>289885</t>
+          <t>279591</t>
         </is>
       </c>
       <c r="D1214" t="inlineStr">
@@ -33209,17 +33209,17 @@
     <row r="1215">
       <c r="A1215" t="inlineStr">
         <is>
-          <t>kk_3296362697</t>
+          <t>kycho229</t>
         </is>
       </c>
       <c r="B1215" t="inlineStr">
         <is>
-          <t>01032224185</t>
+          <t>01047322138</t>
         </is>
       </c>
       <c r="C1215" t="inlineStr">
         <is>
-          <t>237406</t>
+          <t>22747</t>
         </is>
       </c>
       <c r="D1215" t="inlineStr">
@@ -33229,7 +33229,7 @@
       </c>
       <c r="E1215" t="inlineStr">
         <is>
-          <t>etc</t>
+          <t>Owned Channel</t>
         </is>
       </c>
     </row>
@@ -33263,17 +33263,17 @@
     <row r="1217">
       <c r="A1217" t="inlineStr">
         <is>
-          <t>taebaekcc</t>
+          <t>kk_3296362697</t>
         </is>
       </c>
       <c r="B1217" t="inlineStr">
         <is>
-          <t>01090034620</t>
+          <t>01032224185</t>
         </is>
       </c>
       <c r="C1217" t="inlineStr">
         <is>
-          <t>182329</t>
+          <t>237406</t>
         </is>
       </c>
       <c r="D1217" t="inlineStr">
@@ -33290,17 +33290,17 @@
     <row r="1218">
       <c r="A1218" t="inlineStr">
         <is>
-          <t>kk_3114284664</t>
+          <t>kk_3927027066</t>
         </is>
       </c>
       <c r="B1218" t="inlineStr">
         <is>
-          <t>01031259752</t>
+          <t>01046272823</t>
         </is>
       </c>
       <c r="C1218" t="inlineStr">
         <is>
-          <t>222243</t>
+          <t>268818</t>
         </is>
       </c>
       <c r="D1218" t="inlineStr">
@@ -33310,132 +33310,132 @@
       </c>
       <c r="E1218" t="inlineStr">
         <is>
-          <t>etc</t>
+          <t>Direct</t>
         </is>
       </c>
     </row>
     <row r="1219">
       <c r="A1219" t="inlineStr">
         <is>
-          <t>kycho229</t>
+          <t>kk_3801403661</t>
         </is>
       </c>
       <c r="B1219" t="inlineStr">
         <is>
-          <t>01047322138</t>
+          <t>01086386165</t>
         </is>
       </c>
       <c r="C1219" t="inlineStr">
         <is>
-          <t>22747</t>
+          <t>259058</t>
         </is>
       </c>
       <c r="D1219" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="E1219" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Direct</t>
         </is>
       </c>
     </row>
     <row r="1220">
       <c r="A1220" t="inlineStr">
         <is>
-          <t>kk_4600690023</t>
+          <t>kk_4608940431</t>
         </is>
       </c>
       <c r="B1220" t="inlineStr">
         <is>
-          <t>01067632977</t>
+          <t>01034834753</t>
         </is>
       </c>
       <c r="C1220" t="inlineStr">
         <is>
-          <t>289390</t>
+          <t>289885</t>
         </is>
       </c>
       <c r="D1220" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="E1220" t="inlineStr">
         <is>
-          <t>etc</t>
+          <t>Direct</t>
         </is>
       </c>
     </row>
     <row r="1221">
       <c r="A1221" t="inlineStr">
         <is>
-          <t>kk_4358499671</t>
+          <t>kk_4600690023</t>
         </is>
       </c>
       <c r="B1221" t="inlineStr">
         <is>
-          <t>01066507573</t>
+          <t>01067632977</t>
         </is>
       </c>
       <c r="C1221" t="inlineStr">
         <is>
-          <t>279591</t>
+          <t>289390</t>
         </is>
       </c>
       <c r="D1221" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E1221" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>etc</t>
         </is>
       </c>
     </row>
     <row r="1222">
       <c r="A1222" t="inlineStr">
         <is>
-          <t>kk_3927027066</t>
+          <t>taebaekcc</t>
         </is>
       </c>
       <c r="B1222" t="inlineStr">
         <is>
-          <t>01046272823</t>
+          <t>01090034620</t>
         </is>
       </c>
       <c r="C1222" t="inlineStr">
         <is>
-          <t>268818</t>
+          <t>182329</t>
         </is>
       </c>
       <c r="D1222" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E1222" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>etc</t>
         </is>
       </c>
     </row>
     <row r="1223">
       <c r="A1223" t="inlineStr">
         <is>
-          <t>kk_3801403661</t>
+          <t>kk_3114284664</t>
         </is>
       </c>
       <c r="B1223" t="inlineStr">
         <is>
-          <t>01086386165</t>
+          <t>01031259752</t>
         </is>
       </c>
       <c r="C1223" t="inlineStr">
         <is>
-          <t>259058</t>
+          <t>222243</t>
         </is>
       </c>
       <c r="D1223" t="inlineStr">
@@ -33445,7 +33445,7 @@
       </c>
       <c r="E1223" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>etc</t>
         </is>
       </c>
     </row>
@@ -33614,152 +33614,152 @@
     <row r="1230">
       <c r="A1230" t="inlineStr">
         <is>
-          <t>loyed24</t>
+          <t>hihijs34</t>
         </is>
       </c>
       <c r="B1230" t="inlineStr">
         <is>
-          <t>01085487901</t>
+          <t>01093230529</t>
         </is>
       </c>
       <c r="C1230" t="inlineStr">
         <is>
-          <t>244062</t>
+          <t>128947</t>
         </is>
       </c>
       <c r="D1230" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E1230" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0410exclusive2</t>
+          <t>[PF]A+SC_상시(1865MF,구매+장바구니)</t>
         </is>
       </c>
     </row>
     <row r="1231">
       <c r="A1231" t="inlineStr">
         <is>
-          <t>kk_4427490834</t>
+          <t>wisbrain</t>
         </is>
       </c>
       <c r="B1231" t="inlineStr">
         <is>
-          <t>01034704205</t>
+          <t>01047220186</t>
         </is>
       </c>
       <c r="C1231" t="inlineStr">
         <is>
-          <t>281590</t>
+          <t>188067</t>
         </is>
       </c>
       <c r="D1231" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="E1231" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0410exclusive2</t>
+          <t>Direct</t>
         </is>
       </c>
     </row>
     <row r="1232">
       <c r="A1232" t="inlineStr">
         <is>
-          <t>wisbrain</t>
+          <t>kk_4427490834</t>
         </is>
       </c>
       <c r="B1232" t="inlineStr">
         <is>
-          <t>01047220186</t>
+          <t>01034704205</t>
         </is>
       </c>
       <c r="C1232" t="inlineStr">
         <is>
-          <t>188067</t>
+          <t>281590</t>
         </is>
       </c>
       <c r="D1232" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E1232" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>LMS_ECOM_0410exclusive2</t>
         </is>
       </c>
     </row>
     <row r="1233">
       <c r="A1233" t="inlineStr">
         <is>
-          <t>hihijs34</t>
+          <t>loyed24</t>
         </is>
       </c>
       <c r="B1233" t="inlineStr">
         <is>
-          <t>01093230529</t>
+          <t>01085487901</t>
         </is>
       </c>
       <c r="C1233" t="inlineStr">
         <is>
-          <t>128947</t>
+          <t>244062</t>
         </is>
       </c>
       <c r="D1233" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E1233" t="inlineStr">
         <is>
-          <t>[PF]A+SC_상시(1865MF,구매+장바구니)</t>
+          <t>LMS_ECOM_0410exclusive2</t>
         </is>
       </c>
     </row>
     <row r="1234">
       <c r="A1234" t="inlineStr">
         <is>
-          <t>camiblanco</t>
+          <t>columbia7</t>
         </is>
       </c>
       <c r="B1234" t="inlineStr">
         <is>
-          <t>01072190103</t>
+          <t>01050080025</t>
         </is>
       </c>
       <c r="C1234" t="inlineStr">
         <is>
-          <t>232545</t>
+          <t>109980</t>
         </is>
       </c>
       <c r="D1234" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E1234" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>LMS_ECOM_0410exclusive2</t>
         </is>
       </c>
     </row>
     <row r="1235">
       <c r="A1235" t="inlineStr">
         <is>
-          <t>kk_4452401577</t>
+          <t>kk_3349199057</t>
         </is>
       </c>
       <c r="B1235" t="inlineStr">
         <is>
-          <t>01047428000</t>
+          <t>01071630312</t>
         </is>
       </c>
       <c r="C1235" t="inlineStr">
         <is>
-          <t>282525</t>
+          <t>239388</t>
         </is>
       </c>
       <c r="D1235" t="inlineStr">
@@ -33776,44 +33776,44 @@
     <row r="1236">
       <c r="A1236" t="inlineStr">
         <is>
-          <t>kk_3721447783</t>
+          <t>dmsql785612</t>
         </is>
       </c>
       <c r="B1236" t="inlineStr">
         <is>
-          <t>01051311087</t>
+          <t>01051590364</t>
         </is>
       </c>
       <c r="C1236" t="inlineStr">
         <is>
-          <t>252252</t>
+          <t>137279</t>
         </is>
       </c>
       <c r="D1236" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E1236" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>Email_mkt</t>
         </is>
       </c>
     </row>
     <row r="1237">
       <c r="A1237" t="inlineStr">
         <is>
-          <t>kk_3349199057</t>
+          <t>inu21c</t>
         </is>
       </c>
       <c r="B1237" t="inlineStr">
         <is>
-          <t>01071630312</t>
+          <t>01035128236</t>
         </is>
       </c>
       <c r="C1237" t="inlineStr">
         <is>
-          <t>239388</t>
+          <t>131940</t>
         </is>
       </c>
       <c r="D1237" t="inlineStr">
@@ -33830,17 +33830,17 @@
     <row r="1238">
       <c r="A1238" t="inlineStr">
         <is>
-          <t>kk_3973703558</t>
+          <t>kk_3180736217</t>
         </is>
       </c>
       <c r="B1238" t="inlineStr">
         <is>
-          <t>01048590748</t>
+          <t>01036000343</t>
         </is>
       </c>
       <c r="C1238" t="inlineStr">
         <is>
-          <t>271020</t>
+          <t>226314</t>
         </is>
       </c>
       <c r="D1238" t="inlineStr">
@@ -33857,17 +33857,17 @@
     <row r="1239">
       <c r="A1239" t="inlineStr">
         <is>
-          <t>pls4u</t>
+          <t>bobjazz</t>
         </is>
       </c>
       <c r="B1239" t="inlineStr">
         <is>
-          <t>01085985482</t>
+          <t>01084090677</t>
         </is>
       </c>
       <c r="C1239" t="inlineStr">
         <is>
-          <t>88257</t>
+          <t>186218</t>
         </is>
       </c>
       <c r="D1239" t="inlineStr">
@@ -33877,24 +33877,24 @@
       </c>
       <c r="E1239" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0401_trailrunning</t>
+          <t>LMS_ECOM_0410exclusive2</t>
         </is>
       </c>
     </row>
     <row r="1240">
       <c r="A1240" t="inlineStr">
         <is>
-          <t>sjm700</t>
+          <t>kk_4452401577</t>
         </is>
       </c>
       <c r="B1240" t="inlineStr">
         <is>
-          <t>01077331591</t>
+          <t>01047428000</t>
         </is>
       </c>
       <c r="C1240" t="inlineStr">
         <is>
-          <t>118769</t>
+          <t>282525</t>
         </is>
       </c>
       <c r="D1240" t="inlineStr">
@@ -33911,44 +33911,44 @@
     <row r="1241">
       <c r="A1241" t="inlineStr">
         <is>
-          <t>kk_4525043459</t>
+          <t>kk_4292190414</t>
         </is>
       </c>
       <c r="B1241" t="inlineStr">
         <is>
-          <t>01088312135</t>
+          <t>01095177478</t>
         </is>
       </c>
       <c r="C1241" t="inlineStr">
         <is>
-          <t>286464</t>
+          <t>275998</t>
         </is>
       </c>
       <c r="D1241" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="E1241" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0410exclusive2</t>
+          <t>Direct</t>
         </is>
       </c>
     </row>
     <row r="1242">
       <c r="A1242" t="inlineStr">
         <is>
-          <t>kk_4292190414</t>
+          <t>camiblanco</t>
         </is>
       </c>
       <c r="B1242" t="inlineStr">
         <is>
-          <t>01095177478</t>
+          <t>01072190103</t>
         </is>
       </c>
       <c r="C1242" t="inlineStr">
         <is>
-          <t>275998</t>
+          <t>232545</t>
         </is>
       </c>
       <c r="D1242" t="inlineStr">
@@ -33965,44 +33965,44 @@
     <row r="1243">
       <c r="A1243" t="inlineStr">
         <is>
-          <t>kk_2825715315</t>
+          <t>kk_3721447783</t>
         </is>
       </c>
       <c r="B1243" t="inlineStr">
         <is>
-          <t>01077229654</t>
+          <t>01051311087</t>
         </is>
       </c>
       <c r="C1243" t="inlineStr">
         <is>
-          <t>212719</t>
+          <t>252252</t>
         </is>
       </c>
       <c r="D1243" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="E1243" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0410exclusive2</t>
+          <t>Direct</t>
         </is>
       </c>
     </row>
     <row r="1244">
       <c r="A1244" t="inlineStr">
         <is>
-          <t>kk_3754052831</t>
+          <t>sjm700</t>
         </is>
       </c>
       <c r="B1244" t="inlineStr">
         <is>
-          <t>01092180804</t>
+          <t>01077331591</t>
         </is>
       </c>
       <c r="C1244" t="inlineStr">
         <is>
-          <t>254339</t>
+          <t>118769</t>
         </is>
       </c>
       <c r="D1244" t="inlineStr">
@@ -34019,17 +34019,17 @@
     <row r="1245">
       <c r="A1245" t="inlineStr">
         <is>
-          <t>inu21c</t>
+          <t>kk_4578503399</t>
         </is>
       </c>
       <c r="B1245" t="inlineStr">
         <is>
-          <t>01035128236</t>
+          <t>01088660330</t>
         </is>
       </c>
       <c r="C1245" t="inlineStr">
         <is>
-          <t>131940</t>
+          <t>288374</t>
         </is>
       </c>
       <c r="D1245" t="inlineStr">
@@ -34046,44 +34046,44 @@
     <row r="1246">
       <c r="A1246" t="inlineStr">
         <is>
-          <t>yongshin</t>
+          <t>kk_4525043459</t>
         </is>
       </c>
       <c r="B1246" t="inlineStr">
         <is>
-          <t>01053867821</t>
+          <t>01088312135</t>
         </is>
       </c>
       <c r="C1246" t="inlineStr">
         <is>
-          <t>277896</t>
+          <t>286464</t>
         </is>
       </c>
       <c r="D1246" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E1246" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>LMS_ECOM_0410exclusive2</t>
         </is>
       </c>
     </row>
     <row r="1247">
       <c r="A1247" t="inlineStr">
         <is>
-          <t>kk_3180736217</t>
+          <t>kk_3973703558</t>
         </is>
       </c>
       <c r="B1247" t="inlineStr">
         <is>
-          <t>01036000343</t>
+          <t>01048590748</t>
         </is>
       </c>
       <c r="C1247" t="inlineStr">
         <is>
-          <t>226314</t>
+          <t>271020</t>
         </is>
       </c>
       <c r="D1247" t="inlineStr">
@@ -34100,17 +34100,17 @@
     <row r="1248">
       <c r="A1248" t="inlineStr">
         <is>
-          <t>columbia7</t>
+          <t>kk_3754052831</t>
         </is>
       </c>
       <c r="B1248" t="inlineStr">
         <is>
-          <t>01050080025</t>
+          <t>01092180804</t>
         </is>
       </c>
       <c r="C1248" t="inlineStr">
         <is>
-          <t>109980</t>
+          <t>254339</t>
         </is>
       </c>
       <c r="D1248" t="inlineStr">
@@ -34127,17 +34127,17 @@
     <row r="1249">
       <c r="A1249" t="inlineStr">
         <is>
-          <t>kk_4578503399</t>
+          <t>pls4u</t>
         </is>
       </c>
       <c r="B1249" t="inlineStr">
         <is>
-          <t>01088660330</t>
+          <t>01085985482</t>
         </is>
       </c>
       <c r="C1249" t="inlineStr">
         <is>
-          <t>288374</t>
+          <t>88257</t>
         </is>
       </c>
       <c r="D1249" t="inlineStr">
@@ -34147,24 +34147,24 @@
       </c>
       <c r="E1249" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0410exclusive2</t>
+          <t>LMS_ECOM_0401_trailrunning</t>
         </is>
       </c>
     </row>
     <row r="1250">
       <c r="A1250" t="inlineStr">
         <is>
-          <t>bobjazz</t>
+          <t>kk_2825715315</t>
         </is>
       </c>
       <c r="B1250" t="inlineStr">
         <is>
-          <t>01084090677</t>
+          <t>01077229654</t>
         </is>
       </c>
       <c r="C1250" t="inlineStr">
         <is>
-          <t>186218</t>
+          <t>212719</t>
         </is>
       </c>
       <c r="D1250" t="inlineStr">
@@ -34181,27 +34181,27 @@
     <row r="1251">
       <c r="A1251" t="inlineStr">
         <is>
-          <t>dmsql785612</t>
+          <t>yongshin</t>
         </is>
       </c>
       <c r="B1251" t="inlineStr">
         <is>
-          <t>01051590364</t>
+          <t>01053867821</t>
         </is>
       </c>
       <c r="C1251" t="inlineStr">
         <is>
-          <t>137279</t>
+          <t>277896</t>
         </is>
       </c>
       <c r="D1251" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="E1251" t="inlineStr">
         <is>
-          <t>Email_mkt</t>
+          <t>Direct</t>
         </is>
       </c>
     </row>
@@ -34262,44 +34262,44 @@
     <row r="1254">
       <c r="A1254" t="inlineStr">
         <is>
-          <t>sh5204</t>
+          <t>coda1202</t>
         </is>
       </c>
       <c r="B1254" t="inlineStr">
         <is>
-          <t>01054433018</t>
+          <t>01037655629</t>
         </is>
       </c>
       <c r="C1254" t="inlineStr">
         <is>
-          <t>263137</t>
+          <t>117064</t>
         </is>
       </c>
       <c r="D1254" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="E1254" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Direct</t>
         </is>
       </c>
     </row>
     <row r="1255">
       <c r="A1255" t="inlineStr">
         <is>
-          <t>kairos93</t>
+          <t>olive888888</t>
         </is>
       </c>
       <c r="B1255" t="inlineStr">
         <is>
-          <t>01051079223</t>
+          <t>01029817882</t>
         </is>
       </c>
       <c r="C1255" t="inlineStr">
         <is>
-          <t>160644</t>
+          <t>116464</t>
         </is>
       </c>
       <c r="D1255" t="inlineStr">
@@ -34316,17 +34316,17 @@
     <row r="1256">
       <c r="A1256" t="inlineStr">
         <is>
-          <t>olive888888</t>
+          <t>kairos93</t>
         </is>
       </c>
       <c r="B1256" t="inlineStr">
         <is>
-          <t>01029817882</t>
+          <t>01051079223</t>
         </is>
       </c>
       <c r="C1256" t="inlineStr">
         <is>
-          <t>116464</t>
+          <t>160644</t>
         </is>
       </c>
       <c r="D1256" t="inlineStr">
@@ -34343,44 +34343,44 @@
     <row r="1257">
       <c r="A1257" t="inlineStr">
         <is>
-          <t>coda1202</t>
+          <t>sh5204</t>
         </is>
       </c>
       <c r="B1257" t="inlineStr">
         <is>
-          <t>01037655629</t>
+          <t>01054433018</t>
         </is>
       </c>
       <c r="C1257" t="inlineStr">
         <is>
-          <t>117064</t>
+          <t>263137</t>
         </is>
       </c>
       <c r="D1257" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E1257" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>Paid Ad</t>
         </is>
       </c>
     </row>
     <row r="1258">
       <c r="A1258" t="inlineStr">
         <is>
-          <t>kimms66</t>
+          <t>alcoholpower</t>
         </is>
       </c>
       <c r="B1258" t="inlineStr">
         <is>
-          <t>01057634626</t>
+          <t>01027629868</t>
         </is>
       </c>
       <c r="C1258" t="inlineStr">
         <is>
-          <t>180321</t>
+          <t>252954</t>
         </is>
       </c>
       <c r="D1258" t="inlineStr">
@@ -34397,17 +34397,17 @@
     <row r="1259">
       <c r="A1259" t="inlineStr">
         <is>
-          <t>alcoholpower</t>
+          <t>kimms66</t>
         </is>
       </c>
       <c r="B1259" t="inlineStr">
         <is>
-          <t>01027629868</t>
+          <t>01057634626</t>
         </is>
       </c>
       <c r="C1259" t="inlineStr">
         <is>
-          <t>252954</t>
+          <t>180321</t>
         </is>
       </c>
       <c r="D1259" t="inlineStr">

--- a/reports/member_funnel/downloads/member_funnel_7d_non_buyer.xlsx
+++ b/reports/member_funnel/downloads/member_funnel_7d_non_buyer.xlsx
@@ -500,7 +500,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>etc</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -527,7 +527,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>etc</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -797,12 +797,12 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>etc</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>etc</t>
+          <t>미분류</t>
         </is>
       </c>
     </row>
@@ -824,7 +824,7 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>etc</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -1121,7 +1121,7 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>etc</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
@@ -1175,7 +1175,7 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>etc</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
@@ -1310,7 +1310,7 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>etc</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
@@ -1499,12 +1499,12 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>etc</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>etc</t>
+          <t>미분류</t>
         </is>
       </c>
     </row>
@@ -2120,7 +2120,7 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>etc</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
@@ -2282,12 +2282,12 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>etc</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>etc</t>
+          <t>미분류</t>
         </is>
       </c>
     </row>
@@ -2390,12 +2390,12 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>etc</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>etc</t>
+          <t>미분류</t>
         </is>
       </c>
     </row>
@@ -2498,7 +2498,7 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>etc</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
@@ -2552,7 +2552,7 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>etc</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
@@ -3038,7 +3038,7 @@
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>etc</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
@@ -3173,7 +3173,7 @@
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>etc</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
@@ -3335,12 +3335,12 @@
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>etc</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>etc</t>
+          <t>미분류</t>
         </is>
       </c>
     </row>
@@ -3470,7 +3470,7 @@
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>etc</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E113" t="inlineStr">
@@ -3578,7 +3578,7 @@
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>etc</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E117" t="inlineStr">
@@ -3983,7 +3983,7 @@
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>etc</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E132" t="inlineStr">
@@ -4307,7 +4307,7 @@
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>etc</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E144" t="inlineStr">
@@ -4334,7 +4334,7 @@
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>etc</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E145" t="inlineStr">
@@ -4469,7 +4469,7 @@
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>etc</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E150" t="inlineStr">
@@ -4793,7 +4793,7 @@
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>etc</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E162" t="inlineStr">
@@ -4874,7 +4874,7 @@
       </c>
       <c r="D165" t="inlineStr">
         <is>
-          <t>etc</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E165" t="inlineStr">
@@ -4901,7 +4901,7 @@
       </c>
       <c r="D166" t="inlineStr">
         <is>
-          <t>etc</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E166" t="inlineStr">
@@ -4928,7 +4928,7 @@
       </c>
       <c r="D167" t="inlineStr">
         <is>
-          <t>etc</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E167" t="inlineStr">
@@ -5279,7 +5279,7 @@
       </c>
       <c r="D180" t="inlineStr">
         <is>
-          <t>etc</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E180" t="inlineStr">
@@ -5306,7 +5306,7 @@
       </c>
       <c r="D181" t="inlineStr">
         <is>
-          <t>etc</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E181" t="inlineStr">
@@ -5630,7 +5630,7 @@
       </c>
       <c r="D193" t="inlineStr">
         <is>
-          <t>etc</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E193" t="inlineStr">
@@ -5711,12 +5711,12 @@
       </c>
       <c r="D196" t="inlineStr">
         <is>
-          <t>etc</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="E196" t="inlineStr">
         <is>
-          <t>etc</t>
+          <t>미분류</t>
         </is>
       </c>
     </row>
@@ -5738,7 +5738,7 @@
       </c>
       <c r="D197" t="inlineStr">
         <is>
-          <t>etc</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E197" t="inlineStr">
@@ -5927,7 +5927,7 @@
       </c>
       <c r="D204" t="inlineStr">
         <is>
-          <t>etc</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E204" t="inlineStr">
@@ -5981,7 +5981,7 @@
       </c>
       <c r="D206" t="inlineStr">
         <is>
-          <t>etc</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E206" t="inlineStr">
@@ -6224,12 +6224,12 @@
       </c>
       <c r="D215" t="inlineStr">
         <is>
-          <t>etc</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="E215" t="inlineStr">
         <is>
-          <t>etc</t>
+          <t>미분류</t>
         </is>
       </c>
     </row>
@@ -6251,7 +6251,7 @@
       </c>
       <c r="D216" t="inlineStr">
         <is>
-          <t>etc</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E216" t="inlineStr">
@@ -6521,7 +6521,7 @@
       </c>
       <c r="D226" t="inlineStr">
         <is>
-          <t>etc</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E226" t="inlineStr">
@@ -6980,7 +6980,7 @@
       </c>
       <c r="D243" t="inlineStr">
         <is>
-          <t>etc</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E243" t="inlineStr">
@@ -7034,12 +7034,12 @@
       </c>
       <c r="D245" t="inlineStr">
         <is>
-          <t>etc</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="E245" t="inlineStr">
         <is>
-          <t>etc</t>
+          <t>미분류</t>
         </is>
       </c>
     </row>
@@ -7385,7 +7385,7 @@
       </c>
       <c r="D258" t="inlineStr">
         <is>
-          <t>etc</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E258" t="inlineStr">
@@ -7547,7 +7547,7 @@
       </c>
       <c r="D264" t="inlineStr">
         <is>
-          <t>etc</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E264" t="inlineStr">
@@ -7574,7 +7574,7 @@
       </c>
       <c r="D265" t="inlineStr">
         <is>
-          <t>etc</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E265" t="inlineStr">
@@ -7601,7 +7601,7 @@
       </c>
       <c r="D266" t="inlineStr">
         <is>
-          <t>etc</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E266" t="inlineStr">
@@ -7709,7 +7709,7 @@
       </c>
       <c r="D270" t="inlineStr">
         <is>
-          <t>etc</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E270" t="inlineStr">
@@ -7736,7 +7736,7 @@
       </c>
       <c r="D271" t="inlineStr">
         <is>
-          <t>etc</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E271" t="inlineStr">
@@ -7817,7 +7817,7 @@
       </c>
       <c r="D274" t="inlineStr">
         <is>
-          <t>etc</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E274" t="inlineStr">
@@ -7898,7 +7898,7 @@
       </c>
       <c r="D277" t="inlineStr">
         <is>
-          <t>etc</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E277" t="inlineStr">
@@ -7925,7 +7925,7 @@
       </c>
       <c r="D278" t="inlineStr">
         <is>
-          <t>etc</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E278" t="inlineStr">
@@ -8222,7 +8222,7 @@
       </c>
       <c r="D289" t="inlineStr">
         <is>
-          <t>etc</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E289" t="inlineStr">
@@ -8546,7 +8546,7 @@
       </c>
       <c r="D301" t="inlineStr">
         <is>
-          <t>etc</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E301" t="inlineStr">
@@ -8924,7 +8924,7 @@
       </c>
       <c r="D315" t="inlineStr">
         <is>
-          <t>etc</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E315" t="inlineStr">
@@ -9032,7 +9032,7 @@
       </c>
       <c r="D319" t="inlineStr">
         <is>
-          <t>etc</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E319" t="inlineStr">
@@ -9275,7 +9275,7 @@
       </c>
       <c r="D328" t="inlineStr">
         <is>
-          <t>etc</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E328" t="inlineStr">
@@ -9329,7 +9329,7 @@
       </c>
       <c r="D330" t="inlineStr">
         <is>
-          <t>etc</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E330" t="inlineStr">
@@ -9410,7 +9410,7 @@
       </c>
       <c r="D333" t="inlineStr">
         <is>
-          <t>etc</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E333" t="inlineStr">
@@ -9437,7 +9437,7 @@
       </c>
       <c r="D334" t="inlineStr">
         <is>
-          <t>etc</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E334" t="inlineStr">
@@ -9545,7 +9545,7 @@
       </c>
       <c r="D338" t="inlineStr">
         <is>
-          <t>etc</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E338" t="inlineStr">
@@ -9572,7 +9572,7 @@
       </c>
       <c r="D339" t="inlineStr">
         <is>
-          <t>etc</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E339" t="inlineStr">
@@ -9842,7 +9842,7 @@
       </c>
       <c r="D349" t="inlineStr">
         <is>
-          <t>etc</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E349" t="inlineStr">
@@ -9896,7 +9896,7 @@
       </c>
       <c r="D351" t="inlineStr">
         <is>
-          <t>etc</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E351" t="inlineStr">
@@ -10166,7 +10166,7 @@
       </c>
       <c r="D361" t="inlineStr">
         <is>
-          <t>etc</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E361" t="inlineStr">
@@ -10328,12 +10328,12 @@
       </c>
       <c r="D367" t="inlineStr">
         <is>
-          <t>etc</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="E367" t="inlineStr">
         <is>
-          <t>etc</t>
+          <t>미분류</t>
         </is>
       </c>
     </row>
@@ -10598,12 +10598,12 @@
       </c>
       <c r="D377" t="inlineStr">
         <is>
-          <t>etc</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="E377" t="inlineStr">
         <is>
-          <t>etc</t>
+          <t>미분류</t>
         </is>
       </c>
     </row>
@@ -10814,7 +10814,7 @@
       </c>
       <c r="D385" t="inlineStr">
         <is>
-          <t>etc</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E385" t="inlineStr">
@@ -10922,7 +10922,7 @@
       </c>
       <c r="D389" t="inlineStr">
         <is>
-          <t>etc</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E389" t="inlineStr">
@@ -10976,7 +10976,7 @@
       </c>
       <c r="D391" t="inlineStr">
         <is>
-          <t>etc</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E391" t="inlineStr">
@@ -11057,7 +11057,7 @@
       </c>
       <c r="D394" t="inlineStr">
         <is>
-          <t>etc</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E394" t="inlineStr">
@@ -11111,7 +11111,7 @@
       </c>
       <c r="D396" t="inlineStr">
         <is>
-          <t>etc</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E396" t="inlineStr">
@@ -11327,7 +11327,7 @@
       </c>
       <c r="D404" t="inlineStr">
         <is>
-          <t>etc</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E404" t="inlineStr">
@@ -11381,7 +11381,7 @@
       </c>
       <c r="D406" t="inlineStr">
         <is>
-          <t>etc</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E406" t="inlineStr">
@@ -11867,7 +11867,7 @@
       </c>
       <c r="D424" t="inlineStr">
         <is>
-          <t>etc</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E424" t="inlineStr">
@@ -11921,7 +11921,7 @@
       </c>
       <c r="D426" t="inlineStr">
         <is>
-          <t>etc</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E426" t="inlineStr">
@@ -11948,7 +11948,7 @@
       </c>
       <c r="D427" t="inlineStr">
         <is>
-          <t>etc</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E427" t="inlineStr">
@@ -12083,7 +12083,7 @@
       </c>
       <c r="D432" t="inlineStr">
         <is>
-          <t>etc</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E432" t="inlineStr">
@@ -12164,7 +12164,7 @@
       </c>
       <c r="D435" t="inlineStr">
         <is>
-          <t>etc</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E435" t="inlineStr">
@@ -12218,12 +12218,12 @@
       </c>
       <c r="D437" t="inlineStr">
         <is>
-          <t>etc</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="E437" t="inlineStr">
         <is>
-          <t>etc</t>
+          <t>미분류</t>
         </is>
       </c>
     </row>
@@ -12353,12 +12353,12 @@
       </c>
       <c r="D442" t="inlineStr">
         <is>
-          <t>etc</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="E442" t="inlineStr">
         <is>
-          <t>etc</t>
+          <t>미분류</t>
         </is>
       </c>
     </row>
@@ -12515,7 +12515,7 @@
       </c>
       <c r="D448" t="inlineStr">
         <is>
-          <t>etc</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E448" t="inlineStr">
@@ -12596,7 +12596,7 @@
       </c>
       <c r="D451" t="inlineStr">
         <is>
-          <t>etc</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E451" t="inlineStr">
@@ -12839,7 +12839,7 @@
       </c>
       <c r="D460" t="inlineStr">
         <is>
-          <t>etc</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E460" t="inlineStr">
@@ -12866,7 +12866,7 @@
       </c>
       <c r="D461" t="inlineStr">
         <is>
-          <t>etc</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E461" t="inlineStr">
@@ -12974,12 +12974,12 @@
       </c>
       <c r="D465" t="inlineStr">
         <is>
-          <t>etc</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="E465" t="inlineStr">
         <is>
-          <t>etc</t>
+          <t>미분류</t>
         </is>
       </c>
     </row>
@@ -13001,7 +13001,7 @@
       </c>
       <c r="D466" t="inlineStr">
         <is>
-          <t>etc</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E466" t="inlineStr">
@@ -13028,7 +13028,7 @@
       </c>
       <c r="D467" t="inlineStr">
         <is>
-          <t>etc</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E467" t="inlineStr">
@@ -13040,54 +13040,54 @@
     <row r="468">
       <c r="A468" t="inlineStr">
         <is>
-          <t>kk_4839170665</t>
+          <t>kwon9493</t>
         </is>
       </c>
       <c r="B468" t="inlineStr">
         <is>
-          <t>01050116666</t>
+          <t>01035589493</t>
         </is>
       </c>
       <c r="C468" t="inlineStr">
         <is>
-          <t>304086</t>
+          <t>107077</t>
         </is>
       </c>
       <c r="D468" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="E468" t="inlineStr">
         <is>
-          <t>EFW</t>
+          <t>Direct</t>
         </is>
       </c>
     </row>
     <row r="469">
       <c r="A469" t="inlineStr">
         <is>
-          <t>kwon9493</t>
+          <t>kk_4839170665</t>
         </is>
       </c>
       <c r="B469" t="inlineStr">
         <is>
-          <t>01035589493</t>
+          <t>01050116666</t>
         </is>
       </c>
       <c r="C469" t="inlineStr">
         <is>
-          <t>107077</t>
+          <t>304086</t>
         </is>
       </c>
       <c r="D469" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E469" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>EFW</t>
         </is>
       </c>
     </row>
@@ -13163,7 +13163,7 @@
       </c>
       <c r="D472" t="inlineStr">
         <is>
-          <t>etc</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E472" t="inlineStr">
@@ -13379,7 +13379,7 @@
       </c>
       <c r="D480" t="inlineStr">
         <is>
-          <t>etc</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E480" t="inlineStr">
@@ -13406,7 +13406,7 @@
       </c>
       <c r="D481" t="inlineStr">
         <is>
-          <t>etc</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E481" t="inlineStr">
@@ -13541,7 +13541,7 @@
       </c>
       <c r="D486" t="inlineStr">
         <is>
-          <t>etc</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E486" t="inlineStr">
@@ -13649,7 +13649,7 @@
       </c>
       <c r="D490" t="inlineStr">
         <is>
-          <t>etc</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E490" t="inlineStr">
@@ -13676,7 +13676,7 @@
       </c>
       <c r="D491" t="inlineStr">
         <is>
-          <t>etc</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E491" t="inlineStr">
@@ -13811,12 +13811,12 @@
       </c>
       <c r="D496" t="inlineStr">
         <is>
-          <t>etc</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="E496" t="inlineStr">
         <is>
-          <t>etc</t>
+          <t>미분류</t>
         </is>
       </c>
     </row>
@@ -14027,7 +14027,7 @@
       </c>
       <c r="D504" t="inlineStr">
         <is>
-          <t>etc</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E504" t="inlineStr">
@@ -14189,12 +14189,12 @@
       </c>
       <c r="D510" t="inlineStr">
         <is>
-          <t>etc</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="E510" t="inlineStr">
         <is>
-          <t>etc</t>
+          <t>미분류</t>
         </is>
       </c>
     </row>
@@ -14459,7 +14459,7 @@
       </c>
       <c r="D520" t="inlineStr">
         <is>
-          <t>etc</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E520" t="inlineStr">
@@ -14486,7 +14486,7 @@
       </c>
       <c r="D521" t="inlineStr">
         <is>
-          <t>etc</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E521" t="inlineStr">
@@ -14621,7 +14621,7 @@
       </c>
       <c r="D526" t="inlineStr">
         <is>
-          <t>etc</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E526" t="inlineStr">
@@ -14702,7 +14702,7 @@
       </c>
       <c r="D529" t="inlineStr">
         <is>
-          <t>etc</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E529" t="inlineStr">
@@ -15242,7 +15242,7 @@
       </c>
       <c r="D549" t="inlineStr">
         <is>
-          <t>etc</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E549" t="inlineStr">
@@ -15647,7 +15647,7 @@
       </c>
       <c r="D564" t="inlineStr">
         <is>
-          <t>etc</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E564" t="inlineStr">
@@ -15755,7 +15755,7 @@
       </c>
       <c r="D568" t="inlineStr">
         <is>
-          <t>etc</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E568" t="inlineStr">
@@ -15836,7 +15836,7 @@
       </c>
       <c r="D571" t="inlineStr">
         <is>
-          <t>etc</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E571" t="inlineStr">
@@ -16241,7 +16241,7 @@
       </c>
       <c r="D586" t="inlineStr">
         <is>
-          <t>etc</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E586" t="inlineStr">
@@ -16268,7 +16268,7 @@
       </c>
       <c r="D587" t="inlineStr">
         <is>
-          <t>etc</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E587" t="inlineStr">
@@ -16376,7 +16376,7 @@
       </c>
       <c r="D591" t="inlineStr">
         <is>
-          <t>etc</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E591" t="inlineStr">
@@ -16403,12 +16403,12 @@
       </c>
       <c r="D592" t="inlineStr">
         <is>
-          <t>etc</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="E592" t="inlineStr">
         <is>
-          <t>etc</t>
+          <t>미분류</t>
         </is>
       </c>
     </row>
@@ -16430,7 +16430,7 @@
       </c>
       <c r="D593" t="inlineStr">
         <is>
-          <t>etc</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E593" t="inlineStr">
@@ -16457,7 +16457,7 @@
       </c>
       <c r="D594" t="inlineStr">
         <is>
-          <t>etc</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E594" t="inlineStr">
@@ -16673,7 +16673,7 @@
       </c>
       <c r="D602" t="inlineStr">
         <is>
-          <t>etc</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E602" t="inlineStr">
@@ -16700,7 +16700,7 @@
       </c>
       <c r="D603" t="inlineStr">
         <is>
-          <t>etc</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E603" t="inlineStr">
@@ -16781,7 +16781,7 @@
       </c>
       <c r="D606" t="inlineStr">
         <is>
-          <t>etc</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E606" t="inlineStr">
@@ -16808,7 +16808,7 @@
       </c>
       <c r="D607" t="inlineStr">
         <is>
-          <t>etc</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E607" t="inlineStr">
@@ -16835,7 +16835,7 @@
       </c>
       <c r="D608" t="inlineStr">
         <is>
-          <t>etc</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E608" t="inlineStr">
@@ -16889,7 +16889,7 @@
       </c>
       <c r="D610" t="inlineStr">
         <is>
-          <t>etc</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E610" t="inlineStr">
@@ -16997,7 +16997,7 @@
       </c>
       <c r="D614" t="inlineStr">
         <is>
-          <t>etc</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E614" t="inlineStr">
@@ -17051,7 +17051,7 @@
       </c>
       <c r="D616" t="inlineStr">
         <is>
-          <t>etc</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E616" t="inlineStr">
@@ -17105,7 +17105,7 @@
       </c>
       <c r="D618" t="inlineStr">
         <is>
-          <t>etc</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E618" t="inlineStr">
@@ -17132,7 +17132,7 @@
       </c>
       <c r="D619" t="inlineStr">
         <is>
-          <t>etc</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E619" t="inlineStr">
@@ -17159,7 +17159,7 @@
       </c>
       <c r="D620" t="inlineStr">
         <is>
-          <t>etc</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E620" t="inlineStr">
@@ -17213,12 +17213,12 @@
       </c>
       <c r="D622" t="inlineStr">
         <is>
-          <t>etc</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="E622" t="inlineStr">
         <is>
-          <t>etc</t>
+          <t>미분류</t>
         </is>
       </c>
     </row>
@@ -17375,7 +17375,7 @@
       </c>
       <c r="D628" t="inlineStr">
         <is>
-          <t>etc</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E628" t="inlineStr">
@@ -17429,7 +17429,7 @@
       </c>
       <c r="D630" t="inlineStr">
         <is>
-          <t>etc</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E630" t="inlineStr">
@@ -17456,7 +17456,7 @@
       </c>
       <c r="D631" t="inlineStr">
         <is>
-          <t>etc</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E631" t="inlineStr">
@@ -17495,17 +17495,17 @@
     <row r="633">
       <c r="A633" t="inlineStr">
         <is>
-          <t>kk_3483300064</t>
+          <t>kk_4789688431</t>
         </is>
       </c>
       <c r="B633" t="inlineStr">
         <is>
-          <t>01092213404</t>
+          <t>01099981265</t>
         </is>
       </c>
       <c r="C633" t="inlineStr">
         <is>
-          <t>244619</t>
+          <t>302023</t>
         </is>
       </c>
       <c r="D633" t="inlineStr">
@@ -17515,24 +17515,24 @@
       </c>
       <c r="E633" t="inlineStr">
         <is>
-          <t>naver_brandsearch_mobile</t>
+          <t>sa</t>
         </is>
       </c>
     </row>
     <row r="634">
       <c r="A634" t="inlineStr">
         <is>
-          <t>kk_4789688431</t>
+          <t>kk_3483300064</t>
         </is>
       </c>
       <c r="B634" t="inlineStr">
         <is>
-          <t>01099981265</t>
+          <t>01092213404</t>
         </is>
       </c>
       <c r="C634" t="inlineStr">
         <is>
-          <t>302023</t>
+          <t>244619</t>
         </is>
       </c>
       <c r="D634" t="inlineStr">
@@ -17542,7 +17542,7 @@
       </c>
       <c r="E634" t="inlineStr">
         <is>
-          <t>sa</t>
+          <t>naver_brandsearch_mobile</t>
         </is>
       </c>
     </row>
@@ -17699,7 +17699,7 @@
       </c>
       <c r="D640" t="inlineStr">
         <is>
-          <t>etc</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E640" t="inlineStr">
@@ -17753,7 +17753,7 @@
       </c>
       <c r="D642" t="inlineStr">
         <is>
-          <t>etc</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E642" t="inlineStr">
@@ -17780,7 +17780,7 @@
       </c>
       <c r="D643" t="inlineStr">
         <is>
-          <t>etc</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E643" t="inlineStr">
@@ -17807,7 +17807,7 @@
       </c>
       <c r="D644" t="inlineStr">
         <is>
-          <t>etc</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E644" t="inlineStr">
@@ -17900,44 +17900,44 @@
     <row r="648">
       <c r="A648" t="inlineStr">
         <is>
-          <t>zizou95</t>
+          <t>kk_3185218103</t>
         </is>
       </c>
       <c r="B648" t="inlineStr">
         <is>
-          <t>01049139545</t>
+          <t>01023796438</t>
         </is>
       </c>
       <c r="C648" t="inlineStr">
         <is>
-          <t>176662</t>
+          <t>229444</t>
         </is>
       </c>
       <c r="D648" t="inlineStr">
         <is>
-          <t>etc</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E648" t="inlineStr">
         <is>
-          <t>LMS_ECOM_familycoupon</t>
+          <t>KAKAO_alimtalk</t>
         </is>
       </c>
     </row>
     <row r="649">
       <c r="A649" t="inlineStr">
         <is>
-          <t>kk_3185218103</t>
+          <t>zizou95</t>
         </is>
       </c>
       <c r="B649" t="inlineStr">
         <is>
-          <t>01023796438</t>
+          <t>01049139545</t>
         </is>
       </c>
       <c r="C649" t="inlineStr">
         <is>
-          <t>229444</t>
+          <t>176662</t>
         </is>
       </c>
       <c r="D649" t="inlineStr">
@@ -17947,7 +17947,7 @@
       </c>
       <c r="E649" t="inlineStr">
         <is>
-          <t>KAKAO_alimtalk</t>
+          <t>LMS_ECOM_familycoupon</t>
         </is>
       </c>
     </row>
@@ -17996,7 +17996,7 @@
       </c>
       <c r="D651" t="inlineStr">
         <is>
-          <t>etc</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E651" t="inlineStr">
@@ -18104,7 +18104,7 @@
       </c>
       <c r="D655" t="inlineStr">
         <is>
-          <t>etc</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E655" t="inlineStr">
@@ -18158,12 +18158,12 @@
       </c>
       <c r="D657" t="inlineStr">
         <is>
-          <t>etc</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="E657" t="inlineStr">
         <is>
-          <t>etc</t>
+          <t>미분류</t>
         </is>
       </c>
     </row>
@@ -18212,7 +18212,7 @@
       </c>
       <c r="D659" t="inlineStr">
         <is>
-          <t>etc</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E659" t="inlineStr">
@@ -18239,7 +18239,7 @@
       </c>
       <c r="D660" t="inlineStr">
         <is>
-          <t>etc</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E660" t="inlineStr">
@@ -18320,7 +18320,7 @@
       </c>
       <c r="D663" t="inlineStr">
         <is>
-          <t>etc</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E663" t="inlineStr">
@@ -18401,7 +18401,7 @@
       </c>
       <c r="D666" t="inlineStr">
         <is>
-          <t>etc</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E666" t="inlineStr">
@@ -18536,7 +18536,7 @@
       </c>
       <c r="D671" t="inlineStr">
         <is>
-          <t>etc</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E671" t="inlineStr">
@@ -18590,7 +18590,7 @@
       </c>
       <c r="D673" t="inlineStr">
         <is>
-          <t>etc</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E673" t="inlineStr">
@@ -18833,7 +18833,7 @@
       </c>
       <c r="D682" t="inlineStr">
         <is>
-          <t>etc</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E682" t="inlineStr">
@@ -18914,7 +18914,7 @@
       </c>
       <c r="D685" t="inlineStr">
         <is>
-          <t>etc</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E685" t="inlineStr">
@@ -18941,12 +18941,12 @@
       </c>
       <c r="D686" t="inlineStr">
         <is>
-          <t>etc</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="E686" t="inlineStr">
         <is>
-          <t>etc</t>
+          <t>미분류</t>
         </is>
       </c>
     </row>
@@ -19034,22 +19034,22 @@
     <row r="690">
       <c r="A690" t="inlineStr">
         <is>
-          <t>lamerkmk</t>
+          <t>shine310</t>
         </is>
       </c>
       <c r="B690" t="inlineStr">
         <is>
-          <t>01030658494</t>
+          <t>01030650847</t>
         </is>
       </c>
       <c r="C690" t="inlineStr">
         <is>
-          <t>167002</t>
+          <t>171606</t>
         </is>
       </c>
       <c r="D690" t="inlineStr">
         <is>
-          <t>etc</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E690" t="inlineStr">
@@ -19061,22 +19061,22 @@
     <row r="691">
       <c r="A691" t="inlineStr">
         <is>
-          <t>shine310</t>
+          <t>lamerkmk</t>
         </is>
       </c>
       <c r="B691" t="inlineStr">
         <is>
-          <t>01030650847</t>
+          <t>01030658494</t>
         </is>
       </c>
       <c r="C691" t="inlineStr">
         <is>
-          <t>171606</t>
+          <t>167002</t>
         </is>
       </c>
       <c r="D691" t="inlineStr">
         <is>
-          <t>etc</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E691" t="inlineStr">
@@ -19103,7 +19103,7 @@
       </c>
       <c r="D692" t="inlineStr">
         <is>
-          <t>etc</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E692" t="inlineStr">
@@ -19130,7 +19130,7 @@
       </c>
       <c r="D693" t="inlineStr">
         <is>
-          <t>etc</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E693" t="inlineStr">
@@ -19292,7 +19292,7 @@
       </c>
       <c r="D699" t="inlineStr">
         <is>
-          <t>etc</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E699" t="inlineStr">
@@ -19427,7 +19427,7 @@
       </c>
       <c r="D704" t="inlineStr">
         <is>
-          <t>etc</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E704" t="inlineStr">
@@ -19589,7 +19589,7 @@
       </c>
       <c r="D710" t="inlineStr">
         <is>
-          <t>etc</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E710" t="inlineStr">
@@ -19616,7 +19616,7 @@
       </c>
       <c r="D711" t="inlineStr">
         <is>
-          <t>etc</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E711" t="inlineStr">
@@ -19643,7 +19643,7 @@
       </c>
       <c r="D712" t="inlineStr">
         <is>
-          <t>etc</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E712" t="inlineStr">
@@ -19778,7 +19778,7 @@
       </c>
       <c r="D717" t="inlineStr">
         <is>
-          <t>etc</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E717" t="inlineStr">
@@ -19805,7 +19805,7 @@
       </c>
       <c r="D718" t="inlineStr">
         <is>
-          <t>etc</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E718" t="inlineStr">
@@ -19940,7 +19940,7 @@
       </c>
       <c r="D723" t="inlineStr">
         <is>
-          <t>etc</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E723" t="inlineStr">
@@ -19967,7 +19967,7 @@
       </c>
       <c r="D724" t="inlineStr">
         <is>
-          <t>etc</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E724" t="inlineStr">
@@ -20141,17 +20141,17 @@
     <row r="731">
       <c r="A731" t="inlineStr">
         <is>
-          <t>kk_4840658838</t>
+          <t>kk_4840846776</t>
         </is>
       </c>
       <c r="B731" t="inlineStr">
         <is>
-          <t>01039292600</t>
+          <t>01055961435</t>
         </is>
       </c>
       <c r="C731" t="inlineStr">
         <is>
-          <t>304158</t>
+          <t>304170</t>
         </is>
       </c>
       <c r="D731" t="inlineStr">
@@ -20161,24 +20161,24 @@
       </c>
       <c r="E731" t="inlineStr">
         <is>
-          <t>EFW</t>
+          <t>[PF]전환_회원가입(유사)</t>
         </is>
       </c>
     </row>
     <row r="732">
       <c r="A732" t="inlineStr">
         <is>
-          <t>kk_4840846776</t>
+          <t>kk_4840658838</t>
         </is>
       </c>
       <c r="B732" t="inlineStr">
         <is>
-          <t>01055961435</t>
+          <t>01039292600</t>
         </is>
       </c>
       <c r="C732" t="inlineStr">
         <is>
-          <t>304170</t>
+          <t>304158</t>
         </is>
       </c>
       <c r="D732" t="inlineStr">
@@ -20188,7 +20188,7 @@
       </c>
       <c r="E732" t="inlineStr">
         <is>
-          <t>[PF]전환_회원가입(유사)</t>
+          <t>EFW</t>
         </is>
       </c>
     </row>
@@ -20264,7 +20264,7 @@
       </c>
       <c r="D735" t="inlineStr">
         <is>
-          <t>etc</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E735" t="inlineStr">
@@ -20276,22 +20276,22 @@
     <row r="736">
       <c r="A736" t="inlineStr">
         <is>
-          <t>kk_3410691755</t>
+          <t>martyj</t>
         </is>
       </c>
       <c r="B736" t="inlineStr">
         <is>
-          <t>01084564028</t>
+          <t>01073535824</t>
         </is>
       </c>
       <c r="C736" t="inlineStr">
         <is>
-          <t>241474</t>
+          <t>194752</t>
         </is>
       </c>
       <c r="D736" t="inlineStr">
         <is>
-          <t>etc</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E736" t="inlineStr">
@@ -20303,22 +20303,22 @@
     <row r="737">
       <c r="A737" t="inlineStr">
         <is>
-          <t>martyj</t>
+          <t>k032010</t>
         </is>
       </c>
       <c r="B737" t="inlineStr">
         <is>
-          <t>01073535824</t>
+          <t>01090792133</t>
         </is>
       </c>
       <c r="C737" t="inlineStr">
         <is>
-          <t>194752</t>
+          <t>204481</t>
         </is>
       </c>
       <c r="D737" t="inlineStr">
         <is>
-          <t>etc</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E737" t="inlineStr">
@@ -20330,22 +20330,22 @@
     <row r="738">
       <c r="A738" t="inlineStr">
         <is>
-          <t>k032010</t>
+          <t>kk_3410691755</t>
         </is>
       </c>
       <c r="B738" t="inlineStr">
         <is>
-          <t>01090792133</t>
+          <t>01084564028</t>
         </is>
       </c>
       <c r="C738" t="inlineStr">
         <is>
-          <t>204481</t>
+          <t>241474</t>
         </is>
       </c>
       <c r="D738" t="inlineStr">
         <is>
-          <t>etc</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E738" t="inlineStr">
@@ -20372,7 +20372,7 @@
       </c>
       <c r="D739" t="inlineStr">
         <is>
-          <t>etc</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E739" t="inlineStr">
@@ -20399,7 +20399,7 @@
       </c>
       <c r="D740" t="inlineStr">
         <is>
-          <t>etc</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E740" t="inlineStr">
@@ -20453,7 +20453,7 @@
       </c>
       <c r="D742" t="inlineStr">
         <is>
-          <t>etc</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E742" t="inlineStr">
@@ -20480,7 +20480,7 @@
       </c>
       <c r="D743" t="inlineStr">
         <is>
-          <t>etc</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E743" t="inlineStr">
@@ -20615,12 +20615,12 @@
       </c>
       <c r="D748" t="inlineStr">
         <is>
-          <t>etc</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="E748" t="inlineStr">
         <is>
-          <t>etc</t>
+          <t>미분류</t>
         </is>
       </c>
     </row>
@@ -20669,7 +20669,7 @@
       </c>
       <c r="D750" t="inlineStr">
         <is>
-          <t>etc</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E750" t="inlineStr">
@@ -20696,7 +20696,7 @@
       </c>
       <c r="D751" t="inlineStr">
         <is>
-          <t>etc</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E751" t="inlineStr">
@@ -20831,12 +20831,12 @@
       </c>
       <c r="D756" t="inlineStr">
         <is>
-          <t>etc</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="E756" t="inlineStr">
         <is>
-          <t>etc</t>
+          <t>미분류</t>
         </is>
       </c>
     </row>
@@ -20912,7 +20912,7 @@
       </c>
       <c r="D759" t="inlineStr">
         <is>
-          <t>etc</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E759" t="inlineStr">
@@ -20924,76 +20924,76 @@
     <row r="760">
       <c r="A760" t="inlineStr">
         <is>
-          <t>kk_2936953873</t>
+          <t>kk_4615020382</t>
         </is>
       </c>
       <c r="B760" t="inlineStr">
         <is>
-          <t>01098328667</t>
+          <t>01092438164</t>
         </is>
       </c>
       <c r="C760" t="inlineStr">
         <is>
-          <t>216255</t>
+          <t>290598</t>
         </is>
       </c>
       <c r="D760" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E760" t="inlineStr">
         <is>
-          <t>naver_brandsearch_mobile</t>
+          <t>LMS_ECOM_200416_family</t>
         </is>
       </c>
     </row>
     <row r="761">
       <c r="A761" t="inlineStr">
         <is>
-          <t>kk_3180181891</t>
+          <t>kk_2936953873</t>
         </is>
       </c>
       <c r="B761" t="inlineStr">
         <is>
-          <t>01065587969</t>
+          <t>01098328667</t>
         </is>
       </c>
       <c r="C761" t="inlineStr">
         <is>
-          <t>225645</t>
+          <t>216255</t>
         </is>
       </c>
       <c r="D761" t="inlineStr">
         <is>
-          <t>etc</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E761" t="inlineStr">
         <is>
-          <t>LMS_ECOM_200416_family</t>
+          <t>naver_brandsearch_mobile</t>
         </is>
       </c>
     </row>
     <row r="762">
       <c r="A762" t="inlineStr">
         <is>
-          <t>kk_4615020382</t>
+          <t>kk_3180181891</t>
         </is>
       </c>
       <c r="B762" t="inlineStr">
         <is>
-          <t>01092438164</t>
+          <t>01065587969</t>
         </is>
       </c>
       <c r="C762" t="inlineStr">
         <is>
-          <t>290598</t>
+          <t>225645</t>
         </is>
       </c>
       <c r="D762" t="inlineStr">
         <is>
-          <t>etc</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E762" t="inlineStr">
@@ -21047,7 +21047,7 @@
       </c>
       <c r="D764" t="inlineStr">
         <is>
-          <t>etc</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E764" t="inlineStr">
@@ -21074,7 +21074,7 @@
       </c>
       <c r="D765" t="inlineStr">
         <is>
-          <t>etc</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E765" t="inlineStr">
@@ -21506,66 +21506,66 @@
       </c>
       <c r="D781" t="inlineStr">
         <is>
-          <t>etc</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="E781" t="inlineStr">
         <is>
-          <t>etc</t>
+          <t>미분류</t>
         </is>
       </c>
     </row>
     <row r="782">
       <c r="A782" t="inlineStr">
         <is>
-          <t>kk_3224050214</t>
+          <t>jgj0503</t>
         </is>
       </c>
       <c r="B782" t="inlineStr">
         <is>
-          <t>01082488899</t>
+          <t>01063315178</t>
         </is>
       </c>
       <c r="C782" t="inlineStr">
         <is>
-          <t>232892</t>
+          <t>303605</t>
         </is>
       </c>
       <c r="D782" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E782" t="inlineStr">
         <is>
-          <t>KAKAO_alimtalk</t>
+          <t>6968489536332</t>
         </is>
       </c>
     </row>
     <row r="783">
       <c r="A783" t="inlineStr">
         <is>
-          <t>jgj0503</t>
+          <t>kk_3224050214</t>
         </is>
       </c>
       <c r="B783" t="inlineStr">
         <is>
-          <t>01063315178</t>
+          <t>01082488899</t>
         </is>
       </c>
       <c r="C783" t="inlineStr">
         <is>
-          <t>303605</t>
+          <t>232892</t>
         </is>
       </c>
       <c r="D783" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E783" t="inlineStr">
         <is>
-          <t>6968489536332</t>
+          <t>KAKAO_alimtalk</t>
         </is>
       </c>
     </row>
@@ -21749,12 +21749,12 @@
       </c>
       <c r="D790" t="inlineStr">
         <is>
-          <t>etc</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="E790" t="inlineStr">
         <is>
-          <t>etc</t>
+          <t>미분류</t>
         </is>
       </c>
     </row>
@@ -21803,7 +21803,7 @@
       </c>
       <c r="D792" t="inlineStr">
         <is>
-          <t>etc</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E792" t="inlineStr">
@@ -21830,7 +21830,7 @@
       </c>
       <c r="D793" t="inlineStr">
         <is>
-          <t>etc</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E793" t="inlineStr">
@@ -21911,7 +21911,7 @@
       </c>
       <c r="D796" t="inlineStr">
         <is>
-          <t>etc</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E796" t="inlineStr">
@@ -21923,17 +21923,17 @@
     <row r="797">
       <c r="A797" t="inlineStr">
         <is>
-          <t>kk_2915134680</t>
+          <t>kk_4288273717</t>
         </is>
       </c>
       <c r="B797" t="inlineStr">
         <is>
-          <t>01085224711</t>
+          <t>01020746624</t>
         </is>
       </c>
       <c r="C797" t="inlineStr">
         <is>
-          <t>215670</t>
+          <t>275762</t>
         </is>
       </c>
       <c r="D797" t="inlineStr">
@@ -21943,34 +21943,34 @@
       </c>
       <c r="E797" t="inlineStr">
         <is>
-          <t>KAKAO_CH_MESSAGE_0409_HIKE365SUMMER</t>
+          <t>LMS_ECOM_0410exclusive2</t>
         </is>
       </c>
     </row>
     <row r="798">
       <c r="A798" t="inlineStr">
         <is>
-          <t>kk_4288273717</t>
+          <t>kk_2915134680</t>
         </is>
       </c>
       <c r="B798" t="inlineStr">
         <is>
-          <t>01020746624</t>
+          <t>01085224711</t>
         </is>
       </c>
       <c r="C798" t="inlineStr">
         <is>
-          <t>275762</t>
+          <t>215670</t>
         </is>
       </c>
       <c r="D798" t="inlineStr">
         <is>
-          <t>etc</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E798" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0410exclusive2</t>
+          <t>KAKAO_CH_MESSAGE_0409_HIKE365SUMMER</t>
         </is>
       </c>
     </row>
@@ -21992,7 +21992,7 @@
       </c>
       <c r="D799" t="inlineStr">
         <is>
-          <t>etc</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E799" t="inlineStr">
@@ -22085,22 +22085,22 @@
     <row r="803">
       <c r="A803" t="inlineStr">
         <is>
-          <t>kk_3101119679</t>
+          <t>hun7662</t>
         </is>
       </c>
       <c r="B803" t="inlineStr">
         <is>
-          <t>01093993852</t>
+          <t>01042311474</t>
         </is>
       </c>
       <c r="C803" t="inlineStr">
         <is>
-          <t>221630</t>
+          <t>172790</t>
         </is>
       </c>
       <c r="D803" t="inlineStr">
         <is>
-          <t>etc</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E803" t="inlineStr">
@@ -22112,22 +22112,22 @@
     <row r="804">
       <c r="A804" t="inlineStr">
         <is>
-          <t>hun7662</t>
+          <t>kk_3101119679</t>
         </is>
       </c>
       <c r="B804" t="inlineStr">
         <is>
-          <t>01042311474</t>
+          <t>01093993852</t>
         </is>
       </c>
       <c r="C804" t="inlineStr">
         <is>
-          <t>172790</t>
+          <t>221630</t>
         </is>
       </c>
       <c r="D804" t="inlineStr">
         <is>
-          <t>etc</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E804" t="inlineStr">
@@ -22316,7 +22316,7 @@
       </c>
       <c r="D811" t="inlineStr">
         <is>
-          <t>etc</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E811" t="inlineStr">
@@ -22397,7 +22397,7 @@
       </c>
       <c r="D814" t="inlineStr">
         <is>
-          <t>etc</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E814" t="inlineStr">
@@ -22424,7 +22424,7 @@
       </c>
       <c r="D815" t="inlineStr">
         <is>
-          <t>etc</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E815" t="inlineStr">
@@ -22490,135 +22490,135 @@
     <row r="818">
       <c r="A818" t="inlineStr">
         <is>
-          <t>kk_4839765445</t>
+          <t>sun1381</t>
         </is>
       </c>
       <c r="B818" t="inlineStr">
         <is>
-          <t>01076118972</t>
+          <t>01037709416</t>
         </is>
       </c>
       <c r="C818" t="inlineStr">
         <is>
-          <t>304111</t>
+          <t>278160</t>
         </is>
       </c>
       <c r="D818" t="inlineStr">
         <is>
-          <t>Organic Traffic</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E818" t="inlineStr">
         <is>
-          <t>(referral)</t>
+          <t>LMS_ECOM_0410exclusive2</t>
         </is>
       </c>
     </row>
     <row r="819">
       <c r="A819" t="inlineStr">
         <is>
-          <t>sun1381</t>
+          <t>kk_4839145768</t>
         </is>
       </c>
       <c r="B819" t="inlineStr">
         <is>
-          <t>01037709416</t>
+          <t>01097367898</t>
         </is>
       </c>
       <c r="C819" t="inlineStr">
         <is>
-          <t>278160</t>
+          <t>304085</t>
         </is>
       </c>
       <c r="D819" t="inlineStr">
         <is>
-          <t>etc</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E819" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0410exclusive2</t>
+          <t>naver_brandsearch_pc</t>
         </is>
       </c>
     </row>
     <row r="820">
       <c r="A820" t="inlineStr">
         <is>
-          <t>kk_4839145768</t>
+          <t>kk_4839765445</t>
         </is>
       </c>
       <c r="B820" t="inlineStr">
         <is>
-          <t>01097367898</t>
+          <t>01076118972</t>
         </is>
       </c>
       <c r="C820" t="inlineStr">
         <is>
-          <t>304085</t>
+          <t>304111</t>
         </is>
       </c>
       <c r="D820" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Organic Traffic</t>
         </is>
       </c>
       <c r="E820" t="inlineStr">
         <is>
-          <t>naver_brandsearch_pc</t>
+          <t>(referral)</t>
         </is>
       </c>
     </row>
     <row r="821">
       <c r="A821" t="inlineStr">
         <is>
-          <t>kk_3825766318</t>
+          <t>okj2377</t>
         </is>
       </c>
       <c r="B821" t="inlineStr">
         <is>
-          <t>01020085185</t>
+          <t>01033661268</t>
         </is>
       </c>
       <c r="C821" t="inlineStr">
         <is>
-          <t>263222</t>
+          <t>139452</t>
         </is>
       </c>
       <c r="D821" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E821" t="inlineStr">
         <is>
-          <t>컬럼비아_DPA_240530</t>
+          <t>lms_ecom_200416_family</t>
         </is>
       </c>
     </row>
     <row r="822">
       <c r="A822" t="inlineStr">
         <is>
-          <t>okj2377</t>
+          <t>kk_3825766318</t>
         </is>
       </c>
       <c r="B822" t="inlineStr">
         <is>
-          <t>01033661268</t>
+          <t>01020085185</t>
         </is>
       </c>
       <c r="C822" t="inlineStr">
         <is>
-          <t>139452</t>
+          <t>263222</t>
         </is>
       </c>
       <c r="D822" t="inlineStr">
         <is>
-          <t>etc</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E822" t="inlineStr">
         <is>
-          <t>lms_ecom_200416_family</t>
+          <t>컬럼비아_DPA_240530</t>
         </is>
       </c>
     </row>
@@ -22640,7 +22640,7 @@
       </c>
       <c r="D823" t="inlineStr">
         <is>
-          <t>etc</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E823" t="inlineStr">
@@ -22667,7 +22667,7 @@
       </c>
       <c r="D824" t="inlineStr">
         <is>
-          <t>etc</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E824" t="inlineStr">
@@ -22883,7 +22883,7 @@
       </c>
       <c r="D832" t="inlineStr">
         <is>
-          <t>etc</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E832" t="inlineStr">
@@ -22937,7 +22937,7 @@
       </c>
       <c r="D834" t="inlineStr">
         <is>
-          <t>etc</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E834" t="inlineStr">
@@ -22976,54 +22976,54 @@
     <row r="836">
       <c r="A836" t="inlineStr">
         <is>
-          <t>kk_3631606950</t>
+          <t>kk_2999650964</t>
         </is>
       </c>
       <c r="B836" t="inlineStr">
         <is>
-          <t>01063256163</t>
+          <t>01073667501</t>
         </is>
       </c>
       <c r="C836" t="inlineStr">
         <is>
-          <t>248164</t>
+          <t>218535</t>
         </is>
       </c>
       <c r="D836" t="inlineStr">
         <is>
-          <t>etc</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E836" t="inlineStr">
         <is>
-          <t>etc</t>
+          <t>bizboard</t>
         </is>
       </c>
     </row>
     <row r="837">
       <c r="A837" t="inlineStr">
         <is>
-          <t>kk_2999650964</t>
+          <t>kk_3631606950</t>
         </is>
       </c>
       <c r="B837" t="inlineStr">
         <is>
-          <t>01073667501</t>
+          <t>01063256163</t>
         </is>
       </c>
       <c r="C837" t="inlineStr">
         <is>
-          <t>218535</t>
+          <t>248164</t>
         </is>
       </c>
       <c r="D837" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="E837" t="inlineStr">
         <is>
-          <t>bizboard</t>
+          <t>미분류</t>
         </is>
       </c>
     </row>
@@ -23126,7 +23126,7 @@
       </c>
       <c r="D841" t="inlineStr">
         <is>
-          <t>etc</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E841" t="inlineStr">
@@ -23234,7 +23234,7 @@
       </c>
       <c r="D845" t="inlineStr">
         <is>
-          <t>etc</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E845" t="inlineStr">
@@ -23300,54 +23300,54 @@
     <row r="848">
       <c r="A848" t="inlineStr">
         <is>
-          <t>kang481127</t>
+          <t>abril80</t>
         </is>
       </c>
       <c r="B848" t="inlineStr">
         <is>
-          <t>01053764012</t>
+          <t>01032942835</t>
         </is>
       </c>
       <c r="C848" t="inlineStr">
         <is>
-          <t>304276</t>
+          <t>192610</t>
         </is>
       </c>
       <c r="D848" t="inlineStr">
         <is>
-          <t>etc</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E848" t="inlineStr">
         <is>
-          <t>LMS_ECOM_NEWMEMBER</t>
+          <t>Email_mkt</t>
         </is>
       </c>
     </row>
     <row r="849">
       <c r="A849" t="inlineStr">
         <is>
-          <t>abril80</t>
+          <t>kang481127</t>
         </is>
       </c>
       <c r="B849" t="inlineStr">
         <is>
-          <t>01032942835</t>
+          <t>01053764012</t>
         </is>
       </c>
       <c r="C849" t="inlineStr">
         <is>
-          <t>192610</t>
+          <t>304276</t>
         </is>
       </c>
       <c r="D849" t="inlineStr">
         <is>
-          <t>etc</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E849" t="inlineStr">
         <is>
-          <t>Email_mkt</t>
+          <t>LMS_ECOM_NEWMEMBER</t>
         </is>
       </c>
     </row>
@@ -23423,7 +23423,7 @@
       </c>
       <c r="D852" t="inlineStr">
         <is>
-          <t>etc</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E852" t="inlineStr">
@@ -23462,54 +23462,54 @@
     <row r="854">
       <c r="A854" t="inlineStr">
         <is>
-          <t>jh91jung</t>
+          <t>baekdurudu</t>
         </is>
       </c>
       <c r="B854" t="inlineStr">
         <is>
-          <t>01092560926</t>
+          <t>01082556353</t>
         </is>
       </c>
       <c r="C854" t="inlineStr">
         <is>
-          <t>304337</t>
+          <t>60771</t>
         </is>
       </c>
       <c r="D854" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E854" t="inlineStr">
         <is>
-          <t>naversa_pc</t>
+          <t>LMS_ECOM_0214_newyear</t>
         </is>
       </c>
     </row>
     <row r="855">
       <c r="A855" t="inlineStr">
         <is>
-          <t>baekdurudu</t>
+          <t>jh91jung</t>
         </is>
       </c>
       <c r="B855" t="inlineStr">
         <is>
-          <t>01082556353</t>
+          <t>01092560926</t>
         </is>
       </c>
       <c r="C855" t="inlineStr">
         <is>
-          <t>60771</t>
+          <t>304337</t>
         </is>
       </c>
       <c r="D855" t="inlineStr">
         <is>
-          <t>etc</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E855" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0214_newyear</t>
+          <t>naversa_pc</t>
         </is>
       </c>
     </row>
@@ -23558,7 +23558,7 @@
       </c>
       <c r="D857" t="inlineStr">
         <is>
-          <t>etc</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E857" t="inlineStr">
@@ -23570,17 +23570,17 @@
     <row r="858">
       <c r="A858" t="inlineStr">
         <is>
-          <t>kk_4639169718</t>
+          <t>kk_4839680663</t>
         </is>
       </c>
       <c r="B858" t="inlineStr">
         <is>
-          <t>01041380770</t>
+          <t>01046429530</t>
         </is>
       </c>
       <c r="C858" t="inlineStr">
         <is>
-          <t>292319</t>
+          <t>304109</t>
         </is>
       </c>
       <c r="D858" t="inlineStr">
@@ -23590,7 +23590,7 @@
       </c>
       <c r="E858" t="inlineStr">
         <is>
-          <t>naver_brandsearch_mobile</t>
+          <t>6968489536332</t>
         </is>
       </c>
     </row>
@@ -23624,17 +23624,17 @@
     <row r="860">
       <c r="A860" t="inlineStr">
         <is>
-          <t>kk_4839680663</t>
+          <t>kk_4639169718</t>
         </is>
       </c>
       <c r="B860" t="inlineStr">
         <is>
-          <t>01046429530</t>
+          <t>01041380770</t>
         </is>
       </c>
       <c r="C860" t="inlineStr">
         <is>
-          <t>304109</t>
+          <t>292319</t>
         </is>
       </c>
       <c r="D860" t="inlineStr">
@@ -23644,7 +23644,7 @@
       </c>
       <c r="E860" t="inlineStr">
         <is>
-          <t>6968489536332</t>
+          <t>naver_brandsearch_mobile</t>
         </is>
       </c>
     </row>
@@ -23693,7 +23693,7 @@
       </c>
       <c r="D862" t="inlineStr">
         <is>
-          <t>etc</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E862" t="inlineStr">
@@ -23720,7 +23720,7 @@
       </c>
       <c r="D863" t="inlineStr">
         <is>
-          <t>etc</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E863" t="inlineStr">
@@ -23747,7 +23747,7 @@
       </c>
       <c r="D864" t="inlineStr">
         <is>
-          <t>etc</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E864" t="inlineStr">
@@ -23759,54 +23759,54 @@
     <row r="865">
       <c r="A865" t="inlineStr">
         <is>
-          <t>pooh2208</t>
+          <t>hondra</t>
         </is>
       </c>
       <c r="B865" t="inlineStr">
         <is>
-          <t>01062238201</t>
+          <t>01081665020</t>
         </is>
       </c>
       <c r="C865" t="inlineStr">
         <is>
-          <t>85900</t>
+          <t>146125</t>
         </is>
       </c>
       <c r="D865" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E865" t="inlineStr">
         <is>
-          <t>[PF]A SC_상시(1865MF,구매 장바구니)</t>
+          <t>Email_mkt</t>
         </is>
       </c>
     </row>
     <row r="866">
       <c r="A866" t="inlineStr">
         <is>
-          <t>hondra</t>
+          <t>pooh2208</t>
         </is>
       </c>
       <c r="B866" t="inlineStr">
         <is>
-          <t>01081665020</t>
+          <t>01062238201</t>
         </is>
       </c>
       <c r="C866" t="inlineStr">
         <is>
-          <t>146125</t>
+          <t>85900</t>
         </is>
       </c>
       <c r="D866" t="inlineStr">
         <is>
-          <t>etc</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E866" t="inlineStr">
         <is>
-          <t>Email_mkt</t>
+          <t>[PF]A SC_상시(1865MF,구매 장바구니)</t>
         </is>
       </c>
     </row>
@@ -23828,7 +23828,7 @@
       </c>
       <c r="D867" t="inlineStr">
         <is>
-          <t>etc</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E867" t="inlineStr">
@@ -23867,54 +23867,54 @@
     <row r="869">
       <c r="A869" t="inlineStr">
         <is>
-          <t>mtbok</t>
+          <t>isaackwak</t>
         </is>
       </c>
       <c r="B869" t="inlineStr">
         <is>
-          <t>01051284339</t>
+          <t>01090599860</t>
         </is>
       </c>
       <c r="C869" t="inlineStr">
         <is>
-          <t>26917</t>
+          <t>275913</t>
         </is>
       </c>
       <c r="D869" t="inlineStr">
         <is>
-          <t>etc</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="E869" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0410exclusive2</t>
+          <t>Direct</t>
         </is>
       </c>
     </row>
     <row r="870">
       <c r="A870" t="inlineStr">
         <is>
-          <t>isaackwak</t>
+          <t>mtbok</t>
         </is>
       </c>
       <c r="B870" t="inlineStr">
         <is>
-          <t>01090599860</t>
+          <t>01051284339</t>
         </is>
       </c>
       <c r="C870" t="inlineStr">
         <is>
-          <t>275913</t>
+          <t>26917</t>
         </is>
       </c>
       <c r="D870" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E870" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>LMS_ECOM_0410exclusive2</t>
         </is>
       </c>
     </row>
@@ -23948,17 +23948,17 @@
     <row r="872">
       <c r="A872" t="inlineStr">
         <is>
-          <t>pcx916</t>
+          <t>hyschant</t>
         </is>
       </c>
       <c r="B872" t="inlineStr">
         <is>
-          <t>01026644222</t>
+          <t>01065306675</t>
         </is>
       </c>
       <c r="C872" t="inlineStr">
         <is>
-          <t>139541</t>
+          <t>108579</t>
         </is>
       </c>
       <c r="D872" t="inlineStr">
@@ -23968,34 +23968,34 @@
       </c>
       <c r="E872" t="inlineStr">
         <is>
-          <t>KAKAO_CH_event</t>
+          <t>LMS_ECOM_0410exclusive2</t>
         </is>
       </c>
     </row>
     <row r="873">
       <c r="A873" t="inlineStr">
         <is>
-          <t>hyschant</t>
+          <t>pcx916</t>
         </is>
       </c>
       <c r="B873" t="inlineStr">
         <is>
-          <t>01065306675</t>
+          <t>01026644222</t>
         </is>
       </c>
       <c r="C873" t="inlineStr">
         <is>
-          <t>108579</t>
+          <t>139541</t>
         </is>
       </c>
       <c r="D873" t="inlineStr">
         <is>
-          <t>etc</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E873" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0410exclusive2</t>
+          <t>KAKAO_CH_event</t>
         </is>
       </c>
     </row>
@@ -24017,7 +24017,7 @@
       </c>
       <c r="D874" t="inlineStr">
         <is>
-          <t>etc</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E874" t="inlineStr">
@@ -24083,108 +24083,108 @@
     <row r="877">
       <c r="A877" t="inlineStr">
         <is>
-          <t>kk_4839026541</t>
+          <t>kk_2757380967</t>
         </is>
       </c>
       <c r="B877" t="inlineStr">
         <is>
-          <t>01089431507</t>
+          <t>01034635649</t>
         </is>
       </c>
       <c r="C877" t="inlineStr">
         <is>
-          <t>304082</t>
+          <t>208245</t>
         </is>
       </c>
       <c r="D877" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E877" t="inlineStr">
         <is>
-          <t>[PF]전환_상시(2565MF,비구매자)</t>
+          <t>LMS_ECOM_0410exclusive2</t>
         </is>
       </c>
     </row>
     <row r="878">
       <c r="A878" t="inlineStr">
         <is>
-          <t>kk_3181873063</t>
+          <t>kk_4839026541</t>
         </is>
       </c>
       <c r="B878" t="inlineStr">
         <is>
-          <t>01026527131</t>
+          <t>01089431507</t>
         </is>
       </c>
       <c r="C878" t="inlineStr">
         <is>
-          <t>227343</t>
+          <t>304082</t>
         </is>
       </c>
       <c r="D878" t="inlineStr">
         <is>
-          <t>etc</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E878" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0410exclusive2</t>
+          <t>[PF]전환_상시(2565MF,비구매자)</t>
         </is>
       </c>
     </row>
     <row r="879">
       <c r="A879" t="inlineStr">
         <is>
-          <t>kk_2757380967</t>
+          <t>kk_4727921763</t>
         </is>
       </c>
       <c r="B879" t="inlineStr">
         <is>
-          <t>01034635649</t>
+          <t>01045673975</t>
         </is>
       </c>
       <c r="C879" t="inlineStr">
         <is>
-          <t>208245</t>
+          <t>298138</t>
         </is>
       </c>
       <c r="D879" t="inlineStr">
         <is>
-          <t>etc</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="E879" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0410exclusive2</t>
+          <t>Direct</t>
         </is>
       </c>
     </row>
     <row r="880">
       <c r="A880" t="inlineStr">
         <is>
-          <t>kk_4727921763</t>
+          <t>kk_3181873063</t>
         </is>
       </c>
       <c r="B880" t="inlineStr">
         <is>
-          <t>01045673975</t>
+          <t>01026527131</t>
         </is>
       </c>
       <c r="C880" t="inlineStr">
         <is>
-          <t>298138</t>
+          <t>227343</t>
         </is>
       </c>
       <c r="D880" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E880" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>LMS_ECOM_0410exclusive2</t>
         </is>
       </c>
     </row>
@@ -24272,22 +24272,22 @@
     <row r="884">
       <c r="A884" t="inlineStr">
         <is>
-          <t>jeanne</t>
+          <t>pbhds102306</t>
         </is>
       </c>
       <c r="B884" t="inlineStr">
         <is>
-          <t>01047490850</t>
+          <t>01062816264</t>
         </is>
       </c>
       <c r="C884" t="inlineStr">
         <is>
-          <t>195346</t>
+          <t>266784</t>
         </is>
       </c>
       <c r="D884" t="inlineStr">
         <is>
-          <t>etc</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E884" t="inlineStr">
@@ -24299,22 +24299,22 @@
     <row r="885">
       <c r="A885" t="inlineStr">
         <is>
-          <t>sarang21</t>
+          <t>kk_3334413020</t>
         </is>
       </c>
       <c r="B885" t="inlineStr">
         <is>
-          <t>01054975535</t>
+          <t>01080806386</t>
         </is>
       </c>
       <c r="C885" t="inlineStr">
         <is>
-          <t>268553</t>
+          <t>238829</t>
         </is>
       </c>
       <c r="D885" t="inlineStr">
         <is>
-          <t>etc</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E885" t="inlineStr">
@@ -24326,22 +24326,22 @@
     <row r="886">
       <c r="A886" t="inlineStr">
         <is>
-          <t>kk_3251799831</t>
+          <t>jeanne</t>
         </is>
       </c>
       <c r="B886" t="inlineStr">
         <is>
-          <t>01040006581</t>
+          <t>01047490850</t>
         </is>
       </c>
       <c r="C886" t="inlineStr">
         <is>
-          <t>235398</t>
+          <t>195346</t>
         </is>
       </c>
       <c r="D886" t="inlineStr">
         <is>
-          <t>etc</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E886" t="inlineStr">
@@ -24353,22 +24353,22 @@
     <row r="887">
       <c r="A887" t="inlineStr">
         <is>
-          <t>kk_3810304670</t>
+          <t>sarang21</t>
         </is>
       </c>
       <c r="B887" t="inlineStr">
         <is>
-          <t>01041348052</t>
+          <t>01054975535</t>
         </is>
       </c>
       <c r="C887" t="inlineStr">
         <is>
-          <t>261190</t>
+          <t>268553</t>
         </is>
       </c>
       <c r="D887" t="inlineStr">
         <is>
-          <t>etc</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E887" t="inlineStr">
@@ -24380,22 +24380,22 @@
     <row r="888">
       <c r="A888" t="inlineStr">
         <is>
-          <t>kk_3334413020</t>
+          <t>kk_3251799831</t>
         </is>
       </c>
       <c r="B888" t="inlineStr">
         <is>
-          <t>01080806386</t>
+          <t>01040006581</t>
         </is>
       </c>
       <c r="C888" t="inlineStr">
         <is>
-          <t>238829</t>
+          <t>235398</t>
         </is>
       </c>
       <c r="D888" t="inlineStr">
         <is>
-          <t>etc</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E888" t="inlineStr">
@@ -24407,54 +24407,54 @@
     <row r="889">
       <c r="A889" t="inlineStr">
         <is>
-          <t>kk_4849696162</t>
+          <t>kk_3810304670</t>
         </is>
       </c>
       <c r="B889" t="inlineStr">
         <is>
-          <t>01063383734</t>
+          <t>01041348052</t>
         </is>
       </c>
       <c r="C889" t="inlineStr">
         <is>
-          <t>304570</t>
+          <t>261190</t>
         </is>
       </c>
       <c r="D889" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E889" t="inlineStr">
         <is>
-          <t>컬럼비아_DPA_240530</t>
+          <t>LMS_ECOM_200416_family</t>
         </is>
       </c>
     </row>
     <row r="890">
       <c r="A890" t="inlineStr">
         <is>
-          <t>pbhds102306</t>
+          <t>kk_4849696162</t>
         </is>
       </c>
       <c r="B890" t="inlineStr">
         <is>
-          <t>01062816264</t>
+          <t>01063383734</t>
         </is>
       </c>
       <c r="C890" t="inlineStr">
         <is>
-          <t>266784</t>
+          <t>304570</t>
         </is>
       </c>
       <c r="D890" t="inlineStr">
         <is>
-          <t>etc</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E890" t="inlineStr">
         <is>
-          <t>LMS_ECOM_200416_family</t>
+          <t>컬럼비아_DPA_240530</t>
         </is>
       </c>
     </row>
@@ -24476,7 +24476,7 @@
       </c>
       <c r="D891" t="inlineStr">
         <is>
-          <t>etc</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E891" t="inlineStr">
@@ -24530,7 +24530,7 @@
       </c>
       <c r="D893" t="inlineStr">
         <is>
-          <t>etc</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E893" t="inlineStr">
@@ -24557,7 +24557,7 @@
       </c>
       <c r="D894" t="inlineStr">
         <is>
-          <t>etc</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E894" t="inlineStr">
@@ -24584,7 +24584,7 @@
       </c>
       <c r="D895" t="inlineStr">
         <is>
-          <t>etc</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E895" t="inlineStr">
@@ -24596,22 +24596,22 @@
     <row r="896">
       <c r="A896" t="inlineStr">
         <is>
-          <t>kk_4368805733</t>
+          <t>kk_4600405600</t>
         </is>
       </c>
       <c r="B896" t="inlineStr">
         <is>
-          <t>01075528863</t>
+          <t>01053449477</t>
         </is>
       </c>
       <c r="C896" t="inlineStr">
         <is>
-          <t>279909</t>
+          <t>289364</t>
         </is>
       </c>
       <c r="D896" t="inlineStr">
         <is>
-          <t>etc</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E896" t="inlineStr">
@@ -24623,22 +24623,22 @@
     <row r="897">
       <c r="A897" t="inlineStr">
         <is>
-          <t>kk_4600405600</t>
+          <t>kk_4368805733</t>
         </is>
       </c>
       <c r="B897" t="inlineStr">
         <is>
-          <t>01053449477</t>
+          <t>01075528863</t>
         </is>
       </c>
       <c r="C897" t="inlineStr">
         <is>
-          <t>289364</t>
+          <t>279909</t>
         </is>
       </c>
       <c r="D897" t="inlineStr">
         <is>
-          <t>etc</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E897" t="inlineStr">
@@ -24650,22 +24650,22 @@
     <row r="898">
       <c r="A898" t="inlineStr">
         <is>
-          <t>a3789</t>
+          <t>lovemac</t>
         </is>
       </c>
       <c r="B898" t="inlineStr">
         <is>
-          <t>01053102148</t>
+          <t>01058421351</t>
         </is>
       </c>
       <c r="C898" t="inlineStr">
         <is>
-          <t>244924</t>
+          <t>69911</t>
         </is>
       </c>
       <c r="D898" t="inlineStr">
         <is>
-          <t>etc</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E898" t="inlineStr">
@@ -24677,22 +24677,22 @@
     <row r="899">
       <c r="A899" t="inlineStr">
         <is>
-          <t>lovemac</t>
+          <t>a3789</t>
         </is>
       </c>
       <c r="B899" t="inlineStr">
         <is>
-          <t>01058421351</t>
+          <t>01053102148</t>
         </is>
       </c>
       <c r="C899" t="inlineStr">
         <is>
-          <t>69911</t>
+          <t>244924</t>
         </is>
       </c>
       <c r="D899" t="inlineStr">
         <is>
-          <t>etc</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E899" t="inlineStr">
@@ -24719,7 +24719,7 @@
       </c>
       <c r="D900" t="inlineStr">
         <is>
-          <t>etc</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E900" t="inlineStr">
@@ -24746,7 +24746,7 @@
       </c>
       <c r="D901" t="inlineStr">
         <is>
-          <t>etc</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E901" t="inlineStr">
@@ -24800,7 +24800,7 @@
       </c>
       <c r="D903" t="inlineStr">
         <is>
-          <t>etc</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E903" t="inlineStr">
@@ -25043,7 +25043,7 @@
       </c>
       <c r="D912" t="inlineStr">
         <is>
-          <t>etc</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E912" t="inlineStr">
@@ -25097,7 +25097,7 @@
       </c>
       <c r="D914" t="inlineStr">
         <is>
-          <t>etc</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E914" t="inlineStr">
@@ -25136,17 +25136,17 @@
     <row r="916">
       <c r="A916" t="inlineStr">
         <is>
-          <t>kk_4848573198</t>
+          <t>kk_4848049317</t>
         </is>
       </c>
       <c r="B916" t="inlineStr">
         <is>
-          <t>01081135059</t>
+          <t>01064006801</t>
         </is>
       </c>
       <c r="C916" t="inlineStr">
         <is>
-          <t>304535</t>
+          <t>304514</t>
         </is>
       </c>
       <c r="D916" t="inlineStr">
@@ -25156,24 +25156,24 @@
       </c>
       <c r="E916" t="inlineStr">
         <is>
-          <t>(organic)</t>
+          <t>[PF]전환_회원가입(유사)</t>
         </is>
       </c>
     </row>
     <row r="917">
       <c r="A917" t="inlineStr">
         <is>
-          <t>kk_4848049317</t>
+          <t>kk_4848573198</t>
         </is>
       </c>
       <c r="B917" t="inlineStr">
         <is>
-          <t>01064006801</t>
+          <t>01081135059</t>
         </is>
       </c>
       <c r="C917" t="inlineStr">
         <is>
-          <t>304514</t>
+          <t>304535</t>
         </is>
       </c>
       <c r="D917" t="inlineStr">
@@ -25183,7 +25183,7 @@
       </c>
       <c r="E917" t="inlineStr">
         <is>
-          <t>[PF]전환_회원가입(유사)</t>
+          <t>(organic)</t>
         </is>
       </c>
     </row>
@@ -25232,7 +25232,7 @@
       </c>
       <c r="D919" t="inlineStr">
         <is>
-          <t>etc</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E919" t="inlineStr">
@@ -25259,7 +25259,7 @@
       </c>
       <c r="D920" t="inlineStr">
         <is>
-          <t>etc</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E920" t="inlineStr">
@@ -25271,22 +25271,22 @@
     <row r="921">
       <c r="A921" t="inlineStr">
         <is>
-          <t>kk_3793117898</t>
+          <t>kk_3180854377</t>
         </is>
       </c>
       <c r="B921" t="inlineStr">
         <is>
-          <t>01052318168</t>
+          <t>01031216377</t>
         </is>
       </c>
       <c r="C921" t="inlineStr">
         <is>
-          <t>257099</t>
+          <t>226467</t>
         </is>
       </c>
       <c r="D921" t="inlineStr">
         <is>
-          <t>etc</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E921" t="inlineStr">
@@ -25313,7 +25313,7 @@
       </c>
       <c r="D922" t="inlineStr">
         <is>
-          <t>etc</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E922" t="inlineStr">
@@ -25325,22 +25325,22 @@
     <row r="923">
       <c r="A923" t="inlineStr">
         <is>
-          <t>kk_3180854377</t>
+          <t>kk_3793117898</t>
         </is>
       </c>
       <c r="B923" t="inlineStr">
         <is>
-          <t>01031216377</t>
+          <t>01052318168</t>
         </is>
       </c>
       <c r="C923" t="inlineStr">
         <is>
-          <t>226467</t>
+          <t>257099</t>
         </is>
       </c>
       <c r="D923" t="inlineStr">
         <is>
-          <t>etc</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E923" t="inlineStr">
@@ -25367,7 +25367,7 @@
       </c>
       <c r="D924" t="inlineStr">
         <is>
-          <t>etc</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E924" t="inlineStr">
@@ -25946,54 +25946,54 @@
     <row r="946">
       <c r="A946" t="inlineStr">
         <is>
-          <t>kk_4839354093</t>
+          <t>kk_4835738911</t>
         </is>
       </c>
       <c r="B946" t="inlineStr">
         <is>
-          <t>01052243562</t>
+          <t>01034422073</t>
         </is>
       </c>
       <c r="C946" t="inlineStr">
         <is>
-          <t>304098</t>
+          <t>303885</t>
         </is>
       </c>
       <c r="D946" t="inlineStr">
         <is>
-          <t>Organic Traffic</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E946" t="inlineStr">
         <is>
-          <t>(organic)</t>
+          <t>6968489536332</t>
         </is>
       </c>
     </row>
     <row r="947">
       <c r="A947" t="inlineStr">
         <is>
-          <t>kk_4835738911</t>
+          <t>kk_4839354093</t>
         </is>
       </c>
       <c r="B947" t="inlineStr">
         <is>
-          <t>01034422073</t>
+          <t>01052243562</t>
         </is>
       </c>
       <c r="C947" t="inlineStr">
         <is>
-          <t>303885</t>
+          <t>304098</t>
         </is>
       </c>
       <c r="D947" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Organic Traffic</t>
         </is>
       </c>
       <c r="E947" t="inlineStr">
         <is>
-          <t>6968489536332</t>
+          <t>(organic)</t>
         </is>
       </c>
     </row>
@@ -26270,54 +26270,54 @@
     <row r="958">
       <c r="A958" t="inlineStr">
         <is>
-          <t>kk_3919493388</t>
+          <t>kk_3955208505</t>
         </is>
       </c>
       <c r="B958" t="inlineStr">
         <is>
-          <t>01084315028</t>
+          <t>01084144311</t>
         </is>
       </c>
       <c r="C958" t="inlineStr">
         <is>
-          <t>268572</t>
+          <t>270134</t>
         </is>
       </c>
       <c r="D958" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E958" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>KAKAO_CH_MENU_0212_TITANIUM</t>
         </is>
       </c>
     </row>
     <row r="959">
       <c r="A959" t="inlineStr">
         <is>
-          <t>kk_3955208505</t>
+          <t>kk_3919493388</t>
         </is>
       </c>
       <c r="B959" t="inlineStr">
         <is>
-          <t>01084144311</t>
+          <t>01084315028</t>
         </is>
       </c>
       <c r="C959" t="inlineStr">
         <is>
-          <t>270134</t>
+          <t>268572</t>
         </is>
       </c>
       <c r="D959" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E959" t="inlineStr">
         <is>
-          <t>KAKAO_CH_MENU_0212_TITANIUM</t>
+          <t>Paid Ad</t>
         </is>
       </c>
     </row>
@@ -26420,12 +26420,12 @@
       </c>
       <c r="D963" t="inlineStr">
         <is>
-          <t>etc</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="E963" t="inlineStr">
         <is>
-          <t>etc</t>
+          <t>미분류</t>
         </is>
       </c>
     </row>
@@ -26567,54 +26567,54 @@
     <row r="969">
       <c r="A969" t="inlineStr">
         <is>
-          <t>kk_4840108009</t>
+          <t>xey5000</t>
         </is>
       </c>
       <c r="B969" t="inlineStr">
         <is>
-          <t>01053461423</t>
+          <t>01087768710</t>
         </is>
       </c>
       <c r="C969" t="inlineStr">
         <is>
-          <t>304129</t>
+          <t>143826</t>
         </is>
       </c>
       <c r="D969" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E969" t="inlineStr">
         <is>
-          <t>6968489536332</t>
+          <t>KAKAO_CH_MESSAGE_0409_PANTS</t>
         </is>
       </c>
     </row>
     <row r="970">
       <c r="A970" t="inlineStr">
         <is>
-          <t>xey5000</t>
+          <t>kk_4840108009</t>
         </is>
       </c>
       <c r="B970" t="inlineStr">
         <is>
-          <t>01087768710</t>
+          <t>01053461423</t>
         </is>
       </c>
       <c r="C970" t="inlineStr">
         <is>
-          <t>143826</t>
+          <t>304129</t>
         </is>
       </c>
       <c r="D970" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E970" t="inlineStr">
         <is>
-          <t>KAKAO_CH_MESSAGE_0409_PANTS</t>
+          <t>6968489536332</t>
         </is>
       </c>
     </row>
@@ -26636,7 +26636,7 @@
       </c>
       <c r="D971" t="inlineStr">
         <is>
-          <t>etc</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E971" t="inlineStr">
@@ -26864,17 +26864,17 @@
     <row r="980">
       <c r="A980" t="inlineStr">
         <is>
-          <t>holstein</t>
+          <t>kk_3595551743</t>
         </is>
       </c>
       <c r="B980" t="inlineStr">
         <is>
-          <t>01050502500</t>
+          <t>01025839326</t>
         </is>
       </c>
       <c r="C980" t="inlineStr">
         <is>
-          <t>14062</t>
+          <t>246836</t>
         </is>
       </c>
       <c r="D980" t="inlineStr">
@@ -26884,88 +26884,88 @@
       </c>
       <c r="E980" t="inlineStr">
         <is>
-          <t>EDM_TOP</t>
+          <t>LMS_ECOM_0410exclusive2</t>
         </is>
       </c>
     </row>
     <row r="981">
       <c r="A981" t="inlineStr">
         <is>
-          <t>kk_3595551743</t>
+          <t>holstein</t>
         </is>
       </c>
       <c r="B981" t="inlineStr">
         <is>
-          <t>01025839326</t>
+          <t>01050502500</t>
         </is>
       </c>
       <c r="C981" t="inlineStr">
         <is>
-          <t>246836</t>
+          <t>14062</t>
         </is>
       </c>
       <c r="D981" t="inlineStr">
         <is>
-          <t>etc</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E981" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0410exclusive2</t>
+          <t>EDM_TOP</t>
         </is>
       </c>
     </row>
     <row r="982">
       <c r="A982" t="inlineStr">
         <is>
-          <t>kk_4841501713</t>
+          <t>ellieee</t>
         </is>
       </c>
       <c r="B982" t="inlineStr">
         <is>
-          <t>01042996002</t>
+          <t>01098996425</t>
         </is>
       </c>
       <c r="C982" t="inlineStr">
         <is>
-          <t>304195</t>
+          <t>203688</t>
         </is>
       </c>
       <c r="D982" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E982" t="inlineStr">
         <is>
-          <t>6968489536332</t>
+          <t>KAKAO_alimtalk</t>
         </is>
       </c>
     </row>
     <row r="983">
       <c r="A983" t="inlineStr">
         <is>
-          <t>ellieee</t>
+          <t>kk_4841501713</t>
         </is>
       </c>
       <c r="B983" t="inlineStr">
         <is>
-          <t>01098996425</t>
+          <t>01042996002</t>
         </is>
       </c>
       <c r="C983" t="inlineStr">
         <is>
-          <t>203688</t>
+          <t>304195</t>
         </is>
       </c>
       <c r="D983" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E983" t="inlineStr">
         <is>
-          <t>KAKAO_alimtalk</t>
+          <t>6968489536332</t>
         </is>
       </c>
     </row>
@@ -27053,54 +27053,54 @@
     <row r="987">
       <c r="A987" t="inlineStr">
         <is>
-          <t>kk_4375973589</t>
+          <t>kmh7710</t>
         </is>
       </c>
       <c r="B987" t="inlineStr">
         <is>
-          <t>01096223641</t>
+          <t>01077108716</t>
         </is>
       </c>
       <c r="C987" t="inlineStr">
         <is>
-          <t>280163</t>
+          <t>164951</t>
         </is>
       </c>
       <c r="D987" t="inlineStr">
         <is>
-          <t>Organic Traffic</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E987" t="inlineStr">
         <is>
-          <t>LMS_ECOM_familycoupon</t>
+          <t>LMS_ECOM_0214_newyear</t>
         </is>
       </c>
     </row>
     <row r="988">
       <c r="A988" t="inlineStr">
         <is>
-          <t>kmh7710</t>
+          <t>kk_4375973589</t>
         </is>
       </c>
       <c r="B988" t="inlineStr">
         <is>
-          <t>01077108716</t>
+          <t>01096223641</t>
         </is>
       </c>
       <c r="C988" t="inlineStr">
         <is>
-          <t>164951</t>
+          <t>280163</t>
         </is>
       </c>
       <c r="D988" t="inlineStr">
         <is>
-          <t>etc</t>
+          <t>Organic Traffic</t>
         </is>
       </c>
       <c r="E988" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0214_newyear</t>
+          <t>LMS_ECOM_familycoupon</t>
         </is>
       </c>
     </row>
@@ -27122,7 +27122,7 @@
       </c>
       <c r="D989" t="inlineStr">
         <is>
-          <t>etc</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E989" t="inlineStr">
@@ -27296,17 +27296,17 @@
     <row r="996">
       <c r="A996" t="inlineStr">
         <is>
-          <t>kk_4840093815</t>
+          <t>kk_4839477951</t>
         </is>
       </c>
       <c r="B996" t="inlineStr">
         <is>
-          <t>01095450820</t>
+          <t>01020868012</t>
         </is>
       </c>
       <c r="C996" t="inlineStr">
         <is>
-          <t>304126</t>
+          <t>304101</t>
         </is>
       </c>
       <c r="D996" t="inlineStr">
@@ -27316,7 +27316,7 @@
       </c>
       <c r="E996" t="inlineStr">
         <is>
-          <t>EFW</t>
+          <t>6968489536332</t>
         </is>
       </c>
     </row>
@@ -27350,17 +27350,17 @@
     <row r="998">
       <c r="A998" t="inlineStr">
         <is>
-          <t>kk_4839477951</t>
+          <t>kk_4840093815</t>
         </is>
       </c>
       <c r="B998" t="inlineStr">
         <is>
-          <t>01020868012</t>
+          <t>01095450820</t>
         </is>
       </c>
       <c r="C998" t="inlineStr">
         <is>
-          <t>304101</t>
+          <t>304126</t>
         </is>
       </c>
       <c r="D998" t="inlineStr">
@@ -27370,7 +27370,7 @@
       </c>
       <c r="E998" t="inlineStr">
         <is>
-          <t>6968489536332</t>
+          <t>EFW</t>
         </is>
       </c>
     </row>
@@ -27419,7 +27419,7 @@
       </c>
       <c r="D1000" t="inlineStr">
         <is>
-          <t>etc</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E1000" t="inlineStr">
@@ -27458,71 +27458,71 @@
     <row r="1002">
       <c r="A1002" t="inlineStr">
         <is>
-          <t>kk_4843439707</t>
+          <t>kk_2800477789</t>
         </is>
       </c>
       <c r="B1002" t="inlineStr">
         <is>
-          <t>01022248653</t>
+          <t>01035177105</t>
         </is>
       </c>
       <c r="C1002" t="inlineStr">
         <is>
-          <t>304310</t>
+          <t>211095</t>
         </is>
       </c>
       <c r="D1002" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E1002" t="inlineStr">
         <is>
-          <t>6968489536332</t>
+          <t>KAKAO_alimtalk</t>
         </is>
       </c>
     </row>
     <row r="1003">
       <c r="A1003" t="inlineStr">
         <is>
-          <t>kk_2800477789</t>
+          <t>kk_4843439707</t>
         </is>
       </c>
       <c r="B1003" t="inlineStr">
         <is>
-          <t>01035177105</t>
+          <t>01022248653</t>
         </is>
       </c>
       <c r="C1003" t="inlineStr">
         <is>
-          <t>211095</t>
+          <t>304310</t>
         </is>
       </c>
       <c r="D1003" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E1003" t="inlineStr">
         <is>
-          <t>KAKAO_alimtalk</t>
+          <t>6968489536332</t>
         </is>
       </c>
     </row>
     <row r="1004">
       <c r="A1004" t="inlineStr">
         <is>
-          <t>kk_4844530515</t>
+          <t>kk_4844657024</t>
         </is>
       </c>
       <c r="B1004" t="inlineStr">
         <is>
-          <t>01054558799</t>
+          <t>01033551784</t>
         </is>
       </c>
       <c r="C1004" t="inlineStr">
         <is>
-          <t>304366</t>
+          <t>304376</t>
         </is>
       </c>
       <c r="D1004" t="inlineStr">
@@ -27566,17 +27566,17 @@
     <row r="1006">
       <c r="A1006" t="inlineStr">
         <is>
-          <t>kk_4844657024</t>
+          <t>kk_4844530515</t>
         </is>
       </c>
       <c r="B1006" t="inlineStr">
         <is>
-          <t>01033551784</t>
+          <t>01054558799</t>
         </is>
       </c>
       <c r="C1006" t="inlineStr">
         <is>
-          <t>304376</t>
+          <t>304366</t>
         </is>
       </c>
       <c r="D1006" t="inlineStr">
@@ -27608,12 +27608,12 @@
       </c>
       <c r="D1007" t="inlineStr">
         <is>
-          <t>etc</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="E1007" t="inlineStr">
         <is>
-          <t>etc</t>
+          <t>미분류</t>
         </is>
       </c>
     </row>
@@ -27662,7 +27662,7 @@
       </c>
       <c r="D1009" t="inlineStr">
         <is>
-          <t>etc</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E1009" t="inlineStr">
@@ -27701,17 +27701,17 @@
     <row r="1011">
       <c r="A1011" t="inlineStr">
         <is>
-          <t>kk_4845121221</t>
+          <t>kidultyo</t>
         </is>
       </c>
       <c r="B1011" t="inlineStr">
         <is>
-          <t>01044632332</t>
+          <t>01037980315</t>
         </is>
       </c>
       <c r="C1011" t="inlineStr">
         <is>
-          <t>304393</t>
+          <t>304331</t>
         </is>
       </c>
       <c r="D1011" t="inlineStr">
@@ -27728,81 +27728,81 @@
     <row r="1012">
       <c r="A1012" t="inlineStr">
         <is>
-          <t>kk_4844453283</t>
+          <t>kk_4843847622</t>
         </is>
       </c>
       <c r="B1012" t="inlineStr">
         <is>
-          <t>01090262556</t>
+          <t>01046990393</t>
         </is>
       </c>
       <c r="C1012" t="inlineStr">
         <is>
-          <t>304360</t>
+          <t>304336</t>
         </is>
       </c>
       <c r="D1012" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Organic Traffic</t>
         </is>
       </c>
       <c r="E1012" t="inlineStr">
         <is>
-          <t>6968489536332</t>
+          <t>(organic)</t>
         </is>
       </c>
     </row>
     <row r="1013">
       <c r="A1013" t="inlineStr">
         <is>
-          <t>kidultyo</t>
+          <t>kk_4843926419</t>
         </is>
       </c>
       <c r="B1013" t="inlineStr">
         <is>
-          <t>01037980315</t>
+          <t>01034583174</t>
         </is>
       </c>
       <c r="C1013" t="inlineStr">
         <is>
-          <t>304331</t>
+          <t>304338</t>
         </is>
       </c>
       <c r="D1013" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Official SNS</t>
         </is>
       </c>
       <c r="E1013" t="inlineStr">
         <is>
-          <t>6968489536332</t>
+          <t>EFW_04</t>
         </is>
       </c>
     </row>
     <row r="1014">
       <c r="A1014" t="inlineStr">
         <is>
-          <t>kk_4843847622</t>
+          <t>kk_4844453283</t>
         </is>
       </c>
       <c r="B1014" t="inlineStr">
         <is>
-          <t>01046990393</t>
+          <t>01090262556</t>
         </is>
       </c>
       <c r="C1014" t="inlineStr">
         <is>
-          <t>304336</t>
+          <t>304360</t>
         </is>
       </c>
       <c r="D1014" t="inlineStr">
         <is>
-          <t>Organic Traffic</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E1014" t="inlineStr">
         <is>
-          <t>(organic)</t>
+          <t>6968489536332</t>
         </is>
       </c>
     </row>
@@ -27836,81 +27836,81 @@
     <row r="1016">
       <c r="A1016" t="inlineStr">
         <is>
-          <t>kk_4843926419</t>
+          <t>kk_4845121221</t>
         </is>
       </c>
       <c r="B1016" t="inlineStr">
         <is>
-          <t>01034583174</t>
+          <t>01044632332</t>
         </is>
       </c>
       <c r="C1016" t="inlineStr">
         <is>
-          <t>304338</t>
+          <t>304393</t>
         </is>
       </c>
       <c r="D1016" t="inlineStr">
         <is>
-          <t>Official SNS</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E1016" t="inlineStr">
         <is>
-          <t>EFW_04</t>
+          <t>6968489536332</t>
         </is>
       </c>
     </row>
     <row r="1017">
       <c r="A1017" t="inlineStr">
         <is>
-          <t>kk_4840857472</t>
+          <t>kyoungs424</t>
         </is>
       </c>
       <c r="B1017" t="inlineStr">
         <is>
-          <t>01040551807</t>
+          <t>01041509204</t>
         </is>
       </c>
       <c r="C1017" t="inlineStr">
         <is>
-          <t>304172</t>
+          <t>153760</t>
         </is>
       </c>
       <c r="D1017" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E1017" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>KAKAO_alimtalk</t>
         </is>
       </c>
     </row>
     <row r="1018">
       <c r="A1018" t="inlineStr">
         <is>
-          <t>kyoungs424</t>
+          <t>kk_4840857472</t>
         </is>
       </c>
       <c r="B1018" t="inlineStr">
         <is>
-          <t>01041509204</t>
+          <t>01040551807</t>
         </is>
       </c>
       <c r="C1018" t="inlineStr">
         <is>
-          <t>153760</t>
+          <t>304172</t>
         </is>
       </c>
       <c r="D1018" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="E1018" t="inlineStr">
         <is>
-          <t>KAKAO_alimtalk</t>
+          <t>Direct</t>
         </is>
       </c>
     </row>
@@ -27944,54 +27944,54 @@
     <row r="1020">
       <c r="A1020" t="inlineStr">
         <is>
-          <t>kk_4839542021</t>
+          <t>kk_4357899204</t>
         </is>
       </c>
       <c r="B1020" t="inlineStr">
         <is>
-          <t>01089909663</t>
+          <t>01082772838</t>
         </is>
       </c>
       <c r="C1020" t="inlineStr">
         <is>
-          <t>304103</t>
+          <t>279564</t>
         </is>
       </c>
       <c r="D1020" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Official SNS</t>
         </is>
       </c>
       <c r="E1020" t="inlineStr">
         <is>
-          <t>(organic)</t>
+          <t>(referral)</t>
         </is>
       </c>
     </row>
     <row r="1021">
       <c r="A1021" t="inlineStr">
         <is>
-          <t>kk_4357899204</t>
+          <t>kk_4839542021</t>
         </is>
       </c>
       <c r="B1021" t="inlineStr">
         <is>
-          <t>01082772838</t>
+          <t>01089909663</t>
         </is>
       </c>
       <c r="C1021" t="inlineStr">
         <is>
-          <t>279564</t>
+          <t>304103</t>
         </is>
       </c>
       <c r="D1021" t="inlineStr">
         <is>
-          <t>Official SNS</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E1021" t="inlineStr">
         <is>
-          <t>(referral)</t>
+          <t>(organic)</t>
         </is>
       </c>
     </row>
@@ -28040,7 +28040,7 @@
       </c>
       <c r="D1023" t="inlineStr">
         <is>
-          <t>etc</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E1023" t="inlineStr">
@@ -28079,162 +28079,162 @@
     <row r="1025">
       <c r="A1025" t="inlineStr">
         <is>
-          <t>kk_3601210201</t>
+          <t>chibird</t>
         </is>
       </c>
       <c r="B1025" t="inlineStr">
         <is>
-          <t>01092460423</t>
+          <t>01031187674</t>
         </is>
       </c>
       <c r="C1025" t="inlineStr">
         <is>
-          <t>247035</t>
+          <t>219288</t>
         </is>
       </c>
       <c r="D1025" t="inlineStr">
         <is>
-          <t>etc</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E1025" t="inlineStr">
         <is>
-          <t>etc</t>
+          <t>sa</t>
         </is>
       </c>
     </row>
     <row r="1026">
       <c r="A1026" t="inlineStr">
         <is>
-          <t>chibird</t>
+          <t>kk_3601210201</t>
         </is>
       </c>
       <c r="B1026" t="inlineStr">
         <is>
-          <t>01031187674</t>
+          <t>01092460423</t>
         </is>
       </c>
       <c r="C1026" t="inlineStr">
         <is>
-          <t>219288</t>
+          <t>247035</t>
         </is>
       </c>
       <c r="D1026" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="E1026" t="inlineStr">
         <is>
-          <t>sa</t>
+          <t>미분류</t>
         </is>
       </c>
     </row>
     <row r="1027">
       <c r="A1027" t="inlineStr">
         <is>
-          <t>kk_4839906396</t>
+          <t>kk_3725118384</t>
         </is>
       </c>
       <c r="B1027" t="inlineStr">
         <is>
-          <t>01044486524</t>
+          <t>01035977118</t>
         </is>
       </c>
       <c r="C1027" t="inlineStr">
         <is>
-          <t>304113</t>
+          <t>252440</t>
         </is>
       </c>
       <c r="D1027" t="inlineStr">
         <is>
-          <t>Organic Traffic</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E1027" t="inlineStr">
         <is>
-          <t>(organic)</t>
+          <t>LMS_ECOM_0214_newyear</t>
         </is>
       </c>
     </row>
     <row r="1028">
       <c r="A1028" t="inlineStr">
         <is>
-          <t>kk_3725118384</t>
+          <t>kk_4839906396</t>
         </is>
       </c>
       <c r="B1028" t="inlineStr">
         <is>
-          <t>01035977118</t>
+          <t>01044486524</t>
         </is>
       </c>
       <c r="C1028" t="inlineStr">
         <is>
-          <t>252440</t>
+          <t>304113</t>
         </is>
       </c>
       <c r="D1028" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Organic Traffic</t>
         </is>
       </c>
       <c r="E1028" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0214_newyear</t>
+          <t>(organic)</t>
         </is>
       </c>
     </row>
     <row r="1029">
       <c r="A1029" t="inlineStr">
         <is>
-          <t>kk_3798545067</t>
+          <t>kk_4446020087</t>
         </is>
       </c>
       <c r="B1029" t="inlineStr">
         <is>
-          <t>01023751319</t>
+          <t>01089773053</t>
         </is>
       </c>
       <c r="C1029" t="inlineStr">
         <is>
-          <t>258449</t>
+          <t>282273</t>
         </is>
       </c>
       <c r="D1029" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E1029" t="inlineStr">
         <is>
-          <t>sa</t>
+          <t>LMS_ECOM_0214_newyear</t>
         </is>
       </c>
     </row>
     <row r="1030">
       <c r="A1030" t="inlineStr">
         <is>
-          <t>kk_4446020087</t>
+          <t>kk_3798545067</t>
         </is>
       </c>
       <c r="B1030" t="inlineStr">
         <is>
-          <t>01089773053</t>
+          <t>01023751319</t>
         </is>
       </c>
       <c r="C1030" t="inlineStr">
         <is>
-          <t>282273</t>
+          <t>258449</t>
         </is>
       </c>
       <c r="D1030" t="inlineStr">
         <is>
-          <t>etc</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E1030" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0214_newyear</t>
+          <t>sa</t>
         </is>
       </c>
     </row>
@@ -28268,54 +28268,54 @@
     <row r="1032">
       <c r="A1032" t="inlineStr">
         <is>
-          <t>kk_4847975154</t>
+          <t>kk_4847354450</t>
         </is>
       </c>
       <c r="B1032" t="inlineStr">
         <is>
-          <t>01062199172</t>
+          <t>01088042346</t>
         </is>
       </c>
       <c r="C1032" t="inlineStr">
         <is>
-          <t>304512</t>
+          <t>304489</t>
         </is>
       </c>
       <c r="D1032" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E1032" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>6968489536332</t>
         </is>
       </c>
     </row>
     <row r="1033">
       <c r="A1033" t="inlineStr">
         <is>
-          <t>kk_4847354450</t>
+          <t>kk_4847975154</t>
         </is>
       </c>
       <c r="B1033" t="inlineStr">
         <is>
-          <t>01088042346</t>
+          <t>01062199172</t>
         </is>
       </c>
       <c r="C1033" t="inlineStr">
         <is>
-          <t>304489</t>
+          <t>304512</t>
         </is>
       </c>
       <c r="D1033" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="E1033" t="inlineStr">
         <is>
-          <t>6968489536332</t>
+          <t>Direct</t>
         </is>
       </c>
     </row>
@@ -28376,17 +28376,17 @@
     <row r="1036">
       <c r="A1036" t="inlineStr">
         <is>
-          <t>kk_4844452226</t>
+          <t>kk_4843809795</t>
         </is>
       </c>
       <c r="B1036" t="inlineStr">
         <is>
-          <t>01096801866</t>
+          <t>01072864741</t>
         </is>
       </c>
       <c r="C1036" t="inlineStr">
         <is>
-          <t>304359</t>
+          <t>304335</t>
         </is>
       </c>
       <c r="D1036" t="inlineStr">
@@ -28403,125 +28403,125 @@
     <row r="1037">
       <c r="A1037" t="inlineStr">
         <is>
-          <t>kk_4843809795</t>
+          <t>kk_4844609437</t>
         </is>
       </c>
       <c r="B1037" t="inlineStr">
         <is>
-          <t>01072864741</t>
+          <t>01046808931</t>
         </is>
       </c>
       <c r="C1037" t="inlineStr">
         <is>
-          <t>304335</t>
+          <t>304372</t>
         </is>
       </c>
       <c r="D1037" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Official SNS</t>
         </is>
       </c>
       <c r="E1037" t="inlineStr">
         <is>
-          <t>6968489536332</t>
+          <t>(referral)</t>
         </is>
       </c>
     </row>
     <row r="1038">
       <c r="A1038" t="inlineStr">
         <is>
-          <t>kk_4844609437</t>
+          <t>kk_4844452226</t>
         </is>
       </c>
       <c r="B1038" t="inlineStr">
         <is>
-          <t>01046808931</t>
+          <t>01096801866</t>
         </is>
       </c>
       <c r="C1038" t="inlineStr">
         <is>
-          <t>304372</t>
+          <t>304359</t>
         </is>
       </c>
       <c r="D1038" t="inlineStr">
         <is>
-          <t>Official SNS</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E1038" t="inlineStr">
         <is>
-          <t>(referral)</t>
+          <t>6968489536332</t>
         </is>
       </c>
     </row>
     <row r="1039">
       <c r="A1039" t="inlineStr">
         <is>
-          <t>blblhh</t>
+          <t>kona143</t>
         </is>
       </c>
       <c r="B1039" t="inlineStr">
         <is>
-          <t>01033446769</t>
+          <t>01021001916</t>
         </is>
       </c>
       <c r="C1039" t="inlineStr">
         <is>
-          <t>304297</t>
+          <t>304260</t>
         </is>
       </c>
       <c r="D1039" t="inlineStr">
         <is>
-          <t>Organic Traffic</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E1039" t="inlineStr">
         <is>
-          <t>(referral)</t>
+          <t>[PF]전환_회원가입(유사)</t>
         </is>
       </c>
     </row>
     <row r="1040">
       <c r="A1040" t="inlineStr">
         <is>
-          <t>kona143</t>
+          <t>blblhh</t>
         </is>
       </c>
       <c r="B1040" t="inlineStr">
         <is>
-          <t>01021001916</t>
+          <t>01033446769</t>
         </is>
       </c>
       <c r="C1040" t="inlineStr">
         <is>
-          <t>304260</t>
+          <t>304297</t>
         </is>
       </c>
       <c r="D1040" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Organic Traffic</t>
         </is>
       </c>
       <c r="E1040" t="inlineStr">
         <is>
-          <t>[PF]전환_회원가입(유사)</t>
+          <t>(referral)</t>
         </is>
       </c>
     </row>
     <row r="1041">
       <c r="A1041" t="inlineStr">
         <is>
-          <t>kk_2750710108</t>
+          <t>kk_4840913383</t>
         </is>
       </c>
       <c r="B1041" t="inlineStr">
         <is>
-          <t>01062707475</t>
+          <t>01099887927</t>
         </is>
       </c>
       <c r="C1041" t="inlineStr">
         <is>
-          <t>207211</t>
+          <t>304174</t>
         </is>
       </c>
       <c r="D1041" t="inlineStr">
@@ -28538,27 +28538,27 @@
     <row r="1042">
       <c r="A1042" t="inlineStr">
         <is>
-          <t>kk_4840913383</t>
+          <t>kk_4841278242</t>
         </is>
       </c>
       <c r="B1042" t="inlineStr">
         <is>
-          <t>01099887927</t>
+          <t>01046197965</t>
         </is>
       </c>
       <c r="C1042" t="inlineStr">
         <is>
-          <t>304174</t>
+          <t>304190</t>
         </is>
       </c>
       <c r="D1042" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>Organic Traffic</t>
         </is>
       </c>
       <c r="E1042" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>(referral)</t>
         </is>
       </c>
     </row>
@@ -28592,17 +28592,17 @@
     <row r="1044">
       <c r="A1044" t="inlineStr">
         <is>
-          <t>jsb0425</t>
+          <t>kk_2750710108</t>
         </is>
       </c>
       <c r="B1044" t="inlineStr">
         <is>
-          <t>01037883670</t>
+          <t>01062707475</t>
         </is>
       </c>
       <c r="C1044" t="inlineStr">
         <is>
-          <t>104766</t>
+          <t>207211</t>
         </is>
       </c>
       <c r="D1044" t="inlineStr">
@@ -28619,54 +28619,54 @@
     <row r="1045">
       <c r="A1045" t="inlineStr">
         <is>
-          <t>kk_4841278242</t>
+          <t>kk_4840417532</t>
         </is>
       </c>
       <c r="B1045" t="inlineStr">
         <is>
-          <t>01046197965</t>
+          <t>01053409288</t>
         </is>
       </c>
       <c r="C1045" t="inlineStr">
         <is>
-          <t>304190</t>
+          <t>304147</t>
         </is>
       </c>
       <c r="D1045" t="inlineStr">
         <is>
-          <t>Organic Traffic</t>
+          <t>Official SNS</t>
         </is>
       </c>
       <c r="E1045" t="inlineStr">
         <is>
-          <t>(referral)</t>
+          <t>EFW_04</t>
         </is>
       </c>
     </row>
     <row r="1046">
       <c r="A1046" t="inlineStr">
         <is>
-          <t>kk_4840417532</t>
+          <t>jsb0425</t>
         </is>
       </c>
       <c r="B1046" t="inlineStr">
         <is>
-          <t>01053409288</t>
+          <t>01037883670</t>
         </is>
       </c>
       <c r="C1046" t="inlineStr">
         <is>
-          <t>304147</t>
+          <t>104766</t>
         </is>
       </c>
       <c r="D1046" t="inlineStr">
         <is>
-          <t>Official SNS</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="E1046" t="inlineStr">
         <is>
-          <t>EFW_04</t>
+          <t>Direct</t>
         </is>
       </c>
     </row>
@@ -28715,7 +28715,7 @@
       </c>
       <c r="D1048" t="inlineStr">
         <is>
-          <t>etc</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E1048" t="inlineStr">
@@ -28808,27 +28808,27 @@
     <row r="1052">
       <c r="A1052" t="inlineStr">
         <is>
-          <t>kk_4425155772</t>
+          <t>chyim</t>
         </is>
       </c>
       <c r="B1052" t="inlineStr">
         <is>
-          <t>01074070807</t>
+          <t>01037519198</t>
         </is>
       </c>
       <c r="C1052" t="inlineStr">
         <is>
-          <t>281472</t>
+          <t>255862</t>
         </is>
       </c>
       <c r="D1052" t="inlineStr">
         <is>
-          <t>Organic Traffic</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="E1052" t="inlineStr">
         <is>
-          <t>(organic)</t>
+          <t>Direct</t>
         </is>
       </c>
     </row>
@@ -28877,7 +28877,7 @@
       </c>
       <c r="D1054" t="inlineStr">
         <is>
-          <t>etc</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E1054" t="inlineStr">
@@ -28889,27 +28889,27 @@
     <row r="1055">
       <c r="A1055" t="inlineStr">
         <is>
-          <t>chyim</t>
+          <t>kk_4425155772</t>
         </is>
       </c>
       <c r="B1055" t="inlineStr">
         <is>
-          <t>01037519198</t>
+          <t>01074070807</t>
         </is>
       </c>
       <c r="C1055" t="inlineStr">
         <is>
-          <t>255862</t>
+          <t>281472</t>
         </is>
       </c>
       <c r="D1055" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>Organic Traffic</t>
         </is>
       </c>
       <c r="E1055" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>(organic)</t>
         </is>
       </c>
     </row>
@@ -28943,54 +28943,54 @@
     <row r="1057">
       <c r="A1057" t="inlineStr">
         <is>
-          <t>kk_4651201605</t>
+          <t>kk_4846761310</t>
         </is>
       </c>
       <c r="B1057" t="inlineStr">
         <is>
-          <t>01045489411</t>
+          <t>01091189951</t>
         </is>
       </c>
       <c r="C1057" t="inlineStr">
         <is>
-          <t>293053</t>
+          <t>304464</t>
         </is>
       </c>
       <c r="D1057" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E1057" t="inlineStr">
         <is>
-          <t>EDM_0411</t>
+          <t>naver_brandsearch_mobile</t>
         </is>
       </c>
     </row>
     <row r="1058">
       <c r="A1058" t="inlineStr">
         <is>
-          <t>kk_4846761310</t>
+          <t>kk_4651201605</t>
         </is>
       </c>
       <c r="B1058" t="inlineStr">
         <is>
-          <t>01091189951</t>
+          <t>01045489411</t>
         </is>
       </c>
       <c r="C1058" t="inlineStr">
         <is>
-          <t>304464</t>
+          <t>293053</t>
         </is>
       </c>
       <c r="D1058" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E1058" t="inlineStr">
         <is>
-          <t>naver_brandsearch_mobile</t>
+          <t>EDM_0411</t>
         </is>
       </c>
     </row>
@@ -29120,7 +29120,7 @@
       </c>
       <c r="D1063" t="inlineStr">
         <is>
-          <t>etc</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E1063" t="inlineStr">
@@ -29186,108 +29186,108 @@
     <row r="1066">
       <c r="A1066" t="inlineStr">
         <is>
-          <t>kk_3241081989</t>
+          <t>lolia875</t>
         </is>
       </c>
       <c r="B1066" t="inlineStr">
         <is>
-          <t>01072287165</t>
+          <t>01067138715</t>
         </is>
       </c>
       <c r="C1066" t="inlineStr">
         <is>
-          <t>234608</t>
+          <t>161251</t>
         </is>
       </c>
       <c r="D1066" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E1066" t="inlineStr">
         <is>
-          <t>KAKAO_alimtalk</t>
+          <t>6968489536332</t>
         </is>
       </c>
     </row>
     <row r="1067">
       <c r="A1067" t="inlineStr">
         <is>
-          <t>lolia875</t>
+          <t>kk_3241081989</t>
         </is>
       </c>
       <c r="B1067" t="inlineStr">
         <is>
-          <t>01067138715</t>
+          <t>01072287165</t>
         </is>
       </c>
       <c r="C1067" t="inlineStr">
         <is>
-          <t>161251</t>
+          <t>234608</t>
         </is>
       </c>
       <c r="D1067" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E1067" t="inlineStr">
         <is>
-          <t>6968489536332</t>
+          <t>KAKAO_alimtalk</t>
         </is>
       </c>
     </row>
     <row r="1068">
       <c r="A1068" t="inlineStr">
         <is>
-          <t>kk_3140575996</t>
+          <t>kk_3393400723</t>
         </is>
       </c>
       <c r="B1068" t="inlineStr">
         <is>
-          <t>01098546266</t>
+          <t>01089700082</t>
         </is>
       </c>
       <c r="C1068" t="inlineStr">
         <is>
-          <t>222820</t>
+          <t>241049</t>
         </is>
       </c>
       <c r="D1068" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E1068" t="inlineStr">
         <is>
-          <t>naver_brandsearch_mobile</t>
+          <t>KAKAO_alimtalk</t>
         </is>
       </c>
     </row>
     <row r="1069">
       <c r="A1069" t="inlineStr">
         <is>
-          <t>kk_3393400723</t>
+          <t>kk_3140575996</t>
         </is>
       </c>
       <c r="B1069" t="inlineStr">
         <is>
-          <t>01089700082</t>
+          <t>01098546266</t>
         </is>
       </c>
       <c r="C1069" t="inlineStr">
         <is>
-          <t>241049</t>
+          <t>222820</t>
         </is>
       </c>
       <c r="D1069" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E1069" t="inlineStr">
         <is>
-          <t>KAKAO_alimtalk</t>
+          <t>naver_brandsearch_mobile</t>
         </is>
       </c>
     </row>
@@ -29336,7 +29336,7 @@
       </c>
       <c r="D1071" t="inlineStr">
         <is>
-          <t>etc</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E1071" t="inlineStr">
@@ -29348,71 +29348,71 @@
     <row r="1072">
       <c r="A1072" t="inlineStr">
         <is>
-          <t>kk_2750963357</t>
+          <t>kk_3811584672</t>
         </is>
       </c>
       <c r="B1072" t="inlineStr">
         <is>
-          <t>01033989099</t>
+          <t>01072331107</t>
         </is>
       </c>
       <c r="C1072" t="inlineStr">
         <is>
-          <t>207617</t>
+          <t>261468</t>
         </is>
       </c>
       <c r="D1072" t="inlineStr">
         <is>
-          <t>etc</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="E1072" t="inlineStr">
         <is>
-          <t>LMS_ECOM_200416_family</t>
+          <t>Direct</t>
         </is>
       </c>
     </row>
     <row r="1073">
       <c r="A1073" t="inlineStr">
         <is>
-          <t>kk_3811584672</t>
+          <t>hyoju1981</t>
         </is>
       </c>
       <c r="B1073" t="inlineStr">
         <is>
-          <t>01072331107</t>
+          <t>01045321445</t>
         </is>
       </c>
       <c r="C1073" t="inlineStr">
         <is>
-          <t>261468</t>
+          <t>107362</t>
         </is>
       </c>
       <c r="D1073" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E1073" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>KAKAO_alimtalk</t>
         </is>
       </c>
     </row>
     <row r="1074">
       <c r="A1074" t="inlineStr">
         <is>
-          <t>hyoju1981</t>
+          <t>kk_2750963357</t>
         </is>
       </c>
       <c r="B1074" t="inlineStr">
         <is>
-          <t>01045321445</t>
+          <t>01033989099</t>
         </is>
       </c>
       <c r="C1074" t="inlineStr">
         <is>
-          <t>107362</t>
+          <t>207617</t>
         </is>
       </c>
       <c r="D1074" t="inlineStr">
@@ -29422,115 +29422,115 @@
       </c>
       <c r="E1074" t="inlineStr">
         <is>
-          <t>KAKAO_alimtalk</t>
+          <t>LMS_ECOM_200416_family</t>
         </is>
       </c>
     </row>
     <row r="1075">
       <c r="A1075" t="inlineStr">
         <is>
-          <t>kk_4848093455</t>
+          <t>kk_3792750872</t>
         </is>
       </c>
       <c r="B1075" t="inlineStr">
         <is>
-          <t>01023043154</t>
+          <t>01084382636</t>
         </is>
       </c>
       <c r="C1075" t="inlineStr">
         <is>
-          <t>304517</t>
+          <t>256807</t>
         </is>
       </c>
       <c r="D1075" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E1075" t="inlineStr">
         <is>
-          <t>6968489536332</t>
+          <t>KAKAO_CH_MENU_0211_NEW_MEN</t>
         </is>
       </c>
     </row>
     <row r="1076">
       <c r="A1076" t="inlineStr">
         <is>
-          <t>kk_4669827711</t>
+          <t>kk_4406693806</t>
         </is>
       </c>
       <c r="B1076" t="inlineStr">
         <is>
-          <t>01091727683</t>
+          <t>01088675050</t>
         </is>
       </c>
       <c r="C1076" t="inlineStr">
         <is>
-          <t>294249</t>
+          <t>280999</t>
         </is>
       </c>
       <c r="D1076" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Organic Traffic</t>
         </is>
       </c>
       <c r="E1076" t="inlineStr">
         <is>
-          <t>6968489536332</t>
+          <t>(referral)</t>
         </is>
       </c>
     </row>
     <row r="1077">
       <c r="A1077" t="inlineStr">
         <is>
-          <t>kk_4406693806</t>
+          <t>kk_4669827711</t>
         </is>
       </c>
       <c r="B1077" t="inlineStr">
         <is>
-          <t>01088675050</t>
+          <t>01091727683</t>
         </is>
       </c>
       <c r="C1077" t="inlineStr">
         <is>
-          <t>280999</t>
+          <t>294249</t>
         </is>
       </c>
       <c r="D1077" t="inlineStr">
         <is>
-          <t>Organic Traffic</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E1077" t="inlineStr">
         <is>
-          <t>(referral)</t>
+          <t>6968489536332</t>
         </is>
       </c>
     </row>
     <row r="1078">
       <c r="A1078" t="inlineStr">
         <is>
-          <t>kk_3792750872</t>
+          <t>kk_4848093455</t>
         </is>
       </c>
       <c r="B1078" t="inlineStr">
         <is>
-          <t>01084382636</t>
+          <t>01023043154</t>
         </is>
       </c>
       <c r="C1078" t="inlineStr">
         <is>
-          <t>256807</t>
+          <t>304517</t>
         </is>
       </c>
       <c r="D1078" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E1078" t="inlineStr">
         <is>
-          <t>KAKAO_CH_MENU_0211_NEW_MEN</t>
+          <t>6968489536332</t>
         </is>
       </c>
     </row>
@@ -29564,71 +29564,71 @@
     <row r="1080">
       <c r="A1080" t="inlineStr">
         <is>
-          <t>chpuss74</t>
+          <t>kk_2788668233</t>
         </is>
       </c>
       <c r="B1080" t="inlineStr">
         <is>
-          <t>01035361091</t>
+          <t>01041696139</t>
         </is>
       </c>
       <c r="C1080" t="inlineStr">
         <is>
-          <t>154462</t>
+          <t>210002</t>
         </is>
       </c>
       <c r="D1080" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E1080" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>6968489536332</t>
         </is>
       </c>
     </row>
     <row r="1081">
       <c r="A1081" t="inlineStr">
         <is>
-          <t>kk_4845661756</t>
+          <t>chpuss74</t>
         </is>
       </c>
       <c r="B1081" t="inlineStr">
         <is>
-          <t>01095936572</t>
+          <t>01035361091</t>
         </is>
       </c>
       <c r="C1081" t="inlineStr">
         <is>
-          <t>304422</t>
+          <t>154462</t>
         </is>
       </c>
       <c r="D1081" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="E1081" t="inlineStr">
         <is>
-          <t>6968489536332</t>
+          <t>Direct</t>
         </is>
       </c>
     </row>
     <row r="1082">
       <c r="A1082" t="inlineStr">
         <is>
-          <t>kk_3183517395</t>
+          <t>ch5115</t>
         </is>
       </c>
       <c r="B1082" t="inlineStr">
         <is>
-          <t>01082019936</t>
+          <t>01084479339</t>
         </is>
       </c>
       <c r="C1082" t="inlineStr">
         <is>
-          <t>228501</t>
+          <t>240557</t>
         </is>
       </c>
       <c r="D1082" t="inlineStr">
@@ -29645,17 +29645,17 @@
     <row r="1083">
       <c r="A1083" t="inlineStr">
         <is>
-          <t>kk_2788668233</t>
+          <t>kk_4845661756</t>
         </is>
       </c>
       <c r="B1083" t="inlineStr">
         <is>
-          <t>01041696139</t>
+          <t>01095936572</t>
         </is>
       </c>
       <c r="C1083" t="inlineStr">
         <is>
-          <t>210002</t>
+          <t>304422</t>
         </is>
       </c>
       <c r="D1083" t="inlineStr">
@@ -29672,54 +29672,54 @@
     <row r="1084">
       <c r="A1084" t="inlineStr">
         <is>
-          <t>ch5115</t>
+          <t>kk_4846729102</t>
         </is>
       </c>
       <c r="B1084" t="inlineStr">
         <is>
-          <t>01084479339</t>
+          <t>01084771303</t>
         </is>
       </c>
       <c r="C1084" t="inlineStr">
         <is>
-          <t>240557</t>
+          <t>304461</t>
         </is>
       </c>
       <c r="D1084" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E1084" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>6968489536332</t>
         </is>
       </c>
     </row>
     <row r="1085">
       <c r="A1085" t="inlineStr">
         <is>
-          <t>kk_4846729102</t>
+          <t>kk_3183517395</t>
         </is>
       </c>
       <c r="B1085" t="inlineStr">
         <is>
-          <t>01084771303</t>
+          <t>01082019936</t>
         </is>
       </c>
       <c r="C1085" t="inlineStr">
         <is>
-          <t>304461</t>
+          <t>228501</t>
         </is>
       </c>
       <c r="D1085" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="E1085" t="inlineStr">
         <is>
-          <t>6968489536332</t>
+          <t>Direct</t>
         </is>
       </c>
     </row>
@@ -29741,7 +29741,7 @@
       </c>
       <c r="D1086" t="inlineStr">
         <is>
-          <t>etc</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E1086" t="inlineStr">
@@ -29753,27 +29753,27 @@
     <row r="1087">
       <c r="A1087" t="inlineStr">
         <is>
-          <t>kjhk5404</t>
+          <t>kk_3650586439</t>
         </is>
       </c>
       <c r="B1087" t="inlineStr">
         <is>
-          <t>01027390700</t>
+          <t>01029107056</t>
         </is>
       </c>
       <c r="C1087" t="inlineStr">
         <is>
-          <t>280120</t>
+          <t>249153</t>
         </is>
       </c>
       <c r="D1087" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="E1087" t="inlineStr">
         <is>
-          <t>KAKAO_alimtalk</t>
+          <t>Direct</t>
         </is>
       </c>
     </row>
@@ -29807,81 +29807,81 @@
     <row r="1089">
       <c r="A1089" t="inlineStr">
         <is>
-          <t>kk_4844076820</t>
+          <t>kjhk5404</t>
         </is>
       </c>
       <c r="B1089" t="inlineStr">
         <is>
-          <t>01091346366</t>
+          <t>01027390700</t>
         </is>
       </c>
       <c r="C1089" t="inlineStr">
         <is>
-          <t>304343</t>
+          <t>280120</t>
         </is>
       </c>
       <c r="D1089" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E1089" t="inlineStr">
         <is>
-          <t>6968489536332</t>
+          <t>KAKAO_alimtalk</t>
         </is>
       </c>
     </row>
     <row r="1090">
       <c r="A1090" t="inlineStr">
         <is>
-          <t>kk_3650586439</t>
+          <t>kk_2775500473</t>
         </is>
       </c>
       <c r="B1090" t="inlineStr">
         <is>
-          <t>01029107056</t>
+          <t>01045659020</t>
         </is>
       </c>
       <c r="C1090" t="inlineStr">
         <is>
-          <t>249153</t>
+          <t>209371</t>
         </is>
       </c>
       <c r="D1090" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>Organic Traffic</t>
         </is>
       </c>
       <c r="E1090" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>(referral)</t>
         </is>
       </c>
     </row>
     <row r="1091">
       <c r="A1091" t="inlineStr">
         <is>
-          <t>kk_2775500473</t>
+          <t>kk_4844076820</t>
         </is>
       </c>
       <c r="B1091" t="inlineStr">
         <is>
-          <t>01045659020</t>
+          <t>01091346366</t>
         </is>
       </c>
       <c r="C1091" t="inlineStr">
         <is>
-          <t>209371</t>
+          <t>304343</t>
         </is>
       </c>
       <c r="D1091" t="inlineStr">
         <is>
-          <t>Organic Traffic</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E1091" t="inlineStr">
         <is>
-          <t>(referral)</t>
+          <t>6968489536332</t>
         </is>
       </c>
     </row>
@@ -29930,7 +29930,7 @@
       </c>
       <c r="D1093" t="inlineStr">
         <is>
-          <t>etc</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E1093" t="inlineStr">
@@ -30011,7 +30011,7 @@
       </c>
       <c r="D1096" t="inlineStr">
         <is>
-          <t>etc</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E1096" t="inlineStr">
@@ -30023,44 +30023,44 @@
     <row r="1097">
       <c r="A1097" t="inlineStr">
         <is>
-          <t>kk_4228106377</t>
+          <t>z090909x</t>
         </is>
       </c>
       <c r="B1097" t="inlineStr">
         <is>
-          <t>01063165271</t>
+          <t>01092058111</t>
         </is>
       </c>
       <c r="C1097" t="inlineStr">
         <is>
-          <t>273193</t>
+          <t>113003</t>
         </is>
       </c>
       <c r="D1097" t="inlineStr">
         <is>
-          <t>etc</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E1097" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0410exclusive2</t>
+          <t>6968489536332</t>
         </is>
       </c>
     </row>
     <row r="1098">
       <c r="A1098" t="inlineStr">
         <is>
-          <t>kk_3213636735</t>
+          <t>ssama</t>
         </is>
       </c>
       <c r="B1098" t="inlineStr">
         <is>
-          <t>01071338973</t>
+          <t>01056271982</t>
         </is>
       </c>
       <c r="C1098" t="inlineStr">
         <is>
-          <t>232010</t>
+          <t>47874</t>
         </is>
       </c>
       <c r="D1098" t="inlineStr">
@@ -30070,24 +30070,24 @@
       </c>
       <c r="E1098" t="inlineStr">
         <is>
-          <t>KAKAO_CH_MENU_0226_TRAILRUN</t>
+          <t>LMS_ECOM_0410exclusive2</t>
         </is>
       </c>
     </row>
     <row r="1099">
       <c r="A1099" t="inlineStr">
         <is>
-          <t>z090909x</t>
+          <t>kk_4840045474</t>
         </is>
       </c>
       <c r="B1099" t="inlineStr">
         <is>
-          <t>01092058111</t>
+          <t>01096310429</t>
         </is>
       </c>
       <c r="C1099" t="inlineStr">
         <is>
-          <t>113003</t>
+          <t>304122</t>
         </is>
       </c>
       <c r="D1099" t="inlineStr">
@@ -30104,27 +30104,27 @@
     <row r="1100">
       <c r="A1100" t="inlineStr">
         <is>
-          <t>xoxoie2</t>
+          <t>kk_4228106377</t>
         </is>
       </c>
       <c r="B1100" t="inlineStr">
         <is>
-          <t>01043560834</t>
+          <t>01063165271</t>
         </is>
       </c>
       <c r="C1100" t="inlineStr">
         <is>
-          <t>304072</t>
+          <t>273193</t>
         </is>
       </c>
       <c r="D1100" t="inlineStr">
         <is>
-          <t>Official SNS</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E1100" t="inlineStr">
         <is>
-          <t>EFW_04</t>
+          <t>LMS_ECOM_0410exclusive2</t>
         </is>
       </c>
     </row>
@@ -30146,7 +30146,7 @@
       </c>
       <c r="D1101" t="inlineStr">
         <is>
-          <t>etc</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E1101" t="inlineStr">
@@ -30158,162 +30158,162 @@
     <row r="1102">
       <c r="A1102" t="inlineStr">
         <is>
-          <t>eyounjoo</t>
+          <t>xoxoie2</t>
         </is>
       </c>
       <c r="B1102" t="inlineStr">
         <is>
-          <t>01036167949</t>
+          <t>01043560834</t>
         </is>
       </c>
       <c r="C1102" t="inlineStr">
         <is>
-          <t>283223</t>
+          <t>304072</t>
         </is>
       </c>
       <c r="D1102" t="inlineStr">
         <is>
-          <t>etc</t>
+          <t>Official SNS</t>
         </is>
       </c>
       <c r="E1102" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0410exclusive2</t>
+          <t>EFW_04</t>
         </is>
       </c>
     </row>
     <row r="1103">
       <c r="A1103" t="inlineStr">
         <is>
-          <t>ssama</t>
+          <t>kk_3213636735</t>
         </is>
       </c>
       <c r="B1103" t="inlineStr">
         <is>
-          <t>01056271982</t>
+          <t>01071338973</t>
         </is>
       </c>
       <c r="C1103" t="inlineStr">
         <is>
-          <t>47874</t>
+          <t>232010</t>
         </is>
       </c>
       <c r="D1103" t="inlineStr">
         <is>
-          <t>etc</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E1103" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0410exclusive2</t>
+          <t>KAKAO_CH_MENU_0226_TRAILRUN</t>
         </is>
       </c>
     </row>
     <row r="1104">
       <c r="A1104" t="inlineStr">
         <is>
-          <t>kk_4840045474</t>
+          <t>eyounjoo</t>
         </is>
       </c>
       <c r="B1104" t="inlineStr">
         <is>
-          <t>01096310429</t>
+          <t>01036167949</t>
         </is>
       </c>
       <c r="C1104" t="inlineStr">
         <is>
-          <t>304122</t>
+          <t>283223</t>
         </is>
       </c>
       <c r="D1104" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E1104" t="inlineStr">
         <is>
-          <t>6968489536332</t>
+          <t>LMS_ECOM_0410exclusive2</t>
         </is>
       </c>
     </row>
     <row r="1105">
       <c r="A1105" t="inlineStr">
         <is>
-          <t>kk_3024318364</t>
+          <t>kk_3875113278</t>
         </is>
       </c>
       <c r="B1105" t="inlineStr">
         <is>
-          <t>01050308038</t>
+          <t>01099620269</t>
         </is>
       </c>
       <c r="C1105" t="inlineStr">
         <is>
-          <t>219525</t>
+          <t>266546</t>
         </is>
       </c>
       <c r="D1105" t="inlineStr">
         <is>
-          <t>etc</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E1105" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0410exclusive2</t>
+          <t>lms_ecom_200416_family</t>
         </is>
       </c>
     </row>
     <row r="1106">
       <c r="A1106" t="inlineStr">
         <is>
-          <t>kk_3875113278</t>
+          <t>tnwks1115</t>
         </is>
       </c>
       <c r="B1106" t="inlineStr">
         <is>
-          <t>01099620269</t>
+          <t>01024221364</t>
         </is>
       </c>
       <c r="C1106" t="inlineStr">
         <is>
-          <t>266546</t>
+          <t>275948</t>
         </is>
       </c>
       <c r="D1106" t="inlineStr">
         <is>
-          <t>etc</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="E1106" t="inlineStr">
         <is>
-          <t>lms_ecom_200416_family</t>
+          <t>Direct</t>
         </is>
       </c>
     </row>
     <row r="1107">
       <c r="A1107" t="inlineStr">
         <is>
-          <t>tnwks1115</t>
+          <t>kk_3024318364</t>
         </is>
       </c>
       <c r="B1107" t="inlineStr">
         <is>
-          <t>01024221364</t>
+          <t>01050308038</t>
         </is>
       </c>
       <c r="C1107" t="inlineStr">
         <is>
-          <t>275948</t>
+          <t>219525</t>
         </is>
       </c>
       <c r="D1107" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E1107" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>LMS_ECOM_0410exclusive2</t>
         </is>
       </c>
     </row>
@@ -30347,71 +30347,71 @@
     <row r="1109">
       <c r="A1109" t="inlineStr">
         <is>
-          <t>mse001</t>
+          <t>kk_4218204827</t>
         </is>
       </c>
       <c r="B1109" t="inlineStr">
         <is>
-          <t>01085185510</t>
+          <t>01023704903</t>
         </is>
       </c>
       <c r="C1109" t="inlineStr">
         <is>
-          <t>227227</t>
+          <t>272698</t>
         </is>
       </c>
       <c r="D1109" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="E1109" t="inlineStr">
         <is>
-          <t>KAKAO_alimtalk</t>
+          <t>Direct</t>
         </is>
       </c>
     </row>
     <row r="1110">
       <c r="A1110" t="inlineStr">
         <is>
-          <t>kk_4218204827</t>
+          <t>mse001</t>
         </is>
       </c>
       <c r="B1110" t="inlineStr">
         <is>
-          <t>01023704903</t>
+          <t>01085185510</t>
         </is>
       </c>
       <c r="C1110" t="inlineStr">
         <is>
-          <t>272698</t>
+          <t>227227</t>
         </is>
       </c>
       <c r="D1110" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E1110" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>KAKAO_alimtalk</t>
         </is>
       </c>
     </row>
     <row r="1111">
       <c r="A1111" t="inlineStr">
         <is>
-          <t>aca1004</t>
+          <t>kk_3001595757</t>
         </is>
       </c>
       <c r="B1111" t="inlineStr">
         <is>
-          <t>01071740430</t>
+          <t>01059491458</t>
         </is>
       </c>
       <c r="C1111" t="inlineStr">
         <is>
-          <t>171757</t>
+          <t>218616</t>
         </is>
       </c>
       <c r="D1111" t="inlineStr">
@@ -30443,7 +30443,7 @@
       </c>
       <c r="D1112" t="inlineStr">
         <is>
-          <t>etc</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E1112" t="inlineStr">
@@ -30455,17 +30455,17 @@
     <row r="1113">
       <c r="A1113" t="inlineStr">
         <is>
-          <t>kk_3001595757</t>
+          <t>anfrorla</t>
         </is>
       </c>
       <c r="B1113" t="inlineStr">
         <is>
-          <t>01059491458</t>
+          <t>01050991521</t>
         </is>
       </c>
       <c r="C1113" t="inlineStr">
         <is>
-          <t>218616</t>
+          <t>137379</t>
         </is>
       </c>
       <c r="D1113" t="inlineStr">
@@ -30475,34 +30475,34 @@
       </c>
       <c r="E1113" t="inlineStr">
         <is>
-          <t>KAKAO_alimtalk</t>
+          <t>LMS_ECOM_200416_family</t>
         </is>
       </c>
     </row>
     <row r="1114">
       <c r="A1114" t="inlineStr">
         <is>
-          <t>quito3</t>
+          <t>aca1004</t>
         </is>
       </c>
       <c r="B1114" t="inlineStr">
         <is>
-          <t>01073440379</t>
+          <t>01071740430</t>
         </is>
       </c>
       <c r="C1114" t="inlineStr">
         <is>
-          <t>126578</t>
+          <t>171757</t>
         </is>
       </c>
       <c r="D1114" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E1114" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>KAKAO_alimtalk</t>
         </is>
       </c>
     </row>
@@ -30524,7 +30524,7 @@
       </c>
       <c r="D1115" t="inlineStr">
         <is>
-          <t>etc</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E1115" t="inlineStr">
@@ -30536,27 +30536,27 @@
     <row r="1116">
       <c r="A1116" t="inlineStr">
         <is>
-          <t>anfrorla</t>
+          <t>quito3</t>
         </is>
       </c>
       <c r="B1116" t="inlineStr">
         <is>
-          <t>01050991521</t>
+          <t>01073440379</t>
         </is>
       </c>
       <c r="C1116" t="inlineStr">
         <is>
-          <t>137379</t>
+          <t>126578</t>
         </is>
       </c>
       <c r="D1116" t="inlineStr">
         <is>
-          <t>etc</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="E1116" t="inlineStr">
         <is>
-          <t>LMS_ECOM_200416_family</t>
+          <t>Direct</t>
         </is>
       </c>
     </row>
@@ -30578,7 +30578,7 @@
       </c>
       <c r="D1117" t="inlineStr">
         <is>
-          <t>etc</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E1117" t="inlineStr">
@@ -30644,17 +30644,17 @@
     <row r="1120">
       <c r="A1120" t="inlineStr">
         <is>
-          <t>kk_2768186596</t>
+          <t>kk_4375003446</t>
         </is>
       </c>
       <c r="B1120" t="inlineStr">
         <is>
-          <t>01029241198</t>
+          <t>01087457282</t>
         </is>
       </c>
       <c r="C1120" t="inlineStr">
         <is>
-          <t>208962</t>
+          <t>280131</t>
         </is>
       </c>
       <c r="D1120" t="inlineStr">
@@ -30664,132 +30664,132 @@
       </c>
       <c r="E1120" t="inlineStr">
         <is>
-          <t>KAKAO_alimtalk</t>
+          <t>LMS_ECOM_0410exclusive2</t>
         </is>
       </c>
     </row>
     <row r="1121">
       <c r="A1121" t="inlineStr">
         <is>
-          <t>kk_4844817541</t>
+          <t>kk_3169777000</t>
         </is>
       </c>
       <c r="B1121" t="inlineStr">
         <is>
-          <t>01046631832</t>
+          <t>01089348462</t>
         </is>
       </c>
       <c r="C1121" t="inlineStr">
         <is>
-          <t>304380</t>
+          <t>224876</t>
         </is>
       </c>
       <c r="D1121" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="E1121" t="inlineStr">
         <is>
-          <t>[PF]전환_회원가입(유사)</t>
+          <t>Direct</t>
         </is>
       </c>
     </row>
     <row r="1122">
       <c r="A1122" t="inlineStr">
         <is>
-          <t>kk_4375003446</t>
+          <t>kk_4844817541</t>
         </is>
       </c>
       <c r="B1122" t="inlineStr">
         <is>
-          <t>01087457282</t>
+          <t>01046631832</t>
         </is>
       </c>
       <c r="C1122" t="inlineStr">
         <is>
-          <t>280131</t>
+          <t>304380</t>
         </is>
       </c>
       <c r="D1122" t="inlineStr">
         <is>
-          <t>etc</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E1122" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0410exclusive2</t>
+          <t>[PF]전환_회원가입(유사)</t>
         </is>
       </c>
     </row>
     <row r="1123">
       <c r="A1123" t="inlineStr">
         <is>
-          <t>kk_3169777000</t>
+          <t>kk_2768186596</t>
         </is>
       </c>
       <c r="B1123" t="inlineStr">
         <is>
-          <t>01089348462</t>
+          <t>01029241198</t>
         </is>
       </c>
       <c r="C1123" t="inlineStr">
         <is>
-          <t>224876</t>
+          <t>208962</t>
         </is>
       </c>
       <c r="D1123" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E1123" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>KAKAO_alimtalk</t>
         </is>
       </c>
     </row>
     <row r="1124">
       <c r="A1124" t="inlineStr">
         <is>
-          <t>kk_2768989214</t>
+          <t>kk_4472536591</t>
         </is>
       </c>
       <c r="B1124" t="inlineStr">
         <is>
-          <t>01095004289</t>
+          <t>01037057526</t>
         </is>
       </c>
       <c r="C1124" t="inlineStr">
         <is>
-          <t>209015</t>
+          <t>283897</t>
         </is>
       </c>
       <c r="D1124" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E1124" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>KAKAO_alimtalk</t>
         </is>
       </c>
     </row>
     <row r="1125">
       <c r="A1125" t="inlineStr">
         <is>
-          <t>kk_4472536591</t>
+          <t>kk_3688034999</t>
         </is>
       </c>
       <c r="B1125" t="inlineStr">
         <is>
-          <t>01037057526</t>
+          <t>01025408262</t>
         </is>
       </c>
       <c r="C1125" t="inlineStr">
         <is>
-          <t>283897</t>
+          <t>250755</t>
         </is>
       </c>
       <c r="D1125" t="inlineStr">
@@ -30860,44 +30860,44 @@
     <row r="1128">
       <c r="A1128" t="inlineStr">
         <is>
-          <t>kk_3444865211</t>
+          <t>dongheon20</t>
         </is>
       </c>
       <c r="B1128" t="inlineStr">
         <is>
-          <t>01021964871</t>
+          <t>01052298928</t>
         </is>
       </c>
       <c r="C1128" t="inlineStr">
         <is>
-          <t>242799</t>
+          <t>155362</t>
         </is>
       </c>
       <c r="D1128" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E1128" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>6968489536332</t>
         </is>
       </c>
     </row>
     <row r="1129">
       <c r="A1129" t="inlineStr">
         <is>
-          <t>xuswldls</t>
+          <t>kk_2768989214</t>
         </is>
       </c>
       <c r="B1129" t="inlineStr">
         <is>
-          <t>01027349414</t>
+          <t>01095004289</t>
         </is>
       </c>
       <c r="C1129" t="inlineStr">
         <is>
-          <t>133308</t>
+          <t>209015</t>
         </is>
       </c>
       <c r="D1129" t="inlineStr">
@@ -30914,233 +30914,233 @@
     <row r="1130">
       <c r="A1130" t="inlineStr">
         <is>
-          <t>dongheon20</t>
+          <t>kk_3444865211</t>
         </is>
       </c>
       <c r="B1130" t="inlineStr">
         <is>
-          <t>01052298928</t>
+          <t>01021964871</t>
         </is>
       </c>
       <c r="C1130" t="inlineStr">
         <is>
-          <t>155362</t>
+          <t>242799</t>
         </is>
       </c>
       <c r="D1130" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="E1130" t="inlineStr">
         <is>
-          <t>6968489536332</t>
+          <t>Direct</t>
         </is>
       </c>
     </row>
     <row r="1131">
       <c r="A1131" t="inlineStr">
         <is>
-          <t>kk_3688034999</t>
+          <t>xuswldls</t>
         </is>
       </c>
       <c r="B1131" t="inlineStr">
         <is>
-          <t>01025408262</t>
+          <t>01027349414</t>
         </is>
       </c>
       <c r="C1131" t="inlineStr">
         <is>
-          <t>250755</t>
+          <t>133308</t>
         </is>
       </c>
       <c r="D1131" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="E1131" t="inlineStr">
         <is>
-          <t>KAKAO_alimtalk</t>
+          <t>Direct</t>
         </is>
       </c>
     </row>
     <row r="1132">
       <c r="A1132" t="inlineStr">
         <is>
-          <t>jobguidance</t>
+          <t>kk_3837527580</t>
         </is>
       </c>
       <c r="B1132" t="inlineStr">
         <is>
-          <t>01026756920</t>
+          <t>01084311738</t>
         </is>
       </c>
       <c r="C1132" t="inlineStr">
         <is>
-          <t>134664</t>
+          <t>264113</t>
         </is>
       </c>
       <c r="D1132" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E1132" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>LMS_ECOM_0410exclusive2</t>
         </is>
       </c>
     </row>
     <row r="1133">
       <c r="A1133" t="inlineStr">
         <is>
-          <t>kk_3837527580</t>
+          <t>kk_3181917333</t>
         </is>
       </c>
       <c r="B1133" t="inlineStr">
         <is>
-          <t>01084311738</t>
+          <t>01072258509</t>
         </is>
       </c>
       <c r="C1133" t="inlineStr">
         <is>
-          <t>264113</t>
+          <t>227380</t>
         </is>
       </c>
       <c r="D1133" t="inlineStr">
         <is>
-          <t>etc</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="E1133" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0410exclusive2</t>
+          <t>Direct</t>
         </is>
       </c>
     </row>
     <row r="1134">
       <c r="A1134" t="inlineStr">
         <is>
-          <t>kk_3858585698</t>
+          <t>jobguidance</t>
         </is>
       </c>
       <c r="B1134" t="inlineStr">
         <is>
-          <t>01092163429</t>
+          <t>01026756920</t>
         </is>
       </c>
       <c r="C1134" t="inlineStr">
         <is>
-          <t>265508</t>
+          <t>134664</t>
         </is>
       </c>
       <c r="D1134" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="E1134" t="inlineStr">
         <is>
-          <t>KAKAO_alimtalk</t>
+          <t>Direct</t>
         </is>
       </c>
     </row>
     <row r="1135">
       <c r="A1135" t="inlineStr">
         <is>
-          <t>nesto1</t>
+          <t>escalater</t>
         </is>
       </c>
       <c r="B1135" t="inlineStr">
         <is>
-          <t>01056603953</t>
+          <t>01090911461</t>
         </is>
       </c>
       <c r="C1135" t="inlineStr">
         <is>
-          <t>125251</t>
+          <t>240051</t>
         </is>
       </c>
       <c r="D1135" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="E1135" t="inlineStr">
         <is>
-          <t>KAKAO_alimtalk</t>
+          <t>Direct</t>
         </is>
       </c>
     </row>
     <row r="1136">
       <c r="A1136" t="inlineStr">
         <is>
-          <t>escalater</t>
+          <t>nesto1</t>
         </is>
       </c>
       <c r="B1136" t="inlineStr">
         <is>
-          <t>01090911461</t>
+          <t>01056603953</t>
         </is>
       </c>
       <c r="C1136" t="inlineStr">
         <is>
-          <t>240051</t>
+          <t>125251</t>
         </is>
       </c>
       <c r="D1136" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E1136" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>KAKAO_alimtalk</t>
         </is>
       </c>
     </row>
     <row r="1137">
       <c r="A1137" t="inlineStr">
         <is>
-          <t>kk_3181917333</t>
+          <t>kk_3858585698</t>
         </is>
       </c>
       <c r="B1137" t="inlineStr">
         <is>
-          <t>01072258509</t>
+          <t>01092163429</t>
         </is>
       </c>
       <c r="C1137" t="inlineStr">
         <is>
-          <t>227380</t>
+          <t>265508</t>
         </is>
       </c>
       <c r="D1137" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E1137" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>KAKAO_alimtalk</t>
         </is>
       </c>
     </row>
     <row r="1138">
       <c r="A1138" t="inlineStr">
         <is>
-          <t>seul6169</t>
+          <t>hursean</t>
         </is>
       </c>
       <c r="B1138" t="inlineStr">
         <is>
-          <t>01066116699</t>
+          <t>01091975738</t>
         </is>
       </c>
       <c r="C1138" t="inlineStr">
         <is>
-          <t>234239</t>
+          <t>123130</t>
         </is>
       </c>
       <c r="D1138" t="inlineStr">
@@ -31150,29 +31150,29 @@
       </c>
       <c r="E1138" t="inlineStr">
         <is>
-          <t>KAKAO_alimtalk</t>
+          <t>Email_mkt</t>
         </is>
       </c>
     </row>
     <row r="1139">
       <c r="A1139" t="inlineStr">
         <is>
-          <t>aya6969</t>
+          <t>kk_4467707148</t>
         </is>
       </c>
       <c r="B1139" t="inlineStr">
         <is>
-          <t>01076590009</t>
+          <t>01030843332</t>
         </is>
       </c>
       <c r="C1139" t="inlineStr">
         <is>
-          <t>162562</t>
+          <t>283560</t>
         </is>
       </c>
       <c r="D1139" t="inlineStr">
         <is>
-          <t>etc</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E1139" t="inlineStr">
@@ -31184,130 +31184,130 @@
     <row r="1140">
       <c r="A1140" t="inlineStr">
         <is>
-          <t>kk_4840061178</t>
+          <t>kk_3185867832</t>
         </is>
       </c>
       <c r="B1140" t="inlineStr">
         <is>
-          <t>01082357895</t>
+          <t>01022086508</t>
         </is>
       </c>
       <c r="C1140" t="inlineStr">
         <is>
-          <t>304124</t>
+          <t>229863</t>
         </is>
       </c>
       <c r="D1140" t="inlineStr">
         <is>
-          <t>Awareness</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E1140" t="inlineStr">
         <is>
-          <t>benz_running_program_2026_coupon</t>
+          <t>LMS_ECOM_0410exclusive2</t>
         </is>
       </c>
     </row>
     <row r="1141">
       <c r="A1141" t="inlineStr">
         <is>
-          <t>kk_3933534683</t>
+          <t>kk_4338209948</t>
         </is>
       </c>
       <c r="B1141" t="inlineStr">
         <is>
-          <t>01030153796</t>
+          <t>01088132379</t>
         </is>
       </c>
       <c r="C1141" t="inlineStr">
         <is>
-          <t>269069</t>
+          <t>278781</t>
         </is>
       </c>
       <c r="D1141" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E1141" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>KAKAO_alimtalk</t>
         </is>
       </c>
     </row>
     <row r="1142">
       <c r="A1142" t="inlineStr">
         <is>
-          <t>kk_2940110361</t>
+          <t>kk_4840061178</t>
         </is>
       </c>
       <c r="B1142" t="inlineStr">
         <is>
-          <t>01035353200</t>
+          <t>01082357895</t>
         </is>
       </c>
       <c r="C1142" t="inlineStr">
         <is>
-          <t>216362</t>
+          <t>304124</t>
         </is>
       </c>
       <c r="D1142" t="inlineStr">
         <is>
-          <t>etc</t>
+          <t>Awareness</t>
         </is>
       </c>
       <c r="E1142" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0410exclusive2</t>
+          <t>benz_running_program_2026_coupon</t>
         </is>
       </c>
     </row>
     <row r="1143">
       <c r="A1143" t="inlineStr">
         <is>
-          <t>kk_3013902343</t>
+          <t>kk_4523594127</t>
         </is>
       </c>
       <c r="B1143" t="inlineStr">
         <is>
-          <t>01051802326</t>
+          <t>01085735215</t>
         </is>
       </c>
       <c r="C1143" t="inlineStr">
         <is>
-          <t>219219</t>
+          <t>286358</t>
         </is>
       </c>
       <c r="D1143" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E1143" t="inlineStr">
         <is>
-          <t>6968489536332</t>
+          <t>LMS_ECOM_0410exclusive2</t>
         </is>
       </c>
     </row>
     <row r="1144">
       <c r="A1144" t="inlineStr">
         <is>
-          <t>kk_4523594127</t>
+          <t>aya6969</t>
         </is>
       </c>
       <c r="B1144" t="inlineStr">
         <is>
-          <t>01085735215</t>
+          <t>01076590009</t>
         </is>
       </c>
       <c r="C1144" t="inlineStr">
         <is>
-          <t>286358</t>
+          <t>162562</t>
         </is>
       </c>
       <c r="D1144" t="inlineStr">
         <is>
-          <t>etc</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E1144" t="inlineStr">
@@ -31319,49 +31319,49 @@
     <row r="1145">
       <c r="A1145" t="inlineStr">
         <is>
-          <t>kk_4467707148</t>
+          <t>kk_3933534683</t>
         </is>
       </c>
       <c r="B1145" t="inlineStr">
         <is>
-          <t>01030843332</t>
+          <t>01030153796</t>
         </is>
       </c>
       <c r="C1145" t="inlineStr">
         <is>
-          <t>283560</t>
+          <t>269069</t>
         </is>
       </c>
       <c r="D1145" t="inlineStr">
         <is>
-          <t>etc</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="E1145" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0410exclusive2</t>
+          <t>Direct</t>
         </is>
       </c>
     </row>
     <row r="1146">
       <c r="A1146" t="inlineStr">
         <is>
-          <t>mansoogi</t>
+          <t>kk_2940110361</t>
         </is>
       </c>
       <c r="B1146" t="inlineStr">
         <is>
-          <t>01093240897</t>
+          <t>01035353200</t>
         </is>
       </c>
       <c r="C1146" t="inlineStr">
         <is>
-          <t>25243</t>
+          <t>216362</t>
         </is>
       </c>
       <c r="D1146" t="inlineStr">
         <is>
-          <t>etc</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E1146" t="inlineStr">
@@ -31373,17 +31373,17 @@
     <row r="1147">
       <c r="A1147" t="inlineStr">
         <is>
-          <t>kk_4338209948</t>
+          <t>mansoogi</t>
         </is>
       </c>
       <c r="B1147" t="inlineStr">
         <is>
-          <t>01088132379</t>
+          <t>01093240897</t>
         </is>
       </c>
       <c r="C1147" t="inlineStr">
         <is>
-          <t>278781</t>
+          <t>25243</t>
         </is>
       </c>
       <c r="D1147" t="inlineStr">
@@ -31393,61 +31393,61 @@
       </c>
       <c r="E1147" t="inlineStr">
         <is>
-          <t>KAKAO_alimtalk</t>
+          <t>LMS_ECOM_0410exclusive2</t>
         </is>
       </c>
     </row>
     <row r="1148">
       <c r="A1148" t="inlineStr">
         <is>
-          <t>hursean</t>
+          <t>kk_3013902343</t>
         </is>
       </c>
       <c r="B1148" t="inlineStr">
         <is>
-          <t>01091975738</t>
+          <t>01051802326</t>
         </is>
       </c>
       <c r="C1148" t="inlineStr">
         <is>
-          <t>123130</t>
+          <t>219219</t>
         </is>
       </c>
       <c r="D1148" t="inlineStr">
         <is>
-          <t>etc</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E1148" t="inlineStr">
         <is>
-          <t>Email_mkt</t>
+          <t>6968489536332</t>
         </is>
       </c>
     </row>
     <row r="1149">
       <c r="A1149" t="inlineStr">
         <is>
-          <t>kk_3185867832</t>
+          <t>seul6169</t>
         </is>
       </c>
       <c r="B1149" t="inlineStr">
         <is>
-          <t>01022086508</t>
+          <t>01066116699</t>
         </is>
       </c>
       <c r="C1149" t="inlineStr">
         <is>
-          <t>229863</t>
+          <t>234239</t>
         </is>
       </c>
       <c r="D1149" t="inlineStr">
         <is>
-          <t>etc</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E1149" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0410exclusive2</t>
+          <t>KAKAO_alimtalk</t>
         </is>
       </c>
     </row>
@@ -31469,7 +31469,7 @@
       </c>
       <c r="D1150" t="inlineStr">
         <is>
-          <t>etc</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E1150" t="inlineStr">
@@ -31508,49 +31508,49 @@
     <row r="1152">
       <c r="A1152" t="inlineStr">
         <is>
-          <t>kk_3114284664</t>
+          <t>kk_3296362697</t>
         </is>
       </c>
       <c r="B1152" t="inlineStr">
         <is>
-          <t>01031259752</t>
+          <t>01032224185</t>
         </is>
       </c>
       <c r="C1152" t="inlineStr">
         <is>
-          <t>222243</t>
+          <t>237406</t>
         </is>
       </c>
       <c r="D1152" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E1152" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>LMS_ECOM_200416_family</t>
         </is>
       </c>
     </row>
     <row r="1153">
       <c r="A1153" t="inlineStr">
         <is>
-          <t>kk_3801403661</t>
+          <t>kk_4358499671</t>
         </is>
       </c>
       <c r="B1153" t="inlineStr">
         <is>
-          <t>01086386165</t>
+          <t>01066507573</t>
         </is>
       </c>
       <c r="C1153" t="inlineStr">
         <is>
-          <t>259058</t>
+          <t>279591</t>
         </is>
       </c>
       <c r="D1153" t="inlineStr">
         <is>
-          <t>etc</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E1153" t="inlineStr">
@@ -31562,49 +31562,49 @@
     <row r="1154">
       <c r="A1154" t="inlineStr">
         <is>
-          <t>kk_3927027066</t>
+          <t>kk_3114284664</t>
         </is>
       </c>
       <c r="B1154" t="inlineStr">
         <is>
-          <t>01046272823</t>
+          <t>01031259752</t>
         </is>
       </c>
       <c r="C1154" t="inlineStr">
         <is>
-          <t>268818</t>
+          <t>222243</t>
         </is>
       </c>
       <c r="D1154" t="inlineStr">
         <is>
-          <t>etc</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="E1154" t="inlineStr">
         <is>
-          <t>LMS_ECOM_200416_family</t>
+          <t>Direct</t>
         </is>
       </c>
     </row>
     <row r="1155">
       <c r="A1155" t="inlineStr">
         <is>
-          <t>kk_4358499671</t>
+          <t>kk_3378895949</t>
         </is>
       </c>
       <c r="B1155" t="inlineStr">
         <is>
-          <t>01066507573</t>
+          <t>01040411704</t>
         </is>
       </c>
       <c r="C1155" t="inlineStr">
         <is>
-          <t>279591</t>
+          <t>240461</t>
         </is>
       </c>
       <c r="D1155" t="inlineStr">
         <is>
-          <t>etc</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E1155" t="inlineStr">
@@ -31616,17 +31616,17 @@
     <row r="1156">
       <c r="A1156" t="inlineStr">
         <is>
-          <t>kk_3654717861</t>
+          <t>kk_3927027066</t>
         </is>
       </c>
       <c r="B1156" t="inlineStr">
         <is>
-          <t>01022661489</t>
+          <t>01046272823</t>
         </is>
       </c>
       <c r="C1156" t="inlineStr">
         <is>
-          <t>249347</t>
+          <t>268818</t>
         </is>
       </c>
       <c r="D1156" t="inlineStr">
@@ -31636,24 +31636,24 @@
       </c>
       <c r="E1156" t="inlineStr">
         <is>
-          <t>KAKAO_alimtalk</t>
+          <t>LMS_ECOM_200416_family</t>
         </is>
       </c>
     </row>
     <row r="1157">
       <c r="A1157" t="inlineStr">
         <is>
-          <t>kycho229</t>
+          <t>kk_4600690023</t>
         </is>
       </c>
       <c r="B1157" t="inlineStr">
         <is>
-          <t>01047322138</t>
+          <t>01067632977</t>
         </is>
       </c>
       <c r="C1157" t="inlineStr">
         <is>
-          <t>22747</t>
+          <t>289390</t>
         </is>
       </c>
       <c r="D1157" t="inlineStr">
@@ -31663,56 +31663,56 @@
       </c>
       <c r="E1157" t="inlineStr">
         <is>
-          <t>EDM_0416</t>
+          <t>LMS_ECOM_200416_family</t>
         </is>
       </c>
     </row>
     <row r="1158">
       <c r="A1158" t="inlineStr">
         <is>
-          <t>kk_4608940431</t>
+          <t>kk_3654717861</t>
         </is>
       </c>
       <c r="B1158" t="inlineStr">
         <is>
-          <t>01034834753</t>
+          <t>01022661489</t>
         </is>
       </c>
       <c r="C1158" t="inlineStr">
         <is>
-          <t>289885</t>
+          <t>249347</t>
         </is>
       </c>
       <c r="D1158" t="inlineStr">
         <is>
-          <t>etc</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E1158" t="inlineStr">
         <is>
-          <t>LMS_ECOM_200416_family</t>
+          <t>KAKAO_alimtalk</t>
         </is>
       </c>
     </row>
     <row r="1159">
       <c r="A1159" t="inlineStr">
         <is>
-          <t>kk_3296362697</t>
+          <t>kk_3801403661</t>
         </is>
       </c>
       <c r="B1159" t="inlineStr">
         <is>
-          <t>01032224185</t>
+          <t>01086386165</t>
         </is>
       </c>
       <c r="C1159" t="inlineStr">
         <is>
-          <t>237406</t>
+          <t>259058</t>
         </is>
       </c>
       <c r="D1159" t="inlineStr">
         <is>
-          <t>etc</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E1159" t="inlineStr">
@@ -31724,49 +31724,49 @@
     <row r="1160">
       <c r="A1160" t="inlineStr">
         <is>
-          <t>kk_4600690023</t>
+          <t>kycho229</t>
         </is>
       </c>
       <c r="B1160" t="inlineStr">
         <is>
-          <t>01067632977</t>
+          <t>01047322138</t>
         </is>
       </c>
       <c r="C1160" t="inlineStr">
         <is>
-          <t>289390</t>
+          <t>22747</t>
         </is>
       </c>
       <c r="D1160" t="inlineStr">
         <is>
-          <t>etc</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E1160" t="inlineStr">
         <is>
-          <t>LMS_ECOM_200416_family</t>
+          <t>EDM_0416</t>
         </is>
       </c>
     </row>
     <row r="1161">
       <c r="A1161" t="inlineStr">
         <is>
-          <t>taebaekcc</t>
+          <t>kk_4608940431</t>
         </is>
       </c>
       <c r="B1161" t="inlineStr">
         <is>
-          <t>01090034620</t>
+          <t>01034834753</t>
         </is>
       </c>
       <c r="C1161" t="inlineStr">
         <is>
-          <t>182329</t>
+          <t>289885</t>
         </is>
       </c>
       <c r="D1161" t="inlineStr">
         <is>
-          <t>etc</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E1161" t="inlineStr">
@@ -31778,22 +31778,22 @@
     <row r="1162">
       <c r="A1162" t="inlineStr">
         <is>
-          <t>kk_3378895949</t>
+          <t>taebaekcc</t>
         </is>
       </c>
       <c r="B1162" t="inlineStr">
         <is>
-          <t>01040411704</t>
+          <t>01090034620</t>
         </is>
       </c>
       <c r="C1162" t="inlineStr">
         <is>
-          <t>240461</t>
+          <t>182329</t>
         </is>
       </c>
       <c r="D1162" t="inlineStr">
         <is>
-          <t>etc</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E1162" t="inlineStr">
@@ -31859,44 +31859,44 @@
     <row r="1165">
       <c r="A1165" t="inlineStr">
         <is>
-          <t>pentagram</t>
+          <t>kk_2807863527</t>
         </is>
       </c>
       <c r="B1165" t="inlineStr">
         <is>
-          <t>01093327353</t>
+          <t>01042669625</t>
         </is>
       </c>
       <c r="C1165" t="inlineStr">
         <is>
-          <t>131085</t>
+          <t>211605</t>
         </is>
       </c>
       <c r="D1165" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E1165" t="inlineStr">
         <is>
-          <t>KAKAO_alimtalk</t>
+          <t>[PF]전환_회원가입(유사)</t>
         </is>
       </c>
     </row>
     <row r="1166">
       <c r="A1166" t="inlineStr">
         <is>
-          <t>kk_2807863527</t>
+          <t>dltndgy99</t>
         </is>
       </c>
       <c r="B1166" t="inlineStr">
         <is>
-          <t>01042669625</t>
+          <t>01024587982</t>
         </is>
       </c>
       <c r="C1166" t="inlineStr">
         <is>
-          <t>211605</t>
+          <t>156217</t>
         </is>
       </c>
       <c r="D1166" t="inlineStr">
@@ -31906,34 +31906,34 @@
       </c>
       <c r="E1166" t="inlineStr">
         <is>
-          <t>[PF]전환_회원가입(유사)</t>
+          <t>naver_brandsearch_mobile</t>
         </is>
       </c>
     </row>
     <row r="1167">
       <c r="A1167" t="inlineStr">
         <is>
-          <t>dltndgy99</t>
+          <t>pentagram</t>
         </is>
       </c>
       <c r="B1167" t="inlineStr">
         <is>
-          <t>01024587982</t>
+          <t>01093327353</t>
         </is>
       </c>
       <c r="C1167" t="inlineStr">
         <is>
-          <t>156217</t>
+          <t>131085</t>
         </is>
       </c>
       <c r="D1167" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E1167" t="inlineStr">
         <is>
-          <t>naver_brandsearch_mobile</t>
+          <t>KAKAO_alimtalk</t>
         </is>
       </c>
     </row>
@@ -31967,49 +31967,49 @@
     <row r="1169">
       <c r="A1169" t="inlineStr">
         <is>
-          <t>wisbrain</t>
+          <t>kk_4427490834</t>
         </is>
       </c>
       <c r="B1169" t="inlineStr">
         <is>
-          <t>01047220186</t>
+          <t>01034704205</t>
         </is>
       </c>
       <c r="C1169" t="inlineStr">
         <is>
-          <t>188067</t>
+          <t>281590</t>
         </is>
       </c>
       <c r="D1169" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E1169" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>LMS_ECOM_0410exclusive2</t>
         </is>
       </c>
     </row>
     <row r="1170">
       <c r="A1170" t="inlineStr">
         <is>
-          <t>kk_4427490834</t>
+          <t>loyed24</t>
         </is>
       </c>
       <c r="B1170" t="inlineStr">
         <is>
-          <t>01034704205</t>
+          <t>01085487901</t>
         </is>
       </c>
       <c r="C1170" t="inlineStr">
         <is>
-          <t>281590</t>
+          <t>244062</t>
         </is>
       </c>
       <c r="D1170" t="inlineStr">
         <is>
-          <t>etc</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E1170" t="inlineStr">
@@ -32021,103 +32021,103 @@
     <row r="1171">
       <c r="A1171" t="inlineStr">
         <is>
-          <t>loyed24</t>
+          <t>hihijs34</t>
         </is>
       </c>
       <c r="B1171" t="inlineStr">
         <is>
-          <t>01085487901</t>
+          <t>01093230529</t>
         </is>
       </c>
       <c r="C1171" t="inlineStr">
         <is>
-          <t>244062</t>
+          <t>128947</t>
         </is>
       </c>
       <c r="D1171" t="inlineStr">
         <is>
-          <t>etc</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E1171" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0410exclusive2</t>
+          <t>[PF]A+SC_상시(1865MF,구매+장바구니)</t>
         </is>
       </c>
     </row>
     <row r="1172">
       <c r="A1172" t="inlineStr">
         <is>
-          <t>hihijs34</t>
+          <t>wisbrain</t>
         </is>
       </c>
       <c r="B1172" t="inlineStr">
         <is>
-          <t>01093230529</t>
+          <t>01047220186</t>
         </is>
       </c>
       <c r="C1172" t="inlineStr">
         <is>
-          <t>128947</t>
+          <t>188067</t>
         </is>
       </c>
       <c r="D1172" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="E1172" t="inlineStr">
         <is>
-          <t>[PF]A+SC_상시(1865MF,구매+장바구니)</t>
+          <t>Direct</t>
         </is>
       </c>
     </row>
     <row r="1173">
       <c r="A1173" t="inlineStr">
         <is>
-          <t>kk_4292190414</t>
+          <t>kk_4452401577</t>
         </is>
       </c>
       <c r="B1173" t="inlineStr">
         <is>
-          <t>01095177478</t>
+          <t>01047428000</t>
         </is>
       </c>
       <c r="C1173" t="inlineStr">
         <is>
-          <t>275998</t>
+          <t>282525</t>
         </is>
       </c>
       <c r="D1173" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E1173" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>LMS_ECOM_0410exclusive2</t>
         </is>
       </c>
     </row>
     <row r="1174">
       <c r="A1174" t="inlineStr">
         <is>
-          <t>sjm700</t>
+          <t>kk_3180736217</t>
         </is>
       </c>
       <c r="B1174" t="inlineStr">
         <is>
-          <t>01077331591</t>
+          <t>01036000343</t>
         </is>
       </c>
       <c r="C1174" t="inlineStr">
         <is>
-          <t>118769</t>
+          <t>226314</t>
         </is>
       </c>
       <c r="D1174" t="inlineStr">
         <is>
-          <t>etc</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E1174" t="inlineStr">
@@ -32129,49 +32129,49 @@
     <row r="1175">
       <c r="A1175" t="inlineStr">
         <is>
-          <t>kk_4525043459</t>
+          <t>camiblanco</t>
         </is>
       </c>
       <c r="B1175" t="inlineStr">
         <is>
-          <t>01088312135</t>
+          <t>01072190103</t>
         </is>
       </c>
       <c r="C1175" t="inlineStr">
         <is>
-          <t>286464</t>
+          <t>232545</t>
         </is>
       </c>
       <c r="D1175" t="inlineStr">
         <is>
-          <t>etc</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="E1175" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0410exclusive2</t>
+          <t>Direct</t>
         </is>
       </c>
     </row>
     <row r="1176">
       <c r="A1176" t="inlineStr">
         <is>
-          <t>kk_3180736217</t>
+          <t>inu21c</t>
         </is>
       </c>
       <c r="B1176" t="inlineStr">
         <is>
-          <t>01036000343</t>
+          <t>01035128236</t>
         </is>
       </c>
       <c r="C1176" t="inlineStr">
         <is>
-          <t>226314</t>
+          <t>131940</t>
         </is>
       </c>
       <c r="D1176" t="inlineStr">
         <is>
-          <t>etc</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E1176" t="inlineStr">
@@ -32183,17 +32183,17 @@
     <row r="1177">
       <c r="A1177" t="inlineStr">
         <is>
-          <t>camiblanco</t>
+          <t>kk_3721447783</t>
         </is>
       </c>
       <c r="B1177" t="inlineStr">
         <is>
-          <t>01072190103</t>
+          <t>01051311087</t>
         </is>
       </c>
       <c r="C1177" t="inlineStr">
         <is>
-          <t>232545</t>
+          <t>252252</t>
         </is>
       </c>
       <c r="D1177" t="inlineStr">
@@ -32210,22 +32210,22 @@
     <row r="1178">
       <c r="A1178" t="inlineStr">
         <is>
-          <t>inu21c</t>
+          <t>kk_3349199057</t>
         </is>
       </c>
       <c r="B1178" t="inlineStr">
         <is>
-          <t>01035128236</t>
+          <t>01071630312</t>
         </is>
       </c>
       <c r="C1178" t="inlineStr">
         <is>
-          <t>131940</t>
+          <t>239388</t>
         </is>
       </c>
       <c r="D1178" t="inlineStr">
         <is>
-          <t>etc</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E1178" t="inlineStr">
@@ -32237,76 +32237,76 @@
     <row r="1179">
       <c r="A1179" t="inlineStr">
         <is>
-          <t>kk_2825715315</t>
+          <t>kk_4292190414</t>
         </is>
       </c>
       <c r="B1179" t="inlineStr">
         <is>
-          <t>01077229654</t>
+          <t>01095177478</t>
         </is>
       </c>
       <c r="C1179" t="inlineStr">
         <is>
-          <t>212719</t>
+          <t>275998</t>
         </is>
       </c>
       <c r="D1179" t="inlineStr">
         <is>
-          <t>etc</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="E1179" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0410exclusive2</t>
+          <t>Direct</t>
         </is>
       </c>
     </row>
     <row r="1180">
       <c r="A1180" t="inlineStr">
         <is>
-          <t>kk_3721447783</t>
+          <t>kk_4578503399</t>
         </is>
       </c>
       <c r="B1180" t="inlineStr">
         <is>
-          <t>01051311087</t>
+          <t>01088660330</t>
         </is>
       </c>
       <c r="C1180" t="inlineStr">
         <is>
-          <t>252252</t>
+          <t>288374</t>
         </is>
       </c>
       <c r="D1180" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E1180" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>LMS_ECOM_0410exclusive2</t>
         </is>
       </c>
     </row>
     <row r="1181">
       <c r="A1181" t="inlineStr">
         <is>
-          <t>kk_3973703558</t>
+          <t>kk_4525043459</t>
         </is>
       </c>
       <c r="B1181" t="inlineStr">
         <is>
-          <t>01048590748</t>
+          <t>01088312135</t>
         </is>
       </c>
       <c r="C1181" t="inlineStr">
         <is>
-          <t>271020</t>
+          <t>286464</t>
         </is>
       </c>
       <c r="D1181" t="inlineStr">
         <is>
-          <t>etc</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E1181" t="inlineStr">
@@ -32318,157 +32318,157 @@
     <row r="1182">
       <c r="A1182" t="inlineStr">
         <is>
-          <t>bobjazz</t>
+          <t>pls4u</t>
         </is>
       </c>
       <c r="B1182" t="inlineStr">
         <is>
-          <t>01084090677</t>
+          <t>01085985482</t>
         </is>
       </c>
       <c r="C1182" t="inlineStr">
         <is>
-          <t>186218</t>
+          <t>88257</t>
         </is>
       </c>
       <c r="D1182" t="inlineStr">
         <is>
-          <t>etc</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E1182" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0410exclusive2</t>
+          <t>LMS_ECOM_0401_trailrunning</t>
         </is>
       </c>
     </row>
     <row r="1183">
       <c r="A1183" t="inlineStr">
         <is>
-          <t>kk_4578503399</t>
+          <t>dmsql785612</t>
         </is>
       </c>
       <c r="B1183" t="inlineStr">
         <is>
-          <t>01088660330</t>
+          <t>01051590364</t>
         </is>
       </c>
       <c r="C1183" t="inlineStr">
         <is>
-          <t>288374</t>
+          <t>137279</t>
         </is>
       </c>
       <c r="D1183" t="inlineStr">
         <is>
-          <t>etc</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E1183" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0410exclusive2</t>
+          <t>Email_mkt</t>
         </is>
       </c>
     </row>
     <row r="1184">
       <c r="A1184" t="inlineStr">
         <is>
-          <t>pls4u</t>
+          <t>columbia7</t>
         </is>
       </c>
       <c r="B1184" t="inlineStr">
         <is>
-          <t>01085985482</t>
+          <t>01050080025</t>
         </is>
       </c>
       <c r="C1184" t="inlineStr">
         <is>
-          <t>88257</t>
+          <t>109980</t>
         </is>
       </c>
       <c r="D1184" t="inlineStr">
         <is>
-          <t>etc</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E1184" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0401_trailrunning</t>
+          <t>LMS_ECOM_0410exclusive2</t>
         </is>
       </c>
     </row>
     <row r="1185">
       <c r="A1185" t="inlineStr">
         <is>
-          <t>dmsql785612</t>
+          <t>kk_2825715315</t>
         </is>
       </c>
       <c r="B1185" t="inlineStr">
         <is>
-          <t>01051590364</t>
+          <t>01077229654</t>
         </is>
       </c>
       <c r="C1185" t="inlineStr">
         <is>
-          <t>137279</t>
+          <t>212719</t>
         </is>
       </c>
       <c r="D1185" t="inlineStr">
         <is>
-          <t>etc</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E1185" t="inlineStr">
         <is>
-          <t>Email_mkt</t>
+          <t>LMS_ECOM_0410exclusive2</t>
         </is>
       </c>
     </row>
     <row r="1186">
       <c r="A1186" t="inlineStr">
         <is>
-          <t>yongshin</t>
+          <t>sjm700</t>
         </is>
       </c>
       <c r="B1186" t="inlineStr">
         <is>
-          <t>01053867821</t>
+          <t>01077331591</t>
         </is>
       </c>
       <c r="C1186" t="inlineStr">
         <is>
-          <t>277896</t>
+          <t>118769</t>
         </is>
       </c>
       <c r="D1186" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E1186" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>LMS_ECOM_0410exclusive2</t>
         </is>
       </c>
     </row>
     <row r="1187">
       <c r="A1187" t="inlineStr">
         <is>
-          <t>columbia7</t>
+          <t>kk_3973703558</t>
         </is>
       </c>
       <c r="B1187" t="inlineStr">
         <is>
-          <t>01050080025</t>
+          <t>01048590748</t>
         </is>
       </c>
       <c r="C1187" t="inlineStr">
         <is>
-          <t>109980</t>
+          <t>271020</t>
         </is>
       </c>
       <c r="D1187" t="inlineStr">
         <is>
-          <t>etc</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E1187" t="inlineStr">
@@ -32480,49 +32480,49 @@
     <row r="1188">
       <c r="A1188" t="inlineStr">
         <is>
-          <t>kk_3754052831</t>
+          <t>yongshin</t>
         </is>
       </c>
       <c r="B1188" t="inlineStr">
         <is>
-          <t>01092180804</t>
+          <t>01053867821</t>
         </is>
       </c>
       <c r="C1188" t="inlineStr">
         <is>
-          <t>254339</t>
+          <t>277896</t>
         </is>
       </c>
       <c r="D1188" t="inlineStr">
         <is>
-          <t>etc</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="E1188" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0410exclusive2</t>
+          <t>Direct</t>
         </is>
       </c>
     </row>
     <row r="1189">
       <c r="A1189" t="inlineStr">
         <is>
-          <t>kk_3349199057</t>
+          <t>kk_3754052831</t>
         </is>
       </c>
       <c r="B1189" t="inlineStr">
         <is>
-          <t>01071630312</t>
+          <t>01092180804</t>
         </is>
       </c>
       <c r="C1189" t="inlineStr">
         <is>
-          <t>239388</t>
+          <t>254339</t>
         </is>
       </c>
       <c r="D1189" t="inlineStr">
         <is>
-          <t>etc</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E1189" t="inlineStr">
@@ -32534,22 +32534,22 @@
     <row r="1190">
       <c r="A1190" t="inlineStr">
         <is>
-          <t>kk_4452401577</t>
+          <t>bobjazz</t>
         </is>
       </c>
       <c r="B1190" t="inlineStr">
         <is>
-          <t>01047428000</t>
+          <t>01084090677</t>
         </is>
       </c>
       <c r="C1190" t="inlineStr">
         <is>
-          <t>282525</t>
+          <t>186218</t>
         </is>
       </c>
       <c r="D1190" t="inlineStr">
         <is>
-          <t>etc</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E1190" t="inlineStr">
@@ -32588,22 +32588,22 @@
     <row r="1192">
       <c r="A1192" t="inlineStr">
         <is>
-          <t>coda1202</t>
+          <t>kairos93</t>
         </is>
       </c>
       <c r="B1192" t="inlineStr">
         <is>
-          <t>01037655629</t>
+          <t>01051079223</t>
         </is>
       </c>
       <c r="C1192" t="inlineStr">
         <is>
-          <t>117064</t>
+          <t>160644</t>
         </is>
       </c>
       <c r="D1192" t="inlineStr">
         <is>
-          <t>etc</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E1192" t="inlineStr">
@@ -32615,22 +32615,22 @@
     <row r="1193">
       <c r="A1193" t="inlineStr">
         <is>
-          <t>tayfun</t>
+          <t>coda1202</t>
         </is>
       </c>
       <c r="B1193" t="inlineStr">
         <is>
-          <t>01083105230</t>
+          <t>01037655629</t>
         </is>
       </c>
       <c r="C1193" t="inlineStr">
         <is>
-          <t>286336</t>
+          <t>117064</t>
         </is>
       </c>
       <c r="D1193" t="inlineStr">
         <is>
-          <t>etc</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E1193" t="inlineStr">
@@ -32642,22 +32642,22 @@
     <row r="1194">
       <c r="A1194" t="inlineStr">
         <is>
-          <t>sh5204</t>
+          <t>tayfun</t>
         </is>
       </c>
       <c r="B1194" t="inlineStr">
         <is>
-          <t>01054433018</t>
+          <t>01083105230</t>
         </is>
       </c>
       <c r="C1194" t="inlineStr">
         <is>
-          <t>263137</t>
+          <t>286336</t>
         </is>
       </c>
       <c r="D1194" t="inlineStr">
         <is>
-          <t>etc</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E1194" t="inlineStr">
@@ -32669,22 +32669,22 @@
     <row r="1195">
       <c r="A1195" t="inlineStr">
         <is>
-          <t>kairos93</t>
+          <t>olive888888</t>
         </is>
       </c>
       <c r="B1195" t="inlineStr">
         <is>
-          <t>01051079223</t>
+          <t>01029817882</t>
         </is>
       </c>
       <c r="C1195" t="inlineStr">
         <is>
-          <t>160644</t>
+          <t>116464</t>
         </is>
       </c>
       <c r="D1195" t="inlineStr">
         <is>
-          <t>etc</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E1195" t="inlineStr">
@@ -32696,22 +32696,22 @@
     <row r="1196">
       <c r="A1196" t="inlineStr">
         <is>
-          <t>olive888888</t>
+          <t>sh5204</t>
         </is>
       </c>
       <c r="B1196" t="inlineStr">
         <is>
-          <t>01029817882</t>
+          <t>01054433018</t>
         </is>
       </c>
       <c r="C1196" t="inlineStr">
         <is>
-          <t>116464</t>
+          <t>263137</t>
         </is>
       </c>
       <c r="D1196" t="inlineStr">
         <is>
-          <t>etc</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E1196" t="inlineStr">
@@ -32723,22 +32723,22 @@
     <row r="1197">
       <c r="A1197" t="inlineStr">
         <is>
-          <t>happy201106</t>
+          <t>alcoholpower</t>
         </is>
       </c>
       <c r="B1197" t="inlineStr">
         <is>
-          <t>01090012622</t>
+          <t>01027629868</t>
         </is>
       </c>
       <c r="C1197" t="inlineStr">
         <is>
-          <t>136050</t>
+          <t>252954</t>
         </is>
       </c>
       <c r="D1197" t="inlineStr">
         <is>
-          <t>etc</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E1197" t="inlineStr">
@@ -32765,7 +32765,7 @@
       </c>
       <c r="D1198" t="inlineStr">
         <is>
-          <t>etc</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E1198" t="inlineStr">
@@ -32777,22 +32777,22 @@
     <row r="1199">
       <c r="A1199" t="inlineStr">
         <is>
-          <t>alcoholpower</t>
+          <t>happy201106</t>
         </is>
       </c>
       <c r="B1199" t="inlineStr">
         <is>
-          <t>01027629868</t>
+          <t>01090012622</t>
         </is>
       </c>
       <c r="C1199" t="inlineStr">
         <is>
-          <t>252954</t>
+          <t>136050</t>
         </is>
       </c>
       <c r="D1199" t="inlineStr">
         <is>
-          <t>etc</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E1199" t="inlineStr">

--- a/reports/member_funnel/downloads/member_funnel_7d_non_buyer.xlsx
+++ b/reports/member_funnel/downloads/member_funnel_7d_non_buyer.xlsx
@@ -17495,17 +17495,17 @@
     <row r="633">
       <c r="A633" t="inlineStr">
         <is>
-          <t>kk_3483300064</t>
+          <t>kk_4789688431</t>
         </is>
       </c>
       <c r="B633" t="inlineStr">
         <is>
-          <t>01092213404</t>
+          <t>01099981265</t>
         </is>
       </c>
       <c r="C633" t="inlineStr">
         <is>
-          <t>244619</t>
+          <t>302023</t>
         </is>
       </c>
       <c r="D633" t="inlineStr">
@@ -17515,24 +17515,24 @@
       </c>
       <c r="E633" t="inlineStr">
         <is>
-          <t>naver_brandsearch_mobile</t>
+          <t>sa</t>
         </is>
       </c>
     </row>
     <row r="634">
       <c r="A634" t="inlineStr">
         <is>
-          <t>kk_4789688431</t>
+          <t>kk_3483300064</t>
         </is>
       </c>
       <c r="B634" t="inlineStr">
         <is>
-          <t>01099981265</t>
+          <t>01092213404</t>
         </is>
       </c>
       <c r="C634" t="inlineStr">
         <is>
-          <t>302023</t>
+          <t>244619</t>
         </is>
       </c>
       <c r="D634" t="inlineStr">
@@ -17542,7 +17542,7 @@
       </c>
       <c r="E634" t="inlineStr">
         <is>
-          <t>sa</t>
+          <t>naver_brandsearch_mobile</t>
         </is>
       </c>
     </row>
@@ -17900,17 +17900,17 @@
     <row r="648">
       <c r="A648" t="inlineStr">
         <is>
-          <t>kk_3185218103</t>
+          <t>zizou95</t>
         </is>
       </c>
       <c r="B648" t="inlineStr">
         <is>
-          <t>01023796438</t>
+          <t>01049139545</t>
         </is>
       </c>
       <c r="C648" t="inlineStr">
         <is>
-          <t>229444</t>
+          <t>176662</t>
         </is>
       </c>
       <c r="D648" t="inlineStr">
@@ -17920,24 +17920,24 @@
       </c>
       <c r="E648" t="inlineStr">
         <is>
-          <t>KAKAO_alimtalk</t>
+          <t>LMS_ECOM_familycoupon</t>
         </is>
       </c>
     </row>
     <row r="649">
       <c r="A649" t="inlineStr">
         <is>
-          <t>zizou95</t>
+          <t>kk_3185218103</t>
         </is>
       </c>
       <c r="B649" t="inlineStr">
         <is>
-          <t>01049139545</t>
+          <t>01023796438</t>
         </is>
       </c>
       <c r="C649" t="inlineStr">
         <is>
-          <t>176662</t>
+          <t>229444</t>
         </is>
       </c>
       <c r="D649" t="inlineStr">
@@ -17947,7 +17947,7 @@
       </c>
       <c r="E649" t="inlineStr">
         <is>
-          <t>LMS_ECOM_familycoupon</t>
+          <t>KAKAO_alimtalk</t>
         </is>
       </c>
     </row>
@@ -19034,17 +19034,17 @@
     <row r="690">
       <c r="A690" t="inlineStr">
         <is>
-          <t>shine310</t>
+          <t>lamerkmk</t>
         </is>
       </c>
       <c r="B690" t="inlineStr">
         <is>
-          <t>01030650847</t>
+          <t>01030658494</t>
         </is>
       </c>
       <c r="C690" t="inlineStr">
         <is>
-          <t>171606</t>
+          <t>167002</t>
         </is>
       </c>
       <c r="D690" t="inlineStr">
@@ -19061,17 +19061,17 @@
     <row r="691">
       <c r="A691" t="inlineStr">
         <is>
-          <t>lamerkmk</t>
+          <t>shine310</t>
         </is>
       </c>
       <c r="B691" t="inlineStr">
         <is>
-          <t>01030658494</t>
+          <t>01030650847</t>
         </is>
       </c>
       <c r="C691" t="inlineStr">
         <is>
-          <t>167002</t>
+          <t>171606</t>
         </is>
       </c>
       <c r="D691" t="inlineStr">
@@ -19493,54 +19493,54 @@
     <row r="707">
       <c r="A707" t="inlineStr">
         <is>
-          <t>khkim6620</t>
+          <t>kk_4841965432</t>
         </is>
       </c>
       <c r="B707" t="inlineStr">
         <is>
-          <t>01076876567</t>
+          <t>01032510712</t>
         </is>
       </c>
       <c r="C707" t="inlineStr">
         <is>
-          <t>105445</t>
+          <t>304213</t>
         </is>
       </c>
       <c r="D707" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Organic Traffic</t>
         </is>
       </c>
       <c r="E707" t="inlineStr">
         <is>
-          <t>컬럼비아_DPA_240530</t>
+          <t>(referral)</t>
         </is>
       </c>
     </row>
     <row r="708">
       <c r="A708" t="inlineStr">
         <is>
-          <t>kk_4841965432</t>
+          <t>khkim6620</t>
         </is>
       </c>
       <c r="B708" t="inlineStr">
         <is>
-          <t>01032510712</t>
+          <t>01076876567</t>
         </is>
       </c>
       <c r="C708" t="inlineStr">
         <is>
-          <t>304213</t>
+          <t>105445</t>
         </is>
       </c>
       <c r="D708" t="inlineStr">
         <is>
-          <t>Organic Traffic</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E708" t="inlineStr">
         <is>
-          <t>(referral)</t>
+          <t>컬럼비아_DPA_240530</t>
         </is>
       </c>
     </row>
@@ -19574,17 +19574,17 @@
     <row r="710">
       <c r="A710" t="inlineStr">
         <is>
-          <t>mylove01</t>
+          <t>kk_4633959675</t>
         </is>
       </c>
       <c r="B710" t="inlineStr">
         <is>
-          <t>01036889669</t>
+          <t>01050399548</t>
         </is>
       </c>
       <c r="C710" t="inlineStr">
         <is>
-          <t>261917</t>
+          <t>291972</t>
         </is>
       </c>
       <c r="D710" t="inlineStr">
@@ -19594,7 +19594,7 @@
       </c>
       <c r="E710" t="inlineStr">
         <is>
-          <t>LMS_ECOM_200416_family</t>
+          <t>lms_ecom_200416_family</t>
         </is>
       </c>
     </row>
@@ -19628,17 +19628,17 @@
     <row r="712">
       <c r="A712" t="inlineStr">
         <is>
-          <t>kk_4633959675</t>
+          <t>mylove01</t>
         </is>
       </c>
       <c r="B712" t="inlineStr">
         <is>
-          <t>01050399548</t>
+          <t>01036889669</t>
         </is>
       </c>
       <c r="C712" t="inlineStr">
         <is>
-          <t>291972</t>
+          <t>261917</t>
         </is>
       </c>
       <c r="D712" t="inlineStr">
@@ -19648,7 +19648,7 @@
       </c>
       <c r="E712" t="inlineStr">
         <is>
-          <t>lms_ecom_200416_family</t>
+          <t>LMS_ECOM_200416_family</t>
         </is>
       </c>
     </row>
@@ -20141,17 +20141,17 @@
     <row r="731">
       <c r="A731" t="inlineStr">
         <is>
-          <t>kk_4840846776</t>
+          <t>kk_4840658838</t>
         </is>
       </c>
       <c r="B731" t="inlineStr">
         <is>
-          <t>01055961435</t>
+          <t>01039292600</t>
         </is>
       </c>
       <c r="C731" t="inlineStr">
         <is>
-          <t>304170</t>
+          <t>304158</t>
         </is>
       </c>
       <c r="D731" t="inlineStr">
@@ -20161,24 +20161,24 @@
       </c>
       <c r="E731" t="inlineStr">
         <is>
-          <t>[PF]전환_회원가입(유사)</t>
+          <t>EFW</t>
         </is>
       </c>
     </row>
     <row r="732">
       <c r="A732" t="inlineStr">
         <is>
-          <t>kk_4840658838</t>
+          <t>kk_4840846776</t>
         </is>
       </c>
       <c r="B732" t="inlineStr">
         <is>
-          <t>01039292600</t>
+          <t>01055961435</t>
         </is>
       </c>
       <c r="C732" t="inlineStr">
         <is>
-          <t>304158</t>
+          <t>304170</t>
         </is>
       </c>
       <c r="D732" t="inlineStr">
@@ -20188,7 +20188,7 @@
       </c>
       <c r="E732" t="inlineStr">
         <is>
-          <t>EFW</t>
+          <t>[PF]전환_회원가입(유사)</t>
         </is>
       </c>
     </row>
@@ -20276,17 +20276,17 @@
     <row r="736">
       <c r="A736" t="inlineStr">
         <is>
-          <t>k032010</t>
+          <t>martyj</t>
         </is>
       </c>
       <c r="B736" t="inlineStr">
         <is>
-          <t>01090792133</t>
+          <t>01073535824</t>
         </is>
       </c>
       <c r="C736" t="inlineStr">
         <is>
-          <t>204481</t>
+          <t>194752</t>
         </is>
       </c>
       <c r="D736" t="inlineStr">
@@ -20303,17 +20303,17 @@
     <row r="737">
       <c r="A737" t="inlineStr">
         <is>
-          <t>kk_3410691755</t>
+          <t>k032010</t>
         </is>
       </c>
       <c r="B737" t="inlineStr">
         <is>
-          <t>01084564028</t>
+          <t>01090792133</t>
         </is>
       </c>
       <c r="C737" t="inlineStr">
         <is>
-          <t>241474</t>
+          <t>204481</t>
         </is>
       </c>
       <c r="D737" t="inlineStr">
@@ -20330,17 +20330,17 @@
     <row r="738">
       <c r="A738" t="inlineStr">
         <is>
-          <t>martyj</t>
+          <t>kk_3410691755</t>
         </is>
       </c>
       <c r="B738" t="inlineStr">
         <is>
-          <t>01073535824</t>
+          <t>01084564028</t>
         </is>
       </c>
       <c r="C738" t="inlineStr">
         <is>
-          <t>194752</t>
+          <t>241474</t>
         </is>
       </c>
       <c r="D738" t="inlineStr">
@@ -20789,54 +20789,54 @@
     <row r="755">
       <c r="A755" t="inlineStr">
         <is>
-          <t>kk_3633964155</t>
+          <t>kk_3913679442</t>
         </is>
       </c>
       <c r="B755" t="inlineStr">
         <is>
-          <t>01097743709</t>
+          <t>01085569215</t>
         </is>
       </c>
       <c r="C755" t="inlineStr">
         <is>
-          <t>248300</t>
+          <t>268330</t>
         </is>
       </c>
       <c r="D755" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="E755" t="inlineStr">
         <is>
-          <t>KAKAO_CH_MENU_0226_EFW</t>
+          <t>미분류</t>
         </is>
       </c>
     </row>
     <row r="756">
       <c r="A756" t="inlineStr">
         <is>
-          <t>kk_3913679442</t>
+          <t>kk_3633964155</t>
         </is>
       </c>
       <c r="B756" t="inlineStr">
         <is>
-          <t>01085569215</t>
+          <t>01097743709</t>
         </is>
       </c>
       <c r="C756" t="inlineStr">
         <is>
-          <t>268330</t>
+          <t>248300</t>
         </is>
       </c>
       <c r="D756" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E756" t="inlineStr">
         <is>
-          <t>미분류</t>
+          <t>KAKAO_CH_MENU_0226_EFW</t>
         </is>
       </c>
     </row>
@@ -21923,17 +21923,17 @@
     <row r="797">
       <c r="A797" t="inlineStr">
         <is>
-          <t>kk_2915134680</t>
+          <t>kk_4288273717</t>
         </is>
       </c>
       <c r="B797" t="inlineStr">
         <is>
-          <t>01085224711</t>
+          <t>01020746624</t>
         </is>
       </c>
       <c r="C797" t="inlineStr">
         <is>
-          <t>215670</t>
+          <t>275762</t>
         </is>
       </c>
       <c r="D797" t="inlineStr">
@@ -21943,24 +21943,24 @@
       </c>
       <c r="E797" t="inlineStr">
         <is>
-          <t>KAKAO_CH_MESSAGE_0409_HIKE365SUMMER</t>
+          <t>LMS_ECOM_0410exclusive2</t>
         </is>
       </c>
     </row>
     <row r="798">
       <c r="A798" t="inlineStr">
         <is>
-          <t>kk_4288273717</t>
+          <t>kk_2915134680</t>
         </is>
       </c>
       <c r="B798" t="inlineStr">
         <is>
-          <t>01020746624</t>
+          <t>01085224711</t>
         </is>
       </c>
       <c r="C798" t="inlineStr">
         <is>
-          <t>275762</t>
+          <t>215670</t>
         </is>
       </c>
       <c r="D798" t="inlineStr">
@@ -21970,7 +21970,7 @@
       </c>
       <c r="E798" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0410exclusive2</t>
+          <t>KAKAO_CH_MESSAGE_0409_HIKE365SUMMER</t>
         </is>
       </c>
     </row>
@@ -22085,17 +22085,17 @@
     <row r="803">
       <c r="A803" t="inlineStr">
         <is>
-          <t>hun7662</t>
+          <t>kk_3101119679</t>
         </is>
       </c>
       <c r="B803" t="inlineStr">
         <is>
-          <t>01042311474</t>
+          <t>01093993852</t>
         </is>
       </c>
       <c r="C803" t="inlineStr">
         <is>
-          <t>172790</t>
+          <t>221630</t>
         </is>
       </c>
       <c r="D803" t="inlineStr">
@@ -22112,17 +22112,17 @@
     <row r="804">
       <c r="A804" t="inlineStr">
         <is>
-          <t>kk_3101119679</t>
+          <t>hun7662</t>
         </is>
       </c>
       <c r="B804" t="inlineStr">
         <is>
-          <t>01093993852</t>
+          <t>01042311474</t>
         </is>
       </c>
       <c r="C804" t="inlineStr">
         <is>
-          <t>221630</t>
+          <t>172790</t>
         </is>
       </c>
       <c r="D804" t="inlineStr">
@@ -22490,98 +22490,98 @@
     <row r="818">
       <c r="A818" t="inlineStr">
         <is>
-          <t>kk_4839765445</t>
+          <t>sun1381</t>
         </is>
       </c>
       <c r="B818" t="inlineStr">
         <is>
-          <t>01076118972</t>
+          <t>01037709416</t>
         </is>
       </c>
       <c r="C818" t="inlineStr">
         <is>
-          <t>304111</t>
+          <t>278160</t>
         </is>
       </c>
       <c r="D818" t="inlineStr">
         <is>
-          <t>Organic Traffic</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E818" t="inlineStr">
         <is>
-          <t>(referral)</t>
+          <t>LMS_ECOM_0410exclusive2</t>
         </is>
       </c>
     </row>
     <row r="819">
       <c r="A819" t="inlineStr">
         <is>
-          <t>sun1381</t>
+          <t>kk_4839145768</t>
         </is>
       </c>
       <c r="B819" t="inlineStr">
         <is>
-          <t>01037709416</t>
+          <t>01097367898</t>
         </is>
       </c>
       <c r="C819" t="inlineStr">
         <is>
-          <t>278160</t>
+          <t>304085</t>
         </is>
       </c>
       <c r="D819" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E819" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0410exclusive2</t>
+          <t>naver_brandsearch_pc</t>
         </is>
       </c>
     </row>
     <row r="820">
       <c r="A820" t="inlineStr">
         <is>
-          <t>kk_4839145768</t>
+          <t>kk_4839765445</t>
         </is>
       </c>
       <c r="B820" t="inlineStr">
         <is>
-          <t>01097367898</t>
+          <t>01076118972</t>
         </is>
       </c>
       <c r="C820" t="inlineStr">
         <is>
-          <t>304085</t>
+          <t>304111</t>
         </is>
       </c>
       <c r="D820" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Organic Traffic</t>
         </is>
       </c>
       <c r="E820" t="inlineStr">
         <is>
-          <t>naver_brandsearch_pc</t>
+          <t>(referral)</t>
         </is>
       </c>
     </row>
     <row r="821">
       <c r="A821" t="inlineStr">
         <is>
-          <t>okj2377</t>
+          <t>kk_3795665685</t>
         </is>
       </c>
       <c r="B821" t="inlineStr">
         <is>
-          <t>01033661268</t>
+          <t>01025106852</t>
         </is>
       </c>
       <c r="C821" t="inlineStr">
         <is>
-          <t>139452</t>
+          <t>257696</t>
         </is>
       </c>
       <c r="D821" t="inlineStr">
@@ -22591,24 +22591,24 @@
       </c>
       <c r="E821" t="inlineStr">
         <is>
-          <t>lms_ecom_200416_family</t>
+          <t>LMS_ECOM_200416_family</t>
         </is>
       </c>
     </row>
     <row r="822">
       <c r="A822" t="inlineStr">
         <is>
-          <t>kk_3795665685</t>
+          <t>okj2377</t>
         </is>
       </c>
       <c r="B822" t="inlineStr">
         <is>
-          <t>01025106852</t>
+          <t>01033661268</t>
         </is>
       </c>
       <c r="C822" t="inlineStr">
         <is>
-          <t>257696</t>
+          <t>139452</t>
         </is>
       </c>
       <c r="D822" t="inlineStr">
@@ -22618,7 +22618,7 @@
       </c>
       <c r="E822" t="inlineStr">
         <is>
-          <t>LMS_ECOM_200416_family</t>
+          <t>lms_ecom_200416_family</t>
         </is>
       </c>
     </row>
@@ -22976,54 +22976,54 @@
     <row r="836">
       <c r="A836" t="inlineStr">
         <is>
-          <t>kk_3631606950</t>
+          <t>kk_2999650964</t>
         </is>
       </c>
       <c r="B836" t="inlineStr">
         <is>
-          <t>01063256163</t>
+          <t>01073667501</t>
         </is>
       </c>
       <c r="C836" t="inlineStr">
         <is>
-          <t>248164</t>
+          <t>218535</t>
         </is>
       </c>
       <c r="D836" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E836" t="inlineStr">
         <is>
-          <t>미분류</t>
+          <t>bizboard</t>
         </is>
       </c>
     </row>
     <row r="837">
       <c r="A837" t="inlineStr">
         <is>
-          <t>kk_2999650964</t>
+          <t>kk_3631606950</t>
         </is>
       </c>
       <c r="B837" t="inlineStr">
         <is>
-          <t>01073667501</t>
+          <t>01063256163</t>
         </is>
       </c>
       <c r="C837" t="inlineStr">
         <is>
-          <t>218535</t>
+          <t>248164</t>
         </is>
       </c>
       <c r="D837" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="E837" t="inlineStr">
         <is>
-          <t>bizboard</t>
+          <t>미분류</t>
         </is>
       </c>
     </row>
@@ -23462,54 +23462,54 @@
     <row r="854">
       <c r="A854" t="inlineStr">
         <is>
-          <t>jh91jung</t>
+          <t>baekdurudu</t>
         </is>
       </c>
       <c r="B854" t="inlineStr">
         <is>
-          <t>01092560926</t>
+          <t>01082556353</t>
         </is>
       </c>
       <c r="C854" t="inlineStr">
         <is>
-          <t>304337</t>
+          <t>60771</t>
         </is>
       </c>
       <c r="D854" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E854" t="inlineStr">
         <is>
-          <t>naversa_pc</t>
+          <t>LMS_ECOM_0214_newyear</t>
         </is>
       </c>
     </row>
     <row r="855">
       <c r="A855" t="inlineStr">
         <is>
-          <t>baekdurudu</t>
+          <t>jh91jung</t>
         </is>
       </c>
       <c r="B855" t="inlineStr">
         <is>
-          <t>01082556353</t>
+          <t>01092560926</t>
         </is>
       </c>
       <c r="C855" t="inlineStr">
         <is>
-          <t>60771</t>
+          <t>304337</t>
         </is>
       </c>
       <c r="D855" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E855" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0214_newyear</t>
+          <t>naversa_pc</t>
         </is>
       </c>
     </row>
@@ -23570,54 +23570,54 @@
     <row r="858">
       <c r="A858" t="inlineStr">
         <is>
-          <t>kk_4839680663</t>
+          <t>kk_3392066640</t>
         </is>
       </c>
       <c r="B858" t="inlineStr">
         <is>
-          <t>01046429530</t>
+          <t>01065021283</t>
         </is>
       </c>
       <c r="C858" t="inlineStr">
         <is>
-          <t>304109</t>
+          <t>240983</t>
         </is>
       </c>
       <c r="D858" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E858" t="inlineStr">
         <is>
-          <t>6968489536332</t>
+          <t>LMS_ECOM_0410exclusive2</t>
         </is>
       </c>
     </row>
     <row r="859">
       <c r="A859" t="inlineStr">
         <is>
-          <t>kk_3392066640</t>
+          <t>kk_4839680663</t>
         </is>
       </c>
       <c r="B859" t="inlineStr">
         <is>
-          <t>01065021283</t>
+          <t>01046429530</t>
         </is>
       </c>
       <c r="C859" t="inlineStr">
         <is>
-          <t>240983</t>
+          <t>304109</t>
         </is>
       </c>
       <c r="D859" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E859" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0410exclusive2</t>
+          <t>6968489536332</t>
         </is>
       </c>
     </row>
@@ -23867,54 +23867,54 @@
     <row r="869">
       <c r="A869" t="inlineStr">
         <is>
-          <t>mtbok</t>
+          <t>kk_4839433808</t>
         </is>
       </c>
       <c r="B869" t="inlineStr">
         <is>
-          <t>01051284339</t>
+          <t>01025333388</t>
         </is>
       </c>
       <c r="C869" t="inlineStr">
         <is>
-          <t>26917</t>
+          <t>304100</t>
         </is>
       </c>
       <c r="D869" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E869" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0410exclusive2</t>
+          <t>naver_brandsearch_mobile</t>
         </is>
       </c>
     </row>
     <row r="870">
       <c r="A870" t="inlineStr">
         <is>
-          <t>kk_4839433808</t>
+          <t>mtbok</t>
         </is>
       </c>
       <c r="B870" t="inlineStr">
         <is>
-          <t>01025333388</t>
+          <t>01051284339</t>
         </is>
       </c>
       <c r="C870" t="inlineStr">
         <is>
-          <t>304100</t>
+          <t>26917</t>
         </is>
       </c>
       <c r="D870" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E870" t="inlineStr">
         <is>
-          <t>naver_brandsearch_mobile</t>
+          <t>LMS_ECOM_0410exclusive2</t>
         </is>
       </c>
     </row>
@@ -23948,17 +23948,17 @@
     <row r="872">
       <c r="A872" t="inlineStr">
         <is>
-          <t>pcx916</t>
+          <t>hyschant</t>
         </is>
       </c>
       <c r="B872" t="inlineStr">
         <is>
-          <t>01026644222</t>
+          <t>01065306675</t>
         </is>
       </c>
       <c r="C872" t="inlineStr">
         <is>
-          <t>139541</t>
+          <t>108579</t>
         </is>
       </c>
       <c r="D872" t="inlineStr">
@@ -23968,24 +23968,24 @@
       </c>
       <c r="E872" t="inlineStr">
         <is>
-          <t>KAKAO_CH_event</t>
+          <t>LMS_ECOM_0410exclusive2</t>
         </is>
       </c>
     </row>
     <row r="873">
       <c r="A873" t="inlineStr">
         <is>
-          <t>hyschant</t>
+          <t>pcx916</t>
         </is>
       </c>
       <c r="B873" t="inlineStr">
         <is>
-          <t>01065306675</t>
+          <t>01026644222</t>
         </is>
       </c>
       <c r="C873" t="inlineStr">
         <is>
-          <t>108579</t>
+          <t>139541</t>
         </is>
       </c>
       <c r="D873" t="inlineStr">
@@ -23995,7 +23995,7 @@
       </c>
       <c r="E873" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0410exclusive2</t>
+          <t>KAKAO_CH_event</t>
         </is>
       </c>
     </row>
@@ -24083,27 +24083,27 @@
     <row r="877">
       <c r="A877" t="inlineStr">
         <is>
-          <t>kk_4839026541</t>
+          <t>kk_2757380967</t>
         </is>
       </c>
       <c r="B877" t="inlineStr">
         <is>
-          <t>01089431507</t>
+          <t>01034635649</t>
         </is>
       </c>
       <c r="C877" t="inlineStr">
         <is>
-          <t>304082</t>
+          <t>208245</t>
         </is>
       </c>
       <c r="D877" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E877" t="inlineStr">
         <is>
-          <t>[PF]전환_상시(2565MF,비구매자)</t>
+          <t>LMS_ECOM_0410exclusive2</t>
         </is>
       </c>
     </row>
@@ -24137,27 +24137,27 @@
     <row r="879">
       <c r="A879" t="inlineStr">
         <is>
-          <t>kk_2757380967</t>
+          <t>kk_4839026541</t>
         </is>
       </c>
       <c r="B879" t="inlineStr">
         <is>
-          <t>01034635649</t>
+          <t>01089431507</t>
         </is>
       </c>
       <c r="C879" t="inlineStr">
         <is>
-          <t>208245</t>
+          <t>304082</t>
         </is>
       </c>
       <c r="D879" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E879" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0410exclusive2</t>
+          <t>[PF]전환_상시(2565MF,비구매자)</t>
         </is>
       </c>
     </row>
@@ -24245,27 +24245,27 @@
     <row r="883">
       <c r="A883" t="inlineStr">
         <is>
-          <t>kk_4849696162</t>
+          <t>sarang21</t>
         </is>
       </c>
       <c r="B883" t="inlineStr">
         <is>
-          <t>01063383734</t>
+          <t>01054975535</t>
         </is>
       </c>
       <c r="C883" t="inlineStr">
         <is>
-          <t>304570</t>
+          <t>268553</t>
         </is>
       </c>
       <c r="D883" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E883" t="inlineStr">
         <is>
-          <t>컬럼비아_DPA_240530</t>
+          <t>LMS_ECOM_200416_family</t>
         </is>
       </c>
     </row>
@@ -24299,17 +24299,17 @@
     <row r="885">
       <c r="A885" t="inlineStr">
         <is>
-          <t>kk_3334413020</t>
+          <t>kk_3251799831</t>
         </is>
       </c>
       <c r="B885" t="inlineStr">
         <is>
-          <t>01080806386</t>
+          <t>01040006581</t>
         </is>
       </c>
       <c r="C885" t="inlineStr">
         <is>
-          <t>238829</t>
+          <t>235398</t>
         </is>
       </c>
       <c r="D885" t="inlineStr">
@@ -24326,17 +24326,17 @@
     <row r="886">
       <c r="A886" t="inlineStr">
         <is>
-          <t>sarang21</t>
+          <t>kk_3334413020</t>
         </is>
       </c>
       <c r="B886" t="inlineStr">
         <is>
-          <t>01054975535</t>
+          <t>01080806386</t>
         </is>
       </c>
       <c r="C886" t="inlineStr">
         <is>
-          <t>268553</t>
+          <t>238829</t>
         </is>
       </c>
       <c r="D886" t="inlineStr">
@@ -24353,17 +24353,17 @@
     <row r="887">
       <c r="A887" t="inlineStr">
         <is>
-          <t>kk_3251799831</t>
+          <t>kk_3810304670</t>
         </is>
       </c>
       <c r="B887" t="inlineStr">
         <is>
-          <t>01040006581</t>
+          <t>01041348052</t>
         </is>
       </c>
       <c r="C887" t="inlineStr">
         <is>
-          <t>235398</t>
+          <t>261190</t>
         </is>
       </c>
       <c r="D887" t="inlineStr">
@@ -24380,44 +24380,44 @@
     <row r="888">
       <c r="A888" t="inlineStr">
         <is>
-          <t>jeanne</t>
+          <t>kk_4849696162</t>
         </is>
       </c>
       <c r="B888" t="inlineStr">
         <is>
-          <t>01047490850</t>
+          <t>01063383734</t>
         </is>
       </c>
       <c r="C888" t="inlineStr">
         <is>
-          <t>195346</t>
+          <t>304570</t>
         </is>
       </c>
       <c r="D888" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E888" t="inlineStr">
         <is>
-          <t>LMS_ECOM_200416_family</t>
+          <t>컬럼비아_DPA_240530</t>
         </is>
       </c>
     </row>
     <row r="889">
       <c r="A889" t="inlineStr">
         <is>
-          <t>kk_3810304670</t>
+          <t>jeanne</t>
         </is>
       </c>
       <c r="B889" t="inlineStr">
         <is>
-          <t>01041348052</t>
+          <t>01047490850</t>
         </is>
       </c>
       <c r="C889" t="inlineStr">
         <is>
-          <t>261190</t>
+          <t>195346</t>
         </is>
       </c>
       <c r="D889" t="inlineStr">
@@ -24461,17 +24461,17 @@
     <row r="891">
       <c r="A891" t="inlineStr">
         <is>
-          <t>kk_3210379887</t>
+          <t>kk_4469973568</t>
         </is>
       </c>
       <c r="B891" t="inlineStr">
         <is>
-          <t>01024748405</t>
+          <t>01087158602</t>
         </is>
       </c>
       <c r="C891" t="inlineStr">
         <is>
-          <t>231651</t>
+          <t>283741</t>
         </is>
       </c>
       <c r="D891" t="inlineStr">
@@ -24481,24 +24481,24 @@
       </c>
       <c r="E891" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0410exclusive2</t>
+          <t>KAKAO_CH_MENU_0211_NEW_MEN</t>
         </is>
       </c>
     </row>
     <row r="892">
       <c r="A892" t="inlineStr">
         <is>
-          <t>kk_4469973568</t>
+          <t>kk_3210379887</t>
         </is>
       </c>
       <c r="B892" t="inlineStr">
         <is>
-          <t>01087158602</t>
+          <t>01024748405</t>
         </is>
       </c>
       <c r="C892" t="inlineStr">
         <is>
-          <t>283741</t>
+          <t>231651</t>
         </is>
       </c>
       <c r="D892" t="inlineStr">
@@ -24508,7 +24508,7 @@
       </c>
       <c r="E892" t="inlineStr">
         <is>
-          <t>KAKAO_CH_MENU_0211_NEW_MEN</t>
+          <t>LMS_ECOM_0410exclusive2</t>
         </is>
       </c>
     </row>
@@ -24569,17 +24569,17 @@
     <row r="895">
       <c r="A895" t="inlineStr">
         <is>
-          <t>kk_3967419156</t>
+          <t>kk_4600405600</t>
         </is>
       </c>
       <c r="B895" t="inlineStr">
         <is>
-          <t>01030207947</t>
+          <t>01053449477</t>
         </is>
       </c>
       <c r="C895" t="inlineStr">
         <is>
-          <t>270708</t>
+          <t>289364</t>
         </is>
       </c>
       <c r="D895" t="inlineStr">
@@ -24623,17 +24623,17 @@
     <row r="897">
       <c r="A897" t="inlineStr">
         <is>
-          <t>kk_4600405600</t>
+          <t>kk_3967419156</t>
         </is>
       </c>
       <c r="B897" t="inlineStr">
         <is>
-          <t>01053449477</t>
+          <t>01030207947</t>
         </is>
       </c>
       <c r="C897" t="inlineStr">
         <is>
-          <t>289364</t>
+          <t>270708</t>
         </is>
       </c>
       <c r="D897" t="inlineStr">
@@ -24677,17 +24677,17 @@
     <row r="899">
       <c r="A899" t="inlineStr">
         <is>
-          <t>a3789</t>
+          <t>lovemac</t>
         </is>
       </c>
       <c r="B899" t="inlineStr">
         <is>
-          <t>01053102148</t>
+          <t>01058421351</t>
         </is>
       </c>
       <c r="C899" t="inlineStr">
         <is>
-          <t>244924</t>
+          <t>69911</t>
         </is>
       </c>
       <c r="D899" t="inlineStr">
@@ -24704,17 +24704,17 @@
     <row r="900">
       <c r="A900" t="inlineStr">
         <is>
-          <t>lovemac</t>
+          <t>a3789</t>
         </is>
       </c>
       <c r="B900" t="inlineStr">
         <is>
-          <t>01058421351</t>
+          <t>01053102148</t>
         </is>
       </c>
       <c r="C900" t="inlineStr">
         <is>
-          <t>69911</t>
+          <t>244924</t>
         </is>
       </c>
       <c r="D900" t="inlineStr">
@@ -24758,54 +24758,54 @@
     <row r="902">
       <c r="A902" t="inlineStr">
         <is>
-          <t>seizeh</t>
+          <t>l00years</t>
         </is>
       </c>
       <c r="B902" t="inlineStr">
         <is>
-          <t>01090302539</t>
+          <t>01053925529</t>
         </is>
       </c>
       <c r="C902" t="inlineStr">
         <is>
-          <t>68751</t>
+          <t>229454</t>
         </is>
       </c>
       <c r="D902" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E902" t="inlineStr">
         <is>
-          <t>sa</t>
+          <t>LMS_ECOM_0410exclusive2</t>
         </is>
       </c>
     </row>
     <row r="903">
       <c r="A903" t="inlineStr">
         <is>
-          <t>l00years</t>
+          <t>seizeh</t>
         </is>
       </c>
       <c r="B903" t="inlineStr">
         <is>
-          <t>01053925529</t>
+          <t>01090302539</t>
         </is>
       </c>
       <c r="C903" t="inlineStr">
         <is>
-          <t>229454</t>
+          <t>68751</t>
         </is>
       </c>
       <c r="D903" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E903" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0410exclusive2</t>
+          <t>sa</t>
         </is>
       </c>
     </row>
@@ -25136,17 +25136,17 @@
     <row r="916">
       <c r="A916" t="inlineStr">
         <is>
-          <t>kk_4848573198</t>
+          <t>kk_4848049317</t>
         </is>
       </c>
       <c r="B916" t="inlineStr">
         <is>
-          <t>01081135059</t>
+          <t>01064006801</t>
         </is>
       </c>
       <c r="C916" t="inlineStr">
         <is>
-          <t>304535</t>
+          <t>304514</t>
         </is>
       </c>
       <c r="D916" t="inlineStr">
@@ -25156,24 +25156,24 @@
       </c>
       <c r="E916" t="inlineStr">
         <is>
-          <t>(organic)</t>
+          <t>[PF]전환_회원가입(유사)</t>
         </is>
       </c>
     </row>
     <row r="917">
       <c r="A917" t="inlineStr">
         <is>
-          <t>kk_4848049317</t>
+          <t>kk_4848573198</t>
         </is>
       </c>
       <c r="B917" t="inlineStr">
         <is>
-          <t>01064006801</t>
+          <t>01081135059</t>
         </is>
       </c>
       <c r="C917" t="inlineStr">
         <is>
-          <t>304514</t>
+          <t>304535</t>
         </is>
       </c>
       <c r="D917" t="inlineStr">
@@ -25183,7 +25183,7 @@
       </c>
       <c r="E917" t="inlineStr">
         <is>
-          <t>[PF]전환_회원가입(유사)</t>
+          <t>(organic)</t>
         </is>
       </c>
     </row>
@@ -25271,17 +25271,17 @@
     <row r="921">
       <c r="A921" t="inlineStr">
         <is>
-          <t>kk_3800712629</t>
+          <t>kk_3180854377</t>
         </is>
       </c>
       <c r="B921" t="inlineStr">
         <is>
-          <t>01037690698</t>
+          <t>01031216377</t>
         </is>
       </c>
       <c r="C921" t="inlineStr">
         <is>
-          <t>258873</t>
+          <t>226467</t>
         </is>
       </c>
       <c r="D921" t="inlineStr">
@@ -25325,17 +25325,17 @@
     <row r="923">
       <c r="A923" t="inlineStr">
         <is>
-          <t>kk_3180854377</t>
+          <t>kk_3800712629</t>
         </is>
       </c>
       <c r="B923" t="inlineStr">
         <is>
-          <t>01031216377</t>
+          <t>01037690698</t>
         </is>
       </c>
       <c r="C923" t="inlineStr">
         <is>
-          <t>226467</t>
+          <t>258873</t>
         </is>
       </c>
       <c r="D923" t="inlineStr">
@@ -26270,54 +26270,54 @@
     <row r="958">
       <c r="A958" t="inlineStr">
         <is>
-          <t>kk_3919493388</t>
+          <t>kk_3955208505</t>
         </is>
       </c>
       <c r="B958" t="inlineStr">
         <is>
-          <t>01084315028</t>
+          <t>01084144311</t>
         </is>
       </c>
       <c r="C958" t="inlineStr">
         <is>
-          <t>268572</t>
+          <t>270134</t>
         </is>
       </c>
       <c r="D958" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E958" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>KAKAO_CH_MENU_0212_TITANIUM</t>
         </is>
       </c>
     </row>
     <row r="959">
       <c r="A959" t="inlineStr">
         <is>
-          <t>kk_3955208505</t>
+          <t>kk_3919493388</t>
         </is>
       </c>
       <c r="B959" t="inlineStr">
         <is>
-          <t>01084144311</t>
+          <t>01084315028</t>
         </is>
       </c>
       <c r="C959" t="inlineStr">
         <is>
-          <t>270134</t>
+          <t>268572</t>
         </is>
       </c>
       <c r="D959" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E959" t="inlineStr">
         <is>
-          <t>KAKAO_CH_MENU_0212_TITANIUM</t>
+          <t>Paid Ad</t>
         </is>
       </c>
     </row>
@@ -26459,54 +26459,54 @@
     <row r="965">
       <c r="A965" t="inlineStr">
         <is>
-          <t>jin1242</t>
+          <t>nurai</t>
         </is>
       </c>
       <c r="B965" t="inlineStr">
         <is>
-          <t>01038541242</t>
+          <t>01077918645</t>
         </is>
       </c>
       <c r="C965" t="inlineStr">
         <is>
-          <t>133468</t>
+          <t>304477</t>
         </is>
       </c>
       <c r="D965" t="inlineStr">
         <is>
-          <t>Organic Traffic</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E965" t="inlineStr">
         <is>
-          <t>Organic Traffic</t>
+          <t>sa</t>
         </is>
       </c>
     </row>
     <row r="966">
       <c r="A966" t="inlineStr">
         <is>
-          <t>nurai</t>
+          <t>jin1242</t>
         </is>
       </c>
       <c r="B966" t="inlineStr">
         <is>
-          <t>01077918645</t>
+          <t>01038541242</t>
         </is>
       </c>
       <c r="C966" t="inlineStr">
         <is>
-          <t>304477</t>
+          <t>133468</t>
         </is>
       </c>
       <c r="D966" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Organic Traffic</t>
         </is>
       </c>
       <c r="E966" t="inlineStr">
         <is>
-          <t>sa</t>
+          <t>Organic Traffic</t>
         </is>
       </c>
     </row>
@@ -26567,71 +26567,71 @@
     <row r="969">
       <c r="A969" t="inlineStr">
         <is>
-          <t>kk_4840108009</t>
+          <t>xey5000</t>
         </is>
       </c>
       <c r="B969" t="inlineStr">
         <is>
-          <t>01053461423</t>
+          <t>01087768710</t>
         </is>
       </c>
       <c r="C969" t="inlineStr">
         <is>
-          <t>304129</t>
+          <t>143826</t>
         </is>
       </c>
       <c r="D969" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E969" t="inlineStr">
         <is>
-          <t>6968489536332</t>
+          <t>KAKAO_CH_MESSAGE_0409_PANTS</t>
         </is>
       </c>
     </row>
     <row r="970">
       <c r="A970" t="inlineStr">
         <is>
-          <t>xey5000</t>
+          <t>kk_4840108009</t>
         </is>
       </c>
       <c r="B970" t="inlineStr">
         <is>
-          <t>01087768710</t>
+          <t>01053461423</t>
         </is>
       </c>
       <c r="C970" t="inlineStr">
         <is>
-          <t>143826</t>
+          <t>304129</t>
         </is>
       </c>
       <c r="D970" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E970" t="inlineStr">
         <is>
-          <t>KAKAO_CH_MESSAGE_0409_PANTS</t>
+          <t>6968489536332</t>
         </is>
       </c>
     </row>
     <row r="971">
       <c r="A971" t="inlineStr">
         <is>
-          <t>kk_3352367032</t>
+          <t>kk_3179815419</t>
         </is>
       </c>
       <c r="B971" t="inlineStr">
         <is>
-          <t>01037872990</t>
+          <t>01046896857</t>
         </is>
       </c>
       <c r="C971" t="inlineStr">
         <is>
-          <t>239508</t>
+          <t>225498</t>
         </is>
       </c>
       <c r="D971" t="inlineStr">
@@ -26641,24 +26641,24 @@
       </c>
       <c r="E971" t="inlineStr">
         <is>
-          <t>LMS_ECOM_familycoupon</t>
+          <t>KAKAO_CH_event</t>
         </is>
       </c>
     </row>
     <row r="972">
       <c r="A972" t="inlineStr">
         <is>
-          <t>kk_3179815419</t>
+          <t>kk_3352367032</t>
         </is>
       </c>
       <c r="B972" t="inlineStr">
         <is>
-          <t>01046896857</t>
+          <t>01037872990</t>
         </is>
       </c>
       <c r="C972" t="inlineStr">
         <is>
-          <t>225498</t>
+          <t>239508</t>
         </is>
       </c>
       <c r="D972" t="inlineStr">
@@ -26668,7 +26668,7 @@
       </c>
       <c r="E972" t="inlineStr">
         <is>
-          <t>KAKAO_CH_event</t>
+          <t>LMS_ECOM_familycoupon</t>
         </is>
       </c>
     </row>
@@ -26864,17 +26864,17 @@
     <row r="980">
       <c r="A980" t="inlineStr">
         <is>
-          <t>holstein</t>
+          <t>kk_3595551743</t>
         </is>
       </c>
       <c r="B980" t="inlineStr">
         <is>
-          <t>01050502500</t>
+          <t>01025839326</t>
         </is>
       </c>
       <c r="C980" t="inlineStr">
         <is>
-          <t>14062</t>
+          <t>246836</t>
         </is>
       </c>
       <c r="D980" t="inlineStr">
@@ -26884,24 +26884,24 @@
       </c>
       <c r="E980" t="inlineStr">
         <is>
-          <t>EDM_TOP</t>
+          <t>LMS_ECOM_0410exclusive2</t>
         </is>
       </c>
     </row>
     <row r="981">
       <c r="A981" t="inlineStr">
         <is>
-          <t>kk_3595551743</t>
+          <t>holstein</t>
         </is>
       </c>
       <c r="B981" t="inlineStr">
         <is>
-          <t>01025839326</t>
+          <t>01050502500</t>
         </is>
       </c>
       <c r="C981" t="inlineStr">
         <is>
-          <t>246836</t>
+          <t>14062</t>
         </is>
       </c>
       <c r="D981" t="inlineStr">
@@ -26911,61 +26911,61 @@
       </c>
       <c r="E981" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0410exclusive2</t>
+          <t>EDM_TOP</t>
         </is>
       </c>
     </row>
     <row r="982">
       <c r="A982" t="inlineStr">
         <is>
-          <t>kk_4841501713</t>
+          <t>ellieee</t>
         </is>
       </c>
       <c r="B982" t="inlineStr">
         <is>
-          <t>01042996002</t>
+          <t>01098996425</t>
         </is>
       </c>
       <c r="C982" t="inlineStr">
         <is>
-          <t>304195</t>
+          <t>203688</t>
         </is>
       </c>
       <c r="D982" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E982" t="inlineStr">
         <is>
-          <t>6968489536332</t>
+          <t>KAKAO_alimtalk</t>
         </is>
       </c>
     </row>
     <row r="983">
       <c r="A983" t="inlineStr">
         <is>
-          <t>ellieee</t>
+          <t>kk_4841501713</t>
         </is>
       </c>
       <c r="B983" t="inlineStr">
         <is>
-          <t>01098996425</t>
+          <t>01042996002</t>
         </is>
       </c>
       <c r="C983" t="inlineStr">
         <is>
-          <t>203688</t>
+          <t>304195</t>
         </is>
       </c>
       <c r="D983" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E983" t="inlineStr">
         <is>
-          <t>KAKAO_alimtalk</t>
+          <t>6968489536332</t>
         </is>
       </c>
     </row>
@@ -27053,54 +27053,54 @@
     <row r="987">
       <c r="A987" t="inlineStr">
         <is>
-          <t>kk_4375973589</t>
+          <t>kmh7710</t>
         </is>
       </c>
       <c r="B987" t="inlineStr">
         <is>
-          <t>01096223641</t>
+          <t>01077108716</t>
         </is>
       </c>
       <c r="C987" t="inlineStr">
         <is>
-          <t>280163</t>
+          <t>164951</t>
         </is>
       </c>
       <c r="D987" t="inlineStr">
         <is>
-          <t>Organic Traffic</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E987" t="inlineStr">
         <is>
-          <t>LMS_ECOM_familycoupon</t>
+          <t>LMS_ECOM_0214_newyear</t>
         </is>
       </c>
     </row>
     <row r="988">
       <c r="A988" t="inlineStr">
         <is>
-          <t>kmh7710</t>
+          <t>kk_4375973589</t>
         </is>
       </c>
       <c r="B988" t="inlineStr">
         <is>
-          <t>01077108716</t>
+          <t>01096223641</t>
         </is>
       </c>
       <c r="C988" t="inlineStr">
         <is>
-          <t>164951</t>
+          <t>280163</t>
         </is>
       </c>
       <c r="D988" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Organic Traffic</t>
         </is>
       </c>
       <c r="E988" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0214_newyear</t>
+          <t>LMS_ECOM_familycoupon</t>
         </is>
       </c>
     </row>
@@ -27161,17 +27161,17 @@
     <row r="991">
       <c r="A991" t="inlineStr">
         <is>
-          <t>kk_2954504655</t>
+          <t>kk_4844665214</t>
         </is>
       </c>
       <c r="B991" t="inlineStr">
         <is>
-          <t>01024942984</t>
+          <t>01033424745</t>
         </is>
       </c>
       <c r="C991" t="inlineStr">
         <is>
-          <t>242733</t>
+          <t>304377</t>
         </is>
       </c>
       <c r="D991" t="inlineStr">
@@ -27188,17 +27188,17 @@
     <row r="992">
       <c r="A992" t="inlineStr">
         <is>
-          <t>kk_4844665214</t>
+          <t>kk_2954504655</t>
         </is>
       </c>
       <c r="B992" t="inlineStr">
         <is>
-          <t>01033424745</t>
+          <t>01024942984</t>
         </is>
       </c>
       <c r="C992" t="inlineStr">
         <is>
-          <t>304377</t>
+          <t>242733</t>
         </is>
       </c>
       <c r="D992" t="inlineStr">
@@ -27296,17 +27296,17 @@
     <row r="996">
       <c r="A996" t="inlineStr">
         <is>
-          <t>kk_4840093815</t>
+          <t>kk_4839544665</t>
         </is>
       </c>
       <c r="B996" t="inlineStr">
         <is>
-          <t>01095450820</t>
+          <t>01055350199</t>
         </is>
       </c>
       <c r="C996" t="inlineStr">
         <is>
-          <t>304126</t>
+          <t>304104</t>
         </is>
       </c>
       <c r="D996" t="inlineStr">
@@ -27316,24 +27316,24 @@
       </c>
       <c r="E996" t="inlineStr">
         <is>
-          <t>EFW</t>
+          <t>6968489536332</t>
         </is>
       </c>
     </row>
     <row r="997">
       <c r="A997" t="inlineStr">
         <is>
-          <t>kk_4839544665</t>
+          <t>kk_4839477951</t>
         </is>
       </c>
       <c r="B997" t="inlineStr">
         <is>
-          <t>01055350199</t>
+          <t>01020868012</t>
         </is>
       </c>
       <c r="C997" t="inlineStr">
         <is>
-          <t>304104</t>
+          <t>304101</t>
         </is>
       </c>
       <c r="D997" t="inlineStr">
@@ -27350,17 +27350,17 @@
     <row r="998">
       <c r="A998" t="inlineStr">
         <is>
-          <t>kk_4839477951</t>
+          <t>kk_4840093815</t>
         </is>
       </c>
       <c r="B998" t="inlineStr">
         <is>
-          <t>01020868012</t>
+          <t>01095450820</t>
         </is>
       </c>
       <c r="C998" t="inlineStr">
         <is>
-          <t>304101</t>
+          <t>304126</t>
         </is>
       </c>
       <c r="D998" t="inlineStr">
@@ -27370,7 +27370,7 @@
       </c>
       <c r="E998" t="inlineStr">
         <is>
-          <t>6968489536332</t>
+          <t>EFW</t>
         </is>
       </c>
     </row>
@@ -27512,44 +27512,44 @@
     <row r="1004">
       <c r="A1004" t="inlineStr">
         <is>
-          <t>dmsdud552</t>
+          <t>kk_4844530515</t>
         </is>
       </c>
       <c r="B1004" t="inlineStr">
         <is>
-          <t>01054633672</t>
+          <t>01054558799</t>
         </is>
       </c>
       <c r="C1004" t="inlineStr">
         <is>
-          <t>132110</t>
+          <t>304366</t>
         </is>
       </c>
       <c r="D1004" t="inlineStr">
         <is>
-          <t>Organic Traffic</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E1004" t="inlineStr">
         <is>
-          <t>(referral)</t>
+          <t>6968489536332</t>
         </is>
       </c>
     </row>
     <row r="1005">
       <c r="A1005" t="inlineStr">
         <is>
-          <t>kk_4844530515</t>
+          <t>kk_4844657024</t>
         </is>
       </c>
       <c r="B1005" t="inlineStr">
         <is>
-          <t>01054558799</t>
+          <t>01033551784</t>
         </is>
       </c>
       <c r="C1005" t="inlineStr">
         <is>
-          <t>304366</t>
+          <t>304376</t>
         </is>
       </c>
       <c r="D1005" t="inlineStr">
@@ -27566,81 +27566,81 @@
     <row r="1006">
       <c r="A1006" t="inlineStr">
         <is>
-          <t>kk_4844657024</t>
+          <t>dmsdud552</t>
         </is>
       </c>
       <c r="B1006" t="inlineStr">
         <is>
-          <t>01033551784</t>
+          <t>01054633672</t>
         </is>
       </c>
       <c r="C1006" t="inlineStr">
         <is>
-          <t>304376</t>
+          <t>132110</t>
         </is>
       </c>
       <c r="D1006" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Organic Traffic</t>
         </is>
       </c>
       <c r="E1006" t="inlineStr">
         <is>
-          <t>6968489536332</t>
+          <t>(referral)</t>
         </is>
       </c>
     </row>
     <row r="1007">
       <c r="A1007" t="inlineStr">
         <is>
-          <t>kk_4543882817</t>
+          <t>kk_4839643736</t>
         </is>
       </c>
       <c r="B1007" t="inlineStr">
         <is>
-          <t>01023875300</t>
+          <t>01063617035</t>
         </is>
       </c>
       <c r="C1007" t="inlineStr">
         <is>
-          <t>287573</t>
+          <t>304107</t>
         </is>
       </c>
       <c r="D1007" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E1007" t="inlineStr">
         <is>
-          <t>미분류</t>
+          <t>naver_brandsearch_mobile</t>
         </is>
       </c>
     </row>
     <row r="1008">
       <c r="A1008" t="inlineStr">
         <is>
-          <t>kk_4839643736</t>
+          <t>kk_4543882817</t>
         </is>
       </c>
       <c r="B1008" t="inlineStr">
         <is>
-          <t>01063617035</t>
+          <t>01023875300</t>
         </is>
       </c>
       <c r="C1008" t="inlineStr">
         <is>
-          <t>304107</t>
+          <t>287573</t>
         </is>
       </c>
       <c r="D1008" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="E1008" t="inlineStr">
         <is>
-          <t>naver_brandsearch_mobile</t>
+          <t>미분류</t>
         </is>
       </c>
     </row>
@@ -27701,125 +27701,125 @@
     <row r="1011">
       <c r="A1011" t="inlineStr">
         <is>
-          <t>kk_4844453283</t>
+          <t>kk_4843847622</t>
         </is>
       </c>
       <c r="B1011" t="inlineStr">
         <is>
-          <t>01090262556</t>
+          <t>01046990393</t>
         </is>
       </c>
       <c r="C1011" t="inlineStr">
         <is>
-          <t>304360</t>
+          <t>304336</t>
         </is>
       </c>
       <c r="D1011" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Organic Traffic</t>
         </is>
       </c>
       <c r="E1011" t="inlineStr">
         <is>
-          <t>6968489536332</t>
+          <t>(organic)</t>
         </is>
       </c>
     </row>
     <row r="1012">
       <c r="A1012" t="inlineStr">
         <is>
-          <t>kk_4845173313</t>
+          <t>kk_4843926419</t>
         </is>
       </c>
       <c r="B1012" t="inlineStr">
         <is>
-          <t>01024436341</t>
+          <t>01034583174</t>
         </is>
       </c>
       <c r="C1012" t="inlineStr">
         <is>
-          <t>304397</t>
+          <t>304338</t>
         </is>
       </c>
       <c r="D1012" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Official SNS</t>
         </is>
       </c>
       <c r="E1012" t="inlineStr">
         <is>
-          <t>6968489536332</t>
+          <t>EFW_04</t>
         </is>
       </c>
     </row>
     <row r="1013">
       <c r="A1013" t="inlineStr">
         <is>
-          <t>kk_4843926419</t>
+          <t>kk_4844453283</t>
         </is>
       </c>
       <c r="B1013" t="inlineStr">
         <is>
-          <t>01034583174</t>
+          <t>01090262556</t>
         </is>
       </c>
       <c r="C1013" t="inlineStr">
         <is>
-          <t>304338</t>
+          <t>304360</t>
         </is>
       </c>
       <c r="D1013" t="inlineStr">
         <is>
-          <t>Official SNS</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E1013" t="inlineStr">
         <is>
-          <t>EFW_04</t>
+          <t>6968489536332</t>
         </is>
       </c>
     </row>
     <row r="1014">
       <c r="A1014" t="inlineStr">
         <is>
-          <t>kk_4843847622</t>
+          <t>kk_4845121221</t>
         </is>
       </c>
       <c r="B1014" t="inlineStr">
         <is>
-          <t>01046990393</t>
+          <t>01044632332</t>
         </is>
       </c>
       <c r="C1014" t="inlineStr">
         <is>
-          <t>304336</t>
+          <t>304393</t>
         </is>
       </c>
       <c r="D1014" t="inlineStr">
         <is>
-          <t>Organic Traffic</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E1014" t="inlineStr">
         <is>
-          <t>(organic)</t>
+          <t>6968489536332</t>
         </is>
       </c>
     </row>
     <row r="1015">
       <c r="A1015" t="inlineStr">
         <is>
-          <t>kk_4845121221</t>
+          <t>kidultyo</t>
         </is>
       </c>
       <c r="B1015" t="inlineStr">
         <is>
-          <t>01044632332</t>
+          <t>01037980315</t>
         </is>
       </c>
       <c r="C1015" t="inlineStr">
         <is>
-          <t>304393</t>
+          <t>304331</t>
         </is>
       </c>
       <c r="D1015" t="inlineStr">
@@ -27836,17 +27836,17 @@
     <row r="1016">
       <c r="A1016" t="inlineStr">
         <is>
-          <t>kidultyo</t>
+          <t>kk_4845173313</t>
         </is>
       </c>
       <c r="B1016" t="inlineStr">
         <is>
-          <t>01037980315</t>
+          <t>01024436341</t>
         </is>
       </c>
       <c r="C1016" t="inlineStr">
         <is>
-          <t>304331</t>
+          <t>304397</t>
         </is>
       </c>
       <c r="D1016" t="inlineStr">
@@ -27944,54 +27944,54 @@
     <row r="1020">
       <c r="A1020" t="inlineStr">
         <is>
-          <t>kk_4839542021</t>
+          <t>kk_4357899204</t>
         </is>
       </c>
       <c r="B1020" t="inlineStr">
         <is>
-          <t>01089909663</t>
+          <t>01082772838</t>
         </is>
       </c>
       <c r="C1020" t="inlineStr">
         <is>
-          <t>304103</t>
+          <t>279564</t>
         </is>
       </c>
       <c r="D1020" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Official SNS</t>
         </is>
       </c>
       <c r="E1020" t="inlineStr">
         <is>
-          <t>(organic)</t>
+          <t>(referral)</t>
         </is>
       </c>
     </row>
     <row r="1021">
       <c r="A1021" t="inlineStr">
         <is>
-          <t>kk_4357899204</t>
+          <t>kk_4839542021</t>
         </is>
       </c>
       <c r="B1021" t="inlineStr">
         <is>
-          <t>01082772838</t>
+          <t>01089909663</t>
         </is>
       </c>
       <c r="C1021" t="inlineStr">
         <is>
-          <t>279564</t>
+          <t>304103</t>
         </is>
       </c>
       <c r="D1021" t="inlineStr">
         <is>
-          <t>Official SNS</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E1021" t="inlineStr">
         <is>
-          <t>(referral)</t>
+          <t>(organic)</t>
         </is>
       </c>
     </row>
@@ -28079,54 +28079,54 @@
     <row r="1025">
       <c r="A1025" t="inlineStr">
         <is>
-          <t>kk_3601210201</t>
+          <t>chibird</t>
         </is>
       </c>
       <c r="B1025" t="inlineStr">
         <is>
-          <t>01092460423</t>
+          <t>01031187674</t>
         </is>
       </c>
       <c r="C1025" t="inlineStr">
         <is>
-          <t>247035</t>
+          <t>219288</t>
         </is>
       </c>
       <c r="D1025" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E1025" t="inlineStr">
         <is>
-          <t>미분류</t>
+          <t>sa</t>
         </is>
       </c>
     </row>
     <row r="1026">
       <c r="A1026" t="inlineStr">
         <is>
-          <t>chibird</t>
+          <t>kk_3601210201</t>
         </is>
       </c>
       <c r="B1026" t="inlineStr">
         <is>
-          <t>01031187674</t>
+          <t>01092460423</t>
         </is>
       </c>
       <c r="C1026" t="inlineStr">
         <is>
-          <t>219288</t>
+          <t>247035</t>
         </is>
       </c>
       <c r="D1026" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="E1026" t="inlineStr">
         <is>
-          <t>sa</t>
+          <t>미분류</t>
         </is>
       </c>
     </row>
@@ -28268,54 +28268,54 @@
     <row r="1032">
       <c r="A1032" t="inlineStr">
         <is>
-          <t>kk_4847354450</t>
+          <t>kk_4847975154</t>
         </is>
       </c>
       <c r="B1032" t="inlineStr">
         <is>
-          <t>01088042346</t>
+          <t>01062199172</t>
         </is>
       </c>
       <c r="C1032" t="inlineStr">
         <is>
-          <t>304489</t>
+          <t>304512</t>
         </is>
       </c>
       <c r="D1032" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="E1032" t="inlineStr">
         <is>
-          <t>6968489536332</t>
+          <t>Direct</t>
         </is>
       </c>
     </row>
     <row r="1033">
       <c r="A1033" t="inlineStr">
         <is>
-          <t>kk_4847975154</t>
+          <t>kk_4847354450</t>
         </is>
       </c>
       <c r="B1033" t="inlineStr">
         <is>
-          <t>01062199172</t>
+          <t>01088042346</t>
         </is>
       </c>
       <c r="C1033" t="inlineStr">
         <is>
-          <t>304512</t>
+          <t>304489</t>
         </is>
       </c>
       <c r="D1033" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E1033" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>6968489536332</t>
         </is>
       </c>
     </row>
@@ -28376,54 +28376,54 @@
     <row r="1036">
       <c r="A1036" t="inlineStr">
         <is>
-          <t>kk_4844452226</t>
+          <t>kk_4844609437</t>
         </is>
       </c>
       <c r="B1036" t="inlineStr">
         <is>
-          <t>01096801866</t>
+          <t>01046808931</t>
         </is>
       </c>
       <c r="C1036" t="inlineStr">
         <is>
-          <t>304359</t>
+          <t>304372</t>
         </is>
       </c>
       <c r="D1036" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Official SNS</t>
         </is>
       </c>
       <c r="E1036" t="inlineStr">
         <is>
-          <t>6968489536332</t>
+          <t>(referral)</t>
         </is>
       </c>
     </row>
     <row r="1037">
       <c r="A1037" t="inlineStr">
         <is>
-          <t>kk_4844609437</t>
+          <t>kk_4844452226</t>
         </is>
       </c>
       <c r="B1037" t="inlineStr">
         <is>
-          <t>01046808931</t>
+          <t>01096801866</t>
         </is>
       </c>
       <c r="C1037" t="inlineStr">
         <is>
-          <t>304372</t>
+          <t>304359</t>
         </is>
       </c>
       <c r="D1037" t="inlineStr">
         <is>
-          <t>Official SNS</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E1037" t="inlineStr">
         <is>
-          <t>(referral)</t>
+          <t>6968489536332</t>
         </is>
       </c>
     </row>
@@ -28538,17 +28538,17 @@
     <row r="1042">
       <c r="A1042" t="inlineStr">
         <is>
-          <t>jsb0425</t>
+          <t>kk_4840913383</t>
         </is>
       </c>
       <c r="B1042" t="inlineStr">
         <is>
-          <t>01037883670</t>
+          <t>01099887927</t>
         </is>
       </c>
       <c r="C1042" t="inlineStr">
         <is>
-          <t>104766</t>
+          <t>304174</t>
         </is>
       </c>
       <c r="D1042" t="inlineStr">
@@ -28565,98 +28565,98 @@
     <row r="1043">
       <c r="A1043" t="inlineStr">
         <is>
-          <t>kk_3977730443</t>
+          <t>kk_4841278242</t>
         </is>
       </c>
       <c r="B1043" t="inlineStr">
         <is>
-          <t>01064291828</t>
+          <t>01046197965</t>
         </is>
       </c>
       <c r="C1043" t="inlineStr">
         <is>
-          <t>271278</t>
+          <t>304190</t>
         </is>
       </c>
       <c r="D1043" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Organic Traffic</t>
         </is>
       </c>
       <c r="E1043" t="inlineStr">
         <is>
-          <t>naver_brandsearch_mobile</t>
+          <t>(referral)</t>
         </is>
       </c>
     </row>
     <row r="1044">
       <c r="A1044" t="inlineStr">
         <is>
-          <t>kk_4841278242</t>
+          <t>kk_2750710108</t>
         </is>
       </c>
       <c r="B1044" t="inlineStr">
         <is>
-          <t>01046197965</t>
+          <t>01062707475</t>
         </is>
       </c>
       <c r="C1044" t="inlineStr">
         <is>
-          <t>304190</t>
+          <t>207211</t>
         </is>
       </c>
       <c r="D1044" t="inlineStr">
         <is>
-          <t>Organic Traffic</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="E1044" t="inlineStr">
         <is>
-          <t>(referral)</t>
+          <t>Direct</t>
         </is>
       </c>
     </row>
     <row r="1045">
       <c r="A1045" t="inlineStr">
         <is>
-          <t>kk_2750710108</t>
+          <t>kk_3977730443</t>
         </is>
       </c>
       <c r="B1045" t="inlineStr">
         <is>
-          <t>01062707475</t>
+          <t>01064291828</t>
         </is>
       </c>
       <c r="C1045" t="inlineStr">
         <is>
-          <t>207211</t>
+          <t>271278</t>
         </is>
       </c>
       <c r="D1045" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E1045" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>naver_brandsearch_mobile</t>
         </is>
       </c>
     </row>
     <row r="1046">
       <c r="A1046" t="inlineStr">
         <is>
-          <t>kk_4840913383</t>
+          <t>jsb0425</t>
         </is>
       </c>
       <c r="B1046" t="inlineStr">
         <is>
-          <t>01099887927</t>
+          <t>01037883670</t>
         </is>
       </c>
       <c r="C1046" t="inlineStr">
         <is>
-          <t>304174</t>
+          <t>104766</t>
         </is>
       </c>
       <c r="D1046" t="inlineStr">
@@ -28835,71 +28835,71 @@
     <row r="1053">
       <c r="A1053" t="inlineStr">
         <is>
-          <t>kk_4425155772</t>
+          <t>chyim</t>
         </is>
       </c>
       <c r="B1053" t="inlineStr">
         <is>
-          <t>01074070807</t>
+          <t>01037519198</t>
         </is>
       </c>
       <c r="C1053" t="inlineStr">
         <is>
-          <t>281472</t>
+          <t>255862</t>
         </is>
       </c>
       <c r="D1053" t="inlineStr">
         <is>
-          <t>Organic Traffic</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="E1053" t="inlineStr">
         <is>
-          <t>(organic)</t>
+          <t>Direct</t>
         </is>
       </c>
     </row>
     <row r="1054">
       <c r="A1054" t="inlineStr">
         <is>
-          <t>chyim</t>
+          <t>kk_4849353674</t>
         </is>
       </c>
       <c r="B1054" t="inlineStr">
         <is>
-          <t>01037519198</t>
+          <t>01029430913</t>
         </is>
       </c>
       <c r="C1054" t="inlineStr">
         <is>
-          <t>255862</t>
+          <t>304557</t>
         </is>
       </c>
       <c r="D1054" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>Organic Traffic</t>
         </is>
       </c>
       <c r="E1054" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>(referral)</t>
         </is>
       </c>
     </row>
     <row r="1055">
       <c r="A1055" t="inlineStr">
         <is>
-          <t>kk_4849353674</t>
+          <t>kk_4425155772</t>
         </is>
       </c>
       <c r="B1055" t="inlineStr">
         <is>
-          <t>01029430913</t>
+          <t>01074070807</t>
         </is>
       </c>
       <c r="C1055" t="inlineStr">
         <is>
-          <t>304557</t>
+          <t>281472</t>
         </is>
       </c>
       <c r="D1055" t="inlineStr">
@@ -28909,7 +28909,7 @@
       </c>
       <c r="E1055" t="inlineStr">
         <is>
-          <t>(referral)</t>
+          <t>(organic)</t>
         </is>
       </c>
     </row>
@@ -29105,17 +29105,17 @@
     <row r="1063">
       <c r="A1063" t="inlineStr">
         <is>
-          <t>nikemkr</t>
+          <t>kk_4841799872</t>
         </is>
       </c>
       <c r="B1063" t="inlineStr">
         <is>
-          <t>01032361592</t>
+          <t>01023236956</t>
         </is>
       </c>
       <c r="C1063" t="inlineStr">
         <is>
-          <t>145423</t>
+          <t>304205</t>
         </is>
       </c>
       <c r="D1063" t="inlineStr">
@@ -29125,24 +29125,24 @@
       </c>
       <c r="E1063" t="inlineStr">
         <is>
-          <t>naver_brandsearch_mobile</t>
+          <t>컬럼비아_DPA_240530</t>
         </is>
       </c>
     </row>
     <row r="1064">
       <c r="A1064" t="inlineStr">
         <is>
-          <t>kk_4841799872</t>
+          <t>nikemkr</t>
         </is>
       </c>
       <c r="B1064" t="inlineStr">
         <is>
-          <t>01023236956</t>
+          <t>01032361592</t>
         </is>
       </c>
       <c r="C1064" t="inlineStr">
         <is>
-          <t>304205</t>
+          <t>145423</t>
         </is>
       </c>
       <c r="D1064" t="inlineStr">
@@ -29152,7 +29152,7 @@
       </c>
       <c r="E1064" t="inlineStr">
         <is>
-          <t>컬럼비아_DPA_240530</t>
+          <t>naver_brandsearch_mobile</t>
         </is>
       </c>
     </row>
@@ -29186,108 +29186,108 @@
     <row r="1066">
       <c r="A1066" t="inlineStr">
         <is>
-          <t>lolia875</t>
+          <t>kk_3241081989</t>
         </is>
       </c>
       <c r="B1066" t="inlineStr">
         <is>
-          <t>01067138715</t>
+          <t>01072287165</t>
         </is>
       </c>
       <c r="C1066" t="inlineStr">
         <is>
-          <t>161251</t>
+          <t>234608</t>
         </is>
       </c>
       <c r="D1066" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E1066" t="inlineStr">
         <is>
-          <t>6968489536332</t>
+          <t>KAKAO_alimtalk</t>
         </is>
       </c>
     </row>
     <row r="1067">
       <c r="A1067" t="inlineStr">
         <is>
-          <t>kk_3241081989</t>
+          <t>lolia875</t>
         </is>
       </c>
       <c r="B1067" t="inlineStr">
         <is>
-          <t>01072287165</t>
+          <t>01067138715</t>
         </is>
       </c>
       <c r="C1067" t="inlineStr">
         <is>
-          <t>234608</t>
+          <t>161251</t>
         </is>
       </c>
       <c r="D1067" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E1067" t="inlineStr">
         <is>
-          <t>KAKAO_alimtalk</t>
+          <t>6968489536332</t>
         </is>
       </c>
     </row>
     <row r="1068">
       <c r="A1068" t="inlineStr">
         <is>
-          <t>kk_3140575996</t>
+          <t>kk_3393400723</t>
         </is>
       </c>
       <c r="B1068" t="inlineStr">
         <is>
-          <t>01098546266</t>
+          <t>01089700082</t>
         </is>
       </c>
       <c r="C1068" t="inlineStr">
         <is>
-          <t>222820</t>
+          <t>241049</t>
         </is>
       </c>
       <c r="D1068" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E1068" t="inlineStr">
         <is>
-          <t>naver_brandsearch_mobile</t>
+          <t>KAKAO_alimtalk</t>
         </is>
       </c>
     </row>
     <row r="1069">
       <c r="A1069" t="inlineStr">
         <is>
-          <t>kk_3393400723</t>
+          <t>kk_3140575996</t>
         </is>
       </c>
       <c r="B1069" t="inlineStr">
         <is>
-          <t>01089700082</t>
+          <t>01098546266</t>
         </is>
       </c>
       <c r="C1069" t="inlineStr">
         <is>
-          <t>241049</t>
+          <t>222820</t>
         </is>
       </c>
       <c r="D1069" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E1069" t="inlineStr">
         <is>
-          <t>KAKAO_alimtalk</t>
+          <t>naver_brandsearch_mobile</t>
         </is>
       </c>
     </row>
@@ -29375,17 +29375,17 @@
     <row r="1073">
       <c r="A1073" t="inlineStr">
         <is>
-          <t>hyoju1981</t>
+          <t>kk_2750963357</t>
         </is>
       </c>
       <c r="B1073" t="inlineStr">
         <is>
-          <t>01045321445</t>
+          <t>01033989099</t>
         </is>
       </c>
       <c r="C1073" t="inlineStr">
         <is>
-          <t>107362</t>
+          <t>207617</t>
         </is>
       </c>
       <c r="D1073" t="inlineStr">
@@ -29395,24 +29395,24 @@
       </c>
       <c r="E1073" t="inlineStr">
         <is>
-          <t>KAKAO_alimtalk</t>
+          <t>LMS_ECOM_200416_family</t>
         </is>
       </c>
     </row>
     <row r="1074">
       <c r="A1074" t="inlineStr">
         <is>
-          <t>kk_2750963357</t>
+          <t>hyoju1981</t>
         </is>
       </c>
       <c r="B1074" t="inlineStr">
         <is>
-          <t>01033989099</t>
+          <t>01045321445</t>
         </is>
       </c>
       <c r="C1074" t="inlineStr">
         <is>
-          <t>207617</t>
+          <t>107362</t>
         </is>
       </c>
       <c r="D1074" t="inlineStr">
@@ -29422,105 +29422,105 @@
       </c>
       <c r="E1074" t="inlineStr">
         <is>
-          <t>LMS_ECOM_200416_family</t>
+          <t>KAKAO_alimtalk</t>
         </is>
       </c>
     </row>
     <row r="1075">
       <c r="A1075" t="inlineStr">
         <is>
-          <t>kk_4848093455</t>
+          <t>kk_3792750872</t>
         </is>
       </c>
       <c r="B1075" t="inlineStr">
         <is>
-          <t>01023043154</t>
+          <t>01084382636</t>
         </is>
       </c>
       <c r="C1075" t="inlineStr">
         <is>
-          <t>304517</t>
+          <t>256807</t>
         </is>
       </c>
       <c r="D1075" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E1075" t="inlineStr">
         <is>
-          <t>6968489536332</t>
+          <t>KAKAO_CH_MENU_0211_NEW_MEN</t>
         </is>
       </c>
     </row>
     <row r="1076">
       <c r="A1076" t="inlineStr">
         <is>
-          <t>kk_3792750872</t>
+          <t>kk_4406693806</t>
         </is>
       </c>
       <c r="B1076" t="inlineStr">
         <is>
-          <t>01084382636</t>
+          <t>01088675050</t>
         </is>
       </c>
       <c r="C1076" t="inlineStr">
         <is>
-          <t>256807</t>
+          <t>280999</t>
         </is>
       </c>
       <c r="D1076" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Organic Traffic</t>
         </is>
       </c>
       <c r="E1076" t="inlineStr">
         <is>
-          <t>KAKAO_CH_MENU_0211_NEW_MEN</t>
+          <t>(referral)</t>
         </is>
       </c>
     </row>
     <row r="1077">
       <c r="A1077" t="inlineStr">
         <is>
-          <t>kk_4406693806</t>
+          <t>kk_4669827711</t>
         </is>
       </c>
       <c r="B1077" t="inlineStr">
         <is>
-          <t>01088675050</t>
+          <t>01091727683</t>
         </is>
       </c>
       <c r="C1077" t="inlineStr">
         <is>
-          <t>280999</t>
+          <t>294249</t>
         </is>
       </c>
       <c r="D1077" t="inlineStr">
         <is>
-          <t>Organic Traffic</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E1077" t="inlineStr">
         <is>
-          <t>(referral)</t>
+          <t>6968489536332</t>
         </is>
       </c>
     </row>
     <row r="1078">
       <c r="A1078" t="inlineStr">
         <is>
-          <t>kk_4669827711</t>
+          <t>kk_4848093455</t>
         </is>
       </c>
       <c r="B1078" t="inlineStr">
         <is>
-          <t>01091727683</t>
+          <t>01023043154</t>
         </is>
       </c>
       <c r="C1078" t="inlineStr">
         <is>
-          <t>294249</t>
+          <t>304517</t>
         </is>
       </c>
       <c r="D1078" t="inlineStr">
@@ -29537,152 +29537,152 @@
     <row r="1079">
       <c r="A1079" t="inlineStr">
         <is>
-          <t>kk_4846729102</t>
+          <t>ch5115</t>
         </is>
       </c>
       <c r="B1079" t="inlineStr">
         <is>
-          <t>01084771303</t>
+          <t>01084479339</t>
         </is>
       </c>
       <c r="C1079" t="inlineStr">
         <is>
-          <t>304461</t>
+          <t>240557</t>
         </is>
       </c>
       <c r="D1079" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="E1079" t="inlineStr">
         <is>
-          <t>6968489536332</t>
+          <t>Direct</t>
         </is>
       </c>
     </row>
     <row r="1080">
       <c r="A1080" t="inlineStr">
         <is>
-          <t>kk_2788668233</t>
+          <t>imgain0422</t>
         </is>
       </c>
       <c r="B1080" t="inlineStr">
         <is>
-          <t>01041696139</t>
+          <t>01029135546</t>
         </is>
       </c>
       <c r="C1080" t="inlineStr">
         <is>
-          <t>210002</t>
+          <t>181451</t>
         </is>
       </c>
       <c r="D1080" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="E1080" t="inlineStr">
         <is>
-          <t>6968489536332</t>
+          <t>Direct</t>
         </is>
       </c>
     </row>
     <row r="1081">
       <c r="A1081" t="inlineStr">
         <is>
-          <t>kk_4845661756</t>
+          <t>kk_3183517395</t>
         </is>
       </c>
       <c r="B1081" t="inlineStr">
         <is>
-          <t>01095936572</t>
+          <t>01082019936</t>
         </is>
       </c>
       <c r="C1081" t="inlineStr">
         <is>
-          <t>304422</t>
+          <t>228501</t>
         </is>
       </c>
       <c r="D1081" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="E1081" t="inlineStr">
         <is>
-          <t>6968489536332</t>
+          <t>Direct</t>
         </is>
       </c>
     </row>
     <row r="1082">
       <c r="A1082" t="inlineStr">
         <is>
-          <t>chpuss74</t>
+          <t>kk_4846729102</t>
         </is>
       </c>
       <c r="B1082" t="inlineStr">
         <is>
-          <t>01035361091</t>
+          <t>01084771303</t>
         </is>
       </c>
       <c r="C1082" t="inlineStr">
         <is>
-          <t>154462</t>
+          <t>304461</t>
         </is>
       </c>
       <c r="D1082" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E1082" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>6968489536332</t>
         </is>
       </c>
     </row>
     <row r="1083">
       <c r="A1083" t="inlineStr">
         <is>
-          <t>imgain0422</t>
+          <t>kk_2788668233</t>
         </is>
       </c>
       <c r="B1083" t="inlineStr">
         <is>
-          <t>01029135546</t>
+          <t>01041696139</t>
         </is>
       </c>
       <c r="C1083" t="inlineStr">
         <is>
-          <t>181451</t>
+          <t>210002</t>
         </is>
       </c>
       <c r="D1083" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E1083" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>6968489536332</t>
         </is>
       </c>
     </row>
     <row r="1084">
       <c r="A1084" t="inlineStr">
         <is>
-          <t>kk_3183517395</t>
+          <t>chpuss74</t>
         </is>
       </c>
       <c r="B1084" t="inlineStr">
         <is>
-          <t>01082019936</t>
+          <t>01035361091</t>
         </is>
       </c>
       <c r="C1084" t="inlineStr">
         <is>
-          <t>228501</t>
+          <t>154462</t>
         </is>
       </c>
       <c r="D1084" t="inlineStr">
@@ -29699,27 +29699,27 @@
     <row r="1085">
       <c r="A1085" t="inlineStr">
         <is>
-          <t>ch5115</t>
+          <t>kk_4845661756</t>
         </is>
       </c>
       <c r="B1085" t="inlineStr">
         <is>
-          <t>01084479339</t>
+          <t>01095936572</t>
         </is>
       </c>
       <c r="C1085" t="inlineStr">
         <is>
-          <t>240557</t>
+          <t>304422</t>
         </is>
       </c>
       <c r="D1085" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E1085" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>6968489536332</t>
         </is>
       </c>
     </row>
@@ -29780,216 +29780,216 @@
     <row r="1088">
       <c r="A1088" t="inlineStr">
         <is>
-          <t>kjhk5404</t>
+          <t>kk_3650586439</t>
         </is>
       </c>
       <c r="B1088" t="inlineStr">
         <is>
-          <t>01027390700</t>
+          <t>01029107056</t>
         </is>
       </c>
       <c r="C1088" t="inlineStr">
         <is>
-          <t>280120</t>
+          <t>249153</t>
         </is>
       </c>
       <c r="D1088" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="E1088" t="inlineStr">
         <is>
-          <t>KAKAO_alimtalk</t>
+          <t>Direct</t>
         </is>
       </c>
     </row>
     <row r="1089">
       <c r="A1089" t="inlineStr">
         <is>
-          <t>kk_3650586439</t>
+          <t>kjhk5404</t>
         </is>
       </c>
       <c r="B1089" t="inlineStr">
         <is>
-          <t>01029107056</t>
+          <t>01027390700</t>
         </is>
       </c>
       <c r="C1089" t="inlineStr">
         <is>
-          <t>249153</t>
+          <t>280120</t>
         </is>
       </c>
       <c r="D1089" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E1089" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>KAKAO_alimtalk</t>
         </is>
       </c>
     </row>
     <row r="1090">
       <c r="A1090" t="inlineStr">
         <is>
-          <t>kk_4844076820</t>
+          <t>kk_2775500473</t>
         </is>
       </c>
       <c r="B1090" t="inlineStr">
         <is>
-          <t>01091346366</t>
+          <t>01045659020</t>
         </is>
       </c>
       <c r="C1090" t="inlineStr">
         <is>
-          <t>304343</t>
+          <t>209371</t>
         </is>
       </c>
       <c r="D1090" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Organic Traffic</t>
         </is>
       </c>
       <c r="E1090" t="inlineStr">
         <is>
-          <t>6968489536332</t>
+          <t>(referral)</t>
         </is>
       </c>
     </row>
     <row r="1091">
       <c r="A1091" t="inlineStr">
         <is>
-          <t>kk_2775500473</t>
+          <t>kk_4844076820</t>
         </is>
       </c>
       <c r="B1091" t="inlineStr">
         <is>
-          <t>01045659020</t>
+          <t>01091346366</t>
         </is>
       </c>
       <c r="C1091" t="inlineStr">
         <is>
-          <t>209371</t>
+          <t>304343</t>
         </is>
       </c>
       <c r="D1091" t="inlineStr">
         <is>
-          <t>Organic Traffic</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E1091" t="inlineStr">
         <is>
-          <t>(referral)</t>
+          <t>6968489536332</t>
         </is>
       </c>
     </row>
     <row r="1092">
       <c r="A1092" t="inlineStr">
         <is>
-          <t>kk_4522711623</t>
+          <t>kk_4434329905</t>
         </is>
       </c>
       <c r="B1092" t="inlineStr">
         <is>
-          <t>01089870313</t>
+          <t>01071724035</t>
         </is>
       </c>
       <c r="C1092" t="inlineStr">
         <is>
-          <t>286306</t>
+          <t>281922</t>
         </is>
       </c>
       <c r="D1092" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E1092" t="inlineStr">
         <is>
-          <t>6968489536332</t>
+          <t>Email_mkt</t>
         </is>
       </c>
     </row>
     <row r="1093">
       <c r="A1093" t="inlineStr">
         <is>
-          <t>kk_4434329905</t>
+          <t>kk_4522711623</t>
         </is>
       </c>
       <c r="B1093" t="inlineStr">
         <is>
-          <t>01071724035</t>
+          <t>01089870313</t>
         </is>
       </c>
       <c r="C1093" t="inlineStr">
         <is>
-          <t>281922</t>
+          <t>286306</t>
         </is>
       </c>
       <c r="D1093" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E1093" t="inlineStr">
         <is>
-          <t>Email_mkt</t>
+          <t>6968489536332</t>
         </is>
       </c>
     </row>
     <row r="1094">
       <c r="A1094" t="inlineStr">
         <is>
-          <t>w0309</t>
+          <t>kk_4840817001</t>
         </is>
       </c>
       <c r="B1094" t="inlineStr">
         <is>
-          <t>01053481702</t>
+          <t>01085963383</t>
         </is>
       </c>
       <c r="C1094" t="inlineStr">
         <is>
-          <t>126315</t>
+          <t>304168</t>
         </is>
       </c>
       <c r="D1094" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E1094" t="inlineStr">
         <is>
-          <t>Email_mkt</t>
+          <t>6968489536332</t>
         </is>
       </c>
     </row>
     <row r="1095">
       <c r="A1095" t="inlineStr">
         <is>
-          <t>kk_4840817001</t>
+          <t>w0309</t>
         </is>
       </c>
       <c r="B1095" t="inlineStr">
         <is>
-          <t>01085963383</t>
+          <t>01053481702</t>
         </is>
       </c>
       <c r="C1095" t="inlineStr">
         <is>
-          <t>304168</t>
+          <t>126315</t>
         </is>
       </c>
       <c r="D1095" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E1095" t="inlineStr">
         <is>
-          <t>6968489536332</t>
+          <t>Email_mkt</t>
         </is>
       </c>
     </row>
@@ -30023,71 +30023,71 @@
     <row r="1097">
       <c r="A1097" t="inlineStr">
         <is>
-          <t>kk_3213636735</t>
+          <t>xoxoie2</t>
         </is>
       </c>
       <c r="B1097" t="inlineStr">
         <is>
-          <t>01071338973</t>
+          <t>01043560834</t>
         </is>
       </c>
       <c r="C1097" t="inlineStr">
         <is>
-          <t>232010</t>
+          <t>304072</t>
         </is>
       </c>
       <c r="D1097" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Official SNS</t>
         </is>
       </c>
       <c r="E1097" t="inlineStr">
         <is>
-          <t>KAKAO_CH_MENU_0226_TRAILRUN</t>
+          <t>EFW_04</t>
         </is>
       </c>
     </row>
     <row r="1098">
       <c r="A1098" t="inlineStr">
         <is>
-          <t>eyounjoo</t>
+          <t>z090909x</t>
         </is>
       </c>
       <c r="B1098" t="inlineStr">
         <is>
-          <t>01036167949</t>
+          <t>01092058111</t>
         </is>
       </c>
       <c r="C1098" t="inlineStr">
         <is>
-          <t>283223</t>
+          <t>113003</t>
         </is>
       </c>
       <c r="D1098" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E1098" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0410exclusive2</t>
+          <t>6968489536332</t>
         </is>
       </c>
     </row>
     <row r="1099">
       <c r="A1099" t="inlineStr">
         <is>
-          <t>z090909x</t>
+          <t>kk_4840045474</t>
         </is>
       </c>
       <c r="B1099" t="inlineStr">
         <is>
-          <t>01092058111</t>
+          <t>01096310429</t>
         </is>
       </c>
       <c r="C1099" t="inlineStr">
         <is>
-          <t>113003</t>
+          <t>304122</t>
         </is>
       </c>
       <c r="D1099" t="inlineStr">
@@ -30104,17 +30104,17 @@
     <row r="1100">
       <c r="A1100" t="inlineStr">
         <is>
-          <t>ssama</t>
+          <t>eyounjoo</t>
         </is>
       </c>
       <c r="B1100" t="inlineStr">
         <is>
-          <t>01056271982</t>
+          <t>01036167949</t>
         </is>
       </c>
       <c r="C1100" t="inlineStr">
         <is>
-          <t>47874</t>
+          <t>283223</t>
         </is>
       </c>
       <c r="D1100" t="inlineStr">
@@ -30131,17 +30131,17 @@
     <row r="1101">
       <c r="A1101" t="inlineStr">
         <is>
-          <t>gus7526</t>
+          <t>ssama</t>
         </is>
       </c>
       <c r="B1101" t="inlineStr">
         <is>
-          <t>01050931023</t>
+          <t>01056271982</t>
         </is>
       </c>
       <c r="C1101" t="inlineStr">
         <is>
-          <t>140860</t>
+          <t>47874</t>
         </is>
       </c>
       <c r="D1101" t="inlineStr">
@@ -30158,44 +30158,44 @@
     <row r="1102">
       <c r="A1102" t="inlineStr">
         <is>
-          <t>kk_4840045474</t>
+          <t>kk_3213636735</t>
         </is>
       </c>
       <c r="B1102" t="inlineStr">
         <is>
-          <t>01096310429</t>
+          <t>01071338973</t>
         </is>
       </c>
       <c r="C1102" t="inlineStr">
         <is>
-          <t>304122</t>
+          <t>232010</t>
         </is>
       </c>
       <c r="D1102" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E1102" t="inlineStr">
         <is>
-          <t>6968489536332</t>
+          <t>KAKAO_CH_MENU_0226_TRAILRUN</t>
         </is>
       </c>
     </row>
     <row r="1103">
       <c r="A1103" t="inlineStr">
         <is>
-          <t>kk_4228106377</t>
+          <t>gus7526</t>
         </is>
       </c>
       <c r="B1103" t="inlineStr">
         <is>
-          <t>01063165271</t>
+          <t>01050931023</t>
         </is>
       </c>
       <c r="C1103" t="inlineStr">
         <is>
-          <t>273193</t>
+          <t>140860</t>
         </is>
       </c>
       <c r="D1103" t="inlineStr">
@@ -30212,54 +30212,54 @@
     <row r="1104">
       <c r="A1104" t="inlineStr">
         <is>
-          <t>xoxoie2</t>
+          <t>kk_4228106377</t>
         </is>
       </c>
       <c r="B1104" t="inlineStr">
         <is>
-          <t>01043560834</t>
+          <t>01063165271</t>
         </is>
       </c>
       <c r="C1104" t="inlineStr">
         <is>
-          <t>304072</t>
+          <t>273193</t>
         </is>
       </c>
       <c r="D1104" t="inlineStr">
         <is>
-          <t>Official SNS</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E1104" t="inlineStr">
         <is>
-          <t>EFW_04</t>
+          <t>LMS_ECOM_0410exclusive2</t>
         </is>
       </c>
     </row>
     <row r="1105">
       <c r="A1105" t="inlineStr">
         <is>
-          <t>tnwks1115</t>
+          <t>kk_3875113278</t>
         </is>
       </c>
       <c r="B1105" t="inlineStr">
         <is>
-          <t>01024221364</t>
+          <t>01099620269</t>
         </is>
       </c>
       <c r="C1105" t="inlineStr">
         <is>
-          <t>275948</t>
+          <t>266546</t>
         </is>
       </c>
       <c r="D1105" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E1105" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>lms_ecom_200416_family</t>
         </is>
       </c>
     </row>
@@ -30293,27 +30293,27 @@
     <row r="1107">
       <c r="A1107" t="inlineStr">
         <is>
-          <t>kk_3875113278</t>
+          <t>tnwks1115</t>
         </is>
       </c>
       <c r="B1107" t="inlineStr">
         <is>
-          <t>01099620269</t>
+          <t>01024221364</t>
         </is>
       </c>
       <c r="C1107" t="inlineStr">
         <is>
-          <t>266546</t>
+          <t>275948</t>
         </is>
       </c>
       <c r="D1107" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="E1107" t="inlineStr">
         <is>
-          <t>lms_ecom_200416_family</t>
+          <t>Direct</t>
         </is>
       </c>
     </row>
@@ -30347,98 +30347,98 @@
     <row r="1109">
       <c r="A1109" t="inlineStr">
         <is>
-          <t>kk_4218204827</t>
+          <t>mse001</t>
         </is>
       </c>
       <c r="B1109" t="inlineStr">
         <is>
-          <t>01023704903</t>
+          <t>01085185510</t>
         </is>
       </c>
       <c r="C1109" t="inlineStr">
         <is>
-          <t>272698</t>
+          <t>227227</t>
         </is>
       </c>
       <c r="D1109" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E1109" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>KAKAO_alimtalk</t>
         </is>
       </c>
     </row>
     <row r="1110">
       <c r="A1110" t="inlineStr">
         <is>
-          <t>mse001</t>
+          <t>kk_4218204827</t>
         </is>
       </c>
       <c r="B1110" t="inlineStr">
         <is>
-          <t>01085185510</t>
+          <t>01023704903</t>
         </is>
       </c>
       <c r="C1110" t="inlineStr">
         <is>
-          <t>227227</t>
+          <t>272698</t>
         </is>
       </c>
       <c r="D1110" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="E1110" t="inlineStr">
         <is>
-          <t>KAKAO_alimtalk</t>
+          <t>Direct</t>
         </is>
       </c>
     </row>
     <row r="1111">
       <c r="A1111" t="inlineStr">
         <is>
-          <t>quito3</t>
+          <t>aca1004</t>
         </is>
       </c>
       <c r="B1111" t="inlineStr">
         <is>
-          <t>01073440379</t>
+          <t>01071740430</t>
         </is>
       </c>
       <c r="C1111" t="inlineStr">
         <is>
-          <t>126578</t>
+          <t>171757</t>
         </is>
       </c>
       <c r="D1111" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E1111" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>KAKAO_alimtalk</t>
         </is>
       </c>
     </row>
     <row r="1112">
       <c r="A1112" t="inlineStr">
         <is>
-          <t>anfrorla</t>
+          <t>bluesea063</t>
         </is>
       </c>
       <c r="B1112" t="inlineStr">
         <is>
-          <t>01050991521</t>
+          <t>01032902625</t>
         </is>
       </c>
       <c r="C1112" t="inlineStr">
         <is>
-          <t>137379</t>
+          <t>116772</t>
         </is>
       </c>
       <c r="D1112" t="inlineStr">
@@ -30448,34 +30448,34 @@
       </c>
       <c r="E1112" t="inlineStr">
         <is>
-          <t>LMS_ECOM_200416_family</t>
+          <t>LMS_ECOM_0410exclusive2</t>
         </is>
       </c>
     </row>
     <row r="1113">
       <c r="A1113" t="inlineStr">
         <is>
-          <t>aca1004</t>
+          <t>quito3</t>
         </is>
       </c>
       <c r="B1113" t="inlineStr">
         <is>
-          <t>01071740430</t>
+          <t>01073440379</t>
         </is>
       </c>
       <c r="C1113" t="inlineStr">
         <is>
-          <t>171757</t>
+          <t>126578</t>
         </is>
       </c>
       <c r="D1113" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="E1113" t="inlineStr">
         <is>
-          <t>KAKAO_alimtalk</t>
+          <t>Direct</t>
         </is>
       </c>
     </row>
@@ -30509,17 +30509,17 @@
     <row r="1115">
       <c r="A1115" t="inlineStr">
         <is>
-          <t>bluesea063</t>
+          <t>anfrorla</t>
         </is>
       </c>
       <c r="B1115" t="inlineStr">
         <is>
-          <t>01032902625</t>
+          <t>01050991521</t>
         </is>
       </c>
       <c r="C1115" t="inlineStr">
         <is>
-          <t>116772</t>
+          <t>137379</t>
         </is>
       </c>
       <c r="D1115" t="inlineStr">
@@ -30529,7 +30529,7 @@
       </c>
       <c r="E1115" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0410exclusive2</t>
+          <t>LMS_ECOM_200416_family</t>
         </is>
       </c>
     </row>
@@ -30644,71 +30644,71 @@
     <row r="1120">
       <c r="A1120" t="inlineStr">
         <is>
-          <t>kk_4844817541</t>
+          <t>kk_2768186596</t>
         </is>
       </c>
       <c r="B1120" t="inlineStr">
         <is>
-          <t>01046631832</t>
+          <t>01029241198</t>
         </is>
       </c>
       <c r="C1120" t="inlineStr">
         <is>
-          <t>304380</t>
+          <t>208962</t>
         </is>
       </c>
       <c r="D1120" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E1120" t="inlineStr">
         <is>
-          <t>[PF]전환_회원가입(유사)</t>
+          <t>KAKAO_alimtalk</t>
         </is>
       </c>
     </row>
     <row r="1121">
       <c r="A1121" t="inlineStr">
         <is>
-          <t>kk_4375003446</t>
+          <t>kk_3169777000</t>
         </is>
       </c>
       <c r="B1121" t="inlineStr">
         <is>
-          <t>01087457282</t>
+          <t>01089348462</t>
         </is>
       </c>
       <c r="C1121" t="inlineStr">
         <is>
-          <t>280131</t>
+          <t>224876</t>
         </is>
       </c>
       <c r="D1121" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="E1121" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0410exclusive2</t>
+          <t>Direct</t>
         </is>
       </c>
     </row>
     <row r="1122">
       <c r="A1122" t="inlineStr">
         <is>
-          <t>kk_2768186596</t>
+          <t>kk_4375003446</t>
         </is>
       </c>
       <c r="B1122" t="inlineStr">
         <is>
-          <t>01029241198</t>
+          <t>01087457282</t>
         </is>
       </c>
       <c r="C1122" t="inlineStr">
         <is>
-          <t>208962</t>
+          <t>280131</t>
         </is>
       </c>
       <c r="D1122" t="inlineStr">
@@ -30718,51 +30718,51 @@
       </c>
       <c r="E1122" t="inlineStr">
         <is>
-          <t>KAKAO_alimtalk</t>
+          <t>LMS_ECOM_0410exclusive2</t>
         </is>
       </c>
     </row>
     <row r="1123">
       <c r="A1123" t="inlineStr">
         <is>
-          <t>kk_3169777000</t>
+          <t>kk_4844817541</t>
         </is>
       </c>
       <c r="B1123" t="inlineStr">
         <is>
-          <t>01089348462</t>
+          <t>01046631832</t>
         </is>
       </c>
       <c r="C1123" t="inlineStr">
         <is>
-          <t>224876</t>
+          <t>304380</t>
         </is>
       </c>
       <c r="D1123" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E1123" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>[PF]전환_회원가입(유사)</t>
         </is>
       </c>
     </row>
     <row r="1124">
       <c r="A1124" t="inlineStr">
         <is>
-          <t>kk_2768989214</t>
+          <t>kk_3444865211</t>
         </is>
       </c>
       <c r="B1124" t="inlineStr">
         <is>
-          <t>01095004289</t>
+          <t>01021964871</t>
         </is>
       </c>
       <c r="C1124" t="inlineStr">
         <is>
-          <t>209015</t>
+          <t>242799</t>
         </is>
       </c>
       <c r="D1124" t="inlineStr">
@@ -30779,108 +30779,108 @@
     <row r="1125">
       <c r="A1125" t="inlineStr">
         <is>
-          <t>ohsm0065</t>
+          <t>xuswldls</t>
         </is>
       </c>
       <c r="B1125" t="inlineStr">
         <is>
-          <t>01056170065</t>
+          <t>01027349414</t>
         </is>
       </c>
       <c r="C1125" t="inlineStr">
         <is>
-          <t>74567</t>
+          <t>133308</t>
         </is>
       </c>
       <c r="D1125" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="E1125" t="inlineStr">
         <is>
-          <t>[PF]트래픽_유사+관심사</t>
+          <t>Direct</t>
         </is>
       </c>
     </row>
     <row r="1126">
       <c r="A1126" t="inlineStr">
         <is>
-          <t>xuswldls</t>
+          <t>ohsm0065</t>
         </is>
       </c>
       <c r="B1126" t="inlineStr">
         <is>
-          <t>01027349414</t>
+          <t>01056170065</t>
         </is>
       </c>
       <c r="C1126" t="inlineStr">
         <is>
-          <t>133308</t>
+          <t>74567</t>
         </is>
       </c>
       <c r="D1126" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E1126" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>[PF]트래픽_유사+관심사</t>
         </is>
       </c>
     </row>
     <row r="1127">
       <c r="A1127" t="inlineStr">
         <is>
-          <t>kk_4247630261</t>
+          <t>kk_3688034999</t>
         </is>
       </c>
       <c r="B1127" t="inlineStr">
         <is>
-          <t>01091437323</t>
+          <t>01025408262</t>
         </is>
       </c>
       <c r="C1127" t="inlineStr">
         <is>
-          <t>274140</t>
+          <t>250755</t>
         </is>
       </c>
       <c r="D1127" t="inlineStr">
         <is>
-          <t>Organic Traffic</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E1127" t="inlineStr">
         <is>
-          <t>(referral)</t>
+          <t>KAKAO_alimtalk</t>
         </is>
       </c>
     </row>
     <row r="1128">
       <c r="A1128" t="inlineStr">
         <is>
-          <t>kk_4472536591</t>
+          <t>kk_4247630261</t>
         </is>
       </c>
       <c r="B1128" t="inlineStr">
         <is>
-          <t>01037057526</t>
+          <t>01091437323</t>
         </is>
       </c>
       <c r="C1128" t="inlineStr">
         <is>
-          <t>283897</t>
+          <t>274140</t>
         </is>
       </c>
       <c r="D1128" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Organic Traffic</t>
         </is>
       </c>
       <c r="E1128" t="inlineStr">
         <is>
-          <t>KAKAO_alimtalk</t>
+          <t>(referral)</t>
         </is>
       </c>
     </row>
@@ -30914,71 +30914,71 @@
     <row r="1130">
       <c r="A1130" t="inlineStr">
         <is>
-          <t>kk_3688034999</t>
+          <t>kk_2768989214</t>
         </is>
       </c>
       <c r="B1130" t="inlineStr">
         <is>
-          <t>01025408262</t>
+          <t>01095004289</t>
         </is>
       </c>
       <c r="C1130" t="inlineStr">
         <is>
-          <t>250755</t>
+          <t>209015</t>
         </is>
       </c>
       <c r="D1130" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="E1130" t="inlineStr">
         <is>
-          <t>KAKAO_alimtalk</t>
+          <t>Direct</t>
         </is>
       </c>
     </row>
     <row r="1131">
       <c r="A1131" t="inlineStr">
         <is>
-          <t>kk_3444865211</t>
+          <t>kk_4472536591</t>
         </is>
       </c>
       <c r="B1131" t="inlineStr">
         <is>
-          <t>01021964871</t>
+          <t>01037057526</t>
         </is>
       </c>
       <c r="C1131" t="inlineStr">
         <is>
-          <t>242799</t>
+          <t>283897</t>
         </is>
       </c>
       <c r="D1131" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E1131" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>KAKAO_alimtalk</t>
         </is>
       </c>
     </row>
     <row r="1132">
       <c r="A1132" t="inlineStr">
         <is>
-          <t>kk_3837527580</t>
+          <t>kk_3858585698</t>
         </is>
       </c>
       <c r="B1132" t="inlineStr">
         <is>
-          <t>01084311738</t>
+          <t>01092163429</t>
         </is>
       </c>
       <c r="C1132" t="inlineStr">
         <is>
-          <t>264113</t>
+          <t>265508</t>
         </is>
       </c>
       <c r="D1132" t="inlineStr">
@@ -30988,61 +30988,61 @@
       </c>
       <c r="E1132" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0410exclusive2</t>
+          <t>KAKAO_alimtalk</t>
         </is>
       </c>
     </row>
     <row r="1133">
       <c r="A1133" t="inlineStr">
         <is>
-          <t>escalater</t>
+          <t>kk_3837527580</t>
         </is>
       </c>
       <c r="B1133" t="inlineStr">
         <is>
-          <t>01090911461</t>
+          <t>01084311738</t>
         </is>
       </c>
       <c r="C1133" t="inlineStr">
         <is>
-          <t>240051</t>
+          <t>264113</t>
         </is>
       </c>
       <c r="D1133" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E1133" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>LMS_ECOM_0410exclusive2</t>
         </is>
       </c>
     </row>
     <row r="1134">
       <c r="A1134" t="inlineStr">
         <is>
-          <t>kk_3858585698</t>
+          <t>kk_3181917333</t>
         </is>
       </c>
       <c r="B1134" t="inlineStr">
         <is>
-          <t>01092163429</t>
+          <t>01072258509</t>
         </is>
       </c>
       <c r="C1134" t="inlineStr">
         <is>
-          <t>265508</t>
+          <t>227380</t>
         </is>
       </c>
       <c r="D1134" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="E1134" t="inlineStr">
         <is>
-          <t>KAKAO_alimtalk</t>
+          <t>Direct</t>
         </is>
       </c>
     </row>
@@ -31076,17 +31076,17 @@
     <row r="1136">
       <c r="A1136" t="inlineStr">
         <is>
-          <t>kk_3181917333</t>
+          <t>jobguidance</t>
         </is>
       </c>
       <c r="B1136" t="inlineStr">
         <is>
-          <t>01072258509</t>
+          <t>01026756920</t>
         </is>
       </c>
       <c r="C1136" t="inlineStr">
         <is>
-          <t>227380</t>
+          <t>134664</t>
         </is>
       </c>
       <c r="D1136" t="inlineStr">
@@ -31103,17 +31103,17 @@
     <row r="1137">
       <c r="A1137" t="inlineStr">
         <is>
-          <t>jobguidance</t>
+          <t>escalater</t>
         </is>
       </c>
       <c r="B1137" t="inlineStr">
         <is>
-          <t>01026756920</t>
+          <t>01090911461</t>
         </is>
       </c>
       <c r="C1137" t="inlineStr">
         <is>
-          <t>134664</t>
+          <t>240051</t>
         </is>
       </c>
       <c r="D1137" t="inlineStr">
@@ -31130,44 +31130,44 @@
     <row r="1138">
       <c r="A1138" t="inlineStr">
         <is>
-          <t>kk_4338209948</t>
+          <t>kk_4840061178</t>
         </is>
       </c>
       <c r="B1138" t="inlineStr">
         <is>
-          <t>01088132379</t>
+          <t>01082357895</t>
         </is>
       </c>
       <c r="C1138" t="inlineStr">
         <is>
-          <t>278781</t>
+          <t>304124</t>
         </is>
       </c>
       <c r="D1138" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Awareness</t>
         </is>
       </c>
       <c r="E1138" t="inlineStr">
         <is>
-          <t>KAKAO_alimtalk</t>
+          <t>benz_running_program_2026_coupon</t>
         </is>
       </c>
     </row>
     <row r="1139">
       <c r="A1139" t="inlineStr">
         <is>
-          <t>kk_4523594127</t>
+          <t>kk_2940110361</t>
         </is>
       </c>
       <c r="B1139" t="inlineStr">
         <is>
-          <t>01085735215</t>
+          <t>01035353200</t>
         </is>
       </c>
       <c r="C1139" t="inlineStr">
         <is>
-          <t>286358</t>
+          <t>216362</t>
         </is>
       </c>
       <c r="D1139" t="inlineStr">
@@ -31184,17 +31184,17 @@
     <row r="1140">
       <c r="A1140" t="inlineStr">
         <is>
-          <t>aya6969</t>
+          <t>hursean</t>
         </is>
       </c>
       <c r="B1140" t="inlineStr">
         <is>
-          <t>01076590009</t>
+          <t>01091975738</t>
         </is>
       </c>
       <c r="C1140" t="inlineStr">
         <is>
-          <t>162562</t>
+          <t>123130</t>
         </is>
       </c>
       <c r="D1140" t="inlineStr">
@@ -31204,24 +31204,24 @@
       </c>
       <c r="E1140" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0410exclusive2</t>
+          <t>Email_mkt</t>
         </is>
       </c>
     </row>
     <row r="1141">
       <c r="A1141" t="inlineStr">
         <is>
-          <t>seul6169</t>
+          <t>aya6969</t>
         </is>
       </c>
       <c r="B1141" t="inlineStr">
         <is>
-          <t>01066116699</t>
+          <t>01076590009</t>
         </is>
       </c>
       <c r="C1141" t="inlineStr">
         <is>
-          <t>234239</t>
+          <t>162562</t>
         </is>
       </c>
       <c r="D1141" t="inlineStr">
@@ -31231,24 +31231,24 @@
       </c>
       <c r="E1141" t="inlineStr">
         <is>
-          <t>KAKAO_alimtalk</t>
+          <t>LMS_ECOM_0410exclusive2</t>
         </is>
       </c>
     </row>
     <row r="1142">
       <c r="A1142" t="inlineStr">
         <is>
-          <t>kk_4467707148</t>
+          <t>kk_4523594127</t>
         </is>
       </c>
       <c r="B1142" t="inlineStr">
         <is>
-          <t>01030843332</t>
+          <t>01085735215</t>
         </is>
       </c>
       <c r="C1142" t="inlineStr">
         <is>
-          <t>283560</t>
+          <t>286358</t>
         </is>
       </c>
       <c r="D1142" t="inlineStr">
@@ -31265,27 +31265,27 @@
     <row r="1143">
       <c r="A1143" t="inlineStr">
         <is>
-          <t>kk_3013902343</t>
+          <t>mansoogi</t>
         </is>
       </c>
       <c r="B1143" t="inlineStr">
         <is>
-          <t>01051802326</t>
+          <t>01093240897</t>
         </is>
       </c>
       <c r="C1143" t="inlineStr">
         <is>
-          <t>219219</t>
+          <t>25243</t>
         </is>
       </c>
       <c r="D1143" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E1143" t="inlineStr">
         <is>
-          <t>6968489536332</t>
+          <t>LMS_ECOM_0410exclusive2</t>
         </is>
       </c>
     </row>
@@ -31319,17 +31319,17 @@
     <row r="1145">
       <c r="A1145" t="inlineStr">
         <is>
-          <t>mansoogi</t>
+          <t>kk_4467707148</t>
         </is>
       </c>
       <c r="B1145" t="inlineStr">
         <is>
-          <t>01093240897</t>
+          <t>01030843332</t>
         </is>
       </c>
       <c r="C1145" t="inlineStr">
         <is>
-          <t>25243</t>
+          <t>283560</t>
         </is>
       </c>
       <c r="D1145" t="inlineStr">
@@ -31346,17 +31346,17 @@
     <row r="1146">
       <c r="A1146" t="inlineStr">
         <is>
-          <t>hursean</t>
+          <t>seul6169</t>
         </is>
       </c>
       <c r="B1146" t="inlineStr">
         <is>
-          <t>01091975738</t>
+          <t>01066116699</t>
         </is>
       </c>
       <c r="C1146" t="inlineStr">
         <is>
-          <t>123130</t>
+          <t>234239</t>
         </is>
       </c>
       <c r="D1146" t="inlineStr">
@@ -31366,24 +31366,24 @@
       </c>
       <c r="E1146" t="inlineStr">
         <is>
-          <t>Email_mkt</t>
+          <t>KAKAO_alimtalk</t>
         </is>
       </c>
     </row>
     <row r="1147">
       <c r="A1147" t="inlineStr">
         <is>
-          <t>kk_2940110361</t>
+          <t>kk_4338209948</t>
         </is>
       </c>
       <c r="B1147" t="inlineStr">
         <is>
-          <t>01035353200</t>
+          <t>01088132379</t>
         </is>
       </c>
       <c r="C1147" t="inlineStr">
         <is>
-          <t>216362</t>
+          <t>278781</t>
         </is>
       </c>
       <c r="D1147" t="inlineStr">
@@ -31393,61 +31393,61 @@
       </c>
       <c r="E1147" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0410exclusive2</t>
+          <t>KAKAO_alimtalk</t>
         </is>
       </c>
     </row>
     <row r="1148">
       <c r="A1148" t="inlineStr">
         <is>
-          <t>kk_3185867832</t>
+          <t>kk_3013902343</t>
         </is>
       </c>
       <c r="B1148" t="inlineStr">
         <is>
-          <t>01022086508</t>
+          <t>01051802326</t>
         </is>
       </c>
       <c r="C1148" t="inlineStr">
         <is>
-          <t>229863</t>
+          <t>219219</t>
         </is>
       </c>
       <c r="D1148" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E1148" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0410exclusive2</t>
+          <t>6968489536332</t>
         </is>
       </c>
     </row>
     <row r="1149">
       <c r="A1149" t="inlineStr">
         <is>
-          <t>kk_4840061178</t>
+          <t>kk_3185867832</t>
         </is>
       </c>
       <c r="B1149" t="inlineStr">
         <is>
-          <t>01082357895</t>
+          <t>01022086508</t>
         </is>
       </c>
       <c r="C1149" t="inlineStr">
         <is>
-          <t>304124</t>
+          <t>229863</t>
         </is>
       </c>
       <c r="D1149" t="inlineStr">
         <is>
-          <t>Awareness</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E1149" t="inlineStr">
         <is>
-          <t>benz_running_program_2026_coupon</t>
+          <t>LMS_ECOM_0410exclusive2</t>
         </is>
       </c>
     </row>
@@ -31508,17 +31508,17 @@
     <row r="1152">
       <c r="A1152" t="inlineStr">
         <is>
-          <t>kk_3296362697</t>
+          <t>kk_4608940431</t>
         </is>
       </c>
       <c r="B1152" t="inlineStr">
         <is>
-          <t>01032224185</t>
+          <t>01034834753</t>
         </is>
       </c>
       <c r="C1152" t="inlineStr">
         <is>
-          <t>237406</t>
+          <t>289885</t>
         </is>
       </c>
       <c r="D1152" t="inlineStr">
@@ -31535,17 +31535,17 @@
     <row r="1153">
       <c r="A1153" t="inlineStr">
         <is>
-          <t>kk_4608940431</t>
+          <t>taebaekcc</t>
         </is>
       </c>
       <c r="B1153" t="inlineStr">
         <is>
-          <t>01034834753</t>
+          <t>01090034620</t>
         </is>
       </c>
       <c r="C1153" t="inlineStr">
         <is>
-          <t>289885</t>
+          <t>182329</t>
         </is>
       </c>
       <c r="D1153" t="inlineStr">
@@ -31562,44 +31562,44 @@
     <row r="1154">
       <c r="A1154" t="inlineStr">
         <is>
-          <t>kk_3114284664</t>
+          <t>kk_3927027066</t>
         </is>
       </c>
       <c r="B1154" t="inlineStr">
         <is>
-          <t>01031259752</t>
+          <t>01046272823</t>
         </is>
       </c>
       <c r="C1154" t="inlineStr">
         <is>
-          <t>222243</t>
+          <t>268818</t>
         </is>
       </c>
       <c r="D1154" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E1154" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>LMS_ECOM_200416_family</t>
         </is>
       </c>
     </row>
     <row r="1155">
       <c r="A1155" t="inlineStr">
         <is>
-          <t>kk_3801403661</t>
+          <t>kk_3378895949</t>
         </is>
       </c>
       <c r="B1155" t="inlineStr">
         <is>
-          <t>01086386165</t>
+          <t>01040411704</t>
         </is>
       </c>
       <c r="C1155" t="inlineStr">
         <is>
-          <t>259058</t>
+          <t>240461</t>
         </is>
       </c>
       <c r="D1155" t="inlineStr">
@@ -31643,17 +31643,17 @@
     <row r="1157">
       <c r="A1157" t="inlineStr">
         <is>
-          <t>taebaekcc</t>
+          <t>kycho229</t>
         </is>
       </c>
       <c r="B1157" t="inlineStr">
         <is>
-          <t>01090034620</t>
+          <t>01047322138</t>
         </is>
       </c>
       <c r="C1157" t="inlineStr">
         <is>
-          <t>182329</t>
+          <t>22747</t>
         </is>
       </c>
       <c r="D1157" t="inlineStr">
@@ -31663,24 +31663,24 @@
       </c>
       <c r="E1157" t="inlineStr">
         <is>
-          <t>LMS_ECOM_200416_family</t>
+          <t>EDM_0416</t>
         </is>
       </c>
     </row>
     <row r="1158">
       <c r="A1158" t="inlineStr">
         <is>
-          <t>kk_3378895949</t>
+          <t>kk_3654717861</t>
         </is>
       </c>
       <c r="B1158" t="inlineStr">
         <is>
-          <t>01040411704</t>
+          <t>01022661489</t>
         </is>
       </c>
       <c r="C1158" t="inlineStr">
         <is>
-          <t>240461</t>
+          <t>249347</t>
         </is>
       </c>
       <c r="D1158" t="inlineStr">
@@ -31690,24 +31690,24 @@
       </c>
       <c r="E1158" t="inlineStr">
         <is>
-          <t>LMS_ECOM_200416_family</t>
+          <t>KAKAO_alimtalk</t>
         </is>
       </c>
     </row>
     <row r="1159">
       <c r="A1159" t="inlineStr">
         <is>
-          <t>kk_3927027066</t>
+          <t>kk_3801403661</t>
         </is>
       </c>
       <c r="B1159" t="inlineStr">
         <is>
-          <t>01046272823</t>
+          <t>01086386165</t>
         </is>
       </c>
       <c r="C1159" t="inlineStr">
         <is>
-          <t>268818</t>
+          <t>259058</t>
         </is>
       </c>
       <c r="D1159" t="inlineStr">
@@ -31724,44 +31724,44 @@
     <row r="1160">
       <c r="A1160" t="inlineStr">
         <is>
-          <t>kycho229</t>
+          <t>kk_3114284664</t>
         </is>
       </c>
       <c r="B1160" t="inlineStr">
         <is>
-          <t>01047322138</t>
+          <t>01031259752</t>
         </is>
       </c>
       <c r="C1160" t="inlineStr">
         <is>
-          <t>22747</t>
+          <t>222243</t>
         </is>
       </c>
       <c r="D1160" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="E1160" t="inlineStr">
         <is>
-          <t>EDM_0416</t>
+          <t>Direct</t>
         </is>
       </c>
     </row>
     <row r="1161">
       <c r="A1161" t="inlineStr">
         <is>
-          <t>kk_4358499671</t>
+          <t>kk_3296362697</t>
         </is>
       </c>
       <c r="B1161" t="inlineStr">
         <is>
-          <t>01066507573</t>
+          <t>01032224185</t>
         </is>
       </c>
       <c r="C1161" t="inlineStr">
         <is>
-          <t>279591</t>
+          <t>237406</t>
         </is>
       </c>
       <c r="D1161" t="inlineStr">
@@ -31778,17 +31778,17 @@
     <row r="1162">
       <c r="A1162" t="inlineStr">
         <is>
-          <t>kk_3654717861</t>
+          <t>kk_4358499671</t>
         </is>
       </c>
       <c r="B1162" t="inlineStr">
         <is>
-          <t>01022661489</t>
+          <t>01066507573</t>
         </is>
       </c>
       <c r="C1162" t="inlineStr">
         <is>
-          <t>249347</t>
+          <t>279591</t>
         </is>
       </c>
       <c r="D1162" t="inlineStr">
@@ -31798,7 +31798,7 @@
       </c>
       <c r="E1162" t="inlineStr">
         <is>
-          <t>KAKAO_alimtalk</t>
+          <t>LMS_ECOM_200416_family</t>
         </is>
       </c>
     </row>
@@ -31859,71 +31859,71 @@
     <row r="1165">
       <c r="A1165" t="inlineStr">
         <is>
-          <t>pentagram</t>
+          <t>kk_2807863527</t>
         </is>
       </c>
       <c r="B1165" t="inlineStr">
         <is>
-          <t>01093327353</t>
+          <t>01042669625</t>
         </is>
       </c>
       <c r="C1165" t="inlineStr">
         <is>
-          <t>131085</t>
+          <t>211605</t>
         </is>
       </c>
       <c r="D1165" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E1165" t="inlineStr">
         <is>
-          <t>KAKAO_alimtalk</t>
+          <t>[PF]전환_회원가입(유사)</t>
         </is>
       </c>
     </row>
     <row r="1166">
       <c r="A1166" t="inlineStr">
         <is>
-          <t>dltndgy99</t>
+          <t>pentagram</t>
         </is>
       </c>
       <c r="B1166" t="inlineStr">
         <is>
-          <t>01024587982</t>
+          <t>01093327353</t>
         </is>
       </c>
       <c r="C1166" t="inlineStr">
         <is>
-          <t>156217</t>
+          <t>131085</t>
         </is>
       </c>
       <c r="D1166" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E1166" t="inlineStr">
         <is>
-          <t>naver_brandsearch_mobile</t>
+          <t>KAKAO_alimtalk</t>
         </is>
       </c>
     </row>
     <row r="1167">
       <c r="A1167" t="inlineStr">
         <is>
-          <t>kk_2807863527</t>
+          <t>dltndgy99</t>
         </is>
       </c>
       <c r="B1167" t="inlineStr">
         <is>
-          <t>01042669625</t>
+          <t>01024587982</t>
         </is>
       </c>
       <c r="C1167" t="inlineStr">
         <is>
-          <t>211605</t>
+          <t>156217</t>
         </is>
       </c>
       <c r="D1167" t="inlineStr">
@@ -31933,7 +31933,7 @@
       </c>
       <c r="E1167" t="inlineStr">
         <is>
-          <t>[PF]전환_회원가입(유사)</t>
+          <t>naver_brandsearch_mobile</t>
         </is>
       </c>
     </row>
@@ -32102,44 +32102,44 @@
     <row r="1174">
       <c r="A1174" t="inlineStr">
         <is>
-          <t>kk_2825715315</t>
+          <t>kk_4292190414</t>
         </is>
       </c>
       <c r="B1174" t="inlineStr">
         <is>
-          <t>01077229654</t>
+          <t>01095177478</t>
         </is>
       </c>
       <c r="C1174" t="inlineStr">
         <is>
-          <t>212719</t>
+          <t>275998</t>
         </is>
       </c>
       <c r="D1174" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="E1174" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0410exclusive2</t>
+          <t>Direct</t>
         </is>
       </c>
     </row>
     <row r="1175">
       <c r="A1175" t="inlineStr">
         <is>
-          <t>kk_3754052831</t>
+          <t>kk_3349199057</t>
         </is>
       </c>
       <c r="B1175" t="inlineStr">
         <is>
-          <t>01092180804</t>
+          <t>01071630312</t>
         </is>
       </c>
       <c r="C1175" t="inlineStr">
         <is>
-          <t>254339</t>
+          <t>239388</t>
         </is>
       </c>
       <c r="D1175" t="inlineStr">
@@ -32156,17 +32156,17 @@
     <row r="1176">
       <c r="A1176" t="inlineStr">
         <is>
-          <t>bobjazz</t>
+          <t>kk_3180736217</t>
         </is>
       </c>
       <c r="B1176" t="inlineStr">
         <is>
-          <t>01084090677</t>
+          <t>01036000343</t>
         </is>
       </c>
       <c r="C1176" t="inlineStr">
         <is>
-          <t>186218</t>
+          <t>226314</t>
         </is>
       </c>
       <c r="D1176" t="inlineStr">
@@ -32183,44 +32183,44 @@
     <row r="1177">
       <c r="A1177" t="inlineStr">
         <is>
-          <t>columbia7</t>
+          <t>camiblanco</t>
         </is>
       </c>
       <c r="B1177" t="inlineStr">
         <is>
-          <t>01050080025</t>
+          <t>01072190103</t>
         </is>
       </c>
       <c r="C1177" t="inlineStr">
         <is>
-          <t>109980</t>
+          <t>232545</t>
         </is>
       </c>
       <c r="D1177" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="E1177" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0410exclusive2</t>
+          <t>Direct</t>
         </is>
       </c>
     </row>
     <row r="1178">
       <c r="A1178" t="inlineStr">
         <is>
-          <t>dmsql785612</t>
+          <t>bobjazz</t>
         </is>
       </c>
       <c r="B1178" t="inlineStr">
         <is>
-          <t>01051590364</t>
+          <t>01084090677</t>
         </is>
       </c>
       <c r="C1178" t="inlineStr">
         <is>
-          <t>137279</t>
+          <t>186218</t>
         </is>
       </c>
       <c r="D1178" t="inlineStr">
@@ -32230,24 +32230,24 @@
       </c>
       <c r="E1178" t="inlineStr">
         <is>
-          <t>Email_mkt</t>
+          <t>LMS_ECOM_0410exclusive2</t>
         </is>
       </c>
     </row>
     <row r="1179">
       <c r="A1179" t="inlineStr">
         <is>
-          <t>kk_4452401577</t>
+          <t>columbia7</t>
         </is>
       </c>
       <c r="B1179" t="inlineStr">
         <is>
-          <t>01047428000</t>
+          <t>01050080025</t>
         </is>
       </c>
       <c r="C1179" t="inlineStr">
         <is>
-          <t>282525</t>
+          <t>109980</t>
         </is>
       </c>
       <c r="D1179" t="inlineStr">
@@ -32264,98 +32264,98 @@
     <row r="1180">
       <c r="A1180" t="inlineStr">
         <is>
-          <t>kk_4292190414</t>
+          <t>pls4u</t>
         </is>
       </c>
       <c r="B1180" t="inlineStr">
         <is>
-          <t>01095177478</t>
+          <t>01085985482</t>
         </is>
       </c>
       <c r="C1180" t="inlineStr">
         <is>
-          <t>275998</t>
+          <t>88257</t>
         </is>
       </c>
       <c r="D1180" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E1180" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>LMS_ECOM_0401_trailrunning</t>
         </is>
       </c>
     </row>
     <row r="1181">
       <c r="A1181" t="inlineStr">
         <is>
-          <t>kk_3721447783</t>
+          <t>kk_4525043459</t>
         </is>
       </c>
       <c r="B1181" t="inlineStr">
         <is>
-          <t>01051311087</t>
+          <t>01088312135</t>
         </is>
       </c>
       <c r="C1181" t="inlineStr">
         <is>
-          <t>252252</t>
+          <t>286464</t>
         </is>
       </c>
       <c r="D1181" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E1181" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>LMS_ECOM_0410exclusive2</t>
         </is>
       </c>
     </row>
     <row r="1182">
       <c r="A1182" t="inlineStr">
         <is>
-          <t>camiblanco</t>
+          <t>dmsql785612</t>
         </is>
       </c>
       <c r="B1182" t="inlineStr">
         <is>
-          <t>01072190103</t>
+          <t>01051590364</t>
         </is>
       </c>
       <c r="C1182" t="inlineStr">
         <is>
-          <t>232545</t>
+          <t>137279</t>
         </is>
       </c>
       <c r="D1182" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E1182" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>Email_mkt</t>
         </is>
       </c>
     </row>
     <row r="1183">
       <c r="A1183" t="inlineStr">
         <is>
-          <t>kk_3349199057</t>
+          <t>sjm700</t>
         </is>
       </c>
       <c r="B1183" t="inlineStr">
         <is>
-          <t>01071630312</t>
+          <t>01077331591</t>
         </is>
       </c>
       <c r="C1183" t="inlineStr">
         <is>
-          <t>239388</t>
+          <t>118769</t>
         </is>
       </c>
       <c r="D1183" t="inlineStr">
@@ -32372,17 +32372,17 @@
     <row r="1184">
       <c r="A1184" t="inlineStr">
         <is>
-          <t>kk_3180736217</t>
+          <t>kk_4452401577</t>
         </is>
       </c>
       <c r="B1184" t="inlineStr">
         <is>
-          <t>01036000343</t>
+          <t>01047428000</t>
         </is>
       </c>
       <c r="C1184" t="inlineStr">
         <is>
-          <t>226314</t>
+          <t>282525</t>
         </is>
       </c>
       <c r="D1184" t="inlineStr">
@@ -32399,17 +32399,17 @@
     <row r="1185">
       <c r="A1185" t="inlineStr">
         <is>
-          <t>kk_3973703558</t>
+          <t>inu21c</t>
         </is>
       </c>
       <c r="B1185" t="inlineStr">
         <is>
-          <t>01048590748</t>
+          <t>01035128236</t>
         </is>
       </c>
       <c r="C1185" t="inlineStr">
         <is>
-          <t>271020</t>
+          <t>131940</t>
         </is>
       </c>
       <c r="D1185" t="inlineStr">
@@ -32426,71 +32426,71 @@
     <row r="1186">
       <c r="A1186" t="inlineStr">
         <is>
-          <t>yongshin</t>
+          <t>kk_3754052831</t>
         </is>
       </c>
       <c r="B1186" t="inlineStr">
         <is>
-          <t>01053867821</t>
+          <t>01092180804</t>
         </is>
       </c>
       <c r="C1186" t="inlineStr">
         <is>
-          <t>277896</t>
+          <t>254339</t>
         </is>
       </c>
       <c r="D1186" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E1186" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>LMS_ECOM_0410exclusive2</t>
         </is>
       </c>
     </row>
     <row r="1187">
       <c r="A1187" t="inlineStr">
         <is>
-          <t>pls4u</t>
+          <t>kk_3721447783</t>
         </is>
       </c>
       <c r="B1187" t="inlineStr">
         <is>
-          <t>01085985482</t>
+          <t>01051311087</t>
         </is>
       </c>
       <c r="C1187" t="inlineStr">
         <is>
-          <t>88257</t>
+          <t>252252</t>
         </is>
       </c>
       <c r="D1187" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="E1187" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0401_trailrunning</t>
+          <t>Direct</t>
         </is>
       </c>
     </row>
     <row r="1188">
       <c r="A1188" t="inlineStr">
         <is>
-          <t>inu21c</t>
+          <t>kk_3973703558</t>
         </is>
       </c>
       <c r="B1188" t="inlineStr">
         <is>
-          <t>01035128236</t>
+          <t>01048590748</t>
         </is>
       </c>
       <c r="C1188" t="inlineStr">
         <is>
-          <t>131940</t>
+          <t>271020</t>
         </is>
       </c>
       <c r="D1188" t="inlineStr">
@@ -32507,17 +32507,17 @@
     <row r="1189">
       <c r="A1189" t="inlineStr">
         <is>
-          <t>sjm700</t>
+          <t>kk_2825715315</t>
         </is>
       </c>
       <c r="B1189" t="inlineStr">
         <is>
-          <t>01077331591</t>
+          <t>01077229654</t>
         </is>
       </c>
       <c r="C1189" t="inlineStr">
         <is>
-          <t>118769</t>
+          <t>212719</t>
         </is>
       </c>
       <c r="D1189" t="inlineStr">
@@ -32534,27 +32534,27 @@
     <row r="1190">
       <c r="A1190" t="inlineStr">
         <is>
-          <t>kk_4525043459</t>
+          <t>yongshin</t>
         </is>
       </c>
       <c r="B1190" t="inlineStr">
         <is>
-          <t>01088312135</t>
+          <t>01053867821</t>
         </is>
       </c>
       <c r="C1190" t="inlineStr">
         <is>
-          <t>286464</t>
+          <t>277896</t>
         </is>
       </c>
       <c r="D1190" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="E1190" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0410exclusive2</t>
+          <t>Direct</t>
         </is>
       </c>
     </row>
@@ -32588,17 +32588,17 @@
     <row r="1192">
       <c r="A1192" t="inlineStr">
         <is>
-          <t>sh5204</t>
+          <t>olive888888</t>
         </is>
       </c>
       <c r="B1192" t="inlineStr">
         <is>
-          <t>01054433018</t>
+          <t>01029817882</t>
         </is>
       </c>
       <c r="C1192" t="inlineStr">
         <is>
-          <t>263137</t>
+          <t>116464</t>
         </is>
       </c>
       <c r="D1192" t="inlineStr">
@@ -32615,17 +32615,17 @@
     <row r="1193">
       <c r="A1193" t="inlineStr">
         <is>
-          <t>tayfun</t>
+          <t>sh5204</t>
         </is>
       </c>
       <c r="B1193" t="inlineStr">
         <is>
-          <t>01083105230</t>
+          <t>01054433018</t>
         </is>
       </c>
       <c r="C1193" t="inlineStr">
         <is>
-          <t>286336</t>
+          <t>263137</t>
         </is>
       </c>
       <c r="D1193" t="inlineStr">
@@ -32642,17 +32642,17 @@
     <row r="1194">
       <c r="A1194" t="inlineStr">
         <is>
-          <t>kairos93</t>
+          <t>tayfun</t>
         </is>
       </c>
       <c r="B1194" t="inlineStr">
         <is>
-          <t>01051079223</t>
+          <t>01083105230</t>
         </is>
       </c>
       <c r="C1194" t="inlineStr">
         <is>
-          <t>160644</t>
+          <t>286336</t>
         </is>
       </c>
       <c r="D1194" t="inlineStr">
@@ -32669,17 +32669,17 @@
     <row r="1195">
       <c r="A1195" t="inlineStr">
         <is>
-          <t>coda1202</t>
+          <t>kairos93</t>
         </is>
       </c>
       <c r="B1195" t="inlineStr">
         <is>
-          <t>01037655629</t>
+          <t>01051079223</t>
         </is>
       </c>
       <c r="C1195" t="inlineStr">
         <is>
-          <t>117064</t>
+          <t>160644</t>
         </is>
       </c>
       <c r="D1195" t="inlineStr">
@@ -32696,17 +32696,17 @@
     <row r="1196">
       <c r="A1196" t="inlineStr">
         <is>
-          <t>olive888888</t>
+          <t>coda1202</t>
         </is>
       </c>
       <c r="B1196" t="inlineStr">
         <is>
-          <t>01029817882</t>
+          <t>01037655629</t>
         </is>
       </c>
       <c r="C1196" t="inlineStr">
         <is>
-          <t>116464</t>
+          <t>117064</t>
         </is>
       </c>
       <c r="D1196" t="inlineStr">
@@ -32723,17 +32723,17 @@
     <row r="1197">
       <c r="A1197" t="inlineStr">
         <is>
-          <t>happy201106</t>
+          <t>alcoholpower</t>
         </is>
       </c>
       <c r="B1197" t="inlineStr">
         <is>
-          <t>01090012622</t>
+          <t>01027629868</t>
         </is>
       </c>
       <c r="C1197" t="inlineStr">
         <is>
-          <t>136050</t>
+          <t>252954</t>
         </is>
       </c>
       <c r="D1197" t="inlineStr">
@@ -32750,17 +32750,17 @@
     <row r="1198">
       <c r="A1198" t="inlineStr">
         <is>
-          <t>alcoholpower</t>
+          <t>kimms66</t>
         </is>
       </c>
       <c r="B1198" t="inlineStr">
         <is>
-          <t>01027629868</t>
+          <t>01057634626</t>
         </is>
       </c>
       <c r="C1198" t="inlineStr">
         <is>
-          <t>252954</t>
+          <t>180321</t>
         </is>
       </c>
       <c r="D1198" t="inlineStr">
@@ -32777,17 +32777,17 @@
     <row r="1199">
       <c r="A1199" t="inlineStr">
         <is>
-          <t>kimms66</t>
+          <t>happy201106</t>
         </is>
       </c>
       <c r="B1199" t="inlineStr">
         <is>
-          <t>01057634626</t>
+          <t>01090012622</t>
         </is>
       </c>
       <c r="C1199" t="inlineStr">
         <is>
-          <t>180321</t>
+          <t>136050</t>
         </is>
       </c>
       <c r="D1199" t="inlineStr">

--- a/reports/member_funnel/downloads/member_funnel_7d_non_buyer.xlsx
+++ b/reports/member_funnel/downloads/member_funnel_7d_non_buyer.xlsx
@@ -13040,54 +13040,54 @@
     <row r="468">
       <c r="A468" t="inlineStr">
         <is>
-          <t>kk_4839170665</t>
+          <t>kwon9493</t>
         </is>
       </c>
       <c r="B468" t="inlineStr">
         <is>
-          <t>01050116666</t>
+          <t>01035589493</t>
         </is>
       </c>
       <c r="C468" t="inlineStr">
         <is>
-          <t>304086</t>
+          <t>107077</t>
         </is>
       </c>
       <c r="D468" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="E468" t="inlineStr">
         <is>
-          <t>EFW</t>
+          <t>Direct</t>
         </is>
       </c>
     </row>
     <row r="469">
       <c r="A469" t="inlineStr">
         <is>
-          <t>kwon9493</t>
+          <t>kk_4839170665</t>
         </is>
       </c>
       <c r="B469" t="inlineStr">
         <is>
-          <t>01035589493</t>
+          <t>01050116666</t>
         </is>
       </c>
       <c r="C469" t="inlineStr">
         <is>
-          <t>107077</t>
+          <t>304086</t>
         </is>
       </c>
       <c r="D469" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E469" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>EFW</t>
         </is>
       </c>
     </row>
@@ -17495,17 +17495,17 @@
     <row r="633">
       <c r="A633" t="inlineStr">
         <is>
-          <t>kk_4789688431</t>
+          <t>kk_3483300064</t>
         </is>
       </c>
       <c r="B633" t="inlineStr">
         <is>
-          <t>01099981265</t>
+          <t>01092213404</t>
         </is>
       </c>
       <c r="C633" t="inlineStr">
         <is>
-          <t>302023</t>
+          <t>244619</t>
         </is>
       </c>
       <c r="D633" t="inlineStr">
@@ -17515,24 +17515,24 @@
       </c>
       <c r="E633" t="inlineStr">
         <is>
-          <t>sa</t>
+          <t>naver_brandsearch_mobile</t>
         </is>
       </c>
     </row>
     <row r="634">
       <c r="A634" t="inlineStr">
         <is>
-          <t>kk_3483300064</t>
+          <t>kk_4789688431</t>
         </is>
       </c>
       <c r="B634" t="inlineStr">
         <is>
-          <t>01092213404</t>
+          <t>01099981265</t>
         </is>
       </c>
       <c r="C634" t="inlineStr">
         <is>
-          <t>244619</t>
+          <t>302023</t>
         </is>
       </c>
       <c r="D634" t="inlineStr">
@@ -17542,7 +17542,7 @@
       </c>
       <c r="E634" t="inlineStr">
         <is>
-          <t>naver_brandsearch_mobile</t>
+          <t>sa</t>
         </is>
       </c>
     </row>
@@ -17900,17 +17900,17 @@
     <row r="648">
       <c r="A648" t="inlineStr">
         <is>
-          <t>zizou95</t>
+          <t>kk_3185218103</t>
         </is>
       </c>
       <c r="B648" t="inlineStr">
         <is>
-          <t>01049139545</t>
+          <t>01023796438</t>
         </is>
       </c>
       <c r="C648" t="inlineStr">
         <is>
-          <t>176662</t>
+          <t>229444</t>
         </is>
       </c>
       <c r="D648" t="inlineStr">
@@ -17920,24 +17920,24 @@
       </c>
       <c r="E648" t="inlineStr">
         <is>
-          <t>LMS_ECOM_familycoupon</t>
+          <t>KAKAO_alimtalk</t>
         </is>
       </c>
     </row>
     <row r="649">
       <c r="A649" t="inlineStr">
         <is>
-          <t>kk_3185218103</t>
+          <t>zizou95</t>
         </is>
       </c>
       <c r="B649" t="inlineStr">
         <is>
-          <t>01023796438</t>
+          <t>01049139545</t>
         </is>
       </c>
       <c r="C649" t="inlineStr">
         <is>
-          <t>229444</t>
+          <t>176662</t>
         </is>
       </c>
       <c r="D649" t="inlineStr">
@@ -17947,7 +17947,7 @@
       </c>
       <c r="E649" t="inlineStr">
         <is>
-          <t>KAKAO_alimtalk</t>
+          <t>LMS_ECOM_familycoupon</t>
         </is>
       </c>
     </row>
@@ -19034,17 +19034,17 @@
     <row r="690">
       <c r="A690" t="inlineStr">
         <is>
-          <t>lamerkmk</t>
+          <t>shine310</t>
         </is>
       </c>
       <c r="B690" t="inlineStr">
         <is>
-          <t>01030658494</t>
+          <t>01030650847</t>
         </is>
       </c>
       <c r="C690" t="inlineStr">
         <is>
-          <t>167002</t>
+          <t>171606</t>
         </is>
       </c>
       <c r="D690" t="inlineStr">
@@ -19061,17 +19061,17 @@
     <row r="691">
       <c r="A691" t="inlineStr">
         <is>
-          <t>shine310</t>
+          <t>lamerkmk</t>
         </is>
       </c>
       <c r="B691" t="inlineStr">
         <is>
-          <t>01030650847</t>
+          <t>01030658494</t>
         </is>
       </c>
       <c r="C691" t="inlineStr">
         <is>
-          <t>171606</t>
+          <t>167002</t>
         </is>
       </c>
       <c r="D691" t="inlineStr">
@@ -19493,54 +19493,54 @@
     <row r="707">
       <c r="A707" t="inlineStr">
         <is>
-          <t>kk_4841965432</t>
+          <t>khkim6620</t>
         </is>
       </c>
       <c r="B707" t="inlineStr">
         <is>
-          <t>01032510712</t>
+          <t>01076876567</t>
         </is>
       </c>
       <c r="C707" t="inlineStr">
         <is>
-          <t>304213</t>
+          <t>105445</t>
         </is>
       </c>
       <c r="D707" t="inlineStr">
         <is>
-          <t>Organic Traffic</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E707" t="inlineStr">
         <is>
-          <t>(referral)</t>
+          <t>컬럼비아_DPA_240530</t>
         </is>
       </c>
     </row>
     <row r="708">
       <c r="A708" t="inlineStr">
         <is>
-          <t>khkim6620</t>
+          <t>kk_4841965432</t>
         </is>
       </c>
       <c r="B708" t="inlineStr">
         <is>
-          <t>01076876567</t>
+          <t>01032510712</t>
         </is>
       </c>
       <c r="C708" t="inlineStr">
         <is>
-          <t>105445</t>
+          <t>304213</t>
         </is>
       </c>
       <c r="D708" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Organic Traffic</t>
         </is>
       </c>
       <c r="E708" t="inlineStr">
         <is>
-          <t>컬럼비아_DPA_240530</t>
+          <t>(referral)</t>
         </is>
       </c>
     </row>
@@ -20141,17 +20141,17 @@
     <row r="731">
       <c r="A731" t="inlineStr">
         <is>
-          <t>kk_4840658838</t>
+          <t>kk_4840846776</t>
         </is>
       </c>
       <c r="B731" t="inlineStr">
         <is>
-          <t>01039292600</t>
+          <t>01055961435</t>
         </is>
       </c>
       <c r="C731" t="inlineStr">
         <is>
-          <t>304158</t>
+          <t>304170</t>
         </is>
       </c>
       <c r="D731" t="inlineStr">
@@ -20161,24 +20161,24 @@
       </c>
       <c r="E731" t="inlineStr">
         <is>
-          <t>EFW</t>
+          <t>[PF]전환_회원가입(유사)</t>
         </is>
       </c>
     </row>
     <row r="732">
       <c r="A732" t="inlineStr">
         <is>
-          <t>kk_4840846776</t>
+          <t>kk_4840658838</t>
         </is>
       </c>
       <c r="B732" t="inlineStr">
         <is>
-          <t>01055961435</t>
+          <t>01039292600</t>
         </is>
       </c>
       <c r="C732" t="inlineStr">
         <is>
-          <t>304170</t>
+          <t>304158</t>
         </is>
       </c>
       <c r="D732" t="inlineStr">
@@ -20188,7 +20188,7 @@
       </c>
       <c r="E732" t="inlineStr">
         <is>
-          <t>[PF]전환_회원가입(유사)</t>
+          <t>EFW</t>
         </is>
       </c>
     </row>
@@ -20276,17 +20276,17 @@
     <row r="736">
       <c r="A736" t="inlineStr">
         <is>
-          <t>martyj</t>
+          <t>k032010</t>
         </is>
       </c>
       <c r="B736" t="inlineStr">
         <is>
-          <t>01073535824</t>
+          <t>01090792133</t>
         </is>
       </c>
       <c r="C736" t="inlineStr">
         <is>
-          <t>194752</t>
+          <t>204481</t>
         </is>
       </c>
       <c r="D736" t="inlineStr">
@@ -20303,17 +20303,17 @@
     <row r="737">
       <c r="A737" t="inlineStr">
         <is>
-          <t>k032010</t>
+          <t>martyj</t>
         </is>
       </c>
       <c r="B737" t="inlineStr">
         <is>
-          <t>01090792133</t>
+          <t>01073535824</t>
         </is>
       </c>
       <c r="C737" t="inlineStr">
         <is>
-          <t>204481</t>
+          <t>194752</t>
         </is>
       </c>
       <c r="D737" t="inlineStr">
@@ -20384,54 +20384,54 @@
     <row r="740">
       <c r="A740" t="inlineStr">
         <is>
-          <t>ksh6980k</t>
+          <t>hope3250</t>
         </is>
       </c>
       <c r="B740" t="inlineStr">
         <is>
-          <t>01030966980</t>
+          <t>01099083899</t>
         </is>
       </c>
       <c r="C740" t="inlineStr">
         <is>
-          <t>89626</t>
+          <t>176683</t>
         </is>
       </c>
       <c r="D740" t="inlineStr">
         <is>
-          <t>Organic Traffic</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E740" t="inlineStr">
         <is>
-          <t>(organic)</t>
+          <t>LMS_ECOM_200416_family</t>
         </is>
       </c>
     </row>
     <row r="741">
       <c r="A741" t="inlineStr">
         <is>
-          <t>hope3250</t>
+          <t>ksh6980k</t>
         </is>
       </c>
       <c r="B741" t="inlineStr">
         <is>
-          <t>01099083899</t>
+          <t>01030966980</t>
         </is>
       </c>
       <c r="C741" t="inlineStr">
         <is>
-          <t>176683</t>
+          <t>89626</t>
         </is>
       </c>
       <c r="D741" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Organic Traffic</t>
         </is>
       </c>
       <c r="E741" t="inlineStr">
         <is>
-          <t>LMS_ECOM_200416_family</t>
+          <t>(organic)</t>
         </is>
       </c>
     </row>
@@ -20924,44 +20924,44 @@
     <row r="760">
       <c r="A760" t="inlineStr">
         <is>
-          <t>kk_2936953873</t>
+          <t>kk_4615020382</t>
         </is>
       </c>
       <c r="B760" t="inlineStr">
         <is>
-          <t>01098328667</t>
+          <t>01092438164</t>
         </is>
       </c>
       <c r="C760" t="inlineStr">
         <is>
-          <t>216255</t>
+          <t>290598</t>
         </is>
       </c>
       <c r="D760" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E760" t="inlineStr">
         <is>
-          <t>naver_brandsearch_mobile</t>
+          <t>LMS_ECOM_200416_family</t>
         </is>
       </c>
     </row>
     <row r="761">
       <c r="A761" t="inlineStr">
         <is>
-          <t>kk_4615020382</t>
+          <t>kk_3180181891</t>
         </is>
       </c>
       <c r="B761" t="inlineStr">
         <is>
-          <t>01092438164</t>
+          <t>01065587969</t>
         </is>
       </c>
       <c r="C761" t="inlineStr">
         <is>
-          <t>290598</t>
+          <t>225645</t>
         </is>
       </c>
       <c r="D761" t="inlineStr">
@@ -20978,27 +20978,27 @@
     <row r="762">
       <c r="A762" t="inlineStr">
         <is>
-          <t>kk_3180181891</t>
+          <t>kk_2936953873</t>
         </is>
       </c>
       <c r="B762" t="inlineStr">
         <is>
-          <t>01065587969</t>
+          <t>01098328667</t>
         </is>
       </c>
       <c r="C762" t="inlineStr">
         <is>
-          <t>225645</t>
+          <t>216255</t>
         </is>
       </c>
       <c r="D762" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E762" t="inlineStr">
         <is>
-          <t>LMS_ECOM_200416_family</t>
+          <t>naver_brandsearch_mobile</t>
         </is>
       </c>
     </row>
@@ -21518,54 +21518,54 @@
     <row r="782">
       <c r="A782" t="inlineStr">
         <is>
-          <t>kk_3224050214</t>
+          <t>jgj0503</t>
         </is>
       </c>
       <c r="B782" t="inlineStr">
         <is>
-          <t>01082488899</t>
+          <t>01063315178</t>
         </is>
       </c>
       <c r="C782" t="inlineStr">
         <is>
-          <t>232892</t>
+          <t>303605</t>
         </is>
       </c>
       <c r="D782" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E782" t="inlineStr">
         <is>
-          <t>KAKAO_alimtalk</t>
+          <t>6968489536332</t>
         </is>
       </c>
     </row>
     <row r="783">
       <c r="A783" t="inlineStr">
         <is>
-          <t>jgj0503</t>
+          <t>kk_3224050214</t>
         </is>
       </c>
       <c r="B783" t="inlineStr">
         <is>
-          <t>01063315178</t>
+          <t>01082488899</t>
         </is>
       </c>
       <c r="C783" t="inlineStr">
         <is>
-          <t>303605</t>
+          <t>232892</t>
         </is>
       </c>
       <c r="D783" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E783" t="inlineStr">
         <is>
-          <t>6968489536332</t>
+          <t>KAKAO_alimtalk</t>
         </is>
       </c>
     </row>
@@ -22085,17 +22085,17 @@
     <row r="803">
       <c r="A803" t="inlineStr">
         <is>
-          <t>kk_3101119679</t>
+          <t>hun7662</t>
         </is>
       </c>
       <c r="B803" t="inlineStr">
         <is>
-          <t>01093993852</t>
+          <t>01042311474</t>
         </is>
       </c>
       <c r="C803" t="inlineStr">
         <is>
-          <t>221630</t>
+          <t>172790</t>
         </is>
       </c>
       <c r="D803" t="inlineStr">
@@ -22112,17 +22112,17 @@
     <row r="804">
       <c r="A804" t="inlineStr">
         <is>
-          <t>hun7662</t>
+          <t>kk_3101119679</t>
         </is>
       </c>
       <c r="B804" t="inlineStr">
         <is>
-          <t>01042311474</t>
+          <t>01093993852</t>
         </is>
       </c>
       <c r="C804" t="inlineStr">
         <is>
-          <t>172790</t>
+          <t>221630</t>
         </is>
       </c>
       <c r="D804" t="inlineStr">
@@ -22382,17 +22382,17 @@
     <row r="814">
       <c r="A814" t="inlineStr">
         <is>
-          <t>houselong</t>
+          <t>kk_3870022897</t>
         </is>
       </c>
       <c r="B814" t="inlineStr">
         <is>
-          <t>01086426201</t>
+          <t>01022819808</t>
         </is>
       </c>
       <c r="C814" t="inlineStr">
         <is>
-          <t>122085</t>
+          <t>266218</t>
         </is>
       </c>
       <c r="D814" t="inlineStr">
@@ -22409,17 +22409,17 @@
     <row r="815">
       <c r="A815" t="inlineStr">
         <is>
-          <t>kk_3870022897</t>
+          <t>houselong</t>
         </is>
       </c>
       <c r="B815" t="inlineStr">
         <is>
-          <t>01022819808</t>
+          <t>01086426201</t>
         </is>
       </c>
       <c r="C815" t="inlineStr">
         <is>
-          <t>266218</t>
+          <t>122085</t>
         </is>
       </c>
       <c r="D815" t="inlineStr">
@@ -22490,54 +22490,54 @@
     <row r="818">
       <c r="A818" t="inlineStr">
         <is>
-          <t>sun1381</t>
+          <t>kk_4839145768</t>
         </is>
       </c>
       <c r="B818" t="inlineStr">
         <is>
-          <t>01037709416</t>
+          <t>01097367898</t>
         </is>
       </c>
       <c r="C818" t="inlineStr">
         <is>
-          <t>278160</t>
+          <t>304085</t>
         </is>
       </c>
       <c r="D818" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E818" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0410exclusive2</t>
+          <t>naver_brandsearch_pc</t>
         </is>
       </c>
     </row>
     <row r="819">
       <c r="A819" t="inlineStr">
         <is>
-          <t>kk_4839145768</t>
+          <t>sun1381</t>
         </is>
       </c>
       <c r="B819" t="inlineStr">
         <is>
-          <t>01097367898</t>
+          <t>01037709416</t>
         </is>
       </c>
       <c r="C819" t="inlineStr">
         <is>
-          <t>304085</t>
+          <t>278160</t>
         </is>
       </c>
       <c r="D819" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E819" t="inlineStr">
         <is>
-          <t>naver_brandsearch_pc</t>
+          <t>LMS_ECOM_0410exclusive2</t>
         </is>
       </c>
     </row>
@@ -22976,54 +22976,54 @@
     <row r="836">
       <c r="A836" t="inlineStr">
         <is>
-          <t>kk_2999650964</t>
+          <t>kk_3631606950</t>
         </is>
       </c>
       <c r="B836" t="inlineStr">
         <is>
-          <t>01073667501</t>
+          <t>01063256163</t>
         </is>
       </c>
       <c r="C836" t="inlineStr">
         <is>
-          <t>218535</t>
+          <t>248164</t>
         </is>
       </c>
       <c r="D836" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="E836" t="inlineStr">
         <is>
-          <t>bizboard</t>
+          <t>미분류</t>
         </is>
       </c>
     </row>
     <row r="837">
       <c r="A837" t="inlineStr">
         <is>
-          <t>kk_3631606950</t>
+          <t>kk_2999650964</t>
         </is>
       </c>
       <c r="B837" t="inlineStr">
         <is>
-          <t>01063256163</t>
+          <t>01073667501</t>
         </is>
       </c>
       <c r="C837" t="inlineStr">
         <is>
-          <t>248164</t>
+          <t>218535</t>
         </is>
       </c>
       <c r="D837" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E837" t="inlineStr">
         <is>
-          <t>미분류</t>
+          <t>bizboard</t>
         </is>
       </c>
     </row>
@@ -23543,44 +23543,44 @@
     <row r="857">
       <c r="A857" t="inlineStr">
         <is>
-          <t>athend</t>
+          <t>kk_4839680663</t>
         </is>
       </c>
       <c r="B857" t="inlineStr">
         <is>
-          <t>01041786462</t>
+          <t>01046429530</t>
         </is>
       </c>
       <c r="C857" t="inlineStr">
         <is>
-          <t>285491</t>
+          <t>304109</t>
         </is>
       </c>
       <c r="D857" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E857" t="inlineStr">
         <is>
-          <t>KAKAO_alimtalk</t>
+          <t>6968489536332</t>
         </is>
       </c>
     </row>
     <row r="858">
       <c r="A858" t="inlineStr">
         <is>
-          <t>kk_3392066640</t>
+          <t>athend</t>
         </is>
       </c>
       <c r="B858" t="inlineStr">
         <is>
-          <t>01065021283</t>
+          <t>01041786462</t>
         </is>
       </c>
       <c r="C858" t="inlineStr">
         <is>
-          <t>240983</t>
+          <t>285491</t>
         </is>
       </c>
       <c r="D858" t="inlineStr">
@@ -23590,24 +23590,24 @@
       </c>
       <c r="E858" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0410exclusive2</t>
+          <t>KAKAO_alimtalk</t>
         </is>
       </c>
     </row>
     <row r="859">
       <c r="A859" t="inlineStr">
         <is>
-          <t>kk_4839680663</t>
+          <t>kk_4639169718</t>
         </is>
       </c>
       <c r="B859" t="inlineStr">
         <is>
-          <t>01046429530</t>
+          <t>01041380770</t>
         </is>
       </c>
       <c r="C859" t="inlineStr">
         <is>
-          <t>304109</t>
+          <t>292319</t>
         </is>
       </c>
       <c r="D859" t="inlineStr">
@@ -23617,51 +23617,51 @@
       </c>
       <c r="E859" t="inlineStr">
         <is>
-          <t>6968489536332</t>
+          <t>naver_brandsearch_mobile</t>
         </is>
       </c>
     </row>
     <row r="860">
       <c r="A860" t="inlineStr">
         <is>
-          <t>kk_4639169718</t>
+          <t>kk_3392066640</t>
         </is>
       </c>
       <c r="B860" t="inlineStr">
         <is>
-          <t>01041380770</t>
+          <t>01065021283</t>
         </is>
       </c>
       <c r="C860" t="inlineStr">
         <is>
-          <t>292319</t>
+          <t>240983</t>
         </is>
       </c>
       <c r="D860" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E860" t="inlineStr">
         <is>
-          <t>naver_brandsearch_mobile</t>
+          <t>LMS_ECOM_0410exclusive2</t>
         </is>
       </c>
     </row>
     <row r="861">
       <c r="A861" t="inlineStr">
         <is>
-          <t>yockk23</t>
+          <t>toplaser</t>
         </is>
       </c>
       <c r="B861" t="inlineStr">
         <is>
-          <t>01031774006</t>
+          <t>01056735155</t>
         </is>
       </c>
       <c r="C861" t="inlineStr">
         <is>
-          <t>192898</t>
+          <t>288028</t>
         </is>
       </c>
       <c r="D861" t="inlineStr">
@@ -23671,24 +23671,24 @@
       </c>
       <c r="E861" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0304</t>
+          <t>LMS_ECOM_0214_newyear</t>
         </is>
       </c>
     </row>
     <row r="862">
       <c r="A862" t="inlineStr">
         <is>
-          <t>toplaser</t>
+          <t>yockk23</t>
         </is>
       </c>
       <c r="B862" t="inlineStr">
         <is>
-          <t>01056735155</t>
+          <t>01031774006</t>
         </is>
       </c>
       <c r="C862" t="inlineStr">
         <is>
-          <t>288028</t>
+          <t>192898</t>
         </is>
       </c>
       <c r="D862" t="inlineStr">
@@ -23698,7 +23698,7 @@
       </c>
       <c r="E862" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0214_newyear</t>
+          <t>LMS_ECOM_0304</t>
         </is>
       </c>
     </row>
@@ -23759,54 +23759,54 @@
     <row r="865">
       <c r="A865" t="inlineStr">
         <is>
-          <t>pooh2208</t>
+          <t>hondra</t>
         </is>
       </c>
       <c r="B865" t="inlineStr">
         <is>
-          <t>01062238201</t>
+          <t>01081665020</t>
         </is>
       </c>
       <c r="C865" t="inlineStr">
         <is>
-          <t>85900</t>
+          <t>146125</t>
         </is>
       </c>
       <c r="D865" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E865" t="inlineStr">
         <is>
-          <t>[PF]A SC_상시(1865MF,구매 장바구니)</t>
+          <t>Email_mkt</t>
         </is>
       </c>
     </row>
     <row r="866">
       <c r="A866" t="inlineStr">
         <is>
-          <t>hondra</t>
+          <t>pooh2208</t>
         </is>
       </c>
       <c r="B866" t="inlineStr">
         <is>
-          <t>01081665020</t>
+          <t>01062238201</t>
         </is>
       </c>
       <c r="C866" t="inlineStr">
         <is>
-          <t>146125</t>
+          <t>85900</t>
         </is>
       </c>
       <c r="D866" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E866" t="inlineStr">
         <is>
-          <t>Email_mkt</t>
+          <t>[PF]A SC_상시(1865MF,구매 장바구니)</t>
         </is>
       </c>
     </row>
@@ -23867,54 +23867,54 @@
     <row r="869">
       <c r="A869" t="inlineStr">
         <is>
-          <t>kk_4839433808</t>
+          <t>mtbok</t>
         </is>
       </c>
       <c r="B869" t="inlineStr">
         <is>
-          <t>01025333388</t>
+          <t>01051284339</t>
         </is>
       </c>
       <c r="C869" t="inlineStr">
         <is>
-          <t>304100</t>
+          <t>26917</t>
         </is>
       </c>
       <c r="D869" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E869" t="inlineStr">
         <is>
-          <t>naver_brandsearch_mobile</t>
+          <t>LMS_ECOM_0410exclusive2</t>
         </is>
       </c>
     </row>
     <row r="870">
       <c r="A870" t="inlineStr">
         <is>
-          <t>mtbok</t>
+          <t>kk_4839433808</t>
         </is>
       </c>
       <c r="B870" t="inlineStr">
         <is>
-          <t>01051284339</t>
+          <t>01025333388</t>
         </is>
       </c>
       <c r="C870" t="inlineStr">
         <is>
-          <t>26917</t>
+          <t>304100</t>
         </is>
       </c>
       <c r="D870" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E870" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0410exclusive2</t>
+          <t>naver_brandsearch_mobile</t>
         </is>
       </c>
     </row>
@@ -23948,17 +23948,17 @@
     <row r="872">
       <c r="A872" t="inlineStr">
         <is>
-          <t>hyschant</t>
+          <t>pcx916</t>
         </is>
       </c>
       <c r="B872" t="inlineStr">
         <is>
-          <t>01065306675</t>
+          <t>01026644222</t>
         </is>
       </c>
       <c r="C872" t="inlineStr">
         <is>
-          <t>108579</t>
+          <t>139541</t>
         </is>
       </c>
       <c r="D872" t="inlineStr">
@@ -23968,24 +23968,24 @@
       </c>
       <c r="E872" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0410exclusive2</t>
+          <t>KAKAO_CH_event</t>
         </is>
       </c>
     </row>
     <row r="873">
       <c r="A873" t="inlineStr">
         <is>
-          <t>pcx916</t>
+          <t>hyschant</t>
         </is>
       </c>
       <c r="B873" t="inlineStr">
         <is>
-          <t>01026644222</t>
+          <t>01065306675</t>
         </is>
       </c>
       <c r="C873" t="inlineStr">
         <is>
-          <t>139541</t>
+          <t>108579</t>
         </is>
       </c>
       <c r="D873" t="inlineStr">
@@ -23995,7 +23995,7 @@
       </c>
       <c r="E873" t="inlineStr">
         <is>
-          <t>KAKAO_CH_event</t>
+          <t>LMS_ECOM_0410exclusive2</t>
         </is>
       </c>
     </row>
@@ -24137,54 +24137,54 @@
     <row r="879">
       <c r="A879" t="inlineStr">
         <is>
-          <t>kk_4839026541</t>
+          <t>kk_3181873063</t>
         </is>
       </c>
       <c r="B879" t="inlineStr">
         <is>
-          <t>01089431507</t>
+          <t>01026527131</t>
         </is>
       </c>
       <c r="C879" t="inlineStr">
         <is>
-          <t>304082</t>
+          <t>227343</t>
         </is>
       </c>
       <c r="D879" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E879" t="inlineStr">
         <is>
-          <t>[PF]전환_상시(2565MF,비구매자)</t>
+          <t>LMS_ECOM_0410exclusive2</t>
         </is>
       </c>
     </row>
     <row r="880">
       <c r="A880" t="inlineStr">
         <is>
-          <t>kk_3181873063</t>
+          <t>kk_4839026541</t>
         </is>
       </c>
       <c r="B880" t="inlineStr">
         <is>
-          <t>01026527131</t>
+          <t>01089431507</t>
         </is>
       </c>
       <c r="C880" t="inlineStr">
         <is>
-          <t>227343</t>
+          <t>304082</t>
         </is>
       </c>
       <c r="D880" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E880" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0410exclusive2</t>
+          <t>[PF]전환_상시(2565MF,비구매자)</t>
         </is>
       </c>
     </row>
@@ -24245,17 +24245,17 @@
     <row r="883">
       <c r="A883" t="inlineStr">
         <is>
-          <t>sarang21</t>
+          <t>kk_3810304670</t>
         </is>
       </c>
       <c r="B883" t="inlineStr">
         <is>
-          <t>01054975535</t>
+          <t>01041348052</t>
         </is>
       </c>
       <c r="C883" t="inlineStr">
         <is>
-          <t>268553</t>
+          <t>261190</t>
         </is>
       </c>
       <c r="D883" t="inlineStr">
@@ -24272,17 +24272,17 @@
     <row r="884">
       <c r="A884" t="inlineStr">
         <is>
-          <t>pbhds102306</t>
+          <t>kk_3251799831</t>
         </is>
       </c>
       <c r="B884" t="inlineStr">
         <is>
-          <t>01062816264</t>
+          <t>01040006581</t>
         </is>
       </c>
       <c r="C884" t="inlineStr">
         <is>
-          <t>266784</t>
+          <t>235398</t>
         </is>
       </c>
       <c r="D884" t="inlineStr">
@@ -24299,17 +24299,17 @@
     <row r="885">
       <c r="A885" t="inlineStr">
         <is>
-          <t>kk_3251799831</t>
+          <t>kk_3334413020</t>
         </is>
       </c>
       <c r="B885" t="inlineStr">
         <is>
-          <t>01040006581</t>
+          <t>01080806386</t>
         </is>
       </c>
       <c r="C885" t="inlineStr">
         <is>
-          <t>235398</t>
+          <t>238829</t>
         </is>
       </c>
       <c r="D885" t="inlineStr">
@@ -24326,17 +24326,17 @@
     <row r="886">
       <c r="A886" t="inlineStr">
         <is>
-          <t>kk_3334413020</t>
+          <t>sarang21</t>
         </is>
       </c>
       <c r="B886" t="inlineStr">
         <is>
-          <t>01080806386</t>
+          <t>01054975535</t>
         </is>
       </c>
       <c r="C886" t="inlineStr">
         <is>
-          <t>238829</t>
+          <t>268553</t>
         </is>
       </c>
       <c r="D886" t="inlineStr">
@@ -24353,17 +24353,17 @@
     <row r="887">
       <c r="A887" t="inlineStr">
         <is>
-          <t>kk_3810304670</t>
+          <t>pbhds102306</t>
         </is>
       </c>
       <c r="B887" t="inlineStr">
         <is>
-          <t>01041348052</t>
+          <t>01062816264</t>
         </is>
       </c>
       <c r="C887" t="inlineStr">
         <is>
-          <t>261190</t>
+          <t>266784</t>
         </is>
       </c>
       <c r="D887" t="inlineStr">
@@ -24380,98 +24380,98 @@
     <row r="888">
       <c r="A888" t="inlineStr">
         <is>
-          <t>kk_4849696162</t>
+          <t>jeanne</t>
         </is>
       </c>
       <c r="B888" t="inlineStr">
         <is>
-          <t>01063383734</t>
+          <t>01047490850</t>
         </is>
       </c>
       <c r="C888" t="inlineStr">
         <is>
-          <t>304570</t>
+          <t>195346</t>
         </is>
       </c>
       <c r="D888" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E888" t="inlineStr">
         <is>
-          <t>컬럼비아_DPA_240530</t>
+          <t>LMS_ECOM_200416_family</t>
         </is>
       </c>
     </row>
     <row r="889">
       <c r="A889" t="inlineStr">
         <is>
-          <t>jeanne</t>
+          <t>kk_3975997627</t>
         </is>
       </c>
       <c r="B889" t="inlineStr">
         <is>
-          <t>01047490850</t>
+          <t>01066448502</t>
         </is>
       </c>
       <c r="C889" t="inlineStr">
         <is>
-          <t>195346</t>
+          <t>271178</t>
         </is>
       </c>
       <c r="D889" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="E889" t="inlineStr">
         <is>
-          <t>LMS_ECOM_200416_family</t>
+          <t>Direct</t>
         </is>
       </c>
     </row>
     <row r="890">
       <c r="A890" t="inlineStr">
         <is>
-          <t>kk_3975997627</t>
+          <t>kk_4849696162</t>
         </is>
       </c>
       <c r="B890" t="inlineStr">
         <is>
-          <t>01066448502</t>
+          <t>01063383734</t>
         </is>
       </c>
       <c r="C890" t="inlineStr">
         <is>
-          <t>271178</t>
+          <t>304570</t>
         </is>
       </c>
       <c r="D890" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E890" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>컬럼비아_DPA_240530</t>
         </is>
       </c>
     </row>
     <row r="891">
       <c r="A891" t="inlineStr">
         <is>
-          <t>kk_4469973568</t>
+          <t>kk_3210379887</t>
         </is>
       </c>
       <c r="B891" t="inlineStr">
         <is>
-          <t>01087158602</t>
+          <t>01024748405</t>
         </is>
       </c>
       <c r="C891" t="inlineStr">
         <is>
-          <t>283741</t>
+          <t>231651</t>
         </is>
       </c>
       <c r="D891" t="inlineStr">
@@ -24481,24 +24481,24 @@
       </c>
       <c r="E891" t="inlineStr">
         <is>
-          <t>KAKAO_CH_MENU_0211_NEW_MEN</t>
+          <t>LMS_ECOM_0410exclusive2</t>
         </is>
       </c>
     </row>
     <row r="892">
       <c r="A892" t="inlineStr">
         <is>
-          <t>kk_3210379887</t>
+          <t>kk_4469973568</t>
         </is>
       </c>
       <c r="B892" t="inlineStr">
         <is>
-          <t>01024748405</t>
+          <t>01087158602</t>
         </is>
       </c>
       <c r="C892" t="inlineStr">
         <is>
-          <t>231651</t>
+          <t>283741</t>
         </is>
       </c>
       <c r="D892" t="inlineStr">
@@ -24508,7 +24508,7 @@
       </c>
       <c r="E892" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0410exclusive2</t>
+          <t>KAKAO_CH_MENU_0211_NEW_MEN</t>
         </is>
       </c>
     </row>
@@ -24569,17 +24569,17 @@
     <row r="895">
       <c r="A895" t="inlineStr">
         <is>
-          <t>kk_4600405600</t>
+          <t>kk_3967419156</t>
         </is>
       </c>
       <c r="B895" t="inlineStr">
         <is>
-          <t>01053449477</t>
+          <t>01030207947</t>
         </is>
       </c>
       <c r="C895" t="inlineStr">
         <is>
-          <t>289364</t>
+          <t>270708</t>
         </is>
       </c>
       <c r="D895" t="inlineStr">
@@ -24623,17 +24623,17 @@
     <row r="897">
       <c r="A897" t="inlineStr">
         <is>
-          <t>kk_3967419156</t>
+          <t>kk_4600405600</t>
         </is>
       </c>
       <c r="B897" t="inlineStr">
         <is>
-          <t>01030207947</t>
+          <t>01053449477</t>
         </is>
       </c>
       <c r="C897" t="inlineStr">
         <is>
-          <t>270708</t>
+          <t>289364</t>
         </is>
       </c>
       <c r="D897" t="inlineStr">
@@ -24650,17 +24650,17 @@
     <row r="898">
       <c r="A898" t="inlineStr">
         <is>
-          <t>soslsc</t>
+          <t>lovemac</t>
         </is>
       </c>
       <c r="B898" t="inlineStr">
         <is>
-          <t>01023174693</t>
+          <t>01058421351</t>
         </is>
       </c>
       <c r="C898" t="inlineStr">
         <is>
-          <t>171035</t>
+          <t>69911</t>
         </is>
       </c>
       <c r="D898" t="inlineStr">
@@ -24677,17 +24677,17 @@
     <row r="899">
       <c r="A899" t="inlineStr">
         <is>
-          <t>lovemac</t>
+          <t>a3789</t>
         </is>
       </c>
       <c r="B899" t="inlineStr">
         <is>
-          <t>01058421351</t>
+          <t>01053102148</t>
         </is>
       </c>
       <c r="C899" t="inlineStr">
         <is>
-          <t>69911</t>
+          <t>244924</t>
         </is>
       </c>
       <c r="D899" t="inlineStr">
@@ -24704,17 +24704,17 @@
     <row r="900">
       <c r="A900" t="inlineStr">
         <is>
-          <t>a3789</t>
+          <t>soslsc</t>
         </is>
       </c>
       <c r="B900" t="inlineStr">
         <is>
-          <t>01053102148</t>
+          <t>01023174693</t>
         </is>
       </c>
       <c r="C900" t="inlineStr">
         <is>
-          <t>244924</t>
+          <t>171035</t>
         </is>
       </c>
       <c r="D900" t="inlineStr">
@@ -25271,17 +25271,17 @@
     <row r="921">
       <c r="A921" t="inlineStr">
         <is>
-          <t>kk_3180854377</t>
+          <t>kk_3800712629</t>
         </is>
       </c>
       <c r="B921" t="inlineStr">
         <is>
-          <t>01031216377</t>
+          <t>01037690698</t>
         </is>
       </c>
       <c r="C921" t="inlineStr">
         <is>
-          <t>226467</t>
+          <t>258873</t>
         </is>
       </c>
       <c r="D921" t="inlineStr">
@@ -25298,17 +25298,17 @@
     <row r="922">
       <c r="A922" t="inlineStr">
         <is>
-          <t>kk_3793117898</t>
+          <t>kk_3180854377</t>
         </is>
       </c>
       <c r="B922" t="inlineStr">
         <is>
-          <t>01052318168</t>
+          <t>01031216377</t>
         </is>
       </c>
       <c r="C922" t="inlineStr">
         <is>
-          <t>257099</t>
+          <t>226467</t>
         </is>
       </c>
       <c r="D922" t="inlineStr">
@@ -25325,17 +25325,17 @@
     <row r="923">
       <c r="A923" t="inlineStr">
         <is>
-          <t>kk_3800712629</t>
+          <t>kk_3793117898</t>
         </is>
       </c>
       <c r="B923" t="inlineStr">
         <is>
-          <t>01037690698</t>
+          <t>01052318168</t>
         </is>
       </c>
       <c r="C923" t="inlineStr">
         <is>
-          <t>258873</t>
+          <t>257099</t>
         </is>
       </c>
       <c r="D923" t="inlineStr">
@@ -25946,54 +25946,54 @@
     <row r="946">
       <c r="A946" t="inlineStr">
         <is>
-          <t>kk_4835738911</t>
+          <t>kk_4839354093</t>
         </is>
       </c>
       <c r="B946" t="inlineStr">
         <is>
-          <t>01034422073</t>
+          <t>01052243562</t>
         </is>
       </c>
       <c r="C946" t="inlineStr">
         <is>
-          <t>303885</t>
+          <t>304098</t>
         </is>
       </c>
       <c r="D946" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Organic Traffic</t>
         </is>
       </c>
       <c r="E946" t="inlineStr">
         <is>
-          <t>6968489536332</t>
+          <t>(organic)</t>
         </is>
       </c>
     </row>
     <row r="947">
       <c r="A947" t="inlineStr">
         <is>
-          <t>kk_4839354093</t>
+          <t>kk_4835738911</t>
         </is>
       </c>
       <c r="B947" t="inlineStr">
         <is>
-          <t>01052243562</t>
+          <t>01034422073</t>
         </is>
       </c>
       <c r="C947" t="inlineStr">
         <is>
-          <t>304098</t>
+          <t>303885</t>
         </is>
       </c>
       <c r="D947" t="inlineStr">
         <is>
-          <t>Organic Traffic</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E947" t="inlineStr">
         <is>
-          <t>(organic)</t>
+          <t>6968489536332</t>
         </is>
       </c>
     </row>
@@ -26270,54 +26270,54 @@
     <row r="958">
       <c r="A958" t="inlineStr">
         <is>
-          <t>kk_3955208505</t>
+          <t>kk_3919493388</t>
         </is>
       </c>
       <c r="B958" t="inlineStr">
         <is>
-          <t>01084144311</t>
+          <t>01084315028</t>
         </is>
       </c>
       <c r="C958" t="inlineStr">
         <is>
-          <t>270134</t>
+          <t>268572</t>
         </is>
       </c>
       <c r="D958" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E958" t="inlineStr">
         <is>
-          <t>KAKAO_CH_MENU_0212_TITANIUM</t>
+          <t>Paid Ad</t>
         </is>
       </c>
     </row>
     <row r="959">
       <c r="A959" t="inlineStr">
         <is>
-          <t>kk_3919493388</t>
+          <t>kk_3955208505</t>
         </is>
       </c>
       <c r="B959" t="inlineStr">
         <is>
-          <t>01084315028</t>
+          <t>01084144311</t>
         </is>
       </c>
       <c r="C959" t="inlineStr">
         <is>
-          <t>268572</t>
+          <t>270134</t>
         </is>
       </c>
       <c r="D959" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E959" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>KAKAO_CH_MENU_0212_TITANIUM</t>
         </is>
       </c>
     </row>
@@ -26459,54 +26459,54 @@
     <row r="965">
       <c r="A965" t="inlineStr">
         <is>
-          <t>nurai</t>
+          <t>jin1242</t>
         </is>
       </c>
       <c r="B965" t="inlineStr">
         <is>
-          <t>01077918645</t>
+          <t>01038541242</t>
         </is>
       </c>
       <c r="C965" t="inlineStr">
         <is>
-          <t>304477</t>
+          <t>133468</t>
         </is>
       </c>
       <c r="D965" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Organic Traffic</t>
         </is>
       </c>
       <c r="E965" t="inlineStr">
         <is>
-          <t>sa</t>
+          <t>Organic Traffic</t>
         </is>
       </c>
     </row>
     <row r="966">
       <c r="A966" t="inlineStr">
         <is>
-          <t>jin1242</t>
+          <t>nurai</t>
         </is>
       </c>
       <c r="B966" t="inlineStr">
         <is>
-          <t>01038541242</t>
+          <t>01077918645</t>
         </is>
       </c>
       <c r="C966" t="inlineStr">
         <is>
-          <t>133468</t>
+          <t>304477</t>
         </is>
       </c>
       <c r="D966" t="inlineStr">
         <is>
-          <t>Organic Traffic</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E966" t="inlineStr">
         <is>
-          <t>Organic Traffic</t>
+          <t>sa</t>
         </is>
       </c>
     </row>
@@ -26864,17 +26864,17 @@
     <row r="980">
       <c r="A980" t="inlineStr">
         <is>
-          <t>kk_3595551743</t>
+          <t>holstein</t>
         </is>
       </c>
       <c r="B980" t="inlineStr">
         <is>
-          <t>01025839326</t>
+          <t>01050502500</t>
         </is>
       </c>
       <c r="C980" t="inlineStr">
         <is>
-          <t>246836</t>
+          <t>14062</t>
         </is>
       </c>
       <c r="D980" t="inlineStr">
@@ -26884,24 +26884,24 @@
       </c>
       <c r="E980" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0410exclusive2</t>
+          <t>EDM_TOP</t>
         </is>
       </c>
     </row>
     <row r="981">
       <c r="A981" t="inlineStr">
         <is>
-          <t>holstein</t>
+          <t>kk_3595551743</t>
         </is>
       </c>
       <c r="B981" t="inlineStr">
         <is>
-          <t>01050502500</t>
+          <t>01025839326</t>
         </is>
       </c>
       <c r="C981" t="inlineStr">
         <is>
-          <t>14062</t>
+          <t>246836</t>
         </is>
       </c>
       <c r="D981" t="inlineStr">
@@ -26911,7 +26911,7 @@
       </c>
       <c r="E981" t="inlineStr">
         <is>
-          <t>EDM_TOP</t>
+          <t>LMS_ECOM_0410exclusive2</t>
         </is>
       </c>
     </row>
@@ -27053,54 +27053,54 @@
     <row r="987">
       <c r="A987" t="inlineStr">
         <is>
-          <t>kmh7710</t>
+          <t>kk_4375973589</t>
         </is>
       </c>
       <c r="B987" t="inlineStr">
         <is>
-          <t>01077108716</t>
+          <t>01096223641</t>
         </is>
       </c>
       <c r="C987" t="inlineStr">
         <is>
-          <t>164951</t>
+          <t>280163</t>
         </is>
       </c>
       <c r="D987" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Organic Traffic</t>
         </is>
       </c>
       <c r="E987" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0214_newyear</t>
+          <t>LMS_ECOM_familycoupon</t>
         </is>
       </c>
     </row>
     <row r="988">
       <c r="A988" t="inlineStr">
         <is>
-          <t>kk_4375973589</t>
+          <t>kmh7710</t>
         </is>
       </c>
       <c r="B988" t="inlineStr">
         <is>
-          <t>01096223641</t>
+          <t>01077108716</t>
         </is>
       </c>
       <c r="C988" t="inlineStr">
         <is>
-          <t>280163</t>
+          <t>164951</t>
         </is>
       </c>
       <c r="D988" t="inlineStr">
         <is>
-          <t>Organic Traffic</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E988" t="inlineStr">
         <is>
-          <t>LMS_ECOM_familycoupon</t>
+          <t>LMS_ECOM_0214_newyear</t>
         </is>
       </c>
     </row>
@@ -27296,17 +27296,17 @@
     <row r="996">
       <c r="A996" t="inlineStr">
         <is>
-          <t>kk_4839544665</t>
+          <t>kk_4839477951</t>
         </is>
       </c>
       <c r="B996" t="inlineStr">
         <is>
-          <t>01055350199</t>
+          <t>01020868012</t>
         </is>
       </c>
       <c r="C996" t="inlineStr">
         <is>
-          <t>304104</t>
+          <t>304101</t>
         </is>
       </c>
       <c r="D996" t="inlineStr">
@@ -27323,17 +27323,17 @@
     <row r="997">
       <c r="A997" t="inlineStr">
         <is>
-          <t>kk_4839477951</t>
+          <t>kk_4839544665</t>
         </is>
       </c>
       <c r="B997" t="inlineStr">
         <is>
-          <t>01020868012</t>
+          <t>01055350199</t>
         </is>
       </c>
       <c r="C997" t="inlineStr">
         <is>
-          <t>304101</t>
+          <t>304104</t>
         </is>
       </c>
       <c r="D997" t="inlineStr">
@@ -27458,54 +27458,54 @@
     <row r="1002">
       <c r="A1002" t="inlineStr">
         <is>
-          <t>kk_4843439707</t>
+          <t>kk_2800477789</t>
         </is>
       </c>
       <c r="B1002" t="inlineStr">
         <is>
-          <t>01022248653</t>
+          <t>01035177105</t>
         </is>
       </c>
       <c r="C1002" t="inlineStr">
         <is>
-          <t>304310</t>
+          <t>211095</t>
         </is>
       </c>
       <c r="D1002" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E1002" t="inlineStr">
         <is>
-          <t>6968489536332</t>
+          <t>KAKAO_alimtalk</t>
         </is>
       </c>
     </row>
     <row r="1003">
       <c r="A1003" t="inlineStr">
         <is>
-          <t>kk_2800477789</t>
+          <t>kk_4843439707</t>
         </is>
       </c>
       <c r="B1003" t="inlineStr">
         <is>
-          <t>01035177105</t>
+          <t>01022248653</t>
         </is>
       </c>
       <c r="C1003" t="inlineStr">
         <is>
-          <t>211095</t>
+          <t>304310</t>
         </is>
       </c>
       <c r="D1003" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E1003" t="inlineStr">
         <is>
-          <t>KAKAO_alimtalk</t>
+          <t>6968489536332</t>
         </is>
       </c>
     </row>
@@ -27539,108 +27539,108 @@
     <row r="1005">
       <c r="A1005" t="inlineStr">
         <is>
-          <t>kk_4844657024</t>
+          <t>dmsdud552</t>
         </is>
       </c>
       <c r="B1005" t="inlineStr">
         <is>
-          <t>01033551784</t>
+          <t>01054633672</t>
         </is>
       </c>
       <c r="C1005" t="inlineStr">
         <is>
-          <t>304376</t>
+          <t>132110</t>
         </is>
       </c>
       <c r="D1005" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Organic Traffic</t>
         </is>
       </c>
       <c r="E1005" t="inlineStr">
         <is>
-          <t>6968489536332</t>
+          <t>(referral)</t>
         </is>
       </c>
     </row>
     <row r="1006">
       <c r="A1006" t="inlineStr">
         <is>
-          <t>dmsdud552</t>
+          <t>kk_4844657024</t>
         </is>
       </c>
       <c r="B1006" t="inlineStr">
         <is>
-          <t>01054633672</t>
+          <t>01033551784</t>
         </is>
       </c>
       <c r="C1006" t="inlineStr">
         <is>
-          <t>132110</t>
+          <t>304376</t>
         </is>
       </c>
       <c r="D1006" t="inlineStr">
         <is>
-          <t>Organic Traffic</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E1006" t="inlineStr">
         <is>
-          <t>(referral)</t>
+          <t>6968489536332</t>
         </is>
       </c>
     </row>
     <row r="1007">
       <c r="A1007" t="inlineStr">
         <is>
-          <t>kk_4839643736</t>
+          <t>kk_4543882817</t>
         </is>
       </c>
       <c r="B1007" t="inlineStr">
         <is>
-          <t>01063617035</t>
+          <t>01023875300</t>
         </is>
       </c>
       <c r="C1007" t="inlineStr">
         <is>
-          <t>304107</t>
+          <t>287573</t>
         </is>
       </c>
       <c r="D1007" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="E1007" t="inlineStr">
         <is>
-          <t>naver_brandsearch_mobile</t>
+          <t>미분류</t>
         </is>
       </c>
     </row>
     <row r="1008">
       <c r="A1008" t="inlineStr">
         <is>
-          <t>kk_4543882817</t>
+          <t>kk_4839643736</t>
         </is>
       </c>
       <c r="B1008" t="inlineStr">
         <is>
-          <t>01023875300</t>
+          <t>01063617035</t>
         </is>
       </c>
       <c r="C1008" t="inlineStr">
         <is>
-          <t>287573</t>
+          <t>304107</t>
         </is>
       </c>
       <c r="D1008" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E1008" t="inlineStr">
         <is>
-          <t>미분류</t>
+          <t>naver_brandsearch_mobile</t>
         </is>
       </c>
     </row>
@@ -27701,71 +27701,71 @@
     <row r="1011">
       <c r="A1011" t="inlineStr">
         <is>
-          <t>kk_4843847622</t>
+          <t>kk_4843926419</t>
         </is>
       </c>
       <c r="B1011" t="inlineStr">
         <is>
-          <t>01046990393</t>
+          <t>01034583174</t>
         </is>
       </c>
       <c r="C1011" t="inlineStr">
         <is>
-          <t>304336</t>
+          <t>304338</t>
         </is>
       </c>
       <c r="D1011" t="inlineStr">
         <is>
-          <t>Organic Traffic</t>
+          <t>Official SNS</t>
         </is>
       </c>
       <c r="E1011" t="inlineStr">
         <is>
-          <t>(organic)</t>
+          <t>EFW_04</t>
         </is>
       </c>
     </row>
     <row r="1012">
       <c r="A1012" t="inlineStr">
         <is>
-          <t>kk_4843926419</t>
+          <t>kk_4844453283</t>
         </is>
       </c>
       <c r="B1012" t="inlineStr">
         <is>
-          <t>01034583174</t>
+          <t>01090262556</t>
         </is>
       </c>
       <c r="C1012" t="inlineStr">
         <is>
-          <t>304338</t>
+          <t>304360</t>
         </is>
       </c>
       <c r="D1012" t="inlineStr">
         <is>
-          <t>Official SNS</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E1012" t="inlineStr">
         <is>
-          <t>EFW_04</t>
+          <t>6968489536332</t>
         </is>
       </c>
     </row>
     <row r="1013">
       <c r="A1013" t="inlineStr">
         <is>
-          <t>kk_4844453283</t>
+          <t>kk_4845173313</t>
         </is>
       </c>
       <c r="B1013" t="inlineStr">
         <is>
-          <t>01090262556</t>
+          <t>01024436341</t>
         </is>
       </c>
       <c r="C1013" t="inlineStr">
         <is>
-          <t>304360</t>
+          <t>304397</t>
         </is>
       </c>
       <c r="D1013" t="inlineStr">
@@ -27809,44 +27809,44 @@
     <row r="1015">
       <c r="A1015" t="inlineStr">
         <is>
-          <t>kidultyo</t>
+          <t>kk_4843847622</t>
         </is>
       </c>
       <c r="B1015" t="inlineStr">
         <is>
-          <t>01037980315</t>
+          <t>01046990393</t>
         </is>
       </c>
       <c r="C1015" t="inlineStr">
         <is>
-          <t>304331</t>
+          <t>304336</t>
         </is>
       </c>
       <c r="D1015" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Organic Traffic</t>
         </is>
       </c>
       <c r="E1015" t="inlineStr">
         <is>
-          <t>6968489536332</t>
+          <t>(organic)</t>
         </is>
       </c>
     </row>
     <row r="1016">
       <c r="A1016" t="inlineStr">
         <is>
-          <t>kk_4845173313</t>
+          <t>kidultyo</t>
         </is>
       </c>
       <c r="B1016" t="inlineStr">
         <is>
-          <t>01024436341</t>
+          <t>01037980315</t>
         </is>
       </c>
       <c r="C1016" t="inlineStr">
         <is>
-          <t>304397</t>
+          <t>304331</t>
         </is>
       </c>
       <c r="D1016" t="inlineStr">
@@ -27863,71 +27863,71 @@
     <row r="1017">
       <c r="A1017" t="inlineStr">
         <is>
-          <t>kk_2961062530</t>
+          <t>kk_4840857472</t>
         </is>
       </c>
       <c r="B1017" t="inlineStr">
         <is>
-          <t>01050052823</t>
+          <t>01040551807</t>
         </is>
       </c>
       <c r="C1017" t="inlineStr">
         <is>
-          <t>217199</t>
+          <t>304172</t>
         </is>
       </c>
       <c r="D1017" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="E1017" t="inlineStr">
         <is>
-          <t>KAKAO_CH_MENU_0317_S26NEW</t>
+          <t>Direct</t>
         </is>
       </c>
     </row>
     <row r="1018">
       <c r="A1018" t="inlineStr">
         <is>
-          <t>kk_4840857472</t>
+          <t>kyoungs424</t>
         </is>
       </c>
       <c r="B1018" t="inlineStr">
         <is>
-          <t>01040551807</t>
+          <t>01041509204</t>
         </is>
       </c>
       <c r="C1018" t="inlineStr">
         <is>
-          <t>304172</t>
+          <t>153760</t>
         </is>
       </c>
       <c r="D1018" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E1018" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>KAKAO_alimtalk</t>
         </is>
       </c>
     </row>
     <row r="1019">
       <c r="A1019" t="inlineStr">
         <is>
-          <t>kyoungs424</t>
+          <t>kk_2961062530</t>
         </is>
       </c>
       <c r="B1019" t="inlineStr">
         <is>
-          <t>01041509204</t>
+          <t>01050052823</t>
         </is>
       </c>
       <c r="C1019" t="inlineStr">
         <is>
-          <t>153760</t>
+          <t>217199</t>
         </is>
       </c>
       <c r="D1019" t="inlineStr">
@@ -27937,7 +27937,7 @@
       </c>
       <c r="E1019" t="inlineStr">
         <is>
-          <t>KAKAO_alimtalk</t>
+          <t>KAKAO_CH_MENU_0317_S26NEW</t>
         </is>
       </c>
     </row>
@@ -28268,179 +28268,179 @@
     <row r="1032">
       <c r="A1032" t="inlineStr">
         <is>
-          <t>kk_4847975154</t>
+          <t>kk_4847354450</t>
         </is>
       </c>
       <c r="B1032" t="inlineStr">
         <is>
-          <t>01062199172</t>
+          <t>01088042346</t>
         </is>
       </c>
       <c r="C1032" t="inlineStr">
         <is>
-          <t>304512</t>
+          <t>304489</t>
         </is>
       </c>
       <c r="D1032" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E1032" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>6968489536332</t>
         </is>
       </c>
     </row>
     <row r="1033">
       <c r="A1033" t="inlineStr">
         <is>
-          <t>kk_4847354450</t>
+          <t>kk_4847975154</t>
         </is>
       </c>
       <c r="B1033" t="inlineStr">
         <is>
-          <t>01088042346</t>
+          <t>01062199172</t>
         </is>
       </c>
       <c r="C1033" t="inlineStr">
         <is>
-          <t>304489</t>
+          <t>304512</t>
         </is>
       </c>
       <c r="D1033" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="E1033" t="inlineStr">
         <is>
-          <t>6968489536332</t>
+          <t>Direct</t>
         </is>
       </c>
     </row>
     <row r="1034">
       <c r="A1034" t="inlineStr">
         <is>
-          <t>kk_4846749411</t>
+          <t>kk_4846692829</t>
         </is>
       </c>
       <c r="B1034" t="inlineStr">
         <is>
-          <t>01031226749</t>
+          <t>01023649887</t>
         </is>
       </c>
       <c r="C1034" t="inlineStr">
         <is>
-          <t>304462</t>
+          <t>304457</t>
         </is>
       </c>
       <c r="D1034" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Organic Traffic</t>
         </is>
       </c>
       <c r="E1034" t="inlineStr">
         <is>
-          <t>6968489536332</t>
+          <t>(referral)</t>
         </is>
       </c>
     </row>
     <row r="1035">
       <c r="A1035" t="inlineStr">
         <is>
-          <t>kk_4846692829</t>
+          <t>kk_4846749411</t>
         </is>
       </c>
       <c r="B1035" t="inlineStr">
         <is>
-          <t>01023649887</t>
+          <t>01031226749</t>
         </is>
       </c>
       <c r="C1035" t="inlineStr">
         <is>
-          <t>304457</t>
+          <t>304462</t>
         </is>
       </c>
       <c r="D1035" t="inlineStr">
         <is>
-          <t>Organic Traffic</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E1035" t="inlineStr">
         <is>
-          <t>(referral)</t>
+          <t>6968489536332</t>
         </is>
       </c>
     </row>
     <row r="1036">
       <c r="A1036" t="inlineStr">
         <is>
-          <t>kk_4844609437</t>
+          <t>kk_4843809795</t>
         </is>
       </c>
       <c r="B1036" t="inlineStr">
         <is>
-          <t>01046808931</t>
+          <t>01072864741</t>
         </is>
       </c>
       <c r="C1036" t="inlineStr">
         <is>
-          <t>304372</t>
+          <t>304335</t>
         </is>
       </c>
       <c r="D1036" t="inlineStr">
         <is>
-          <t>Official SNS</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E1036" t="inlineStr">
         <is>
-          <t>(referral)</t>
+          <t>6968489536332</t>
         </is>
       </c>
     </row>
     <row r="1037">
       <c r="A1037" t="inlineStr">
         <is>
-          <t>kk_4844452226</t>
+          <t>kk_4844609437</t>
         </is>
       </c>
       <c r="B1037" t="inlineStr">
         <is>
-          <t>01096801866</t>
+          <t>01046808931</t>
         </is>
       </c>
       <c r="C1037" t="inlineStr">
         <is>
-          <t>304359</t>
+          <t>304372</t>
         </is>
       </c>
       <c r="D1037" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Official SNS</t>
         </is>
       </c>
       <c r="E1037" t="inlineStr">
         <is>
-          <t>6968489536332</t>
+          <t>(referral)</t>
         </is>
       </c>
     </row>
     <row r="1038">
       <c r="A1038" t="inlineStr">
         <is>
-          <t>kk_4843809795</t>
+          <t>kk_4844452226</t>
         </is>
       </c>
       <c r="B1038" t="inlineStr">
         <is>
-          <t>01072864741</t>
+          <t>01096801866</t>
         </is>
       </c>
       <c r="C1038" t="inlineStr">
         <is>
-          <t>304335</t>
+          <t>304359</t>
         </is>
       </c>
       <c r="D1038" t="inlineStr">
@@ -28538,71 +28538,71 @@
     <row r="1042">
       <c r="A1042" t="inlineStr">
         <is>
-          <t>kk_4840913383</t>
+          <t>kk_4841278242</t>
         </is>
       </c>
       <c r="B1042" t="inlineStr">
         <is>
-          <t>01099887927</t>
+          <t>01046197965</t>
         </is>
       </c>
       <c r="C1042" t="inlineStr">
         <is>
-          <t>304174</t>
+          <t>304190</t>
         </is>
       </c>
       <c r="D1042" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>Organic Traffic</t>
         </is>
       </c>
       <c r="E1042" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>(referral)</t>
         </is>
       </c>
     </row>
     <row r="1043">
       <c r="A1043" t="inlineStr">
         <is>
-          <t>kk_4841278242</t>
+          <t>kk_4840913383</t>
         </is>
       </c>
       <c r="B1043" t="inlineStr">
         <is>
-          <t>01046197965</t>
+          <t>01099887927</t>
         </is>
       </c>
       <c r="C1043" t="inlineStr">
         <is>
-          <t>304190</t>
+          <t>304174</t>
         </is>
       </c>
       <c r="D1043" t="inlineStr">
         <is>
-          <t>Organic Traffic</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="E1043" t="inlineStr">
         <is>
-          <t>(referral)</t>
+          <t>Direct</t>
         </is>
       </c>
     </row>
     <row r="1044">
       <c r="A1044" t="inlineStr">
         <is>
-          <t>kk_2750710108</t>
+          <t>jsb0425</t>
         </is>
       </c>
       <c r="B1044" t="inlineStr">
         <is>
-          <t>01062707475</t>
+          <t>01037883670</t>
         </is>
       </c>
       <c r="C1044" t="inlineStr">
         <is>
-          <t>207211</t>
+          <t>104766</t>
         </is>
       </c>
       <c r="D1044" t="inlineStr">
@@ -28646,17 +28646,17 @@
     <row r="1046">
       <c r="A1046" t="inlineStr">
         <is>
-          <t>jsb0425</t>
+          <t>kk_2750710108</t>
         </is>
       </c>
       <c r="B1046" t="inlineStr">
         <is>
-          <t>01037883670</t>
+          <t>01062707475</t>
         </is>
       </c>
       <c r="C1046" t="inlineStr">
         <is>
-          <t>104766</t>
+          <t>207211</t>
         </is>
       </c>
       <c r="D1046" t="inlineStr">
@@ -28754,17 +28754,17 @@
     <row r="1050">
       <c r="A1050" t="inlineStr">
         <is>
-          <t>kimchhgood</t>
+          <t>kk_3776403631</t>
         </is>
       </c>
       <c r="B1050" t="inlineStr">
         <is>
-          <t>01092133961</t>
+          <t>01034755755</t>
         </is>
       </c>
       <c r="C1050" t="inlineStr">
         <is>
-          <t>53493</t>
+          <t>255908</t>
         </is>
       </c>
       <c r="D1050" t="inlineStr">
@@ -28774,24 +28774,24 @@
       </c>
       <c r="E1050" t="inlineStr">
         <is>
-          <t>EDM_TOP</t>
+          <t>KAKAO_alimtalk</t>
         </is>
       </c>
     </row>
     <row r="1051">
       <c r="A1051" t="inlineStr">
         <is>
-          <t>kk_3776403631</t>
+          <t>kimchhgood</t>
         </is>
       </c>
       <c r="B1051" t="inlineStr">
         <is>
-          <t>01034755755</t>
+          <t>01092133961</t>
         </is>
       </c>
       <c r="C1051" t="inlineStr">
         <is>
-          <t>255908</t>
+          <t>53493</t>
         </is>
       </c>
       <c r="D1051" t="inlineStr">
@@ -28801,115 +28801,115 @@
       </c>
       <c r="E1051" t="inlineStr">
         <is>
-          <t>KAKAO_alimtalk</t>
+          <t>EDM_TOP</t>
         </is>
       </c>
     </row>
     <row r="1052">
       <c r="A1052" t="inlineStr">
         <is>
-          <t>kk_3186206141</t>
+          <t>kk_4849353674</t>
         </is>
       </c>
       <c r="B1052" t="inlineStr">
         <is>
-          <t>01094810924</t>
+          <t>01029430913</t>
         </is>
       </c>
       <c r="C1052" t="inlineStr">
         <is>
-          <t>230180</t>
+          <t>304557</t>
         </is>
       </c>
       <c r="D1052" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Organic Traffic</t>
         </is>
       </c>
       <c r="E1052" t="inlineStr">
         <is>
-          <t>lms_ecom_200416_family</t>
+          <t>(referral)</t>
         </is>
       </c>
     </row>
     <row r="1053">
       <c r="A1053" t="inlineStr">
         <is>
-          <t>chyim</t>
+          <t>kk_4425155772</t>
         </is>
       </c>
       <c r="B1053" t="inlineStr">
         <is>
-          <t>01037519198</t>
+          <t>01074070807</t>
         </is>
       </c>
       <c r="C1053" t="inlineStr">
         <is>
-          <t>255862</t>
+          <t>281472</t>
         </is>
       </c>
       <c r="D1053" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>Organic Traffic</t>
         </is>
       </c>
       <c r="E1053" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>(organic)</t>
         </is>
       </c>
     </row>
     <row r="1054">
       <c r="A1054" t="inlineStr">
         <is>
-          <t>kk_4849353674</t>
+          <t>chyim</t>
         </is>
       </c>
       <c r="B1054" t="inlineStr">
         <is>
-          <t>01029430913</t>
+          <t>01037519198</t>
         </is>
       </c>
       <c r="C1054" t="inlineStr">
         <is>
-          <t>304557</t>
+          <t>255862</t>
         </is>
       </c>
       <c r="D1054" t="inlineStr">
         <is>
-          <t>Organic Traffic</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="E1054" t="inlineStr">
         <is>
-          <t>(referral)</t>
+          <t>Direct</t>
         </is>
       </c>
     </row>
     <row r="1055">
       <c r="A1055" t="inlineStr">
         <is>
-          <t>kk_4425155772</t>
+          <t>kk_3186206141</t>
         </is>
       </c>
       <c r="B1055" t="inlineStr">
         <is>
-          <t>01074070807</t>
+          <t>01094810924</t>
         </is>
       </c>
       <c r="C1055" t="inlineStr">
         <is>
-          <t>281472</t>
+          <t>230180</t>
         </is>
       </c>
       <c r="D1055" t="inlineStr">
         <is>
-          <t>Organic Traffic</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E1055" t="inlineStr">
         <is>
-          <t>(organic)</t>
+          <t>lms_ecom_200416_family</t>
         </is>
       </c>
     </row>
@@ -28970,54 +28970,54 @@
     <row r="1058">
       <c r="A1058" t="inlineStr">
         <is>
-          <t>kk_4846761310</t>
+          <t>kk_4651201605</t>
         </is>
       </c>
       <c r="B1058" t="inlineStr">
         <is>
-          <t>01091189951</t>
+          <t>01045489411</t>
         </is>
       </c>
       <c r="C1058" t="inlineStr">
         <is>
-          <t>304464</t>
+          <t>293053</t>
         </is>
       </c>
       <c r="D1058" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E1058" t="inlineStr">
         <is>
-          <t>naver_brandsearch_mobile</t>
+          <t>EDM_0411</t>
         </is>
       </c>
     </row>
     <row r="1059">
       <c r="A1059" t="inlineStr">
         <is>
-          <t>kk_4651201605</t>
+          <t>kk_4846761310</t>
         </is>
       </c>
       <c r="B1059" t="inlineStr">
         <is>
-          <t>01045489411</t>
+          <t>01091189951</t>
         </is>
       </c>
       <c r="C1059" t="inlineStr">
         <is>
-          <t>293053</t>
+          <t>304464</t>
         </is>
       </c>
       <c r="D1059" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E1059" t="inlineStr">
         <is>
-          <t>EDM_0411</t>
+          <t>naver_brandsearch_mobile</t>
         </is>
       </c>
     </row>
@@ -29078,44 +29078,44 @@
     <row r="1062">
       <c r="A1062" t="inlineStr">
         <is>
-          <t>kk_4703272205</t>
+          <t>kk_4841799872</t>
         </is>
       </c>
       <c r="B1062" t="inlineStr">
         <is>
-          <t>01062682325</t>
+          <t>01023236956</t>
         </is>
       </c>
       <c r="C1062" t="inlineStr">
         <is>
-          <t>296093</t>
+          <t>304205</t>
         </is>
       </c>
       <c r="D1062" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E1062" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0410exclusive2</t>
+          <t>컬럼비아_DPA_240530</t>
         </is>
       </c>
     </row>
     <row r="1063">
       <c r="A1063" t="inlineStr">
         <is>
-          <t>kk_4841799872</t>
+          <t>nikemkr</t>
         </is>
       </c>
       <c r="B1063" t="inlineStr">
         <is>
-          <t>01023236956</t>
+          <t>01032361592</t>
         </is>
       </c>
       <c r="C1063" t="inlineStr">
         <is>
-          <t>304205</t>
+          <t>145423</t>
         </is>
       </c>
       <c r="D1063" t="inlineStr">
@@ -29125,88 +29125,88 @@
       </c>
       <c r="E1063" t="inlineStr">
         <is>
-          <t>컬럼비아_DPA_240530</t>
+          <t>naver_brandsearch_mobile</t>
         </is>
       </c>
     </row>
     <row r="1064">
       <c r="A1064" t="inlineStr">
         <is>
-          <t>nikemkr</t>
+          <t>kk_4703272205</t>
         </is>
       </c>
       <c r="B1064" t="inlineStr">
         <is>
-          <t>01032361592</t>
+          <t>01062682325</t>
         </is>
       </c>
       <c r="C1064" t="inlineStr">
         <is>
-          <t>145423</t>
+          <t>296093</t>
         </is>
       </c>
       <c r="D1064" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E1064" t="inlineStr">
         <is>
-          <t>naver_brandsearch_mobile</t>
+          <t>LMS_ECOM_0410exclusive2</t>
         </is>
       </c>
     </row>
     <row r="1065">
       <c r="A1065" t="inlineStr">
         <is>
-          <t>sbhbi</t>
+          <t>kk_3241081989</t>
         </is>
       </c>
       <c r="B1065" t="inlineStr">
         <is>
-          <t>01047153767</t>
+          <t>01072287165</t>
         </is>
       </c>
       <c r="C1065" t="inlineStr">
         <is>
-          <t>174291</t>
+          <t>234608</t>
         </is>
       </c>
       <c r="D1065" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E1065" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>KAKAO_alimtalk</t>
         </is>
       </c>
     </row>
     <row r="1066">
       <c r="A1066" t="inlineStr">
         <is>
-          <t>kk_3241081989</t>
+          <t>sbhbi</t>
         </is>
       </c>
       <c r="B1066" t="inlineStr">
         <is>
-          <t>01072287165</t>
+          <t>01047153767</t>
         </is>
       </c>
       <c r="C1066" t="inlineStr">
         <is>
-          <t>234608</t>
+          <t>174291</t>
         </is>
       </c>
       <c r="D1066" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="E1066" t="inlineStr">
         <is>
-          <t>KAKAO_alimtalk</t>
+          <t>Direct</t>
         </is>
       </c>
     </row>
@@ -29456,44 +29456,44 @@
     <row r="1076">
       <c r="A1076" t="inlineStr">
         <is>
-          <t>kk_4406693806</t>
+          <t>kk_4669827711</t>
         </is>
       </c>
       <c r="B1076" t="inlineStr">
         <is>
-          <t>01088675050</t>
+          <t>01091727683</t>
         </is>
       </c>
       <c r="C1076" t="inlineStr">
         <is>
-          <t>280999</t>
+          <t>294249</t>
         </is>
       </c>
       <c r="D1076" t="inlineStr">
         <is>
-          <t>Organic Traffic</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E1076" t="inlineStr">
         <is>
-          <t>(referral)</t>
+          <t>6968489536332</t>
         </is>
       </c>
     </row>
     <row r="1077">
       <c r="A1077" t="inlineStr">
         <is>
-          <t>kk_4669827711</t>
+          <t>kk_4848093455</t>
         </is>
       </c>
       <c r="B1077" t="inlineStr">
         <is>
-          <t>01091727683</t>
+          <t>01023043154</t>
         </is>
       </c>
       <c r="C1077" t="inlineStr">
         <is>
-          <t>294249</t>
+          <t>304517</t>
         </is>
       </c>
       <c r="D1077" t="inlineStr">
@@ -29510,44 +29510,44 @@
     <row r="1078">
       <c r="A1078" t="inlineStr">
         <is>
-          <t>kk_4848093455</t>
+          <t>kk_4406693806</t>
         </is>
       </c>
       <c r="B1078" t="inlineStr">
         <is>
-          <t>01023043154</t>
+          <t>01088675050</t>
         </is>
       </c>
       <c r="C1078" t="inlineStr">
         <is>
-          <t>304517</t>
+          <t>280999</t>
         </is>
       </c>
       <c r="D1078" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Organic Traffic</t>
         </is>
       </c>
       <c r="E1078" t="inlineStr">
         <is>
-          <t>6968489536332</t>
+          <t>(referral)</t>
         </is>
       </c>
     </row>
     <row r="1079">
       <c r="A1079" t="inlineStr">
         <is>
-          <t>ch5115</t>
+          <t>chpuss74</t>
         </is>
       </c>
       <c r="B1079" t="inlineStr">
         <is>
-          <t>01084479339</t>
+          <t>01035361091</t>
         </is>
       </c>
       <c r="C1079" t="inlineStr">
         <is>
-          <t>240557</t>
+          <t>154462</t>
         </is>
       </c>
       <c r="D1079" t="inlineStr">
@@ -29564,206 +29564,206 @@
     <row r="1080">
       <c r="A1080" t="inlineStr">
         <is>
-          <t>imgain0422</t>
+          <t>kk_4846729102</t>
         </is>
       </c>
       <c r="B1080" t="inlineStr">
         <is>
-          <t>01029135546</t>
+          <t>01084771303</t>
         </is>
       </c>
       <c r="C1080" t="inlineStr">
         <is>
-          <t>181451</t>
+          <t>304461</t>
         </is>
       </c>
       <c r="D1080" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E1080" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>6968489536332</t>
         </is>
       </c>
     </row>
     <row r="1081">
       <c r="A1081" t="inlineStr">
         <is>
-          <t>kk_3183517395</t>
+          <t>kk_4845661756</t>
         </is>
       </c>
       <c r="B1081" t="inlineStr">
         <is>
-          <t>01082019936</t>
+          <t>01095936572</t>
         </is>
       </c>
       <c r="C1081" t="inlineStr">
         <is>
-          <t>228501</t>
+          <t>304422</t>
         </is>
       </c>
       <c r="D1081" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E1081" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>6968489536332</t>
         </is>
       </c>
     </row>
     <row r="1082">
       <c r="A1082" t="inlineStr">
         <is>
-          <t>kk_4846729102</t>
+          <t>ch5115</t>
         </is>
       </c>
       <c r="B1082" t="inlineStr">
         <is>
-          <t>01084771303</t>
+          <t>01084479339</t>
         </is>
       </c>
       <c r="C1082" t="inlineStr">
         <is>
-          <t>304461</t>
+          <t>240557</t>
         </is>
       </c>
       <c r="D1082" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="E1082" t="inlineStr">
         <is>
-          <t>6968489536332</t>
+          <t>Direct</t>
         </is>
       </c>
     </row>
     <row r="1083">
       <c r="A1083" t="inlineStr">
         <is>
-          <t>kk_2788668233</t>
+          <t>imgain0422</t>
         </is>
       </c>
       <c r="B1083" t="inlineStr">
         <is>
-          <t>01041696139</t>
+          <t>01029135546</t>
         </is>
       </c>
       <c r="C1083" t="inlineStr">
         <is>
-          <t>210002</t>
+          <t>181451</t>
         </is>
       </c>
       <c r="D1083" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="E1083" t="inlineStr">
         <is>
-          <t>6968489536332</t>
+          <t>Direct</t>
         </is>
       </c>
     </row>
     <row r="1084">
       <c r="A1084" t="inlineStr">
         <is>
-          <t>chpuss74</t>
+          <t>kk_2788668233</t>
         </is>
       </c>
       <c r="B1084" t="inlineStr">
         <is>
-          <t>01035361091</t>
+          <t>01041696139</t>
         </is>
       </c>
       <c r="C1084" t="inlineStr">
         <is>
-          <t>154462</t>
+          <t>210002</t>
         </is>
       </c>
       <c r="D1084" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E1084" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>6968489536332</t>
         </is>
       </c>
     </row>
     <row r="1085">
       <c r="A1085" t="inlineStr">
         <is>
-          <t>kk_4845661756</t>
+          <t>kk_3183517395</t>
         </is>
       </c>
       <c r="B1085" t="inlineStr">
         <is>
-          <t>01095936572</t>
+          <t>01082019936</t>
         </is>
       </c>
       <c r="C1085" t="inlineStr">
         <is>
-          <t>304422</t>
+          <t>228501</t>
         </is>
       </c>
       <c r="D1085" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="E1085" t="inlineStr">
         <is>
-          <t>6968489536332</t>
+          <t>Direct</t>
         </is>
       </c>
     </row>
     <row r="1086">
       <c r="A1086" t="inlineStr">
         <is>
-          <t>goawind</t>
+          <t>kk_2775500473</t>
         </is>
       </c>
       <c r="B1086" t="inlineStr">
         <is>
-          <t>01032738938</t>
+          <t>01045659020</t>
         </is>
       </c>
       <c r="C1086" t="inlineStr">
         <is>
-          <t>232021</t>
+          <t>209371</t>
         </is>
       </c>
       <c r="D1086" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>Organic Traffic</t>
         </is>
       </c>
       <c r="E1086" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>(referral)</t>
         </is>
       </c>
     </row>
     <row r="1087">
       <c r="A1087" t="inlineStr">
         <is>
-          <t>kk_3242479813</t>
+          <t>kjhk5404</t>
         </is>
       </c>
       <c r="B1087" t="inlineStr">
         <is>
-          <t>01040431115</t>
+          <t>01027390700</t>
         </is>
       </c>
       <c r="C1087" t="inlineStr">
         <is>
-          <t>234768</t>
+          <t>280120</t>
         </is>
       </c>
       <c r="D1087" t="inlineStr">
@@ -29773,7 +29773,7 @@
       </c>
       <c r="E1087" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0410exclusive2</t>
+          <t>KAKAO_alimtalk</t>
         </is>
       </c>
     </row>
@@ -29807,17 +29807,17 @@
     <row r="1089">
       <c r="A1089" t="inlineStr">
         <is>
-          <t>kjhk5404</t>
+          <t>kk_3242479813</t>
         </is>
       </c>
       <c r="B1089" t="inlineStr">
         <is>
-          <t>01027390700</t>
+          <t>01040431115</t>
         </is>
       </c>
       <c r="C1089" t="inlineStr">
         <is>
-          <t>280120</t>
+          <t>234768</t>
         </is>
       </c>
       <c r="D1089" t="inlineStr">
@@ -29827,61 +29827,61 @@
       </c>
       <c r="E1089" t="inlineStr">
         <is>
-          <t>KAKAO_alimtalk</t>
+          <t>LMS_ECOM_0410exclusive2</t>
         </is>
       </c>
     </row>
     <row r="1090">
       <c r="A1090" t="inlineStr">
         <is>
-          <t>kk_2775500473</t>
+          <t>kk_4844076820</t>
         </is>
       </c>
       <c r="B1090" t="inlineStr">
         <is>
-          <t>01045659020</t>
+          <t>01091346366</t>
         </is>
       </c>
       <c r="C1090" t="inlineStr">
         <is>
-          <t>209371</t>
+          <t>304343</t>
         </is>
       </c>
       <c r="D1090" t="inlineStr">
         <is>
-          <t>Organic Traffic</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E1090" t="inlineStr">
         <is>
-          <t>(referral)</t>
+          <t>6968489536332</t>
         </is>
       </c>
     </row>
     <row r="1091">
       <c r="A1091" t="inlineStr">
         <is>
-          <t>kk_4844076820</t>
+          <t>goawind</t>
         </is>
       </c>
       <c r="B1091" t="inlineStr">
         <is>
-          <t>01091346366</t>
+          <t>01032738938</t>
         </is>
       </c>
       <c r="C1091" t="inlineStr">
         <is>
-          <t>304343</t>
+          <t>232021</t>
         </is>
       </c>
       <c r="D1091" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="E1091" t="inlineStr">
         <is>
-          <t>6968489536332</t>
+          <t>Direct</t>
         </is>
       </c>
     </row>
@@ -29942,54 +29942,54 @@
     <row r="1094">
       <c r="A1094" t="inlineStr">
         <is>
-          <t>kk_4840817001</t>
+          <t>w0309</t>
         </is>
       </c>
       <c r="B1094" t="inlineStr">
         <is>
-          <t>01085963383</t>
+          <t>01053481702</t>
         </is>
       </c>
       <c r="C1094" t="inlineStr">
         <is>
-          <t>304168</t>
+          <t>126315</t>
         </is>
       </c>
       <c r="D1094" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E1094" t="inlineStr">
         <is>
-          <t>6968489536332</t>
+          <t>Email_mkt</t>
         </is>
       </c>
     </row>
     <row r="1095">
       <c r="A1095" t="inlineStr">
         <is>
-          <t>w0309</t>
+          <t>kk_4840817001</t>
         </is>
       </c>
       <c r="B1095" t="inlineStr">
         <is>
-          <t>01053481702</t>
+          <t>01085963383</t>
         </is>
       </c>
       <c r="C1095" t="inlineStr">
         <is>
-          <t>126315</t>
+          <t>304168</t>
         </is>
       </c>
       <c r="D1095" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E1095" t="inlineStr">
         <is>
-          <t>Email_mkt</t>
+          <t>6968489536332</t>
         </is>
       </c>
     </row>
@@ -30023,125 +30023,125 @@
     <row r="1097">
       <c r="A1097" t="inlineStr">
         <is>
-          <t>xoxoie2</t>
+          <t>kk_4840045474</t>
         </is>
       </c>
       <c r="B1097" t="inlineStr">
         <is>
-          <t>01043560834</t>
+          <t>01096310429</t>
         </is>
       </c>
       <c r="C1097" t="inlineStr">
         <is>
-          <t>304072</t>
+          <t>304122</t>
         </is>
       </c>
       <c r="D1097" t="inlineStr">
         <is>
-          <t>Official SNS</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E1097" t="inlineStr">
         <is>
-          <t>EFW_04</t>
+          <t>6968489536332</t>
         </is>
       </c>
     </row>
     <row r="1098">
       <c r="A1098" t="inlineStr">
         <is>
-          <t>z090909x</t>
+          <t>xoxoie2</t>
         </is>
       </c>
       <c r="B1098" t="inlineStr">
         <is>
-          <t>01092058111</t>
+          <t>01043560834</t>
         </is>
       </c>
       <c r="C1098" t="inlineStr">
         <is>
-          <t>113003</t>
+          <t>304072</t>
         </is>
       </c>
       <c r="D1098" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Official SNS</t>
         </is>
       </c>
       <c r="E1098" t="inlineStr">
         <is>
-          <t>6968489536332</t>
+          <t>EFW_04</t>
         </is>
       </c>
     </row>
     <row r="1099">
       <c r="A1099" t="inlineStr">
         <is>
-          <t>kk_4840045474</t>
+          <t>eyounjoo</t>
         </is>
       </c>
       <c r="B1099" t="inlineStr">
         <is>
-          <t>01096310429</t>
+          <t>01036167949</t>
         </is>
       </c>
       <c r="C1099" t="inlineStr">
         <is>
-          <t>304122</t>
+          <t>283223</t>
         </is>
       </c>
       <c r="D1099" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E1099" t="inlineStr">
         <is>
-          <t>6968489536332</t>
+          <t>LMS_ECOM_0410exclusive2</t>
         </is>
       </c>
     </row>
     <row r="1100">
       <c r="A1100" t="inlineStr">
         <is>
-          <t>eyounjoo</t>
+          <t>z090909x</t>
         </is>
       </c>
       <c r="B1100" t="inlineStr">
         <is>
-          <t>01036167949</t>
+          <t>01092058111</t>
         </is>
       </c>
       <c r="C1100" t="inlineStr">
         <is>
-          <t>283223</t>
+          <t>113003</t>
         </is>
       </c>
       <c r="D1100" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E1100" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0410exclusive2</t>
+          <t>6968489536332</t>
         </is>
       </c>
     </row>
     <row r="1101">
       <c r="A1101" t="inlineStr">
         <is>
-          <t>ssama</t>
+          <t>kk_4228106377</t>
         </is>
       </c>
       <c r="B1101" t="inlineStr">
         <is>
-          <t>01056271982</t>
+          <t>01063165271</t>
         </is>
       </c>
       <c r="C1101" t="inlineStr">
         <is>
-          <t>47874</t>
+          <t>273193</t>
         </is>
       </c>
       <c r="D1101" t="inlineStr">
@@ -30212,17 +30212,17 @@
     <row r="1104">
       <c r="A1104" t="inlineStr">
         <is>
-          <t>kk_4228106377</t>
+          <t>ssama</t>
         </is>
       </c>
       <c r="B1104" t="inlineStr">
         <is>
-          <t>01063165271</t>
+          <t>01056271982</t>
         </is>
       </c>
       <c r="C1104" t="inlineStr">
         <is>
-          <t>273193</t>
+          <t>47874</t>
         </is>
       </c>
       <c r="D1104" t="inlineStr">
@@ -30266,54 +30266,54 @@
     <row r="1106">
       <c r="A1106" t="inlineStr">
         <is>
-          <t>kk_3024318364</t>
+          <t>tnwks1115</t>
         </is>
       </c>
       <c r="B1106" t="inlineStr">
         <is>
-          <t>01050308038</t>
+          <t>01024221364</t>
         </is>
       </c>
       <c r="C1106" t="inlineStr">
         <is>
-          <t>219525</t>
+          <t>275948</t>
         </is>
       </c>
       <c r="D1106" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="E1106" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0410exclusive2</t>
+          <t>Direct</t>
         </is>
       </c>
     </row>
     <row r="1107">
       <c r="A1107" t="inlineStr">
         <is>
-          <t>tnwks1115</t>
+          <t>kk_3024318364</t>
         </is>
       </c>
       <c r="B1107" t="inlineStr">
         <is>
-          <t>01024221364</t>
+          <t>01050308038</t>
         </is>
       </c>
       <c r="C1107" t="inlineStr">
         <is>
-          <t>275948</t>
+          <t>219525</t>
         </is>
       </c>
       <c r="D1107" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E1107" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>LMS_ECOM_0410exclusive2</t>
         </is>
       </c>
     </row>
@@ -30347,71 +30347,71 @@
     <row r="1109">
       <c r="A1109" t="inlineStr">
         <is>
-          <t>mse001</t>
+          <t>kk_4218204827</t>
         </is>
       </c>
       <c r="B1109" t="inlineStr">
         <is>
-          <t>01085185510</t>
+          <t>01023704903</t>
         </is>
       </c>
       <c r="C1109" t="inlineStr">
         <is>
-          <t>227227</t>
+          <t>272698</t>
         </is>
       </c>
       <c r="D1109" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="E1109" t="inlineStr">
         <is>
-          <t>KAKAO_alimtalk</t>
+          <t>Direct</t>
         </is>
       </c>
     </row>
     <row r="1110">
       <c r="A1110" t="inlineStr">
         <is>
-          <t>kk_4218204827</t>
+          <t>mse001</t>
         </is>
       </c>
       <c r="B1110" t="inlineStr">
         <is>
-          <t>01023704903</t>
+          <t>01085185510</t>
         </is>
       </c>
       <c r="C1110" t="inlineStr">
         <is>
-          <t>272698</t>
+          <t>227227</t>
         </is>
       </c>
       <c r="D1110" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E1110" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>KAKAO_alimtalk</t>
         </is>
       </c>
     </row>
     <row r="1111">
       <c r="A1111" t="inlineStr">
         <is>
-          <t>aca1004</t>
+          <t>bluesea063</t>
         </is>
       </c>
       <c r="B1111" t="inlineStr">
         <is>
-          <t>01071740430</t>
+          <t>01032902625</t>
         </is>
       </c>
       <c r="C1111" t="inlineStr">
         <is>
-          <t>171757</t>
+          <t>116772</t>
         </is>
       </c>
       <c r="D1111" t="inlineStr">
@@ -30421,24 +30421,24 @@
       </c>
       <c r="E1111" t="inlineStr">
         <is>
-          <t>KAKAO_alimtalk</t>
+          <t>LMS_ECOM_0410exclusive2</t>
         </is>
       </c>
     </row>
     <row r="1112">
       <c r="A1112" t="inlineStr">
         <is>
-          <t>bluesea063</t>
+          <t>anfrorla</t>
         </is>
       </c>
       <c r="B1112" t="inlineStr">
         <is>
-          <t>01032902625</t>
+          <t>01050991521</t>
         </is>
       </c>
       <c r="C1112" t="inlineStr">
         <is>
-          <t>116772</t>
+          <t>137379</t>
         </is>
       </c>
       <c r="D1112" t="inlineStr">
@@ -30448,7 +30448,7 @@
       </c>
       <c r="E1112" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0410exclusive2</t>
+          <t>LMS_ECOM_200416_family</t>
         </is>
       </c>
     </row>
@@ -30509,17 +30509,17 @@
     <row r="1115">
       <c r="A1115" t="inlineStr">
         <is>
-          <t>anfrorla</t>
+          <t>kk_3001595757</t>
         </is>
       </c>
       <c r="B1115" t="inlineStr">
         <is>
-          <t>01050991521</t>
+          <t>01059491458</t>
         </is>
       </c>
       <c r="C1115" t="inlineStr">
         <is>
-          <t>137379</t>
+          <t>218616</t>
         </is>
       </c>
       <c r="D1115" t="inlineStr">
@@ -30529,24 +30529,24 @@
       </c>
       <c r="E1115" t="inlineStr">
         <is>
-          <t>LMS_ECOM_200416_family</t>
+          <t>KAKAO_alimtalk</t>
         </is>
       </c>
     </row>
     <row r="1116">
       <c r="A1116" t="inlineStr">
         <is>
-          <t>kk_3001595757</t>
+          <t>aca1004</t>
         </is>
       </c>
       <c r="B1116" t="inlineStr">
         <is>
-          <t>01059491458</t>
+          <t>01071740430</t>
         </is>
       </c>
       <c r="C1116" t="inlineStr">
         <is>
-          <t>218616</t>
+          <t>171757</t>
         </is>
       </c>
       <c r="D1116" t="inlineStr">
@@ -30644,152 +30644,152 @@
     <row r="1120">
       <c r="A1120" t="inlineStr">
         <is>
-          <t>kk_2768186596</t>
+          <t>kk_3169777000</t>
         </is>
       </c>
       <c r="B1120" t="inlineStr">
         <is>
-          <t>01029241198</t>
+          <t>01089348462</t>
         </is>
       </c>
       <c r="C1120" t="inlineStr">
         <is>
-          <t>208962</t>
+          <t>224876</t>
         </is>
       </c>
       <c r="D1120" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="E1120" t="inlineStr">
         <is>
-          <t>KAKAO_alimtalk</t>
+          <t>Direct</t>
         </is>
       </c>
     </row>
     <row r="1121">
       <c r="A1121" t="inlineStr">
         <is>
-          <t>kk_3169777000</t>
+          <t>kk_4375003446</t>
         </is>
       </c>
       <c r="B1121" t="inlineStr">
         <is>
-          <t>01089348462</t>
+          <t>01087457282</t>
         </is>
       </c>
       <c r="C1121" t="inlineStr">
         <is>
-          <t>224876</t>
+          <t>280131</t>
         </is>
       </c>
       <c r="D1121" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E1121" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>LMS_ECOM_0410exclusive2</t>
         </is>
       </c>
     </row>
     <row r="1122">
       <c r="A1122" t="inlineStr">
         <is>
-          <t>kk_4375003446</t>
+          <t>kk_4844817541</t>
         </is>
       </c>
       <c r="B1122" t="inlineStr">
         <is>
-          <t>01087457282</t>
+          <t>01046631832</t>
         </is>
       </c>
       <c r="C1122" t="inlineStr">
         <is>
-          <t>280131</t>
+          <t>304380</t>
         </is>
       </c>
       <c r="D1122" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E1122" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0410exclusive2</t>
+          <t>[PF]전환_회원가입(유사)</t>
         </is>
       </c>
     </row>
     <row r="1123">
       <c r="A1123" t="inlineStr">
         <is>
-          <t>kk_4844817541</t>
+          <t>kk_2768186596</t>
         </is>
       </c>
       <c r="B1123" t="inlineStr">
         <is>
-          <t>01046631832</t>
+          <t>01029241198</t>
         </is>
       </c>
       <c r="C1123" t="inlineStr">
         <is>
-          <t>304380</t>
+          <t>208962</t>
         </is>
       </c>
       <c r="D1123" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E1123" t="inlineStr">
         <is>
-          <t>[PF]전환_회원가입(유사)</t>
+          <t>KAKAO_alimtalk</t>
         </is>
       </c>
     </row>
     <row r="1124">
       <c r="A1124" t="inlineStr">
         <is>
-          <t>kk_3444865211</t>
+          <t>kk_3688034999</t>
         </is>
       </c>
       <c r="B1124" t="inlineStr">
         <is>
-          <t>01021964871</t>
+          <t>01025408262</t>
         </is>
       </c>
       <c r="C1124" t="inlineStr">
         <is>
-          <t>242799</t>
+          <t>250755</t>
         </is>
       </c>
       <c r="D1124" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E1124" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>KAKAO_alimtalk</t>
         </is>
       </c>
     </row>
     <row r="1125">
       <c r="A1125" t="inlineStr">
         <is>
-          <t>xuswldls</t>
+          <t>kk_3444865211</t>
         </is>
       </c>
       <c r="B1125" t="inlineStr">
         <is>
-          <t>01027349414</t>
+          <t>01021964871</t>
         </is>
       </c>
       <c r="C1125" t="inlineStr">
         <is>
-          <t>133308</t>
+          <t>242799</t>
         </is>
       </c>
       <c r="D1125" t="inlineStr">
@@ -30806,17 +30806,17 @@
     <row r="1126">
       <c r="A1126" t="inlineStr">
         <is>
-          <t>ohsm0065</t>
+          <t>dongheon20</t>
         </is>
       </c>
       <c r="B1126" t="inlineStr">
         <is>
-          <t>01056170065</t>
+          <t>01052298928</t>
         </is>
       </c>
       <c r="C1126" t="inlineStr">
         <is>
-          <t>74567</t>
+          <t>155362</t>
         </is>
       </c>
       <c r="D1126" t="inlineStr">
@@ -30826,34 +30826,34 @@
       </c>
       <c r="E1126" t="inlineStr">
         <is>
-          <t>[PF]트래픽_유사+관심사</t>
+          <t>6968489536332</t>
         </is>
       </c>
     </row>
     <row r="1127">
       <c r="A1127" t="inlineStr">
         <is>
-          <t>kk_3688034999</t>
+          <t>ohsm0065</t>
         </is>
       </c>
       <c r="B1127" t="inlineStr">
         <is>
-          <t>01025408262</t>
+          <t>01056170065</t>
         </is>
       </c>
       <c r="C1127" t="inlineStr">
         <is>
-          <t>250755</t>
+          <t>74567</t>
         </is>
       </c>
       <c r="D1127" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E1127" t="inlineStr">
         <is>
-          <t>KAKAO_alimtalk</t>
+          <t>[PF]트래픽_유사+관심사</t>
         </is>
       </c>
     </row>
@@ -30887,287 +30887,287 @@
     <row r="1129">
       <c r="A1129" t="inlineStr">
         <is>
-          <t>dongheon20</t>
+          <t>kk_2768989214</t>
         </is>
       </c>
       <c r="B1129" t="inlineStr">
         <is>
-          <t>01052298928</t>
+          <t>01095004289</t>
         </is>
       </c>
       <c r="C1129" t="inlineStr">
         <is>
-          <t>155362</t>
+          <t>209015</t>
         </is>
       </c>
       <c r="D1129" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="E1129" t="inlineStr">
         <is>
-          <t>6968489536332</t>
+          <t>Direct</t>
         </is>
       </c>
     </row>
     <row r="1130">
       <c r="A1130" t="inlineStr">
         <is>
-          <t>kk_2768989214</t>
+          <t>kk_4472536591</t>
         </is>
       </c>
       <c r="B1130" t="inlineStr">
         <is>
-          <t>01095004289</t>
+          <t>01037057526</t>
         </is>
       </c>
       <c r="C1130" t="inlineStr">
         <is>
-          <t>209015</t>
+          <t>283897</t>
         </is>
       </c>
       <c r="D1130" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E1130" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>KAKAO_alimtalk</t>
         </is>
       </c>
     </row>
     <row r="1131">
       <c r="A1131" t="inlineStr">
         <is>
-          <t>kk_4472536591</t>
+          <t>xuswldls</t>
         </is>
       </c>
       <c r="B1131" t="inlineStr">
         <is>
-          <t>01037057526</t>
+          <t>01027349414</t>
         </is>
       </c>
       <c r="C1131" t="inlineStr">
         <is>
-          <t>283897</t>
+          <t>133308</t>
         </is>
       </c>
       <c r="D1131" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="E1131" t="inlineStr">
         <is>
-          <t>KAKAO_alimtalk</t>
+          <t>Direct</t>
         </is>
       </c>
     </row>
     <row r="1132">
       <c r="A1132" t="inlineStr">
         <is>
-          <t>kk_3858585698</t>
+          <t>jobguidance</t>
         </is>
       </c>
       <c r="B1132" t="inlineStr">
         <is>
-          <t>01092163429</t>
+          <t>01026756920</t>
         </is>
       </c>
       <c r="C1132" t="inlineStr">
         <is>
-          <t>265508</t>
+          <t>134664</t>
         </is>
       </c>
       <c r="D1132" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="E1132" t="inlineStr">
         <is>
-          <t>KAKAO_alimtalk</t>
+          <t>Direct</t>
         </is>
       </c>
     </row>
     <row r="1133">
       <c r="A1133" t="inlineStr">
         <is>
-          <t>kk_3837527580</t>
+          <t>kk_3181917333</t>
         </is>
       </c>
       <c r="B1133" t="inlineStr">
         <is>
-          <t>01084311738</t>
+          <t>01072258509</t>
         </is>
       </c>
       <c r="C1133" t="inlineStr">
         <is>
-          <t>264113</t>
+          <t>227380</t>
         </is>
       </c>
       <c r="D1133" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="E1133" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0410exclusive2</t>
+          <t>Direct</t>
         </is>
       </c>
     </row>
     <row r="1134">
       <c r="A1134" t="inlineStr">
         <is>
-          <t>kk_3181917333</t>
+          <t>kk_3837527580</t>
         </is>
       </c>
       <c r="B1134" t="inlineStr">
         <is>
-          <t>01072258509</t>
+          <t>01084311738</t>
         </is>
       </c>
       <c r="C1134" t="inlineStr">
         <is>
-          <t>227380</t>
+          <t>264113</t>
         </is>
       </c>
       <c r="D1134" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E1134" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>LMS_ECOM_0410exclusive2</t>
         </is>
       </c>
     </row>
     <row r="1135">
       <c r="A1135" t="inlineStr">
         <is>
-          <t>nesto1</t>
+          <t>escalater</t>
         </is>
       </c>
       <c r="B1135" t="inlineStr">
         <is>
-          <t>01056603953</t>
+          <t>01090911461</t>
         </is>
       </c>
       <c r="C1135" t="inlineStr">
         <is>
-          <t>125251</t>
+          <t>240051</t>
         </is>
       </c>
       <c r="D1135" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="E1135" t="inlineStr">
         <is>
-          <t>KAKAO_alimtalk</t>
+          <t>Direct</t>
         </is>
       </c>
     </row>
     <row r="1136">
       <c r="A1136" t="inlineStr">
         <is>
-          <t>jobguidance</t>
+          <t>kk_3858585698</t>
         </is>
       </c>
       <c r="B1136" t="inlineStr">
         <is>
-          <t>01026756920</t>
+          <t>01092163429</t>
         </is>
       </c>
       <c r="C1136" t="inlineStr">
         <is>
-          <t>134664</t>
+          <t>265508</t>
         </is>
       </c>
       <c r="D1136" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E1136" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>KAKAO_alimtalk</t>
         </is>
       </c>
     </row>
     <row r="1137">
       <c r="A1137" t="inlineStr">
         <is>
-          <t>escalater</t>
+          <t>nesto1</t>
         </is>
       </c>
       <c r="B1137" t="inlineStr">
         <is>
-          <t>01090911461</t>
+          <t>01056603953</t>
         </is>
       </c>
       <c r="C1137" t="inlineStr">
         <is>
-          <t>240051</t>
+          <t>125251</t>
         </is>
       </c>
       <c r="D1137" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E1137" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>KAKAO_alimtalk</t>
         </is>
       </c>
     </row>
     <row r="1138">
       <c r="A1138" t="inlineStr">
         <is>
-          <t>kk_4840061178</t>
+          <t>kk_4338209948</t>
         </is>
       </c>
       <c r="B1138" t="inlineStr">
         <is>
-          <t>01082357895</t>
+          <t>01088132379</t>
         </is>
       </c>
       <c r="C1138" t="inlineStr">
         <is>
-          <t>304124</t>
+          <t>278781</t>
         </is>
       </c>
       <c r="D1138" t="inlineStr">
         <is>
-          <t>Awareness</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E1138" t="inlineStr">
         <is>
-          <t>benz_running_program_2026_coupon</t>
+          <t>KAKAO_alimtalk</t>
         </is>
       </c>
     </row>
     <row r="1139">
       <c r="A1139" t="inlineStr">
         <is>
-          <t>kk_2940110361</t>
+          <t>kk_3185867832</t>
         </is>
       </c>
       <c r="B1139" t="inlineStr">
         <is>
-          <t>01035353200</t>
+          <t>01022086508</t>
         </is>
       </c>
       <c r="C1139" t="inlineStr">
         <is>
-          <t>216362</t>
+          <t>229863</t>
         </is>
       </c>
       <c r="D1139" t="inlineStr">
@@ -31184,17 +31184,17 @@
     <row r="1140">
       <c r="A1140" t="inlineStr">
         <is>
-          <t>hursean</t>
+          <t>kk_2940110361</t>
         </is>
       </c>
       <c r="B1140" t="inlineStr">
         <is>
-          <t>01091975738</t>
+          <t>01035353200</t>
         </is>
       </c>
       <c r="C1140" t="inlineStr">
         <is>
-          <t>123130</t>
+          <t>216362</t>
         </is>
       </c>
       <c r="D1140" t="inlineStr">
@@ -31204,24 +31204,24 @@
       </c>
       <c r="E1140" t="inlineStr">
         <is>
-          <t>Email_mkt</t>
+          <t>LMS_ECOM_0410exclusive2</t>
         </is>
       </c>
     </row>
     <row r="1141">
       <c r="A1141" t="inlineStr">
         <is>
-          <t>aya6969</t>
+          <t>kk_4467707148</t>
         </is>
       </c>
       <c r="B1141" t="inlineStr">
         <is>
-          <t>01076590009</t>
+          <t>01030843332</t>
         </is>
       </c>
       <c r="C1141" t="inlineStr">
         <is>
-          <t>162562</t>
+          <t>283560</t>
         </is>
       </c>
       <c r="D1141" t="inlineStr">
@@ -31238,17 +31238,17 @@
     <row r="1142">
       <c r="A1142" t="inlineStr">
         <is>
-          <t>kk_4523594127</t>
+          <t>mansoogi</t>
         </is>
       </c>
       <c r="B1142" t="inlineStr">
         <is>
-          <t>01085735215</t>
+          <t>01093240897</t>
         </is>
       </c>
       <c r="C1142" t="inlineStr">
         <is>
-          <t>286358</t>
+          <t>25243</t>
         </is>
       </c>
       <c r="D1142" t="inlineStr">
@@ -31265,98 +31265,98 @@
     <row r="1143">
       <c r="A1143" t="inlineStr">
         <is>
-          <t>mansoogi</t>
+          <t>kk_4840061178</t>
         </is>
       </c>
       <c r="B1143" t="inlineStr">
         <is>
-          <t>01093240897</t>
+          <t>01082357895</t>
         </is>
       </c>
       <c r="C1143" t="inlineStr">
         <is>
-          <t>25243</t>
+          <t>304124</t>
         </is>
       </c>
       <c r="D1143" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Awareness</t>
         </is>
       </c>
       <c r="E1143" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0410exclusive2</t>
+          <t>benz_running_program_2026_coupon</t>
         </is>
       </c>
     </row>
     <row r="1144">
       <c r="A1144" t="inlineStr">
         <is>
-          <t>kk_3933534683</t>
+          <t>hursean</t>
         </is>
       </c>
       <c r="B1144" t="inlineStr">
         <is>
-          <t>01030153796</t>
+          <t>01091975738</t>
         </is>
       </c>
       <c r="C1144" t="inlineStr">
         <is>
-          <t>269069</t>
+          <t>123130</t>
         </is>
       </c>
       <c r="D1144" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E1144" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>Email_mkt</t>
         </is>
       </c>
     </row>
     <row r="1145">
       <c r="A1145" t="inlineStr">
         <is>
-          <t>kk_4467707148</t>
+          <t>kk_3013902343</t>
         </is>
       </c>
       <c r="B1145" t="inlineStr">
         <is>
-          <t>01030843332</t>
+          <t>01051802326</t>
         </is>
       </c>
       <c r="C1145" t="inlineStr">
         <is>
-          <t>283560</t>
+          <t>219219</t>
         </is>
       </c>
       <c r="D1145" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E1145" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0410exclusive2</t>
+          <t>6968489536332</t>
         </is>
       </c>
     </row>
     <row r="1146">
       <c r="A1146" t="inlineStr">
         <is>
-          <t>seul6169</t>
+          <t>aya6969</t>
         </is>
       </c>
       <c r="B1146" t="inlineStr">
         <is>
-          <t>01066116699</t>
+          <t>01076590009</t>
         </is>
       </c>
       <c r="C1146" t="inlineStr">
         <is>
-          <t>234239</t>
+          <t>162562</t>
         </is>
       </c>
       <c r="D1146" t="inlineStr">
@@ -31366,24 +31366,24 @@
       </c>
       <c r="E1146" t="inlineStr">
         <is>
-          <t>KAKAO_alimtalk</t>
+          <t>LMS_ECOM_0410exclusive2</t>
         </is>
       </c>
     </row>
     <row r="1147">
       <c r="A1147" t="inlineStr">
         <is>
-          <t>kk_4338209948</t>
+          <t>kk_4523594127</t>
         </is>
       </c>
       <c r="B1147" t="inlineStr">
         <is>
-          <t>01088132379</t>
+          <t>01085735215</t>
         </is>
       </c>
       <c r="C1147" t="inlineStr">
         <is>
-          <t>278781</t>
+          <t>286358</t>
         </is>
       </c>
       <c r="D1147" t="inlineStr">
@@ -31393,61 +31393,61 @@
       </c>
       <c r="E1147" t="inlineStr">
         <is>
-          <t>KAKAO_alimtalk</t>
+          <t>LMS_ECOM_0410exclusive2</t>
         </is>
       </c>
     </row>
     <row r="1148">
       <c r="A1148" t="inlineStr">
         <is>
-          <t>kk_3013902343</t>
+          <t>seul6169</t>
         </is>
       </c>
       <c r="B1148" t="inlineStr">
         <is>
-          <t>01051802326</t>
+          <t>01066116699</t>
         </is>
       </c>
       <c r="C1148" t="inlineStr">
         <is>
-          <t>219219</t>
+          <t>234239</t>
         </is>
       </c>
       <c r="D1148" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E1148" t="inlineStr">
         <is>
-          <t>6968489536332</t>
+          <t>KAKAO_alimtalk</t>
         </is>
       </c>
     </row>
     <row r="1149">
       <c r="A1149" t="inlineStr">
         <is>
-          <t>kk_3185867832</t>
+          <t>kk_3933534683</t>
         </is>
       </c>
       <c r="B1149" t="inlineStr">
         <is>
-          <t>01022086508</t>
+          <t>01030153796</t>
         </is>
       </c>
       <c r="C1149" t="inlineStr">
         <is>
-          <t>229863</t>
+          <t>269069</t>
         </is>
       </c>
       <c r="D1149" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="E1149" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0410exclusive2</t>
+          <t>Direct</t>
         </is>
       </c>
     </row>
@@ -31508,17 +31508,17 @@
     <row r="1152">
       <c r="A1152" t="inlineStr">
         <is>
-          <t>kk_4608940431</t>
+          <t>kk_3296362697</t>
         </is>
       </c>
       <c r="B1152" t="inlineStr">
         <is>
-          <t>01034834753</t>
+          <t>01032224185</t>
         </is>
       </c>
       <c r="C1152" t="inlineStr">
         <is>
-          <t>289885</t>
+          <t>237406</t>
         </is>
       </c>
       <c r="D1152" t="inlineStr">
@@ -31535,17 +31535,17 @@
     <row r="1153">
       <c r="A1153" t="inlineStr">
         <is>
-          <t>taebaekcc</t>
+          <t>kycho229</t>
         </is>
       </c>
       <c r="B1153" t="inlineStr">
         <is>
-          <t>01090034620</t>
+          <t>01047322138</t>
         </is>
       </c>
       <c r="C1153" t="inlineStr">
         <is>
-          <t>182329</t>
+          <t>22747</t>
         </is>
       </c>
       <c r="D1153" t="inlineStr">
@@ -31555,24 +31555,24 @@
       </c>
       <c r="E1153" t="inlineStr">
         <is>
-          <t>LMS_ECOM_200416_family</t>
+          <t>EDM_0416</t>
         </is>
       </c>
     </row>
     <row r="1154">
       <c r="A1154" t="inlineStr">
         <is>
-          <t>kk_3927027066</t>
+          <t>kk_4358499671</t>
         </is>
       </c>
       <c r="B1154" t="inlineStr">
         <is>
-          <t>01046272823</t>
+          <t>01066507573</t>
         </is>
       </c>
       <c r="C1154" t="inlineStr">
         <is>
-          <t>268818</t>
+          <t>279591</t>
         </is>
       </c>
       <c r="D1154" t="inlineStr">
@@ -31589,17 +31589,17 @@
     <row r="1155">
       <c r="A1155" t="inlineStr">
         <is>
-          <t>kk_3378895949</t>
+          <t>kk_4600690023</t>
         </is>
       </c>
       <c r="B1155" t="inlineStr">
         <is>
-          <t>01040411704</t>
+          <t>01067632977</t>
         </is>
       </c>
       <c r="C1155" t="inlineStr">
         <is>
-          <t>240461</t>
+          <t>289390</t>
         </is>
       </c>
       <c r="D1155" t="inlineStr">
@@ -31616,17 +31616,17 @@
     <row r="1156">
       <c r="A1156" t="inlineStr">
         <is>
-          <t>kk_4600690023</t>
+          <t>kk_3378895949</t>
         </is>
       </c>
       <c r="B1156" t="inlineStr">
         <is>
-          <t>01067632977</t>
+          <t>01040411704</t>
         </is>
       </c>
       <c r="C1156" t="inlineStr">
         <is>
-          <t>289390</t>
+          <t>240461</t>
         </is>
       </c>
       <c r="D1156" t="inlineStr">
@@ -31643,17 +31643,17 @@
     <row r="1157">
       <c r="A1157" t="inlineStr">
         <is>
-          <t>kycho229</t>
+          <t>kk_3654717861</t>
         </is>
       </c>
       <c r="B1157" t="inlineStr">
         <is>
-          <t>01047322138</t>
+          <t>01022661489</t>
         </is>
       </c>
       <c r="C1157" t="inlineStr">
         <is>
-          <t>22747</t>
+          <t>249347</t>
         </is>
       </c>
       <c r="D1157" t="inlineStr">
@@ -31663,24 +31663,24 @@
       </c>
       <c r="E1157" t="inlineStr">
         <is>
-          <t>EDM_0416</t>
+          <t>KAKAO_alimtalk</t>
         </is>
       </c>
     </row>
     <row r="1158">
       <c r="A1158" t="inlineStr">
         <is>
-          <t>kk_3654717861</t>
+          <t>kk_3801403661</t>
         </is>
       </c>
       <c r="B1158" t="inlineStr">
         <is>
-          <t>01022661489</t>
+          <t>01086386165</t>
         </is>
       </c>
       <c r="C1158" t="inlineStr">
         <is>
-          <t>249347</t>
+          <t>259058</t>
         </is>
       </c>
       <c r="D1158" t="inlineStr">
@@ -31690,78 +31690,78 @@
       </c>
       <c r="E1158" t="inlineStr">
         <is>
-          <t>KAKAO_alimtalk</t>
+          <t>LMS_ECOM_200416_family</t>
         </is>
       </c>
     </row>
     <row r="1159">
       <c r="A1159" t="inlineStr">
         <is>
-          <t>kk_3801403661</t>
+          <t>kk_3114284664</t>
         </is>
       </c>
       <c r="B1159" t="inlineStr">
         <is>
-          <t>01086386165</t>
+          <t>01031259752</t>
         </is>
       </c>
       <c r="C1159" t="inlineStr">
         <is>
-          <t>259058</t>
+          <t>222243</t>
         </is>
       </c>
       <c r="D1159" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="E1159" t="inlineStr">
         <is>
-          <t>LMS_ECOM_200416_family</t>
+          <t>Direct</t>
         </is>
       </c>
     </row>
     <row r="1160">
       <c r="A1160" t="inlineStr">
         <is>
-          <t>kk_3114284664</t>
+          <t>kk_3927027066</t>
         </is>
       </c>
       <c r="B1160" t="inlineStr">
         <is>
-          <t>01031259752</t>
+          <t>01046272823</t>
         </is>
       </c>
       <c r="C1160" t="inlineStr">
         <is>
-          <t>222243</t>
+          <t>268818</t>
         </is>
       </c>
       <c r="D1160" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E1160" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>LMS_ECOM_200416_family</t>
         </is>
       </c>
     </row>
     <row r="1161">
       <c r="A1161" t="inlineStr">
         <is>
-          <t>kk_3296362697</t>
+          <t>taebaekcc</t>
         </is>
       </c>
       <c r="B1161" t="inlineStr">
         <is>
-          <t>01032224185</t>
+          <t>01090034620</t>
         </is>
       </c>
       <c r="C1161" t="inlineStr">
         <is>
-          <t>237406</t>
+          <t>182329</t>
         </is>
       </c>
       <c r="D1161" t="inlineStr">
@@ -31778,17 +31778,17 @@
     <row r="1162">
       <c r="A1162" t="inlineStr">
         <is>
-          <t>kk_4358499671</t>
+          <t>kk_4608940431</t>
         </is>
       </c>
       <c r="B1162" t="inlineStr">
         <is>
-          <t>01066507573</t>
+          <t>01034834753</t>
         </is>
       </c>
       <c r="C1162" t="inlineStr">
         <is>
-          <t>279591</t>
+          <t>289885</t>
         </is>
       </c>
       <c r="D1162" t="inlineStr">
@@ -31859,71 +31859,71 @@
     <row r="1165">
       <c r="A1165" t="inlineStr">
         <is>
-          <t>kk_2807863527</t>
+          <t>pentagram</t>
         </is>
       </c>
       <c r="B1165" t="inlineStr">
         <is>
-          <t>01042669625</t>
+          <t>01093327353</t>
         </is>
       </c>
       <c r="C1165" t="inlineStr">
         <is>
-          <t>211605</t>
+          <t>131085</t>
         </is>
       </c>
       <c r="D1165" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E1165" t="inlineStr">
         <is>
-          <t>[PF]전환_회원가입(유사)</t>
+          <t>KAKAO_alimtalk</t>
         </is>
       </c>
     </row>
     <row r="1166">
       <c r="A1166" t="inlineStr">
         <is>
-          <t>pentagram</t>
+          <t>dltndgy99</t>
         </is>
       </c>
       <c r="B1166" t="inlineStr">
         <is>
-          <t>01093327353</t>
+          <t>01024587982</t>
         </is>
       </c>
       <c r="C1166" t="inlineStr">
         <is>
-          <t>131085</t>
+          <t>156217</t>
         </is>
       </c>
       <c r="D1166" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E1166" t="inlineStr">
         <is>
-          <t>KAKAO_alimtalk</t>
+          <t>naver_brandsearch_mobile</t>
         </is>
       </c>
     </row>
     <row r="1167">
       <c r="A1167" t="inlineStr">
         <is>
-          <t>dltndgy99</t>
+          <t>kk_2807863527</t>
         </is>
       </c>
       <c r="B1167" t="inlineStr">
         <is>
-          <t>01024587982</t>
+          <t>01042669625</t>
         </is>
       </c>
       <c r="C1167" t="inlineStr">
         <is>
-          <t>156217</t>
+          <t>211605</t>
         </is>
       </c>
       <c r="D1167" t="inlineStr">
@@ -31933,7 +31933,7 @@
       </c>
       <c r="E1167" t="inlineStr">
         <is>
-          <t>naver_brandsearch_mobile</t>
+          <t>[PF]전환_회원가입(유사)</t>
         </is>
       </c>
     </row>
@@ -31967,81 +31967,81 @@
     <row r="1169">
       <c r="A1169" t="inlineStr">
         <is>
-          <t>wisbrain</t>
+          <t>kk_4427490834</t>
         </is>
       </c>
       <c r="B1169" t="inlineStr">
         <is>
-          <t>01047220186</t>
+          <t>01034704205</t>
         </is>
       </c>
       <c r="C1169" t="inlineStr">
         <is>
-          <t>188067</t>
+          <t>281590</t>
         </is>
       </c>
       <c r="D1169" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E1169" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>LMS_ECOM_0410exclusive2</t>
         </is>
       </c>
     </row>
     <row r="1170">
       <c r="A1170" t="inlineStr">
         <is>
-          <t>kk_4427490834</t>
+          <t>hihijs34</t>
         </is>
       </c>
       <c r="B1170" t="inlineStr">
         <is>
-          <t>01034704205</t>
+          <t>01093230529</t>
         </is>
       </c>
       <c r="C1170" t="inlineStr">
         <is>
-          <t>281590</t>
+          <t>128947</t>
         </is>
       </c>
       <c r="D1170" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E1170" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0410exclusive2</t>
+          <t>[PF]A+SC_상시(1865MF,구매+장바구니)</t>
         </is>
       </c>
     </row>
     <row r="1171">
       <c r="A1171" t="inlineStr">
         <is>
-          <t>hihijs34</t>
+          <t>wisbrain</t>
         </is>
       </c>
       <c r="B1171" t="inlineStr">
         <is>
-          <t>01093230529</t>
+          <t>01047220186</t>
         </is>
       </c>
       <c r="C1171" t="inlineStr">
         <is>
-          <t>128947</t>
+          <t>188067</t>
         </is>
       </c>
       <c r="D1171" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="E1171" t="inlineStr">
         <is>
-          <t>[PF]A+SC_상시(1865MF,구매+장바구니)</t>
+          <t>Direct</t>
         </is>
       </c>
     </row>
@@ -32075,71 +32075,71 @@
     <row r="1173">
       <c r="A1173" t="inlineStr">
         <is>
-          <t>kk_4578503399</t>
+          <t>yongshin</t>
         </is>
       </c>
       <c r="B1173" t="inlineStr">
         <is>
-          <t>01088660330</t>
+          <t>01053867821</t>
         </is>
       </c>
       <c r="C1173" t="inlineStr">
         <is>
-          <t>288374</t>
+          <t>277896</t>
         </is>
       </c>
       <c r="D1173" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="E1173" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0410exclusive2</t>
+          <t>Direct</t>
         </is>
       </c>
     </row>
     <row r="1174">
       <c r="A1174" t="inlineStr">
         <is>
-          <t>kk_4292190414</t>
+          <t>kk_3180736217</t>
         </is>
       </c>
       <c r="B1174" t="inlineStr">
         <is>
-          <t>01095177478</t>
+          <t>01036000343</t>
         </is>
       </c>
       <c r="C1174" t="inlineStr">
         <is>
-          <t>275998</t>
+          <t>226314</t>
         </is>
       </c>
       <c r="D1174" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E1174" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>LMS_ECOM_0410exclusive2</t>
         </is>
       </c>
     </row>
     <row r="1175">
       <c r="A1175" t="inlineStr">
         <is>
-          <t>kk_3349199057</t>
+          <t>pls4u</t>
         </is>
       </c>
       <c r="B1175" t="inlineStr">
         <is>
-          <t>01071630312</t>
+          <t>01085985482</t>
         </is>
       </c>
       <c r="C1175" t="inlineStr">
         <is>
-          <t>239388</t>
+          <t>88257</t>
         </is>
       </c>
       <c r="D1175" t="inlineStr">
@@ -32149,78 +32149,78 @@
       </c>
       <c r="E1175" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0410exclusive2</t>
+          <t>LMS_ECOM_0401_trailrunning</t>
         </is>
       </c>
     </row>
     <row r="1176">
       <c r="A1176" t="inlineStr">
         <is>
-          <t>kk_3180736217</t>
+          <t>kk_4292190414</t>
         </is>
       </c>
       <c r="B1176" t="inlineStr">
         <is>
-          <t>01036000343</t>
+          <t>01095177478</t>
         </is>
       </c>
       <c r="C1176" t="inlineStr">
         <is>
-          <t>226314</t>
+          <t>275998</t>
         </is>
       </c>
       <c r="D1176" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="E1176" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0410exclusive2</t>
+          <t>Direct</t>
         </is>
       </c>
     </row>
     <row r="1177">
       <c r="A1177" t="inlineStr">
         <is>
-          <t>camiblanco</t>
+          <t>kk_3754052831</t>
         </is>
       </c>
       <c r="B1177" t="inlineStr">
         <is>
-          <t>01072190103</t>
+          <t>01092180804</t>
         </is>
       </c>
       <c r="C1177" t="inlineStr">
         <is>
-          <t>232545</t>
+          <t>254339</t>
         </is>
       </c>
       <c r="D1177" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E1177" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>LMS_ECOM_0410exclusive2</t>
         </is>
       </c>
     </row>
     <row r="1178">
       <c r="A1178" t="inlineStr">
         <is>
-          <t>bobjazz</t>
+          <t>columbia7</t>
         </is>
       </c>
       <c r="B1178" t="inlineStr">
         <is>
-          <t>01084090677</t>
+          <t>01050080025</t>
         </is>
       </c>
       <c r="C1178" t="inlineStr">
         <is>
-          <t>186218</t>
+          <t>109980</t>
         </is>
       </c>
       <c r="D1178" t="inlineStr">
@@ -32237,17 +32237,17 @@
     <row r="1179">
       <c r="A1179" t="inlineStr">
         <is>
-          <t>columbia7</t>
+          <t>kk_2825715315</t>
         </is>
       </c>
       <c r="B1179" t="inlineStr">
         <is>
-          <t>01050080025</t>
+          <t>01077229654</t>
         </is>
       </c>
       <c r="C1179" t="inlineStr">
         <is>
-          <t>109980</t>
+          <t>212719</t>
         </is>
       </c>
       <c r="D1179" t="inlineStr">
@@ -32264,17 +32264,17 @@
     <row r="1180">
       <c r="A1180" t="inlineStr">
         <is>
-          <t>pls4u</t>
+          <t>bobjazz</t>
         </is>
       </c>
       <c r="B1180" t="inlineStr">
         <is>
-          <t>01085985482</t>
+          <t>01084090677</t>
         </is>
       </c>
       <c r="C1180" t="inlineStr">
         <is>
-          <t>88257</t>
+          <t>186218</t>
         </is>
       </c>
       <c r="D1180" t="inlineStr">
@@ -32284,24 +32284,24 @@
       </c>
       <c r="E1180" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0401_trailrunning</t>
+          <t>LMS_ECOM_0410exclusive2</t>
         </is>
       </c>
     </row>
     <row r="1181">
       <c r="A1181" t="inlineStr">
         <is>
-          <t>kk_4525043459</t>
+          <t>kk_4578503399</t>
         </is>
       </c>
       <c r="B1181" t="inlineStr">
         <is>
-          <t>01088312135</t>
+          <t>01088660330</t>
         </is>
       </c>
       <c r="C1181" t="inlineStr">
         <is>
-          <t>286464</t>
+          <t>288374</t>
         </is>
       </c>
       <c r="D1181" t="inlineStr">
@@ -32318,44 +32318,44 @@
     <row r="1182">
       <c r="A1182" t="inlineStr">
         <is>
-          <t>dmsql785612</t>
+          <t>kk_3721447783</t>
         </is>
       </c>
       <c r="B1182" t="inlineStr">
         <is>
-          <t>01051590364</t>
+          <t>01051311087</t>
         </is>
       </c>
       <c r="C1182" t="inlineStr">
         <is>
-          <t>137279</t>
+          <t>252252</t>
         </is>
       </c>
       <c r="D1182" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="E1182" t="inlineStr">
         <is>
-          <t>Email_mkt</t>
+          <t>Direct</t>
         </is>
       </c>
     </row>
     <row r="1183">
       <c r="A1183" t="inlineStr">
         <is>
-          <t>sjm700</t>
+          <t>inu21c</t>
         </is>
       </c>
       <c r="B1183" t="inlineStr">
         <is>
-          <t>01077331591</t>
+          <t>01035128236</t>
         </is>
       </c>
       <c r="C1183" t="inlineStr">
         <is>
-          <t>118769</t>
+          <t>131940</t>
         </is>
       </c>
       <c r="D1183" t="inlineStr">
@@ -32372,44 +32372,44 @@
     <row r="1184">
       <c r="A1184" t="inlineStr">
         <is>
-          <t>kk_4452401577</t>
+          <t>camiblanco</t>
         </is>
       </c>
       <c r="B1184" t="inlineStr">
         <is>
-          <t>01047428000</t>
+          <t>01072190103</t>
         </is>
       </c>
       <c r="C1184" t="inlineStr">
         <is>
-          <t>282525</t>
+          <t>232545</t>
         </is>
       </c>
       <c r="D1184" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="E1184" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0410exclusive2</t>
+          <t>Direct</t>
         </is>
       </c>
     </row>
     <row r="1185">
       <c r="A1185" t="inlineStr">
         <is>
-          <t>inu21c</t>
+          <t>kk_4452401577</t>
         </is>
       </c>
       <c r="B1185" t="inlineStr">
         <is>
-          <t>01035128236</t>
+          <t>01047428000</t>
         </is>
       </c>
       <c r="C1185" t="inlineStr">
         <is>
-          <t>131940</t>
+          <t>282525</t>
         </is>
       </c>
       <c r="D1185" t="inlineStr">
@@ -32426,17 +32426,17 @@
     <row r="1186">
       <c r="A1186" t="inlineStr">
         <is>
-          <t>kk_3754052831</t>
+          <t>kk_3973703558</t>
         </is>
       </c>
       <c r="B1186" t="inlineStr">
         <is>
-          <t>01092180804</t>
+          <t>01048590748</t>
         </is>
       </c>
       <c r="C1186" t="inlineStr">
         <is>
-          <t>254339</t>
+          <t>271020</t>
         </is>
       </c>
       <c r="D1186" t="inlineStr">
@@ -32453,44 +32453,44 @@
     <row r="1187">
       <c r="A1187" t="inlineStr">
         <is>
-          <t>kk_3721447783</t>
+          <t>dmsql785612</t>
         </is>
       </c>
       <c r="B1187" t="inlineStr">
         <is>
-          <t>01051311087</t>
+          <t>01051590364</t>
         </is>
       </c>
       <c r="C1187" t="inlineStr">
         <is>
-          <t>252252</t>
+          <t>137279</t>
         </is>
       </c>
       <c r="D1187" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E1187" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>Email_mkt</t>
         </is>
       </c>
     </row>
     <row r="1188">
       <c r="A1188" t="inlineStr">
         <is>
-          <t>kk_3973703558</t>
+          <t>kk_3349199057</t>
         </is>
       </c>
       <c r="B1188" t="inlineStr">
         <is>
-          <t>01048590748</t>
+          <t>01071630312</t>
         </is>
       </c>
       <c r="C1188" t="inlineStr">
         <is>
-          <t>271020</t>
+          <t>239388</t>
         </is>
       </c>
       <c r="D1188" t="inlineStr">
@@ -32507,17 +32507,17 @@
     <row r="1189">
       <c r="A1189" t="inlineStr">
         <is>
-          <t>kk_2825715315</t>
+          <t>sjm700</t>
         </is>
       </c>
       <c r="B1189" t="inlineStr">
         <is>
-          <t>01077229654</t>
+          <t>01077331591</t>
         </is>
       </c>
       <c r="C1189" t="inlineStr">
         <is>
-          <t>212719</t>
+          <t>118769</t>
         </is>
       </c>
       <c r="D1189" t="inlineStr">
@@ -32534,27 +32534,27 @@
     <row r="1190">
       <c r="A1190" t="inlineStr">
         <is>
-          <t>yongshin</t>
+          <t>kk_4525043459</t>
         </is>
       </c>
       <c r="B1190" t="inlineStr">
         <is>
-          <t>01053867821</t>
+          <t>01088312135</t>
         </is>
       </c>
       <c r="C1190" t="inlineStr">
         <is>
-          <t>277896</t>
+          <t>286464</t>
         </is>
       </c>
       <c r="D1190" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E1190" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>LMS_ECOM_0410exclusive2</t>
         </is>
       </c>
     </row>
@@ -32588,17 +32588,17 @@
     <row r="1192">
       <c r="A1192" t="inlineStr">
         <is>
-          <t>olive888888</t>
+          <t>sh5204</t>
         </is>
       </c>
       <c r="B1192" t="inlineStr">
         <is>
-          <t>01029817882</t>
+          <t>01054433018</t>
         </is>
       </c>
       <c r="C1192" t="inlineStr">
         <is>
-          <t>116464</t>
+          <t>263137</t>
         </is>
       </c>
       <c r="D1192" t="inlineStr">
@@ -32615,17 +32615,17 @@
     <row r="1193">
       <c r="A1193" t="inlineStr">
         <is>
-          <t>sh5204</t>
+          <t>tayfun</t>
         </is>
       </c>
       <c r="B1193" t="inlineStr">
         <is>
-          <t>01054433018</t>
+          <t>01083105230</t>
         </is>
       </c>
       <c r="C1193" t="inlineStr">
         <is>
-          <t>263137</t>
+          <t>286336</t>
         </is>
       </c>
       <c r="D1193" t="inlineStr">
@@ -32642,17 +32642,17 @@
     <row r="1194">
       <c r="A1194" t="inlineStr">
         <is>
-          <t>tayfun</t>
+          <t>olive888888</t>
         </is>
       </c>
       <c r="B1194" t="inlineStr">
         <is>
-          <t>01083105230</t>
+          <t>01029817882</t>
         </is>
       </c>
       <c r="C1194" t="inlineStr">
         <is>
-          <t>286336</t>
+          <t>116464</t>
         </is>
       </c>
       <c r="D1194" t="inlineStr">
@@ -32723,17 +32723,17 @@
     <row r="1197">
       <c r="A1197" t="inlineStr">
         <is>
-          <t>alcoholpower</t>
+          <t>happy201106</t>
         </is>
       </c>
       <c r="B1197" t="inlineStr">
         <is>
-          <t>01027629868</t>
+          <t>01090012622</t>
         </is>
       </c>
       <c r="C1197" t="inlineStr">
         <is>
-          <t>252954</t>
+          <t>136050</t>
         </is>
       </c>
       <c r="D1197" t="inlineStr">
@@ -32750,17 +32750,17 @@
     <row r="1198">
       <c r="A1198" t="inlineStr">
         <is>
-          <t>kimms66</t>
+          <t>alcoholpower</t>
         </is>
       </c>
       <c r="B1198" t="inlineStr">
         <is>
-          <t>01057634626</t>
+          <t>01027629868</t>
         </is>
       </c>
       <c r="C1198" t="inlineStr">
         <is>
-          <t>180321</t>
+          <t>252954</t>
         </is>
       </c>
       <c r="D1198" t="inlineStr">
@@ -32777,17 +32777,17 @@
     <row r="1199">
       <c r="A1199" t="inlineStr">
         <is>
-          <t>happy201106</t>
+          <t>kimms66</t>
         </is>
       </c>
       <c r="B1199" t="inlineStr">
         <is>
-          <t>01090012622</t>
+          <t>01057634626</t>
         </is>
       </c>
       <c r="C1199" t="inlineStr">
         <is>
-          <t>136050</t>
+          <t>180321</t>
         </is>
       </c>
       <c r="D1199" t="inlineStr">

--- a/reports/member_funnel/downloads/member_funnel_7d_non_buyer.xlsx
+++ b/reports/member_funnel/downloads/member_funnel_7d_non_buyer.xlsx
@@ -16523,17 +16523,17 @@
     <row r="597">
       <c r="A597" t="inlineStr">
         <is>
-          <t>kk_3483300064</t>
+          <t>kk_4789688431</t>
         </is>
       </c>
       <c r="B597" t="inlineStr">
         <is>
-          <t>01092213404</t>
+          <t>01099981265</t>
         </is>
       </c>
       <c r="C597" t="inlineStr">
         <is>
-          <t>244619</t>
+          <t>302023</t>
         </is>
       </c>
       <c r="D597" t="inlineStr">
@@ -16543,24 +16543,24 @@
       </c>
       <c r="E597" t="inlineStr">
         <is>
-          <t>naver_brandsearch_mobile</t>
+          <t>sa</t>
         </is>
       </c>
     </row>
     <row r="598">
       <c r="A598" t="inlineStr">
         <is>
-          <t>kk_4789688431</t>
+          <t>kk_3483300064</t>
         </is>
       </c>
       <c r="B598" t="inlineStr">
         <is>
-          <t>01099981265</t>
+          <t>01092213404</t>
         </is>
       </c>
       <c r="C598" t="inlineStr">
         <is>
-          <t>302023</t>
+          <t>244619</t>
         </is>
       </c>
       <c r="D598" t="inlineStr">
@@ -16570,7 +16570,7 @@
       </c>
       <c r="E598" t="inlineStr">
         <is>
-          <t>sa</t>
+          <t>naver_brandsearch_mobile</t>
         </is>
       </c>
     </row>
@@ -18035,17 +18035,17 @@
     <row r="653">
       <c r="A653" t="inlineStr">
         <is>
-          <t>shine310</t>
+          <t>lamerkmk</t>
         </is>
       </c>
       <c r="B653" t="inlineStr">
         <is>
-          <t>01030650847</t>
+          <t>01030658494</t>
         </is>
       </c>
       <c r="C653" t="inlineStr">
         <is>
-          <t>171606</t>
+          <t>167002</t>
         </is>
       </c>
       <c r="D653" t="inlineStr">
@@ -18062,17 +18062,17 @@
     <row r="654">
       <c r="A654" t="inlineStr">
         <is>
-          <t>lamerkmk</t>
+          <t>shine310</t>
         </is>
       </c>
       <c r="B654" t="inlineStr">
         <is>
-          <t>01030658494</t>
+          <t>01030650847</t>
         </is>
       </c>
       <c r="C654" t="inlineStr">
         <is>
-          <t>167002</t>
+          <t>171606</t>
         </is>
       </c>
       <c r="D654" t="inlineStr">
@@ -18494,54 +18494,54 @@
     <row r="670">
       <c r="A670" t="inlineStr">
         <is>
-          <t>khkim6620</t>
+          <t>kk_4841965432</t>
         </is>
       </c>
       <c r="B670" t="inlineStr">
         <is>
-          <t>01076876567</t>
+          <t>01032510712</t>
         </is>
       </c>
       <c r="C670" t="inlineStr">
         <is>
-          <t>105445</t>
+          <t>304213</t>
         </is>
       </c>
       <c r="D670" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Organic Traffic</t>
         </is>
       </c>
       <c r="E670" t="inlineStr">
         <is>
-          <t>컬럼비아_DPA_240530</t>
+          <t>(referral)</t>
         </is>
       </c>
     </row>
     <row r="671">
       <c r="A671" t="inlineStr">
         <is>
-          <t>kk_4841965432</t>
+          <t>khkim6620</t>
         </is>
       </c>
       <c r="B671" t="inlineStr">
         <is>
-          <t>01032510712</t>
+          <t>01076876567</t>
         </is>
       </c>
       <c r="C671" t="inlineStr">
         <is>
-          <t>304213</t>
+          <t>105445</t>
         </is>
       </c>
       <c r="D671" t="inlineStr">
         <is>
-          <t>Organic Traffic</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E671" t="inlineStr">
         <is>
-          <t>(referral)</t>
+          <t>컬럼비아_DPA_240530</t>
         </is>
       </c>
     </row>
@@ -18575,17 +18575,17 @@
     <row r="673">
       <c r="A673" t="inlineStr">
         <is>
-          <t>kk_3800115869</t>
+          <t>mylove01</t>
         </is>
       </c>
       <c r="B673" t="inlineStr">
         <is>
-          <t>01074564372</t>
+          <t>01036889669</t>
         </is>
       </c>
       <c r="C673" t="inlineStr">
         <is>
-          <t>258779</t>
+          <t>261917</t>
         </is>
       </c>
       <c r="D673" t="inlineStr">
@@ -18602,17 +18602,17 @@
     <row r="674">
       <c r="A674" t="inlineStr">
         <is>
-          <t>mylove01</t>
+          <t>kk_4633959675</t>
         </is>
       </c>
       <c r="B674" t="inlineStr">
         <is>
-          <t>01036889669</t>
+          <t>01050399548</t>
         </is>
       </c>
       <c r="C674" t="inlineStr">
         <is>
-          <t>261917</t>
+          <t>291972</t>
         </is>
       </c>
       <c r="D674" t="inlineStr">
@@ -18622,24 +18622,24 @@
       </c>
       <c r="E674" t="inlineStr">
         <is>
-          <t>LMS_ECOM_200416_family</t>
+          <t>lms_ecom_200416_family</t>
         </is>
       </c>
     </row>
     <row r="675">
       <c r="A675" t="inlineStr">
         <is>
-          <t>kk_4633959675</t>
+          <t>kk_3800115869</t>
         </is>
       </c>
       <c r="B675" t="inlineStr">
         <is>
-          <t>01050399548</t>
+          <t>01074564372</t>
         </is>
       </c>
       <c r="C675" t="inlineStr">
         <is>
-          <t>291972</t>
+          <t>258779</t>
         </is>
       </c>
       <c r="D675" t="inlineStr">
@@ -18649,7 +18649,7 @@
       </c>
       <c r="E675" t="inlineStr">
         <is>
-          <t>lms_ecom_200416_family</t>
+          <t>LMS_ECOM_200416_family</t>
         </is>
       </c>
     </row>
@@ -19088,17 +19088,17 @@
     <row r="692">
       <c r="A692" t="inlineStr">
         <is>
-          <t>kk_4840846776</t>
+          <t>kk_4840658838</t>
         </is>
       </c>
       <c r="B692" t="inlineStr">
         <is>
-          <t>01055961435</t>
+          <t>01039292600</t>
         </is>
       </c>
       <c r="C692" t="inlineStr">
         <is>
-          <t>304170</t>
+          <t>304158</t>
         </is>
       </c>
       <c r="D692" t="inlineStr">
@@ -19108,24 +19108,24 @@
       </c>
       <c r="E692" t="inlineStr">
         <is>
-          <t>[PF]전환_회원가입(유사)</t>
+          <t>EFW</t>
         </is>
       </c>
     </row>
     <row r="693">
       <c r="A693" t="inlineStr">
         <is>
-          <t>kk_4840658838</t>
+          <t>kk_4840846776</t>
         </is>
       </c>
       <c r="B693" t="inlineStr">
         <is>
-          <t>01039292600</t>
+          <t>01055961435</t>
         </is>
       </c>
       <c r="C693" t="inlineStr">
         <is>
-          <t>304158</t>
+          <t>304170</t>
         </is>
       </c>
       <c r="D693" t="inlineStr">
@@ -19135,7 +19135,7 @@
       </c>
       <c r="E693" t="inlineStr">
         <is>
-          <t>EFW</t>
+          <t>[PF]전환_회원가입(유사)</t>
         </is>
       </c>
     </row>
@@ -19871,17 +19871,17 @@
     <row r="721">
       <c r="A721" t="inlineStr">
         <is>
-          <t>kk_4615020382</t>
+          <t>kk_3180181891</t>
         </is>
       </c>
       <c r="B721" t="inlineStr">
         <is>
-          <t>01092438164</t>
+          <t>01065587969</t>
         </is>
       </c>
       <c r="C721" t="inlineStr">
         <is>
-          <t>290598</t>
+          <t>225645</t>
         </is>
       </c>
       <c r="D721" t="inlineStr">
@@ -19925,17 +19925,17 @@
     <row r="723">
       <c r="A723" t="inlineStr">
         <is>
-          <t>kk_3180181891</t>
+          <t>kk_4615020382</t>
         </is>
       </c>
       <c r="B723" t="inlineStr">
         <is>
-          <t>01065587969</t>
+          <t>01092438164</t>
         </is>
       </c>
       <c r="C723" t="inlineStr">
         <is>
-          <t>225645</t>
+          <t>290598</t>
         </is>
       </c>
       <c r="D723" t="inlineStr">
@@ -21275,17 +21275,17 @@
     <row r="773">
       <c r="A773" t="inlineStr">
         <is>
-          <t>houselong</t>
+          <t>kk_3870022897</t>
         </is>
       </c>
       <c r="B773" t="inlineStr">
         <is>
-          <t>01086426201</t>
+          <t>01022819808</t>
         </is>
       </c>
       <c r="C773" t="inlineStr">
         <is>
-          <t>122085</t>
+          <t>266218</t>
         </is>
       </c>
       <c r="D773" t="inlineStr">
@@ -21302,17 +21302,17 @@
     <row r="774">
       <c r="A774" t="inlineStr">
         <is>
-          <t>kk_3870022897</t>
+          <t>houselong</t>
         </is>
       </c>
       <c r="B774" t="inlineStr">
         <is>
-          <t>01022819808</t>
+          <t>01086426201</t>
         </is>
       </c>
       <c r="C774" t="inlineStr">
         <is>
-          <t>266218</t>
+          <t>122085</t>
         </is>
       </c>
       <c r="D774" t="inlineStr">
@@ -21383,54 +21383,54 @@
     <row r="777">
       <c r="A777" t="inlineStr">
         <is>
-          <t>kk_4839145768</t>
+          <t>sun1381</t>
         </is>
       </c>
       <c r="B777" t="inlineStr">
         <is>
-          <t>01097367898</t>
+          <t>01037709416</t>
         </is>
       </c>
       <c r="C777" t="inlineStr">
         <is>
-          <t>304085</t>
+          <t>278160</t>
         </is>
       </c>
       <c r="D777" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E777" t="inlineStr">
         <is>
-          <t>naver_brandsearch_pc</t>
+          <t>LMS_ECOM_0410exclusive2</t>
         </is>
       </c>
     </row>
     <row r="778">
       <c r="A778" t="inlineStr">
         <is>
-          <t>sun1381</t>
+          <t>kk_4839145768</t>
         </is>
       </c>
       <c r="B778" t="inlineStr">
         <is>
-          <t>01037709416</t>
+          <t>01097367898</t>
         </is>
       </c>
       <c r="C778" t="inlineStr">
         <is>
-          <t>278160</t>
+          <t>304085</t>
         </is>
       </c>
       <c r="D778" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E778" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0410exclusive2</t>
+          <t>naver_brandsearch_pc</t>
         </is>
       </c>
     </row>
@@ -21491,54 +21491,54 @@
     <row r="781">
       <c r="A781" t="inlineStr">
         <is>
-          <t>kk_3795665685</t>
+          <t>kk_3825766318</t>
         </is>
       </c>
       <c r="B781" t="inlineStr">
         <is>
-          <t>01025106852</t>
+          <t>01020085185</t>
         </is>
       </c>
       <c r="C781" t="inlineStr">
         <is>
-          <t>257696</t>
+          <t>263222</t>
         </is>
       </c>
       <c r="D781" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E781" t="inlineStr">
         <is>
-          <t>LMS_ECOM_200416_family</t>
+          <t>컬럼비아_DPA_240530</t>
         </is>
       </c>
     </row>
     <row r="782">
       <c r="A782" t="inlineStr">
         <is>
-          <t>kk_3825766318</t>
+          <t>kk_3795665685</t>
         </is>
       </c>
       <c r="B782" t="inlineStr">
         <is>
-          <t>01020085185</t>
+          <t>01025106852</t>
         </is>
       </c>
       <c r="C782" t="inlineStr">
         <is>
-          <t>263222</t>
+          <t>257696</t>
         </is>
       </c>
       <c r="D782" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E782" t="inlineStr">
         <is>
-          <t>컬럼비아_DPA_240530</t>
+          <t>LMS_ECOM_200416_family</t>
         </is>
       </c>
     </row>
@@ -21869,54 +21869,54 @@
     <row r="795">
       <c r="A795" t="inlineStr">
         <is>
-          <t>kk_3631606950</t>
+          <t>kk_2999650964</t>
         </is>
       </c>
       <c r="B795" t="inlineStr">
         <is>
-          <t>01063256163</t>
+          <t>01073667501</t>
         </is>
       </c>
       <c r="C795" t="inlineStr">
         <is>
-          <t>248164</t>
+          <t>218535</t>
         </is>
       </c>
       <c r="D795" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E795" t="inlineStr">
         <is>
-          <t>미분류</t>
+          <t>bizboard</t>
         </is>
       </c>
     </row>
     <row r="796">
       <c r="A796" t="inlineStr">
         <is>
-          <t>kk_2999650964</t>
+          <t>kk_3631606950</t>
         </is>
       </c>
       <c r="B796" t="inlineStr">
         <is>
-          <t>01073667501</t>
+          <t>01063256163</t>
         </is>
       </c>
       <c r="C796" t="inlineStr">
         <is>
-          <t>218535</t>
+          <t>248164</t>
         </is>
       </c>
       <c r="D796" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="E796" t="inlineStr">
         <is>
-          <t>bizboard</t>
+          <t>미분류</t>
         </is>
       </c>
     </row>
@@ -22193,17 +22193,17 @@
     <row r="807">
       <c r="A807" t="inlineStr">
         <is>
-          <t>abril80</t>
+          <t>kang481127</t>
         </is>
       </c>
       <c r="B807" t="inlineStr">
         <is>
-          <t>01032942835</t>
+          <t>01053764012</t>
         </is>
       </c>
       <c r="C807" t="inlineStr">
         <is>
-          <t>192610</t>
+          <t>304276</t>
         </is>
       </c>
       <c r="D807" t="inlineStr">
@@ -22213,24 +22213,24 @@
       </c>
       <c r="E807" t="inlineStr">
         <is>
-          <t>Email_mkt</t>
+          <t>LMS_ECOM_NEWMEMBER</t>
         </is>
       </c>
     </row>
     <row r="808">
       <c r="A808" t="inlineStr">
         <is>
-          <t>kang481127</t>
+          <t>abril80</t>
         </is>
       </c>
       <c r="B808" t="inlineStr">
         <is>
-          <t>01053764012</t>
+          <t>01032942835</t>
         </is>
       </c>
       <c r="C808" t="inlineStr">
         <is>
-          <t>304276</t>
+          <t>192610</t>
         </is>
       </c>
       <c r="D808" t="inlineStr">
@@ -22240,7 +22240,7 @@
       </c>
       <c r="E808" t="inlineStr">
         <is>
-          <t>LMS_ECOM_NEWMEMBER</t>
+          <t>Email_mkt</t>
         </is>
       </c>
     </row>
@@ -22436,44 +22436,44 @@
     <row r="816">
       <c r="A816" t="inlineStr">
         <is>
-          <t>kk_3392066640</t>
+          <t>kk_4639169718</t>
         </is>
       </c>
       <c r="B816" t="inlineStr">
         <is>
-          <t>01065021283</t>
+          <t>01041380770</t>
         </is>
       </c>
       <c r="C816" t="inlineStr">
         <is>
-          <t>240983</t>
+          <t>292319</t>
         </is>
       </c>
       <c r="D816" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E816" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0410exclusive2</t>
+          <t>naver_brandsearch_mobile</t>
         </is>
       </c>
     </row>
     <row r="817">
       <c r="A817" t="inlineStr">
         <is>
-          <t>athend</t>
+          <t>kk_3392066640</t>
         </is>
       </c>
       <c r="B817" t="inlineStr">
         <is>
-          <t>01041786462</t>
+          <t>01065021283</t>
         </is>
       </c>
       <c r="C817" t="inlineStr">
         <is>
-          <t>285491</t>
+          <t>240983</t>
         </is>
       </c>
       <c r="D817" t="inlineStr">
@@ -22483,51 +22483,51 @@
       </c>
       <c r="E817" t="inlineStr">
         <is>
-          <t>KAKAO_alimtalk</t>
+          <t>LMS_ECOM_0410exclusive2</t>
         </is>
       </c>
     </row>
     <row r="818">
       <c r="A818" t="inlineStr">
         <is>
-          <t>kk_4839680663</t>
+          <t>athend</t>
         </is>
       </c>
       <c r="B818" t="inlineStr">
         <is>
-          <t>01046429530</t>
+          <t>01041786462</t>
         </is>
       </c>
       <c r="C818" t="inlineStr">
         <is>
-          <t>304109</t>
+          <t>285491</t>
         </is>
       </c>
       <c r="D818" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E818" t="inlineStr">
         <is>
-          <t>6968489536332</t>
+          <t>KAKAO_alimtalk</t>
         </is>
       </c>
     </row>
     <row r="819">
       <c r="A819" t="inlineStr">
         <is>
-          <t>kk_4639169718</t>
+          <t>kk_4839680663</t>
         </is>
       </c>
       <c r="B819" t="inlineStr">
         <is>
-          <t>01041380770</t>
+          <t>01046429530</t>
         </is>
       </c>
       <c r="C819" t="inlineStr">
         <is>
-          <t>292319</t>
+          <t>304109</t>
         </is>
       </c>
       <c r="D819" t="inlineStr">
@@ -22537,24 +22537,24 @@
       </c>
       <c r="E819" t="inlineStr">
         <is>
-          <t>naver_brandsearch_mobile</t>
+          <t>6968489536332</t>
         </is>
       </c>
     </row>
     <row r="820">
       <c r="A820" t="inlineStr">
         <is>
-          <t>kk_4452113218</t>
+          <t>toplaser</t>
         </is>
       </c>
       <c r="B820" t="inlineStr">
         <is>
-          <t>01066888294</t>
+          <t>01056735155</t>
         </is>
       </c>
       <c r="C820" t="inlineStr">
         <is>
-          <t>282506</t>
+          <t>288028</t>
         </is>
       </c>
       <c r="D820" t="inlineStr">
@@ -22564,24 +22564,24 @@
       </c>
       <c r="E820" t="inlineStr">
         <is>
-          <t>KAKAO_CH_MESSAGE_0226_GOODBYEWINTER</t>
+          <t>LMS_ECOM_0214_newyear</t>
         </is>
       </c>
     </row>
     <row r="821">
       <c r="A821" t="inlineStr">
         <is>
-          <t>toplaser</t>
+          <t>yockk23</t>
         </is>
       </c>
       <c r="B821" t="inlineStr">
         <is>
-          <t>01056735155</t>
+          <t>01031774006</t>
         </is>
       </c>
       <c r="C821" t="inlineStr">
         <is>
-          <t>288028</t>
+          <t>192898</t>
         </is>
       </c>
       <c r="D821" t="inlineStr">
@@ -22591,24 +22591,24 @@
       </c>
       <c r="E821" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0214_newyear</t>
+          <t>LMS_ECOM_0304</t>
         </is>
       </c>
     </row>
     <row r="822">
       <c r="A822" t="inlineStr">
         <is>
-          <t>yockk23</t>
+          <t>kk_4452113218</t>
         </is>
       </c>
       <c r="B822" t="inlineStr">
         <is>
-          <t>01031774006</t>
+          <t>01066888294</t>
         </is>
       </c>
       <c r="C822" t="inlineStr">
         <is>
-          <t>192898</t>
+          <t>282506</t>
         </is>
       </c>
       <c r="D822" t="inlineStr">
@@ -22618,7 +22618,7 @@
       </c>
       <c r="E822" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0304</t>
+          <t>KAKAO_CH_MESSAGE_0226_GOODBYEWINTER</t>
         </is>
       </c>
     </row>
@@ -22733,81 +22733,81 @@
     <row r="827">
       <c r="A827" t="inlineStr">
         <is>
-          <t>isaackwak</t>
+          <t>kk_4839433808</t>
         </is>
       </c>
       <c r="B827" t="inlineStr">
         <is>
-          <t>01090599860</t>
+          <t>01025333388</t>
         </is>
       </c>
       <c r="C827" t="inlineStr">
         <is>
-          <t>275913</t>
+          <t>304100</t>
         </is>
       </c>
       <c r="D827" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E827" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>naver_brandsearch_mobile</t>
         </is>
       </c>
     </row>
     <row r="828">
       <c r="A828" t="inlineStr">
         <is>
-          <t>kk_4839433808</t>
+          <t>mtbok</t>
         </is>
       </c>
       <c r="B828" t="inlineStr">
         <is>
-          <t>01025333388</t>
+          <t>01051284339</t>
         </is>
       </c>
       <c r="C828" t="inlineStr">
         <is>
-          <t>304100</t>
+          <t>26917</t>
         </is>
       </c>
       <c r="D828" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E828" t="inlineStr">
         <is>
-          <t>naver_brandsearch_mobile</t>
+          <t>LMS_ECOM_0410exclusive2</t>
         </is>
       </c>
     </row>
     <row r="829">
       <c r="A829" t="inlineStr">
         <is>
-          <t>mtbok</t>
+          <t>isaackwak</t>
         </is>
       </c>
       <c r="B829" t="inlineStr">
         <is>
-          <t>01051284339</t>
+          <t>01090599860</t>
         </is>
       </c>
       <c r="C829" t="inlineStr">
         <is>
-          <t>26917</t>
+          <t>275913</t>
         </is>
       </c>
       <c r="D829" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="E829" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0410exclusive2</t>
+          <t>Direct</t>
         </is>
       </c>
     </row>
@@ -22976,81 +22976,81 @@
     <row r="836">
       <c r="A836" t="inlineStr">
         <is>
-          <t>kk_3181873063</t>
+          <t>kk_4727921763</t>
         </is>
       </c>
       <c r="B836" t="inlineStr">
         <is>
-          <t>01026527131</t>
+          <t>01045673975</t>
         </is>
       </c>
       <c r="C836" t="inlineStr">
         <is>
-          <t>227343</t>
+          <t>298138</t>
         </is>
       </c>
       <c r="D836" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="E836" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0410exclusive2</t>
+          <t>Direct</t>
         </is>
       </c>
     </row>
     <row r="837">
       <c r="A837" t="inlineStr">
         <is>
-          <t>kk_4839026541</t>
+          <t>kk_3181873063</t>
         </is>
       </c>
       <c r="B837" t="inlineStr">
         <is>
-          <t>01089431507</t>
+          <t>01026527131</t>
         </is>
       </c>
       <c r="C837" t="inlineStr">
         <is>
-          <t>304082</t>
+          <t>227343</t>
         </is>
       </c>
       <c r="D837" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E837" t="inlineStr">
         <is>
-          <t>[PF]전환_상시(2565MF,비구매자)</t>
+          <t>LMS_ECOM_0410exclusive2</t>
         </is>
       </c>
     </row>
     <row r="838">
       <c r="A838" t="inlineStr">
         <is>
-          <t>kk_4727921763</t>
+          <t>kk_4839026541</t>
         </is>
       </c>
       <c r="B838" t="inlineStr">
         <is>
-          <t>01045673975</t>
+          <t>01089431507</t>
         </is>
       </c>
       <c r="C838" t="inlineStr">
         <is>
-          <t>298138</t>
+          <t>304082</t>
         </is>
       </c>
       <c r="D838" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E838" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>[PF]전환_상시(2565MF,비구매자)</t>
         </is>
       </c>
     </row>
@@ -23138,17 +23138,17 @@
     <row r="842">
       <c r="A842" t="inlineStr">
         <is>
-          <t>kk_3334413020</t>
+          <t>jeanne</t>
         </is>
       </c>
       <c r="B842" t="inlineStr">
         <is>
-          <t>01080806386</t>
+          <t>01047490850</t>
         </is>
       </c>
       <c r="C842" t="inlineStr">
         <is>
-          <t>238829</t>
+          <t>195346</t>
         </is>
       </c>
       <c r="D842" t="inlineStr">
@@ -23192,17 +23192,17 @@
     <row r="844">
       <c r="A844" t="inlineStr">
         <is>
-          <t>jeanne</t>
+          <t>sarang21</t>
         </is>
       </c>
       <c r="B844" t="inlineStr">
         <is>
-          <t>01047490850</t>
+          <t>01054975535</t>
         </is>
       </c>
       <c r="C844" t="inlineStr">
         <is>
-          <t>195346</t>
+          <t>268553</t>
         </is>
       </c>
       <c r="D844" t="inlineStr">
@@ -23219,17 +23219,17 @@
     <row r="845">
       <c r="A845" t="inlineStr">
         <is>
-          <t>pbhds102306</t>
+          <t>kk_3810304670</t>
         </is>
       </c>
       <c r="B845" t="inlineStr">
         <is>
-          <t>01062816264</t>
+          <t>01041348052</t>
         </is>
       </c>
       <c r="C845" t="inlineStr">
         <is>
-          <t>266784</t>
+          <t>261190</t>
         </is>
       </c>
       <c r="D845" t="inlineStr">
@@ -23246,44 +23246,44 @@
     <row r="846">
       <c r="A846" t="inlineStr">
         <is>
-          <t>kk_4849696162</t>
+          <t>pbhds102306</t>
         </is>
       </c>
       <c r="B846" t="inlineStr">
         <is>
-          <t>01063383734</t>
+          <t>01062816264</t>
         </is>
       </c>
       <c r="C846" t="inlineStr">
         <is>
-          <t>304570</t>
+          <t>266784</t>
         </is>
       </c>
       <c r="D846" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E846" t="inlineStr">
         <is>
-          <t>컬럼비아_DPA_240530</t>
+          <t>LMS_ECOM_200416_family</t>
         </is>
       </c>
     </row>
     <row r="847">
       <c r="A847" t="inlineStr">
         <is>
-          <t>kk_3810304670</t>
+          <t>kk_3251799831</t>
         </is>
       </c>
       <c r="B847" t="inlineStr">
         <is>
-          <t>01041348052</t>
+          <t>01040006581</t>
         </is>
       </c>
       <c r="C847" t="inlineStr">
         <is>
-          <t>261190</t>
+          <t>235398</t>
         </is>
       </c>
       <c r="D847" t="inlineStr">
@@ -23300,44 +23300,44 @@
     <row r="848">
       <c r="A848" t="inlineStr">
         <is>
-          <t>sarang21</t>
+          <t>kk_4849696162</t>
         </is>
       </c>
       <c r="B848" t="inlineStr">
         <is>
-          <t>01054975535</t>
+          <t>01063383734</t>
         </is>
       </c>
       <c r="C848" t="inlineStr">
         <is>
-          <t>268553</t>
+          <t>304570</t>
         </is>
       </c>
       <c r="D848" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E848" t="inlineStr">
         <is>
-          <t>LMS_ECOM_200416_family</t>
+          <t>컬럼비아_DPA_240530</t>
         </is>
       </c>
     </row>
     <row r="849">
       <c r="A849" t="inlineStr">
         <is>
-          <t>kk_3251799831</t>
+          <t>kk_3334413020</t>
         </is>
       </c>
       <c r="B849" t="inlineStr">
         <is>
-          <t>01040006581</t>
+          <t>01080806386</t>
         </is>
       </c>
       <c r="C849" t="inlineStr">
         <is>
-          <t>235398</t>
+          <t>238829</t>
         </is>
       </c>
       <c r="D849" t="inlineStr">
@@ -23354,17 +23354,17 @@
     <row r="850">
       <c r="A850" t="inlineStr">
         <is>
-          <t>kk_4469973568</t>
+          <t>kk_3210379887</t>
         </is>
       </c>
       <c r="B850" t="inlineStr">
         <is>
-          <t>01087158602</t>
+          <t>01024748405</t>
         </is>
       </c>
       <c r="C850" t="inlineStr">
         <is>
-          <t>283741</t>
+          <t>231651</t>
         </is>
       </c>
       <c r="D850" t="inlineStr">
@@ -23374,24 +23374,24 @@
       </c>
       <c r="E850" t="inlineStr">
         <is>
-          <t>KAKAO_CH_MENU_0211_NEW_MEN</t>
+          <t>LMS_ECOM_0410exclusive2</t>
         </is>
       </c>
     </row>
     <row r="851">
       <c r="A851" t="inlineStr">
         <is>
-          <t>kk_3210379887</t>
+          <t>kk_4469973568</t>
         </is>
       </c>
       <c r="B851" t="inlineStr">
         <is>
-          <t>01024748405</t>
+          <t>01087158602</t>
         </is>
       </c>
       <c r="C851" t="inlineStr">
         <is>
-          <t>231651</t>
+          <t>283741</t>
         </is>
       </c>
       <c r="D851" t="inlineStr">
@@ -23401,7 +23401,7 @@
       </c>
       <c r="E851" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0410exclusive2</t>
+          <t>KAKAO_CH_MENU_0211_NEW_MEN</t>
         </is>
       </c>
     </row>
@@ -23462,17 +23462,17 @@
     <row r="854">
       <c r="A854" t="inlineStr">
         <is>
-          <t>kk_3967419156</t>
+          <t>kk_4600405600</t>
         </is>
       </c>
       <c r="B854" t="inlineStr">
         <is>
-          <t>01030207947</t>
+          <t>01053449477</t>
         </is>
       </c>
       <c r="C854" t="inlineStr">
         <is>
-          <t>270708</t>
+          <t>289364</t>
         </is>
       </c>
       <c r="D854" t="inlineStr">
@@ -23489,17 +23489,17 @@
     <row r="855">
       <c r="A855" t="inlineStr">
         <is>
-          <t>kk_4600405600</t>
+          <t>kk_3967419156</t>
         </is>
       </c>
       <c r="B855" t="inlineStr">
         <is>
-          <t>01053449477</t>
+          <t>01030207947</t>
         </is>
       </c>
       <c r="C855" t="inlineStr">
         <is>
-          <t>289364</t>
+          <t>270708</t>
         </is>
       </c>
       <c r="D855" t="inlineStr">
@@ -23543,17 +23543,17 @@
     <row r="857">
       <c r="A857" t="inlineStr">
         <is>
-          <t>soslsc</t>
+          <t>a3789</t>
         </is>
       </c>
       <c r="B857" t="inlineStr">
         <is>
-          <t>01023174693</t>
+          <t>01053102148</t>
         </is>
       </c>
       <c r="C857" t="inlineStr">
         <is>
-          <t>171035</t>
+          <t>244924</t>
         </is>
       </c>
       <c r="D857" t="inlineStr">
@@ -23570,17 +23570,17 @@
     <row r="858">
       <c r="A858" t="inlineStr">
         <is>
-          <t>a3789</t>
+          <t>soslsc</t>
         </is>
       </c>
       <c r="B858" t="inlineStr">
         <is>
-          <t>01053102148</t>
+          <t>01023174693</t>
         </is>
       </c>
       <c r="C858" t="inlineStr">
         <is>
-          <t>244924</t>
+          <t>171035</t>
         </is>
       </c>
       <c r="D858" t="inlineStr">
@@ -23651,54 +23651,54 @@
     <row r="861">
       <c r="A861" t="inlineStr">
         <is>
-          <t>l00years</t>
+          <t>seizeh</t>
         </is>
       </c>
       <c r="B861" t="inlineStr">
         <is>
-          <t>01053925529</t>
+          <t>01090302539</t>
         </is>
       </c>
       <c r="C861" t="inlineStr">
         <is>
-          <t>229454</t>
+          <t>68751</t>
         </is>
       </c>
       <c r="D861" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E861" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0410exclusive2</t>
+          <t>sa</t>
         </is>
       </c>
     </row>
     <row r="862">
       <c r="A862" t="inlineStr">
         <is>
-          <t>seizeh</t>
+          <t>l00years</t>
         </is>
       </c>
       <c r="B862" t="inlineStr">
         <is>
-          <t>01090302539</t>
+          <t>01053925529</t>
         </is>
       </c>
       <c r="C862" t="inlineStr">
         <is>
-          <t>68751</t>
+          <t>229454</t>
         </is>
       </c>
       <c r="D862" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E862" t="inlineStr">
         <is>
-          <t>sa</t>
+          <t>LMS_ECOM_0410exclusive2</t>
         </is>
       </c>
     </row>
@@ -24029,17 +24029,17 @@
     <row r="875">
       <c r="A875" t="inlineStr">
         <is>
-          <t>kk_4848049317</t>
+          <t>kk_4848573198</t>
         </is>
       </c>
       <c r="B875" t="inlineStr">
         <is>
-          <t>01064006801</t>
+          <t>01081135059</t>
         </is>
       </c>
       <c r="C875" t="inlineStr">
         <is>
-          <t>304514</t>
+          <t>304535</t>
         </is>
       </c>
       <c r="D875" t="inlineStr">
@@ -24049,24 +24049,24 @@
       </c>
       <c r="E875" t="inlineStr">
         <is>
-          <t>[PF]전환_회원가입(유사)</t>
+          <t>(organic)</t>
         </is>
       </c>
     </row>
     <row r="876">
       <c r="A876" t="inlineStr">
         <is>
-          <t>kk_4848573198</t>
+          <t>kk_4848049317</t>
         </is>
       </c>
       <c r="B876" t="inlineStr">
         <is>
-          <t>01081135059</t>
+          <t>01064006801</t>
         </is>
       </c>
       <c r="C876" t="inlineStr">
         <is>
-          <t>304535</t>
+          <t>304514</t>
         </is>
       </c>
       <c r="D876" t="inlineStr">
@@ -24076,7 +24076,7 @@
       </c>
       <c r="E876" t="inlineStr">
         <is>
-          <t>(organic)</t>
+          <t>[PF]전환_회원가입(유사)</t>
         </is>
       </c>
     </row>
@@ -24164,17 +24164,17 @@
     <row r="880">
       <c r="A880" t="inlineStr">
         <is>
-          <t>kk_3793117898</t>
+          <t>kk_3180854377</t>
         </is>
       </c>
       <c r="B880" t="inlineStr">
         <is>
-          <t>01052318168</t>
+          <t>01031216377</t>
         </is>
       </c>
       <c r="C880" t="inlineStr">
         <is>
-          <t>257099</t>
+          <t>226467</t>
         </is>
       </c>
       <c r="D880" t="inlineStr">
@@ -24191,17 +24191,17 @@
     <row r="881">
       <c r="A881" t="inlineStr">
         <is>
-          <t>kk_3180854377</t>
+          <t>kk_3793117898</t>
         </is>
       </c>
       <c r="B881" t="inlineStr">
         <is>
-          <t>01031216377</t>
+          <t>01052318168</t>
         </is>
       </c>
       <c r="C881" t="inlineStr">
         <is>
-          <t>226467</t>
+          <t>257099</t>
         </is>
       </c>
       <c r="D881" t="inlineStr">
@@ -25028,54 +25028,54 @@
     <row r="912">
       <c r="A912" t="inlineStr">
         <is>
-          <t>kk_3919493388</t>
+          <t>kk_3955208505</t>
         </is>
       </c>
       <c r="B912" t="inlineStr">
         <is>
-          <t>01084315028</t>
+          <t>01084144311</t>
         </is>
       </c>
       <c r="C912" t="inlineStr">
         <is>
-          <t>268572</t>
+          <t>270134</t>
         </is>
       </c>
       <c r="D912" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E912" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>KAKAO_CH_MENU_0212_TITANIUM</t>
         </is>
       </c>
     </row>
     <row r="913">
       <c r="A913" t="inlineStr">
         <is>
-          <t>kk_3955208505</t>
+          <t>kk_3919493388</t>
         </is>
       </c>
       <c r="B913" t="inlineStr">
         <is>
-          <t>01084144311</t>
+          <t>01084315028</t>
         </is>
       </c>
       <c r="C913" t="inlineStr">
         <is>
-          <t>270134</t>
+          <t>268572</t>
         </is>
       </c>
       <c r="D913" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E913" t="inlineStr">
         <is>
-          <t>KAKAO_CH_MENU_0212_TITANIUM</t>
+          <t>Paid Ad</t>
         </is>
       </c>
     </row>
@@ -25622,17 +25622,17 @@
     <row r="934">
       <c r="A934" t="inlineStr">
         <is>
-          <t>kk_3595551743</t>
+          <t>holstein</t>
         </is>
       </c>
       <c r="B934" t="inlineStr">
         <is>
-          <t>01025839326</t>
+          <t>01050502500</t>
         </is>
       </c>
       <c r="C934" t="inlineStr">
         <is>
-          <t>246836</t>
+          <t>14062</t>
         </is>
       </c>
       <c r="D934" t="inlineStr">
@@ -25642,24 +25642,24 @@
       </c>
       <c r="E934" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0410exclusive2</t>
+          <t>EDM_TOP</t>
         </is>
       </c>
     </row>
     <row r="935">
       <c r="A935" t="inlineStr">
         <is>
-          <t>holstein</t>
+          <t>kk_3595551743</t>
         </is>
       </c>
       <c r="B935" t="inlineStr">
         <is>
-          <t>01050502500</t>
+          <t>01025839326</t>
         </is>
       </c>
       <c r="C935" t="inlineStr">
         <is>
-          <t>14062</t>
+          <t>246836</t>
         </is>
       </c>
       <c r="D935" t="inlineStr">
@@ -25669,7 +25669,7 @@
       </c>
       <c r="E935" t="inlineStr">
         <is>
-          <t>EDM_TOP</t>
+          <t>LMS_ECOM_0410exclusive2</t>
         </is>
       </c>
     </row>
@@ -25919,17 +25919,17 @@
     <row r="945">
       <c r="A945" t="inlineStr">
         <is>
-          <t>kk_2954504655</t>
+          <t>kk_4844665214</t>
         </is>
       </c>
       <c r="B945" t="inlineStr">
         <is>
-          <t>01024942984</t>
+          <t>01033424745</t>
         </is>
       </c>
       <c r="C945" t="inlineStr">
         <is>
-          <t>242733</t>
+          <t>304377</t>
         </is>
       </c>
       <c r="D945" t="inlineStr">
@@ -25946,54 +25946,54 @@
     <row r="946">
       <c r="A946" t="inlineStr">
         <is>
-          <t>kk_4844665214</t>
+          <t>kk_4843611952</t>
         </is>
       </c>
       <c r="B946" t="inlineStr">
         <is>
-          <t>01033424745</t>
+          <t>01068610131</t>
         </is>
       </c>
       <c r="C946" t="inlineStr">
         <is>
-          <t>304377</t>
+          <t>304327</t>
         </is>
       </c>
       <c r="D946" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E946" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>6968489536332</t>
         </is>
       </c>
     </row>
     <row r="947">
       <c r="A947" t="inlineStr">
         <is>
-          <t>kk_4843611952</t>
+          <t>kk_2954504655</t>
         </is>
       </c>
       <c r="B947" t="inlineStr">
         <is>
-          <t>01068610131</t>
+          <t>01024942984</t>
         </is>
       </c>
       <c r="C947" t="inlineStr">
         <is>
-          <t>304327</t>
+          <t>242733</t>
         </is>
       </c>
       <c r="D947" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="E947" t="inlineStr">
         <is>
-          <t>6968489536332</t>
+          <t>Direct</t>
         </is>
       </c>
     </row>
@@ -26270,54 +26270,54 @@
     <row r="958">
       <c r="A958" t="inlineStr">
         <is>
-          <t>dmsdud552</t>
+          <t>kk_4844530515</t>
         </is>
       </c>
       <c r="B958" t="inlineStr">
         <is>
-          <t>01054633672</t>
+          <t>01054558799</t>
         </is>
       </c>
       <c r="C958" t="inlineStr">
         <is>
-          <t>132110</t>
+          <t>304366</t>
         </is>
       </c>
       <c r="D958" t="inlineStr">
         <is>
-          <t>Organic Traffic</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E958" t="inlineStr">
         <is>
-          <t>(referral)</t>
+          <t>6968489536332</t>
         </is>
       </c>
     </row>
     <row r="959">
       <c r="A959" t="inlineStr">
         <is>
-          <t>kk_4844530515</t>
+          <t>dmsdud552</t>
         </is>
       </c>
       <c r="B959" t="inlineStr">
         <is>
-          <t>01054558799</t>
+          <t>01054633672</t>
         </is>
       </c>
       <c r="C959" t="inlineStr">
         <is>
-          <t>304366</t>
+          <t>132110</t>
         </is>
       </c>
       <c r="D959" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Organic Traffic</t>
         </is>
       </c>
       <c r="E959" t="inlineStr">
         <is>
-          <t>6968489536332</t>
+          <t>(referral)</t>
         </is>
       </c>
     </row>
@@ -26432,125 +26432,125 @@
     <row r="964">
       <c r="A964" t="inlineStr">
         <is>
-          <t>kk_4845121221</t>
+          <t>kk_4843847622</t>
         </is>
       </c>
       <c r="B964" t="inlineStr">
         <is>
-          <t>01044632332</t>
+          <t>01046990393</t>
         </is>
       </c>
       <c r="C964" t="inlineStr">
         <is>
-          <t>304393</t>
+          <t>304336</t>
         </is>
       </c>
       <c r="D964" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Organic Traffic</t>
         </is>
       </c>
       <c r="E964" t="inlineStr">
         <is>
-          <t>6968489536332</t>
+          <t>(organic)</t>
         </is>
       </c>
     </row>
     <row r="965">
       <c r="A965" t="inlineStr">
         <is>
-          <t>kk_4845173313</t>
+          <t>kk_4843926419</t>
         </is>
       </c>
       <c r="B965" t="inlineStr">
         <is>
-          <t>01024436341</t>
+          <t>01034583174</t>
         </is>
       </c>
       <c r="C965" t="inlineStr">
         <is>
-          <t>304397</t>
+          <t>304338</t>
         </is>
       </c>
       <c r="D965" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Official SNS</t>
         </is>
       </c>
       <c r="E965" t="inlineStr">
         <is>
-          <t>6968489536332</t>
+          <t>EFW_04</t>
         </is>
       </c>
     </row>
     <row r="966">
       <c r="A966" t="inlineStr">
         <is>
-          <t>kk_4843926419</t>
+          <t>kk_4845121221</t>
         </is>
       </c>
       <c r="B966" t="inlineStr">
         <is>
-          <t>01034583174</t>
+          <t>01044632332</t>
         </is>
       </c>
       <c r="C966" t="inlineStr">
         <is>
-          <t>304338</t>
+          <t>304393</t>
         </is>
       </c>
       <c r="D966" t="inlineStr">
         <is>
-          <t>Official SNS</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E966" t="inlineStr">
         <is>
-          <t>EFW_04</t>
+          <t>6968489536332</t>
         </is>
       </c>
     </row>
     <row r="967">
       <c r="A967" t="inlineStr">
         <is>
-          <t>kk_4843847622</t>
+          <t>kk_4845173313</t>
         </is>
       </c>
       <c r="B967" t="inlineStr">
         <is>
-          <t>01046990393</t>
+          <t>01024436341</t>
         </is>
       </c>
       <c r="C967" t="inlineStr">
         <is>
-          <t>304336</t>
+          <t>304397</t>
         </is>
       </c>
       <c r="D967" t="inlineStr">
         <is>
-          <t>Organic Traffic</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E967" t="inlineStr">
         <is>
-          <t>(organic)</t>
+          <t>6968489536332</t>
         </is>
       </c>
     </row>
     <row r="968">
       <c r="A968" t="inlineStr">
         <is>
-          <t>kk_4844453283</t>
+          <t>kidultyo</t>
         </is>
       </c>
       <c r="B968" t="inlineStr">
         <is>
-          <t>01090262556</t>
+          <t>01037980315</t>
         </is>
       </c>
       <c r="C968" t="inlineStr">
         <is>
-          <t>304360</t>
+          <t>304331</t>
         </is>
       </c>
       <c r="D968" t="inlineStr">
@@ -26567,17 +26567,17 @@
     <row r="969">
       <c r="A969" t="inlineStr">
         <is>
-          <t>kidultyo</t>
+          <t>kk_4844453283</t>
         </is>
       </c>
       <c r="B969" t="inlineStr">
         <is>
-          <t>01037980315</t>
+          <t>01090262556</t>
         </is>
       </c>
       <c r="C969" t="inlineStr">
         <is>
-          <t>304331</t>
+          <t>304360</t>
         </is>
       </c>
       <c r="D969" t="inlineStr">
@@ -26594,71 +26594,71 @@
     <row r="970">
       <c r="A970" t="inlineStr">
         <is>
-          <t>kyoungs424</t>
+          <t>kk_4840857472</t>
         </is>
       </c>
       <c r="B970" t="inlineStr">
         <is>
-          <t>01041509204</t>
+          <t>01040551807</t>
         </is>
       </c>
       <c r="C970" t="inlineStr">
         <is>
-          <t>153760</t>
+          <t>304172</t>
         </is>
       </c>
       <c r="D970" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="E970" t="inlineStr">
         <is>
-          <t>KAKAO_alimtalk</t>
+          <t>Direct</t>
         </is>
       </c>
     </row>
     <row r="971">
       <c r="A971" t="inlineStr">
         <is>
-          <t>kk_4840857472</t>
+          <t>kk_2961062530</t>
         </is>
       </c>
       <c r="B971" t="inlineStr">
         <is>
-          <t>01040551807</t>
+          <t>01050052823</t>
         </is>
       </c>
       <c r="C971" t="inlineStr">
         <is>
-          <t>304172</t>
+          <t>217199</t>
         </is>
       </c>
       <c r="D971" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E971" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>KAKAO_CH_MENU_0317_S26NEW</t>
         </is>
       </c>
     </row>
     <row r="972">
       <c r="A972" t="inlineStr">
         <is>
-          <t>kk_2961062530</t>
+          <t>kyoungs424</t>
         </is>
       </c>
       <c r="B972" t="inlineStr">
         <is>
-          <t>01050052823</t>
+          <t>01041509204</t>
         </is>
       </c>
       <c r="C972" t="inlineStr">
         <is>
-          <t>217199</t>
+          <t>153760</t>
         </is>
       </c>
       <c r="D972" t="inlineStr">
@@ -26668,7 +26668,7 @@
       </c>
       <c r="E972" t="inlineStr">
         <is>
-          <t>KAKAO_CH_MENU_0317_S26NEW</t>
+          <t>KAKAO_alimtalk</t>
         </is>
       </c>
     </row>
@@ -26756,108 +26756,108 @@
     <row r="976">
       <c r="A976" t="inlineStr">
         <is>
-          <t>kphilius</t>
+          <t>kk_4518898382</t>
         </is>
       </c>
       <c r="B976" t="inlineStr">
         <is>
-          <t>01026117522</t>
+          <t>01063727378</t>
         </is>
       </c>
       <c r="C976" t="inlineStr">
         <is>
-          <t>217796</t>
+          <t>286129</t>
         </is>
       </c>
       <c r="D976" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E976" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>LMS_ECOM_0214_newyear</t>
         </is>
       </c>
     </row>
     <row r="977">
       <c r="A977" t="inlineStr">
         <is>
-          <t>kk_4518898382</t>
+          <t>kphilius</t>
         </is>
       </c>
       <c r="B977" t="inlineStr">
         <is>
-          <t>01063727378</t>
+          <t>01026117522</t>
         </is>
       </c>
       <c r="C977" t="inlineStr">
         <is>
-          <t>286129</t>
+          <t>217796</t>
         </is>
       </c>
       <c r="D977" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="E977" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0214_newyear</t>
+          <t>Direct</t>
         </is>
       </c>
     </row>
     <row r="978">
       <c r="A978" t="inlineStr">
         <is>
-          <t>chibird</t>
+          <t>kk_3601210201</t>
         </is>
       </c>
       <c r="B978" t="inlineStr">
         <is>
-          <t>01031187674</t>
+          <t>01092460423</t>
         </is>
       </c>
       <c r="C978" t="inlineStr">
         <is>
-          <t>219288</t>
+          <t>247035</t>
         </is>
       </c>
       <c r="D978" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="E978" t="inlineStr">
         <is>
-          <t>sa</t>
+          <t>미분류</t>
         </is>
       </c>
     </row>
     <row r="979">
       <c r="A979" t="inlineStr">
         <is>
-          <t>kk_3601210201</t>
+          <t>chibird</t>
         </is>
       </c>
       <c r="B979" t="inlineStr">
         <is>
-          <t>01092460423</t>
+          <t>01031187674</t>
         </is>
       </c>
       <c r="C979" t="inlineStr">
         <is>
-          <t>247035</t>
+          <t>219288</t>
         </is>
       </c>
       <c r="D979" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E979" t="inlineStr">
         <is>
-          <t>미분류</t>
+          <t>sa</t>
         </is>
       </c>
     </row>
@@ -26918,54 +26918,54 @@
     <row r="982">
       <c r="A982" t="inlineStr">
         <is>
-          <t>kk_4446020087</t>
+          <t>kk_3798545067</t>
         </is>
       </c>
       <c r="B982" t="inlineStr">
         <is>
-          <t>01089773053</t>
+          <t>01023751319</t>
         </is>
       </c>
       <c r="C982" t="inlineStr">
         <is>
-          <t>282273</t>
+          <t>258449</t>
         </is>
       </c>
       <c r="D982" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E982" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0214_newyear</t>
+          <t>sa</t>
         </is>
       </c>
     </row>
     <row r="983">
       <c r="A983" t="inlineStr">
         <is>
-          <t>kk_3798545067</t>
+          <t>kk_4446020087</t>
         </is>
       </c>
       <c r="B983" t="inlineStr">
         <is>
-          <t>01023751319</t>
+          <t>01089773053</t>
         </is>
       </c>
       <c r="C983" t="inlineStr">
         <is>
-          <t>258449</t>
+          <t>282273</t>
         </is>
       </c>
       <c r="D983" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E983" t="inlineStr">
         <is>
-          <t>sa</t>
+          <t>LMS_ECOM_0214_newyear</t>
         </is>
       </c>
     </row>
@@ -27242,108 +27242,108 @@
     <row r="994">
       <c r="A994" t="inlineStr">
         <is>
-          <t>kk_4841278242</t>
+          <t>kk_4840417532</t>
         </is>
       </c>
       <c r="B994" t="inlineStr">
         <is>
-          <t>01046197965</t>
+          <t>01053409288</t>
         </is>
       </c>
       <c r="C994" t="inlineStr">
         <is>
-          <t>304190</t>
+          <t>304147</t>
         </is>
       </c>
       <c r="D994" t="inlineStr">
         <is>
-          <t>Organic Traffic</t>
+          <t>Official SNS</t>
         </is>
       </c>
       <c r="E994" t="inlineStr">
         <is>
-          <t>(referral)</t>
+          <t>EFW_04</t>
         </is>
       </c>
     </row>
     <row r="995">
       <c r="A995" t="inlineStr">
         <is>
-          <t>kk_4840913383</t>
+          <t>kk_3977730443</t>
         </is>
       </c>
       <c r="B995" t="inlineStr">
         <is>
-          <t>01099887927</t>
+          <t>01064291828</t>
         </is>
       </c>
       <c r="C995" t="inlineStr">
         <is>
-          <t>304174</t>
+          <t>271278</t>
         </is>
       </c>
       <c r="D995" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E995" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>naver_brandsearch_mobile</t>
         </is>
       </c>
     </row>
     <row r="996">
       <c r="A996" t="inlineStr">
         <is>
-          <t>kk_3977730443</t>
+          <t>kk_4840913383</t>
         </is>
       </c>
       <c r="B996" t="inlineStr">
         <is>
-          <t>01064291828</t>
+          <t>01099887927</t>
         </is>
       </c>
       <c r="C996" t="inlineStr">
         <is>
-          <t>271278</t>
+          <t>304174</t>
         </is>
       </c>
       <c r="D996" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="E996" t="inlineStr">
         <is>
-          <t>naver_brandsearch_mobile</t>
+          <t>Direct</t>
         </is>
       </c>
     </row>
     <row r="997">
       <c r="A997" t="inlineStr">
         <is>
-          <t>kk_4840417532</t>
+          <t>kk_4841278242</t>
         </is>
       </c>
       <c r="B997" t="inlineStr">
         <is>
-          <t>01053409288</t>
+          <t>01046197965</t>
         </is>
       </c>
       <c r="C997" t="inlineStr">
         <is>
-          <t>304147</t>
+          <t>304190</t>
         </is>
       </c>
       <c r="D997" t="inlineStr">
         <is>
-          <t>Official SNS</t>
+          <t>Organic Traffic</t>
         </is>
       </c>
       <c r="E997" t="inlineStr">
         <is>
-          <t>EFW_04</t>
+          <t>(referral)</t>
         </is>
       </c>
     </row>
@@ -27485,27 +27485,27 @@
     <row r="1003">
       <c r="A1003" t="inlineStr">
         <is>
-          <t>chyim</t>
+          <t>kk_3186206141</t>
         </is>
       </c>
       <c r="B1003" t="inlineStr">
         <is>
-          <t>01037519198</t>
+          <t>01094810924</t>
         </is>
       </c>
       <c r="C1003" t="inlineStr">
         <is>
-          <t>255862</t>
+          <t>230180</t>
         </is>
       </c>
       <c r="D1003" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E1003" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>lms_ecom_200416_family</t>
         </is>
       </c>
     </row>
@@ -27539,27 +27539,27 @@
     <row r="1005">
       <c r="A1005" t="inlineStr">
         <is>
-          <t>kk_3186206141</t>
+          <t>chyim</t>
         </is>
       </c>
       <c r="B1005" t="inlineStr">
         <is>
-          <t>01094810924</t>
+          <t>01037519198</t>
         </is>
       </c>
       <c r="C1005" t="inlineStr">
         <is>
-          <t>230180</t>
+          <t>255862</t>
         </is>
       </c>
       <c r="D1005" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="E1005" t="inlineStr">
         <is>
-          <t>lms_ecom_200416_family</t>
+          <t>Direct</t>
         </is>
       </c>
     </row>
@@ -27620,44 +27620,44 @@
     <row r="1008">
       <c r="A1008" t="inlineStr">
         <is>
-          <t>willper</t>
+          <t>kk_4651201605</t>
         </is>
       </c>
       <c r="B1008" t="inlineStr">
         <is>
-          <t>01085343440</t>
+          <t>01045489411</t>
         </is>
       </c>
       <c r="C1008" t="inlineStr">
         <is>
-          <t>304408</t>
+          <t>293053</t>
         </is>
       </c>
       <c r="D1008" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E1008" t="inlineStr">
         <is>
-          <t>6968489536332</t>
+          <t>EDM_0411</t>
         </is>
       </c>
     </row>
     <row r="1009">
       <c r="A1009" t="inlineStr">
         <is>
-          <t>kk_4846761310</t>
+          <t>willper</t>
         </is>
       </c>
       <c r="B1009" t="inlineStr">
         <is>
-          <t>01091189951</t>
+          <t>01085343440</t>
         </is>
       </c>
       <c r="C1009" t="inlineStr">
         <is>
-          <t>304464</t>
+          <t>304408</t>
         </is>
       </c>
       <c r="D1009" t="inlineStr">
@@ -27667,34 +27667,34 @@
       </c>
       <c r="E1009" t="inlineStr">
         <is>
-          <t>naver_brandsearch_mobile</t>
+          <t>6968489536332</t>
         </is>
       </c>
     </row>
     <row r="1010">
       <c r="A1010" t="inlineStr">
         <is>
-          <t>kk_4651201605</t>
+          <t>kk_4846761310</t>
         </is>
       </c>
       <c r="B1010" t="inlineStr">
         <is>
-          <t>01045489411</t>
+          <t>01091189951</t>
         </is>
       </c>
       <c r="C1010" t="inlineStr">
         <is>
-          <t>293053</t>
+          <t>304464</t>
         </is>
       </c>
       <c r="D1010" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E1010" t="inlineStr">
         <is>
-          <t>EDM_0411</t>
+          <t>naver_brandsearch_mobile</t>
         </is>
       </c>
     </row>
@@ -27755,17 +27755,17 @@
     <row r="1013">
       <c r="A1013" t="inlineStr">
         <is>
-          <t>kk_4841799872</t>
+          <t>nikemkr</t>
         </is>
       </c>
       <c r="B1013" t="inlineStr">
         <is>
-          <t>01023236956</t>
+          <t>01032361592</t>
         </is>
       </c>
       <c r="C1013" t="inlineStr">
         <is>
-          <t>304205</t>
+          <t>145423</t>
         </is>
       </c>
       <c r="D1013" t="inlineStr">
@@ -27775,24 +27775,24 @@
       </c>
       <c r="E1013" t="inlineStr">
         <is>
-          <t>컬럼비아_DPA_240530</t>
+          <t>naver_brandsearch_mobile</t>
         </is>
       </c>
     </row>
     <row r="1014">
       <c r="A1014" t="inlineStr">
         <is>
-          <t>nikemkr</t>
+          <t>kk_4841799872</t>
         </is>
       </c>
       <c r="B1014" t="inlineStr">
         <is>
-          <t>01032361592</t>
+          <t>01023236956</t>
         </is>
       </c>
       <c r="C1014" t="inlineStr">
         <is>
-          <t>145423</t>
+          <t>304205</t>
         </is>
       </c>
       <c r="D1014" t="inlineStr">
@@ -27802,7 +27802,7 @@
       </c>
       <c r="E1014" t="inlineStr">
         <is>
-          <t>naver_brandsearch_mobile</t>
+          <t>컬럼비아_DPA_240530</t>
         </is>
       </c>
     </row>
@@ -27836,81 +27836,81 @@
     <row r="1016">
       <c r="A1016" t="inlineStr">
         <is>
-          <t>lolia875</t>
+          <t>sbhbi</t>
         </is>
       </c>
       <c r="B1016" t="inlineStr">
         <is>
-          <t>01067138715</t>
+          <t>01047153767</t>
         </is>
       </c>
       <c r="C1016" t="inlineStr">
         <is>
-          <t>161251</t>
+          <t>174291</t>
         </is>
       </c>
       <c r="D1016" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="E1016" t="inlineStr">
         <is>
-          <t>6968489536332</t>
+          <t>Direct</t>
         </is>
       </c>
     </row>
     <row r="1017">
       <c r="A1017" t="inlineStr">
         <is>
-          <t>kk_3241081989</t>
+          <t>lolia875</t>
         </is>
       </c>
       <c r="B1017" t="inlineStr">
         <is>
-          <t>01072287165</t>
+          <t>01067138715</t>
         </is>
       </c>
       <c r="C1017" t="inlineStr">
         <is>
-          <t>234608</t>
+          <t>161251</t>
         </is>
       </c>
       <c r="D1017" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E1017" t="inlineStr">
         <is>
-          <t>KAKAO_alimtalk</t>
+          <t>6968489536332</t>
         </is>
       </c>
     </row>
     <row r="1018">
       <c r="A1018" t="inlineStr">
         <is>
-          <t>sbhbi</t>
+          <t>kk_3241081989</t>
         </is>
       </c>
       <c r="B1018" t="inlineStr">
         <is>
-          <t>01047153767</t>
+          <t>01072287165</t>
         </is>
       </c>
       <c r="C1018" t="inlineStr">
         <is>
-          <t>174291</t>
+          <t>234608</t>
         </is>
       </c>
       <c r="D1018" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E1018" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>KAKAO_alimtalk</t>
         </is>
       </c>
     </row>
@@ -28025,27 +28025,27 @@
     <row r="1023">
       <c r="A1023" t="inlineStr">
         <is>
-          <t>kk_3811584672</t>
+          <t>kk_2750963357</t>
         </is>
       </c>
       <c r="B1023" t="inlineStr">
         <is>
-          <t>01072331107</t>
+          <t>01033989099</t>
         </is>
       </c>
       <c r="C1023" t="inlineStr">
         <is>
-          <t>261468</t>
+          <t>207617</t>
         </is>
       </c>
       <c r="D1023" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E1023" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>LMS_ECOM_200416_family</t>
         </is>
       </c>
     </row>
@@ -28079,81 +28079,81 @@
     <row r="1025">
       <c r="A1025" t="inlineStr">
         <is>
-          <t>kk_2750963357</t>
+          <t>kk_3811584672</t>
         </is>
       </c>
       <c r="B1025" t="inlineStr">
         <is>
-          <t>01033989099</t>
+          <t>01072331107</t>
         </is>
       </c>
       <c r="C1025" t="inlineStr">
         <is>
-          <t>207617</t>
+          <t>261468</t>
         </is>
       </c>
       <c r="D1025" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="E1025" t="inlineStr">
         <is>
-          <t>LMS_ECOM_200416_family</t>
+          <t>Direct</t>
         </is>
       </c>
     </row>
     <row r="1026">
       <c r="A1026" t="inlineStr">
         <is>
-          <t>kk_4848093455</t>
+          <t>kk_3792750872</t>
         </is>
       </c>
       <c r="B1026" t="inlineStr">
         <is>
-          <t>01023043154</t>
+          <t>01084382636</t>
         </is>
       </c>
       <c r="C1026" t="inlineStr">
         <is>
-          <t>304517</t>
+          <t>256807</t>
         </is>
       </c>
       <c r="D1026" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E1026" t="inlineStr">
         <is>
-          <t>6968489536332</t>
+          <t>KAKAO_CH_MENU_0211_NEW_MEN</t>
         </is>
       </c>
     </row>
     <row r="1027">
       <c r="A1027" t="inlineStr">
         <is>
-          <t>kk_3792750872</t>
+          <t>kk_4848093455</t>
         </is>
       </c>
       <c r="B1027" t="inlineStr">
         <is>
-          <t>01084382636</t>
+          <t>01023043154</t>
         </is>
       </c>
       <c r="C1027" t="inlineStr">
         <is>
-          <t>256807</t>
+          <t>304517</t>
         </is>
       </c>
       <c r="D1027" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E1027" t="inlineStr">
         <is>
-          <t>KAKAO_CH_MENU_0211_NEW_MEN</t>
+          <t>6968489536332</t>
         </is>
       </c>
     </row>
@@ -28214,54 +28214,54 @@
     <row r="1030">
       <c r="A1030" t="inlineStr">
         <is>
-          <t>ch5115</t>
+          <t>kk_4846729102</t>
         </is>
       </c>
       <c r="B1030" t="inlineStr">
         <is>
-          <t>01084479339</t>
+          <t>01084771303</t>
         </is>
       </c>
       <c r="C1030" t="inlineStr">
         <is>
-          <t>240557</t>
+          <t>304461</t>
         </is>
       </c>
       <c r="D1030" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E1030" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>6968489536332</t>
         </is>
       </c>
     </row>
     <row r="1031">
       <c r="A1031" t="inlineStr">
         <is>
-          <t>kk_3183517395</t>
+          <t>kk_4845661756</t>
         </is>
       </c>
       <c r="B1031" t="inlineStr">
         <is>
-          <t>01082019936</t>
+          <t>01095936572</t>
         </is>
       </c>
       <c r="C1031" t="inlineStr">
         <is>
-          <t>228501</t>
+          <t>304422</t>
         </is>
       </c>
       <c r="D1031" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E1031" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>6968489536332</t>
         </is>
       </c>
     </row>
@@ -28295,71 +28295,71 @@
     <row r="1033">
       <c r="A1033" t="inlineStr">
         <is>
-          <t>kk_2788668233</t>
+          <t>ch5115</t>
         </is>
       </c>
       <c r="B1033" t="inlineStr">
         <is>
-          <t>01041696139</t>
+          <t>01084479339</t>
         </is>
       </c>
       <c r="C1033" t="inlineStr">
         <is>
-          <t>210002</t>
+          <t>240557</t>
         </is>
       </c>
       <c r="D1033" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="E1033" t="inlineStr">
         <is>
-          <t>6968489536332</t>
+          <t>Direct</t>
         </is>
       </c>
     </row>
     <row r="1034">
       <c r="A1034" t="inlineStr">
         <is>
-          <t>kk_4846729102</t>
+          <t>imgain0422</t>
         </is>
       </c>
       <c r="B1034" t="inlineStr">
         <is>
-          <t>01084771303</t>
+          <t>01029135546</t>
         </is>
       </c>
       <c r="C1034" t="inlineStr">
         <is>
-          <t>304461</t>
+          <t>181451</t>
         </is>
       </c>
       <c r="D1034" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="E1034" t="inlineStr">
         <is>
-          <t>6968489536332</t>
+          <t>Direct</t>
         </is>
       </c>
     </row>
     <row r="1035">
       <c r="A1035" t="inlineStr">
         <is>
-          <t>kk_4845661756</t>
+          <t>kk_2788668233</t>
         </is>
       </c>
       <c r="B1035" t="inlineStr">
         <is>
-          <t>01095936572</t>
+          <t>01041696139</t>
         </is>
       </c>
       <c r="C1035" t="inlineStr">
         <is>
-          <t>304422</t>
+          <t>210002</t>
         </is>
       </c>
       <c r="D1035" t="inlineStr">
@@ -28376,17 +28376,17 @@
     <row r="1036">
       <c r="A1036" t="inlineStr">
         <is>
-          <t>imgain0422</t>
+          <t>kk_3183517395</t>
         </is>
       </c>
       <c r="B1036" t="inlineStr">
         <is>
-          <t>01029135546</t>
+          <t>01082019936</t>
         </is>
       </c>
       <c r="C1036" t="inlineStr">
         <is>
-          <t>181451</t>
+          <t>228501</t>
         </is>
       </c>
       <c r="D1036" t="inlineStr">
@@ -28403,27 +28403,27 @@
     <row r="1037">
       <c r="A1037" t="inlineStr">
         <is>
-          <t>kk_2775500473</t>
+          <t>kk_3242479813</t>
         </is>
       </c>
       <c r="B1037" t="inlineStr">
         <is>
-          <t>01045659020</t>
+          <t>01040431115</t>
         </is>
       </c>
       <c r="C1037" t="inlineStr">
         <is>
-          <t>209371</t>
+          <t>234768</t>
         </is>
       </c>
       <c r="D1037" t="inlineStr">
         <is>
-          <t>Organic Traffic</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E1037" t="inlineStr">
         <is>
-          <t>(referral)</t>
+          <t>LMS_ECOM_0410exclusive2</t>
         </is>
       </c>
     </row>
@@ -28511,125 +28511,125 @@
     <row r="1041">
       <c r="A1041" t="inlineStr">
         <is>
-          <t>kk_4844076820</t>
+          <t>kk_2775500473</t>
         </is>
       </c>
       <c r="B1041" t="inlineStr">
         <is>
-          <t>01091346366</t>
+          <t>01045659020</t>
         </is>
       </c>
       <c r="C1041" t="inlineStr">
         <is>
-          <t>304343</t>
+          <t>209371</t>
         </is>
       </c>
       <c r="D1041" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Organic Traffic</t>
         </is>
       </c>
       <c r="E1041" t="inlineStr">
         <is>
-          <t>6968489536332</t>
+          <t>(referral)</t>
         </is>
       </c>
     </row>
     <row r="1042">
       <c r="A1042" t="inlineStr">
         <is>
-          <t>kk_3242479813</t>
+          <t>kk_4844076820</t>
         </is>
       </c>
       <c r="B1042" t="inlineStr">
         <is>
-          <t>01040431115</t>
+          <t>01091346366</t>
         </is>
       </c>
       <c r="C1042" t="inlineStr">
         <is>
-          <t>234768</t>
+          <t>304343</t>
         </is>
       </c>
       <c r="D1042" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E1042" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0410exclusive2</t>
+          <t>6968489536332</t>
         </is>
       </c>
     </row>
     <row r="1043">
       <c r="A1043" t="inlineStr">
         <is>
-          <t>kk_4434329905</t>
+          <t>kk_4522711623</t>
         </is>
       </c>
       <c r="B1043" t="inlineStr">
         <is>
-          <t>01071724035</t>
+          <t>01089870313</t>
         </is>
       </c>
       <c r="C1043" t="inlineStr">
         <is>
-          <t>281922</t>
+          <t>286306</t>
         </is>
       </c>
       <c r="D1043" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E1043" t="inlineStr">
         <is>
-          <t>Email_mkt</t>
+          <t>6968489536332</t>
         </is>
       </c>
     </row>
     <row r="1044">
       <c r="A1044" t="inlineStr">
         <is>
-          <t>kk_4522711623</t>
+          <t>kk_4434329905</t>
         </is>
       </c>
       <c r="B1044" t="inlineStr">
         <is>
-          <t>01089870313</t>
+          <t>01071724035</t>
         </is>
       </c>
       <c r="C1044" t="inlineStr">
         <is>
-          <t>286306</t>
+          <t>281922</t>
         </is>
       </c>
       <c r="D1044" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E1044" t="inlineStr">
         <is>
-          <t>6968489536332</t>
+          <t>Email_mkt</t>
         </is>
       </c>
     </row>
     <row r="1045">
       <c r="A1045" t="inlineStr">
         <is>
-          <t>kk_4840817001</t>
+          <t>kk_4841778210</t>
         </is>
       </c>
       <c r="B1045" t="inlineStr">
         <is>
-          <t>01085963383</t>
+          <t>01087814274</t>
         </is>
       </c>
       <c r="C1045" t="inlineStr">
         <is>
-          <t>304168</t>
+          <t>304202</t>
         </is>
       </c>
       <c r="D1045" t="inlineStr">
@@ -28639,105 +28639,105 @@
       </c>
       <c r="E1045" t="inlineStr">
         <is>
-          <t>6968489536332</t>
+          <t>naver_brandsearch_mobile</t>
         </is>
       </c>
     </row>
     <row r="1046">
       <c r="A1046" t="inlineStr">
         <is>
-          <t>kk_4841778210</t>
+          <t>w0309</t>
         </is>
       </c>
       <c r="B1046" t="inlineStr">
         <is>
-          <t>01087814274</t>
+          <t>01053481702</t>
         </is>
       </c>
       <c r="C1046" t="inlineStr">
         <is>
-          <t>304202</t>
+          <t>126315</t>
         </is>
       </c>
       <c r="D1046" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E1046" t="inlineStr">
         <is>
-          <t>naver_brandsearch_mobile</t>
+          <t>Email_mkt</t>
         </is>
       </c>
     </row>
     <row r="1047">
       <c r="A1047" t="inlineStr">
         <is>
-          <t>w0309</t>
+          <t>kk_4840817001</t>
         </is>
       </c>
       <c r="B1047" t="inlineStr">
         <is>
-          <t>01053481702</t>
+          <t>01085963383</t>
         </is>
       </c>
       <c r="C1047" t="inlineStr">
         <is>
-          <t>126315</t>
+          <t>304168</t>
         </is>
       </c>
       <c r="D1047" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E1047" t="inlineStr">
         <is>
-          <t>Email_mkt</t>
+          <t>6968489536332</t>
         </is>
       </c>
     </row>
     <row r="1048">
       <c r="A1048" t="inlineStr">
         <is>
-          <t>z090909x</t>
+          <t>kk_3213636735</t>
         </is>
       </c>
       <c r="B1048" t="inlineStr">
         <is>
-          <t>01092058111</t>
+          <t>01071338973</t>
         </is>
       </c>
       <c r="C1048" t="inlineStr">
         <is>
-          <t>113003</t>
+          <t>232010</t>
         </is>
       </c>
       <c r="D1048" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E1048" t="inlineStr">
         <is>
-          <t>6968489536332</t>
+          <t>KAKAO_CH_MENU_0226_TRAILRUN</t>
         </is>
       </c>
     </row>
     <row r="1049">
       <c r="A1049" t="inlineStr">
         <is>
-          <t>eyounjoo</t>
+          <t>gus7526</t>
         </is>
       </c>
       <c r="B1049" t="inlineStr">
         <is>
-          <t>01036167949</t>
+          <t>01050931023</t>
         </is>
       </c>
       <c r="C1049" t="inlineStr">
         <is>
-          <t>283223</t>
+          <t>140860</t>
         </is>
       </c>
       <c r="D1049" t="inlineStr">
@@ -28754,71 +28754,71 @@
     <row r="1050">
       <c r="A1050" t="inlineStr">
         <is>
-          <t>ssama</t>
+          <t>z090909x</t>
         </is>
       </c>
       <c r="B1050" t="inlineStr">
         <is>
-          <t>01056271982</t>
+          <t>01092058111</t>
         </is>
       </c>
       <c r="C1050" t="inlineStr">
         <is>
-          <t>47874</t>
+          <t>113003</t>
         </is>
       </c>
       <c r="D1050" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E1050" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0410exclusive2</t>
+          <t>6968489536332</t>
         </is>
       </c>
     </row>
     <row r="1051">
       <c r="A1051" t="inlineStr">
         <is>
-          <t>kk_4840045474</t>
+          <t>xoxoie2</t>
         </is>
       </c>
       <c r="B1051" t="inlineStr">
         <is>
-          <t>01096310429</t>
+          <t>01043560834</t>
         </is>
       </c>
       <c r="C1051" t="inlineStr">
         <is>
-          <t>304122</t>
+          <t>304072</t>
         </is>
       </c>
       <c r="D1051" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Official SNS</t>
         </is>
       </c>
       <c r="E1051" t="inlineStr">
         <is>
-          <t>6968489536332</t>
+          <t>EFW_04</t>
         </is>
       </c>
     </row>
     <row r="1052">
       <c r="A1052" t="inlineStr">
         <is>
-          <t>kk_3213636735</t>
+          <t>ssama</t>
         </is>
       </c>
       <c r="B1052" t="inlineStr">
         <is>
-          <t>01071338973</t>
+          <t>01056271982</t>
         </is>
       </c>
       <c r="C1052" t="inlineStr">
         <is>
-          <t>232010</t>
+          <t>47874</t>
         </is>
       </c>
       <c r="D1052" t="inlineStr">
@@ -28828,51 +28828,51 @@
       </c>
       <c r="E1052" t="inlineStr">
         <is>
-          <t>KAKAO_CH_MENU_0226_TRAILRUN</t>
+          <t>LMS_ECOM_0410exclusive2</t>
         </is>
       </c>
     </row>
     <row r="1053">
       <c r="A1053" t="inlineStr">
         <is>
-          <t>xoxoie2</t>
+          <t>kk_4840045474</t>
         </is>
       </c>
       <c r="B1053" t="inlineStr">
         <is>
-          <t>01043560834</t>
+          <t>01096310429</t>
         </is>
       </c>
       <c r="C1053" t="inlineStr">
         <is>
-          <t>304072</t>
+          <t>304122</t>
         </is>
       </c>
       <c r="D1053" t="inlineStr">
         <is>
-          <t>Official SNS</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E1053" t="inlineStr">
         <is>
-          <t>EFW_04</t>
+          <t>6968489536332</t>
         </is>
       </c>
     </row>
     <row r="1054">
       <c r="A1054" t="inlineStr">
         <is>
-          <t>gus7526</t>
+          <t>kk_4228106377</t>
         </is>
       </c>
       <c r="B1054" t="inlineStr">
         <is>
-          <t>01050931023</t>
+          <t>01063165271</t>
         </is>
       </c>
       <c r="C1054" t="inlineStr">
         <is>
-          <t>140860</t>
+          <t>273193</t>
         </is>
       </c>
       <c r="D1054" t="inlineStr">
@@ -28889,17 +28889,17 @@
     <row r="1055">
       <c r="A1055" t="inlineStr">
         <is>
-          <t>kk_4228106377</t>
+          <t>eyounjoo</t>
         </is>
       </c>
       <c r="B1055" t="inlineStr">
         <is>
-          <t>01063165271</t>
+          <t>01036167949</t>
         </is>
       </c>
       <c r="C1055" t="inlineStr">
         <is>
-          <t>273193</t>
+          <t>283223</t>
         </is>
       </c>
       <c r="D1055" t="inlineStr">
@@ -29078,17 +29078,17 @@
     <row r="1062">
       <c r="A1062" t="inlineStr">
         <is>
-          <t>kk_3001595757</t>
+          <t>kk_4352927664</t>
         </is>
       </c>
       <c r="B1062" t="inlineStr">
         <is>
-          <t>01059491458</t>
+          <t>01058770905</t>
         </is>
       </c>
       <c r="C1062" t="inlineStr">
         <is>
-          <t>218616</t>
+          <t>279347</t>
         </is>
       </c>
       <c r="D1062" t="inlineStr">
@@ -29098,51 +29098,51 @@
       </c>
       <c r="E1062" t="inlineStr">
         <is>
-          <t>KAKAO_alimtalk</t>
+          <t>LMS_ECOM_200416_family</t>
         </is>
       </c>
     </row>
     <row r="1063">
       <c r="A1063" t="inlineStr">
         <is>
-          <t>anfrorla</t>
+          <t>quito3</t>
         </is>
       </c>
       <c r="B1063" t="inlineStr">
         <is>
-          <t>01050991521</t>
+          <t>01073440379</t>
         </is>
       </c>
       <c r="C1063" t="inlineStr">
         <is>
-          <t>137379</t>
+          <t>126578</t>
         </is>
       </c>
       <c r="D1063" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="E1063" t="inlineStr">
         <is>
-          <t>LMS_ECOM_200416_family</t>
+          <t>Direct</t>
         </is>
       </c>
     </row>
     <row r="1064">
       <c r="A1064" t="inlineStr">
         <is>
-          <t>aca1004</t>
+          <t>bluesea063</t>
         </is>
       </c>
       <c r="B1064" t="inlineStr">
         <is>
-          <t>01071740430</t>
+          <t>01032902625</t>
         </is>
       </c>
       <c r="C1064" t="inlineStr">
         <is>
-          <t>171757</t>
+          <t>116772</t>
         </is>
       </c>
       <c r="D1064" t="inlineStr">
@@ -29152,24 +29152,24 @@
       </c>
       <c r="E1064" t="inlineStr">
         <is>
-          <t>KAKAO_alimtalk</t>
+          <t>LMS_ECOM_0410exclusive2</t>
         </is>
       </c>
     </row>
     <row r="1065">
       <c r="A1065" t="inlineStr">
         <is>
-          <t>bluesea063</t>
+          <t>aca1004</t>
         </is>
       </c>
       <c r="B1065" t="inlineStr">
         <is>
-          <t>01032902625</t>
+          <t>01071740430</t>
         </is>
       </c>
       <c r="C1065" t="inlineStr">
         <is>
-          <t>116772</t>
+          <t>171757</t>
         </is>
       </c>
       <c r="D1065" t="inlineStr">
@@ -29179,51 +29179,51 @@
       </c>
       <c r="E1065" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0410exclusive2</t>
+          <t>KAKAO_alimtalk</t>
         </is>
       </c>
     </row>
     <row r="1066">
       <c r="A1066" t="inlineStr">
         <is>
-          <t>quito3</t>
+          <t>anfrorla</t>
         </is>
       </c>
       <c r="B1066" t="inlineStr">
         <is>
-          <t>01073440379</t>
+          <t>01050991521</t>
         </is>
       </c>
       <c r="C1066" t="inlineStr">
         <is>
-          <t>126578</t>
+          <t>137379</t>
         </is>
       </c>
       <c r="D1066" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E1066" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>LMS_ECOM_200416_family</t>
         </is>
       </c>
     </row>
     <row r="1067">
       <c r="A1067" t="inlineStr">
         <is>
-          <t>kk_4352927664</t>
+          <t>kk_3001595757</t>
         </is>
       </c>
       <c r="B1067" t="inlineStr">
         <is>
-          <t>01058770905</t>
+          <t>01059491458</t>
         </is>
       </c>
       <c r="C1067" t="inlineStr">
         <is>
-          <t>279347</t>
+          <t>218616</t>
         </is>
       </c>
       <c r="D1067" t="inlineStr">
@@ -29233,24 +29233,24 @@
       </c>
       <c r="E1067" t="inlineStr">
         <is>
-          <t>LMS_ECOM_200416_family</t>
+          <t>KAKAO_alimtalk</t>
         </is>
       </c>
     </row>
     <row r="1068">
       <c r="A1068" t="inlineStr">
         <is>
-          <t>kk_3894722641</t>
+          <t>kk_3765548639</t>
         </is>
       </c>
       <c r="B1068" t="inlineStr">
         <is>
-          <t>01064889500</t>
+          <t>01024327187</t>
         </is>
       </c>
       <c r="C1068" t="inlineStr">
         <is>
-          <t>267511</t>
+          <t>255087</t>
         </is>
       </c>
       <c r="D1068" t="inlineStr">
@@ -29260,24 +29260,24 @@
       </c>
       <c r="E1068" t="inlineStr">
         <is>
-          <t>Email_mkt</t>
+          <t>KAKAO_CH_MESSAGE_0409_RAINBOOTS</t>
         </is>
       </c>
     </row>
     <row r="1069">
       <c r="A1069" t="inlineStr">
         <is>
-          <t>kk_3765548639</t>
+          <t>kk_3894722641</t>
         </is>
       </c>
       <c r="B1069" t="inlineStr">
         <is>
-          <t>01024327187</t>
+          <t>01064889500</t>
         </is>
       </c>
       <c r="C1069" t="inlineStr">
         <is>
-          <t>255087</t>
+          <t>267511</t>
         </is>
       </c>
       <c r="D1069" t="inlineStr">
@@ -29287,7 +29287,7 @@
       </c>
       <c r="E1069" t="inlineStr">
         <is>
-          <t>KAKAO_CH_MESSAGE_0409_RAINBOOTS</t>
+          <t>Email_mkt</t>
         </is>
       </c>
     </row>
@@ -29321,189 +29321,189 @@
     <row r="1071">
       <c r="A1071" t="inlineStr">
         <is>
-          <t>kk_4844817541</t>
+          <t>kk_2768186596</t>
         </is>
       </c>
       <c r="B1071" t="inlineStr">
         <is>
-          <t>01046631832</t>
+          <t>01029241198</t>
         </is>
       </c>
       <c r="C1071" t="inlineStr">
         <is>
-          <t>304380</t>
+          <t>208962</t>
         </is>
       </c>
       <c r="D1071" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E1071" t="inlineStr">
         <is>
-          <t>[PF]전환_회원가입(유사)</t>
+          <t>KAKAO_alimtalk</t>
         </is>
       </c>
     </row>
     <row r="1072">
       <c r="A1072" t="inlineStr">
         <is>
-          <t>kk_4375003446</t>
+          <t>kk_4844817541</t>
         </is>
       </c>
       <c r="B1072" t="inlineStr">
         <is>
-          <t>01087457282</t>
+          <t>01046631832</t>
         </is>
       </c>
       <c r="C1072" t="inlineStr">
         <is>
-          <t>280131</t>
+          <t>304380</t>
         </is>
       </c>
       <c r="D1072" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E1072" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0410exclusive2</t>
+          <t>[PF]전환_회원가입(유사)</t>
         </is>
       </c>
     </row>
     <row r="1073">
       <c r="A1073" t="inlineStr">
         <is>
-          <t>kk_2768186596</t>
+          <t>kk_3169777000</t>
         </is>
       </c>
       <c r="B1073" t="inlineStr">
         <is>
-          <t>01029241198</t>
+          <t>01089348462</t>
         </is>
       </c>
       <c r="C1073" t="inlineStr">
         <is>
-          <t>208962</t>
+          <t>224876</t>
         </is>
       </c>
       <c r="D1073" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="E1073" t="inlineStr">
         <is>
-          <t>KAKAO_alimtalk</t>
+          <t>Direct</t>
         </is>
       </c>
     </row>
     <row r="1074">
       <c r="A1074" t="inlineStr">
         <is>
-          <t>kk_3169777000</t>
+          <t>kk_4375003446</t>
         </is>
       </c>
       <c r="B1074" t="inlineStr">
         <is>
-          <t>01089348462</t>
+          <t>01087457282</t>
         </is>
       </c>
       <c r="C1074" t="inlineStr">
         <is>
-          <t>224876</t>
+          <t>280131</t>
         </is>
       </c>
       <c r="D1074" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E1074" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>LMS_ECOM_0410exclusive2</t>
         </is>
       </c>
     </row>
     <row r="1075">
       <c r="A1075" t="inlineStr">
         <is>
-          <t>xuswldls</t>
+          <t>kk_3688034999</t>
         </is>
       </c>
       <c r="B1075" t="inlineStr">
         <is>
-          <t>01027349414</t>
+          <t>01025408262</t>
         </is>
       </c>
       <c r="C1075" t="inlineStr">
         <is>
-          <t>133308</t>
+          <t>250755</t>
         </is>
       </c>
       <c r="D1075" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E1075" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>KAKAO_alimtalk</t>
         </is>
       </c>
     </row>
     <row r="1076">
       <c r="A1076" t="inlineStr">
         <is>
-          <t>kk_3688034999</t>
+          <t>kk_2768989214</t>
         </is>
       </c>
       <c r="B1076" t="inlineStr">
         <is>
-          <t>01025408262</t>
+          <t>0109500